--- a/rapporten/trend-agent.xlsx
+++ b/rapporten/trend-agent.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -508,6 +508,28 @@
       </c>
       <c r="E3" s="3">
         <f>B3/$B$2-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>10002.9</v>
+      </c>
+      <c r="C4" s="2">
+        <f>B4-B3</f>
+        <v/>
+      </c>
+      <c r="D4" s="3">
+        <f>B4/B3-1</f>
+        <v/>
+      </c>
+      <c r="E4" s="3">
+        <f>B4/$B$2-1</f>
         <v/>
       </c>
     </row>
@@ -1005,33 +1027,33 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SAP.DE</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.107</v>
+        <v>0.114</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.4003803759831661</v>
+        <v>0.4084865976800374</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.07670677554735827</v>
+        <v>0.0918427437459377</v>
       </c>
       <c r="H3" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="I3" t="n">
-        <v>191.46</v>
+        <v>541.15</v>
       </c>
     </row>
     <row r="4">
@@ -1040,33 +1062,33 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>SAP.DE</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.103</v>
+        <v>0.107</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.3710767071995553</v>
+        <v>0.4003803759831661</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.08656893158854384</v>
+        <v>0.07670677554735827</v>
       </c>
       <c r="H4" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="I4" t="n">
-        <v>535.0700000000001</v>
+        <v>191.46</v>
       </c>
     </row>
     <row r="5">
@@ -1110,12 +1132,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>XLE</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Energie-ETF</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1124,19 +1146,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.1</v>
+        <v>0.096</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.4636794379477818</v>
+        <v>0.1659766135256344</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.3168630074747318</v>
+        <v>0.01937925769182725</v>
       </c>
       <c r="H6" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="I6" t="n">
-        <v>275.04</v>
+        <v>66.01000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -1159,19 +1181,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.099</v>
+        <v>0.092</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.6075823888407603</v>
+        <v>0.5629673802877717</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.2604003513955775</v>
+        <v>0.2497757898679558</v>
       </c>
       <c r="H7" t="n">
         <v>0.72</v>
       </c>
       <c r="I7" t="n">
-        <v>209.05</v>
+        <v>209</v>
       </c>
     </row>
     <row r="8">
@@ -1180,12 +1202,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>XLE</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Energie-ETF</t>
+          <t>ExxonMobil</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1194,19 +1216,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.091</v>
+        <v>0.089</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.1538039418207375</v>
+        <v>0.1941877612611411</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.008267991234740091</v>
+        <v>0.03711059822559015</v>
       </c>
       <c r="H8" t="n">
-        <v>1.18</v>
+        <v>0.95</v>
       </c>
       <c r="I8" t="n">
-        <v>65.08</v>
+        <v>172.15</v>
       </c>
     </row>
     <row r="9">
@@ -1215,33 +1237,33 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>TTE.PA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.078</v>
+        <v>0.067</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.1766238972258136</v>
+        <v>0.1158077105987207</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.02245359081159148</v>
+        <v>0.01359404338891568</v>
       </c>
       <c r="H9" t="n">
-        <v>0.96</v>
+        <v>1.13</v>
       </c>
       <c r="I9" t="n">
-        <v>168.94</v>
+        <v>78.53</v>
       </c>
     </row>
     <row r="10">
@@ -1250,12 +1272,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1264,19 +1286,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.065</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.267877730112988</v>
+        <v>0.09542484300005727</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.2372005402266932</v>
+        <v>0.05080301305570689</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="I10" t="n">
-        <v>418.78</v>
+        <v>389.27</v>
       </c>
     </row>
     <row r="11">
@@ -1285,33 +1307,33 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TTE.PA</t>
+          <t>META</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TotalEnergies</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.067</v>
+        <v>0.064</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.1158077105987207</v>
+        <v>0.124813041804527</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.01359404338891568</v>
+        <v>0.1473948604914039</v>
       </c>
       <c r="H11" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="I11" t="n">
-        <v>78.53</v>
+        <v>742.96</v>
       </c>
     </row>
   </sheetData>

--- a/rapporten/trend-agent.xlsx
+++ b/rapporten/trend-agent.xlsx
@@ -8,10 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overzicht" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Posities" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trades" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trends" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Uitleg" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Grafieken" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Posities" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trades" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trends" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Uitleg" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -147,6 +148,86 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5440680" cy="3337560"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5440680" cy="3337560"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>38</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5440680" cy="3337560"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -518,7 +599,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>10002.9</v>
+        <v>10014.42</v>
       </c>
       <c r="C4" s="2">
         <f>B4-B3</f>
@@ -539,6 +620,20 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -727,7 +822,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -919,13 +1014,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -987,353 +1082,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SHELL.AS</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Shell</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>EU</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>0.158</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>0.2339653505448274</v>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v>0.09228717796316999</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="I2" t="n">
-        <v>45.03</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>MSFT</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>0.114</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>0.4084865976800374</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>0.0918427437459377</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="I3" t="n">
-        <v>541.15</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>SAP.DE</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>EU</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>0.107</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>0.4003803759831661</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>0.07670677554735827</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="I4" t="n">
-        <v>191.46</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>WKL.AS</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Wolters Kluwer</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>EU</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>0.101</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>0.2419977004394382</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>0.1329305658222011</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="I5" t="n">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>XLE</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Energie-ETF</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>0.096</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>0.1659766135256344</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>0.01937925769182725</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="I6" t="n">
-        <v>66.01000000000001</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>PLTR</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Palantir</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>0.092</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>0.5629673802877717</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>0.2497757898679558</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="I7" t="n">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>XOM</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>ExxonMobil</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>0.089</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>0.1941877612611411</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>0.03711059822559015</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="I8" t="n">
-        <v>172.15</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>TTE.PA</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>TotalEnergies</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>EU</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>0.1158077105987207</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>0.01359404338891568</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="I9" t="n">
-        <v>78.53</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Visa</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>0.09542484300005727</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>0.05080301305570689</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="I10" t="n">
-        <v>389.27</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Meta Platforms</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>0.064</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>0.124813041804527</v>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>0.1473948604914039</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="I11" t="n">
-        <v>742.96</v>
+          <t>(geen kandidaten die aan alle regels voldoen)</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1341,7 +1093,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/rapporten/trend-agent.xlsx
+++ b/rapporten/trend-agent.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trades" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trends" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Uitleg" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Grafiekdata" sheetId="7" state="hidden" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,7 +26,7 @@
     <numFmt numFmtId="164" formatCode="€ #,##0.00;[Red]-€ #,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.00%;[Red]-0.00%"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,6 +37,29 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="0052514E"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000B0B0B"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000B0B0B"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <color rgb="0052514E"/>
+      <sz val="10.5"/>
     </font>
   </fonts>
   <fills count="3">
@@ -63,7 +87,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -73,6 +97,15 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -150,81 +183,1473 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.03"/>
+          <w val="0.96"/>
+          <h val="0.8"/>
+        </manualLayout>
+      </layout>
+      <stockChart>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$A$2:$A$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$B$2:$B$66</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!C1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$A$2:$A$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$C$2:$C$66</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!D1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$A$2:$A$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$D$2:$D$66</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!E1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$A$2:$A$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$E$2:$E$66</f>
+              <numCache>
+                <pt idx="0"/>
+                <pt idx="1"/>
+                <pt idx="2"/>
+                <pt idx="3"/>
+                <pt idx="4"/>
+                <pt idx="5"/>
+                <pt idx="6"/>
+                <pt idx="7"/>
+                <pt idx="8"/>
+                <pt idx="9"/>
+                <pt idx="10"/>
+                <pt idx="11"/>
+                <pt idx="12"/>
+                <pt idx="13"/>
+                <pt idx="14"/>
+                <pt idx="15"/>
+                <pt idx="16"/>
+                <pt idx="17"/>
+                <pt idx="18"/>
+                <pt idx="19"/>
+                <pt idx="20"/>
+                <pt idx="21"/>
+                <pt idx="22"/>
+                <pt idx="23"/>
+                <pt idx="24"/>
+                <pt idx="25"/>
+                <pt idx="26"/>
+                <pt idx="27"/>
+                <pt idx="28"/>
+                <pt idx="29"/>
+                <pt idx="30"/>
+                <pt idx="31"/>
+                <pt idx="32"/>
+                <pt idx="33"/>
+                <pt idx="34"/>
+                <pt idx="35"/>
+                <pt idx="36"/>
+                <pt idx="37"/>
+                <pt idx="38"/>
+                <pt idx="39"/>
+                <pt idx="40"/>
+                <pt idx="41"/>
+                <pt idx="42"/>
+                <pt idx="43"/>
+                <pt idx="44"/>
+                <pt idx="45"/>
+                <pt idx="46"/>
+                <pt idx="47"/>
+                <pt idx="48"/>
+                <pt idx="49"/>
+                <pt idx="50"/>
+                <pt idx="51"/>
+                <pt idx="52"/>
+                <pt idx="53"/>
+                <pt idx="54"/>
+                <pt idx="55"/>
+                <pt idx="56"/>
+                <pt idx="57"/>
+                <pt idx="58"/>
+                <pt idx="59"/>
+                <pt idx="60"/>
+                <pt idx="61"/>
+                <pt idx="62"/>
+                <pt idx="63"/>
+                <pt idx="64"/>
+              </numCache>
+            </numRef>
+          </val>
+        </ser>
+        <hiLowLines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+              <a:solidFill>
+                <a:srgbClr val="52514E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </hiLowLines>
+        <upDownBars>
+          <gapWidth val="60"/>
+          <upBars>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="008300"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="008300"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </upBars>
+          <downBars>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="E34948"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="E34948"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </downBars>
+        </upDownBars>
+        <axId val="10"/>
+        <axId val="100"/>
+      </stockChart>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!F1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="2A78D6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$A$2:$A$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$F$2:$F$66</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="5"/>
+          <order val="5"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!G1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="EB6834"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$A$2:$A$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$G$2:$G$66</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="6"/>
+          <order val="6"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!H1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="52514E"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$A$2:$A$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$H$2:$H$66</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="7"/>
+          <order val="7"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!I1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22225">
+              <a:solidFill>
+                <a:srgbClr val="E34948"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$A$2:$A$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$I$2:$I$66</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <numFmt formatCode="@" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="13"/>
+        <tickMarkSkip val="13"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="47.5"/>
+          <min val="32.5"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="E6E5E1"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>koers EUR</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="#,##0.00" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+        <majorUnit val="2.5"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.03"/>
+          <w val="0.96"/>
+          <h val="0.8"/>
+        </manualLayout>
+      </layout>
+      <stockChart>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!L1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$K$2:$K$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$L$2:$L$66</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!M1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$K$2:$K$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$M$2:$M$66</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!N1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$K$2:$K$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$N$2:$N$66</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!O1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$K$2:$K$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$O$2:$O$66</f>
+              <numCache>
+                <pt idx="0"/>
+                <pt idx="1"/>
+                <pt idx="2"/>
+                <pt idx="3"/>
+                <pt idx="4"/>
+                <pt idx="5"/>
+                <pt idx="6"/>
+                <pt idx="7"/>
+                <pt idx="8"/>
+                <pt idx="9"/>
+                <pt idx="10"/>
+                <pt idx="11"/>
+                <pt idx="12"/>
+                <pt idx="13"/>
+                <pt idx="14"/>
+                <pt idx="15"/>
+                <pt idx="16"/>
+                <pt idx="17"/>
+                <pt idx="18"/>
+                <pt idx="19"/>
+                <pt idx="20"/>
+                <pt idx="21"/>
+                <pt idx="22"/>
+                <pt idx="23"/>
+                <pt idx="24"/>
+                <pt idx="25"/>
+                <pt idx="26"/>
+                <pt idx="27"/>
+                <pt idx="28"/>
+                <pt idx="29"/>
+                <pt idx="30"/>
+                <pt idx="31"/>
+                <pt idx="32"/>
+                <pt idx="33"/>
+                <pt idx="34"/>
+                <pt idx="35"/>
+                <pt idx="36"/>
+                <pt idx="37"/>
+                <pt idx="38"/>
+                <pt idx="39"/>
+                <pt idx="40"/>
+                <pt idx="41"/>
+                <pt idx="42"/>
+                <pt idx="43"/>
+                <pt idx="44"/>
+                <pt idx="45"/>
+                <pt idx="46"/>
+                <pt idx="47"/>
+                <pt idx="48"/>
+                <pt idx="49"/>
+                <pt idx="50"/>
+                <pt idx="51"/>
+                <pt idx="52"/>
+                <pt idx="53"/>
+                <pt idx="54"/>
+                <pt idx="55"/>
+                <pt idx="56"/>
+                <pt idx="57"/>
+                <pt idx="58"/>
+                <pt idx="59"/>
+                <pt idx="60"/>
+                <pt idx="61"/>
+                <pt idx="62"/>
+                <pt idx="63"/>
+                <pt idx="64"/>
+              </numCache>
+            </numRef>
+          </val>
+        </ser>
+        <hiLowLines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+              <a:solidFill>
+                <a:srgbClr val="52514E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </hiLowLines>
+        <upDownBars>
+          <gapWidth val="60"/>
+          <upBars>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="008300"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="008300"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </upBars>
+          <downBars>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="E34948"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="E34948"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </downBars>
+        </upDownBars>
+        <axId val="10"/>
+        <axId val="100"/>
+      </stockChart>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!P1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="2A78D6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$K$2:$K$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$P$2:$P$66</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="5"/>
+          <order val="5"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!Q1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="EB6834"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$K$2:$K$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$Q$2:$Q$66</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="6"/>
+          <order val="6"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!R1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="52514E"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$K$2:$K$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$R$2:$R$66</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="7"/>
+          <order val="7"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!S1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22225">
+              <a:solidFill>
+                <a:srgbClr val="E34948"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$K$2:$K$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$S$2:$S$66</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <numFmt formatCode="@" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="13"/>
+        <tickMarkSkip val="13"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="220"/>
+          <min val="120"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="E6E5E1"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>koers EUR</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="#,##0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+        <majorUnit val="20"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.03"/>
+          <w val="0.96"/>
+          <h val="0.8"/>
+        </manualLayout>
+      </layout>
+      <stockChart>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!V1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$U$2:$U$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$V$2:$V$66</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!W1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$U$2:$U$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$W$2:$W$66</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!X1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$U$2:$U$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$X$2:$X$66</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!Y1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$U$2:$U$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$Y$2:$Y$66</f>
+              <numCache>
+                <pt idx="0"/>
+                <pt idx="1"/>
+                <pt idx="2"/>
+                <pt idx="3"/>
+                <pt idx="4"/>
+                <pt idx="5"/>
+                <pt idx="6"/>
+                <pt idx="7"/>
+                <pt idx="8"/>
+                <pt idx="9"/>
+                <pt idx="10"/>
+                <pt idx="11"/>
+                <pt idx="12"/>
+                <pt idx="13"/>
+                <pt idx="14"/>
+                <pt idx="15"/>
+                <pt idx="16"/>
+                <pt idx="17"/>
+                <pt idx="18"/>
+                <pt idx="19"/>
+                <pt idx="20"/>
+                <pt idx="21"/>
+                <pt idx="22"/>
+                <pt idx="23"/>
+                <pt idx="24"/>
+                <pt idx="25"/>
+                <pt idx="26"/>
+                <pt idx="27"/>
+                <pt idx="28"/>
+                <pt idx="29"/>
+                <pt idx="30"/>
+                <pt idx="31"/>
+                <pt idx="32"/>
+                <pt idx="33"/>
+                <pt idx="34"/>
+                <pt idx="35"/>
+                <pt idx="36"/>
+                <pt idx="37"/>
+                <pt idx="38"/>
+                <pt idx="39"/>
+                <pt idx="40"/>
+                <pt idx="41"/>
+                <pt idx="42"/>
+                <pt idx="43"/>
+                <pt idx="44"/>
+                <pt idx="45"/>
+                <pt idx="46"/>
+                <pt idx="47"/>
+                <pt idx="48"/>
+                <pt idx="49"/>
+                <pt idx="50"/>
+                <pt idx="51"/>
+                <pt idx="52"/>
+                <pt idx="53"/>
+                <pt idx="54"/>
+                <pt idx="55"/>
+                <pt idx="56"/>
+                <pt idx="57"/>
+                <pt idx="58"/>
+                <pt idx="59"/>
+                <pt idx="60"/>
+                <pt idx="61"/>
+                <pt idx="62"/>
+                <pt idx="63"/>
+                <pt idx="64"/>
+              </numCache>
+            </numRef>
+          </val>
+        </ser>
+        <hiLowLines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+              <a:solidFill>
+                <a:srgbClr val="52514E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </hiLowLines>
+        <upDownBars>
+          <gapWidth val="60"/>
+          <upBars>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="008300"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="008300"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </upBars>
+          <downBars>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="E34948"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="E34948"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </downBars>
+        </upDownBars>
+        <axId val="10"/>
+        <axId val="100"/>
+      </stockChart>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!Z1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="2A78D6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$U$2:$U$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$Z$2:$Z$66</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="5"/>
+          <order val="5"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!AA1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="EB6834"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$U$2:$U$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$AA$2:$AA$66</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="6"/>
+          <order val="6"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!AB1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="52514E"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$U$2:$U$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$AB$2:$AB$66</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="7"/>
+          <order val="7"/>
+          <tx>
+            <strRef>
+              <f>'Grafiekdata'!AC1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22225">
+              <a:solidFill>
+                <a:srgbClr val="E34948"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Grafiekdata'!$U$2:$U$66</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Grafiekdata'!$AC$2:$AC$66</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <numFmt formatCode="@" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="13"/>
+        <tickMarkSkip val="13"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="600"/>
+          <min val="350"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="E6E5E1"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>koers USD</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="#,##0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+        <majorUnit val="50"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>0</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5440680" cy="3337560"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
+    <ext cx="5580000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
     <clientData/>
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>3</col>
       <colOff>0</colOff>
-      <row>19</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5440680" cy="3337560"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
+    <ext cx="5580000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
     <clientData/>
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>1</col>
       <colOff>0</colOff>
-      <row>38</row>
+      <row>28</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5440680" cy="3337560"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
+    <ext cx="5580000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
     <clientData/>
   </oneCellAnchor>
 </wsDr>
@@ -519,7 +1944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -614,6 +2039,28 @@
         <v/>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>10027.51</v>
+      </c>
+      <c r="C5" s="2">
+        <f>B5-B4</f>
+        <v/>
+      </c>
+      <c r="D5" s="3">
+        <f>B5/B4-1</f>
+        <v/>
+      </c>
+      <c r="E5" s="3">
+        <f>B5/$B$2-1</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -623,12 +2070,175 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="B1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="84" customWidth="1" min="2" max="2"/>
+    <col width="3" customWidth="1" min="3" max="3"/>
+    <col width="84" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Grafieken van vandaag</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="B2" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00008300"/>
+              <sz val="12"/>
+            </rPr>
+            <t>▮ groen</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="0052514E"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve"> = dag gestegen    </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00E34948"/>
+              <sz val="12"/>
+            </rPr>
+            <t>▮ rood</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="0052514E"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve"> = dag gedaald    </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="002A78D6"/>
+              <sz val="12"/>
+            </rPr>
+            <t>━ blauw</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="0052514E"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve"> = gemiddelde 50 dagen    </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00EB6834"/>
+              <sz val="12"/>
+            </rPr>
+            <t>━ oranje</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="0052514E"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve"> = gemiddelde 200 dagen    </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="0052514E"/>
+              <sz val="12"/>
+            </rPr>
+            <t>╌ grijs</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="0052514E"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve"> = instap    </t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="00E34948"/>
+              <sz val="12"/>
+            </rPr>
+            <t>╌ rood</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="0052514E"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve"> = stop-loss, hier verkoopt de bot</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Elke kaars is één handelsdag; het dunne streepje loopt van de laagste naar de hoogste koers van die dag. Ga met de muis over een kaars of lijn om de waarde te zien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Trend-agent: open posities</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Shell (SHELL.AS)  ·  45,95 EUR</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>SAP (SAP.DE)  ·  197,28 EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Gestegen: 25,7% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +2,0% (winst). De bot verkoopt als de koers onder 43,24 zakt (-5,9%).</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Gestegen: 44,0% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +3,0% (winst). De bot verkoopt als de koers onder 181,02 zakt (-8,2%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>Microsoft (MSFT)  ·  543,45 USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Gestegen: 41,4% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +1,5% (winst). De bot verkoopt als de koers onder 509,90 zakt (-6,2%).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -762,7 +2372,7 @@
         <v>191.56</v>
       </c>
       <c r="F3" t="n">
-        <v>180.83</v>
+        <v>181.02</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1205,4 +2815,5904 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AC66"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Shell (SHELL.AS): Datum</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Hoogste</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Laagste</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Slot</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>50-daags gemiddelde</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>200-daags gemiddelde</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Instap</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Stop-loss (hier verkoopt de bot)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>SAP (SAP.DE): Datum</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Hoogste</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Laagste</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Slot</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>50-daags gemiddelde</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>200-daags gemiddelde</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Instap</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Stop-loss (hier verkoopt de bot)</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Microsoft (MSFT): Datum</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Hoogste</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Laagste</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Slot</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>50-daags gemiddelde</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>200-daags gemiddelde</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>Instap</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>Stop-loss (hier verkoopt de bot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>15 jul</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>36.4566</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37.1001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>36.4566</v>
+      </c>
+      <c r="E2" t="n">
+        <v>36.5506</v>
+      </c>
+      <c r="F2" t="n">
+        <v>35.581</v>
+      </c>
+      <c r="H2" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I2" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>15 jul</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>134.42</v>
+      </c>
+      <c r="M2" t="n">
+        <v>139.44</v>
+      </c>
+      <c r="N2" t="n">
+        <v>133.52</v>
+      </c>
+      <c r="O2" t="n">
+        <v>136.98</v>
+      </c>
+      <c r="P2" t="n">
+        <v>145.0924</v>
+      </c>
+      <c r="R2" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S2" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>14 jul</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>382.1007</v>
+      </c>
+      <c r="W2" t="n">
+        <v>387.4606</v>
+      </c>
+      <c r="X2" t="n">
+        <v>377.9385</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>384.2067</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>401.4825</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>16 jul</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>36.5803</v>
+      </c>
+      <c r="C3" t="n">
+        <v>37.011</v>
+      </c>
+      <c r="D3" t="n">
+        <v>36.3724</v>
+      </c>
+      <c r="E3" t="n">
+        <v>36.8773</v>
+      </c>
+      <c r="F3" t="n">
+        <v>35.6114</v>
+      </c>
+      <c r="H3" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I3" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>16 jul</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>137.2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>138.24</v>
+      </c>
+      <c r="N3" t="n">
+        <v>135.14</v>
+      </c>
+      <c r="O3" t="n">
+        <v>137.64</v>
+      </c>
+      <c r="P3" t="n">
+        <v>144.8176</v>
+      </c>
+      <c r="R3" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S3" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>15 jul</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>387.0713</v>
+      </c>
+      <c r="W3" t="n">
+        <v>398.2104</v>
+      </c>
+      <c r="X3" t="n">
+        <v>385.674</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>394.8866</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>401.1249</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>17 jul</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>36.912</v>
+      </c>
+      <c r="C4" t="n">
+        <v>37.8871</v>
+      </c>
+      <c r="D4" t="n">
+        <v>36.912</v>
+      </c>
+      <c r="E4" t="n">
+        <v>37.6594</v>
+      </c>
+      <c r="F4" t="n">
+        <v>35.6614</v>
+      </c>
+      <c r="H4" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I4" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>17 jul</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>140.6</v>
+      </c>
+      <c r="M4" t="n">
+        <v>141.54</v>
+      </c>
+      <c r="N4" t="n">
+        <v>137.32</v>
+      </c>
+      <c r="O4" t="n">
+        <v>137.92</v>
+      </c>
+      <c r="P4" t="n">
+        <v>144.652</v>
+      </c>
+      <c r="R4" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S4" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>16 jul</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>397.5616</v>
+      </c>
+      <c r="W4" t="n">
+        <v>405.2271</v>
+      </c>
+      <c r="X4" t="n">
+        <v>391.3133</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>400.3463</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>400.8928</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>20 jul</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>38.0653</v>
+      </c>
+      <c r="C5" t="n">
+        <v>38.1742</v>
+      </c>
+      <c r="D5" t="n">
+        <v>37.1496</v>
+      </c>
+      <c r="E5" t="n">
+        <v>37.5307</v>
+      </c>
+      <c r="F5" t="n">
+        <v>35.7021</v>
+      </c>
+      <c r="H5" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I5" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>20 jul</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>138</v>
+      </c>
+      <c r="M5" t="n">
+        <v>140.04</v>
+      </c>
+      <c r="N5" t="n">
+        <v>134.98</v>
+      </c>
+      <c r="O5" t="n">
+        <v>138.26</v>
+      </c>
+      <c r="P5" t="n">
+        <v>144.528</v>
+      </c>
+      <c r="R5" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S5" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>17 jul</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>394.118</v>
+      </c>
+      <c r="W5" t="n">
+        <v>397.6414</v>
+      </c>
+      <c r="X5" t="n">
+        <v>388.6583</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>393.08</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>400.5601</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>21 jul</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>37.5703</v>
+      </c>
+      <c r="C6" t="n">
+        <v>37.8277</v>
+      </c>
+      <c r="D6" t="n">
+        <v>37.4169</v>
+      </c>
+      <c r="E6" t="n">
+        <v>37.8277</v>
+      </c>
+      <c r="F6" t="n">
+        <v>35.7452</v>
+      </c>
+      <c r="G6" t="n">
+        <v>33.7592</v>
+      </c>
+      <c r="H6" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I6" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>21 jul</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>137.74</v>
+      </c>
+      <c r="M6" t="n">
+        <v>137.84</v>
+      </c>
+      <c r="N6" t="n">
+        <v>135.34</v>
+      </c>
+      <c r="O6" t="n">
+        <v>136.42</v>
+      </c>
+      <c r="P6" t="n">
+        <v>144.4084</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>174.8719</v>
+      </c>
+      <c r="R6" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S6" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>20 jul</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>390.6746</v>
+      </c>
+      <c r="W6" t="n">
+        <v>402.4224</v>
+      </c>
+      <c r="X6" t="n">
+        <v>388.9179</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>401.5341</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>400.345</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>436.4743</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>22 jul</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>38.095</v>
+      </c>
+      <c r="C7" t="n">
+        <v>38.6098</v>
+      </c>
+      <c r="D7" t="n">
+        <v>37.9267</v>
+      </c>
+      <c r="E7" t="n">
+        <v>38.2682</v>
+      </c>
+      <c r="F7" t="n">
+        <v>35.799</v>
+      </c>
+      <c r="G7" t="n">
+        <v>33.7968</v>
+      </c>
+      <c r="H7" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I7" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>22 jul</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>136.02</v>
+      </c>
+      <c r="M7" t="n">
+        <v>136.4</v>
+      </c>
+      <c r="N7" t="n">
+        <v>132.04</v>
+      </c>
+      <c r="O7" t="n">
+        <v>132.04</v>
+      </c>
+      <c r="P7" t="n">
+        <v>144.324</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>174.4005</v>
+      </c>
+      <c r="R7" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S7" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>21 jul</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>398.0606</v>
+      </c>
+      <c r="W7" t="n">
+        <v>400.7156</v>
+      </c>
+      <c r="X7" t="n">
+        <v>395.5753</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>397.0026</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>399.9036</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>435.882</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>23 jul</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>38.491</v>
+      </c>
+      <c r="C8" t="n">
+        <v>39.0454</v>
+      </c>
+      <c r="D8" t="n">
+        <v>38.3425</v>
+      </c>
+      <c r="E8" t="n">
+        <v>38.8028</v>
+      </c>
+      <c r="F8" t="n">
+        <v>35.863</v>
+      </c>
+      <c r="G8" t="n">
+        <v>33.8375</v>
+      </c>
+      <c r="H8" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I8" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>23 jul</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>131</v>
+      </c>
+      <c r="M8" t="n">
+        <v>132.42</v>
+      </c>
+      <c r="N8" t="n">
+        <v>127.5</v>
+      </c>
+      <c r="O8" t="n">
+        <v>128.32</v>
+      </c>
+      <c r="P8" t="n">
+        <v>144.066</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>173.9035</v>
+      </c>
+      <c r="R8" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S8" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>22 jul</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>398.8292</v>
+      </c>
+      <c r="W8" t="n">
+        <v>400.2465</v>
+      </c>
+      <c r="X8" t="n">
+        <v>386.2329</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>389.6066</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>399.4268</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>435.2723</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>24 jul</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>38.4019</v>
+      </c>
+      <c r="C9" t="n">
+        <v>38.6593</v>
+      </c>
+      <c r="D9" t="n">
+        <v>38.1594</v>
+      </c>
+      <c r="E9" t="n">
+        <v>38.3871</v>
+      </c>
+      <c r="F9" t="n">
+        <v>35.9135</v>
+      </c>
+      <c r="G9" t="n">
+        <v>33.8757</v>
+      </c>
+      <c r="H9" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I9" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>24 jul</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>130.88</v>
+      </c>
+      <c r="M9" t="n">
+        <v>141.32</v>
+      </c>
+      <c r="N9" t="n">
+        <v>130.86</v>
+      </c>
+      <c r="O9" t="n">
+        <v>140.2</v>
+      </c>
+      <c r="P9" t="n">
+        <v>143.9888</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>173.4491</v>
+      </c>
+      <c r="R9" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S9" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>23 jul</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>389.2373</v>
+      </c>
+      <c r="W9" t="n">
+        <v>391.0439</v>
+      </c>
+      <c r="X9" t="n">
+        <v>376.6809</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>380.863</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>398.8242</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>434.611</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>27 jul</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>37.5802</v>
+      </c>
+      <c r="C10" t="n">
+        <v>38.1099</v>
+      </c>
+      <c r="D10" t="n">
+        <v>37.4317</v>
+      </c>
+      <c r="E10" t="n">
+        <v>37.9515</v>
+      </c>
+      <c r="F10" t="n">
+        <v>35.931</v>
+      </c>
+      <c r="G10" t="n">
+        <v>33.9167</v>
+      </c>
+      <c r="H10" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I10" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>27 jul</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>142.38</v>
+      </c>
+      <c r="M10" t="n">
+        <v>151.56</v>
+      </c>
+      <c r="N10" t="n">
+        <v>142</v>
+      </c>
+      <c r="O10" t="n">
+        <v>151.28</v>
+      </c>
+      <c r="P10" t="n">
+        <v>144.0572</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>173.0393</v>
+      </c>
+      <c r="R10" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S10" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>24 jul</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>386.3227</v>
+      </c>
+      <c r="W10" t="n">
+        <v>388.299</v>
+      </c>
+      <c r="X10" t="n">
+        <v>379.9348</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>380.9828</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>398.3214</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>433.8946</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>28 jul</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>37.7139</v>
+      </c>
+      <c r="C11" t="n">
+        <v>38.0109</v>
+      </c>
+      <c r="D11" t="n">
+        <v>37.4713</v>
+      </c>
+      <c r="E11" t="n">
+        <v>37.4713</v>
+      </c>
+      <c r="F11" t="n">
+        <v>35.9372</v>
+      </c>
+      <c r="G11" t="n">
+        <v>33.9548</v>
+      </c>
+      <c r="H11" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I11" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>28 jul</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>152.2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>159.76</v>
+      </c>
+      <c r="N11" t="n">
+        <v>151</v>
+      </c>
+      <c r="O11" t="n">
+        <v>159.24</v>
+      </c>
+      <c r="P11" t="n">
+        <v>144.1076</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>172.6663</v>
+      </c>
+      <c r="R11" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S11" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>27 jul</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>389.347</v>
+      </c>
+      <c r="W11" t="n">
+        <v>393.4593</v>
+      </c>
+      <c r="X11" t="n">
+        <v>387.261</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>388.3689</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>398.0172</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>433.238</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>29 jul</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>38.0653</v>
+      </c>
+      <c r="C12" t="n">
+        <v>38.59</v>
+      </c>
+      <c r="D12" t="n">
+        <v>37.7089</v>
+      </c>
+      <c r="E12" t="n">
+        <v>38.4415</v>
+      </c>
+      <c r="F12" t="n">
+        <v>35.9692</v>
+      </c>
+      <c r="G12" t="n">
+        <v>33.9987</v>
+      </c>
+      <c r="H12" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I12" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>29 jul</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>159.84</v>
+      </c>
+      <c r="M12" t="n">
+        <v>163.3</v>
+      </c>
+      <c r="N12" t="n">
+        <v>156.48</v>
+      </c>
+      <c r="O12" t="n">
+        <v>162.04</v>
+      </c>
+      <c r="P12" t="n">
+        <v>144.28</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>172.343</v>
+      </c>
+      <c r="R12" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S12" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>28 jul</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>392.4213</v>
+      </c>
+      <c r="W12" t="n">
+        <v>399.5678</v>
+      </c>
+      <c r="X12" t="n">
+        <v>390.5647</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>392.6109</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>397.7139</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>432.5982</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>30 jul</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>38.6098</v>
+      </c>
+      <c r="C13" t="n">
+        <v>39.1444</v>
+      </c>
+      <c r="D13" t="n">
+        <v>38.3277</v>
+      </c>
+      <c r="E13" t="n">
+        <v>38.5108</v>
+      </c>
+      <c r="F13" t="n">
+        <v>35.9978</v>
+      </c>
+      <c r="G13" t="n">
+        <v>34.0424</v>
+      </c>
+      <c r="H13" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I13" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>30 jul</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>162.5</v>
+      </c>
+      <c r="M13" t="n">
+        <v>163.16</v>
+      </c>
+      <c r="N13" t="n">
+        <v>155.2</v>
+      </c>
+      <c r="O13" t="n">
+        <v>155.92</v>
+      </c>
+      <c r="P13" t="n">
+        <v>144.3804</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>171.9849</v>
+      </c>
+      <c r="R13" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S13" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>29 jul</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>392.6608</v>
+      </c>
+      <c r="W13" t="n">
+        <v>400.4961</v>
+      </c>
+      <c r="X13" t="n">
+        <v>388.0095</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>389.8062</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>397.1057</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>431.9565</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>31 jul</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>38.6098</v>
+      </c>
+      <c r="C14" t="n">
+        <v>39.575</v>
+      </c>
+      <c r="D14" t="n">
+        <v>38.4464</v>
+      </c>
+      <c r="E14" t="n">
+        <v>39.3226</v>
+      </c>
+      <c r="F14" t="n">
+        <v>36.0495</v>
+      </c>
+      <c r="G14" t="n">
+        <v>34.0907</v>
+      </c>
+      <c r="H14" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I14" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>31 jul</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>154.9</v>
+      </c>
+      <c r="M14" t="n">
+        <v>158.26</v>
+      </c>
+      <c r="N14" t="n">
+        <v>153.6</v>
+      </c>
+      <c r="O14" t="n">
+        <v>157.68</v>
+      </c>
+      <c r="P14" t="n">
+        <v>144.4984</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>171.6292</v>
+      </c>
+      <c r="R14" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S14" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>30 jul</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>437.0772</v>
+      </c>
+      <c r="W14" t="n">
+        <v>457.8281</v>
+      </c>
+      <c r="X14" t="n">
+        <v>431.6275</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>450.2524</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>397.6741</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>431.6738</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>3 aug</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>38.3128</v>
+      </c>
+      <c r="C15" t="n">
+        <v>39.4067</v>
+      </c>
+      <c r="D15" t="n">
+        <v>38.2138</v>
+      </c>
+      <c r="E15" t="n">
+        <v>39.4067</v>
+      </c>
+      <c r="F15" t="n">
+        <v>36.1112</v>
+      </c>
+      <c r="G15" t="n">
+        <v>34.1393</v>
+      </c>
+      <c r="H15" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I15" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>3 aug</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>160</v>
+      </c>
+      <c r="M15" t="n">
+        <v>168.7</v>
+      </c>
+      <c r="N15" t="n">
+        <v>159.6</v>
+      </c>
+      <c r="O15" t="n">
+        <v>164.64</v>
+      </c>
+      <c r="P15" t="n">
+        <v>144.7016</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>171.301</v>
+      </c>
+      <c r="R15" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S15" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>31 jul</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>449.1545</v>
+      </c>
+      <c r="W15" t="n">
+        <v>465.9628</v>
+      </c>
+      <c r="X15" t="n">
+        <v>448.4857</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>463.8468</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>398.6364</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>431.4438</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>4 aug</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>39.3028</v>
+      </c>
+      <c r="C16" t="n">
+        <v>39.6443</v>
+      </c>
+      <c r="D16" t="n">
+        <v>38.2039</v>
+      </c>
+      <c r="E16" t="n">
+        <v>38.486</v>
+      </c>
+      <c r="F16" t="n">
+        <v>36.1495</v>
+      </c>
+      <c r="G16" t="n">
+        <v>34.1818</v>
+      </c>
+      <c r="H16" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I16" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>4 aug</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>162.86</v>
+      </c>
+      <c r="M16" t="n">
+        <v>168.56</v>
+      </c>
+      <c r="N16" t="n">
+        <v>162.4</v>
+      </c>
+      <c r="O16" t="n">
+        <v>167.38</v>
+      </c>
+      <c r="P16" t="n">
+        <v>145.02</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>170.9913</v>
+      </c>
+      <c r="R16" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S16" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>3 aug</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>475.2354</v>
+      </c>
+      <c r="W16" t="n">
+        <v>490.7262</v>
+      </c>
+      <c r="X16" t="n">
+        <v>474.1075</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>486.7337</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>399.9838</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>431.3306</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>5 aug</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>38.4811</v>
+      </c>
+      <c r="C17" t="n">
+        <v>38.7632</v>
+      </c>
+      <c r="D17" t="n">
+        <v>37.9366</v>
+      </c>
+      <c r="E17" t="n">
+        <v>38.0307</v>
+      </c>
+      <c r="F17" t="n">
+        <v>36.1966</v>
+      </c>
+      <c r="G17" t="n">
+        <v>34.2215</v>
+      </c>
+      <c r="H17" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I17" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>5 aug</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>167.92</v>
+      </c>
+      <c r="M17" t="n">
+        <v>172.6</v>
+      </c>
+      <c r="N17" t="n">
+        <v>167.3</v>
+      </c>
+      <c r="O17" t="n">
+        <v>169.26</v>
+      </c>
+      <c r="P17" t="n">
+        <v>145.4052</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>170.7022</v>
+      </c>
+      <c r="R17" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S17" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>4 aug</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
+        <v>479.9964</v>
+      </c>
+      <c r="W17" t="n">
+        <v>498.5016</v>
+      </c>
+      <c r="X17" t="n">
+        <v>478.2697</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>491.884</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>401.4555</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>431.2438</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>6 aug</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>38.0752</v>
+      </c>
+      <c r="C18" t="n">
+        <v>38.4069</v>
+      </c>
+      <c r="D18" t="n">
+        <v>37.9168</v>
+      </c>
+      <c r="E18" t="n">
+        <v>38.392</v>
+      </c>
+      <c r="F18" t="n">
+        <v>36.2474</v>
+      </c>
+      <c r="G18" t="n">
+        <v>34.2607</v>
+      </c>
+      <c r="H18" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I18" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>6 aug</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>171.44</v>
+      </c>
+      <c r="M18" t="n">
+        <v>173.1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>168.08</v>
+      </c>
+      <c r="O18" t="n">
+        <v>170.98</v>
+      </c>
+      <c r="P18" t="n">
+        <v>145.7928</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>170.384</v>
+      </c>
+      <c r="R18" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S18" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>5 aug</t>
+        </is>
+      </c>
+      <c r="V18" t="n">
+        <v>495.4273</v>
+      </c>
+      <c r="W18" t="n">
+        <v>497.3038</v>
+      </c>
+      <c r="X18" t="n">
+        <v>484.7674</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>486.5441</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>402.8307</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>431.1393</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>7 aug</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>38.5207</v>
+      </c>
+      <c r="C19" t="n">
+        <v>38.5999</v>
+      </c>
+      <c r="D19" t="n">
+        <v>37.897</v>
+      </c>
+      <c r="E19" t="n">
+        <v>38.0059</v>
+      </c>
+      <c r="F19" t="n">
+        <v>36.2952</v>
+      </c>
+      <c r="G19" t="n">
+        <v>34.294</v>
+      </c>
+      <c r="H19" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I19" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>7 aug</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>173.82</v>
+      </c>
+      <c r="M19" t="n">
+        <v>179.56</v>
+      </c>
+      <c r="N19" t="n">
+        <v>173.82</v>
+      </c>
+      <c r="O19" t="n">
+        <v>177.96</v>
+      </c>
+      <c r="P19" t="n">
+        <v>146.2468</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>170.0918</v>
+      </c>
+      <c r="R19" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S19" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>6 aug</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
+        <v>487.632</v>
+      </c>
+      <c r="W19" t="n">
+        <v>500.6176</v>
+      </c>
+      <c r="X19" t="n">
+        <v>487.6021</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>498.9207</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>404.5041</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>431.087</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>10 aug</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>38.0356</v>
+      </c>
+      <c r="C20" t="n">
+        <v>38.4366</v>
+      </c>
+      <c r="D20" t="n">
+        <v>37.803</v>
+      </c>
+      <c r="E20" t="n">
+        <v>38.4019</v>
+      </c>
+      <c r="F20" t="n">
+        <v>36.3315</v>
+      </c>
+      <c r="G20" t="n">
+        <v>34.3294</v>
+      </c>
+      <c r="H20" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I20" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>10 aug</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>178.92</v>
+      </c>
+      <c r="M20" t="n">
+        <v>179.96</v>
+      </c>
+      <c r="N20" t="n">
+        <v>175.86</v>
+      </c>
+      <c r="O20" t="n">
+        <v>179.3</v>
+      </c>
+      <c r="P20" t="n">
+        <v>146.4748</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>169.8238</v>
+      </c>
+      <c r="R20" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S20" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>7 aug</t>
+        </is>
+      </c>
+      <c r="V20" t="n">
+        <v>498.272</v>
+      </c>
+      <c r="W20" t="n">
+        <v>504.2308</v>
+      </c>
+      <c r="X20" t="n">
+        <v>497.7929</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>499.0505</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>406.2472</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>431.0194</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>11 aug</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>38.7385</v>
+      </c>
+      <c r="C21" t="n">
+        <v>39.0058</v>
+      </c>
+      <c r="D21" t="n">
+        <v>38.6148</v>
+      </c>
+      <c r="E21" t="n">
+        <v>38.9662</v>
+      </c>
+      <c r="F21" t="n">
+        <v>36.374</v>
+      </c>
+      <c r="G21" t="n">
+        <v>34.3685</v>
+      </c>
+      <c r="H21" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I21" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>11 aug</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>180</v>
+      </c>
+      <c r="M21" t="n">
+        <v>183.24</v>
+      </c>
+      <c r="N21" t="n">
+        <v>178.14</v>
+      </c>
+      <c r="O21" t="n">
+        <v>180.7</v>
+      </c>
+      <c r="P21" t="n">
+        <v>146.8316</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>169.5375</v>
+      </c>
+      <c r="R21" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S21" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>10 aug</t>
+        </is>
+      </c>
+      <c r="V21" t="n">
+        <v>502.4941</v>
+      </c>
+      <c r="W21" t="n">
+        <v>512.7646999999999</v>
+      </c>
+      <c r="X21" t="n">
+        <v>501.3262</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>505.1091</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>407.8257</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>430.9778</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>12 aug</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>38.8573</v>
+      </c>
+      <c r="C22" t="n">
+        <v>38.986</v>
+      </c>
+      <c r="D22" t="n">
+        <v>38.3871</v>
+      </c>
+      <c r="E22" t="n">
+        <v>38.6494</v>
+      </c>
+      <c r="F22" t="n">
+        <v>36.3981</v>
+      </c>
+      <c r="G22" t="n">
+        <v>34.4068</v>
+      </c>
+      <c r="H22" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I22" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>12 aug</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>180.3</v>
+      </c>
+      <c r="M22" t="n">
+        <v>180.98</v>
+      </c>
+      <c r="N22" t="n">
+        <v>175.4</v>
+      </c>
+      <c r="O22" t="n">
+        <v>175.96</v>
+      </c>
+      <c r="P22" t="n">
+        <v>147.232</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>169.2701</v>
+      </c>
+      <c r="R22" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S22" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>11 aug</t>
+        </is>
+      </c>
+      <c r="V22" t="n">
+        <v>503.3824</v>
+      </c>
+      <c r="W22" t="n">
+        <v>504.3805</v>
+      </c>
+      <c r="X22" t="n">
+        <v>498.6113</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>502.8633</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>408.895</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>430.9106</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>13 aug</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>39</v>
+      </c>
+      <c r="C23" t="n">
+        <v>39.005</v>
+      </c>
+      <c r="D23" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="E23" t="n">
+        <v>38.605</v>
+      </c>
+      <c r="F23" t="n">
+        <v>36.4313</v>
+      </c>
+      <c r="G23" t="n">
+        <v>34.4429</v>
+      </c>
+      <c r="H23" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I23" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>13 aug</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>177.48</v>
+      </c>
+      <c r="M23" t="n">
+        <v>178.3</v>
+      </c>
+      <c r="N23" t="n">
+        <v>174.8</v>
+      </c>
+      <c r="O23" t="n">
+        <v>175.38</v>
+      </c>
+      <c r="P23" t="n">
+        <v>147.4496</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>168.9889</v>
+      </c>
+      <c r="R23" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S23" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>12 aug</t>
+        </is>
+      </c>
+      <c r="V23" t="n">
+        <v>499.0505</v>
+      </c>
+      <c r="W23" t="n">
+        <v>500.5577</v>
+      </c>
+      <c r="X23" t="n">
+        <v>490.5964</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>491.5047</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>409.532</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>430.7866</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>14 aug</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>38.65</v>
+      </c>
+      <c r="C24" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>38.56</v>
+      </c>
+      <c r="E24" t="n">
+        <v>38.97</v>
+      </c>
+      <c r="F24" t="n">
+        <v>36.4703</v>
+      </c>
+      <c r="G24" t="n">
+        <v>34.4805</v>
+      </c>
+      <c r="H24" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I24" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>14 aug</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>182</v>
+      </c>
+      <c r="M24" t="n">
+        <v>185.74</v>
+      </c>
+      <c r="N24" t="n">
+        <v>179.28</v>
+      </c>
+      <c r="O24" t="n">
+        <v>180.14</v>
+      </c>
+      <c r="P24" t="n">
+        <v>147.8228</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>168.7386</v>
+      </c>
+      <c r="R24" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S24" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>13 aug</t>
+        </is>
+      </c>
+      <c r="V24" t="n">
+        <v>492.3431</v>
+      </c>
+      <c r="W24" t="n">
+        <v>500.398</v>
+      </c>
+      <c r="X24" t="n">
+        <v>492.0837</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>495.9464</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>410.6414</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>430.6696</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>17 aug</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>38.97</v>
+      </c>
+      <c r="C25" t="n">
+        <v>39.27</v>
+      </c>
+      <c r="D25" t="n">
+        <v>38.765</v>
+      </c>
+      <c r="E25" t="n">
+        <v>39.15</v>
+      </c>
+      <c r="F25" t="n">
+        <v>36.5118</v>
+      </c>
+      <c r="G25" t="n">
+        <v>34.5207</v>
+      </c>
+      <c r="H25" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I25" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>17 aug</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>178.94</v>
+      </c>
+      <c r="M25" t="n">
+        <v>180.9</v>
+      </c>
+      <c r="N25" t="n">
+        <v>177.66</v>
+      </c>
+      <c r="O25" t="n">
+        <v>179.58</v>
+      </c>
+      <c r="P25" t="n">
+        <v>148.2524</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>168.5337</v>
+      </c>
+      <c r="R25" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S25" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>14 aug</t>
+        </is>
+      </c>
+      <c r="V25" t="n">
+        <v>495.4273</v>
+      </c>
+      <c r="W25" t="n">
+        <v>499.0705</v>
+      </c>
+      <c r="X25" t="n">
+        <v>492.9919</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>494.4691</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>412</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>430.5061</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>18 aug</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>39.49</v>
+      </c>
+      <c r="C26" t="n">
+        <v>39.945</v>
+      </c>
+      <c r="D26" t="n">
+        <v>39.46</v>
+      </c>
+      <c r="E26" t="n">
+        <v>39.785</v>
+      </c>
+      <c r="F26" t="n">
+        <v>36.5781</v>
+      </c>
+      <c r="G26" t="n">
+        <v>34.5641</v>
+      </c>
+      <c r="H26" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I26" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>18 aug</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>179.14</v>
+      </c>
+      <c r="M26" t="n">
+        <v>183.9</v>
+      </c>
+      <c r="N26" t="n">
+        <v>177.98</v>
+      </c>
+      <c r="O26" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="P26" t="n">
+        <v>148.8084</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>168.3358</v>
+      </c>
+      <c r="R26" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S26" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>17 aug</t>
+        </is>
+      </c>
+      <c r="V26" t="n">
+        <v>489.2191</v>
+      </c>
+      <c r="W26" t="n">
+        <v>491.7343</v>
+      </c>
+      <c r="X26" t="n">
+        <v>477.5111</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>479.4474</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>413.044</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>430.2151</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>19 aug</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>39.835</v>
+      </c>
+      <c r="C27" t="n">
+        <v>40.14</v>
+      </c>
+      <c r="D27" t="n">
+        <v>39.74</v>
+      </c>
+      <c r="E27" t="n">
+        <v>39.94</v>
+      </c>
+      <c r="F27" t="n">
+        <v>36.6336</v>
+      </c>
+      <c r="G27" t="n">
+        <v>34.6092</v>
+      </c>
+      <c r="H27" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I27" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>19 aug</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>181.7</v>
+      </c>
+      <c r="M27" t="n">
+        <v>186.98</v>
+      </c>
+      <c r="N27" t="n">
+        <v>180.38</v>
+      </c>
+      <c r="O27" t="n">
+        <v>185.9</v>
+      </c>
+      <c r="P27" t="n">
+        <v>149.5324</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>168.1618</v>
+      </c>
+      <c r="R27" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S27" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>18 aug</t>
+        </is>
+      </c>
+      <c r="V27" t="n">
+        <v>480.6352</v>
+      </c>
+      <c r="W27" t="n">
+        <v>483.3601</v>
+      </c>
+      <c r="X27" t="n">
+        <v>476.2534</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>480.725</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>414.3408</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>429.933</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>20 aug</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>39.865</v>
+      </c>
+      <c r="C28" t="n">
+        <v>40.51</v>
+      </c>
+      <c r="D28" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="E28" t="n">
+        <v>40.28</v>
+      </c>
+      <c r="F28" t="n">
+        <v>36.6884</v>
+      </c>
+      <c r="G28" t="n">
+        <v>34.6545</v>
+      </c>
+      <c r="H28" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I28" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>20 aug</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>183.78</v>
+      </c>
+      <c r="M28" t="n">
+        <v>186.1</v>
+      </c>
+      <c r="N28" t="n">
+        <v>182.52</v>
+      </c>
+      <c r="O28" t="n">
+        <v>185.64</v>
+      </c>
+      <c r="P28" t="n">
+        <v>150.4472</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>167.9648</v>
+      </c>
+      <c r="R28" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S28" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>19 aug</t>
+        </is>
+      </c>
+      <c r="V28" t="n">
+        <v>479.168</v>
+      </c>
+      <c r="W28" t="n">
+        <v>488.3806</v>
+      </c>
+      <c r="X28" t="n">
+        <v>478.4593</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>483.4</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>415.7895</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>429.7427</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>21 aug</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="C29" t="n">
+        <v>40.37</v>
+      </c>
+      <c r="D29" t="n">
+        <v>39.84</v>
+      </c>
+      <c r="E29" t="n">
+        <v>39.91</v>
+      </c>
+      <c r="F29" t="n">
+        <v>36.7478</v>
+      </c>
+      <c r="G29" t="n">
+        <v>34.6988</v>
+      </c>
+      <c r="H29" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I29" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>21 aug</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>185.18</v>
+      </c>
+      <c r="M29" t="n">
+        <v>188.4</v>
+      </c>
+      <c r="N29" t="n">
+        <v>183.6</v>
+      </c>
+      <c r="O29" t="n">
+        <v>188.12</v>
+      </c>
+      <c r="P29" t="n">
+        <v>151.4044</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>167.794</v>
+      </c>
+      <c r="R29" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S29" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>20 aug</t>
+        </is>
+      </c>
+      <c r="V29" t="n">
+        <v>483.3</v>
+      </c>
+      <c r="W29" t="n">
+        <v>484.16</v>
+      </c>
+      <c r="X29" t="n">
+        <v>479.5</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>481.15</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>417.3594</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>429.5805</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>24 aug</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>39.88</v>
+      </c>
+      <c r="C30" t="n">
+        <v>40.085</v>
+      </c>
+      <c r="D30" t="n">
+        <v>39.68</v>
+      </c>
+      <c r="E30" t="n">
+        <v>39.775</v>
+      </c>
+      <c r="F30" t="n">
+        <v>36.8369</v>
+      </c>
+      <c r="G30" t="n">
+        <v>34.7421</v>
+      </c>
+      <c r="H30" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I30" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>24 aug</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>186.86</v>
+      </c>
+      <c r="M30" t="n">
+        <v>188.16</v>
+      </c>
+      <c r="N30" t="n">
+        <v>185.52</v>
+      </c>
+      <c r="O30" t="n">
+        <v>187.2</v>
+      </c>
+      <c r="P30" t="n">
+        <v>152.2848</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>167.6093</v>
+      </c>
+      <c r="R30" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S30" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>21 aug</t>
+        </is>
+      </c>
+      <c r="V30" t="n">
+        <v>479.88</v>
+      </c>
+      <c r="W30" t="n">
+        <v>486.36</v>
+      </c>
+      <c r="X30" t="n">
+        <v>478.53</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>483.24</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>419.092</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>429.4327</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>25 aug</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>39.77</v>
+      </c>
+      <c r="C31" t="n">
+        <v>39.915</v>
+      </c>
+      <c r="D31" t="n">
+        <v>39.385</v>
+      </c>
+      <c r="E31" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="F31" t="n">
+        <v>36.926</v>
+      </c>
+      <c r="G31" t="n">
+        <v>34.783</v>
+      </c>
+      <c r="H31" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I31" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>25 aug</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>186.4</v>
+      </c>
+      <c r="M31" t="n">
+        <v>187.62</v>
+      </c>
+      <c r="N31" t="n">
+        <v>182.74</v>
+      </c>
+      <c r="O31" t="n">
+        <v>185.46</v>
+      </c>
+      <c r="P31" t="n">
+        <v>153.136</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>167.4651</v>
+      </c>
+      <c r="R31" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S31" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>24 aug</t>
+        </is>
+      </c>
+      <c r="V31" t="n">
+        <v>483.21</v>
+      </c>
+      <c r="W31" t="n">
+        <v>490.61</v>
+      </c>
+      <c r="X31" t="n">
+        <v>481.86</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>487.31</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>421.046</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>429.3185</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>26 aug</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>39.275</v>
+      </c>
+      <c r="C32" t="n">
+        <v>39.47</v>
+      </c>
+      <c r="D32" t="n">
+        <v>38.91</v>
+      </c>
+      <c r="E32" t="n">
+        <v>39.42</v>
+      </c>
+      <c r="F32" t="n">
+        <v>37.0192</v>
+      </c>
+      <c r="G32" t="n">
+        <v>34.8202</v>
+      </c>
+      <c r="H32" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I32" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>26 aug</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>179.92</v>
+      </c>
+      <c r="M32" t="n">
+        <v>182.16</v>
+      </c>
+      <c r="N32" t="n">
+        <v>176.82</v>
+      </c>
+      <c r="O32" t="n">
+        <v>180.02</v>
+      </c>
+      <c r="P32" t="n">
+        <v>153.9128</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>167.3049</v>
+      </c>
+      <c r="R32" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S32" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>25 aug</t>
+        </is>
+      </c>
+      <c r="V32" t="n">
+        <v>485.44</v>
+      </c>
+      <c r="W32" t="n">
+        <v>492.44</v>
+      </c>
+      <c r="X32" t="n">
+        <v>484.3</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>491.71</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>423.0801</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>429.262</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>27 aug</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>39.16</v>
+      </c>
+      <c r="C33" t="n">
+        <v>39.295</v>
+      </c>
+      <c r="D33" t="n">
+        <v>38.65</v>
+      </c>
+      <c r="E33" t="n">
+        <v>38.76</v>
+      </c>
+      <c r="F33" t="n">
+        <v>37.117</v>
+      </c>
+      <c r="G33" t="n">
+        <v>34.8559</v>
+      </c>
+      <c r="H33" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I33" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>27 aug</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="M33" t="n">
+        <v>190.8</v>
+      </c>
+      <c r="N33" t="n">
+        <v>181.14</v>
+      </c>
+      <c r="O33" t="n">
+        <v>189.88</v>
+      </c>
+      <c r="P33" t="n">
+        <v>155.0132</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>167.1911</v>
+      </c>
+      <c r="R33" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S33" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>26 aug</t>
+        </is>
+      </c>
+      <c r="V33" t="n">
+        <v>487.85</v>
+      </c>
+      <c r="W33" t="n">
+        <v>497.4</v>
+      </c>
+      <c r="X33" t="n">
+        <v>487.31</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>496.37</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>425.0273</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>429.2786</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>28 aug</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>39</v>
+      </c>
+      <c r="C34" t="n">
+        <v>39.18</v>
+      </c>
+      <c r="D34" t="n">
+        <v>38.845</v>
+      </c>
+      <c r="E34" t="n">
+        <v>39.145</v>
+      </c>
+      <c r="F34" t="n">
+        <v>37.2162</v>
+      </c>
+      <c r="G34" t="n">
+        <v>34.8941</v>
+      </c>
+      <c r="H34" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I34" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>28 aug</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>189.5</v>
+      </c>
+      <c r="M34" t="n">
+        <v>191.94</v>
+      </c>
+      <c r="N34" t="n">
+        <v>187.98</v>
+      </c>
+      <c r="O34" t="n">
+        <v>191.32</v>
+      </c>
+      <c r="P34" t="n">
+        <v>156.1568</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>167.0806</v>
+      </c>
+      <c r="R34" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S34" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>27 aug</t>
+        </is>
+      </c>
+      <c r="V34" t="n">
+        <v>494.88</v>
+      </c>
+      <c r="W34" t="n">
+        <v>506.48</v>
+      </c>
+      <c r="X34" t="n">
+        <v>490.08</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>505.06</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>427.2667</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>429.3401</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>31 aug</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>39.54</v>
+      </c>
+      <c r="C35" t="n">
+        <v>39.91</v>
+      </c>
+      <c r="D35" t="n">
+        <v>39.24</v>
+      </c>
+      <c r="E35" t="n">
+        <v>39.335</v>
+      </c>
+      <c r="F35" t="n">
+        <v>37.3111</v>
+      </c>
+      <c r="G35" t="n">
+        <v>34.9333</v>
+      </c>
+      <c r="H35" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I35" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>31 aug</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>188.46</v>
+      </c>
+      <c r="M35" t="n">
+        <v>192.12</v>
+      </c>
+      <c r="N35" t="n">
+        <v>188.2</v>
+      </c>
+      <c r="O35" t="n">
+        <v>190.9</v>
+      </c>
+      <c r="P35" t="n">
+        <v>157.3304</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>166.9613</v>
+      </c>
+      <c r="R35" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S35" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>28 aug</t>
+        </is>
+      </c>
+      <c r="V35" t="n">
+        <v>505.33</v>
+      </c>
+      <c r="W35" t="n">
+        <v>517.78</v>
+      </c>
+      <c r="X35" t="n">
+        <v>504.87</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>513.53</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>429.9734</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>429.3984</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>1 sep</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>39.77</v>
+      </c>
+      <c r="C36" t="n">
+        <v>40.19</v>
+      </c>
+      <c r="D36" t="n">
+        <v>39.645</v>
+      </c>
+      <c r="E36" t="n">
+        <v>40.155</v>
+      </c>
+      <c r="F36" t="n">
+        <v>37.4239</v>
+      </c>
+      <c r="G36" t="n">
+        <v>34.9763</v>
+      </c>
+      <c r="H36" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I36" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>1 sep</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>186</v>
+      </c>
+      <c r="M36" t="n">
+        <v>187.86</v>
+      </c>
+      <c r="N36" t="n">
+        <v>183.32</v>
+      </c>
+      <c r="O36" t="n">
+        <v>184.26</v>
+      </c>
+      <c r="P36" t="n">
+        <v>158.3252</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>166.8103</v>
+      </c>
+      <c r="R36" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S36" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>31 aug</t>
+        </is>
+      </c>
+      <c r="V36" t="n">
+        <v>510.38</v>
+      </c>
+      <c r="W36" t="n">
+        <v>512.1900000000001</v>
+      </c>
+      <c r="X36" t="n">
+        <v>506.39</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>507.29</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>432.5454</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>429.4122</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2 sep</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>40.35</v>
+      </c>
+      <c r="C37" t="n">
+        <v>40.615</v>
+      </c>
+      <c r="D37" t="n">
+        <v>39.975</v>
+      </c>
+      <c r="E37" t="n">
+        <v>40.21</v>
+      </c>
+      <c r="F37" t="n">
+        <v>37.5499</v>
+      </c>
+      <c r="G37" t="n">
+        <v>35.0217</v>
+      </c>
+      <c r="H37" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I37" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>2 sep</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>182.18</v>
+      </c>
+      <c r="M37" t="n">
+        <v>184.7</v>
+      </c>
+      <c r="N37" t="n">
+        <v>180.72</v>
+      </c>
+      <c r="O37" t="n">
+        <v>181.44</v>
+      </c>
+      <c r="P37" t="n">
+        <v>159.2568</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>166.6796</v>
+      </c>
+      <c r="R37" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S37" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>1 sep</t>
+        </is>
+      </c>
+      <c r="V37" t="n">
+        <v>497.52</v>
+      </c>
+      <c r="W37" t="n">
+        <v>505.97</v>
+      </c>
+      <c r="X37" t="n">
+        <v>496.78</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>501.02</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>435.2328</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>429.3825</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>3 sep</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>40.095</v>
+      </c>
+      <c r="C38" t="n">
+        <v>40.215</v>
+      </c>
+      <c r="D38" t="n">
+        <v>39.54</v>
+      </c>
+      <c r="E38" t="n">
+        <v>40.04</v>
+      </c>
+      <c r="F38" t="n">
+        <v>37.6767</v>
+      </c>
+      <c r="G38" t="n">
+        <v>35.0679</v>
+      </c>
+      <c r="H38" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I38" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>3 sep</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>182.08</v>
+      </c>
+      <c r="M38" t="n">
+        <v>187.56</v>
+      </c>
+      <c r="N38" t="n">
+        <v>182</v>
+      </c>
+      <c r="O38" t="n">
+        <v>185.58</v>
+      </c>
+      <c r="P38" t="n">
+        <v>160.3228</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>166.5898</v>
+      </c>
+      <c r="R38" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S38" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>2 sep</t>
+        </is>
+      </c>
+      <c r="V38" t="n">
+        <v>499.85</v>
+      </c>
+      <c r="W38" t="n">
+        <v>500.27</v>
+      </c>
+      <c r="X38" t="n">
+        <v>493.81</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>496.82</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>437.7045</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>429.3706</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>4 sep</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>40.145</v>
+      </c>
+      <c r="C39" t="n">
+        <v>40.28</v>
+      </c>
+      <c r="D39" t="n">
+        <v>39.665</v>
+      </c>
+      <c r="E39" t="n">
+        <v>40.105</v>
+      </c>
+      <c r="F39" t="n">
+        <v>37.8115</v>
+      </c>
+      <c r="G39" t="n">
+        <v>35.113</v>
+      </c>
+      <c r="H39" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I39" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>4 sep</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>187.8</v>
+      </c>
+      <c r="M39" t="n">
+        <v>189.9</v>
+      </c>
+      <c r="N39" t="n">
+        <v>184.96</v>
+      </c>
+      <c r="O39" t="n">
+        <v>185.68</v>
+      </c>
+      <c r="P39" t="n">
+        <v>161.3336</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>166.5086</v>
+      </c>
+      <c r="R39" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S39" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>3 sep</t>
+        </is>
+      </c>
+      <c r="V39" t="n">
+        <v>501.66</v>
+      </c>
+      <c r="W39" t="n">
+        <v>515.65</v>
+      </c>
+      <c r="X39" t="n">
+        <v>500.8</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>510.12</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>440.6114</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>429.3912</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>7 sep</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>40.26</v>
+      </c>
+      <c r="C40" t="n">
+        <v>40.845</v>
+      </c>
+      <c r="D40" t="n">
+        <v>40.12</v>
+      </c>
+      <c r="E40" t="n">
+        <v>40.56</v>
+      </c>
+      <c r="F40" t="n">
+        <v>37.9551</v>
+      </c>
+      <c r="G40" t="n">
+        <v>35.1619</v>
+      </c>
+      <c r="H40" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I40" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>7 sep</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>183.56</v>
+      </c>
+      <c r="M40" t="n">
+        <v>184.3</v>
+      </c>
+      <c r="N40" t="n">
+        <v>179.92</v>
+      </c>
+      <c r="O40" t="n">
+        <v>182.8</v>
+      </c>
+      <c r="P40" t="n">
+        <v>162.2568</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>166.4122</v>
+      </c>
+      <c r="R40" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S40" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>4 sep</t>
+        </is>
+      </c>
+      <c r="V40" t="n">
+        <v>510</v>
+      </c>
+      <c r="W40" t="n">
+        <v>511</v>
+      </c>
+      <c r="X40" t="n">
+        <v>499.36</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>499.7</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>443.5621</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>429.3729</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>8 sep</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>40.83</v>
+      </c>
+      <c r="C41" t="n">
+        <v>41.18</v>
+      </c>
+      <c r="D41" t="n">
+        <v>40.6325</v>
+      </c>
+      <c r="E41" t="n">
+        <v>40.855</v>
+      </c>
+      <c r="F41" t="n">
+        <v>38.0977</v>
+      </c>
+      <c r="G41" t="n">
+        <v>35.2131</v>
+      </c>
+      <c r="H41" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I41" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>8 sep</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>182.32</v>
+      </c>
+      <c r="M41" t="n">
+        <v>183.76</v>
+      </c>
+      <c r="N41" t="n">
+        <v>180.02</v>
+      </c>
+      <c r="O41" t="n">
+        <v>181.7</v>
+      </c>
+      <c r="P41" t="n">
+        <v>163.2108</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>166.3049</v>
+      </c>
+      <c r="R41" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S41" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>8 sep</t>
+        </is>
+      </c>
+      <c r="V41" t="n">
+        <v>493.01</v>
+      </c>
+      <c r="W41" t="n">
+        <v>495.19</v>
+      </c>
+      <c r="X41" t="n">
+        <v>490.15</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>493.95</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>445.9957</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>429.3939</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>9 sep</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="C42" t="n">
+        <v>41.385</v>
+      </c>
+      <c r="D42" t="n">
+        <v>40.85</v>
+      </c>
+      <c r="E42" t="n">
+        <v>40.94</v>
+      </c>
+      <c r="F42" t="n">
+        <v>38.2513</v>
+      </c>
+      <c r="G42" t="n">
+        <v>35.2646</v>
+      </c>
+      <c r="H42" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I42" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>9 sep</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>183</v>
+      </c>
+      <c r="M42" t="n">
+        <v>187.04</v>
+      </c>
+      <c r="N42" t="n">
+        <v>181.36</v>
+      </c>
+      <c r="O42" t="n">
+        <v>182.86</v>
+      </c>
+      <c r="P42" t="n">
+        <v>164.0504</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>166.2113</v>
+      </c>
+      <c r="R42" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S42" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>9 sep</t>
+        </is>
+      </c>
+      <c r="V42" t="n">
+        <v>493.07</v>
+      </c>
+      <c r="W42" t="n">
+        <v>494.39</v>
+      </c>
+      <c r="X42" t="n">
+        <v>489.8</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>491.65</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>448.4712</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>429.4364</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>10 sep</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>40.98</v>
+      </c>
+      <c r="C43" t="n">
+        <v>41.77</v>
+      </c>
+      <c r="D43" t="n">
+        <v>40.93</v>
+      </c>
+      <c r="E43" t="n">
+        <v>41.23</v>
+      </c>
+      <c r="F43" t="n">
+        <v>38.4034</v>
+      </c>
+      <c r="G43" t="n">
+        <v>35.3174</v>
+      </c>
+      <c r="H43" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I43" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>10 sep</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>180</v>
+      </c>
+      <c r="M43" t="n">
+        <v>180.4</v>
+      </c>
+      <c r="N43" t="n">
+        <v>176.2</v>
+      </c>
+      <c r="O43" t="n">
+        <v>177.82</v>
+      </c>
+      <c r="P43" t="n">
+        <v>164.7724</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>166.0803</v>
+      </c>
+      <c r="R43" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S43" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>10 sep</t>
+        </is>
+      </c>
+      <c r="V43" t="n">
+        <v>488.32</v>
+      </c>
+      <c r="W43" t="n">
+        <v>494.52</v>
+      </c>
+      <c r="X43" t="n">
+        <v>486</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>492.44</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>450.8736</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>429.5215</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>11 sep</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>41.345</v>
+      </c>
+      <c r="C44" t="n">
+        <v>41.715</v>
+      </c>
+      <c r="D44" t="n">
+        <v>40.905</v>
+      </c>
+      <c r="E44" t="n">
+        <v>41.415</v>
+      </c>
+      <c r="F44" t="n">
+        <v>38.5608</v>
+      </c>
+      <c r="G44" t="n">
+        <v>35.3717</v>
+      </c>
+      <c r="H44" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I44" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>11 sep</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>175.68</v>
+      </c>
+      <c r="M44" t="n">
+        <v>178.84</v>
+      </c>
+      <c r="N44" t="n">
+        <v>172.16</v>
+      </c>
+      <c r="O44" t="n">
+        <v>177.26</v>
+      </c>
+      <c r="P44" t="n">
+        <v>165.5248</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>165.9594</v>
+      </c>
+      <c r="R44" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S44" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>11 sep</t>
+        </is>
+      </c>
+      <c r="V44" t="n">
+        <v>495.65</v>
+      </c>
+      <c r="W44" t="n">
+        <v>498.97</v>
+      </c>
+      <c r="X44" t="n">
+        <v>492.58</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>495.63</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>453.115</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>429.6539</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>14 sep</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>41.88</v>
+      </c>
+      <c r="C45" t="n">
+        <v>42.285</v>
+      </c>
+      <c r="D45" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="E45" t="n">
+        <v>41.91</v>
+      </c>
+      <c r="F45" t="n">
+        <v>38.7226</v>
+      </c>
+      <c r="G45" t="n">
+        <v>35.4269</v>
+      </c>
+      <c r="H45" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I45" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>14 sep</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>180.82</v>
+      </c>
+      <c r="M45" t="n">
+        <v>186.76</v>
+      </c>
+      <c r="N45" t="n">
+        <v>180.82</v>
+      </c>
+      <c r="O45" t="n">
+        <v>186.26</v>
+      </c>
+      <c r="P45" t="n">
+        <v>166.4488</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>165.8745</v>
+      </c>
+      <c r="R45" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S45" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>14 sep</t>
+        </is>
+      </c>
+      <c r="V45" t="n">
+        <v>497.06</v>
+      </c>
+      <c r="W45" t="n">
+        <v>509.95</v>
+      </c>
+      <c r="X45" t="n">
+        <v>495.34</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>505.41</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>455.4281</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>429.8259</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>15 sep</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>41.845</v>
+      </c>
+      <c r="C46" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="D46" t="n">
+        <v>41.72</v>
+      </c>
+      <c r="E46" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="F46" t="n">
+        <v>38.8782</v>
+      </c>
+      <c r="G46" t="n">
+        <v>35.4854</v>
+      </c>
+      <c r="H46" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I46" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>15 sep</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>186.64</v>
+      </c>
+      <c r="M46" t="n">
+        <v>187.26</v>
+      </c>
+      <c r="N46" t="n">
+        <v>183.2</v>
+      </c>
+      <c r="O46" t="n">
+        <v>187.08</v>
+      </c>
+      <c r="P46" t="n">
+        <v>167.3124</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>165.7921</v>
+      </c>
+      <c r="R46" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S46" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>15 sep</t>
+        </is>
+      </c>
+      <c r="V46" t="n">
+        <v>500.06</v>
+      </c>
+      <c r="W46" t="n">
+        <v>505.9</v>
+      </c>
+      <c r="X46" t="n">
+        <v>495.54</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>497.12</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>457.6502</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>429.9416</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>16 sep</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>42.72</v>
+      </c>
+      <c r="C47" t="n">
+        <v>42.85</v>
+      </c>
+      <c r="D47" t="n">
+        <v>41.67</v>
+      </c>
+      <c r="E47" t="n">
+        <v>41.825</v>
+      </c>
+      <c r="F47" t="n">
+        <v>38.9989</v>
+      </c>
+      <c r="G47" t="n">
+        <v>35.5403</v>
+      </c>
+      <c r="H47" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I47" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>16 sep</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>185.86</v>
+      </c>
+      <c r="M47" t="n">
+        <v>186.76</v>
+      </c>
+      <c r="N47" t="n">
+        <v>182.18</v>
+      </c>
+      <c r="O47" t="n">
+        <v>186.56</v>
+      </c>
+      <c r="P47" t="n">
+        <v>168.2844</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>165.6996</v>
+      </c>
+      <c r="R47" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S47" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>16 sep</t>
+        </is>
+      </c>
+      <c r="V47" t="n">
+        <v>493.03</v>
+      </c>
+      <c r="W47" t="n">
+        <v>495.97</v>
+      </c>
+      <c r="X47" t="n">
+        <v>487.23</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>490.3</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>459.694</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>429.9809</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>17 sep</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>41.58</v>
+      </c>
+      <c r="C48" t="n">
+        <v>42.055</v>
+      </c>
+      <c r="D48" t="n">
+        <v>41.38</v>
+      </c>
+      <c r="E48" t="n">
+        <v>41.56</v>
+      </c>
+      <c r="F48" t="n">
+        <v>39.1225</v>
+      </c>
+      <c r="G48" t="n">
+        <v>35.5926</v>
+      </c>
+      <c r="H48" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I48" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>17 sep</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>188.54</v>
+      </c>
+      <c r="M48" t="n">
+        <v>189.2</v>
+      </c>
+      <c r="N48" t="n">
+        <v>184.62</v>
+      </c>
+      <c r="O48" t="n">
+        <v>188</v>
+      </c>
+      <c r="P48" t="n">
+        <v>169.2896</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>165.6125</v>
+      </c>
+      <c r="R48" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S48" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>17 sep</t>
+        </is>
+      </c>
+      <c r="V48" t="n">
+        <v>497.8</v>
+      </c>
+      <c r="W48" t="n">
+        <v>501.47</v>
+      </c>
+      <c r="X48" t="n">
+        <v>493.17</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>497.75</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>461.9966</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>430.0251</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>18 sep</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>41.465</v>
+      </c>
+      <c r="C49" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="D49" t="n">
+        <v>40.955</v>
+      </c>
+      <c r="E49" t="n">
+        <v>41.315</v>
+      </c>
+      <c r="F49" t="n">
+        <v>39.2414</v>
+      </c>
+      <c r="G49" t="n">
+        <v>35.6436</v>
+      </c>
+      <c r="H49" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I49" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>18 sep</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>186.1</v>
+      </c>
+      <c r="M49" t="n">
+        <v>187.26</v>
+      </c>
+      <c r="N49" t="n">
+        <v>182.56</v>
+      </c>
+      <c r="O49" t="n">
+        <v>183.12</v>
+      </c>
+      <c r="P49" t="n">
+        <v>170.2004</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>165.5062</v>
+      </c>
+      <c r="R49" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S49" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>18 sep</t>
+        </is>
+      </c>
+      <c r="V49" t="n">
+        <v>497.97</v>
+      </c>
+      <c r="W49" t="n">
+        <v>498.65</v>
+      </c>
+      <c r="X49" t="n">
+        <v>491.1</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>493.78</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>464.1995</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>430.0757</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>21 sep</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>41.04</v>
+      </c>
+      <c r="C50" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="D50" t="n">
+        <v>40.775</v>
+      </c>
+      <c r="E50" t="n">
+        <v>40.775</v>
+      </c>
+      <c r="F50" t="n">
+        <v>39.3341</v>
+      </c>
+      <c r="G50" t="n">
+        <v>35.6939</v>
+      </c>
+      <c r="H50" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I50" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>21 sep</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>184.7</v>
+      </c>
+      <c r="M50" t="n">
+        <v>185.86</v>
+      </c>
+      <c r="N50" t="n">
+        <v>182.48</v>
+      </c>
+      <c r="O50" t="n">
+        <v>182.86</v>
+      </c>
+      <c r="P50" t="n">
+        <v>171.0432</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>165.4052</v>
+      </c>
+      <c r="R50" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S50" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>21 sep</t>
+        </is>
+      </c>
+      <c r="V50" t="n">
+        <v>494.95</v>
+      </c>
+      <c r="W50" t="n">
+        <v>501.87</v>
+      </c>
+      <c r="X50" t="n">
+        <v>491.33</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>501.61</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>466.5442</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>430.1492</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>22 sep</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>40.84</v>
+      </c>
+      <c r="C51" t="n">
+        <v>41.165</v>
+      </c>
+      <c r="D51" t="n">
+        <v>40.215</v>
+      </c>
+      <c r="E51" t="n">
+        <v>41.01</v>
+      </c>
+      <c r="F51" t="n">
+        <v>39.4244</v>
+      </c>
+      <c r="G51" t="n">
+        <v>35.746</v>
+      </c>
+      <c r="H51" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I51" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>22 sep</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>182.14</v>
+      </c>
+      <c r="M51" t="n">
+        <v>187.48</v>
+      </c>
+      <c r="N51" t="n">
+        <v>181.52</v>
+      </c>
+      <c r="O51" t="n">
+        <v>182.32</v>
+      </c>
+      <c r="P51" t="n">
+        <v>171.9552</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>165.2836</v>
+      </c>
+      <c r="R51" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S51" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>22 sep</t>
+        </is>
+      </c>
+      <c r="V51" t="n">
+        <v>507.32</v>
+      </c>
+      <c r="W51" t="n">
+        <v>508.5</v>
+      </c>
+      <c r="X51" t="n">
+        <v>493.65</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>498</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>468.699</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>430.2656</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>23 sep</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>41</v>
+      </c>
+      <c r="C52" t="n">
+        <v>41.755</v>
+      </c>
+      <c r="D52" t="n">
+        <v>40.995</v>
+      </c>
+      <c r="E52" t="n">
+        <v>41.69</v>
+      </c>
+      <c r="F52" t="n">
+        <v>39.5272</v>
+      </c>
+      <c r="G52" t="n">
+        <v>35.8024</v>
+      </c>
+      <c r="H52" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I52" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>23 sep</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>184.9</v>
+      </c>
+      <c r="M52" t="n">
+        <v>187.8</v>
+      </c>
+      <c r="N52" t="n">
+        <v>183.48</v>
+      </c>
+      <c r="O52" t="n">
+        <v>186.46</v>
+      </c>
+      <c r="P52" t="n">
+        <v>172.9448</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>165.1675</v>
+      </c>
+      <c r="R52" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S52" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>23 sep</t>
+        </is>
+      </c>
+      <c r="V52" t="n">
+        <v>500.76</v>
+      </c>
+      <c r="W52" t="n">
+        <v>509.44</v>
+      </c>
+      <c r="X52" t="n">
+        <v>495.88</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>500.59</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>471.0267</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>430.3795</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>24 sep</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>41.825</v>
+      </c>
+      <c r="C53" t="n">
+        <v>42.52</v>
+      </c>
+      <c r="D53" t="n">
+        <v>41.78</v>
+      </c>
+      <c r="E53" t="n">
+        <v>42.43</v>
+      </c>
+      <c r="F53" t="n">
+        <v>39.6382</v>
+      </c>
+      <c r="G53" t="n">
+        <v>35.8638</v>
+      </c>
+      <c r="H53" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I53" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>24 sep</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>184.52</v>
+      </c>
+      <c r="M53" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="N53" t="n">
+        <v>182.26</v>
+      </c>
+      <c r="O53" t="n">
+        <v>184.18</v>
+      </c>
+      <c r="P53" t="n">
+        <v>173.8756</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>165.0554</v>
+      </c>
+      <c r="R53" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S53" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>24 sep</t>
+        </is>
+      </c>
+      <c r="V53" t="n">
+        <v>495.07</v>
+      </c>
+      <c r="W53" t="n">
+        <v>498.9</v>
+      </c>
+      <c r="X53" t="n">
+        <v>491.22</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>497.93</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>473.0876</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>430.4686</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>25 sep</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>41.99</v>
+      </c>
+      <c r="C54" t="n">
+        <v>42.33</v>
+      </c>
+      <c r="D54" t="n">
+        <v>41.71</v>
+      </c>
+      <c r="E54" t="n">
+        <v>42.06</v>
+      </c>
+      <c r="F54" t="n">
+        <v>39.7263</v>
+      </c>
+      <c r="G54" t="n">
+        <v>35.9239</v>
+      </c>
+      <c r="H54" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I54" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>25 sep</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>184.42</v>
+      </c>
+      <c r="M54" t="n">
+        <v>185.92</v>
+      </c>
+      <c r="N54" t="n">
+        <v>183.76</v>
+      </c>
+      <c r="O54" t="n">
+        <v>185.92</v>
+      </c>
+      <c r="P54" t="n">
+        <v>174.8356</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>164.9525</v>
+      </c>
+      <c r="R54" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S54" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>25 sep</t>
+        </is>
+      </c>
+      <c r="V54" t="n">
+        <v>499.04</v>
+      </c>
+      <c r="W54" t="n">
+        <v>519.4</v>
+      </c>
+      <c r="X54" t="n">
+        <v>497.25</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>516.17</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>475.4041</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>430.6098</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>28 sep</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>42.45</v>
+      </c>
+      <c r="C55" t="n">
+        <v>42.995</v>
+      </c>
+      <c r="D55" t="n">
+        <v>42.38</v>
+      </c>
+      <c r="E55" t="n">
+        <v>42.725</v>
+      </c>
+      <c r="F55" t="n">
+        <v>39.8301</v>
+      </c>
+      <c r="G55" t="n">
+        <v>35.9888</v>
+      </c>
+      <c r="H55" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I55" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>28 sep</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>185.2</v>
+      </c>
+      <c r="M55" t="n">
+        <v>186.76</v>
+      </c>
+      <c r="N55" t="n">
+        <v>178.88</v>
+      </c>
+      <c r="O55" t="n">
+        <v>184.02</v>
+      </c>
+      <c r="P55" t="n">
+        <v>175.7508</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>164.8355</v>
+      </c>
+      <c r="R55" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S55" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>28 sep</t>
+        </is>
+      </c>
+      <c r="V55" t="n">
+        <v>505.47</v>
+      </c>
+      <c r="W55" t="n">
+        <v>513.33</v>
+      </c>
+      <c r="X55" t="n">
+        <v>502.22</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>509.22</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>477.7269</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>430.7113</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>29 sep</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>42.57</v>
+      </c>
+      <c r="C56" t="n">
+        <v>42.665</v>
+      </c>
+      <c r="D56" t="n">
+        <v>41.73</v>
+      </c>
+      <c r="E56" t="n">
+        <v>42.05</v>
+      </c>
+      <c r="F56" t="n">
+        <v>39.9146</v>
+      </c>
+      <c r="G56" t="n">
+        <v>36.0498</v>
+      </c>
+      <c r="H56" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I56" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>29 sep</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>183.22</v>
+      </c>
+      <c r="M56" t="n">
+        <v>186.34</v>
+      </c>
+      <c r="N56" t="n">
+        <v>182.28</v>
+      </c>
+      <c r="O56" t="n">
+        <v>185.32</v>
+      </c>
+      <c r="P56" t="n">
+        <v>176.7288</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>164.733</v>
+      </c>
+      <c r="R56" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S56" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>29 sep</t>
+        </is>
+      </c>
+      <c r="V56" t="n">
+        <v>508.31</v>
+      </c>
+      <c r="W56" t="n">
+        <v>513.64</v>
+      </c>
+      <c r="X56" t="n">
+        <v>502.4</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>508.96</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>479.8754</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>430.8784</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>30 sep</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>41.975</v>
+      </c>
+      <c r="C57" t="n">
+        <v>42.095</v>
+      </c>
+      <c r="D57" t="n">
+        <v>41.58</v>
+      </c>
+      <c r="E57" t="n">
+        <v>41.91</v>
+      </c>
+      <c r="F57" t="n">
+        <v>39.9874</v>
+      </c>
+      <c r="G57" t="n">
+        <v>36.1135</v>
+      </c>
+      <c r="H57" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I57" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>30 sep</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="M57" t="n">
+        <v>186.2</v>
+      </c>
+      <c r="N57" t="n">
+        <v>181.06</v>
+      </c>
+      <c r="O57" t="n">
+        <v>185.66</v>
+      </c>
+      <c r="P57" t="n">
+        <v>177.8012</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>164.6377</v>
+      </c>
+      <c r="R57" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S57" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>30 sep</t>
+        </is>
+      </c>
+      <c r="V57" t="n">
+        <v>511.61</v>
+      </c>
+      <c r="W57" t="n">
+        <v>519.83</v>
+      </c>
+      <c r="X57" t="n">
+        <v>510.31</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>512.9</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>482.1933</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>431.0408</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>1 okt</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>41.625</v>
+      </c>
+      <c r="C58" t="n">
+        <v>42.36</v>
+      </c>
+      <c r="D58" t="n">
+        <v>41.165</v>
+      </c>
+      <c r="E58" t="n">
+        <v>42.24</v>
+      </c>
+      <c r="F58" t="n">
+        <v>40.0562</v>
+      </c>
+      <c r="G58" t="n">
+        <v>36.1777</v>
+      </c>
+      <c r="H58" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I58" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>1 okt</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>184.68</v>
+      </c>
+      <c r="M58" t="n">
+        <v>190.26</v>
+      </c>
+      <c r="N58" t="n">
+        <v>181.34</v>
+      </c>
+      <c r="O58" t="n">
+        <v>186.74</v>
+      </c>
+      <c r="P58" t="n">
+        <v>178.9696</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>164.5407</v>
+      </c>
+      <c r="R58" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S58" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>1 okt</t>
+        </is>
+      </c>
+      <c r="V58" t="n">
+        <v>519.88</v>
+      </c>
+      <c r="W58" t="n">
+        <v>522.85</v>
+      </c>
+      <c r="X58" t="n">
+        <v>512.17</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>512.8</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>484.6572</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>431.2272</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2 okt</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>42.11</v>
+      </c>
+      <c r="C59" t="n">
+        <v>42.745</v>
+      </c>
+      <c r="D59" t="n">
+        <v>41.985</v>
+      </c>
+      <c r="E59" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="F59" t="n">
+        <v>40.1364</v>
+      </c>
+      <c r="G59" t="n">
+        <v>36.2422</v>
+      </c>
+      <c r="H59" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I59" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>2 okt</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>187.82</v>
+      </c>
+      <c r="M59" t="n">
+        <v>188.74</v>
+      </c>
+      <c r="N59" t="n">
+        <v>183.92</v>
+      </c>
+      <c r="O59" t="n">
+        <v>183.92</v>
+      </c>
+      <c r="P59" t="n">
+        <v>179.844</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>164.4442</v>
+      </c>
+      <c r="R59" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S59" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>2 okt</t>
+        </is>
+      </c>
+      <c r="V59" t="n">
+        <v>519.39</v>
+      </c>
+      <c r="W59" t="n">
+        <v>522.5</v>
+      </c>
+      <c r="X59" t="n">
+        <v>513.66</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>517.53</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>487.3905</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>431.4557</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>5 okt</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>42.645</v>
+      </c>
+      <c r="C60" t="n">
+        <v>43.11</v>
+      </c>
+      <c r="D60" t="n">
+        <v>42.35</v>
+      </c>
+      <c r="E60" t="n">
+        <v>42.865</v>
+      </c>
+      <c r="F60" t="n">
+        <v>40.2347</v>
+      </c>
+      <c r="G60" t="n">
+        <v>36.3069</v>
+      </c>
+      <c r="H60" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I60" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>5 okt</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>185.06</v>
+      </c>
+      <c r="M60" t="n">
+        <v>188.5</v>
+      </c>
+      <c r="N60" t="n">
+        <v>184.66</v>
+      </c>
+      <c r="O60" t="n">
+        <v>185.04</v>
+      </c>
+      <c r="P60" t="n">
+        <v>180.5192</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>164.3515</v>
+      </c>
+      <c r="R60" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S60" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>5 okt</t>
+        </is>
+      </c>
+      <c r="V60" t="n">
+        <v>521.62</v>
+      </c>
+      <c r="W60" t="n">
+        <v>532.35</v>
+      </c>
+      <c r="X60" t="n">
+        <v>521.47</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>525.1799999999999</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>490.2745</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>431.7147</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>6 okt</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>42.86</v>
+      </c>
+      <c r="C61" t="n">
+        <v>43.285</v>
+      </c>
+      <c r="D61" t="n">
+        <v>42.43</v>
+      </c>
+      <c r="E61" t="n">
+        <v>43.185</v>
+      </c>
+      <c r="F61" t="n">
+        <v>40.349</v>
+      </c>
+      <c r="G61" t="n">
+        <v>36.3726</v>
+      </c>
+      <c r="H61" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I61" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>6 okt</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>186.56</v>
+      </c>
+      <c r="M61" t="n">
+        <v>190.22</v>
+      </c>
+      <c r="N61" t="n">
+        <v>186.06</v>
+      </c>
+      <c r="O61" t="n">
+        <v>188.6</v>
+      </c>
+      <c r="P61" t="n">
+        <v>181.1064</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>164.2647</v>
+      </c>
+      <c r="R61" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S61" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>6 okt</t>
+        </is>
+      </c>
+      <c r="V61" t="n">
+        <v>531.6799999999999</v>
+      </c>
+      <c r="W61" t="n">
+        <v>535.6900000000001</v>
+      </c>
+      <c r="X61" t="n">
+        <v>528.78</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>529.3</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>493.0931</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>431.9956</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>7 okt</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>43.37</v>
+      </c>
+      <c r="C62" t="n">
+        <v>43.835</v>
+      </c>
+      <c r="D62" t="n">
+        <v>43.145</v>
+      </c>
+      <c r="E62" t="n">
+        <v>43.25</v>
+      </c>
+      <c r="F62" t="n">
+        <v>40.4451</v>
+      </c>
+      <c r="G62" t="n">
+        <v>36.4388</v>
+      </c>
+      <c r="H62" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I62" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>7 okt</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>187</v>
+      </c>
+      <c r="M62" t="n">
+        <v>188.72</v>
+      </c>
+      <c r="N62" t="n">
+        <v>186.04</v>
+      </c>
+      <c r="O62" t="n">
+        <v>187.62</v>
+      </c>
+      <c r="P62" t="n">
+        <v>181.618</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>164.1762</v>
+      </c>
+      <c r="R62" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S62" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>7 okt</t>
+        </is>
+      </c>
+      <c r="V62" t="n">
+        <v>530.73</v>
+      </c>
+      <c r="W62" t="n">
+        <v>531.73</v>
+      </c>
+      <c r="X62" t="n">
+        <v>524.6900000000001</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>529.76</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>495.8361</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>432.2398</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>8 okt</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>43.555</v>
+      </c>
+      <c r="C63" t="n">
+        <v>44.815</v>
+      </c>
+      <c r="D63" t="n">
+        <v>43.5425</v>
+      </c>
+      <c r="E63" t="n">
+        <v>44.75</v>
+      </c>
+      <c r="F63" t="n">
+        <v>40.5699</v>
+      </c>
+      <c r="G63" t="n">
+        <v>36.5123</v>
+      </c>
+      <c r="H63" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I63" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>8 okt</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
+        <v>187.04</v>
+      </c>
+      <c r="M63" t="n">
+        <v>189.82</v>
+      </c>
+      <c r="N63" t="n">
+        <v>183.76</v>
+      </c>
+      <c r="O63" t="n">
+        <v>184.62</v>
+      </c>
+      <c r="P63" t="n">
+        <v>182.192</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>164.074</v>
+      </c>
+      <c r="R63" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S63" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>8 okt</t>
+        </is>
+      </c>
+      <c r="V63" t="n">
+        <v>529.8099999999999</v>
+      </c>
+      <c r="W63" t="n">
+        <v>533.51</v>
+      </c>
+      <c r="X63" t="n">
+        <v>518.79</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>522.61</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>498.4921</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>432.4385</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>9 okt</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>44.42</v>
+      </c>
+      <c r="C64" t="n">
+        <v>45.155</v>
+      </c>
+      <c r="D64" t="n">
+        <v>43.94</v>
+      </c>
+      <c r="E64" t="n">
+        <v>45.035</v>
+      </c>
+      <c r="F64" t="n">
+        <v>40.6842</v>
+      </c>
+      <c r="G64" t="n">
+        <v>36.5866</v>
+      </c>
+      <c r="H64" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I64" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>9 okt</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>188.98</v>
+      </c>
+      <c r="M64" t="n">
+        <v>192.58</v>
+      </c>
+      <c r="N64" t="n">
+        <v>188.86</v>
+      </c>
+      <c r="O64" t="n">
+        <v>191.46</v>
+      </c>
+      <c r="P64" t="n">
+        <v>182.8676</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>164.0101</v>
+      </c>
+      <c r="R64" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S64" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>9 okt</t>
+        </is>
+      </c>
+      <c r="V64" t="n">
+        <v>528.24</v>
+      </c>
+      <c r="W64" t="n">
+        <v>537.22</v>
+      </c>
+      <c r="X64" t="n">
+        <v>526.24</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>535.0700000000001</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>500.1885</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>432.7046</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>12 okt</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>44.725</v>
+      </c>
+      <c r="C65" t="n">
+        <v>45.81</v>
+      </c>
+      <c r="D65" t="n">
+        <v>44.695</v>
+      </c>
+      <c r="E65" t="n">
+        <v>45.56</v>
+      </c>
+      <c r="F65" t="n">
+        <v>40.8072</v>
+      </c>
+      <c r="G65" t="n">
+        <v>36.6625</v>
+      </c>
+      <c r="H65" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I65" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>12 okt</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
+        <v>190.58</v>
+      </c>
+      <c r="M65" t="n">
+        <v>197.88</v>
+      </c>
+      <c r="N65" t="n">
+        <v>189.78</v>
+      </c>
+      <c r="O65" t="n">
+        <v>194.46</v>
+      </c>
+      <c r="P65" t="n">
+        <v>183.464</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>163.9576</v>
+      </c>
+      <c r="R65" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S65" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>12 okt</t>
+        </is>
+      </c>
+      <c r="V65" t="n">
+        <v>537.53</v>
+      </c>
+      <c r="W65" t="n">
+        <v>542.74</v>
+      </c>
+      <c r="X65" t="n">
+        <v>535.7</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>541.15</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>501.7346</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>432.9914</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>13 okt</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>45.69</v>
+      </c>
+      <c r="C66" t="n">
+        <v>45.97</v>
+      </c>
+      <c r="D66" t="n">
+        <v>45.35</v>
+      </c>
+      <c r="E66" t="n">
+        <v>45.95</v>
+      </c>
+      <c r="F66" t="n">
+        <v>40.9565</v>
+      </c>
+      <c r="G66" t="n">
+        <v>36.7398</v>
+      </c>
+      <c r="H66" t="n">
+        <v>45.05751734733581</v>
+      </c>
+      <c r="I66" t="n">
+        <v>43.23680321420942</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>13 okt</t>
+        </is>
+      </c>
+      <c r="L66" t="n">
+        <v>196</v>
+      </c>
+      <c r="M66" t="n">
+        <v>198.18</v>
+      </c>
+      <c r="N66" t="n">
+        <v>194.02</v>
+      </c>
+      <c r="O66" t="n">
+        <v>197.28</v>
+      </c>
+      <c r="P66" t="n">
+        <v>184.062</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>163.9196</v>
+      </c>
+      <c r="R66" t="n">
+        <v>191.5557367172241</v>
+      </c>
+      <c r="S66" t="n">
+        <v>181.0157045636858</v>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>13 okt</t>
+        </is>
+      </c>
+      <c r="V66" t="n">
+        <v>544.64</v>
+      </c>
+      <c r="W66" t="n">
+        <v>551.15</v>
+      </c>
+      <c r="X66" t="n">
+        <v>543.0599999999999</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>543.45</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>502.8689</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>433.2839</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>535.3375423278808</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>509.8989698529924</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/rapporten/trend-agent.xlsx
+++ b/rapporten/trend-agent.xlsx
@@ -2046,7 +2046,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>10027.51</v>
+        <v>10029.19</v>
       </c>
       <c r="C5" s="2">
         <f>B5-B4</f>
@@ -2201,38 +2201,38 @@
     <row r="6" ht="22" customHeight="1">
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Shell (SHELL.AS)  ·  45,95 EUR</t>
+          <t>Shell (SHELL.AS)  ·  46,29 EUR</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>SAP (SAP.DE)  ·  197,28 EUR</t>
+          <t>SAP (SAP.DE)  ·  200,50 EUR</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>Gestegen: 25,7% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +2,0% (winst). De bot verkoopt als de koers onder 43,24 zakt (-5,9%).</t>
+          <t>Gestegen: 25,5% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +2,7% (winst). De bot verkoopt als de koers onder 43,59 zakt (-5,8%).</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>Gestegen: 44,0% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +3,0% (winst). De bot verkoopt als de koers onder 181,02 zakt (-8,2%).</t>
+          <t>Gestegen: 45,7% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +4,7% (winst). De bot verkoopt als de koers onder 184,37 zakt (-8,0%).</t>
         </is>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Microsoft (MSFT)  ·  543,45 USD</t>
+          <t>Microsoft (MSFT)  ·  533,69 USD</t>
         </is>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Gestegen: 41,4% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +1,5% (winst). De bot verkoopt als de koers onder 509,90 zakt (-6,2%).</t>
+          <t>Gestegen: 35,2% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: -0,3% (verlies). De bot verkoopt als de koers onder 509,90 zakt (-4,5%).</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
         <v>45.06</v>
       </c>
       <c r="F2" t="n">
-        <v>43.24</v>
+        <v>43.59</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>191.56</v>
       </c>
       <c r="F3" t="n">
-        <v>181.02</v>
+        <v>184.37</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2692,10 +2692,353 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>(geen kandidaten die aan alle regels voldoen)</t>
-        </is>
+          <t>SHELL.AS</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>0.2293077511599</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>0.08419197521715405</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I2" t="n">
+        <v>46.29</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SAP.DE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>0.4537413186041173</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>0.07173400704295707</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I3" t="n">
+        <v>200.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>WKL.AS</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Wolters Kluwer</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0.116</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0.3133184485032652</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0.1645312027016144</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="I4" t="n">
+        <v>79.98</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>XLE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Energie-ETF</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0.106</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0.1931250609053237</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0.03188213977858134</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="I5" t="n">
+        <v>67.63</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>XOM</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ExxonMobil</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0.2206657103115155</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0.04541688430175994</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I6" t="n">
+        <v>177.01</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0.3330707534804345</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0.07356374252377029</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="I7" t="n">
+        <v>533.6900000000001</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>TTE.PA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>TotalEnergies</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0.1572873705295681</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0.0137947190612262</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="I8" t="n">
+        <v>80.66</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Palantir</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0.4948675808622736</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0.1646384101996907</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="I9" t="n">
+        <v>200.97</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>0.1107263312675328</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>0.101280166976637</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="I10" t="n">
+        <v>737.54</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>0.07399126212527274</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>0.04209040456874846</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>391.43</v>
       </c>
     </row>
   </sheetData>
@@ -2966,75 +3309,75 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>15 jul</t>
+          <t>16 jul</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>36.4566</v>
+        <v>36.5803</v>
       </c>
       <c r="C2" t="n">
-        <v>37.1001</v>
+        <v>37.011</v>
       </c>
       <c r="D2" t="n">
-        <v>36.4566</v>
+        <v>36.3724</v>
       </c>
       <c r="E2" t="n">
-        <v>36.5506</v>
+        <v>36.8773</v>
       </c>
       <c r="F2" t="n">
-        <v>35.581</v>
+        <v>35.6114</v>
       </c>
       <c r="H2" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I2" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>15 jul</t>
+          <t>16 jul</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>134.42</v>
+        <v>137.2</v>
       </c>
       <c r="M2" t="n">
-        <v>139.44</v>
+        <v>138.24</v>
       </c>
       <c r="N2" t="n">
-        <v>133.52</v>
+        <v>135.14</v>
       </c>
       <c r="O2" t="n">
-        <v>136.98</v>
+        <v>137.64</v>
       </c>
       <c r="P2" t="n">
-        <v>145.0924</v>
+        <v>144.8176</v>
       </c>
       <c r="R2" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S2" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>14 jul</t>
+          <t>15 jul</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>382.1007</v>
+        <v>387.0713</v>
       </c>
       <c r="W2" t="n">
-        <v>387.4606</v>
+        <v>398.2104</v>
       </c>
       <c r="X2" t="n">
-        <v>377.9385</v>
+        <v>385.674</v>
       </c>
       <c r="Y2" t="n">
-        <v>384.2067</v>
+        <v>394.8866</v>
       </c>
       <c r="Z2" t="n">
-        <v>401.4825</v>
+        <v>401.1249</v>
       </c>
       <c r="AB2" t="n">
         <v>535.3375423278808</v>
@@ -3046,75 +3389,75 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>16 jul</t>
+          <t>17 jul</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>36.5803</v>
+        <v>36.912</v>
       </c>
       <c r="C3" t="n">
-        <v>37.011</v>
+        <v>37.8871</v>
       </c>
       <c r="D3" t="n">
-        <v>36.3724</v>
+        <v>36.912</v>
       </c>
       <c r="E3" t="n">
-        <v>36.8773</v>
+        <v>37.6594</v>
       </c>
       <c r="F3" t="n">
-        <v>35.6114</v>
+        <v>35.6614</v>
       </c>
       <c r="H3" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I3" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>16 jul</t>
+          <t>17 jul</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>137.2</v>
+        <v>140.6</v>
       </c>
       <c r="M3" t="n">
-        <v>138.24</v>
+        <v>141.54</v>
       </c>
       <c r="N3" t="n">
-        <v>135.14</v>
+        <v>137.32</v>
       </c>
       <c r="O3" t="n">
-        <v>137.64</v>
+        <v>137.92</v>
       </c>
       <c r="P3" t="n">
-        <v>144.8176</v>
+        <v>144.652</v>
       </c>
       <c r="R3" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S3" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>15 jul</t>
+          <t>16 jul</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>387.0713</v>
+        <v>397.5616</v>
       </c>
       <c r="W3" t="n">
-        <v>398.2104</v>
+        <v>405.2271</v>
       </c>
       <c r="X3" t="n">
-        <v>385.674</v>
+        <v>391.3133</v>
       </c>
       <c r="Y3" t="n">
-        <v>394.8866</v>
+        <v>400.3463</v>
       </c>
       <c r="Z3" t="n">
-        <v>401.1249</v>
+        <v>400.8928</v>
       </c>
       <c r="AB3" t="n">
         <v>535.3375423278808</v>
@@ -3126,75 +3469,75 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>17 jul</t>
+          <t>20 jul</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>36.912</v>
+        <v>38.0653</v>
       </c>
       <c r="C4" t="n">
-        <v>37.8871</v>
+        <v>38.1742</v>
       </c>
       <c r="D4" t="n">
-        <v>36.912</v>
+        <v>37.1496</v>
       </c>
       <c r="E4" t="n">
-        <v>37.6594</v>
+        <v>37.5307</v>
       </c>
       <c r="F4" t="n">
-        <v>35.6614</v>
+        <v>35.7021</v>
       </c>
       <c r="H4" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I4" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>17 jul</t>
+          <t>20 jul</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>140.6</v>
+        <v>138</v>
       </c>
       <c r="M4" t="n">
-        <v>141.54</v>
+        <v>140.04</v>
       </c>
       <c r="N4" t="n">
-        <v>137.32</v>
+        <v>134.98</v>
       </c>
       <c r="O4" t="n">
-        <v>137.92</v>
+        <v>138.26</v>
       </c>
       <c r="P4" t="n">
-        <v>144.652</v>
+        <v>144.528</v>
       </c>
       <c r="R4" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S4" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>16 jul</t>
+          <t>17 jul</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>397.5616</v>
+        <v>394.118</v>
       </c>
       <c r="W4" t="n">
-        <v>405.2271</v>
+        <v>397.6414</v>
       </c>
       <c r="X4" t="n">
-        <v>391.3133</v>
+        <v>388.6583</v>
       </c>
       <c r="Y4" t="n">
-        <v>400.3463</v>
+        <v>393.08</v>
       </c>
       <c r="Z4" t="n">
-        <v>400.8928</v>
+        <v>400.5601</v>
       </c>
       <c r="AB4" t="n">
         <v>535.3375423278808</v>
@@ -3206,75 +3549,75 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20 jul</t>
+          <t>21 jul</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>38.0653</v>
+        <v>37.5703</v>
       </c>
       <c r="C5" t="n">
-        <v>38.1742</v>
+        <v>37.8277</v>
       </c>
       <c r="D5" t="n">
-        <v>37.1496</v>
+        <v>37.4169</v>
       </c>
       <c r="E5" t="n">
-        <v>37.5307</v>
+        <v>37.8277</v>
       </c>
       <c r="F5" t="n">
-        <v>35.7021</v>
+        <v>35.7452</v>
       </c>
       <c r="H5" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I5" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>20 jul</t>
+          <t>21 jul</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>138</v>
+        <v>137.74</v>
       </c>
       <c r="M5" t="n">
-        <v>140.04</v>
+        <v>137.84</v>
       </c>
       <c r="N5" t="n">
-        <v>134.98</v>
+        <v>135.34</v>
       </c>
       <c r="O5" t="n">
-        <v>138.26</v>
+        <v>136.42</v>
       </c>
       <c r="P5" t="n">
-        <v>144.528</v>
+        <v>144.4084</v>
       </c>
       <c r="R5" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S5" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>17 jul</t>
+          <t>20 jul</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>394.118</v>
+        <v>390.6746</v>
       </c>
       <c r="W5" t="n">
-        <v>397.6414</v>
+        <v>402.4224</v>
       </c>
       <c r="X5" t="n">
-        <v>388.6583</v>
+        <v>388.9179</v>
       </c>
       <c r="Y5" t="n">
-        <v>393.08</v>
+        <v>401.5341</v>
       </c>
       <c r="Z5" t="n">
-        <v>400.5601</v>
+        <v>400.345</v>
       </c>
       <c r="AB5" t="n">
         <v>535.3375423278808</v>
@@ -3286,84 +3629,84 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>21 jul</t>
+          <t>22 jul</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>37.5703</v>
+        <v>38.095</v>
       </c>
       <c r="C6" t="n">
-        <v>37.8277</v>
+        <v>38.6098</v>
       </c>
       <c r="D6" t="n">
-        <v>37.4169</v>
+        <v>37.9267</v>
       </c>
       <c r="E6" t="n">
-        <v>37.8277</v>
+        <v>38.2682</v>
       </c>
       <c r="F6" t="n">
-        <v>35.7452</v>
+        <v>35.799</v>
       </c>
       <c r="G6" t="n">
-        <v>33.7592</v>
+        <v>33.7968</v>
       </c>
       <c r="H6" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I6" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>21 jul</t>
+          <t>22 jul</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>137.74</v>
+        <v>136.02</v>
       </c>
       <c r="M6" t="n">
-        <v>137.84</v>
+        <v>136.4</v>
       </c>
       <c r="N6" t="n">
-        <v>135.34</v>
+        <v>132.04</v>
       </c>
       <c r="O6" t="n">
-        <v>136.42</v>
+        <v>132.04</v>
       </c>
       <c r="P6" t="n">
-        <v>144.4084</v>
+        <v>144.324</v>
       </c>
       <c r="Q6" t="n">
-        <v>174.8719</v>
+        <v>174.4005</v>
       </c>
       <c r="R6" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S6" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>20 jul</t>
+          <t>21 jul</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>390.6746</v>
+        <v>398.0606</v>
       </c>
       <c r="W6" t="n">
-        <v>402.4224</v>
+        <v>400.7156</v>
       </c>
       <c r="X6" t="n">
-        <v>388.9179</v>
+        <v>395.5753</v>
       </c>
       <c r="Y6" t="n">
-        <v>401.5341</v>
+        <v>397.0026</v>
       </c>
       <c r="Z6" t="n">
-        <v>400.345</v>
+        <v>399.9036</v>
       </c>
       <c r="AA6" t="n">
-        <v>436.4743</v>
+        <v>435.882</v>
       </c>
       <c r="AB6" t="n">
         <v>535.3375423278808</v>
@@ -3375,84 +3718,84 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>22 jul</t>
+          <t>23 jul</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>38.095</v>
+        <v>38.491</v>
       </c>
       <c r="C7" t="n">
-        <v>38.6098</v>
+        <v>39.0454</v>
       </c>
       <c r="D7" t="n">
-        <v>37.9267</v>
+        <v>38.3425</v>
       </c>
       <c r="E7" t="n">
-        <v>38.2682</v>
+        <v>38.8028</v>
       </c>
       <c r="F7" t="n">
-        <v>35.799</v>
+        <v>35.863</v>
       </c>
       <c r="G7" t="n">
-        <v>33.7968</v>
+        <v>33.8375</v>
       </c>
       <c r="H7" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I7" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>22 jul</t>
+          <t>23 jul</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>136.02</v>
+        <v>131</v>
       </c>
       <c r="M7" t="n">
-        <v>136.4</v>
+        <v>132.42</v>
       </c>
       <c r="N7" t="n">
-        <v>132.04</v>
+        <v>127.5</v>
       </c>
       <c r="O7" t="n">
-        <v>132.04</v>
+        <v>128.32</v>
       </c>
       <c r="P7" t="n">
-        <v>144.324</v>
+        <v>144.066</v>
       </c>
       <c r="Q7" t="n">
-        <v>174.4005</v>
+        <v>173.9035</v>
       </c>
       <c r="R7" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S7" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>21 jul</t>
+          <t>22 jul</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>398.0606</v>
+        <v>398.8292</v>
       </c>
       <c r="W7" t="n">
-        <v>400.7156</v>
+        <v>400.2465</v>
       </c>
       <c r="X7" t="n">
-        <v>395.5753</v>
+        <v>386.2329</v>
       </c>
       <c r="Y7" t="n">
-        <v>397.0026</v>
+        <v>389.6066</v>
       </c>
       <c r="Z7" t="n">
-        <v>399.9036</v>
+        <v>399.4268</v>
       </c>
       <c r="AA7" t="n">
-        <v>435.882</v>
+        <v>435.2723</v>
       </c>
       <c r="AB7" t="n">
         <v>535.3375423278808</v>
@@ -3464,84 +3807,84 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>23 jul</t>
+          <t>24 jul</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>38.491</v>
+        <v>38.4019</v>
       </c>
       <c r="C8" t="n">
-        <v>39.0454</v>
+        <v>38.6593</v>
       </c>
       <c r="D8" t="n">
-        <v>38.3425</v>
+        <v>38.1594</v>
       </c>
       <c r="E8" t="n">
-        <v>38.8028</v>
+        <v>38.3871</v>
       </c>
       <c r="F8" t="n">
-        <v>35.863</v>
+        <v>35.9135</v>
       </c>
       <c r="G8" t="n">
-        <v>33.8375</v>
+        <v>33.8757</v>
       </c>
       <c r="H8" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I8" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>23 jul</t>
+          <t>24 jul</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>131</v>
+        <v>130.88</v>
       </c>
       <c r="M8" t="n">
-        <v>132.42</v>
+        <v>141.32</v>
       </c>
       <c r="N8" t="n">
-        <v>127.5</v>
+        <v>130.86</v>
       </c>
       <c r="O8" t="n">
-        <v>128.32</v>
+        <v>140.2</v>
       </c>
       <c r="P8" t="n">
-        <v>144.066</v>
+        <v>143.9888</v>
       </c>
       <c r="Q8" t="n">
-        <v>173.9035</v>
+        <v>173.4491</v>
       </c>
       <c r="R8" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S8" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>22 jul</t>
+          <t>23 jul</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>398.8292</v>
+        <v>389.2373</v>
       </c>
       <c r="W8" t="n">
-        <v>400.2465</v>
+        <v>391.0439</v>
       </c>
       <c r="X8" t="n">
-        <v>386.2329</v>
+        <v>376.6809</v>
       </c>
       <c r="Y8" t="n">
-        <v>389.6066</v>
+        <v>380.863</v>
       </c>
       <c r="Z8" t="n">
-        <v>399.4268</v>
+        <v>398.8242</v>
       </c>
       <c r="AA8" t="n">
-        <v>435.2723</v>
+        <v>434.611</v>
       </c>
       <c r="AB8" t="n">
         <v>535.3375423278808</v>
@@ -3553,84 +3896,84 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>24 jul</t>
+          <t>27 jul</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>38.4019</v>
+        <v>37.5802</v>
       </c>
       <c r="C9" t="n">
-        <v>38.6593</v>
+        <v>38.1099</v>
       </c>
       <c r="D9" t="n">
-        <v>38.1594</v>
+        <v>37.4317</v>
       </c>
       <c r="E9" t="n">
-        <v>38.3871</v>
+        <v>37.9515</v>
       </c>
       <c r="F9" t="n">
-        <v>35.9135</v>
+        <v>35.931</v>
       </c>
       <c r="G9" t="n">
-        <v>33.8757</v>
+        <v>33.9167</v>
       </c>
       <c r="H9" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I9" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>24 jul</t>
+          <t>27 jul</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>130.88</v>
+        <v>142.38</v>
       </c>
       <c r="M9" t="n">
-        <v>141.32</v>
+        <v>151.56</v>
       </c>
       <c r="N9" t="n">
-        <v>130.86</v>
+        <v>142</v>
       </c>
       <c r="O9" t="n">
-        <v>140.2</v>
+        <v>151.28</v>
       </c>
       <c r="P9" t="n">
-        <v>143.9888</v>
+        <v>144.0572</v>
       </c>
       <c r="Q9" t="n">
-        <v>173.4491</v>
+        <v>173.0393</v>
       </c>
       <c r="R9" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S9" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>23 jul</t>
+          <t>24 jul</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>389.2373</v>
+        <v>386.3227</v>
       </c>
       <c r="W9" t="n">
-        <v>391.0439</v>
+        <v>388.299</v>
       </c>
       <c r="X9" t="n">
-        <v>376.6809</v>
+        <v>379.9348</v>
       </c>
       <c r="Y9" t="n">
-        <v>380.863</v>
+        <v>380.9828</v>
       </c>
       <c r="Z9" t="n">
-        <v>398.8242</v>
+        <v>398.3214</v>
       </c>
       <c r="AA9" t="n">
-        <v>434.611</v>
+        <v>433.8946</v>
       </c>
       <c r="AB9" t="n">
         <v>535.3375423278808</v>
@@ -3642,84 +3985,84 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>27 jul</t>
+          <t>28 jul</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>37.5802</v>
+        <v>37.7139</v>
       </c>
       <c r="C10" t="n">
-        <v>38.1099</v>
+        <v>38.0109</v>
       </c>
       <c r="D10" t="n">
-        <v>37.4317</v>
+        <v>37.4713</v>
       </c>
       <c r="E10" t="n">
-        <v>37.9515</v>
+        <v>37.4713</v>
       </c>
       <c r="F10" t="n">
-        <v>35.931</v>
+        <v>35.9372</v>
       </c>
       <c r="G10" t="n">
-        <v>33.9167</v>
+        <v>33.9548</v>
       </c>
       <c r="H10" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I10" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>27 jul</t>
+          <t>28 jul</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>142.38</v>
+        <v>152.2</v>
       </c>
       <c r="M10" t="n">
-        <v>151.56</v>
+        <v>159.76</v>
       </c>
       <c r="N10" t="n">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="O10" t="n">
-        <v>151.28</v>
+        <v>159.24</v>
       </c>
       <c r="P10" t="n">
-        <v>144.0572</v>
+        <v>144.1076</v>
       </c>
       <c r="Q10" t="n">
-        <v>173.0393</v>
+        <v>172.6663</v>
       </c>
       <c r="R10" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S10" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>24 jul</t>
+          <t>27 jul</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>386.3227</v>
+        <v>389.347</v>
       </c>
       <c r="W10" t="n">
-        <v>388.299</v>
+        <v>393.4593</v>
       </c>
       <c r="X10" t="n">
-        <v>379.9348</v>
+        <v>387.261</v>
       </c>
       <c r="Y10" t="n">
-        <v>380.9828</v>
+        <v>388.3689</v>
       </c>
       <c r="Z10" t="n">
-        <v>398.3214</v>
+        <v>398.0172</v>
       </c>
       <c r="AA10" t="n">
-        <v>433.8946</v>
+        <v>433.238</v>
       </c>
       <c r="AB10" t="n">
         <v>535.3375423278808</v>
@@ -3731,84 +4074,84 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>28 jul</t>
+          <t>29 jul</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>37.7139</v>
+        <v>38.0653</v>
       </c>
       <c r="C11" t="n">
-        <v>38.0109</v>
+        <v>38.59</v>
       </c>
       <c r="D11" t="n">
-        <v>37.4713</v>
+        <v>37.7089</v>
       </c>
       <c r="E11" t="n">
-        <v>37.4713</v>
+        <v>38.4415</v>
       </c>
       <c r="F11" t="n">
-        <v>35.9372</v>
+        <v>35.9692</v>
       </c>
       <c r="G11" t="n">
-        <v>33.9548</v>
+        <v>33.9987</v>
       </c>
       <c r="H11" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I11" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>28 jul</t>
+          <t>29 jul</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>152.2</v>
+        <v>159.84</v>
       </c>
       <c r="M11" t="n">
-        <v>159.76</v>
+        <v>163.3</v>
       </c>
       <c r="N11" t="n">
-        <v>151</v>
+        <v>156.48</v>
       </c>
       <c r="O11" t="n">
-        <v>159.24</v>
+        <v>162.04</v>
       </c>
       <c r="P11" t="n">
-        <v>144.1076</v>
+        <v>144.28</v>
       </c>
       <c r="Q11" t="n">
-        <v>172.6663</v>
+        <v>172.343</v>
       </c>
       <c r="R11" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S11" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>27 jul</t>
+          <t>28 jul</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>389.347</v>
+        <v>392.4213</v>
       </c>
       <c r="W11" t="n">
-        <v>393.4593</v>
+        <v>399.5678</v>
       </c>
       <c r="X11" t="n">
-        <v>387.261</v>
+        <v>390.5647</v>
       </c>
       <c r="Y11" t="n">
-        <v>388.3689</v>
+        <v>392.6109</v>
       </c>
       <c r="Z11" t="n">
-        <v>398.0172</v>
+        <v>397.7139</v>
       </c>
       <c r="AA11" t="n">
-        <v>433.238</v>
+        <v>432.5982</v>
       </c>
       <c r="AB11" t="n">
         <v>535.3375423278808</v>
@@ -3820,84 +4163,84 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>29 jul</t>
+          <t>30 jul</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>38.0653</v>
+        <v>38.6098</v>
       </c>
       <c r="C12" t="n">
-        <v>38.59</v>
+        <v>39.1444</v>
       </c>
       <c r="D12" t="n">
-        <v>37.7089</v>
+        <v>38.3277</v>
       </c>
       <c r="E12" t="n">
-        <v>38.4415</v>
+        <v>38.5108</v>
       </c>
       <c r="F12" t="n">
-        <v>35.9692</v>
+        <v>35.9978</v>
       </c>
       <c r="G12" t="n">
-        <v>33.9987</v>
+        <v>34.0424</v>
       </c>
       <c r="H12" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I12" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>29 jul</t>
+          <t>30 jul</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>159.84</v>
+        <v>162.5</v>
       </c>
       <c r="M12" t="n">
-        <v>163.3</v>
+        <v>163.16</v>
       </c>
       <c r="N12" t="n">
-        <v>156.48</v>
+        <v>155.2</v>
       </c>
       <c r="O12" t="n">
-        <v>162.04</v>
+        <v>155.92</v>
       </c>
       <c r="P12" t="n">
-        <v>144.28</v>
+        <v>144.3804</v>
       </c>
       <c r="Q12" t="n">
-        <v>172.343</v>
+        <v>171.9849</v>
       </c>
       <c r="R12" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S12" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>28 jul</t>
+          <t>29 jul</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>392.4213</v>
+        <v>392.6608</v>
       </c>
       <c r="W12" t="n">
-        <v>399.5678</v>
+        <v>400.4961</v>
       </c>
       <c r="X12" t="n">
-        <v>390.5647</v>
+        <v>388.0095</v>
       </c>
       <c r="Y12" t="n">
-        <v>392.6109</v>
+        <v>389.8062</v>
       </c>
       <c r="Z12" t="n">
-        <v>397.7139</v>
+        <v>397.1057</v>
       </c>
       <c r="AA12" t="n">
-        <v>432.5982</v>
+        <v>431.9565</v>
       </c>
       <c r="AB12" t="n">
         <v>535.3375423278808</v>
@@ -3909,84 +4252,84 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>30 jul</t>
+          <t>31 jul</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>38.6098</v>
       </c>
       <c r="C13" t="n">
-        <v>39.1444</v>
+        <v>39.575</v>
       </c>
       <c r="D13" t="n">
-        <v>38.3277</v>
+        <v>38.4464</v>
       </c>
       <c r="E13" t="n">
-        <v>38.5108</v>
+        <v>39.3226</v>
       </c>
       <c r="F13" t="n">
-        <v>35.9978</v>
+        <v>36.0495</v>
       </c>
       <c r="G13" t="n">
-        <v>34.0424</v>
+        <v>34.0907</v>
       </c>
       <c r="H13" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I13" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>30 jul</t>
+          <t>31 jul</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>162.5</v>
+        <v>154.9</v>
       </c>
       <c r="M13" t="n">
-        <v>163.16</v>
+        <v>158.26</v>
       </c>
       <c r="N13" t="n">
-        <v>155.2</v>
+        <v>153.6</v>
       </c>
       <c r="O13" t="n">
-        <v>155.92</v>
+        <v>157.68</v>
       </c>
       <c r="P13" t="n">
-        <v>144.3804</v>
+        <v>144.4984</v>
       </c>
       <c r="Q13" t="n">
-        <v>171.9849</v>
+        <v>171.6292</v>
       </c>
       <c r="R13" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S13" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>29 jul</t>
+          <t>30 jul</t>
         </is>
       </c>
       <c r="V13" t="n">
-        <v>392.6608</v>
+        <v>437.0772</v>
       </c>
       <c r="W13" t="n">
-        <v>400.4961</v>
+        <v>457.8281</v>
       </c>
       <c r="X13" t="n">
-        <v>388.0095</v>
+        <v>431.6275</v>
       </c>
       <c r="Y13" t="n">
-        <v>389.8062</v>
+        <v>450.2524</v>
       </c>
       <c r="Z13" t="n">
-        <v>397.1057</v>
+        <v>397.6741</v>
       </c>
       <c r="AA13" t="n">
-        <v>431.9565</v>
+        <v>431.6738</v>
       </c>
       <c r="AB13" t="n">
         <v>535.3375423278808</v>
@@ -3998,84 +4341,84 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>31 jul</t>
+          <t>3 aug</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>38.6098</v>
+        <v>38.3128</v>
       </c>
       <c r="C14" t="n">
-        <v>39.575</v>
+        <v>39.4067</v>
       </c>
       <c r="D14" t="n">
-        <v>38.4464</v>
+        <v>38.2138</v>
       </c>
       <c r="E14" t="n">
-        <v>39.3226</v>
+        <v>39.4067</v>
       </c>
       <c r="F14" t="n">
-        <v>36.0495</v>
+        <v>36.1112</v>
       </c>
       <c r="G14" t="n">
-        <v>34.0907</v>
+        <v>34.1393</v>
       </c>
       <c r="H14" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I14" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>31 jul</t>
+          <t>3 aug</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>154.9</v>
+        <v>160</v>
       </c>
       <c r="M14" t="n">
-        <v>158.26</v>
+        <v>168.7</v>
       </c>
       <c r="N14" t="n">
-        <v>153.6</v>
+        <v>159.6</v>
       </c>
       <c r="O14" t="n">
-        <v>157.68</v>
+        <v>164.64</v>
       </c>
       <c r="P14" t="n">
-        <v>144.4984</v>
+        <v>144.7016</v>
       </c>
       <c r="Q14" t="n">
-        <v>171.6292</v>
+        <v>171.301</v>
       </c>
       <c r="R14" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S14" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>30 jul</t>
+          <t>31 jul</t>
         </is>
       </c>
       <c r="V14" t="n">
-        <v>437.0772</v>
+        <v>449.1545</v>
       </c>
       <c r="W14" t="n">
-        <v>457.8281</v>
+        <v>465.9628</v>
       </c>
       <c r="X14" t="n">
-        <v>431.6275</v>
+        <v>448.4857</v>
       </c>
       <c r="Y14" t="n">
-        <v>450.2524</v>
+        <v>463.8468</v>
       </c>
       <c r="Z14" t="n">
-        <v>397.6741</v>
+        <v>398.6364</v>
       </c>
       <c r="AA14" t="n">
-        <v>431.6738</v>
+        <v>431.4438</v>
       </c>
       <c r="AB14" t="n">
         <v>535.3375423278808</v>
@@ -4087,84 +4430,84 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3 aug</t>
+          <t>4 aug</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>38.3128</v>
+        <v>39.3028</v>
       </c>
       <c r="C15" t="n">
-        <v>39.4067</v>
+        <v>39.6443</v>
       </c>
       <c r="D15" t="n">
-        <v>38.2138</v>
+        <v>38.2039</v>
       </c>
       <c r="E15" t="n">
-        <v>39.4067</v>
+        <v>38.486</v>
       </c>
       <c r="F15" t="n">
-        <v>36.1112</v>
+        <v>36.1495</v>
       </c>
       <c r="G15" t="n">
-        <v>34.1393</v>
+        <v>34.1818</v>
       </c>
       <c r="H15" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I15" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>3 aug</t>
+          <t>4 aug</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>160</v>
+        <v>162.86</v>
       </c>
       <c r="M15" t="n">
-        <v>168.7</v>
+        <v>168.56</v>
       </c>
       <c r="N15" t="n">
-        <v>159.6</v>
+        <v>162.4</v>
       </c>
       <c r="O15" t="n">
-        <v>164.64</v>
+        <v>167.38</v>
       </c>
       <c r="P15" t="n">
-        <v>144.7016</v>
+        <v>145.02</v>
       </c>
       <c r="Q15" t="n">
-        <v>171.301</v>
+        <v>170.9913</v>
       </c>
       <c r="R15" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S15" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>31 jul</t>
+          <t>3 aug</t>
         </is>
       </c>
       <c r="V15" t="n">
-        <v>449.1545</v>
+        <v>475.2354</v>
       </c>
       <c r="W15" t="n">
-        <v>465.9628</v>
+        <v>490.7262</v>
       </c>
       <c r="X15" t="n">
-        <v>448.4857</v>
+        <v>474.1075</v>
       </c>
       <c r="Y15" t="n">
-        <v>463.8468</v>
+        <v>486.7337</v>
       </c>
       <c r="Z15" t="n">
-        <v>398.6364</v>
+        <v>399.9838</v>
       </c>
       <c r="AA15" t="n">
-        <v>431.4438</v>
+        <v>431.3306</v>
       </c>
       <c r="AB15" t="n">
         <v>535.3375423278808</v>
@@ -4176,84 +4519,84 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4 aug</t>
+          <t>5 aug</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>39.3028</v>
+        <v>38.4811</v>
       </c>
       <c r="C16" t="n">
-        <v>39.6443</v>
+        <v>38.7632</v>
       </c>
       <c r="D16" t="n">
-        <v>38.2039</v>
+        <v>37.9366</v>
       </c>
       <c r="E16" t="n">
-        <v>38.486</v>
+        <v>38.0307</v>
       </c>
       <c r="F16" t="n">
-        <v>36.1495</v>
+        <v>36.1966</v>
       </c>
       <c r="G16" t="n">
-        <v>34.1818</v>
+        <v>34.2215</v>
       </c>
       <c r="H16" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I16" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>4 aug</t>
+          <t>5 aug</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>162.86</v>
+        <v>167.92</v>
       </c>
       <c r="M16" t="n">
-        <v>168.56</v>
+        <v>172.6</v>
       </c>
       <c r="N16" t="n">
-        <v>162.4</v>
+        <v>167.3</v>
       </c>
       <c r="O16" t="n">
-        <v>167.38</v>
+        <v>169.26</v>
       </c>
       <c r="P16" t="n">
-        <v>145.02</v>
+        <v>145.4052</v>
       </c>
       <c r="Q16" t="n">
-        <v>170.9913</v>
+        <v>170.7022</v>
       </c>
       <c r="R16" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S16" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>3 aug</t>
+          <t>4 aug</t>
         </is>
       </c>
       <c r="V16" t="n">
-        <v>475.2354</v>
+        <v>479.9964</v>
       </c>
       <c r="W16" t="n">
-        <v>490.7262</v>
+        <v>498.5016</v>
       </c>
       <c r="X16" t="n">
-        <v>474.1075</v>
+        <v>478.2697</v>
       </c>
       <c r="Y16" t="n">
-        <v>486.7337</v>
+        <v>491.884</v>
       </c>
       <c r="Z16" t="n">
-        <v>399.9838</v>
+        <v>401.4555</v>
       </c>
       <c r="AA16" t="n">
-        <v>431.3306</v>
+        <v>431.2438</v>
       </c>
       <c r="AB16" t="n">
         <v>535.3375423278808</v>
@@ -4265,84 +4608,84 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5 aug</t>
+          <t>6 aug</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>38.4811</v>
+        <v>38.0752</v>
       </c>
       <c r="C17" t="n">
-        <v>38.7632</v>
+        <v>38.4069</v>
       </c>
       <c r="D17" t="n">
-        <v>37.9366</v>
+        <v>37.9168</v>
       </c>
       <c r="E17" t="n">
-        <v>38.0307</v>
+        <v>38.392</v>
       </c>
       <c r="F17" t="n">
-        <v>36.1966</v>
+        <v>36.2474</v>
       </c>
       <c r="G17" t="n">
-        <v>34.2215</v>
+        <v>34.2607</v>
       </c>
       <c r="H17" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I17" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>5 aug</t>
+          <t>6 aug</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>167.92</v>
+        <v>171.44</v>
       </c>
       <c r="M17" t="n">
-        <v>172.6</v>
+        <v>173.1</v>
       </c>
       <c r="N17" t="n">
-        <v>167.3</v>
+        <v>168.08</v>
       </c>
       <c r="O17" t="n">
-        <v>169.26</v>
+        <v>170.98</v>
       </c>
       <c r="P17" t="n">
-        <v>145.4052</v>
+        <v>145.7928</v>
       </c>
       <c r="Q17" t="n">
-        <v>170.7022</v>
+        <v>170.384</v>
       </c>
       <c r="R17" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S17" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>4 aug</t>
+          <t>5 aug</t>
         </is>
       </c>
       <c r="V17" t="n">
-        <v>479.9964</v>
+        <v>495.4273</v>
       </c>
       <c r="W17" t="n">
-        <v>498.5016</v>
+        <v>497.3038</v>
       </c>
       <c r="X17" t="n">
-        <v>478.2697</v>
+        <v>484.7674</v>
       </c>
       <c r="Y17" t="n">
-        <v>491.884</v>
+        <v>486.5441</v>
       </c>
       <c r="Z17" t="n">
-        <v>401.4555</v>
+        <v>402.8307</v>
       </c>
       <c r="AA17" t="n">
-        <v>431.2438</v>
+        <v>431.1393</v>
       </c>
       <c r="AB17" t="n">
         <v>535.3375423278808</v>
@@ -4354,84 +4697,84 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>6 aug</t>
+          <t>7 aug</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>38.0752</v>
+        <v>38.5207</v>
       </c>
       <c r="C18" t="n">
-        <v>38.4069</v>
+        <v>38.5999</v>
       </c>
       <c r="D18" t="n">
-        <v>37.9168</v>
+        <v>37.897</v>
       </c>
       <c r="E18" t="n">
-        <v>38.392</v>
+        <v>38.0059</v>
       </c>
       <c r="F18" t="n">
-        <v>36.2474</v>
+        <v>36.2952</v>
       </c>
       <c r="G18" t="n">
-        <v>34.2607</v>
+        <v>34.294</v>
       </c>
       <c r="H18" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I18" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>6 aug</t>
+          <t>7 aug</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>171.44</v>
+        <v>173.82</v>
       </c>
       <c r="M18" t="n">
-        <v>173.1</v>
+        <v>179.56</v>
       </c>
       <c r="N18" t="n">
-        <v>168.08</v>
+        <v>173.82</v>
       </c>
       <c r="O18" t="n">
-        <v>170.98</v>
+        <v>177.96</v>
       </c>
       <c r="P18" t="n">
-        <v>145.7928</v>
+        <v>146.2468</v>
       </c>
       <c r="Q18" t="n">
-        <v>170.384</v>
+        <v>170.0918</v>
       </c>
       <c r="R18" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S18" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>5 aug</t>
+          <t>6 aug</t>
         </is>
       </c>
       <c r="V18" t="n">
-        <v>495.4273</v>
+        <v>487.632</v>
       </c>
       <c r="W18" t="n">
-        <v>497.3038</v>
+        <v>500.6176</v>
       </c>
       <c r="X18" t="n">
-        <v>484.7674</v>
+        <v>487.6021</v>
       </c>
       <c r="Y18" t="n">
-        <v>486.5441</v>
+        <v>498.9207</v>
       </c>
       <c r="Z18" t="n">
-        <v>402.8307</v>
+        <v>404.5041</v>
       </c>
       <c r="AA18" t="n">
-        <v>431.1393</v>
+        <v>431.087</v>
       </c>
       <c r="AB18" t="n">
         <v>535.3375423278808</v>
@@ -4443,84 +4786,84 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>7 aug</t>
+          <t>10 aug</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>38.5207</v>
+        <v>38.0356</v>
       </c>
       <c r="C19" t="n">
-        <v>38.5999</v>
+        <v>38.4366</v>
       </c>
       <c r="D19" t="n">
-        <v>37.897</v>
+        <v>37.803</v>
       </c>
       <c r="E19" t="n">
-        <v>38.0059</v>
+        <v>38.4019</v>
       </c>
       <c r="F19" t="n">
-        <v>36.2952</v>
+        <v>36.3315</v>
       </c>
       <c r="G19" t="n">
-        <v>34.294</v>
+        <v>34.3294</v>
       </c>
       <c r="H19" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I19" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>7 aug</t>
+          <t>10 aug</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>173.82</v>
+        <v>178.92</v>
       </c>
       <c r="M19" t="n">
-        <v>179.56</v>
+        <v>179.96</v>
       </c>
       <c r="N19" t="n">
-        <v>173.82</v>
+        <v>175.86</v>
       </c>
       <c r="O19" t="n">
-        <v>177.96</v>
+        <v>179.3</v>
       </c>
       <c r="P19" t="n">
-        <v>146.2468</v>
+        <v>146.4748</v>
       </c>
       <c r="Q19" t="n">
-        <v>170.0918</v>
+        <v>169.8238</v>
       </c>
       <c r="R19" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S19" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>6 aug</t>
+          <t>7 aug</t>
         </is>
       </c>
       <c r="V19" t="n">
-        <v>487.632</v>
+        <v>498.272</v>
       </c>
       <c r="W19" t="n">
-        <v>500.6176</v>
+        <v>504.2308</v>
       </c>
       <c r="X19" t="n">
-        <v>487.6021</v>
+        <v>497.7929</v>
       </c>
       <c r="Y19" t="n">
-        <v>498.9207</v>
+        <v>499.0505</v>
       </c>
       <c r="Z19" t="n">
-        <v>404.5041</v>
+        <v>406.2472</v>
       </c>
       <c r="AA19" t="n">
-        <v>431.087</v>
+        <v>431.0194</v>
       </c>
       <c r="AB19" t="n">
         <v>535.3375423278808</v>
@@ -4532,84 +4875,84 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10 aug</t>
+          <t>11 aug</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>38.0356</v>
+        <v>38.7385</v>
       </c>
       <c r="C20" t="n">
-        <v>38.4366</v>
+        <v>39.0058</v>
       </c>
       <c r="D20" t="n">
-        <v>37.803</v>
+        <v>38.6148</v>
       </c>
       <c r="E20" t="n">
-        <v>38.4019</v>
+        <v>38.9662</v>
       </c>
       <c r="F20" t="n">
-        <v>36.3315</v>
+        <v>36.374</v>
       </c>
       <c r="G20" t="n">
-        <v>34.3294</v>
+        <v>34.3685</v>
       </c>
       <c r="H20" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I20" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>10 aug</t>
+          <t>11 aug</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>178.92</v>
+        <v>180</v>
       </c>
       <c r="M20" t="n">
-        <v>179.96</v>
+        <v>183.24</v>
       </c>
       <c r="N20" t="n">
-        <v>175.86</v>
+        <v>178.14</v>
       </c>
       <c r="O20" t="n">
-        <v>179.3</v>
+        <v>180.7</v>
       </c>
       <c r="P20" t="n">
-        <v>146.4748</v>
+        <v>146.8316</v>
       </c>
       <c r="Q20" t="n">
-        <v>169.8238</v>
+        <v>169.5375</v>
       </c>
       <c r="R20" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S20" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>7 aug</t>
+          <t>10 aug</t>
         </is>
       </c>
       <c r="V20" t="n">
-        <v>498.272</v>
+        <v>502.4941</v>
       </c>
       <c r="W20" t="n">
-        <v>504.2308</v>
+        <v>512.7646999999999</v>
       </c>
       <c r="X20" t="n">
-        <v>497.7929</v>
+        <v>501.3262</v>
       </c>
       <c r="Y20" t="n">
-        <v>499.0505</v>
+        <v>505.1091</v>
       </c>
       <c r="Z20" t="n">
-        <v>406.2472</v>
+        <v>407.8257</v>
       </c>
       <c r="AA20" t="n">
-        <v>431.0194</v>
+        <v>430.9778</v>
       </c>
       <c r="AB20" t="n">
         <v>535.3375423278808</v>
@@ -4621,84 +4964,84 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>11 aug</t>
+          <t>12 aug</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>38.7385</v>
+        <v>38.8573</v>
       </c>
       <c r="C21" t="n">
-        <v>39.0058</v>
+        <v>38.986</v>
       </c>
       <c r="D21" t="n">
-        <v>38.6148</v>
+        <v>38.3871</v>
       </c>
       <c r="E21" t="n">
-        <v>38.9662</v>
+        <v>38.6494</v>
       </c>
       <c r="F21" t="n">
-        <v>36.374</v>
+        <v>36.3981</v>
       </c>
       <c r="G21" t="n">
-        <v>34.3685</v>
+        <v>34.4068</v>
       </c>
       <c r="H21" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I21" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>11 aug</t>
+          <t>12 aug</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>180</v>
+        <v>180.3</v>
       </c>
       <c r="M21" t="n">
-        <v>183.24</v>
+        <v>180.98</v>
       </c>
       <c r="N21" t="n">
-        <v>178.14</v>
+        <v>175.4</v>
       </c>
       <c r="O21" t="n">
-        <v>180.7</v>
+        <v>175.96</v>
       </c>
       <c r="P21" t="n">
-        <v>146.8316</v>
+        <v>147.232</v>
       </c>
       <c r="Q21" t="n">
-        <v>169.5375</v>
+        <v>169.2701</v>
       </c>
       <c r="R21" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S21" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>10 aug</t>
+          <t>11 aug</t>
         </is>
       </c>
       <c r="V21" t="n">
-        <v>502.4941</v>
+        <v>503.3824</v>
       </c>
       <c r="W21" t="n">
-        <v>512.7646999999999</v>
+        <v>504.3805</v>
       </c>
       <c r="X21" t="n">
-        <v>501.3262</v>
+        <v>498.6113</v>
       </c>
       <c r="Y21" t="n">
-        <v>505.1091</v>
+        <v>502.8633</v>
       </c>
       <c r="Z21" t="n">
-        <v>407.8257</v>
+        <v>408.895</v>
       </c>
       <c r="AA21" t="n">
-        <v>430.9778</v>
+        <v>430.9106</v>
       </c>
       <c r="AB21" t="n">
         <v>535.3375423278808</v>
@@ -4710,84 +5053,84 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>12 aug</t>
+          <t>13 aug</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>38.8573</v>
+        <v>39</v>
       </c>
       <c r="C22" t="n">
-        <v>38.986</v>
+        <v>39.005</v>
       </c>
       <c r="D22" t="n">
-        <v>38.3871</v>
+        <v>38.2</v>
       </c>
       <c r="E22" t="n">
-        <v>38.6494</v>
+        <v>38.605</v>
       </c>
       <c r="F22" t="n">
-        <v>36.3981</v>
+        <v>36.4313</v>
       </c>
       <c r="G22" t="n">
-        <v>34.4068</v>
+        <v>34.4429</v>
       </c>
       <c r="H22" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I22" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>12 aug</t>
+          <t>13 aug</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>180.3</v>
+        <v>177.48</v>
       </c>
       <c r="M22" t="n">
-        <v>180.98</v>
+        <v>178.3</v>
       </c>
       <c r="N22" t="n">
-        <v>175.4</v>
+        <v>174.8</v>
       </c>
       <c r="O22" t="n">
-        <v>175.96</v>
+        <v>175.38</v>
       </c>
       <c r="P22" t="n">
-        <v>147.232</v>
+        <v>147.4496</v>
       </c>
       <c r="Q22" t="n">
-        <v>169.2701</v>
+        <v>168.9889</v>
       </c>
       <c r="R22" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S22" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>11 aug</t>
+          <t>12 aug</t>
         </is>
       </c>
       <c r="V22" t="n">
-        <v>503.3824</v>
+        <v>499.0505</v>
       </c>
       <c r="W22" t="n">
-        <v>504.3805</v>
+        <v>500.5577</v>
       </c>
       <c r="X22" t="n">
-        <v>498.6113</v>
+        <v>490.5964</v>
       </c>
       <c r="Y22" t="n">
-        <v>502.8633</v>
+        <v>491.5047</v>
       </c>
       <c r="Z22" t="n">
-        <v>408.895</v>
+        <v>409.532</v>
       </c>
       <c r="AA22" t="n">
-        <v>430.9106</v>
+        <v>430.7866</v>
       </c>
       <c r="AB22" t="n">
         <v>535.3375423278808</v>
@@ -4799,84 +5142,84 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>13 aug</t>
+          <t>14 aug</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>39</v>
+        <v>38.65</v>
       </c>
       <c r="C23" t="n">
-        <v>39.005</v>
+        <v>39.1</v>
       </c>
       <c r="D23" t="n">
-        <v>38.2</v>
+        <v>38.56</v>
       </c>
       <c r="E23" t="n">
-        <v>38.605</v>
+        <v>38.97</v>
       </c>
       <c r="F23" t="n">
-        <v>36.4313</v>
+        <v>36.4703</v>
       </c>
       <c r="G23" t="n">
-        <v>34.4429</v>
+        <v>34.4805</v>
       </c>
       <c r="H23" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I23" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>13 aug</t>
+          <t>14 aug</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>177.48</v>
+        <v>182</v>
       </c>
       <c r="M23" t="n">
-        <v>178.3</v>
+        <v>185.74</v>
       </c>
       <c r="N23" t="n">
-        <v>174.8</v>
+        <v>179.28</v>
       </c>
       <c r="O23" t="n">
-        <v>175.38</v>
+        <v>180.14</v>
       </c>
       <c r="P23" t="n">
-        <v>147.4496</v>
+        <v>147.8228</v>
       </c>
       <c r="Q23" t="n">
-        <v>168.9889</v>
+        <v>168.7386</v>
       </c>
       <c r="R23" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S23" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>12 aug</t>
+          <t>13 aug</t>
         </is>
       </c>
       <c r="V23" t="n">
-        <v>499.0505</v>
+        <v>492.3431</v>
       </c>
       <c r="W23" t="n">
-        <v>500.5577</v>
+        <v>500.398</v>
       </c>
       <c r="X23" t="n">
-        <v>490.5964</v>
+        <v>492.0837</v>
       </c>
       <c r="Y23" t="n">
-        <v>491.5047</v>
+        <v>495.9464</v>
       </c>
       <c r="Z23" t="n">
-        <v>409.532</v>
+        <v>410.6414</v>
       </c>
       <c r="AA23" t="n">
-        <v>430.7866</v>
+        <v>430.6696</v>
       </c>
       <c r="AB23" t="n">
         <v>535.3375423278808</v>
@@ -4888,84 +5231,84 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>14 aug</t>
+          <t>17 aug</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>38.65</v>
+        <v>38.97</v>
       </c>
       <c r="C24" t="n">
-        <v>39.1</v>
+        <v>39.27</v>
       </c>
       <c r="D24" t="n">
-        <v>38.56</v>
+        <v>38.765</v>
       </c>
       <c r="E24" t="n">
-        <v>38.97</v>
+        <v>39.15</v>
       </c>
       <c r="F24" t="n">
-        <v>36.4703</v>
+        <v>36.5118</v>
       </c>
       <c r="G24" t="n">
-        <v>34.4805</v>
+        <v>34.5207</v>
       </c>
       <c r="H24" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I24" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>14 aug</t>
+          <t>17 aug</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>182</v>
+        <v>178.94</v>
       </c>
       <c r="M24" t="n">
-        <v>185.74</v>
+        <v>180.9</v>
       </c>
       <c r="N24" t="n">
-        <v>179.28</v>
+        <v>177.66</v>
       </c>
       <c r="O24" t="n">
-        <v>180.14</v>
+        <v>179.58</v>
       </c>
       <c r="P24" t="n">
-        <v>147.8228</v>
+        <v>148.2524</v>
       </c>
       <c r="Q24" t="n">
-        <v>168.7386</v>
+        <v>168.5337</v>
       </c>
       <c r="R24" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S24" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>13 aug</t>
+          <t>14 aug</t>
         </is>
       </c>
       <c r="V24" t="n">
-        <v>492.3431</v>
+        <v>495.4273</v>
       </c>
       <c r="W24" t="n">
-        <v>500.398</v>
+        <v>499.0705</v>
       </c>
       <c r="X24" t="n">
-        <v>492.0837</v>
+        <v>492.9919</v>
       </c>
       <c r="Y24" t="n">
-        <v>495.9464</v>
+        <v>494.4691</v>
       </c>
       <c r="Z24" t="n">
-        <v>410.6414</v>
+        <v>412</v>
       </c>
       <c r="AA24" t="n">
-        <v>430.6696</v>
+        <v>430.5061</v>
       </c>
       <c r="AB24" t="n">
         <v>535.3375423278808</v>
@@ -4977,84 +5320,84 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>17 aug</t>
+          <t>18 aug</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>38.97</v>
+        <v>39.49</v>
       </c>
       <c r="C25" t="n">
-        <v>39.27</v>
+        <v>39.945</v>
       </c>
       <c r="D25" t="n">
-        <v>38.765</v>
+        <v>39.46</v>
       </c>
       <c r="E25" t="n">
-        <v>39.15</v>
+        <v>39.785</v>
       </c>
       <c r="F25" t="n">
-        <v>36.5118</v>
+        <v>36.5781</v>
       </c>
       <c r="G25" t="n">
-        <v>34.5207</v>
+        <v>34.5641</v>
       </c>
       <c r="H25" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I25" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>17 aug</t>
+          <t>18 aug</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>178.94</v>
+        <v>179.14</v>
       </c>
       <c r="M25" t="n">
-        <v>180.9</v>
+        <v>183.9</v>
       </c>
       <c r="N25" t="n">
-        <v>177.66</v>
+        <v>177.98</v>
       </c>
       <c r="O25" t="n">
-        <v>179.58</v>
+        <v>182.5</v>
       </c>
       <c r="P25" t="n">
-        <v>148.2524</v>
+        <v>148.8084</v>
       </c>
       <c r="Q25" t="n">
-        <v>168.5337</v>
+        <v>168.3358</v>
       </c>
       <c r="R25" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S25" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>14 aug</t>
+          <t>17 aug</t>
         </is>
       </c>
       <c r="V25" t="n">
-        <v>495.4273</v>
+        <v>489.2191</v>
       </c>
       <c r="W25" t="n">
-        <v>499.0705</v>
+        <v>491.7343</v>
       </c>
       <c r="X25" t="n">
-        <v>492.9919</v>
+        <v>477.5111</v>
       </c>
       <c r="Y25" t="n">
-        <v>494.4691</v>
+        <v>479.4474</v>
       </c>
       <c r="Z25" t="n">
-        <v>412</v>
+        <v>413.044</v>
       </c>
       <c r="AA25" t="n">
-        <v>430.5061</v>
+        <v>430.2151</v>
       </c>
       <c r="AB25" t="n">
         <v>535.3375423278808</v>
@@ -5066,84 +5409,84 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>18 aug</t>
+          <t>19 aug</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>39.49</v>
+        <v>39.835</v>
       </c>
       <c r="C26" t="n">
-        <v>39.945</v>
+        <v>40.14</v>
       </c>
       <c r="D26" t="n">
-        <v>39.46</v>
+        <v>39.74</v>
       </c>
       <c r="E26" t="n">
-        <v>39.785</v>
+        <v>39.94</v>
       </c>
       <c r="F26" t="n">
-        <v>36.5781</v>
+        <v>36.6336</v>
       </c>
       <c r="G26" t="n">
-        <v>34.5641</v>
+        <v>34.6092</v>
       </c>
       <c r="H26" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I26" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>18 aug</t>
+          <t>19 aug</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>179.14</v>
+        <v>181.7</v>
       </c>
       <c r="M26" t="n">
-        <v>183.9</v>
+        <v>186.98</v>
       </c>
       <c r="N26" t="n">
-        <v>177.98</v>
+        <v>180.38</v>
       </c>
       <c r="O26" t="n">
-        <v>182.5</v>
+        <v>185.9</v>
       </c>
       <c r="P26" t="n">
-        <v>148.8084</v>
+        <v>149.5324</v>
       </c>
       <c r="Q26" t="n">
-        <v>168.3358</v>
+        <v>168.1618</v>
       </c>
       <c r="R26" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S26" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>17 aug</t>
+          <t>18 aug</t>
         </is>
       </c>
       <c r="V26" t="n">
-        <v>489.2191</v>
+        <v>480.6352</v>
       </c>
       <c r="W26" t="n">
-        <v>491.7343</v>
+        <v>483.3601</v>
       </c>
       <c r="X26" t="n">
-        <v>477.5111</v>
+        <v>476.2534</v>
       </c>
       <c r="Y26" t="n">
-        <v>479.4474</v>
+        <v>480.725</v>
       </c>
       <c r="Z26" t="n">
-        <v>413.044</v>
+        <v>414.3408</v>
       </c>
       <c r="AA26" t="n">
-        <v>430.2151</v>
+        <v>429.933</v>
       </c>
       <c r="AB26" t="n">
         <v>535.3375423278808</v>
@@ -5155,84 +5498,84 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>19 aug</t>
+          <t>20 aug</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>39.835</v>
+        <v>39.865</v>
       </c>
       <c r="C27" t="n">
-        <v>40.14</v>
+        <v>40.51</v>
       </c>
       <c r="D27" t="n">
-        <v>39.74</v>
+        <v>39.8</v>
       </c>
       <c r="E27" t="n">
-        <v>39.94</v>
+        <v>40.28</v>
       </c>
       <c r="F27" t="n">
-        <v>36.6336</v>
+        <v>36.6884</v>
       </c>
       <c r="G27" t="n">
-        <v>34.6092</v>
+        <v>34.6545</v>
       </c>
       <c r="H27" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I27" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>19 aug</t>
+          <t>20 aug</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>181.7</v>
+        <v>183.78</v>
       </c>
       <c r="M27" t="n">
-        <v>186.98</v>
+        <v>186.1</v>
       </c>
       <c r="N27" t="n">
-        <v>180.38</v>
+        <v>182.52</v>
       </c>
       <c r="O27" t="n">
-        <v>185.9</v>
+        <v>185.64</v>
       </c>
       <c r="P27" t="n">
-        <v>149.5324</v>
+        <v>150.4472</v>
       </c>
       <c r="Q27" t="n">
-        <v>168.1618</v>
+        <v>167.9648</v>
       </c>
       <c r="R27" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S27" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>18 aug</t>
+          <t>19 aug</t>
         </is>
       </c>
       <c r="V27" t="n">
-        <v>480.6352</v>
+        <v>479.168</v>
       </c>
       <c r="W27" t="n">
-        <v>483.3601</v>
+        <v>488.3806</v>
       </c>
       <c r="X27" t="n">
-        <v>476.2534</v>
+        <v>478.4593</v>
       </c>
       <c r="Y27" t="n">
-        <v>480.725</v>
+        <v>483.4</v>
       </c>
       <c r="Z27" t="n">
-        <v>414.3408</v>
+        <v>415.7895</v>
       </c>
       <c r="AA27" t="n">
-        <v>429.933</v>
+        <v>429.7427</v>
       </c>
       <c r="AB27" t="n">
         <v>535.3375423278808</v>
@@ -5244,84 +5587,84 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20 aug</t>
+          <t>21 aug</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>39.865</v>
+        <v>40.1</v>
       </c>
       <c r="C28" t="n">
-        <v>40.51</v>
+        <v>40.37</v>
       </c>
       <c r="D28" t="n">
-        <v>39.8</v>
+        <v>39.84</v>
       </c>
       <c r="E28" t="n">
-        <v>40.28</v>
+        <v>39.91</v>
       </c>
       <c r="F28" t="n">
-        <v>36.6884</v>
+        <v>36.7478</v>
       </c>
       <c r="G28" t="n">
-        <v>34.6545</v>
+        <v>34.6988</v>
       </c>
       <c r="H28" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I28" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>20 aug</t>
+          <t>21 aug</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>183.78</v>
+        <v>185.18</v>
       </c>
       <c r="M28" t="n">
-        <v>186.1</v>
+        <v>188.4</v>
       </c>
       <c r="N28" t="n">
-        <v>182.52</v>
+        <v>183.6</v>
       </c>
       <c r="O28" t="n">
-        <v>185.64</v>
+        <v>188.12</v>
       </c>
       <c r="P28" t="n">
-        <v>150.4472</v>
+        <v>151.4044</v>
       </c>
       <c r="Q28" t="n">
-        <v>167.9648</v>
+        <v>167.794</v>
       </c>
       <c r="R28" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S28" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>19 aug</t>
+          <t>20 aug</t>
         </is>
       </c>
       <c r="V28" t="n">
-        <v>479.168</v>
+        <v>483.3</v>
       </c>
       <c r="W28" t="n">
-        <v>488.3806</v>
+        <v>484.16</v>
       </c>
       <c r="X28" t="n">
-        <v>478.4593</v>
+        <v>479.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>483.4</v>
+        <v>481.15</v>
       </c>
       <c r="Z28" t="n">
-        <v>415.7895</v>
+        <v>417.3594</v>
       </c>
       <c r="AA28" t="n">
-        <v>429.7427</v>
+        <v>429.5805</v>
       </c>
       <c r="AB28" t="n">
         <v>535.3375423278808</v>
@@ -5333,84 +5676,84 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>21 aug</t>
+          <t>24 aug</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>40.1</v>
+        <v>39.88</v>
       </c>
       <c r="C29" t="n">
-        <v>40.37</v>
+        <v>40.085</v>
       </c>
       <c r="D29" t="n">
-        <v>39.84</v>
+        <v>39.68</v>
       </c>
       <c r="E29" t="n">
-        <v>39.91</v>
+        <v>39.775</v>
       </c>
       <c r="F29" t="n">
-        <v>36.7478</v>
+        <v>36.8369</v>
       </c>
       <c r="G29" t="n">
-        <v>34.6988</v>
+        <v>34.7421</v>
       </c>
       <c r="H29" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I29" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>21 aug</t>
+          <t>24 aug</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>185.18</v>
+        <v>186.86</v>
       </c>
       <c r="M29" t="n">
-        <v>188.4</v>
+        <v>188.16</v>
       </c>
       <c r="N29" t="n">
-        <v>183.6</v>
+        <v>185.52</v>
       </c>
       <c r="O29" t="n">
-        <v>188.12</v>
+        <v>187.2</v>
       </c>
       <c r="P29" t="n">
-        <v>151.4044</v>
+        <v>152.2848</v>
       </c>
       <c r="Q29" t="n">
-        <v>167.794</v>
+        <v>167.6093</v>
       </c>
       <c r="R29" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S29" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>20 aug</t>
+          <t>21 aug</t>
         </is>
       </c>
       <c r="V29" t="n">
-        <v>483.3</v>
+        <v>479.88</v>
       </c>
       <c r="W29" t="n">
-        <v>484.16</v>
+        <v>486.36</v>
       </c>
       <c r="X29" t="n">
-        <v>479.5</v>
+        <v>478.53</v>
       </c>
       <c r="Y29" t="n">
-        <v>481.15</v>
+        <v>483.24</v>
       </c>
       <c r="Z29" t="n">
-        <v>417.3594</v>
+        <v>419.092</v>
       </c>
       <c r="AA29" t="n">
-        <v>429.5805</v>
+        <v>429.4327</v>
       </c>
       <c r="AB29" t="n">
         <v>535.3375423278808</v>
@@ -5422,84 +5765,84 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>24 aug</t>
+          <t>25 aug</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>39.88</v>
+        <v>39.77</v>
       </c>
       <c r="C30" t="n">
-        <v>40.085</v>
+        <v>39.915</v>
       </c>
       <c r="D30" t="n">
-        <v>39.68</v>
+        <v>39.385</v>
       </c>
       <c r="E30" t="n">
-        <v>39.775</v>
+        <v>39.6</v>
       </c>
       <c r="F30" t="n">
-        <v>36.8369</v>
+        <v>36.926</v>
       </c>
       <c r="G30" t="n">
-        <v>34.7421</v>
+        <v>34.783</v>
       </c>
       <c r="H30" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I30" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>24 aug</t>
+          <t>25 aug</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>186.86</v>
+        <v>186.4</v>
       </c>
       <c r="M30" t="n">
-        <v>188.16</v>
+        <v>187.62</v>
       </c>
       <c r="N30" t="n">
-        <v>185.52</v>
+        <v>182.74</v>
       </c>
       <c r="O30" t="n">
-        <v>187.2</v>
+        <v>185.46</v>
       </c>
       <c r="P30" t="n">
-        <v>152.2848</v>
+        <v>153.136</v>
       </c>
       <c r="Q30" t="n">
-        <v>167.6093</v>
+        <v>167.4651</v>
       </c>
       <c r="R30" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S30" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>21 aug</t>
+          <t>24 aug</t>
         </is>
       </c>
       <c r="V30" t="n">
-        <v>479.88</v>
+        <v>483.21</v>
       </c>
       <c r="W30" t="n">
-        <v>486.36</v>
+        <v>490.61</v>
       </c>
       <c r="X30" t="n">
-        <v>478.53</v>
+        <v>481.86</v>
       </c>
       <c r="Y30" t="n">
-        <v>483.24</v>
+        <v>487.31</v>
       </c>
       <c r="Z30" t="n">
-        <v>419.092</v>
+        <v>421.046</v>
       </c>
       <c r="AA30" t="n">
-        <v>429.4327</v>
+        <v>429.3186</v>
       </c>
       <c r="AB30" t="n">
         <v>535.3375423278808</v>
@@ -5511,84 +5854,84 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>25 aug</t>
+          <t>26 aug</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>39.77</v>
+        <v>39.275</v>
       </c>
       <c r="C31" t="n">
-        <v>39.915</v>
+        <v>39.47</v>
       </c>
       <c r="D31" t="n">
-        <v>39.385</v>
+        <v>38.91</v>
       </c>
       <c r="E31" t="n">
-        <v>39.6</v>
+        <v>39.42</v>
       </c>
       <c r="F31" t="n">
-        <v>36.926</v>
+        <v>37.0192</v>
       </c>
       <c r="G31" t="n">
-        <v>34.783</v>
+        <v>34.8202</v>
       </c>
       <c r="H31" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I31" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>25 aug</t>
+          <t>26 aug</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>186.4</v>
+        <v>179.92</v>
       </c>
       <c r="M31" t="n">
-        <v>187.62</v>
+        <v>182.16</v>
       </c>
       <c r="N31" t="n">
-        <v>182.74</v>
+        <v>176.82</v>
       </c>
       <c r="O31" t="n">
-        <v>185.46</v>
+        <v>180.02</v>
       </c>
       <c r="P31" t="n">
-        <v>153.136</v>
+        <v>153.9128</v>
       </c>
       <c r="Q31" t="n">
-        <v>167.4651</v>
+        <v>167.3049</v>
       </c>
       <c r="R31" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S31" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>24 aug</t>
+          <t>25 aug</t>
         </is>
       </c>
       <c r="V31" t="n">
-        <v>483.21</v>
+        <v>485.44</v>
       </c>
       <c r="W31" t="n">
-        <v>490.61</v>
+        <v>492.44</v>
       </c>
       <c r="X31" t="n">
-        <v>481.86</v>
+        <v>484.3</v>
       </c>
       <c r="Y31" t="n">
-        <v>487.31</v>
+        <v>491.71</v>
       </c>
       <c r="Z31" t="n">
-        <v>421.046</v>
+        <v>423.0801</v>
       </c>
       <c r="AA31" t="n">
-        <v>429.3185</v>
+        <v>429.262</v>
       </c>
       <c r="AB31" t="n">
         <v>535.3375423278808</v>
@@ -5600,84 +5943,84 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>26 aug</t>
+          <t>27 aug</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>39.275</v>
+        <v>39.16</v>
       </c>
       <c r="C32" t="n">
-        <v>39.47</v>
+        <v>39.295</v>
       </c>
       <c r="D32" t="n">
-        <v>38.91</v>
+        <v>38.65</v>
       </c>
       <c r="E32" t="n">
-        <v>39.42</v>
+        <v>38.76</v>
       </c>
       <c r="F32" t="n">
-        <v>37.0192</v>
+        <v>37.117</v>
       </c>
       <c r="G32" t="n">
-        <v>34.8202</v>
+        <v>34.8559</v>
       </c>
       <c r="H32" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I32" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>26 aug</t>
+          <t>27 aug</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>179.92</v>
+        <v>182.5</v>
       </c>
       <c r="M32" t="n">
-        <v>182.16</v>
+        <v>190.8</v>
       </c>
       <c r="N32" t="n">
-        <v>176.82</v>
+        <v>181.14</v>
       </c>
       <c r="O32" t="n">
-        <v>180.02</v>
+        <v>189.88</v>
       </c>
       <c r="P32" t="n">
-        <v>153.9128</v>
+        <v>155.0132</v>
       </c>
       <c r="Q32" t="n">
-        <v>167.3049</v>
+        <v>167.1911</v>
       </c>
       <c r="R32" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S32" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>25 aug</t>
+          <t>26 aug</t>
         </is>
       </c>
       <c r="V32" t="n">
-        <v>485.44</v>
+        <v>487.85</v>
       </c>
       <c r="W32" t="n">
-        <v>492.44</v>
+        <v>497.4</v>
       </c>
       <c r="X32" t="n">
-        <v>484.3</v>
+        <v>487.31</v>
       </c>
       <c r="Y32" t="n">
-        <v>491.71</v>
+        <v>496.37</v>
       </c>
       <c r="Z32" t="n">
-        <v>423.0801</v>
+        <v>425.0273</v>
       </c>
       <c r="AA32" t="n">
-        <v>429.262</v>
+        <v>429.2786</v>
       </c>
       <c r="AB32" t="n">
         <v>535.3375423278808</v>
@@ -5689,84 +6032,84 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>27 aug</t>
+          <t>28 aug</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>39.16</v>
+        <v>39</v>
       </c>
       <c r="C33" t="n">
-        <v>39.295</v>
+        <v>39.18</v>
       </c>
       <c r="D33" t="n">
-        <v>38.65</v>
+        <v>38.845</v>
       </c>
       <c r="E33" t="n">
-        <v>38.76</v>
+        <v>39.145</v>
       </c>
       <c r="F33" t="n">
-        <v>37.117</v>
+        <v>37.2162</v>
       </c>
       <c r="G33" t="n">
-        <v>34.8559</v>
+        <v>34.8941</v>
       </c>
       <c r="H33" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I33" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>27 aug</t>
+          <t>28 aug</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>182.5</v>
+        <v>189.5</v>
       </c>
       <c r="M33" t="n">
-        <v>190.8</v>
+        <v>191.94</v>
       </c>
       <c r="N33" t="n">
-        <v>181.14</v>
+        <v>187.98</v>
       </c>
       <c r="O33" t="n">
-        <v>189.88</v>
+        <v>191.32</v>
       </c>
       <c r="P33" t="n">
-        <v>155.0132</v>
+        <v>156.1568</v>
       </c>
       <c r="Q33" t="n">
-        <v>167.1911</v>
+        <v>167.0806</v>
       </c>
       <c r="R33" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S33" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>26 aug</t>
+          <t>27 aug</t>
         </is>
       </c>
       <c r="V33" t="n">
-        <v>487.85</v>
+        <v>494.88</v>
       </c>
       <c r="W33" t="n">
-        <v>497.4</v>
+        <v>506.48</v>
       </c>
       <c r="X33" t="n">
-        <v>487.31</v>
+        <v>490.08</v>
       </c>
       <c r="Y33" t="n">
-        <v>496.37</v>
+        <v>505.06</v>
       </c>
       <c r="Z33" t="n">
-        <v>425.0273</v>
+        <v>427.2667</v>
       </c>
       <c r="AA33" t="n">
-        <v>429.2786</v>
+        <v>429.3401</v>
       </c>
       <c r="AB33" t="n">
         <v>535.3375423278808</v>
@@ -5778,84 +6121,84 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>28 aug</t>
+          <t>31 aug</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>39</v>
+        <v>39.54</v>
       </c>
       <c r="C34" t="n">
-        <v>39.18</v>
+        <v>39.91</v>
       </c>
       <c r="D34" t="n">
-        <v>38.845</v>
+        <v>39.24</v>
       </c>
       <c r="E34" t="n">
-        <v>39.145</v>
+        <v>39.335</v>
       </c>
       <c r="F34" t="n">
-        <v>37.2162</v>
+        <v>37.3111</v>
       </c>
       <c r="G34" t="n">
-        <v>34.8941</v>
+        <v>34.9333</v>
       </c>
       <c r="H34" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I34" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>28 aug</t>
+          <t>31 aug</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>189.5</v>
+        <v>188.46</v>
       </c>
       <c r="M34" t="n">
-        <v>191.94</v>
+        <v>192.12</v>
       </c>
       <c r="N34" t="n">
-        <v>187.98</v>
+        <v>188.2</v>
       </c>
       <c r="O34" t="n">
-        <v>191.32</v>
+        <v>190.9</v>
       </c>
       <c r="P34" t="n">
-        <v>156.1568</v>
+        <v>157.3304</v>
       </c>
       <c r="Q34" t="n">
-        <v>167.0806</v>
+        <v>166.9613</v>
       </c>
       <c r="R34" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S34" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>27 aug</t>
+          <t>28 aug</t>
         </is>
       </c>
       <c r="V34" t="n">
-        <v>494.88</v>
+        <v>505.33</v>
       </c>
       <c r="W34" t="n">
-        <v>506.48</v>
+        <v>517.78</v>
       </c>
       <c r="X34" t="n">
-        <v>490.08</v>
+        <v>504.87</v>
       </c>
       <c r="Y34" t="n">
-        <v>505.06</v>
+        <v>513.53</v>
       </c>
       <c r="Z34" t="n">
-        <v>427.2667</v>
+        <v>429.9734</v>
       </c>
       <c r="AA34" t="n">
-        <v>429.3401</v>
+        <v>429.3984</v>
       </c>
       <c r="AB34" t="n">
         <v>535.3375423278808</v>
@@ -5867,84 +6210,84 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>31 aug</t>
+          <t>1 sep</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>39.54</v>
+        <v>39.77</v>
       </c>
       <c r="C35" t="n">
-        <v>39.91</v>
+        <v>40.19</v>
       </c>
       <c r="D35" t="n">
-        <v>39.24</v>
+        <v>39.645</v>
       </c>
       <c r="E35" t="n">
-        <v>39.335</v>
+        <v>40.155</v>
       </c>
       <c r="F35" t="n">
-        <v>37.3111</v>
+        <v>37.4239</v>
       </c>
       <c r="G35" t="n">
-        <v>34.9333</v>
+        <v>34.9763</v>
       </c>
       <c r="H35" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I35" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>31 aug</t>
+          <t>1 sep</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>188.46</v>
+        <v>186</v>
       </c>
       <c r="M35" t="n">
-        <v>192.12</v>
+        <v>187.86</v>
       </c>
       <c r="N35" t="n">
-        <v>188.2</v>
+        <v>183.32</v>
       </c>
       <c r="O35" t="n">
-        <v>190.9</v>
+        <v>184.26</v>
       </c>
       <c r="P35" t="n">
-        <v>157.3304</v>
+        <v>158.3252</v>
       </c>
       <c r="Q35" t="n">
-        <v>166.9613</v>
+        <v>166.8103</v>
       </c>
       <c r="R35" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S35" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>28 aug</t>
+          <t>31 aug</t>
         </is>
       </c>
       <c r="V35" t="n">
-        <v>505.33</v>
+        <v>510.38</v>
       </c>
       <c r="W35" t="n">
-        <v>517.78</v>
+        <v>512.1900000000001</v>
       </c>
       <c r="X35" t="n">
-        <v>504.87</v>
+        <v>506.39</v>
       </c>
       <c r="Y35" t="n">
-        <v>513.53</v>
+        <v>507.29</v>
       </c>
       <c r="Z35" t="n">
-        <v>429.9734</v>
+        <v>432.5454</v>
       </c>
       <c r="AA35" t="n">
-        <v>429.3984</v>
+        <v>429.4122</v>
       </c>
       <c r="AB35" t="n">
         <v>535.3375423278808</v>
@@ -5956,84 +6299,84 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1 sep</t>
+          <t>2 sep</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>39.77</v>
+        <v>40.35</v>
       </c>
       <c r="C36" t="n">
-        <v>40.19</v>
+        <v>40.615</v>
       </c>
       <c r="D36" t="n">
-        <v>39.645</v>
+        <v>39.975</v>
       </c>
       <c r="E36" t="n">
-        <v>40.155</v>
+        <v>40.21</v>
       </c>
       <c r="F36" t="n">
-        <v>37.4239</v>
+        <v>37.5499</v>
       </c>
       <c r="G36" t="n">
-        <v>34.9763</v>
+        <v>35.0217</v>
       </c>
       <c r="H36" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I36" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>1 sep</t>
+          <t>2 sep</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>186</v>
+        <v>182.18</v>
       </c>
       <c r="M36" t="n">
-        <v>187.86</v>
+        <v>184.7</v>
       </c>
       <c r="N36" t="n">
-        <v>183.32</v>
+        <v>180.72</v>
       </c>
       <c r="O36" t="n">
-        <v>184.26</v>
+        <v>181.44</v>
       </c>
       <c r="P36" t="n">
-        <v>158.3252</v>
+        <v>159.2568</v>
       </c>
       <c r="Q36" t="n">
-        <v>166.8103</v>
+        <v>166.6796</v>
       </c>
       <c r="R36" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S36" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>31 aug</t>
+          <t>1 sep</t>
         </is>
       </c>
       <c r="V36" t="n">
-        <v>510.38</v>
+        <v>497.52</v>
       </c>
       <c r="W36" t="n">
-        <v>512.1900000000001</v>
+        <v>505.97</v>
       </c>
       <c r="X36" t="n">
-        <v>506.39</v>
+        <v>496.78</v>
       </c>
       <c r="Y36" t="n">
-        <v>507.29</v>
+        <v>501.02</v>
       </c>
       <c r="Z36" t="n">
-        <v>432.5454</v>
+        <v>435.2328</v>
       </c>
       <c r="AA36" t="n">
-        <v>429.4122</v>
+        <v>429.3825</v>
       </c>
       <c r="AB36" t="n">
         <v>535.3375423278808</v>
@@ -6045,84 +6388,84 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2 sep</t>
+          <t>3 sep</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>40.35</v>
+        <v>40.095</v>
       </c>
       <c r="C37" t="n">
-        <v>40.615</v>
+        <v>40.215</v>
       </c>
       <c r="D37" t="n">
-        <v>39.975</v>
+        <v>39.54</v>
       </c>
       <c r="E37" t="n">
-        <v>40.21</v>
+        <v>40.04</v>
       </c>
       <c r="F37" t="n">
-        <v>37.5499</v>
+        <v>37.6767</v>
       </c>
       <c r="G37" t="n">
-        <v>35.0217</v>
+        <v>35.0679</v>
       </c>
       <c r="H37" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I37" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2 sep</t>
+          <t>3 sep</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>182.18</v>
+        <v>182.08</v>
       </c>
       <c r="M37" t="n">
-        <v>184.7</v>
+        <v>187.56</v>
       </c>
       <c r="N37" t="n">
-        <v>180.72</v>
+        <v>182</v>
       </c>
       <c r="O37" t="n">
-        <v>181.44</v>
+        <v>185.58</v>
       </c>
       <c r="P37" t="n">
-        <v>159.2568</v>
+        <v>160.3228</v>
       </c>
       <c r="Q37" t="n">
-        <v>166.6796</v>
+        <v>166.5898</v>
       </c>
       <c r="R37" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S37" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>1 sep</t>
+          <t>2 sep</t>
         </is>
       </c>
       <c r="V37" t="n">
-        <v>497.52</v>
+        <v>499.85</v>
       </c>
       <c r="W37" t="n">
-        <v>505.97</v>
+        <v>500.27</v>
       </c>
       <c r="X37" t="n">
-        <v>496.78</v>
+        <v>493.81</v>
       </c>
       <c r="Y37" t="n">
-        <v>501.02</v>
+        <v>496.82</v>
       </c>
       <c r="Z37" t="n">
-        <v>435.2328</v>
+        <v>437.7045</v>
       </c>
       <c r="AA37" t="n">
-        <v>429.3825</v>
+        <v>429.3706</v>
       </c>
       <c r="AB37" t="n">
         <v>535.3375423278808</v>
@@ -6134,84 +6477,84 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3 sep</t>
+          <t>4 sep</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>40.095</v>
+        <v>40.145</v>
       </c>
       <c r="C38" t="n">
-        <v>40.215</v>
+        <v>40.28</v>
       </c>
       <c r="D38" t="n">
-        <v>39.54</v>
+        <v>39.665</v>
       </c>
       <c r="E38" t="n">
-        <v>40.04</v>
+        <v>40.105</v>
       </c>
       <c r="F38" t="n">
-        <v>37.6767</v>
+        <v>37.8115</v>
       </c>
       <c r="G38" t="n">
-        <v>35.0679</v>
+        <v>35.113</v>
       </c>
       <c r="H38" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I38" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>3 sep</t>
+          <t>4 sep</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>182.08</v>
+        <v>187.8</v>
       </c>
       <c r="M38" t="n">
-        <v>187.56</v>
+        <v>189.9</v>
       </c>
       <c r="N38" t="n">
-        <v>182</v>
+        <v>184.96</v>
       </c>
       <c r="O38" t="n">
-        <v>185.58</v>
+        <v>185.68</v>
       </c>
       <c r="P38" t="n">
-        <v>160.3228</v>
+        <v>161.3336</v>
       </c>
       <c r="Q38" t="n">
-        <v>166.5898</v>
+        <v>166.5086</v>
       </c>
       <c r="R38" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S38" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>2 sep</t>
+          <t>3 sep</t>
         </is>
       </c>
       <c r="V38" t="n">
-        <v>499.85</v>
+        <v>501.66</v>
       </c>
       <c r="W38" t="n">
-        <v>500.27</v>
+        <v>515.65</v>
       </c>
       <c r="X38" t="n">
-        <v>493.81</v>
+        <v>500.8</v>
       </c>
       <c r="Y38" t="n">
-        <v>496.82</v>
+        <v>510.12</v>
       </c>
       <c r="Z38" t="n">
-        <v>437.7045</v>
+        <v>440.6114</v>
       </c>
       <c r="AA38" t="n">
-        <v>429.3706</v>
+        <v>429.3912</v>
       </c>
       <c r="AB38" t="n">
         <v>535.3375423278808</v>
@@ -6223,84 +6566,84 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>4 sep</t>
+          <t>7 sep</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>40.145</v>
+        <v>40.26</v>
       </c>
       <c r="C39" t="n">
-        <v>40.28</v>
+        <v>40.845</v>
       </c>
       <c r="D39" t="n">
-        <v>39.665</v>
+        <v>40.12</v>
       </c>
       <c r="E39" t="n">
-        <v>40.105</v>
+        <v>40.56</v>
       </c>
       <c r="F39" t="n">
-        <v>37.8115</v>
+        <v>37.9551</v>
       </c>
       <c r="G39" t="n">
-        <v>35.113</v>
+        <v>35.1619</v>
       </c>
       <c r="H39" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I39" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>4 sep</t>
+          <t>7 sep</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>187.8</v>
+        <v>183.56</v>
       </c>
       <c r="M39" t="n">
-        <v>189.9</v>
+        <v>184.3</v>
       </c>
       <c r="N39" t="n">
-        <v>184.96</v>
+        <v>179.92</v>
       </c>
       <c r="O39" t="n">
-        <v>185.68</v>
+        <v>182.8</v>
       </c>
       <c r="P39" t="n">
-        <v>161.3336</v>
+        <v>162.2568</v>
       </c>
       <c r="Q39" t="n">
-        <v>166.5086</v>
+        <v>166.4122</v>
       </c>
       <c r="R39" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S39" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>3 sep</t>
+          <t>4 sep</t>
         </is>
       </c>
       <c r="V39" t="n">
-        <v>501.66</v>
+        <v>510</v>
       </c>
       <c r="W39" t="n">
-        <v>515.65</v>
+        <v>511</v>
       </c>
       <c r="X39" t="n">
-        <v>500.8</v>
+        <v>499.36</v>
       </c>
       <c r="Y39" t="n">
-        <v>510.12</v>
+        <v>499.7</v>
       </c>
       <c r="Z39" t="n">
-        <v>440.6114</v>
+        <v>443.5621</v>
       </c>
       <c r="AA39" t="n">
-        <v>429.3912</v>
+        <v>429.3729</v>
       </c>
       <c r="AB39" t="n">
         <v>535.3375423278808</v>
@@ -6312,84 +6655,84 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>7 sep</t>
+          <t>8 sep</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>40.26</v>
+        <v>40.83</v>
       </c>
       <c r="C40" t="n">
-        <v>40.845</v>
+        <v>41.18</v>
       </c>
       <c r="D40" t="n">
-        <v>40.12</v>
+        <v>40.6325</v>
       </c>
       <c r="E40" t="n">
-        <v>40.56</v>
+        <v>40.855</v>
       </c>
       <c r="F40" t="n">
-        <v>37.9551</v>
+        <v>38.0977</v>
       </c>
       <c r="G40" t="n">
-        <v>35.1619</v>
+        <v>35.2131</v>
       </c>
       <c r="H40" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I40" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>7 sep</t>
+          <t>8 sep</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>183.56</v>
+        <v>182.32</v>
       </c>
       <c r="M40" t="n">
-        <v>184.3</v>
+        <v>183.76</v>
       </c>
       <c r="N40" t="n">
-        <v>179.92</v>
+        <v>180.02</v>
       </c>
       <c r="O40" t="n">
-        <v>182.8</v>
+        <v>181.7</v>
       </c>
       <c r="P40" t="n">
-        <v>162.2568</v>
+        <v>163.2108</v>
       </c>
       <c r="Q40" t="n">
-        <v>166.4122</v>
+        <v>166.3049</v>
       </c>
       <c r="R40" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S40" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>4 sep</t>
+          <t>8 sep</t>
         </is>
       </c>
       <c r="V40" t="n">
-        <v>510</v>
+        <v>493.01</v>
       </c>
       <c r="W40" t="n">
-        <v>511</v>
+        <v>495.19</v>
       </c>
       <c r="X40" t="n">
-        <v>499.36</v>
+        <v>490.15</v>
       </c>
       <c r="Y40" t="n">
-        <v>499.7</v>
+        <v>493.95</v>
       </c>
       <c r="Z40" t="n">
-        <v>443.5621</v>
+        <v>445.9957</v>
       </c>
       <c r="AA40" t="n">
-        <v>429.3729</v>
+        <v>429.3939</v>
       </c>
       <c r="AB40" t="n">
         <v>535.3375423278808</v>
@@ -6401,84 +6744,84 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>8 sep</t>
+          <t>9 sep</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>40.83</v>
+        <v>41.1</v>
       </c>
       <c r="C41" t="n">
-        <v>41.18</v>
+        <v>41.385</v>
       </c>
       <c r="D41" t="n">
-        <v>40.6325</v>
+        <v>40.85</v>
       </c>
       <c r="E41" t="n">
-        <v>40.855</v>
+        <v>40.94</v>
       </c>
       <c r="F41" t="n">
-        <v>38.0977</v>
+        <v>38.2513</v>
       </c>
       <c r="G41" t="n">
-        <v>35.2131</v>
+        <v>35.2646</v>
       </c>
       <c r="H41" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I41" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>8 sep</t>
+          <t>9 sep</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>182.32</v>
+        <v>183</v>
       </c>
       <c r="M41" t="n">
-        <v>183.76</v>
+        <v>187.04</v>
       </c>
       <c r="N41" t="n">
-        <v>180.02</v>
+        <v>181.36</v>
       </c>
       <c r="O41" t="n">
-        <v>181.7</v>
+        <v>182.86</v>
       </c>
       <c r="P41" t="n">
-        <v>163.2108</v>
+        <v>164.0504</v>
       </c>
       <c r="Q41" t="n">
-        <v>166.3049</v>
+        <v>166.2113</v>
       </c>
       <c r="R41" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S41" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>8 sep</t>
+          <t>9 sep</t>
         </is>
       </c>
       <c r="V41" t="n">
-        <v>493.01</v>
+        <v>493.07</v>
       </c>
       <c r="W41" t="n">
-        <v>495.19</v>
+        <v>494.39</v>
       </c>
       <c r="X41" t="n">
-        <v>490.15</v>
+        <v>489.8</v>
       </c>
       <c r="Y41" t="n">
-        <v>493.95</v>
+        <v>491.65</v>
       </c>
       <c r="Z41" t="n">
-        <v>445.9957</v>
+        <v>448.4712</v>
       </c>
       <c r="AA41" t="n">
-        <v>429.3939</v>
+        <v>429.4364</v>
       </c>
       <c r="AB41" t="n">
         <v>535.3375423278808</v>
@@ -6490,84 +6833,84 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>9 sep</t>
+          <t>10 sep</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>41.1</v>
+        <v>40.98</v>
       </c>
       <c r="C42" t="n">
-        <v>41.385</v>
+        <v>41.77</v>
       </c>
       <c r="D42" t="n">
-        <v>40.85</v>
+        <v>40.93</v>
       </c>
       <c r="E42" t="n">
-        <v>40.94</v>
+        <v>41.23</v>
       </c>
       <c r="F42" t="n">
-        <v>38.2513</v>
+        <v>38.4034</v>
       </c>
       <c r="G42" t="n">
-        <v>35.2646</v>
+        <v>35.3174</v>
       </c>
       <c r="H42" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I42" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>9 sep</t>
+          <t>10 sep</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="M42" t="n">
-        <v>187.04</v>
+        <v>180.4</v>
       </c>
       <c r="N42" t="n">
-        <v>181.36</v>
+        <v>176.2</v>
       </c>
       <c r="O42" t="n">
-        <v>182.86</v>
+        <v>177.82</v>
       </c>
       <c r="P42" t="n">
-        <v>164.0504</v>
+        <v>164.7724</v>
       </c>
       <c r="Q42" t="n">
-        <v>166.2113</v>
+        <v>166.0803</v>
       </c>
       <c r="R42" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S42" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>9 sep</t>
+          <t>10 sep</t>
         </is>
       </c>
       <c r="V42" t="n">
-        <v>493.07</v>
+        <v>488.32</v>
       </c>
       <c r="W42" t="n">
-        <v>494.39</v>
+        <v>494.52</v>
       </c>
       <c r="X42" t="n">
-        <v>489.8</v>
+        <v>486</v>
       </c>
       <c r="Y42" t="n">
-        <v>491.65</v>
+        <v>492.44</v>
       </c>
       <c r="Z42" t="n">
-        <v>448.4712</v>
+        <v>450.8736</v>
       </c>
       <c r="AA42" t="n">
-        <v>429.4364</v>
+        <v>429.5215</v>
       </c>
       <c r="AB42" t="n">
         <v>535.3375423278808</v>
@@ -6579,84 +6922,84 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10 sep</t>
+          <t>11 sep</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>40.98</v>
+        <v>41.345</v>
       </c>
       <c r="C43" t="n">
-        <v>41.77</v>
+        <v>41.715</v>
       </c>
       <c r="D43" t="n">
-        <v>40.93</v>
+        <v>40.905</v>
       </c>
       <c r="E43" t="n">
-        <v>41.23</v>
+        <v>41.415</v>
       </c>
       <c r="F43" t="n">
-        <v>38.4034</v>
+        <v>38.5608</v>
       </c>
       <c r="G43" t="n">
-        <v>35.3174</v>
+        <v>35.3717</v>
       </c>
       <c r="H43" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I43" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>10 sep</t>
+          <t>11 sep</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>180</v>
+        <v>175.68</v>
       </c>
       <c r="M43" t="n">
-        <v>180.4</v>
+        <v>178.84</v>
       </c>
       <c r="N43" t="n">
-        <v>176.2</v>
+        <v>172.16</v>
       </c>
       <c r="O43" t="n">
-        <v>177.82</v>
+        <v>177.26</v>
       </c>
       <c r="P43" t="n">
-        <v>164.7724</v>
+        <v>165.5248</v>
       </c>
       <c r="Q43" t="n">
-        <v>166.0803</v>
+        <v>165.9594</v>
       </c>
       <c r="R43" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S43" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>10 sep</t>
+          <t>11 sep</t>
         </is>
       </c>
       <c r="V43" t="n">
-        <v>488.32</v>
+        <v>495.65</v>
       </c>
       <c r="W43" t="n">
-        <v>494.52</v>
+        <v>498.97</v>
       </c>
       <c r="X43" t="n">
-        <v>486</v>
+        <v>492.58</v>
       </c>
       <c r="Y43" t="n">
-        <v>492.44</v>
+        <v>495.63</v>
       </c>
       <c r="Z43" t="n">
-        <v>450.8736</v>
+        <v>453.115</v>
       </c>
       <c r="AA43" t="n">
-        <v>429.5215</v>
+        <v>429.654</v>
       </c>
       <c r="AB43" t="n">
         <v>535.3375423278808</v>
@@ -6668,84 +7011,84 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>11 sep</t>
+          <t>14 sep</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>41.345</v>
+        <v>41.88</v>
       </c>
       <c r="C44" t="n">
-        <v>41.715</v>
+        <v>42.285</v>
       </c>
       <c r="D44" t="n">
-        <v>40.905</v>
+        <v>41.8</v>
       </c>
       <c r="E44" t="n">
-        <v>41.415</v>
+        <v>41.91</v>
       </c>
       <c r="F44" t="n">
-        <v>38.5608</v>
+        <v>38.7226</v>
       </c>
       <c r="G44" t="n">
-        <v>35.3717</v>
+        <v>35.4269</v>
       </c>
       <c r="H44" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I44" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>11 sep</t>
+          <t>14 sep</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>175.68</v>
+        <v>180.82</v>
       </c>
       <c r="M44" t="n">
-        <v>178.84</v>
+        <v>186.76</v>
       </c>
       <c r="N44" t="n">
-        <v>172.16</v>
+        <v>180.82</v>
       </c>
       <c r="O44" t="n">
-        <v>177.26</v>
+        <v>186.26</v>
       </c>
       <c r="P44" t="n">
-        <v>165.5248</v>
+        <v>166.4488</v>
       </c>
       <c r="Q44" t="n">
-        <v>165.9594</v>
+        <v>165.8745</v>
       </c>
       <c r="R44" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S44" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>11 sep</t>
+          <t>14 sep</t>
         </is>
       </c>
       <c r="V44" t="n">
-        <v>495.65</v>
+        <v>497.06</v>
       </c>
       <c r="W44" t="n">
-        <v>498.97</v>
+        <v>509.95</v>
       </c>
       <c r="X44" t="n">
-        <v>492.58</v>
+        <v>495.34</v>
       </c>
       <c r="Y44" t="n">
-        <v>495.63</v>
+        <v>505.41</v>
       </c>
       <c r="Z44" t="n">
-        <v>453.115</v>
+        <v>455.4281</v>
       </c>
       <c r="AA44" t="n">
-        <v>429.6539</v>
+        <v>429.8259</v>
       </c>
       <c r="AB44" t="n">
         <v>535.3375423278808</v>
@@ -6757,84 +7100,84 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>14 sep</t>
+          <t>15 sep</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>41.88</v>
+        <v>41.845</v>
       </c>
       <c r="C45" t="n">
-        <v>42.285</v>
+        <v>42.7</v>
       </c>
       <c r="D45" t="n">
-        <v>41.8</v>
+        <v>41.72</v>
       </c>
       <c r="E45" t="n">
-        <v>41.91</v>
+        <v>42.7</v>
       </c>
       <c r="F45" t="n">
-        <v>38.7226</v>
+        <v>38.8782</v>
       </c>
       <c r="G45" t="n">
-        <v>35.4269</v>
+        <v>35.4854</v>
       </c>
       <c r="H45" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I45" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>14 sep</t>
+          <t>15 sep</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>180.82</v>
+        <v>186.64</v>
       </c>
       <c r="M45" t="n">
-        <v>186.76</v>
+        <v>187.26</v>
       </c>
       <c r="N45" t="n">
-        <v>180.82</v>
+        <v>183.2</v>
       </c>
       <c r="O45" t="n">
-        <v>186.26</v>
+        <v>187.08</v>
       </c>
       <c r="P45" t="n">
-        <v>166.4488</v>
+        <v>167.3124</v>
       </c>
       <c r="Q45" t="n">
-        <v>165.8745</v>
+        <v>165.7921</v>
       </c>
       <c r="R45" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S45" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>14 sep</t>
+          <t>15 sep</t>
         </is>
       </c>
       <c r="V45" t="n">
-        <v>497.06</v>
+        <v>500.06</v>
       </c>
       <c r="W45" t="n">
-        <v>509.95</v>
+        <v>505.9</v>
       </c>
       <c r="X45" t="n">
-        <v>495.34</v>
+        <v>495.54</v>
       </c>
       <c r="Y45" t="n">
-        <v>505.41</v>
+        <v>497.12</v>
       </c>
       <c r="Z45" t="n">
-        <v>455.4281</v>
+        <v>457.6502</v>
       </c>
       <c r="AA45" t="n">
-        <v>429.8259</v>
+        <v>429.9416</v>
       </c>
       <c r="AB45" t="n">
         <v>535.3375423278808</v>
@@ -6846,84 +7189,84 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>15 sep</t>
+          <t>16 sep</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>41.845</v>
+        <v>42.72</v>
       </c>
       <c r="C46" t="n">
-        <v>42.7</v>
+        <v>42.85</v>
       </c>
       <c r="D46" t="n">
-        <v>41.72</v>
+        <v>41.67</v>
       </c>
       <c r="E46" t="n">
-        <v>42.7</v>
+        <v>41.825</v>
       </c>
       <c r="F46" t="n">
-        <v>38.8782</v>
+        <v>38.9989</v>
       </c>
       <c r="G46" t="n">
-        <v>35.4854</v>
+        <v>35.5403</v>
       </c>
       <c r="H46" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I46" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>15 sep</t>
+          <t>16 sep</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>186.64</v>
+        <v>185.86</v>
       </c>
       <c r="M46" t="n">
-        <v>187.26</v>
+        <v>186.76</v>
       </c>
       <c r="N46" t="n">
-        <v>183.2</v>
+        <v>182.18</v>
       </c>
       <c r="O46" t="n">
-        <v>187.08</v>
+        <v>186.56</v>
       </c>
       <c r="P46" t="n">
-        <v>167.3124</v>
+        <v>168.2844</v>
       </c>
       <c r="Q46" t="n">
-        <v>165.7921</v>
+        <v>165.6996</v>
       </c>
       <c r="R46" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S46" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>15 sep</t>
+          <t>16 sep</t>
         </is>
       </c>
       <c r="V46" t="n">
-        <v>500.06</v>
+        <v>493.03</v>
       </c>
       <c r="W46" t="n">
-        <v>505.9</v>
+        <v>495.97</v>
       </c>
       <c r="X46" t="n">
-        <v>495.54</v>
+        <v>487.23</v>
       </c>
       <c r="Y46" t="n">
-        <v>497.12</v>
+        <v>490.3</v>
       </c>
       <c r="Z46" t="n">
-        <v>457.6502</v>
+        <v>459.694</v>
       </c>
       <c r="AA46" t="n">
-        <v>429.9416</v>
+        <v>429.9809</v>
       </c>
       <c r="AB46" t="n">
         <v>535.3375423278808</v>
@@ -6935,84 +7278,84 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>16 sep</t>
+          <t>17 sep</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>42.72</v>
+        <v>41.58</v>
       </c>
       <c r="C47" t="n">
-        <v>42.85</v>
+        <v>42.055</v>
       </c>
       <c r="D47" t="n">
-        <v>41.67</v>
+        <v>41.38</v>
       </c>
       <c r="E47" t="n">
-        <v>41.825</v>
+        <v>41.56</v>
       </c>
       <c r="F47" t="n">
-        <v>38.9989</v>
+        <v>39.1225</v>
       </c>
       <c r="G47" t="n">
-        <v>35.5403</v>
+        <v>35.5926</v>
       </c>
       <c r="H47" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I47" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>16 sep</t>
+          <t>17 sep</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>185.86</v>
+        <v>188.54</v>
       </c>
       <c r="M47" t="n">
-        <v>186.76</v>
+        <v>189.2</v>
       </c>
       <c r="N47" t="n">
-        <v>182.18</v>
+        <v>184.62</v>
       </c>
       <c r="O47" t="n">
-        <v>186.56</v>
+        <v>188</v>
       </c>
       <c r="P47" t="n">
-        <v>168.2844</v>
+        <v>169.2896</v>
       </c>
       <c r="Q47" t="n">
-        <v>165.6996</v>
+        <v>165.6125</v>
       </c>
       <c r="R47" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S47" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>16 sep</t>
+          <t>17 sep</t>
         </is>
       </c>
       <c r="V47" t="n">
-        <v>493.03</v>
+        <v>497.8</v>
       </c>
       <c r="W47" t="n">
-        <v>495.97</v>
+        <v>501.47</v>
       </c>
       <c r="X47" t="n">
-        <v>487.23</v>
+        <v>493.17</v>
       </c>
       <c r="Y47" t="n">
-        <v>490.3</v>
+        <v>497.75</v>
       </c>
       <c r="Z47" t="n">
-        <v>459.694</v>
+        <v>461.9966</v>
       </c>
       <c r="AA47" t="n">
-        <v>429.9809</v>
+        <v>430.0251</v>
       </c>
       <c r="AB47" t="n">
         <v>535.3375423278808</v>
@@ -7024,84 +7367,84 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>17 sep</t>
+          <t>18 sep</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>41.58</v>
+        <v>41.465</v>
       </c>
       <c r="C48" t="n">
-        <v>42.055</v>
+        <v>41.5</v>
       </c>
       <c r="D48" t="n">
-        <v>41.38</v>
+        <v>40.955</v>
       </c>
       <c r="E48" t="n">
-        <v>41.56</v>
+        <v>41.315</v>
       </c>
       <c r="F48" t="n">
-        <v>39.1225</v>
+        <v>39.2414</v>
       </c>
       <c r="G48" t="n">
-        <v>35.5926</v>
+        <v>35.6436</v>
       </c>
       <c r="H48" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I48" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>17 sep</t>
+          <t>18 sep</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>188.54</v>
+        <v>186.1</v>
       </c>
       <c r="M48" t="n">
-        <v>189.2</v>
+        <v>187.26</v>
       </c>
       <c r="N48" t="n">
-        <v>184.62</v>
+        <v>182.56</v>
       </c>
       <c r="O48" t="n">
-        <v>188</v>
+        <v>183.12</v>
       </c>
       <c r="P48" t="n">
-        <v>169.2896</v>
+        <v>170.2004</v>
       </c>
       <c r="Q48" t="n">
-        <v>165.6125</v>
+        <v>165.5062</v>
       </c>
       <c r="R48" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S48" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>17 sep</t>
+          <t>18 sep</t>
         </is>
       </c>
       <c r="V48" t="n">
-        <v>497.8</v>
+        <v>497.97</v>
       </c>
       <c r="W48" t="n">
-        <v>501.47</v>
+        <v>498.65</v>
       </c>
       <c r="X48" t="n">
-        <v>493.17</v>
+        <v>491.1</v>
       </c>
       <c r="Y48" t="n">
-        <v>497.75</v>
+        <v>493.78</v>
       </c>
       <c r="Z48" t="n">
-        <v>461.9966</v>
+        <v>464.1995</v>
       </c>
       <c r="AA48" t="n">
-        <v>430.0251</v>
+        <v>430.0757</v>
       </c>
       <c r="AB48" t="n">
         <v>535.3375423278808</v>
@@ -7113,84 +7456,84 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>18 sep</t>
+          <t>21 sep</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>41.465</v>
+        <v>41.04</v>
       </c>
       <c r="C49" t="n">
-        <v>41.5</v>
+        <v>41.4</v>
       </c>
       <c r="D49" t="n">
-        <v>40.955</v>
+        <v>40.775</v>
       </c>
       <c r="E49" t="n">
-        <v>41.315</v>
+        <v>40.775</v>
       </c>
       <c r="F49" t="n">
-        <v>39.2414</v>
+        <v>39.3341</v>
       </c>
       <c r="G49" t="n">
-        <v>35.6436</v>
+        <v>35.6939</v>
       </c>
       <c r="H49" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I49" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>18 sep</t>
+          <t>21 sep</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>186.1</v>
+        <v>184.7</v>
       </c>
       <c r="M49" t="n">
-        <v>187.26</v>
+        <v>185.86</v>
       </c>
       <c r="N49" t="n">
-        <v>182.56</v>
+        <v>182.48</v>
       </c>
       <c r="O49" t="n">
-        <v>183.12</v>
+        <v>182.86</v>
       </c>
       <c r="P49" t="n">
-        <v>170.2004</v>
+        <v>171.0432</v>
       </c>
       <c r="Q49" t="n">
-        <v>165.5062</v>
+        <v>165.4052</v>
       </c>
       <c r="R49" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S49" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>18 sep</t>
+          <t>21 sep</t>
         </is>
       </c>
       <c r="V49" t="n">
-        <v>497.97</v>
+        <v>494.95</v>
       </c>
       <c r="W49" t="n">
-        <v>498.65</v>
+        <v>501.87</v>
       </c>
       <c r="X49" t="n">
-        <v>491.1</v>
+        <v>491.33</v>
       </c>
       <c r="Y49" t="n">
-        <v>493.78</v>
+        <v>501.61</v>
       </c>
       <c r="Z49" t="n">
-        <v>464.1995</v>
+        <v>466.5442</v>
       </c>
       <c r="AA49" t="n">
-        <v>430.0757</v>
+        <v>430.1492</v>
       </c>
       <c r="AB49" t="n">
         <v>535.3375423278808</v>
@@ -7202,84 +7545,84 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>21 sep</t>
+          <t>22 sep</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>41.04</v>
+        <v>40.84</v>
       </c>
       <c r="C50" t="n">
-        <v>41.4</v>
+        <v>41.165</v>
       </c>
       <c r="D50" t="n">
-        <v>40.775</v>
+        <v>40.215</v>
       </c>
       <c r="E50" t="n">
-        <v>40.775</v>
+        <v>41.01</v>
       </c>
       <c r="F50" t="n">
-        <v>39.3341</v>
+        <v>39.4244</v>
       </c>
       <c r="G50" t="n">
-        <v>35.6939</v>
+        <v>35.746</v>
       </c>
       <c r="H50" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I50" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>21 sep</t>
+          <t>22 sep</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>184.7</v>
+        <v>182.14</v>
       </c>
       <c r="M50" t="n">
-        <v>185.86</v>
+        <v>187.48</v>
       </c>
       <c r="N50" t="n">
-        <v>182.48</v>
+        <v>181.52</v>
       </c>
       <c r="O50" t="n">
-        <v>182.86</v>
+        <v>182.32</v>
       </c>
       <c r="P50" t="n">
-        <v>171.0432</v>
+        <v>171.9552</v>
       </c>
       <c r="Q50" t="n">
-        <v>165.4052</v>
+        <v>165.2836</v>
       </c>
       <c r="R50" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S50" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>21 sep</t>
+          <t>22 sep</t>
         </is>
       </c>
       <c r="V50" t="n">
-        <v>494.95</v>
+        <v>507.32</v>
       </c>
       <c r="W50" t="n">
-        <v>501.87</v>
+        <v>508.5</v>
       </c>
       <c r="X50" t="n">
-        <v>491.33</v>
+        <v>493.65</v>
       </c>
       <c r="Y50" t="n">
-        <v>501.61</v>
+        <v>498</v>
       </c>
       <c r="Z50" t="n">
-        <v>466.5442</v>
+        <v>468.699</v>
       </c>
       <c r="AA50" t="n">
-        <v>430.1492</v>
+        <v>430.2656</v>
       </c>
       <c r="AB50" t="n">
         <v>535.3375423278808</v>
@@ -7291,84 +7634,84 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>22 sep</t>
+          <t>23 sep</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>40.84</v>
+        <v>41</v>
       </c>
       <c r="C51" t="n">
-        <v>41.165</v>
+        <v>41.755</v>
       </c>
       <c r="D51" t="n">
-        <v>40.215</v>
+        <v>40.995</v>
       </c>
       <c r="E51" t="n">
-        <v>41.01</v>
+        <v>41.69</v>
       </c>
       <c r="F51" t="n">
-        <v>39.4244</v>
+        <v>39.5272</v>
       </c>
       <c r="G51" t="n">
-        <v>35.746</v>
+        <v>35.8024</v>
       </c>
       <c r="H51" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I51" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>22 sep</t>
+          <t>23 sep</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>182.14</v>
+        <v>184.9</v>
       </c>
       <c r="M51" t="n">
-        <v>187.48</v>
+        <v>187.8</v>
       </c>
       <c r="N51" t="n">
-        <v>181.52</v>
+        <v>183.48</v>
       </c>
       <c r="O51" t="n">
-        <v>182.32</v>
+        <v>186.46</v>
       </c>
       <c r="P51" t="n">
-        <v>171.9552</v>
+        <v>172.9448</v>
       </c>
       <c r="Q51" t="n">
-        <v>165.2836</v>
+        <v>165.1675</v>
       </c>
       <c r="R51" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S51" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>22 sep</t>
+          <t>23 sep</t>
         </is>
       </c>
       <c r="V51" t="n">
-        <v>507.32</v>
+        <v>500.76</v>
       </c>
       <c r="W51" t="n">
-        <v>508.5</v>
+        <v>509.44</v>
       </c>
       <c r="X51" t="n">
-        <v>493.65</v>
+        <v>495.88</v>
       </c>
       <c r="Y51" t="n">
-        <v>498</v>
+        <v>500.59</v>
       </c>
       <c r="Z51" t="n">
-        <v>468.699</v>
+        <v>471.0267</v>
       </c>
       <c r="AA51" t="n">
-        <v>430.2656</v>
+        <v>430.3795</v>
       </c>
       <c r="AB51" t="n">
         <v>535.3375423278808</v>
@@ -7380,84 +7723,84 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>23 sep</t>
+          <t>24 sep</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>41</v>
+        <v>41.825</v>
       </c>
       <c r="C52" t="n">
-        <v>41.755</v>
+        <v>42.52</v>
       </c>
       <c r="D52" t="n">
-        <v>40.995</v>
+        <v>41.78</v>
       </c>
       <c r="E52" t="n">
-        <v>41.69</v>
+        <v>42.43</v>
       </c>
       <c r="F52" t="n">
-        <v>39.5272</v>
+        <v>39.6382</v>
       </c>
       <c r="G52" t="n">
-        <v>35.8024</v>
+        <v>35.8638</v>
       </c>
       <c r="H52" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I52" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>23 sep</t>
+          <t>24 sep</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>184.9</v>
+        <v>184.52</v>
       </c>
       <c r="M52" t="n">
-        <v>187.8</v>
+        <v>185.5</v>
       </c>
       <c r="N52" t="n">
-        <v>183.48</v>
+        <v>182.26</v>
       </c>
       <c r="O52" t="n">
-        <v>186.46</v>
+        <v>184.18</v>
       </c>
       <c r="P52" t="n">
-        <v>172.9448</v>
+        <v>173.8756</v>
       </c>
       <c r="Q52" t="n">
-        <v>165.1675</v>
+        <v>165.0554</v>
       </c>
       <c r="R52" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S52" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>23 sep</t>
+          <t>24 sep</t>
         </is>
       </c>
       <c r="V52" t="n">
-        <v>500.76</v>
+        <v>495.07</v>
       </c>
       <c r="W52" t="n">
-        <v>509.44</v>
+        <v>498.9</v>
       </c>
       <c r="X52" t="n">
-        <v>495.88</v>
+        <v>491.22</v>
       </c>
       <c r="Y52" t="n">
-        <v>500.59</v>
+        <v>497.93</v>
       </c>
       <c r="Z52" t="n">
-        <v>471.0267</v>
+        <v>473.0876</v>
       </c>
       <c r="AA52" t="n">
-        <v>430.3795</v>
+        <v>430.4686</v>
       </c>
       <c r="AB52" t="n">
         <v>535.3375423278808</v>
@@ -7469,84 +7812,84 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>24 sep</t>
+          <t>25 sep</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>41.825</v>
+        <v>41.99</v>
       </c>
       <c r="C53" t="n">
-        <v>42.52</v>
+        <v>42.33</v>
       </c>
       <c r="D53" t="n">
-        <v>41.78</v>
+        <v>41.71</v>
       </c>
       <c r="E53" t="n">
-        <v>42.43</v>
+        <v>42.06</v>
       </c>
       <c r="F53" t="n">
-        <v>39.6382</v>
+        <v>39.7263</v>
       </c>
       <c r="G53" t="n">
-        <v>35.8638</v>
+        <v>35.9239</v>
       </c>
       <c r="H53" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I53" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>24 sep</t>
+          <t>25 sep</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>184.52</v>
+        <v>184.42</v>
       </c>
       <c r="M53" t="n">
-        <v>185.5</v>
+        <v>185.92</v>
       </c>
       <c r="N53" t="n">
-        <v>182.26</v>
+        <v>183.76</v>
       </c>
       <c r="O53" t="n">
-        <v>184.18</v>
+        <v>185.92</v>
       </c>
       <c r="P53" t="n">
-        <v>173.8756</v>
+        <v>174.8356</v>
       </c>
       <c r="Q53" t="n">
-        <v>165.0554</v>
+        <v>164.9525</v>
       </c>
       <c r="R53" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S53" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>24 sep</t>
+          <t>25 sep</t>
         </is>
       </c>
       <c r="V53" t="n">
-        <v>495.07</v>
+        <v>499.04</v>
       </c>
       <c r="W53" t="n">
-        <v>498.9</v>
+        <v>519.4</v>
       </c>
       <c r="X53" t="n">
-        <v>491.22</v>
+        <v>497.25</v>
       </c>
       <c r="Y53" t="n">
-        <v>497.93</v>
+        <v>516.17</v>
       </c>
       <c r="Z53" t="n">
-        <v>473.0876</v>
+        <v>475.4041</v>
       </c>
       <c r="AA53" t="n">
-        <v>430.4686</v>
+        <v>430.6098</v>
       </c>
       <c r="AB53" t="n">
         <v>535.3375423278808</v>
@@ -7558,84 +7901,84 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>25 sep</t>
+          <t>28 sep</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>41.99</v>
+        <v>42.45</v>
       </c>
       <c r="C54" t="n">
-        <v>42.33</v>
+        <v>42.995</v>
       </c>
       <c r="D54" t="n">
-        <v>41.71</v>
+        <v>42.38</v>
       </c>
       <c r="E54" t="n">
-        <v>42.06</v>
+        <v>42.725</v>
       </c>
       <c r="F54" t="n">
-        <v>39.7263</v>
+        <v>39.8301</v>
       </c>
       <c r="G54" t="n">
-        <v>35.9239</v>
+        <v>35.9888</v>
       </c>
       <c r="H54" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I54" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>25 sep</t>
+          <t>28 sep</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>184.42</v>
+        <v>185.2</v>
       </c>
       <c r="M54" t="n">
-        <v>185.92</v>
+        <v>186.76</v>
       </c>
       <c r="N54" t="n">
-        <v>183.76</v>
+        <v>178.88</v>
       </c>
       <c r="O54" t="n">
-        <v>185.92</v>
+        <v>184.02</v>
       </c>
       <c r="P54" t="n">
-        <v>174.8356</v>
+        <v>175.7508</v>
       </c>
       <c r="Q54" t="n">
-        <v>164.9525</v>
+        <v>164.8355</v>
       </c>
       <c r="R54" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S54" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>25 sep</t>
+          <t>28 sep</t>
         </is>
       </c>
       <c r="V54" t="n">
-        <v>499.04</v>
+        <v>505.47</v>
       </c>
       <c r="W54" t="n">
-        <v>519.4</v>
+        <v>513.33</v>
       </c>
       <c r="X54" t="n">
-        <v>497.25</v>
+        <v>502.22</v>
       </c>
       <c r="Y54" t="n">
-        <v>516.17</v>
+        <v>509.22</v>
       </c>
       <c r="Z54" t="n">
-        <v>475.4041</v>
+        <v>477.7269</v>
       </c>
       <c r="AA54" t="n">
-        <v>430.6098</v>
+        <v>430.7113</v>
       </c>
       <c r="AB54" t="n">
         <v>535.3375423278808</v>
@@ -7647,84 +7990,84 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>28 sep</t>
+          <t>29 sep</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>42.45</v>
+        <v>42.57</v>
       </c>
       <c r="C55" t="n">
-        <v>42.995</v>
+        <v>42.665</v>
       </c>
       <c r="D55" t="n">
-        <v>42.38</v>
+        <v>41.73</v>
       </c>
       <c r="E55" t="n">
-        <v>42.725</v>
+        <v>42.05</v>
       </c>
       <c r="F55" t="n">
-        <v>39.8301</v>
+        <v>39.9146</v>
       </c>
       <c r="G55" t="n">
-        <v>35.9888</v>
+        <v>36.0498</v>
       </c>
       <c r="H55" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I55" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>28 sep</t>
+          <t>29 sep</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>185.2</v>
+        <v>183.22</v>
       </c>
       <c r="M55" t="n">
-        <v>186.76</v>
+        <v>186.34</v>
       </c>
       <c r="N55" t="n">
-        <v>178.88</v>
+        <v>182.28</v>
       </c>
       <c r="O55" t="n">
-        <v>184.02</v>
+        <v>185.32</v>
       </c>
       <c r="P55" t="n">
-        <v>175.7508</v>
+        <v>176.7288</v>
       </c>
       <c r="Q55" t="n">
-        <v>164.8355</v>
+        <v>164.733</v>
       </c>
       <c r="R55" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S55" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>28 sep</t>
+          <t>29 sep</t>
         </is>
       </c>
       <c r="V55" t="n">
-        <v>505.47</v>
+        <v>508.31</v>
       </c>
       <c r="W55" t="n">
-        <v>513.33</v>
+        <v>513.64</v>
       </c>
       <c r="X55" t="n">
-        <v>502.22</v>
+        <v>502.4</v>
       </c>
       <c r="Y55" t="n">
-        <v>509.22</v>
+        <v>508.96</v>
       </c>
       <c r="Z55" t="n">
-        <v>477.7269</v>
+        <v>479.8754</v>
       </c>
       <c r="AA55" t="n">
-        <v>430.7113</v>
+        <v>430.8784</v>
       </c>
       <c r="AB55" t="n">
         <v>535.3375423278808</v>
@@ -7736,84 +8079,84 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>29 sep</t>
+          <t>30 sep</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>42.57</v>
+        <v>41.975</v>
       </c>
       <c r="C56" t="n">
-        <v>42.665</v>
+        <v>42.095</v>
       </c>
       <c r="D56" t="n">
-        <v>41.73</v>
+        <v>41.58</v>
       </c>
       <c r="E56" t="n">
-        <v>42.05</v>
+        <v>41.91</v>
       </c>
       <c r="F56" t="n">
-        <v>39.9146</v>
+        <v>39.9874</v>
       </c>
       <c r="G56" t="n">
-        <v>36.0498</v>
+        <v>36.1135</v>
       </c>
       <c r="H56" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I56" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>29 sep</t>
+          <t>30 sep</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>183.22</v>
+        <v>184.5</v>
       </c>
       <c r="M56" t="n">
-        <v>186.34</v>
+        <v>186.2</v>
       </c>
       <c r="N56" t="n">
-        <v>182.28</v>
+        <v>181.06</v>
       </c>
       <c r="O56" t="n">
-        <v>185.32</v>
+        <v>185.66</v>
       </c>
       <c r="P56" t="n">
-        <v>176.7288</v>
+        <v>177.8012</v>
       </c>
       <c r="Q56" t="n">
-        <v>164.733</v>
+        <v>164.6377</v>
       </c>
       <c r="R56" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S56" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>29 sep</t>
+          <t>30 sep</t>
         </is>
       </c>
       <c r="V56" t="n">
-        <v>508.31</v>
+        <v>511.61</v>
       </c>
       <c r="W56" t="n">
-        <v>513.64</v>
+        <v>519.83</v>
       </c>
       <c r="X56" t="n">
-        <v>502.4</v>
+        <v>510.31</v>
       </c>
       <c r="Y56" t="n">
-        <v>508.96</v>
+        <v>512.9</v>
       </c>
       <c r="Z56" t="n">
-        <v>479.8754</v>
+        <v>482.1933</v>
       </c>
       <c r="AA56" t="n">
-        <v>430.8784</v>
+        <v>431.0408</v>
       </c>
       <c r="AB56" t="n">
         <v>535.3375423278808</v>
@@ -7825,84 +8168,84 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>30 sep</t>
+          <t>1 okt</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>41.975</v>
+        <v>41.625</v>
       </c>
       <c r="C57" t="n">
-        <v>42.095</v>
+        <v>42.36</v>
       </c>
       <c r="D57" t="n">
-        <v>41.58</v>
+        <v>41.165</v>
       </c>
       <c r="E57" t="n">
-        <v>41.91</v>
+        <v>42.24</v>
       </c>
       <c r="F57" t="n">
-        <v>39.9874</v>
+        <v>40.0562</v>
       </c>
       <c r="G57" t="n">
-        <v>36.1135</v>
+        <v>36.1777</v>
       </c>
       <c r="H57" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I57" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>30 sep</t>
+          <t>1 okt</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>184.5</v>
+        <v>184.68</v>
       </c>
       <c r="M57" t="n">
-        <v>186.2</v>
+        <v>190.26</v>
       </c>
       <c r="N57" t="n">
-        <v>181.06</v>
+        <v>181.34</v>
       </c>
       <c r="O57" t="n">
-        <v>185.66</v>
+        <v>186.74</v>
       </c>
       <c r="P57" t="n">
-        <v>177.8012</v>
+        <v>178.9696</v>
       </c>
       <c r="Q57" t="n">
-        <v>164.6377</v>
+        <v>164.5407</v>
       </c>
       <c r="R57" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S57" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>30 sep</t>
+          <t>1 okt</t>
         </is>
       </c>
       <c r="V57" t="n">
-        <v>511.61</v>
+        <v>519.88</v>
       </c>
       <c r="W57" t="n">
-        <v>519.83</v>
+        <v>522.85</v>
       </c>
       <c r="X57" t="n">
-        <v>510.31</v>
+        <v>512.17</v>
       </c>
       <c r="Y57" t="n">
-        <v>512.9</v>
+        <v>512.8</v>
       </c>
       <c r="Z57" t="n">
-        <v>482.1933</v>
+        <v>484.6572</v>
       </c>
       <c r="AA57" t="n">
-        <v>431.0408</v>
+        <v>431.2272</v>
       </c>
       <c r="AB57" t="n">
         <v>535.3375423278808</v>
@@ -7914,84 +8257,84 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1 okt</t>
+          <t>2 okt</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>41.625</v>
+        <v>42.11</v>
       </c>
       <c r="C58" t="n">
-        <v>42.36</v>
+        <v>42.745</v>
       </c>
       <c r="D58" t="n">
-        <v>41.165</v>
+        <v>41.985</v>
       </c>
       <c r="E58" t="n">
-        <v>42.24</v>
+        <v>42.4</v>
       </c>
       <c r="F58" t="n">
-        <v>40.0562</v>
+        <v>40.1364</v>
       </c>
       <c r="G58" t="n">
-        <v>36.1777</v>
+        <v>36.2422</v>
       </c>
       <c r="H58" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I58" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>1 okt</t>
+          <t>2 okt</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>184.68</v>
+        <v>187.82</v>
       </c>
       <c r="M58" t="n">
-        <v>190.26</v>
+        <v>188.74</v>
       </c>
       <c r="N58" t="n">
-        <v>181.34</v>
+        <v>183.92</v>
       </c>
       <c r="O58" t="n">
-        <v>186.74</v>
+        <v>183.92</v>
       </c>
       <c r="P58" t="n">
-        <v>178.9696</v>
+        <v>179.844</v>
       </c>
       <c r="Q58" t="n">
-        <v>164.5407</v>
+        <v>164.4442</v>
       </c>
       <c r="R58" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S58" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>1 okt</t>
+          <t>2 okt</t>
         </is>
       </c>
       <c r="V58" t="n">
-        <v>519.88</v>
+        <v>519.39</v>
       </c>
       <c r="W58" t="n">
-        <v>522.85</v>
+        <v>522.5</v>
       </c>
       <c r="X58" t="n">
-        <v>512.17</v>
+        <v>513.66</v>
       </c>
       <c r="Y58" t="n">
-        <v>512.8</v>
+        <v>517.53</v>
       </c>
       <c r="Z58" t="n">
-        <v>484.6572</v>
+        <v>487.3905</v>
       </c>
       <c r="AA58" t="n">
-        <v>431.2272</v>
+        <v>431.4557</v>
       </c>
       <c r="AB58" t="n">
         <v>535.3375423278808</v>
@@ -8003,84 +8346,84 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2 okt</t>
+          <t>5 okt</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>42.11</v>
+        <v>42.645</v>
       </c>
       <c r="C59" t="n">
-        <v>42.745</v>
+        <v>43.11</v>
       </c>
       <c r="D59" t="n">
-        <v>41.985</v>
+        <v>42.35</v>
       </c>
       <c r="E59" t="n">
-        <v>42.4</v>
+        <v>42.865</v>
       </c>
       <c r="F59" t="n">
-        <v>40.1364</v>
+        <v>40.2347</v>
       </c>
       <c r="G59" t="n">
-        <v>36.2422</v>
+        <v>36.3069</v>
       </c>
       <c r="H59" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I59" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2 okt</t>
+          <t>5 okt</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>187.82</v>
+        <v>185.06</v>
       </c>
       <c r="M59" t="n">
-        <v>188.74</v>
+        <v>188.5</v>
       </c>
       <c r="N59" t="n">
-        <v>183.92</v>
+        <v>184.66</v>
       </c>
       <c r="O59" t="n">
-        <v>183.92</v>
+        <v>185.04</v>
       </c>
       <c r="P59" t="n">
-        <v>179.844</v>
+        <v>180.5192</v>
       </c>
       <c r="Q59" t="n">
-        <v>164.4442</v>
+        <v>164.3515</v>
       </c>
       <c r="R59" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S59" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>2 okt</t>
+          <t>5 okt</t>
         </is>
       </c>
       <c r="V59" t="n">
-        <v>519.39</v>
+        <v>521.62</v>
       </c>
       <c r="W59" t="n">
-        <v>522.5</v>
+        <v>532.35</v>
       </c>
       <c r="X59" t="n">
-        <v>513.66</v>
+        <v>521.47</v>
       </c>
       <c r="Y59" t="n">
-        <v>517.53</v>
+        <v>525.1799999999999</v>
       </c>
       <c r="Z59" t="n">
-        <v>487.3905</v>
+        <v>490.2745</v>
       </c>
       <c r="AA59" t="n">
-        <v>431.4557</v>
+        <v>431.7147</v>
       </c>
       <c r="AB59" t="n">
         <v>535.3375423278808</v>
@@ -8092,84 +8435,84 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>5 okt</t>
+          <t>6 okt</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>42.645</v>
+        <v>42.86</v>
       </c>
       <c r="C60" t="n">
-        <v>43.11</v>
+        <v>43.285</v>
       </c>
       <c r="D60" t="n">
-        <v>42.35</v>
+        <v>42.43</v>
       </c>
       <c r="E60" t="n">
-        <v>42.865</v>
+        <v>43.185</v>
       </c>
       <c r="F60" t="n">
-        <v>40.2347</v>
+        <v>40.349</v>
       </c>
       <c r="G60" t="n">
-        <v>36.3069</v>
+        <v>36.3726</v>
       </c>
       <c r="H60" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I60" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>5 okt</t>
+          <t>6 okt</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>185.06</v>
+        <v>186.56</v>
       </c>
       <c r="M60" t="n">
-        <v>188.5</v>
+        <v>190.22</v>
       </c>
       <c r="N60" t="n">
-        <v>184.66</v>
+        <v>186.06</v>
       </c>
       <c r="O60" t="n">
-        <v>185.04</v>
+        <v>188.6</v>
       </c>
       <c r="P60" t="n">
-        <v>180.5192</v>
+        <v>181.1064</v>
       </c>
       <c r="Q60" t="n">
-        <v>164.3515</v>
+        <v>164.2647</v>
       </c>
       <c r="R60" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S60" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>5 okt</t>
+          <t>6 okt</t>
         </is>
       </c>
       <c r="V60" t="n">
-        <v>521.62</v>
+        <v>531.6799999999999</v>
       </c>
       <c r="W60" t="n">
-        <v>532.35</v>
+        <v>535.6900000000001</v>
       </c>
       <c r="X60" t="n">
-        <v>521.47</v>
+        <v>528.78</v>
       </c>
       <c r="Y60" t="n">
-        <v>525.1799999999999</v>
+        <v>529.3</v>
       </c>
       <c r="Z60" t="n">
-        <v>490.2745</v>
+        <v>493.0931</v>
       </c>
       <c r="AA60" t="n">
-        <v>431.7147</v>
+        <v>431.9956</v>
       </c>
       <c r="AB60" t="n">
         <v>535.3375423278808</v>
@@ -8181,84 +8524,84 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>6 okt</t>
+          <t>7 okt</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>42.86</v>
+        <v>43.37</v>
       </c>
       <c r="C61" t="n">
-        <v>43.285</v>
+        <v>43.835</v>
       </c>
       <c r="D61" t="n">
-        <v>42.43</v>
+        <v>43.145</v>
       </c>
       <c r="E61" t="n">
-        <v>43.185</v>
+        <v>43.25</v>
       </c>
       <c r="F61" t="n">
-        <v>40.349</v>
+        <v>40.4451</v>
       </c>
       <c r="G61" t="n">
-        <v>36.3726</v>
+        <v>36.4388</v>
       </c>
       <c r="H61" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I61" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>6 okt</t>
+          <t>7 okt</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>186.56</v>
+        <v>187</v>
       </c>
       <c r="M61" t="n">
-        <v>190.22</v>
+        <v>188.72</v>
       </c>
       <c r="N61" t="n">
-        <v>186.06</v>
+        <v>186.04</v>
       </c>
       <c r="O61" t="n">
-        <v>188.6</v>
+        <v>187.62</v>
       </c>
       <c r="P61" t="n">
-        <v>181.1064</v>
+        <v>181.618</v>
       </c>
       <c r="Q61" t="n">
-        <v>164.2647</v>
+        <v>164.1762</v>
       </c>
       <c r="R61" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S61" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>6 okt</t>
+          <t>7 okt</t>
         </is>
       </c>
       <c r="V61" t="n">
-        <v>531.6799999999999</v>
+        <v>530.73</v>
       </c>
       <c r="W61" t="n">
-        <v>535.6900000000001</v>
+        <v>531.73</v>
       </c>
       <c r="X61" t="n">
-        <v>528.78</v>
+        <v>524.6900000000001</v>
       </c>
       <c r="Y61" t="n">
-        <v>529.3</v>
+        <v>529.76</v>
       </c>
       <c r="Z61" t="n">
-        <v>493.0931</v>
+        <v>495.8361</v>
       </c>
       <c r="AA61" t="n">
-        <v>431.9956</v>
+        <v>432.2398</v>
       </c>
       <c r="AB61" t="n">
         <v>535.3375423278808</v>
@@ -8270,84 +8613,84 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>7 okt</t>
+          <t>8 okt</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>43.37</v>
+        <v>43.555</v>
       </c>
       <c r="C62" t="n">
-        <v>43.835</v>
+        <v>44.815</v>
       </c>
       <c r="D62" t="n">
-        <v>43.145</v>
+        <v>43.5425</v>
       </c>
       <c r="E62" t="n">
-        <v>43.25</v>
+        <v>44.75</v>
       </c>
       <c r="F62" t="n">
-        <v>40.4451</v>
+        <v>40.5699</v>
       </c>
       <c r="G62" t="n">
-        <v>36.4388</v>
+        <v>36.5123</v>
       </c>
       <c r="H62" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I62" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>7 okt</t>
+          <t>8 okt</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>187</v>
+        <v>187.04</v>
       </c>
       <c r="M62" t="n">
-        <v>188.72</v>
+        <v>189.82</v>
       </c>
       <c r="N62" t="n">
-        <v>186.04</v>
+        <v>183.76</v>
       </c>
       <c r="O62" t="n">
-        <v>187.62</v>
+        <v>184.62</v>
       </c>
       <c r="P62" t="n">
-        <v>181.618</v>
+        <v>182.192</v>
       </c>
       <c r="Q62" t="n">
-        <v>164.1762</v>
+        <v>164.074</v>
       </c>
       <c r="R62" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S62" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>7 okt</t>
+          <t>8 okt</t>
         </is>
       </c>
       <c r="V62" t="n">
-        <v>530.73</v>
+        <v>529.8099999999999</v>
       </c>
       <c r="W62" t="n">
-        <v>531.73</v>
+        <v>533.51</v>
       </c>
       <c r="X62" t="n">
-        <v>524.6900000000001</v>
+        <v>518.79</v>
       </c>
       <c r="Y62" t="n">
-        <v>529.76</v>
+        <v>522.61</v>
       </c>
       <c r="Z62" t="n">
-        <v>495.8361</v>
+        <v>498.4921</v>
       </c>
       <c r="AA62" t="n">
-        <v>432.2398</v>
+        <v>432.4385</v>
       </c>
       <c r="AB62" t="n">
         <v>535.3375423278808</v>
@@ -8359,84 +8702,84 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>8 okt</t>
+          <t>9 okt</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>43.555</v>
+        <v>44.42</v>
       </c>
       <c r="C63" t="n">
-        <v>44.815</v>
+        <v>45.155</v>
       </c>
       <c r="D63" t="n">
-        <v>43.5425</v>
+        <v>43.94</v>
       </c>
       <c r="E63" t="n">
-        <v>44.75</v>
+        <v>45.035</v>
       </c>
       <c r="F63" t="n">
-        <v>40.5699</v>
+        <v>40.6842</v>
       </c>
       <c r="G63" t="n">
-        <v>36.5123</v>
+        <v>36.5866</v>
       </c>
       <c r="H63" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I63" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>8 okt</t>
+          <t>9 okt</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>187.04</v>
+        <v>188.98</v>
       </c>
       <c r="M63" t="n">
-        <v>189.82</v>
+        <v>192.58</v>
       </c>
       <c r="N63" t="n">
-        <v>183.76</v>
+        <v>188.86</v>
       </c>
       <c r="O63" t="n">
-        <v>184.62</v>
+        <v>191.46</v>
       </c>
       <c r="P63" t="n">
-        <v>182.192</v>
+        <v>182.8676</v>
       </c>
       <c r="Q63" t="n">
-        <v>164.074</v>
+        <v>164.0101</v>
       </c>
       <c r="R63" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S63" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>8 okt</t>
+          <t>9 okt</t>
         </is>
       </c>
       <c r="V63" t="n">
-        <v>529.8099999999999</v>
+        <v>528.24</v>
       </c>
       <c r="W63" t="n">
-        <v>533.51</v>
+        <v>537.22</v>
       </c>
       <c r="X63" t="n">
-        <v>518.79</v>
+        <v>526.24</v>
       </c>
       <c r="Y63" t="n">
-        <v>522.61</v>
+        <v>535.0700000000001</v>
       </c>
       <c r="Z63" t="n">
-        <v>498.4921</v>
+        <v>500.1885</v>
       </c>
       <c r="AA63" t="n">
-        <v>432.4385</v>
+        <v>432.7046</v>
       </c>
       <c r="AB63" t="n">
         <v>535.3375423278808</v>
@@ -8448,84 +8791,84 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>9 okt</t>
+          <t>12 okt</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>44.42</v>
+        <v>44.725</v>
       </c>
       <c r="C64" t="n">
-        <v>45.155</v>
+        <v>45.81</v>
       </c>
       <c r="D64" t="n">
-        <v>43.94</v>
+        <v>44.695</v>
       </c>
       <c r="E64" t="n">
-        <v>45.035</v>
+        <v>45.56</v>
       </c>
       <c r="F64" t="n">
-        <v>40.6842</v>
+        <v>40.8072</v>
       </c>
       <c r="G64" t="n">
-        <v>36.5866</v>
+        <v>36.6625</v>
       </c>
       <c r="H64" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I64" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>9 okt</t>
+          <t>12 okt</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>188.98</v>
+        <v>190.58</v>
       </c>
       <c r="M64" t="n">
-        <v>192.58</v>
+        <v>197.88</v>
       </c>
       <c r="N64" t="n">
-        <v>188.86</v>
+        <v>189.78</v>
       </c>
       <c r="O64" t="n">
-        <v>191.46</v>
+        <v>194.46</v>
       </c>
       <c r="P64" t="n">
-        <v>182.8676</v>
+        <v>183.464</v>
       </c>
       <c r="Q64" t="n">
-        <v>164.0101</v>
+        <v>163.9576</v>
       </c>
       <c r="R64" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S64" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>9 okt</t>
+          <t>12 okt</t>
         </is>
       </c>
       <c r="V64" t="n">
-        <v>528.24</v>
+        <v>537.53</v>
       </c>
       <c r="W64" t="n">
-        <v>537.22</v>
+        <v>542.74</v>
       </c>
       <c r="X64" t="n">
-        <v>526.24</v>
+        <v>535.7</v>
       </c>
       <c r="Y64" t="n">
-        <v>535.0700000000001</v>
+        <v>541.15</v>
       </c>
       <c r="Z64" t="n">
-        <v>500.1885</v>
+        <v>501.7346</v>
       </c>
       <c r="AA64" t="n">
-        <v>432.7046</v>
+        <v>432.9914</v>
       </c>
       <c r="AB64" t="n">
         <v>535.3375423278808</v>
@@ -8537,84 +8880,84 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>12 okt</t>
+          <t>13 okt</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>44.725</v>
+        <v>45.69</v>
       </c>
       <c r="C65" t="n">
-        <v>45.81</v>
+        <v>45.97</v>
       </c>
       <c r="D65" t="n">
-        <v>44.695</v>
+        <v>45.35</v>
       </c>
       <c r="E65" t="n">
-        <v>45.56</v>
+        <v>45.95</v>
       </c>
       <c r="F65" t="n">
-        <v>40.8072</v>
+        <v>40.9565</v>
       </c>
       <c r="G65" t="n">
-        <v>36.6625</v>
+        <v>36.7398</v>
       </c>
       <c r="H65" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I65" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>12 okt</t>
+          <t>13 okt</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>190.58</v>
+        <v>196</v>
       </c>
       <c r="M65" t="n">
-        <v>197.88</v>
+        <v>198.18</v>
       </c>
       <c r="N65" t="n">
-        <v>189.78</v>
+        <v>194.02</v>
       </c>
       <c r="O65" t="n">
-        <v>194.46</v>
+        <v>197.28</v>
       </c>
       <c r="P65" t="n">
-        <v>183.464</v>
+        <v>184.062</v>
       </c>
       <c r="Q65" t="n">
-        <v>163.9576</v>
+        <v>163.9196</v>
       </c>
       <c r="R65" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S65" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>12 okt</t>
+          <t>13 okt</t>
         </is>
       </c>
       <c r="V65" t="n">
-        <v>537.53</v>
+        <v>544.64</v>
       </c>
       <c r="W65" t="n">
-        <v>542.74</v>
+        <v>551.15</v>
       </c>
       <c r="X65" t="n">
-        <v>535.7</v>
+        <v>543.0599999999999</v>
       </c>
       <c r="Y65" t="n">
-        <v>541.15</v>
+        <v>543.45</v>
       </c>
       <c r="Z65" t="n">
-        <v>501.7346</v>
+        <v>502.8689</v>
       </c>
       <c r="AA65" t="n">
-        <v>432.9914</v>
+        <v>433.2839</v>
       </c>
       <c r="AB65" t="n">
         <v>535.3375423278808</v>
@@ -8626,84 +8969,84 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>13 okt</t>
+          <t>15 okt</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>45.69</v>
+        <v>46.295</v>
       </c>
       <c r="C66" t="n">
-        <v>45.97</v>
+        <v>46.635</v>
       </c>
       <c r="D66" t="n">
-        <v>45.35</v>
+        <v>46.29</v>
       </c>
       <c r="E66" t="n">
-        <v>45.95</v>
+        <v>46.295</v>
       </c>
       <c r="F66" t="n">
-        <v>40.9565</v>
+        <v>41.1218</v>
       </c>
       <c r="G66" t="n">
-        <v>36.7398</v>
+        <v>36.8175</v>
       </c>
       <c r="H66" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I66" t="n">
-        <v>43.23680321420942</v>
+        <v>43.5896418435233</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>13 okt</t>
+          <t>15 okt</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>196</v>
+        <v>199.48</v>
       </c>
       <c r="M66" t="n">
-        <v>198.18</v>
+        <v>200.85</v>
       </c>
       <c r="N66" t="n">
-        <v>194.02</v>
+        <v>198</v>
       </c>
       <c r="O66" t="n">
-        <v>197.28</v>
+        <v>200.5</v>
       </c>
       <c r="P66" t="n">
-        <v>184.062</v>
+        <v>184.6868</v>
       </c>
       <c r="Q66" t="n">
-        <v>163.9196</v>
+        <v>163.9292</v>
       </c>
       <c r="R66" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S66" t="n">
-        <v>181.0157045636858</v>
+        <v>184.3707068307059</v>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>13 okt</t>
+          <t>14 okt</t>
         </is>
       </c>
       <c r="V66" t="n">
-        <v>544.64</v>
+        <v>545.27</v>
       </c>
       <c r="W66" t="n">
-        <v>551.15</v>
+        <v>545.75</v>
       </c>
       <c r="X66" t="n">
-        <v>543.0599999999999</v>
+        <v>532.54</v>
       </c>
       <c r="Y66" t="n">
-        <v>543.45</v>
+        <v>533.6900000000001</v>
       </c>
       <c r="Z66" t="n">
-        <v>502.8689</v>
+        <v>503.705</v>
       </c>
       <c r="AA66" t="n">
-        <v>433.2839</v>
+        <v>433.5292</v>
       </c>
       <c r="AB66" t="n">
         <v>535.3375423278808</v>

--- a/rapporten/trend-agent.xlsx
+++ b/rapporten/trend-agent.xlsx
@@ -2046,7 +2046,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>10029.19</v>
+        <v>10024.69</v>
       </c>
       <c r="C5" s="2">
         <f>B5-B4</f>
@@ -2201,24 +2201,24 @@
     <row r="6" ht="22" customHeight="1">
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Shell (SHELL.AS)  ·  46,29 EUR</t>
+          <t>Shell (SHELL.AS)  ·  46,42 EUR</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>SAP (SAP.DE)  ·  200,50 EUR</t>
+          <t>SAP (SAP.DE)  ·  197,44 EUR</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>Gestegen: 25,5% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +2,7% (winst). De bot verkoopt als de koers onder 43,59 zakt (-5,8%).</t>
+          <t>Gestegen: 25,9% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +3,0% (winst). De bot verkoopt als de koers onder 43,70 zakt (-5,9%).</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>Gestegen: 45,7% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +4,7% (winst). De bot verkoopt als de koers onder 184,37 zakt (-8,0%).</t>
+          <t>Gestegen: 43,4% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +3,1% (winst). De bot verkoopt als de koers onder 181,20 zakt (-8,2%).</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
         <v>45.06</v>
       </c>
       <c r="F2" t="n">
-        <v>43.59</v>
+        <v>43.7</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>191.56</v>
       </c>
       <c r="F3" t="n">
-        <v>184.37</v>
+        <v>181.2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -2711,19 +2711,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.148</v>
+        <v>0.153</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.2293077511599</v>
+        <v>0.2326269751575816</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.08419197521715405</v>
+        <v>0.08711937563323313</v>
       </c>
       <c r="H2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="I2" t="n">
-        <v>46.29</v>
+        <v>46.42</v>
       </c>
     </row>
     <row r="3">
@@ -2746,19 +2746,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.119</v>
+        <v>0.111</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.4537413186041173</v>
+        <v>0.4315545610691773</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.07173400704295707</v>
+        <v>0.05537738138204262</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>200.5</v>
+        <v>197.44</v>
       </c>
     </row>
     <row r="4">
@@ -2767,33 +2767,33 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>WKL.AS</t>
+          <t>XLE</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Wolters Kluwer</t>
+          <t>Energie-ETF</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.116</v>
+        <v>0.106</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.3133184485032652</v>
+        <v>0.1931250609053237</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.1645312027016144</v>
+        <v>0.03188213977858134</v>
       </c>
       <c r="H4" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="I4" t="n">
-        <v>79.98</v>
+        <v>67.63</v>
       </c>
     </row>
     <row r="5">
@@ -2802,33 +2802,33 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>XLE</t>
+          <t>WKL.AS</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Energie-ETF</t>
+          <t>Wolters Kluwer</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.106</v>
+        <v>0.105</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.1931250609053237</v>
+        <v>0.2831045068412423</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.03188213977858134</v>
+        <v>0.1377402306703215</v>
       </c>
       <c r="H5" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="I5" t="n">
-        <v>67.63</v>
+        <v>78.14</v>
       </c>
     </row>
     <row r="6">
@@ -2921,19 +2921,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.082</v>
+        <v>0.079</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.1572873705295681</v>
+        <v>0.1514047516541992</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.0137947190612262</v>
+        <v>0.008641489101263833</v>
       </c>
       <c r="H8" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="I8" t="n">
-        <v>80.66</v>
+        <v>80.25</v>
       </c>
     </row>
     <row r="9">
@@ -3331,7 +3331,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I2" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S2" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I3" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S3" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I4" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S4" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I5" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S5" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I6" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S6" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I7" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -3772,7 +3772,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S7" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -3832,7 +3832,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I8" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S8" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I9" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S9" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I10" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S10" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -4099,7 +4099,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I11" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S11" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I12" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S12" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I13" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -4306,7 +4306,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S13" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I14" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S14" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I15" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S15" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -4544,7 +4544,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I16" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S16" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I17" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S17" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I18" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S18" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I19" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S19" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I20" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S20" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I21" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S21" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I22" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -5107,7 +5107,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S22" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I23" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -5196,7 +5196,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S23" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
@@ -5256,7 +5256,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I24" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -5285,7 +5285,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S24" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I25" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S25" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
@@ -5434,7 +5434,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I26" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S26" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I27" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S27" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
@@ -5612,7 +5612,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I28" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S28" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I29" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -5730,7 +5730,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S29" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
@@ -5790,7 +5790,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I30" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S30" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>421.046</v>
       </c>
       <c r="AA30" t="n">
-        <v>429.3186</v>
+        <v>429.3185</v>
       </c>
       <c r="AB30" t="n">
         <v>535.3375423278808</v>
@@ -5879,7 +5879,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I31" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -5908,7 +5908,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S31" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I32" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S32" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U32" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I33" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -6086,7 +6086,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S33" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I34" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S34" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U34" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I35" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -6264,7 +6264,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S35" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I36" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S36" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I37" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S37" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U37" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I38" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S38" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I39" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S39" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U39" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I40" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S40" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U40" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I41" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S41" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U41" t="inlineStr">
         <is>
@@ -6858,7 +6858,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I42" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S42" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U42" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I43" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S43" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>453.115</v>
       </c>
       <c r="AA43" t="n">
-        <v>429.654</v>
+        <v>429.6539</v>
       </c>
       <c r="AB43" t="n">
         <v>535.3375423278808</v>
@@ -7036,7 +7036,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I44" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S44" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U44" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I45" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -7154,7 +7154,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S45" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I46" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S46" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U46" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I47" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S47" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U47" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I48" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S48" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U48" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I49" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -7510,7 +7510,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S49" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
@@ -7570,7 +7570,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I50" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -7599,7 +7599,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S50" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U50" t="inlineStr">
         <is>
@@ -7659,7 +7659,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I51" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S51" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U51" t="inlineStr">
         <is>
@@ -7748,7 +7748,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I52" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S52" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U52" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I53" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S53" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U53" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I54" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S54" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U54" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I55" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -8044,7 +8044,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S55" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U55" t="inlineStr">
         <is>
@@ -8104,7 +8104,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I56" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -8133,7 +8133,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S56" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U56" t="inlineStr">
         <is>
@@ -8193,7 +8193,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I57" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -8222,7 +8222,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S57" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U57" t="inlineStr">
         <is>
@@ -8282,7 +8282,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I58" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S58" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U58" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I59" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S59" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U59" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I60" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -8489,7 +8489,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S60" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U60" t="inlineStr">
         <is>
@@ -8549,7 +8549,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I61" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S61" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I62" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -8667,7 +8667,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S62" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U62" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I63" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S63" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>
@@ -8816,7 +8816,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I64" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -8845,7 +8845,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S64" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U64" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
         <v>45.05751734733581</v>
       </c>
       <c r="I65" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -8934,7 +8934,7 @@
         <v>191.5557367172241</v>
       </c>
       <c r="S65" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U65" t="inlineStr">
         <is>
@@ -8969,61 +8969,61 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>15 okt</t>
+          <t>14 okt</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>46.295</v>
+        <v>45.95</v>
       </c>
       <c r="C66" t="n">
-        <v>46.635</v>
+        <v>46.675</v>
       </c>
       <c r="D66" t="n">
-        <v>46.29</v>
+        <v>45.91</v>
       </c>
       <c r="E66" t="n">
-        <v>46.295</v>
+        <v>46.42</v>
       </c>
       <c r="F66" t="n">
-        <v>41.1218</v>
+        <v>41.1243</v>
       </c>
       <c r="G66" t="n">
-        <v>36.8175</v>
+        <v>36.8181</v>
       </c>
       <c r="H66" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I66" t="n">
-        <v>43.5896418435233</v>
+        <v>43.69749859401158</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>15 okt</t>
+          <t>14 okt</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>199.48</v>
+        <v>196.6</v>
       </c>
       <c r="M66" t="n">
-        <v>200.85</v>
+        <v>199.36</v>
       </c>
       <c r="N66" t="n">
-        <v>198</v>
+        <v>195.26</v>
       </c>
       <c r="O66" t="n">
-        <v>200.5</v>
+        <v>197.44</v>
       </c>
       <c r="P66" t="n">
-        <v>184.6868</v>
+        <v>184.6256</v>
       </c>
       <c r="Q66" t="n">
-        <v>163.9292</v>
+        <v>163.9139</v>
       </c>
       <c r="R66" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S66" t="n">
-        <v>184.3707068307059</v>
+        <v>181.19713810512</v>
       </c>
       <c r="U66" t="inlineStr">
         <is>

--- a/rapporten/trend-agent.xlsx
+++ b/rapporten/trend-agent.xlsx
@@ -2046,7 +2046,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>10024.69</v>
+        <v>10024.11</v>
       </c>
       <c r="C5" s="2">
         <f>B5-B4</f>

--- a/rapporten/trend-agent.xlsx
+++ b/rapporten/trend-agent.xlsx
@@ -607,7 +607,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="47.5"/>
+          <max val="50"/>
           <min val="32.5"/>
         </scaling>
         <delete val="0"/>
@@ -1944,7 +1944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2058,6 +2058,28 @@
       </c>
       <c r="E5" s="3">
         <f>B5/$B$2-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>10038.89</v>
+      </c>
+      <c r="C6" s="2">
+        <f>B6-B5</f>
+        <v/>
+      </c>
+      <c r="D6" s="3">
+        <f>B6/B5-1</f>
+        <v/>
+      </c>
+      <c r="E6" s="3">
+        <f>B6/$B$2-1</f>
         <v/>
       </c>
     </row>
@@ -2201,38 +2223,38 @@
     <row r="6" ht="22" customHeight="1">
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Shell (SHELL.AS)  ·  46,42 EUR</t>
+          <t>Shell (SHELL.AS)  ·  46,47 EUR</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>SAP (SAP.DE)  ·  197,44 EUR</t>
+          <t>SAP (SAP.DE)  ·  201,70 EUR</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>Gestegen: 25,9% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +3,0% (winst). De bot verkoopt als de koers onder 43,70 zakt (-5,9%).</t>
+          <t>Gestegen: 23,4% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +3,1% (winst). De bot verkoopt als de koers onder 43,77 zakt (-5,8%).</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>Gestegen: 43,4% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +3,1% (winst). De bot verkoopt als de koers onder 181,20 zakt (-8,2%).</t>
+          <t>Gestegen: 46,2% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +5,3% (winst). De bot verkoopt als de koers onder 184,62 zakt (-8,5%).</t>
         </is>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Microsoft (MSFT)  ·  533,69 USD</t>
+          <t>Microsoft (MSFT)  ·  539,33 USD</t>
         </is>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Gestegen: 35,2% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: -0,3% (verlies). De bot verkoopt als de koers onder 509,90 zakt (-4,5%).</t>
+          <t>Gestegen: 34,7% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +0,7% (winst). De bot verkoopt als de koers onder 509,90 zakt (-5,5%).</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2355,7 @@
         <v>45.06</v>
       </c>
       <c r="F2" t="n">
-        <v>43.7</v>
+        <v>43.77</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2372,7 +2394,7 @@
         <v>191.56</v>
       </c>
       <c r="F3" t="n">
-        <v>181.2</v>
+        <v>184.62</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -2711,19 +2733,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.153</v>
+        <v>0.164</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.2326269751575816</v>
+        <v>0.2381862222388915</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.08711937563323313</v>
+        <v>0.1110579885961303</v>
       </c>
       <c r="H2" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="I2" t="n">
-        <v>46.42</v>
+        <v>46.47</v>
       </c>
     </row>
     <row r="3">
@@ -2732,12 +2754,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SAP.DE</t>
+          <t>WKL.AS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Wolters Kluwer</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2746,19 +2768,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.111</v>
+        <v>0.124</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.4315545610691773</v>
+        <v>0.3405060169515768</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.05537738138204262</v>
+        <v>0.1789658335213713</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.16</v>
       </c>
       <c r="I3" t="n">
-        <v>197.44</v>
+        <v>81.16</v>
       </c>
     </row>
     <row r="4">
@@ -2767,33 +2789,33 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>XLE</t>
+          <t>SAP.DE</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Energie-ETF</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.106</v>
+        <v>0.121</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.1931250609053237</v>
+        <v>0.458845689005648</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.03188213977858134</v>
+        <v>0.08115351408542626</v>
       </c>
       <c r="H4" t="n">
-        <v>1.08</v>
+        <v>0.84</v>
       </c>
       <c r="I4" t="n">
-        <v>67.63</v>
+        <v>201.7</v>
       </c>
     </row>
     <row r="5">
@@ -2802,33 +2824,33 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>WKL.AS</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Wolters Kluwer</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.105</v>
+        <v>0.107</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.2831045068412423</v>
+        <v>0.3720616506602334</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.1377402306703215</v>
+        <v>0.1000000622426656</v>
       </c>
       <c r="H5" t="n">
-        <v>1.16</v>
+        <v>0.92</v>
       </c>
       <c r="I5" t="n">
-        <v>78.14</v>
+        <v>539.33</v>
       </c>
     </row>
     <row r="6">
@@ -2851,19 +2873,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.101</v>
+        <v>0.095</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.2206657103115155</v>
+        <v>0.1928670152973544</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.04541688430175994</v>
+        <v>0.06937292471322043</v>
       </c>
       <c r="H6" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="I6" t="n">
-        <v>177.01</v>
+        <v>174.65</v>
       </c>
     </row>
     <row r="7">
@@ -2872,12 +2894,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>XLE</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Energie-ETF</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2886,19 +2908,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.093</v>
+        <v>0.094</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.3330707534804345</v>
+        <v>0.1606375865113454</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.07356374252377029</v>
+        <v>0.04553455585461719</v>
       </c>
       <c r="H7" t="n">
-        <v>0.84</v>
+        <v>1.07</v>
       </c>
       <c r="I7" t="n">
-        <v>533.6900000000001</v>
+        <v>66.55</v>
       </c>
     </row>
     <row r="8">
@@ -2907,33 +2929,33 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TTE.PA</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TotalEnergies</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.079</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.1514047516541992</v>
+        <v>0.1165282612920207</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.008641489101263833</v>
+        <v>0.0772922491948338</v>
       </c>
       <c r="H8" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="I8" t="n">
-        <v>80.25</v>
+        <v>399.6</v>
       </c>
     </row>
     <row r="9">
@@ -2942,33 +2964,33 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>TTE.PA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Palantir</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.076</v>
+        <v>0.079</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.4948675808622736</v>
+        <v>0.1426303106972868</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.1646384101996907</v>
+        <v>0.01570314902035075</v>
       </c>
       <c r="H9" t="n">
-        <v>0.71</v>
+        <v>1.12</v>
       </c>
       <c r="I9" t="n">
-        <v>200.97</v>
+        <v>80.34999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -2977,12 +2999,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Nasdaq-100 ETF</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2991,19 +3013,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.053</v>
+        <v>0.078</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.1107263312675328</v>
+        <v>0.04813342696777312</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.101280166976637</v>
+        <v>0.03416769022464061</v>
       </c>
       <c r="H10" t="n">
-        <v>1.16</v>
+        <v>1.41</v>
       </c>
       <c r="I10" t="n">
-        <v>737.54</v>
+        <v>728.04</v>
       </c>
     </row>
     <row r="11">
@@ -3012,12 +3034,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Palantir</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3026,19 +3048,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.052</v>
+        <v>0.077</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.07399126212527274</v>
+        <v>0.5145791857122965</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.04209040456874846</v>
+        <v>0.1500516474223639</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0.71</v>
       </c>
       <c r="I11" t="n">
-        <v>391.43</v>
+        <v>200.5</v>
       </c>
     </row>
   </sheetData>
@@ -3309,75 +3331,75 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>16 jul</t>
+          <t>17 jul</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>36.5803</v>
+        <v>36.912</v>
       </c>
       <c r="C2" t="n">
-        <v>37.011</v>
+        <v>37.8871</v>
       </c>
       <c r="D2" t="n">
-        <v>36.3724</v>
+        <v>36.912</v>
       </c>
       <c r="E2" t="n">
-        <v>36.8773</v>
+        <v>37.6594</v>
       </c>
       <c r="F2" t="n">
-        <v>35.6114</v>
+        <v>35.6614</v>
       </c>
       <c r="H2" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I2" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>16 jul</t>
+          <t>17 jul</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>137.2</v>
+        <v>140.6</v>
       </c>
       <c r="M2" t="n">
-        <v>138.24</v>
+        <v>141.54</v>
       </c>
       <c r="N2" t="n">
-        <v>135.14</v>
+        <v>137.32</v>
       </c>
       <c r="O2" t="n">
-        <v>137.64</v>
+        <v>137.92</v>
       </c>
       <c r="P2" t="n">
-        <v>144.8176</v>
+        <v>144.652</v>
       </c>
       <c r="R2" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S2" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>15 jul</t>
+          <t>16 jul</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>387.0713</v>
+        <v>397.5616</v>
       </c>
       <c r="W2" t="n">
-        <v>398.2104</v>
+        <v>405.2271</v>
       </c>
       <c r="X2" t="n">
-        <v>385.674</v>
+        <v>391.3133</v>
       </c>
       <c r="Y2" t="n">
-        <v>394.8866</v>
+        <v>400.3463</v>
       </c>
       <c r="Z2" t="n">
-        <v>401.1249</v>
+        <v>400.8928</v>
       </c>
       <c r="AB2" t="n">
         <v>535.3375423278808</v>
@@ -3389,75 +3411,75 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>17 jul</t>
+          <t>20 jul</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>36.912</v>
+        <v>38.0653</v>
       </c>
       <c r="C3" t="n">
-        <v>37.8871</v>
+        <v>38.1742</v>
       </c>
       <c r="D3" t="n">
-        <v>36.912</v>
+        <v>37.1496</v>
       </c>
       <c r="E3" t="n">
-        <v>37.6594</v>
+        <v>37.5307</v>
       </c>
       <c r="F3" t="n">
-        <v>35.6614</v>
+        <v>35.7021</v>
       </c>
       <c r="H3" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I3" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>17 jul</t>
+          <t>20 jul</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>140.6</v>
+        <v>138</v>
       </c>
       <c r="M3" t="n">
-        <v>141.54</v>
+        <v>140.04</v>
       </c>
       <c r="N3" t="n">
-        <v>137.32</v>
+        <v>134.98</v>
       </c>
       <c r="O3" t="n">
-        <v>137.92</v>
+        <v>138.26</v>
       </c>
       <c r="P3" t="n">
-        <v>144.652</v>
+        <v>144.528</v>
       </c>
       <c r="R3" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S3" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>16 jul</t>
+          <t>17 jul</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>397.5616</v>
+        <v>394.118</v>
       </c>
       <c r="W3" t="n">
-        <v>405.2271</v>
+        <v>397.6414</v>
       </c>
       <c r="X3" t="n">
-        <v>391.3133</v>
+        <v>388.6583</v>
       </c>
       <c r="Y3" t="n">
-        <v>400.3463</v>
+        <v>393.08</v>
       </c>
       <c r="Z3" t="n">
-        <v>400.8928</v>
+        <v>400.5601</v>
       </c>
       <c r="AB3" t="n">
         <v>535.3375423278808</v>
@@ -3469,75 +3491,75 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20 jul</t>
+          <t>21 jul</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38.0653</v>
+        <v>37.5703</v>
       </c>
       <c r="C4" t="n">
-        <v>38.1742</v>
+        <v>37.8277</v>
       </c>
       <c r="D4" t="n">
-        <v>37.1496</v>
+        <v>37.4169</v>
       </c>
       <c r="E4" t="n">
-        <v>37.5307</v>
+        <v>37.8277</v>
       </c>
       <c r="F4" t="n">
-        <v>35.7021</v>
+        <v>35.7452</v>
       </c>
       <c r="H4" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I4" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>20 jul</t>
+          <t>21 jul</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>138</v>
+        <v>137.74</v>
       </c>
       <c r="M4" t="n">
-        <v>140.04</v>
+        <v>137.84</v>
       </c>
       <c r="N4" t="n">
-        <v>134.98</v>
+        <v>135.34</v>
       </c>
       <c r="O4" t="n">
-        <v>138.26</v>
+        <v>136.42</v>
       </c>
       <c r="P4" t="n">
-        <v>144.528</v>
+        <v>144.4084</v>
       </c>
       <c r="R4" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S4" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>17 jul</t>
+          <t>20 jul</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>394.118</v>
+        <v>390.6746</v>
       </c>
       <c r="W4" t="n">
-        <v>397.6414</v>
+        <v>402.4224</v>
       </c>
       <c r="X4" t="n">
-        <v>388.6583</v>
+        <v>388.9179</v>
       </c>
       <c r="Y4" t="n">
-        <v>393.08</v>
+        <v>401.5341</v>
       </c>
       <c r="Z4" t="n">
-        <v>400.5601</v>
+        <v>400.345</v>
       </c>
       <c r="AB4" t="n">
         <v>535.3375423278808</v>
@@ -3549,75 +3571,75 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>21 jul</t>
+          <t>22 jul</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>37.5703</v>
+        <v>38.095</v>
       </c>
       <c r="C5" t="n">
-        <v>37.8277</v>
+        <v>38.6098</v>
       </c>
       <c r="D5" t="n">
-        <v>37.4169</v>
+        <v>37.9267</v>
       </c>
       <c r="E5" t="n">
-        <v>37.8277</v>
+        <v>38.2682</v>
       </c>
       <c r="F5" t="n">
-        <v>35.7452</v>
+        <v>35.799</v>
       </c>
       <c r="H5" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I5" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>21 jul</t>
+          <t>22 jul</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>137.74</v>
+        <v>136.02</v>
       </c>
       <c r="M5" t="n">
-        <v>137.84</v>
+        <v>136.4</v>
       </c>
       <c r="N5" t="n">
-        <v>135.34</v>
+        <v>132.04</v>
       </c>
       <c r="O5" t="n">
-        <v>136.42</v>
+        <v>132.04</v>
       </c>
       <c r="P5" t="n">
-        <v>144.4084</v>
+        <v>144.324</v>
       </c>
       <c r="R5" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S5" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>20 jul</t>
+          <t>21 jul</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>390.6746</v>
+        <v>398.0606</v>
       </c>
       <c r="W5" t="n">
-        <v>402.4224</v>
+        <v>400.7156</v>
       </c>
       <c r="X5" t="n">
-        <v>388.9179</v>
+        <v>395.5753</v>
       </c>
       <c r="Y5" t="n">
-        <v>401.5341</v>
+        <v>397.0026</v>
       </c>
       <c r="Z5" t="n">
-        <v>400.345</v>
+        <v>399.9036</v>
       </c>
       <c r="AB5" t="n">
         <v>535.3375423278808</v>
@@ -3629,84 +3651,84 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>22 jul</t>
+          <t>23 jul</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>38.095</v>
+        <v>38.491</v>
       </c>
       <c r="C6" t="n">
-        <v>38.6098</v>
+        <v>39.0454</v>
       </c>
       <c r="D6" t="n">
-        <v>37.9267</v>
+        <v>38.3425</v>
       </c>
       <c r="E6" t="n">
-        <v>38.2682</v>
+        <v>38.8028</v>
       </c>
       <c r="F6" t="n">
-        <v>35.799</v>
+        <v>35.863</v>
       </c>
       <c r="G6" t="n">
-        <v>33.7968</v>
+        <v>33.8375</v>
       </c>
       <c r="H6" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I6" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>22 jul</t>
+          <t>23 jul</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>136.02</v>
+        <v>131</v>
       </c>
       <c r="M6" t="n">
-        <v>136.4</v>
+        <v>132.42</v>
       </c>
       <c r="N6" t="n">
-        <v>132.04</v>
+        <v>127.5</v>
       </c>
       <c r="O6" t="n">
-        <v>132.04</v>
+        <v>128.32</v>
       </c>
       <c r="P6" t="n">
-        <v>144.324</v>
+        <v>144.066</v>
       </c>
       <c r="Q6" t="n">
-        <v>174.4005</v>
+        <v>173.9035</v>
       </c>
       <c r="R6" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S6" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>21 jul</t>
+          <t>22 jul</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>398.0606</v>
+        <v>398.8292</v>
       </c>
       <c r="W6" t="n">
-        <v>400.7156</v>
+        <v>400.2465</v>
       </c>
       <c r="X6" t="n">
-        <v>395.5753</v>
+        <v>386.2329</v>
       </c>
       <c r="Y6" t="n">
-        <v>397.0026</v>
+        <v>389.6066</v>
       </c>
       <c r="Z6" t="n">
-        <v>399.9036</v>
+        <v>399.4268</v>
       </c>
       <c r="AA6" t="n">
-        <v>435.882</v>
+        <v>435.2723</v>
       </c>
       <c r="AB6" t="n">
         <v>535.3375423278808</v>
@@ -3718,84 +3740,84 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>23 jul</t>
+          <t>24 jul</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>38.491</v>
+        <v>38.4019</v>
       </c>
       <c r="C7" t="n">
-        <v>39.0454</v>
+        <v>38.6593</v>
       </c>
       <c r="D7" t="n">
-        <v>38.3425</v>
+        <v>38.1594</v>
       </c>
       <c r="E7" t="n">
-        <v>38.8028</v>
+        <v>38.3871</v>
       </c>
       <c r="F7" t="n">
-        <v>35.863</v>
+        <v>35.9135</v>
       </c>
       <c r="G7" t="n">
-        <v>33.8375</v>
+        <v>33.8757</v>
       </c>
       <c r="H7" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I7" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>23 jul</t>
+          <t>24 jul</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>131</v>
+        <v>130.88</v>
       </c>
       <c r="M7" t="n">
-        <v>132.42</v>
+        <v>141.32</v>
       </c>
       <c r="N7" t="n">
-        <v>127.5</v>
+        <v>130.86</v>
       </c>
       <c r="O7" t="n">
-        <v>128.32</v>
+        <v>140.2</v>
       </c>
       <c r="P7" t="n">
-        <v>144.066</v>
+        <v>143.9888</v>
       </c>
       <c r="Q7" t="n">
-        <v>173.9035</v>
+        <v>173.4491</v>
       </c>
       <c r="R7" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S7" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>22 jul</t>
+          <t>23 jul</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>398.8292</v>
+        <v>389.2373</v>
       </c>
       <c r="W7" t="n">
-        <v>400.2465</v>
+        <v>391.0439</v>
       </c>
       <c r="X7" t="n">
-        <v>386.2329</v>
+        <v>376.6809</v>
       </c>
       <c r="Y7" t="n">
-        <v>389.6066</v>
+        <v>380.863</v>
       </c>
       <c r="Z7" t="n">
-        <v>399.4268</v>
+        <v>398.8242</v>
       </c>
       <c r="AA7" t="n">
-        <v>435.2723</v>
+        <v>434.611</v>
       </c>
       <c r="AB7" t="n">
         <v>535.3375423278808</v>
@@ -3807,84 +3829,84 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>24 jul</t>
+          <t>27 jul</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>38.4019</v>
+        <v>37.5802</v>
       </c>
       <c r="C8" t="n">
-        <v>38.6593</v>
+        <v>38.1099</v>
       </c>
       <c r="D8" t="n">
-        <v>38.1594</v>
+        <v>37.4317</v>
       </c>
       <c r="E8" t="n">
-        <v>38.3871</v>
+        <v>37.9515</v>
       </c>
       <c r="F8" t="n">
-        <v>35.9135</v>
+        <v>35.931</v>
       </c>
       <c r="G8" t="n">
-        <v>33.8757</v>
+        <v>33.9167</v>
       </c>
       <c r="H8" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I8" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>24 jul</t>
+          <t>27 jul</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>130.88</v>
+        <v>142.38</v>
       </c>
       <c r="M8" t="n">
-        <v>141.32</v>
+        <v>151.56</v>
       </c>
       <c r="N8" t="n">
-        <v>130.86</v>
+        <v>142</v>
       </c>
       <c r="O8" t="n">
-        <v>140.2</v>
+        <v>151.28</v>
       </c>
       <c r="P8" t="n">
-        <v>143.9888</v>
+        <v>144.0572</v>
       </c>
       <c r="Q8" t="n">
-        <v>173.4491</v>
+        <v>173.0393</v>
       </c>
       <c r="R8" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S8" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>23 jul</t>
+          <t>24 jul</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>389.2373</v>
+        <v>386.3227</v>
       </c>
       <c r="W8" t="n">
-        <v>391.0439</v>
+        <v>388.299</v>
       </c>
       <c r="X8" t="n">
-        <v>376.6809</v>
+        <v>379.9348</v>
       </c>
       <c r="Y8" t="n">
-        <v>380.863</v>
+        <v>380.9828</v>
       </c>
       <c r="Z8" t="n">
-        <v>398.8242</v>
+        <v>398.3214</v>
       </c>
       <c r="AA8" t="n">
-        <v>434.611</v>
+        <v>433.8946</v>
       </c>
       <c r="AB8" t="n">
         <v>535.3375423278808</v>
@@ -3896,84 +3918,84 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>27 jul</t>
+          <t>28 jul</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>37.5802</v>
+        <v>37.7139</v>
       </c>
       <c r="C9" t="n">
-        <v>38.1099</v>
+        <v>38.0109</v>
       </c>
       <c r="D9" t="n">
-        <v>37.4317</v>
+        <v>37.4713</v>
       </c>
       <c r="E9" t="n">
-        <v>37.9515</v>
+        <v>37.4713</v>
       </c>
       <c r="F9" t="n">
-        <v>35.931</v>
+        <v>35.9372</v>
       </c>
       <c r="G9" t="n">
-        <v>33.9167</v>
+        <v>33.9548</v>
       </c>
       <c r="H9" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I9" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>27 jul</t>
+          <t>28 jul</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>142.38</v>
+        <v>152.2</v>
       </c>
       <c r="M9" t="n">
-        <v>151.56</v>
+        <v>159.76</v>
       </c>
       <c r="N9" t="n">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="O9" t="n">
-        <v>151.28</v>
+        <v>159.24</v>
       </c>
       <c r="P9" t="n">
-        <v>144.0572</v>
+        <v>144.1076</v>
       </c>
       <c r="Q9" t="n">
-        <v>173.0393</v>
+        <v>172.6663</v>
       </c>
       <c r="R9" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S9" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>24 jul</t>
+          <t>27 jul</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>386.3227</v>
+        <v>389.347</v>
       </c>
       <c r="W9" t="n">
-        <v>388.299</v>
+        <v>393.4593</v>
       </c>
       <c r="X9" t="n">
-        <v>379.9348</v>
+        <v>387.261</v>
       </c>
       <c r="Y9" t="n">
-        <v>380.9828</v>
+        <v>388.3689</v>
       </c>
       <c r="Z9" t="n">
-        <v>398.3214</v>
+        <v>398.0172</v>
       </c>
       <c r="AA9" t="n">
-        <v>433.8946</v>
+        <v>433.238</v>
       </c>
       <c r="AB9" t="n">
         <v>535.3375423278808</v>
@@ -3985,84 +4007,84 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>28 jul</t>
+          <t>29 jul</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>37.7139</v>
+        <v>38.0653</v>
       </c>
       <c r="C10" t="n">
-        <v>38.0109</v>
+        <v>38.59</v>
       </c>
       <c r="D10" t="n">
-        <v>37.4713</v>
+        <v>37.7089</v>
       </c>
       <c r="E10" t="n">
-        <v>37.4713</v>
+        <v>38.4415</v>
       </c>
       <c r="F10" t="n">
-        <v>35.9372</v>
+        <v>35.9692</v>
       </c>
       <c r="G10" t="n">
-        <v>33.9548</v>
+        <v>33.9987</v>
       </c>
       <c r="H10" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I10" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>28 jul</t>
+          <t>29 jul</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>152.2</v>
+        <v>159.84</v>
       </c>
       <c r="M10" t="n">
-        <v>159.76</v>
+        <v>163.3</v>
       </c>
       <c r="N10" t="n">
-        <v>151</v>
+        <v>156.48</v>
       </c>
       <c r="O10" t="n">
-        <v>159.24</v>
+        <v>162.04</v>
       </c>
       <c r="P10" t="n">
-        <v>144.1076</v>
+        <v>144.28</v>
       </c>
       <c r="Q10" t="n">
-        <v>172.6663</v>
+        <v>172.343</v>
       </c>
       <c r="R10" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S10" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>27 jul</t>
+          <t>28 jul</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>389.347</v>
+        <v>392.4213</v>
       </c>
       <c r="W10" t="n">
-        <v>393.4593</v>
+        <v>399.5678</v>
       </c>
       <c r="X10" t="n">
-        <v>387.261</v>
+        <v>390.5647</v>
       </c>
       <c r="Y10" t="n">
-        <v>388.3689</v>
+        <v>392.6109</v>
       </c>
       <c r="Z10" t="n">
-        <v>398.0172</v>
+        <v>397.7139</v>
       </c>
       <c r="AA10" t="n">
-        <v>433.238</v>
+        <v>432.5982</v>
       </c>
       <c r="AB10" t="n">
         <v>535.3375423278808</v>
@@ -4074,84 +4096,84 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>29 jul</t>
+          <t>30 jul</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>38.0653</v>
+        <v>38.6098</v>
       </c>
       <c r="C11" t="n">
-        <v>38.59</v>
+        <v>39.1444</v>
       </c>
       <c r="D11" t="n">
-        <v>37.7089</v>
+        <v>38.3277</v>
       </c>
       <c r="E11" t="n">
-        <v>38.4415</v>
+        <v>38.5108</v>
       </c>
       <c r="F11" t="n">
-        <v>35.9692</v>
+        <v>35.9978</v>
       </c>
       <c r="G11" t="n">
-        <v>33.9987</v>
+        <v>34.0424</v>
       </c>
       <c r="H11" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I11" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>29 jul</t>
+          <t>30 jul</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>159.84</v>
+        <v>162.5</v>
       </c>
       <c r="M11" t="n">
-        <v>163.3</v>
+        <v>163.16</v>
       </c>
       <c r="N11" t="n">
-        <v>156.48</v>
+        <v>155.2</v>
       </c>
       <c r="O11" t="n">
-        <v>162.04</v>
+        <v>155.92</v>
       </c>
       <c r="P11" t="n">
-        <v>144.28</v>
+        <v>144.3804</v>
       </c>
       <c r="Q11" t="n">
-        <v>172.343</v>
+        <v>171.9849</v>
       </c>
       <c r="R11" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S11" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>28 jul</t>
+          <t>29 jul</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>392.4213</v>
+        <v>392.6608</v>
       </c>
       <c r="W11" t="n">
-        <v>399.5678</v>
+        <v>400.4961</v>
       </c>
       <c r="X11" t="n">
-        <v>390.5647</v>
+        <v>388.0095</v>
       </c>
       <c r="Y11" t="n">
-        <v>392.6109</v>
+        <v>389.8062</v>
       </c>
       <c r="Z11" t="n">
-        <v>397.7139</v>
+        <v>397.1057</v>
       </c>
       <c r="AA11" t="n">
-        <v>432.5982</v>
+        <v>431.9565</v>
       </c>
       <c r="AB11" t="n">
         <v>535.3375423278808</v>
@@ -4163,84 +4185,84 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>30 jul</t>
+          <t>31 jul</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>38.6098</v>
       </c>
       <c r="C12" t="n">
-        <v>39.1444</v>
+        <v>39.575</v>
       </c>
       <c r="D12" t="n">
-        <v>38.3277</v>
+        <v>38.4464</v>
       </c>
       <c r="E12" t="n">
-        <v>38.5108</v>
+        <v>39.3226</v>
       </c>
       <c r="F12" t="n">
-        <v>35.9978</v>
+        <v>36.0495</v>
       </c>
       <c r="G12" t="n">
-        <v>34.0424</v>
+        <v>34.0907</v>
       </c>
       <c r="H12" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I12" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>30 jul</t>
+          <t>31 jul</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>162.5</v>
+        <v>154.9</v>
       </c>
       <c r="M12" t="n">
-        <v>163.16</v>
+        <v>158.26</v>
       </c>
       <c r="N12" t="n">
-        <v>155.2</v>
+        <v>153.6</v>
       </c>
       <c r="O12" t="n">
-        <v>155.92</v>
+        <v>157.68</v>
       </c>
       <c r="P12" t="n">
-        <v>144.3804</v>
+        <v>144.4984</v>
       </c>
       <c r="Q12" t="n">
-        <v>171.9849</v>
+        <v>171.6292</v>
       </c>
       <c r="R12" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S12" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>29 jul</t>
+          <t>30 jul</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>392.6608</v>
+        <v>437.0772</v>
       </c>
       <c r="W12" t="n">
-        <v>400.4961</v>
+        <v>457.8281</v>
       </c>
       <c r="X12" t="n">
-        <v>388.0095</v>
+        <v>431.6275</v>
       </c>
       <c r="Y12" t="n">
-        <v>389.8062</v>
+        <v>450.2524</v>
       </c>
       <c r="Z12" t="n">
-        <v>397.1057</v>
+        <v>397.6741</v>
       </c>
       <c r="AA12" t="n">
-        <v>431.9565</v>
+        <v>431.6738</v>
       </c>
       <c r="AB12" t="n">
         <v>535.3375423278808</v>
@@ -4252,84 +4274,84 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>31 jul</t>
+          <t>3 aug</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>38.6098</v>
+        <v>38.3128</v>
       </c>
       <c r="C13" t="n">
-        <v>39.575</v>
+        <v>39.4067</v>
       </c>
       <c r="D13" t="n">
-        <v>38.4464</v>
+        <v>38.2138</v>
       </c>
       <c r="E13" t="n">
-        <v>39.3226</v>
+        <v>39.4067</v>
       </c>
       <c r="F13" t="n">
-        <v>36.0495</v>
+        <v>36.1112</v>
       </c>
       <c r="G13" t="n">
-        <v>34.0907</v>
+        <v>34.1393</v>
       </c>
       <c r="H13" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I13" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>31 jul</t>
+          <t>3 aug</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>154.9</v>
+        <v>160</v>
       </c>
       <c r="M13" t="n">
-        <v>158.26</v>
+        <v>168.7</v>
       </c>
       <c r="N13" t="n">
-        <v>153.6</v>
+        <v>159.6</v>
       </c>
       <c r="O13" t="n">
-        <v>157.68</v>
+        <v>164.64</v>
       </c>
       <c r="P13" t="n">
-        <v>144.4984</v>
+        <v>144.7016</v>
       </c>
       <c r="Q13" t="n">
-        <v>171.6292</v>
+        <v>171.301</v>
       </c>
       <c r="R13" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S13" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>30 jul</t>
+          <t>31 jul</t>
         </is>
       </c>
       <c r="V13" t="n">
-        <v>437.0772</v>
+        <v>449.1545</v>
       </c>
       <c r="W13" t="n">
-        <v>457.8281</v>
+        <v>465.9628</v>
       </c>
       <c r="X13" t="n">
-        <v>431.6275</v>
+        <v>448.4857</v>
       </c>
       <c r="Y13" t="n">
-        <v>450.2524</v>
+        <v>463.8468</v>
       </c>
       <c r="Z13" t="n">
-        <v>397.6741</v>
+        <v>398.6364</v>
       </c>
       <c r="AA13" t="n">
-        <v>431.6738</v>
+        <v>431.4438</v>
       </c>
       <c r="AB13" t="n">
         <v>535.3375423278808</v>
@@ -4341,84 +4363,84 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3 aug</t>
+          <t>4 aug</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>38.3128</v>
+        <v>39.3028</v>
       </c>
       <c r="C14" t="n">
-        <v>39.4067</v>
+        <v>39.6443</v>
       </c>
       <c r="D14" t="n">
-        <v>38.2138</v>
+        <v>38.2039</v>
       </c>
       <c r="E14" t="n">
-        <v>39.4067</v>
+        <v>38.486</v>
       </c>
       <c r="F14" t="n">
-        <v>36.1112</v>
+        <v>36.1495</v>
       </c>
       <c r="G14" t="n">
-        <v>34.1393</v>
+        <v>34.1818</v>
       </c>
       <c r="H14" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I14" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>3 aug</t>
+          <t>4 aug</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>160</v>
+        <v>162.86</v>
       </c>
       <c r="M14" t="n">
-        <v>168.7</v>
+        <v>168.56</v>
       </c>
       <c r="N14" t="n">
-        <v>159.6</v>
+        <v>162.4</v>
       </c>
       <c r="O14" t="n">
-        <v>164.64</v>
+        <v>167.38</v>
       </c>
       <c r="P14" t="n">
-        <v>144.7016</v>
+        <v>145.02</v>
       </c>
       <c r="Q14" t="n">
-        <v>171.301</v>
+        <v>170.9913</v>
       </c>
       <c r="R14" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S14" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>31 jul</t>
+          <t>3 aug</t>
         </is>
       </c>
       <c r="V14" t="n">
-        <v>449.1545</v>
+        <v>475.2354</v>
       </c>
       <c r="W14" t="n">
-        <v>465.9628</v>
+        <v>490.7262</v>
       </c>
       <c r="X14" t="n">
-        <v>448.4857</v>
+        <v>474.1075</v>
       </c>
       <c r="Y14" t="n">
-        <v>463.8468</v>
+        <v>486.7337</v>
       </c>
       <c r="Z14" t="n">
-        <v>398.6364</v>
+        <v>399.9838</v>
       </c>
       <c r="AA14" t="n">
-        <v>431.4438</v>
+        <v>431.3306</v>
       </c>
       <c r="AB14" t="n">
         <v>535.3375423278808</v>
@@ -4430,84 +4452,84 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4 aug</t>
+          <t>5 aug</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>39.3028</v>
+        <v>38.4811</v>
       </c>
       <c r="C15" t="n">
-        <v>39.6443</v>
+        <v>38.7632</v>
       </c>
       <c r="D15" t="n">
-        <v>38.2039</v>
+        <v>37.9366</v>
       </c>
       <c r="E15" t="n">
-        <v>38.486</v>
+        <v>38.0307</v>
       </c>
       <c r="F15" t="n">
-        <v>36.1495</v>
+        <v>36.1966</v>
       </c>
       <c r="G15" t="n">
-        <v>34.1818</v>
+        <v>34.2215</v>
       </c>
       <c r="H15" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I15" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>4 aug</t>
+          <t>5 aug</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>162.86</v>
+        <v>167.92</v>
       </c>
       <c r="M15" t="n">
-        <v>168.56</v>
+        <v>172.6</v>
       </c>
       <c r="N15" t="n">
-        <v>162.4</v>
+        <v>167.3</v>
       </c>
       <c r="O15" t="n">
-        <v>167.38</v>
+        <v>169.26</v>
       </c>
       <c r="P15" t="n">
-        <v>145.02</v>
+        <v>145.4052</v>
       </c>
       <c r="Q15" t="n">
-        <v>170.9913</v>
+        <v>170.7022</v>
       </c>
       <c r="R15" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S15" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>3 aug</t>
+          <t>4 aug</t>
         </is>
       </c>
       <c r="V15" t="n">
-        <v>475.2354</v>
+        <v>479.9964</v>
       </c>
       <c r="W15" t="n">
-        <v>490.7262</v>
+        <v>498.5016</v>
       </c>
       <c r="X15" t="n">
-        <v>474.1075</v>
+        <v>478.2697</v>
       </c>
       <c r="Y15" t="n">
-        <v>486.7337</v>
+        <v>491.884</v>
       </c>
       <c r="Z15" t="n">
-        <v>399.9838</v>
+        <v>401.4555</v>
       </c>
       <c r="AA15" t="n">
-        <v>431.3306</v>
+        <v>431.2438</v>
       </c>
       <c r="AB15" t="n">
         <v>535.3375423278808</v>
@@ -4519,84 +4541,84 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5 aug</t>
+          <t>6 aug</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>38.4811</v>
+        <v>38.0752</v>
       </c>
       <c r="C16" t="n">
-        <v>38.7632</v>
+        <v>38.4069</v>
       </c>
       <c r="D16" t="n">
-        <v>37.9366</v>
+        <v>37.9168</v>
       </c>
       <c r="E16" t="n">
-        <v>38.0307</v>
+        <v>38.392</v>
       </c>
       <c r="F16" t="n">
-        <v>36.1966</v>
+        <v>36.2474</v>
       </c>
       <c r="G16" t="n">
-        <v>34.2215</v>
+        <v>34.2607</v>
       </c>
       <c r="H16" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I16" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>5 aug</t>
+          <t>6 aug</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>167.92</v>
+        <v>171.44</v>
       </c>
       <c r="M16" t="n">
-        <v>172.6</v>
+        <v>173.1</v>
       </c>
       <c r="N16" t="n">
-        <v>167.3</v>
+        <v>168.08</v>
       </c>
       <c r="O16" t="n">
-        <v>169.26</v>
+        <v>170.98</v>
       </c>
       <c r="P16" t="n">
-        <v>145.4052</v>
+        <v>145.7928</v>
       </c>
       <c r="Q16" t="n">
-        <v>170.7022</v>
+        <v>170.384</v>
       </c>
       <c r="R16" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S16" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>4 aug</t>
+          <t>5 aug</t>
         </is>
       </c>
       <c r="V16" t="n">
-        <v>479.9964</v>
+        <v>495.4273</v>
       </c>
       <c r="W16" t="n">
-        <v>498.5016</v>
+        <v>497.3038</v>
       </c>
       <c r="X16" t="n">
-        <v>478.2697</v>
+        <v>484.7674</v>
       </c>
       <c r="Y16" t="n">
-        <v>491.884</v>
+        <v>486.5441</v>
       </c>
       <c r="Z16" t="n">
-        <v>401.4555</v>
+        <v>402.8307</v>
       </c>
       <c r="AA16" t="n">
-        <v>431.2438</v>
+        <v>431.1393</v>
       </c>
       <c r="AB16" t="n">
         <v>535.3375423278808</v>
@@ -4608,84 +4630,84 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>6 aug</t>
+          <t>7 aug</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>38.0752</v>
+        <v>38.5207</v>
       </c>
       <c r="C17" t="n">
-        <v>38.4069</v>
+        <v>38.5999</v>
       </c>
       <c r="D17" t="n">
-        <v>37.9168</v>
+        <v>37.897</v>
       </c>
       <c r="E17" t="n">
-        <v>38.392</v>
+        <v>38.0059</v>
       </c>
       <c r="F17" t="n">
-        <v>36.2474</v>
+        <v>36.2952</v>
       </c>
       <c r="G17" t="n">
-        <v>34.2607</v>
+        <v>34.294</v>
       </c>
       <c r="H17" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I17" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>6 aug</t>
+          <t>7 aug</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>171.44</v>
+        <v>173.82</v>
       </c>
       <c r="M17" t="n">
-        <v>173.1</v>
+        <v>179.56</v>
       </c>
       <c r="N17" t="n">
-        <v>168.08</v>
+        <v>173.82</v>
       </c>
       <c r="O17" t="n">
-        <v>170.98</v>
+        <v>177.96</v>
       </c>
       <c r="P17" t="n">
-        <v>145.7928</v>
+        <v>146.2468</v>
       </c>
       <c r="Q17" t="n">
-        <v>170.384</v>
+        <v>170.0918</v>
       </c>
       <c r="R17" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S17" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>5 aug</t>
+          <t>6 aug</t>
         </is>
       </c>
       <c r="V17" t="n">
-        <v>495.4273</v>
+        <v>487.632</v>
       </c>
       <c r="W17" t="n">
-        <v>497.3038</v>
+        <v>500.6176</v>
       </c>
       <c r="X17" t="n">
-        <v>484.7674</v>
+        <v>487.6021</v>
       </c>
       <c r="Y17" t="n">
-        <v>486.5441</v>
+        <v>498.9207</v>
       </c>
       <c r="Z17" t="n">
-        <v>402.8307</v>
+        <v>404.5041</v>
       </c>
       <c r="AA17" t="n">
-        <v>431.1393</v>
+        <v>431.087</v>
       </c>
       <c r="AB17" t="n">
         <v>535.3375423278808</v>
@@ -4697,84 +4719,84 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>7 aug</t>
+          <t>10 aug</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>38.5207</v>
+        <v>38.0356</v>
       </c>
       <c r="C18" t="n">
-        <v>38.5999</v>
+        <v>38.4366</v>
       </c>
       <c r="D18" t="n">
-        <v>37.897</v>
+        <v>37.803</v>
       </c>
       <c r="E18" t="n">
-        <v>38.0059</v>
+        <v>38.4019</v>
       </c>
       <c r="F18" t="n">
-        <v>36.2952</v>
+        <v>36.3315</v>
       </c>
       <c r="G18" t="n">
-        <v>34.294</v>
+        <v>34.3294</v>
       </c>
       <c r="H18" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I18" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>7 aug</t>
+          <t>10 aug</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>173.82</v>
+        <v>178.92</v>
       </c>
       <c r="M18" t="n">
-        <v>179.56</v>
+        <v>179.96</v>
       </c>
       <c r="N18" t="n">
-        <v>173.82</v>
+        <v>175.86</v>
       </c>
       <c r="O18" t="n">
-        <v>177.96</v>
+        <v>179.3</v>
       </c>
       <c r="P18" t="n">
-        <v>146.2468</v>
+        <v>146.4748</v>
       </c>
       <c r="Q18" t="n">
-        <v>170.0918</v>
+        <v>169.8238</v>
       </c>
       <c r="R18" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S18" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>6 aug</t>
+          <t>7 aug</t>
         </is>
       </c>
       <c r="V18" t="n">
-        <v>487.632</v>
+        <v>498.272</v>
       </c>
       <c r="W18" t="n">
-        <v>500.6176</v>
+        <v>504.2308</v>
       </c>
       <c r="X18" t="n">
-        <v>487.6021</v>
+        <v>497.7929</v>
       </c>
       <c r="Y18" t="n">
-        <v>498.9207</v>
+        <v>499.0505</v>
       </c>
       <c r="Z18" t="n">
-        <v>404.5041</v>
+        <v>406.2472</v>
       </c>
       <c r="AA18" t="n">
-        <v>431.087</v>
+        <v>431.0194</v>
       </c>
       <c r="AB18" t="n">
         <v>535.3375423278808</v>
@@ -4786,84 +4808,84 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10 aug</t>
+          <t>11 aug</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>38.0356</v>
+        <v>38.7385</v>
       </c>
       <c r="C19" t="n">
-        <v>38.4366</v>
+        <v>39.0058</v>
       </c>
       <c r="D19" t="n">
-        <v>37.803</v>
+        <v>38.6148</v>
       </c>
       <c r="E19" t="n">
-        <v>38.4019</v>
+        <v>38.9662</v>
       </c>
       <c r="F19" t="n">
-        <v>36.3315</v>
+        <v>36.374</v>
       </c>
       <c r="G19" t="n">
-        <v>34.3294</v>
+        <v>34.3685</v>
       </c>
       <c r="H19" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I19" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>10 aug</t>
+          <t>11 aug</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>178.92</v>
+        <v>180</v>
       </c>
       <c r="M19" t="n">
-        <v>179.96</v>
+        <v>183.24</v>
       </c>
       <c r="N19" t="n">
-        <v>175.86</v>
+        <v>178.14</v>
       </c>
       <c r="O19" t="n">
-        <v>179.3</v>
+        <v>180.7</v>
       </c>
       <c r="P19" t="n">
-        <v>146.4748</v>
+        <v>146.8316</v>
       </c>
       <c r="Q19" t="n">
-        <v>169.8238</v>
+        <v>169.5375</v>
       </c>
       <c r="R19" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S19" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>7 aug</t>
+          <t>10 aug</t>
         </is>
       </c>
       <c r="V19" t="n">
-        <v>498.272</v>
+        <v>502.4941</v>
       </c>
       <c r="W19" t="n">
-        <v>504.2308</v>
+        <v>512.7646999999999</v>
       </c>
       <c r="X19" t="n">
-        <v>497.7929</v>
+        <v>501.3262</v>
       </c>
       <c r="Y19" t="n">
-        <v>499.0505</v>
+        <v>505.1091</v>
       </c>
       <c r="Z19" t="n">
-        <v>406.2472</v>
+        <v>407.8257</v>
       </c>
       <c r="AA19" t="n">
-        <v>431.0194</v>
+        <v>430.9778</v>
       </c>
       <c r="AB19" t="n">
         <v>535.3375423278808</v>
@@ -4875,84 +4897,84 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>11 aug</t>
+          <t>12 aug</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>38.7385</v>
+        <v>38.8573</v>
       </c>
       <c r="C20" t="n">
-        <v>39.0058</v>
+        <v>38.986</v>
       </c>
       <c r="D20" t="n">
-        <v>38.6148</v>
+        <v>38.3871</v>
       </c>
       <c r="E20" t="n">
-        <v>38.9662</v>
+        <v>38.6494</v>
       </c>
       <c r="F20" t="n">
-        <v>36.374</v>
+        <v>36.3981</v>
       </c>
       <c r="G20" t="n">
-        <v>34.3685</v>
+        <v>34.4068</v>
       </c>
       <c r="H20" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I20" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>11 aug</t>
+          <t>12 aug</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>180</v>
+        <v>180.3</v>
       </c>
       <c r="M20" t="n">
-        <v>183.24</v>
+        <v>180.98</v>
       </c>
       <c r="N20" t="n">
-        <v>178.14</v>
+        <v>175.4</v>
       </c>
       <c r="O20" t="n">
-        <v>180.7</v>
+        <v>175.96</v>
       </c>
       <c r="P20" t="n">
-        <v>146.8316</v>
+        <v>147.232</v>
       </c>
       <c r="Q20" t="n">
-        <v>169.5375</v>
+        <v>169.2701</v>
       </c>
       <c r="R20" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S20" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>10 aug</t>
+          <t>11 aug</t>
         </is>
       </c>
       <c r="V20" t="n">
-        <v>502.4941</v>
+        <v>503.3824</v>
       </c>
       <c r="W20" t="n">
-        <v>512.7646999999999</v>
+        <v>504.3805</v>
       </c>
       <c r="X20" t="n">
-        <v>501.3262</v>
+        <v>498.6113</v>
       </c>
       <c r="Y20" t="n">
-        <v>505.1091</v>
+        <v>502.8633</v>
       </c>
       <c r="Z20" t="n">
-        <v>407.8257</v>
+        <v>408.895</v>
       </c>
       <c r="AA20" t="n">
-        <v>430.9778</v>
+        <v>430.9106</v>
       </c>
       <c r="AB20" t="n">
         <v>535.3375423278808</v>
@@ -4964,84 +4986,84 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>12 aug</t>
+          <t>13 aug</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>38.8573</v>
+        <v>39</v>
       </c>
       <c r="C21" t="n">
-        <v>38.986</v>
+        <v>39.005</v>
       </c>
       <c r="D21" t="n">
-        <v>38.3871</v>
+        <v>38.2</v>
       </c>
       <c r="E21" t="n">
-        <v>38.6494</v>
+        <v>38.605</v>
       </c>
       <c r="F21" t="n">
-        <v>36.3981</v>
+        <v>36.4313</v>
       </c>
       <c r="G21" t="n">
-        <v>34.4068</v>
+        <v>34.4429</v>
       </c>
       <c r="H21" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I21" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>12 aug</t>
+          <t>13 aug</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>180.3</v>
+        <v>177.48</v>
       </c>
       <c r="M21" t="n">
-        <v>180.98</v>
+        <v>178.3</v>
       </c>
       <c r="N21" t="n">
-        <v>175.4</v>
+        <v>174.8</v>
       </c>
       <c r="O21" t="n">
-        <v>175.96</v>
+        <v>175.38</v>
       </c>
       <c r="P21" t="n">
-        <v>147.232</v>
+        <v>147.4496</v>
       </c>
       <c r="Q21" t="n">
-        <v>169.2701</v>
+        <v>168.9889</v>
       </c>
       <c r="R21" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S21" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>11 aug</t>
+          <t>12 aug</t>
         </is>
       </c>
       <c r="V21" t="n">
-        <v>503.3824</v>
+        <v>499.0505</v>
       </c>
       <c r="W21" t="n">
-        <v>504.3805</v>
+        <v>500.5577</v>
       </c>
       <c r="X21" t="n">
-        <v>498.6113</v>
+        <v>490.5964</v>
       </c>
       <c r="Y21" t="n">
-        <v>502.8633</v>
+        <v>491.5047</v>
       </c>
       <c r="Z21" t="n">
-        <v>408.895</v>
+        <v>409.532</v>
       </c>
       <c r="AA21" t="n">
-        <v>430.9106</v>
+        <v>430.7866</v>
       </c>
       <c r="AB21" t="n">
         <v>535.3375423278808</v>
@@ -5053,84 +5075,84 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>13 aug</t>
+          <t>14 aug</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>39</v>
+        <v>38.65</v>
       </c>
       <c r="C22" t="n">
-        <v>39.005</v>
+        <v>39.1</v>
       </c>
       <c r="D22" t="n">
-        <v>38.2</v>
+        <v>38.56</v>
       </c>
       <c r="E22" t="n">
-        <v>38.605</v>
+        <v>38.97</v>
       </c>
       <c r="F22" t="n">
-        <v>36.4313</v>
+        <v>36.4703</v>
       </c>
       <c r="G22" t="n">
-        <v>34.4429</v>
+        <v>34.4805</v>
       </c>
       <c r="H22" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I22" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>13 aug</t>
+          <t>14 aug</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>177.48</v>
+        <v>182</v>
       </c>
       <c r="M22" t="n">
-        <v>178.3</v>
+        <v>185.74</v>
       </c>
       <c r="N22" t="n">
-        <v>174.8</v>
+        <v>179.28</v>
       </c>
       <c r="O22" t="n">
-        <v>175.38</v>
+        <v>180.14</v>
       </c>
       <c r="P22" t="n">
-        <v>147.4496</v>
+        <v>147.8228</v>
       </c>
       <c r="Q22" t="n">
-        <v>168.9889</v>
+        <v>168.7386</v>
       </c>
       <c r="R22" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S22" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>12 aug</t>
+          <t>13 aug</t>
         </is>
       </c>
       <c r="V22" t="n">
-        <v>499.0505</v>
+        <v>492.3431</v>
       </c>
       <c r="W22" t="n">
-        <v>500.5577</v>
+        <v>500.398</v>
       </c>
       <c r="X22" t="n">
-        <v>490.5964</v>
+        <v>492.0837</v>
       </c>
       <c r="Y22" t="n">
-        <v>491.5047</v>
+        <v>495.9464</v>
       </c>
       <c r="Z22" t="n">
-        <v>409.532</v>
+        <v>410.6414</v>
       </c>
       <c r="AA22" t="n">
-        <v>430.7866</v>
+        <v>430.6696</v>
       </c>
       <c r="AB22" t="n">
         <v>535.3375423278808</v>
@@ -5142,84 +5164,84 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>14 aug</t>
+          <t>17 aug</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>38.65</v>
+        <v>38.97</v>
       </c>
       <c r="C23" t="n">
-        <v>39.1</v>
+        <v>39.27</v>
       </c>
       <c r="D23" t="n">
-        <v>38.56</v>
+        <v>38.765</v>
       </c>
       <c r="E23" t="n">
-        <v>38.97</v>
+        <v>39.15</v>
       </c>
       <c r="F23" t="n">
-        <v>36.4703</v>
+        <v>36.5118</v>
       </c>
       <c r="G23" t="n">
-        <v>34.4805</v>
+        <v>34.5207</v>
       </c>
       <c r="H23" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I23" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>14 aug</t>
+          <t>17 aug</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>182</v>
+        <v>178.94</v>
       </c>
       <c r="M23" t="n">
-        <v>185.74</v>
+        <v>180.9</v>
       </c>
       <c r="N23" t="n">
-        <v>179.28</v>
+        <v>177.66</v>
       </c>
       <c r="O23" t="n">
-        <v>180.14</v>
+        <v>179.58</v>
       </c>
       <c r="P23" t="n">
-        <v>147.8228</v>
+        <v>148.2524</v>
       </c>
       <c r="Q23" t="n">
-        <v>168.7386</v>
+        <v>168.5337</v>
       </c>
       <c r="R23" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S23" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>13 aug</t>
+          <t>14 aug</t>
         </is>
       </c>
       <c r="V23" t="n">
-        <v>492.3431</v>
+        <v>495.4273</v>
       </c>
       <c r="W23" t="n">
-        <v>500.398</v>
+        <v>499.0705</v>
       </c>
       <c r="X23" t="n">
-        <v>492.0837</v>
+        <v>492.9919</v>
       </c>
       <c r="Y23" t="n">
-        <v>495.9464</v>
+        <v>494.4691</v>
       </c>
       <c r="Z23" t="n">
-        <v>410.6414</v>
+        <v>412</v>
       </c>
       <c r="AA23" t="n">
-        <v>430.6696</v>
+        <v>430.5061</v>
       </c>
       <c r="AB23" t="n">
         <v>535.3375423278808</v>
@@ -5231,84 +5253,84 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>17 aug</t>
+          <t>18 aug</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>38.97</v>
+        <v>39.49</v>
       </c>
       <c r="C24" t="n">
-        <v>39.27</v>
+        <v>39.945</v>
       </c>
       <c r="D24" t="n">
-        <v>38.765</v>
+        <v>39.46</v>
       </c>
       <c r="E24" t="n">
-        <v>39.15</v>
+        <v>39.785</v>
       </c>
       <c r="F24" t="n">
-        <v>36.5118</v>
+        <v>36.5781</v>
       </c>
       <c r="G24" t="n">
-        <v>34.5207</v>
+        <v>34.5641</v>
       </c>
       <c r="H24" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I24" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>17 aug</t>
+          <t>18 aug</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>178.94</v>
+        <v>179.14</v>
       </c>
       <c r="M24" t="n">
-        <v>180.9</v>
+        <v>183.9</v>
       </c>
       <c r="N24" t="n">
-        <v>177.66</v>
+        <v>177.98</v>
       </c>
       <c r="O24" t="n">
-        <v>179.58</v>
+        <v>182.5</v>
       </c>
       <c r="P24" t="n">
-        <v>148.2524</v>
+        <v>148.8084</v>
       </c>
       <c r="Q24" t="n">
-        <v>168.5337</v>
+        <v>168.3358</v>
       </c>
       <c r="R24" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S24" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>14 aug</t>
+          <t>17 aug</t>
         </is>
       </c>
       <c r="V24" t="n">
-        <v>495.4273</v>
+        <v>489.2191</v>
       </c>
       <c r="W24" t="n">
-        <v>499.0705</v>
+        <v>491.7343</v>
       </c>
       <c r="X24" t="n">
-        <v>492.9919</v>
+        <v>477.5111</v>
       </c>
       <c r="Y24" t="n">
-        <v>494.4691</v>
+        <v>479.4474</v>
       </c>
       <c r="Z24" t="n">
-        <v>412</v>
+        <v>413.044</v>
       </c>
       <c r="AA24" t="n">
-        <v>430.5061</v>
+        <v>430.2151</v>
       </c>
       <c r="AB24" t="n">
         <v>535.3375423278808</v>
@@ -5320,84 +5342,84 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>18 aug</t>
+          <t>19 aug</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>39.49</v>
+        <v>39.835</v>
       </c>
       <c r="C25" t="n">
-        <v>39.945</v>
+        <v>40.14</v>
       </c>
       <c r="D25" t="n">
-        <v>39.46</v>
+        <v>39.74</v>
       </c>
       <c r="E25" t="n">
-        <v>39.785</v>
+        <v>39.94</v>
       </c>
       <c r="F25" t="n">
-        <v>36.5781</v>
+        <v>36.6336</v>
       </c>
       <c r="G25" t="n">
-        <v>34.5641</v>
+        <v>34.6092</v>
       </c>
       <c r="H25" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I25" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>18 aug</t>
+          <t>19 aug</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>179.14</v>
+        <v>181.7</v>
       </c>
       <c r="M25" t="n">
-        <v>183.9</v>
+        <v>186.98</v>
       </c>
       <c r="N25" t="n">
-        <v>177.98</v>
+        <v>180.38</v>
       </c>
       <c r="O25" t="n">
-        <v>182.5</v>
+        <v>185.9</v>
       </c>
       <c r="P25" t="n">
-        <v>148.8084</v>
+        <v>149.5324</v>
       </c>
       <c r="Q25" t="n">
-        <v>168.3358</v>
+        <v>168.1618</v>
       </c>
       <c r="R25" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S25" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>17 aug</t>
+          <t>18 aug</t>
         </is>
       </c>
       <c r="V25" t="n">
-        <v>489.2191</v>
+        <v>480.6352</v>
       </c>
       <c r="W25" t="n">
-        <v>491.7343</v>
+        <v>483.3601</v>
       </c>
       <c r="X25" t="n">
-        <v>477.5111</v>
+        <v>476.2534</v>
       </c>
       <c r="Y25" t="n">
-        <v>479.4474</v>
+        <v>480.725</v>
       </c>
       <c r="Z25" t="n">
-        <v>413.044</v>
+        <v>414.3408</v>
       </c>
       <c r="AA25" t="n">
-        <v>430.2151</v>
+        <v>429.933</v>
       </c>
       <c r="AB25" t="n">
         <v>535.3375423278808</v>
@@ -5409,84 +5431,84 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>19 aug</t>
+          <t>20 aug</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>39.835</v>
+        <v>39.865</v>
       </c>
       <c r="C26" t="n">
-        <v>40.14</v>
+        <v>40.51</v>
       </c>
       <c r="D26" t="n">
-        <v>39.74</v>
+        <v>39.8</v>
       </c>
       <c r="E26" t="n">
-        <v>39.94</v>
+        <v>40.28</v>
       </c>
       <c r="F26" t="n">
-        <v>36.6336</v>
+        <v>36.6884</v>
       </c>
       <c r="G26" t="n">
-        <v>34.6092</v>
+        <v>34.6545</v>
       </c>
       <c r="H26" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I26" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>19 aug</t>
+          <t>20 aug</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>181.7</v>
+        <v>183.78</v>
       </c>
       <c r="M26" t="n">
-        <v>186.98</v>
+        <v>186.1</v>
       </c>
       <c r="N26" t="n">
-        <v>180.38</v>
+        <v>182.52</v>
       </c>
       <c r="O26" t="n">
-        <v>185.9</v>
+        <v>185.64</v>
       </c>
       <c r="P26" t="n">
-        <v>149.5324</v>
+        <v>150.4472</v>
       </c>
       <c r="Q26" t="n">
-        <v>168.1618</v>
+        <v>167.9648</v>
       </c>
       <c r="R26" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S26" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>18 aug</t>
+          <t>19 aug</t>
         </is>
       </c>
       <c r="V26" t="n">
-        <v>480.6352</v>
+        <v>479.168</v>
       </c>
       <c r="W26" t="n">
-        <v>483.3601</v>
+        <v>488.3806</v>
       </c>
       <c r="X26" t="n">
-        <v>476.2534</v>
+        <v>478.4593</v>
       </c>
       <c r="Y26" t="n">
-        <v>480.725</v>
+        <v>483.4</v>
       </c>
       <c r="Z26" t="n">
-        <v>414.3408</v>
+        <v>415.7895</v>
       </c>
       <c r="AA26" t="n">
-        <v>429.933</v>
+        <v>429.7427</v>
       </c>
       <c r="AB26" t="n">
         <v>535.3375423278808</v>
@@ -5498,84 +5520,84 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>20 aug</t>
+          <t>21 aug</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>39.865</v>
+        <v>40.1</v>
       </c>
       <c r="C27" t="n">
-        <v>40.51</v>
+        <v>40.37</v>
       </c>
       <c r="D27" t="n">
-        <v>39.8</v>
+        <v>39.84</v>
       </c>
       <c r="E27" t="n">
-        <v>40.28</v>
+        <v>39.91</v>
       </c>
       <c r="F27" t="n">
-        <v>36.6884</v>
+        <v>36.7478</v>
       </c>
       <c r="G27" t="n">
-        <v>34.6545</v>
+        <v>34.6988</v>
       </c>
       <c r="H27" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I27" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>20 aug</t>
+          <t>21 aug</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>183.78</v>
+        <v>185.18</v>
       </c>
       <c r="M27" t="n">
-        <v>186.1</v>
+        <v>188.4</v>
       </c>
       <c r="N27" t="n">
-        <v>182.52</v>
+        <v>183.6</v>
       </c>
       <c r="O27" t="n">
-        <v>185.64</v>
+        <v>188.12</v>
       </c>
       <c r="P27" t="n">
-        <v>150.4472</v>
+        <v>151.4044</v>
       </c>
       <c r="Q27" t="n">
-        <v>167.9648</v>
+        <v>167.794</v>
       </c>
       <c r="R27" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S27" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>19 aug</t>
+          <t>20 aug</t>
         </is>
       </c>
       <c r="V27" t="n">
-        <v>479.168</v>
+        <v>483.3</v>
       </c>
       <c r="W27" t="n">
-        <v>488.3806</v>
+        <v>484.16</v>
       </c>
       <c r="X27" t="n">
-        <v>478.4593</v>
+        <v>479.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>483.4</v>
+        <v>481.15</v>
       </c>
       <c r="Z27" t="n">
-        <v>415.7895</v>
+        <v>417.3594</v>
       </c>
       <c r="AA27" t="n">
-        <v>429.7427</v>
+        <v>429.5805</v>
       </c>
       <c r="AB27" t="n">
         <v>535.3375423278808</v>
@@ -5587,84 +5609,84 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>21 aug</t>
+          <t>24 aug</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>40.1</v>
+        <v>39.88</v>
       </c>
       <c r="C28" t="n">
-        <v>40.37</v>
+        <v>40.085</v>
       </c>
       <c r="D28" t="n">
-        <v>39.84</v>
+        <v>39.68</v>
       </c>
       <c r="E28" t="n">
-        <v>39.91</v>
+        <v>39.775</v>
       </c>
       <c r="F28" t="n">
-        <v>36.7478</v>
+        <v>36.8369</v>
       </c>
       <c r="G28" t="n">
-        <v>34.6988</v>
+        <v>34.7421</v>
       </c>
       <c r="H28" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I28" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>21 aug</t>
+          <t>24 aug</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>185.18</v>
+        <v>186.86</v>
       </c>
       <c r="M28" t="n">
-        <v>188.4</v>
+        <v>188.16</v>
       </c>
       <c r="N28" t="n">
-        <v>183.6</v>
+        <v>185.52</v>
       </c>
       <c r="O28" t="n">
-        <v>188.12</v>
+        <v>187.2</v>
       </c>
       <c r="P28" t="n">
-        <v>151.4044</v>
+        <v>152.2848</v>
       </c>
       <c r="Q28" t="n">
-        <v>167.794</v>
+        <v>167.6093</v>
       </c>
       <c r="R28" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S28" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>20 aug</t>
+          <t>21 aug</t>
         </is>
       </c>
       <c r="V28" t="n">
-        <v>483.3</v>
+        <v>479.88</v>
       </c>
       <c r="W28" t="n">
-        <v>484.16</v>
+        <v>486.36</v>
       </c>
       <c r="X28" t="n">
-        <v>479.5</v>
+        <v>478.53</v>
       </c>
       <c r="Y28" t="n">
-        <v>481.15</v>
+        <v>483.24</v>
       </c>
       <c r="Z28" t="n">
-        <v>417.3594</v>
+        <v>419.092</v>
       </c>
       <c r="AA28" t="n">
-        <v>429.5805</v>
+        <v>429.4327</v>
       </c>
       <c r="AB28" t="n">
         <v>535.3375423278808</v>
@@ -5676,84 +5698,84 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>24 aug</t>
+          <t>25 aug</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>39.88</v>
+        <v>39.77</v>
       </c>
       <c r="C29" t="n">
-        <v>40.085</v>
+        <v>39.915</v>
       </c>
       <c r="D29" t="n">
-        <v>39.68</v>
+        <v>39.385</v>
       </c>
       <c r="E29" t="n">
-        <v>39.775</v>
+        <v>39.6</v>
       </c>
       <c r="F29" t="n">
-        <v>36.8369</v>
+        <v>36.926</v>
       </c>
       <c r="G29" t="n">
-        <v>34.7421</v>
+        <v>34.783</v>
       </c>
       <c r="H29" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I29" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>24 aug</t>
+          <t>25 aug</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>186.86</v>
+        <v>186.4</v>
       </c>
       <c r="M29" t="n">
-        <v>188.16</v>
+        <v>187.62</v>
       </c>
       <c r="N29" t="n">
-        <v>185.52</v>
+        <v>182.74</v>
       </c>
       <c r="O29" t="n">
-        <v>187.2</v>
+        <v>185.46</v>
       </c>
       <c r="P29" t="n">
-        <v>152.2848</v>
+        <v>153.136</v>
       </c>
       <c r="Q29" t="n">
-        <v>167.6093</v>
+        <v>167.4651</v>
       </c>
       <c r="R29" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S29" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>21 aug</t>
+          <t>24 aug</t>
         </is>
       </c>
       <c r="V29" t="n">
-        <v>479.88</v>
+        <v>483.21</v>
       </c>
       <c r="W29" t="n">
-        <v>486.36</v>
+        <v>490.61</v>
       </c>
       <c r="X29" t="n">
-        <v>478.53</v>
+        <v>481.86</v>
       </c>
       <c r="Y29" t="n">
-        <v>483.24</v>
+        <v>487.31</v>
       </c>
       <c r="Z29" t="n">
-        <v>419.092</v>
+        <v>421.046</v>
       </c>
       <c r="AA29" t="n">
-        <v>429.4327</v>
+        <v>429.3186</v>
       </c>
       <c r="AB29" t="n">
         <v>535.3375423278808</v>
@@ -5765,84 +5787,84 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>25 aug</t>
+          <t>26 aug</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>39.77</v>
+        <v>39.275</v>
       </c>
       <c r="C30" t="n">
-        <v>39.915</v>
+        <v>39.47</v>
       </c>
       <c r="D30" t="n">
-        <v>39.385</v>
+        <v>38.91</v>
       </c>
       <c r="E30" t="n">
-        <v>39.6</v>
+        <v>39.42</v>
       </c>
       <c r="F30" t="n">
-        <v>36.926</v>
+        <v>37.0192</v>
       </c>
       <c r="G30" t="n">
-        <v>34.783</v>
+        <v>34.8202</v>
       </c>
       <c r="H30" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I30" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>25 aug</t>
+          <t>26 aug</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>186.4</v>
+        <v>179.92</v>
       </c>
       <c r="M30" t="n">
-        <v>187.62</v>
+        <v>182.16</v>
       </c>
       <c r="N30" t="n">
-        <v>182.74</v>
+        <v>176.82</v>
       </c>
       <c r="O30" t="n">
-        <v>185.46</v>
+        <v>180.02</v>
       </c>
       <c r="P30" t="n">
-        <v>153.136</v>
+        <v>153.9128</v>
       </c>
       <c r="Q30" t="n">
-        <v>167.4651</v>
+        <v>167.3049</v>
       </c>
       <c r="R30" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S30" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>24 aug</t>
+          <t>25 aug</t>
         </is>
       </c>
       <c r="V30" t="n">
-        <v>483.21</v>
+        <v>485.44</v>
       </c>
       <c r="W30" t="n">
-        <v>490.61</v>
+        <v>492.44</v>
       </c>
       <c r="X30" t="n">
-        <v>481.86</v>
+        <v>484.3</v>
       </c>
       <c r="Y30" t="n">
-        <v>487.31</v>
+        <v>491.71</v>
       </c>
       <c r="Z30" t="n">
-        <v>421.046</v>
+        <v>423.0801</v>
       </c>
       <c r="AA30" t="n">
-        <v>429.3185</v>
+        <v>429.262</v>
       </c>
       <c r="AB30" t="n">
         <v>535.3375423278808</v>
@@ -5854,84 +5876,84 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>26 aug</t>
+          <t>27 aug</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>39.275</v>
+        <v>39.16</v>
       </c>
       <c r="C31" t="n">
-        <v>39.47</v>
+        <v>39.295</v>
       </c>
       <c r="D31" t="n">
-        <v>38.91</v>
+        <v>38.65</v>
       </c>
       <c r="E31" t="n">
-        <v>39.42</v>
+        <v>38.76</v>
       </c>
       <c r="F31" t="n">
-        <v>37.0192</v>
+        <v>37.117</v>
       </c>
       <c r="G31" t="n">
-        <v>34.8202</v>
+        <v>34.8559</v>
       </c>
       <c r="H31" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I31" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>26 aug</t>
+          <t>27 aug</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>179.92</v>
+        <v>182.5</v>
       </c>
       <c r="M31" t="n">
-        <v>182.16</v>
+        <v>190.8</v>
       </c>
       <c r="N31" t="n">
-        <v>176.82</v>
+        <v>181.14</v>
       </c>
       <c r="O31" t="n">
-        <v>180.02</v>
+        <v>189.88</v>
       </c>
       <c r="P31" t="n">
-        <v>153.9128</v>
+        <v>155.0132</v>
       </c>
       <c r="Q31" t="n">
-        <v>167.3049</v>
+        <v>167.1911</v>
       </c>
       <c r="R31" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S31" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>25 aug</t>
+          <t>26 aug</t>
         </is>
       </c>
       <c r="V31" t="n">
-        <v>485.44</v>
+        <v>487.85</v>
       </c>
       <c r="W31" t="n">
-        <v>492.44</v>
+        <v>497.4</v>
       </c>
       <c r="X31" t="n">
-        <v>484.3</v>
+        <v>487.31</v>
       </c>
       <c r="Y31" t="n">
-        <v>491.71</v>
+        <v>496.37</v>
       </c>
       <c r="Z31" t="n">
-        <v>423.0801</v>
+        <v>425.0273</v>
       </c>
       <c r="AA31" t="n">
-        <v>429.262</v>
+        <v>429.2786</v>
       </c>
       <c r="AB31" t="n">
         <v>535.3375423278808</v>
@@ -5943,84 +5965,84 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>27 aug</t>
+          <t>28 aug</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>39.16</v>
+        <v>39</v>
       </c>
       <c r="C32" t="n">
-        <v>39.295</v>
+        <v>39.18</v>
       </c>
       <c r="D32" t="n">
-        <v>38.65</v>
+        <v>38.845</v>
       </c>
       <c r="E32" t="n">
-        <v>38.76</v>
+        <v>39.145</v>
       </c>
       <c r="F32" t="n">
-        <v>37.117</v>
+        <v>37.2162</v>
       </c>
       <c r="G32" t="n">
-        <v>34.8559</v>
+        <v>34.8941</v>
       </c>
       <c r="H32" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I32" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>27 aug</t>
+          <t>28 aug</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>182.5</v>
+        <v>189.5</v>
       </c>
       <c r="M32" t="n">
-        <v>190.8</v>
+        <v>191.94</v>
       </c>
       <c r="N32" t="n">
-        <v>181.14</v>
+        <v>187.98</v>
       </c>
       <c r="O32" t="n">
-        <v>189.88</v>
+        <v>191.32</v>
       </c>
       <c r="P32" t="n">
-        <v>155.0132</v>
+        <v>156.1568</v>
       </c>
       <c r="Q32" t="n">
-        <v>167.1911</v>
+        <v>167.0806</v>
       </c>
       <c r="R32" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S32" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>26 aug</t>
+          <t>27 aug</t>
         </is>
       </c>
       <c r="V32" t="n">
-        <v>487.85</v>
+        <v>494.88</v>
       </c>
       <c r="W32" t="n">
-        <v>497.4</v>
+        <v>506.48</v>
       </c>
       <c r="X32" t="n">
-        <v>487.31</v>
+        <v>490.08</v>
       </c>
       <c r="Y32" t="n">
-        <v>496.37</v>
+        <v>505.06</v>
       </c>
       <c r="Z32" t="n">
-        <v>425.0273</v>
+        <v>427.2667</v>
       </c>
       <c r="AA32" t="n">
-        <v>429.2786</v>
+        <v>429.3401</v>
       </c>
       <c r="AB32" t="n">
         <v>535.3375423278808</v>
@@ -6032,84 +6054,84 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>28 aug</t>
+          <t>31 aug</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>39</v>
+        <v>39.54</v>
       </c>
       <c r="C33" t="n">
-        <v>39.18</v>
+        <v>39.91</v>
       </c>
       <c r="D33" t="n">
-        <v>38.845</v>
+        <v>39.24</v>
       </c>
       <c r="E33" t="n">
-        <v>39.145</v>
+        <v>39.335</v>
       </c>
       <c r="F33" t="n">
-        <v>37.2162</v>
+        <v>37.3111</v>
       </c>
       <c r="G33" t="n">
-        <v>34.8941</v>
+        <v>34.9333</v>
       </c>
       <c r="H33" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I33" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>28 aug</t>
+          <t>31 aug</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>189.5</v>
+        <v>188.46</v>
       </c>
       <c r="M33" t="n">
-        <v>191.94</v>
+        <v>192.12</v>
       </c>
       <c r="N33" t="n">
-        <v>187.98</v>
+        <v>188.2</v>
       </c>
       <c r="O33" t="n">
-        <v>191.32</v>
+        <v>190.9</v>
       </c>
       <c r="P33" t="n">
-        <v>156.1568</v>
+        <v>157.3304</v>
       </c>
       <c r="Q33" t="n">
-        <v>167.0806</v>
+        <v>166.9613</v>
       </c>
       <c r="R33" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S33" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>27 aug</t>
+          <t>28 aug</t>
         </is>
       </c>
       <c r="V33" t="n">
-        <v>494.88</v>
+        <v>505.33</v>
       </c>
       <c r="W33" t="n">
-        <v>506.48</v>
+        <v>517.78</v>
       </c>
       <c r="X33" t="n">
-        <v>490.08</v>
+        <v>504.87</v>
       </c>
       <c r="Y33" t="n">
-        <v>505.06</v>
+        <v>513.53</v>
       </c>
       <c r="Z33" t="n">
-        <v>427.2667</v>
+        <v>429.9734</v>
       </c>
       <c r="AA33" t="n">
-        <v>429.3401</v>
+        <v>429.3984</v>
       </c>
       <c r="AB33" t="n">
         <v>535.3375423278808</v>
@@ -6121,84 +6143,84 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>31 aug</t>
+          <t>1 sep</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>39.54</v>
+        <v>39.77</v>
       </c>
       <c r="C34" t="n">
-        <v>39.91</v>
+        <v>40.19</v>
       </c>
       <c r="D34" t="n">
-        <v>39.24</v>
+        <v>39.645</v>
       </c>
       <c r="E34" t="n">
-        <v>39.335</v>
+        <v>40.155</v>
       </c>
       <c r="F34" t="n">
-        <v>37.3111</v>
+        <v>37.4239</v>
       </c>
       <c r="G34" t="n">
-        <v>34.9333</v>
+        <v>34.9763</v>
       </c>
       <c r="H34" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I34" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>31 aug</t>
+          <t>1 sep</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>188.46</v>
+        <v>186</v>
       </c>
       <c r="M34" t="n">
-        <v>192.12</v>
+        <v>187.86</v>
       </c>
       <c r="N34" t="n">
-        <v>188.2</v>
+        <v>183.32</v>
       </c>
       <c r="O34" t="n">
-        <v>190.9</v>
+        <v>184.26</v>
       </c>
       <c r="P34" t="n">
-        <v>157.3304</v>
+        <v>158.3252</v>
       </c>
       <c r="Q34" t="n">
-        <v>166.9613</v>
+        <v>166.8103</v>
       </c>
       <c r="R34" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S34" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>28 aug</t>
+          <t>31 aug</t>
         </is>
       </c>
       <c r="V34" t="n">
-        <v>505.33</v>
+        <v>510.38</v>
       </c>
       <c r="W34" t="n">
-        <v>517.78</v>
+        <v>512.1900000000001</v>
       </c>
       <c r="X34" t="n">
-        <v>504.87</v>
+        <v>506.39</v>
       </c>
       <c r="Y34" t="n">
-        <v>513.53</v>
+        <v>507.29</v>
       </c>
       <c r="Z34" t="n">
-        <v>429.9734</v>
+        <v>432.5454</v>
       </c>
       <c r="AA34" t="n">
-        <v>429.3984</v>
+        <v>429.4122</v>
       </c>
       <c r="AB34" t="n">
         <v>535.3375423278808</v>
@@ -6210,84 +6232,84 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1 sep</t>
+          <t>2 sep</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>39.77</v>
+        <v>40.35</v>
       </c>
       <c r="C35" t="n">
-        <v>40.19</v>
+        <v>40.615</v>
       </c>
       <c r="D35" t="n">
-        <v>39.645</v>
+        <v>39.975</v>
       </c>
       <c r="E35" t="n">
-        <v>40.155</v>
+        <v>40.21</v>
       </c>
       <c r="F35" t="n">
-        <v>37.4239</v>
+        <v>37.5499</v>
       </c>
       <c r="G35" t="n">
-        <v>34.9763</v>
+        <v>35.0217</v>
       </c>
       <c r="H35" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I35" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1 sep</t>
+          <t>2 sep</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>186</v>
+        <v>182.18</v>
       </c>
       <c r="M35" t="n">
-        <v>187.86</v>
+        <v>184.7</v>
       </c>
       <c r="N35" t="n">
-        <v>183.32</v>
+        <v>180.72</v>
       </c>
       <c r="O35" t="n">
-        <v>184.26</v>
+        <v>181.44</v>
       </c>
       <c r="P35" t="n">
-        <v>158.3252</v>
+        <v>159.2568</v>
       </c>
       <c r="Q35" t="n">
-        <v>166.8103</v>
+        <v>166.6796</v>
       </c>
       <c r="R35" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S35" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>31 aug</t>
+          <t>1 sep</t>
         </is>
       </c>
       <c r="V35" t="n">
-        <v>510.38</v>
+        <v>497.52</v>
       </c>
       <c r="W35" t="n">
-        <v>512.1900000000001</v>
+        <v>505.97</v>
       </c>
       <c r="X35" t="n">
-        <v>506.39</v>
+        <v>496.78</v>
       </c>
       <c r="Y35" t="n">
-        <v>507.29</v>
+        <v>501.02</v>
       </c>
       <c r="Z35" t="n">
-        <v>432.5454</v>
+        <v>435.2328</v>
       </c>
       <c r="AA35" t="n">
-        <v>429.4122</v>
+        <v>429.3825</v>
       </c>
       <c r="AB35" t="n">
         <v>535.3375423278808</v>
@@ -6299,84 +6321,84 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2 sep</t>
+          <t>3 sep</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>40.35</v>
+        <v>40.095</v>
       </c>
       <c r="C36" t="n">
-        <v>40.615</v>
+        <v>40.215</v>
       </c>
       <c r="D36" t="n">
-        <v>39.975</v>
+        <v>39.54</v>
       </c>
       <c r="E36" t="n">
-        <v>40.21</v>
+        <v>40.04</v>
       </c>
       <c r="F36" t="n">
-        <v>37.5499</v>
+        <v>37.6767</v>
       </c>
       <c r="G36" t="n">
-        <v>35.0217</v>
+        <v>35.0679</v>
       </c>
       <c r="H36" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I36" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2 sep</t>
+          <t>3 sep</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>182.18</v>
+        <v>182.08</v>
       </c>
       <c r="M36" t="n">
-        <v>184.7</v>
+        <v>187.56</v>
       </c>
       <c r="N36" t="n">
-        <v>180.72</v>
+        <v>182</v>
       </c>
       <c r="O36" t="n">
-        <v>181.44</v>
+        <v>185.58</v>
       </c>
       <c r="P36" t="n">
-        <v>159.2568</v>
+        <v>160.3228</v>
       </c>
       <c r="Q36" t="n">
-        <v>166.6796</v>
+        <v>166.5898</v>
       </c>
       <c r="R36" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S36" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>1 sep</t>
+          <t>2 sep</t>
         </is>
       </c>
       <c r="V36" t="n">
-        <v>497.52</v>
+        <v>499.85</v>
       </c>
       <c r="W36" t="n">
-        <v>505.97</v>
+        <v>500.27</v>
       </c>
       <c r="X36" t="n">
-        <v>496.78</v>
+        <v>493.81</v>
       </c>
       <c r="Y36" t="n">
-        <v>501.02</v>
+        <v>496.82</v>
       </c>
       <c r="Z36" t="n">
-        <v>435.2328</v>
+        <v>437.7045</v>
       </c>
       <c r="AA36" t="n">
-        <v>429.3825</v>
+        <v>429.3706</v>
       </c>
       <c r="AB36" t="n">
         <v>535.3375423278808</v>
@@ -6388,84 +6410,84 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3 sep</t>
+          <t>4 sep</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>40.095</v>
+        <v>40.145</v>
       </c>
       <c r="C37" t="n">
-        <v>40.215</v>
+        <v>40.28</v>
       </c>
       <c r="D37" t="n">
-        <v>39.54</v>
+        <v>39.665</v>
       </c>
       <c r="E37" t="n">
-        <v>40.04</v>
+        <v>40.105</v>
       </c>
       <c r="F37" t="n">
-        <v>37.6767</v>
+        <v>37.8115</v>
       </c>
       <c r="G37" t="n">
-        <v>35.0679</v>
+        <v>35.113</v>
       </c>
       <c r="H37" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I37" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>3 sep</t>
+          <t>4 sep</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>182.08</v>
+        <v>187.8</v>
       </c>
       <c r="M37" t="n">
-        <v>187.56</v>
+        <v>189.9</v>
       </c>
       <c r="N37" t="n">
-        <v>182</v>
+        <v>184.96</v>
       </c>
       <c r="O37" t="n">
-        <v>185.58</v>
+        <v>185.68</v>
       </c>
       <c r="P37" t="n">
-        <v>160.3228</v>
+        <v>161.3336</v>
       </c>
       <c r="Q37" t="n">
-        <v>166.5898</v>
+        <v>166.5086</v>
       </c>
       <c r="R37" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S37" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>2 sep</t>
+          <t>3 sep</t>
         </is>
       </c>
       <c r="V37" t="n">
-        <v>499.85</v>
+        <v>501.66</v>
       </c>
       <c r="W37" t="n">
-        <v>500.27</v>
+        <v>515.65</v>
       </c>
       <c r="X37" t="n">
-        <v>493.81</v>
+        <v>500.8</v>
       </c>
       <c r="Y37" t="n">
-        <v>496.82</v>
+        <v>510.12</v>
       </c>
       <c r="Z37" t="n">
-        <v>437.7045</v>
+        <v>440.6114</v>
       </c>
       <c r="AA37" t="n">
-        <v>429.3706</v>
+        <v>429.3912</v>
       </c>
       <c r="AB37" t="n">
         <v>535.3375423278808</v>
@@ -6477,84 +6499,84 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>4 sep</t>
+          <t>7 sep</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>40.145</v>
+        <v>40.26</v>
       </c>
       <c r="C38" t="n">
-        <v>40.28</v>
+        <v>40.845</v>
       </c>
       <c r="D38" t="n">
-        <v>39.665</v>
+        <v>40.12</v>
       </c>
       <c r="E38" t="n">
-        <v>40.105</v>
+        <v>40.56</v>
       </c>
       <c r="F38" t="n">
-        <v>37.8115</v>
+        <v>37.9551</v>
       </c>
       <c r="G38" t="n">
-        <v>35.113</v>
+        <v>35.1619</v>
       </c>
       <c r="H38" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I38" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>4 sep</t>
+          <t>7 sep</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>187.8</v>
+        <v>183.56</v>
       </c>
       <c r="M38" t="n">
-        <v>189.9</v>
+        <v>184.3</v>
       </c>
       <c r="N38" t="n">
-        <v>184.96</v>
+        <v>179.92</v>
       </c>
       <c r="O38" t="n">
-        <v>185.68</v>
+        <v>182.8</v>
       </c>
       <c r="P38" t="n">
-        <v>161.3336</v>
+        <v>162.2568</v>
       </c>
       <c r="Q38" t="n">
-        <v>166.5086</v>
+        <v>166.4122</v>
       </c>
       <c r="R38" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S38" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>3 sep</t>
+          <t>4 sep</t>
         </is>
       </c>
       <c r="V38" t="n">
-        <v>501.66</v>
+        <v>510</v>
       </c>
       <c r="W38" t="n">
-        <v>515.65</v>
+        <v>511</v>
       </c>
       <c r="X38" t="n">
-        <v>500.8</v>
+        <v>499.36</v>
       </c>
       <c r="Y38" t="n">
-        <v>510.12</v>
+        <v>499.7</v>
       </c>
       <c r="Z38" t="n">
-        <v>440.6114</v>
+        <v>443.5621</v>
       </c>
       <c r="AA38" t="n">
-        <v>429.3912</v>
+        <v>429.3729</v>
       </c>
       <c r="AB38" t="n">
         <v>535.3375423278808</v>
@@ -6566,84 +6588,84 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>7 sep</t>
+          <t>8 sep</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>40.26</v>
+        <v>40.83</v>
       </c>
       <c r="C39" t="n">
-        <v>40.845</v>
+        <v>41.18</v>
       </c>
       <c r="D39" t="n">
-        <v>40.12</v>
+        <v>40.6325</v>
       </c>
       <c r="E39" t="n">
-        <v>40.56</v>
+        <v>40.855</v>
       </c>
       <c r="F39" t="n">
-        <v>37.9551</v>
+        <v>38.0977</v>
       </c>
       <c r="G39" t="n">
-        <v>35.1619</v>
+        <v>35.2131</v>
       </c>
       <c r="H39" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I39" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>7 sep</t>
+          <t>8 sep</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>183.56</v>
+        <v>182.32</v>
       </c>
       <c r="M39" t="n">
-        <v>184.3</v>
+        <v>183.76</v>
       </c>
       <c r="N39" t="n">
-        <v>179.92</v>
+        <v>180.02</v>
       </c>
       <c r="O39" t="n">
-        <v>182.8</v>
+        <v>181.7</v>
       </c>
       <c r="P39" t="n">
-        <v>162.2568</v>
+        <v>163.2108</v>
       </c>
       <c r="Q39" t="n">
-        <v>166.4122</v>
+        <v>166.3049</v>
       </c>
       <c r="R39" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S39" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>4 sep</t>
+          <t>8 sep</t>
         </is>
       </c>
       <c r="V39" t="n">
-        <v>510</v>
+        <v>493.01</v>
       </c>
       <c r="W39" t="n">
-        <v>511</v>
+        <v>495.19</v>
       </c>
       <c r="X39" t="n">
-        <v>499.36</v>
+        <v>490.15</v>
       </c>
       <c r="Y39" t="n">
-        <v>499.7</v>
+        <v>493.95</v>
       </c>
       <c r="Z39" t="n">
-        <v>443.5621</v>
+        <v>445.9957</v>
       </c>
       <c r="AA39" t="n">
-        <v>429.3729</v>
+        <v>429.3939</v>
       </c>
       <c r="AB39" t="n">
         <v>535.3375423278808</v>
@@ -6655,84 +6677,84 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>8 sep</t>
+          <t>9 sep</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>40.83</v>
+        <v>41.1</v>
       </c>
       <c r="C40" t="n">
-        <v>41.18</v>
+        <v>41.385</v>
       </c>
       <c r="D40" t="n">
-        <v>40.6325</v>
+        <v>40.85</v>
       </c>
       <c r="E40" t="n">
-        <v>40.855</v>
+        <v>40.94</v>
       </c>
       <c r="F40" t="n">
-        <v>38.0977</v>
+        <v>38.2513</v>
       </c>
       <c r="G40" t="n">
-        <v>35.2131</v>
+        <v>35.2646</v>
       </c>
       <c r="H40" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I40" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>8 sep</t>
+          <t>9 sep</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>182.32</v>
+        <v>183</v>
       </c>
       <c r="M40" t="n">
-        <v>183.76</v>
+        <v>187.04</v>
       </c>
       <c r="N40" t="n">
-        <v>180.02</v>
+        <v>181.36</v>
       </c>
       <c r="O40" t="n">
-        <v>181.7</v>
+        <v>182.86</v>
       </c>
       <c r="P40" t="n">
-        <v>163.2108</v>
+        <v>164.0504</v>
       </c>
       <c r="Q40" t="n">
-        <v>166.3049</v>
+        <v>166.2113</v>
       </c>
       <c r="R40" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S40" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>8 sep</t>
+          <t>9 sep</t>
         </is>
       </c>
       <c r="V40" t="n">
-        <v>493.01</v>
+        <v>493.07</v>
       </c>
       <c r="W40" t="n">
-        <v>495.19</v>
+        <v>494.39</v>
       </c>
       <c r="X40" t="n">
-        <v>490.15</v>
+        <v>489.8</v>
       </c>
       <c r="Y40" t="n">
-        <v>493.95</v>
+        <v>491.65</v>
       </c>
       <c r="Z40" t="n">
-        <v>445.9957</v>
+        <v>448.4712</v>
       </c>
       <c r="AA40" t="n">
-        <v>429.3939</v>
+        <v>429.4364</v>
       </c>
       <c r="AB40" t="n">
         <v>535.3375423278808</v>
@@ -6744,84 +6766,84 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>9 sep</t>
+          <t>10 sep</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>41.1</v>
+        <v>40.98</v>
       </c>
       <c r="C41" t="n">
-        <v>41.385</v>
+        <v>41.77</v>
       </c>
       <c r="D41" t="n">
-        <v>40.85</v>
+        <v>40.93</v>
       </c>
       <c r="E41" t="n">
-        <v>40.94</v>
+        <v>41.23</v>
       </c>
       <c r="F41" t="n">
-        <v>38.2513</v>
+        <v>38.4034</v>
       </c>
       <c r="G41" t="n">
-        <v>35.2646</v>
+        <v>35.3174</v>
       </c>
       <c r="H41" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I41" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>9 sep</t>
+          <t>10 sep</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="M41" t="n">
-        <v>187.04</v>
+        <v>180.4</v>
       </c>
       <c r="N41" t="n">
-        <v>181.36</v>
+        <v>176.2</v>
       </c>
       <c r="O41" t="n">
-        <v>182.86</v>
+        <v>177.82</v>
       </c>
       <c r="P41" t="n">
-        <v>164.0504</v>
+        <v>164.7724</v>
       </c>
       <c r="Q41" t="n">
-        <v>166.2113</v>
+        <v>166.0803</v>
       </c>
       <c r="R41" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S41" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>9 sep</t>
+          <t>10 sep</t>
         </is>
       </c>
       <c r="V41" t="n">
-        <v>493.07</v>
+        <v>488.32</v>
       </c>
       <c r="W41" t="n">
-        <v>494.39</v>
+        <v>494.52</v>
       </c>
       <c r="X41" t="n">
-        <v>489.8</v>
+        <v>486</v>
       </c>
       <c r="Y41" t="n">
-        <v>491.65</v>
+        <v>492.44</v>
       </c>
       <c r="Z41" t="n">
-        <v>448.4712</v>
+        <v>450.8736</v>
       </c>
       <c r="AA41" t="n">
-        <v>429.4364</v>
+        <v>429.5215</v>
       </c>
       <c r="AB41" t="n">
         <v>535.3375423278808</v>
@@ -6833,84 +6855,84 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>10 sep</t>
+          <t>11 sep</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>40.98</v>
+        <v>41.345</v>
       </c>
       <c r="C42" t="n">
-        <v>41.77</v>
+        <v>41.715</v>
       </c>
       <c r="D42" t="n">
-        <v>40.93</v>
+        <v>40.905</v>
       </c>
       <c r="E42" t="n">
-        <v>41.23</v>
+        <v>41.415</v>
       </c>
       <c r="F42" t="n">
-        <v>38.4034</v>
+        <v>38.5608</v>
       </c>
       <c r="G42" t="n">
-        <v>35.3174</v>
+        <v>35.3717</v>
       </c>
       <c r="H42" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I42" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>10 sep</t>
+          <t>11 sep</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>180</v>
+        <v>175.68</v>
       </c>
       <c r="M42" t="n">
-        <v>180.4</v>
+        <v>178.84</v>
       </c>
       <c r="N42" t="n">
-        <v>176.2</v>
+        <v>172.16</v>
       </c>
       <c r="O42" t="n">
-        <v>177.82</v>
+        <v>177.26</v>
       </c>
       <c r="P42" t="n">
-        <v>164.7724</v>
+        <v>165.5248</v>
       </c>
       <c r="Q42" t="n">
-        <v>166.0803</v>
+        <v>165.9594</v>
       </c>
       <c r="R42" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S42" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>10 sep</t>
+          <t>11 sep</t>
         </is>
       </c>
       <c r="V42" t="n">
-        <v>488.32</v>
+        <v>495.65</v>
       </c>
       <c r="W42" t="n">
-        <v>494.52</v>
+        <v>498.97</v>
       </c>
       <c r="X42" t="n">
-        <v>486</v>
+        <v>492.58</v>
       </c>
       <c r="Y42" t="n">
-        <v>492.44</v>
+        <v>495.63</v>
       </c>
       <c r="Z42" t="n">
-        <v>450.8736</v>
+        <v>453.115</v>
       </c>
       <c r="AA42" t="n">
-        <v>429.5215</v>
+        <v>429.654</v>
       </c>
       <c r="AB42" t="n">
         <v>535.3375423278808</v>
@@ -6922,84 +6944,84 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>11 sep</t>
+          <t>14 sep</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>41.345</v>
+        <v>41.88</v>
       </c>
       <c r="C43" t="n">
-        <v>41.715</v>
+        <v>42.285</v>
       </c>
       <c r="D43" t="n">
-        <v>40.905</v>
+        <v>41.8</v>
       </c>
       <c r="E43" t="n">
-        <v>41.415</v>
+        <v>41.91</v>
       </c>
       <c r="F43" t="n">
-        <v>38.5608</v>
+        <v>38.7226</v>
       </c>
       <c r="G43" t="n">
-        <v>35.3717</v>
+        <v>35.4269</v>
       </c>
       <c r="H43" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I43" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>11 sep</t>
+          <t>14 sep</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>175.68</v>
+        <v>180.82</v>
       </c>
       <c r="M43" t="n">
-        <v>178.84</v>
+        <v>186.76</v>
       </c>
       <c r="N43" t="n">
-        <v>172.16</v>
+        <v>180.82</v>
       </c>
       <c r="O43" t="n">
-        <v>177.26</v>
+        <v>186.26</v>
       </c>
       <c r="P43" t="n">
-        <v>165.5248</v>
+        <v>166.4488</v>
       </c>
       <c r="Q43" t="n">
-        <v>165.9594</v>
+        <v>165.8745</v>
       </c>
       <c r="R43" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S43" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>11 sep</t>
+          <t>14 sep</t>
         </is>
       </c>
       <c r="V43" t="n">
-        <v>495.65</v>
+        <v>497.06</v>
       </c>
       <c r="W43" t="n">
-        <v>498.97</v>
+        <v>509.95</v>
       </c>
       <c r="X43" t="n">
-        <v>492.58</v>
+        <v>495.34</v>
       </c>
       <c r="Y43" t="n">
-        <v>495.63</v>
+        <v>505.41</v>
       </c>
       <c r="Z43" t="n">
-        <v>453.115</v>
+        <v>455.4281</v>
       </c>
       <c r="AA43" t="n">
-        <v>429.6539</v>
+        <v>429.8259</v>
       </c>
       <c r="AB43" t="n">
         <v>535.3375423278808</v>
@@ -7011,84 +7033,84 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>14 sep</t>
+          <t>15 sep</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>41.88</v>
+        <v>41.845</v>
       </c>
       <c r="C44" t="n">
-        <v>42.285</v>
+        <v>42.7</v>
       </c>
       <c r="D44" t="n">
-        <v>41.8</v>
+        <v>41.72</v>
       </c>
       <c r="E44" t="n">
-        <v>41.91</v>
+        <v>42.7</v>
       </c>
       <c r="F44" t="n">
-        <v>38.7226</v>
+        <v>38.8782</v>
       </c>
       <c r="G44" t="n">
-        <v>35.4269</v>
+        <v>35.4854</v>
       </c>
       <c r="H44" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I44" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>14 sep</t>
+          <t>15 sep</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>180.82</v>
+        <v>186.64</v>
       </c>
       <c r="M44" t="n">
-        <v>186.76</v>
+        <v>187.26</v>
       </c>
       <c r="N44" t="n">
-        <v>180.82</v>
+        <v>183.2</v>
       </c>
       <c r="O44" t="n">
-        <v>186.26</v>
+        <v>187.08</v>
       </c>
       <c r="P44" t="n">
-        <v>166.4488</v>
+        <v>167.3124</v>
       </c>
       <c r="Q44" t="n">
-        <v>165.8745</v>
+        <v>165.7921</v>
       </c>
       <c r="R44" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S44" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>14 sep</t>
+          <t>15 sep</t>
         </is>
       </c>
       <c r="V44" t="n">
-        <v>497.06</v>
+        <v>500.06</v>
       </c>
       <c r="W44" t="n">
-        <v>509.95</v>
+        <v>505.9</v>
       </c>
       <c r="X44" t="n">
-        <v>495.34</v>
+        <v>495.54</v>
       </c>
       <c r="Y44" t="n">
-        <v>505.41</v>
+        <v>497.12</v>
       </c>
       <c r="Z44" t="n">
-        <v>455.4281</v>
+        <v>457.6502</v>
       </c>
       <c r="AA44" t="n">
-        <v>429.8259</v>
+        <v>429.9416</v>
       </c>
       <c r="AB44" t="n">
         <v>535.3375423278808</v>
@@ -7100,84 +7122,84 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>15 sep</t>
+          <t>16 sep</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>41.845</v>
+        <v>42.72</v>
       </c>
       <c r="C45" t="n">
-        <v>42.7</v>
+        <v>42.85</v>
       </c>
       <c r="D45" t="n">
-        <v>41.72</v>
+        <v>41.67</v>
       </c>
       <c r="E45" t="n">
-        <v>42.7</v>
+        <v>41.825</v>
       </c>
       <c r="F45" t="n">
-        <v>38.8782</v>
+        <v>38.9989</v>
       </c>
       <c r="G45" t="n">
-        <v>35.4854</v>
+        <v>35.5403</v>
       </c>
       <c r="H45" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I45" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>15 sep</t>
+          <t>16 sep</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>186.64</v>
+        <v>185.86</v>
       </c>
       <c r="M45" t="n">
-        <v>187.26</v>
+        <v>186.76</v>
       </c>
       <c r="N45" t="n">
-        <v>183.2</v>
+        <v>182.18</v>
       </c>
       <c r="O45" t="n">
-        <v>187.08</v>
+        <v>186.56</v>
       </c>
       <c r="P45" t="n">
-        <v>167.3124</v>
+        <v>168.2844</v>
       </c>
       <c r="Q45" t="n">
-        <v>165.7921</v>
+        <v>165.6996</v>
       </c>
       <c r="R45" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S45" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>15 sep</t>
+          <t>16 sep</t>
         </is>
       </c>
       <c r="V45" t="n">
-        <v>500.06</v>
+        <v>493.03</v>
       </c>
       <c r="W45" t="n">
-        <v>505.9</v>
+        <v>495.97</v>
       </c>
       <c r="X45" t="n">
-        <v>495.54</v>
+        <v>487.23</v>
       </c>
       <c r="Y45" t="n">
-        <v>497.12</v>
+        <v>490.3</v>
       </c>
       <c r="Z45" t="n">
-        <v>457.6502</v>
+        <v>459.694</v>
       </c>
       <c r="AA45" t="n">
-        <v>429.9416</v>
+        <v>429.9809</v>
       </c>
       <c r="AB45" t="n">
         <v>535.3375423278808</v>
@@ -7189,84 +7211,84 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>16 sep</t>
+          <t>17 sep</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>42.72</v>
+        <v>41.58</v>
       </c>
       <c r="C46" t="n">
-        <v>42.85</v>
+        <v>42.055</v>
       </c>
       <c r="D46" t="n">
-        <v>41.67</v>
+        <v>41.38</v>
       </c>
       <c r="E46" t="n">
-        <v>41.825</v>
+        <v>41.56</v>
       </c>
       <c r="F46" t="n">
-        <v>38.9989</v>
+        <v>39.1225</v>
       </c>
       <c r="G46" t="n">
-        <v>35.5403</v>
+        <v>35.5926</v>
       </c>
       <c r="H46" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I46" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>16 sep</t>
+          <t>17 sep</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>185.86</v>
+        <v>188.54</v>
       </c>
       <c r="M46" t="n">
-        <v>186.76</v>
+        <v>189.2</v>
       </c>
       <c r="N46" t="n">
-        <v>182.18</v>
+        <v>184.62</v>
       </c>
       <c r="O46" t="n">
-        <v>186.56</v>
+        <v>188</v>
       </c>
       <c r="P46" t="n">
-        <v>168.2844</v>
+        <v>169.2896</v>
       </c>
       <c r="Q46" t="n">
-        <v>165.6996</v>
+        <v>165.6125</v>
       </c>
       <c r="R46" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S46" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>16 sep</t>
+          <t>17 sep</t>
         </is>
       </c>
       <c r="V46" t="n">
-        <v>493.03</v>
+        <v>497.8</v>
       </c>
       <c r="W46" t="n">
-        <v>495.97</v>
+        <v>501.47</v>
       </c>
       <c r="X46" t="n">
-        <v>487.23</v>
+        <v>493.17</v>
       </c>
       <c r="Y46" t="n">
-        <v>490.3</v>
+        <v>497.75</v>
       </c>
       <c r="Z46" t="n">
-        <v>459.694</v>
+        <v>461.9966</v>
       </c>
       <c r="AA46" t="n">
-        <v>429.9809</v>
+        <v>430.0251</v>
       </c>
       <c r="AB46" t="n">
         <v>535.3375423278808</v>
@@ -7278,84 +7300,84 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>17 sep</t>
+          <t>18 sep</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>41.58</v>
+        <v>41.465</v>
       </c>
       <c r="C47" t="n">
-        <v>42.055</v>
+        <v>41.5</v>
       </c>
       <c r="D47" t="n">
-        <v>41.38</v>
+        <v>40.955</v>
       </c>
       <c r="E47" t="n">
-        <v>41.56</v>
+        <v>41.315</v>
       </c>
       <c r="F47" t="n">
-        <v>39.1225</v>
+        <v>39.2414</v>
       </c>
       <c r="G47" t="n">
-        <v>35.5926</v>
+        <v>35.6436</v>
       </c>
       <c r="H47" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I47" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>17 sep</t>
+          <t>18 sep</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>188.54</v>
+        <v>186.1</v>
       </c>
       <c r="M47" t="n">
-        <v>189.2</v>
+        <v>187.26</v>
       </c>
       <c r="N47" t="n">
-        <v>184.62</v>
+        <v>182.56</v>
       </c>
       <c r="O47" t="n">
-        <v>188</v>
+        <v>183.12</v>
       </c>
       <c r="P47" t="n">
-        <v>169.2896</v>
+        <v>170.2004</v>
       </c>
       <c r="Q47" t="n">
-        <v>165.6125</v>
+        <v>165.5062</v>
       </c>
       <c r="R47" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S47" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>17 sep</t>
+          <t>18 sep</t>
         </is>
       </c>
       <c r="V47" t="n">
-        <v>497.8</v>
+        <v>497.97</v>
       </c>
       <c r="W47" t="n">
-        <v>501.47</v>
+        <v>498.65</v>
       </c>
       <c r="X47" t="n">
-        <v>493.17</v>
+        <v>491.1</v>
       </c>
       <c r="Y47" t="n">
-        <v>497.75</v>
+        <v>493.78</v>
       </c>
       <c r="Z47" t="n">
-        <v>461.9966</v>
+        <v>464.1995</v>
       </c>
       <c r="AA47" t="n">
-        <v>430.0251</v>
+        <v>430.0757</v>
       </c>
       <c r="AB47" t="n">
         <v>535.3375423278808</v>
@@ -7367,84 +7389,84 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>18 sep</t>
+          <t>21 sep</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>41.465</v>
+        <v>41.04</v>
       </c>
       <c r="C48" t="n">
-        <v>41.5</v>
+        <v>41.4</v>
       </c>
       <c r="D48" t="n">
-        <v>40.955</v>
+        <v>40.775</v>
       </c>
       <c r="E48" t="n">
-        <v>41.315</v>
+        <v>40.775</v>
       </c>
       <c r="F48" t="n">
-        <v>39.2414</v>
+        <v>39.3341</v>
       </c>
       <c r="G48" t="n">
-        <v>35.6436</v>
+        <v>35.6939</v>
       </c>
       <c r="H48" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I48" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>18 sep</t>
+          <t>21 sep</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>186.1</v>
+        <v>184.7</v>
       </c>
       <c r="M48" t="n">
-        <v>187.26</v>
+        <v>185.86</v>
       </c>
       <c r="N48" t="n">
-        <v>182.56</v>
+        <v>182.48</v>
       </c>
       <c r="O48" t="n">
-        <v>183.12</v>
+        <v>182.86</v>
       </c>
       <c r="P48" t="n">
-        <v>170.2004</v>
+        <v>171.0432</v>
       </c>
       <c r="Q48" t="n">
-        <v>165.5062</v>
+        <v>165.4052</v>
       </c>
       <c r="R48" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S48" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>18 sep</t>
+          <t>21 sep</t>
         </is>
       </c>
       <c r="V48" t="n">
-        <v>497.97</v>
+        <v>494.95</v>
       </c>
       <c r="W48" t="n">
-        <v>498.65</v>
+        <v>501.87</v>
       </c>
       <c r="X48" t="n">
-        <v>491.1</v>
+        <v>491.33</v>
       </c>
       <c r="Y48" t="n">
-        <v>493.78</v>
+        <v>501.61</v>
       </c>
       <c r="Z48" t="n">
-        <v>464.1995</v>
+        <v>466.5442</v>
       </c>
       <c r="AA48" t="n">
-        <v>430.0757</v>
+        <v>430.1492</v>
       </c>
       <c r="AB48" t="n">
         <v>535.3375423278808</v>
@@ -7456,84 +7478,84 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>21 sep</t>
+          <t>22 sep</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>41.04</v>
+        <v>40.84</v>
       </c>
       <c r="C49" t="n">
-        <v>41.4</v>
+        <v>41.165</v>
       </c>
       <c r="D49" t="n">
-        <v>40.775</v>
+        <v>40.215</v>
       </c>
       <c r="E49" t="n">
-        <v>40.775</v>
+        <v>41.01</v>
       </c>
       <c r="F49" t="n">
-        <v>39.3341</v>
+        <v>39.4244</v>
       </c>
       <c r="G49" t="n">
-        <v>35.6939</v>
+        <v>35.746</v>
       </c>
       <c r="H49" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I49" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>21 sep</t>
+          <t>22 sep</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>184.7</v>
+        <v>182.14</v>
       </c>
       <c r="M49" t="n">
-        <v>185.86</v>
+        <v>187.48</v>
       </c>
       <c r="N49" t="n">
-        <v>182.48</v>
+        <v>181.52</v>
       </c>
       <c r="O49" t="n">
-        <v>182.86</v>
+        <v>182.32</v>
       </c>
       <c r="P49" t="n">
-        <v>171.0432</v>
+        <v>171.9552</v>
       </c>
       <c r="Q49" t="n">
-        <v>165.4052</v>
+        <v>165.2836</v>
       </c>
       <c r="R49" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S49" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>21 sep</t>
+          <t>22 sep</t>
         </is>
       </c>
       <c r="V49" t="n">
-        <v>494.95</v>
+        <v>507.32</v>
       </c>
       <c r="W49" t="n">
-        <v>501.87</v>
+        <v>508.5</v>
       </c>
       <c r="X49" t="n">
-        <v>491.33</v>
+        <v>493.65</v>
       </c>
       <c r="Y49" t="n">
-        <v>501.61</v>
+        <v>498</v>
       </c>
       <c r="Z49" t="n">
-        <v>466.5442</v>
+        <v>468.699</v>
       </c>
       <c r="AA49" t="n">
-        <v>430.1492</v>
+        <v>430.2656</v>
       </c>
       <c r="AB49" t="n">
         <v>535.3375423278808</v>
@@ -7545,84 +7567,84 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>22 sep</t>
+          <t>23 sep</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>40.84</v>
+        <v>41</v>
       </c>
       <c r="C50" t="n">
-        <v>41.165</v>
+        <v>41.755</v>
       </c>
       <c r="D50" t="n">
-        <v>40.215</v>
+        <v>40.995</v>
       </c>
       <c r="E50" t="n">
-        <v>41.01</v>
+        <v>41.69</v>
       </c>
       <c r="F50" t="n">
-        <v>39.4244</v>
+        <v>39.5272</v>
       </c>
       <c r="G50" t="n">
-        <v>35.746</v>
+        <v>35.8024</v>
       </c>
       <c r="H50" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I50" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>22 sep</t>
+          <t>23 sep</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>182.14</v>
+        <v>184.9</v>
       </c>
       <c r="M50" t="n">
-        <v>187.48</v>
+        <v>187.8</v>
       </c>
       <c r="N50" t="n">
-        <v>181.52</v>
+        <v>183.48</v>
       </c>
       <c r="O50" t="n">
-        <v>182.32</v>
+        <v>186.46</v>
       </c>
       <c r="P50" t="n">
-        <v>171.9552</v>
+        <v>172.9448</v>
       </c>
       <c r="Q50" t="n">
-        <v>165.2836</v>
+        <v>165.1675</v>
       </c>
       <c r="R50" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S50" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>22 sep</t>
+          <t>23 sep</t>
         </is>
       </c>
       <c r="V50" t="n">
-        <v>507.32</v>
+        <v>500.76</v>
       </c>
       <c r="W50" t="n">
-        <v>508.5</v>
+        <v>509.44</v>
       </c>
       <c r="X50" t="n">
-        <v>493.65</v>
+        <v>495.88</v>
       </c>
       <c r="Y50" t="n">
-        <v>498</v>
+        <v>500.59</v>
       </c>
       <c r="Z50" t="n">
-        <v>468.699</v>
+        <v>471.0267</v>
       </c>
       <c r="AA50" t="n">
-        <v>430.2656</v>
+        <v>430.3795</v>
       </c>
       <c r="AB50" t="n">
         <v>535.3375423278808</v>
@@ -7634,84 +7656,84 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>23 sep</t>
+          <t>24 sep</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>41</v>
+        <v>41.825</v>
       </c>
       <c r="C51" t="n">
-        <v>41.755</v>
+        <v>42.52</v>
       </c>
       <c r="D51" t="n">
-        <v>40.995</v>
+        <v>41.78</v>
       </c>
       <c r="E51" t="n">
-        <v>41.69</v>
+        <v>42.43</v>
       </c>
       <c r="F51" t="n">
-        <v>39.5272</v>
+        <v>39.6382</v>
       </c>
       <c r="G51" t="n">
-        <v>35.8024</v>
+        <v>35.8638</v>
       </c>
       <c r="H51" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I51" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>23 sep</t>
+          <t>24 sep</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>184.9</v>
+        <v>184.52</v>
       </c>
       <c r="M51" t="n">
-        <v>187.8</v>
+        <v>185.5</v>
       </c>
       <c r="N51" t="n">
-        <v>183.48</v>
+        <v>182.26</v>
       </c>
       <c r="O51" t="n">
-        <v>186.46</v>
+        <v>184.18</v>
       </c>
       <c r="P51" t="n">
-        <v>172.9448</v>
+        <v>173.8756</v>
       </c>
       <c r="Q51" t="n">
-        <v>165.1675</v>
+        <v>165.0554</v>
       </c>
       <c r="R51" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S51" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>23 sep</t>
+          <t>24 sep</t>
         </is>
       </c>
       <c r="V51" t="n">
-        <v>500.76</v>
+        <v>495.07</v>
       </c>
       <c r="W51" t="n">
-        <v>509.44</v>
+        <v>498.9</v>
       </c>
       <c r="X51" t="n">
-        <v>495.88</v>
+        <v>491.22</v>
       </c>
       <c r="Y51" t="n">
-        <v>500.59</v>
+        <v>497.93</v>
       </c>
       <c r="Z51" t="n">
-        <v>471.0267</v>
+        <v>473.0876</v>
       </c>
       <c r="AA51" t="n">
-        <v>430.3795</v>
+        <v>430.4686</v>
       </c>
       <c r="AB51" t="n">
         <v>535.3375423278808</v>
@@ -7723,84 +7745,84 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>24 sep</t>
+          <t>25 sep</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>41.825</v>
+        <v>41.99</v>
       </c>
       <c r="C52" t="n">
-        <v>42.52</v>
+        <v>42.33</v>
       </c>
       <c r="D52" t="n">
-        <v>41.78</v>
+        <v>41.71</v>
       </c>
       <c r="E52" t="n">
-        <v>42.43</v>
+        <v>42.06</v>
       </c>
       <c r="F52" t="n">
-        <v>39.6382</v>
+        <v>39.7263</v>
       </c>
       <c r="G52" t="n">
-        <v>35.8638</v>
+        <v>35.9239</v>
       </c>
       <c r="H52" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I52" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>24 sep</t>
+          <t>25 sep</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>184.52</v>
+        <v>184.42</v>
       </c>
       <c r="M52" t="n">
-        <v>185.5</v>
+        <v>185.92</v>
       </c>
       <c r="N52" t="n">
-        <v>182.26</v>
+        <v>183.76</v>
       </c>
       <c r="O52" t="n">
-        <v>184.18</v>
+        <v>185.92</v>
       </c>
       <c r="P52" t="n">
-        <v>173.8756</v>
+        <v>174.8356</v>
       </c>
       <c r="Q52" t="n">
-        <v>165.0554</v>
+        <v>164.9525</v>
       </c>
       <c r="R52" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S52" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>24 sep</t>
+          <t>25 sep</t>
         </is>
       </c>
       <c r="V52" t="n">
-        <v>495.07</v>
+        <v>499.04</v>
       </c>
       <c r="W52" t="n">
-        <v>498.9</v>
+        <v>519.4</v>
       </c>
       <c r="X52" t="n">
-        <v>491.22</v>
+        <v>497.25</v>
       </c>
       <c r="Y52" t="n">
-        <v>497.93</v>
+        <v>516.17</v>
       </c>
       <c r="Z52" t="n">
-        <v>473.0876</v>
+        <v>475.4041</v>
       </c>
       <c r="AA52" t="n">
-        <v>430.4686</v>
+        <v>430.6098</v>
       </c>
       <c r="AB52" t="n">
         <v>535.3375423278808</v>
@@ -7812,84 +7834,84 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>25 sep</t>
+          <t>28 sep</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>41.99</v>
+        <v>42.45</v>
       </c>
       <c r="C53" t="n">
-        <v>42.33</v>
+        <v>42.995</v>
       </c>
       <c r="D53" t="n">
-        <v>41.71</v>
+        <v>42.38</v>
       </c>
       <c r="E53" t="n">
-        <v>42.06</v>
+        <v>42.725</v>
       </c>
       <c r="F53" t="n">
-        <v>39.7263</v>
+        <v>39.8301</v>
       </c>
       <c r="G53" t="n">
-        <v>35.9239</v>
+        <v>35.9888</v>
       </c>
       <c r="H53" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I53" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>25 sep</t>
+          <t>28 sep</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>184.42</v>
+        <v>185.2</v>
       </c>
       <c r="M53" t="n">
-        <v>185.92</v>
+        <v>186.76</v>
       </c>
       <c r="N53" t="n">
-        <v>183.76</v>
+        <v>178.88</v>
       </c>
       <c r="O53" t="n">
-        <v>185.92</v>
+        <v>184.02</v>
       </c>
       <c r="P53" t="n">
-        <v>174.8356</v>
+        <v>175.7508</v>
       </c>
       <c r="Q53" t="n">
-        <v>164.9525</v>
+        <v>164.8355</v>
       </c>
       <c r="R53" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S53" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>25 sep</t>
+          <t>28 sep</t>
         </is>
       </c>
       <c r="V53" t="n">
-        <v>499.04</v>
+        <v>505.47</v>
       </c>
       <c r="W53" t="n">
-        <v>519.4</v>
+        <v>513.33</v>
       </c>
       <c r="X53" t="n">
-        <v>497.25</v>
+        <v>502.22</v>
       </c>
       <c r="Y53" t="n">
-        <v>516.17</v>
+        <v>509.22</v>
       </c>
       <c r="Z53" t="n">
-        <v>475.4041</v>
+        <v>477.7269</v>
       </c>
       <c r="AA53" t="n">
-        <v>430.6098</v>
+        <v>430.7113</v>
       </c>
       <c r="AB53" t="n">
         <v>535.3375423278808</v>
@@ -7901,84 +7923,84 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>28 sep</t>
+          <t>29 sep</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>42.45</v>
+        <v>42.57</v>
       </c>
       <c r="C54" t="n">
-        <v>42.995</v>
+        <v>42.665</v>
       </c>
       <c r="D54" t="n">
-        <v>42.38</v>
+        <v>41.73</v>
       </c>
       <c r="E54" t="n">
-        <v>42.725</v>
+        <v>42.05</v>
       </c>
       <c r="F54" t="n">
-        <v>39.8301</v>
+        <v>39.9146</v>
       </c>
       <c r="G54" t="n">
-        <v>35.9888</v>
+        <v>36.0498</v>
       </c>
       <c r="H54" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I54" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>28 sep</t>
+          <t>29 sep</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>185.2</v>
+        <v>183.22</v>
       </c>
       <c r="M54" t="n">
-        <v>186.76</v>
+        <v>186.34</v>
       </c>
       <c r="N54" t="n">
-        <v>178.88</v>
+        <v>182.28</v>
       </c>
       <c r="O54" t="n">
-        <v>184.02</v>
+        <v>185.32</v>
       </c>
       <c r="P54" t="n">
-        <v>175.7508</v>
+        <v>176.7288</v>
       </c>
       <c r="Q54" t="n">
-        <v>164.8355</v>
+        <v>164.733</v>
       </c>
       <c r="R54" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S54" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>28 sep</t>
+          <t>29 sep</t>
         </is>
       </c>
       <c r="V54" t="n">
-        <v>505.47</v>
+        <v>508.31</v>
       </c>
       <c r="W54" t="n">
-        <v>513.33</v>
+        <v>513.64</v>
       </c>
       <c r="X54" t="n">
-        <v>502.22</v>
+        <v>502.4</v>
       </c>
       <c r="Y54" t="n">
-        <v>509.22</v>
+        <v>508.96</v>
       </c>
       <c r="Z54" t="n">
-        <v>477.7269</v>
+        <v>479.8754</v>
       </c>
       <c r="AA54" t="n">
-        <v>430.7113</v>
+        <v>430.8784</v>
       </c>
       <c r="AB54" t="n">
         <v>535.3375423278808</v>
@@ -7990,84 +8012,84 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>29 sep</t>
+          <t>30 sep</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>42.57</v>
+        <v>41.975</v>
       </c>
       <c r="C55" t="n">
-        <v>42.665</v>
+        <v>42.095</v>
       </c>
       <c r="D55" t="n">
-        <v>41.73</v>
+        <v>41.58</v>
       </c>
       <c r="E55" t="n">
-        <v>42.05</v>
+        <v>41.91</v>
       </c>
       <c r="F55" t="n">
-        <v>39.9146</v>
+        <v>39.9874</v>
       </c>
       <c r="G55" t="n">
-        <v>36.0498</v>
+        <v>36.1135</v>
       </c>
       <c r="H55" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I55" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>29 sep</t>
+          <t>30 sep</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>183.22</v>
+        <v>184.5</v>
       </c>
       <c r="M55" t="n">
-        <v>186.34</v>
+        <v>186.2</v>
       </c>
       <c r="N55" t="n">
-        <v>182.28</v>
+        <v>181.06</v>
       </c>
       <c r="O55" t="n">
-        <v>185.32</v>
+        <v>185.66</v>
       </c>
       <c r="P55" t="n">
-        <v>176.7288</v>
+        <v>177.8012</v>
       </c>
       <c r="Q55" t="n">
-        <v>164.733</v>
+        <v>164.6377</v>
       </c>
       <c r="R55" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S55" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>29 sep</t>
+          <t>30 sep</t>
         </is>
       </c>
       <c r="V55" t="n">
-        <v>508.31</v>
+        <v>511.61</v>
       </c>
       <c r="W55" t="n">
-        <v>513.64</v>
+        <v>519.83</v>
       </c>
       <c r="X55" t="n">
-        <v>502.4</v>
+        <v>510.31</v>
       </c>
       <c r="Y55" t="n">
-        <v>508.96</v>
+        <v>512.9</v>
       </c>
       <c r="Z55" t="n">
-        <v>479.8754</v>
+        <v>482.1933</v>
       </c>
       <c r="AA55" t="n">
-        <v>430.8784</v>
+        <v>431.0408</v>
       </c>
       <c r="AB55" t="n">
         <v>535.3375423278808</v>
@@ -8079,84 +8101,84 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>30 sep</t>
+          <t>1 okt</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>41.975</v>
+        <v>41.625</v>
       </c>
       <c r="C56" t="n">
-        <v>42.095</v>
+        <v>42.36</v>
       </c>
       <c r="D56" t="n">
-        <v>41.58</v>
+        <v>41.165</v>
       </c>
       <c r="E56" t="n">
-        <v>41.91</v>
+        <v>42.24</v>
       </c>
       <c r="F56" t="n">
-        <v>39.9874</v>
+        <v>40.0562</v>
       </c>
       <c r="G56" t="n">
-        <v>36.1135</v>
+        <v>36.1777</v>
       </c>
       <c r="H56" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I56" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>30 sep</t>
+          <t>1 okt</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>184.5</v>
+        <v>184.68</v>
       </c>
       <c r="M56" t="n">
-        <v>186.2</v>
+        <v>190.26</v>
       </c>
       <c r="N56" t="n">
-        <v>181.06</v>
+        <v>181.34</v>
       </c>
       <c r="O56" t="n">
-        <v>185.66</v>
+        <v>186.74</v>
       </c>
       <c r="P56" t="n">
-        <v>177.8012</v>
+        <v>178.9696</v>
       </c>
       <c r="Q56" t="n">
-        <v>164.6377</v>
+        <v>164.5407</v>
       </c>
       <c r="R56" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S56" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>30 sep</t>
+          <t>1 okt</t>
         </is>
       </c>
       <c r="V56" t="n">
-        <v>511.61</v>
+        <v>519.88</v>
       </c>
       <c r="W56" t="n">
-        <v>519.83</v>
+        <v>522.85</v>
       </c>
       <c r="X56" t="n">
-        <v>510.31</v>
+        <v>512.17</v>
       </c>
       <c r="Y56" t="n">
-        <v>512.9</v>
+        <v>512.8</v>
       </c>
       <c r="Z56" t="n">
-        <v>482.1933</v>
+        <v>484.6572</v>
       </c>
       <c r="AA56" t="n">
-        <v>431.0408</v>
+        <v>431.2272</v>
       </c>
       <c r="AB56" t="n">
         <v>535.3375423278808</v>
@@ -8168,84 +8190,84 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1 okt</t>
+          <t>2 okt</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>41.625</v>
+        <v>42.11</v>
       </c>
       <c r="C57" t="n">
-        <v>42.36</v>
+        <v>42.745</v>
       </c>
       <c r="D57" t="n">
-        <v>41.165</v>
+        <v>41.985</v>
       </c>
       <c r="E57" t="n">
-        <v>42.24</v>
+        <v>42.4</v>
       </c>
       <c r="F57" t="n">
-        <v>40.0562</v>
+        <v>40.1364</v>
       </c>
       <c r="G57" t="n">
-        <v>36.1777</v>
+        <v>36.2422</v>
       </c>
       <c r="H57" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I57" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>1 okt</t>
+          <t>2 okt</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>184.68</v>
+        <v>187.82</v>
       </c>
       <c r="M57" t="n">
-        <v>190.26</v>
+        <v>188.74</v>
       </c>
       <c r="N57" t="n">
-        <v>181.34</v>
+        <v>183.92</v>
       </c>
       <c r="O57" t="n">
-        <v>186.74</v>
+        <v>183.92</v>
       </c>
       <c r="P57" t="n">
-        <v>178.9696</v>
+        <v>179.844</v>
       </c>
       <c r="Q57" t="n">
-        <v>164.5407</v>
+        <v>164.4442</v>
       </c>
       <c r="R57" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S57" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>1 okt</t>
+          <t>2 okt</t>
         </is>
       </c>
       <c r="V57" t="n">
-        <v>519.88</v>
+        <v>519.39</v>
       </c>
       <c r="W57" t="n">
-        <v>522.85</v>
+        <v>522.5</v>
       </c>
       <c r="X57" t="n">
-        <v>512.17</v>
+        <v>513.66</v>
       </c>
       <c r="Y57" t="n">
-        <v>512.8</v>
+        <v>517.53</v>
       </c>
       <c r="Z57" t="n">
-        <v>484.6572</v>
+        <v>487.3905</v>
       </c>
       <c r="AA57" t="n">
-        <v>431.2272</v>
+        <v>431.4557</v>
       </c>
       <c r="AB57" t="n">
         <v>535.3375423278808</v>
@@ -8257,84 +8279,84 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2 okt</t>
+          <t>5 okt</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>42.11</v>
+        <v>42.645</v>
       </c>
       <c r="C58" t="n">
-        <v>42.745</v>
+        <v>43.11</v>
       </c>
       <c r="D58" t="n">
-        <v>41.985</v>
+        <v>42.35</v>
       </c>
       <c r="E58" t="n">
-        <v>42.4</v>
+        <v>42.865</v>
       </c>
       <c r="F58" t="n">
-        <v>40.1364</v>
+        <v>40.2347</v>
       </c>
       <c r="G58" t="n">
-        <v>36.2422</v>
+        <v>36.3069</v>
       </c>
       <c r="H58" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I58" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2 okt</t>
+          <t>5 okt</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>187.82</v>
+        <v>185.06</v>
       </c>
       <c r="M58" t="n">
-        <v>188.74</v>
+        <v>188.5</v>
       </c>
       <c r="N58" t="n">
-        <v>183.92</v>
+        <v>184.66</v>
       </c>
       <c r="O58" t="n">
-        <v>183.92</v>
+        <v>185.04</v>
       </c>
       <c r="P58" t="n">
-        <v>179.844</v>
+        <v>180.5192</v>
       </c>
       <c r="Q58" t="n">
-        <v>164.4442</v>
+        <v>164.3515</v>
       </c>
       <c r="R58" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S58" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>2 okt</t>
+          <t>5 okt</t>
         </is>
       </c>
       <c r="V58" t="n">
-        <v>519.39</v>
+        <v>521.62</v>
       </c>
       <c r="W58" t="n">
-        <v>522.5</v>
+        <v>532.35</v>
       </c>
       <c r="X58" t="n">
-        <v>513.66</v>
+        <v>521.47</v>
       </c>
       <c r="Y58" t="n">
-        <v>517.53</v>
+        <v>525.1799999999999</v>
       </c>
       <c r="Z58" t="n">
-        <v>487.3905</v>
+        <v>490.2745</v>
       </c>
       <c r="AA58" t="n">
-        <v>431.4557</v>
+        <v>431.7147</v>
       </c>
       <c r="AB58" t="n">
         <v>535.3375423278808</v>
@@ -8346,84 +8368,84 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>5 okt</t>
+          <t>6 okt</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>42.645</v>
+        <v>42.86</v>
       </c>
       <c r="C59" t="n">
-        <v>43.11</v>
+        <v>43.285</v>
       </c>
       <c r="D59" t="n">
-        <v>42.35</v>
+        <v>42.43</v>
       </c>
       <c r="E59" t="n">
-        <v>42.865</v>
+        <v>43.185</v>
       </c>
       <c r="F59" t="n">
-        <v>40.2347</v>
+        <v>40.349</v>
       </c>
       <c r="G59" t="n">
-        <v>36.3069</v>
+        <v>36.3726</v>
       </c>
       <c r="H59" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I59" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>5 okt</t>
+          <t>6 okt</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>185.06</v>
+        <v>186.56</v>
       </c>
       <c r="M59" t="n">
-        <v>188.5</v>
+        <v>190.22</v>
       </c>
       <c r="N59" t="n">
-        <v>184.66</v>
+        <v>186.06</v>
       </c>
       <c r="O59" t="n">
-        <v>185.04</v>
+        <v>188.6</v>
       </c>
       <c r="P59" t="n">
-        <v>180.5192</v>
+        <v>181.1064</v>
       </c>
       <c r="Q59" t="n">
-        <v>164.3515</v>
+        <v>164.2647</v>
       </c>
       <c r="R59" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S59" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>5 okt</t>
+          <t>6 okt</t>
         </is>
       </c>
       <c r="V59" t="n">
-        <v>521.62</v>
+        <v>531.6799999999999</v>
       </c>
       <c r="W59" t="n">
-        <v>532.35</v>
+        <v>535.6900000000001</v>
       </c>
       <c r="X59" t="n">
-        <v>521.47</v>
+        <v>528.78</v>
       </c>
       <c r="Y59" t="n">
-        <v>525.1799999999999</v>
+        <v>529.3</v>
       </c>
       <c r="Z59" t="n">
-        <v>490.2745</v>
+        <v>493.0931</v>
       </c>
       <c r="AA59" t="n">
-        <v>431.7147</v>
+        <v>431.9956</v>
       </c>
       <c r="AB59" t="n">
         <v>535.3375423278808</v>
@@ -8435,84 +8457,84 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>6 okt</t>
+          <t>7 okt</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>42.86</v>
+        <v>43.37</v>
       </c>
       <c r="C60" t="n">
-        <v>43.285</v>
+        <v>43.835</v>
       </c>
       <c r="D60" t="n">
-        <v>42.43</v>
+        <v>43.145</v>
       </c>
       <c r="E60" t="n">
-        <v>43.185</v>
+        <v>43.25</v>
       </c>
       <c r="F60" t="n">
-        <v>40.349</v>
+        <v>40.4451</v>
       </c>
       <c r="G60" t="n">
-        <v>36.3726</v>
+        <v>36.4388</v>
       </c>
       <c r="H60" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I60" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>6 okt</t>
+          <t>7 okt</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>186.56</v>
+        <v>187</v>
       </c>
       <c r="M60" t="n">
-        <v>190.22</v>
+        <v>188.72</v>
       </c>
       <c r="N60" t="n">
-        <v>186.06</v>
+        <v>186.04</v>
       </c>
       <c r="O60" t="n">
-        <v>188.6</v>
+        <v>187.62</v>
       </c>
       <c r="P60" t="n">
-        <v>181.1064</v>
+        <v>181.618</v>
       </c>
       <c r="Q60" t="n">
-        <v>164.2647</v>
+        <v>164.1762</v>
       </c>
       <c r="R60" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S60" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>6 okt</t>
+          <t>7 okt</t>
         </is>
       </c>
       <c r="V60" t="n">
-        <v>531.6799999999999</v>
+        <v>530.73</v>
       </c>
       <c r="W60" t="n">
-        <v>535.6900000000001</v>
+        <v>531.73</v>
       </c>
       <c r="X60" t="n">
-        <v>528.78</v>
+        <v>524.6900000000001</v>
       </c>
       <c r="Y60" t="n">
-        <v>529.3</v>
+        <v>529.76</v>
       </c>
       <c r="Z60" t="n">
-        <v>493.0931</v>
+        <v>495.8361</v>
       </c>
       <c r="AA60" t="n">
-        <v>431.9956</v>
+        <v>432.2398</v>
       </c>
       <c r="AB60" t="n">
         <v>535.3375423278808</v>
@@ -8524,84 +8546,84 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>7 okt</t>
+          <t>8 okt</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>43.37</v>
+        <v>43.555</v>
       </c>
       <c r="C61" t="n">
-        <v>43.835</v>
+        <v>44.815</v>
       </c>
       <c r="D61" t="n">
-        <v>43.145</v>
+        <v>43.5425</v>
       </c>
       <c r="E61" t="n">
-        <v>43.25</v>
+        <v>44.75</v>
       </c>
       <c r="F61" t="n">
-        <v>40.4451</v>
+        <v>40.5699</v>
       </c>
       <c r="G61" t="n">
-        <v>36.4388</v>
+        <v>36.5123</v>
       </c>
       <c r="H61" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I61" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>7 okt</t>
+          <t>8 okt</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>187</v>
+        <v>187.04</v>
       </c>
       <c r="M61" t="n">
-        <v>188.72</v>
+        <v>189.82</v>
       </c>
       <c r="N61" t="n">
-        <v>186.04</v>
+        <v>183.76</v>
       </c>
       <c r="O61" t="n">
-        <v>187.62</v>
+        <v>184.62</v>
       </c>
       <c r="P61" t="n">
-        <v>181.618</v>
+        <v>182.192</v>
       </c>
       <c r="Q61" t="n">
-        <v>164.1762</v>
+        <v>164.074</v>
       </c>
       <c r="R61" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S61" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>7 okt</t>
+          <t>8 okt</t>
         </is>
       </c>
       <c r="V61" t="n">
-        <v>530.73</v>
+        <v>529.8099999999999</v>
       </c>
       <c r="W61" t="n">
-        <v>531.73</v>
+        <v>533.51</v>
       </c>
       <c r="X61" t="n">
-        <v>524.6900000000001</v>
+        <v>518.79</v>
       </c>
       <c r="Y61" t="n">
-        <v>529.76</v>
+        <v>522.61</v>
       </c>
       <c r="Z61" t="n">
-        <v>495.8361</v>
+        <v>498.4921</v>
       </c>
       <c r="AA61" t="n">
-        <v>432.2398</v>
+        <v>432.4385</v>
       </c>
       <c r="AB61" t="n">
         <v>535.3375423278808</v>
@@ -8613,84 +8635,84 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>8 okt</t>
+          <t>9 okt</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>43.555</v>
+        <v>44.42</v>
       </c>
       <c r="C62" t="n">
-        <v>44.815</v>
+        <v>45.155</v>
       </c>
       <c r="D62" t="n">
-        <v>43.5425</v>
+        <v>43.94</v>
       </c>
       <c r="E62" t="n">
-        <v>44.75</v>
+        <v>45.035</v>
       </c>
       <c r="F62" t="n">
-        <v>40.5699</v>
+        <v>40.6842</v>
       </c>
       <c r="G62" t="n">
-        <v>36.5123</v>
+        <v>36.5866</v>
       </c>
       <c r="H62" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I62" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>8 okt</t>
+          <t>9 okt</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>187.04</v>
+        <v>188.98</v>
       </c>
       <c r="M62" t="n">
-        <v>189.82</v>
+        <v>192.58</v>
       </c>
       <c r="N62" t="n">
-        <v>183.76</v>
+        <v>188.86</v>
       </c>
       <c r="O62" t="n">
-        <v>184.62</v>
+        <v>191.46</v>
       </c>
       <c r="P62" t="n">
-        <v>182.192</v>
+        <v>182.8676</v>
       </c>
       <c r="Q62" t="n">
-        <v>164.074</v>
+        <v>164.0101</v>
       </c>
       <c r="R62" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S62" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>8 okt</t>
+          <t>9 okt</t>
         </is>
       </c>
       <c r="V62" t="n">
-        <v>529.8099999999999</v>
+        <v>528.24</v>
       </c>
       <c r="W62" t="n">
-        <v>533.51</v>
+        <v>537.22</v>
       </c>
       <c r="X62" t="n">
-        <v>518.79</v>
+        <v>526.24</v>
       </c>
       <c r="Y62" t="n">
-        <v>522.61</v>
+        <v>535.0700000000001</v>
       </c>
       <c r="Z62" t="n">
-        <v>498.4921</v>
+        <v>500.1885</v>
       </c>
       <c r="AA62" t="n">
-        <v>432.4385</v>
+        <v>432.7046</v>
       </c>
       <c r="AB62" t="n">
         <v>535.3375423278808</v>
@@ -8702,84 +8724,84 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>9 okt</t>
+          <t>12 okt</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>44.42</v>
+        <v>44.725</v>
       </c>
       <c r="C63" t="n">
-        <v>45.155</v>
+        <v>45.81</v>
       </c>
       <c r="D63" t="n">
-        <v>43.94</v>
+        <v>44.695</v>
       </c>
       <c r="E63" t="n">
-        <v>45.035</v>
+        <v>45.56</v>
       </c>
       <c r="F63" t="n">
-        <v>40.6842</v>
+        <v>40.8072</v>
       </c>
       <c r="G63" t="n">
-        <v>36.5866</v>
+        <v>36.6625</v>
       </c>
       <c r="H63" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I63" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>9 okt</t>
+          <t>12 okt</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>188.98</v>
+        <v>190.58</v>
       </c>
       <c r="M63" t="n">
-        <v>192.58</v>
+        <v>197.88</v>
       </c>
       <c r="N63" t="n">
-        <v>188.86</v>
+        <v>189.78</v>
       </c>
       <c r="O63" t="n">
-        <v>191.46</v>
+        <v>194.46</v>
       </c>
       <c r="P63" t="n">
-        <v>182.8676</v>
+        <v>183.464</v>
       </c>
       <c r="Q63" t="n">
-        <v>164.0101</v>
+        <v>163.9576</v>
       </c>
       <c r="R63" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S63" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>9 okt</t>
+          <t>12 okt</t>
         </is>
       </c>
       <c r="V63" t="n">
-        <v>528.24</v>
+        <v>537.53</v>
       </c>
       <c r="W63" t="n">
-        <v>537.22</v>
+        <v>542.74</v>
       </c>
       <c r="X63" t="n">
-        <v>526.24</v>
+        <v>535.7</v>
       </c>
       <c r="Y63" t="n">
-        <v>535.0700000000001</v>
+        <v>541.15</v>
       </c>
       <c r="Z63" t="n">
-        <v>500.1885</v>
+        <v>501.7346</v>
       </c>
       <c r="AA63" t="n">
-        <v>432.7046</v>
+        <v>432.9914</v>
       </c>
       <c r="AB63" t="n">
         <v>535.3375423278808</v>
@@ -8791,84 +8813,84 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>12 okt</t>
+          <t>13 okt</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>44.725</v>
+        <v>45.69</v>
       </c>
       <c r="C64" t="n">
-        <v>45.81</v>
+        <v>45.97</v>
       </c>
       <c r="D64" t="n">
-        <v>44.695</v>
+        <v>45.35</v>
       </c>
       <c r="E64" t="n">
-        <v>45.56</v>
+        <v>45.95</v>
       </c>
       <c r="F64" t="n">
-        <v>40.8072</v>
+        <v>40.9565</v>
       </c>
       <c r="G64" t="n">
-        <v>36.6625</v>
+        <v>36.7398</v>
       </c>
       <c r="H64" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I64" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>12 okt</t>
+          <t>13 okt</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>190.58</v>
+        <v>196</v>
       </c>
       <c r="M64" t="n">
-        <v>197.88</v>
+        <v>198.18</v>
       </c>
       <c r="N64" t="n">
-        <v>189.78</v>
+        <v>194.02</v>
       </c>
       <c r="O64" t="n">
-        <v>194.46</v>
+        <v>197.28</v>
       </c>
       <c r="P64" t="n">
-        <v>183.464</v>
+        <v>184.062</v>
       </c>
       <c r="Q64" t="n">
-        <v>163.9576</v>
+        <v>163.9196</v>
       </c>
       <c r="R64" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S64" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>12 okt</t>
+          <t>13 okt</t>
         </is>
       </c>
       <c r="V64" t="n">
-        <v>537.53</v>
+        <v>544.64</v>
       </c>
       <c r="W64" t="n">
-        <v>542.74</v>
+        <v>551.15</v>
       </c>
       <c r="X64" t="n">
-        <v>535.7</v>
+        <v>543.0599999999999</v>
       </c>
       <c r="Y64" t="n">
-        <v>541.15</v>
+        <v>543.45</v>
       </c>
       <c r="Z64" t="n">
-        <v>501.7346</v>
+        <v>502.8689</v>
       </c>
       <c r="AA64" t="n">
-        <v>432.9914</v>
+        <v>433.2839</v>
       </c>
       <c r="AB64" t="n">
         <v>535.3375423278808</v>
@@ -8880,84 +8902,84 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>13 okt</t>
+          <t>14 okt</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>45.69</v>
+        <v>45.95</v>
       </c>
       <c r="C65" t="n">
-        <v>45.97</v>
+        <v>46.675</v>
       </c>
       <c r="D65" t="n">
-        <v>45.35</v>
+        <v>45.91</v>
       </c>
       <c r="E65" t="n">
-        <v>45.95</v>
+        <v>46.455</v>
       </c>
       <c r="F65" t="n">
-        <v>40.9565</v>
+        <v>41.125</v>
       </c>
       <c r="G65" t="n">
-        <v>36.7398</v>
+        <v>36.8183</v>
       </c>
       <c r="H65" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I65" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>13 okt</t>
+          <t>14 okt</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>196</v>
+        <v>196.6</v>
       </c>
       <c r="M65" t="n">
-        <v>198.18</v>
+        <v>199.36</v>
       </c>
       <c r="N65" t="n">
-        <v>194.02</v>
+        <v>195.26</v>
       </c>
       <c r="O65" t="n">
-        <v>197.28</v>
+        <v>196.94</v>
       </c>
       <c r="P65" t="n">
-        <v>184.062</v>
+        <v>184.6156</v>
       </c>
       <c r="Q65" t="n">
-        <v>163.9196</v>
+        <v>163.9114</v>
       </c>
       <c r="R65" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S65" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>13 okt</t>
+          <t>14 okt</t>
         </is>
       </c>
       <c r="V65" t="n">
-        <v>544.64</v>
+        <v>545.27</v>
       </c>
       <c r="W65" t="n">
-        <v>551.15</v>
+        <v>545.75</v>
       </c>
       <c r="X65" t="n">
-        <v>543.0599999999999</v>
+        <v>532.54</v>
       </c>
       <c r="Y65" t="n">
-        <v>543.45</v>
+        <v>533.6900000000001</v>
       </c>
       <c r="Z65" t="n">
-        <v>502.8689</v>
+        <v>503.705</v>
       </c>
       <c r="AA65" t="n">
-        <v>433.2839</v>
+        <v>433.5292</v>
       </c>
       <c r="AB65" t="n">
         <v>535.3375423278808</v>
@@ -8969,84 +8991,84 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>14 okt</t>
+          <t>15 okt</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>45.95</v>
+        <v>46.295</v>
       </c>
       <c r="C66" t="n">
-        <v>46.675</v>
+        <v>46.735</v>
       </c>
       <c r="D66" t="n">
-        <v>45.91</v>
+        <v>46.125</v>
       </c>
       <c r="E66" t="n">
-        <v>46.42</v>
+        <v>46.47</v>
       </c>
       <c r="F66" t="n">
-        <v>41.1243</v>
+        <v>41.2866</v>
       </c>
       <c r="G66" t="n">
-        <v>36.8181</v>
+        <v>36.8971</v>
       </c>
       <c r="H66" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I66" t="n">
-        <v>43.69749859401158</v>
+        <v>43.77107320513044</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>14 okt</t>
+          <t>15 okt</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>196.6</v>
+        <v>199.48</v>
       </c>
       <c r="M66" t="n">
-        <v>199.36</v>
+        <v>203</v>
       </c>
       <c r="N66" t="n">
-        <v>195.26</v>
+        <v>196.98</v>
       </c>
       <c r="O66" t="n">
-        <v>197.44</v>
+        <v>201.7</v>
       </c>
       <c r="P66" t="n">
-        <v>184.6256</v>
+        <v>185.23</v>
       </c>
       <c r="Q66" t="n">
-        <v>163.9139</v>
+        <v>163.9061</v>
       </c>
       <c r="R66" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S66" t="n">
-        <v>181.19713810512</v>
+        <v>184.6214196341379</v>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>14 okt</t>
+          <t>15 okt</t>
         </is>
       </c>
       <c r="V66" t="n">
-        <v>545.27</v>
+        <v>533.655</v>
       </c>
       <c r="W66" t="n">
-        <v>545.75</v>
+        <v>541.1331</v>
       </c>
       <c r="X66" t="n">
-        <v>532.54</v>
+        <v>531.22</v>
       </c>
       <c r="Y66" t="n">
-        <v>533.6900000000001</v>
+        <v>539.33</v>
       </c>
       <c r="Z66" t="n">
-        <v>503.705</v>
+        <v>504.7607</v>
       </c>
       <c r="AA66" t="n">
-        <v>433.5292</v>
+        <v>433.8057</v>
       </c>
       <c r="AB66" t="n">
         <v>535.3375423278808</v>

--- a/rapporten/trend-agent.xlsx
+++ b/rapporten/trend-agent.xlsx
@@ -1944,7 +1944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2080,6 +2080,28 @@
       </c>
       <c r="E6" s="3">
         <f>B6/$B$2-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>10028.47</v>
+      </c>
+      <c r="C7" s="2">
+        <f>B7-B6</f>
+        <v/>
+      </c>
+      <c r="D7" s="3">
+        <f>B7/B6-1</f>
+        <v/>
+      </c>
+      <c r="E7" s="3">
+        <f>B7/$B$2-1</f>
         <v/>
       </c>
     </row>
@@ -2223,38 +2245,38 @@
     <row r="6" ht="22" customHeight="1">
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Shell (SHELL.AS)  ·  46,47 EUR</t>
+          <t>Shell (SHELL.AS)  ·  46,89 EUR</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>SAP (SAP.DE)  ·  201,70 EUR</t>
+          <t>SAP (SAP.DE)  ·  199,02 EUR</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>Gestegen: 23,4% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +3,1% (winst). De bot verkoopt als de koers onder 43,77 zakt (-5,8%).</t>
+          <t>Gestegen: 24,9% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +4,1% (winst). De bot verkoopt als de koers onder 44,19 zakt (-5,8%).</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>Gestegen: 46,2% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +5,3% (winst). De bot verkoopt als de koers onder 184,62 zakt (-8,5%).</t>
+          <t>Gestegen: 43,9% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +3,9% (winst). De bot verkoopt als de koers onder 185,13 zakt (-7,0%).</t>
         </is>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Microsoft (MSFT)  ·  539,33 USD</t>
+          <t>Microsoft (MSFT)  ·  528,95 USD</t>
         </is>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Gestegen: 34,7% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +0,7% (winst). De bot verkoopt als de koers onder 509,90 zakt (-5,5%).</t>
+          <t>Gestegen: 34,6% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: -1,2% (verlies). De bot verkoopt als de koers onder 509,90 zakt (-3,6%).</t>
         </is>
       </c>
     </row>
@@ -2355,7 +2377,7 @@
         <v>45.06</v>
       </c>
       <c r="F2" t="n">
-        <v>43.77</v>
+        <v>44.19</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2394,7 +2416,7 @@
         <v>191.56</v>
       </c>
       <c r="F3" t="n">
-        <v>184.62</v>
+        <v>185.13</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -2733,19 +2755,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.164</v>
+        <v>0.168</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.2381862222388915</v>
+        <v>0.2395676373843243</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1110579885961303</v>
+        <v>0.1282482637207707</v>
       </c>
       <c r="H2" t="n">
-        <v>1.02</v>
+        <v>0.95</v>
       </c>
       <c r="I2" t="n">
-        <v>46.47</v>
+        <v>46.89</v>
       </c>
     </row>
     <row r="3">
@@ -2754,12 +2776,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>WKL.AS</t>
+          <t>SAP.DE</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Wolters Kluwer</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2768,19 +2790,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.124</v>
+        <v>0.118</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.3405060169515768</v>
+        <v>0.458877048407452</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.1789658335213713</v>
+        <v>0.05861704400245182</v>
       </c>
       <c r="H3" t="n">
-        <v>1.16</v>
+        <v>0.76</v>
       </c>
       <c r="I3" t="n">
-        <v>81.16</v>
+        <v>199.02</v>
       </c>
     </row>
     <row r="4">
@@ -2789,12 +2811,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SAP.DE</t>
+          <t>WKL.AS</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Wolters Kluwer</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2803,19 +2825,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.121</v>
+        <v>0.117</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.458845689005648</v>
+        <v>0.3816995948695561</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.08115351408542626</v>
+        <v>0.1660958773618408</v>
       </c>
       <c r="H4" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="I4" t="n">
-        <v>201.7</v>
+        <v>81.72</v>
       </c>
     </row>
     <row r="5">
@@ -2824,12 +2846,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>XLE</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Energie-ETF</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2838,19 +2860,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.107</v>
+        <v>0.112</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.3720616506602334</v>
+        <v>0.1845972630411206</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.1000000622426656</v>
+        <v>0.06444725185155553</v>
       </c>
       <c r="H5" t="n">
-        <v>0.92</v>
+        <v>1.11</v>
       </c>
       <c r="I5" t="n">
-        <v>539.33</v>
+        <v>68.23</v>
       </c>
     </row>
     <row r="6">
@@ -2873,19 +2895,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.095</v>
+        <v>0.109</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.1928670152973544</v>
+        <v>0.214201341584364</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.06937292471322043</v>
+        <v>0.09622092879266231</v>
       </c>
       <c r="H6" t="n">
-        <v>0.96</v>
+        <v>0.87</v>
       </c>
       <c r="I6" t="n">
-        <v>174.65</v>
+        <v>178.98</v>
       </c>
     </row>
     <row r="7">
@@ -2894,12 +2916,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>XLE</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Energie-ETF</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2908,19 +2930,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.094</v>
+        <v>0.09</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.1606375865113454</v>
+        <v>0.118584115369734</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.04553455585461719</v>
+        <v>0.08825992631827484</v>
       </c>
       <c r="H7" t="n">
-        <v>1.07</v>
+        <v>0.93</v>
       </c>
       <c r="I7" t="n">
-        <v>66.55</v>
+        <v>402.58</v>
       </c>
     </row>
     <row r="8">
@@ -2929,12 +2951,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2946,16 +2968,16 @@
         <v>0.08699999999999999</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.1165282612920207</v>
+        <v>0.3173227071769877</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.0772922491948338</v>
+        <v>0.06268209383632595</v>
       </c>
       <c r="H8" t="n">
-        <v>1.02</v>
+        <v>0.87</v>
       </c>
       <c r="I8" t="n">
-        <v>399.6</v>
+        <v>528.95</v>
       </c>
     </row>
     <row r="9">
@@ -2978,19 +3000,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.079</v>
+        <v>0.06</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.1426303106972868</v>
+        <v>0.1178118803253723</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.01570314902035075</v>
+        <v>0.02207572811713332</v>
       </c>
       <c r="H9" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>80.34999999999999</v>
+        <v>80.45</v>
       </c>
     </row>
     <row r="10">
@@ -2999,33 +3021,33 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>OR.PA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Nasdaq-100 ETF</t>
+          <t>L'Oreal</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.078</v>
+        <v>0.054</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.04813342696777312</v>
+        <v>0.07287130324360569</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.03416769022464061</v>
+        <v>0.06906077237170871</v>
       </c>
       <c r="H10" t="n">
-        <v>1.41</v>
+        <v>0.97</v>
       </c>
       <c r="I10" t="n">
-        <v>728.04</v>
+        <v>406.35</v>
       </c>
     </row>
     <row r="11">
@@ -3048,19 +3070,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.077</v>
+        <v>0.051</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.5145791857122965</v>
+        <v>0.3795327427459936</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.1500516474223639</v>
+        <v>0.0555492111949154</v>
       </c>
       <c r="H11" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="I11" t="n">
-        <v>200.5</v>
+        <v>186.03</v>
       </c>
     </row>
   </sheetData>
@@ -3331,75 +3353,75 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>17 jul</t>
+          <t>20 jul</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>36.912</v>
+        <v>38.0653</v>
       </c>
       <c r="C2" t="n">
-        <v>37.8871</v>
+        <v>38.1742</v>
       </c>
       <c r="D2" t="n">
-        <v>36.912</v>
+        <v>37.1496</v>
       </c>
       <c r="E2" t="n">
-        <v>37.6594</v>
+        <v>37.5307</v>
       </c>
       <c r="F2" t="n">
-        <v>35.6614</v>
+        <v>35.7021</v>
       </c>
       <c r="H2" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I2" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>17 jul</t>
+          <t>20 jul</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>140.6</v>
+        <v>138</v>
       </c>
       <c r="M2" t="n">
-        <v>141.54</v>
+        <v>140.04</v>
       </c>
       <c r="N2" t="n">
-        <v>137.32</v>
+        <v>134.98</v>
       </c>
       <c r="O2" t="n">
-        <v>137.92</v>
+        <v>138.26</v>
       </c>
       <c r="P2" t="n">
-        <v>144.652</v>
+        <v>144.528</v>
       </c>
       <c r="R2" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S2" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>16 jul</t>
+          <t>17 jul</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>397.5616</v>
+        <v>394.118</v>
       </c>
       <c r="W2" t="n">
-        <v>405.2271</v>
+        <v>397.6414</v>
       </c>
       <c r="X2" t="n">
-        <v>391.3133</v>
+        <v>388.6583</v>
       </c>
       <c r="Y2" t="n">
-        <v>400.3463</v>
+        <v>393.08</v>
       </c>
       <c r="Z2" t="n">
-        <v>400.8928</v>
+        <v>400.5601</v>
       </c>
       <c r="AB2" t="n">
         <v>535.3375423278808</v>
@@ -3411,75 +3433,75 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20 jul</t>
+          <t>21 jul</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38.0653</v>
+        <v>37.5703</v>
       </c>
       <c r="C3" t="n">
-        <v>38.1742</v>
+        <v>37.8277</v>
       </c>
       <c r="D3" t="n">
-        <v>37.1496</v>
+        <v>37.4169</v>
       </c>
       <c r="E3" t="n">
-        <v>37.5307</v>
+        <v>37.8277</v>
       </c>
       <c r="F3" t="n">
-        <v>35.7021</v>
+        <v>35.7452</v>
       </c>
       <c r="H3" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I3" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>20 jul</t>
+          <t>21 jul</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>138</v>
+        <v>137.74</v>
       </c>
       <c r="M3" t="n">
-        <v>140.04</v>
+        <v>137.84</v>
       </c>
       <c r="N3" t="n">
-        <v>134.98</v>
+        <v>135.34</v>
       </c>
       <c r="O3" t="n">
-        <v>138.26</v>
+        <v>136.42</v>
       </c>
       <c r="P3" t="n">
-        <v>144.528</v>
+        <v>144.4084</v>
       </c>
       <c r="R3" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S3" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>17 jul</t>
+          <t>20 jul</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>394.118</v>
+        <v>390.6746</v>
       </c>
       <c r="W3" t="n">
-        <v>397.6414</v>
+        <v>402.4224</v>
       </c>
       <c r="X3" t="n">
-        <v>388.6583</v>
+        <v>388.9179</v>
       </c>
       <c r="Y3" t="n">
-        <v>393.08</v>
+        <v>401.5341</v>
       </c>
       <c r="Z3" t="n">
-        <v>400.5601</v>
+        <v>400.345</v>
       </c>
       <c r="AB3" t="n">
         <v>535.3375423278808</v>
@@ -3491,75 +3513,75 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>21 jul</t>
+          <t>22 jul</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>37.5703</v>
+        <v>38.095</v>
       </c>
       <c r="C4" t="n">
-        <v>37.8277</v>
+        <v>38.6098</v>
       </c>
       <c r="D4" t="n">
-        <v>37.4169</v>
+        <v>37.9267</v>
       </c>
       <c r="E4" t="n">
-        <v>37.8277</v>
+        <v>38.2682</v>
       </c>
       <c r="F4" t="n">
-        <v>35.7452</v>
+        <v>35.799</v>
       </c>
       <c r="H4" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I4" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>21 jul</t>
+          <t>22 jul</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>137.74</v>
+        <v>136.02</v>
       </c>
       <c r="M4" t="n">
-        <v>137.84</v>
+        <v>136.4</v>
       </c>
       <c r="N4" t="n">
-        <v>135.34</v>
+        <v>132.04</v>
       </c>
       <c r="O4" t="n">
-        <v>136.42</v>
+        <v>132.04</v>
       </c>
       <c r="P4" t="n">
-        <v>144.4084</v>
+        <v>144.324</v>
       </c>
       <c r="R4" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S4" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>20 jul</t>
+          <t>21 jul</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>390.6746</v>
+        <v>398.0606</v>
       </c>
       <c r="W4" t="n">
-        <v>402.4224</v>
+        <v>400.7156</v>
       </c>
       <c r="X4" t="n">
-        <v>388.9179</v>
+        <v>395.5753</v>
       </c>
       <c r="Y4" t="n">
-        <v>401.5341</v>
+        <v>397.0026</v>
       </c>
       <c r="Z4" t="n">
-        <v>400.345</v>
+        <v>399.9036</v>
       </c>
       <c r="AB4" t="n">
         <v>535.3375423278808</v>
@@ -3571,75 +3593,75 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>22 jul</t>
+          <t>23 jul</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>38.095</v>
+        <v>38.491</v>
       </c>
       <c r="C5" t="n">
-        <v>38.6098</v>
+        <v>39.0454</v>
       </c>
       <c r="D5" t="n">
-        <v>37.9267</v>
+        <v>38.3425</v>
       </c>
       <c r="E5" t="n">
-        <v>38.2682</v>
+        <v>38.8028</v>
       </c>
       <c r="F5" t="n">
-        <v>35.799</v>
+        <v>35.863</v>
       </c>
       <c r="H5" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I5" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>22 jul</t>
+          <t>23 jul</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>136.02</v>
+        <v>131</v>
       </c>
       <c r="M5" t="n">
-        <v>136.4</v>
+        <v>132.42</v>
       </c>
       <c r="N5" t="n">
-        <v>132.04</v>
+        <v>127.5</v>
       </c>
       <c r="O5" t="n">
-        <v>132.04</v>
+        <v>128.32</v>
       </c>
       <c r="P5" t="n">
-        <v>144.324</v>
+        <v>144.066</v>
       </c>
       <c r="R5" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S5" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21 jul</t>
+          <t>22 jul</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>398.0606</v>
+        <v>398.8292</v>
       </c>
       <c r="W5" t="n">
-        <v>400.7156</v>
+        <v>400.2465</v>
       </c>
       <c r="X5" t="n">
-        <v>395.5753</v>
+        <v>386.2329</v>
       </c>
       <c r="Y5" t="n">
-        <v>397.0026</v>
+        <v>389.6066</v>
       </c>
       <c r="Z5" t="n">
-        <v>399.9036</v>
+        <v>399.4268</v>
       </c>
       <c r="AB5" t="n">
         <v>535.3375423278808</v>
@@ -3651,84 +3673,84 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>23 jul</t>
+          <t>24 jul</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>38.491</v>
+        <v>38.4019</v>
       </c>
       <c r="C6" t="n">
-        <v>39.0454</v>
+        <v>38.6593</v>
       </c>
       <c r="D6" t="n">
-        <v>38.3425</v>
+        <v>38.1594</v>
       </c>
       <c r="E6" t="n">
-        <v>38.8028</v>
+        <v>38.3871</v>
       </c>
       <c r="F6" t="n">
-        <v>35.863</v>
+        <v>35.9135</v>
       </c>
       <c r="G6" t="n">
-        <v>33.8375</v>
+        <v>33.8757</v>
       </c>
       <c r="H6" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I6" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>23 jul</t>
+          <t>24 jul</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>131</v>
+        <v>130.88</v>
       </c>
       <c r="M6" t="n">
-        <v>132.42</v>
+        <v>141.32</v>
       </c>
       <c r="N6" t="n">
-        <v>127.5</v>
+        <v>130.86</v>
       </c>
       <c r="O6" t="n">
-        <v>128.32</v>
+        <v>140.2</v>
       </c>
       <c r="P6" t="n">
-        <v>144.066</v>
+        <v>143.9888</v>
       </c>
       <c r="Q6" t="n">
-        <v>173.9035</v>
+        <v>173.4491</v>
       </c>
       <c r="R6" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S6" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>22 jul</t>
+          <t>23 jul</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>398.8292</v>
+        <v>389.2373</v>
       </c>
       <c r="W6" t="n">
-        <v>400.2465</v>
+        <v>391.0439</v>
       </c>
       <c r="X6" t="n">
-        <v>386.2329</v>
+        <v>376.6809</v>
       </c>
       <c r="Y6" t="n">
-        <v>389.6066</v>
+        <v>380.863</v>
       </c>
       <c r="Z6" t="n">
-        <v>399.4268</v>
+        <v>398.8242</v>
       </c>
       <c r="AA6" t="n">
-        <v>435.2723</v>
+        <v>434.611</v>
       </c>
       <c r="AB6" t="n">
         <v>535.3375423278808</v>
@@ -3740,84 +3762,84 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>24 jul</t>
+          <t>27 jul</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>38.4019</v>
+        <v>37.5802</v>
       </c>
       <c r="C7" t="n">
-        <v>38.6593</v>
+        <v>38.1099</v>
       </c>
       <c r="D7" t="n">
-        <v>38.1594</v>
+        <v>37.4317</v>
       </c>
       <c r="E7" t="n">
-        <v>38.3871</v>
+        <v>37.9515</v>
       </c>
       <c r="F7" t="n">
-        <v>35.9135</v>
+        <v>35.931</v>
       </c>
       <c r="G7" t="n">
-        <v>33.8757</v>
+        <v>33.9167</v>
       </c>
       <c r="H7" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I7" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>24 jul</t>
+          <t>27 jul</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>130.88</v>
+        <v>142.38</v>
       </c>
       <c r="M7" t="n">
-        <v>141.32</v>
+        <v>151.56</v>
       </c>
       <c r="N7" t="n">
-        <v>130.86</v>
+        <v>142</v>
       </c>
       <c r="O7" t="n">
-        <v>140.2</v>
+        <v>151.28</v>
       </c>
       <c r="P7" t="n">
-        <v>143.9888</v>
+        <v>144.0572</v>
       </c>
       <c r="Q7" t="n">
-        <v>173.4491</v>
+        <v>173.0393</v>
       </c>
       <c r="R7" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S7" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>23 jul</t>
+          <t>24 jul</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>389.2373</v>
+        <v>386.3227</v>
       </c>
       <c r="W7" t="n">
-        <v>391.0439</v>
+        <v>388.299</v>
       </c>
       <c r="X7" t="n">
-        <v>376.6809</v>
+        <v>379.9348</v>
       </c>
       <c r="Y7" t="n">
-        <v>380.863</v>
+        <v>380.9828</v>
       </c>
       <c r="Z7" t="n">
-        <v>398.8242</v>
+        <v>398.3214</v>
       </c>
       <c r="AA7" t="n">
-        <v>434.611</v>
+        <v>433.8946</v>
       </c>
       <c r="AB7" t="n">
         <v>535.3375423278808</v>
@@ -3829,84 +3851,84 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>27 jul</t>
+          <t>28 jul</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>37.5802</v>
+        <v>37.7139</v>
       </c>
       <c r="C8" t="n">
-        <v>38.1099</v>
+        <v>38.0109</v>
       </c>
       <c r="D8" t="n">
-        <v>37.4317</v>
+        <v>37.4713</v>
       </c>
       <c r="E8" t="n">
-        <v>37.9515</v>
+        <v>37.4713</v>
       </c>
       <c r="F8" t="n">
-        <v>35.931</v>
+        <v>35.9372</v>
       </c>
       <c r="G8" t="n">
-        <v>33.9167</v>
+        <v>33.9548</v>
       </c>
       <c r="H8" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I8" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>27 jul</t>
+          <t>28 jul</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>142.38</v>
+        <v>152.2</v>
       </c>
       <c r="M8" t="n">
-        <v>151.56</v>
+        <v>159.76</v>
       </c>
       <c r="N8" t="n">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="O8" t="n">
-        <v>151.28</v>
+        <v>159.24</v>
       </c>
       <c r="P8" t="n">
-        <v>144.0572</v>
+        <v>144.1076</v>
       </c>
       <c r="Q8" t="n">
-        <v>173.0393</v>
+        <v>172.6663</v>
       </c>
       <c r="R8" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S8" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>24 jul</t>
+          <t>27 jul</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>386.3227</v>
+        <v>389.347</v>
       </c>
       <c r="W8" t="n">
-        <v>388.299</v>
+        <v>393.4593</v>
       </c>
       <c r="X8" t="n">
-        <v>379.9348</v>
+        <v>387.261</v>
       </c>
       <c r="Y8" t="n">
-        <v>380.9828</v>
+        <v>388.3689</v>
       </c>
       <c r="Z8" t="n">
-        <v>398.3214</v>
+        <v>398.0172</v>
       </c>
       <c r="AA8" t="n">
-        <v>433.8946</v>
+        <v>433.238</v>
       </c>
       <c r="AB8" t="n">
         <v>535.3375423278808</v>
@@ -3918,84 +3940,84 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>28 jul</t>
+          <t>29 jul</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>37.7139</v>
+        <v>38.0653</v>
       </c>
       <c r="C9" t="n">
-        <v>38.0109</v>
+        <v>38.59</v>
       </c>
       <c r="D9" t="n">
-        <v>37.4713</v>
+        <v>37.7089</v>
       </c>
       <c r="E9" t="n">
-        <v>37.4713</v>
+        <v>38.4415</v>
       </c>
       <c r="F9" t="n">
-        <v>35.9372</v>
+        <v>35.9692</v>
       </c>
       <c r="G9" t="n">
-        <v>33.9548</v>
+        <v>33.9987</v>
       </c>
       <c r="H9" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I9" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>28 jul</t>
+          <t>29 jul</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>152.2</v>
+        <v>159.84</v>
       </c>
       <c r="M9" t="n">
-        <v>159.76</v>
+        <v>163.3</v>
       </c>
       <c r="N9" t="n">
-        <v>151</v>
+        <v>156.48</v>
       </c>
       <c r="O9" t="n">
-        <v>159.24</v>
+        <v>162.04</v>
       </c>
       <c r="P9" t="n">
-        <v>144.1076</v>
+        <v>144.28</v>
       </c>
       <c r="Q9" t="n">
-        <v>172.6663</v>
+        <v>172.343</v>
       </c>
       <c r="R9" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S9" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>27 jul</t>
+          <t>28 jul</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>389.347</v>
+        <v>392.4213</v>
       </c>
       <c r="W9" t="n">
-        <v>393.4593</v>
+        <v>399.5678</v>
       </c>
       <c r="X9" t="n">
-        <v>387.261</v>
+        <v>390.5647</v>
       </c>
       <c r="Y9" t="n">
-        <v>388.3689</v>
+        <v>392.6109</v>
       </c>
       <c r="Z9" t="n">
-        <v>398.0172</v>
+        <v>397.7139</v>
       </c>
       <c r="AA9" t="n">
-        <v>433.238</v>
+        <v>432.5982</v>
       </c>
       <c r="AB9" t="n">
         <v>535.3375423278808</v>
@@ -4007,84 +4029,84 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>29 jul</t>
+          <t>30 jul</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>38.0653</v>
+        <v>38.6098</v>
       </c>
       <c r="C10" t="n">
-        <v>38.59</v>
+        <v>39.1444</v>
       </c>
       <c r="D10" t="n">
-        <v>37.7089</v>
+        <v>38.3277</v>
       </c>
       <c r="E10" t="n">
-        <v>38.4415</v>
+        <v>38.5108</v>
       </c>
       <c r="F10" t="n">
-        <v>35.9692</v>
+        <v>35.9978</v>
       </c>
       <c r="G10" t="n">
-        <v>33.9987</v>
+        <v>34.0424</v>
       </c>
       <c r="H10" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I10" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>29 jul</t>
+          <t>30 jul</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>159.84</v>
+        <v>162.5</v>
       </c>
       <c r="M10" t="n">
-        <v>163.3</v>
+        <v>163.16</v>
       </c>
       <c r="N10" t="n">
-        <v>156.48</v>
+        <v>155.2</v>
       </c>
       <c r="O10" t="n">
-        <v>162.04</v>
+        <v>155.92</v>
       </c>
       <c r="P10" t="n">
-        <v>144.28</v>
+        <v>144.3804</v>
       </c>
       <c r="Q10" t="n">
-        <v>172.343</v>
+        <v>171.9849</v>
       </c>
       <c r="R10" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S10" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>28 jul</t>
+          <t>29 jul</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>392.4213</v>
+        <v>392.6608</v>
       </c>
       <c r="W10" t="n">
-        <v>399.5678</v>
+        <v>400.4961</v>
       </c>
       <c r="X10" t="n">
-        <v>390.5647</v>
+        <v>388.0095</v>
       </c>
       <c r="Y10" t="n">
-        <v>392.6109</v>
+        <v>389.8062</v>
       </c>
       <c r="Z10" t="n">
-        <v>397.7139</v>
+        <v>397.1057</v>
       </c>
       <c r="AA10" t="n">
-        <v>432.5982</v>
+        <v>431.9565</v>
       </c>
       <c r="AB10" t="n">
         <v>535.3375423278808</v>
@@ -4096,84 +4118,84 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>30 jul</t>
+          <t>31 jul</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>38.6098</v>
       </c>
       <c r="C11" t="n">
-        <v>39.1444</v>
+        <v>39.575</v>
       </c>
       <c r="D11" t="n">
-        <v>38.3277</v>
+        <v>38.4464</v>
       </c>
       <c r="E11" t="n">
-        <v>38.5108</v>
+        <v>39.3226</v>
       </c>
       <c r="F11" t="n">
-        <v>35.9978</v>
+        <v>36.0495</v>
       </c>
       <c r="G11" t="n">
-        <v>34.0424</v>
+        <v>34.0907</v>
       </c>
       <c r="H11" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I11" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>30 jul</t>
+          <t>31 jul</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>162.5</v>
+        <v>154.9</v>
       </c>
       <c r="M11" t="n">
-        <v>163.16</v>
+        <v>158.26</v>
       </c>
       <c r="N11" t="n">
-        <v>155.2</v>
+        <v>153.6</v>
       </c>
       <c r="O11" t="n">
-        <v>155.92</v>
+        <v>157.68</v>
       </c>
       <c r="P11" t="n">
-        <v>144.3804</v>
+        <v>144.4984</v>
       </c>
       <c r="Q11" t="n">
-        <v>171.9849</v>
+        <v>171.6292</v>
       </c>
       <c r="R11" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S11" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>29 jul</t>
+          <t>30 jul</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>392.6608</v>
+        <v>437.0772</v>
       </c>
       <c r="W11" t="n">
-        <v>400.4961</v>
+        <v>457.8281</v>
       </c>
       <c r="X11" t="n">
-        <v>388.0095</v>
+        <v>431.6275</v>
       </c>
       <c r="Y11" t="n">
-        <v>389.8062</v>
+        <v>450.2524</v>
       </c>
       <c r="Z11" t="n">
-        <v>397.1057</v>
+        <v>397.6741</v>
       </c>
       <c r="AA11" t="n">
-        <v>431.9565</v>
+        <v>431.6738</v>
       </c>
       <c r="AB11" t="n">
         <v>535.3375423278808</v>
@@ -4185,84 +4207,84 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>31 jul</t>
+          <t>3 aug</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>38.6098</v>
+        <v>38.3128</v>
       </c>
       <c r="C12" t="n">
-        <v>39.575</v>
+        <v>39.4067</v>
       </c>
       <c r="D12" t="n">
-        <v>38.4464</v>
+        <v>38.2138</v>
       </c>
       <c r="E12" t="n">
-        <v>39.3226</v>
+        <v>39.4067</v>
       </c>
       <c r="F12" t="n">
-        <v>36.0495</v>
+        <v>36.1112</v>
       </c>
       <c r="G12" t="n">
-        <v>34.0907</v>
+        <v>34.1393</v>
       </c>
       <c r="H12" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I12" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>31 jul</t>
+          <t>3 aug</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>154.9</v>
+        <v>160</v>
       </c>
       <c r="M12" t="n">
-        <v>158.26</v>
+        <v>168.7</v>
       </c>
       <c r="N12" t="n">
-        <v>153.6</v>
+        <v>159.6</v>
       </c>
       <c r="O12" t="n">
-        <v>157.68</v>
+        <v>164.64</v>
       </c>
       <c r="P12" t="n">
-        <v>144.4984</v>
+        <v>144.7016</v>
       </c>
       <c r="Q12" t="n">
-        <v>171.6292</v>
+        <v>171.301</v>
       </c>
       <c r="R12" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S12" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>30 jul</t>
+          <t>31 jul</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>437.0772</v>
+        <v>449.1545</v>
       </c>
       <c r="W12" t="n">
-        <v>457.8281</v>
+        <v>465.9628</v>
       </c>
       <c r="X12" t="n">
-        <v>431.6275</v>
+        <v>448.4857</v>
       </c>
       <c r="Y12" t="n">
-        <v>450.2524</v>
+        <v>463.8468</v>
       </c>
       <c r="Z12" t="n">
-        <v>397.6741</v>
+        <v>398.6364</v>
       </c>
       <c r="AA12" t="n">
-        <v>431.6738</v>
+        <v>431.4438</v>
       </c>
       <c r="AB12" t="n">
         <v>535.3375423278808</v>
@@ -4274,84 +4296,84 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3 aug</t>
+          <t>4 aug</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>38.3128</v>
+        <v>39.3028</v>
       </c>
       <c r="C13" t="n">
-        <v>39.4067</v>
+        <v>39.6443</v>
       </c>
       <c r="D13" t="n">
-        <v>38.2138</v>
+        <v>38.2039</v>
       </c>
       <c r="E13" t="n">
-        <v>39.4067</v>
+        <v>38.486</v>
       </c>
       <c r="F13" t="n">
-        <v>36.1112</v>
+        <v>36.1495</v>
       </c>
       <c r="G13" t="n">
-        <v>34.1393</v>
+        <v>34.1818</v>
       </c>
       <c r="H13" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I13" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>3 aug</t>
+          <t>4 aug</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>160</v>
+        <v>162.86</v>
       </c>
       <c r="M13" t="n">
-        <v>168.7</v>
+        <v>168.56</v>
       </c>
       <c r="N13" t="n">
-        <v>159.6</v>
+        <v>162.4</v>
       </c>
       <c r="O13" t="n">
-        <v>164.64</v>
+        <v>167.38</v>
       </c>
       <c r="P13" t="n">
-        <v>144.7016</v>
+        <v>145.02</v>
       </c>
       <c r="Q13" t="n">
-        <v>171.301</v>
+        <v>170.9913</v>
       </c>
       <c r="R13" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S13" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>31 jul</t>
+          <t>3 aug</t>
         </is>
       </c>
       <c r="V13" t="n">
-        <v>449.1545</v>
+        <v>475.2354</v>
       </c>
       <c r="W13" t="n">
-        <v>465.9628</v>
+        <v>490.7262</v>
       </c>
       <c r="X13" t="n">
-        <v>448.4857</v>
+        <v>474.1075</v>
       </c>
       <c r="Y13" t="n">
-        <v>463.8468</v>
+        <v>486.7337</v>
       </c>
       <c r="Z13" t="n">
-        <v>398.6364</v>
+        <v>399.9838</v>
       </c>
       <c r="AA13" t="n">
-        <v>431.4438</v>
+        <v>431.3306</v>
       </c>
       <c r="AB13" t="n">
         <v>535.3375423278808</v>
@@ -4363,84 +4385,84 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4 aug</t>
+          <t>5 aug</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>39.3028</v>
+        <v>38.4811</v>
       </c>
       <c r="C14" t="n">
-        <v>39.6443</v>
+        <v>38.7632</v>
       </c>
       <c r="D14" t="n">
-        <v>38.2039</v>
+        <v>37.9366</v>
       </c>
       <c r="E14" t="n">
-        <v>38.486</v>
+        <v>38.0307</v>
       </c>
       <c r="F14" t="n">
-        <v>36.1495</v>
+        <v>36.1966</v>
       </c>
       <c r="G14" t="n">
-        <v>34.1818</v>
+        <v>34.2215</v>
       </c>
       <c r="H14" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I14" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>4 aug</t>
+          <t>5 aug</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>162.86</v>
+        <v>167.92</v>
       </c>
       <c r="M14" t="n">
-        <v>168.56</v>
+        <v>172.6</v>
       </c>
       <c r="N14" t="n">
-        <v>162.4</v>
+        <v>167.3</v>
       </c>
       <c r="O14" t="n">
-        <v>167.38</v>
+        <v>169.26</v>
       </c>
       <c r="P14" t="n">
-        <v>145.02</v>
+        <v>145.4052</v>
       </c>
       <c r="Q14" t="n">
-        <v>170.9913</v>
+        <v>170.7022</v>
       </c>
       <c r="R14" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S14" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>3 aug</t>
+          <t>4 aug</t>
         </is>
       </c>
       <c r="V14" t="n">
-        <v>475.2354</v>
+        <v>479.9964</v>
       </c>
       <c r="W14" t="n">
-        <v>490.7262</v>
+        <v>498.5016</v>
       </c>
       <c r="X14" t="n">
-        <v>474.1075</v>
+        <v>478.2697</v>
       </c>
       <c r="Y14" t="n">
-        <v>486.7337</v>
+        <v>491.884</v>
       </c>
       <c r="Z14" t="n">
-        <v>399.9838</v>
+        <v>401.4555</v>
       </c>
       <c r="AA14" t="n">
-        <v>431.3306</v>
+        <v>431.2438</v>
       </c>
       <c r="AB14" t="n">
         <v>535.3375423278808</v>
@@ -4452,84 +4474,84 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5 aug</t>
+          <t>6 aug</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>38.4811</v>
+        <v>38.0752</v>
       </c>
       <c r="C15" t="n">
-        <v>38.7632</v>
+        <v>38.4069</v>
       </c>
       <c r="D15" t="n">
-        <v>37.9366</v>
+        <v>37.9168</v>
       </c>
       <c r="E15" t="n">
-        <v>38.0307</v>
+        <v>38.392</v>
       </c>
       <c r="F15" t="n">
-        <v>36.1966</v>
+        <v>36.2474</v>
       </c>
       <c r="G15" t="n">
-        <v>34.2215</v>
+        <v>34.2607</v>
       </c>
       <c r="H15" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I15" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>5 aug</t>
+          <t>6 aug</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>167.92</v>
+        <v>171.44</v>
       </c>
       <c r="M15" t="n">
-        <v>172.6</v>
+        <v>173.1</v>
       </c>
       <c r="N15" t="n">
-        <v>167.3</v>
+        <v>168.08</v>
       </c>
       <c r="O15" t="n">
-        <v>169.26</v>
+        <v>170.98</v>
       </c>
       <c r="P15" t="n">
-        <v>145.4052</v>
+        <v>145.7928</v>
       </c>
       <c r="Q15" t="n">
-        <v>170.7022</v>
+        <v>170.384</v>
       </c>
       <c r="R15" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S15" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>4 aug</t>
+          <t>5 aug</t>
         </is>
       </c>
       <c r="V15" t="n">
-        <v>479.9964</v>
+        <v>495.4273</v>
       </c>
       <c r="W15" t="n">
-        <v>498.5016</v>
+        <v>497.3038</v>
       </c>
       <c r="X15" t="n">
-        <v>478.2697</v>
+        <v>484.7674</v>
       </c>
       <c r="Y15" t="n">
-        <v>491.884</v>
+        <v>486.5441</v>
       </c>
       <c r="Z15" t="n">
-        <v>401.4555</v>
+        <v>402.8307</v>
       </c>
       <c r="AA15" t="n">
-        <v>431.2438</v>
+        <v>431.1393</v>
       </c>
       <c r="AB15" t="n">
         <v>535.3375423278808</v>
@@ -4541,84 +4563,84 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6 aug</t>
+          <t>7 aug</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>38.0752</v>
+        <v>38.5207</v>
       </c>
       <c r="C16" t="n">
-        <v>38.4069</v>
+        <v>38.5999</v>
       </c>
       <c r="D16" t="n">
-        <v>37.9168</v>
+        <v>37.897</v>
       </c>
       <c r="E16" t="n">
-        <v>38.392</v>
+        <v>38.0059</v>
       </c>
       <c r="F16" t="n">
-        <v>36.2474</v>
+        <v>36.2952</v>
       </c>
       <c r="G16" t="n">
-        <v>34.2607</v>
+        <v>34.294</v>
       </c>
       <c r="H16" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I16" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>6 aug</t>
+          <t>7 aug</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>171.44</v>
+        <v>173.82</v>
       </c>
       <c r="M16" t="n">
-        <v>173.1</v>
+        <v>179.56</v>
       </c>
       <c r="N16" t="n">
-        <v>168.08</v>
+        <v>173.82</v>
       </c>
       <c r="O16" t="n">
-        <v>170.98</v>
+        <v>177.96</v>
       </c>
       <c r="P16" t="n">
-        <v>145.7928</v>
+        <v>146.2468</v>
       </c>
       <c r="Q16" t="n">
-        <v>170.384</v>
+        <v>170.0918</v>
       </c>
       <c r="R16" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S16" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>5 aug</t>
+          <t>6 aug</t>
         </is>
       </c>
       <c r="V16" t="n">
-        <v>495.4273</v>
+        <v>487.632</v>
       </c>
       <c r="W16" t="n">
-        <v>497.3038</v>
+        <v>500.6176</v>
       </c>
       <c r="X16" t="n">
-        <v>484.7674</v>
+        <v>487.6021</v>
       </c>
       <c r="Y16" t="n">
-        <v>486.5441</v>
+        <v>498.9207</v>
       </c>
       <c r="Z16" t="n">
-        <v>402.8307</v>
+        <v>404.5041</v>
       </c>
       <c r="AA16" t="n">
-        <v>431.1393</v>
+        <v>431.087</v>
       </c>
       <c r="AB16" t="n">
         <v>535.3375423278808</v>
@@ -4630,84 +4652,84 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>7 aug</t>
+          <t>10 aug</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>38.5207</v>
+        <v>38.0356</v>
       </c>
       <c r="C17" t="n">
-        <v>38.5999</v>
+        <v>38.4366</v>
       </c>
       <c r="D17" t="n">
-        <v>37.897</v>
+        <v>37.803</v>
       </c>
       <c r="E17" t="n">
-        <v>38.0059</v>
+        <v>38.4019</v>
       </c>
       <c r="F17" t="n">
-        <v>36.2952</v>
+        <v>36.3315</v>
       </c>
       <c r="G17" t="n">
-        <v>34.294</v>
+        <v>34.3294</v>
       </c>
       <c r="H17" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I17" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>7 aug</t>
+          <t>10 aug</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>173.82</v>
+        <v>178.92</v>
       </c>
       <c r="M17" t="n">
-        <v>179.56</v>
+        <v>179.96</v>
       </c>
       <c r="N17" t="n">
-        <v>173.82</v>
+        <v>175.86</v>
       </c>
       <c r="O17" t="n">
-        <v>177.96</v>
+        <v>179.3</v>
       </c>
       <c r="P17" t="n">
-        <v>146.2468</v>
+        <v>146.4748</v>
       </c>
       <c r="Q17" t="n">
-        <v>170.0918</v>
+        <v>169.8238</v>
       </c>
       <c r="R17" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S17" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>6 aug</t>
+          <t>7 aug</t>
         </is>
       </c>
       <c r="V17" t="n">
-        <v>487.632</v>
+        <v>498.272</v>
       </c>
       <c r="W17" t="n">
-        <v>500.6176</v>
+        <v>504.2308</v>
       </c>
       <c r="X17" t="n">
-        <v>487.6021</v>
+        <v>497.7929</v>
       </c>
       <c r="Y17" t="n">
-        <v>498.9207</v>
+        <v>499.0505</v>
       </c>
       <c r="Z17" t="n">
-        <v>404.5041</v>
+        <v>406.2472</v>
       </c>
       <c r="AA17" t="n">
-        <v>431.087</v>
+        <v>431.0194</v>
       </c>
       <c r="AB17" t="n">
         <v>535.3375423278808</v>
@@ -4719,84 +4741,84 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10 aug</t>
+          <t>11 aug</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>38.0356</v>
+        <v>38.7385</v>
       </c>
       <c r="C18" t="n">
-        <v>38.4366</v>
+        <v>39.0058</v>
       </c>
       <c r="D18" t="n">
-        <v>37.803</v>
+        <v>38.6148</v>
       </c>
       <c r="E18" t="n">
-        <v>38.4019</v>
+        <v>38.9662</v>
       </c>
       <c r="F18" t="n">
-        <v>36.3315</v>
+        <v>36.374</v>
       </c>
       <c r="G18" t="n">
-        <v>34.3294</v>
+        <v>34.3685</v>
       </c>
       <c r="H18" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I18" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>10 aug</t>
+          <t>11 aug</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>178.92</v>
+        <v>180</v>
       </c>
       <c r="M18" t="n">
-        <v>179.96</v>
+        <v>183.24</v>
       </c>
       <c r="N18" t="n">
-        <v>175.86</v>
+        <v>178.14</v>
       </c>
       <c r="O18" t="n">
-        <v>179.3</v>
+        <v>180.7</v>
       </c>
       <c r="P18" t="n">
-        <v>146.4748</v>
+        <v>146.8316</v>
       </c>
       <c r="Q18" t="n">
-        <v>169.8238</v>
+        <v>169.5375</v>
       </c>
       <c r="R18" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S18" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>7 aug</t>
+          <t>10 aug</t>
         </is>
       </c>
       <c r="V18" t="n">
-        <v>498.272</v>
+        <v>502.4941</v>
       </c>
       <c r="W18" t="n">
-        <v>504.2308</v>
+        <v>512.7646999999999</v>
       </c>
       <c r="X18" t="n">
-        <v>497.7929</v>
+        <v>501.3262</v>
       </c>
       <c r="Y18" t="n">
-        <v>499.0505</v>
+        <v>505.1091</v>
       </c>
       <c r="Z18" t="n">
-        <v>406.2472</v>
+        <v>407.8257</v>
       </c>
       <c r="AA18" t="n">
-        <v>431.0194</v>
+        <v>430.9778</v>
       </c>
       <c r="AB18" t="n">
         <v>535.3375423278808</v>
@@ -4808,84 +4830,84 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>11 aug</t>
+          <t>12 aug</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>38.7385</v>
+        <v>38.8573</v>
       </c>
       <c r="C19" t="n">
-        <v>39.0058</v>
+        <v>38.986</v>
       </c>
       <c r="D19" t="n">
-        <v>38.6148</v>
+        <v>38.3871</v>
       </c>
       <c r="E19" t="n">
-        <v>38.9662</v>
+        <v>38.6494</v>
       </c>
       <c r="F19" t="n">
-        <v>36.374</v>
+        <v>36.3981</v>
       </c>
       <c r="G19" t="n">
-        <v>34.3685</v>
+        <v>34.4068</v>
       </c>
       <c r="H19" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I19" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>11 aug</t>
+          <t>12 aug</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>180</v>
+        <v>180.3</v>
       </c>
       <c r="M19" t="n">
-        <v>183.24</v>
+        <v>180.98</v>
       </c>
       <c r="N19" t="n">
-        <v>178.14</v>
+        <v>175.4</v>
       </c>
       <c r="O19" t="n">
-        <v>180.7</v>
+        <v>175.96</v>
       </c>
       <c r="P19" t="n">
-        <v>146.8316</v>
+        <v>147.232</v>
       </c>
       <c r="Q19" t="n">
-        <v>169.5375</v>
+        <v>169.2701</v>
       </c>
       <c r="R19" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S19" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>10 aug</t>
+          <t>11 aug</t>
         </is>
       </c>
       <c r="V19" t="n">
-        <v>502.4941</v>
+        <v>503.3824</v>
       </c>
       <c r="W19" t="n">
-        <v>512.7646999999999</v>
+        <v>504.3805</v>
       </c>
       <c r="X19" t="n">
-        <v>501.3262</v>
+        <v>498.6113</v>
       </c>
       <c r="Y19" t="n">
-        <v>505.1091</v>
+        <v>502.8633</v>
       </c>
       <c r="Z19" t="n">
-        <v>407.8257</v>
+        <v>408.895</v>
       </c>
       <c r="AA19" t="n">
-        <v>430.9778</v>
+        <v>430.9106</v>
       </c>
       <c r="AB19" t="n">
         <v>535.3375423278808</v>
@@ -4897,84 +4919,84 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>12 aug</t>
+          <t>13 aug</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>38.8573</v>
+        <v>39</v>
       </c>
       <c r="C20" t="n">
-        <v>38.986</v>
+        <v>39.005</v>
       </c>
       <c r="D20" t="n">
-        <v>38.3871</v>
+        <v>38.2</v>
       </c>
       <c r="E20" t="n">
-        <v>38.6494</v>
+        <v>38.605</v>
       </c>
       <c r="F20" t="n">
-        <v>36.3981</v>
+        <v>36.4313</v>
       </c>
       <c r="G20" t="n">
-        <v>34.4068</v>
+        <v>34.4429</v>
       </c>
       <c r="H20" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I20" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>12 aug</t>
+          <t>13 aug</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>180.3</v>
+        <v>177.48</v>
       </c>
       <c r="M20" t="n">
-        <v>180.98</v>
+        <v>178.3</v>
       </c>
       <c r="N20" t="n">
-        <v>175.4</v>
+        <v>174.8</v>
       </c>
       <c r="O20" t="n">
-        <v>175.96</v>
+        <v>175.38</v>
       </c>
       <c r="P20" t="n">
-        <v>147.232</v>
+        <v>147.4496</v>
       </c>
       <c r="Q20" t="n">
-        <v>169.2701</v>
+        <v>168.9889</v>
       </c>
       <c r="R20" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S20" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>11 aug</t>
+          <t>12 aug</t>
         </is>
       </c>
       <c r="V20" t="n">
-        <v>503.3824</v>
+        <v>499.0505</v>
       </c>
       <c r="W20" t="n">
-        <v>504.3805</v>
+        <v>500.5577</v>
       </c>
       <c r="X20" t="n">
-        <v>498.6113</v>
+        <v>490.5964</v>
       </c>
       <c r="Y20" t="n">
-        <v>502.8633</v>
+        <v>491.5047</v>
       </c>
       <c r="Z20" t="n">
-        <v>408.895</v>
+        <v>409.532</v>
       </c>
       <c r="AA20" t="n">
-        <v>430.9106</v>
+        <v>430.7866</v>
       </c>
       <c r="AB20" t="n">
         <v>535.3375423278808</v>
@@ -4986,84 +5008,84 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>13 aug</t>
+          <t>14 aug</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>39</v>
+        <v>38.65</v>
       </c>
       <c r="C21" t="n">
-        <v>39.005</v>
+        <v>39.1</v>
       </c>
       <c r="D21" t="n">
-        <v>38.2</v>
+        <v>38.56</v>
       </c>
       <c r="E21" t="n">
-        <v>38.605</v>
+        <v>38.97</v>
       </c>
       <c r="F21" t="n">
-        <v>36.4313</v>
+        <v>36.4703</v>
       </c>
       <c r="G21" t="n">
-        <v>34.4429</v>
+        <v>34.4805</v>
       </c>
       <c r="H21" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I21" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>13 aug</t>
+          <t>14 aug</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>177.48</v>
+        <v>182</v>
       </c>
       <c r="M21" t="n">
-        <v>178.3</v>
+        <v>185.74</v>
       </c>
       <c r="N21" t="n">
-        <v>174.8</v>
+        <v>179.28</v>
       </c>
       <c r="O21" t="n">
-        <v>175.38</v>
+        <v>180.14</v>
       </c>
       <c r="P21" t="n">
-        <v>147.4496</v>
+        <v>147.8228</v>
       </c>
       <c r="Q21" t="n">
-        <v>168.9889</v>
+        <v>168.7386</v>
       </c>
       <c r="R21" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S21" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>12 aug</t>
+          <t>13 aug</t>
         </is>
       </c>
       <c r="V21" t="n">
-        <v>499.0505</v>
+        <v>492.3431</v>
       </c>
       <c r="W21" t="n">
-        <v>500.5577</v>
+        <v>500.398</v>
       </c>
       <c r="X21" t="n">
-        <v>490.5964</v>
+        <v>492.0837</v>
       </c>
       <c r="Y21" t="n">
-        <v>491.5047</v>
+        <v>495.9464</v>
       </c>
       <c r="Z21" t="n">
-        <v>409.532</v>
+        <v>410.6414</v>
       </c>
       <c r="AA21" t="n">
-        <v>430.7866</v>
+        <v>430.6696</v>
       </c>
       <c r="AB21" t="n">
         <v>535.3375423278808</v>
@@ -5075,84 +5097,84 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>14 aug</t>
+          <t>17 aug</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>38.65</v>
+        <v>38.97</v>
       </c>
       <c r="C22" t="n">
-        <v>39.1</v>
+        <v>39.27</v>
       </c>
       <c r="D22" t="n">
-        <v>38.56</v>
+        <v>38.765</v>
       </c>
       <c r="E22" t="n">
-        <v>38.97</v>
+        <v>39.15</v>
       </c>
       <c r="F22" t="n">
-        <v>36.4703</v>
+        <v>36.5118</v>
       </c>
       <c r="G22" t="n">
-        <v>34.4805</v>
+        <v>34.5207</v>
       </c>
       <c r="H22" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I22" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>14 aug</t>
+          <t>17 aug</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>182</v>
+        <v>178.94</v>
       </c>
       <c r="M22" t="n">
-        <v>185.74</v>
+        <v>180.9</v>
       </c>
       <c r="N22" t="n">
-        <v>179.28</v>
+        <v>177.66</v>
       </c>
       <c r="O22" t="n">
-        <v>180.14</v>
+        <v>179.58</v>
       </c>
       <c r="P22" t="n">
-        <v>147.8228</v>
+        <v>148.2524</v>
       </c>
       <c r="Q22" t="n">
-        <v>168.7386</v>
+        <v>168.5337</v>
       </c>
       <c r="R22" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S22" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>13 aug</t>
+          <t>14 aug</t>
         </is>
       </c>
       <c r="V22" t="n">
-        <v>492.3431</v>
+        <v>495.4273</v>
       </c>
       <c r="W22" t="n">
-        <v>500.398</v>
+        <v>499.0705</v>
       </c>
       <c r="X22" t="n">
-        <v>492.0837</v>
+        <v>492.9919</v>
       </c>
       <c r="Y22" t="n">
-        <v>495.9464</v>
+        <v>494.4691</v>
       </c>
       <c r="Z22" t="n">
-        <v>410.6414</v>
+        <v>412</v>
       </c>
       <c r="AA22" t="n">
-        <v>430.6696</v>
+        <v>430.5061</v>
       </c>
       <c r="AB22" t="n">
         <v>535.3375423278808</v>
@@ -5164,84 +5186,84 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>17 aug</t>
+          <t>18 aug</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>38.97</v>
+        <v>39.49</v>
       </c>
       <c r="C23" t="n">
-        <v>39.27</v>
+        <v>39.945</v>
       </c>
       <c r="D23" t="n">
-        <v>38.765</v>
+        <v>39.46</v>
       </c>
       <c r="E23" t="n">
-        <v>39.15</v>
+        <v>39.785</v>
       </c>
       <c r="F23" t="n">
-        <v>36.5118</v>
+        <v>36.5781</v>
       </c>
       <c r="G23" t="n">
-        <v>34.5207</v>
+        <v>34.5641</v>
       </c>
       <c r="H23" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I23" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>17 aug</t>
+          <t>18 aug</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>178.94</v>
+        <v>179.14</v>
       </c>
       <c r="M23" t="n">
-        <v>180.9</v>
+        <v>183.9</v>
       </c>
       <c r="N23" t="n">
-        <v>177.66</v>
+        <v>177.98</v>
       </c>
       <c r="O23" t="n">
-        <v>179.58</v>
+        <v>182.5</v>
       </c>
       <c r="P23" t="n">
-        <v>148.2524</v>
+        <v>148.8084</v>
       </c>
       <c r="Q23" t="n">
-        <v>168.5337</v>
+        <v>168.3358</v>
       </c>
       <c r="R23" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S23" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>14 aug</t>
+          <t>17 aug</t>
         </is>
       </c>
       <c r="V23" t="n">
-        <v>495.4273</v>
+        <v>489.2191</v>
       </c>
       <c r="W23" t="n">
-        <v>499.0705</v>
+        <v>491.7343</v>
       </c>
       <c r="X23" t="n">
-        <v>492.9919</v>
+        <v>477.5111</v>
       </c>
       <c r="Y23" t="n">
-        <v>494.4691</v>
+        <v>479.4474</v>
       </c>
       <c r="Z23" t="n">
-        <v>412</v>
+        <v>413.044</v>
       </c>
       <c r="AA23" t="n">
-        <v>430.5061</v>
+        <v>430.2151</v>
       </c>
       <c r="AB23" t="n">
         <v>535.3375423278808</v>
@@ -5253,84 +5275,84 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>18 aug</t>
+          <t>19 aug</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>39.49</v>
+        <v>39.835</v>
       </c>
       <c r="C24" t="n">
-        <v>39.945</v>
+        <v>40.14</v>
       </c>
       <c r="D24" t="n">
-        <v>39.46</v>
+        <v>39.74</v>
       </c>
       <c r="E24" t="n">
-        <v>39.785</v>
+        <v>39.94</v>
       </c>
       <c r="F24" t="n">
-        <v>36.5781</v>
+        <v>36.6336</v>
       </c>
       <c r="G24" t="n">
-        <v>34.5641</v>
+        <v>34.6092</v>
       </c>
       <c r="H24" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I24" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>18 aug</t>
+          <t>19 aug</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>179.14</v>
+        <v>181.7</v>
       </c>
       <c r="M24" t="n">
-        <v>183.9</v>
+        <v>186.98</v>
       </c>
       <c r="N24" t="n">
-        <v>177.98</v>
+        <v>180.38</v>
       </c>
       <c r="O24" t="n">
-        <v>182.5</v>
+        <v>185.9</v>
       </c>
       <c r="P24" t="n">
-        <v>148.8084</v>
+        <v>149.5324</v>
       </c>
       <c r="Q24" t="n">
-        <v>168.3358</v>
+        <v>168.1618</v>
       </c>
       <c r="R24" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S24" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>17 aug</t>
+          <t>18 aug</t>
         </is>
       </c>
       <c r="V24" t="n">
-        <v>489.2191</v>
+        <v>480.6352</v>
       </c>
       <c r="W24" t="n">
-        <v>491.7343</v>
+        <v>483.3601</v>
       </c>
       <c r="X24" t="n">
-        <v>477.5111</v>
+        <v>476.2534</v>
       </c>
       <c r="Y24" t="n">
-        <v>479.4474</v>
+        <v>480.725</v>
       </c>
       <c r="Z24" t="n">
-        <v>413.044</v>
+        <v>414.3408</v>
       </c>
       <c r="AA24" t="n">
-        <v>430.2151</v>
+        <v>429.933</v>
       </c>
       <c r="AB24" t="n">
         <v>535.3375423278808</v>
@@ -5342,84 +5364,84 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>19 aug</t>
+          <t>20 aug</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>39.835</v>
+        <v>39.865</v>
       </c>
       <c r="C25" t="n">
-        <v>40.14</v>
+        <v>40.51</v>
       </c>
       <c r="D25" t="n">
-        <v>39.74</v>
+        <v>39.8</v>
       </c>
       <c r="E25" t="n">
-        <v>39.94</v>
+        <v>40.28</v>
       </c>
       <c r="F25" t="n">
-        <v>36.6336</v>
+        <v>36.6884</v>
       </c>
       <c r="G25" t="n">
-        <v>34.6092</v>
+        <v>34.6545</v>
       </c>
       <c r="H25" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I25" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>19 aug</t>
+          <t>20 aug</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>181.7</v>
+        <v>183.78</v>
       </c>
       <c r="M25" t="n">
-        <v>186.98</v>
+        <v>186.1</v>
       </c>
       <c r="N25" t="n">
-        <v>180.38</v>
+        <v>182.52</v>
       </c>
       <c r="O25" t="n">
-        <v>185.9</v>
+        <v>185.64</v>
       </c>
       <c r="P25" t="n">
-        <v>149.5324</v>
+        <v>150.4472</v>
       </c>
       <c r="Q25" t="n">
-        <v>168.1618</v>
+        <v>167.9648</v>
       </c>
       <c r="R25" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S25" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>18 aug</t>
+          <t>19 aug</t>
         </is>
       </c>
       <c r="V25" t="n">
-        <v>480.6352</v>
+        <v>479.168</v>
       </c>
       <c r="W25" t="n">
-        <v>483.3601</v>
+        <v>488.3806</v>
       </c>
       <c r="X25" t="n">
-        <v>476.2534</v>
+        <v>478.4593</v>
       </c>
       <c r="Y25" t="n">
-        <v>480.725</v>
+        <v>483.4</v>
       </c>
       <c r="Z25" t="n">
-        <v>414.3408</v>
+        <v>415.7895</v>
       </c>
       <c r="AA25" t="n">
-        <v>429.933</v>
+        <v>429.7427</v>
       </c>
       <c r="AB25" t="n">
         <v>535.3375423278808</v>
@@ -5431,84 +5453,84 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>20 aug</t>
+          <t>21 aug</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>39.865</v>
+        <v>40.1</v>
       </c>
       <c r="C26" t="n">
-        <v>40.51</v>
+        <v>40.37</v>
       </c>
       <c r="D26" t="n">
-        <v>39.8</v>
+        <v>39.84</v>
       </c>
       <c r="E26" t="n">
-        <v>40.28</v>
+        <v>39.91</v>
       </c>
       <c r="F26" t="n">
-        <v>36.6884</v>
+        <v>36.7478</v>
       </c>
       <c r="G26" t="n">
-        <v>34.6545</v>
+        <v>34.6988</v>
       </c>
       <c r="H26" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I26" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>20 aug</t>
+          <t>21 aug</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>183.78</v>
+        <v>185.18</v>
       </c>
       <c r="M26" t="n">
-        <v>186.1</v>
+        <v>188.4</v>
       </c>
       <c r="N26" t="n">
-        <v>182.52</v>
+        <v>183.6</v>
       </c>
       <c r="O26" t="n">
-        <v>185.64</v>
+        <v>188.12</v>
       </c>
       <c r="P26" t="n">
-        <v>150.4472</v>
+        <v>151.4044</v>
       </c>
       <c r="Q26" t="n">
-        <v>167.9648</v>
+        <v>167.794</v>
       </c>
       <c r="R26" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S26" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>19 aug</t>
+          <t>20 aug</t>
         </is>
       </c>
       <c r="V26" t="n">
-        <v>479.168</v>
+        <v>483.3</v>
       </c>
       <c r="W26" t="n">
-        <v>488.3806</v>
+        <v>484.16</v>
       </c>
       <c r="X26" t="n">
-        <v>478.4593</v>
+        <v>479.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>483.4</v>
+        <v>481.15</v>
       </c>
       <c r="Z26" t="n">
-        <v>415.7895</v>
+        <v>417.3594</v>
       </c>
       <c r="AA26" t="n">
-        <v>429.7427</v>
+        <v>429.5805</v>
       </c>
       <c r="AB26" t="n">
         <v>535.3375423278808</v>
@@ -5520,84 +5542,84 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>21 aug</t>
+          <t>24 aug</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>40.1</v>
+        <v>39.88</v>
       </c>
       <c r="C27" t="n">
-        <v>40.37</v>
+        <v>40.085</v>
       </c>
       <c r="D27" t="n">
-        <v>39.84</v>
+        <v>39.68</v>
       </c>
       <c r="E27" t="n">
-        <v>39.91</v>
+        <v>39.775</v>
       </c>
       <c r="F27" t="n">
-        <v>36.7478</v>
+        <v>36.8369</v>
       </c>
       <c r="G27" t="n">
-        <v>34.6988</v>
+        <v>34.7421</v>
       </c>
       <c r="H27" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I27" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>21 aug</t>
+          <t>24 aug</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>185.18</v>
+        <v>186.86</v>
       </c>
       <c r="M27" t="n">
-        <v>188.4</v>
+        <v>188.16</v>
       </c>
       <c r="N27" t="n">
-        <v>183.6</v>
+        <v>185.52</v>
       </c>
       <c r="O27" t="n">
-        <v>188.12</v>
+        <v>187.2</v>
       </c>
       <c r="P27" t="n">
-        <v>151.4044</v>
+        <v>152.2848</v>
       </c>
       <c r="Q27" t="n">
-        <v>167.794</v>
+        <v>167.6093</v>
       </c>
       <c r="R27" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S27" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>20 aug</t>
+          <t>21 aug</t>
         </is>
       </c>
       <c r="V27" t="n">
-        <v>483.3</v>
+        <v>479.88</v>
       </c>
       <c r="W27" t="n">
-        <v>484.16</v>
+        <v>486.36</v>
       </c>
       <c r="X27" t="n">
-        <v>479.5</v>
+        <v>478.53</v>
       </c>
       <c r="Y27" t="n">
-        <v>481.15</v>
+        <v>483.24</v>
       </c>
       <c r="Z27" t="n">
-        <v>417.3594</v>
+        <v>419.092</v>
       </c>
       <c r="AA27" t="n">
-        <v>429.5805</v>
+        <v>429.4327</v>
       </c>
       <c r="AB27" t="n">
         <v>535.3375423278808</v>
@@ -5609,84 +5631,84 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>24 aug</t>
+          <t>25 aug</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>39.88</v>
+        <v>39.77</v>
       </c>
       <c r="C28" t="n">
-        <v>40.085</v>
+        <v>39.915</v>
       </c>
       <c r="D28" t="n">
-        <v>39.68</v>
+        <v>39.385</v>
       </c>
       <c r="E28" t="n">
-        <v>39.775</v>
+        <v>39.6</v>
       </c>
       <c r="F28" t="n">
-        <v>36.8369</v>
+        <v>36.926</v>
       </c>
       <c r="G28" t="n">
-        <v>34.7421</v>
+        <v>34.783</v>
       </c>
       <c r="H28" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I28" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>24 aug</t>
+          <t>25 aug</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>186.86</v>
+        <v>186.4</v>
       </c>
       <c r="M28" t="n">
-        <v>188.16</v>
+        <v>187.62</v>
       </c>
       <c r="N28" t="n">
-        <v>185.52</v>
+        <v>182.74</v>
       </c>
       <c r="O28" t="n">
-        <v>187.2</v>
+        <v>185.46</v>
       </c>
       <c r="P28" t="n">
-        <v>152.2848</v>
+        <v>153.136</v>
       </c>
       <c r="Q28" t="n">
-        <v>167.6093</v>
+        <v>167.4651</v>
       </c>
       <c r="R28" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S28" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>21 aug</t>
+          <t>24 aug</t>
         </is>
       </c>
       <c r="V28" t="n">
-        <v>479.88</v>
+        <v>483.21</v>
       </c>
       <c r="W28" t="n">
-        <v>486.36</v>
+        <v>490.61</v>
       </c>
       <c r="X28" t="n">
-        <v>478.53</v>
+        <v>481.86</v>
       </c>
       <c r="Y28" t="n">
-        <v>483.24</v>
+        <v>487.31</v>
       </c>
       <c r="Z28" t="n">
-        <v>419.092</v>
+        <v>421.046</v>
       </c>
       <c r="AA28" t="n">
-        <v>429.4327</v>
+        <v>429.3186</v>
       </c>
       <c r="AB28" t="n">
         <v>535.3375423278808</v>
@@ -5698,84 +5720,84 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>25 aug</t>
+          <t>26 aug</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>39.77</v>
+        <v>39.275</v>
       </c>
       <c r="C29" t="n">
-        <v>39.915</v>
+        <v>39.47</v>
       </c>
       <c r="D29" t="n">
-        <v>39.385</v>
+        <v>38.91</v>
       </c>
       <c r="E29" t="n">
-        <v>39.6</v>
+        <v>39.42</v>
       </c>
       <c r="F29" t="n">
-        <v>36.926</v>
+        <v>37.0192</v>
       </c>
       <c r="G29" t="n">
-        <v>34.783</v>
+        <v>34.8202</v>
       </c>
       <c r="H29" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I29" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>25 aug</t>
+          <t>26 aug</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>186.4</v>
+        <v>179.92</v>
       </c>
       <c r="M29" t="n">
-        <v>187.62</v>
+        <v>182.16</v>
       </c>
       <c r="N29" t="n">
-        <v>182.74</v>
+        <v>176.82</v>
       </c>
       <c r="O29" t="n">
-        <v>185.46</v>
+        <v>180.02</v>
       </c>
       <c r="P29" t="n">
-        <v>153.136</v>
+        <v>153.9128</v>
       </c>
       <c r="Q29" t="n">
-        <v>167.4651</v>
+        <v>167.3049</v>
       </c>
       <c r="R29" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S29" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>24 aug</t>
+          <t>25 aug</t>
         </is>
       </c>
       <c r="V29" t="n">
-        <v>483.21</v>
+        <v>485.44</v>
       </c>
       <c r="W29" t="n">
-        <v>490.61</v>
+        <v>492.44</v>
       </c>
       <c r="X29" t="n">
-        <v>481.86</v>
+        <v>484.3</v>
       </c>
       <c r="Y29" t="n">
-        <v>487.31</v>
+        <v>491.71</v>
       </c>
       <c r="Z29" t="n">
-        <v>421.046</v>
+        <v>423.0801</v>
       </c>
       <c r="AA29" t="n">
-        <v>429.3186</v>
+        <v>429.262</v>
       </c>
       <c r="AB29" t="n">
         <v>535.3375423278808</v>
@@ -5787,84 +5809,84 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>26 aug</t>
+          <t>27 aug</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>39.275</v>
+        <v>39.16</v>
       </c>
       <c r="C30" t="n">
-        <v>39.47</v>
+        <v>39.295</v>
       </c>
       <c r="D30" t="n">
-        <v>38.91</v>
+        <v>38.65</v>
       </c>
       <c r="E30" t="n">
-        <v>39.42</v>
+        <v>38.76</v>
       </c>
       <c r="F30" t="n">
-        <v>37.0192</v>
+        <v>37.117</v>
       </c>
       <c r="G30" t="n">
-        <v>34.8202</v>
+        <v>34.8559</v>
       </c>
       <c r="H30" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I30" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>26 aug</t>
+          <t>27 aug</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>179.92</v>
+        <v>182.5</v>
       </c>
       <c r="M30" t="n">
-        <v>182.16</v>
+        <v>190.8</v>
       </c>
       <c r="N30" t="n">
-        <v>176.82</v>
+        <v>181.14</v>
       </c>
       <c r="O30" t="n">
-        <v>180.02</v>
+        <v>189.88</v>
       </c>
       <c r="P30" t="n">
-        <v>153.9128</v>
+        <v>155.0132</v>
       </c>
       <c r="Q30" t="n">
-        <v>167.3049</v>
+        <v>167.1911</v>
       </c>
       <c r="R30" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S30" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>25 aug</t>
+          <t>26 aug</t>
         </is>
       </c>
       <c r="V30" t="n">
-        <v>485.44</v>
+        <v>487.85</v>
       </c>
       <c r="W30" t="n">
-        <v>492.44</v>
+        <v>497.4</v>
       </c>
       <c r="X30" t="n">
-        <v>484.3</v>
+        <v>487.31</v>
       </c>
       <c r="Y30" t="n">
-        <v>491.71</v>
+        <v>496.37</v>
       </c>
       <c r="Z30" t="n">
-        <v>423.0801</v>
+        <v>425.0273</v>
       </c>
       <c r="AA30" t="n">
-        <v>429.262</v>
+        <v>429.2786</v>
       </c>
       <c r="AB30" t="n">
         <v>535.3375423278808</v>
@@ -5876,84 +5898,84 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>27 aug</t>
+          <t>28 aug</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>39.16</v>
+        <v>39</v>
       </c>
       <c r="C31" t="n">
-        <v>39.295</v>
+        <v>39.18</v>
       </c>
       <c r="D31" t="n">
-        <v>38.65</v>
+        <v>38.845</v>
       </c>
       <c r="E31" t="n">
-        <v>38.76</v>
+        <v>39.145</v>
       </c>
       <c r="F31" t="n">
-        <v>37.117</v>
+        <v>37.2162</v>
       </c>
       <c r="G31" t="n">
-        <v>34.8559</v>
+        <v>34.8941</v>
       </c>
       <c r="H31" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I31" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>27 aug</t>
+          <t>28 aug</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>182.5</v>
+        <v>189.5</v>
       </c>
       <c r="M31" t="n">
-        <v>190.8</v>
+        <v>191.94</v>
       </c>
       <c r="N31" t="n">
-        <v>181.14</v>
+        <v>187.98</v>
       </c>
       <c r="O31" t="n">
-        <v>189.88</v>
+        <v>191.32</v>
       </c>
       <c r="P31" t="n">
-        <v>155.0132</v>
+        <v>156.1568</v>
       </c>
       <c r="Q31" t="n">
-        <v>167.1911</v>
+        <v>167.0806</v>
       </c>
       <c r="R31" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S31" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>26 aug</t>
+          <t>27 aug</t>
         </is>
       </c>
       <c r="V31" t="n">
-        <v>487.85</v>
+        <v>494.88</v>
       </c>
       <c r="W31" t="n">
-        <v>497.4</v>
+        <v>506.48</v>
       </c>
       <c r="X31" t="n">
-        <v>487.31</v>
+        <v>490.08</v>
       </c>
       <c r="Y31" t="n">
-        <v>496.37</v>
+        <v>505.06</v>
       </c>
       <c r="Z31" t="n">
-        <v>425.0273</v>
+        <v>427.2667</v>
       </c>
       <c r="AA31" t="n">
-        <v>429.2786</v>
+        <v>429.3401</v>
       </c>
       <c r="AB31" t="n">
         <v>535.3375423278808</v>
@@ -5965,84 +5987,84 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>28 aug</t>
+          <t>31 aug</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>39</v>
+        <v>39.54</v>
       </c>
       <c r="C32" t="n">
-        <v>39.18</v>
+        <v>39.91</v>
       </c>
       <c r="D32" t="n">
-        <v>38.845</v>
+        <v>39.24</v>
       </c>
       <c r="E32" t="n">
-        <v>39.145</v>
+        <v>39.335</v>
       </c>
       <c r="F32" t="n">
-        <v>37.2162</v>
+        <v>37.3111</v>
       </c>
       <c r="G32" t="n">
-        <v>34.8941</v>
+        <v>34.9333</v>
       </c>
       <c r="H32" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I32" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>28 aug</t>
+          <t>31 aug</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>189.5</v>
+        <v>188.46</v>
       </c>
       <c r="M32" t="n">
-        <v>191.94</v>
+        <v>192.12</v>
       </c>
       <c r="N32" t="n">
-        <v>187.98</v>
+        <v>188.2</v>
       </c>
       <c r="O32" t="n">
-        <v>191.32</v>
+        <v>190.9</v>
       </c>
       <c r="P32" t="n">
-        <v>156.1568</v>
+        <v>157.3304</v>
       </c>
       <c r="Q32" t="n">
-        <v>167.0806</v>
+        <v>166.9613</v>
       </c>
       <c r="R32" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S32" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>27 aug</t>
+          <t>28 aug</t>
         </is>
       </c>
       <c r="V32" t="n">
-        <v>494.88</v>
+        <v>505.33</v>
       </c>
       <c r="W32" t="n">
-        <v>506.48</v>
+        <v>517.78</v>
       </c>
       <c r="X32" t="n">
-        <v>490.08</v>
+        <v>504.87</v>
       </c>
       <c r="Y32" t="n">
-        <v>505.06</v>
+        <v>513.53</v>
       </c>
       <c r="Z32" t="n">
-        <v>427.2667</v>
+        <v>429.9734</v>
       </c>
       <c r="AA32" t="n">
-        <v>429.3401</v>
+        <v>429.3984</v>
       </c>
       <c r="AB32" t="n">
         <v>535.3375423278808</v>
@@ -6054,84 +6076,84 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>31 aug</t>
+          <t>1 sep</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>39.54</v>
+        <v>39.77</v>
       </c>
       <c r="C33" t="n">
-        <v>39.91</v>
+        <v>40.19</v>
       </c>
       <c r="D33" t="n">
-        <v>39.24</v>
+        <v>39.645</v>
       </c>
       <c r="E33" t="n">
-        <v>39.335</v>
+        <v>40.155</v>
       </c>
       <c r="F33" t="n">
-        <v>37.3111</v>
+        <v>37.4239</v>
       </c>
       <c r="G33" t="n">
-        <v>34.9333</v>
+        <v>34.9763</v>
       </c>
       <c r="H33" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I33" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>31 aug</t>
+          <t>1 sep</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>188.46</v>
+        <v>186</v>
       </c>
       <c r="M33" t="n">
-        <v>192.12</v>
+        <v>187.86</v>
       </c>
       <c r="N33" t="n">
-        <v>188.2</v>
+        <v>183.32</v>
       </c>
       <c r="O33" t="n">
-        <v>190.9</v>
+        <v>184.26</v>
       </c>
       <c r="P33" t="n">
-        <v>157.3304</v>
+        <v>158.3252</v>
       </c>
       <c r="Q33" t="n">
-        <v>166.9613</v>
+        <v>166.8103</v>
       </c>
       <c r="R33" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S33" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>28 aug</t>
+          <t>31 aug</t>
         </is>
       </c>
       <c r="V33" t="n">
-        <v>505.33</v>
+        <v>510.38</v>
       </c>
       <c r="W33" t="n">
-        <v>517.78</v>
+        <v>512.1900000000001</v>
       </c>
       <c r="X33" t="n">
-        <v>504.87</v>
+        <v>506.39</v>
       </c>
       <c r="Y33" t="n">
-        <v>513.53</v>
+        <v>507.29</v>
       </c>
       <c r="Z33" t="n">
-        <v>429.9734</v>
+        <v>432.5454</v>
       </c>
       <c r="AA33" t="n">
-        <v>429.3984</v>
+        <v>429.4122</v>
       </c>
       <c r="AB33" t="n">
         <v>535.3375423278808</v>
@@ -6143,84 +6165,84 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1 sep</t>
+          <t>2 sep</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>39.77</v>
+        <v>40.35</v>
       </c>
       <c r="C34" t="n">
-        <v>40.19</v>
+        <v>40.615</v>
       </c>
       <c r="D34" t="n">
-        <v>39.645</v>
+        <v>39.975</v>
       </c>
       <c r="E34" t="n">
-        <v>40.155</v>
+        <v>40.21</v>
       </c>
       <c r="F34" t="n">
-        <v>37.4239</v>
+        <v>37.5499</v>
       </c>
       <c r="G34" t="n">
-        <v>34.9763</v>
+        <v>35.0217</v>
       </c>
       <c r="H34" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I34" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>1 sep</t>
+          <t>2 sep</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>186</v>
+        <v>182.18</v>
       </c>
       <c r="M34" t="n">
-        <v>187.86</v>
+        <v>184.7</v>
       </c>
       <c r="N34" t="n">
-        <v>183.32</v>
+        <v>180.72</v>
       </c>
       <c r="O34" t="n">
-        <v>184.26</v>
+        <v>181.44</v>
       </c>
       <c r="P34" t="n">
-        <v>158.3252</v>
+        <v>159.2568</v>
       </c>
       <c r="Q34" t="n">
-        <v>166.8103</v>
+        <v>166.6796</v>
       </c>
       <c r="R34" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S34" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>31 aug</t>
+          <t>1 sep</t>
         </is>
       </c>
       <c r="V34" t="n">
-        <v>510.38</v>
+        <v>497.52</v>
       </c>
       <c r="W34" t="n">
-        <v>512.1900000000001</v>
+        <v>505.97</v>
       </c>
       <c r="X34" t="n">
-        <v>506.39</v>
+        <v>496.78</v>
       </c>
       <c r="Y34" t="n">
-        <v>507.29</v>
+        <v>501.02</v>
       </c>
       <c r="Z34" t="n">
-        <v>432.5454</v>
+        <v>435.2328</v>
       </c>
       <c r="AA34" t="n">
-        <v>429.4122</v>
+        <v>429.3825</v>
       </c>
       <c r="AB34" t="n">
         <v>535.3375423278808</v>
@@ -6232,84 +6254,84 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2 sep</t>
+          <t>3 sep</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>40.35</v>
+        <v>40.095</v>
       </c>
       <c r="C35" t="n">
-        <v>40.615</v>
+        <v>40.215</v>
       </c>
       <c r="D35" t="n">
-        <v>39.975</v>
+        <v>39.54</v>
       </c>
       <c r="E35" t="n">
-        <v>40.21</v>
+        <v>40.04</v>
       </c>
       <c r="F35" t="n">
-        <v>37.5499</v>
+        <v>37.6767</v>
       </c>
       <c r="G35" t="n">
-        <v>35.0217</v>
+        <v>35.0679</v>
       </c>
       <c r="H35" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I35" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2 sep</t>
+          <t>3 sep</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>182.18</v>
+        <v>182.08</v>
       </c>
       <c r="M35" t="n">
-        <v>184.7</v>
+        <v>187.56</v>
       </c>
       <c r="N35" t="n">
-        <v>180.72</v>
+        <v>182</v>
       </c>
       <c r="O35" t="n">
-        <v>181.44</v>
+        <v>185.58</v>
       </c>
       <c r="P35" t="n">
-        <v>159.2568</v>
+        <v>160.3228</v>
       </c>
       <c r="Q35" t="n">
-        <v>166.6796</v>
+        <v>166.5898</v>
       </c>
       <c r="R35" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S35" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>1 sep</t>
+          <t>2 sep</t>
         </is>
       </c>
       <c r="V35" t="n">
-        <v>497.52</v>
+        <v>499.85</v>
       </c>
       <c r="W35" t="n">
-        <v>505.97</v>
+        <v>500.27</v>
       </c>
       <c r="X35" t="n">
-        <v>496.78</v>
+        <v>493.81</v>
       </c>
       <c r="Y35" t="n">
-        <v>501.02</v>
+        <v>496.82</v>
       </c>
       <c r="Z35" t="n">
-        <v>435.2328</v>
+        <v>437.7045</v>
       </c>
       <c r="AA35" t="n">
-        <v>429.3825</v>
+        <v>429.3706</v>
       </c>
       <c r="AB35" t="n">
         <v>535.3375423278808</v>
@@ -6321,84 +6343,84 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3 sep</t>
+          <t>4 sep</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>40.095</v>
+        <v>40.145</v>
       </c>
       <c r="C36" t="n">
-        <v>40.215</v>
+        <v>40.28</v>
       </c>
       <c r="D36" t="n">
-        <v>39.54</v>
+        <v>39.665</v>
       </c>
       <c r="E36" t="n">
-        <v>40.04</v>
+        <v>40.105</v>
       </c>
       <c r="F36" t="n">
-        <v>37.6767</v>
+        <v>37.8115</v>
       </c>
       <c r="G36" t="n">
-        <v>35.0679</v>
+        <v>35.113</v>
       </c>
       <c r="H36" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I36" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>3 sep</t>
+          <t>4 sep</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>182.08</v>
+        <v>187.8</v>
       </c>
       <c r="M36" t="n">
-        <v>187.56</v>
+        <v>189.9</v>
       </c>
       <c r="N36" t="n">
-        <v>182</v>
+        <v>184.96</v>
       </c>
       <c r="O36" t="n">
-        <v>185.58</v>
+        <v>185.68</v>
       </c>
       <c r="P36" t="n">
-        <v>160.3228</v>
+        <v>161.3336</v>
       </c>
       <c r="Q36" t="n">
-        <v>166.5898</v>
+        <v>166.5086</v>
       </c>
       <c r="R36" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S36" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>2 sep</t>
+          <t>3 sep</t>
         </is>
       </c>
       <c r="V36" t="n">
-        <v>499.85</v>
+        <v>501.66</v>
       </c>
       <c r="W36" t="n">
-        <v>500.27</v>
+        <v>515.65</v>
       </c>
       <c r="X36" t="n">
-        <v>493.81</v>
+        <v>500.8</v>
       </c>
       <c r="Y36" t="n">
-        <v>496.82</v>
+        <v>510.12</v>
       </c>
       <c r="Z36" t="n">
-        <v>437.7045</v>
+        <v>440.6114</v>
       </c>
       <c r="AA36" t="n">
-        <v>429.3706</v>
+        <v>429.3912</v>
       </c>
       <c r="AB36" t="n">
         <v>535.3375423278808</v>
@@ -6410,84 +6432,84 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>4 sep</t>
+          <t>7 sep</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>40.145</v>
+        <v>40.26</v>
       </c>
       <c r="C37" t="n">
-        <v>40.28</v>
+        <v>40.845</v>
       </c>
       <c r="D37" t="n">
-        <v>39.665</v>
+        <v>40.12</v>
       </c>
       <c r="E37" t="n">
-        <v>40.105</v>
+        <v>40.56</v>
       </c>
       <c r="F37" t="n">
-        <v>37.8115</v>
+        <v>37.9551</v>
       </c>
       <c r="G37" t="n">
-        <v>35.113</v>
+        <v>35.1619</v>
       </c>
       <c r="H37" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I37" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>4 sep</t>
+          <t>7 sep</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>187.8</v>
+        <v>183.56</v>
       </c>
       <c r="M37" t="n">
-        <v>189.9</v>
+        <v>184.3</v>
       </c>
       <c r="N37" t="n">
-        <v>184.96</v>
+        <v>179.92</v>
       </c>
       <c r="O37" t="n">
-        <v>185.68</v>
+        <v>182.8</v>
       </c>
       <c r="P37" t="n">
-        <v>161.3336</v>
+        <v>162.2568</v>
       </c>
       <c r="Q37" t="n">
-        <v>166.5086</v>
+        <v>166.4122</v>
       </c>
       <c r="R37" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S37" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>3 sep</t>
+          <t>4 sep</t>
         </is>
       </c>
       <c r="V37" t="n">
-        <v>501.66</v>
+        <v>510</v>
       </c>
       <c r="W37" t="n">
-        <v>515.65</v>
+        <v>511</v>
       </c>
       <c r="X37" t="n">
-        <v>500.8</v>
+        <v>499.36</v>
       </c>
       <c r="Y37" t="n">
-        <v>510.12</v>
+        <v>499.7</v>
       </c>
       <c r="Z37" t="n">
-        <v>440.6114</v>
+        <v>443.5621</v>
       </c>
       <c r="AA37" t="n">
-        <v>429.3912</v>
+        <v>429.3729</v>
       </c>
       <c r="AB37" t="n">
         <v>535.3375423278808</v>
@@ -6499,84 +6521,84 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>7 sep</t>
+          <t>8 sep</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>40.26</v>
+        <v>40.83</v>
       </c>
       <c r="C38" t="n">
-        <v>40.845</v>
+        <v>41.18</v>
       </c>
       <c r="D38" t="n">
-        <v>40.12</v>
+        <v>40.6325</v>
       </c>
       <c r="E38" t="n">
-        <v>40.56</v>
+        <v>40.855</v>
       </c>
       <c r="F38" t="n">
-        <v>37.9551</v>
+        <v>38.0977</v>
       </c>
       <c r="G38" t="n">
-        <v>35.1619</v>
+        <v>35.2131</v>
       </c>
       <c r="H38" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I38" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>7 sep</t>
+          <t>8 sep</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>183.56</v>
+        <v>182.32</v>
       </c>
       <c r="M38" t="n">
-        <v>184.3</v>
+        <v>183.76</v>
       </c>
       <c r="N38" t="n">
-        <v>179.92</v>
+        <v>180.02</v>
       </c>
       <c r="O38" t="n">
-        <v>182.8</v>
+        <v>181.7</v>
       </c>
       <c r="P38" t="n">
-        <v>162.2568</v>
+        <v>163.2108</v>
       </c>
       <c r="Q38" t="n">
-        <v>166.4122</v>
+        <v>166.3049</v>
       </c>
       <c r="R38" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S38" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>4 sep</t>
+          <t>8 sep</t>
         </is>
       </c>
       <c r="V38" t="n">
-        <v>510</v>
+        <v>493.01</v>
       </c>
       <c r="W38" t="n">
-        <v>511</v>
+        <v>495.19</v>
       </c>
       <c r="X38" t="n">
-        <v>499.36</v>
+        <v>490.15</v>
       </c>
       <c r="Y38" t="n">
-        <v>499.7</v>
+        <v>493.95</v>
       </c>
       <c r="Z38" t="n">
-        <v>443.5621</v>
+        <v>445.9957</v>
       </c>
       <c r="AA38" t="n">
-        <v>429.3729</v>
+        <v>429.3939</v>
       </c>
       <c r="AB38" t="n">
         <v>535.3375423278808</v>
@@ -6588,84 +6610,84 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>8 sep</t>
+          <t>9 sep</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>40.83</v>
+        <v>41.1</v>
       </c>
       <c r="C39" t="n">
-        <v>41.18</v>
+        <v>41.385</v>
       </c>
       <c r="D39" t="n">
-        <v>40.6325</v>
+        <v>40.85</v>
       </c>
       <c r="E39" t="n">
-        <v>40.855</v>
+        <v>40.94</v>
       </c>
       <c r="F39" t="n">
-        <v>38.0977</v>
+        <v>38.2513</v>
       </c>
       <c r="G39" t="n">
-        <v>35.2131</v>
+        <v>35.2646</v>
       </c>
       <c r="H39" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I39" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>8 sep</t>
+          <t>9 sep</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>182.32</v>
+        <v>183</v>
       </c>
       <c r="M39" t="n">
-        <v>183.76</v>
+        <v>187.04</v>
       </c>
       <c r="N39" t="n">
-        <v>180.02</v>
+        <v>181.36</v>
       </c>
       <c r="O39" t="n">
-        <v>181.7</v>
+        <v>182.86</v>
       </c>
       <c r="P39" t="n">
-        <v>163.2108</v>
+        <v>164.0504</v>
       </c>
       <c r="Q39" t="n">
-        <v>166.3049</v>
+        <v>166.2113</v>
       </c>
       <c r="R39" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S39" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>8 sep</t>
+          <t>9 sep</t>
         </is>
       </c>
       <c r="V39" t="n">
-        <v>493.01</v>
+        <v>493.07</v>
       </c>
       <c r="W39" t="n">
-        <v>495.19</v>
+        <v>494.39</v>
       </c>
       <c r="X39" t="n">
-        <v>490.15</v>
+        <v>489.8</v>
       </c>
       <c r="Y39" t="n">
-        <v>493.95</v>
+        <v>491.65</v>
       </c>
       <c r="Z39" t="n">
-        <v>445.9957</v>
+        <v>448.4712</v>
       </c>
       <c r="AA39" t="n">
-        <v>429.3939</v>
+        <v>429.4364</v>
       </c>
       <c r="AB39" t="n">
         <v>535.3375423278808</v>
@@ -6677,84 +6699,84 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>9 sep</t>
+          <t>10 sep</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>41.1</v>
+        <v>40.98</v>
       </c>
       <c r="C40" t="n">
-        <v>41.385</v>
+        <v>41.77</v>
       </c>
       <c r="D40" t="n">
-        <v>40.85</v>
+        <v>40.93</v>
       </c>
       <c r="E40" t="n">
-        <v>40.94</v>
+        <v>41.23</v>
       </c>
       <c r="F40" t="n">
-        <v>38.2513</v>
+        <v>38.4034</v>
       </c>
       <c r="G40" t="n">
-        <v>35.2646</v>
+        <v>35.3174</v>
       </c>
       <c r="H40" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I40" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>9 sep</t>
+          <t>10 sep</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="M40" t="n">
-        <v>187.04</v>
+        <v>180.4</v>
       </c>
       <c r="N40" t="n">
-        <v>181.36</v>
+        <v>176.2</v>
       </c>
       <c r="O40" t="n">
-        <v>182.86</v>
+        <v>177.82</v>
       </c>
       <c r="P40" t="n">
-        <v>164.0504</v>
+        <v>164.7724</v>
       </c>
       <c r="Q40" t="n">
-        <v>166.2113</v>
+        <v>166.0803</v>
       </c>
       <c r="R40" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S40" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>9 sep</t>
+          <t>10 sep</t>
         </is>
       </c>
       <c r="V40" t="n">
-        <v>493.07</v>
+        <v>488.32</v>
       </c>
       <c r="W40" t="n">
-        <v>494.39</v>
+        <v>494.52</v>
       </c>
       <c r="X40" t="n">
-        <v>489.8</v>
+        <v>486</v>
       </c>
       <c r="Y40" t="n">
-        <v>491.65</v>
+        <v>492.44</v>
       </c>
       <c r="Z40" t="n">
-        <v>448.4712</v>
+        <v>450.8736</v>
       </c>
       <c r="AA40" t="n">
-        <v>429.4364</v>
+        <v>429.5215</v>
       </c>
       <c r="AB40" t="n">
         <v>535.3375423278808</v>
@@ -6766,84 +6788,84 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10 sep</t>
+          <t>11 sep</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>40.98</v>
+        <v>41.345</v>
       </c>
       <c r="C41" t="n">
-        <v>41.77</v>
+        <v>41.715</v>
       </c>
       <c r="D41" t="n">
-        <v>40.93</v>
+        <v>40.905</v>
       </c>
       <c r="E41" t="n">
-        <v>41.23</v>
+        <v>41.415</v>
       </c>
       <c r="F41" t="n">
-        <v>38.4034</v>
+        <v>38.5608</v>
       </c>
       <c r="G41" t="n">
-        <v>35.3174</v>
+        <v>35.3717</v>
       </c>
       <c r="H41" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I41" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>10 sep</t>
+          <t>11 sep</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>180</v>
+        <v>175.68</v>
       </c>
       <c r="M41" t="n">
-        <v>180.4</v>
+        <v>178.84</v>
       </c>
       <c r="N41" t="n">
-        <v>176.2</v>
+        <v>172.16</v>
       </c>
       <c r="O41" t="n">
-        <v>177.82</v>
+        <v>177.26</v>
       </c>
       <c r="P41" t="n">
-        <v>164.7724</v>
+        <v>165.5248</v>
       </c>
       <c r="Q41" t="n">
-        <v>166.0803</v>
+        <v>165.9594</v>
       </c>
       <c r="R41" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S41" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>10 sep</t>
+          <t>11 sep</t>
         </is>
       </c>
       <c r="V41" t="n">
-        <v>488.32</v>
+        <v>495.65</v>
       </c>
       <c r="W41" t="n">
-        <v>494.52</v>
+        <v>498.97</v>
       </c>
       <c r="X41" t="n">
-        <v>486</v>
+        <v>492.58</v>
       </c>
       <c r="Y41" t="n">
-        <v>492.44</v>
+        <v>495.63</v>
       </c>
       <c r="Z41" t="n">
-        <v>450.8736</v>
+        <v>453.115</v>
       </c>
       <c r="AA41" t="n">
-        <v>429.5215</v>
+        <v>429.654</v>
       </c>
       <c r="AB41" t="n">
         <v>535.3375423278808</v>
@@ -6855,84 +6877,84 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>11 sep</t>
+          <t>14 sep</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>41.345</v>
+        <v>41.88</v>
       </c>
       <c r="C42" t="n">
-        <v>41.715</v>
+        <v>42.285</v>
       </c>
       <c r="D42" t="n">
-        <v>40.905</v>
+        <v>41.8</v>
       </c>
       <c r="E42" t="n">
-        <v>41.415</v>
+        <v>41.91</v>
       </c>
       <c r="F42" t="n">
-        <v>38.5608</v>
+        <v>38.7226</v>
       </c>
       <c r="G42" t="n">
-        <v>35.3717</v>
+        <v>35.4269</v>
       </c>
       <c r="H42" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I42" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>11 sep</t>
+          <t>14 sep</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>175.68</v>
+        <v>180.82</v>
       </c>
       <c r="M42" t="n">
-        <v>178.84</v>
+        <v>186.76</v>
       </c>
       <c r="N42" t="n">
-        <v>172.16</v>
+        <v>180.82</v>
       </c>
       <c r="O42" t="n">
-        <v>177.26</v>
+        <v>186.26</v>
       </c>
       <c r="P42" t="n">
-        <v>165.5248</v>
+        <v>166.4488</v>
       </c>
       <c r="Q42" t="n">
-        <v>165.9594</v>
+        <v>165.8745</v>
       </c>
       <c r="R42" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S42" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>11 sep</t>
+          <t>14 sep</t>
         </is>
       </c>
       <c r="V42" t="n">
-        <v>495.65</v>
+        <v>497.06</v>
       </c>
       <c r="W42" t="n">
-        <v>498.97</v>
+        <v>509.95</v>
       </c>
       <c r="X42" t="n">
-        <v>492.58</v>
+        <v>495.34</v>
       </c>
       <c r="Y42" t="n">
-        <v>495.63</v>
+        <v>505.41</v>
       </c>
       <c r="Z42" t="n">
-        <v>453.115</v>
+        <v>455.4281</v>
       </c>
       <c r="AA42" t="n">
-        <v>429.654</v>
+        <v>429.8259</v>
       </c>
       <c r="AB42" t="n">
         <v>535.3375423278808</v>
@@ -6944,84 +6966,84 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>14 sep</t>
+          <t>15 sep</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>41.88</v>
+        <v>41.845</v>
       </c>
       <c r="C43" t="n">
-        <v>42.285</v>
+        <v>42.7</v>
       </c>
       <c r="D43" t="n">
-        <v>41.8</v>
+        <v>41.72</v>
       </c>
       <c r="E43" t="n">
-        <v>41.91</v>
+        <v>42.7</v>
       </c>
       <c r="F43" t="n">
-        <v>38.7226</v>
+        <v>38.8782</v>
       </c>
       <c r="G43" t="n">
-        <v>35.4269</v>
+        <v>35.4854</v>
       </c>
       <c r="H43" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I43" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>14 sep</t>
+          <t>15 sep</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>180.82</v>
+        <v>186.64</v>
       </c>
       <c r="M43" t="n">
-        <v>186.76</v>
+        <v>187.26</v>
       </c>
       <c r="N43" t="n">
-        <v>180.82</v>
+        <v>183.2</v>
       </c>
       <c r="O43" t="n">
-        <v>186.26</v>
+        <v>187.08</v>
       </c>
       <c r="P43" t="n">
-        <v>166.4488</v>
+        <v>167.3124</v>
       </c>
       <c r="Q43" t="n">
-        <v>165.8745</v>
+        <v>165.7921</v>
       </c>
       <c r="R43" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S43" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>14 sep</t>
+          <t>15 sep</t>
         </is>
       </c>
       <c r="V43" t="n">
-        <v>497.06</v>
+        <v>500.06</v>
       </c>
       <c r="W43" t="n">
-        <v>509.95</v>
+        <v>505.9</v>
       </c>
       <c r="X43" t="n">
-        <v>495.34</v>
+        <v>495.54</v>
       </c>
       <c r="Y43" t="n">
-        <v>505.41</v>
+        <v>497.12</v>
       </c>
       <c r="Z43" t="n">
-        <v>455.4281</v>
+        <v>457.6502</v>
       </c>
       <c r="AA43" t="n">
-        <v>429.8259</v>
+        <v>429.9416</v>
       </c>
       <c r="AB43" t="n">
         <v>535.3375423278808</v>
@@ -7033,84 +7055,84 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>15 sep</t>
+          <t>16 sep</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>41.845</v>
+        <v>42.72</v>
       </c>
       <c r="C44" t="n">
-        <v>42.7</v>
+        <v>42.85</v>
       </c>
       <c r="D44" t="n">
-        <v>41.72</v>
+        <v>41.67</v>
       </c>
       <c r="E44" t="n">
-        <v>42.7</v>
+        <v>41.825</v>
       </c>
       <c r="F44" t="n">
-        <v>38.8782</v>
+        <v>38.9989</v>
       </c>
       <c r="G44" t="n">
-        <v>35.4854</v>
+        <v>35.5403</v>
       </c>
       <c r="H44" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I44" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>15 sep</t>
+          <t>16 sep</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>186.64</v>
+        <v>185.86</v>
       </c>
       <c r="M44" t="n">
-        <v>187.26</v>
+        <v>186.76</v>
       </c>
       <c r="N44" t="n">
-        <v>183.2</v>
+        <v>182.18</v>
       </c>
       <c r="O44" t="n">
-        <v>187.08</v>
+        <v>186.56</v>
       </c>
       <c r="P44" t="n">
-        <v>167.3124</v>
+        <v>168.2844</v>
       </c>
       <c r="Q44" t="n">
-        <v>165.7921</v>
+        <v>165.6996</v>
       </c>
       <c r="R44" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S44" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>15 sep</t>
+          <t>16 sep</t>
         </is>
       </c>
       <c r="V44" t="n">
-        <v>500.06</v>
+        <v>493.03</v>
       </c>
       <c r="W44" t="n">
-        <v>505.9</v>
+        <v>495.97</v>
       </c>
       <c r="X44" t="n">
-        <v>495.54</v>
+        <v>487.23</v>
       </c>
       <c r="Y44" t="n">
-        <v>497.12</v>
+        <v>490.3</v>
       </c>
       <c r="Z44" t="n">
-        <v>457.6502</v>
+        <v>459.694</v>
       </c>
       <c r="AA44" t="n">
-        <v>429.9416</v>
+        <v>429.9809</v>
       </c>
       <c r="AB44" t="n">
         <v>535.3375423278808</v>
@@ -7122,84 +7144,84 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>16 sep</t>
+          <t>17 sep</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>42.72</v>
+        <v>41.58</v>
       </c>
       <c r="C45" t="n">
-        <v>42.85</v>
+        <v>42.055</v>
       </c>
       <c r="D45" t="n">
-        <v>41.67</v>
+        <v>41.38</v>
       </c>
       <c r="E45" t="n">
-        <v>41.825</v>
+        <v>41.56</v>
       </c>
       <c r="F45" t="n">
-        <v>38.9989</v>
+        <v>39.1225</v>
       </c>
       <c r="G45" t="n">
-        <v>35.5403</v>
+        <v>35.5926</v>
       </c>
       <c r="H45" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I45" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>16 sep</t>
+          <t>17 sep</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>185.86</v>
+        <v>188.54</v>
       </c>
       <c r="M45" t="n">
-        <v>186.76</v>
+        <v>189.2</v>
       </c>
       <c r="N45" t="n">
-        <v>182.18</v>
+        <v>184.62</v>
       </c>
       <c r="O45" t="n">
-        <v>186.56</v>
+        <v>188</v>
       </c>
       <c r="P45" t="n">
-        <v>168.2844</v>
+        <v>169.2896</v>
       </c>
       <c r="Q45" t="n">
-        <v>165.6996</v>
+        <v>165.6125</v>
       </c>
       <c r="R45" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S45" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>16 sep</t>
+          <t>17 sep</t>
         </is>
       </c>
       <c r="V45" t="n">
-        <v>493.03</v>
+        <v>497.8</v>
       </c>
       <c r="W45" t="n">
-        <v>495.97</v>
+        <v>501.47</v>
       </c>
       <c r="X45" t="n">
-        <v>487.23</v>
+        <v>493.17</v>
       </c>
       <c r="Y45" t="n">
-        <v>490.3</v>
+        <v>497.75</v>
       </c>
       <c r="Z45" t="n">
-        <v>459.694</v>
+        <v>461.9966</v>
       </c>
       <c r="AA45" t="n">
-        <v>429.9809</v>
+        <v>430.0251</v>
       </c>
       <c r="AB45" t="n">
         <v>535.3375423278808</v>
@@ -7211,84 +7233,84 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>17 sep</t>
+          <t>18 sep</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>41.58</v>
+        <v>41.465</v>
       </c>
       <c r="C46" t="n">
-        <v>42.055</v>
+        <v>41.5</v>
       </c>
       <c r="D46" t="n">
-        <v>41.38</v>
+        <v>40.955</v>
       </c>
       <c r="E46" t="n">
-        <v>41.56</v>
+        <v>41.315</v>
       </c>
       <c r="F46" t="n">
-        <v>39.1225</v>
+        <v>39.2414</v>
       </c>
       <c r="G46" t="n">
-        <v>35.5926</v>
+        <v>35.6436</v>
       </c>
       <c r="H46" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I46" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>17 sep</t>
+          <t>18 sep</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>188.54</v>
+        <v>186.1</v>
       </c>
       <c r="M46" t="n">
-        <v>189.2</v>
+        <v>187.26</v>
       </c>
       <c r="N46" t="n">
-        <v>184.62</v>
+        <v>182.56</v>
       </c>
       <c r="O46" t="n">
-        <v>188</v>
+        <v>183.12</v>
       </c>
       <c r="P46" t="n">
-        <v>169.2896</v>
+        <v>170.2004</v>
       </c>
       <c r="Q46" t="n">
-        <v>165.6125</v>
+        <v>165.5062</v>
       </c>
       <c r="R46" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S46" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>17 sep</t>
+          <t>18 sep</t>
         </is>
       </c>
       <c r="V46" t="n">
-        <v>497.8</v>
+        <v>497.97</v>
       </c>
       <c r="W46" t="n">
-        <v>501.47</v>
+        <v>498.65</v>
       </c>
       <c r="X46" t="n">
-        <v>493.17</v>
+        <v>491.1</v>
       </c>
       <c r="Y46" t="n">
-        <v>497.75</v>
+        <v>493.78</v>
       </c>
       <c r="Z46" t="n">
-        <v>461.9966</v>
+        <v>464.1995</v>
       </c>
       <c r="AA46" t="n">
-        <v>430.0251</v>
+        <v>430.0757</v>
       </c>
       <c r="AB46" t="n">
         <v>535.3375423278808</v>
@@ -7300,84 +7322,84 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>18 sep</t>
+          <t>21 sep</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>41.465</v>
+        <v>41.04</v>
       </c>
       <c r="C47" t="n">
-        <v>41.5</v>
+        <v>41.4</v>
       </c>
       <c r="D47" t="n">
-        <v>40.955</v>
+        <v>40.775</v>
       </c>
       <c r="E47" t="n">
-        <v>41.315</v>
+        <v>40.775</v>
       </c>
       <c r="F47" t="n">
-        <v>39.2414</v>
+        <v>39.3341</v>
       </c>
       <c r="G47" t="n">
-        <v>35.6436</v>
+        <v>35.6939</v>
       </c>
       <c r="H47" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I47" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>18 sep</t>
+          <t>21 sep</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>186.1</v>
+        <v>184.7</v>
       </c>
       <c r="M47" t="n">
-        <v>187.26</v>
+        <v>185.86</v>
       </c>
       <c r="N47" t="n">
-        <v>182.56</v>
+        <v>182.48</v>
       </c>
       <c r="O47" t="n">
-        <v>183.12</v>
+        <v>182.86</v>
       </c>
       <c r="P47" t="n">
-        <v>170.2004</v>
+        <v>171.0432</v>
       </c>
       <c r="Q47" t="n">
-        <v>165.5062</v>
+        <v>165.4052</v>
       </c>
       <c r="R47" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S47" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>18 sep</t>
+          <t>21 sep</t>
         </is>
       </c>
       <c r="V47" t="n">
-        <v>497.97</v>
+        <v>494.95</v>
       </c>
       <c r="W47" t="n">
-        <v>498.65</v>
+        <v>501.87</v>
       </c>
       <c r="X47" t="n">
-        <v>491.1</v>
+        <v>491.33</v>
       </c>
       <c r="Y47" t="n">
-        <v>493.78</v>
+        <v>501.61</v>
       </c>
       <c r="Z47" t="n">
-        <v>464.1995</v>
+        <v>466.5442</v>
       </c>
       <c r="AA47" t="n">
-        <v>430.0757</v>
+        <v>430.1492</v>
       </c>
       <c r="AB47" t="n">
         <v>535.3375423278808</v>
@@ -7389,84 +7411,84 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>21 sep</t>
+          <t>22 sep</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>41.04</v>
+        <v>40.84</v>
       </c>
       <c r="C48" t="n">
-        <v>41.4</v>
+        <v>41.165</v>
       </c>
       <c r="D48" t="n">
-        <v>40.775</v>
+        <v>40.215</v>
       </c>
       <c r="E48" t="n">
-        <v>40.775</v>
+        <v>41.01</v>
       </c>
       <c r="F48" t="n">
-        <v>39.3341</v>
+        <v>39.4244</v>
       </c>
       <c r="G48" t="n">
-        <v>35.6939</v>
+        <v>35.746</v>
       </c>
       <c r="H48" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I48" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>21 sep</t>
+          <t>22 sep</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>184.7</v>
+        <v>182.14</v>
       </c>
       <c r="M48" t="n">
-        <v>185.86</v>
+        <v>187.48</v>
       </c>
       <c r="N48" t="n">
-        <v>182.48</v>
+        <v>181.52</v>
       </c>
       <c r="O48" t="n">
-        <v>182.86</v>
+        <v>182.32</v>
       </c>
       <c r="P48" t="n">
-        <v>171.0432</v>
+        <v>171.9552</v>
       </c>
       <c r="Q48" t="n">
-        <v>165.4052</v>
+        <v>165.2836</v>
       </c>
       <c r="R48" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S48" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>21 sep</t>
+          <t>22 sep</t>
         </is>
       </c>
       <c r="V48" t="n">
-        <v>494.95</v>
+        <v>507.32</v>
       </c>
       <c r="W48" t="n">
-        <v>501.87</v>
+        <v>508.5</v>
       </c>
       <c r="X48" t="n">
-        <v>491.33</v>
+        <v>493.65</v>
       </c>
       <c r="Y48" t="n">
-        <v>501.61</v>
+        <v>498</v>
       </c>
       <c r="Z48" t="n">
-        <v>466.5442</v>
+        <v>468.699</v>
       </c>
       <c r="AA48" t="n">
-        <v>430.1492</v>
+        <v>430.2656</v>
       </c>
       <c r="AB48" t="n">
         <v>535.3375423278808</v>
@@ -7478,84 +7500,84 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>22 sep</t>
+          <t>23 sep</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>40.84</v>
+        <v>41</v>
       </c>
       <c r="C49" t="n">
-        <v>41.165</v>
+        <v>41.755</v>
       </c>
       <c r="D49" t="n">
-        <v>40.215</v>
+        <v>40.995</v>
       </c>
       <c r="E49" t="n">
-        <v>41.01</v>
+        <v>41.69</v>
       </c>
       <c r="F49" t="n">
-        <v>39.4244</v>
+        <v>39.5272</v>
       </c>
       <c r="G49" t="n">
-        <v>35.746</v>
+        <v>35.8024</v>
       </c>
       <c r="H49" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I49" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>22 sep</t>
+          <t>23 sep</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>182.14</v>
+        <v>184.9</v>
       </c>
       <c r="M49" t="n">
-        <v>187.48</v>
+        <v>187.8</v>
       </c>
       <c r="N49" t="n">
-        <v>181.52</v>
+        <v>183.48</v>
       </c>
       <c r="O49" t="n">
-        <v>182.32</v>
+        <v>186.46</v>
       </c>
       <c r="P49" t="n">
-        <v>171.9552</v>
+        <v>172.9448</v>
       </c>
       <c r="Q49" t="n">
-        <v>165.2836</v>
+        <v>165.1675</v>
       </c>
       <c r="R49" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S49" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>22 sep</t>
+          <t>23 sep</t>
         </is>
       </c>
       <c r="V49" t="n">
-        <v>507.32</v>
+        <v>500.76</v>
       </c>
       <c r="W49" t="n">
-        <v>508.5</v>
+        <v>509.44</v>
       </c>
       <c r="X49" t="n">
-        <v>493.65</v>
+        <v>495.88</v>
       </c>
       <c r="Y49" t="n">
-        <v>498</v>
+        <v>500.59</v>
       </c>
       <c r="Z49" t="n">
-        <v>468.699</v>
+        <v>471.0267</v>
       </c>
       <c r="AA49" t="n">
-        <v>430.2656</v>
+        <v>430.3795</v>
       </c>
       <c r="AB49" t="n">
         <v>535.3375423278808</v>
@@ -7567,84 +7589,84 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>23 sep</t>
+          <t>24 sep</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>41</v>
+        <v>41.825</v>
       </c>
       <c r="C50" t="n">
-        <v>41.755</v>
+        <v>42.52</v>
       </c>
       <c r="D50" t="n">
-        <v>40.995</v>
+        <v>41.78</v>
       </c>
       <c r="E50" t="n">
-        <v>41.69</v>
+        <v>42.43</v>
       </c>
       <c r="F50" t="n">
-        <v>39.5272</v>
+        <v>39.6382</v>
       </c>
       <c r="G50" t="n">
-        <v>35.8024</v>
+        <v>35.8638</v>
       </c>
       <c r="H50" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I50" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>23 sep</t>
+          <t>24 sep</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>184.9</v>
+        <v>184.52</v>
       </c>
       <c r="M50" t="n">
-        <v>187.8</v>
+        <v>185.5</v>
       </c>
       <c r="N50" t="n">
-        <v>183.48</v>
+        <v>182.26</v>
       </c>
       <c r="O50" t="n">
-        <v>186.46</v>
+        <v>184.18</v>
       </c>
       <c r="P50" t="n">
-        <v>172.9448</v>
+        <v>173.8756</v>
       </c>
       <c r="Q50" t="n">
-        <v>165.1675</v>
+        <v>165.0554</v>
       </c>
       <c r="R50" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S50" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>23 sep</t>
+          <t>24 sep</t>
         </is>
       </c>
       <c r="V50" t="n">
-        <v>500.76</v>
+        <v>495.07</v>
       </c>
       <c r="W50" t="n">
-        <v>509.44</v>
+        <v>498.9</v>
       </c>
       <c r="X50" t="n">
-        <v>495.88</v>
+        <v>491.22</v>
       </c>
       <c r="Y50" t="n">
-        <v>500.59</v>
+        <v>497.93</v>
       </c>
       <c r="Z50" t="n">
-        <v>471.0267</v>
+        <v>473.0876</v>
       </c>
       <c r="AA50" t="n">
-        <v>430.3795</v>
+        <v>430.4686</v>
       </c>
       <c r="AB50" t="n">
         <v>535.3375423278808</v>
@@ -7656,84 +7678,84 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>24 sep</t>
+          <t>25 sep</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>41.825</v>
+        <v>41.99</v>
       </c>
       <c r="C51" t="n">
-        <v>42.52</v>
+        <v>42.33</v>
       </c>
       <c r="D51" t="n">
-        <v>41.78</v>
+        <v>41.71</v>
       </c>
       <c r="E51" t="n">
-        <v>42.43</v>
+        <v>42.06</v>
       </c>
       <c r="F51" t="n">
-        <v>39.6382</v>
+        <v>39.7263</v>
       </c>
       <c r="G51" t="n">
-        <v>35.8638</v>
+        <v>35.9239</v>
       </c>
       <c r="H51" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I51" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>24 sep</t>
+          <t>25 sep</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>184.52</v>
+        <v>184.42</v>
       </c>
       <c r="M51" t="n">
-        <v>185.5</v>
+        <v>185.92</v>
       </c>
       <c r="N51" t="n">
-        <v>182.26</v>
+        <v>183.76</v>
       </c>
       <c r="O51" t="n">
-        <v>184.18</v>
+        <v>185.92</v>
       </c>
       <c r="P51" t="n">
-        <v>173.8756</v>
+        <v>174.8356</v>
       </c>
       <c r="Q51" t="n">
-        <v>165.0554</v>
+        <v>164.9525</v>
       </c>
       <c r="R51" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S51" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>24 sep</t>
+          <t>25 sep</t>
         </is>
       </c>
       <c r="V51" t="n">
-        <v>495.07</v>
+        <v>499.04</v>
       </c>
       <c r="W51" t="n">
-        <v>498.9</v>
+        <v>519.4</v>
       </c>
       <c r="X51" t="n">
-        <v>491.22</v>
+        <v>497.25</v>
       </c>
       <c r="Y51" t="n">
-        <v>497.93</v>
+        <v>516.17</v>
       </c>
       <c r="Z51" t="n">
-        <v>473.0876</v>
+        <v>475.4041</v>
       </c>
       <c r="AA51" t="n">
-        <v>430.4686</v>
+        <v>430.6098</v>
       </c>
       <c r="AB51" t="n">
         <v>535.3375423278808</v>
@@ -7745,84 +7767,84 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>25 sep</t>
+          <t>28 sep</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>41.99</v>
+        <v>42.45</v>
       </c>
       <c r="C52" t="n">
-        <v>42.33</v>
+        <v>42.995</v>
       </c>
       <c r="D52" t="n">
-        <v>41.71</v>
+        <v>42.38</v>
       </c>
       <c r="E52" t="n">
-        <v>42.06</v>
+        <v>42.725</v>
       </c>
       <c r="F52" t="n">
-        <v>39.7263</v>
+        <v>39.8301</v>
       </c>
       <c r="G52" t="n">
-        <v>35.9239</v>
+        <v>35.9888</v>
       </c>
       <c r="H52" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I52" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>25 sep</t>
+          <t>28 sep</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>184.42</v>
+        <v>185.2</v>
       </c>
       <c r="M52" t="n">
-        <v>185.92</v>
+        <v>186.76</v>
       </c>
       <c r="N52" t="n">
-        <v>183.76</v>
+        <v>178.88</v>
       </c>
       <c r="O52" t="n">
-        <v>185.92</v>
+        <v>184.02</v>
       </c>
       <c r="P52" t="n">
-        <v>174.8356</v>
+        <v>175.7508</v>
       </c>
       <c r="Q52" t="n">
-        <v>164.9525</v>
+        <v>164.8355</v>
       </c>
       <c r="R52" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S52" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>25 sep</t>
+          <t>28 sep</t>
         </is>
       </c>
       <c r="V52" t="n">
-        <v>499.04</v>
+        <v>505.47</v>
       </c>
       <c r="W52" t="n">
-        <v>519.4</v>
+        <v>513.33</v>
       </c>
       <c r="X52" t="n">
-        <v>497.25</v>
+        <v>502.22</v>
       </c>
       <c r="Y52" t="n">
-        <v>516.17</v>
+        <v>509.22</v>
       </c>
       <c r="Z52" t="n">
-        <v>475.4041</v>
+        <v>477.7269</v>
       </c>
       <c r="AA52" t="n">
-        <v>430.6098</v>
+        <v>430.7113</v>
       </c>
       <c r="AB52" t="n">
         <v>535.3375423278808</v>
@@ -7834,84 +7856,84 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>28 sep</t>
+          <t>29 sep</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>42.45</v>
+        <v>42.57</v>
       </c>
       <c r="C53" t="n">
-        <v>42.995</v>
+        <v>42.665</v>
       </c>
       <c r="D53" t="n">
-        <v>42.38</v>
+        <v>41.73</v>
       </c>
       <c r="E53" t="n">
-        <v>42.725</v>
+        <v>42.05</v>
       </c>
       <c r="F53" t="n">
-        <v>39.8301</v>
+        <v>39.9146</v>
       </c>
       <c r="G53" t="n">
-        <v>35.9888</v>
+        <v>36.0498</v>
       </c>
       <c r="H53" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I53" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>28 sep</t>
+          <t>29 sep</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>185.2</v>
+        <v>183.22</v>
       </c>
       <c r="M53" t="n">
-        <v>186.76</v>
+        <v>186.34</v>
       </c>
       <c r="N53" t="n">
-        <v>178.88</v>
+        <v>182.28</v>
       </c>
       <c r="O53" t="n">
-        <v>184.02</v>
+        <v>185.32</v>
       </c>
       <c r="P53" t="n">
-        <v>175.7508</v>
+        <v>176.7288</v>
       </c>
       <c r="Q53" t="n">
-        <v>164.8355</v>
+        <v>164.733</v>
       </c>
       <c r="R53" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S53" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>28 sep</t>
+          <t>29 sep</t>
         </is>
       </c>
       <c r="V53" t="n">
-        <v>505.47</v>
+        <v>508.31</v>
       </c>
       <c r="W53" t="n">
-        <v>513.33</v>
+        <v>513.64</v>
       </c>
       <c r="X53" t="n">
-        <v>502.22</v>
+        <v>502.4</v>
       </c>
       <c r="Y53" t="n">
-        <v>509.22</v>
+        <v>508.96</v>
       </c>
       <c r="Z53" t="n">
-        <v>477.7269</v>
+        <v>479.8754</v>
       </c>
       <c r="AA53" t="n">
-        <v>430.7113</v>
+        <v>430.8784</v>
       </c>
       <c r="AB53" t="n">
         <v>535.3375423278808</v>
@@ -7923,84 +7945,84 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>29 sep</t>
+          <t>30 sep</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>42.57</v>
+        <v>41.975</v>
       </c>
       <c r="C54" t="n">
-        <v>42.665</v>
+        <v>42.095</v>
       </c>
       <c r="D54" t="n">
-        <v>41.73</v>
+        <v>41.58</v>
       </c>
       <c r="E54" t="n">
-        <v>42.05</v>
+        <v>41.91</v>
       </c>
       <c r="F54" t="n">
-        <v>39.9146</v>
+        <v>39.9874</v>
       </c>
       <c r="G54" t="n">
-        <v>36.0498</v>
+        <v>36.1135</v>
       </c>
       <c r="H54" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I54" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>29 sep</t>
+          <t>30 sep</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>183.22</v>
+        <v>184.5</v>
       </c>
       <c r="M54" t="n">
-        <v>186.34</v>
+        <v>186.2</v>
       </c>
       <c r="N54" t="n">
-        <v>182.28</v>
+        <v>181.06</v>
       </c>
       <c r="O54" t="n">
-        <v>185.32</v>
+        <v>185.66</v>
       </c>
       <c r="P54" t="n">
-        <v>176.7288</v>
+        <v>177.8012</v>
       </c>
       <c r="Q54" t="n">
-        <v>164.733</v>
+        <v>164.6377</v>
       </c>
       <c r="R54" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S54" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>29 sep</t>
+          <t>30 sep</t>
         </is>
       </c>
       <c r="V54" t="n">
-        <v>508.31</v>
+        <v>511.61</v>
       </c>
       <c r="W54" t="n">
-        <v>513.64</v>
+        <v>519.83</v>
       </c>
       <c r="X54" t="n">
-        <v>502.4</v>
+        <v>510.31</v>
       </c>
       <c r="Y54" t="n">
-        <v>508.96</v>
+        <v>512.9</v>
       </c>
       <c r="Z54" t="n">
-        <v>479.8754</v>
+        <v>482.1933</v>
       </c>
       <c r="AA54" t="n">
-        <v>430.8784</v>
+        <v>431.0408</v>
       </c>
       <c r="AB54" t="n">
         <v>535.3375423278808</v>
@@ -8012,84 +8034,84 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>30 sep</t>
+          <t>1 okt</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>41.975</v>
+        <v>41.625</v>
       </c>
       <c r="C55" t="n">
-        <v>42.095</v>
+        <v>42.36</v>
       </c>
       <c r="D55" t="n">
-        <v>41.58</v>
+        <v>41.165</v>
       </c>
       <c r="E55" t="n">
-        <v>41.91</v>
+        <v>42.24</v>
       </c>
       <c r="F55" t="n">
-        <v>39.9874</v>
+        <v>40.0562</v>
       </c>
       <c r="G55" t="n">
-        <v>36.1135</v>
+        <v>36.1777</v>
       </c>
       <c r="H55" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I55" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>30 sep</t>
+          <t>1 okt</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>184.5</v>
+        <v>184.68</v>
       </c>
       <c r="M55" t="n">
-        <v>186.2</v>
+        <v>190.26</v>
       </c>
       <c r="N55" t="n">
-        <v>181.06</v>
+        <v>181.34</v>
       </c>
       <c r="O55" t="n">
-        <v>185.66</v>
+        <v>186.74</v>
       </c>
       <c r="P55" t="n">
-        <v>177.8012</v>
+        <v>178.9696</v>
       </c>
       <c r="Q55" t="n">
-        <v>164.6377</v>
+        <v>164.5407</v>
       </c>
       <c r="R55" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S55" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>30 sep</t>
+          <t>1 okt</t>
         </is>
       </c>
       <c r="V55" t="n">
-        <v>511.61</v>
+        <v>519.88</v>
       </c>
       <c r="W55" t="n">
-        <v>519.83</v>
+        <v>522.85</v>
       </c>
       <c r="X55" t="n">
-        <v>510.31</v>
+        <v>512.17</v>
       </c>
       <c r="Y55" t="n">
-        <v>512.9</v>
+        <v>512.8</v>
       </c>
       <c r="Z55" t="n">
-        <v>482.1933</v>
+        <v>484.6572</v>
       </c>
       <c r="AA55" t="n">
-        <v>431.0408</v>
+        <v>431.2272</v>
       </c>
       <c r="AB55" t="n">
         <v>535.3375423278808</v>
@@ -8101,84 +8123,84 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1 okt</t>
+          <t>2 okt</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>41.625</v>
+        <v>42.11</v>
       </c>
       <c r="C56" t="n">
-        <v>42.36</v>
+        <v>42.745</v>
       </c>
       <c r="D56" t="n">
-        <v>41.165</v>
+        <v>41.985</v>
       </c>
       <c r="E56" t="n">
-        <v>42.24</v>
+        <v>42.4</v>
       </c>
       <c r="F56" t="n">
-        <v>40.0562</v>
+        <v>40.1364</v>
       </c>
       <c r="G56" t="n">
-        <v>36.1777</v>
+        <v>36.2422</v>
       </c>
       <c r="H56" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I56" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>1 okt</t>
+          <t>2 okt</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>184.68</v>
+        <v>187.82</v>
       </c>
       <c r="M56" t="n">
-        <v>190.26</v>
+        <v>188.74</v>
       </c>
       <c r="N56" t="n">
-        <v>181.34</v>
+        <v>183.92</v>
       </c>
       <c r="O56" t="n">
-        <v>186.74</v>
+        <v>183.92</v>
       </c>
       <c r="P56" t="n">
-        <v>178.9696</v>
+        <v>179.844</v>
       </c>
       <c r="Q56" t="n">
-        <v>164.5407</v>
+        <v>164.4442</v>
       </c>
       <c r="R56" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S56" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>1 okt</t>
+          <t>2 okt</t>
         </is>
       </c>
       <c r="V56" t="n">
-        <v>519.88</v>
+        <v>519.39</v>
       </c>
       <c r="W56" t="n">
-        <v>522.85</v>
+        <v>522.5</v>
       </c>
       <c r="X56" t="n">
-        <v>512.17</v>
+        <v>513.66</v>
       </c>
       <c r="Y56" t="n">
-        <v>512.8</v>
+        <v>517.53</v>
       </c>
       <c r="Z56" t="n">
-        <v>484.6572</v>
+        <v>487.3905</v>
       </c>
       <c r="AA56" t="n">
-        <v>431.2272</v>
+        <v>431.4557</v>
       </c>
       <c r="AB56" t="n">
         <v>535.3375423278808</v>
@@ -8190,84 +8212,84 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2 okt</t>
+          <t>5 okt</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>42.11</v>
+        <v>42.645</v>
       </c>
       <c r="C57" t="n">
-        <v>42.745</v>
+        <v>43.11</v>
       </c>
       <c r="D57" t="n">
-        <v>41.985</v>
+        <v>42.35</v>
       </c>
       <c r="E57" t="n">
-        <v>42.4</v>
+        <v>42.865</v>
       </c>
       <c r="F57" t="n">
-        <v>40.1364</v>
+        <v>40.2347</v>
       </c>
       <c r="G57" t="n">
-        <v>36.2422</v>
+        <v>36.3069</v>
       </c>
       <c r="H57" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I57" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2 okt</t>
+          <t>5 okt</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>187.82</v>
+        <v>185.06</v>
       </c>
       <c r="M57" t="n">
-        <v>188.74</v>
+        <v>188.5</v>
       </c>
       <c r="N57" t="n">
-        <v>183.92</v>
+        <v>184.66</v>
       </c>
       <c r="O57" t="n">
-        <v>183.92</v>
+        <v>185.04</v>
       </c>
       <c r="P57" t="n">
-        <v>179.844</v>
+        <v>180.5192</v>
       </c>
       <c r="Q57" t="n">
-        <v>164.4442</v>
+        <v>164.3515</v>
       </c>
       <c r="R57" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S57" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>2 okt</t>
+          <t>5 okt</t>
         </is>
       </c>
       <c r="V57" t="n">
-        <v>519.39</v>
+        <v>521.62</v>
       </c>
       <c r="W57" t="n">
-        <v>522.5</v>
+        <v>532.35</v>
       </c>
       <c r="X57" t="n">
-        <v>513.66</v>
+        <v>521.47</v>
       </c>
       <c r="Y57" t="n">
-        <v>517.53</v>
+        <v>525.1799999999999</v>
       </c>
       <c r="Z57" t="n">
-        <v>487.3905</v>
+        <v>490.2745</v>
       </c>
       <c r="AA57" t="n">
-        <v>431.4557</v>
+        <v>431.7147</v>
       </c>
       <c r="AB57" t="n">
         <v>535.3375423278808</v>
@@ -8279,84 +8301,84 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>5 okt</t>
+          <t>6 okt</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>42.645</v>
+        <v>42.86</v>
       </c>
       <c r="C58" t="n">
-        <v>43.11</v>
+        <v>43.285</v>
       </c>
       <c r="D58" t="n">
-        <v>42.35</v>
+        <v>42.43</v>
       </c>
       <c r="E58" t="n">
-        <v>42.865</v>
+        <v>43.185</v>
       </c>
       <c r="F58" t="n">
-        <v>40.2347</v>
+        <v>40.349</v>
       </c>
       <c r="G58" t="n">
-        <v>36.3069</v>
+        <v>36.3726</v>
       </c>
       <c r="H58" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I58" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>5 okt</t>
+          <t>6 okt</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>185.06</v>
+        <v>186.56</v>
       </c>
       <c r="M58" t="n">
-        <v>188.5</v>
+        <v>190.22</v>
       </c>
       <c r="N58" t="n">
-        <v>184.66</v>
+        <v>186.06</v>
       </c>
       <c r="O58" t="n">
-        <v>185.04</v>
+        <v>188.6</v>
       </c>
       <c r="P58" t="n">
-        <v>180.5192</v>
+        <v>181.1064</v>
       </c>
       <c r="Q58" t="n">
-        <v>164.3515</v>
+        <v>164.2647</v>
       </c>
       <c r="R58" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S58" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>5 okt</t>
+          <t>6 okt</t>
         </is>
       </c>
       <c r="V58" t="n">
-        <v>521.62</v>
+        <v>531.6799999999999</v>
       </c>
       <c r="W58" t="n">
-        <v>532.35</v>
+        <v>535.6900000000001</v>
       </c>
       <c r="X58" t="n">
-        <v>521.47</v>
+        <v>528.78</v>
       </c>
       <c r="Y58" t="n">
-        <v>525.1799999999999</v>
+        <v>529.3</v>
       </c>
       <c r="Z58" t="n">
-        <v>490.2745</v>
+        <v>493.0931</v>
       </c>
       <c r="AA58" t="n">
-        <v>431.7147</v>
+        <v>431.9956</v>
       </c>
       <c r="AB58" t="n">
         <v>535.3375423278808</v>
@@ -8368,84 +8390,84 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>6 okt</t>
+          <t>7 okt</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>42.86</v>
+        <v>43.37</v>
       </c>
       <c r="C59" t="n">
-        <v>43.285</v>
+        <v>43.835</v>
       </c>
       <c r="D59" t="n">
-        <v>42.43</v>
+        <v>43.145</v>
       </c>
       <c r="E59" t="n">
-        <v>43.185</v>
+        <v>43.25</v>
       </c>
       <c r="F59" t="n">
-        <v>40.349</v>
+        <v>40.4451</v>
       </c>
       <c r="G59" t="n">
-        <v>36.3726</v>
+        <v>36.4388</v>
       </c>
       <c r="H59" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I59" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>6 okt</t>
+          <t>7 okt</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>186.56</v>
+        <v>187</v>
       </c>
       <c r="M59" t="n">
-        <v>190.22</v>
+        <v>188.72</v>
       </c>
       <c r="N59" t="n">
-        <v>186.06</v>
+        <v>186.04</v>
       </c>
       <c r="O59" t="n">
-        <v>188.6</v>
+        <v>187.62</v>
       </c>
       <c r="P59" t="n">
-        <v>181.1064</v>
+        <v>181.618</v>
       </c>
       <c r="Q59" t="n">
-        <v>164.2647</v>
+        <v>164.1762</v>
       </c>
       <c r="R59" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S59" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>6 okt</t>
+          <t>7 okt</t>
         </is>
       </c>
       <c r="V59" t="n">
-        <v>531.6799999999999</v>
+        <v>530.73</v>
       </c>
       <c r="W59" t="n">
-        <v>535.6900000000001</v>
+        <v>531.73</v>
       </c>
       <c r="X59" t="n">
-        <v>528.78</v>
+        <v>524.6900000000001</v>
       </c>
       <c r="Y59" t="n">
-        <v>529.3</v>
+        <v>529.76</v>
       </c>
       <c r="Z59" t="n">
-        <v>493.0931</v>
+        <v>495.8361</v>
       </c>
       <c r="AA59" t="n">
-        <v>431.9956</v>
+        <v>432.2398</v>
       </c>
       <c r="AB59" t="n">
         <v>535.3375423278808</v>
@@ -8457,84 +8479,84 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>7 okt</t>
+          <t>8 okt</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>43.37</v>
+        <v>43.555</v>
       </c>
       <c r="C60" t="n">
-        <v>43.835</v>
+        <v>44.815</v>
       </c>
       <c r="D60" t="n">
-        <v>43.145</v>
+        <v>43.5425</v>
       </c>
       <c r="E60" t="n">
-        <v>43.25</v>
+        <v>44.75</v>
       </c>
       <c r="F60" t="n">
-        <v>40.4451</v>
+        <v>40.5699</v>
       </c>
       <c r="G60" t="n">
-        <v>36.4388</v>
+        <v>36.5123</v>
       </c>
       <c r="H60" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I60" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>7 okt</t>
+          <t>8 okt</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>187</v>
+        <v>187.04</v>
       </c>
       <c r="M60" t="n">
-        <v>188.72</v>
+        <v>189.82</v>
       </c>
       <c r="N60" t="n">
-        <v>186.04</v>
+        <v>183.76</v>
       </c>
       <c r="O60" t="n">
-        <v>187.62</v>
+        <v>184.62</v>
       </c>
       <c r="P60" t="n">
-        <v>181.618</v>
+        <v>182.192</v>
       </c>
       <c r="Q60" t="n">
-        <v>164.1762</v>
+        <v>164.074</v>
       </c>
       <c r="R60" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S60" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>7 okt</t>
+          <t>8 okt</t>
         </is>
       </c>
       <c r="V60" t="n">
-        <v>530.73</v>
+        <v>529.8099999999999</v>
       </c>
       <c r="W60" t="n">
-        <v>531.73</v>
+        <v>533.51</v>
       </c>
       <c r="X60" t="n">
-        <v>524.6900000000001</v>
+        <v>518.79</v>
       </c>
       <c r="Y60" t="n">
-        <v>529.76</v>
+        <v>522.61</v>
       </c>
       <c r="Z60" t="n">
-        <v>495.8361</v>
+        <v>498.4921</v>
       </c>
       <c r="AA60" t="n">
-        <v>432.2398</v>
+        <v>432.4385</v>
       </c>
       <c r="AB60" t="n">
         <v>535.3375423278808</v>
@@ -8546,84 +8568,84 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>8 okt</t>
+          <t>9 okt</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>43.555</v>
+        <v>44.42</v>
       </c>
       <c r="C61" t="n">
-        <v>44.815</v>
+        <v>45.155</v>
       </c>
       <c r="D61" t="n">
-        <v>43.5425</v>
+        <v>43.94</v>
       </c>
       <c r="E61" t="n">
-        <v>44.75</v>
+        <v>45.035</v>
       </c>
       <c r="F61" t="n">
-        <v>40.5699</v>
+        <v>40.6842</v>
       </c>
       <c r="G61" t="n">
-        <v>36.5123</v>
+        <v>36.5866</v>
       </c>
       <c r="H61" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I61" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>8 okt</t>
+          <t>9 okt</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>187.04</v>
+        <v>188.98</v>
       </c>
       <c r="M61" t="n">
-        <v>189.82</v>
+        <v>192.58</v>
       </c>
       <c r="N61" t="n">
-        <v>183.76</v>
+        <v>188.86</v>
       </c>
       <c r="O61" t="n">
-        <v>184.62</v>
+        <v>191.46</v>
       </c>
       <c r="P61" t="n">
-        <v>182.192</v>
+        <v>182.8676</v>
       </c>
       <c r="Q61" t="n">
-        <v>164.074</v>
+        <v>164.0101</v>
       </c>
       <c r="R61" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S61" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>8 okt</t>
+          <t>9 okt</t>
         </is>
       </c>
       <c r="V61" t="n">
-        <v>529.8099999999999</v>
+        <v>528.24</v>
       </c>
       <c r="W61" t="n">
-        <v>533.51</v>
+        <v>537.22</v>
       </c>
       <c r="X61" t="n">
-        <v>518.79</v>
+        <v>526.24</v>
       </c>
       <c r="Y61" t="n">
-        <v>522.61</v>
+        <v>535.0700000000001</v>
       </c>
       <c r="Z61" t="n">
-        <v>498.4921</v>
+        <v>500.1885</v>
       </c>
       <c r="AA61" t="n">
-        <v>432.4385</v>
+        <v>432.7046</v>
       </c>
       <c r="AB61" t="n">
         <v>535.3375423278808</v>
@@ -8635,84 +8657,84 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>9 okt</t>
+          <t>12 okt</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>44.42</v>
+        <v>44.725</v>
       </c>
       <c r="C62" t="n">
-        <v>45.155</v>
+        <v>45.81</v>
       </c>
       <c r="D62" t="n">
-        <v>43.94</v>
+        <v>44.695</v>
       </c>
       <c r="E62" t="n">
-        <v>45.035</v>
+        <v>45.56</v>
       </c>
       <c r="F62" t="n">
-        <v>40.6842</v>
+        <v>40.8072</v>
       </c>
       <c r="G62" t="n">
-        <v>36.5866</v>
+        <v>36.6625</v>
       </c>
       <c r="H62" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I62" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>9 okt</t>
+          <t>12 okt</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>188.98</v>
+        <v>190.58</v>
       </c>
       <c r="M62" t="n">
-        <v>192.58</v>
+        <v>197.88</v>
       </c>
       <c r="N62" t="n">
-        <v>188.86</v>
+        <v>189.78</v>
       </c>
       <c r="O62" t="n">
-        <v>191.46</v>
+        <v>194.46</v>
       </c>
       <c r="P62" t="n">
-        <v>182.8676</v>
+        <v>183.464</v>
       </c>
       <c r="Q62" t="n">
-        <v>164.0101</v>
+        <v>163.9576</v>
       </c>
       <c r="R62" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S62" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>9 okt</t>
+          <t>12 okt</t>
         </is>
       </c>
       <c r="V62" t="n">
-        <v>528.24</v>
+        <v>537.53</v>
       </c>
       <c r="W62" t="n">
-        <v>537.22</v>
+        <v>542.74</v>
       </c>
       <c r="X62" t="n">
-        <v>526.24</v>
+        <v>535.7</v>
       </c>
       <c r="Y62" t="n">
-        <v>535.0700000000001</v>
+        <v>541.15</v>
       </c>
       <c r="Z62" t="n">
-        <v>500.1885</v>
+        <v>501.7346</v>
       </c>
       <c r="AA62" t="n">
-        <v>432.7046</v>
+        <v>432.9914</v>
       </c>
       <c r="AB62" t="n">
         <v>535.3375423278808</v>
@@ -8724,84 +8746,84 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>12 okt</t>
+          <t>13 okt</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>44.725</v>
+        <v>45.69</v>
       </c>
       <c r="C63" t="n">
-        <v>45.81</v>
+        <v>45.97</v>
       </c>
       <c r="D63" t="n">
-        <v>44.695</v>
+        <v>45.35</v>
       </c>
       <c r="E63" t="n">
-        <v>45.56</v>
+        <v>45.95</v>
       </c>
       <c r="F63" t="n">
-        <v>40.8072</v>
+        <v>40.9565</v>
       </c>
       <c r="G63" t="n">
-        <v>36.6625</v>
+        <v>36.7398</v>
       </c>
       <c r="H63" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I63" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>12 okt</t>
+          <t>13 okt</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>190.58</v>
+        <v>196</v>
       </c>
       <c r="M63" t="n">
-        <v>197.88</v>
+        <v>198.18</v>
       </c>
       <c r="N63" t="n">
-        <v>189.78</v>
+        <v>194.02</v>
       </c>
       <c r="O63" t="n">
-        <v>194.46</v>
+        <v>197.28</v>
       </c>
       <c r="P63" t="n">
-        <v>183.464</v>
+        <v>184.062</v>
       </c>
       <c r="Q63" t="n">
-        <v>163.9576</v>
+        <v>163.9196</v>
       </c>
       <c r="R63" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S63" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>12 okt</t>
+          <t>13 okt</t>
         </is>
       </c>
       <c r="V63" t="n">
-        <v>537.53</v>
+        <v>544.64</v>
       </c>
       <c r="W63" t="n">
-        <v>542.74</v>
+        <v>551.15</v>
       </c>
       <c r="X63" t="n">
-        <v>535.7</v>
+        <v>543.0599999999999</v>
       </c>
       <c r="Y63" t="n">
-        <v>541.15</v>
+        <v>543.45</v>
       </c>
       <c r="Z63" t="n">
-        <v>501.7346</v>
+        <v>502.8689</v>
       </c>
       <c r="AA63" t="n">
-        <v>432.9914</v>
+        <v>433.2839</v>
       </c>
       <c r="AB63" t="n">
         <v>535.3375423278808</v>
@@ -8813,84 +8835,84 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>13 okt</t>
+          <t>14 okt</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>45.69</v>
+        <v>45.95</v>
       </c>
       <c r="C64" t="n">
-        <v>45.97</v>
+        <v>46.675</v>
       </c>
       <c r="D64" t="n">
-        <v>45.35</v>
+        <v>45.91</v>
       </c>
       <c r="E64" t="n">
-        <v>45.95</v>
+        <v>46.455</v>
       </c>
       <c r="F64" t="n">
-        <v>40.9565</v>
+        <v>41.125</v>
       </c>
       <c r="G64" t="n">
-        <v>36.7398</v>
+        <v>36.8183</v>
       </c>
       <c r="H64" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I64" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>13 okt</t>
+          <t>14 okt</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>196</v>
+        <v>196.6</v>
       </c>
       <c r="M64" t="n">
-        <v>198.18</v>
+        <v>199.36</v>
       </c>
       <c r="N64" t="n">
-        <v>194.02</v>
+        <v>195.26</v>
       </c>
       <c r="O64" t="n">
-        <v>197.28</v>
+        <v>196.94</v>
       </c>
       <c r="P64" t="n">
-        <v>184.062</v>
+        <v>184.6156</v>
       </c>
       <c r="Q64" t="n">
-        <v>163.9196</v>
+        <v>163.9114</v>
       </c>
       <c r="R64" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S64" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>13 okt</t>
+          <t>14 okt</t>
         </is>
       </c>
       <c r="V64" t="n">
-        <v>544.64</v>
+        <v>545.27</v>
       </c>
       <c r="W64" t="n">
-        <v>551.15</v>
+        <v>545.75</v>
       </c>
       <c r="X64" t="n">
-        <v>543.0599999999999</v>
+        <v>532.54</v>
       </c>
       <c r="Y64" t="n">
-        <v>543.45</v>
+        <v>533.6900000000001</v>
       </c>
       <c r="Z64" t="n">
-        <v>502.8689</v>
+        <v>503.705</v>
       </c>
       <c r="AA64" t="n">
-        <v>433.2839</v>
+        <v>433.5292</v>
       </c>
       <c r="AB64" t="n">
         <v>535.3375423278808</v>
@@ -8902,84 +8924,84 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>14 okt</t>
+          <t>15 okt</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>45.95</v>
+        <v>46.295</v>
       </c>
       <c r="C65" t="n">
-        <v>46.675</v>
+        <v>46.735</v>
       </c>
       <c r="D65" t="n">
-        <v>45.91</v>
+        <v>46.125</v>
       </c>
       <c r="E65" t="n">
-        <v>46.455</v>
+        <v>46.375</v>
       </c>
       <c r="F65" t="n">
-        <v>41.125</v>
+        <v>41.2847</v>
       </c>
       <c r="G65" t="n">
-        <v>36.8183</v>
+        <v>36.8966</v>
       </c>
       <c r="H65" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I65" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>14 okt</t>
+          <t>15 okt</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>196.6</v>
+        <v>199.48</v>
       </c>
       <c r="M65" t="n">
-        <v>199.36</v>
+        <v>203</v>
       </c>
       <c r="N65" t="n">
-        <v>195.26</v>
+        <v>196.98</v>
       </c>
       <c r="O65" t="n">
-        <v>196.94</v>
+        <v>201.25</v>
       </c>
       <c r="P65" t="n">
-        <v>184.6156</v>
+        <v>185.221</v>
       </c>
       <c r="Q65" t="n">
-        <v>163.9114</v>
+        <v>163.9038</v>
       </c>
       <c r="R65" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S65" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>14 okt</t>
+          <t>15 okt</t>
         </is>
       </c>
       <c r="V65" t="n">
-        <v>545.27</v>
+        <v>533.3200000000001</v>
       </c>
       <c r="W65" t="n">
-        <v>545.75</v>
+        <v>541.13</v>
       </c>
       <c r="X65" t="n">
-        <v>532.54</v>
+        <v>531.22</v>
       </c>
       <c r="Y65" t="n">
-        <v>533.6900000000001</v>
+        <v>539.4400000000001</v>
       </c>
       <c r="Z65" t="n">
-        <v>503.705</v>
+        <v>504.7629</v>
       </c>
       <c r="AA65" t="n">
-        <v>433.5292</v>
+        <v>433.8063</v>
       </c>
       <c r="AB65" t="n">
         <v>535.3375423278808</v>
@@ -8991,84 +9013,84 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>15 okt</t>
+          <t>16 okt</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>46.295</v>
+        <v>46.14</v>
       </c>
       <c r="C66" t="n">
-        <v>46.735</v>
+        <v>47.025</v>
       </c>
       <c r="D66" t="n">
-        <v>46.125</v>
+        <v>46.075</v>
       </c>
       <c r="E66" t="n">
-        <v>46.47</v>
+        <v>46.89</v>
       </c>
       <c r="F66" t="n">
-        <v>41.2866</v>
+        <v>41.4624</v>
       </c>
       <c r="G66" t="n">
-        <v>36.8971</v>
+        <v>36.977</v>
       </c>
       <c r="H66" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I66" t="n">
-        <v>43.77107320513044</v>
+        <v>44.18785640171596</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>15 okt</t>
+          <t>16 okt</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>199.48</v>
+        <v>200.6</v>
       </c>
       <c r="M66" t="n">
-        <v>203</v>
+        <v>204.2</v>
       </c>
       <c r="N66" t="n">
-        <v>196.98</v>
+        <v>198.68</v>
       </c>
       <c r="O66" t="n">
-        <v>201.7</v>
+        <v>199.02</v>
       </c>
       <c r="P66" t="n">
-        <v>185.23</v>
+        <v>185.6422</v>
       </c>
       <c r="Q66" t="n">
-        <v>163.9061</v>
+        <v>163.9056</v>
       </c>
       <c r="R66" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S66" t="n">
-        <v>184.6214196341379</v>
+        <v>185.1271307809012</v>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>15 okt</t>
+          <t>16 okt</t>
         </is>
       </c>
       <c r="V66" t="n">
-        <v>533.655</v>
+        <v>541.0599999999999</v>
       </c>
       <c r="W66" t="n">
-        <v>541.1331</v>
+        <v>543.8099999999999</v>
       </c>
       <c r="X66" t="n">
-        <v>531.22</v>
+        <v>524.4299999999999</v>
       </c>
       <c r="Y66" t="n">
-        <v>539.33</v>
+        <v>528.95</v>
       </c>
       <c r="Z66" t="n">
-        <v>504.7607</v>
+        <v>505.3635</v>
       </c>
       <c r="AA66" t="n">
-        <v>433.8057</v>
+        <v>434.029</v>
       </c>
       <c r="AB66" t="n">
         <v>535.3375423278808</v>

--- a/rapporten/trend-agent.xlsx
+++ b/rapporten/trend-agent.xlsx
@@ -608,7 +608,7 @@
         <scaling>
           <orientation val="minMax"/>
           <max val="50"/>
-          <min val="32.5"/>
+          <min val="30"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -641,7 +641,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
-        <majorUnit val="2.5"/>
+        <majorUnit val="5"/>
       </valAx>
     </plotArea>
     <plotVisOnly val="1"/>
@@ -1944,7 +1944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2102,6 +2102,28 @@
       </c>
       <c r="E7" s="3">
         <f>B7/$B$2-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>10035.41</v>
+      </c>
+      <c r="C8" s="2">
+        <f>B8-B7</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>B8/B7-1</f>
+        <v/>
+      </c>
+      <c r="E8" s="3">
+        <f>B8/$B$2-1</f>
         <v/>
       </c>
     </row>
@@ -2245,38 +2267,38 @@
     <row r="6" ht="22" customHeight="1">
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Shell (SHELL.AS)  ·  46,89 EUR</t>
+          <t>Shell (SHELL.AS)  ·  46,87 EUR</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>SAP (SAP.DE)  ·  199,02 EUR</t>
+          <t>SAP (SAP.DE)  ·  200,05 EUR</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>Gestegen: 24,9% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +4,1% (winst). De bot verkoopt als de koers onder 44,19 zakt (-5,8%).</t>
+          <t>Gestegen: 23,9% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +4,0% (winst). De bot verkoopt als de koers onder 44,25 zakt (-5,6%).</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>Gestegen: 43,9% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +3,9% (winst). De bot verkoopt als de koers onder 185,13 zakt (-7,0%).</t>
+          <t>Gestegen: 46,6% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +4,4% (winst). De bot verkoopt als de koers onder 185,25 zakt (-7,4%).</t>
         </is>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Microsoft (MSFT)  ·  528,95 USD</t>
+          <t>Microsoft (MSFT)  ·  533,61 USD</t>
         </is>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Gestegen: 34,6% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: -1,2% (verlies). De bot verkoopt als de koers onder 509,90 zakt (-3,6%).</t>
+          <t>Gestegen: 32,9% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: -0,3% (verlies). De bot verkoopt als de koers onder 509,90 zakt (-4,4%).</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2399,7 @@
         <v>45.06</v>
       </c>
       <c r="F2" t="n">
-        <v>44.19</v>
+        <v>44.25</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2416,7 +2438,7 @@
         <v>191.56</v>
       </c>
       <c r="F3" t="n">
-        <v>185.13</v>
+        <v>185.25</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -2755,19 +2777,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.168</v>
+        <v>0.162</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.2395676373843243</v>
+        <v>0.2246445101732573</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1282482637207707</v>
+        <v>0.1343338554093498</v>
       </c>
       <c r="H2" t="n">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>46.89</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="3">
@@ -2790,19 +2812,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.118</v>
+        <v>0.139</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.458877048407452</v>
+        <v>0.5150712906978585</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.05861704400245182</v>
+        <v>0.0924530820554903</v>
       </c>
       <c r="H3" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="I3" t="n">
-        <v>199.02</v>
+        <v>200.05</v>
       </c>
     </row>
     <row r="4">
@@ -2825,19 +2847,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.117</v>
+        <v>0.136</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.3816995948695561</v>
+        <v>0.4224140684231807</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.1660958773618408</v>
+        <v>0.2338614136676298</v>
       </c>
       <c r="H4" t="n">
         <v>0.85</v>
       </c>
       <c r="I4" t="n">
-        <v>81.72</v>
+        <v>84.09999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -2846,12 +2868,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>XLE</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Energie-ETF</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2860,19 +2882,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.112</v>
+        <v>0.102</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.1845972630411206</v>
+        <v>0.1348680903497113</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.06444725185155553</v>
+        <v>0.09440926500027724</v>
       </c>
       <c r="H5" t="n">
-        <v>1.11</v>
+        <v>0.91</v>
       </c>
       <c r="I5" t="n">
-        <v>68.23</v>
+        <v>403.06</v>
       </c>
     </row>
     <row r="6">
@@ -2881,12 +2903,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>XLE</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>Energie-ETF</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2895,19 +2917,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.109</v>
+        <v>0.101</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.214201341584364</v>
+        <v>0.1661213443947605</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.09622092879266231</v>
+        <v>0.0607696881620563</v>
       </c>
       <c r="H6" t="n">
-        <v>0.87</v>
+        <v>1.1</v>
       </c>
       <c r="I6" t="n">
-        <v>178.98</v>
+        <v>67.81999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -2916,12 +2938,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2930,19 +2952,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.09</v>
+        <v>0.097</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.118584115369734</v>
+        <v>0.3440968709158025</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.08825992631827484</v>
+        <v>0.08066342636544954</v>
       </c>
       <c r="H7" t="n">
-        <v>0.93</v>
+        <v>0.82</v>
       </c>
       <c r="I7" t="n">
-        <v>402.58</v>
+        <v>533.61</v>
       </c>
     </row>
     <row r="8">
@@ -2951,12 +2973,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>ExxonMobil</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2965,19 +2987,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.097</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.3173227071769877</v>
+        <v>0.1828122320570467</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.06268209383632595</v>
+        <v>0.090192005659393</v>
       </c>
       <c r="H8" t="n">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
       <c r="I8" t="n">
-        <v>528.95</v>
+        <v>178.29</v>
       </c>
     </row>
     <row r="9">
@@ -2986,33 +3008,33 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TTE.PA</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TotalEnergies</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.1178118803253723</v>
+        <v>0.4282404380072085</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.02207572811713332</v>
+        <v>0.01908208044663007</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>80.45</v>
+        <v>242.46</v>
       </c>
     </row>
     <row r="10">
@@ -3021,33 +3043,33 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>OR.PA</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>L'Oreal</t>
+          <t>Palantir</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.054</v>
+        <v>0.065</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.07287130324360569</v>
+        <v>0.4636287345557388</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.06906077237170871</v>
+        <v>0.09302518550586836</v>
       </c>
       <c r="H10" t="n">
-        <v>0.97</v>
+        <v>0.71</v>
       </c>
       <c r="I10" t="n">
-        <v>406.35</v>
+        <v>194.16</v>
       </c>
     </row>
     <row r="11">
@@ -3056,33 +3078,33 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>TTE.PA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Palantir</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.051</v>
+        <v>0.052</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.3795327427459936</v>
+        <v>0.09445359121940089</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.0555492111949154</v>
+        <v>0.02504985976212115</v>
       </c>
       <c r="H11" t="n">
-        <v>0.72</v>
+        <v>1.02</v>
       </c>
       <c r="I11" t="n">
-        <v>186.03</v>
+        <v>80.37</v>
       </c>
     </row>
   </sheetData>
@@ -3353,75 +3375,75 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20 jul</t>
+          <t>21 jul</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>38.0653</v>
+        <v>37.5703</v>
       </c>
       <c r="C2" t="n">
-        <v>38.1742</v>
+        <v>37.8277</v>
       </c>
       <c r="D2" t="n">
-        <v>37.1496</v>
+        <v>37.4169</v>
       </c>
       <c r="E2" t="n">
-        <v>37.5307</v>
+        <v>37.8277</v>
       </c>
       <c r="F2" t="n">
-        <v>35.7021</v>
+        <v>35.7452</v>
       </c>
       <c r="H2" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I2" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>20 jul</t>
+          <t>21 jul</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>138</v>
+        <v>137.74</v>
       </c>
       <c r="M2" t="n">
-        <v>140.04</v>
+        <v>137.84</v>
       </c>
       <c r="N2" t="n">
-        <v>134.98</v>
+        <v>135.34</v>
       </c>
       <c r="O2" t="n">
-        <v>138.26</v>
+        <v>136.42</v>
       </c>
       <c r="P2" t="n">
-        <v>144.528</v>
+        <v>144.4084</v>
       </c>
       <c r="R2" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S2" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>17 jul</t>
+          <t>20 jul</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>394.118</v>
+        <v>390.6746</v>
       </c>
       <c r="W2" t="n">
-        <v>397.6414</v>
+        <v>402.4224</v>
       </c>
       <c r="X2" t="n">
-        <v>388.6583</v>
+        <v>388.9179</v>
       </c>
       <c r="Y2" t="n">
-        <v>393.08</v>
+        <v>401.5341</v>
       </c>
       <c r="Z2" t="n">
-        <v>400.5601</v>
+        <v>400.345</v>
       </c>
       <c r="AB2" t="n">
         <v>535.3375423278808</v>
@@ -3433,75 +3455,75 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>21 jul</t>
+          <t>22 jul</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>37.5703</v>
+        <v>38.095</v>
       </c>
       <c r="C3" t="n">
-        <v>37.8277</v>
+        <v>38.6098</v>
       </c>
       <c r="D3" t="n">
-        <v>37.4169</v>
+        <v>37.9267</v>
       </c>
       <c r="E3" t="n">
-        <v>37.8277</v>
+        <v>38.2682</v>
       </c>
       <c r="F3" t="n">
-        <v>35.7452</v>
+        <v>35.799</v>
       </c>
       <c r="H3" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I3" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>21 jul</t>
+          <t>22 jul</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>137.74</v>
+        <v>136.02</v>
       </c>
       <c r="M3" t="n">
-        <v>137.84</v>
+        <v>136.4</v>
       </c>
       <c r="N3" t="n">
-        <v>135.34</v>
+        <v>132.04</v>
       </c>
       <c r="O3" t="n">
-        <v>136.42</v>
+        <v>132.04</v>
       </c>
       <c r="P3" t="n">
-        <v>144.4084</v>
+        <v>144.324</v>
       </c>
       <c r="R3" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S3" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>20 jul</t>
+          <t>21 jul</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>390.6746</v>
+        <v>398.0606</v>
       </c>
       <c r="W3" t="n">
-        <v>402.4224</v>
+        <v>400.7156</v>
       </c>
       <c r="X3" t="n">
-        <v>388.9179</v>
+        <v>395.5753</v>
       </c>
       <c r="Y3" t="n">
-        <v>401.5341</v>
+        <v>397.0026</v>
       </c>
       <c r="Z3" t="n">
-        <v>400.345</v>
+        <v>399.9036</v>
       </c>
       <c r="AB3" t="n">
         <v>535.3375423278808</v>
@@ -3513,75 +3535,75 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>22 jul</t>
+          <t>23 jul</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38.095</v>
+        <v>38.491</v>
       </c>
       <c r="C4" t="n">
-        <v>38.6098</v>
+        <v>39.0454</v>
       </c>
       <c r="D4" t="n">
-        <v>37.9267</v>
+        <v>38.3425</v>
       </c>
       <c r="E4" t="n">
-        <v>38.2682</v>
+        <v>38.8028</v>
       </c>
       <c r="F4" t="n">
-        <v>35.799</v>
+        <v>35.863</v>
       </c>
       <c r="H4" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I4" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>22 jul</t>
+          <t>23 jul</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>136.02</v>
+        <v>131</v>
       </c>
       <c r="M4" t="n">
-        <v>136.4</v>
+        <v>132.42</v>
       </c>
       <c r="N4" t="n">
-        <v>132.04</v>
+        <v>127.5</v>
       </c>
       <c r="O4" t="n">
-        <v>132.04</v>
+        <v>128.32</v>
       </c>
       <c r="P4" t="n">
-        <v>144.324</v>
+        <v>144.066</v>
       </c>
       <c r="R4" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S4" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>21 jul</t>
+          <t>22 jul</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>398.0606</v>
+        <v>398.8292</v>
       </c>
       <c r="W4" t="n">
-        <v>400.7156</v>
+        <v>400.2465</v>
       </c>
       <c r="X4" t="n">
-        <v>395.5753</v>
+        <v>386.2329</v>
       </c>
       <c r="Y4" t="n">
-        <v>397.0026</v>
+        <v>389.6066</v>
       </c>
       <c r="Z4" t="n">
-        <v>399.9036</v>
+        <v>399.4268</v>
       </c>
       <c r="AB4" t="n">
         <v>535.3375423278808</v>
@@ -3593,75 +3615,75 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>23 jul</t>
+          <t>24 jul</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>38.491</v>
+        <v>38.4019</v>
       </c>
       <c r="C5" t="n">
-        <v>39.0454</v>
+        <v>38.6593</v>
       </c>
       <c r="D5" t="n">
-        <v>38.3425</v>
+        <v>38.1594</v>
       </c>
       <c r="E5" t="n">
-        <v>38.8028</v>
+        <v>38.3871</v>
       </c>
       <c r="F5" t="n">
-        <v>35.863</v>
+        <v>35.9135</v>
       </c>
       <c r="H5" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I5" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>23 jul</t>
+          <t>24 jul</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>131</v>
+        <v>130.88</v>
       </c>
       <c r="M5" t="n">
-        <v>132.42</v>
+        <v>141.32</v>
       </c>
       <c r="N5" t="n">
-        <v>127.5</v>
+        <v>130.86</v>
       </c>
       <c r="O5" t="n">
-        <v>128.32</v>
+        <v>140.2</v>
       </c>
       <c r="P5" t="n">
-        <v>144.066</v>
+        <v>143.9888</v>
       </c>
       <c r="R5" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S5" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22 jul</t>
+          <t>23 jul</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>398.8292</v>
+        <v>389.2373</v>
       </c>
       <c r="W5" t="n">
-        <v>400.2465</v>
+        <v>391.0439</v>
       </c>
       <c r="X5" t="n">
-        <v>386.2329</v>
+        <v>376.6809</v>
       </c>
       <c r="Y5" t="n">
-        <v>389.6066</v>
+        <v>380.863</v>
       </c>
       <c r="Z5" t="n">
-        <v>399.4268</v>
+        <v>398.8242</v>
       </c>
       <c r="AB5" t="n">
         <v>535.3375423278808</v>
@@ -3673,84 +3695,84 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>24 jul</t>
+          <t>27 jul</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>38.4019</v>
+        <v>37.5802</v>
       </c>
       <c r="C6" t="n">
-        <v>38.6593</v>
+        <v>38.1099</v>
       </c>
       <c r="D6" t="n">
-        <v>38.1594</v>
+        <v>37.4317</v>
       </c>
       <c r="E6" t="n">
-        <v>38.3871</v>
+        <v>37.9515</v>
       </c>
       <c r="F6" t="n">
-        <v>35.9135</v>
+        <v>35.931</v>
       </c>
       <c r="G6" t="n">
-        <v>33.8757</v>
+        <v>33.9167</v>
       </c>
       <c r="H6" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I6" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>24 jul</t>
+          <t>27 jul</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>130.88</v>
+        <v>142.38</v>
       </c>
       <c r="M6" t="n">
-        <v>141.32</v>
+        <v>151.56</v>
       </c>
       <c r="N6" t="n">
-        <v>130.86</v>
+        <v>142</v>
       </c>
       <c r="O6" t="n">
-        <v>140.2</v>
+        <v>151.28</v>
       </c>
       <c r="P6" t="n">
-        <v>143.9888</v>
+        <v>144.0572</v>
       </c>
       <c r="Q6" t="n">
-        <v>173.4491</v>
+        <v>173.0393</v>
       </c>
       <c r="R6" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S6" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>23 jul</t>
+          <t>24 jul</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>389.2373</v>
+        <v>386.3227</v>
       </c>
       <c r="W6" t="n">
-        <v>391.0439</v>
+        <v>388.299</v>
       </c>
       <c r="X6" t="n">
-        <v>376.6809</v>
+        <v>379.9348</v>
       </c>
       <c r="Y6" t="n">
-        <v>380.863</v>
+        <v>380.9828</v>
       </c>
       <c r="Z6" t="n">
-        <v>398.8242</v>
+        <v>398.3214</v>
       </c>
       <c r="AA6" t="n">
-        <v>434.611</v>
+        <v>433.8946</v>
       </c>
       <c r="AB6" t="n">
         <v>535.3375423278808</v>
@@ -3762,84 +3784,84 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>27 jul</t>
+          <t>28 jul</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>37.5802</v>
+        <v>37.7139</v>
       </c>
       <c r="C7" t="n">
-        <v>38.1099</v>
+        <v>38.0109</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4317</v>
+        <v>37.4713</v>
       </c>
       <c r="E7" t="n">
-        <v>37.9515</v>
+        <v>37.4713</v>
       </c>
       <c r="F7" t="n">
-        <v>35.931</v>
+        <v>35.9372</v>
       </c>
       <c r="G7" t="n">
-        <v>33.9167</v>
+        <v>33.9548</v>
       </c>
       <c r="H7" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I7" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>27 jul</t>
+          <t>28 jul</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>142.38</v>
+        <v>152.2</v>
       </c>
       <c r="M7" t="n">
-        <v>151.56</v>
+        <v>159.76</v>
       </c>
       <c r="N7" t="n">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="O7" t="n">
-        <v>151.28</v>
+        <v>159.24</v>
       </c>
       <c r="P7" t="n">
-        <v>144.0572</v>
+        <v>144.1076</v>
       </c>
       <c r="Q7" t="n">
-        <v>173.0393</v>
+        <v>172.6663</v>
       </c>
       <c r="R7" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S7" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>24 jul</t>
+          <t>27 jul</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>386.3227</v>
+        <v>389.347</v>
       </c>
       <c r="W7" t="n">
-        <v>388.299</v>
+        <v>393.4593</v>
       </c>
       <c r="X7" t="n">
-        <v>379.9348</v>
+        <v>387.261</v>
       </c>
       <c r="Y7" t="n">
-        <v>380.9828</v>
+        <v>388.3689</v>
       </c>
       <c r="Z7" t="n">
-        <v>398.3214</v>
+        <v>398.0172</v>
       </c>
       <c r="AA7" t="n">
-        <v>433.8946</v>
+        <v>433.238</v>
       </c>
       <c r="AB7" t="n">
         <v>535.3375423278808</v>
@@ -3851,84 +3873,84 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>28 jul</t>
+          <t>29 jul</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>37.7139</v>
+        <v>38.0653</v>
       </c>
       <c r="C8" t="n">
-        <v>38.0109</v>
+        <v>38.59</v>
       </c>
       <c r="D8" t="n">
-        <v>37.4713</v>
+        <v>37.7089</v>
       </c>
       <c r="E8" t="n">
-        <v>37.4713</v>
+        <v>38.4415</v>
       </c>
       <c r="F8" t="n">
-        <v>35.9372</v>
+        <v>35.9692</v>
       </c>
       <c r="G8" t="n">
-        <v>33.9548</v>
+        <v>33.9987</v>
       </c>
       <c r="H8" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I8" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>28 jul</t>
+          <t>29 jul</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>152.2</v>
+        <v>159.84</v>
       </c>
       <c r="M8" t="n">
-        <v>159.76</v>
+        <v>163.3</v>
       </c>
       <c r="N8" t="n">
-        <v>151</v>
+        <v>156.48</v>
       </c>
       <c r="O8" t="n">
-        <v>159.24</v>
+        <v>162.04</v>
       </c>
       <c r="P8" t="n">
-        <v>144.1076</v>
+        <v>144.28</v>
       </c>
       <c r="Q8" t="n">
-        <v>172.6663</v>
+        <v>172.343</v>
       </c>
       <c r="R8" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S8" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>27 jul</t>
+          <t>28 jul</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>389.347</v>
+        <v>392.4213</v>
       </c>
       <c r="W8" t="n">
-        <v>393.4593</v>
+        <v>399.5678</v>
       </c>
       <c r="X8" t="n">
-        <v>387.261</v>
+        <v>390.5647</v>
       </c>
       <c r="Y8" t="n">
-        <v>388.3689</v>
+        <v>392.6109</v>
       </c>
       <c r="Z8" t="n">
-        <v>398.0172</v>
+        <v>397.7139</v>
       </c>
       <c r="AA8" t="n">
-        <v>433.238</v>
+        <v>432.5982</v>
       </c>
       <c r="AB8" t="n">
         <v>535.3375423278808</v>
@@ -3940,84 +3962,84 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>29 jul</t>
+          <t>30 jul</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>38.0653</v>
+        <v>38.6098</v>
       </c>
       <c r="C9" t="n">
-        <v>38.59</v>
+        <v>39.1444</v>
       </c>
       <c r="D9" t="n">
-        <v>37.7089</v>
+        <v>38.3277</v>
       </c>
       <c r="E9" t="n">
-        <v>38.4415</v>
+        <v>38.5108</v>
       </c>
       <c r="F9" t="n">
-        <v>35.9692</v>
+        <v>35.9978</v>
       </c>
       <c r="G9" t="n">
-        <v>33.9987</v>
+        <v>34.0424</v>
       </c>
       <c r="H9" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I9" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>29 jul</t>
+          <t>30 jul</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>159.84</v>
+        <v>162.5</v>
       </c>
       <c r="M9" t="n">
-        <v>163.3</v>
+        <v>163.16</v>
       </c>
       <c r="N9" t="n">
-        <v>156.48</v>
+        <v>155.2</v>
       </c>
       <c r="O9" t="n">
-        <v>162.04</v>
+        <v>155.92</v>
       </c>
       <c r="P9" t="n">
-        <v>144.28</v>
+        <v>144.3804</v>
       </c>
       <c r="Q9" t="n">
-        <v>172.343</v>
+        <v>171.9849</v>
       </c>
       <c r="R9" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S9" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>28 jul</t>
+          <t>29 jul</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>392.4213</v>
+        <v>392.6608</v>
       </c>
       <c r="W9" t="n">
-        <v>399.5678</v>
+        <v>400.4961</v>
       </c>
       <c r="X9" t="n">
-        <v>390.5647</v>
+        <v>388.0095</v>
       </c>
       <c r="Y9" t="n">
-        <v>392.6109</v>
+        <v>389.8062</v>
       </c>
       <c r="Z9" t="n">
-        <v>397.7139</v>
+        <v>397.1057</v>
       </c>
       <c r="AA9" t="n">
-        <v>432.5982</v>
+        <v>431.9565</v>
       </c>
       <c r="AB9" t="n">
         <v>535.3375423278808</v>
@@ -4029,84 +4051,84 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>30 jul</t>
+          <t>31 jul</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>38.6098</v>
       </c>
       <c r="C10" t="n">
-        <v>39.1444</v>
+        <v>39.575</v>
       </c>
       <c r="D10" t="n">
-        <v>38.3277</v>
+        <v>38.4464</v>
       </c>
       <c r="E10" t="n">
-        <v>38.5108</v>
+        <v>39.3226</v>
       </c>
       <c r="F10" t="n">
-        <v>35.9978</v>
+        <v>36.0495</v>
       </c>
       <c r="G10" t="n">
-        <v>34.0424</v>
+        <v>34.0907</v>
       </c>
       <c r="H10" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I10" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>30 jul</t>
+          <t>31 jul</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>162.5</v>
+        <v>154.9</v>
       </c>
       <c r="M10" t="n">
-        <v>163.16</v>
+        <v>158.26</v>
       </c>
       <c r="N10" t="n">
-        <v>155.2</v>
+        <v>153.6</v>
       </c>
       <c r="O10" t="n">
-        <v>155.92</v>
+        <v>157.68</v>
       </c>
       <c r="P10" t="n">
-        <v>144.3804</v>
+        <v>144.4984</v>
       </c>
       <c r="Q10" t="n">
-        <v>171.9849</v>
+        <v>171.6292</v>
       </c>
       <c r="R10" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S10" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>29 jul</t>
+          <t>30 jul</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>392.6608</v>
+        <v>437.0772</v>
       </c>
       <c r="W10" t="n">
-        <v>400.4961</v>
+        <v>457.8281</v>
       </c>
       <c r="X10" t="n">
-        <v>388.0095</v>
+        <v>431.6275</v>
       </c>
       <c r="Y10" t="n">
-        <v>389.8062</v>
+        <v>450.2524</v>
       </c>
       <c r="Z10" t="n">
-        <v>397.1057</v>
+        <v>397.6741</v>
       </c>
       <c r="AA10" t="n">
-        <v>431.9565</v>
+        <v>431.6738</v>
       </c>
       <c r="AB10" t="n">
         <v>535.3375423278808</v>
@@ -4118,84 +4140,84 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>31 jul</t>
+          <t>3 aug</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>38.6098</v>
+        <v>38.3128</v>
       </c>
       <c r="C11" t="n">
-        <v>39.575</v>
+        <v>39.4067</v>
       </c>
       <c r="D11" t="n">
-        <v>38.4464</v>
+        <v>38.2138</v>
       </c>
       <c r="E11" t="n">
-        <v>39.3226</v>
+        <v>39.4067</v>
       </c>
       <c r="F11" t="n">
-        <v>36.0495</v>
+        <v>36.1112</v>
       </c>
       <c r="G11" t="n">
-        <v>34.0907</v>
+        <v>34.1393</v>
       </c>
       <c r="H11" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I11" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>31 jul</t>
+          <t>3 aug</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>154.9</v>
+        <v>160</v>
       </c>
       <c r="M11" t="n">
-        <v>158.26</v>
+        <v>168.7</v>
       </c>
       <c r="N11" t="n">
-        <v>153.6</v>
+        <v>159.6</v>
       </c>
       <c r="O11" t="n">
-        <v>157.68</v>
+        <v>164.64</v>
       </c>
       <c r="P11" t="n">
-        <v>144.4984</v>
+        <v>144.7016</v>
       </c>
       <c r="Q11" t="n">
-        <v>171.6292</v>
+        <v>171.301</v>
       </c>
       <c r="R11" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S11" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>30 jul</t>
+          <t>31 jul</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>437.0772</v>
+        <v>449.1545</v>
       </c>
       <c r="W11" t="n">
-        <v>457.8281</v>
+        <v>465.9628</v>
       </c>
       <c r="X11" t="n">
-        <v>431.6275</v>
+        <v>448.4857</v>
       </c>
       <c r="Y11" t="n">
-        <v>450.2524</v>
+        <v>463.8468</v>
       </c>
       <c r="Z11" t="n">
-        <v>397.6741</v>
+        <v>398.6364</v>
       </c>
       <c r="AA11" t="n">
-        <v>431.6738</v>
+        <v>431.4438</v>
       </c>
       <c r="AB11" t="n">
         <v>535.3375423278808</v>
@@ -4207,84 +4229,84 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3 aug</t>
+          <t>4 aug</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>38.3128</v>
+        <v>39.3028</v>
       </c>
       <c r="C12" t="n">
-        <v>39.4067</v>
+        <v>39.6443</v>
       </c>
       <c r="D12" t="n">
-        <v>38.2138</v>
+        <v>38.2039</v>
       </c>
       <c r="E12" t="n">
-        <v>39.4067</v>
+        <v>38.486</v>
       </c>
       <c r="F12" t="n">
-        <v>36.1112</v>
+        <v>36.1495</v>
       </c>
       <c r="G12" t="n">
-        <v>34.1393</v>
+        <v>34.1818</v>
       </c>
       <c r="H12" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I12" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>3 aug</t>
+          <t>4 aug</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>160</v>
+        <v>162.86</v>
       </c>
       <c r="M12" t="n">
-        <v>168.7</v>
+        <v>168.56</v>
       </c>
       <c r="N12" t="n">
-        <v>159.6</v>
+        <v>162.4</v>
       </c>
       <c r="O12" t="n">
-        <v>164.64</v>
+        <v>167.38</v>
       </c>
       <c r="P12" t="n">
-        <v>144.7016</v>
+        <v>145.02</v>
       </c>
       <c r="Q12" t="n">
-        <v>171.301</v>
+        <v>170.9913</v>
       </c>
       <c r="R12" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S12" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>31 jul</t>
+          <t>3 aug</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>449.1545</v>
+        <v>475.2354</v>
       </c>
       <c r="W12" t="n">
-        <v>465.9628</v>
+        <v>490.7262</v>
       </c>
       <c r="X12" t="n">
-        <v>448.4857</v>
+        <v>474.1075</v>
       </c>
       <c r="Y12" t="n">
-        <v>463.8468</v>
+        <v>486.7337</v>
       </c>
       <c r="Z12" t="n">
-        <v>398.6364</v>
+        <v>399.9838</v>
       </c>
       <c r="AA12" t="n">
-        <v>431.4438</v>
+        <v>431.3306</v>
       </c>
       <c r="AB12" t="n">
         <v>535.3375423278808</v>
@@ -4296,84 +4318,84 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4 aug</t>
+          <t>5 aug</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>39.3028</v>
+        <v>38.4811</v>
       </c>
       <c r="C13" t="n">
-        <v>39.6443</v>
+        <v>38.7632</v>
       </c>
       <c r="D13" t="n">
-        <v>38.2039</v>
+        <v>37.9366</v>
       </c>
       <c r="E13" t="n">
-        <v>38.486</v>
+        <v>38.0307</v>
       </c>
       <c r="F13" t="n">
-        <v>36.1495</v>
+        <v>36.1966</v>
       </c>
       <c r="G13" t="n">
-        <v>34.1818</v>
+        <v>34.2215</v>
       </c>
       <c r="H13" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I13" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>4 aug</t>
+          <t>5 aug</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>162.86</v>
+        <v>167.92</v>
       </c>
       <c r="M13" t="n">
-        <v>168.56</v>
+        <v>172.6</v>
       </c>
       <c r="N13" t="n">
-        <v>162.4</v>
+        <v>167.3</v>
       </c>
       <c r="O13" t="n">
-        <v>167.38</v>
+        <v>169.26</v>
       </c>
       <c r="P13" t="n">
-        <v>145.02</v>
+        <v>145.4052</v>
       </c>
       <c r="Q13" t="n">
-        <v>170.9913</v>
+        <v>170.7022</v>
       </c>
       <c r="R13" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S13" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>3 aug</t>
+          <t>4 aug</t>
         </is>
       </c>
       <c r="V13" t="n">
-        <v>475.2354</v>
+        <v>479.9964</v>
       </c>
       <c r="W13" t="n">
-        <v>490.7262</v>
+        <v>498.5016</v>
       </c>
       <c r="X13" t="n">
-        <v>474.1075</v>
+        <v>478.2697</v>
       </c>
       <c r="Y13" t="n">
-        <v>486.7337</v>
+        <v>491.884</v>
       </c>
       <c r="Z13" t="n">
-        <v>399.9838</v>
+        <v>401.4555</v>
       </c>
       <c r="AA13" t="n">
-        <v>431.3306</v>
+        <v>431.2438</v>
       </c>
       <c r="AB13" t="n">
         <v>535.3375423278808</v>
@@ -4385,84 +4407,84 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5 aug</t>
+          <t>6 aug</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>38.4811</v>
+        <v>38.0752</v>
       </c>
       <c r="C14" t="n">
-        <v>38.7632</v>
+        <v>38.4069</v>
       </c>
       <c r="D14" t="n">
-        <v>37.9366</v>
+        <v>37.9168</v>
       </c>
       <c r="E14" t="n">
-        <v>38.0307</v>
+        <v>38.392</v>
       </c>
       <c r="F14" t="n">
-        <v>36.1966</v>
+        <v>36.2474</v>
       </c>
       <c r="G14" t="n">
-        <v>34.2215</v>
+        <v>34.2607</v>
       </c>
       <c r="H14" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I14" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>5 aug</t>
+          <t>6 aug</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>167.92</v>
+        <v>171.44</v>
       </c>
       <c r="M14" t="n">
-        <v>172.6</v>
+        <v>173.1</v>
       </c>
       <c r="N14" t="n">
-        <v>167.3</v>
+        <v>168.08</v>
       </c>
       <c r="O14" t="n">
-        <v>169.26</v>
+        <v>170.98</v>
       </c>
       <c r="P14" t="n">
-        <v>145.4052</v>
+        <v>145.7928</v>
       </c>
       <c r="Q14" t="n">
-        <v>170.7022</v>
+        <v>170.384</v>
       </c>
       <c r="R14" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S14" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>4 aug</t>
+          <t>5 aug</t>
         </is>
       </c>
       <c r="V14" t="n">
-        <v>479.9964</v>
+        <v>495.4273</v>
       </c>
       <c r="W14" t="n">
-        <v>498.5016</v>
+        <v>497.3038</v>
       </c>
       <c r="X14" t="n">
-        <v>478.2697</v>
+        <v>484.7674</v>
       </c>
       <c r="Y14" t="n">
-        <v>491.884</v>
+        <v>486.5441</v>
       </c>
       <c r="Z14" t="n">
-        <v>401.4555</v>
+        <v>402.8307</v>
       </c>
       <c r="AA14" t="n">
-        <v>431.2438</v>
+        <v>431.1393</v>
       </c>
       <c r="AB14" t="n">
         <v>535.3375423278808</v>
@@ -4474,84 +4496,84 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6 aug</t>
+          <t>7 aug</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>38.0752</v>
+        <v>38.5207</v>
       </c>
       <c r="C15" t="n">
-        <v>38.4069</v>
+        <v>38.5999</v>
       </c>
       <c r="D15" t="n">
-        <v>37.9168</v>
+        <v>37.897</v>
       </c>
       <c r="E15" t="n">
-        <v>38.392</v>
+        <v>38.0059</v>
       </c>
       <c r="F15" t="n">
-        <v>36.2474</v>
+        <v>36.2952</v>
       </c>
       <c r="G15" t="n">
-        <v>34.2607</v>
+        <v>34.294</v>
       </c>
       <c r="H15" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I15" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>6 aug</t>
+          <t>7 aug</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>171.44</v>
+        <v>173.82</v>
       </c>
       <c r="M15" t="n">
-        <v>173.1</v>
+        <v>179.56</v>
       </c>
       <c r="N15" t="n">
-        <v>168.08</v>
+        <v>173.82</v>
       </c>
       <c r="O15" t="n">
-        <v>170.98</v>
+        <v>177.96</v>
       </c>
       <c r="P15" t="n">
-        <v>145.7928</v>
+        <v>146.2468</v>
       </c>
       <c r="Q15" t="n">
-        <v>170.384</v>
+        <v>170.0918</v>
       </c>
       <c r="R15" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S15" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>5 aug</t>
+          <t>6 aug</t>
         </is>
       </c>
       <c r="V15" t="n">
-        <v>495.4273</v>
+        <v>487.632</v>
       </c>
       <c r="W15" t="n">
-        <v>497.3038</v>
+        <v>500.6176</v>
       </c>
       <c r="X15" t="n">
-        <v>484.7674</v>
+        <v>487.6021</v>
       </c>
       <c r="Y15" t="n">
-        <v>486.5441</v>
+        <v>498.9207</v>
       </c>
       <c r="Z15" t="n">
-        <v>402.8307</v>
+        <v>404.5041</v>
       </c>
       <c r="AA15" t="n">
-        <v>431.1393</v>
+        <v>431.087</v>
       </c>
       <c r="AB15" t="n">
         <v>535.3375423278808</v>
@@ -4563,84 +4585,84 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>7 aug</t>
+          <t>10 aug</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>38.5207</v>
+        <v>38.0356</v>
       </c>
       <c r="C16" t="n">
-        <v>38.5999</v>
+        <v>38.4366</v>
       </c>
       <c r="D16" t="n">
-        <v>37.897</v>
+        <v>37.803</v>
       </c>
       <c r="E16" t="n">
-        <v>38.0059</v>
+        <v>38.4019</v>
       </c>
       <c r="F16" t="n">
-        <v>36.2952</v>
+        <v>36.3315</v>
       </c>
       <c r="G16" t="n">
-        <v>34.294</v>
+        <v>34.3294</v>
       </c>
       <c r="H16" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I16" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>7 aug</t>
+          <t>10 aug</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>173.82</v>
+        <v>178.92</v>
       </c>
       <c r="M16" t="n">
-        <v>179.56</v>
+        <v>179.96</v>
       </c>
       <c r="N16" t="n">
-        <v>173.82</v>
+        <v>175.86</v>
       </c>
       <c r="O16" t="n">
-        <v>177.96</v>
+        <v>179.3</v>
       </c>
       <c r="P16" t="n">
-        <v>146.2468</v>
+        <v>146.4748</v>
       </c>
       <c r="Q16" t="n">
-        <v>170.0918</v>
+        <v>169.8238</v>
       </c>
       <c r="R16" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S16" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>6 aug</t>
+          <t>7 aug</t>
         </is>
       </c>
       <c r="V16" t="n">
-        <v>487.632</v>
+        <v>498.272</v>
       </c>
       <c r="W16" t="n">
-        <v>500.6176</v>
+        <v>504.2308</v>
       </c>
       <c r="X16" t="n">
-        <v>487.6021</v>
+        <v>497.7929</v>
       </c>
       <c r="Y16" t="n">
-        <v>498.9207</v>
+        <v>499.0505</v>
       </c>
       <c r="Z16" t="n">
-        <v>404.5041</v>
+        <v>406.2472</v>
       </c>
       <c r="AA16" t="n">
-        <v>431.087</v>
+        <v>431.0194</v>
       </c>
       <c r="AB16" t="n">
         <v>535.3375423278808</v>
@@ -4652,84 +4674,84 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10 aug</t>
+          <t>11 aug</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>38.0356</v>
+        <v>38.7385</v>
       </c>
       <c r="C17" t="n">
-        <v>38.4366</v>
+        <v>39.0058</v>
       </c>
       <c r="D17" t="n">
-        <v>37.803</v>
+        <v>38.6148</v>
       </c>
       <c r="E17" t="n">
-        <v>38.4019</v>
+        <v>38.9662</v>
       </c>
       <c r="F17" t="n">
-        <v>36.3315</v>
+        <v>36.374</v>
       </c>
       <c r="G17" t="n">
-        <v>34.3294</v>
+        <v>34.3685</v>
       </c>
       <c r="H17" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I17" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>10 aug</t>
+          <t>11 aug</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>178.92</v>
+        <v>180</v>
       </c>
       <c r="M17" t="n">
-        <v>179.96</v>
+        <v>183.24</v>
       </c>
       <c r="N17" t="n">
-        <v>175.86</v>
+        <v>178.14</v>
       </c>
       <c r="O17" t="n">
-        <v>179.3</v>
+        <v>180.7</v>
       </c>
       <c r="P17" t="n">
-        <v>146.4748</v>
+        <v>146.8316</v>
       </c>
       <c r="Q17" t="n">
-        <v>169.8238</v>
+        <v>169.5375</v>
       </c>
       <c r="R17" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S17" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>7 aug</t>
+          <t>10 aug</t>
         </is>
       </c>
       <c r="V17" t="n">
-        <v>498.272</v>
+        <v>502.4941</v>
       </c>
       <c r="W17" t="n">
-        <v>504.2308</v>
+        <v>512.7646999999999</v>
       </c>
       <c r="X17" t="n">
-        <v>497.7929</v>
+        <v>501.3262</v>
       </c>
       <c r="Y17" t="n">
-        <v>499.0505</v>
+        <v>505.1091</v>
       </c>
       <c r="Z17" t="n">
-        <v>406.2472</v>
+        <v>407.8257</v>
       </c>
       <c r="AA17" t="n">
-        <v>431.0194</v>
+        <v>430.9778</v>
       </c>
       <c r="AB17" t="n">
         <v>535.3375423278808</v>
@@ -4741,84 +4763,84 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>11 aug</t>
+          <t>12 aug</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>38.7385</v>
+        <v>38.8573</v>
       </c>
       <c r="C18" t="n">
-        <v>39.0058</v>
+        <v>38.986</v>
       </c>
       <c r="D18" t="n">
-        <v>38.6148</v>
+        <v>38.3871</v>
       </c>
       <c r="E18" t="n">
-        <v>38.9662</v>
+        <v>38.6494</v>
       </c>
       <c r="F18" t="n">
-        <v>36.374</v>
+        <v>36.3981</v>
       </c>
       <c r="G18" t="n">
-        <v>34.3685</v>
+        <v>34.4068</v>
       </c>
       <c r="H18" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I18" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>11 aug</t>
+          <t>12 aug</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>180</v>
+        <v>180.3</v>
       </c>
       <c r="M18" t="n">
-        <v>183.24</v>
+        <v>180.98</v>
       </c>
       <c r="N18" t="n">
-        <v>178.14</v>
+        <v>175.4</v>
       </c>
       <c r="O18" t="n">
-        <v>180.7</v>
+        <v>175.96</v>
       </c>
       <c r="P18" t="n">
-        <v>146.8316</v>
+        <v>147.232</v>
       </c>
       <c r="Q18" t="n">
-        <v>169.5375</v>
+        <v>169.2701</v>
       </c>
       <c r="R18" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S18" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>10 aug</t>
+          <t>11 aug</t>
         </is>
       </c>
       <c r="V18" t="n">
-        <v>502.4941</v>
+        <v>503.3824</v>
       </c>
       <c r="W18" t="n">
-        <v>512.7646999999999</v>
+        <v>504.3805</v>
       </c>
       <c r="X18" t="n">
-        <v>501.3262</v>
+        <v>498.6113</v>
       </c>
       <c r="Y18" t="n">
-        <v>505.1091</v>
+        <v>502.8633</v>
       </c>
       <c r="Z18" t="n">
-        <v>407.8257</v>
+        <v>408.895</v>
       </c>
       <c r="AA18" t="n">
-        <v>430.9778</v>
+        <v>430.9106</v>
       </c>
       <c r="AB18" t="n">
         <v>535.3375423278808</v>
@@ -4830,84 +4852,84 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>12 aug</t>
+          <t>13 aug</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>38.8573</v>
+        <v>39</v>
       </c>
       <c r="C19" t="n">
-        <v>38.986</v>
+        <v>39.005</v>
       </c>
       <c r="D19" t="n">
-        <v>38.3871</v>
+        <v>38.2</v>
       </c>
       <c r="E19" t="n">
-        <v>38.6494</v>
+        <v>38.605</v>
       </c>
       <c r="F19" t="n">
-        <v>36.3981</v>
+        <v>36.4313</v>
       </c>
       <c r="G19" t="n">
-        <v>34.4068</v>
+        <v>34.4429</v>
       </c>
       <c r="H19" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I19" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>12 aug</t>
+          <t>13 aug</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>180.3</v>
+        <v>177.48</v>
       </c>
       <c r="M19" t="n">
-        <v>180.98</v>
+        <v>178.3</v>
       </c>
       <c r="N19" t="n">
-        <v>175.4</v>
+        <v>174.8</v>
       </c>
       <c r="O19" t="n">
-        <v>175.96</v>
+        <v>175.38</v>
       </c>
       <c r="P19" t="n">
-        <v>147.232</v>
+        <v>147.4496</v>
       </c>
       <c r="Q19" t="n">
-        <v>169.2701</v>
+        <v>168.9889</v>
       </c>
       <c r="R19" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S19" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>11 aug</t>
+          <t>12 aug</t>
         </is>
       </c>
       <c r="V19" t="n">
-        <v>503.3824</v>
+        <v>499.0505</v>
       </c>
       <c r="W19" t="n">
-        <v>504.3805</v>
+        <v>500.5577</v>
       </c>
       <c r="X19" t="n">
-        <v>498.6113</v>
+        <v>490.5964</v>
       </c>
       <c r="Y19" t="n">
-        <v>502.8633</v>
+        <v>491.5047</v>
       </c>
       <c r="Z19" t="n">
-        <v>408.895</v>
+        <v>409.532</v>
       </c>
       <c r="AA19" t="n">
-        <v>430.9106</v>
+        <v>430.7866</v>
       </c>
       <c r="AB19" t="n">
         <v>535.3375423278808</v>
@@ -4919,84 +4941,84 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>13 aug</t>
+          <t>14 aug</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>39</v>
+        <v>38.65</v>
       </c>
       <c r="C20" t="n">
-        <v>39.005</v>
+        <v>39.1</v>
       </c>
       <c r="D20" t="n">
-        <v>38.2</v>
+        <v>38.56</v>
       </c>
       <c r="E20" t="n">
-        <v>38.605</v>
+        <v>38.97</v>
       </c>
       <c r="F20" t="n">
-        <v>36.4313</v>
+        <v>36.4703</v>
       </c>
       <c r="G20" t="n">
-        <v>34.4429</v>
+        <v>34.4805</v>
       </c>
       <c r="H20" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I20" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>13 aug</t>
+          <t>14 aug</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>177.48</v>
+        <v>182</v>
       </c>
       <c r="M20" t="n">
-        <v>178.3</v>
+        <v>185.74</v>
       </c>
       <c r="N20" t="n">
-        <v>174.8</v>
+        <v>179.28</v>
       </c>
       <c r="O20" t="n">
-        <v>175.38</v>
+        <v>180.14</v>
       </c>
       <c r="P20" t="n">
-        <v>147.4496</v>
+        <v>147.8228</v>
       </c>
       <c r="Q20" t="n">
-        <v>168.9889</v>
+        <v>168.7386</v>
       </c>
       <c r="R20" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S20" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>12 aug</t>
+          <t>13 aug</t>
         </is>
       </c>
       <c r="V20" t="n">
-        <v>499.0505</v>
+        <v>492.3431</v>
       </c>
       <c r="W20" t="n">
-        <v>500.5577</v>
+        <v>500.398</v>
       </c>
       <c r="X20" t="n">
-        <v>490.5964</v>
+        <v>492.0837</v>
       </c>
       <c r="Y20" t="n">
-        <v>491.5047</v>
+        <v>495.9464</v>
       </c>
       <c r="Z20" t="n">
-        <v>409.532</v>
+        <v>410.6414</v>
       </c>
       <c r="AA20" t="n">
-        <v>430.7866</v>
+        <v>430.6696</v>
       </c>
       <c r="AB20" t="n">
         <v>535.3375423278808</v>
@@ -5008,84 +5030,84 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>14 aug</t>
+          <t>17 aug</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>38.65</v>
+        <v>38.97</v>
       </c>
       <c r="C21" t="n">
-        <v>39.1</v>
+        <v>39.27</v>
       </c>
       <c r="D21" t="n">
-        <v>38.56</v>
+        <v>38.765</v>
       </c>
       <c r="E21" t="n">
-        <v>38.97</v>
+        <v>39.15</v>
       </c>
       <c r="F21" t="n">
-        <v>36.4703</v>
+        <v>36.5118</v>
       </c>
       <c r="G21" t="n">
-        <v>34.4805</v>
+        <v>34.5207</v>
       </c>
       <c r="H21" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I21" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>14 aug</t>
+          <t>17 aug</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>182</v>
+        <v>178.94</v>
       </c>
       <c r="M21" t="n">
-        <v>185.74</v>
+        <v>180.9</v>
       </c>
       <c r="N21" t="n">
-        <v>179.28</v>
+        <v>177.66</v>
       </c>
       <c r="O21" t="n">
-        <v>180.14</v>
+        <v>179.58</v>
       </c>
       <c r="P21" t="n">
-        <v>147.8228</v>
+        <v>148.2524</v>
       </c>
       <c r="Q21" t="n">
-        <v>168.7386</v>
+        <v>168.5337</v>
       </c>
       <c r="R21" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S21" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>13 aug</t>
+          <t>14 aug</t>
         </is>
       </c>
       <c r="V21" t="n">
-        <v>492.3431</v>
+        <v>495.4273</v>
       </c>
       <c r="W21" t="n">
-        <v>500.398</v>
+        <v>499.0705</v>
       </c>
       <c r="X21" t="n">
-        <v>492.0837</v>
+        <v>492.9919</v>
       </c>
       <c r="Y21" t="n">
-        <v>495.9464</v>
+        <v>494.4691</v>
       </c>
       <c r="Z21" t="n">
-        <v>410.6414</v>
+        <v>412</v>
       </c>
       <c r="AA21" t="n">
-        <v>430.6696</v>
+        <v>430.5061</v>
       </c>
       <c r="AB21" t="n">
         <v>535.3375423278808</v>
@@ -5097,84 +5119,84 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>17 aug</t>
+          <t>18 aug</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>38.97</v>
+        <v>39.49</v>
       </c>
       <c r="C22" t="n">
-        <v>39.27</v>
+        <v>39.945</v>
       </c>
       <c r="D22" t="n">
-        <v>38.765</v>
+        <v>39.46</v>
       </c>
       <c r="E22" t="n">
-        <v>39.15</v>
+        <v>39.785</v>
       </c>
       <c r="F22" t="n">
-        <v>36.5118</v>
+        <v>36.5781</v>
       </c>
       <c r="G22" t="n">
-        <v>34.5207</v>
+        <v>34.5641</v>
       </c>
       <c r="H22" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I22" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>17 aug</t>
+          <t>18 aug</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>178.94</v>
+        <v>179.14</v>
       </c>
       <c r="M22" t="n">
-        <v>180.9</v>
+        <v>183.9</v>
       </c>
       <c r="N22" t="n">
-        <v>177.66</v>
+        <v>177.98</v>
       </c>
       <c r="O22" t="n">
-        <v>179.58</v>
+        <v>182.5</v>
       </c>
       <c r="P22" t="n">
-        <v>148.2524</v>
+        <v>148.8084</v>
       </c>
       <c r="Q22" t="n">
-        <v>168.5337</v>
+        <v>168.3358</v>
       </c>
       <c r="R22" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S22" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>14 aug</t>
+          <t>17 aug</t>
         </is>
       </c>
       <c r="V22" t="n">
-        <v>495.4273</v>
+        <v>489.2191</v>
       </c>
       <c r="W22" t="n">
-        <v>499.0705</v>
+        <v>491.7343</v>
       </c>
       <c r="X22" t="n">
-        <v>492.9919</v>
+        <v>477.5111</v>
       </c>
       <c r="Y22" t="n">
-        <v>494.4691</v>
+        <v>479.4474</v>
       </c>
       <c r="Z22" t="n">
-        <v>412</v>
+        <v>413.044</v>
       </c>
       <c r="AA22" t="n">
-        <v>430.5061</v>
+        <v>430.2151</v>
       </c>
       <c r="AB22" t="n">
         <v>535.3375423278808</v>
@@ -5186,84 +5208,84 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>18 aug</t>
+          <t>19 aug</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>39.49</v>
+        <v>39.835</v>
       </c>
       <c r="C23" t="n">
-        <v>39.945</v>
+        <v>40.14</v>
       </c>
       <c r="D23" t="n">
-        <v>39.46</v>
+        <v>39.74</v>
       </c>
       <c r="E23" t="n">
-        <v>39.785</v>
+        <v>39.94</v>
       </c>
       <c r="F23" t="n">
-        <v>36.5781</v>
+        <v>36.6336</v>
       </c>
       <c r="G23" t="n">
-        <v>34.5641</v>
+        <v>34.6092</v>
       </c>
       <c r="H23" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I23" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>18 aug</t>
+          <t>19 aug</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>179.14</v>
+        <v>181.7</v>
       </c>
       <c r="M23" t="n">
-        <v>183.9</v>
+        <v>186.98</v>
       </c>
       <c r="N23" t="n">
-        <v>177.98</v>
+        <v>180.38</v>
       </c>
       <c r="O23" t="n">
-        <v>182.5</v>
+        <v>185.9</v>
       </c>
       <c r="P23" t="n">
-        <v>148.8084</v>
+        <v>149.5324</v>
       </c>
       <c r="Q23" t="n">
-        <v>168.3358</v>
+        <v>168.1618</v>
       </c>
       <c r="R23" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S23" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>17 aug</t>
+          <t>18 aug</t>
         </is>
       </c>
       <c r="V23" t="n">
-        <v>489.2191</v>
+        <v>480.6352</v>
       </c>
       <c r="W23" t="n">
-        <v>491.7343</v>
+        <v>483.3601</v>
       </c>
       <c r="X23" t="n">
-        <v>477.5111</v>
+        <v>476.2534</v>
       </c>
       <c r="Y23" t="n">
-        <v>479.4474</v>
+        <v>480.725</v>
       </c>
       <c r="Z23" t="n">
-        <v>413.044</v>
+        <v>414.3408</v>
       </c>
       <c r="AA23" t="n">
-        <v>430.2151</v>
+        <v>429.933</v>
       </c>
       <c r="AB23" t="n">
         <v>535.3375423278808</v>
@@ -5275,84 +5297,84 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>19 aug</t>
+          <t>20 aug</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>39.835</v>
+        <v>39.865</v>
       </c>
       <c r="C24" t="n">
-        <v>40.14</v>
+        <v>40.51</v>
       </c>
       <c r="D24" t="n">
-        <v>39.74</v>
+        <v>39.8</v>
       </c>
       <c r="E24" t="n">
-        <v>39.94</v>
+        <v>40.28</v>
       </c>
       <c r="F24" t="n">
-        <v>36.6336</v>
+        <v>36.6884</v>
       </c>
       <c r="G24" t="n">
-        <v>34.6092</v>
+        <v>34.6545</v>
       </c>
       <c r="H24" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I24" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>19 aug</t>
+          <t>20 aug</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>181.7</v>
+        <v>183.78</v>
       </c>
       <c r="M24" t="n">
-        <v>186.98</v>
+        <v>186.1</v>
       </c>
       <c r="N24" t="n">
-        <v>180.38</v>
+        <v>182.52</v>
       </c>
       <c r="O24" t="n">
-        <v>185.9</v>
+        <v>185.64</v>
       </c>
       <c r="P24" t="n">
-        <v>149.5324</v>
+        <v>150.4472</v>
       </c>
       <c r="Q24" t="n">
-        <v>168.1618</v>
+        <v>167.9648</v>
       </c>
       <c r="R24" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S24" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>18 aug</t>
+          <t>19 aug</t>
         </is>
       </c>
       <c r="V24" t="n">
-        <v>480.6352</v>
+        <v>479.168</v>
       </c>
       <c r="W24" t="n">
-        <v>483.3601</v>
+        <v>488.3806</v>
       </c>
       <c r="X24" t="n">
-        <v>476.2534</v>
+        <v>478.4593</v>
       </c>
       <c r="Y24" t="n">
-        <v>480.725</v>
+        <v>483.4</v>
       </c>
       <c r="Z24" t="n">
-        <v>414.3408</v>
+        <v>415.7895</v>
       </c>
       <c r="AA24" t="n">
-        <v>429.933</v>
+        <v>429.7427</v>
       </c>
       <c r="AB24" t="n">
         <v>535.3375423278808</v>
@@ -5364,84 +5386,84 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20 aug</t>
+          <t>21 aug</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>39.865</v>
+        <v>40.1</v>
       </c>
       <c r="C25" t="n">
-        <v>40.51</v>
+        <v>40.37</v>
       </c>
       <c r="D25" t="n">
-        <v>39.8</v>
+        <v>39.84</v>
       </c>
       <c r="E25" t="n">
-        <v>40.28</v>
+        <v>39.91</v>
       </c>
       <c r="F25" t="n">
-        <v>36.6884</v>
+        <v>36.7478</v>
       </c>
       <c r="G25" t="n">
-        <v>34.6545</v>
+        <v>34.6988</v>
       </c>
       <c r="H25" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I25" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>20 aug</t>
+          <t>21 aug</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>183.78</v>
+        <v>185.18</v>
       </c>
       <c r="M25" t="n">
-        <v>186.1</v>
+        <v>188.4</v>
       </c>
       <c r="N25" t="n">
-        <v>182.52</v>
+        <v>183.6</v>
       </c>
       <c r="O25" t="n">
-        <v>185.64</v>
+        <v>188.12</v>
       </c>
       <c r="P25" t="n">
-        <v>150.4472</v>
+        <v>151.4044</v>
       </c>
       <c r="Q25" t="n">
-        <v>167.9648</v>
+        <v>167.794</v>
       </c>
       <c r="R25" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S25" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>19 aug</t>
+          <t>20 aug</t>
         </is>
       </c>
       <c r="V25" t="n">
-        <v>479.168</v>
+        <v>483.3</v>
       </c>
       <c r="W25" t="n">
-        <v>488.3806</v>
+        <v>484.16</v>
       </c>
       <c r="X25" t="n">
-        <v>478.4593</v>
+        <v>479.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>483.4</v>
+        <v>481.15</v>
       </c>
       <c r="Z25" t="n">
-        <v>415.7895</v>
+        <v>417.3594</v>
       </c>
       <c r="AA25" t="n">
-        <v>429.7427</v>
+        <v>429.5805</v>
       </c>
       <c r="AB25" t="n">
         <v>535.3375423278808</v>
@@ -5453,84 +5475,84 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>21 aug</t>
+          <t>24 aug</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>40.1</v>
+        <v>39.88</v>
       </c>
       <c r="C26" t="n">
-        <v>40.37</v>
+        <v>40.085</v>
       </c>
       <c r="D26" t="n">
-        <v>39.84</v>
+        <v>39.68</v>
       </c>
       <c r="E26" t="n">
-        <v>39.91</v>
+        <v>39.775</v>
       </c>
       <c r="F26" t="n">
-        <v>36.7478</v>
+        <v>36.8369</v>
       </c>
       <c r="G26" t="n">
-        <v>34.6988</v>
+        <v>34.7421</v>
       </c>
       <c r="H26" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I26" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>21 aug</t>
+          <t>24 aug</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>185.18</v>
+        <v>186.86</v>
       </c>
       <c r="M26" t="n">
-        <v>188.4</v>
+        <v>188.16</v>
       </c>
       <c r="N26" t="n">
-        <v>183.6</v>
+        <v>185.52</v>
       </c>
       <c r="O26" t="n">
-        <v>188.12</v>
+        <v>187.2</v>
       </c>
       <c r="P26" t="n">
-        <v>151.4044</v>
+        <v>152.2848</v>
       </c>
       <c r="Q26" t="n">
-        <v>167.794</v>
+        <v>167.6093</v>
       </c>
       <c r="R26" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S26" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>20 aug</t>
+          <t>21 aug</t>
         </is>
       </c>
       <c r="V26" t="n">
-        <v>483.3</v>
+        <v>479.88</v>
       </c>
       <c r="W26" t="n">
-        <v>484.16</v>
+        <v>486.36</v>
       </c>
       <c r="X26" t="n">
-        <v>479.5</v>
+        <v>478.53</v>
       </c>
       <c r="Y26" t="n">
-        <v>481.15</v>
+        <v>483.24</v>
       </c>
       <c r="Z26" t="n">
-        <v>417.3594</v>
+        <v>419.092</v>
       </c>
       <c r="AA26" t="n">
-        <v>429.5805</v>
+        <v>429.4327</v>
       </c>
       <c r="AB26" t="n">
         <v>535.3375423278808</v>
@@ -5542,84 +5564,84 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>24 aug</t>
+          <t>25 aug</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>39.88</v>
+        <v>39.77</v>
       </c>
       <c r="C27" t="n">
-        <v>40.085</v>
+        <v>39.915</v>
       </c>
       <c r="D27" t="n">
-        <v>39.68</v>
+        <v>39.385</v>
       </c>
       <c r="E27" t="n">
-        <v>39.775</v>
+        <v>39.6</v>
       </c>
       <c r="F27" t="n">
-        <v>36.8369</v>
+        <v>36.926</v>
       </c>
       <c r="G27" t="n">
-        <v>34.7421</v>
+        <v>34.783</v>
       </c>
       <c r="H27" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I27" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>24 aug</t>
+          <t>25 aug</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>186.86</v>
+        <v>186.4</v>
       </c>
       <c r="M27" t="n">
-        <v>188.16</v>
+        <v>187.62</v>
       </c>
       <c r="N27" t="n">
-        <v>185.52</v>
+        <v>182.74</v>
       </c>
       <c r="O27" t="n">
-        <v>187.2</v>
+        <v>185.46</v>
       </c>
       <c r="P27" t="n">
-        <v>152.2848</v>
+        <v>153.136</v>
       </c>
       <c r="Q27" t="n">
-        <v>167.6093</v>
+        <v>167.4651</v>
       </c>
       <c r="R27" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S27" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>21 aug</t>
+          <t>24 aug</t>
         </is>
       </c>
       <c r="V27" t="n">
-        <v>479.88</v>
+        <v>483.21</v>
       </c>
       <c r="W27" t="n">
-        <v>486.36</v>
+        <v>490.61</v>
       </c>
       <c r="X27" t="n">
-        <v>478.53</v>
+        <v>481.86</v>
       </c>
       <c r="Y27" t="n">
-        <v>483.24</v>
+        <v>487.31</v>
       </c>
       <c r="Z27" t="n">
-        <v>419.092</v>
+        <v>421.046</v>
       </c>
       <c r="AA27" t="n">
-        <v>429.4327</v>
+        <v>429.3185</v>
       </c>
       <c r="AB27" t="n">
         <v>535.3375423278808</v>
@@ -5631,84 +5653,84 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>25 aug</t>
+          <t>26 aug</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>39.77</v>
+        <v>39.275</v>
       </c>
       <c r="C28" t="n">
-        <v>39.915</v>
+        <v>39.47</v>
       </c>
       <c r="D28" t="n">
-        <v>39.385</v>
+        <v>38.91</v>
       </c>
       <c r="E28" t="n">
-        <v>39.6</v>
+        <v>39.42</v>
       </c>
       <c r="F28" t="n">
-        <v>36.926</v>
+        <v>37.0192</v>
       </c>
       <c r="G28" t="n">
-        <v>34.783</v>
+        <v>34.8202</v>
       </c>
       <c r="H28" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I28" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>25 aug</t>
+          <t>26 aug</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>186.4</v>
+        <v>179.92</v>
       </c>
       <c r="M28" t="n">
-        <v>187.62</v>
+        <v>182.16</v>
       </c>
       <c r="N28" t="n">
-        <v>182.74</v>
+        <v>176.82</v>
       </c>
       <c r="O28" t="n">
-        <v>185.46</v>
+        <v>180.02</v>
       </c>
       <c r="P28" t="n">
-        <v>153.136</v>
+        <v>153.9128</v>
       </c>
       <c r="Q28" t="n">
-        <v>167.4651</v>
+        <v>167.3049</v>
       </c>
       <c r="R28" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S28" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>24 aug</t>
+          <t>25 aug</t>
         </is>
       </c>
       <c r="V28" t="n">
-        <v>483.21</v>
+        <v>485.44</v>
       </c>
       <c r="W28" t="n">
-        <v>490.61</v>
+        <v>492.44</v>
       </c>
       <c r="X28" t="n">
-        <v>481.86</v>
+        <v>484.3</v>
       </c>
       <c r="Y28" t="n">
-        <v>487.31</v>
+        <v>491.71</v>
       </c>
       <c r="Z28" t="n">
-        <v>421.046</v>
+        <v>423.0801</v>
       </c>
       <c r="AA28" t="n">
-        <v>429.3186</v>
+        <v>429.262</v>
       </c>
       <c r="AB28" t="n">
         <v>535.3375423278808</v>
@@ -5720,84 +5742,84 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>26 aug</t>
+          <t>27 aug</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>39.275</v>
+        <v>39.16</v>
       </c>
       <c r="C29" t="n">
-        <v>39.47</v>
+        <v>39.295</v>
       </c>
       <c r="D29" t="n">
-        <v>38.91</v>
+        <v>38.65</v>
       </c>
       <c r="E29" t="n">
-        <v>39.42</v>
+        <v>38.76</v>
       </c>
       <c r="F29" t="n">
-        <v>37.0192</v>
+        <v>37.117</v>
       </c>
       <c r="G29" t="n">
-        <v>34.8202</v>
+        <v>34.8559</v>
       </c>
       <c r="H29" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I29" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>26 aug</t>
+          <t>27 aug</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>179.92</v>
+        <v>182.5</v>
       </c>
       <c r="M29" t="n">
-        <v>182.16</v>
+        <v>190.8</v>
       </c>
       <c r="N29" t="n">
-        <v>176.82</v>
+        <v>181.14</v>
       </c>
       <c r="O29" t="n">
-        <v>180.02</v>
+        <v>189.88</v>
       </c>
       <c r="P29" t="n">
-        <v>153.9128</v>
+        <v>155.0132</v>
       </c>
       <c r="Q29" t="n">
-        <v>167.3049</v>
+        <v>167.1911</v>
       </c>
       <c r="R29" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S29" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>25 aug</t>
+          <t>26 aug</t>
         </is>
       </c>
       <c r="V29" t="n">
-        <v>485.44</v>
+        <v>487.85</v>
       </c>
       <c r="W29" t="n">
-        <v>492.44</v>
+        <v>497.4</v>
       </c>
       <c r="X29" t="n">
-        <v>484.3</v>
+        <v>487.31</v>
       </c>
       <c r="Y29" t="n">
-        <v>491.71</v>
+        <v>496.37</v>
       </c>
       <c r="Z29" t="n">
-        <v>423.0801</v>
+        <v>425.0273</v>
       </c>
       <c r="AA29" t="n">
-        <v>429.262</v>
+        <v>429.2786</v>
       </c>
       <c r="AB29" t="n">
         <v>535.3375423278808</v>
@@ -5809,84 +5831,84 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>27 aug</t>
+          <t>28 aug</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>39.16</v>
+        <v>39</v>
       </c>
       <c r="C30" t="n">
-        <v>39.295</v>
+        <v>39.18</v>
       </c>
       <c r="D30" t="n">
-        <v>38.65</v>
+        <v>38.845</v>
       </c>
       <c r="E30" t="n">
-        <v>38.76</v>
+        <v>39.145</v>
       </c>
       <c r="F30" t="n">
-        <v>37.117</v>
+        <v>37.2162</v>
       </c>
       <c r="G30" t="n">
-        <v>34.8559</v>
+        <v>34.8941</v>
       </c>
       <c r="H30" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I30" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>27 aug</t>
+          <t>28 aug</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>182.5</v>
+        <v>189.5</v>
       </c>
       <c r="M30" t="n">
-        <v>190.8</v>
+        <v>191.94</v>
       </c>
       <c r="N30" t="n">
-        <v>181.14</v>
+        <v>187.98</v>
       </c>
       <c r="O30" t="n">
-        <v>189.88</v>
+        <v>191.32</v>
       </c>
       <c r="P30" t="n">
-        <v>155.0132</v>
+        <v>156.1568</v>
       </c>
       <c r="Q30" t="n">
-        <v>167.1911</v>
+        <v>167.0806</v>
       </c>
       <c r="R30" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S30" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>26 aug</t>
+          <t>27 aug</t>
         </is>
       </c>
       <c r="V30" t="n">
-        <v>487.85</v>
+        <v>494.88</v>
       </c>
       <c r="W30" t="n">
-        <v>497.4</v>
+        <v>506.48</v>
       </c>
       <c r="X30" t="n">
-        <v>487.31</v>
+        <v>490.08</v>
       </c>
       <c r="Y30" t="n">
-        <v>496.37</v>
+        <v>505.06</v>
       </c>
       <c r="Z30" t="n">
-        <v>425.0273</v>
+        <v>427.2667</v>
       </c>
       <c r="AA30" t="n">
-        <v>429.2786</v>
+        <v>429.3401</v>
       </c>
       <c r="AB30" t="n">
         <v>535.3375423278808</v>
@@ -5898,84 +5920,84 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>28 aug</t>
+          <t>31 aug</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>39</v>
+        <v>39.54</v>
       </c>
       <c r="C31" t="n">
-        <v>39.18</v>
+        <v>39.91</v>
       </c>
       <c r="D31" t="n">
-        <v>38.845</v>
+        <v>39.24</v>
       </c>
       <c r="E31" t="n">
-        <v>39.145</v>
+        <v>39.335</v>
       </c>
       <c r="F31" t="n">
-        <v>37.2162</v>
+        <v>37.3111</v>
       </c>
       <c r="G31" t="n">
-        <v>34.8941</v>
+        <v>34.9333</v>
       </c>
       <c r="H31" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I31" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>28 aug</t>
+          <t>31 aug</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>189.5</v>
+        <v>188.46</v>
       </c>
       <c r="M31" t="n">
-        <v>191.94</v>
+        <v>192.12</v>
       </c>
       <c r="N31" t="n">
-        <v>187.98</v>
+        <v>188.2</v>
       </c>
       <c r="O31" t="n">
-        <v>191.32</v>
+        <v>190.9</v>
       </c>
       <c r="P31" t="n">
-        <v>156.1568</v>
+        <v>157.3304</v>
       </c>
       <c r="Q31" t="n">
-        <v>167.0806</v>
+        <v>166.9613</v>
       </c>
       <c r="R31" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S31" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>27 aug</t>
+          <t>28 aug</t>
         </is>
       </c>
       <c r="V31" t="n">
-        <v>494.88</v>
+        <v>505.33</v>
       </c>
       <c r="W31" t="n">
-        <v>506.48</v>
+        <v>517.78</v>
       </c>
       <c r="X31" t="n">
-        <v>490.08</v>
+        <v>504.87</v>
       </c>
       <c r="Y31" t="n">
-        <v>505.06</v>
+        <v>513.53</v>
       </c>
       <c r="Z31" t="n">
-        <v>427.2667</v>
+        <v>429.9734</v>
       </c>
       <c r="AA31" t="n">
-        <v>429.3401</v>
+        <v>429.3984</v>
       </c>
       <c r="AB31" t="n">
         <v>535.3375423278808</v>
@@ -5987,84 +6009,84 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>31 aug</t>
+          <t>1 sep</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>39.54</v>
+        <v>39.77</v>
       </c>
       <c r="C32" t="n">
-        <v>39.91</v>
+        <v>40.19</v>
       </c>
       <c r="D32" t="n">
-        <v>39.24</v>
+        <v>39.645</v>
       </c>
       <c r="E32" t="n">
-        <v>39.335</v>
+        <v>40.155</v>
       </c>
       <c r="F32" t="n">
-        <v>37.3111</v>
+        <v>37.4239</v>
       </c>
       <c r="G32" t="n">
-        <v>34.9333</v>
+        <v>34.9763</v>
       </c>
       <c r="H32" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I32" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>31 aug</t>
+          <t>1 sep</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>188.46</v>
+        <v>186</v>
       </c>
       <c r="M32" t="n">
-        <v>192.12</v>
+        <v>187.86</v>
       </c>
       <c r="N32" t="n">
-        <v>188.2</v>
+        <v>183.32</v>
       </c>
       <c r="O32" t="n">
-        <v>190.9</v>
+        <v>184.26</v>
       </c>
       <c r="P32" t="n">
-        <v>157.3304</v>
+        <v>158.3252</v>
       </c>
       <c r="Q32" t="n">
-        <v>166.9613</v>
+        <v>166.8103</v>
       </c>
       <c r="R32" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S32" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>28 aug</t>
+          <t>31 aug</t>
         </is>
       </c>
       <c r="V32" t="n">
-        <v>505.33</v>
+        <v>510.38</v>
       </c>
       <c r="W32" t="n">
-        <v>517.78</v>
+        <v>512.1900000000001</v>
       </c>
       <c r="X32" t="n">
-        <v>504.87</v>
+        <v>506.39</v>
       </c>
       <c r="Y32" t="n">
-        <v>513.53</v>
+        <v>507.29</v>
       </c>
       <c r="Z32" t="n">
-        <v>429.9734</v>
+        <v>432.5454</v>
       </c>
       <c r="AA32" t="n">
-        <v>429.3984</v>
+        <v>429.4122</v>
       </c>
       <c r="AB32" t="n">
         <v>535.3375423278808</v>
@@ -6076,84 +6098,84 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1 sep</t>
+          <t>2 sep</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>39.77</v>
+        <v>40.35</v>
       </c>
       <c r="C33" t="n">
-        <v>40.19</v>
+        <v>40.615</v>
       </c>
       <c r="D33" t="n">
-        <v>39.645</v>
+        <v>39.975</v>
       </c>
       <c r="E33" t="n">
-        <v>40.155</v>
+        <v>40.21</v>
       </c>
       <c r="F33" t="n">
-        <v>37.4239</v>
+        <v>37.5499</v>
       </c>
       <c r="G33" t="n">
-        <v>34.9763</v>
+        <v>35.0217</v>
       </c>
       <c r="H33" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I33" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1 sep</t>
+          <t>2 sep</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>186</v>
+        <v>182.18</v>
       </c>
       <c r="M33" t="n">
-        <v>187.86</v>
+        <v>184.7</v>
       </c>
       <c r="N33" t="n">
-        <v>183.32</v>
+        <v>180.72</v>
       </c>
       <c r="O33" t="n">
-        <v>184.26</v>
+        <v>181.44</v>
       </c>
       <c r="P33" t="n">
-        <v>158.3252</v>
+        <v>159.2568</v>
       </c>
       <c r="Q33" t="n">
-        <v>166.8103</v>
+        <v>166.6796</v>
       </c>
       <c r="R33" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S33" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>31 aug</t>
+          <t>1 sep</t>
         </is>
       </c>
       <c r="V33" t="n">
-        <v>510.38</v>
+        <v>497.52</v>
       </c>
       <c r="W33" t="n">
-        <v>512.1900000000001</v>
+        <v>505.97</v>
       </c>
       <c r="X33" t="n">
-        <v>506.39</v>
+        <v>496.78</v>
       </c>
       <c r="Y33" t="n">
-        <v>507.29</v>
+        <v>501.02</v>
       </c>
       <c r="Z33" t="n">
-        <v>432.5454</v>
+        <v>435.2328</v>
       </c>
       <c r="AA33" t="n">
-        <v>429.4122</v>
+        <v>429.3825</v>
       </c>
       <c r="AB33" t="n">
         <v>535.3375423278808</v>
@@ -6165,84 +6187,84 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2 sep</t>
+          <t>3 sep</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>40.35</v>
+        <v>40.095</v>
       </c>
       <c r="C34" t="n">
-        <v>40.615</v>
+        <v>40.215</v>
       </c>
       <c r="D34" t="n">
-        <v>39.975</v>
+        <v>39.54</v>
       </c>
       <c r="E34" t="n">
-        <v>40.21</v>
+        <v>40.04</v>
       </c>
       <c r="F34" t="n">
-        <v>37.5499</v>
+        <v>37.6767</v>
       </c>
       <c r="G34" t="n">
-        <v>35.0217</v>
+        <v>35.0679</v>
       </c>
       <c r="H34" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I34" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2 sep</t>
+          <t>3 sep</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>182.18</v>
+        <v>182.08</v>
       </c>
       <c r="M34" t="n">
-        <v>184.7</v>
+        <v>187.56</v>
       </c>
       <c r="N34" t="n">
-        <v>180.72</v>
+        <v>182</v>
       </c>
       <c r="O34" t="n">
-        <v>181.44</v>
+        <v>185.58</v>
       </c>
       <c r="P34" t="n">
-        <v>159.2568</v>
+        <v>160.3228</v>
       </c>
       <c r="Q34" t="n">
-        <v>166.6796</v>
+        <v>166.5898</v>
       </c>
       <c r="R34" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S34" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>1 sep</t>
+          <t>2 sep</t>
         </is>
       </c>
       <c r="V34" t="n">
-        <v>497.52</v>
+        <v>499.85</v>
       </c>
       <c r="W34" t="n">
-        <v>505.97</v>
+        <v>500.27</v>
       </c>
       <c r="X34" t="n">
-        <v>496.78</v>
+        <v>493.81</v>
       </c>
       <c r="Y34" t="n">
-        <v>501.02</v>
+        <v>496.82</v>
       </c>
       <c r="Z34" t="n">
-        <v>435.2328</v>
+        <v>437.7045</v>
       </c>
       <c r="AA34" t="n">
-        <v>429.3825</v>
+        <v>429.3706</v>
       </c>
       <c r="AB34" t="n">
         <v>535.3375423278808</v>
@@ -6254,84 +6276,84 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3 sep</t>
+          <t>4 sep</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>40.095</v>
+        <v>40.145</v>
       </c>
       <c r="C35" t="n">
-        <v>40.215</v>
+        <v>40.28</v>
       </c>
       <c r="D35" t="n">
-        <v>39.54</v>
+        <v>39.665</v>
       </c>
       <c r="E35" t="n">
-        <v>40.04</v>
+        <v>40.105</v>
       </c>
       <c r="F35" t="n">
-        <v>37.6767</v>
+        <v>37.8115</v>
       </c>
       <c r="G35" t="n">
-        <v>35.0679</v>
+        <v>35.113</v>
       </c>
       <c r="H35" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I35" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>3 sep</t>
+          <t>4 sep</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>182.08</v>
+        <v>187.8</v>
       </c>
       <c r="M35" t="n">
-        <v>187.56</v>
+        <v>189.9</v>
       </c>
       <c r="N35" t="n">
-        <v>182</v>
+        <v>184.96</v>
       </c>
       <c r="O35" t="n">
-        <v>185.58</v>
+        <v>185.68</v>
       </c>
       <c r="P35" t="n">
-        <v>160.3228</v>
+        <v>161.3336</v>
       </c>
       <c r="Q35" t="n">
-        <v>166.5898</v>
+        <v>166.5086</v>
       </c>
       <c r="R35" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S35" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>2 sep</t>
+          <t>3 sep</t>
         </is>
       </c>
       <c r="V35" t="n">
-        <v>499.85</v>
+        <v>501.66</v>
       </c>
       <c r="W35" t="n">
-        <v>500.27</v>
+        <v>515.65</v>
       </c>
       <c r="X35" t="n">
-        <v>493.81</v>
+        <v>500.8</v>
       </c>
       <c r="Y35" t="n">
-        <v>496.82</v>
+        <v>510.12</v>
       </c>
       <c r="Z35" t="n">
-        <v>437.7045</v>
+        <v>440.6114</v>
       </c>
       <c r="AA35" t="n">
-        <v>429.3706</v>
+        <v>429.3912</v>
       </c>
       <c r="AB35" t="n">
         <v>535.3375423278808</v>
@@ -6343,84 +6365,84 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>4 sep</t>
+          <t>7 sep</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>40.145</v>
+        <v>40.26</v>
       </c>
       <c r="C36" t="n">
-        <v>40.28</v>
+        <v>40.845</v>
       </c>
       <c r="D36" t="n">
-        <v>39.665</v>
+        <v>40.12</v>
       </c>
       <c r="E36" t="n">
-        <v>40.105</v>
+        <v>40.56</v>
       </c>
       <c r="F36" t="n">
-        <v>37.8115</v>
+        <v>37.9551</v>
       </c>
       <c r="G36" t="n">
-        <v>35.113</v>
+        <v>35.1619</v>
       </c>
       <c r="H36" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I36" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>4 sep</t>
+          <t>7 sep</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>187.8</v>
+        <v>183.56</v>
       </c>
       <c r="M36" t="n">
-        <v>189.9</v>
+        <v>184.3</v>
       </c>
       <c r="N36" t="n">
-        <v>184.96</v>
+        <v>179.92</v>
       </c>
       <c r="O36" t="n">
-        <v>185.68</v>
+        <v>182.8</v>
       </c>
       <c r="P36" t="n">
-        <v>161.3336</v>
+        <v>162.2568</v>
       </c>
       <c r="Q36" t="n">
-        <v>166.5086</v>
+        <v>166.4122</v>
       </c>
       <c r="R36" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S36" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>3 sep</t>
+          <t>4 sep</t>
         </is>
       </c>
       <c r="V36" t="n">
-        <v>501.66</v>
+        <v>510</v>
       </c>
       <c r="W36" t="n">
-        <v>515.65</v>
+        <v>511</v>
       </c>
       <c r="X36" t="n">
-        <v>500.8</v>
+        <v>499.36</v>
       </c>
       <c r="Y36" t="n">
-        <v>510.12</v>
+        <v>499.7</v>
       </c>
       <c r="Z36" t="n">
-        <v>440.6114</v>
+        <v>443.5621</v>
       </c>
       <c r="AA36" t="n">
-        <v>429.3912</v>
+        <v>429.3729</v>
       </c>
       <c r="AB36" t="n">
         <v>535.3375423278808</v>
@@ -6432,84 +6454,84 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>7 sep</t>
+          <t>8 sep</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>40.26</v>
+        <v>40.83</v>
       </c>
       <c r="C37" t="n">
-        <v>40.845</v>
+        <v>41.18</v>
       </c>
       <c r="D37" t="n">
-        <v>40.12</v>
+        <v>40.6325</v>
       </c>
       <c r="E37" t="n">
-        <v>40.56</v>
+        <v>40.855</v>
       </c>
       <c r="F37" t="n">
-        <v>37.9551</v>
+        <v>38.0977</v>
       </c>
       <c r="G37" t="n">
-        <v>35.1619</v>
+        <v>35.2131</v>
       </c>
       <c r="H37" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I37" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>7 sep</t>
+          <t>8 sep</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>183.56</v>
+        <v>182.32</v>
       </c>
       <c r="M37" t="n">
-        <v>184.3</v>
+        <v>183.76</v>
       </c>
       <c r="N37" t="n">
-        <v>179.92</v>
+        <v>180.02</v>
       </c>
       <c r="O37" t="n">
-        <v>182.8</v>
+        <v>181.7</v>
       </c>
       <c r="P37" t="n">
-        <v>162.2568</v>
+        <v>163.2108</v>
       </c>
       <c r="Q37" t="n">
-        <v>166.4122</v>
+        <v>166.3049</v>
       </c>
       <c r="R37" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S37" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>4 sep</t>
+          <t>8 sep</t>
         </is>
       </c>
       <c r="V37" t="n">
-        <v>510</v>
+        <v>493.01</v>
       </c>
       <c r="W37" t="n">
-        <v>511</v>
+        <v>495.19</v>
       </c>
       <c r="X37" t="n">
-        <v>499.36</v>
+        <v>490.15</v>
       </c>
       <c r="Y37" t="n">
-        <v>499.7</v>
+        <v>493.95</v>
       </c>
       <c r="Z37" t="n">
-        <v>443.5621</v>
+        <v>445.9957</v>
       </c>
       <c r="AA37" t="n">
-        <v>429.3729</v>
+        <v>429.3939</v>
       </c>
       <c r="AB37" t="n">
         <v>535.3375423278808</v>
@@ -6521,84 +6543,84 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>8 sep</t>
+          <t>9 sep</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>40.83</v>
+        <v>41.1</v>
       </c>
       <c r="C38" t="n">
-        <v>41.18</v>
+        <v>41.385</v>
       </c>
       <c r="D38" t="n">
-        <v>40.6325</v>
+        <v>40.85</v>
       </c>
       <c r="E38" t="n">
-        <v>40.855</v>
+        <v>40.94</v>
       </c>
       <c r="F38" t="n">
-        <v>38.0977</v>
+        <v>38.2513</v>
       </c>
       <c r="G38" t="n">
-        <v>35.2131</v>
+        <v>35.2646</v>
       </c>
       <c r="H38" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I38" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>8 sep</t>
+          <t>9 sep</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>182.32</v>
+        <v>183</v>
       </c>
       <c r="M38" t="n">
-        <v>183.76</v>
+        <v>187.04</v>
       </c>
       <c r="N38" t="n">
-        <v>180.02</v>
+        <v>181.36</v>
       </c>
       <c r="O38" t="n">
-        <v>181.7</v>
+        <v>182.86</v>
       </c>
       <c r="P38" t="n">
-        <v>163.2108</v>
+        <v>164.0504</v>
       </c>
       <c r="Q38" t="n">
-        <v>166.3049</v>
+        <v>166.2113</v>
       </c>
       <c r="R38" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S38" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>8 sep</t>
+          <t>9 sep</t>
         </is>
       </c>
       <c r="V38" t="n">
-        <v>493.01</v>
+        <v>493.07</v>
       </c>
       <c r="W38" t="n">
-        <v>495.19</v>
+        <v>494.39</v>
       </c>
       <c r="X38" t="n">
-        <v>490.15</v>
+        <v>489.8</v>
       </c>
       <c r="Y38" t="n">
-        <v>493.95</v>
+        <v>491.65</v>
       </c>
       <c r="Z38" t="n">
-        <v>445.9957</v>
+        <v>448.4712</v>
       </c>
       <c r="AA38" t="n">
-        <v>429.3939</v>
+        <v>429.4364</v>
       </c>
       <c r="AB38" t="n">
         <v>535.3375423278808</v>
@@ -6610,84 +6632,84 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>9 sep</t>
+          <t>10 sep</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>41.1</v>
+        <v>40.98</v>
       </c>
       <c r="C39" t="n">
-        <v>41.385</v>
+        <v>41.77</v>
       </c>
       <c r="D39" t="n">
-        <v>40.85</v>
+        <v>40.93</v>
       </c>
       <c r="E39" t="n">
-        <v>40.94</v>
+        <v>41.23</v>
       </c>
       <c r="F39" t="n">
-        <v>38.2513</v>
+        <v>38.4034</v>
       </c>
       <c r="G39" t="n">
-        <v>35.2646</v>
+        <v>35.3174</v>
       </c>
       <c r="H39" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I39" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>9 sep</t>
+          <t>10 sep</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="M39" t="n">
-        <v>187.04</v>
+        <v>180.4</v>
       </c>
       <c r="N39" t="n">
-        <v>181.36</v>
+        <v>176.2</v>
       </c>
       <c r="O39" t="n">
-        <v>182.86</v>
+        <v>177.82</v>
       </c>
       <c r="P39" t="n">
-        <v>164.0504</v>
+        <v>164.7724</v>
       </c>
       <c r="Q39" t="n">
-        <v>166.2113</v>
+        <v>166.0803</v>
       </c>
       <c r="R39" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S39" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>9 sep</t>
+          <t>10 sep</t>
         </is>
       </c>
       <c r="V39" t="n">
-        <v>493.07</v>
+        <v>488.32</v>
       </c>
       <c r="W39" t="n">
-        <v>494.39</v>
+        <v>494.52</v>
       </c>
       <c r="X39" t="n">
-        <v>489.8</v>
+        <v>486</v>
       </c>
       <c r="Y39" t="n">
-        <v>491.65</v>
+        <v>492.44</v>
       </c>
       <c r="Z39" t="n">
-        <v>448.4712</v>
+        <v>450.8736</v>
       </c>
       <c r="AA39" t="n">
-        <v>429.4364</v>
+        <v>429.5215</v>
       </c>
       <c r="AB39" t="n">
         <v>535.3375423278808</v>
@@ -6699,84 +6721,84 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10 sep</t>
+          <t>11 sep</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>40.98</v>
+        <v>41.345</v>
       </c>
       <c r="C40" t="n">
-        <v>41.77</v>
+        <v>41.715</v>
       </c>
       <c r="D40" t="n">
-        <v>40.93</v>
+        <v>40.905</v>
       </c>
       <c r="E40" t="n">
-        <v>41.23</v>
+        <v>41.415</v>
       </c>
       <c r="F40" t="n">
-        <v>38.4034</v>
+        <v>38.5608</v>
       </c>
       <c r="G40" t="n">
-        <v>35.3174</v>
+        <v>35.3717</v>
       </c>
       <c r="H40" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I40" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>10 sep</t>
+          <t>11 sep</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>180</v>
+        <v>175.68</v>
       </c>
       <c r="M40" t="n">
-        <v>180.4</v>
+        <v>178.84</v>
       </c>
       <c r="N40" t="n">
-        <v>176.2</v>
+        <v>172.16</v>
       </c>
       <c r="O40" t="n">
-        <v>177.82</v>
+        <v>177.26</v>
       </c>
       <c r="P40" t="n">
-        <v>164.7724</v>
+        <v>165.5248</v>
       </c>
       <c r="Q40" t="n">
-        <v>166.0803</v>
+        <v>165.9594</v>
       </c>
       <c r="R40" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S40" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>10 sep</t>
+          <t>11 sep</t>
         </is>
       </c>
       <c r="V40" t="n">
-        <v>488.32</v>
+        <v>495.65</v>
       </c>
       <c r="W40" t="n">
-        <v>494.52</v>
+        <v>498.97</v>
       </c>
       <c r="X40" t="n">
-        <v>486</v>
+        <v>492.58</v>
       </c>
       <c r="Y40" t="n">
-        <v>492.44</v>
+        <v>495.63</v>
       </c>
       <c r="Z40" t="n">
-        <v>450.8736</v>
+        <v>453.115</v>
       </c>
       <c r="AA40" t="n">
-        <v>429.5215</v>
+        <v>429.654</v>
       </c>
       <c r="AB40" t="n">
         <v>535.3375423278808</v>
@@ -6788,84 +6810,84 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>11 sep</t>
+          <t>14 sep</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>41.345</v>
+        <v>41.88</v>
       </c>
       <c r="C41" t="n">
-        <v>41.715</v>
+        <v>42.285</v>
       </c>
       <c r="D41" t="n">
-        <v>40.905</v>
+        <v>41.8</v>
       </c>
       <c r="E41" t="n">
-        <v>41.415</v>
+        <v>41.91</v>
       </c>
       <c r="F41" t="n">
-        <v>38.5608</v>
+        <v>38.7226</v>
       </c>
       <c r="G41" t="n">
-        <v>35.3717</v>
+        <v>35.4269</v>
       </c>
       <c r="H41" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I41" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>11 sep</t>
+          <t>14 sep</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>175.68</v>
+        <v>180.82</v>
       </c>
       <c r="M41" t="n">
-        <v>178.84</v>
+        <v>186.76</v>
       </c>
       <c r="N41" t="n">
-        <v>172.16</v>
+        <v>180.82</v>
       </c>
       <c r="O41" t="n">
-        <v>177.26</v>
+        <v>186.26</v>
       </c>
       <c r="P41" t="n">
-        <v>165.5248</v>
+        <v>166.4488</v>
       </c>
       <c r="Q41" t="n">
-        <v>165.9594</v>
+        <v>165.8745</v>
       </c>
       <c r="R41" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S41" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>11 sep</t>
+          <t>14 sep</t>
         </is>
       </c>
       <c r="V41" t="n">
-        <v>495.65</v>
+        <v>497.06</v>
       </c>
       <c r="W41" t="n">
-        <v>498.97</v>
+        <v>509.95</v>
       </c>
       <c r="X41" t="n">
-        <v>492.58</v>
+        <v>495.34</v>
       </c>
       <c r="Y41" t="n">
-        <v>495.63</v>
+        <v>505.41</v>
       </c>
       <c r="Z41" t="n">
-        <v>453.115</v>
+        <v>455.4281</v>
       </c>
       <c r="AA41" t="n">
-        <v>429.654</v>
+        <v>429.8259</v>
       </c>
       <c r="AB41" t="n">
         <v>535.3375423278808</v>
@@ -6877,84 +6899,84 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>14 sep</t>
+          <t>15 sep</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>41.88</v>
+        <v>41.845</v>
       </c>
       <c r="C42" t="n">
-        <v>42.285</v>
+        <v>42.7</v>
       </c>
       <c r="D42" t="n">
-        <v>41.8</v>
+        <v>41.72</v>
       </c>
       <c r="E42" t="n">
-        <v>41.91</v>
+        <v>42.7</v>
       </c>
       <c r="F42" t="n">
-        <v>38.7226</v>
+        <v>38.8782</v>
       </c>
       <c r="G42" t="n">
-        <v>35.4269</v>
+        <v>35.4854</v>
       </c>
       <c r="H42" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I42" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>14 sep</t>
+          <t>15 sep</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>180.82</v>
+        <v>186.64</v>
       </c>
       <c r="M42" t="n">
-        <v>186.76</v>
+        <v>187.26</v>
       </c>
       <c r="N42" t="n">
-        <v>180.82</v>
+        <v>183.2</v>
       </c>
       <c r="O42" t="n">
-        <v>186.26</v>
+        <v>187.08</v>
       </c>
       <c r="P42" t="n">
-        <v>166.4488</v>
+        <v>167.3124</v>
       </c>
       <c r="Q42" t="n">
-        <v>165.8745</v>
+        <v>165.7921</v>
       </c>
       <c r="R42" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S42" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>14 sep</t>
+          <t>15 sep</t>
         </is>
       </c>
       <c r="V42" t="n">
-        <v>497.06</v>
+        <v>500.06</v>
       </c>
       <c r="W42" t="n">
-        <v>509.95</v>
+        <v>505.9</v>
       </c>
       <c r="X42" t="n">
-        <v>495.34</v>
+        <v>495.54</v>
       </c>
       <c r="Y42" t="n">
-        <v>505.41</v>
+        <v>497.12</v>
       </c>
       <c r="Z42" t="n">
-        <v>455.4281</v>
+        <v>457.6502</v>
       </c>
       <c r="AA42" t="n">
-        <v>429.8259</v>
+        <v>429.9416</v>
       </c>
       <c r="AB42" t="n">
         <v>535.3375423278808</v>
@@ -6966,84 +6988,84 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>15 sep</t>
+          <t>16 sep</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>41.845</v>
+        <v>42.72</v>
       </c>
       <c r="C43" t="n">
-        <v>42.7</v>
+        <v>42.85</v>
       </c>
       <c r="D43" t="n">
-        <v>41.72</v>
+        <v>41.67</v>
       </c>
       <c r="E43" t="n">
-        <v>42.7</v>
+        <v>41.825</v>
       </c>
       <c r="F43" t="n">
-        <v>38.8782</v>
+        <v>38.9989</v>
       </c>
       <c r="G43" t="n">
-        <v>35.4854</v>
+        <v>35.5403</v>
       </c>
       <c r="H43" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I43" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>15 sep</t>
+          <t>16 sep</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>186.64</v>
+        <v>185.86</v>
       </c>
       <c r="M43" t="n">
-        <v>187.26</v>
+        <v>186.76</v>
       </c>
       <c r="N43" t="n">
-        <v>183.2</v>
+        <v>182.18</v>
       </c>
       <c r="O43" t="n">
-        <v>187.08</v>
+        <v>186.56</v>
       </c>
       <c r="P43" t="n">
-        <v>167.3124</v>
+        <v>168.2844</v>
       </c>
       <c r="Q43" t="n">
-        <v>165.7921</v>
+        <v>165.6996</v>
       </c>
       <c r="R43" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S43" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>15 sep</t>
+          <t>16 sep</t>
         </is>
       </c>
       <c r="V43" t="n">
-        <v>500.06</v>
+        <v>493.03</v>
       </c>
       <c r="W43" t="n">
-        <v>505.9</v>
+        <v>495.97</v>
       </c>
       <c r="X43" t="n">
-        <v>495.54</v>
+        <v>487.23</v>
       </c>
       <c r="Y43" t="n">
-        <v>497.12</v>
+        <v>490.3</v>
       </c>
       <c r="Z43" t="n">
-        <v>457.6502</v>
+        <v>459.694</v>
       </c>
       <c r="AA43" t="n">
-        <v>429.9416</v>
+        <v>429.9809</v>
       </c>
       <c r="AB43" t="n">
         <v>535.3375423278808</v>
@@ -7055,84 +7077,84 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>16 sep</t>
+          <t>17 sep</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>42.72</v>
+        <v>41.58</v>
       </c>
       <c r="C44" t="n">
-        <v>42.85</v>
+        <v>42.055</v>
       </c>
       <c r="D44" t="n">
-        <v>41.67</v>
+        <v>41.38</v>
       </c>
       <c r="E44" t="n">
-        <v>41.825</v>
+        <v>41.56</v>
       </c>
       <c r="F44" t="n">
-        <v>38.9989</v>
+        <v>39.1225</v>
       </c>
       <c r="G44" t="n">
-        <v>35.5403</v>
+        <v>35.5926</v>
       </c>
       <c r="H44" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I44" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>16 sep</t>
+          <t>17 sep</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>185.86</v>
+        <v>188.54</v>
       </c>
       <c r="M44" t="n">
-        <v>186.76</v>
+        <v>189.2</v>
       </c>
       <c r="N44" t="n">
-        <v>182.18</v>
+        <v>184.62</v>
       </c>
       <c r="O44" t="n">
-        <v>186.56</v>
+        <v>188</v>
       </c>
       <c r="P44" t="n">
-        <v>168.2844</v>
+        <v>169.2896</v>
       </c>
       <c r="Q44" t="n">
-        <v>165.6996</v>
+        <v>165.6125</v>
       </c>
       <c r="R44" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S44" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>16 sep</t>
+          <t>17 sep</t>
         </is>
       </c>
       <c r="V44" t="n">
-        <v>493.03</v>
+        <v>497.8</v>
       </c>
       <c r="W44" t="n">
-        <v>495.97</v>
+        <v>501.47</v>
       </c>
       <c r="X44" t="n">
-        <v>487.23</v>
+        <v>493.17</v>
       </c>
       <c r="Y44" t="n">
-        <v>490.3</v>
+        <v>497.75</v>
       </c>
       <c r="Z44" t="n">
-        <v>459.694</v>
+        <v>461.9966</v>
       </c>
       <c r="AA44" t="n">
-        <v>429.9809</v>
+        <v>430.0251</v>
       </c>
       <c r="AB44" t="n">
         <v>535.3375423278808</v>
@@ -7144,84 +7166,84 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>17 sep</t>
+          <t>18 sep</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>41.58</v>
+        <v>41.465</v>
       </c>
       <c r="C45" t="n">
-        <v>42.055</v>
+        <v>41.5</v>
       </c>
       <c r="D45" t="n">
-        <v>41.38</v>
+        <v>40.955</v>
       </c>
       <c r="E45" t="n">
-        <v>41.56</v>
+        <v>41.315</v>
       </c>
       <c r="F45" t="n">
-        <v>39.1225</v>
+        <v>39.2414</v>
       </c>
       <c r="G45" t="n">
-        <v>35.5926</v>
+        <v>35.6436</v>
       </c>
       <c r="H45" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I45" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>17 sep</t>
+          <t>18 sep</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>188.54</v>
+        <v>186.1</v>
       </c>
       <c r="M45" t="n">
-        <v>189.2</v>
+        <v>187.26</v>
       </c>
       <c r="N45" t="n">
-        <v>184.62</v>
+        <v>182.56</v>
       </c>
       <c r="O45" t="n">
-        <v>188</v>
+        <v>183.12</v>
       </c>
       <c r="P45" t="n">
-        <v>169.2896</v>
+        <v>170.2004</v>
       </c>
       <c r="Q45" t="n">
-        <v>165.6125</v>
+        <v>165.5062</v>
       </c>
       <c r="R45" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S45" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>17 sep</t>
+          <t>18 sep</t>
         </is>
       </c>
       <c r="V45" t="n">
-        <v>497.8</v>
+        <v>497.97</v>
       </c>
       <c r="W45" t="n">
-        <v>501.47</v>
+        <v>498.65</v>
       </c>
       <c r="X45" t="n">
-        <v>493.17</v>
+        <v>491.1</v>
       </c>
       <c r="Y45" t="n">
-        <v>497.75</v>
+        <v>493.78</v>
       </c>
       <c r="Z45" t="n">
-        <v>461.9966</v>
+        <v>464.1995</v>
       </c>
       <c r="AA45" t="n">
-        <v>430.0251</v>
+        <v>430.0757</v>
       </c>
       <c r="AB45" t="n">
         <v>535.3375423278808</v>
@@ -7233,84 +7255,84 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>18 sep</t>
+          <t>21 sep</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>41.465</v>
+        <v>41.04</v>
       </c>
       <c r="C46" t="n">
-        <v>41.5</v>
+        <v>41.4</v>
       </c>
       <c r="D46" t="n">
-        <v>40.955</v>
+        <v>40.775</v>
       </c>
       <c r="E46" t="n">
-        <v>41.315</v>
+        <v>40.775</v>
       </c>
       <c r="F46" t="n">
-        <v>39.2414</v>
+        <v>39.3341</v>
       </c>
       <c r="G46" t="n">
-        <v>35.6436</v>
+        <v>35.6939</v>
       </c>
       <c r="H46" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I46" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>18 sep</t>
+          <t>21 sep</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>186.1</v>
+        <v>184.7</v>
       </c>
       <c r="M46" t="n">
-        <v>187.26</v>
+        <v>185.86</v>
       </c>
       <c r="N46" t="n">
-        <v>182.56</v>
+        <v>182.48</v>
       </c>
       <c r="O46" t="n">
-        <v>183.12</v>
+        <v>182.86</v>
       </c>
       <c r="P46" t="n">
-        <v>170.2004</v>
+        <v>171.0432</v>
       </c>
       <c r="Q46" t="n">
-        <v>165.5062</v>
+        <v>165.4052</v>
       </c>
       <c r="R46" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S46" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>18 sep</t>
+          <t>21 sep</t>
         </is>
       </c>
       <c r="V46" t="n">
-        <v>497.97</v>
+        <v>494.95</v>
       </c>
       <c r="W46" t="n">
-        <v>498.65</v>
+        <v>501.87</v>
       </c>
       <c r="X46" t="n">
-        <v>491.1</v>
+        <v>491.33</v>
       </c>
       <c r="Y46" t="n">
-        <v>493.78</v>
+        <v>501.61</v>
       </c>
       <c r="Z46" t="n">
-        <v>464.1995</v>
+        <v>466.5442</v>
       </c>
       <c r="AA46" t="n">
-        <v>430.0757</v>
+        <v>430.1492</v>
       </c>
       <c r="AB46" t="n">
         <v>535.3375423278808</v>
@@ -7322,84 +7344,84 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>21 sep</t>
+          <t>22 sep</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>41.04</v>
+        <v>40.84</v>
       </c>
       <c r="C47" t="n">
-        <v>41.4</v>
+        <v>41.165</v>
       </c>
       <c r="D47" t="n">
-        <v>40.775</v>
+        <v>40.215</v>
       </c>
       <c r="E47" t="n">
-        <v>40.775</v>
+        <v>41.01</v>
       </c>
       <c r="F47" t="n">
-        <v>39.3341</v>
+        <v>39.4244</v>
       </c>
       <c r="G47" t="n">
-        <v>35.6939</v>
+        <v>35.746</v>
       </c>
       <c r="H47" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I47" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>21 sep</t>
+          <t>22 sep</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>184.7</v>
+        <v>182.14</v>
       </c>
       <c r="M47" t="n">
-        <v>185.86</v>
+        <v>187.48</v>
       </c>
       <c r="N47" t="n">
-        <v>182.48</v>
+        <v>181.52</v>
       </c>
       <c r="O47" t="n">
-        <v>182.86</v>
+        <v>182.32</v>
       </c>
       <c r="P47" t="n">
-        <v>171.0432</v>
+        <v>171.9552</v>
       </c>
       <c r="Q47" t="n">
-        <v>165.4052</v>
+        <v>165.2836</v>
       </c>
       <c r="R47" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S47" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>21 sep</t>
+          <t>22 sep</t>
         </is>
       </c>
       <c r="V47" t="n">
-        <v>494.95</v>
+        <v>507.32</v>
       </c>
       <c r="W47" t="n">
-        <v>501.87</v>
+        <v>508.5</v>
       </c>
       <c r="X47" t="n">
-        <v>491.33</v>
+        <v>493.65</v>
       </c>
       <c r="Y47" t="n">
-        <v>501.61</v>
+        <v>498</v>
       </c>
       <c r="Z47" t="n">
-        <v>466.5442</v>
+        <v>468.699</v>
       </c>
       <c r="AA47" t="n">
-        <v>430.1492</v>
+        <v>430.2656</v>
       </c>
       <c r="AB47" t="n">
         <v>535.3375423278808</v>
@@ -7411,84 +7433,84 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>22 sep</t>
+          <t>23 sep</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>40.84</v>
+        <v>41</v>
       </c>
       <c r="C48" t="n">
-        <v>41.165</v>
+        <v>41.755</v>
       </c>
       <c r="D48" t="n">
-        <v>40.215</v>
+        <v>40.995</v>
       </c>
       <c r="E48" t="n">
-        <v>41.01</v>
+        <v>41.69</v>
       </c>
       <c r="F48" t="n">
-        <v>39.4244</v>
+        <v>39.5272</v>
       </c>
       <c r="G48" t="n">
-        <v>35.746</v>
+        <v>35.8024</v>
       </c>
       <c r="H48" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I48" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>22 sep</t>
+          <t>23 sep</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>182.14</v>
+        <v>184.9</v>
       </c>
       <c r="M48" t="n">
-        <v>187.48</v>
+        <v>187.8</v>
       </c>
       <c r="N48" t="n">
-        <v>181.52</v>
+        <v>183.48</v>
       </c>
       <c r="O48" t="n">
-        <v>182.32</v>
+        <v>186.46</v>
       </c>
       <c r="P48" t="n">
-        <v>171.9552</v>
+        <v>172.9448</v>
       </c>
       <c r="Q48" t="n">
-        <v>165.2836</v>
+        <v>165.1675</v>
       </c>
       <c r="R48" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S48" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>22 sep</t>
+          <t>23 sep</t>
         </is>
       </c>
       <c r="V48" t="n">
-        <v>507.32</v>
+        <v>500.76</v>
       </c>
       <c r="W48" t="n">
-        <v>508.5</v>
+        <v>509.44</v>
       </c>
       <c r="X48" t="n">
-        <v>493.65</v>
+        <v>495.88</v>
       </c>
       <c r="Y48" t="n">
-        <v>498</v>
+        <v>500.59</v>
       </c>
       <c r="Z48" t="n">
-        <v>468.699</v>
+        <v>471.0267</v>
       </c>
       <c r="AA48" t="n">
-        <v>430.2656</v>
+        <v>430.3795</v>
       </c>
       <c r="AB48" t="n">
         <v>535.3375423278808</v>
@@ -7500,84 +7522,84 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>23 sep</t>
+          <t>24 sep</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>41</v>
+        <v>41.825</v>
       </c>
       <c r="C49" t="n">
-        <v>41.755</v>
+        <v>42.52</v>
       </c>
       <c r="D49" t="n">
-        <v>40.995</v>
+        <v>41.78</v>
       </c>
       <c r="E49" t="n">
-        <v>41.69</v>
+        <v>42.43</v>
       </c>
       <c r="F49" t="n">
-        <v>39.5272</v>
+        <v>39.6382</v>
       </c>
       <c r="G49" t="n">
-        <v>35.8024</v>
+        <v>35.8638</v>
       </c>
       <c r="H49" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I49" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>23 sep</t>
+          <t>24 sep</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>184.9</v>
+        <v>184.52</v>
       </c>
       <c r="M49" t="n">
-        <v>187.8</v>
+        <v>185.5</v>
       </c>
       <c r="N49" t="n">
-        <v>183.48</v>
+        <v>182.26</v>
       </c>
       <c r="O49" t="n">
-        <v>186.46</v>
+        <v>184.18</v>
       </c>
       <c r="P49" t="n">
-        <v>172.9448</v>
+        <v>173.8756</v>
       </c>
       <c r="Q49" t="n">
-        <v>165.1675</v>
+        <v>165.0554</v>
       </c>
       <c r="R49" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S49" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>23 sep</t>
+          <t>24 sep</t>
         </is>
       </c>
       <c r="V49" t="n">
-        <v>500.76</v>
+        <v>495.07</v>
       </c>
       <c r="W49" t="n">
-        <v>509.44</v>
+        <v>498.9</v>
       </c>
       <c r="X49" t="n">
-        <v>495.88</v>
+        <v>491.22</v>
       </c>
       <c r="Y49" t="n">
-        <v>500.59</v>
+        <v>497.93</v>
       </c>
       <c r="Z49" t="n">
-        <v>471.0267</v>
+        <v>473.0876</v>
       </c>
       <c r="AA49" t="n">
-        <v>430.3795</v>
+        <v>430.4686</v>
       </c>
       <c r="AB49" t="n">
         <v>535.3375423278808</v>
@@ -7589,84 +7611,84 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>24 sep</t>
+          <t>25 sep</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>41.825</v>
+        <v>41.99</v>
       </c>
       <c r="C50" t="n">
-        <v>42.52</v>
+        <v>42.33</v>
       </c>
       <c r="D50" t="n">
-        <v>41.78</v>
+        <v>41.71</v>
       </c>
       <c r="E50" t="n">
-        <v>42.43</v>
+        <v>42.06</v>
       </c>
       <c r="F50" t="n">
-        <v>39.6382</v>
+        <v>39.7263</v>
       </c>
       <c r="G50" t="n">
-        <v>35.8638</v>
+        <v>35.9239</v>
       </c>
       <c r="H50" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I50" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>24 sep</t>
+          <t>25 sep</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>184.52</v>
+        <v>184.42</v>
       </c>
       <c r="M50" t="n">
-        <v>185.5</v>
+        <v>185.92</v>
       </c>
       <c r="N50" t="n">
-        <v>182.26</v>
+        <v>183.76</v>
       </c>
       <c r="O50" t="n">
-        <v>184.18</v>
+        <v>185.92</v>
       </c>
       <c r="P50" t="n">
-        <v>173.8756</v>
+        <v>174.8356</v>
       </c>
       <c r="Q50" t="n">
-        <v>165.0554</v>
+        <v>164.9525</v>
       </c>
       <c r="R50" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S50" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>24 sep</t>
+          <t>25 sep</t>
         </is>
       </c>
       <c r="V50" t="n">
-        <v>495.07</v>
+        <v>499.04</v>
       </c>
       <c r="W50" t="n">
-        <v>498.9</v>
+        <v>519.4</v>
       </c>
       <c r="X50" t="n">
-        <v>491.22</v>
+        <v>497.25</v>
       </c>
       <c r="Y50" t="n">
-        <v>497.93</v>
+        <v>516.17</v>
       </c>
       <c r="Z50" t="n">
-        <v>473.0876</v>
+        <v>475.4041</v>
       </c>
       <c r="AA50" t="n">
-        <v>430.4686</v>
+        <v>430.6098</v>
       </c>
       <c r="AB50" t="n">
         <v>535.3375423278808</v>
@@ -7678,84 +7700,84 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>25 sep</t>
+          <t>28 sep</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>41.99</v>
+        <v>42.45</v>
       </c>
       <c r="C51" t="n">
-        <v>42.33</v>
+        <v>42.995</v>
       </c>
       <c r="D51" t="n">
-        <v>41.71</v>
+        <v>42.38</v>
       </c>
       <c r="E51" t="n">
-        <v>42.06</v>
+        <v>42.725</v>
       </c>
       <c r="F51" t="n">
-        <v>39.7263</v>
+        <v>39.8301</v>
       </c>
       <c r="G51" t="n">
-        <v>35.9239</v>
+        <v>35.9888</v>
       </c>
       <c r="H51" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I51" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>25 sep</t>
+          <t>28 sep</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>184.42</v>
+        <v>185.2</v>
       </c>
       <c r="M51" t="n">
-        <v>185.92</v>
+        <v>186.76</v>
       </c>
       <c r="N51" t="n">
-        <v>183.76</v>
+        <v>178.88</v>
       </c>
       <c r="O51" t="n">
-        <v>185.92</v>
+        <v>184.02</v>
       </c>
       <c r="P51" t="n">
-        <v>174.8356</v>
+        <v>175.7508</v>
       </c>
       <c r="Q51" t="n">
-        <v>164.9525</v>
+        <v>164.8355</v>
       </c>
       <c r="R51" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S51" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>25 sep</t>
+          <t>28 sep</t>
         </is>
       </c>
       <c r="V51" t="n">
-        <v>499.04</v>
+        <v>505.47</v>
       </c>
       <c r="W51" t="n">
-        <v>519.4</v>
+        <v>513.33</v>
       </c>
       <c r="X51" t="n">
-        <v>497.25</v>
+        <v>502.22</v>
       </c>
       <c r="Y51" t="n">
-        <v>516.17</v>
+        <v>509.22</v>
       </c>
       <c r="Z51" t="n">
-        <v>475.4041</v>
+        <v>477.7269</v>
       </c>
       <c r="AA51" t="n">
-        <v>430.6098</v>
+        <v>430.7113</v>
       </c>
       <c r="AB51" t="n">
         <v>535.3375423278808</v>
@@ -7767,84 +7789,84 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>28 sep</t>
+          <t>29 sep</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>42.45</v>
+        <v>42.57</v>
       </c>
       <c r="C52" t="n">
-        <v>42.995</v>
+        <v>42.665</v>
       </c>
       <c r="D52" t="n">
-        <v>42.38</v>
+        <v>41.73</v>
       </c>
       <c r="E52" t="n">
-        <v>42.725</v>
+        <v>42.05</v>
       </c>
       <c r="F52" t="n">
-        <v>39.8301</v>
+        <v>39.9146</v>
       </c>
       <c r="G52" t="n">
-        <v>35.9888</v>
+        <v>36.0498</v>
       </c>
       <c r="H52" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I52" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>28 sep</t>
+          <t>29 sep</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>185.2</v>
+        <v>183.22</v>
       </c>
       <c r="M52" t="n">
-        <v>186.76</v>
+        <v>186.34</v>
       </c>
       <c r="N52" t="n">
-        <v>178.88</v>
+        <v>182.28</v>
       </c>
       <c r="O52" t="n">
-        <v>184.02</v>
+        <v>185.32</v>
       </c>
       <c r="P52" t="n">
-        <v>175.7508</v>
+        <v>176.7288</v>
       </c>
       <c r="Q52" t="n">
-        <v>164.8355</v>
+        <v>164.733</v>
       </c>
       <c r="R52" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S52" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>28 sep</t>
+          <t>29 sep</t>
         </is>
       </c>
       <c r="V52" t="n">
-        <v>505.47</v>
+        <v>508.31</v>
       </c>
       <c r="W52" t="n">
-        <v>513.33</v>
+        <v>513.64</v>
       </c>
       <c r="X52" t="n">
-        <v>502.22</v>
+        <v>502.4</v>
       </c>
       <c r="Y52" t="n">
-        <v>509.22</v>
+        <v>508.96</v>
       </c>
       <c r="Z52" t="n">
-        <v>477.7269</v>
+        <v>479.8754</v>
       </c>
       <c r="AA52" t="n">
-        <v>430.7113</v>
+        <v>430.8784</v>
       </c>
       <c r="AB52" t="n">
         <v>535.3375423278808</v>
@@ -7856,84 +7878,84 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>29 sep</t>
+          <t>30 sep</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>42.57</v>
+        <v>41.975</v>
       </c>
       <c r="C53" t="n">
-        <v>42.665</v>
+        <v>42.095</v>
       </c>
       <c r="D53" t="n">
-        <v>41.73</v>
+        <v>41.58</v>
       </c>
       <c r="E53" t="n">
-        <v>42.05</v>
+        <v>41.91</v>
       </c>
       <c r="F53" t="n">
-        <v>39.9146</v>
+        <v>39.9874</v>
       </c>
       <c r="G53" t="n">
-        <v>36.0498</v>
+        <v>36.1135</v>
       </c>
       <c r="H53" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I53" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>29 sep</t>
+          <t>30 sep</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>183.22</v>
+        <v>184.5</v>
       </c>
       <c r="M53" t="n">
-        <v>186.34</v>
+        <v>186.2</v>
       </c>
       <c r="N53" t="n">
-        <v>182.28</v>
+        <v>181.06</v>
       </c>
       <c r="O53" t="n">
-        <v>185.32</v>
+        <v>185.66</v>
       </c>
       <c r="P53" t="n">
-        <v>176.7288</v>
+        <v>177.8012</v>
       </c>
       <c r="Q53" t="n">
-        <v>164.733</v>
+        <v>164.6377</v>
       </c>
       <c r="R53" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S53" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>29 sep</t>
+          <t>30 sep</t>
         </is>
       </c>
       <c r="V53" t="n">
-        <v>508.31</v>
+        <v>511.61</v>
       </c>
       <c r="W53" t="n">
-        <v>513.64</v>
+        <v>519.83</v>
       </c>
       <c r="X53" t="n">
-        <v>502.4</v>
+        <v>510.31</v>
       </c>
       <c r="Y53" t="n">
-        <v>508.96</v>
+        <v>512.9</v>
       </c>
       <c r="Z53" t="n">
-        <v>479.8754</v>
+        <v>482.1933</v>
       </c>
       <c r="AA53" t="n">
-        <v>430.8784</v>
+        <v>431.0408</v>
       </c>
       <c r="AB53" t="n">
         <v>535.3375423278808</v>
@@ -7945,84 +7967,84 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>30 sep</t>
+          <t>1 okt</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>41.975</v>
+        <v>41.625</v>
       </c>
       <c r="C54" t="n">
-        <v>42.095</v>
+        <v>42.36</v>
       </c>
       <c r="D54" t="n">
-        <v>41.58</v>
+        <v>41.165</v>
       </c>
       <c r="E54" t="n">
-        <v>41.91</v>
+        <v>42.24</v>
       </c>
       <c r="F54" t="n">
-        <v>39.9874</v>
+        <v>40.0562</v>
       </c>
       <c r="G54" t="n">
-        <v>36.1135</v>
+        <v>36.1777</v>
       </c>
       <c r="H54" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I54" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>30 sep</t>
+          <t>1 okt</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>184.5</v>
+        <v>184.68</v>
       </c>
       <c r="M54" t="n">
-        <v>186.2</v>
+        <v>190.26</v>
       </c>
       <c r="N54" t="n">
-        <v>181.06</v>
+        <v>181.34</v>
       </c>
       <c r="O54" t="n">
-        <v>185.66</v>
+        <v>186.74</v>
       </c>
       <c r="P54" t="n">
-        <v>177.8012</v>
+        <v>178.9696</v>
       </c>
       <c r="Q54" t="n">
-        <v>164.6377</v>
+        <v>164.5407</v>
       </c>
       <c r="R54" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S54" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>30 sep</t>
+          <t>1 okt</t>
         </is>
       </c>
       <c r="V54" t="n">
-        <v>511.61</v>
+        <v>519.88</v>
       </c>
       <c r="W54" t="n">
-        <v>519.83</v>
+        <v>522.85</v>
       </c>
       <c r="X54" t="n">
-        <v>510.31</v>
+        <v>512.17</v>
       </c>
       <c r="Y54" t="n">
-        <v>512.9</v>
+        <v>512.8</v>
       </c>
       <c r="Z54" t="n">
-        <v>482.1933</v>
+        <v>484.6572</v>
       </c>
       <c r="AA54" t="n">
-        <v>431.0408</v>
+        <v>431.2272</v>
       </c>
       <c r="AB54" t="n">
         <v>535.3375423278808</v>
@@ -8034,84 +8056,84 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1 okt</t>
+          <t>2 okt</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>41.625</v>
+        <v>42.11</v>
       </c>
       <c r="C55" t="n">
-        <v>42.36</v>
+        <v>42.745</v>
       </c>
       <c r="D55" t="n">
-        <v>41.165</v>
+        <v>41.985</v>
       </c>
       <c r="E55" t="n">
-        <v>42.24</v>
+        <v>42.4</v>
       </c>
       <c r="F55" t="n">
-        <v>40.0562</v>
+        <v>40.1364</v>
       </c>
       <c r="G55" t="n">
-        <v>36.1777</v>
+        <v>36.2422</v>
       </c>
       <c r="H55" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I55" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>1 okt</t>
+          <t>2 okt</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>184.68</v>
+        <v>187.82</v>
       </c>
       <c r="M55" t="n">
-        <v>190.26</v>
+        <v>188.74</v>
       </c>
       <c r="N55" t="n">
-        <v>181.34</v>
+        <v>183.92</v>
       </c>
       <c r="O55" t="n">
-        <v>186.74</v>
+        <v>183.92</v>
       </c>
       <c r="P55" t="n">
-        <v>178.9696</v>
+        <v>179.844</v>
       </c>
       <c r="Q55" t="n">
-        <v>164.5407</v>
+        <v>164.4442</v>
       </c>
       <c r="R55" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S55" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>1 okt</t>
+          <t>2 okt</t>
         </is>
       </c>
       <c r="V55" t="n">
-        <v>519.88</v>
+        <v>519.39</v>
       </c>
       <c r="W55" t="n">
-        <v>522.85</v>
+        <v>522.5</v>
       </c>
       <c r="X55" t="n">
-        <v>512.17</v>
+        <v>513.66</v>
       </c>
       <c r="Y55" t="n">
-        <v>512.8</v>
+        <v>517.53</v>
       </c>
       <c r="Z55" t="n">
-        <v>484.6572</v>
+        <v>487.3905</v>
       </c>
       <c r="AA55" t="n">
-        <v>431.2272</v>
+        <v>431.4557</v>
       </c>
       <c r="AB55" t="n">
         <v>535.3375423278808</v>
@@ -8123,84 +8145,84 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2 okt</t>
+          <t>5 okt</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>42.11</v>
+        <v>42.645</v>
       </c>
       <c r="C56" t="n">
-        <v>42.745</v>
+        <v>43.11</v>
       </c>
       <c r="D56" t="n">
-        <v>41.985</v>
+        <v>42.35</v>
       </c>
       <c r="E56" t="n">
-        <v>42.4</v>
+        <v>42.865</v>
       </c>
       <c r="F56" t="n">
-        <v>40.1364</v>
+        <v>40.2347</v>
       </c>
       <c r="G56" t="n">
-        <v>36.2422</v>
+        <v>36.3069</v>
       </c>
       <c r="H56" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I56" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2 okt</t>
+          <t>5 okt</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>187.82</v>
+        <v>185.06</v>
       </c>
       <c r="M56" t="n">
-        <v>188.74</v>
+        <v>188.5</v>
       </c>
       <c r="N56" t="n">
-        <v>183.92</v>
+        <v>184.66</v>
       </c>
       <c r="O56" t="n">
-        <v>183.92</v>
+        <v>185.04</v>
       </c>
       <c r="P56" t="n">
-        <v>179.844</v>
+        <v>180.5192</v>
       </c>
       <c r="Q56" t="n">
-        <v>164.4442</v>
+        <v>164.3515</v>
       </c>
       <c r="R56" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S56" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>2 okt</t>
+          <t>5 okt</t>
         </is>
       </c>
       <c r="V56" t="n">
-        <v>519.39</v>
+        <v>521.62</v>
       </c>
       <c r="W56" t="n">
-        <v>522.5</v>
+        <v>532.35</v>
       </c>
       <c r="X56" t="n">
-        <v>513.66</v>
+        <v>521.47</v>
       </c>
       <c r="Y56" t="n">
-        <v>517.53</v>
+        <v>525.1799999999999</v>
       </c>
       <c r="Z56" t="n">
-        <v>487.3905</v>
+        <v>490.2745</v>
       </c>
       <c r="AA56" t="n">
-        <v>431.4557</v>
+        <v>431.7147</v>
       </c>
       <c r="AB56" t="n">
         <v>535.3375423278808</v>
@@ -8212,84 +8234,84 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>5 okt</t>
+          <t>6 okt</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>42.645</v>
+        <v>42.86</v>
       </c>
       <c r="C57" t="n">
-        <v>43.11</v>
+        <v>43.285</v>
       </c>
       <c r="D57" t="n">
-        <v>42.35</v>
+        <v>42.43</v>
       </c>
       <c r="E57" t="n">
-        <v>42.865</v>
+        <v>43.185</v>
       </c>
       <c r="F57" t="n">
-        <v>40.2347</v>
+        <v>40.349</v>
       </c>
       <c r="G57" t="n">
-        <v>36.3069</v>
+        <v>36.3726</v>
       </c>
       <c r="H57" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I57" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>5 okt</t>
+          <t>6 okt</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>185.06</v>
+        <v>186.56</v>
       </c>
       <c r="M57" t="n">
-        <v>188.5</v>
+        <v>190.22</v>
       </c>
       <c r="N57" t="n">
-        <v>184.66</v>
+        <v>186.06</v>
       </c>
       <c r="O57" t="n">
-        <v>185.04</v>
+        <v>188.6</v>
       </c>
       <c r="P57" t="n">
-        <v>180.5192</v>
+        <v>181.1064</v>
       </c>
       <c r="Q57" t="n">
-        <v>164.3515</v>
+        <v>164.2647</v>
       </c>
       <c r="R57" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S57" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>5 okt</t>
+          <t>6 okt</t>
         </is>
       </c>
       <c r="V57" t="n">
-        <v>521.62</v>
+        <v>531.6799999999999</v>
       </c>
       <c r="W57" t="n">
-        <v>532.35</v>
+        <v>535.6900000000001</v>
       </c>
       <c r="X57" t="n">
-        <v>521.47</v>
+        <v>528.78</v>
       </c>
       <c r="Y57" t="n">
-        <v>525.1799999999999</v>
+        <v>529.3</v>
       </c>
       <c r="Z57" t="n">
-        <v>490.2745</v>
+        <v>493.0931</v>
       </c>
       <c r="AA57" t="n">
-        <v>431.7147</v>
+        <v>431.9956</v>
       </c>
       <c r="AB57" t="n">
         <v>535.3375423278808</v>
@@ -8301,84 +8323,84 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>6 okt</t>
+          <t>7 okt</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>42.86</v>
+        <v>43.37</v>
       </c>
       <c r="C58" t="n">
-        <v>43.285</v>
+        <v>43.835</v>
       </c>
       <c r="D58" t="n">
-        <v>42.43</v>
+        <v>43.145</v>
       </c>
       <c r="E58" t="n">
-        <v>43.185</v>
+        <v>43.25</v>
       </c>
       <c r="F58" t="n">
-        <v>40.349</v>
+        <v>40.4451</v>
       </c>
       <c r="G58" t="n">
-        <v>36.3726</v>
+        <v>36.4388</v>
       </c>
       <c r="H58" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I58" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>6 okt</t>
+          <t>7 okt</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>186.56</v>
+        <v>187</v>
       </c>
       <c r="M58" t="n">
-        <v>190.22</v>
+        <v>188.72</v>
       </c>
       <c r="N58" t="n">
-        <v>186.06</v>
+        <v>186.04</v>
       </c>
       <c r="O58" t="n">
-        <v>188.6</v>
+        <v>187.62</v>
       </c>
       <c r="P58" t="n">
-        <v>181.1064</v>
+        <v>181.618</v>
       </c>
       <c r="Q58" t="n">
-        <v>164.2647</v>
+        <v>164.1762</v>
       </c>
       <c r="R58" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S58" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>6 okt</t>
+          <t>7 okt</t>
         </is>
       </c>
       <c r="V58" t="n">
-        <v>531.6799999999999</v>
+        <v>530.73</v>
       </c>
       <c r="W58" t="n">
-        <v>535.6900000000001</v>
+        <v>531.73</v>
       </c>
       <c r="X58" t="n">
-        <v>528.78</v>
+        <v>524.6900000000001</v>
       </c>
       <c r="Y58" t="n">
-        <v>529.3</v>
+        <v>529.76</v>
       </c>
       <c r="Z58" t="n">
-        <v>493.0931</v>
+        <v>495.8361</v>
       </c>
       <c r="AA58" t="n">
-        <v>431.9956</v>
+        <v>432.2398</v>
       </c>
       <c r="AB58" t="n">
         <v>535.3375423278808</v>
@@ -8390,84 +8412,84 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>7 okt</t>
+          <t>8 okt</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>43.37</v>
+        <v>43.555</v>
       </c>
       <c r="C59" t="n">
-        <v>43.835</v>
+        <v>44.815</v>
       </c>
       <c r="D59" t="n">
-        <v>43.145</v>
+        <v>43.5425</v>
       </c>
       <c r="E59" t="n">
-        <v>43.25</v>
+        <v>44.75</v>
       </c>
       <c r="F59" t="n">
-        <v>40.4451</v>
+        <v>40.5699</v>
       </c>
       <c r="G59" t="n">
-        <v>36.4388</v>
+        <v>36.5123</v>
       </c>
       <c r="H59" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I59" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>7 okt</t>
+          <t>8 okt</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>187</v>
+        <v>187.04</v>
       </c>
       <c r="M59" t="n">
-        <v>188.72</v>
+        <v>189.82</v>
       </c>
       <c r="N59" t="n">
-        <v>186.04</v>
+        <v>183.76</v>
       </c>
       <c r="O59" t="n">
-        <v>187.62</v>
+        <v>184.62</v>
       </c>
       <c r="P59" t="n">
-        <v>181.618</v>
+        <v>182.192</v>
       </c>
       <c r="Q59" t="n">
-        <v>164.1762</v>
+        <v>164.074</v>
       </c>
       <c r="R59" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S59" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>7 okt</t>
+          <t>8 okt</t>
         </is>
       </c>
       <c r="V59" t="n">
-        <v>530.73</v>
+        <v>529.8099999999999</v>
       </c>
       <c r="W59" t="n">
-        <v>531.73</v>
+        <v>533.51</v>
       </c>
       <c r="X59" t="n">
-        <v>524.6900000000001</v>
+        <v>518.79</v>
       </c>
       <c r="Y59" t="n">
-        <v>529.76</v>
+        <v>522.61</v>
       </c>
       <c r="Z59" t="n">
-        <v>495.8361</v>
+        <v>498.4921</v>
       </c>
       <c r="AA59" t="n">
-        <v>432.2398</v>
+        <v>432.4385</v>
       </c>
       <c r="AB59" t="n">
         <v>535.3375423278808</v>
@@ -8479,84 +8501,84 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>8 okt</t>
+          <t>9 okt</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>43.555</v>
+        <v>44.42</v>
       </c>
       <c r="C60" t="n">
-        <v>44.815</v>
+        <v>45.155</v>
       </c>
       <c r="D60" t="n">
-        <v>43.5425</v>
+        <v>43.94</v>
       </c>
       <c r="E60" t="n">
-        <v>44.75</v>
+        <v>45.035</v>
       </c>
       <c r="F60" t="n">
-        <v>40.5699</v>
+        <v>40.6842</v>
       </c>
       <c r="G60" t="n">
-        <v>36.5123</v>
+        <v>36.5866</v>
       </c>
       <c r="H60" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I60" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>8 okt</t>
+          <t>9 okt</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>187.04</v>
+        <v>188.98</v>
       </c>
       <c r="M60" t="n">
-        <v>189.82</v>
+        <v>192.58</v>
       </c>
       <c r="N60" t="n">
-        <v>183.76</v>
+        <v>188.86</v>
       </c>
       <c r="O60" t="n">
-        <v>184.62</v>
+        <v>191.46</v>
       </c>
       <c r="P60" t="n">
-        <v>182.192</v>
+        <v>182.8676</v>
       </c>
       <c r="Q60" t="n">
-        <v>164.074</v>
+        <v>164.0101</v>
       </c>
       <c r="R60" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S60" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>8 okt</t>
+          <t>9 okt</t>
         </is>
       </c>
       <c r="V60" t="n">
-        <v>529.8099999999999</v>
+        <v>528.24</v>
       </c>
       <c r="W60" t="n">
-        <v>533.51</v>
+        <v>537.22</v>
       </c>
       <c r="X60" t="n">
-        <v>518.79</v>
+        <v>526.24</v>
       </c>
       <c r="Y60" t="n">
-        <v>522.61</v>
+        <v>535.0700000000001</v>
       </c>
       <c r="Z60" t="n">
-        <v>498.4921</v>
+        <v>500.1885</v>
       </c>
       <c r="AA60" t="n">
-        <v>432.4385</v>
+        <v>432.7046</v>
       </c>
       <c r="AB60" t="n">
         <v>535.3375423278808</v>
@@ -8568,84 +8590,84 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>9 okt</t>
+          <t>12 okt</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>44.42</v>
+        <v>44.725</v>
       </c>
       <c r="C61" t="n">
-        <v>45.155</v>
+        <v>45.81</v>
       </c>
       <c r="D61" t="n">
-        <v>43.94</v>
+        <v>44.695</v>
       </c>
       <c r="E61" t="n">
-        <v>45.035</v>
+        <v>45.56</v>
       </c>
       <c r="F61" t="n">
-        <v>40.6842</v>
+        <v>40.8072</v>
       </c>
       <c r="G61" t="n">
-        <v>36.5866</v>
+        <v>36.6625</v>
       </c>
       <c r="H61" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I61" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>9 okt</t>
+          <t>12 okt</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>188.98</v>
+        <v>190.58</v>
       </c>
       <c r="M61" t="n">
-        <v>192.58</v>
+        <v>197.88</v>
       </c>
       <c r="N61" t="n">
-        <v>188.86</v>
+        <v>189.78</v>
       </c>
       <c r="O61" t="n">
-        <v>191.46</v>
+        <v>194.46</v>
       </c>
       <c r="P61" t="n">
-        <v>182.8676</v>
+        <v>183.464</v>
       </c>
       <c r="Q61" t="n">
-        <v>164.0101</v>
+        <v>163.9576</v>
       </c>
       <c r="R61" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S61" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>9 okt</t>
+          <t>12 okt</t>
         </is>
       </c>
       <c r="V61" t="n">
-        <v>528.24</v>
+        <v>537.53</v>
       </c>
       <c r="W61" t="n">
-        <v>537.22</v>
+        <v>542.74</v>
       </c>
       <c r="X61" t="n">
-        <v>526.24</v>
+        <v>535.7</v>
       </c>
       <c r="Y61" t="n">
-        <v>535.0700000000001</v>
+        <v>541.15</v>
       </c>
       <c r="Z61" t="n">
-        <v>500.1885</v>
+        <v>501.7346</v>
       </c>
       <c r="AA61" t="n">
-        <v>432.7046</v>
+        <v>432.9914</v>
       </c>
       <c r="AB61" t="n">
         <v>535.3375423278808</v>
@@ -8657,84 +8679,84 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>12 okt</t>
+          <t>13 okt</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>44.725</v>
+        <v>45.69</v>
       </c>
       <c r="C62" t="n">
-        <v>45.81</v>
+        <v>45.97</v>
       </c>
       <c r="D62" t="n">
-        <v>44.695</v>
+        <v>45.35</v>
       </c>
       <c r="E62" t="n">
-        <v>45.56</v>
+        <v>45.95</v>
       </c>
       <c r="F62" t="n">
-        <v>40.8072</v>
+        <v>40.9565</v>
       </c>
       <c r="G62" t="n">
-        <v>36.6625</v>
+        <v>36.7398</v>
       </c>
       <c r="H62" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I62" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>12 okt</t>
+          <t>13 okt</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>190.58</v>
+        <v>196</v>
       </c>
       <c r="M62" t="n">
-        <v>197.88</v>
+        <v>198.18</v>
       </c>
       <c r="N62" t="n">
-        <v>189.78</v>
+        <v>194.02</v>
       </c>
       <c r="O62" t="n">
-        <v>194.46</v>
+        <v>197.28</v>
       </c>
       <c r="P62" t="n">
-        <v>183.464</v>
+        <v>184.062</v>
       </c>
       <c r="Q62" t="n">
-        <v>163.9576</v>
+        <v>163.9196</v>
       </c>
       <c r="R62" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S62" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>12 okt</t>
+          <t>13 okt</t>
         </is>
       </c>
       <c r="V62" t="n">
-        <v>537.53</v>
+        <v>544.64</v>
       </c>
       <c r="W62" t="n">
-        <v>542.74</v>
+        <v>551.15</v>
       </c>
       <c r="X62" t="n">
-        <v>535.7</v>
+        <v>543.0599999999999</v>
       </c>
       <c r="Y62" t="n">
-        <v>541.15</v>
+        <v>543.45</v>
       </c>
       <c r="Z62" t="n">
-        <v>501.7346</v>
+        <v>502.8689</v>
       </c>
       <c r="AA62" t="n">
-        <v>432.9914</v>
+        <v>433.2839</v>
       </c>
       <c r="AB62" t="n">
         <v>535.3375423278808</v>
@@ -8746,84 +8768,84 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>13 okt</t>
+          <t>14 okt</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>45.69</v>
+        <v>45.95</v>
       </c>
       <c r="C63" t="n">
-        <v>45.97</v>
+        <v>46.675</v>
       </c>
       <c r="D63" t="n">
-        <v>45.35</v>
+        <v>45.91</v>
       </c>
       <c r="E63" t="n">
-        <v>45.95</v>
+        <v>46.455</v>
       </c>
       <c r="F63" t="n">
-        <v>40.9565</v>
+        <v>41.125</v>
       </c>
       <c r="G63" t="n">
-        <v>36.7398</v>
+        <v>36.8183</v>
       </c>
       <c r="H63" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I63" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>13 okt</t>
+          <t>14 okt</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>196</v>
+        <v>196.6</v>
       </c>
       <c r="M63" t="n">
-        <v>198.18</v>
+        <v>199.36</v>
       </c>
       <c r="N63" t="n">
-        <v>194.02</v>
+        <v>195.26</v>
       </c>
       <c r="O63" t="n">
-        <v>197.28</v>
+        <v>196.94</v>
       </c>
       <c r="P63" t="n">
-        <v>184.062</v>
+        <v>184.6156</v>
       </c>
       <c r="Q63" t="n">
-        <v>163.9196</v>
+        <v>163.9114</v>
       </c>
       <c r="R63" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S63" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>13 okt</t>
+          <t>14 okt</t>
         </is>
       </c>
       <c r="V63" t="n">
-        <v>544.64</v>
+        <v>545.27</v>
       </c>
       <c r="W63" t="n">
-        <v>551.15</v>
+        <v>545.75</v>
       </c>
       <c r="X63" t="n">
-        <v>543.0599999999999</v>
+        <v>532.54</v>
       </c>
       <c r="Y63" t="n">
-        <v>543.45</v>
+        <v>533.6900000000001</v>
       </c>
       <c r="Z63" t="n">
-        <v>502.8689</v>
+        <v>503.705</v>
       </c>
       <c r="AA63" t="n">
-        <v>433.2839</v>
+        <v>433.5292</v>
       </c>
       <c r="AB63" t="n">
         <v>535.3375423278808</v>
@@ -8835,84 +8857,84 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>14 okt</t>
+          <t>15 okt</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>45.95</v>
+        <v>46.295</v>
       </c>
       <c r="C64" t="n">
-        <v>46.675</v>
+        <v>46.735</v>
       </c>
       <c r="D64" t="n">
-        <v>45.91</v>
+        <v>46.125</v>
       </c>
       <c r="E64" t="n">
-        <v>46.455</v>
+        <v>46.375</v>
       </c>
       <c r="F64" t="n">
-        <v>41.125</v>
+        <v>41.2847</v>
       </c>
       <c r="G64" t="n">
-        <v>36.8183</v>
+        <v>36.8966</v>
       </c>
       <c r="H64" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I64" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>14 okt</t>
+          <t>15 okt</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>196.6</v>
+        <v>199.48</v>
       </c>
       <c r="M64" t="n">
-        <v>199.36</v>
+        <v>203</v>
       </c>
       <c r="N64" t="n">
-        <v>195.26</v>
+        <v>196.98</v>
       </c>
       <c r="O64" t="n">
-        <v>196.94</v>
+        <v>201.25</v>
       </c>
       <c r="P64" t="n">
-        <v>184.6156</v>
+        <v>185.221</v>
       </c>
       <c r="Q64" t="n">
-        <v>163.9114</v>
+        <v>163.9038</v>
       </c>
       <c r="R64" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S64" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>14 okt</t>
+          <t>15 okt</t>
         </is>
       </c>
       <c r="V64" t="n">
-        <v>545.27</v>
+        <v>533.3200000000001</v>
       </c>
       <c r="W64" t="n">
-        <v>545.75</v>
+        <v>541.13</v>
       </c>
       <c r="X64" t="n">
-        <v>532.54</v>
+        <v>531.22</v>
       </c>
       <c r="Y64" t="n">
-        <v>533.6900000000001</v>
+        <v>539.4400000000001</v>
       </c>
       <c r="Z64" t="n">
-        <v>503.705</v>
+        <v>504.7629</v>
       </c>
       <c r="AA64" t="n">
-        <v>433.5292</v>
+        <v>433.8063</v>
       </c>
       <c r="AB64" t="n">
         <v>535.3375423278808</v>
@@ -8924,84 +8946,84 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>15 okt</t>
+          <t>16 okt</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>46.295</v>
+        <v>46.14</v>
       </c>
       <c r="C65" t="n">
-        <v>46.735</v>
+        <v>47.025</v>
       </c>
       <c r="D65" t="n">
-        <v>46.125</v>
+        <v>46.075</v>
       </c>
       <c r="E65" t="n">
-        <v>46.375</v>
+        <v>46.88</v>
       </c>
       <c r="F65" t="n">
-        <v>41.2847</v>
+        <v>41.4622</v>
       </c>
       <c r="G65" t="n">
-        <v>36.8966</v>
+        <v>36.977</v>
       </c>
       <c r="H65" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I65" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>15 okt</t>
+          <t>16 okt</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>199.48</v>
+        <v>200.6</v>
       </c>
       <c r="M65" t="n">
-        <v>203</v>
+        <v>204.2</v>
       </c>
       <c r="N65" t="n">
-        <v>196.98</v>
+        <v>198.68</v>
       </c>
       <c r="O65" t="n">
-        <v>201.25</v>
+        <v>199.22</v>
       </c>
       <c r="P65" t="n">
-        <v>185.221</v>
+        <v>185.6462</v>
       </c>
       <c r="Q65" t="n">
-        <v>163.9038</v>
+        <v>163.9066</v>
       </c>
       <c r="R65" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S65" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>15 okt</t>
+          <t>16 okt</t>
         </is>
       </c>
       <c r="V65" t="n">
-        <v>533.3200000000001</v>
+        <v>541.3099999999999</v>
       </c>
       <c r="W65" t="n">
-        <v>541.13</v>
+        <v>543.8200000000001</v>
       </c>
       <c r="X65" t="n">
-        <v>531.22</v>
+        <v>524.4299999999999</v>
       </c>
       <c r="Y65" t="n">
-        <v>539.4400000000001</v>
+        <v>529.05</v>
       </c>
       <c r="Z65" t="n">
-        <v>504.7629</v>
+        <v>505.3655</v>
       </c>
       <c r="AA65" t="n">
-        <v>433.8063</v>
+        <v>434.0295</v>
       </c>
       <c r="AB65" t="n">
         <v>535.3375423278808</v>
@@ -9013,84 +9035,84 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>16 okt</t>
+          <t>19 okt</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>46.14</v>
+        <v>47.37</v>
       </c>
       <c r="C66" t="n">
-        <v>47.025</v>
+        <v>47.45</v>
       </c>
       <c r="D66" t="n">
-        <v>46.075</v>
+        <v>46.74</v>
       </c>
       <c r="E66" t="n">
-        <v>46.89</v>
+        <v>46.865</v>
       </c>
       <c r="F66" t="n">
-        <v>41.4624</v>
+        <v>41.6314</v>
       </c>
       <c r="G66" t="n">
-        <v>36.977</v>
+        <v>37.0625</v>
       </c>
       <c r="H66" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I66" t="n">
-        <v>44.18785640171596</v>
+        <v>44.24892779758999</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>16 okt</t>
+          <t>19 okt</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>200.6</v>
+        <v>199.56</v>
       </c>
       <c r="M66" t="n">
-        <v>204.2</v>
+        <v>200.8</v>
       </c>
       <c r="N66" t="n">
-        <v>198.68</v>
+        <v>197.32</v>
       </c>
       <c r="O66" t="n">
-        <v>199.02</v>
+        <v>200.05</v>
       </c>
       <c r="P66" t="n">
-        <v>185.6422</v>
+        <v>186.0612</v>
       </c>
       <c r="Q66" t="n">
-        <v>163.9056</v>
+        <v>163.8822</v>
       </c>
       <c r="R66" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S66" t="n">
-        <v>185.1271307809012</v>
+        <v>185.2514168875558</v>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>16 okt</t>
+          <t>19 okt</t>
         </is>
       </c>
       <c r="V66" t="n">
-        <v>541.0599999999999</v>
+        <v>528.74</v>
       </c>
       <c r="W66" t="n">
-        <v>543.8099999999999</v>
+        <v>535.5684</v>
       </c>
       <c r="X66" t="n">
-        <v>524.4299999999999</v>
+        <v>528.74</v>
       </c>
       <c r="Y66" t="n">
-        <v>528.95</v>
+        <v>533.61</v>
       </c>
       <c r="Z66" t="n">
-        <v>505.3635</v>
+        <v>506.0567</v>
       </c>
       <c r="AA66" t="n">
-        <v>434.029</v>
+        <v>434.2947</v>
       </c>
       <c r="AB66" t="n">
         <v>535.3375423278808</v>

--- a/rapporten/trend-agent.xlsx
+++ b/rapporten/trend-agent.xlsx
@@ -1944,7 +1944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2124,6 +2124,28 @@
       </c>
       <c r="E8" s="3">
         <f>B8/$B$2-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>10034.22</v>
+      </c>
+      <c r="C9" s="2">
+        <f>B9-B8</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>B9/B8-1</f>
+        <v/>
+      </c>
+      <c r="E9" s="3">
+        <f>B9/$B$2-1</f>
         <v/>
       </c>
     </row>
@@ -2267,38 +2289,38 @@
     <row r="6" ht="22" customHeight="1">
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Shell (SHELL.AS)  ·  46,87 EUR</t>
+          <t>Shell (SHELL.AS)  ·  46,65 EUR</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>SAP (SAP.DE)  ·  200,05 EUR</t>
+          <t>SAP (SAP.DE)  ·  201,80 EUR</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>Gestegen: 23,9% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +4,0% (winst). De bot verkoopt als de koers onder 44,25 zakt (-5,6%).</t>
+          <t>Gestegen: 21,9% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +3,5% (winst). De bot verkoopt als de koers onder 44,25 zakt (-5,1%).</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>Gestegen: 46,6% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +4,4% (winst). De bot verkoopt als de koers onder 185,25 zakt (-7,4%).</t>
+          <t>Gestegen: 52,8% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +5,3% (winst). De bot verkoopt als de koers onder 185,60 zakt (-8,0%).</t>
         </is>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Microsoft (MSFT)  ·  533,61 USD</t>
+          <t>Microsoft (MSFT)  ·  532,13 USD</t>
         </is>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Gestegen: 32,9% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: -0,3% (verlies). De bot verkoopt als de koers onder 509,90 zakt (-4,4%).</t>
+          <t>Gestegen: 34,0% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: -0,6% (verlies). De bot verkoopt als de koers onder 509,90 zakt (-4,2%).</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2460,7 @@
         <v>191.56</v>
       </c>
       <c r="F3" t="n">
-        <v>185.25</v>
+        <v>185.6</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -2763,12 +2785,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SHELL.AS</t>
+          <t>SAP.DE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Shell</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -2777,19 +2799,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.162</v>
+        <v>0.157</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.2246445101732573</v>
+        <v>0.5726308567134148</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1343338554093498</v>
+        <v>0.1035765196225973</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.79</v>
       </c>
       <c r="I2" t="n">
-        <v>46.87</v>
+        <v>201.8</v>
       </c>
     </row>
     <row r="3">
@@ -2798,12 +2820,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SAP.DE</t>
+          <t>SHELL.AS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Shell</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2812,19 +2834,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.139</v>
+        <v>0.155</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.5150712906978585</v>
+        <v>0.202231355413828</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.0924530820554903</v>
+        <v>0.144083379034855</v>
       </c>
       <c r="H3" t="n">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="I3" t="n">
-        <v>200.05</v>
+        <v>46.65</v>
       </c>
     </row>
     <row r="4">
@@ -2847,19 +2869,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.136</v>
+        <v>0.139</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.4224140684231807</v>
+        <v>0.4252740074694488</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.2338614136676298</v>
+        <v>0.2475482210588058</v>
       </c>
       <c r="H4" t="n">
-        <v>0.85</v>
+        <v>0.87</v>
       </c>
       <c r="I4" t="n">
-        <v>84.09999999999999</v>
+        <v>83.95999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -2882,19 +2904,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.102</v>
+        <v>0.114</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.1348680903497113</v>
+        <v>0.1539420798306623</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.09440926500027724</v>
+        <v>0.1003378669884039</v>
       </c>
       <c r="H5" t="n">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="I5" t="n">
-        <v>403.06</v>
+        <v>407.07</v>
       </c>
     </row>
     <row r="6">
@@ -2917,19 +2939,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.101</v>
+        <v>0.105</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.1661213443947605</v>
+        <v>0.1547116218244047</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.0607696881620563</v>
+        <v>0.08797635009809124</v>
       </c>
       <c r="H6" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="I6" t="n">
-        <v>67.81999999999999</v>
+        <v>67.95999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -2952,19 +2974,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.097</v>
+        <v>0.1</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.3440968709158025</v>
+        <v>0.3658137450233532</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.08066342636544954</v>
+        <v>0.06084412276972406</v>
       </c>
       <c r="H7" t="n">
         <v>0.82</v>
       </c>
       <c r="I7" t="n">
-        <v>533.61</v>
+        <v>532.13</v>
       </c>
     </row>
     <row r="8">
@@ -2990,16 +3012,16 @@
         <v>0.097</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.1828122320570467</v>
+        <v>0.159222186923127</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.090192005659393</v>
+        <v>0.1237523434000534</v>
       </c>
       <c r="H8" t="n">
         <v>0.86</v>
       </c>
       <c r="I8" t="n">
-        <v>178.29</v>
+        <v>177.89</v>
       </c>
     </row>
     <row r="9">
@@ -3022,19 +3044,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.081</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.4282404380072085</v>
+        <v>0.4900400502344047</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.01908208044663007</v>
+        <v>0.02550545142542404</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="I9" t="n">
-        <v>242.46</v>
+        <v>242.45</v>
       </c>
     </row>
     <row r="10">
@@ -3057,19 +3079,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.065</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.4636287345557388</v>
+        <v>0.5460383463892116</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.09302518550586836</v>
+        <v>0.05188705112248648</v>
       </c>
       <c r="H10" t="n">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="I10" t="n">
-        <v>194.16</v>
+        <v>192.59</v>
       </c>
     </row>
     <row r="11">
@@ -3078,12 +3100,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TTE.PA</t>
+          <t>OR.PA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TotalEnergies</t>
+          <t>L'Oreal</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3092,19 +3114,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.052</v>
+        <v>0.062</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.09445359121940089</v>
+        <v>0.09610947838646444</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.02504985976212115</v>
+        <v>0.05341323775929396</v>
       </c>
       <c r="H11" t="n">
-        <v>1.02</v>
+        <v>0.99</v>
       </c>
       <c r="I11" t="n">
-        <v>80.37</v>
+        <v>404.3</v>
       </c>
     </row>
   </sheetData>
@@ -3375,23 +3397,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>21 jul</t>
+          <t>22 jul</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>37.5703</v>
+        <v>38.095</v>
       </c>
       <c r="C2" t="n">
-        <v>37.8277</v>
+        <v>38.6098</v>
       </c>
       <c r="D2" t="n">
-        <v>37.4169</v>
+        <v>37.9267</v>
       </c>
       <c r="E2" t="n">
-        <v>37.8277</v>
+        <v>38.2682</v>
       </c>
       <c r="F2" t="n">
-        <v>35.7452</v>
+        <v>35.799</v>
       </c>
       <c r="H2" t="n">
         <v>45.05751734733581</v>
@@ -3401,49 +3423,49 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>21 jul</t>
+          <t>22 jul</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>137.74</v>
+        <v>136.02</v>
       </c>
       <c r="M2" t="n">
-        <v>137.84</v>
+        <v>136.4</v>
       </c>
       <c r="N2" t="n">
-        <v>135.34</v>
+        <v>132.04</v>
       </c>
       <c r="O2" t="n">
-        <v>136.42</v>
+        <v>132.04</v>
       </c>
       <c r="P2" t="n">
-        <v>144.4084</v>
+        <v>144.324</v>
       </c>
       <c r="R2" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S2" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>20 jul</t>
+          <t>21 jul</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>390.6746</v>
+        <v>398.0606</v>
       </c>
       <c r="W2" t="n">
-        <v>402.4224</v>
+        <v>400.7156</v>
       </c>
       <c r="X2" t="n">
-        <v>388.9179</v>
+        <v>395.5753</v>
       </c>
       <c r="Y2" t="n">
-        <v>401.5341</v>
+        <v>397.0026</v>
       </c>
       <c r="Z2" t="n">
-        <v>400.345</v>
+        <v>399.9036</v>
       </c>
       <c r="AB2" t="n">
         <v>535.3375423278808</v>
@@ -3455,23 +3477,23 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>22 jul</t>
+          <t>23 jul</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38.095</v>
+        <v>38.491</v>
       </c>
       <c r="C3" t="n">
-        <v>38.6098</v>
+        <v>39.0454</v>
       </c>
       <c r="D3" t="n">
-        <v>37.9267</v>
+        <v>38.3425</v>
       </c>
       <c r="E3" t="n">
-        <v>38.2682</v>
+        <v>38.8028</v>
       </c>
       <c r="F3" t="n">
-        <v>35.799</v>
+        <v>35.863</v>
       </c>
       <c r="H3" t="n">
         <v>45.05751734733581</v>
@@ -3481,49 +3503,49 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>22 jul</t>
+          <t>23 jul</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>136.02</v>
+        <v>131</v>
       </c>
       <c r="M3" t="n">
-        <v>136.4</v>
+        <v>132.42</v>
       </c>
       <c r="N3" t="n">
-        <v>132.04</v>
+        <v>127.5</v>
       </c>
       <c r="O3" t="n">
-        <v>132.04</v>
+        <v>128.32</v>
       </c>
       <c r="P3" t="n">
-        <v>144.324</v>
+        <v>144.066</v>
       </c>
       <c r="R3" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S3" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>21 jul</t>
+          <t>22 jul</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>398.0606</v>
+        <v>398.8292</v>
       </c>
       <c r="W3" t="n">
-        <v>400.7156</v>
+        <v>400.2465</v>
       </c>
       <c r="X3" t="n">
-        <v>395.5753</v>
+        <v>386.2329</v>
       </c>
       <c r="Y3" t="n">
-        <v>397.0026</v>
+        <v>389.6066</v>
       </c>
       <c r="Z3" t="n">
-        <v>399.9036</v>
+        <v>399.4268</v>
       </c>
       <c r="AB3" t="n">
         <v>535.3375423278808</v>
@@ -3535,23 +3557,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>23 jul</t>
+          <t>24 jul</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38.491</v>
+        <v>38.4019</v>
       </c>
       <c r="C4" t="n">
-        <v>39.0454</v>
+        <v>38.6593</v>
       </c>
       <c r="D4" t="n">
-        <v>38.3425</v>
+        <v>38.1594</v>
       </c>
       <c r="E4" t="n">
-        <v>38.8028</v>
+        <v>38.3871</v>
       </c>
       <c r="F4" t="n">
-        <v>35.863</v>
+        <v>35.9135</v>
       </c>
       <c r="H4" t="n">
         <v>45.05751734733581</v>
@@ -3561,49 +3583,49 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>23 jul</t>
+          <t>24 jul</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>131</v>
+        <v>130.88</v>
       </c>
       <c r="M4" t="n">
-        <v>132.42</v>
+        <v>141.32</v>
       </c>
       <c r="N4" t="n">
-        <v>127.5</v>
+        <v>130.86</v>
       </c>
       <c r="O4" t="n">
-        <v>128.32</v>
+        <v>140.2</v>
       </c>
       <c r="P4" t="n">
-        <v>144.066</v>
+        <v>143.9888</v>
       </c>
       <c r="R4" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S4" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>22 jul</t>
+          <t>23 jul</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>398.8292</v>
+        <v>389.2373</v>
       </c>
       <c r="W4" t="n">
-        <v>400.2465</v>
+        <v>391.0439</v>
       </c>
       <c r="X4" t="n">
-        <v>386.2329</v>
+        <v>376.6809</v>
       </c>
       <c r="Y4" t="n">
-        <v>389.6066</v>
+        <v>380.863</v>
       </c>
       <c r="Z4" t="n">
-        <v>399.4268</v>
+        <v>398.8242</v>
       </c>
       <c r="AB4" t="n">
         <v>535.3375423278808</v>
@@ -3615,23 +3637,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>24 jul</t>
+          <t>27 jul</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>38.4019</v>
+        <v>37.5802</v>
       </c>
       <c r="C5" t="n">
-        <v>38.6593</v>
+        <v>38.1099</v>
       </c>
       <c r="D5" t="n">
-        <v>38.1594</v>
+        <v>37.4317</v>
       </c>
       <c r="E5" t="n">
-        <v>38.3871</v>
+        <v>37.9515</v>
       </c>
       <c r="F5" t="n">
-        <v>35.9135</v>
+        <v>35.931</v>
       </c>
       <c r="H5" t="n">
         <v>45.05751734733581</v>
@@ -3641,49 +3663,49 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>24 jul</t>
+          <t>27 jul</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>130.88</v>
+        <v>142.38</v>
       </c>
       <c r="M5" t="n">
-        <v>141.32</v>
+        <v>151.56</v>
       </c>
       <c r="N5" t="n">
-        <v>130.86</v>
+        <v>142</v>
       </c>
       <c r="O5" t="n">
-        <v>140.2</v>
+        <v>151.28</v>
       </c>
       <c r="P5" t="n">
-        <v>143.9888</v>
+        <v>144.0572</v>
       </c>
       <c r="R5" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S5" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>23 jul</t>
+          <t>24 jul</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>389.2373</v>
+        <v>386.3227</v>
       </c>
       <c r="W5" t="n">
-        <v>391.0439</v>
+        <v>388.299</v>
       </c>
       <c r="X5" t="n">
-        <v>376.6809</v>
+        <v>379.9348</v>
       </c>
       <c r="Y5" t="n">
-        <v>380.863</v>
+        <v>380.9828</v>
       </c>
       <c r="Z5" t="n">
-        <v>398.8242</v>
+        <v>398.3214</v>
       </c>
       <c r="AB5" t="n">
         <v>535.3375423278808</v>
@@ -3695,26 +3717,26 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>27 jul</t>
+          <t>28 jul</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>37.5802</v>
+        <v>37.7139</v>
       </c>
       <c r="C6" t="n">
-        <v>38.1099</v>
+        <v>38.0109</v>
       </c>
       <c r="D6" t="n">
-        <v>37.4317</v>
+        <v>37.4713</v>
       </c>
       <c r="E6" t="n">
-        <v>37.9515</v>
+        <v>37.4713</v>
       </c>
       <c r="F6" t="n">
-        <v>35.931</v>
+        <v>35.9372</v>
       </c>
       <c r="G6" t="n">
-        <v>33.9167</v>
+        <v>33.9548</v>
       </c>
       <c r="H6" t="n">
         <v>45.05751734733581</v>
@@ -3724,55 +3746,55 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>27 jul</t>
+          <t>28 jul</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>142.38</v>
+        <v>152.2</v>
       </c>
       <c r="M6" t="n">
-        <v>151.56</v>
+        <v>159.76</v>
       </c>
       <c r="N6" t="n">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="O6" t="n">
-        <v>151.28</v>
+        <v>159.24</v>
       </c>
       <c r="P6" t="n">
-        <v>144.0572</v>
+        <v>144.1076</v>
       </c>
       <c r="Q6" t="n">
-        <v>173.0393</v>
+        <v>172.6663</v>
       </c>
       <c r="R6" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S6" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>24 jul</t>
+          <t>27 jul</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>386.3227</v>
+        <v>389.347</v>
       </c>
       <c r="W6" t="n">
-        <v>388.299</v>
+        <v>393.4593</v>
       </c>
       <c r="X6" t="n">
-        <v>379.9348</v>
+        <v>387.261</v>
       </c>
       <c r="Y6" t="n">
-        <v>380.9828</v>
+        <v>388.3689</v>
       </c>
       <c r="Z6" t="n">
-        <v>398.3214</v>
+        <v>398.0172</v>
       </c>
       <c r="AA6" t="n">
-        <v>433.8946</v>
+        <v>433.238</v>
       </c>
       <c r="AB6" t="n">
         <v>535.3375423278808</v>
@@ -3784,26 +3806,26 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>28 jul</t>
+          <t>29 jul</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>37.7139</v>
+        <v>38.0653</v>
       </c>
       <c r="C7" t="n">
-        <v>38.0109</v>
+        <v>38.59</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4713</v>
+        <v>37.7089</v>
       </c>
       <c r="E7" t="n">
-        <v>37.4713</v>
+        <v>38.4415</v>
       </c>
       <c r="F7" t="n">
-        <v>35.9372</v>
+        <v>35.9692</v>
       </c>
       <c r="G7" t="n">
-        <v>33.9548</v>
+        <v>33.9987</v>
       </c>
       <c r="H7" t="n">
         <v>45.05751734733581</v>
@@ -3813,55 +3835,55 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>28 jul</t>
+          <t>29 jul</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>152.2</v>
+        <v>159.84</v>
       </c>
       <c r="M7" t="n">
-        <v>159.76</v>
+        <v>163.3</v>
       </c>
       <c r="N7" t="n">
-        <v>151</v>
+        <v>156.48</v>
       </c>
       <c r="O7" t="n">
-        <v>159.24</v>
+        <v>162.04</v>
       </c>
       <c r="P7" t="n">
-        <v>144.1076</v>
+        <v>144.28</v>
       </c>
       <c r="Q7" t="n">
-        <v>172.6663</v>
+        <v>172.343</v>
       </c>
       <c r="R7" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S7" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>27 jul</t>
+          <t>28 jul</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>389.347</v>
+        <v>392.4213</v>
       </c>
       <c r="W7" t="n">
-        <v>393.4593</v>
+        <v>399.5678</v>
       </c>
       <c r="X7" t="n">
-        <v>387.261</v>
+        <v>390.5647</v>
       </c>
       <c r="Y7" t="n">
-        <v>388.3689</v>
+        <v>392.6109</v>
       </c>
       <c r="Z7" t="n">
-        <v>398.0172</v>
+        <v>397.7139</v>
       </c>
       <c r="AA7" t="n">
-        <v>433.238</v>
+        <v>432.5982</v>
       </c>
       <c r="AB7" t="n">
         <v>535.3375423278808</v>
@@ -3873,26 +3895,26 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>29 jul</t>
+          <t>30 jul</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>38.0653</v>
+        <v>38.6098</v>
       </c>
       <c r="C8" t="n">
-        <v>38.59</v>
+        <v>39.1444</v>
       </c>
       <c r="D8" t="n">
-        <v>37.7089</v>
+        <v>38.3277</v>
       </c>
       <c r="E8" t="n">
-        <v>38.4415</v>
+        <v>38.5108</v>
       </c>
       <c r="F8" t="n">
-        <v>35.9692</v>
+        <v>35.9978</v>
       </c>
       <c r="G8" t="n">
-        <v>33.9987</v>
+        <v>34.0424</v>
       </c>
       <c r="H8" t="n">
         <v>45.05751734733581</v>
@@ -3902,55 +3924,55 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>29 jul</t>
+          <t>30 jul</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>159.84</v>
+        <v>162.5</v>
       </c>
       <c r="M8" t="n">
-        <v>163.3</v>
+        <v>163.16</v>
       </c>
       <c r="N8" t="n">
-        <v>156.48</v>
+        <v>155.2</v>
       </c>
       <c r="O8" t="n">
-        <v>162.04</v>
+        <v>155.92</v>
       </c>
       <c r="P8" t="n">
-        <v>144.28</v>
+        <v>144.3804</v>
       </c>
       <c r="Q8" t="n">
-        <v>172.343</v>
+        <v>171.9849</v>
       </c>
       <c r="R8" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S8" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>28 jul</t>
+          <t>29 jul</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>392.4213</v>
+        <v>392.6608</v>
       </c>
       <c r="W8" t="n">
-        <v>399.5678</v>
+        <v>400.4961</v>
       </c>
       <c r="X8" t="n">
-        <v>390.5647</v>
+        <v>388.0095</v>
       </c>
       <c r="Y8" t="n">
-        <v>392.6109</v>
+        <v>389.8062</v>
       </c>
       <c r="Z8" t="n">
-        <v>397.7139</v>
+        <v>397.1057</v>
       </c>
       <c r="AA8" t="n">
-        <v>432.5982</v>
+        <v>431.9565</v>
       </c>
       <c r="AB8" t="n">
         <v>535.3375423278808</v>
@@ -3962,26 +3984,26 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>30 jul</t>
+          <t>31 jul</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>38.6098</v>
       </c>
       <c r="C9" t="n">
-        <v>39.1444</v>
+        <v>39.575</v>
       </c>
       <c r="D9" t="n">
-        <v>38.3277</v>
+        <v>38.4464</v>
       </c>
       <c r="E9" t="n">
-        <v>38.5108</v>
+        <v>39.3226</v>
       </c>
       <c r="F9" t="n">
-        <v>35.9978</v>
+        <v>36.0495</v>
       </c>
       <c r="G9" t="n">
-        <v>34.0424</v>
+        <v>34.0907</v>
       </c>
       <c r="H9" t="n">
         <v>45.05751734733581</v>
@@ -3991,55 +4013,55 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>30 jul</t>
+          <t>31 jul</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>162.5</v>
+        <v>154.9</v>
       </c>
       <c r="M9" t="n">
-        <v>163.16</v>
+        <v>158.26</v>
       </c>
       <c r="N9" t="n">
-        <v>155.2</v>
+        <v>153.6</v>
       </c>
       <c r="O9" t="n">
-        <v>155.92</v>
+        <v>157.68</v>
       </c>
       <c r="P9" t="n">
-        <v>144.3804</v>
+        <v>144.4984</v>
       </c>
       <c r="Q9" t="n">
-        <v>171.9849</v>
+        <v>171.6292</v>
       </c>
       <c r="R9" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S9" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>29 jul</t>
+          <t>30 jul</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>392.6608</v>
+        <v>437.0772</v>
       </c>
       <c r="W9" t="n">
-        <v>400.4961</v>
+        <v>457.8281</v>
       </c>
       <c r="X9" t="n">
-        <v>388.0095</v>
+        <v>431.6275</v>
       </c>
       <c r="Y9" t="n">
-        <v>389.8062</v>
+        <v>450.2524</v>
       </c>
       <c r="Z9" t="n">
-        <v>397.1057</v>
+        <v>397.6741</v>
       </c>
       <c r="AA9" t="n">
-        <v>431.9565</v>
+        <v>431.6738</v>
       </c>
       <c r="AB9" t="n">
         <v>535.3375423278808</v>
@@ -4051,26 +4073,26 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>31 jul</t>
+          <t>3 aug</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>38.6098</v>
+        <v>38.3128</v>
       </c>
       <c r="C10" t="n">
-        <v>39.575</v>
+        <v>39.4067</v>
       </c>
       <c r="D10" t="n">
-        <v>38.4464</v>
+        <v>38.2138</v>
       </c>
       <c r="E10" t="n">
-        <v>39.3226</v>
+        <v>39.4067</v>
       </c>
       <c r="F10" t="n">
-        <v>36.0495</v>
+        <v>36.1112</v>
       </c>
       <c r="G10" t="n">
-        <v>34.0907</v>
+        <v>34.1393</v>
       </c>
       <c r="H10" t="n">
         <v>45.05751734733581</v>
@@ -4080,55 +4102,55 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>31 jul</t>
+          <t>3 aug</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>154.9</v>
+        <v>160</v>
       </c>
       <c r="M10" t="n">
-        <v>158.26</v>
+        <v>168.7</v>
       </c>
       <c r="N10" t="n">
-        <v>153.6</v>
+        <v>159.6</v>
       </c>
       <c r="O10" t="n">
-        <v>157.68</v>
+        <v>164.64</v>
       </c>
       <c r="P10" t="n">
-        <v>144.4984</v>
+        <v>144.7016</v>
       </c>
       <c r="Q10" t="n">
-        <v>171.6292</v>
+        <v>171.301</v>
       </c>
       <c r="R10" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S10" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>30 jul</t>
+          <t>31 jul</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>437.0772</v>
+        <v>449.1545</v>
       </c>
       <c r="W10" t="n">
-        <v>457.8281</v>
+        <v>465.9628</v>
       </c>
       <c r="X10" t="n">
-        <v>431.6275</v>
+        <v>448.4857</v>
       </c>
       <c r="Y10" t="n">
-        <v>450.2524</v>
+        <v>463.8468</v>
       </c>
       <c r="Z10" t="n">
-        <v>397.6741</v>
+        <v>398.6364</v>
       </c>
       <c r="AA10" t="n">
-        <v>431.6738</v>
+        <v>431.4438</v>
       </c>
       <c r="AB10" t="n">
         <v>535.3375423278808</v>
@@ -4140,26 +4162,26 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3 aug</t>
+          <t>4 aug</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>38.3128</v>
+        <v>39.3028</v>
       </c>
       <c r="C11" t="n">
-        <v>39.4067</v>
+        <v>39.6443</v>
       </c>
       <c r="D11" t="n">
-        <v>38.2138</v>
+        <v>38.2039</v>
       </c>
       <c r="E11" t="n">
-        <v>39.4067</v>
+        <v>38.486</v>
       </c>
       <c r="F11" t="n">
-        <v>36.1112</v>
+        <v>36.1495</v>
       </c>
       <c r="G11" t="n">
-        <v>34.1393</v>
+        <v>34.1818</v>
       </c>
       <c r="H11" t="n">
         <v>45.05751734733581</v>
@@ -4169,55 +4191,55 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>3 aug</t>
+          <t>4 aug</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>160</v>
+        <v>162.86</v>
       </c>
       <c r="M11" t="n">
-        <v>168.7</v>
+        <v>168.56</v>
       </c>
       <c r="N11" t="n">
-        <v>159.6</v>
+        <v>162.4</v>
       </c>
       <c r="O11" t="n">
-        <v>164.64</v>
+        <v>167.38</v>
       </c>
       <c r="P11" t="n">
-        <v>144.7016</v>
+        <v>145.02</v>
       </c>
       <c r="Q11" t="n">
-        <v>171.301</v>
+        <v>170.9913</v>
       </c>
       <c r="R11" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S11" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>31 jul</t>
+          <t>3 aug</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>449.1545</v>
+        <v>475.2354</v>
       </c>
       <c r="W11" t="n">
-        <v>465.9628</v>
+        <v>490.7262</v>
       </c>
       <c r="X11" t="n">
-        <v>448.4857</v>
+        <v>474.1075</v>
       </c>
       <c r="Y11" t="n">
-        <v>463.8468</v>
+        <v>486.7337</v>
       </c>
       <c r="Z11" t="n">
-        <v>398.6364</v>
+        <v>399.9838</v>
       </c>
       <c r="AA11" t="n">
-        <v>431.4438</v>
+        <v>431.3306</v>
       </c>
       <c r="AB11" t="n">
         <v>535.3375423278808</v>
@@ -4229,26 +4251,26 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4 aug</t>
+          <t>5 aug</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>39.3028</v>
+        <v>38.4811</v>
       </c>
       <c r="C12" t="n">
-        <v>39.6443</v>
+        <v>38.7632</v>
       </c>
       <c r="D12" t="n">
-        <v>38.2039</v>
+        <v>37.9366</v>
       </c>
       <c r="E12" t="n">
-        <v>38.486</v>
+        <v>38.0307</v>
       </c>
       <c r="F12" t="n">
-        <v>36.1495</v>
+        <v>36.1966</v>
       </c>
       <c r="G12" t="n">
-        <v>34.1818</v>
+        <v>34.2215</v>
       </c>
       <c r="H12" t="n">
         <v>45.05751734733581</v>
@@ -4258,55 +4280,55 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>4 aug</t>
+          <t>5 aug</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>162.86</v>
+        <v>167.92</v>
       </c>
       <c r="M12" t="n">
-        <v>168.56</v>
+        <v>172.6</v>
       </c>
       <c r="N12" t="n">
-        <v>162.4</v>
+        <v>167.3</v>
       </c>
       <c r="O12" t="n">
-        <v>167.38</v>
+        <v>169.26</v>
       </c>
       <c r="P12" t="n">
-        <v>145.02</v>
+        <v>145.4052</v>
       </c>
       <c r="Q12" t="n">
-        <v>170.9913</v>
+        <v>170.7022</v>
       </c>
       <c r="R12" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S12" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>3 aug</t>
+          <t>4 aug</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>475.2354</v>
+        <v>479.9964</v>
       </c>
       <c r="W12" t="n">
-        <v>490.7262</v>
+        <v>498.5016</v>
       </c>
       <c r="X12" t="n">
-        <v>474.1075</v>
+        <v>478.2697</v>
       </c>
       <c r="Y12" t="n">
-        <v>486.7337</v>
+        <v>491.884</v>
       </c>
       <c r="Z12" t="n">
-        <v>399.9838</v>
+        <v>401.4555</v>
       </c>
       <c r="AA12" t="n">
-        <v>431.3306</v>
+        <v>431.2438</v>
       </c>
       <c r="AB12" t="n">
         <v>535.3375423278808</v>
@@ -4318,26 +4340,26 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5 aug</t>
+          <t>6 aug</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>38.4811</v>
+        <v>38.0752</v>
       </c>
       <c r="C13" t="n">
-        <v>38.7632</v>
+        <v>38.4069</v>
       </c>
       <c r="D13" t="n">
-        <v>37.9366</v>
+        <v>37.9168</v>
       </c>
       <c r="E13" t="n">
-        <v>38.0307</v>
+        <v>38.392</v>
       </c>
       <c r="F13" t="n">
-        <v>36.1966</v>
+        <v>36.2474</v>
       </c>
       <c r="G13" t="n">
-        <v>34.2215</v>
+        <v>34.2607</v>
       </c>
       <c r="H13" t="n">
         <v>45.05751734733581</v>
@@ -4347,55 +4369,55 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>5 aug</t>
+          <t>6 aug</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>167.92</v>
+        <v>171.44</v>
       </c>
       <c r="M13" t="n">
-        <v>172.6</v>
+        <v>173.1</v>
       </c>
       <c r="N13" t="n">
-        <v>167.3</v>
+        <v>168.08</v>
       </c>
       <c r="O13" t="n">
-        <v>169.26</v>
+        <v>170.98</v>
       </c>
       <c r="P13" t="n">
-        <v>145.4052</v>
+        <v>145.7928</v>
       </c>
       <c r="Q13" t="n">
-        <v>170.7022</v>
+        <v>170.384</v>
       </c>
       <c r="R13" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S13" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>4 aug</t>
+          <t>5 aug</t>
         </is>
       </c>
       <c r="V13" t="n">
-        <v>479.9964</v>
+        <v>495.4273</v>
       </c>
       <c r="W13" t="n">
-        <v>498.5016</v>
+        <v>497.3038</v>
       </c>
       <c r="X13" t="n">
-        <v>478.2697</v>
+        <v>484.7674</v>
       </c>
       <c r="Y13" t="n">
-        <v>491.884</v>
+        <v>486.5441</v>
       </c>
       <c r="Z13" t="n">
-        <v>401.4555</v>
+        <v>402.8307</v>
       </c>
       <c r="AA13" t="n">
-        <v>431.2438</v>
+        <v>431.1393</v>
       </c>
       <c r="AB13" t="n">
         <v>535.3375423278808</v>
@@ -4407,26 +4429,26 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6 aug</t>
+          <t>7 aug</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>38.0752</v>
+        <v>38.5207</v>
       </c>
       <c r="C14" t="n">
-        <v>38.4069</v>
+        <v>38.5999</v>
       </c>
       <c r="D14" t="n">
-        <v>37.9168</v>
+        <v>37.897</v>
       </c>
       <c r="E14" t="n">
-        <v>38.392</v>
+        <v>38.0059</v>
       </c>
       <c r="F14" t="n">
-        <v>36.2474</v>
+        <v>36.2952</v>
       </c>
       <c r="G14" t="n">
-        <v>34.2607</v>
+        <v>34.294</v>
       </c>
       <c r="H14" t="n">
         <v>45.05751734733581</v>
@@ -4436,55 +4458,55 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>6 aug</t>
+          <t>7 aug</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>171.44</v>
+        <v>173.82</v>
       </c>
       <c r="M14" t="n">
-        <v>173.1</v>
+        <v>179.56</v>
       </c>
       <c r="N14" t="n">
-        <v>168.08</v>
+        <v>173.82</v>
       </c>
       <c r="O14" t="n">
-        <v>170.98</v>
+        <v>177.96</v>
       </c>
       <c r="P14" t="n">
-        <v>145.7928</v>
+        <v>146.2468</v>
       </c>
       <c r="Q14" t="n">
-        <v>170.384</v>
+        <v>170.0918</v>
       </c>
       <c r="R14" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S14" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>5 aug</t>
+          <t>6 aug</t>
         </is>
       </c>
       <c r="V14" t="n">
-        <v>495.4273</v>
+        <v>487.632</v>
       </c>
       <c r="W14" t="n">
-        <v>497.3038</v>
+        <v>500.6176</v>
       </c>
       <c r="X14" t="n">
-        <v>484.7674</v>
+        <v>487.6021</v>
       </c>
       <c r="Y14" t="n">
-        <v>486.5441</v>
+        <v>498.9207</v>
       </c>
       <c r="Z14" t="n">
-        <v>402.8307</v>
+        <v>404.5041</v>
       </c>
       <c r="AA14" t="n">
-        <v>431.1393</v>
+        <v>431.087</v>
       </c>
       <c r="AB14" t="n">
         <v>535.3375423278808</v>
@@ -4496,26 +4518,26 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>7 aug</t>
+          <t>10 aug</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>38.5207</v>
+        <v>38.0356</v>
       </c>
       <c r="C15" t="n">
-        <v>38.5999</v>
+        <v>38.4366</v>
       </c>
       <c r="D15" t="n">
-        <v>37.897</v>
+        <v>37.803</v>
       </c>
       <c r="E15" t="n">
-        <v>38.0059</v>
+        <v>38.4019</v>
       </c>
       <c r="F15" t="n">
-        <v>36.2952</v>
+        <v>36.3315</v>
       </c>
       <c r="G15" t="n">
-        <v>34.294</v>
+        <v>34.3294</v>
       </c>
       <c r="H15" t="n">
         <v>45.05751734733581</v>
@@ -4525,55 +4547,55 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>7 aug</t>
+          <t>10 aug</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>173.82</v>
+        <v>178.92</v>
       </c>
       <c r="M15" t="n">
-        <v>179.56</v>
+        <v>179.96</v>
       </c>
       <c r="N15" t="n">
-        <v>173.82</v>
+        <v>175.86</v>
       </c>
       <c r="O15" t="n">
-        <v>177.96</v>
+        <v>179.3</v>
       </c>
       <c r="P15" t="n">
-        <v>146.2468</v>
+        <v>146.4748</v>
       </c>
       <c r="Q15" t="n">
-        <v>170.0918</v>
+        <v>169.8238</v>
       </c>
       <c r="R15" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S15" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>6 aug</t>
+          <t>7 aug</t>
         </is>
       </c>
       <c r="V15" t="n">
-        <v>487.632</v>
+        <v>498.272</v>
       </c>
       <c r="W15" t="n">
-        <v>500.6176</v>
+        <v>504.2308</v>
       </c>
       <c r="X15" t="n">
-        <v>487.6021</v>
+        <v>497.7929</v>
       </c>
       <c r="Y15" t="n">
-        <v>498.9207</v>
+        <v>499.0505</v>
       </c>
       <c r="Z15" t="n">
-        <v>404.5041</v>
+        <v>406.2472</v>
       </c>
       <c r="AA15" t="n">
-        <v>431.087</v>
+        <v>431.0194</v>
       </c>
       <c r="AB15" t="n">
         <v>535.3375423278808</v>
@@ -4585,26 +4607,26 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10 aug</t>
+          <t>11 aug</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>38.0356</v>
+        <v>38.7385</v>
       </c>
       <c r="C16" t="n">
-        <v>38.4366</v>
+        <v>39.0058</v>
       </c>
       <c r="D16" t="n">
-        <v>37.803</v>
+        <v>38.6148</v>
       </c>
       <c r="E16" t="n">
-        <v>38.4019</v>
+        <v>38.9662</v>
       </c>
       <c r="F16" t="n">
-        <v>36.3315</v>
+        <v>36.374</v>
       </c>
       <c r="G16" t="n">
-        <v>34.3294</v>
+        <v>34.3685</v>
       </c>
       <c r="H16" t="n">
         <v>45.05751734733581</v>
@@ -4614,55 +4636,55 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>10 aug</t>
+          <t>11 aug</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>178.92</v>
+        <v>180</v>
       </c>
       <c r="M16" t="n">
-        <v>179.96</v>
+        <v>183.24</v>
       </c>
       <c r="N16" t="n">
-        <v>175.86</v>
+        <v>178.14</v>
       </c>
       <c r="O16" t="n">
-        <v>179.3</v>
+        <v>180.7</v>
       </c>
       <c r="P16" t="n">
-        <v>146.4748</v>
+        <v>146.8316</v>
       </c>
       <c r="Q16" t="n">
-        <v>169.8238</v>
+        <v>169.5375</v>
       </c>
       <c r="R16" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S16" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>7 aug</t>
+          <t>10 aug</t>
         </is>
       </c>
       <c r="V16" t="n">
-        <v>498.272</v>
+        <v>502.4941</v>
       </c>
       <c r="W16" t="n">
-        <v>504.2308</v>
+        <v>512.7646999999999</v>
       </c>
       <c r="X16" t="n">
-        <v>497.7929</v>
+        <v>501.3262</v>
       </c>
       <c r="Y16" t="n">
-        <v>499.0505</v>
+        <v>505.1091</v>
       </c>
       <c r="Z16" t="n">
-        <v>406.2472</v>
+        <v>407.8257</v>
       </c>
       <c r="AA16" t="n">
-        <v>431.0194</v>
+        <v>430.9778</v>
       </c>
       <c r="AB16" t="n">
         <v>535.3375423278808</v>
@@ -4674,26 +4696,26 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>11 aug</t>
+          <t>12 aug</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>38.7385</v>
+        <v>38.8573</v>
       </c>
       <c r="C17" t="n">
-        <v>39.0058</v>
+        <v>38.986</v>
       </c>
       <c r="D17" t="n">
-        <v>38.6148</v>
+        <v>38.3871</v>
       </c>
       <c r="E17" t="n">
-        <v>38.9662</v>
+        <v>38.6494</v>
       </c>
       <c r="F17" t="n">
-        <v>36.374</v>
+        <v>36.3981</v>
       </c>
       <c r="G17" t="n">
-        <v>34.3685</v>
+        <v>34.4068</v>
       </c>
       <c r="H17" t="n">
         <v>45.05751734733581</v>
@@ -4703,55 +4725,55 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>11 aug</t>
+          <t>12 aug</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>180</v>
+        <v>180.3</v>
       </c>
       <c r="M17" t="n">
-        <v>183.24</v>
+        <v>180.98</v>
       </c>
       <c r="N17" t="n">
-        <v>178.14</v>
+        <v>175.4</v>
       </c>
       <c r="O17" t="n">
-        <v>180.7</v>
+        <v>175.96</v>
       </c>
       <c r="P17" t="n">
-        <v>146.8316</v>
+        <v>147.232</v>
       </c>
       <c r="Q17" t="n">
-        <v>169.5375</v>
+        <v>169.2701</v>
       </c>
       <c r="R17" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S17" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>10 aug</t>
+          <t>11 aug</t>
         </is>
       </c>
       <c r="V17" t="n">
-        <v>502.4941</v>
+        <v>503.3824</v>
       </c>
       <c r="W17" t="n">
-        <v>512.7646999999999</v>
+        <v>504.3805</v>
       </c>
       <c r="X17" t="n">
-        <v>501.3262</v>
+        <v>498.6113</v>
       </c>
       <c r="Y17" t="n">
-        <v>505.1091</v>
+        <v>502.8633</v>
       </c>
       <c r="Z17" t="n">
-        <v>407.8257</v>
+        <v>408.895</v>
       </c>
       <c r="AA17" t="n">
-        <v>430.9778</v>
+        <v>430.9106</v>
       </c>
       <c r="AB17" t="n">
         <v>535.3375423278808</v>
@@ -4763,26 +4785,26 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>12 aug</t>
+          <t>13 aug</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>38.8573</v>
+        <v>39</v>
       </c>
       <c r="C18" t="n">
-        <v>38.986</v>
+        <v>39.005</v>
       </c>
       <c r="D18" t="n">
-        <v>38.3871</v>
+        <v>38.2</v>
       </c>
       <c r="E18" t="n">
-        <v>38.6494</v>
+        <v>38.605</v>
       </c>
       <c r="F18" t="n">
-        <v>36.3981</v>
+        <v>36.4313</v>
       </c>
       <c r="G18" t="n">
-        <v>34.4068</v>
+        <v>34.4429</v>
       </c>
       <c r="H18" t="n">
         <v>45.05751734733581</v>
@@ -4792,55 +4814,55 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>12 aug</t>
+          <t>13 aug</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>180.3</v>
+        <v>177.48</v>
       </c>
       <c r="M18" t="n">
-        <v>180.98</v>
+        <v>178.3</v>
       </c>
       <c r="N18" t="n">
-        <v>175.4</v>
+        <v>174.8</v>
       </c>
       <c r="O18" t="n">
-        <v>175.96</v>
+        <v>175.38</v>
       </c>
       <c r="P18" t="n">
-        <v>147.232</v>
+        <v>147.4496</v>
       </c>
       <c r="Q18" t="n">
-        <v>169.2701</v>
+        <v>168.9889</v>
       </c>
       <c r="R18" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S18" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>11 aug</t>
+          <t>12 aug</t>
         </is>
       </c>
       <c r="V18" t="n">
-        <v>503.3824</v>
+        <v>499.0505</v>
       </c>
       <c r="W18" t="n">
-        <v>504.3805</v>
+        <v>500.5577</v>
       </c>
       <c r="X18" t="n">
-        <v>498.6113</v>
+        <v>490.5964</v>
       </c>
       <c r="Y18" t="n">
-        <v>502.8633</v>
+        <v>491.5047</v>
       </c>
       <c r="Z18" t="n">
-        <v>408.895</v>
+        <v>409.532</v>
       </c>
       <c r="AA18" t="n">
-        <v>430.9106</v>
+        <v>430.7866</v>
       </c>
       <c r="AB18" t="n">
         <v>535.3375423278808</v>
@@ -4852,26 +4874,26 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>13 aug</t>
+          <t>14 aug</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>39</v>
+        <v>38.65</v>
       </c>
       <c r="C19" t="n">
-        <v>39.005</v>
+        <v>39.1</v>
       </c>
       <c r="D19" t="n">
-        <v>38.2</v>
+        <v>38.56</v>
       </c>
       <c r="E19" t="n">
-        <v>38.605</v>
+        <v>38.97</v>
       </c>
       <c r="F19" t="n">
-        <v>36.4313</v>
+        <v>36.4703</v>
       </c>
       <c r="G19" t="n">
-        <v>34.4429</v>
+        <v>34.4805</v>
       </c>
       <c r="H19" t="n">
         <v>45.05751734733581</v>
@@ -4881,55 +4903,55 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>13 aug</t>
+          <t>14 aug</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>177.48</v>
+        <v>182</v>
       </c>
       <c r="M19" t="n">
-        <v>178.3</v>
+        <v>185.74</v>
       </c>
       <c r="N19" t="n">
-        <v>174.8</v>
+        <v>179.28</v>
       </c>
       <c r="O19" t="n">
-        <v>175.38</v>
+        <v>180.14</v>
       </c>
       <c r="P19" t="n">
-        <v>147.4496</v>
+        <v>147.8228</v>
       </c>
       <c r="Q19" t="n">
-        <v>168.9889</v>
+        <v>168.7386</v>
       </c>
       <c r="R19" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S19" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>12 aug</t>
+          <t>13 aug</t>
         </is>
       </c>
       <c r="V19" t="n">
-        <v>499.0505</v>
+        <v>492.3431</v>
       </c>
       <c r="W19" t="n">
-        <v>500.5577</v>
+        <v>500.398</v>
       </c>
       <c r="X19" t="n">
-        <v>490.5964</v>
+        <v>492.0837</v>
       </c>
       <c r="Y19" t="n">
-        <v>491.5047</v>
+        <v>495.9464</v>
       </c>
       <c r="Z19" t="n">
-        <v>409.532</v>
+        <v>410.6414</v>
       </c>
       <c r="AA19" t="n">
-        <v>430.7866</v>
+        <v>430.6696</v>
       </c>
       <c r="AB19" t="n">
         <v>535.3375423278808</v>
@@ -4941,26 +4963,26 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>14 aug</t>
+          <t>17 aug</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>38.65</v>
+        <v>38.97</v>
       </c>
       <c r="C20" t="n">
-        <v>39.1</v>
+        <v>39.27</v>
       </c>
       <c r="D20" t="n">
-        <v>38.56</v>
+        <v>38.765</v>
       </c>
       <c r="E20" t="n">
-        <v>38.97</v>
+        <v>39.15</v>
       </c>
       <c r="F20" t="n">
-        <v>36.4703</v>
+        <v>36.5118</v>
       </c>
       <c r="G20" t="n">
-        <v>34.4805</v>
+        <v>34.5207</v>
       </c>
       <c r="H20" t="n">
         <v>45.05751734733581</v>
@@ -4970,55 +4992,55 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>14 aug</t>
+          <t>17 aug</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>182</v>
+        <v>178.94</v>
       </c>
       <c r="M20" t="n">
-        <v>185.74</v>
+        <v>180.9</v>
       </c>
       <c r="N20" t="n">
-        <v>179.28</v>
+        <v>177.66</v>
       </c>
       <c r="O20" t="n">
-        <v>180.14</v>
+        <v>179.58</v>
       </c>
       <c r="P20" t="n">
-        <v>147.8228</v>
+        <v>148.2524</v>
       </c>
       <c r="Q20" t="n">
-        <v>168.7386</v>
+        <v>168.5337</v>
       </c>
       <c r="R20" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S20" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>13 aug</t>
+          <t>14 aug</t>
         </is>
       </c>
       <c r="V20" t="n">
-        <v>492.3431</v>
+        <v>495.4273</v>
       </c>
       <c r="W20" t="n">
-        <v>500.398</v>
+        <v>499.0705</v>
       </c>
       <c r="X20" t="n">
-        <v>492.0837</v>
+        <v>492.9919</v>
       </c>
       <c r="Y20" t="n">
-        <v>495.9464</v>
+        <v>494.4691</v>
       </c>
       <c r="Z20" t="n">
-        <v>410.6414</v>
+        <v>412</v>
       </c>
       <c r="AA20" t="n">
-        <v>430.6696</v>
+        <v>430.5061</v>
       </c>
       <c r="AB20" t="n">
         <v>535.3375423278808</v>
@@ -5030,26 +5052,26 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>17 aug</t>
+          <t>18 aug</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>38.97</v>
+        <v>39.49</v>
       </c>
       <c r="C21" t="n">
-        <v>39.27</v>
+        <v>39.945</v>
       </c>
       <c r="D21" t="n">
-        <v>38.765</v>
+        <v>39.46</v>
       </c>
       <c r="E21" t="n">
-        <v>39.15</v>
+        <v>39.785</v>
       </c>
       <c r="F21" t="n">
-        <v>36.5118</v>
+        <v>36.5781</v>
       </c>
       <c r="G21" t="n">
-        <v>34.5207</v>
+        <v>34.5641</v>
       </c>
       <c r="H21" t="n">
         <v>45.05751734733581</v>
@@ -5059,55 +5081,55 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>17 aug</t>
+          <t>18 aug</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>178.94</v>
+        <v>179.14</v>
       </c>
       <c r="M21" t="n">
-        <v>180.9</v>
+        <v>183.9</v>
       </c>
       <c r="N21" t="n">
-        <v>177.66</v>
+        <v>177.98</v>
       </c>
       <c r="O21" t="n">
-        <v>179.58</v>
+        <v>182.5</v>
       </c>
       <c r="P21" t="n">
-        <v>148.2524</v>
+        <v>148.8084</v>
       </c>
       <c r="Q21" t="n">
-        <v>168.5337</v>
+        <v>168.3358</v>
       </c>
       <c r="R21" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S21" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>14 aug</t>
+          <t>17 aug</t>
         </is>
       </c>
       <c r="V21" t="n">
-        <v>495.4273</v>
+        <v>489.2191</v>
       </c>
       <c r="W21" t="n">
-        <v>499.0705</v>
+        <v>491.7343</v>
       </c>
       <c r="X21" t="n">
-        <v>492.9919</v>
+        <v>477.5111</v>
       </c>
       <c r="Y21" t="n">
-        <v>494.4691</v>
+        <v>479.4474</v>
       </c>
       <c r="Z21" t="n">
-        <v>412</v>
+        <v>413.044</v>
       </c>
       <c r="AA21" t="n">
-        <v>430.5061</v>
+        <v>430.2151</v>
       </c>
       <c r="AB21" t="n">
         <v>535.3375423278808</v>
@@ -5119,26 +5141,26 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>18 aug</t>
+          <t>19 aug</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>39.49</v>
+        <v>39.835</v>
       </c>
       <c r="C22" t="n">
-        <v>39.945</v>
+        <v>40.14</v>
       </c>
       <c r="D22" t="n">
-        <v>39.46</v>
+        <v>39.74</v>
       </c>
       <c r="E22" t="n">
-        <v>39.785</v>
+        <v>39.94</v>
       </c>
       <c r="F22" t="n">
-        <v>36.5781</v>
+        <v>36.6336</v>
       </c>
       <c r="G22" t="n">
-        <v>34.5641</v>
+        <v>34.6092</v>
       </c>
       <c r="H22" t="n">
         <v>45.05751734733581</v>
@@ -5148,55 +5170,55 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>18 aug</t>
+          <t>19 aug</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>179.14</v>
+        <v>181.7</v>
       </c>
       <c r="M22" t="n">
-        <v>183.9</v>
+        <v>186.98</v>
       </c>
       <c r="N22" t="n">
-        <v>177.98</v>
+        <v>180.38</v>
       </c>
       <c r="O22" t="n">
-        <v>182.5</v>
+        <v>185.9</v>
       </c>
       <c r="P22" t="n">
-        <v>148.8084</v>
+        <v>149.5324</v>
       </c>
       <c r="Q22" t="n">
-        <v>168.3358</v>
+        <v>168.1618</v>
       </c>
       <c r="R22" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S22" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>17 aug</t>
+          <t>18 aug</t>
         </is>
       </c>
       <c r="V22" t="n">
-        <v>489.2191</v>
+        <v>480.6352</v>
       </c>
       <c r="W22" t="n">
-        <v>491.7343</v>
+        <v>483.3601</v>
       </c>
       <c r="X22" t="n">
-        <v>477.5111</v>
+        <v>476.2534</v>
       </c>
       <c r="Y22" t="n">
-        <v>479.4474</v>
+        <v>480.725</v>
       </c>
       <c r="Z22" t="n">
-        <v>413.044</v>
+        <v>414.3408</v>
       </c>
       <c r="AA22" t="n">
-        <v>430.2151</v>
+        <v>429.933</v>
       </c>
       <c r="AB22" t="n">
         <v>535.3375423278808</v>
@@ -5208,26 +5230,26 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>19 aug</t>
+          <t>20 aug</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>39.835</v>
+        <v>39.865</v>
       </c>
       <c r="C23" t="n">
-        <v>40.14</v>
+        <v>40.51</v>
       </c>
       <c r="D23" t="n">
-        <v>39.74</v>
+        <v>39.8</v>
       </c>
       <c r="E23" t="n">
-        <v>39.94</v>
+        <v>40.28</v>
       </c>
       <c r="F23" t="n">
-        <v>36.6336</v>
+        <v>36.6884</v>
       </c>
       <c r="G23" t="n">
-        <v>34.6092</v>
+        <v>34.6545</v>
       </c>
       <c r="H23" t="n">
         <v>45.05751734733581</v>
@@ -5237,55 +5259,55 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>19 aug</t>
+          <t>20 aug</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>181.7</v>
+        <v>183.78</v>
       </c>
       <c r="M23" t="n">
-        <v>186.98</v>
+        <v>186.1</v>
       </c>
       <c r="N23" t="n">
-        <v>180.38</v>
+        <v>182.52</v>
       </c>
       <c r="O23" t="n">
-        <v>185.9</v>
+        <v>185.64</v>
       </c>
       <c r="P23" t="n">
-        <v>149.5324</v>
+        <v>150.4472</v>
       </c>
       <c r="Q23" t="n">
-        <v>168.1618</v>
+        <v>167.9648</v>
       </c>
       <c r="R23" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S23" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>18 aug</t>
+          <t>19 aug</t>
         </is>
       </c>
       <c r="V23" t="n">
-        <v>480.6352</v>
+        <v>479.168</v>
       </c>
       <c r="W23" t="n">
-        <v>483.3601</v>
+        <v>488.3806</v>
       </c>
       <c r="X23" t="n">
-        <v>476.2534</v>
+        <v>478.4593</v>
       </c>
       <c r="Y23" t="n">
-        <v>480.725</v>
+        <v>483.4</v>
       </c>
       <c r="Z23" t="n">
-        <v>414.3408</v>
+        <v>415.7895</v>
       </c>
       <c r="AA23" t="n">
-        <v>429.933</v>
+        <v>429.7427</v>
       </c>
       <c r="AB23" t="n">
         <v>535.3375423278808</v>
@@ -5297,26 +5319,26 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20 aug</t>
+          <t>21 aug</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>39.865</v>
+        <v>40.1</v>
       </c>
       <c r="C24" t="n">
-        <v>40.51</v>
+        <v>40.37</v>
       </c>
       <c r="D24" t="n">
-        <v>39.8</v>
+        <v>39.84</v>
       </c>
       <c r="E24" t="n">
-        <v>40.28</v>
+        <v>39.91</v>
       </c>
       <c r="F24" t="n">
-        <v>36.6884</v>
+        <v>36.7478</v>
       </c>
       <c r="G24" t="n">
-        <v>34.6545</v>
+        <v>34.6988</v>
       </c>
       <c r="H24" t="n">
         <v>45.05751734733581</v>
@@ -5326,55 +5348,55 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>20 aug</t>
+          <t>21 aug</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>183.78</v>
+        <v>185.18</v>
       </c>
       <c r="M24" t="n">
-        <v>186.1</v>
+        <v>188.4</v>
       </c>
       <c r="N24" t="n">
-        <v>182.52</v>
+        <v>183.6</v>
       </c>
       <c r="O24" t="n">
-        <v>185.64</v>
+        <v>188.12</v>
       </c>
       <c r="P24" t="n">
-        <v>150.4472</v>
+        <v>151.4044</v>
       </c>
       <c r="Q24" t="n">
-        <v>167.9648</v>
+        <v>167.794</v>
       </c>
       <c r="R24" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S24" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>19 aug</t>
+          <t>20 aug</t>
         </is>
       </c>
       <c r="V24" t="n">
-        <v>479.168</v>
+        <v>483.3</v>
       </c>
       <c r="W24" t="n">
-        <v>488.3806</v>
+        <v>484.16</v>
       </c>
       <c r="X24" t="n">
-        <v>478.4593</v>
+        <v>479.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>483.4</v>
+        <v>481.15</v>
       </c>
       <c r="Z24" t="n">
-        <v>415.7895</v>
+        <v>417.3594</v>
       </c>
       <c r="AA24" t="n">
-        <v>429.7427</v>
+        <v>429.5805</v>
       </c>
       <c r="AB24" t="n">
         <v>535.3375423278808</v>
@@ -5386,26 +5408,26 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>21 aug</t>
+          <t>24 aug</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>40.1</v>
+        <v>39.88</v>
       </c>
       <c r="C25" t="n">
-        <v>40.37</v>
+        <v>40.085</v>
       </c>
       <c r="D25" t="n">
-        <v>39.84</v>
+        <v>39.68</v>
       </c>
       <c r="E25" t="n">
-        <v>39.91</v>
+        <v>39.775</v>
       </c>
       <c r="F25" t="n">
-        <v>36.7478</v>
+        <v>36.8369</v>
       </c>
       <c r="G25" t="n">
-        <v>34.6988</v>
+        <v>34.7421</v>
       </c>
       <c r="H25" t="n">
         <v>45.05751734733581</v>
@@ -5415,55 +5437,55 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>21 aug</t>
+          <t>24 aug</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>185.18</v>
+        <v>186.86</v>
       </c>
       <c r="M25" t="n">
-        <v>188.4</v>
+        <v>188.16</v>
       </c>
       <c r="N25" t="n">
-        <v>183.6</v>
+        <v>185.52</v>
       </c>
       <c r="O25" t="n">
-        <v>188.12</v>
+        <v>187.2</v>
       </c>
       <c r="P25" t="n">
-        <v>151.4044</v>
+        <v>152.2848</v>
       </c>
       <c r="Q25" t="n">
-        <v>167.794</v>
+        <v>167.6093</v>
       </c>
       <c r="R25" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S25" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>20 aug</t>
+          <t>21 aug</t>
         </is>
       </c>
       <c r="V25" t="n">
-        <v>483.3</v>
+        <v>479.88</v>
       </c>
       <c r="W25" t="n">
-        <v>484.16</v>
+        <v>486.36</v>
       </c>
       <c r="X25" t="n">
-        <v>479.5</v>
+        <v>478.53</v>
       </c>
       <c r="Y25" t="n">
-        <v>481.15</v>
+        <v>483.24</v>
       </c>
       <c r="Z25" t="n">
-        <v>417.3594</v>
+        <v>419.092</v>
       </c>
       <c r="AA25" t="n">
-        <v>429.5805</v>
+        <v>429.4327</v>
       </c>
       <c r="AB25" t="n">
         <v>535.3375423278808</v>
@@ -5475,26 +5497,26 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>24 aug</t>
+          <t>25 aug</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>39.88</v>
+        <v>39.77</v>
       </c>
       <c r="C26" t="n">
-        <v>40.085</v>
+        <v>39.915</v>
       </c>
       <c r="D26" t="n">
-        <v>39.68</v>
+        <v>39.385</v>
       </c>
       <c r="E26" t="n">
-        <v>39.775</v>
+        <v>39.6</v>
       </c>
       <c r="F26" t="n">
-        <v>36.8369</v>
+        <v>36.926</v>
       </c>
       <c r="G26" t="n">
-        <v>34.7421</v>
+        <v>34.783</v>
       </c>
       <c r="H26" t="n">
         <v>45.05751734733581</v>
@@ -5504,55 +5526,55 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>24 aug</t>
+          <t>25 aug</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>186.86</v>
+        <v>186.4</v>
       </c>
       <c r="M26" t="n">
-        <v>188.16</v>
+        <v>187.62</v>
       </c>
       <c r="N26" t="n">
-        <v>185.52</v>
+        <v>182.74</v>
       </c>
       <c r="O26" t="n">
-        <v>187.2</v>
+        <v>185.46</v>
       </c>
       <c r="P26" t="n">
-        <v>152.2848</v>
+        <v>153.136</v>
       </c>
       <c r="Q26" t="n">
-        <v>167.6093</v>
+        <v>167.4651</v>
       </c>
       <c r="R26" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S26" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>21 aug</t>
+          <t>24 aug</t>
         </is>
       </c>
       <c r="V26" t="n">
-        <v>479.88</v>
+        <v>483.21</v>
       </c>
       <c r="W26" t="n">
-        <v>486.36</v>
+        <v>490.61</v>
       </c>
       <c r="X26" t="n">
-        <v>478.53</v>
+        <v>481.86</v>
       </c>
       <c r="Y26" t="n">
-        <v>483.24</v>
+        <v>487.31</v>
       </c>
       <c r="Z26" t="n">
-        <v>419.092</v>
+        <v>421.046</v>
       </c>
       <c r="AA26" t="n">
-        <v>429.4327</v>
+        <v>429.3185</v>
       </c>
       <c r="AB26" t="n">
         <v>535.3375423278808</v>
@@ -5564,26 +5586,26 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>25 aug</t>
+          <t>26 aug</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>39.77</v>
+        <v>39.275</v>
       </c>
       <c r="C27" t="n">
-        <v>39.915</v>
+        <v>39.47</v>
       </c>
       <c r="D27" t="n">
-        <v>39.385</v>
+        <v>38.91</v>
       </c>
       <c r="E27" t="n">
-        <v>39.6</v>
+        <v>39.42</v>
       </c>
       <c r="F27" t="n">
-        <v>36.926</v>
+        <v>37.0192</v>
       </c>
       <c r="G27" t="n">
-        <v>34.783</v>
+        <v>34.8202</v>
       </c>
       <c r="H27" t="n">
         <v>45.05751734733581</v>
@@ -5593,55 +5615,55 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>25 aug</t>
+          <t>26 aug</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>186.4</v>
+        <v>179.92</v>
       </c>
       <c r="M27" t="n">
-        <v>187.62</v>
+        <v>182.16</v>
       </c>
       <c r="N27" t="n">
-        <v>182.74</v>
+        <v>176.82</v>
       </c>
       <c r="O27" t="n">
-        <v>185.46</v>
+        <v>180.02</v>
       </c>
       <c r="P27" t="n">
-        <v>153.136</v>
+        <v>153.9128</v>
       </c>
       <c r="Q27" t="n">
-        <v>167.4651</v>
+        <v>167.3049</v>
       </c>
       <c r="R27" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S27" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>24 aug</t>
+          <t>25 aug</t>
         </is>
       </c>
       <c r="V27" t="n">
-        <v>483.21</v>
+        <v>485.44</v>
       </c>
       <c r="W27" t="n">
-        <v>490.61</v>
+        <v>492.44</v>
       </c>
       <c r="X27" t="n">
-        <v>481.86</v>
+        <v>484.3</v>
       </c>
       <c r="Y27" t="n">
-        <v>487.31</v>
+        <v>491.71</v>
       </c>
       <c r="Z27" t="n">
-        <v>421.046</v>
+        <v>423.0801</v>
       </c>
       <c r="AA27" t="n">
-        <v>429.3185</v>
+        <v>429.262</v>
       </c>
       <c r="AB27" t="n">
         <v>535.3375423278808</v>
@@ -5653,26 +5675,26 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>26 aug</t>
+          <t>27 aug</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>39.275</v>
+        <v>39.16</v>
       </c>
       <c r="C28" t="n">
-        <v>39.47</v>
+        <v>39.295</v>
       </c>
       <c r="D28" t="n">
-        <v>38.91</v>
+        <v>38.65</v>
       </c>
       <c r="E28" t="n">
-        <v>39.42</v>
+        <v>38.76</v>
       </c>
       <c r="F28" t="n">
-        <v>37.0192</v>
+        <v>37.117</v>
       </c>
       <c r="G28" t="n">
-        <v>34.8202</v>
+        <v>34.8559</v>
       </c>
       <c r="H28" t="n">
         <v>45.05751734733581</v>
@@ -5682,55 +5704,55 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>26 aug</t>
+          <t>27 aug</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>179.92</v>
+        <v>182.5</v>
       </c>
       <c r="M28" t="n">
-        <v>182.16</v>
+        <v>190.8</v>
       </c>
       <c r="N28" t="n">
-        <v>176.82</v>
+        <v>181.14</v>
       </c>
       <c r="O28" t="n">
-        <v>180.02</v>
+        <v>189.88</v>
       </c>
       <c r="P28" t="n">
-        <v>153.9128</v>
+        <v>155.0132</v>
       </c>
       <c r="Q28" t="n">
-        <v>167.3049</v>
+        <v>167.1911</v>
       </c>
       <c r="R28" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S28" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>25 aug</t>
+          <t>26 aug</t>
         </is>
       </c>
       <c r="V28" t="n">
-        <v>485.44</v>
+        <v>487.85</v>
       </c>
       <c r="W28" t="n">
-        <v>492.44</v>
+        <v>497.4</v>
       </c>
       <c r="X28" t="n">
-        <v>484.3</v>
+        <v>487.31</v>
       </c>
       <c r="Y28" t="n">
-        <v>491.71</v>
+        <v>496.37</v>
       </c>
       <c r="Z28" t="n">
-        <v>423.0801</v>
+        <v>425.0273</v>
       </c>
       <c r="AA28" t="n">
-        <v>429.262</v>
+        <v>429.2786</v>
       </c>
       <c r="AB28" t="n">
         <v>535.3375423278808</v>
@@ -5742,26 +5764,26 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>27 aug</t>
+          <t>28 aug</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>39.16</v>
+        <v>39</v>
       </c>
       <c r="C29" t="n">
-        <v>39.295</v>
+        <v>39.18</v>
       </c>
       <c r="D29" t="n">
-        <v>38.65</v>
+        <v>38.845</v>
       </c>
       <c r="E29" t="n">
-        <v>38.76</v>
+        <v>39.145</v>
       </c>
       <c r="F29" t="n">
-        <v>37.117</v>
+        <v>37.2162</v>
       </c>
       <c r="G29" t="n">
-        <v>34.8559</v>
+        <v>34.8941</v>
       </c>
       <c r="H29" t="n">
         <v>45.05751734733581</v>
@@ -5771,55 +5793,55 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>27 aug</t>
+          <t>28 aug</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>182.5</v>
+        <v>189.5</v>
       </c>
       <c r="M29" t="n">
-        <v>190.8</v>
+        <v>191.94</v>
       </c>
       <c r="N29" t="n">
-        <v>181.14</v>
+        <v>187.98</v>
       </c>
       <c r="O29" t="n">
-        <v>189.88</v>
+        <v>191.32</v>
       </c>
       <c r="P29" t="n">
-        <v>155.0132</v>
+        <v>156.1568</v>
       </c>
       <c r="Q29" t="n">
-        <v>167.1911</v>
+        <v>167.0806</v>
       </c>
       <c r="R29" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S29" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>26 aug</t>
+          <t>27 aug</t>
         </is>
       </c>
       <c r="V29" t="n">
-        <v>487.85</v>
+        <v>494.88</v>
       </c>
       <c r="W29" t="n">
-        <v>497.4</v>
+        <v>506.48</v>
       </c>
       <c r="X29" t="n">
-        <v>487.31</v>
+        <v>490.08</v>
       </c>
       <c r="Y29" t="n">
-        <v>496.37</v>
+        <v>505.06</v>
       </c>
       <c r="Z29" t="n">
-        <v>425.0273</v>
+        <v>427.2667</v>
       </c>
       <c r="AA29" t="n">
-        <v>429.2786</v>
+        <v>429.3401</v>
       </c>
       <c r="AB29" t="n">
         <v>535.3375423278808</v>
@@ -5831,26 +5853,26 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>28 aug</t>
+          <t>31 aug</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>39</v>
+        <v>39.54</v>
       </c>
       <c r="C30" t="n">
-        <v>39.18</v>
+        <v>39.91</v>
       </c>
       <c r="D30" t="n">
-        <v>38.845</v>
+        <v>39.24</v>
       </c>
       <c r="E30" t="n">
-        <v>39.145</v>
+        <v>39.335</v>
       </c>
       <c r="F30" t="n">
-        <v>37.2162</v>
+        <v>37.3111</v>
       </c>
       <c r="G30" t="n">
-        <v>34.8941</v>
+        <v>34.9333</v>
       </c>
       <c r="H30" t="n">
         <v>45.05751734733581</v>
@@ -5860,55 +5882,55 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>28 aug</t>
+          <t>31 aug</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>189.5</v>
+        <v>188.46</v>
       </c>
       <c r="M30" t="n">
-        <v>191.94</v>
+        <v>192.12</v>
       </c>
       <c r="N30" t="n">
-        <v>187.98</v>
+        <v>188.2</v>
       </c>
       <c r="O30" t="n">
-        <v>191.32</v>
+        <v>190.9</v>
       </c>
       <c r="P30" t="n">
-        <v>156.1568</v>
+        <v>157.3304</v>
       </c>
       <c r="Q30" t="n">
-        <v>167.0806</v>
+        <v>166.9613</v>
       </c>
       <c r="R30" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S30" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>27 aug</t>
+          <t>28 aug</t>
         </is>
       </c>
       <c r="V30" t="n">
-        <v>494.88</v>
+        <v>505.33</v>
       </c>
       <c r="W30" t="n">
-        <v>506.48</v>
+        <v>517.78</v>
       </c>
       <c r="X30" t="n">
-        <v>490.08</v>
+        <v>504.87</v>
       </c>
       <c r="Y30" t="n">
-        <v>505.06</v>
+        <v>513.53</v>
       </c>
       <c r="Z30" t="n">
-        <v>427.2667</v>
+        <v>429.9734</v>
       </c>
       <c r="AA30" t="n">
-        <v>429.3401</v>
+        <v>429.3984</v>
       </c>
       <c r="AB30" t="n">
         <v>535.3375423278808</v>
@@ -5920,26 +5942,26 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>31 aug</t>
+          <t>1 sep</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>39.54</v>
+        <v>39.77</v>
       </c>
       <c r="C31" t="n">
-        <v>39.91</v>
+        <v>40.19</v>
       </c>
       <c r="D31" t="n">
-        <v>39.24</v>
+        <v>39.645</v>
       </c>
       <c r="E31" t="n">
-        <v>39.335</v>
+        <v>40.155</v>
       </c>
       <c r="F31" t="n">
-        <v>37.3111</v>
+        <v>37.4239</v>
       </c>
       <c r="G31" t="n">
-        <v>34.9333</v>
+        <v>34.9763</v>
       </c>
       <c r="H31" t="n">
         <v>45.05751734733581</v>
@@ -5949,55 +5971,55 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>31 aug</t>
+          <t>1 sep</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>188.46</v>
+        <v>186</v>
       </c>
       <c r="M31" t="n">
-        <v>192.12</v>
+        <v>187.86</v>
       </c>
       <c r="N31" t="n">
-        <v>188.2</v>
+        <v>183.32</v>
       </c>
       <c r="O31" t="n">
-        <v>190.9</v>
+        <v>184.26</v>
       </c>
       <c r="P31" t="n">
-        <v>157.3304</v>
+        <v>158.3252</v>
       </c>
       <c r="Q31" t="n">
-        <v>166.9613</v>
+        <v>166.8103</v>
       </c>
       <c r="R31" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S31" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>28 aug</t>
+          <t>31 aug</t>
         </is>
       </c>
       <c r="V31" t="n">
-        <v>505.33</v>
+        <v>510.38</v>
       </c>
       <c r="W31" t="n">
-        <v>517.78</v>
+        <v>512.1900000000001</v>
       </c>
       <c r="X31" t="n">
-        <v>504.87</v>
+        <v>506.39</v>
       </c>
       <c r="Y31" t="n">
-        <v>513.53</v>
+        <v>507.29</v>
       </c>
       <c r="Z31" t="n">
-        <v>429.9734</v>
+        <v>432.5454</v>
       </c>
       <c r="AA31" t="n">
-        <v>429.3984</v>
+        <v>429.4122</v>
       </c>
       <c r="AB31" t="n">
         <v>535.3375423278808</v>
@@ -6009,26 +6031,26 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1 sep</t>
+          <t>2 sep</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>39.77</v>
+        <v>40.35</v>
       </c>
       <c r="C32" t="n">
-        <v>40.19</v>
+        <v>40.615</v>
       </c>
       <c r="D32" t="n">
-        <v>39.645</v>
+        <v>39.975</v>
       </c>
       <c r="E32" t="n">
-        <v>40.155</v>
+        <v>40.21</v>
       </c>
       <c r="F32" t="n">
-        <v>37.4239</v>
+        <v>37.5499</v>
       </c>
       <c r="G32" t="n">
-        <v>34.9763</v>
+        <v>35.0217</v>
       </c>
       <c r="H32" t="n">
         <v>45.05751734733581</v>
@@ -6038,55 +6060,55 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1 sep</t>
+          <t>2 sep</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>186</v>
+        <v>182.18</v>
       </c>
       <c r="M32" t="n">
-        <v>187.86</v>
+        <v>184.7</v>
       </c>
       <c r="N32" t="n">
-        <v>183.32</v>
+        <v>180.72</v>
       </c>
       <c r="O32" t="n">
-        <v>184.26</v>
+        <v>181.44</v>
       </c>
       <c r="P32" t="n">
-        <v>158.3252</v>
+        <v>159.2568</v>
       </c>
       <c r="Q32" t="n">
-        <v>166.8103</v>
+        <v>166.6796</v>
       </c>
       <c r="R32" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S32" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>31 aug</t>
+          <t>1 sep</t>
         </is>
       </c>
       <c r="V32" t="n">
-        <v>510.38</v>
+        <v>497.52</v>
       </c>
       <c r="W32" t="n">
-        <v>512.1900000000001</v>
+        <v>505.97</v>
       </c>
       <c r="X32" t="n">
-        <v>506.39</v>
+        <v>496.78</v>
       </c>
       <c r="Y32" t="n">
-        <v>507.29</v>
+        <v>501.02</v>
       </c>
       <c r="Z32" t="n">
-        <v>432.5454</v>
+        <v>435.2328</v>
       </c>
       <c r="AA32" t="n">
-        <v>429.4122</v>
+        <v>429.3825</v>
       </c>
       <c r="AB32" t="n">
         <v>535.3375423278808</v>
@@ -6098,26 +6120,26 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2 sep</t>
+          <t>3 sep</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>40.35</v>
+        <v>40.095</v>
       </c>
       <c r="C33" t="n">
-        <v>40.615</v>
+        <v>40.215</v>
       </c>
       <c r="D33" t="n">
-        <v>39.975</v>
+        <v>39.54</v>
       </c>
       <c r="E33" t="n">
-        <v>40.21</v>
+        <v>40.04</v>
       </c>
       <c r="F33" t="n">
-        <v>37.5499</v>
+        <v>37.6767</v>
       </c>
       <c r="G33" t="n">
-        <v>35.0217</v>
+        <v>35.0679</v>
       </c>
       <c r="H33" t="n">
         <v>45.05751734733581</v>
@@ -6127,55 +6149,55 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2 sep</t>
+          <t>3 sep</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>182.18</v>
+        <v>182.08</v>
       </c>
       <c r="M33" t="n">
-        <v>184.7</v>
+        <v>187.56</v>
       </c>
       <c r="N33" t="n">
-        <v>180.72</v>
+        <v>182</v>
       </c>
       <c r="O33" t="n">
-        <v>181.44</v>
+        <v>185.58</v>
       </c>
       <c r="P33" t="n">
-        <v>159.2568</v>
+        <v>160.3228</v>
       </c>
       <c r="Q33" t="n">
-        <v>166.6796</v>
+        <v>166.5898</v>
       </c>
       <c r="R33" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S33" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>1 sep</t>
+          <t>2 sep</t>
         </is>
       </c>
       <c r="V33" t="n">
-        <v>497.52</v>
+        <v>499.85</v>
       </c>
       <c r="W33" t="n">
-        <v>505.97</v>
+        <v>500.27</v>
       </c>
       <c r="X33" t="n">
-        <v>496.78</v>
+        <v>493.81</v>
       </c>
       <c r="Y33" t="n">
-        <v>501.02</v>
+        <v>496.82</v>
       </c>
       <c r="Z33" t="n">
-        <v>435.2328</v>
+        <v>437.7045</v>
       </c>
       <c r="AA33" t="n">
-        <v>429.3825</v>
+        <v>429.3706</v>
       </c>
       <c r="AB33" t="n">
         <v>535.3375423278808</v>
@@ -6187,26 +6209,26 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3 sep</t>
+          <t>4 sep</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>40.095</v>
+        <v>40.145</v>
       </c>
       <c r="C34" t="n">
-        <v>40.215</v>
+        <v>40.28</v>
       </c>
       <c r="D34" t="n">
-        <v>39.54</v>
+        <v>39.665</v>
       </c>
       <c r="E34" t="n">
-        <v>40.04</v>
+        <v>40.105</v>
       </c>
       <c r="F34" t="n">
-        <v>37.6767</v>
+        <v>37.8115</v>
       </c>
       <c r="G34" t="n">
-        <v>35.0679</v>
+        <v>35.113</v>
       </c>
       <c r="H34" t="n">
         <v>45.05751734733581</v>
@@ -6216,55 +6238,55 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>3 sep</t>
+          <t>4 sep</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>182.08</v>
+        <v>187.8</v>
       </c>
       <c r="M34" t="n">
-        <v>187.56</v>
+        <v>189.9</v>
       </c>
       <c r="N34" t="n">
-        <v>182</v>
+        <v>184.96</v>
       </c>
       <c r="O34" t="n">
-        <v>185.58</v>
+        <v>185.68</v>
       </c>
       <c r="P34" t="n">
-        <v>160.3228</v>
+        <v>161.3336</v>
       </c>
       <c r="Q34" t="n">
-        <v>166.5898</v>
+        <v>166.5086</v>
       </c>
       <c r="R34" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S34" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>2 sep</t>
+          <t>3 sep</t>
         </is>
       </c>
       <c r="V34" t="n">
-        <v>499.85</v>
+        <v>501.66</v>
       </c>
       <c r="W34" t="n">
-        <v>500.27</v>
+        <v>515.65</v>
       </c>
       <c r="X34" t="n">
-        <v>493.81</v>
+        <v>500.8</v>
       </c>
       <c r="Y34" t="n">
-        <v>496.82</v>
+        <v>510.12</v>
       </c>
       <c r="Z34" t="n">
-        <v>437.7045</v>
+        <v>440.6114</v>
       </c>
       <c r="AA34" t="n">
-        <v>429.3706</v>
+        <v>429.3912</v>
       </c>
       <c r="AB34" t="n">
         <v>535.3375423278808</v>
@@ -6276,26 +6298,26 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>4 sep</t>
+          <t>7 sep</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>40.145</v>
+        <v>40.26</v>
       </c>
       <c r="C35" t="n">
-        <v>40.28</v>
+        <v>40.845</v>
       </c>
       <c r="D35" t="n">
-        <v>39.665</v>
+        <v>40.12</v>
       </c>
       <c r="E35" t="n">
-        <v>40.105</v>
+        <v>40.56</v>
       </c>
       <c r="F35" t="n">
-        <v>37.8115</v>
+        <v>37.9551</v>
       </c>
       <c r="G35" t="n">
-        <v>35.113</v>
+        <v>35.1619</v>
       </c>
       <c r="H35" t="n">
         <v>45.05751734733581</v>
@@ -6305,55 +6327,55 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>4 sep</t>
+          <t>7 sep</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>187.8</v>
+        <v>183.56</v>
       </c>
       <c r="M35" t="n">
-        <v>189.9</v>
+        <v>184.3</v>
       </c>
       <c r="N35" t="n">
-        <v>184.96</v>
+        <v>179.92</v>
       </c>
       <c r="O35" t="n">
-        <v>185.68</v>
+        <v>182.8</v>
       </c>
       <c r="P35" t="n">
-        <v>161.3336</v>
+        <v>162.2568</v>
       </c>
       <c r="Q35" t="n">
-        <v>166.5086</v>
+        <v>166.4122</v>
       </c>
       <c r="R35" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S35" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>3 sep</t>
+          <t>4 sep</t>
         </is>
       </c>
       <c r="V35" t="n">
-        <v>501.66</v>
+        <v>510</v>
       </c>
       <c r="W35" t="n">
-        <v>515.65</v>
+        <v>511</v>
       </c>
       <c r="X35" t="n">
-        <v>500.8</v>
+        <v>499.36</v>
       </c>
       <c r="Y35" t="n">
-        <v>510.12</v>
+        <v>499.7</v>
       </c>
       <c r="Z35" t="n">
-        <v>440.6114</v>
+        <v>443.5621</v>
       </c>
       <c r="AA35" t="n">
-        <v>429.3912</v>
+        <v>429.3729</v>
       </c>
       <c r="AB35" t="n">
         <v>535.3375423278808</v>
@@ -6365,26 +6387,26 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>7 sep</t>
+          <t>8 sep</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>40.26</v>
+        <v>40.83</v>
       </c>
       <c r="C36" t="n">
-        <v>40.845</v>
+        <v>41.18</v>
       </c>
       <c r="D36" t="n">
-        <v>40.12</v>
+        <v>40.6325</v>
       </c>
       <c r="E36" t="n">
-        <v>40.56</v>
+        <v>40.855</v>
       </c>
       <c r="F36" t="n">
-        <v>37.9551</v>
+        <v>38.0977</v>
       </c>
       <c r="G36" t="n">
-        <v>35.1619</v>
+        <v>35.2131</v>
       </c>
       <c r="H36" t="n">
         <v>45.05751734733581</v>
@@ -6394,55 +6416,55 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>7 sep</t>
+          <t>8 sep</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>183.56</v>
+        <v>182.32</v>
       </c>
       <c r="M36" t="n">
-        <v>184.3</v>
+        <v>183.76</v>
       </c>
       <c r="N36" t="n">
-        <v>179.92</v>
+        <v>180.02</v>
       </c>
       <c r="O36" t="n">
-        <v>182.8</v>
+        <v>181.7</v>
       </c>
       <c r="P36" t="n">
-        <v>162.2568</v>
+        <v>163.2108</v>
       </c>
       <c r="Q36" t="n">
-        <v>166.4122</v>
+        <v>166.3049</v>
       </c>
       <c r="R36" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S36" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>4 sep</t>
+          <t>8 sep</t>
         </is>
       </c>
       <c r="V36" t="n">
-        <v>510</v>
+        <v>493.01</v>
       </c>
       <c r="W36" t="n">
-        <v>511</v>
+        <v>495.19</v>
       </c>
       <c r="X36" t="n">
-        <v>499.36</v>
+        <v>490.15</v>
       </c>
       <c r="Y36" t="n">
-        <v>499.7</v>
+        <v>493.95</v>
       </c>
       <c r="Z36" t="n">
-        <v>443.5621</v>
+        <v>445.9957</v>
       </c>
       <c r="AA36" t="n">
-        <v>429.3729</v>
+        <v>429.3939</v>
       </c>
       <c r="AB36" t="n">
         <v>535.3375423278808</v>
@@ -6454,26 +6476,26 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>8 sep</t>
+          <t>9 sep</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>40.83</v>
+        <v>41.1</v>
       </c>
       <c r="C37" t="n">
-        <v>41.18</v>
+        <v>41.385</v>
       </c>
       <c r="D37" t="n">
-        <v>40.6325</v>
+        <v>40.85</v>
       </c>
       <c r="E37" t="n">
-        <v>40.855</v>
+        <v>40.94</v>
       </c>
       <c r="F37" t="n">
-        <v>38.0977</v>
+        <v>38.2513</v>
       </c>
       <c r="G37" t="n">
-        <v>35.2131</v>
+        <v>35.2646</v>
       </c>
       <c r="H37" t="n">
         <v>45.05751734733581</v>
@@ -6483,55 +6505,55 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>8 sep</t>
+          <t>9 sep</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>182.32</v>
+        <v>183</v>
       </c>
       <c r="M37" t="n">
-        <v>183.76</v>
+        <v>187.04</v>
       </c>
       <c r="N37" t="n">
-        <v>180.02</v>
+        <v>181.36</v>
       </c>
       <c r="O37" t="n">
-        <v>181.7</v>
+        <v>182.86</v>
       </c>
       <c r="P37" t="n">
-        <v>163.2108</v>
+        <v>164.0504</v>
       </c>
       <c r="Q37" t="n">
-        <v>166.3049</v>
+        <v>166.2113</v>
       </c>
       <c r="R37" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S37" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>8 sep</t>
+          <t>9 sep</t>
         </is>
       </c>
       <c r="V37" t="n">
-        <v>493.01</v>
+        <v>493.07</v>
       </c>
       <c r="W37" t="n">
-        <v>495.19</v>
+        <v>494.39</v>
       </c>
       <c r="X37" t="n">
-        <v>490.15</v>
+        <v>489.8</v>
       </c>
       <c r="Y37" t="n">
-        <v>493.95</v>
+        <v>491.65</v>
       </c>
       <c r="Z37" t="n">
-        <v>445.9957</v>
+        <v>448.4712</v>
       </c>
       <c r="AA37" t="n">
-        <v>429.3939</v>
+        <v>429.4364</v>
       </c>
       <c r="AB37" t="n">
         <v>535.3375423278808</v>
@@ -6543,26 +6565,26 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>9 sep</t>
+          <t>10 sep</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>41.1</v>
+        <v>40.98</v>
       </c>
       <c r="C38" t="n">
-        <v>41.385</v>
+        <v>41.77</v>
       </c>
       <c r="D38" t="n">
-        <v>40.85</v>
+        <v>40.93</v>
       </c>
       <c r="E38" t="n">
-        <v>40.94</v>
+        <v>41.23</v>
       </c>
       <c r="F38" t="n">
-        <v>38.2513</v>
+        <v>38.4034</v>
       </c>
       <c r="G38" t="n">
-        <v>35.2646</v>
+        <v>35.3174</v>
       </c>
       <c r="H38" t="n">
         <v>45.05751734733581</v>
@@ -6572,55 +6594,55 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>9 sep</t>
+          <t>10 sep</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="M38" t="n">
-        <v>187.04</v>
+        <v>180.4</v>
       </c>
       <c r="N38" t="n">
-        <v>181.36</v>
+        <v>176.2</v>
       </c>
       <c r="O38" t="n">
-        <v>182.86</v>
+        <v>177.82</v>
       </c>
       <c r="P38" t="n">
-        <v>164.0504</v>
+        <v>164.7724</v>
       </c>
       <c r="Q38" t="n">
-        <v>166.2113</v>
+        <v>166.0803</v>
       </c>
       <c r="R38" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S38" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>9 sep</t>
+          <t>10 sep</t>
         </is>
       </c>
       <c r="V38" t="n">
-        <v>493.07</v>
+        <v>488.32</v>
       </c>
       <c r="W38" t="n">
-        <v>494.39</v>
+        <v>494.52</v>
       </c>
       <c r="X38" t="n">
-        <v>489.8</v>
+        <v>486</v>
       </c>
       <c r="Y38" t="n">
-        <v>491.65</v>
+        <v>492.44</v>
       </c>
       <c r="Z38" t="n">
-        <v>448.4712</v>
+        <v>450.8736</v>
       </c>
       <c r="AA38" t="n">
-        <v>429.4364</v>
+        <v>429.5215</v>
       </c>
       <c r="AB38" t="n">
         <v>535.3375423278808</v>
@@ -6632,26 +6654,26 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10 sep</t>
+          <t>11 sep</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>40.98</v>
+        <v>41.345</v>
       </c>
       <c r="C39" t="n">
-        <v>41.77</v>
+        <v>41.715</v>
       </c>
       <c r="D39" t="n">
-        <v>40.93</v>
+        <v>40.905</v>
       </c>
       <c r="E39" t="n">
-        <v>41.23</v>
+        <v>41.415</v>
       </c>
       <c r="F39" t="n">
-        <v>38.4034</v>
+        <v>38.5608</v>
       </c>
       <c r="G39" t="n">
-        <v>35.3174</v>
+        <v>35.3717</v>
       </c>
       <c r="H39" t="n">
         <v>45.05751734733581</v>
@@ -6661,55 +6683,55 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>10 sep</t>
+          <t>11 sep</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>180</v>
+        <v>175.68</v>
       </c>
       <c r="M39" t="n">
-        <v>180.4</v>
+        <v>178.84</v>
       </c>
       <c r="N39" t="n">
-        <v>176.2</v>
+        <v>172.16</v>
       </c>
       <c r="O39" t="n">
-        <v>177.82</v>
+        <v>177.26</v>
       </c>
       <c r="P39" t="n">
-        <v>164.7724</v>
+        <v>165.5248</v>
       </c>
       <c r="Q39" t="n">
-        <v>166.0803</v>
+        <v>165.9594</v>
       </c>
       <c r="R39" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S39" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>10 sep</t>
+          <t>11 sep</t>
         </is>
       </c>
       <c r="V39" t="n">
-        <v>488.32</v>
+        <v>495.65</v>
       </c>
       <c r="W39" t="n">
-        <v>494.52</v>
+        <v>498.97</v>
       </c>
       <c r="X39" t="n">
-        <v>486</v>
+        <v>492.58</v>
       </c>
       <c r="Y39" t="n">
-        <v>492.44</v>
+        <v>495.63</v>
       </c>
       <c r="Z39" t="n">
-        <v>450.8736</v>
+        <v>453.115</v>
       </c>
       <c r="AA39" t="n">
-        <v>429.5215</v>
+        <v>429.6539</v>
       </c>
       <c r="AB39" t="n">
         <v>535.3375423278808</v>
@@ -6721,26 +6743,26 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>11 sep</t>
+          <t>14 sep</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>41.345</v>
+        <v>41.88</v>
       </c>
       <c r="C40" t="n">
-        <v>41.715</v>
+        <v>42.285</v>
       </c>
       <c r="D40" t="n">
-        <v>40.905</v>
+        <v>41.8</v>
       </c>
       <c r="E40" t="n">
-        <v>41.415</v>
+        <v>41.91</v>
       </c>
       <c r="F40" t="n">
-        <v>38.5608</v>
+        <v>38.7226</v>
       </c>
       <c r="G40" t="n">
-        <v>35.3717</v>
+        <v>35.4269</v>
       </c>
       <c r="H40" t="n">
         <v>45.05751734733581</v>
@@ -6750,55 +6772,55 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>11 sep</t>
+          <t>14 sep</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>175.68</v>
+        <v>180.82</v>
       </c>
       <c r="M40" t="n">
-        <v>178.84</v>
+        <v>186.76</v>
       </c>
       <c r="N40" t="n">
-        <v>172.16</v>
+        <v>180.82</v>
       </c>
       <c r="O40" t="n">
-        <v>177.26</v>
+        <v>186.26</v>
       </c>
       <c r="P40" t="n">
-        <v>165.5248</v>
+        <v>166.4488</v>
       </c>
       <c r="Q40" t="n">
-        <v>165.9594</v>
+        <v>165.8745</v>
       </c>
       <c r="R40" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S40" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>11 sep</t>
+          <t>14 sep</t>
         </is>
       </c>
       <c r="V40" t="n">
-        <v>495.65</v>
+        <v>497.06</v>
       </c>
       <c r="W40" t="n">
-        <v>498.97</v>
+        <v>509.95</v>
       </c>
       <c r="X40" t="n">
-        <v>492.58</v>
+        <v>495.34</v>
       </c>
       <c r="Y40" t="n">
-        <v>495.63</v>
+        <v>505.41</v>
       </c>
       <c r="Z40" t="n">
-        <v>453.115</v>
+        <v>455.4281</v>
       </c>
       <c r="AA40" t="n">
-        <v>429.654</v>
+        <v>429.8259</v>
       </c>
       <c r="AB40" t="n">
         <v>535.3375423278808</v>
@@ -6810,26 +6832,26 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>14 sep</t>
+          <t>15 sep</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>41.88</v>
+        <v>41.845</v>
       </c>
       <c r="C41" t="n">
-        <v>42.285</v>
+        <v>42.7</v>
       </c>
       <c r="D41" t="n">
-        <v>41.8</v>
+        <v>41.72</v>
       </c>
       <c r="E41" t="n">
-        <v>41.91</v>
+        <v>42.7</v>
       </c>
       <c r="F41" t="n">
-        <v>38.7226</v>
+        <v>38.8782</v>
       </c>
       <c r="G41" t="n">
-        <v>35.4269</v>
+        <v>35.4854</v>
       </c>
       <c r="H41" t="n">
         <v>45.05751734733581</v>
@@ -6839,55 +6861,55 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>14 sep</t>
+          <t>15 sep</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>180.82</v>
+        <v>186.64</v>
       </c>
       <c r="M41" t="n">
-        <v>186.76</v>
+        <v>187.26</v>
       </c>
       <c r="N41" t="n">
-        <v>180.82</v>
+        <v>183.2</v>
       </c>
       <c r="O41" t="n">
-        <v>186.26</v>
+        <v>187.08</v>
       </c>
       <c r="P41" t="n">
-        <v>166.4488</v>
+        <v>167.3124</v>
       </c>
       <c r="Q41" t="n">
-        <v>165.8745</v>
+        <v>165.7921</v>
       </c>
       <c r="R41" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S41" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>14 sep</t>
+          <t>15 sep</t>
         </is>
       </c>
       <c r="V41" t="n">
-        <v>497.06</v>
+        <v>500.06</v>
       </c>
       <c r="W41" t="n">
-        <v>509.95</v>
+        <v>505.9</v>
       </c>
       <c r="X41" t="n">
-        <v>495.34</v>
+        <v>495.54</v>
       </c>
       <c r="Y41" t="n">
-        <v>505.41</v>
+        <v>497.12</v>
       </c>
       <c r="Z41" t="n">
-        <v>455.4281</v>
+        <v>457.6502</v>
       </c>
       <c r="AA41" t="n">
-        <v>429.8259</v>
+        <v>429.9416</v>
       </c>
       <c r="AB41" t="n">
         <v>535.3375423278808</v>
@@ -6899,26 +6921,26 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>15 sep</t>
+          <t>16 sep</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>41.845</v>
+        <v>42.72</v>
       </c>
       <c r="C42" t="n">
-        <v>42.7</v>
+        <v>42.85</v>
       </c>
       <c r="D42" t="n">
-        <v>41.72</v>
+        <v>41.67</v>
       </c>
       <c r="E42" t="n">
-        <v>42.7</v>
+        <v>41.825</v>
       </c>
       <c r="F42" t="n">
-        <v>38.8782</v>
+        <v>38.9989</v>
       </c>
       <c r="G42" t="n">
-        <v>35.4854</v>
+        <v>35.5403</v>
       </c>
       <c r="H42" t="n">
         <v>45.05751734733581</v>
@@ -6928,55 +6950,55 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>15 sep</t>
+          <t>16 sep</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>186.64</v>
+        <v>185.86</v>
       </c>
       <c r="M42" t="n">
-        <v>187.26</v>
+        <v>186.76</v>
       </c>
       <c r="N42" t="n">
-        <v>183.2</v>
+        <v>182.18</v>
       </c>
       <c r="O42" t="n">
-        <v>187.08</v>
+        <v>186.56</v>
       </c>
       <c r="P42" t="n">
-        <v>167.3124</v>
+        <v>168.2844</v>
       </c>
       <c r="Q42" t="n">
-        <v>165.7921</v>
+        <v>165.6996</v>
       </c>
       <c r="R42" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S42" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>15 sep</t>
+          <t>16 sep</t>
         </is>
       </c>
       <c r="V42" t="n">
-        <v>500.06</v>
+        <v>493.03</v>
       </c>
       <c r="W42" t="n">
-        <v>505.9</v>
+        <v>495.97</v>
       </c>
       <c r="X42" t="n">
-        <v>495.54</v>
+        <v>487.23</v>
       </c>
       <c r="Y42" t="n">
-        <v>497.12</v>
+        <v>490.3</v>
       </c>
       <c r="Z42" t="n">
-        <v>457.6502</v>
+        <v>459.694</v>
       </c>
       <c r="AA42" t="n">
-        <v>429.9416</v>
+        <v>429.9809</v>
       </c>
       <c r="AB42" t="n">
         <v>535.3375423278808</v>
@@ -6988,26 +7010,26 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>16 sep</t>
+          <t>17 sep</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>42.72</v>
+        <v>41.58</v>
       </c>
       <c r="C43" t="n">
-        <v>42.85</v>
+        <v>42.055</v>
       </c>
       <c r="D43" t="n">
-        <v>41.67</v>
+        <v>41.38</v>
       </c>
       <c r="E43" t="n">
-        <v>41.825</v>
+        <v>41.56</v>
       </c>
       <c r="F43" t="n">
-        <v>38.9989</v>
+        <v>39.1225</v>
       </c>
       <c r="G43" t="n">
-        <v>35.5403</v>
+        <v>35.5926</v>
       </c>
       <c r="H43" t="n">
         <v>45.05751734733581</v>
@@ -7017,55 +7039,55 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>16 sep</t>
+          <t>17 sep</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>185.86</v>
+        <v>188.54</v>
       </c>
       <c r="M43" t="n">
-        <v>186.76</v>
+        <v>189.2</v>
       </c>
       <c r="N43" t="n">
-        <v>182.18</v>
+        <v>184.62</v>
       </c>
       <c r="O43" t="n">
-        <v>186.56</v>
+        <v>188</v>
       </c>
       <c r="P43" t="n">
-        <v>168.2844</v>
+        <v>169.2896</v>
       </c>
       <c r="Q43" t="n">
-        <v>165.6996</v>
+        <v>165.6125</v>
       </c>
       <c r="R43" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S43" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>16 sep</t>
+          <t>17 sep</t>
         </is>
       </c>
       <c r="V43" t="n">
-        <v>493.03</v>
+        <v>497.8</v>
       </c>
       <c r="W43" t="n">
-        <v>495.97</v>
+        <v>501.47</v>
       </c>
       <c r="X43" t="n">
-        <v>487.23</v>
+        <v>493.17</v>
       </c>
       <c r="Y43" t="n">
-        <v>490.3</v>
+        <v>497.75</v>
       </c>
       <c r="Z43" t="n">
-        <v>459.694</v>
+        <v>461.9966</v>
       </c>
       <c r="AA43" t="n">
-        <v>429.9809</v>
+        <v>430.0251</v>
       </c>
       <c r="AB43" t="n">
         <v>535.3375423278808</v>
@@ -7077,26 +7099,26 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>17 sep</t>
+          <t>18 sep</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>41.58</v>
+        <v>41.465</v>
       </c>
       <c r="C44" t="n">
-        <v>42.055</v>
+        <v>41.5</v>
       </c>
       <c r="D44" t="n">
-        <v>41.38</v>
+        <v>40.955</v>
       </c>
       <c r="E44" t="n">
-        <v>41.56</v>
+        <v>41.315</v>
       </c>
       <c r="F44" t="n">
-        <v>39.1225</v>
+        <v>39.2414</v>
       </c>
       <c r="G44" t="n">
-        <v>35.5926</v>
+        <v>35.6436</v>
       </c>
       <c r="H44" t="n">
         <v>45.05751734733581</v>
@@ -7106,55 +7128,55 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>17 sep</t>
+          <t>18 sep</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>188.54</v>
+        <v>186.1</v>
       </c>
       <c r="M44" t="n">
-        <v>189.2</v>
+        <v>187.26</v>
       </c>
       <c r="N44" t="n">
-        <v>184.62</v>
+        <v>182.56</v>
       </c>
       <c r="O44" t="n">
-        <v>188</v>
+        <v>183.12</v>
       </c>
       <c r="P44" t="n">
-        <v>169.2896</v>
+        <v>170.2004</v>
       </c>
       <c r="Q44" t="n">
-        <v>165.6125</v>
+        <v>165.5062</v>
       </c>
       <c r="R44" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S44" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>17 sep</t>
+          <t>18 sep</t>
         </is>
       </c>
       <c r="V44" t="n">
-        <v>497.8</v>
+        <v>497.97</v>
       </c>
       <c r="W44" t="n">
-        <v>501.47</v>
+        <v>498.65</v>
       </c>
       <c r="X44" t="n">
-        <v>493.17</v>
+        <v>491.1</v>
       </c>
       <c r="Y44" t="n">
-        <v>497.75</v>
+        <v>493.78</v>
       </c>
       <c r="Z44" t="n">
-        <v>461.9966</v>
+        <v>464.1995</v>
       </c>
       <c r="AA44" t="n">
-        <v>430.0251</v>
+        <v>430.0757</v>
       </c>
       <c r="AB44" t="n">
         <v>535.3375423278808</v>
@@ -7166,26 +7188,26 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>18 sep</t>
+          <t>21 sep</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>41.465</v>
+        <v>41.04</v>
       </c>
       <c r="C45" t="n">
-        <v>41.5</v>
+        <v>41.4</v>
       </c>
       <c r="D45" t="n">
-        <v>40.955</v>
+        <v>40.775</v>
       </c>
       <c r="E45" t="n">
-        <v>41.315</v>
+        <v>40.775</v>
       </c>
       <c r="F45" t="n">
-        <v>39.2414</v>
+        <v>39.3341</v>
       </c>
       <c r="G45" t="n">
-        <v>35.6436</v>
+        <v>35.6939</v>
       </c>
       <c r="H45" t="n">
         <v>45.05751734733581</v>
@@ -7195,55 +7217,55 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>18 sep</t>
+          <t>21 sep</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>186.1</v>
+        <v>184.7</v>
       </c>
       <c r="M45" t="n">
-        <v>187.26</v>
+        <v>185.86</v>
       </c>
       <c r="N45" t="n">
-        <v>182.56</v>
+        <v>182.48</v>
       </c>
       <c r="O45" t="n">
-        <v>183.12</v>
+        <v>182.86</v>
       </c>
       <c r="P45" t="n">
-        <v>170.2004</v>
+        <v>171.0432</v>
       </c>
       <c r="Q45" t="n">
-        <v>165.5062</v>
+        <v>165.4052</v>
       </c>
       <c r="R45" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S45" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>18 sep</t>
+          <t>21 sep</t>
         </is>
       </c>
       <c r="V45" t="n">
-        <v>497.97</v>
+        <v>494.95</v>
       </c>
       <c r="W45" t="n">
-        <v>498.65</v>
+        <v>501.87</v>
       </c>
       <c r="X45" t="n">
-        <v>491.1</v>
+        <v>491.33</v>
       </c>
       <c r="Y45" t="n">
-        <v>493.78</v>
+        <v>501.61</v>
       </c>
       <c r="Z45" t="n">
-        <v>464.1995</v>
+        <v>466.5442</v>
       </c>
       <c r="AA45" t="n">
-        <v>430.0757</v>
+        <v>430.1492</v>
       </c>
       <c r="AB45" t="n">
         <v>535.3375423278808</v>
@@ -7255,26 +7277,26 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>21 sep</t>
+          <t>22 sep</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>41.04</v>
+        <v>40.84</v>
       </c>
       <c r="C46" t="n">
-        <v>41.4</v>
+        <v>41.165</v>
       </c>
       <c r="D46" t="n">
-        <v>40.775</v>
+        <v>40.215</v>
       </c>
       <c r="E46" t="n">
-        <v>40.775</v>
+        <v>41.01</v>
       </c>
       <c r="F46" t="n">
-        <v>39.3341</v>
+        <v>39.4244</v>
       </c>
       <c r="G46" t="n">
-        <v>35.6939</v>
+        <v>35.746</v>
       </c>
       <c r="H46" t="n">
         <v>45.05751734733581</v>
@@ -7284,55 +7306,55 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>21 sep</t>
+          <t>22 sep</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>184.7</v>
+        <v>182.14</v>
       </c>
       <c r="M46" t="n">
-        <v>185.86</v>
+        <v>187.48</v>
       </c>
       <c r="N46" t="n">
-        <v>182.48</v>
+        <v>181.52</v>
       </c>
       <c r="O46" t="n">
-        <v>182.86</v>
+        <v>182.32</v>
       </c>
       <c r="P46" t="n">
-        <v>171.0432</v>
+        <v>171.9552</v>
       </c>
       <c r="Q46" t="n">
-        <v>165.4052</v>
+        <v>165.2836</v>
       </c>
       <c r="R46" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S46" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>21 sep</t>
+          <t>22 sep</t>
         </is>
       </c>
       <c r="V46" t="n">
-        <v>494.95</v>
+        <v>507.32</v>
       </c>
       <c r="W46" t="n">
-        <v>501.87</v>
+        <v>508.5</v>
       </c>
       <c r="X46" t="n">
-        <v>491.33</v>
+        <v>493.65</v>
       </c>
       <c r="Y46" t="n">
-        <v>501.61</v>
+        <v>498</v>
       </c>
       <c r="Z46" t="n">
-        <v>466.5442</v>
+        <v>468.699</v>
       </c>
       <c r="AA46" t="n">
-        <v>430.1492</v>
+        <v>430.2656</v>
       </c>
       <c r="AB46" t="n">
         <v>535.3375423278808</v>
@@ -7344,26 +7366,26 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>22 sep</t>
+          <t>23 sep</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>40.84</v>
+        <v>41</v>
       </c>
       <c r="C47" t="n">
-        <v>41.165</v>
+        <v>41.755</v>
       </c>
       <c r="D47" t="n">
-        <v>40.215</v>
+        <v>40.995</v>
       </c>
       <c r="E47" t="n">
-        <v>41.01</v>
+        <v>41.69</v>
       </c>
       <c r="F47" t="n">
-        <v>39.4244</v>
+        <v>39.5272</v>
       </c>
       <c r="G47" t="n">
-        <v>35.746</v>
+        <v>35.8024</v>
       </c>
       <c r="H47" t="n">
         <v>45.05751734733581</v>
@@ -7373,55 +7395,55 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>22 sep</t>
+          <t>23 sep</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>182.14</v>
+        <v>184.9</v>
       </c>
       <c r="M47" t="n">
-        <v>187.48</v>
+        <v>187.8</v>
       </c>
       <c r="N47" t="n">
-        <v>181.52</v>
+        <v>183.48</v>
       </c>
       <c r="O47" t="n">
-        <v>182.32</v>
+        <v>186.46</v>
       </c>
       <c r="P47" t="n">
-        <v>171.9552</v>
+        <v>172.9448</v>
       </c>
       <c r="Q47" t="n">
-        <v>165.2836</v>
+        <v>165.1675</v>
       </c>
       <c r="R47" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S47" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>22 sep</t>
+          <t>23 sep</t>
         </is>
       </c>
       <c r="V47" t="n">
-        <v>507.32</v>
+        <v>500.76</v>
       </c>
       <c r="W47" t="n">
-        <v>508.5</v>
+        <v>509.44</v>
       </c>
       <c r="X47" t="n">
-        <v>493.65</v>
+        <v>495.88</v>
       </c>
       <c r="Y47" t="n">
-        <v>498</v>
+        <v>500.59</v>
       </c>
       <c r="Z47" t="n">
-        <v>468.699</v>
+        <v>471.0267</v>
       </c>
       <c r="AA47" t="n">
-        <v>430.2656</v>
+        <v>430.3795</v>
       </c>
       <c r="AB47" t="n">
         <v>535.3375423278808</v>
@@ -7433,26 +7455,26 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>23 sep</t>
+          <t>24 sep</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>41</v>
+        <v>41.825</v>
       </c>
       <c r="C48" t="n">
-        <v>41.755</v>
+        <v>42.52</v>
       </c>
       <c r="D48" t="n">
-        <v>40.995</v>
+        <v>41.78</v>
       </c>
       <c r="E48" t="n">
-        <v>41.69</v>
+        <v>42.43</v>
       </c>
       <c r="F48" t="n">
-        <v>39.5272</v>
+        <v>39.6382</v>
       </c>
       <c r="G48" t="n">
-        <v>35.8024</v>
+        <v>35.8638</v>
       </c>
       <c r="H48" t="n">
         <v>45.05751734733581</v>
@@ -7462,55 +7484,55 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>23 sep</t>
+          <t>24 sep</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>184.9</v>
+        <v>184.52</v>
       </c>
       <c r="M48" t="n">
-        <v>187.8</v>
+        <v>185.5</v>
       </c>
       <c r="N48" t="n">
-        <v>183.48</v>
+        <v>182.26</v>
       </c>
       <c r="O48" t="n">
-        <v>186.46</v>
+        <v>184.18</v>
       </c>
       <c r="P48" t="n">
-        <v>172.9448</v>
+        <v>173.8756</v>
       </c>
       <c r="Q48" t="n">
-        <v>165.1675</v>
+        <v>165.0554</v>
       </c>
       <c r="R48" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S48" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>23 sep</t>
+          <t>24 sep</t>
         </is>
       </c>
       <c r="V48" t="n">
-        <v>500.76</v>
+        <v>495.07</v>
       </c>
       <c r="W48" t="n">
-        <v>509.44</v>
+        <v>498.9</v>
       </c>
       <c r="X48" t="n">
-        <v>495.88</v>
+        <v>491.22</v>
       </c>
       <c r="Y48" t="n">
-        <v>500.59</v>
+        <v>497.93</v>
       </c>
       <c r="Z48" t="n">
-        <v>471.0267</v>
+        <v>473.0876</v>
       </c>
       <c r="AA48" t="n">
-        <v>430.3795</v>
+        <v>430.4686</v>
       </c>
       <c r="AB48" t="n">
         <v>535.3375423278808</v>
@@ -7522,26 +7544,26 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>24 sep</t>
+          <t>25 sep</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>41.825</v>
+        <v>41.99</v>
       </c>
       <c r="C49" t="n">
-        <v>42.52</v>
+        <v>42.33</v>
       </c>
       <c r="D49" t="n">
-        <v>41.78</v>
+        <v>41.71</v>
       </c>
       <c r="E49" t="n">
-        <v>42.43</v>
+        <v>42.06</v>
       </c>
       <c r="F49" t="n">
-        <v>39.6382</v>
+        <v>39.7263</v>
       </c>
       <c r="G49" t="n">
-        <v>35.8638</v>
+        <v>35.9239</v>
       </c>
       <c r="H49" t="n">
         <v>45.05751734733581</v>
@@ -7551,55 +7573,55 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>24 sep</t>
+          <t>25 sep</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>184.52</v>
+        <v>184.42</v>
       </c>
       <c r="M49" t="n">
-        <v>185.5</v>
+        <v>185.92</v>
       </c>
       <c r="N49" t="n">
-        <v>182.26</v>
+        <v>183.76</v>
       </c>
       <c r="O49" t="n">
-        <v>184.18</v>
+        <v>185.92</v>
       </c>
       <c r="P49" t="n">
-        <v>173.8756</v>
+        <v>174.8356</v>
       </c>
       <c r="Q49" t="n">
-        <v>165.0554</v>
+        <v>164.9525</v>
       </c>
       <c r="R49" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S49" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>24 sep</t>
+          <t>25 sep</t>
         </is>
       </c>
       <c r="V49" t="n">
-        <v>495.07</v>
+        <v>499.04</v>
       </c>
       <c r="W49" t="n">
-        <v>498.9</v>
+        <v>519.4</v>
       </c>
       <c r="X49" t="n">
-        <v>491.22</v>
+        <v>497.25</v>
       </c>
       <c r="Y49" t="n">
-        <v>497.93</v>
+        <v>516.17</v>
       </c>
       <c r="Z49" t="n">
-        <v>473.0876</v>
+        <v>475.4041</v>
       </c>
       <c r="AA49" t="n">
-        <v>430.4686</v>
+        <v>430.6098</v>
       </c>
       <c r="AB49" t="n">
         <v>535.3375423278808</v>
@@ -7611,26 +7633,26 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>25 sep</t>
+          <t>28 sep</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>41.99</v>
+        <v>42.45</v>
       </c>
       <c r="C50" t="n">
-        <v>42.33</v>
+        <v>42.995</v>
       </c>
       <c r="D50" t="n">
-        <v>41.71</v>
+        <v>42.38</v>
       </c>
       <c r="E50" t="n">
-        <v>42.06</v>
+        <v>42.725</v>
       </c>
       <c r="F50" t="n">
-        <v>39.7263</v>
+        <v>39.8301</v>
       </c>
       <c r="G50" t="n">
-        <v>35.9239</v>
+        <v>35.9888</v>
       </c>
       <c r="H50" t="n">
         <v>45.05751734733581</v>
@@ -7640,55 +7662,55 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>25 sep</t>
+          <t>28 sep</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>184.42</v>
+        <v>185.2</v>
       </c>
       <c r="M50" t="n">
-        <v>185.92</v>
+        <v>186.76</v>
       </c>
       <c r="N50" t="n">
-        <v>183.76</v>
+        <v>178.88</v>
       </c>
       <c r="O50" t="n">
-        <v>185.92</v>
+        <v>184.02</v>
       </c>
       <c r="P50" t="n">
-        <v>174.8356</v>
+        <v>175.7508</v>
       </c>
       <c r="Q50" t="n">
-        <v>164.9525</v>
+        <v>164.8355</v>
       </c>
       <c r="R50" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S50" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>25 sep</t>
+          <t>28 sep</t>
         </is>
       </c>
       <c r="V50" t="n">
-        <v>499.04</v>
+        <v>505.47</v>
       </c>
       <c r="W50" t="n">
-        <v>519.4</v>
+        <v>513.33</v>
       </c>
       <c r="X50" t="n">
-        <v>497.25</v>
+        <v>502.22</v>
       </c>
       <c r="Y50" t="n">
-        <v>516.17</v>
+        <v>509.22</v>
       </c>
       <c r="Z50" t="n">
-        <v>475.4041</v>
+        <v>477.7269</v>
       </c>
       <c r="AA50" t="n">
-        <v>430.6098</v>
+        <v>430.7113</v>
       </c>
       <c r="AB50" t="n">
         <v>535.3375423278808</v>
@@ -7700,26 +7722,26 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>28 sep</t>
+          <t>29 sep</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>42.45</v>
+        <v>42.57</v>
       </c>
       <c r="C51" t="n">
-        <v>42.995</v>
+        <v>42.665</v>
       </c>
       <c r="D51" t="n">
-        <v>42.38</v>
+        <v>41.73</v>
       </c>
       <c r="E51" t="n">
-        <v>42.725</v>
+        <v>42.05</v>
       </c>
       <c r="F51" t="n">
-        <v>39.8301</v>
+        <v>39.9146</v>
       </c>
       <c r="G51" t="n">
-        <v>35.9888</v>
+        <v>36.0498</v>
       </c>
       <c r="H51" t="n">
         <v>45.05751734733581</v>
@@ -7729,55 +7751,55 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>28 sep</t>
+          <t>29 sep</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>185.2</v>
+        <v>183.22</v>
       </c>
       <c r="M51" t="n">
-        <v>186.76</v>
+        <v>186.34</v>
       </c>
       <c r="N51" t="n">
-        <v>178.88</v>
+        <v>182.28</v>
       </c>
       <c r="O51" t="n">
-        <v>184.02</v>
+        <v>185.32</v>
       </c>
       <c r="P51" t="n">
-        <v>175.7508</v>
+        <v>176.7288</v>
       </c>
       <c r="Q51" t="n">
-        <v>164.8355</v>
+        <v>164.733</v>
       </c>
       <c r="R51" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S51" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>28 sep</t>
+          <t>29 sep</t>
         </is>
       </c>
       <c r="V51" t="n">
-        <v>505.47</v>
+        <v>508.31</v>
       </c>
       <c r="W51" t="n">
-        <v>513.33</v>
+        <v>513.64</v>
       </c>
       <c r="X51" t="n">
-        <v>502.22</v>
+        <v>502.4</v>
       </c>
       <c r="Y51" t="n">
-        <v>509.22</v>
+        <v>508.96</v>
       </c>
       <c r="Z51" t="n">
-        <v>477.7269</v>
+        <v>479.8754</v>
       </c>
       <c r="AA51" t="n">
-        <v>430.7113</v>
+        <v>430.8784</v>
       </c>
       <c r="AB51" t="n">
         <v>535.3375423278808</v>
@@ -7789,26 +7811,26 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>29 sep</t>
+          <t>30 sep</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>42.57</v>
+        <v>41.975</v>
       </c>
       <c r="C52" t="n">
-        <v>42.665</v>
+        <v>42.095</v>
       </c>
       <c r="D52" t="n">
-        <v>41.73</v>
+        <v>41.58</v>
       </c>
       <c r="E52" t="n">
-        <v>42.05</v>
+        <v>41.91</v>
       </c>
       <c r="F52" t="n">
-        <v>39.9146</v>
+        <v>39.9874</v>
       </c>
       <c r="G52" t="n">
-        <v>36.0498</v>
+        <v>36.1135</v>
       </c>
       <c r="H52" t="n">
         <v>45.05751734733581</v>
@@ -7818,55 +7840,55 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>29 sep</t>
+          <t>30 sep</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>183.22</v>
+        <v>184.5</v>
       </c>
       <c r="M52" t="n">
-        <v>186.34</v>
+        <v>186.2</v>
       </c>
       <c r="N52" t="n">
-        <v>182.28</v>
+        <v>181.06</v>
       </c>
       <c r="O52" t="n">
-        <v>185.32</v>
+        <v>185.66</v>
       </c>
       <c r="P52" t="n">
-        <v>176.7288</v>
+        <v>177.8012</v>
       </c>
       <c r="Q52" t="n">
-        <v>164.733</v>
+        <v>164.6377</v>
       </c>
       <c r="R52" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S52" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>29 sep</t>
+          <t>30 sep</t>
         </is>
       </c>
       <c r="V52" t="n">
-        <v>508.31</v>
+        <v>511.61</v>
       </c>
       <c r="W52" t="n">
-        <v>513.64</v>
+        <v>519.83</v>
       </c>
       <c r="X52" t="n">
-        <v>502.4</v>
+        <v>510.31</v>
       </c>
       <c r="Y52" t="n">
-        <v>508.96</v>
+        <v>512.9</v>
       </c>
       <c r="Z52" t="n">
-        <v>479.8754</v>
+        <v>482.1933</v>
       </c>
       <c r="AA52" t="n">
-        <v>430.8784</v>
+        <v>431.0408</v>
       </c>
       <c r="AB52" t="n">
         <v>535.3375423278808</v>
@@ -7878,26 +7900,26 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>30 sep</t>
+          <t>1 okt</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>41.975</v>
+        <v>41.625</v>
       </c>
       <c r="C53" t="n">
-        <v>42.095</v>
+        <v>42.36</v>
       </c>
       <c r="D53" t="n">
-        <v>41.58</v>
+        <v>41.165</v>
       </c>
       <c r="E53" t="n">
-        <v>41.91</v>
+        <v>42.24</v>
       </c>
       <c r="F53" t="n">
-        <v>39.9874</v>
+        <v>40.0562</v>
       </c>
       <c r="G53" t="n">
-        <v>36.1135</v>
+        <v>36.1777</v>
       </c>
       <c r="H53" t="n">
         <v>45.05751734733581</v>
@@ -7907,55 +7929,55 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>30 sep</t>
+          <t>1 okt</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>184.5</v>
+        <v>184.68</v>
       </c>
       <c r="M53" t="n">
-        <v>186.2</v>
+        <v>190.26</v>
       </c>
       <c r="N53" t="n">
-        <v>181.06</v>
+        <v>181.34</v>
       </c>
       <c r="O53" t="n">
-        <v>185.66</v>
+        <v>186.74</v>
       </c>
       <c r="P53" t="n">
-        <v>177.8012</v>
+        <v>178.9696</v>
       </c>
       <c r="Q53" t="n">
-        <v>164.6377</v>
+        <v>164.5407</v>
       </c>
       <c r="R53" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S53" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>30 sep</t>
+          <t>1 okt</t>
         </is>
       </c>
       <c r="V53" t="n">
-        <v>511.61</v>
+        <v>519.88</v>
       </c>
       <c r="W53" t="n">
-        <v>519.83</v>
+        <v>522.85</v>
       </c>
       <c r="X53" t="n">
-        <v>510.31</v>
+        <v>512.17</v>
       </c>
       <c r="Y53" t="n">
-        <v>512.9</v>
+        <v>512.8</v>
       </c>
       <c r="Z53" t="n">
-        <v>482.1933</v>
+        <v>484.6572</v>
       </c>
       <c r="AA53" t="n">
-        <v>431.0408</v>
+        <v>431.2272</v>
       </c>
       <c r="AB53" t="n">
         <v>535.3375423278808</v>
@@ -7967,26 +7989,26 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1 okt</t>
+          <t>2 okt</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>41.625</v>
+        <v>42.11</v>
       </c>
       <c r="C54" t="n">
-        <v>42.36</v>
+        <v>42.745</v>
       </c>
       <c r="D54" t="n">
-        <v>41.165</v>
+        <v>41.985</v>
       </c>
       <c r="E54" t="n">
-        <v>42.24</v>
+        <v>42.4</v>
       </c>
       <c r="F54" t="n">
-        <v>40.0562</v>
+        <v>40.1364</v>
       </c>
       <c r="G54" t="n">
-        <v>36.1777</v>
+        <v>36.2422</v>
       </c>
       <c r="H54" t="n">
         <v>45.05751734733581</v>
@@ -7996,55 +8018,55 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>1 okt</t>
+          <t>2 okt</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>184.68</v>
+        <v>187.82</v>
       </c>
       <c r="M54" t="n">
-        <v>190.26</v>
+        <v>188.74</v>
       </c>
       <c r="N54" t="n">
-        <v>181.34</v>
+        <v>183.92</v>
       </c>
       <c r="O54" t="n">
-        <v>186.74</v>
+        <v>183.92</v>
       </c>
       <c r="P54" t="n">
-        <v>178.9696</v>
+        <v>179.844</v>
       </c>
       <c r="Q54" t="n">
-        <v>164.5407</v>
+        <v>164.4442</v>
       </c>
       <c r="R54" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S54" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>1 okt</t>
+          <t>2 okt</t>
         </is>
       </c>
       <c r="V54" t="n">
-        <v>519.88</v>
+        <v>519.39</v>
       </c>
       <c r="W54" t="n">
-        <v>522.85</v>
+        <v>522.5</v>
       </c>
       <c r="X54" t="n">
-        <v>512.17</v>
+        <v>513.66</v>
       </c>
       <c r="Y54" t="n">
-        <v>512.8</v>
+        <v>517.53</v>
       </c>
       <c r="Z54" t="n">
-        <v>484.6572</v>
+        <v>487.3905</v>
       </c>
       <c r="AA54" t="n">
-        <v>431.2272</v>
+        <v>431.4557</v>
       </c>
       <c r="AB54" t="n">
         <v>535.3375423278808</v>
@@ -8056,26 +8078,26 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2 okt</t>
+          <t>5 okt</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>42.11</v>
+        <v>42.645</v>
       </c>
       <c r="C55" t="n">
-        <v>42.745</v>
+        <v>43.11</v>
       </c>
       <c r="D55" t="n">
-        <v>41.985</v>
+        <v>42.35</v>
       </c>
       <c r="E55" t="n">
-        <v>42.4</v>
+        <v>42.865</v>
       </c>
       <c r="F55" t="n">
-        <v>40.1364</v>
+        <v>40.2347</v>
       </c>
       <c r="G55" t="n">
-        <v>36.2422</v>
+        <v>36.3069</v>
       </c>
       <c r="H55" t="n">
         <v>45.05751734733581</v>
@@ -8085,55 +8107,55 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2 okt</t>
+          <t>5 okt</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>187.82</v>
+        <v>185.06</v>
       </c>
       <c r="M55" t="n">
-        <v>188.74</v>
+        <v>188.5</v>
       </c>
       <c r="N55" t="n">
-        <v>183.92</v>
+        <v>184.66</v>
       </c>
       <c r="O55" t="n">
-        <v>183.92</v>
+        <v>185.04</v>
       </c>
       <c r="P55" t="n">
-        <v>179.844</v>
+        <v>180.5192</v>
       </c>
       <c r="Q55" t="n">
-        <v>164.4442</v>
+        <v>164.3515</v>
       </c>
       <c r="R55" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S55" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>2 okt</t>
+          <t>5 okt</t>
         </is>
       </c>
       <c r="V55" t="n">
-        <v>519.39</v>
+        <v>521.62</v>
       </c>
       <c r="W55" t="n">
-        <v>522.5</v>
+        <v>532.35</v>
       </c>
       <c r="X55" t="n">
-        <v>513.66</v>
+        <v>521.47</v>
       </c>
       <c r="Y55" t="n">
-        <v>517.53</v>
+        <v>525.1799999999999</v>
       </c>
       <c r="Z55" t="n">
-        <v>487.3905</v>
+        <v>490.2745</v>
       </c>
       <c r="AA55" t="n">
-        <v>431.4557</v>
+        <v>431.7147</v>
       </c>
       <c r="AB55" t="n">
         <v>535.3375423278808</v>
@@ -8145,26 +8167,26 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>5 okt</t>
+          <t>6 okt</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>42.645</v>
+        <v>42.86</v>
       </c>
       <c r="C56" t="n">
-        <v>43.11</v>
+        <v>43.285</v>
       </c>
       <c r="D56" t="n">
-        <v>42.35</v>
+        <v>42.43</v>
       </c>
       <c r="E56" t="n">
-        <v>42.865</v>
+        <v>43.185</v>
       </c>
       <c r="F56" t="n">
-        <v>40.2347</v>
+        <v>40.349</v>
       </c>
       <c r="G56" t="n">
-        <v>36.3069</v>
+        <v>36.3726</v>
       </c>
       <c r="H56" t="n">
         <v>45.05751734733581</v>
@@ -8174,55 +8196,55 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>5 okt</t>
+          <t>6 okt</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>185.06</v>
+        <v>186.56</v>
       </c>
       <c r="M56" t="n">
-        <v>188.5</v>
+        <v>190.22</v>
       </c>
       <c r="N56" t="n">
-        <v>184.66</v>
+        <v>186.06</v>
       </c>
       <c r="O56" t="n">
-        <v>185.04</v>
+        <v>188.6</v>
       </c>
       <c r="P56" t="n">
-        <v>180.5192</v>
+        <v>181.1064</v>
       </c>
       <c r="Q56" t="n">
-        <v>164.3515</v>
+        <v>164.2647</v>
       </c>
       <c r="R56" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S56" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>5 okt</t>
+          <t>6 okt</t>
         </is>
       </c>
       <c r="V56" t="n">
-        <v>521.62</v>
+        <v>531.6799999999999</v>
       </c>
       <c r="W56" t="n">
-        <v>532.35</v>
+        <v>535.6900000000001</v>
       </c>
       <c r="X56" t="n">
-        <v>521.47</v>
+        <v>528.78</v>
       </c>
       <c r="Y56" t="n">
-        <v>525.1799999999999</v>
+        <v>529.3</v>
       </c>
       <c r="Z56" t="n">
-        <v>490.2745</v>
+        <v>493.0931</v>
       </c>
       <c r="AA56" t="n">
-        <v>431.7147</v>
+        <v>431.9956</v>
       </c>
       <c r="AB56" t="n">
         <v>535.3375423278808</v>
@@ -8234,26 +8256,26 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>6 okt</t>
+          <t>7 okt</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>42.86</v>
+        <v>43.37</v>
       </c>
       <c r="C57" t="n">
-        <v>43.285</v>
+        <v>43.835</v>
       </c>
       <c r="D57" t="n">
-        <v>42.43</v>
+        <v>43.145</v>
       </c>
       <c r="E57" t="n">
-        <v>43.185</v>
+        <v>43.25</v>
       </c>
       <c r="F57" t="n">
-        <v>40.349</v>
+        <v>40.4451</v>
       </c>
       <c r="G57" t="n">
-        <v>36.3726</v>
+        <v>36.4388</v>
       </c>
       <c r="H57" t="n">
         <v>45.05751734733581</v>
@@ -8263,55 +8285,55 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>6 okt</t>
+          <t>7 okt</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>186.56</v>
+        <v>187</v>
       </c>
       <c r="M57" t="n">
-        <v>190.22</v>
+        <v>188.72</v>
       </c>
       <c r="N57" t="n">
-        <v>186.06</v>
+        <v>186.04</v>
       </c>
       <c r="O57" t="n">
-        <v>188.6</v>
+        <v>187.62</v>
       </c>
       <c r="P57" t="n">
-        <v>181.1064</v>
+        <v>181.618</v>
       </c>
       <c r="Q57" t="n">
-        <v>164.2647</v>
+        <v>164.1762</v>
       </c>
       <c r="R57" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S57" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>6 okt</t>
+          <t>7 okt</t>
         </is>
       </c>
       <c r="V57" t="n">
-        <v>531.6799999999999</v>
+        <v>530.73</v>
       </c>
       <c r="W57" t="n">
-        <v>535.6900000000001</v>
+        <v>531.73</v>
       </c>
       <c r="X57" t="n">
-        <v>528.78</v>
+        <v>524.6900000000001</v>
       </c>
       <c r="Y57" t="n">
-        <v>529.3</v>
+        <v>529.76</v>
       </c>
       <c r="Z57" t="n">
-        <v>493.0931</v>
+        <v>495.8361</v>
       </c>
       <c r="AA57" t="n">
-        <v>431.9956</v>
+        <v>432.2398</v>
       </c>
       <c r="AB57" t="n">
         <v>535.3375423278808</v>
@@ -8323,26 +8345,26 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>7 okt</t>
+          <t>8 okt</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>43.37</v>
+        <v>43.555</v>
       </c>
       <c r="C58" t="n">
-        <v>43.835</v>
+        <v>44.815</v>
       </c>
       <c r="D58" t="n">
-        <v>43.145</v>
+        <v>43.5425</v>
       </c>
       <c r="E58" t="n">
-        <v>43.25</v>
+        <v>44.75</v>
       </c>
       <c r="F58" t="n">
-        <v>40.4451</v>
+        <v>40.5699</v>
       </c>
       <c r="G58" t="n">
-        <v>36.4388</v>
+        <v>36.5123</v>
       </c>
       <c r="H58" t="n">
         <v>45.05751734733581</v>
@@ -8352,55 +8374,55 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>7 okt</t>
+          <t>8 okt</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>187</v>
+        <v>187.04</v>
       </c>
       <c r="M58" t="n">
-        <v>188.72</v>
+        <v>189.82</v>
       </c>
       <c r="N58" t="n">
-        <v>186.04</v>
+        <v>183.76</v>
       </c>
       <c r="O58" t="n">
-        <v>187.62</v>
+        <v>184.62</v>
       </c>
       <c r="P58" t="n">
-        <v>181.618</v>
+        <v>182.192</v>
       </c>
       <c r="Q58" t="n">
-        <v>164.1762</v>
+        <v>164.074</v>
       </c>
       <c r="R58" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S58" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>7 okt</t>
+          <t>8 okt</t>
         </is>
       </c>
       <c r="V58" t="n">
-        <v>530.73</v>
+        <v>529.8099999999999</v>
       </c>
       <c r="W58" t="n">
-        <v>531.73</v>
+        <v>533.51</v>
       </c>
       <c r="X58" t="n">
-        <v>524.6900000000001</v>
+        <v>518.79</v>
       </c>
       <c r="Y58" t="n">
-        <v>529.76</v>
+        <v>522.61</v>
       </c>
       <c r="Z58" t="n">
-        <v>495.8361</v>
+        <v>498.4921</v>
       </c>
       <c r="AA58" t="n">
-        <v>432.2398</v>
+        <v>432.4385</v>
       </c>
       <c r="AB58" t="n">
         <v>535.3375423278808</v>
@@ -8412,26 +8434,26 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>8 okt</t>
+          <t>9 okt</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>43.555</v>
+        <v>44.42</v>
       </c>
       <c r="C59" t="n">
-        <v>44.815</v>
+        <v>45.155</v>
       </c>
       <c r="D59" t="n">
-        <v>43.5425</v>
+        <v>43.94</v>
       </c>
       <c r="E59" t="n">
-        <v>44.75</v>
+        <v>45.035</v>
       </c>
       <c r="F59" t="n">
-        <v>40.5699</v>
+        <v>40.6842</v>
       </c>
       <c r="G59" t="n">
-        <v>36.5123</v>
+        <v>36.5866</v>
       </c>
       <c r="H59" t="n">
         <v>45.05751734733581</v>
@@ -8441,55 +8463,55 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>8 okt</t>
+          <t>9 okt</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>187.04</v>
+        <v>188.98</v>
       </c>
       <c r="M59" t="n">
-        <v>189.82</v>
+        <v>192.58</v>
       </c>
       <c r="N59" t="n">
-        <v>183.76</v>
+        <v>188.86</v>
       </c>
       <c r="O59" t="n">
-        <v>184.62</v>
+        <v>191.46</v>
       </c>
       <c r="P59" t="n">
-        <v>182.192</v>
+        <v>182.8676</v>
       </c>
       <c r="Q59" t="n">
-        <v>164.074</v>
+        <v>164.0101</v>
       </c>
       <c r="R59" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S59" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>8 okt</t>
+          <t>9 okt</t>
         </is>
       </c>
       <c r="V59" t="n">
-        <v>529.8099999999999</v>
+        <v>528.24</v>
       </c>
       <c r="W59" t="n">
-        <v>533.51</v>
+        <v>537.22</v>
       </c>
       <c r="X59" t="n">
-        <v>518.79</v>
+        <v>526.24</v>
       </c>
       <c r="Y59" t="n">
-        <v>522.61</v>
+        <v>535.0700000000001</v>
       </c>
       <c r="Z59" t="n">
-        <v>498.4921</v>
+        <v>500.1885</v>
       </c>
       <c r="AA59" t="n">
-        <v>432.4385</v>
+        <v>432.7046</v>
       </c>
       <c r="AB59" t="n">
         <v>535.3375423278808</v>
@@ -8501,26 +8523,26 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>9 okt</t>
+          <t>12 okt</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>44.42</v>
+        <v>44.725</v>
       </c>
       <c r="C60" t="n">
-        <v>45.155</v>
+        <v>45.81</v>
       </c>
       <c r="D60" t="n">
-        <v>43.94</v>
+        <v>44.695</v>
       </c>
       <c r="E60" t="n">
-        <v>45.035</v>
+        <v>45.56</v>
       </c>
       <c r="F60" t="n">
-        <v>40.6842</v>
+        <v>40.8072</v>
       </c>
       <c r="G60" t="n">
-        <v>36.5866</v>
+        <v>36.6625</v>
       </c>
       <c r="H60" t="n">
         <v>45.05751734733581</v>
@@ -8530,55 +8552,55 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>9 okt</t>
+          <t>12 okt</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>188.98</v>
+        <v>190.58</v>
       </c>
       <c r="M60" t="n">
-        <v>192.58</v>
+        <v>197.88</v>
       </c>
       <c r="N60" t="n">
-        <v>188.86</v>
+        <v>189.78</v>
       </c>
       <c r="O60" t="n">
-        <v>191.46</v>
+        <v>194.46</v>
       </c>
       <c r="P60" t="n">
-        <v>182.8676</v>
+        <v>183.464</v>
       </c>
       <c r="Q60" t="n">
-        <v>164.0101</v>
+        <v>163.9576</v>
       </c>
       <c r="R60" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S60" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>9 okt</t>
+          <t>12 okt</t>
         </is>
       </c>
       <c r="V60" t="n">
-        <v>528.24</v>
+        <v>537.53</v>
       </c>
       <c r="W60" t="n">
-        <v>537.22</v>
+        <v>542.74</v>
       </c>
       <c r="X60" t="n">
-        <v>526.24</v>
+        <v>535.7</v>
       </c>
       <c r="Y60" t="n">
-        <v>535.0700000000001</v>
+        <v>541.15</v>
       </c>
       <c r="Z60" t="n">
-        <v>500.1885</v>
+        <v>501.7346</v>
       </c>
       <c r="AA60" t="n">
-        <v>432.7046</v>
+        <v>432.9914</v>
       </c>
       <c r="AB60" t="n">
         <v>535.3375423278808</v>
@@ -8590,26 +8612,26 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>12 okt</t>
+          <t>13 okt</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>44.725</v>
+        <v>45.69</v>
       </c>
       <c r="C61" t="n">
-        <v>45.81</v>
+        <v>45.97</v>
       </c>
       <c r="D61" t="n">
-        <v>44.695</v>
+        <v>45.35</v>
       </c>
       <c r="E61" t="n">
-        <v>45.56</v>
+        <v>45.95</v>
       </c>
       <c r="F61" t="n">
-        <v>40.8072</v>
+        <v>40.9565</v>
       </c>
       <c r="G61" t="n">
-        <v>36.6625</v>
+        <v>36.7398</v>
       </c>
       <c r="H61" t="n">
         <v>45.05751734733581</v>
@@ -8619,55 +8641,55 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>12 okt</t>
+          <t>13 okt</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>190.58</v>
+        <v>196</v>
       </c>
       <c r="M61" t="n">
-        <v>197.88</v>
+        <v>198.18</v>
       </c>
       <c r="N61" t="n">
-        <v>189.78</v>
+        <v>194.02</v>
       </c>
       <c r="O61" t="n">
-        <v>194.46</v>
+        <v>197.28</v>
       </c>
       <c r="P61" t="n">
-        <v>183.464</v>
+        <v>184.062</v>
       </c>
       <c r="Q61" t="n">
-        <v>163.9576</v>
+        <v>163.9196</v>
       </c>
       <c r="R61" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S61" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>12 okt</t>
+          <t>13 okt</t>
         </is>
       </c>
       <c r="V61" t="n">
-        <v>537.53</v>
+        <v>544.64</v>
       </c>
       <c r="W61" t="n">
-        <v>542.74</v>
+        <v>551.15</v>
       </c>
       <c r="X61" t="n">
-        <v>535.7</v>
+        <v>543.0599999999999</v>
       </c>
       <c r="Y61" t="n">
-        <v>541.15</v>
+        <v>543.45</v>
       </c>
       <c r="Z61" t="n">
-        <v>501.7346</v>
+        <v>502.8689</v>
       </c>
       <c r="AA61" t="n">
-        <v>432.9914</v>
+        <v>433.2839</v>
       </c>
       <c r="AB61" t="n">
         <v>535.3375423278808</v>
@@ -8679,26 +8701,26 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>13 okt</t>
+          <t>14 okt</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>45.69</v>
+        <v>45.95</v>
       </c>
       <c r="C62" t="n">
-        <v>45.97</v>
+        <v>46.675</v>
       </c>
       <c r="D62" t="n">
-        <v>45.35</v>
+        <v>45.91</v>
       </c>
       <c r="E62" t="n">
-        <v>45.95</v>
+        <v>46.455</v>
       </c>
       <c r="F62" t="n">
-        <v>40.9565</v>
+        <v>41.125</v>
       </c>
       <c r="G62" t="n">
-        <v>36.7398</v>
+        <v>36.8183</v>
       </c>
       <c r="H62" t="n">
         <v>45.05751734733581</v>
@@ -8708,55 +8730,55 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>13 okt</t>
+          <t>14 okt</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>196</v>
+        <v>196.6</v>
       </c>
       <c r="M62" t="n">
-        <v>198.18</v>
+        <v>199.36</v>
       </c>
       <c r="N62" t="n">
-        <v>194.02</v>
+        <v>195.26</v>
       </c>
       <c r="O62" t="n">
-        <v>197.28</v>
+        <v>196.94</v>
       </c>
       <c r="P62" t="n">
-        <v>184.062</v>
+        <v>184.6156</v>
       </c>
       <c r="Q62" t="n">
-        <v>163.9196</v>
+        <v>163.9114</v>
       </c>
       <c r="R62" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S62" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>13 okt</t>
+          <t>14 okt</t>
         </is>
       </c>
       <c r="V62" t="n">
-        <v>544.64</v>
+        <v>545.27</v>
       </c>
       <c r="W62" t="n">
-        <v>551.15</v>
+        <v>545.75</v>
       </c>
       <c r="X62" t="n">
-        <v>543.0599999999999</v>
+        <v>532.54</v>
       </c>
       <c r="Y62" t="n">
-        <v>543.45</v>
+        <v>533.6900000000001</v>
       </c>
       <c r="Z62" t="n">
-        <v>502.8689</v>
+        <v>503.705</v>
       </c>
       <c r="AA62" t="n">
-        <v>433.2839</v>
+        <v>433.5292</v>
       </c>
       <c r="AB62" t="n">
         <v>535.3375423278808</v>
@@ -8768,26 +8790,26 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>14 okt</t>
+          <t>15 okt</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>45.95</v>
+        <v>46.295</v>
       </c>
       <c r="C63" t="n">
-        <v>46.675</v>
+        <v>46.735</v>
       </c>
       <c r="D63" t="n">
-        <v>45.91</v>
+        <v>46.125</v>
       </c>
       <c r="E63" t="n">
-        <v>46.455</v>
+        <v>46.375</v>
       </c>
       <c r="F63" t="n">
-        <v>41.125</v>
+        <v>41.2847</v>
       </c>
       <c r="G63" t="n">
-        <v>36.8183</v>
+        <v>36.8966</v>
       </c>
       <c r="H63" t="n">
         <v>45.05751734733581</v>
@@ -8797,55 +8819,55 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>14 okt</t>
+          <t>15 okt</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>196.6</v>
+        <v>199.48</v>
       </c>
       <c r="M63" t="n">
-        <v>199.36</v>
+        <v>203</v>
       </c>
       <c r="N63" t="n">
-        <v>195.26</v>
+        <v>196.98</v>
       </c>
       <c r="O63" t="n">
-        <v>196.94</v>
+        <v>201.25</v>
       </c>
       <c r="P63" t="n">
-        <v>184.6156</v>
+        <v>185.221</v>
       </c>
       <c r="Q63" t="n">
-        <v>163.9114</v>
+        <v>163.9038</v>
       </c>
       <c r="R63" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S63" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>14 okt</t>
+          <t>15 okt</t>
         </is>
       </c>
       <c r="V63" t="n">
-        <v>545.27</v>
+        <v>533.3200000000001</v>
       </c>
       <c r="W63" t="n">
-        <v>545.75</v>
+        <v>541.13</v>
       </c>
       <c r="X63" t="n">
-        <v>532.54</v>
+        <v>531.22</v>
       </c>
       <c r="Y63" t="n">
-        <v>533.6900000000001</v>
+        <v>539.4400000000001</v>
       </c>
       <c r="Z63" t="n">
-        <v>503.705</v>
+        <v>504.7629</v>
       </c>
       <c r="AA63" t="n">
-        <v>433.5292</v>
+        <v>433.8063</v>
       </c>
       <c r="AB63" t="n">
         <v>535.3375423278808</v>
@@ -8857,26 +8879,26 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>15 okt</t>
+          <t>16 okt</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>46.295</v>
+        <v>46.14</v>
       </c>
       <c r="C64" t="n">
-        <v>46.735</v>
+        <v>47.025</v>
       </c>
       <c r="D64" t="n">
-        <v>46.125</v>
+        <v>46.075</v>
       </c>
       <c r="E64" t="n">
-        <v>46.375</v>
+        <v>46.88</v>
       </c>
       <c r="F64" t="n">
-        <v>41.2847</v>
+        <v>41.4622</v>
       </c>
       <c r="G64" t="n">
-        <v>36.8966</v>
+        <v>36.977</v>
       </c>
       <c r="H64" t="n">
         <v>45.05751734733581</v>
@@ -8886,55 +8908,55 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>15 okt</t>
+          <t>16 okt</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>199.48</v>
+        <v>200.6</v>
       </c>
       <c r="M64" t="n">
-        <v>203</v>
+        <v>204.2</v>
       </c>
       <c r="N64" t="n">
-        <v>196.98</v>
+        <v>198.68</v>
       </c>
       <c r="O64" t="n">
-        <v>201.25</v>
+        <v>199.22</v>
       </c>
       <c r="P64" t="n">
-        <v>185.221</v>
+        <v>185.6462</v>
       </c>
       <c r="Q64" t="n">
-        <v>163.9038</v>
+        <v>163.9066</v>
       </c>
       <c r="R64" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S64" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>15 okt</t>
+          <t>16 okt</t>
         </is>
       </c>
       <c r="V64" t="n">
-        <v>533.3200000000001</v>
+        <v>541.3099999999999</v>
       </c>
       <c r="W64" t="n">
-        <v>541.13</v>
+        <v>543.8200000000001</v>
       </c>
       <c r="X64" t="n">
-        <v>531.22</v>
+        <v>524.4299999999999</v>
       </c>
       <c r="Y64" t="n">
-        <v>539.4400000000001</v>
+        <v>529.05</v>
       </c>
       <c r="Z64" t="n">
-        <v>504.7629</v>
+        <v>505.3655</v>
       </c>
       <c r="AA64" t="n">
-        <v>433.8063</v>
+        <v>434.0295</v>
       </c>
       <c r="AB64" t="n">
         <v>535.3375423278808</v>
@@ -8946,26 +8968,26 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>16 okt</t>
+          <t>19 okt</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>46.14</v>
+        <v>47.37</v>
       </c>
       <c r="C65" t="n">
-        <v>47.025</v>
+        <v>47.45</v>
       </c>
       <c r="D65" t="n">
-        <v>46.075</v>
+        <v>46.74</v>
       </c>
       <c r="E65" t="n">
-        <v>46.88</v>
+        <v>46.86</v>
       </c>
       <c r="F65" t="n">
-        <v>41.4622</v>
+        <v>41.6313</v>
       </c>
       <c r="G65" t="n">
-        <v>36.977</v>
+        <v>37.0625</v>
       </c>
       <c r="H65" t="n">
         <v>45.05751734733581</v>
@@ -8975,55 +8997,55 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>16 okt</t>
+          <t>19 okt</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>200.6</v>
+        <v>199.56</v>
       </c>
       <c r="M65" t="n">
-        <v>204.2</v>
+        <v>200.8</v>
       </c>
       <c r="N65" t="n">
-        <v>198.68</v>
+        <v>197.32</v>
       </c>
       <c r="O65" t="n">
-        <v>199.22</v>
+        <v>199.84</v>
       </c>
       <c r="P65" t="n">
-        <v>185.6462</v>
+        <v>186.057</v>
       </c>
       <c r="Q65" t="n">
-        <v>163.9066</v>
+        <v>163.8811</v>
       </c>
       <c r="R65" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S65" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>16 okt</t>
+          <t>19 okt</t>
         </is>
       </c>
       <c r="V65" t="n">
-        <v>541.3099999999999</v>
+        <v>528.7</v>
       </c>
       <c r="W65" t="n">
-        <v>543.8200000000001</v>
+        <v>535.5700000000001</v>
       </c>
       <c r="X65" t="n">
-        <v>524.4299999999999</v>
+        <v>528.0599999999999</v>
       </c>
       <c r="Y65" t="n">
-        <v>529.05</v>
+        <v>533.52</v>
       </c>
       <c r="Z65" t="n">
-        <v>505.3655</v>
+        <v>506.0549</v>
       </c>
       <c r="AA65" t="n">
-        <v>434.0295</v>
+        <v>434.2942</v>
       </c>
       <c r="AB65" t="n">
         <v>535.3375423278808</v>
@@ -9035,26 +9057,26 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>19 okt</t>
+          <t>20 okt</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>47.37</v>
+        <v>46.875</v>
       </c>
       <c r="C66" t="n">
-        <v>47.45</v>
+        <v>47.505</v>
       </c>
       <c r="D66" t="n">
-        <v>46.74</v>
+        <v>46.36</v>
       </c>
       <c r="E66" t="n">
-        <v>46.865</v>
+        <v>46.65</v>
       </c>
       <c r="F66" t="n">
-        <v>41.6314</v>
+        <v>41.785</v>
       </c>
       <c r="G66" t="n">
-        <v>37.0625</v>
+        <v>37.152</v>
       </c>
       <c r="H66" t="n">
         <v>45.05751734733581</v>
@@ -9064,55 +9086,55 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>19 okt</t>
+          <t>20 okt</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>199.56</v>
+        <v>201.3</v>
       </c>
       <c r="M66" t="n">
-        <v>200.8</v>
+        <v>203.45</v>
       </c>
       <c r="N66" t="n">
-        <v>197.32</v>
+        <v>199.46</v>
       </c>
       <c r="O66" t="n">
-        <v>200.05</v>
+        <v>201.8</v>
       </c>
       <c r="P66" t="n">
-        <v>186.0612</v>
+        <v>186.479</v>
       </c>
       <c r="Q66" t="n">
-        <v>163.8822</v>
+        <v>163.8749</v>
       </c>
       <c r="R66" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S66" t="n">
-        <v>185.2514168875558</v>
+        <v>185.5978535243443</v>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>19 okt</t>
+          <t>20 okt</t>
         </is>
       </c>
       <c r="V66" t="n">
-        <v>528.74</v>
+        <v>533.91</v>
       </c>
       <c r="W66" t="n">
-        <v>535.5684</v>
+        <v>534.21</v>
       </c>
       <c r="X66" t="n">
-        <v>528.74</v>
+        <v>525.84</v>
       </c>
       <c r="Y66" t="n">
-        <v>533.61</v>
+        <v>532.13</v>
       </c>
       <c r="Z66" t="n">
-        <v>506.0567</v>
+        <v>506.5953</v>
       </c>
       <c r="AA66" t="n">
-        <v>434.2947</v>
+        <v>434.6051</v>
       </c>
       <c r="AB66" t="n">
         <v>535.3375423278808</v>

--- a/rapporten/trend-agent.xlsx
+++ b/rapporten/trend-agent.xlsx
@@ -1944,7 +1944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2146,6 +2146,28 @@
       </c>
       <c r="E9" s="3">
         <f>B9/$B$2-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>10050.37</v>
+      </c>
+      <c r="C10" s="2">
+        <f>B10-B9</f>
+        <v/>
+      </c>
+      <c r="D10" s="3">
+        <f>B10/B9-1</f>
+        <v/>
+      </c>
+      <c r="E10" s="3">
+        <f>B10/$B$2-1</f>
         <v/>
       </c>
     </row>
@@ -2289,38 +2311,38 @@
     <row r="6" ht="22" customHeight="1">
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Shell (SHELL.AS)  ·  46,65 EUR</t>
+          <t>Shell (SHELL.AS)  ·  46,82 EUR</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>SAP (SAP.DE)  ·  201,80 EUR</t>
+          <t>SAP (SAP.DE)  ·  208,55 EUR</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>Gestegen: 21,9% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +3,5% (winst). De bot verkoopt als de koers onder 44,25 zakt (-5,1%).</t>
+          <t>Gestegen: 20,7% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +3,9% (winst). De bot verkoopt als de koers onder 44,25 zakt (-5,5%).</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>Gestegen: 52,8% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +5,3% (winst). De bot verkoopt als de koers onder 185,60 zakt (-8,0%).</t>
+          <t>Gestegen: 62,5% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +8,9% (winst). De bot verkoopt als de koers onder 192,41 zakt (-7,7%).</t>
         </is>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Microsoft (MSFT)  ·  532,13 USD</t>
+          <t>Microsoft (MSFT)  ·  532,81 USD</t>
         </is>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Gestegen: 34,0% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: -0,6% (verlies). De bot verkoopt als de koers onder 509,90 zakt (-4,2%).</t>
+          <t>Gestegen: 36,8% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: -0,5% (verlies). De bot verkoopt als de koers onder 510,08 zakt (-4,3%).</t>
         </is>
       </c>
     </row>
@@ -2460,7 +2482,7 @@
         <v>191.56</v>
       </c>
       <c r="F3" t="n">
-        <v>185.6</v>
+        <v>192.41</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -2499,7 +2521,7 @@
         <v>535.34</v>
       </c>
       <c r="F4" t="n">
-        <v>509.9</v>
+        <v>510.08</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -2785,12 +2807,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SAP.DE</t>
+          <t>SHELL.AS</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Shell</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -2799,19 +2821,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.157</v>
+        <v>0.165</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.5726308567134148</v>
+        <v>0.2196820093062304</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1035765196225973</v>
+        <v>0.1416728020259477</v>
       </c>
       <c r="H2" t="n">
-        <v>0.79</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>201.8</v>
+        <v>46.82</v>
       </c>
     </row>
     <row r="3">
@@ -2820,12 +2842,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SHELL.AS</t>
+          <t>SAP.DE</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Shell</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2834,19 +2856,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.155</v>
+        <v>0.157</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.202231355413828</v>
+        <v>0.4875178858152791</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.144083379034855</v>
+        <v>0.1438678953149359</v>
       </c>
       <c r="H3" t="n">
-        <v>0.93</v>
+        <v>0.82</v>
       </c>
       <c r="I3" t="n">
-        <v>46.65</v>
+        <v>208.55</v>
       </c>
     </row>
     <row r="4">
@@ -2869,19 +2891,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.139</v>
+        <v>0.134</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.4252740074694488</v>
+        <v>0.3805541971350928</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.2475482210588058</v>
+        <v>0.2720742350824041</v>
       </c>
       <c r="H4" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="I4" t="n">
-        <v>83.95999999999999</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5">
@@ -2904,19 +2926,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.114</v>
+        <v>0.128</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.1539420798306623</v>
+        <v>0.162622256869972</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.1003378669884039</v>
+        <v>0.1270024842103736</v>
       </c>
       <c r="H5" t="n">
-        <v>0.88</v>
+        <v>0.91</v>
       </c>
       <c r="I5" t="n">
-        <v>407.07</v>
+        <v>408.02</v>
       </c>
     </row>
     <row r="6">
@@ -2925,12 +2947,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>XLE</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Energie-ETF</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2939,19 +2961,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.105</v>
+        <v>0.11</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.1547116218244047</v>
+        <v>0.3989544490721604</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.08797635009809124</v>
+        <v>0.06989959349115216</v>
       </c>
       <c r="H6" t="n">
-        <v>1.11</v>
+        <v>0.83</v>
       </c>
       <c r="I6" t="n">
-        <v>67.95999999999999</v>
+        <v>532.8099999999999</v>
       </c>
     </row>
     <row r="7">
@@ -2960,12 +2982,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>XLE</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Energie-ETF</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2974,19 +2996,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.1</v>
+        <v>0.106</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.3658137450233532</v>
+        <v>0.1545147734296179</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.06084412276972406</v>
+        <v>0.1031078483723875</v>
       </c>
       <c r="H7" t="n">
-        <v>0.82</v>
+        <v>1.07</v>
       </c>
       <c r="I7" t="n">
-        <v>532.13</v>
+        <v>68.15000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -2995,12 +3017,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -3009,19 +3031,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.097</v>
+        <v>0.092</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.159222186923127</v>
+        <v>0.5427591598384727</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.1237523434000534</v>
+        <v>0.03600820447719344</v>
       </c>
       <c r="H8" t="n">
-        <v>0.86</v>
+        <v>0.65</v>
       </c>
       <c r="I8" t="n">
-        <v>177.89</v>
+        <v>241.68</v>
       </c>
     </row>
     <row r="9">
@@ -3030,12 +3052,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>ExxonMobil</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -3044,19 +3066,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.081</v>
+        <v>0.09</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.4900400502344047</v>
+        <v>0.1424766396033437</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.02550545142542404</v>
+        <v>0.1221094373649858</v>
       </c>
       <c r="H9" t="n">
-        <v>0.68</v>
+        <v>0.86</v>
       </c>
       <c r="I9" t="n">
-        <v>242.45</v>
+        <v>178.09</v>
       </c>
     </row>
     <row r="10">
@@ -3079,19 +3101,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.5460383463892116</v>
+        <v>0.634441128155953</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.05188705112248648</v>
+        <v>0.09001027343165191</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="I10" t="n">
-        <v>192.59</v>
+        <v>201.64</v>
       </c>
     </row>
     <row r="11">
@@ -3114,19 +3136,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.062</v>
+        <v>0.053</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.09610947838646444</v>
+        <v>0.08380035461310609</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.05341323775929396</v>
+        <v>0.04261875764702339</v>
       </c>
       <c r="H11" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="I11" t="n">
-        <v>404.3</v>
+        <v>406.1</v>
       </c>
     </row>
   </sheetData>
@@ -3397,23 +3419,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>22 jul</t>
+          <t>23 jul</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>38.095</v>
+        <v>38.491</v>
       </c>
       <c r="C2" t="n">
-        <v>38.6098</v>
+        <v>39.0454</v>
       </c>
       <c r="D2" t="n">
-        <v>37.9267</v>
+        <v>38.3425</v>
       </c>
       <c r="E2" t="n">
-        <v>38.2682</v>
+        <v>38.8028</v>
       </c>
       <c r="F2" t="n">
-        <v>35.799</v>
+        <v>35.863</v>
       </c>
       <c r="H2" t="n">
         <v>45.05751734733581</v>
@@ -3423,77 +3445,77 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>22 jul</t>
+          <t>23 jul</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>136.02</v>
+        <v>131</v>
       </c>
       <c r="M2" t="n">
-        <v>136.4</v>
+        <v>132.42</v>
       </c>
       <c r="N2" t="n">
-        <v>132.04</v>
+        <v>127.5</v>
       </c>
       <c r="O2" t="n">
-        <v>132.04</v>
+        <v>128.32</v>
       </c>
       <c r="P2" t="n">
-        <v>144.324</v>
+        <v>144.066</v>
       </c>
       <c r="R2" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S2" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>21 jul</t>
+          <t>22 jul</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>398.0606</v>
+        <v>398.8292</v>
       </c>
       <c r="W2" t="n">
-        <v>400.7156</v>
+        <v>400.2465</v>
       </c>
       <c r="X2" t="n">
-        <v>395.5753</v>
+        <v>386.2329</v>
       </c>
       <c r="Y2" t="n">
-        <v>397.0026</v>
+        <v>389.6066</v>
       </c>
       <c r="Z2" t="n">
-        <v>399.9036</v>
+        <v>399.4268</v>
       </c>
       <c r="AB2" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC2" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>23 jul</t>
+          <t>24 jul</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38.491</v>
+        <v>38.4019</v>
       </c>
       <c r="C3" t="n">
-        <v>39.0454</v>
+        <v>38.6593</v>
       </c>
       <c r="D3" t="n">
-        <v>38.3425</v>
+        <v>38.1594</v>
       </c>
       <c r="E3" t="n">
-        <v>38.8028</v>
+        <v>38.3871</v>
       </c>
       <c r="F3" t="n">
-        <v>35.863</v>
+        <v>35.9135</v>
       </c>
       <c r="H3" t="n">
         <v>45.05751734733581</v>
@@ -3503,77 +3525,77 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>23 jul</t>
+          <t>24 jul</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>131</v>
+        <v>130.88</v>
       </c>
       <c r="M3" t="n">
-        <v>132.42</v>
+        <v>141.32</v>
       </c>
       <c r="N3" t="n">
-        <v>127.5</v>
+        <v>130.86</v>
       </c>
       <c r="O3" t="n">
-        <v>128.32</v>
+        <v>140.2</v>
       </c>
       <c r="P3" t="n">
-        <v>144.066</v>
+        <v>143.9888</v>
       </c>
       <c r="R3" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S3" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>22 jul</t>
+          <t>23 jul</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>398.8292</v>
+        <v>389.2373</v>
       </c>
       <c r="W3" t="n">
-        <v>400.2465</v>
+        <v>391.0439</v>
       </c>
       <c r="X3" t="n">
-        <v>386.2329</v>
+        <v>376.6809</v>
       </c>
       <c r="Y3" t="n">
-        <v>389.6066</v>
+        <v>380.863</v>
       </c>
       <c r="Z3" t="n">
-        <v>399.4268</v>
+        <v>398.8242</v>
       </c>
       <c r="AB3" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC3" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>24 jul</t>
+          <t>27 jul</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38.4019</v>
+        <v>37.5802</v>
       </c>
       <c r="C4" t="n">
-        <v>38.6593</v>
+        <v>38.1099</v>
       </c>
       <c r="D4" t="n">
-        <v>38.1594</v>
+        <v>37.4317</v>
       </c>
       <c r="E4" t="n">
-        <v>38.3871</v>
+        <v>37.9515</v>
       </c>
       <c r="F4" t="n">
-        <v>35.9135</v>
+        <v>35.931</v>
       </c>
       <c r="H4" t="n">
         <v>45.05751734733581</v>
@@ -3583,77 +3605,77 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>24 jul</t>
+          <t>27 jul</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>130.88</v>
+        <v>142.38</v>
       </c>
       <c r="M4" t="n">
-        <v>141.32</v>
+        <v>151.56</v>
       </c>
       <c r="N4" t="n">
-        <v>130.86</v>
+        <v>142</v>
       </c>
       <c r="O4" t="n">
-        <v>140.2</v>
+        <v>151.28</v>
       </c>
       <c r="P4" t="n">
-        <v>143.9888</v>
+        <v>144.0572</v>
       </c>
       <c r="R4" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S4" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>23 jul</t>
+          <t>24 jul</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>389.2373</v>
+        <v>386.3227</v>
       </c>
       <c r="W4" t="n">
-        <v>391.0439</v>
+        <v>388.299</v>
       </c>
       <c r="X4" t="n">
-        <v>376.6809</v>
+        <v>379.9348</v>
       </c>
       <c r="Y4" t="n">
-        <v>380.863</v>
+        <v>380.9828</v>
       </c>
       <c r="Z4" t="n">
-        <v>398.8242</v>
+        <v>398.3214</v>
       </c>
       <c r="AB4" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC4" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>27 jul</t>
+          <t>28 jul</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>37.5802</v>
+        <v>37.7139</v>
       </c>
       <c r="C5" t="n">
-        <v>38.1099</v>
+        <v>38.0109</v>
       </c>
       <c r="D5" t="n">
-        <v>37.4317</v>
+        <v>37.4713</v>
       </c>
       <c r="E5" t="n">
-        <v>37.9515</v>
+        <v>37.4713</v>
       </c>
       <c r="F5" t="n">
-        <v>35.931</v>
+        <v>35.9372</v>
       </c>
       <c r="H5" t="n">
         <v>45.05751734733581</v>
@@ -3663,80 +3685,80 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>27 jul</t>
+          <t>28 jul</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>142.38</v>
+        <v>152.2</v>
       </c>
       <c r="M5" t="n">
-        <v>151.56</v>
+        <v>159.76</v>
       </c>
       <c r="N5" t="n">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="O5" t="n">
-        <v>151.28</v>
+        <v>159.24</v>
       </c>
       <c r="P5" t="n">
-        <v>144.0572</v>
+        <v>144.1076</v>
       </c>
       <c r="R5" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S5" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>24 jul</t>
+          <t>27 jul</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>386.3227</v>
+        <v>389.347</v>
       </c>
       <c r="W5" t="n">
-        <v>388.299</v>
+        <v>393.4593</v>
       </c>
       <c r="X5" t="n">
-        <v>379.9348</v>
+        <v>387.261</v>
       </c>
       <c r="Y5" t="n">
-        <v>380.9828</v>
+        <v>388.3689</v>
       </c>
       <c r="Z5" t="n">
-        <v>398.3214</v>
+        <v>398.0172</v>
       </c>
       <c r="AB5" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC5" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>28 jul</t>
+          <t>29 jul</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>37.7139</v>
+        <v>38.0653</v>
       </c>
       <c r="C6" t="n">
-        <v>38.0109</v>
+        <v>38.59</v>
       </c>
       <c r="D6" t="n">
-        <v>37.4713</v>
+        <v>37.7089</v>
       </c>
       <c r="E6" t="n">
-        <v>37.4713</v>
+        <v>38.4415</v>
       </c>
       <c r="F6" t="n">
-        <v>35.9372</v>
+        <v>35.9692</v>
       </c>
       <c r="G6" t="n">
-        <v>33.9548</v>
+        <v>33.9987</v>
       </c>
       <c r="H6" t="n">
         <v>45.05751734733581</v>
@@ -3746,86 +3768,86 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>28 jul</t>
+          <t>29 jul</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>152.2</v>
+        <v>159.84</v>
       </c>
       <c r="M6" t="n">
-        <v>159.76</v>
+        <v>163.3</v>
       </c>
       <c r="N6" t="n">
-        <v>151</v>
+        <v>156.48</v>
       </c>
       <c r="O6" t="n">
-        <v>159.24</v>
+        <v>162.04</v>
       </c>
       <c r="P6" t="n">
-        <v>144.1076</v>
+        <v>144.28</v>
       </c>
       <c r="Q6" t="n">
-        <v>172.6663</v>
+        <v>172.343</v>
       </c>
       <c r="R6" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S6" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>27 jul</t>
+          <t>28 jul</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>389.347</v>
+        <v>392.4213</v>
       </c>
       <c r="W6" t="n">
-        <v>393.4593</v>
+        <v>399.5678</v>
       </c>
       <c r="X6" t="n">
-        <v>387.261</v>
+        <v>390.5647</v>
       </c>
       <c r="Y6" t="n">
-        <v>388.3689</v>
+        <v>392.6109</v>
       </c>
       <c r="Z6" t="n">
-        <v>398.0172</v>
+        <v>397.7139</v>
       </c>
       <c r="AA6" t="n">
-        <v>433.238</v>
+        <v>432.5982</v>
       </c>
       <c r="AB6" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC6" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>29 jul</t>
+          <t>30 jul</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>38.0653</v>
+        <v>38.6098</v>
       </c>
       <c r="C7" t="n">
-        <v>38.59</v>
+        <v>39.1444</v>
       </c>
       <c r="D7" t="n">
-        <v>37.7089</v>
+        <v>38.3277</v>
       </c>
       <c r="E7" t="n">
-        <v>38.4415</v>
+        <v>38.5108</v>
       </c>
       <c r="F7" t="n">
-        <v>35.9692</v>
+        <v>35.9978</v>
       </c>
       <c r="G7" t="n">
-        <v>33.9987</v>
+        <v>34.0424</v>
       </c>
       <c r="H7" t="n">
         <v>45.05751734733581</v>
@@ -3835,86 +3857,86 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>29 jul</t>
+          <t>30 jul</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>159.84</v>
+        <v>162.5</v>
       </c>
       <c r="M7" t="n">
-        <v>163.3</v>
+        <v>163.16</v>
       </c>
       <c r="N7" t="n">
-        <v>156.48</v>
+        <v>155.2</v>
       </c>
       <c r="O7" t="n">
-        <v>162.04</v>
+        <v>155.92</v>
       </c>
       <c r="P7" t="n">
-        <v>144.28</v>
+        <v>144.3804</v>
       </c>
       <c r="Q7" t="n">
-        <v>172.343</v>
+        <v>171.9849</v>
       </c>
       <c r="R7" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S7" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>28 jul</t>
+          <t>29 jul</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>392.4213</v>
+        <v>392.6608</v>
       </c>
       <c r="W7" t="n">
-        <v>399.5678</v>
+        <v>400.4961</v>
       </c>
       <c r="X7" t="n">
-        <v>390.5647</v>
+        <v>388.0095</v>
       </c>
       <c r="Y7" t="n">
-        <v>392.6109</v>
+        <v>389.8062</v>
       </c>
       <c r="Z7" t="n">
-        <v>397.7139</v>
+        <v>397.1057</v>
       </c>
       <c r="AA7" t="n">
-        <v>432.5982</v>
+        <v>431.9565</v>
       </c>
       <c r="AB7" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC7" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>30 jul</t>
+          <t>31 jul</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>38.6098</v>
       </c>
       <c r="C8" t="n">
-        <v>39.1444</v>
+        <v>39.575</v>
       </c>
       <c r="D8" t="n">
-        <v>38.3277</v>
+        <v>38.4464</v>
       </c>
       <c r="E8" t="n">
-        <v>38.5108</v>
+        <v>39.3226</v>
       </c>
       <c r="F8" t="n">
-        <v>35.9978</v>
+        <v>36.0495</v>
       </c>
       <c r="G8" t="n">
-        <v>34.0424</v>
+        <v>34.0907</v>
       </c>
       <c r="H8" t="n">
         <v>45.05751734733581</v>
@@ -3924,86 +3946,86 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>30 jul</t>
+          <t>31 jul</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>162.5</v>
+        <v>154.9</v>
       </c>
       <c r="M8" t="n">
-        <v>163.16</v>
+        <v>158.26</v>
       </c>
       <c r="N8" t="n">
-        <v>155.2</v>
+        <v>153.6</v>
       </c>
       <c r="O8" t="n">
-        <v>155.92</v>
+        <v>157.68</v>
       </c>
       <c r="P8" t="n">
-        <v>144.3804</v>
+        <v>144.4984</v>
       </c>
       <c r="Q8" t="n">
-        <v>171.9849</v>
+        <v>171.6292</v>
       </c>
       <c r="R8" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S8" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>29 jul</t>
+          <t>30 jul</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>392.6608</v>
+        <v>437.0772</v>
       </c>
       <c r="W8" t="n">
-        <v>400.4961</v>
+        <v>457.8281</v>
       </c>
       <c r="X8" t="n">
-        <v>388.0095</v>
+        <v>431.6275</v>
       </c>
       <c r="Y8" t="n">
-        <v>389.8062</v>
+        <v>450.2524</v>
       </c>
       <c r="Z8" t="n">
-        <v>397.1057</v>
+        <v>397.6741</v>
       </c>
       <c r="AA8" t="n">
-        <v>431.9565</v>
+        <v>431.6738</v>
       </c>
       <c r="AB8" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC8" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>31 jul</t>
+          <t>3 aug</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>38.6098</v>
+        <v>38.3128</v>
       </c>
       <c r="C9" t="n">
-        <v>39.575</v>
+        <v>39.4067</v>
       </c>
       <c r="D9" t="n">
-        <v>38.4464</v>
+        <v>38.2138</v>
       </c>
       <c r="E9" t="n">
-        <v>39.3226</v>
+        <v>39.4067</v>
       </c>
       <c r="F9" t="n">
-        <v>36.0495</v>
+        <v>36.1112</v>
       </c>
       <c r="G9" t="n">
-        <v>34.0907</v>
+        <v>34.1393</v>
       </c>
       <c r="H9" t="n">
         <v>45.05751734733581</v>
@@ -4013,86 +4035,86 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>31 jul</t>
+          <t>3 aug</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>154.9</v>
+        <v>160</v>
       </c>
       <c r="M9" t="n">
-        <v>158.26</v>
+        <v>168.7</v>
       </c>
       <c r="N9" t="n">
-        <v>153.6</v>
+        <v>159.6</v>
       </c>
       <c r="O9" t="n">
-        <v>157.68</v>
+        <v>164.64</v>
       </c>
       <c r="P9" t="n">
-        <v>144.4984</v>
+        <v>144.7016</v>
       </c>
       <c r="Q9" t="n">
-        <v>171.6292</v>
+        <v>171.301</v>
       </c>
       <c r="R9" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S9" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>30 jul</t>
+          <t>31 jul</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>437.0772</v>
+        <v>449.1545</v>
       </c>
       <c r="W9" t="n">
-        <v>457.8281</v>
+        <v>465.9628</v>
       </c>
       <c r="X9" t="n">
-        <v>431.6275</v>
+        <v>448.4857</v>
       </c>
       <c r="Y9" t="n">
-        <v>450.2524</v>
+        <v>463.8468</v>
       </c>
       <c r="Z9" t="n">
-        <v>397.6741</v>
+        <v>398.6364</v>
       </c>
       <c r="AA9" t="n">
-        <v>431.6738</v>
+        <v>431.4438</v>
       </c>
       <c r="AB9" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC9" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3 aug</t>
+          <t>4 aug</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>38.3128</v>
+        <v>39.3028</v>
       </c>
       <c r="C10" t="n">
-        <v>39.4067</v>
+        <v>39.6443</v>
       </c>
       <c r="D10" t="n">
-        <v>38.2138</v>
+        <v>38.2039</v>
       </c>
       <c r="E10" t="n">
-        <v>39.4067</v>
+        <v>38.486</v>
       </c>
       <c r="F10" t="n">
-        <v>36.1112</v>
+        <v>36.1495</v>
       </c>
       <c r="G10" t="n">
-        <v>34.1393</v>
+        <v>34.1818</v>
       </c>
       <c r="H10" t="n">
         <v>45.05751734733581</v>
@@ -4102,86 +4124,86 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>3 aug</t>
+          <t>4 aug</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>160</v>
+        <v>162.86</v>
       </c>
       <c r="M10" t="n">
-        <v>168.7</v>
+        <v>168.56</v>
       </c>
       <c r="N10" t="n">
-        <v>159.6</v>
+        <v>162.4</v>
       </c>
       <c r="O10" t="n">
-        <v>164.64</v>
+        <v>167.38</v>
       </c>
       <c r="P10" t="n">
-        <v>144.7016</v>
+        <v>145.02</v>
       </c>
       <c r="Q10" t="n">
-        <v>171.301</v>
+        <v>170.9913</v>
       </c>
       <c r="R10" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S10" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>31 jul</t>
+          <t>3 aug</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>449.1545</v>
+        <v>475.2354</v>
       </c>
       <c r="W10" t="n">
-        <v>465.9628</v>
+        <v>490.7262</v>
       </c>
       <c r="X10" t="n">
-        <v>448.4857</v>
+        <v>474.1075</v>
       </c>
       <c r="Y10" t="n">
-        <v>463.8468</v>
+        <v>486.7337</v>
       </c>
       <c r="Z10" t="n">
-        <v>398.6364</v>
+        <v>399.9838</v>
       </c>
       <c r="AA10" t="n">
-        <v>431.4438</v>
+        <v>431.3306</v>
       </c>
       <c r="AB10" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC10" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>4 aug</t>
+          <t>5 aug</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>39.3028</v>
+        <v>38.4811</v>
       </c>
       <c r="C11" t="n">
-        <v>39.6443</v>
+        <v>38.7632</v>
       </c>
       <c r="D11" t="n">
-        <v>38.2039</v>
+        <v>37.9366</v>
       </c>
       <c r="E11" t="n">
-        <v>38.486</v>
+        <v>38.0307</v>
       </c>
       <c r="F11" t="n">
-        <v>36.1495</v>
+        <v>36.1966</v>
       </c>
       <c r="G11" t="n">
-        <v>34.1818</v>
+        <v>34.2215</v>
       </c>
       <c r="H11" t="n">
         <v>45.05751734733581</v>
@@ -4191,86 +4213,86 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>4 aug</t>
+          <t>5 aug</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>162.86</v>
+        <v>167.92</v>
       </c>
       <c r="M11" t="n">
-        <v>168.56</v>
+        <v>172.6</v>
       </c>
       <c r="N11" t="n">
-        <v>162.4</v>
+        <v>167.3</v>
       </c>
       <c r="O11" t="n">
-        <v>167.38</v>
+        <v>169.26</v>
       </c>
       <c r="P11" t="n">
-        <v>145.02</v>
+        <v>145.4052</v>
       </c>
       <c r="Q11" t="n">
-        <v>170.9913</v>
+        <v>170.7022</v>
       </c>
       <c r="R11" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S11" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>3 aug</t>
+          <t>4 aug</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>475.2354</v>
+        <v>479.9964</v>
       </c>
       <c r="W11" t="n">
-        <v>490.7262</v>
+        <v>498.5016</v>
       </c>
       <c r="X11" t="n">
-        <v>474.1075</v>
+        <v>478.2697</v>
       </c>
       <c r="Y11" t="n">
-        <v>486.7337</v>
+        <v>491.884</v>
       </c>
       <c r="Z11" t="n">
-        <v>399.9838</v>
+        <v>401.4555</v>
       </c>
       <c r="AA11" t="n">
-        <v>431.3306</v>
+        <v>431.2438</v>
       </c>
       <c r="AB11" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC11" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5 aug</t>
+          <t>6 aug</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>38.4811</v>
+        <v>38.0752</v>
       </c>
       <c r="C12" t="n">
-        <v>38.7632</v>
+        <v>38.4069</v>
       </c>
       <c r="D12" t="n">
-        <v>37.9366</v>
+        <v>37.9168</v>
       </c>
       <c r="E12" t="n">
-        <v>38.0307</v>
+        <v>38.392</v>
       </c>
       <c r="F12" t="n">
-        <v>36.1966</v>
+        <v>36.2474</v>
       </c>
       <c r="G12" t="n">
-        <v>34.2215</v>
+        <v>34.2607</v>
       </c>
       <c r="H12" t="n">
         <v>45.05751734733581</v>
@@ -4280,86 +4302,86 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>5 aug</t>
+          <t>6 aug</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>167.92</v>
+        <v>171.44</v>
       </c>
       <c r="M12" t="n">
-        <v>172.6</v>
+        <v>173.1</v>
       </c>
       <c r="N12" t="n">
-        <v>167.3</v>
+        <v>168.08</v>
       </c>
       <c r="O12" t="n">
-        <v>169.26</v>
+        <v>170.98</v>
       </c>
       <c r="P12" t="n">
-        <v>145.4052</v>
+        <v>145.7928</v>
       </c>
       <c r="Q12" t="n">
-        <v>170.7022</v>
+        <v>170.384</v>
       </c>
       <c r="R12" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S12" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>4 aug</t>
+          <t>5 aug</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>479.9964</v>
+        <v>495.4273</v>
       </c>
       <c r="W12" t="n">
-        <v>498.5016</v>
+        <v>497.3038</v>
       </c>
       <c r="X12" t="n">
-        <v>478.2697</v>
+        <v>484.7674</v>
       </c>
       <c r="Y12" t="n">
-        <v>491.884</v>
+        <v>486.5441</v>
       </c>
       <c r="Z12" t="n">
-        <v>401.4555</v>
+        <v>402.8307</v>
       </c>
       <c r="AA12" t="n">
-        <v>431.2438</v>
+        <v>431.1393</v>
       </c>
       <c r="AB12" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC12" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6 aug</t>
+          <t>7 aug</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>38.0752</v>
+        <v>38.5207</v>
       </c>
       <c r="C13" t="n">
-        <v>38.4069</v>
+        <v>38.5999</v>
       </c>
       <c r="D13" t="n">
-        <v>37.9168</v>
+        <v>37.897</v>
       </c>
       <c r="E13" t="n">
-        <v>38.392</v>
+        <v>38.0059</v>
       </c>
       <c r="F13" t="n">
-        <v>36.2474</v>
+        <v>36.2952</v>
       </c>
       <c r="G13" t="n">
-        <v>34.2607</v>
+        <v>34.294</v>
       </c>
       <c r="H13" t="n">
         <v>45.05751734733581</v>
@@ -4369,86 +4391,86 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>6 aug</t>
+          <t>7 aug</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>171.44</v>
+        <v>173.82</v>
       </c>
       <c r="M13" t="n">
-        <v>173.1</v>
+        <v>179.56</v>
       </c>
       <c r="N13" t="n">
-        <v>168.08</v>
+        <v>173.82</v>
       </c>
       <c r="O13" t="n">
-        <v>170.98</v>
+        <v>177.96</v>
       </c>
       <c r="P13" t="n">
-        <v>145.7928</v>
+        <v>146.2468</v>
       </c>
       <c r="Q13" t="n">
-        <v>170.384</v>
+        <v>170.0918</v>
       </c>
       <c r="R13" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S13" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>5 aug</t>
+          <t>6 aug</t>
         </is>
       </c>
       <c r="V13" t="n">
-        <v>495.4273</v>
+        <v>487.632</v>
       </c>
       <c r="W13" t="n">
-        <v>497.3038</v>
+        <v>500.6176</v>
       </c>
       <c r="X13" t="n">
-        <v>484.7674</v>
+        <v>487.6021</v>
       </c>
       <c r="Y13" t="n">
-        <v>486.5441</v>
+        <v>498.9207</v>
       </c>
       <c r="Z13" t="n">
-        <v>402.8307</v>
+        <v>404.5041</v>
       </c>
       <c r="AA13" t="n">
-        <v>431.1393</v>
+        <v>431.087</v>
       </c>
       <c r="AB13" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC13" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>7 aug</t>
+          <t>10 aug</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>38.5207</v>
+        <v>38.0356</v>
       </c>
       <c r="C14" t="n">
-        <v>38.5999</v>
+        <v>38.4366</v>
       </c>
       <c r="D14" t="n">
-        <v>37.897</v>
+        <v>37.803</v>
       </c>
       <c r="E14" t="n">
-        <v>38.0059</v>
+        <v>38.4019</v>
       </c>
       <c r="F14" t="n">
-        <v>36.2952</v>
+        <v>36.3315</v>
       </c>
       <c r="G14" t="n">
-        <v>34.294</v>
+        <v>34.3294</v>
       </c>
       <c r="H14" t="n">
         <v>45.05751734733581</v>
@@ -4458,86 +4480,86 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>7 aug</t>
+          <t>10 aug</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>173.82</v>
+        <v>178.92</v>
       </c>
       <c r="M14" t="n">
-        <v>179.56</v>
+        <v>179.96</v>
       </c>
       <c r="N14" t="n">
-        <v>173.82</v>
+        <v>175.86</v>
       </c>
       <c r="O14" t="n">
-        <v>177.96</v>
+        <v>179.3</v>
       </c>
       <c r="P14" t="n">
-        <v>146.2468</v>
+        <v>146.4748</v>
       </c>
       <c r="Q14" t="n">
-        <v>170.0918</v>
+        <v>169.8238</v>
       </c>
       <c r="R14" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S14" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>6 aug</t>
+          <t>7 aug</t>
         </is>
       </c>
       <c r="V14" t="n">
-        <v>487.632</v>
+        <v>498.272</v>
       </c>
       <c r="W14" t="n">
-        <v>500.6176</v>
+        <v>504.2308</v>
       </c>
       <c r="X14" t="n">
-        <v>487.6021</v>
+        <v>497.7929</v>
       </c>
       <c r="Y14" t="n">
-        <v>498.9207</v>
+        <v>499.0505</v>
       </c>
       <c r="Z14" t="n">
-        <v>404.5041</v>
+        <v>406.2472</v>
       </c>
       <c r="AA14" t="n">
-        <v>431.087</v>
+        <v>431.0194</v>
       </c>
       <c r="AB14" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC14" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10 aug</t>
+          <t>11 aug</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>38.0356</v>
+        <v>38.7385</v>
       </c>
       <c r="C15" t="n">
-        <v>38.4366</v>
+        <v>39.0058</v>
       </c>
       <c r="D15" t="n">
-        <v>37.803</v>
+        <v>38.6148</v>
       </c>
       <c r="E15" t="n">
-        <v>38.4019</v>
+        <v>38.9662</v>
       </c>
       <c r="F15" t="n">
-        <v>36.3315</v>
+        <v>36.374</v>
       </c>
       <c r="G15" t="n">
-        <v>34.3294</v>
+        <v>34.3685</v>
       </c>
       <c r="H15" t="n">
         <v>45.05751734733581</v>
@@ -4547,86 +4569,86 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>10 aug</t>
+          <t>11 aug</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>178.92</v>
+        <v>180</v>
       </c>
       <c r="M15" t="n">
-        <v>179.96</v>
+        <v>183.24</v>
       </c>
       <c r="N15" t="n">
-        <v>175.86</v>
+        <v>178.14</v>
       </c>
       <c r="O15" t="n">
-        <v>179.3</v>
+        <v>180.7</v>
       </c>
       <c r="P15" t="n">
-        <v>146.4748</v>
+        <v>146.8316</v>
       </c>
       <c r="Q15" t="n">
-        <v>169.8238</v>
+        <v>169.5375</v>
       </c>
       <c r="R15" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S15" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>7 aug</t>
+          <t>10 aug</t>
         </is>
       </c>
       <c r="V15" t="n">
-        <v>498.272</v>
+        <v>502.4941</v>
       </c>
       <c r="W15" t="n">
-        <v>504.2308</v>
+        <v>512.7646999999999</v>
       </c>
       <c r="X15" t="n">
-        <v>497.7929</v>
+        <v>501.3262</v>
       </c>
       <c r="Y15" t="n">
-        <v>499.0505</v>
+        <v>505.1091</v>
       </c>
       <c r="Z15" t="n">
-        <v>406.2472</v>
+        <v>407.8257</v>
       </c>
       <c r="AA15" t="n">
-        <v>431.0194</v>
+        <v>430.9778</v>
       </c>
       <c r="AB15" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC15" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>11 aug</t>
+          <t>12 aug</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>38.7385</v>
+        <v>38.8573</v>
       </c>
       <c r="C16" t="n">
-        <v>39.0058</v>
+        <v>38.986</v>
       </c>
       <c r="D16" t="n">
-        <v>38.6148</v>
+        <v>38.3871</v>
       </c>
       <c r="E16" t="n">
-        <v>38.9662</v>
+        <v>38.6494</v>
       </c>
       <c r="F16" t="n">
-        <v>36.374</v>
+        <v>36.3981</v>
       </c>
       <c r="G16" t="n">
-        <v>34.3685</v>
+        <v>34.4068</v>
       </c>
       <c r="H16" t="n">
         <v>45.05751734733581</v>
@@ -4636,86 +4658,86 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>11 aug</t>
+          <t>12 aug</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>180</v>
+        <v>180.3</v>
       </c>
       <c r="M16" t="n">
-        <v>183.24</v>
+        <v>180.98</v>
       </c>
       <c r="N16" t="n">
-        <v>178.14</v>
+        <v>175.4</v>
       </c>
       <c r="O16" t="n">
-        <v>180.7</v>
+        <v>175.96</v>
       </c>
       <c r="P16" t="n">
-        <v>146.8316</v>
+        <v>147.232</v>
       </c>
       <c r="Q16" t="n">
-        <v>169.5375</v>
+        <v>169.2701</v>
       </c>
       <c r="R16" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S16" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>10 aug</t>
+          <t>11 aug</t>
         </is>
       </c>
       <c r="V16" t="n">
-        <v>502.4941</v>
+        <v>503.3824</v>
       </c>
       <c r="W16" t="n">
-        <v>512.7646999999999</v>
+        <v>504.3805</v>
       </c>
       <c r="X16" t="n">
-        <v>501.3262</v>
+        <v>498.6113</v>
       </c>
       <c r="Y16" t="n">
-        <v>505.1091</v>
+        <v>502.8633</v>
       </c>
       <c r="Z16" t="n">
-        <v>407.8257</v>
+        <v>408.895</v>
       </c>
       <c r="AA16" t="n">
-        <v>430.9778</v>
+        <v>430.9106</v>
       </c>
       <c r="AB16" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC16" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>12 aug</t>
+          <t>13 aug</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>38.8573</v>
+        <v>39</v>
       </c>
       <c r="C17" t="n">
-        <v>38.986</v>
+        <v>39.005</v>
       </c>
       <c r="D17" t="n">
-        <v>38.3871</v>
+        <v>38.2</v>
       </c>
       <c r="E17" t="n">
-        <v>38.6494</v>
+        <v>38.605</v>
       </c>
       <c r="F17" t="n">
-        <v>36.3981</v>
+        <v>36.4313</v>
       </c>
       <c r="G17" t="n">
-        <v>34.4068</v>
+        <v>34.4429</v>
       </c>
       <c r="H17" t="n">
         <v>45.05751734733581</v>
@@ -4725,86 +4747,86 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>12 aug</t>
+          <t>13 aug</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>180.3</v>
+        <v>177.48</v>
       </c>
       <c r="M17" t="n">
-        <v>180.98</v>
+        <v>178.3</v>
       </c>
       <c r="N17" t="n">
-        <v>175.4</v>
+        <v>174.8</v>
       </c>
       <c r="O17" t="n">
-        <v>175.96</v>
+        <v>175.38</v>
       </c>
       <c r="P17" t="n">
-        <v>147.232</v>
+        <v>147.4496</v>
       </c>
       <c r="Q17" t="n">
-        <v>169.2701</v>
+        <v>168.9889</v>
       </c>
       <c r="R17" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S17" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>11 aug</t>
+          <t>12 aug</t>
         </is>
       </c>
       <c r="V17" t="n">
-        <v>503.3824</v>
+        <v>499.0505</v>
       </c>
       <c r="W17" t="n">
-        <v>504.3805</v>
+        <v>500.5577</v>
       </c>
       <c r="X17" t="n">
-        <v>498.6113</v>
+        <v>490.5964</v>
       </c>
       <c r="Y17" t="n">
-        <v>502.8633</v>
+        <v>491.5047</v>
       </c>
       <c r="Z17" t="n">
-        <v>408.895</v>
+        <v>409.532</v>
       </c>
       <c r="AA17" t="n">
-        <v>430.9106</v>
+        <v>430.7866</v>
       </c>
       <c r="AB17" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC17" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>13 aug</t>
+          <t>14 aug</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>39</v>
+        <v>38.65</v>
       </c>
       <c r="C18" t="n">
-        <v>39.005</v>
+        <v>39.1</v>
       </c>
       <c r="D18" t="n">
-        <v>38.2</v>
+        <v>38.56</v>
       </c>
       <c r="E18" t="n">
-        <v>38.605</v>
+        <v>38.97</v>
       </c>
       <c r="F18" t="n">
-        <v>36.4313</v>
+        <v>36.4703</v>
       </c>
       <c r="G18" t="n">
-        <v>34.4429</v>
+        <v>34.4805</v>
       </c>
       <c r="H18" t="n">
         <v>45.05751734733581</v>
@@ -4814,86 +4836,86 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>13 aug</t>
+          <t>14 aug</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>177.48</v>
+        <v>182</v>
       </c>
       <c r="M18" t="n">
-        <v>178.3</v>
+        <v>185.74</v>
       </c>
       <c r="N18" t="n">
-        <v>174.8</v>
+        <v>179.28</v>
       </c>
       <c r="O18" t="n">
-        <v>175.38</v>
+        <v>180.14</v>
       </c>
       <c r="P18" t="n">
-        <v>147.4496</v>
+        <v>147.8228</v>
       </c>
       <c r="Q18" t="n">
-        <v>168.9889</v>
+        <v>168.7386</v>
       </c>
       <c r="R18" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S18" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>12 aug</t>
+          <t>13 aug</t>
         </is>
       </c>
       <c r="V18" t="n">
-        <v>499.0505</v>
+        <v>492.3431</v>
       </c>
       <c r="W18" t="n">
-        <v>500.5577</v>
+        <v>500.398</v>
       </c>
       <c r="X18" t="n">
-        <v>490.5964</v>
+        <v>492.0837</v>
       </c>
       <c r="Y18" t="n">
-        <v>491.5047</v>
+        <v>495.9464</v>
       </c>
       <c r="Z18" t="n">
-        <v>409.532</v>
+        <v>410.6414</v>
       </c>
       <c r="AA18" t="n">
-        <v>430.7866</v>
+        <v>430.6696</v>
       </c>
       <c r="AB18" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC18" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>14 aug</t>
+          <t>17 aug</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>38.65</v>
+        <v>38.97</v>
       </c>
       <c r="C19" t="n">
-        <v>39.1</v>
+        <v>39.27</v>
       </c>
       <c r="D19" t="n">
-        <v>38.56</v>
+        <v>38.765</v>
       </c>
       <c r="E19" t="n">
-        <v>38.97</v>
+        <v>39.15</v>
       </c>
       <c r="F19" t="n">
-        <v>36.4703</v>
+        <v>36.5118</v>
       </c>
       <c r="G19" t="n">
-        <v>34.4805</v>
+        <v>34.5207</v>
       </c>
       <c r="H19" t="n">
         <v>45.05751734733581</v>
@@ -4903,86 +4925,86 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>14 aug</t>
+          <t>17 aug</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>182</v>
+        <v>178.94</v>
       </c>
       <c r="M19" t="n">
-        <v>185.74</v>
+        <v>180.9</v>
       </c>
       <c r="N19" t="n">
-        <v>179.28</v>
+        <v>177.66</v>
       </c>
       <c r="O19" t="n">
-        <v>180.14</v>
+        <v>179.58</v>
       </c>
       <c r="P19" t="n">
-        <v>147.8228</v>
+        <v>148.2524</v>
       </c>
       <c r="Q19" t="n">
-        <v>168.7386</v>
+        <v>168.5337</v>
       </c>
       <c r="R19" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S19" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>13 aug</t>
+          <t>14 aug</t>
         </is>
       </c>
       <c r="V19" t="n">
-        <v>492.3431</v>
+        <v>495.4273</v>
       </c>
       <c r="W19" t="n">
-        <v>500.398</v>
+        <v>499.0705</v>
       </c>
       <c r="X19" t="n">
-        <v>492.0837</v>
+        <v>492.9919</v>
       </c>
       <c r="Y19" t="n">
-        <v>495.9464</v>
+        <v>494.4691</v>
       </c>
       <c r="Z19" t="n">
-        <v>410.6414</v>
+        <v>412</v>
       </c>
       <c r="AA19" t="n">
-        <v>430.6696</v>
+        <v>430.5061</v>
       </c>
       <c r="AB19" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC19" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>17 aug</t>
+          <t>18 aug</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>38.97</v>
+        <v>39.49</v>
       </c>
       <c r="C20" t="n">
-        <v>39.27</v>
+        <v>39.945</v>
       </c>
       <c r="D20" t="n">
-        <v>38.765</v>
+        <v>39.46</v>
       </c>
       <c r="E20" t="n">
-        <v>39.15</v>
+        <v>39.785</v>
       </c>
       <c r="F20" t="n">
-        <v>36.5118</v>
+        <v>36.5781</v>
       </c>
       <c r="G20" t="n">
-        <v>34.5207</v>
+        <v>34.5641</v>
       </c>
       <c r="H20" t="n">
         <v>45.05751734733581</v>
@@ -4992,86 +5014,86 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>17 aug</t>
+          <t>18 aug</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>178.94</v>
+        <v>179.14</v>
       </c>
       <c r="M20" t="n">
-        <v>180.9</v>
+        <v>183.9</v>
       </c>
       <c r="N20" t="n">
-        <v>177.66</v>
+        <v>177.98</v>
       </c>
       <c r="O20" t="n">
-        <v>179.58</v>
+        <v>182.5</v>
       </c>
       <c r="P20" t="n">
-        <v>148.2524</v>
+        <v>148.8084</v>
       </c>
       <c r="Q20" t="n">
-        <v>168.5337</v>
+        <v>168.3358</v>
       </c>
       <c r="R20" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S20" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>14 aug</t>
+          <t>17 aug</t>
         </is>
       </c>
       <c r="V20" t="n">
-        <v>495.4273</v>
+        <v>489.2191</v>
       </c>
       <c r="W20" t="n">
-        <v>499.0705</v>
+        <v>491.7343</v>
       </c>
       <c r="X20" t="n">
-        <v>492.9919</v>
+        <v>477.5111</v>
       </c>
       <c r="Y20" t="n">
-        <v>494.4691</v>
+        <v>479.4474</v>
       </c>
       <c r="Z20" t="n">
-        <v>412</v>
+        <v>413.044</v>
       </c>
       <c r="AA20" t="n">
-        <v>430.5061</v>
+        <v>430.2151</v>
       </c>
       <c r="AB20" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC20" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>18 aug</t>
+          <t>19 aug</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>39.49</v>
+        <v>39.835</v>
       </c>
       <c r="C21" t="n">
-        <v>39.945</v>
+        <v>40.14</v>
       </c>
       <c r="D21" t="n">
-        <v>39.46</v>
+        <v>39.74</v>
       </c>
       <c r="E21" t="n">
-        <v>39.785</v>
+        <v>39.94</v>
       </c>
       <c r="F21" t="n">
-        <v>36.5781</v>
+        <v>36.6336</v>
       </c>
       <c r="G21" t="n">
-        <v>34.5641</v>
+        <v>34.6092</v>
       </c>
       <c r="H21" t="n">
         <v>45.05751734733581</v>
@@ -5081,86 +5103,86 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>18 aug</t>
+          <t>19 aug</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>179.14</v>
+        <v>181.7</v>
       </c>
       <c r="M21" t="n">
-        <v>183.9</v>
+        <v>186.98</v>
       </c>
       <c r="N21" t="n">
-        <v>177.98</v>
+        <v>180.38</v>
       </c>
       <c r="O21" t="n">
-        <v>182.5</v>
+        <v>185.9</v>
       </c>
       <c r="P21" t="n">
-        <v>148.8084</v>
+        <v>149.5324</v>
       </c>
       <c r="Q21" t="n">
-        <v>168.3358</v>
+        <v>168.1618</v>
       </c>
       <c r="R21" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S21" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>17 aug</t>
+          <t>18 aug</t>
         </is>
       </c>
       <c r="V21" t="n">
-        <v>489.2191</v>
+        <v>480.6352</v>
       </c>
       <c r="W21" t="n">
-        <v>491.7343</v>
+        <v>483.3601</v>
       </c>
       <c r="X21" t="n">
-        <v>477.5111</v>
+        <v>476.2534</v>
       </c>
       <c r="Y21" t="n">
-        <v>479.4474</v>
+        <v>480.725</v>
       </c>
       <c r="Z21" t="n">
-        <v>413.044</v>
+        <v>414.3408</v>
       </c>
       <c r="AA21" t="n">
-        <v>430.2151</v>
+        <v>429.933</v>
       </c>
       <c r="AB21" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC21" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>19 aug</t>
+          <t>20 aug</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>39.835</v>
+        <v>39.865</v>
       </c>
       <c r="C22" t="n">
-        <v>40.14</v>
+        <v>40.51</v>
       </c>
       <c r="D22" t="n">
-        <v>39.74</v>
+        <v>39.8</v>
       </c>
       <c r="E22" t="n">
-        <v>39.94</v>
+        <v>40.28</v>
       </c>
       <c r="F22" t="n">
-        <v>36.6336</v>
+        <v>36.6884</v>
       </c>
       <c r="G22" t="n">
-        <v>34.6092</v>
+        <v>34.6545</v>
       </c>
       <c r="H22" t="n">
         <v>45.05751734733581</v>
@@ -5170,86 +5192,86 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>19 aug</t>
+          <t>20 aug</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>181.7</v>
+        <v>183.78</v>
       </c>
       <c r="M22" t="n">
-        <v>186.98</v>
+        <v>186.1</v>
       </c>
       <c r="N22" t="n">
-        <v>180.38</v>
+        <v>182.52</v>
       </c>
       <c r="O22" t="n">
-        <v>185.9</v>
+        <v>185.64</v>
       </c>
       <c r="P22" t="n">
-        <v>149.5324</v>
+        <v>150.4472</v>
       </c>
       <c r="Q22" t="n">
-        <v>168.1618</v>
+        <v>167.9648</v>
       </c>
       <c r="R22" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S22" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>18 aug</t>
+          <t>19 aug</t>
         </is>
       </c>
       <c r="V22" t="n">
-        <v>480.6352</v>
+        <v>479.168</v>
       </c>
       <c r="W22" t="n">
-        <v>483.3601</v>
+        <v>488.3806</v>
       </c>
       <c r="X22" t="n">
-        <v>476.2534</v>
+        <v>478.4593</v>
       </c>
       <c r="Y22" t="n">
-        <v>480.725</v>
+        <v>483.4</v>
       </c>
       <c r="Z22" t="n">
-        <v>414.3408</v>
+        <v>415.7895</v>
       </c>
       <c r="AA22" t="n">
-        <v>429.933</v>
+        <v>429.7427</v>
       </c>
       <c r="AB22" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC22" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20 aug</t>
+          <t>21 aug</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>39.865</v>
+        <v>40.1</v>
       </c>
       <c r="C23" t="n">
-        <v>40.51</v>
+        <v>40.37</v>
       </c>
       <c r="D23" t="n">
-        <v>39.8</v>
+        <v>39.84</v>
       </c>
       <c r="E23" t="n">
-        <v>40.28</v>
+        <v>39.91</v>
       </c>
       <c r="F23" t="n">
-        <v>36.6884</v>
+        <v>36.7478</v>
       </c>
       <c r="G23" t="n">
-        <v>34.6545</v>
+        <v>34.6988</v>
       </c>
       <c r="H23" t="n">
         <v>45.05751734733581</v>
@@ -5259,86 +5281,86 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>20 aug</t>
+          <t>21 aug</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>183.78</v>
+        <v>185.18</v>
       </c>
       <c r="M23" t="n">
-        <v>186.1</v>
+        <v>188.4</v>
       </c>
       <c r="N23" t="n">
-        <v>182.52</v>
+        <v>183.6</v>
       </c>
       <c r="O23" t="n">
-        <v>185.64</v>
+        <v>188.12</v>
       </c>
       <c r="P23" t="n">
-        <v>150.4472</v>
+        <v>151.4044</v>
       </c>
       <c r="Q23" t="n">
-        <v>167.9648</v>
+        <v>167.794</v>
       </c>
       <c r="R23" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S23" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>19 aug</t>
+          <t>20 aug</t>
         </is>
       </c>
       <c r="V23" t="n">
-        <v>479.168</v>
+        <v>483.3</v>
       </c>
       <c r="W23" t="n">
-        <v>488.3806</v>
+        <v>484.16</v>
       </c>
       <c r="X23" t="n">
-        <v>478.4593</v>
+        <v>479.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>483.4</v>
+        <v>481.15</v>
       </c>
       <c r="Z23" t="n">
-        <v>415.7895</v>
+        <v>417.3594</v>
       </c>
       <c r="AA23" t="n">
-        <v>429.7427</v>
+        <v>429.5805</v>
       </c>
       <c r="AB23" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC23" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>21 aug</t>
+          <t>24 aug</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>40.1</v>
+        <v>39.88</v>
       </c>
       <c r="C24" t="n">
-        <v>40.37</v>
+        <v>40.085</v>
       </c>
       <c r="D24" t="n">
-        <v>39.84</v>
+        <v>39.68</v>
       </c>
       <c r="E24" t="n">
-        <v>39.91</v>
+        <v>39.775</v>
       </c>
       <c r="F24" t="n">
-        <v>36.7478</v>
+        <v>36.8369</v>
       </c>
       <c r="G24" t="n">
-        <v>34.6988</v>
+        <v>34.7421</v>
       </c>
       <c r="H24" t="n">
         <v>45.05751734733581</v>
@@ -5348,86 +5370,86 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>21 aug</t>
+          <t>24 aug</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>185.18</v>
+        <v>186.86</v>
       </c>
       <c r="M24" t="n">
-        <v>188.4</v>
+        <v>188.16</v>
       </c>
       <c r="N24" t="n">
-        <v>183.6</v>
+        <v>185.52</v>
       </c>
       <c r="O24" t="n">
-        <v>188.12</v>
+        <v>187.2</v>
       </c>
       <c r="P24" t="n">
-        <v>151.4044</v>
+        <v>152.2848</v>
       </c>
       <c r="Q24" t="n">
-        <v>167.794</v>
+        <v>167.6093</v>
       </c>
       <c r="R24" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S24" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>20 aug</t>
+          <t>21 aug</t>
         </is>
       </c>
       <c r="V24" t="n">
-        <v>483.3</v>
+        <v>479.88</v>
       </c>
       <c r="W24" t="n">
-        <v>484.16</v>
+        <v>486.36</v>
       </c>
       <c r="X24" t="n">
-        <v>479.5</v>
+        <v>478.53</v>
       </c>
       <c r="Y24" t="n">
-        <v>481.15</v>
+        <v>483.24</v>
       </c>
       <c r="Z24" t="n">
-        <v>417.3594</v>
+        <v>419.092</v>
       </c>
       <c r="AA24" t="n">
-        <v>429.5805</v>
+        <v>429.4327</v>
       </c>
       <c r="AB24" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC24" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>24 aug</t>
+          <t>25 aug</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>39.88</v>
+        <v>39.77</v>
       </c>
       <c r="C25" t="n">
-        <v>40.085</v>
+        <v>39.915</v>
       </c>
       <c r="D25" t="n">
-        <v>39.68</v>
+        <v>39.385</v>
       </c>
       <c r="E25" t="n">
-        <v>39.775</v>
+        <v>39.6</v>
       </c>
       <c r="F25" t="n">
-        <v>36.8369</v>
+        <v>36.926</v>
       </c>
       <c r="G25" t="n">
-        <v>34.7421</v>
+        <v>34.783</v>
       </c>
       <c r="H25" t="n">
         <v>45.05751734733581</v>
@@ -5437,86 +5459,86 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>24 aug</t>
+          <t>25 aug</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>186.86</v>
+        <v>186.4</v>
       </c>
       <c r="M25" t="n">
-        <v>188.16</v>
+        <v>187.62</v>
       </c>
       <c r="N25" t="n">
-        <v>185.52</v>
+        <v>182.74</v>
       </c>
       <c r="O25" t="n">
-        <v>187.2</v>
+        <v>185.46</v>
       </c>
       <c r="P25" t="n">
-        <v>152.2848</v>
+        <v>153.136</v>
       </c>
       <c r="Q25" t="n">
-        <v>167.6093</v>
+        <v>167.4651</v>
       </c>
       <c r="R25" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S25" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>21 aug</t>
+          <t>24 aug</t>
         </is>
       </c>
       <c r="V25" t="n">
-        <v>479.88</v>
+        <v>483.21</v>
       </c>
       <c r="W25" t="n">
-        <v>486.36</v>
+        <v>490.61</v>
       </c>
       <c r="X25" t="n">
-        <v>478.53</v>
+        <v>481.86</v>
       </c>
       <c r="Y25" t="n">
-        <v>483.24</v>
+        <v>487.31</v>
       </c>
       <c r="Z25" t="n">
-        <v>419.092</v>
+        <v>421.046</v>
       </c>
       <c r="AA25" t="n">
-        <v>429.4327</v>
+        <v>429.3185</v>
       </c>
       <c r="AB25" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC25" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>25 aug</t>
+          <t>26 aug</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>39.77</v>
+        <v>39.275</v>
       </c>
       <c r="C26" t="n">
-        <v>39.915</v>
+        <v>39.47</v>
       </c>
       <c r="D26" t="n">
-        <v>39.385</v>
+        <v>38.91</v>
       </c>
       <c r="E26" t="n">
-        <v>39.6</v>
+        <v>39.42</v>
       </c>
       <c r="F26" t="n">
-        <v>36.926</v>
+        <v>37.0192</v>
       </c>
       <c r="G26" t="n">
-        <v>34.783</v>
+        <v>34.8202</v>
       </c>
       <c r="H26" t="n">
         <v>45.05751734733581</v>
@@ -5526,86 +5548,86 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>25 aug</t>
+          <t>26 aug</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>186.4</v>
+        <v>179.92</v>
       </c>
       <c r="M26" t="n">
-        <v>187.62</v>
+        <v>182.16</v>
       </c>
       <c r="N26" t="n">
-        <v>182.74</v>
+        <v>176.82</v>
       </c>
       <c r="O26" t="n">
-        <v>185.46</v>
+        <v>180.02</v>
       </c>
       <c r="P26" t="n">
-        <v>153.136</v>
+        <v>153.9128</v>
       </c>
       <c r="Q26" t="n">
-        <v>167.4651</v>
+        <v>167.3049</v>
       </c>
       <c r="R26" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S26" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>24 aug</t>
+          <t>25 aug</t>
         </is>
       </c>
       <c r="V26" t="n">
-        <v>483.21</v>
+        <v>485.44</v>
       </c>
       <c r="W26" t="n">
-        <v>490.61</v>
+        <v>492.44</v>
       </c>
       <c r="X26" t="n">
-        <v>481.86</v>
+        <v>484.3</v>
       </c>
       <c r="Y26" t="n">
-        <v>487.31</v>
+        <v>491.71</v>
       </c>
       <c r="Z26" t="n">
-        <v>421.046</v>
+        <v>423.0801</v>
       </c>
       <c r="AA26" t="n">
-        <v>429.3185</v>
+        <v>429.262</v>
       </c>
       <c r="AB26" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC26" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>26 aug</t>
+          <t>27 aug</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>39.275</v>
+        <v>39.16</v>
       </c>
       <c r="C27" t="n">
-        <v>39.47</v>
+        <v>39.295</v>
       </c>
       <c r="D27" t="n">
-        <v>38.91</v>
+        <v>38.65</v>
       </c>
       <c r="E27" t="n">
-        <v>39.42</v>
+        <v>38.76</v>
       </c>
       <c r="F27" t="n">
-        <v>37.0192</v>
+        <v>37.117</v>
       </c>
       <c r="G27" t="n">
-        <v>34.8202</v>
+        <v>34.8559</v>
       </c>
       <c r="H27" t="n">
         <v>45.05751734733581</v>
@@ -5615,86 +5637,86 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>26 aug</t>
+          <t>27 aug</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>179.92</v>
+        <v>182.5</v>
       </c>
       <c r="M27" t="n">
-        <v>182.16</v>
+        <v>190.8</v>
       </c>
       <c r="N27" t="n">
-        <v>176.82</v>
+        <v>181.14</v>
       </c>
       <c r="O27" t="n">
-        <v>180.02</v>
+        <v>189.88</v>
       </c>
       <c r="P27" t="n">
-        <v>153.9128</v>
+        <v>155.0132</v>
       </c>
       <c r="Q27" t="n">
-        <v>167.3049</v>
+        <v>167.1911</v>
       </c>
       <c r="R27" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S27" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>25 aug</t>
+          <t>26 aug</t>
         </is>
       </c>
       <c r="V27" t="n">
-        <v>485.44</v>
+        <v>487.85</v>
       </c>
       <c r="W27" t="n">
-        <v>492.44</v>
+        <v>497.4</v>
       </c>
       <c r="X27" t="n">
-        <v>484.3</v>
+        <v>487.31</v>
       </c>
       <c r="Y27" t="n">
-        <v>491.71</v>
+        <v>496.37</v>
       </c>
       <c r="Z27" t="n">
-        <v>423.0801</v>
+        <v>425.0273</v>
       </c>
       <c r="AA27" t="n">
-        <v>429.262</v>
+        <v>429.2786</v>
       </c>
       <c r="AB27" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC27" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>27 aug</t>
+          <t>28 aug</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>39.16</v>
+        <v>39</v>
       </c>
       <c r="C28" t="n">
-        <v>39.295</v>
+        <v>39.18</v>
       </c>
       <c r="D28" t="n">
-        <v>38.65</v>
+        <v>38.845</v>
       </c>
       <c r="E28" t="n">
-        <v>38.76</v>
+        <v>39.145</v>
       </c>
       <c r="F28" t="n">
-        <v>37.117</v>
+        <v>37.2162</v>
       </c>
       <c r="G28" t="n">
-        <v>34.8559</v>
+        <v>34.8941</v>
       </c>
       <c r="H28" t="n">
         <v>45.05751734733581</v>
@@ -5704,86 +5726,86 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>27 aug</t>
+          <t>28 aug</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>182.5</v>
+        <v>189.5</v>
       </c>
       <c r="M28" t="n">
-        <v>190.8</v>
+        <v>191.94</v>
       </c>
       <c r="N28" t="n">
-        <v>181.14</v>
+        <v>187.98</v>
       </c>
       <c r="O28" t="n">
-        <v>189.88</v>
+        <v>191.32</v>
       </c>
       <c r="P28" t="n">
-        <v>155.0132</v>
+        <v>156.1568</v>
       </c>
       <c r="Q28" t="n">
-        <v>167.1911</v>
+        <v>167.0806</v>
       </c>
       <c r="R28" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S28" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>26 aug</t>
+          <t>27 aug</t>
         </is>
       </c>
       <c r="V28" t="n">
-        <v>487.85</v>
+        <v>494.88</v>
       </c>
       <c r="W28" t="n">
-        <v>497.4</v>
+        <v>506.48</v>
       </c>
       <c r="X28" t="n">
-        <v>487.31</v>
+        <v>490.08</v>
       </c>
       <c r="Y28" t="n">
-        <v>496.37</v>
+        <v>505.06</v>
       </c>
       <c r="Z28" t="n">
-        <v>425.0273</v>
+        <v>427.2667</v>
       </c>
       <c r="AA28" t="n">
-        <v>429.2786</v>
+        <v>429.3401</v>
       </c>
       <c r="AB28" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC28" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>28 aug</t>
+          <t>31 aug</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>39</v>
+        <v>39.54</v>
       </c>
       <c r="C29" t="n">
-        <v>39.18</v>
+        <v>39.91</v>
       </c>
       <c r="D29" t="n">
-        <v>38.845</v>
+        <v>39.24</v>
       </c>
       <c r="E29" t="n">
-        <v>39.145</v>
+        <v>39.335</v>
       </c>
       <c r="F29" t="n">
-        <v>37.2162</v>
+        <v>37.3111</v>
       </c>
       <c r="G29" t="n">
-        <v>34.8941</v>
+        <v>34.9333</v>
       </c>
       <c r="H29" t="n">
         <v>45.05751734733581</v>
@@ -5793,86 +5815,86 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>28 aug</t>
+          <t>31 aug</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>189.5</v>
+        <v>188.46</v>
       </c>
       <c r="M29" t="n">
-        <v>191.94</v>
+        <v>192.12</v>
       </c>
       <c r="N29" t="n">
-        <v>187.98</v>
+        <v>188.2</v>
       </c>
       <c r="O29" t="n">
-        <v>191.32</v>
+        <v>190.9</v>
       </c>
       <c r="P29" t="n">
-        <v>156.1568</v>
+        <v>157.3304</v>
       </c>
       <c r="Q29" t="n">
-        <v>167.0806</v>
+        <v>166.9613</v>
       </c>
       <c r="R29" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S29" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>27 aug</t>
+          <t>28 aug</t>
         </is>
       </c>
       <c r="V29" t="n">
-        <v>494.88</v>
+        <v>505.33</v>
       </c>
       <c r="W29" t="n">
-        <v>506.48</v>
+        <v>517.78</v>
       </c>
       <c r="X29" t="n">
-        <v>490.08</v>
+        <v>504.87</v>
       </c>
       <c r="Y29" t="n">
-        <v>505.06</v>
+        <v>513.53</v>
       </c>
       <c r="Z29" t="n">
-        <v>427.2667</v>
+        <v>429.9734</v>
       </c>
       <c r="AA29" t="n">
-        <v>429.3401</v>
+        <v>429.3984</v>
       </c>
       <c r="AB29" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC29" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>31 aug</t>
+          <t>1 sep</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>39.54</v>
+        <v>39.77</v>
       </c>
       <c r="C30" t="n">
-        <v>39.91</v>
+        <v>40.19</v>
       </c>
       <c r="D30" t="n">
-        <v>39.24</v>
+        <v>39.645</v>
       </c>
       <c r="E30" t="n">
-        <v>39.335</v>
+        <v>40.155</v>
       </c>
       <c r="F30" t="n">
-        <v>37.3111</v>
+        <v>37.4239</v>
       </c>
       <c r="G30" t="n">
-        <v>34.9333</v>
+        <v>34.9763</v>
       </c>
       <c r="H30" t="n">
         <v>45.05751734733581</v>
@@ -5882,86 +5904,86 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>31 aug</t>
+          <t>1 sep</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>188.46</v>
+        <v>186</v>
       </c>
       <c r="M30" t="n">
-        <v>192.12</v>
+        <v>187.86</v>
       </c>
       <c r="N30" t="n">
-        <v>188.2</v>
+        <v>183.32</v>
       </c>
       <c r="O30" t="n">
-        <v>190.9</v>
+        <v>184.26</v>
       </c>
       <c r="P30" t="n">
-        <v>157.3304</v>
+        <v>158.3252</v>
       </c>
       <c r="Q30" t="n">
-        <v>166.9613</v>
+        <v>166.8103</v>
       </c>
       <c r="R30" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S30" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>28 aug</t>
+          <t>31 aug</t>
         </is>
       </c>
       <c r="V30" t="n">
-        <v>505.33</v>
+        <v>510.38</v>
       </c>
       <c r="W30" t="n">
-        <v>517.78</v>
+        <v>512.1900000000001</v>
       </c>
       <c r="X30" t="n">
-        <v>504.87</v>
+        <v>506.39</v>
       </c>
       <c r="Y30" t="n">
-        <v>513.53</v>
+        <v>507.29</v>
       </c>
       <c r="Z30" t="n">
-        <v>429.9734</v>
+        <v>432.5454</v>
       </c>
       <c r="AA30" t="n">
-        <v>429.3984</v>
+        <v>429.4122</v>
       </c>
       <c r="AB30" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC30" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1 sep</t>
+          <t>2 sep</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>39.77</v>
+        <v>40.35</v>
       </c>
       <c r="C31" t="n">
-        <v>40.19</v>
+        <v>40.615</v>
       </c>
       <c r="D31" t="n">
-        <v>39.645</v>
+        <v>39.975</v>
       </c>
       <c r="E31" t="n">
-        <v>40.155</v>
+        <v>40.21</v>
       </c>
       <c r="F31" t="n">
-        <v>37.4239</v>
+        <v>37.5499</v>
       </c>
       <c r="G31" t="n">
-        <v>34.9763</v>
+        <v>35.0217</v>
       </c>
       <c r="H31" t="n">
         <v>45.05751734733581</v>
@@ -5971,86 +5993,86 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>1 sep</t>
+          <t>2 sep</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>186</v>
+        <v>182.18</v>
       </c>
       <c r="M31" t="n">
-        <v>187.86</v>
+        <v>184.7</v>
       </c>
       <c r="N31" t="n">
-        <v>183.32</v>
+        <v>180.72</v>
       </c>
       <c r="O31" t="n">
-        <v>184.26</v>
+        <v>181.44</v>
       </c>
       <c r="P31" t="n">
-        <v>158.3252</v>
+        <v>159.2568</v>
       </c>
       <c r="Q31" t="n">
-        <v>166.8103</v>
+        <v>166.6796</v>
       </c>
       <c r="R31" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S31" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>31 aug</t>
+          <t>1 sep</t>
         </is>
       </c>
       <c r="V31" t="n">
-        <v>510.38</v>
+        <v>497.52</v>
       </c>
       <c r="W31" t="n">
-        <v>512.1900000000001</v>
+        <v>505.97</v>
       </c>
       <c r="X31" t="n">
-        <v>506.39</v>
+        <v>496.78</v>
       </c>
       <c r="Y31" t="n">
-        <v>507.29</v>
+        <v>501.02</v>
       </c>
       <c r="Z31" t="n">
-        <v>432.5454</v>
+        <v>435.2328</v>
       </c>
       <c r="AA31" t="n">
-        <v>429.4122</v>
+        <v>429.3825</v>
       </c>
       <c r="AB31" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC31" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2 sep</t>
+          <t>3 sep</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>40.35</v>
+        <v>40.095</v>
       </c>
       <c r="C32" t="n">
-        <v>40.615</v>
+        <v>40.215</v>
       </c>
       <c r="D32" t="n">
-        <v>39.975</v>
+        <v>39.54</v>
       </c>
       <c r="E32" t="n">
-        <v>40.21</v>
+        <v>40.04</v>
       </c>
       <c r="F32" t="n">
-        <v>37.5499</v>
+        <v>37.6767</v>
       </c>
       <c r="G32" t="n">
-        <v>35.0217</v>
+        <v>35.0679</v>
       </c>
       <c r="H32" t="n">
         <v>45.05751734733581</v>
@@ -6060,86 +6082,86 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2 sep</t>
+          <t>3 sep</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>182.18</v>
+        <v>182.08</v>
       </c>
       <c r="M32" t="n">
-        <v>184.7</v>
+        <v>187.56</v>
       </c>
       <c r="N32" t="n">
-        <v>180.72</v>
+        <v>182</v>
       </c>
       <c r="O32" t="n">
-        <v>181.44</v>
+        <v>185.58</v>
       </c>
       <c r="P32" t="n">
-        <v>159.2568</v>
+        <v>160.3228</v>
       </c>
       <c r="Q32" t="n">
-        <v>166.6796</v>
+        <v>166.5898</v>
       </c>
       <c r="R32" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S32" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>1 sep</t>
+          <t>2 sep</t>
         </is>
       </c>
       <c r="V32" t="n">
-        <v>497.52</v>
+        <v>499.85</v>
       </c>
       <c r="W32" t="n">
-        <v>505.97</v>
+        <v>500.27</v>
       </c>
       <c r="X32" t="n">
-        <v>496.78</v>
+        <v>493.81</v>
       </c>
       <c r="Y32" t="n">
-        <v>501.02</v>
+        <v>496.82</v>
       </c>
       <c r="Z32" t="n">
-        <v>435.2328</v>
+        <v>437.7045</v>
       </c>
       <c r="AA32" t="n">
-        <v>429.3825</v>
+        <v>429.3706</v>
       </c>
       <c r="AB32" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC32" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3 sep</t>
+          <t>4 sep</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>40.095</v>
+        <v>40.145</v>
       </c>
       <c r="C33" t="n">
-        <v>40.215</v>
+        <v>40.28</v>
       </c>
       <c r="D33" t="n">
-        <v>39.54</v>
+        <v>39.665</v>
       </c>
       <c r="E33" t="n">
-        <v>40.04</v>
+        <v>40.105</v>
       </c>
       <c r="F33" t="n">
-        <v>37.6767</v>
+        <v>37.8115</v>
       </c>
       <c r="G33" t="n">
-        <v>35.0679</v>
+        <v>35.113</v>
       </c>
       <c r="H33" t="n">
         <v>45.05751734733581</v>
@@ -6149,86 +6171,86 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>3 sep</t>
+          <t>4 sep</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>182.08</v>
+        <v>187.8</v>
       </c>
       <c r="M33" t="n">
-        <v>187.56</v>
+        <v>189.9</v>
       </c>
       <c r="N33" t="n">
-        <v>182</v>
+        <v>184.96</v>
       </c>
       <c r="O33" t="n">
-        <v>185.58</v>
+        <v>185.68</v>
       </c>
       <c r="P33" t="n">
-        <v>160.3228</v>
+        <v>161.3336</v>
       </c>
       <c r="Q33" t="n">
-        <v>166.5898</v>
+        <v>166.5086</v>
       </c>
       <c r="R33" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S33" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>2 sep</t>
+          <t>3 sep</t>
         </is>
       </c>
       <c r="V33" t="n">
-        <v>499.85</v>
+        <v>501.66</v>
       </c>
       <c r="W33" t="n">
-        <v>500.27</v>
+        <v>515.65</v>
       </c>
       <c r="X33" t="n">
-        <v>493.81</v>
+        <v>500.8</v>
       </c>
       <c r="Y33" t="n">
-        <v>496.82</v>
+        <v>510.12</v>
       </c>
       <c r="Z33" t="n">
-        <v>437.7045</v>
+        <v>440.6114</v>
       </c>
       <c r="AA33" t="n">
-        <v>429.3706</v>
+        <v>429.3912</v>
       </c>
       <c r="AB33" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC33" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>4 sep</t>
+          <t>7 sep</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>40.145</v>
+        <v>40.26</v>
       </c>
       <c r="C34" t="n">
-        <v>40.28</v>
+        <v>40.845</v>
       </c>
       <c r="D34" t="n">
-        <v>39.665</v>
+        <v>40.12</v>
       </c>
       <c r="E34" t="n">
-        <v>40.105</v>
+        <v>40.56</v>
       </c>
       <c r="F34" t="n">
-        <v>37.8115</v>
+        <v>37.9551</v>
       </c>
       <c r="G34" t="n">
-        <v>35.113</v>
+        <v>35.1619</v>
       </c>
       <c r="H34" t="n">
         <v>45.05751734733581</v>
@@ -6238,86 +6260,86 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>4 sep</t>
+          <t>7 sep</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>187.8</v>
+        <v>183.56</v>
       </c>
       <c r="M34" t="n">
-        <v>189.9</v>
+        <v>184.3</v>
       </c>
       <c r="N34" t="n">
-        <v>184.96</v>
+        <v>179.92</v>
       </c>
       <c r="O34" t="n">
-        <v>185.68</v>
+        <v>182.8</v>
       </c>
       <c r="P34" t="n">
-        <v>161.3336</v>
+        <v>162.2568</v>
       </c>
       <c r="Q34" t="n">
-        <v>166.5086</v>
+        <v>166.4122</v>
       </c>
       <c r="R34" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S34" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>3 sep</t>
+          <t>4 sep</t>
         </is>
       </c>
       <c r="V34" t="n">
-        <v>501.66</v>
+        <v>510</v>
       </c>
       <c r="W34" t="n">
-        <v>515.65</v>
+        <v>511</v>
       </c>
       <c r="X34" t="n">
-        <v>500.8</v>
+        <v>499.36</v>
       </c>
       <c r="Y34" t="n">
-        <v>510.12</v>
+        <v>499.7</v>
       </c>
       <c r="Z34" t="n">
-        <v>440.6114</v>
+        <v>443.5621</v>
       </c>
       <c r="AA34" t="n">
-        <v>429.3912</v>
+        <v>429.3729</v>
       </c>
       <c r="AB34" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC34" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>7 sep</t>
+          <t>8 sep</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>40.26</v>
+        <v>40.83</v>
       </c>
       <c r="C35" t="n">
-        <v>40.845</v>
+        <v>41.18</v>
       </c>
       <c r="D35" t="n">
-        <v>40.12</v>
+        <v>40.6325</v>
       </c>
       <c r="E35" t="n">
-        <v>40.56</v>
+        <v>40.855</v>
       </c>
       <c r="F35" t="n">
-        <v>37.9551</v>
+        <v>38.0977</v>
       </c>
       <c r="G35" t="n">
-        <v>35.1619</v>
+        <v>35.2131</v>
       </c>
       <c r="H35" t="n">
         <v>45.05751734733581</v>
@@ -6327,86 +6349,86 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>7 sep</t>
+          <t>8 sep</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>183.56</v>
+        <v>182.32</v>
       </c>
       <c r="M35" t="n">
-        <v>184.3</v>
+        <v>183.76</v>
       </c>
       <c r="N35" t="n">
-        <v>179.92</v>
+        <v>180.02</v>
       </c>
       <c r="O35" t="n">
-        <v>182.8</v>
+        <v>181.7</v>
       </c>
       <c r="P35" t="n">
-        <v>162.2568</v>
+        <v>163.2108</v>
       </c>
       <c r="Q35" t="n">
-        <v>166.4122</v>
+        <v>166.3049</v>
       </c>
       <c r="R35" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S35" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>4 sep</t>
+          <t>8 sep</t>
         </is>
       </c>
       <c r="V35" t="n">
-        <v>510</v>
+        <v>493.01</v>
       </c>
       <c r="W35" t="n">
-        <v>511</v>
+        <v>495.19</v>
       </c>
       <c r="X35" t="n">
-        <v>499.36</v>
+        <v>490.15</v>
       </c>
       <c r="Y35" t="n">
-        <v>499.7</v>
+        <v>493.95</v>
       </c>
       <c r="Z35" t="n">
-        <v>443.5621</v>
+        <v>445.9957</v>
       </c>
       <c r="AA35" t="n">
-        <v>429.3729</v>
+        <v>429.3939</v>
       </c>
       <c r="AB35" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC35" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>8 sep</t>
+          <t>9 sep</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>40.83</v>
+        <v>41.1</v>
       </c>
       <c r="C36" t="n">
-        <v>41.18</v>
+        <v>41.385</v>
       </c>
       <c r="D36" t="n">
-        <v>40.6325</v>
+        <v>40.85</v>
       </c>
       <c r="E36" t="n">
-        <v>40.855</v>
+        <v>40.94</v>
       </c>
       <c r="F36" t="n">
-        <v>38.0977</v>
+        <v>38.2513</v>
       </c>
       <c r="G36" t="n">
-        <v>35.2131</v>
+        <v>35.2646</v>
       </c>
       <c r="H36" t="n">
         <v>45.05751734733581</v>
@@ -6416,86 +6438,86 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>8 sep</t>
+          <t>9 sep</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>182.32</v>
+        <v>183</v>
       </c>
       <c r="M36" t="n">
-        <v>183.76</v>
+        <v>187.04</v>
       </c>
       <c r="N36" t="n">
-        <v>180.02</v>
+        <v>181.36</v>
       </c>
       <c r="O36" t="n">
-        <v>181.7</v>
+        <v>182.86</v>
       </c>
       <c r="P36" t="n">
-        <v>163.2108</v>
+        <v>164.0504</v>
       </c>
       <c r="Q36" t="n">
-        <v>166.3049</v>
+        <v>166.2113</v>
       </c>
       <c r="R36" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S36" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>8 sep</t>
+          <t>9 sep</t>
         </is>
       </c>
       <c r="V36" t="n">
-        <v>493.01</v>
+        <v>493.07</v>
       </c>
       <c r="W36" t="n">
-        <v>495.19</v>
+        <v>494.39</v>
       </c>
       <c r="X36" t="n">
-        <v>490.15</v>
+        <v>489.8</v>
       </c>
       <c r="Y36" t="n">
-        <v>493.95</v>
+        <v>491.65</v>
       </c>
       <c r="Z36" t="n">
-        <v>445.9957</v>
+        <v>448.4712</v>
       </c>
       <c r="AA36" t="n">
-        <v>429.3939</v>
+        <v>429.4364</v>
       </c>
       <c r="AB36" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC36" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>9 sep</t>
+          <t>10 sep</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>41.1</v>
+        <v>40.98</v>
       </c>
       <c r="C37" t="n">
-        <v>41.385</v>
+        <v>41.77</v>
       </c>
       <c r="D37" t="n">
-        <v>40.85</v>
+        <v>40.93</v>
       </c>
       <c r="E37" t="n">
-        <v>40.94</v>
+        <v>41.23</v>
       </c>
       <c r="F37" t="n">
-        <v>38.2513</v>
+        <v>38.4034</v>
       </c>
       <c r="G37" t="n">
-        <v>35.2646</v>
+        <v>35.3174</v>
       </c>
       <c r="H37" t="n">
         <v>45.05751734733581</v>
@@ -6505,86 +6527,86 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>9 sep</t>
+          <t>10 sep</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="M37" t="n">
-        <v>187.04</v>
+        <v>180.4</v>
       </c>
       <c r="N37" t="n">
-        <v>181.36</v>
+        <v>176.2</v>
       </c>
       <c r="O37" t="n">
-        <v>182.86</v>
+        <v>177.82</v>
       </c>
       <c r="P37" t="n">
-        <v>164.0504</v>
+        <v>164.7724</v>
       </c>
       <c r="Q37" t="n">
-        <v>166.2113</v>
+        <v>166.0803</v>
       </c>
       <c r="R37" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S37" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>9 sep</t>
+          <t>10 sep</t>
         </is>
       </c>
       <c r="V37" t="n">
-        <v>493.07</v>
+        <v>488.32</v>
       </c>
       <c r="W37" t="n">
-        <v>494.39</v>
+        <v>494.52</v>
       </c>
       <c r="X37" t="n">
-        <v>489.8</v>
+        <v>486</v>
       </c>
       <c r="Y37" t="n">
-        <v>491.65</v>
+        <v>492.44</v>
       </c>
       <c r="Z37" t="n">
-        <v>448.4712</v>
+        <v>450.8736</v>
       </c>
       <c r="AA37" t="n">
-        <v>429.4364</v>
+        <v>429.5215</v>
       </c>
       <c r="AB37" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC37" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10 sep</t>
+          <t>11 sep</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>40.98</v>
+        <v>41.345</v>
       </c>
       <c r="C38" t="n">
-        <v>41.77</v>
+        <v>41.715</v>
       </c>
       <c r="D38" t="n">
-        <v>40.93</v>
+        <v>40.905</v>
       </c>
       <c r="E38" t="n">
-        <v>41.23</v>
+        <v>41.415</v>
       </c>
       <c r="F38" t="n">
-        <v>38.4034</v>
+        <v>38.5608</v>
       </c>
       <c r="G38" t="n">
-        <v>35.3174</v>
+        <v>35.3717</v>
       </c>
       <c r="H38" t="n">
         <v>45.05751734733581</v>
@@ -6594,86 +6616,86 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>10 sep</t>
+          <t>11 sep</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>180</v>
+        <v>175.68</v>
       </c>
       <c r="M38" t="n">
-        <v>180.4</v>
+        <v>178.84</v>
       </c>
       <c r="N38" t="n">
-        <v>176.2</v>
+        <v>172.16</v>
       </c>
       <c r="O38" t="n">
-        <v>177.82</v>
+        <v>177.26</v>
       </c>
       <c r="P38" t="n">
-        <v>164.7724</v>
+        <v>165.5248</v>
       </c>
       <c r="Q38" t="n">
-        <v>166.0803</v>
+        <v>165.9594</v>
       </c>
       <c r="R38" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S38" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>10 sep</t>
+          <t>11 sep</t>
         </is>
       </c>
       <c r="V38" t="n">
-        <v>488.32</v>
+        <v>495.65</v>
       </c>
       <c r="W38" t="n">
-        <v>494.52</v>
+        <v>498.97</v>
       </c>
       <c r="X38" t="n">
-        <v>486</v>
+        <v>492.58</v>
       </c>
       <c r="Y38" t="n">
-        <v>492.44</v>
+        <v>495.63</v>
       </c>
       <c r="Z38" t="n">
-        <v>450.8736</v>
+        <v>453.115</v>
       </c>
       <c r="AA38" t="n">
-        <v>429.5215</v>
+        <v>429.6539</v>
       </c>
       <c r="AB38" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC38" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>11 sep</t>
+          <t>14 sep</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>41.345</v>
+        <v>41.88</v>
       </c>
       <c r="C39" t="n">
-        <v>41.715</v>
+        <v>42.285</v>
       </c>
       <c r="D39" t="n">
-        <v>40.905</v>
+        <v>41.8</v>
       </c>
       <c r="E39" t="n">
-        <v>41.415</v>
+        <v>41.91</v>
       </c>
       <c r="F39" t="n">
-        <v>38.5608</v>
+        <v>38.7226</v>
       </c>
       <c r="G39" t="n">
-        <v>35.3717</v>
+        <v>35.4269</v>
       </c>
       <c r="H39" t="n">
         <v>45.05751734733581</v>
@@ -6683,86 +6705,86 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>11 sep</t>
+          <t>14 sep</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>175.68</v>
+        <v>180.82</v>
       </c>
       <c r="M39" t="n">
-        <v>178.84</v>
+        <v>186.76</v>
       </c>
       <c r="N39" t="n">
-        <v>172.16</v>
+        <v>180.82</v>
       </c>
       <c r="O39" t="n">
-        <v>177.26</v>
+        <v>186.26</v>
       </c>
       <c r="P39" t="n">
-        <v>165.5248</v>
+        <v>166.4488</v>
       </c>
       <c r="Q39" t="n">
-        <v>165.9594</v>
+        <v>165.8745</v>
       </c>
       <c r="R39" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S39" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>11 sep</t>
+          <t>14 sep</t>
         </is>
       </c>
       <c r="V39" t="n">
-        <v>495.65</v>
+        <v>497.06</v>
       </c>
       <c r="W39" t="n">
-        <v>498.97</v>
+        <v>509.95</v>
       </c>
       <c r="X39" t="n">
-        <v>492.58</v>
+        <v>495.34</v>
       </c>
       <c r="Y39" t="n">
-        <v>495.63</v>
+        <v>505.41</v>
       </c>
       <c r="Z39" t="n">
-        <v>453.115</v>
+        <v>455.4281</v>
       </c>
       <c r="AA39" t="n">
-        <v>429.6539</v>
+        <v>429.8259</v>
       </c>
       <c r="AB39" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC39" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>14 sep</t>
+          <t>15 sep</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>41.88</v>
+        <v>41.845</v>
       </c>
       <c r="C40" t="n">
-        <v>42.285</v>
+        <v>42.7</v>
       </c>
       <c r="D40" t="n">
-        <v>41.8</v>
+        <v>41.72</v>
       </c>
       <c r="E40" t="n">
-        <v>41.91</v>
+        <v>42.7</v>
       </c>
       <c r="F40" t="n">
-        <v>38.7226</v>
+        <v>38.8782</v>
       </c>
       <c r="G40" t="n">
-        <v>35.4269</v>
+        <v>35.4854</v>
       </c>
       <c r="H40" t="n">
         <v>45.05751734733581</v>
@@ -6772,86 +6794,86 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>14 sep</t>
+          <t>15 sep</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>180.82</v>
+        <v>186.64</v>
       </c>
       <c r="M40" t="n">
-        <v>186.76</v>
+        <v>187.26</v>
       </c>
       <c r="N40" t="n">
-        <v>180.82</v>
+        <v>183.2</v>
       </c>
       <c r="O40" t="n">
-        <v>186.26</v>
+        <v>187.08</v>
       </c>
       <c r="P40" t="n">
-        <v>166.4488</v>
+        <v>167.3124</v>
       </c>
       <c r="Q40" t="n">
-        <v>165.8745</v>
+        <v>165.7921</v>
       </c>
       <c r="R40" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S40" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>14 sep</t>
+          <t>15 sep</t>
         </is>
       </c>
       <c r="V40" t="n">
-        <v>497.06</v>
+        <v>500.06</v>
       </c>
       <c r="W40" t="n">
-        <v>509.95</v>
+        <v>505.9</v>
       </c>
       <c r="X40" t="n">
-        <v>495.34</v>
+        <v>495.54</v>
       </c>
       <c r="Y40" t="n">
-        <v>505.41</v>
+        <v>497.12</v>
       </c>
       <c r="Z40" t="n">
-        <v>455.4281</v>
+        <v>457.6502</v>
       </c>
       <c r="AA40" t="n">
-        <v>429.8259</v>
+        <v>429.9416</v>
       </c>
       <c r="AB40" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC40" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>15 sep</t>
+          <t>16 sep</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>41.845</v>
+        <v>42.72</v>
       </c>
       <c r="C41" t="n">
-        <v>42.7</v>
+        <v>42.85</v>
       </c>
       <c r="D41" t="n">
-        <v>41.72</v>
+        <v>41.67</v>
       </c>
       <c r="E41" t="n">
-        <v>42.7</v>
+        <v>41.825</v>
       </c>
       <c r="F41" t="n">
-        <v>38.8782</v>
+        <v>38.9989</v>
       </c>
       <c r="G41" t="n">
-        <v>35.4854</v>
+        <v>35.5403</v>
       </c>
       <c r="H41" t="n">
         <v>45.05751734733581</v>
@@ -6861,86 +6883,86 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>15 sep</t>
+          <t>16 sep</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>186.64</v>
+        <v>185.86</v>
       </c>
       <c r="M41" t="n">
-        <v>187.26</v>
+        <v>186.76</v>
       </c>
       <c r="N41" t="n">
-        <v>183.2</v>
+        <v>182.18</v>
       </c>
       <c r="O41" t="n">
-        <v>187.08</v>
+        <v>186.56</v>
       </c>
       <c r="P41" t="n">
-        <v>167.3124</v>
+        <v>168.2844</v>
       </c>
       <c r="Q41" t="n">
-        <v>165.7921</v>
+        <v>165.6996</v>
       </c>
       <c r="R41" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S41" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>15 sep</t>
+          <t>16 sep</t>
         </is>
       </c>
       <c r="V41" t="n">
-        <v>500.06</v>
+        <v>493.03</v>
       </c>
       <c r="W41" t="n">
-        <v>505.9</v>
+        <v>495.97</v>
       </c>
       <c r="X41" t="n">
-        <v>495.54</v>
+        <v>487.23</v>
       </c>
       <c r="Y41" t="n">
-        <v>497.12</v>
+        <v>490.3</v>
       </c>
       <c r="Z41" t="n">
-        <v>457.6502</v>
+        <v>459.694</v>
       </c>
       <c r="AA41" t="n">
-        <v>429.9416</v>
+        <v>429.9809</v>
       </c>
       <c r="AB41" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC41" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>16 sep</t>
+          <t>17 sep</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>42.72</v>
+        <v>41.58</v>
       </c>
       <c r="C42" t="n">
-        <v>42.85</v>
+        <v>42.055</v>
       </c>
       <c r="D42" t="n">
-        <v>41.67</v>
+        <v>41.38</v>
       </c>
       <c r="E42" t="n">
-        <v>41.825</v>
+        <v>41.56</v>
       </c>
       <c r="F42" t="n">
-        <v>38.9989</v>
+        <v>39.1225</v>
       </c>
       <c r="G42" t="n">
-        <v>35.5403</v>
+        <v>35.5926</v>
       </c>
       <c r="H42" t="n">
         <v>45.05751734733581</v>
@@ -6950,86 +6972,86 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>16 sep</t>
+          <t>17 sep</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>185.86</v>
+        <v>188.54</v>
       </c>
       <c r="M42" t="n">
-        <v>186.76</v>
+        <v>189.2</v>
       </c>
       <c r="N42" t="n">
-        <v>182.18</v>
+        <v>184.62</v>
       </c>
       <c r="O42" t="n">
-        <v>186.56</v>
+        <v>188</v>
       </c>
       <c r="P42" t="n">
-        <v>168.2844</v>
+        <v>169.2896</v>
       </c>
       <c r="Q42" t="n">
-        <v>165.6996</v>
+        <v>165.6125</v>
       </c>
       <c r="R42" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S42" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>16 sep</t>
+          <t>17 sep</t>
         </is>
       </c>
       <c r="V42" t="n">
-        <v>493.03</v>
+        <v>497.8</v>
       </c>
       <c r="W42" t="n">
-        <v>495.97</v>
+        <v>501.47</v>
       </c>
       <c r="X42" t="n">
-        <v>487.23</v>
+        <v>493.17</v>
       </c>
       <c r="Y42" t="n">
-        <v>490.3</v>
+        <v>497.75</v>
       </c>
       <c r="Z42" t="n">
-        <v>459.694</v>
+        <v>461.9966</v>
       </c>
       <c r="AA42" t="n">
-        <v>429.9809</v>
+        <v>430.0251</v>
       </c>
       <c r="AB42" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC42" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>17 sep</t>
+          <t>18 sep</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>41.58</v>
+        <v>41.465</v>
       </c>
       <c r="C43" t="n">
-        <v>42.055</v>
+        <v>41.5</v>
       </c>
       <c r="D43" t="n">
-        <v>41.38</v>
+        <v>40.955</v>
       </c>
       <c r="E43" t="n">
-        <v>41.56</v>
+        <v>41.315</v>
       </c>
       <c r="F43" t="n">
-        <v>39.1225</v>
+        <v>39.2414</v>
       </c>
       <c r="G43" t="n">
-        <v>35.5926</v>
+        <v>35.6436</v>
       </c>
       <c r="H43" t="n">
         <v>45.05751734733581</v>
@@ -7039,86 +7061,86 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>17 sep</t>
+          <t>18 sep</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>188.54</v>
+        <v>186.1</v>
       </c>
       <c r="M43" t="n">
-        <v>189.2</v>
+        <v>187.26</v>
       </c>
       <c r="N43" t="n">
-        <v>184.62</v>
+        <v>182.56</v>
       </c>
       <c r="O43" t="n">
-        <v>188</v>
+        <v>183.12</v>
       </c>
       <c r="P43" t="n">
-        <v>169.2896</v>
+        <v>170.2004</v>
       </c>
       <c r="Q43" t="n">
-        <v>165.6125</v>
+        <v>165.5062</v>
       </c>
       <c r="R43" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S43" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>17 sep</t>
+          <t>18 sep</t>
         </is>
       </c>
       <c r="V43" t="n">
-        <v>497.8</v>
+        <v>497.97</v>
       </c>
       <c r="W43" t="n">
-        <v>501.47</v>
+        <v>498.65</v>
       </c>
       <c r="X43" t="n">
-        <v>493.17</v>
+        <v>491.1</v>
       </c>
       <c r="Y43" t="n">
-        <v>497.75</v>
+        <v>493.78</v>
       </c>
       <c r="Z43" t="n">
-        <v>461.9966</v>
+        <v>464.1995</v>
       </c>
       <c r="AA43" t="n">
-        <v>430.0251</v>
+        <v>430.0757</v>
       </c>
       <c r="AB43" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC43" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>18 sep</t>
+          <t>21 sep</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>41.465</v>
+        <v>41.04</v>
       </c>
       <c r="C44" t="n">
-        <v>41.5</v>
+        <v>41.4</v>
       </c>
       <c r="D44" t="n">
-        <v>40.955</v>
+        <v>40.775</v>
       </c>
       <c r="E44" t="n">
-        <v>41.315</v>
+        <v>40.775</v>
       </c>
       <c r="F44" t="n">
-        <v>39.2414</v>
+        <v>39.3341</v>
       </c>
       <c r="G44" t="n">
-        <v>35.6436</v>
+        <v>35.6939</v>
       </c>
       <c r="H44" t="n">
         <v>45.05751734733581</v>
@@ -7128,86 +7150,86 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>18 sep</t>
+          <t>21 sep</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>186.1</v>
+        <v>184.7</v>
       </c>
       <c r="M44" t="n">
-        <v>187.26</v>
+        <v>185.86</v>
       </c>
       <c r="N44" t="n">
-        <v>182.56</v>
+        <v>182.48</v>
       </c>
       <c r="O44" t="n">
-        <v>183.12</v>
+        <v>182.86</v>
       </c>
       <c r="P44" t="n">
-        <v>170.2004</v>
+        <v>171.0432</v>
       </c>
       <c r="Q44" t="n">
-        <v>165.5062</v>
+        <v>165.4052</v>
       </c>
       <c r="R44" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S44" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>18 sep</t>
+          <t>21 sep</t>
         </is>
       </c>
       <c r="V44" t="n">
-        <v>497.97</v>
+        <v>494.95</v>
       </c>
       <c r="W44" t="n">
-        <v>498.65</v>
+        <v>501.87</v>
       </c>
       <c r="X44" t="n">
-        <v>491.1</v>
+        <v>491.33</v>
       </c>
       <c r="Y44" t="n">
-        <v>493.78</v>
+        <v>501.61</v>
       </c>
       <c r="Z44" t="n">
-        <v>464.1995</v>
+        <v>466.5442</v>
       </c>
       <c r="AA44" t="n">
-        <v>430.0757</v>
+        <v>430.1492</v>
       </c>
       <c r="AB44" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC44" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>21 sep</t>
+          <t>22 sep</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>41.04</v>
+        <v>40.84</v>
       </c>
       <c r="C45" t="n">
-        <v>41.4</v>
+        <v>41.165</v>
       </c>
       <c r="D45" t="n">
-        <v>40.775</v>
+        <v>40.215</v>
       </c>
       <c r="E45" t="n">
-        <v>40.775</v>
+        <v>41.01</v>
       </c>
       <c r="F45" t="n">
-        <v>39.3341</v>
+        <v>39.4244</v>
       </c>
       <c r="G45" t="n">
-        <v>35.6939</v>
+        <v>35.746</v>
       </c>
       <c r="H45" t="n">
         <v>45.05751734733581</v>
@@ -7217,86 +7239,86 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>21 sep</t>
+          <t>22 sep</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>184.7</v>
+        <v>182.14</v>
       </c>
       <c r="M45" t="n">
-        <v>185.86</v>
+        <v>187.48</v>
       </c>
       <c r="N45" t="n">
-        <v>182.48</v>
+        <v>181.52</v>
       </c>
       <c r="O45" t="n">
-        <v>182.86</v>
+        <v>182.32</v>
       </c>
       <c r="P45" t="n">
-        <v>171.0432</v>
+        <v>171.9552</v>
       </c>
       <c r="Q45" t="n">
-        <v>165.4052</v>
+        <v>165.2836</v>
       </c>
       <c r="R45" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S45" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>21 sep</t>
+          <t>22 sep</t>
         </is>
       </c>
       <c r="V45" t="n">
-        <v>494.95</v>
+        <v>507.32</v>
       </c>
       <c r="W45" t="n">
-        <v>501.87</v>
+        <v>508.5</v>
       </c>
       <c r="X45" t="n">
-        <v>491.33</v>
+        <v>493.65</v>
       </c>
       <c r="Y45" t="n">
-        <v>501.61</v>
+        <v>498</v>
       </c>
       <c r="Z45" t="n">
-        <v>466.5442</v>
+        <v>468.699</v>
       </c>
       <c r="AA45" t="n">
-        <v>430.1492</v>
+        <v>430.2656</v>
       </c>
       <c r="AB45" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC45" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>22 sep</t>
+          <t>23 sep</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>40.84</v>
+        <v>41</v>
       </c>
       <c r="C46" t="n">
-        <v>41.165</v>
+        <v>41.755</v>
       </c>
       <c r="D46" t="n">
-        <v>40.215</v>
+        <v>40.995</v>
       </c>
       <c r="E46" t="n">
-        <v>41.01</v>
+        <v>41.69</v>
       </c>
       <c r="F46" t="n">
-        <v>39.4244</v>
+        <v>39.5272</v>
       </c>
       <c r="G46" t="n">
-        <v>35.746</v>
+        <v>35.8024</v>
       </c>
       <c r="H46" t="n">
         <v>45.05751734733581</v>
@@ -7306,86 +7328,86 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>22 sep</t>
+          <t>23 sep</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>182.14</v>
+        <v>184.9</v>
       </c>
       <c r="M46" t="n">
-        <v>187.48</v>
+        <v>187.8</v>
       </c>
       <c r="N46" t="n">
-        <v>181.52</v>
+        <v>183.48</v>
       </c>
       <c r="O46" t="n">
-        <v>182.32</v>
+        <v>186.46</v>
       </c>
       <c r="P46" t="n">
-        <v>171.9552</v>
+        <v>172.9448</v>
       </c>
       <c r="Q46" t="n">
-        <v>165.2836</v>
+        <v>165.1675</v>
       </c>
       <c r="R46" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S46" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>22 sep</t>
+          <t>23 sep</t>
         </is>
       </c>
       <c r="V46" t="n">
-        <v>507.32</v>
+        <v>500.76</v>
       </c>
       <c r="W46" t="n">
-        <v>508.5</v>
+        <v>509.44</v>
       </c>
       <c r="X46" t="n">
-        <v>493.65</v>
+        <v>495.88</v>
       </c>
       <c r="Y46" t="n">
-        <v>498</v>
+        <v>500.59</v>
       </c>
       <c r="Z46" t="n">
-        <v>468.699</v>
+        <v>471.0267</v>
       </c>
       <c r="AA46" t="n">
-        <v>430.2656</v>
+        <v>430.3795</v>
       </c>
       <c r="AB46" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC46" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>23 sep</t>
+          <t>24 sep</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>41</v>
+        <v>41.825</v>
       </c>
       <c r="C47" t="n">
-        <v>41.755</v>
+        <v>42.52</v>
       </c>
       <c r="D47" t="n">
-        <v>40.995</v>
+        <v>41.78</v>
       </c>
       <c r="E47" t="n">
-        <v>41.69</v>
+        <v>42.43</v>
       </c>
       <c r="F47" t="n">
-        <v>39.5272</v>
+        <v>39.6382</v>
       </c>
       <c r="G47" t="n">
-        <v>35.8024</v>
+        <v>35.8638</v>
       </c>
       <c r="H47" t="n">
         <v>45.05751734733581</v>
@@ -7395,86 +7417,86 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>23 sep</t>
+          <t>24 sep</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>184.9</v>
+        <v>184.52</v>
       </c>
       <c r="M47" t="n">
-        <v>187.8</v>
+        <v>185.5</v>
       </c>
       <c r="N47" t="n">
-        <v>183.48</v>
+        <v>182.26</v>
       </c>
       <c r="O47" t="n">
-        <v>186.46</v>
+        <v>184.18</v>
       </c>
       <c r="P47" t="n">
-        <v>172.9448</v>
+        <v>173.8756</v>
       </c>
       <c r="Q47" t="n">
-        <v>165.1675</v>
+        <v>165.0554</v>
       </c>
       <c r="R47" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S47" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>23 sep</t>
+          <t>24 sep</t>
         </is>
       </c>
       <c r="V47" t="n">
-        <v>500.76</v>
+        <v>495.07</v>
       </c>
       <c r="W47" t="n">
-        <v>509.44</v>
+        <v>498.9</v>
       </c>
       <c r="X47" t="n">
-        <v>495.88</v>
+        <v>491.22</v>
       </c>
       <c r="Y47" t="n">
-        <v>500.59</v>
+        <v>497.93</v>
       </c>
       <c r="Z47" t="n">
-        <v>471.0267</v>
+        <v>473.0876</v>
       </c>
       <c r="AA47" t="n">
-        <v>430.3795</v>
+        <v>430.4686</v>
       </c>
       <c r="AB47" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC47" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>24 sep</t>
+          <t>25 sep</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>41.825</v>
+        <v>41.99</v>
       </c>
       <c r="C48" t="n">
-        <v>42.52</v>
+        <v>42.33</v>
       </c>
       <c r="D48" t="n">
-        <v>41.78</v>
+        <v>41.71</v>
       </c>
       <c r="E48" t="n">
-        <v>42.43</v>
+        <v>42.06</v>
       </c>
       <c r="F48" t="n">
-        <v>39.6382</v>
+        <v>39.7263</v>
       </c>
       <c r="G48" t="n">
-        <v>35.8638</v>
+        <v>35.9239</v>
       </c>
       <c r="H48" t="n">
         <v>45.05751734733581</v>
@@ -7484,86 +7506,86 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>24 sep</t>
+          <t>25 sep</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>184.52</v>
+        <v>184.42</v>
       </c>
       <c r="M48" t="n">
-        <v>185.5</v>
+        <v>185.92</v>
       </c>
       <c r="N48" t="n">
-        <v>182.26</v>
+        <v>183.76</v>
       </c>
       <c r="O48" t="n">
-        <v>184.18</v>
+        <v>185.92</v>
       </c>
       <c r="P48" t="n">
-        <v>173.8756</v>
+        <v>174.8356</v>
       </c>
       <c r="Q48" t="n">
-        <v>165.0554</v>
+        <v>164.9525</v>
       </c>
       <c r="R48" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S48" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>24 sep</t>
+          <t>25 sep</t>
         </is>
       </c>
       <c r="V48" t="n">
-        <v>495.07</v>
+        <v>499.04</v>
       </c>
       <c r="W48" t="n">
-        <v>498.9</v>
+        <v>519.4</v>
       </c>
       <c r="X48" t="n">
-        <v>491.22</v>
+        <v>497.25</v>
       </c>
       <c r="Y48" t="n">
-        <v>497.93</v>
+        <v>516.17</v>
       </c>
       <c r="Z48" t="n">
-        <v>473.0876</v>
+        <v>475.4041</v>
       </c>
       <c r="AA48" t="n">
-        <v>430.4686</v>
+        <v>430.6098</v>
       </c>
       <c r="AB48" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC48" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>25 sep</t>
+          <t>28 sep</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>41.99</v>
+        <v>42.45</v>
       </c>
       <c r="C49" t="n">
-        <v>42.33</v>
+        <v>42.995</v>
       </c>
       <c r="D49" t="n">
-        <v>41.71</v>
+        <v>42.38</v>
       </c>
       <c r="E49" t="n">
-        <v>42.06</v>
+        <v>42.725</v>
       </c>
       <c r="F49" t="n">
-        <v>39.7263</v>
+        <v>39.8301</v>
       </c>
       <c r="G49" t="n">
-        <v>35.9239</v>
+        <v>35.9888</v>
       </c>
       <c r="H49" t="n">
         <v>45.05751734733581</v>
@@ -7573,86 +7595,86 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>25 sep</t>
+          <t>28 sep</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>184.42</v>
+        <v>185.2</v>
       </c>
       <c r="M49" t="n">
-        <v>185.92</v>
+        <v>186.76</v>
       </c>
       <c r="N49" t="n">
-        <v>183.76</v>
+        <v>178.88</v>
       </c>
       <c r="O49" t="n">
-        <v>185.92</v>
+        <v>184.02</v>
       </c>
       <c r="P49" t="n">
-        <v>174.8356</v>
+        <v>175.7508</v>
       </c>
       <c r="Q49" t="n">
-        <v>164.9525</v>
+        <v>164.8355</v>
       </c>
       <c r="R49" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S49" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>25 sep</t>
+          <t>28 sep</t>
         </is>
       </c>
       <c r="V49" t="n">
-        <v>499.04</v>
+        <v>505.47</v>
       </c>
       <c r="W49" t="n">
-        <v>519.4</v>
+        <v>513.33</v>
       </c>
       <c r="X49" t="n">
-        <v>497.25</v>
+        <v>502.22</v>
       </c>
       <c r="Y49" t="n">
-        <v>516.17</v>
+        <v>509.22</v>
       </c>
       <c r="Z49" t="n">
-        <v>475.4041</v>
+        <v>477.7269</v>
       </c>
       <c r="AA49" t="n">
-        <v>430.6098</v>
+        <v>430.7113</v>
       </c>
       <c r="AB49" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC49" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>28 sep</t>
+          <t>29 sep</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>42.45</v>
+        <v>42.57</v>
       </c>
       <c r="C50" t="n">
-        <v>42.995</v>
+        <v>42.665</v>
       </c>
       <c r="D50" t="n">
-        <v>42.38</v>
+        <v>41.73</v>
       </c>
       <c r="E50" t="n">
-        <v>42.725</v>
+        <v>42.05</v>
       </c>
       <c r="F50" t="n">
-        <v>39.8301</v>
+        <v>39.9146</v>
       </c>
       <c r="G50" t="n">
-        <v>35.9888</v>
+        <v>36.0498</v>
       </c>
       <c r="H50" t="n">
         <v>45.05751734733581</v>
@@ -7662,86 +7684,86 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>28 sep</t>
+          <t>29 sep</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>185.2</v>
+        <v>183.22</v>
       </c>
       <c r="M50" t="n">
-        <v>186.76</v>
+        <v>186.34</v>
       </c>
       <c r="N50" t="n">
-        <v>178.88</v>
+        <v>182.28</v>
       </c>
       <c r="O50" t="n">
-        <v>184.02</v>
+        <v>185.32</v>
       </c>
       <c r="P50" t="n">
-        <v>175.7508</v>
+        <v>176.7288</v>
       </c>
       <c r="Q50" t="n">
-        <v>164.8355</v>
+        <v>164.733</v>
       </c>
       <c r="R50" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S50" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>28 sep</t>
+          <t>29 sep</t>
         </is>
       </c>
       <c r="V50" t="n">
-        <v>505.47</v>
+        <v>508.31</v>
       </c>
       <c r="W50" t="n">
-        <v>513.33</v>
+        <v>513.64</v>
       </c>
       <c r="X50" t="n">
-        <v>502.22</v>
+        <v>502.4</v>
       </c>
       <c r="Y50" t="n">
-        <v>509.22</v>
+        <v>508.96</v>
       </c>
       <c r="Z50" t="n">
-        <v>477.7269</v>
+        <v>479.8754</v>
       </c>
       <c r="AA50" t="n">
-        <v>430.7113</v>
+        <v>430.8784</v>
       </c>
       <c r="AB50" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC50" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>29 sep</t>
+          <t>30 sep</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>42.57</v>
+        <v>41.975</v>
       </c>
       <c r="C51" t="n">
-        <v>42.665</v>
+        <v>42.095</v>
       </c>
       <c r="D51" t="n">
-        <v>41.73</v>
+        <v>41.58</v>
       </c>
       <c r="E51" t="n">
-        <v>42.05</v>
+        <v>41.91</v>
       </c>
       <c r="F51" t="n">
-        <v>39.9146</v>
+        <v>39.9874</v>
       </c>
       <c r="G51" t="n">
-        <v>36.0498</v>
+        <v>36.1135</v>
       </c>
       <c r="H51" t="n">
         <v>45.05751734733581</v>
@@ -7751,86 +7773,86 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>29 sep</t>
+          <t>30 sep</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>183.22</v>
+        <v>184.5</v>
       </c>
       <c r="M51" t="n">
-        <v>186.34</v>
+        <v>186.2</v>
       </c>
       <c r="N51" t="n">
-        <v>182.28</v>
+        <v>181.06</v>
       </c>
       <c r="O51" t="n">
-        <v>185.32</v>
+        <v>185.66</v>
       </c>
       <c r="P51" t="n">
-        <v>176.7288</v>
+        <v>177.8012</v>
       </c>
       <c r="Q51" t="n">
-        <v>164.733</v>
+        <v>164.6377</v>
       </c>
       <c r="R51" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S51" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>29 sep</t>
+          <t>30 sep</t>
         </is>
       </c>
       <c r="V51" t="n">
-        <v>508.31</v>
+        <v>511.61</v>
       </c>
       <c r="W51" t="n">
-        <v>513.64</v>
+        <v>519.83</v>
       </c>
       <c r="X51" t="n">
-        <v>502.4</v>
+        <v>510.31</v>
       </c>
       <c r="Y51" t="n">
-        <v>508.96</v>
+        <v>512.9</v>
       </c>
       <c r="Z51" t="n">
-        <v>479.8754</v>
+        <v>482.1933</v>
       </c>
       <c r="AA51" t="n">
-        <v>430.8784</v>
+        <v>431.0408</v>
       </c>
       <c r="AB51" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC51" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>30 sep</t>
+          <t>1 okt</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>41.975</v>
+        <v>41.625</v>
       </c>
       <c r="C52" t="n">
-        <v>42.095</v>
+        <v>42.36</v>
       </c>
       <c r="D52" t="n">
-        <v>41.58</v>
+        <v>41.165</v>
       </c>
       <c r="E52" t="n">
-        <v>41.91</v>
+        <v>42.24</v>
       </c>
       <c r="F52" t="n">
-        <v>39.9874</v>
+        <v>40.0562</v>
       </c>
       <c r="G52" t="n">
-        <v>36.1135</v>
+        <v>36.1777</v>
       </c>
       <c r="H52" t="n">
         <v>45.05751734733581</v>
@@ -7840,86 +7862,86 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>30 sep</t>
+          <t>1 okt</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>184.5</v>
+        <v>184.68</v>
       </c>
       <c r="M52" t="n">
-        <v>186.2</v>
+        <v>190.26</v>
       </c>
       <c r="N52" t="n">
-        <v>181.06</v>
+        <v>181.34</v>
       </c>
       <c r="O52" t="n">
-        <v>185.66</v>
+        <v>186.74</v>
       </c>
       <c r="P52" t="n">
-        <v>177.8012</v>
+        <v>178.9696</v>
       </c>
       <c r="Q52" t="n">
-        <v>164.6377</v>
+        <v>164.5407</v>
       </c>
       <c r="R52" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S52" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>30 sep</t>
+          <t>1 okt</t>
         </is>
       </c>
       <c r="V52" t="n">
-        <v>511.61</v>
+        <v>519.88</v>
       </c>
       <c r="W52" t="n">
-        <v>519.83</v>
+        <v>522.85</v>
       </c>
       <c r="X52" t="n">
-        <v>510.31</v>
+        <v>512.17</v>
       </c>
       <c r="Y52" t="n">
-        <v>512.9</v>
+        <v>512.8</v>
       </c>
       <c r="Z52" t="n">
-        <v>482.1933</v>
+        <v>484.6572</v>
       </c>
       <c r="AA52" t="n">
-        <v>431.0408</v>
+        <v>431.2272</v>
       </c>
       <c r="AB52" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC52" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1 okt</t>
+          <t>2 okt</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>41.625</v>
+        <v>42.11</v>
       </c>
       <c r="C53" t="n">
-        <v>42.36</v>
+        <v>42.745</v>
       </c>
       <c r="D53" t="n">
-        <v>41.165</v>
+        <v>41.985</v>
       </c>
       <c r="E53" t="n">
-        <v>42.24</v>
+        <v>42.4</v>
       </c>
       <c r="F53" t="n">
-        <v>40.0562</v>
+        <v>40.1364</v>
       </c>
       <c r="G53" t="n">
-        <v>36.1777</v>
+        <v>36.2422</v>
       </c>
       <c r="H53" t="n">
         <v>45.05751734733581</v>
@@ -7929,86 +7951,86 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>1 okt</t>
+          <t>2 okt</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>184.68</v>
+        <v>187.82</v>
       </c>
       <c r="M53" t="n">
-        <v>190.26</v>
+        <v>188.74</v>
       </c>
       <c r="N53" t="n">
-        <v>181.34</v>
+        <v>183.92</v>
       </c>
       <c r="O53" t="n">
-        <v>186.74</v>
+        <v>183.92</v>
       </c>
       <c r="P53" t="n">
-        <v>178.9696</v>
+        <v>179.844</v>
       </c>
       <c r="Q53" t="n">
-        <v>164.5407</v>
+        <v>164.4442</v>
       </c>
       <c r="R53" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S53" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>1 okt</t>
+          <t>2 okt</t>
         </is>
       </c>
       <c r="V53" t="n">
-        <v>519.88</v>
+        <v>519.39</v>
       </c>
       <c r="W53" t="n">
-        <v>522.85</v>
+        <v>522.5</v>
       </c>
       <c r="X53" t="n">
-        <v>512.17</v>
+        <v>513.66</v>
       </c>
       <c r="Y53" t="n">
-        <v>512.8</v>
+        <v>517.53</v>
       </c>
       <c r="Z53" t="n">
-        <v>484.6572</v>
+        <v>487.3905</v>
       </c>
       <c r="AA53" t="n">
-        <v>431.2272</v>
+        <v>431.4557</v>
       </c>
       <c r="AB53" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC53" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2 okt</t>
+          <t>5 okt</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>42.11</v>
+        <v>42.645</v>
       </c>
       <c r="C54" t="n">
-        <v>42.745</v>
+        <v>43.11</v>
       </c>
       <c r="D54" t="n">
-        <v>41.985</v>
+        <v>42.35</v>
       </c>
       <c r="E54" t="n">
-        <v>42.4</v>
+        <v>42.865</v>
       </c>
       <c r="F54" t="n">
-        <v>40.1364</v>
+        <v>40.2347</v>
       </c>
       <c r="G54" t="n">
-        <v>36.2422</v>
+        <v>36.3069</v>
       </c>
       <c r="H54" t="n">
         <v>45.05751734733581</v>
@@ -8018,86 +8040,86 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2 okt</t>
+          <t>5 okt</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>187.82</v>
+        <v>185.06</v>
       </c>
       <c r="M54" t="n">
-        <v>188.74</v>
+        <v>188.5</v>
       </c>
       <c r="N54" t="n">
-        <v>183.92</v>
+        <v>184.66</v>
       </c>
       <c r="O54" t="n">
-        <v>183.92</v>
+        <v>185.04</v>
       </c>
       <c r="P54" t="n">
-        <v>179.844</v>
+        <v>180.5192</v>
       </c>
       <c r="Q54" t="n">
-        <v>164.4442</v>
+        <v>164.3515</v>
       </c>
       <c r="R54" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S54" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>2 okt</t>
+          <t>5 okt</t>
         </is>
       </c>
       <c r="V54" t="n">
-        <v>519.39</v>
+        <v>521.62</v>
       </c>
       <c r="W54" t="n">
-        <v>522.5</v>
+        <v>532.35</v>
       </c>
       <c r="X54" t="n">
-        <v>513.66</v>
+        <v>521.47</v>
       </c>
       <c r="Y54" t="n">
-        <v>517.53</v>
+        <v>525.1799999999999</v>
       </c>
       <c r="Z54" t="n">
-        <v>487.3905</v>
+        <v>490.2745</v>
       </c>
       <c r="AA54" t="n">
-        <v>431.4557</v>
+        <v>431.7147</v>
       </c>
       <c r="AB54" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC54" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>5 okt</t>
+          <t>6 okt</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>42.645</v>
+        <v>42.86</v>
       </c>
       <c r="C55" t="n">
-        <v>43.11</v>
+        <v>43.285</v>
       </c>
       <c r="D55" t="n">
-        <v>42.35</v>
+        <v>42.43</v>
       </c>
       <c r="E55" t="n">
-        <v>42.865</v>
+        <v>43.185</v>
       </c>
       <c r="F55" t="n">
-        <v>40.2347</v>
+        <v>40.349</v>
       </c>
       <c r="G55" t="n">
-        <v>36.3069</v>
+        <v>36.3726</v>
       </c>
       <c r="H55" t="n">
         <v>45.05751734733581</v>
@@ -8107,86 +8129,86 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>5 okt</t>
+          <t>6 okt</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>185.06</v>
+        <v>186.56</v>
       </c>
       <c r="M55" t="n">
-        <v>188.5</v>
+        <v>190.22</v>
       </c>
       <c r="N55" t="n">
-        <v>184.66</v>
+        <v>186.06</v>
       </c>
       <c r="O55" t="n">
-        <v>185.04</v>
+        <v>188.6</v>
       </c>
       <c r="P55" t="n">
-        <v>180.5192</v>
+        <v>181.1064</v>
       </c>
       <c r="Q55" t="n">
-        <v>164.3515</v>
+        <v>164.2647</v>
       </c>
       <c r="R55" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S55" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>5 okt</t>
+          <t>6 okt</t>
         </is>
       </c>
       <c r="V55" t="n">
-        <v>521.62</v>
+        <v>531.6799999999999</v>
       </c>
       <c r="W55" t="n">
-        <v>532.35</v>
+        <v>535.6900000000001</v>
       </c>
       <c r="X55" t="n">
-        <v>521.47</v>
+        <v>528.78</v>
       </c>
       <c r="Y55" t="n">
-        <v>525.1799999999999</v>
+        <v>529.3</v>
       </c>
       <c r="Z55" t="n">
-        <v>490.2745</v>
+        <v>493.0931</v>
       </c>
       <c r="AA55" t="n">
-        <v>431.7147</v>
+        <v>431.9956</v>
       </c>
       <c r="AB55" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC55" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>6 okt</t>
+          <t>7 okt</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>42.86</v>
+        <v>43.37</v>
       </c>
       <c r="C56" t="n">
-        <v>43.285</v>
+        <v>43.835</v>
       </c>
       <c r="D56" t="n">
-        <v>42.43</v>
+        <v>43.145</v>
       </c>
       <c r="E56" t="n">
-        <v>43.185</v>
+        <v>43.25</v>
       </c>
       <c r="F56" t="n">
-        <v>40.349</v>
+        <v>40.4451</v>
       </c>
       <c r="G56" t="n">
-        <v>36.3726</v>
+        <v>36.4388</v>
       </c>
       <c r="H56" t="n">
         <v>45.05751734733581</v>
@@ -8196,86 +8218,86 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>6 okt</t>
+          <t>7 okt</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>186.56</v>
+        <v>187</v>
       </c>
       <c r="M56" t="n">
-        <v>190.22</v>
+        <v>188.72</v>
       </c>
       <c r="N56" t="n">
-        <v>186.06</v>
+        <v>186.04</v>
       </c>
       <c r="O56" t="n">
-        <v>188.6</v>
+        <v>187.62</v>
       </c>
       <c r="P56" t="n">
-        <v>181.1064</v>
+        <v>181.618</v>
       </c>
       <c r="Q56" t="n">
-        <v>164.2647</v>
+        <v>164.1762</v>
       </c>
       <c r="R56" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S56" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>6 okt</t>
+          <t>7 okt</t>
         </is>
       </c>
       <c r="V56" t="n">
-        <v>531.6799999999999</v>
+        <v>530.73</v>
       </c>
       <c r="W56" t="n">
-        <v>535.6900000000001</v>
+        <v>531.73</v>
       </c>
       <c r="X56" t="n">
-        <v>528.78</v>
+        <v>524.6900000000001</v>
       </c>
       <c r="Y56" t="n">
-        <v>529.3</v>
+        <v>529.76</v>
       </c>
       <c r="Z56" t="n">
-        <v>493.0931</v>
+        <v>495.8361</v>
       </c>
       <c r="AA56" t="n">
-        <v>431.9956</v>
+        <v>432.2398</v>
       </c>
       <c r="AB56" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC56" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>7 okt</t>
+          <t>8 okt</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>43.37</v>
+        <v>43.555</v>
       </c>
       <c r="C57" t="n">
-        <v>43.835</v>
+        <v>44.815</v>
       </c>
       <c r="D57" t="n">
-        <v>43.145</v>
+        <v>43.5425</v>
       </c>
       <c r="E57" t="n">
-        <v>43.25</v>
+        <v>44.75</v>
       </c>
       <c r="F57" t="n">
-        <v>40.4451</v>
+        <v>40.5699</v>
       </c>
       <c r="G57" t="n">
-        <v>36.4388</v>
+        <v>36.5123</v>
       </c>
       <c r="H57" t="n">
         <v>45.05751734733581</v>
@@ -8285,86 +8307,86 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>7 okt</t>
+          <t>8 okt</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>187</v>
+        <v>187.04</v>
       </c>
       <c r="M57" t="n">
-        <v>188.72</v>
+        <v>189.82</v>
       </c>
       <c r="N57" t="n">
-        <v>186.04</v>
+        <v>183.76</v>
       </c>
       <c r="O57" t="n">
-        <v>187.62</v>
+        <v>184.62</v>
       </c>
       <c r="P57" t="n">
-        <v>181.618</v>
+        <v>182.192</v>
       </c>
       <c r="Q57" t="n">
-        <v>164.1762</v>
+        <v>164.074</v>
       </c>
       <c r="R57" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S57" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>7 okt</t>
+          <t>8 okt</t>
         </is>
       </c>
       <c r="V57" t="n">
-        <v>530.73</v>
+        <v>529.8099999999999</v>
       </c>
       <c r="W57" t="n">
-        <v>531.73</v>
+        <v>533.51</v>
       </c>
       <c r="X57" t="n">
-        <v>524.6900000000001</v>
+        <v>518.79</v>
       </c>
       <c r="Y57" t="n">
-        <v>529.76</v>
+        <v>522.61</v>
       </c>
       <c r="Z57" t="n">
-        <v>495.8361</v>
+        <v>498.4921</v>
       </c>
       <c r="AA57" t="n">
-        <v>432.2398</v>
+        <v>432.4385</v>
       </c>
       <c r="AB57" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC57" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>8 okt</t>
+          <t>9 okt</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>43.555</v>
+        <v>44.42</v>
       </c>
       <c r="C58" t="n">
-        <v>44.815</v>
+        <v>45.155</v>
       </c>
       <c r="D58" t="n">
-        <v>43.5425</v>
+        <v>43.94</v>
       </c>
       <c r="E58" t="n">
-        <v>44.75</v>
+        <v>45.035</v>
       </c>
       <c r="F58" t="n">
-        <v>40.5699</v>
+        <v>40.6842</v>
       </c>
       <c r="G58" t="n">
-        <v>36.5123</v>
+        <v>36.5866</v>
       </c>
       <c r="H58" t="n">
         <v>45.05751734733581</v>
@@ -8374,86 +8396,86 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>8 okt</t>
+          <t>9 okt</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>187.04</v>
+        <v>188.98</v>
       </c>
       <c r="M58" t="n">
-        <v>189.82</v>
+        <v>192.58</v>
       </c>
       <c r="N58" t="n">
-        <v>183.76</v>
+        <v>188.86</v>
       </c>
       <c r="O58" t="n">
-        <v>184.62</v>
+        <v>191.46</v>
       </c>
       <c r="P58" t="n">
-        <v>182.192</v>
+        <v>182.8676</v>
       </c>
       <c r="Q58" t="n">
-        <v>164.074</v>
+        <v>164.0101</v>
       </c>
       <c r="R58" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S58" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>8 okt</t>
+          <t>9 okt</t>
         </is>
       </c>
       <c r="V58" t="n">
-        <v>529.8099999999999</v>
+        <v>528.24</v>
       </c>
       <c r="W58" t="n">
-        <v>533.51</v>
+        <v>537.22</v>
       </c>
       <c r="X58" t="n">
-        <v>518.79</v>
+        <v>526.24</v>
       </c>
       <c r="Y58" t="n">
-        <v>522.61</v>
+        <v>535.0700000000001</v>
       </c>
       <c r="Z58" t="n">
-        <v>498.4921</v>
+        <v>500.1885</v>
       </c>
       <c r="AA58" t="n">
-        <v>432.4385</v>
+        <v>432.7046</v>
       </c>
       <c r="AB58" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC58" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>9 okt</t>
+          <t>12 okt</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>44.42</v>
+        <v>44.725</v>
       </c>
       <c r="C59" t="n">
-        <v>45.155</v>
+        <v>45.81</v>
       </c>
       <c r="D59" t="n">
-        <v>43.94</v>
+        <v>44.695</v>
       </c>
       <c r="E59" t="n">
-        <v>45.035</v>
+        <v>45.56</v>
       </c>
       <c r="F59" t="n">
-        <v>40.6842</v>
+        <v>40.8072</v>
       </c>
       <c r="G59" t="n">
-        <v>36.5866</v>
+        <v>36.6625</v>
       </c>
       <c r="H59" t="n">
         <v>45.05751734733581</v>
@@ -8463,86 +8485,86 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>9 okt</t>
+          <t>12 okt</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>188.98</v>
+        <v>190.58</v>
       </c>
       <c r="M59" t="n">
-        <v>192.58</v>
+        <v>197.88</v>
       </c>
       <c r="N59" t="n">
-        <v>188.86</v>
+        <v>189.78</v>
       </c>
       <c r="O59" t="n">
-        <v>191.46</v>
+        <v>194.46</v>
       </c>
       <c r="P59" t="n">
-        <v>182.8676</v>
+        <v>183.464</v>
       </c>
       <c r="Q59" t="n">
-        <v>164.0101</v>
+        <v>163.9576</v>
       </c>
       <c r="R59" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S59" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>9 okt</t>
+          <t>12 okt</t>
         </is>
       </c>
       <c r="V59" t="n">
-        <v>528.24</v>
+        <v>537.53</v>
       </c>
       <c r="W59" t="n">
-        <v>537.22</v>
+        <v>542.74</v>
       </c>
       <c r="X59" t="n">
-        <v>526.24</v>
+        <v>535.7</v>
       </c>
       <c r="Y59" t="n">
-        <v>535.0700000000001</v>
+        <v>541.15</v>
       </c>
       <c r="Z59" t="n">
-        <v>500.1885</v>
+        <v>501.7346</v>
       </c>
       <c r="AA59" t="n">
-        <v>432.7046</v>
+        <v>432.9914</v>
       </c>
       <c r="AB59" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC59" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>12 okt</t>
+          <t>13 okt</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>44.725</v>
+        <v>45.69</v>
       </c>
       <c r="C60" t="n">
-        <v>45.81</v>
+        <v>45.97</v>
       </c>
       <c r="D60" t="n">
-        <v>44.695</v>
+        <v>45.35</v>
       </c>
       <c r="E60" t="n">
-        <v>45.56</v>
+        <v>45.95</v>
       </c>
       <c r="F60" t="n">
-        <v>40.8072</v>
+        <v>40.9565</v>
       </c>
       <c r="G60" t="n">
-        <v>36.6625</v>
+        <v>36.7398</v>
       </c>
       <c r="H60" t="n">
         <v>45.05751734733581</v>
@@ -8552,86 +8574,86 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>12 okt</t>
+          <t>13 okt</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>190.58</v>
+        <v>196</v>
       </c>
       <c r="M60" t="n">
-        <v>197.88</v>
+        <v>198.18</v>
       </c>
       <c r="N60" t="n">
-        <v>189.78</v>
+        <v>194.02</v>
       </c>
       <c r="O60" t="n">
-        <v>194.46</v>
+        <v>197.28</v>
       </c>
       <c r="P60" t="n">
-        <v>183.464</v>
+        <v>184.062</v>
       </c>
       <c r="Q60" t="n">
-        <v>163.9576</v>
+        <v>163.9196</v>
       </c>
       <c r="R60" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S60" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>12 okt</t>
+          <t>13 okt</t>
         </is>
       </c>
       <c r="V60" t="n">
-        <v>537.53</v>
+        <v>544.64</v>
       </c>
       <c r="W60" t="n">
-        <v>542.74</v>
+        <v>551.15</v>
       </c>
       <c r="X60" t="n">
-        <v>535.7</v>
+        <v>543.0599999999999</v>
       </c>
       <c r="Y60" t="n">
-        <v>541.15</v>
+        <v>543.45</v>
       </c>
       <c r="Z60" t="n">
-        <v>501.7346</v>
+        <v>502.8689</v>
       </c>
       <c r="AA60" t="n">
-        <v>432.9914</v>
+        <v>433.2839</v>
       </c>
       <c r="AB60" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC60" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>13 okt</t>
+          <t>14 okt</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>45.69</v>
+        <v>45.95</v>
       </c>
       <c r="C61" t="n">
-        <v>45.97</v>
+        <v>46.675</v>
       </c>
       <c r="D61" t="n">
-        <v>45.35</v>
+        <v>45.91</v>
       </c>
       <c r="E61" t="n">
-        <v>45.95</v>
+        <v>46.455</v>
       </c>
       <c r="F61" t="n">
-        <v>40.9565</v>
+        <v>41.125</v>
       </c>
       <c r="G61" t="n">
-        <v>36.7398</v>
+        <v>36.8183</v>
       </c>
       <c r="H61" t="n">
         <v>45.05751734733581</v>
@@ -8641,86 +8663,86 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>13 okt</t>
+          <t>14 okt</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>196</v>
+        <v>196.6</v>
       </c>
       <c r="M61" t="n">
-        <v>198.18</v>
+        <v>199.36</v>
       </c>
       <c r="N61" t="n">
-        <v>194.02</v>
+        <v>195.26</v>
       </c>
       <c r="O61" t="n">
-        <v>197.28</v>
+        <v>196.94</v>
       </c>
       <c r="P61" t="n">
-        <v>184.062</v>
+        <v>184.6156</v>
       </c>
       <c r="Q61" t="n">
-        <v>163.9196</v>
+        <v>163.9114</v>
       </c>
       <c r="R61" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S61" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>13 okt</t>
+          <t>14 okt</t>
         </is>
       </c>
       <c r="V61" t="n">
-        <v>544.64</v>
+        <v>545.27</v>
       </c>
       <c r="W61" t="n">
-        <v>551.15</v>
+        <v>545.75</v>
       </c>
       <c r="X61" t="n">
-        <v>543.0599999999999</v>
+        <v>532.54</v>
       </c>
       <c r="Y61" t="n">
-        <v>543.45</v>
+        <v>533.6900000000001</v>
       </c>
       <c r="Z61" t="n">
-        <v>502.8689</v>
+        <v>503.705</v>
       </c>
       <c r="AA61" t="n">
-        <v>433.2839</v>
+        <v>433.5292</v>
       </c>
       <c r="AB61" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC61" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>14 okt</t>
+          <t>15 okt</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>45.95</v>
+        <v>46.295</v>
       </c>
       <c r="C62" t="n">
-        <v>46.675</v>
+        <v>46.735</v>
       </c>
       <c r="D62" t="n">
-        <v>45.91</v>
+        <v>46.125</v>
       </c>
       <c r="E62" t="n">
-        <v>46.455</v>
+        <v>46.375</v>
       </c>
       <c r="F62" t="n">
-        <v>41.125</v>
+        <v>41.2847</v>
       </c>
       <c r="G62" t="n">
-        <v>36.8183</v>
+        <v>36.8966</v>
       </c>
       <c r="H62" t="n">
         <v>45.05751734733581</v>
@@ -8730,86 +8752,86 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>14 okt</t>
+          <t>15 okt</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>196.6</v>
+        <v>199.48</v>
       </c>
       <c r="M62" t="n">
-        <v>199.36</v>
+        <v>203</v>
       </c>
       <c r="N62" t="n">
-        <v>195.26</v>
+        <v>196.98</v>
       </c>
       <c r="O62" t="n">
-        <v>196.94</v>
+        <v>201.25</v>
       </c>
       <c r="P62" t="n">
-        <v>184.6156</v>
+        <v>185.221</v>
       </c>
       <c r="Q62" t="n">
-        <v>163.9114</v>
+        <v>163.9038</v>
       </c>
       <c r="R62" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S62" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>14 okt</t>
+          <t>15 okt</t>
         </is>
       </c>
       <c r="V62" t="n">
-        <v>545.27</v>
+        <v>533.3200000000001</v>
       </c>
       <c r="W62" t="n">
-        <v>545.75</v>
+        <v>541.13</v>
       </c>
       <c r="X62" t="n">
-        <v>532.54</v>
+        <v>531.22</v>
       </c>
       <c r="Y62" t="n">
-        <v>533.6900000000001</v>
+        <v>539.4400000000001</v>
       </c>
       <c r="Z62" t="n">
-        <v>503.705</v>
+        <v>504.7629</v>
       </c>
       <c r="AA62" t="n">
-        <v>433.5292</v>
+        <v>433.8063</v>
       </c>
       <c r="AB62" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC62" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>15 okt</t>
+          <t>16 okt</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>46.295</v>
+        <v>46.14</v>
       </c>
       <c r="C63" t="n">
-        <v>46.735</v>
+        <v>47.025</v>
       </c>
       <c r="D63" t="n">
-        <v>46.125</v>
+        <v>46.075</v>
       </c>
       <c r="E63" t="n">
-        <v>46.375</v>
+        <v>46.88</v>
       </c>
       <c r="F63" t="n">
-        <v>41.2847</v>
+        <v>41.4622</v>
       </c>
       <c r="G63" t="n">
-        <v>36.8966</v>
+        <v>36.977</v>
       </c>
       <c r="H63" t="n">
         <v>45.05751734733581</v>
@@ -8819,86 +8841,86 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>15 okt</t>
+          <t>16 okt</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>199.48</v>
+        <v>200.6</v>
       </c>
       <c r="M63" t="n">
-        <v>203</v>
+        <v>204.2</v>
       </c>
       <c r="N63" t="n">
-        <v>196.98</v>
+        <v>198.68</v>
       </c>
       <c r="O63" t="n">
-        <v>201.25</v>
+        <v>199.22</v>
       </c>
       <c r="P63" t="n">
-        <v>185.221</v>
+        <v>185.6462</v>
       </c>
       <c r="Q63" t="n">
-        <v>163.9038</v>
+        <v>163.9066</v>
       </c>
       <c r="R63" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S63" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>15 okt</t>
+          <t>16 okt</t>
         </is>
       </c>
       <c r="V63" t="n">
-        <v>533.3200000000001</v>
+        <v>541.3099999999999</v>
       </c>
       <c r="W63" t="n">
-        <v>541.13</v>
+        <v>543.8200000000001</v>
       </c>
       <c r="X63" t="n">
-        <v>531.22</v>
+        <v>524.4299999999999</v>
       </c>
       <c r="Y63" t="n">
-        <v>539.4400000000001</v>
+        <v>529.05</v>
       </c>
       <c r="Z63" t="n">
-        <v>504.7629</v>
+        <v>505.3655</v>
       </c>
       <c r="AA63" t="n">
-        <v>433.8063</v>
+        <v>434.0295</v>
       </c>
       <c r="AB63" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC63" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>16 okt</t>
+          <t>19 okt</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>46.14</v>
+        <v>47.37</v>
       </c>
       <c r="C64" t="n">
-        <v>47.025</v>
+        <v>47.45</v>
       </c>
       <c r="D64" t="n">
-        <v>46.075</v>
+        <v>46.74</v>
       </c>
       <c r="E64" t="n">
-        <v>46.88</v>
+        <v>46.86</v>
       </c>
       <c r="F64" t="n">
-        <v>41.4622</v>
+        <v>41.6313</v>
       </c>
       <c r="G64" t="n">
-        <v>36.977</v>
+        <v>37.0625</v>
       </c>
       <c r="H64" t="n">
         <v>45.05751734733581</v>
@@ -8908,86 +8930,86 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>16 okt</t>
+          <t>19 okt</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>200.6</v>
+        <v>199.56</v>
       </c>
       <c r="M64" t="n">
-        <v>204.2</v>
+        <v>200.8</v>
       </c>
       <c r="N64" t="n">
-        <v>198.68</v>
+        <v>197.32</v>
       </c>
       <c r="O64" t="n">
-        <v>199.22</v>
+        <v>199.84</v>
       </c>
       <c r="P64" t="n">
-        <v>185.6462</v>
+        <v>186.057</v>
       </c>
       <c r="Q64" t="n">
-        <v>163.9066</v>
+        <v>163.8811</v>
       </c>
       <c r="R64" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S64" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>16 okt</t>
+          <t>19 okt</t>
         </is>
       </c>
       <c r="V64" t="n">
-        <v>541.3099999999999</v>
+        <v>528.7</v>
       </c>
       <c r="W64" t="n">
-        <v>543.8200000000001</v>
+        <v>535.5700000000001</v>
       </c>
       <c r="X64" t="n">
-        <v>524.4299999999999</v>
+        <v>528.0599999999999</v>
       </c>
       <c r="Y64" t="n">
-        <v>529.05</v>
+        <v>533.52</v>
       </c>
       <c r="Z64" t="n">
-        <v>505.3655</v>
+        <v>506.0549</v>
       </c>
       <c r="AA64" t="n">
-        <v>434.0295</v>
+        <v>434.2942</v>
       </c>
       <c r="AB64" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC64" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>19 okt</t>
+          <t>20 okt</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>47.37</v>
+        <v>46.875</v>
       </c>
       <c r="C65" t="n">
-        <v>47.45</v>
+        <v>47.505</v>
       </c>
       <c r="D65" t="n">
-        <v>46.74</v>
+        <v>46.36</v>
       </c>
       <c r="E65" t="n">
-        <v>46.86</v>
+        <v>46.57</v>
       </c>
       <c r="F65" t="n">
-        <v>41.6313</v>
+        <v>41.7834</v>
       </c>
       <c r="G65" t="n">
-        <v>37.0625</v>
+        <v>37.1516</v>
       </c>
       <c r="H65" t="n">
         <v>45.05751734733581</v>
@@ -8997,86 +9019,86 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>19 okt</t>
+          <t>20 okt</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>199.56</v>
+        <v>201.3</v>
       </c>
       <c r="M65" t="n">
-        <v>200.8</v>
+        <v>203.45</v>
       </c>
       <c r="N65" t="n">
-        <v>197.32</v>
+        <v>199.46</v>
       </c>
       <c r="O65" t="n">
-        <v>199.84</v>
+        <v>201.55</v>
       </c>
       <c r="P65" t="n">
-        <v>186.057</v>
+        <v>186.474</v>
       </c>
       <c r="Q65" t="n">
-        <v>163.8811</v>
+        <v>163.8736</v>
       </c>
       <c r="R65" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S65" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>19 okt</t>
+          <t>20 okt</t>
         </is>
       </c>
       <c r="V65" t="n">
-        <v>528.7</v>
+        <v>533.91</v>
       </c>
       <c r="W65" t="n">
-        <v>535.5700000000001</v>
+        <v>534.21</v>
       </c>
       <c r="X65" t="n">
-        <v>528.0599999999999</v>
+        <v>525.84</v>
       </c>
       <c r="Y65" t="n">
-        <v>533.52</v>
+        <v>531.87</v>
       </c>
       <c r="Z65" t="n">
-        <v>506.0549</v>
+        <v>506.5901</v>
       </c>
       <c r="AA65" t="n">
-        <v>434.2942</v>
+        <v>434.6038</v>
       </c>
       <c r="AB65" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC65" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>20 okt</t>
+          <t>21 okt</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>46.875</v>
+        <v>46.97</v>
       </c>
       <c r="C66" t="n">
-        <v>47.505</v>
+        <v>47.135</v>
       </c>
       <c r="D66" t="n">
-        <v>46.36</v>
+        <v>46.73</v>
       </c>
       <c r="E66" t="n">
-        <v>46.65</v>
+        <v>46.82</v>
       </c>
       <c r="F66" t="n">
-        <v>41.785</v>
+        <v>41.9468</v>
       </c>
       <c r="G66" t="n">
-        <v>37.152</v>
+        <v>37.2378</v>
       </c>
       <c r="H66" t="n">
         <v>45.05751734733581</v>
@@ -9086,61 +9108,61 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>20 okt</t>
+          <t>21 okt</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>201.3</v>
+        <v>201.8</v>
       </c>
       <c r="M66" t="n">
-        <v>203.45</v>
+        <v>208.65</v>
       </c>
       <c r="N66" t="n">
-        <v>199.46</v>
+        <v>200</v>
       </c>
       <c r="O66" t="n">
-        <v>201.8</v>
+        <v>208.55</v>
       </c>
       <c r="P66" t="n">
-        <v>186.479</v>
+        <v>187.1258</v>
       </c>
       <c r="Q66" t="n">
-        <v>163.8749</v>
+        <v>163.8723</v>
       </c>
       <c r="R66" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S66" t="n">
-        <v>185.5978535243443</v>
+        <v>192.4057115827288</v>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>20 okt</t>
+          <t>21 okt</t>
         </is>
       </c>
       <c r="V66" t="n">
-        <v>533.91</v>
+        <v>529.4400000000001</v>
       </c>
       <c r="W66" t="n">
-        <v>534.21</v>
+        <v>533.28</v>
       </c>
       <c r="X66" t="n">
-        <v>525.84</v>
+        <v>525.02</v>
       </c>
       <c r="Y66" t="n">
-        <v>532.13</v>
+        <v>532.8099999999999</v>
       </c>
       <c r="Z66" t="n">
-        <v>506.5953</v>
+        <v>507.1891</v>
       </c>
       <c r="AA66" t="n">
-        <v>434.6051</v>
+        <v>434.9185</v>
       </c>
       <c r="AB66" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC66" t="n">
-        <v>509.8989698529924</v>
+        <v>510.0814339773996</v>
       </c>
     </row>
   </sheetData>

--- a/rapporten/trend-agent.xlsx
+++ b/rapporten/trend-agent.xlsx
@@ -1074,7 +1074,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="220"/>
+          <max val="240"/>
           <min val="120"/>
         </scaling>
         <delete val="0"/>
@@ -1944,7 +1944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2168,6 +2168,28 @@
       </c>
       <c r="E10" s="3">
         <f>B10/$B$2-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>10053.9</v>
+      </c>
+      <c r="C11" s="2">
+        <f>B11-B10</f>
+        <v/>
+      </c>
+      <c r="D11" s="3">
+        <f>B11/B10-1</f>
+        <v/>
+      </c>
+      <c r="E11" s="3">
+        <f>B11/$B$2-1</f>
         <v/>
       </c>
     </row>
@@ -2311,38 +2333,38 @@
     <row r="6" ht="22" customHeight="1">
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Shell (SHELL.AS)  ·  46,82 EUR</t>
+          <t>Shell (SHELL.AS)  ·  46,62 EUR</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>SAP (SAP.DE)  ·  208,55 EUR</t>
+          <t>SAP (SAP.DE)  ·  216,45 EUR</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>Gestegen: 20,7% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +3,9% (winst). De bot verkoopt als de koers onder 44,25 zakt (-5,5%).</t>
+          <t>Gestegen: 21,5% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +3,5% (winst). De bot verkoopt als de koers onder 44,25 zakt (-5,1%).</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>Gestegen: 62,5% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +8,9% (winst). De bot verkoopt als de koers onder 192,41 zakt (-7,7%).</t>
+          <t>Gestegen: 54,4% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +13,0% (winst). De bot verkoopt als de koers onder 198,88 zakt (-8,1%).</t>
         </is>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Microsoft (MSFT)  ·  532,81 USD</t>
+          <t>Microsoft (MSFT)  ·  521,58 USD</t>
         </is>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Gestegen: 36,8% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: -0,5% (verlies). De bot verkoopt als de koers onder 510,08 zakt (-4,3%).</t>
+          <t>Gestegen: 36,9% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: -2,6% (verlies). De bot verkoopt als de koers onder 510,08 zakt (-2,2%).</t>
         </is>
       </c>
     </row>
@@ -2482,7 +2504,7 @@
         <v>191.56</v>
       </c>
       <c r="F3" t="n">
-        <v>192.41</v>
+        <v>198.88</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -2821,19 +2843,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.165</v>
+        <v>0.163</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.2196820093062304</v>
+        <v>0.2285431751901195</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1416728020259477</v>
+        <v>0.1183737475618283</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="I2" t="n">
-        <v>46.82</v>
+        <v>46.62</v>
       </c>
     </row>
     <row r="3">
@@ -2859,16 +2881,16 @@
         <v>0.157</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.4875178858152791</v>
+        <v>0.4307905783633839</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.1438678953149359</v>
+        <v>0.1608387276334073</v>
       </c>
       <c r="H3" t="n">
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
       <c r="I3" t="n">
-        <v>208.55</v>
+        <v>216.45</v>
       </c>
     </row>
     <row r="4">
@@ -2877,33 +2899,33 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>WKL.AS</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Wolters Kluwer</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.134</v>
+        <v>0.136</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.3805541971350928</v>
+        <v>0.1668063138699023</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.2720742350824041</v>
+        <v>0.1460223781510612</v>
       </c>
       <c r="H4" t="n">
-        <v>0.88</v>
+        <v>0.98</v>
       </c>
       <c r="I4" t="n">
-        <v>85</v>
+        <v>414.31</v>
       </c>
     </row>
     <row r="5">
@@ -2912,33 +2934,33 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>WKL.AS</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Wolters Kluwer</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="E5" t="n">
         <v>0.128</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.162622256869972</v>
+        <v>0.3072365918928017</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.1270024842103736</v>
+        <v>0.2859259711371527</v>
       </c>
       <c r="H5" t="n">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="I5" t="n">
-        <v>408.02</v>
+        <v>86.8</v>
       </c>
     </row>
     <row r="6">
@@ -2961,19 +2983,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.11</v>
+        <v>0.097</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.3989544490721604</v>
+        <v>0.369038160307817</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.06989959349115216</v>
+        <v>0.04193056374579474</v>
       </c>
       <c r="H6" t="n">
         <v>0.83</v>
       </c>
       <c r="I6" t="n">
-        <v>532.8099999999999</v>
+        <v>521.58</v>
       </c>
     </row>
     <row r="7">
@@ -2996,19 +3018,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.106</v>
+        <v>0.092</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.1545147734296179</v>
+        <v>0.1402498925928488</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.1031078483723875</v>
+        <v>0.08353379811437622</v>
       </c>
       <c r="H7" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="I7" t="n">
-        <v>68.15000000000001</v>
+        <v>67.58</v>
       </c>
     </row>
     <row r="8">
@@ -3034,16 +3056,16 @@
         <v>0.092</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.5427591598384727</v>
+        <v>0.5317135319600113</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.03600820447719344</v>
+        <v>0.05328732875047293</v>
       </c>
       <c r="H8" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="I8" t="n">
-        <v>241.68</v>
+        <v>250.24</v>
       </c>
     </row>
     <row r="9">
@@ -3066,19 +3088,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.09</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.1424766396033437</v>
+        <v>0.1430104559621492</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.1221094373649858</v>
+        <v>0.1054394371425038</v>
       </c>
       <c r="H9" t="n">
-        <v>0.86</v>
+        <v>0.84</v>
       </c>
       <c r="I9" t="n">
-        <v>178.09</v>
+        <v>178.23</v>
       </c>
     </row>
     <row r="10">
@@ -3101,19 +3123,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.076</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.634441128155953</v>
+        <v>0.5968922568347694</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.09001027343165191</v>
+        <v>0.02346316365570966</v>
       </c>
       <c r="H10" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>201.64</v>
+        <v>196.29</v>
       </c>
     </row>
     <row r="11">
@@ -3136,19 +3158,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.053</v>
+        <v>0.074</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.08380035461310609</v>
+        <v>0.1001198437642969</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.04261875764702339</v>
+        <v>0.0858081311339931</v>
       </c>
       <c r="H11" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="I11" t="n">
-        <v>406.1</v>
+        <v>413.15</v>
       </c>
     </row>
   </sheetData>
@@ -3419,23 +3441,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>23 jul</t>
+          <t>24 jul</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>38.491</v>
+        <v>38.4019</v>
       </c>
       <c r="C2" t="n">
-        <v>39.0454</v>
+        <v>38.6593</v>
       </c>
       <c r="D2" t="n">
-        <v>38.3425</v>
+        <v>38.1594</v>
       </c>
       <c r="E2" t="n">
-        <v>38.8028</v>
+        <v>38.3871</v>
       </c>
       <c r="F2" t="n">
-        <v>35.863</v>
+        <v>35.9135</v>
       </c>
       <c r="H2" t="n">
         <v>45.05751734733581</v>
@@ -3445,49 +3467,49 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>23 jul</t>
+          <t>24 jul</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>131</v>
+        <v>130.88</v>
       </c>
       <c r="M2" t="n">
-        <v>132.42</v>
+        <v>141.32</v>
       </c>
       <c r="N2" t="n">
-        <v>127.5</v>
+        <v>130.86</v>
       </c>
       <c r="O2" t="n">
-        <v>128.32</v>
+        <v>140.2</v>
       </c>
       <c r="P2" t="n">
-        <v>144.066</v>
+        <v>143.9888</v>
       </c>
       <c r="R2" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S2" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>22 jul</t>
+          <t>23 jul</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>398.8292</v>
+        <v>389.2373</v>
       </c>
       <c r="W2" t="n">
-        <v>400.2465</v>
+        <v>391.0439</v>
       </c>
       <c r="X2" t="n">
-        <v>386.2329</v>
+        <v>376.6809</v>
       </c>
       <c r="Y2" t="n">
-        <v>389.6066</v>
+        <v>380.863</v>
       </c>
       <c r="Z2" t="n">
-        <v>399.4268</v>
+        <v>398.8242</v>
       </c>
       <c r="AB2" t="n">
         <v>535.3375423278808</v>
@@ -3499,23 +3521,23 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>24 jul</t>
+          <t>27 jul</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38.4019</v>
+        <v>37.5802</v>
       </c>
       <c r="C3" t="n">
-        <v>38.6593</v>
+        <v>38.1099</v>
       </c>
       <c r="D3" t="n">
-        <v>38.1594</v>
+        <v>37.4317</v>
       </c>
       <c r="E3" t="n">
-        <v>38.3871</v>
+        <v>37.9515</v>
       </c>
       <c r="F3" t="n">
-        <v>35.9135</v>
+        <v>35.931</v>
       </c>
       <c r="H3" t="n">
         <v>45.05751734733581</v>
@@ -3525,49 +3547,49 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>24 jul</t>
+          <t>27 jul</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>130.88</v>
+        <v>142.38</v>
       </c>
       <c r="M3" t="n">
-        <v>141.32</v>
+        <v>151.56</v>
       </c>
       <c r="N3" t="n">
-        <v>130.86</v>
+        <v>142</v>
       </c>
       <c r="O3" t="n">
-        <v>140.2</v>
+        <v>151.28</v>
       </c>
       <c r="P3" t="n">
-        <v>143.9888</v>
+        <v>144.0572</v>
       </c>
       <c r="R3" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S3" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>23 jul</t>
+          <t>24 jul</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>389.2373</v>
+        <v>386.3227</v>
       </c>
       <c r="W3" t="n">
-        <v>391.0439</v>
+        <v>388.299</v>
       </c>
       <c r="X3" t="n">
-        <v>376.6809</v>
+        <v>379.9348</v>
       </c>
       <c r="Y3" t="n">
-        <v>380.863</v>
+        <v>380.9828</v>
       </c>
       <c r="Z3" t="n">
-        <v>398.8242</v>
+        <v>398.3214</v>
       </c>
       <c r="AB3" t="n">
         <v>535.3375423278808</v>
@@ -3579,23 +3601,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>27 jul</t>
+          <t>28 jul</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>37.5802</v>
+        <v>37.7139</v>
       </c>
       <c r="C4" t="n">
-        <v>38.1099</v>
+        <v>38.0109</v>
       </c>
       <c r="D4" t="n">
-        <v>37.4317</v>
+        <v>37.4713</v>
       </c>
       <c r="E4" t="n">
-        <v>37.9515</v>
+        <v>37.4713</v>
       </c>
       <c r="F4" t="n">
-        <v>35.931</v>
+        <v>35.9372</v>
       </c>
       <c r="H4" t="n">
         <v>45.05751734733581</v>
@@ -3605,49 +3627,49 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>27 jul</t>
+          <t>28 jul</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>142.38</v>
+        <v>152.2</v>
       </c>
       <c r="M4" t="n">
-        <v>151.56</v>
+        <v>159.76</v>
       </c>
       <c r="N4" t="n">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="O4" t="n">
-        <v>151.28</v>
+        <v>159.24</v>
       </c>
       <c r="P4" t="n">
-        <v>144.0572</v>
+        <v>144.1076</v>
       </c>
       <c r="R4" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S4" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>24 jul</t>
+          <t>27 jul</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>386.3227</v>
+        <v>389.347</v>
       </c>
       <c r="W4" t="n">
-        <v>388.299</v>
+        <v>393.4593</v>
       </c>
       <c r="X4" t="n">
-        <v>379.9348</v>
+        <v>387.261</v>
       </c>
       <c r="Y4" t="n">
-        <v>380.9828</v>
+        <v>388.3689</v>
       </c>
       <c r="Z4" t="n">
-        <v>398.3214</v>
+        <v>398.0172</v>
       </c>
       <c r="AB4" t="n">
         <v>535.3375423278808</v>
@@ -3659,23 +3681,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>28 jul</t>
+          <t>29 jul</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>37.7139</v>
+        <v>38.0653</v>
       </c>
       <c r="C5" t="n">
-        <v>38.0109</v>
+        <v>38.59</v>
       </c>
       <c r="D5" t="n">
-        <v>37.4713</v>
+        <v>37.7089</v>
       </c>
       <c r="E5" t="n">
-        <v>37.4713</v>
+        <v>38.4415</v>
       </c>
       <c r="F5" t="n">
-        <v>35.9372</v>
+        <v>35.9692</v>
       </c>
       <c r="H5" t="n">
         <v>45.05751734733581</v>
@@ -3685,49 +3707,49 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>28 jul</t>
+          <t>29 jul</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>152.2</v>
+        <v>159.84</v>
       </c>
       <c r="M5" t="n">
-        <v>159.76</v>
+        <v>163.3</v>
       </c>
       <c r="N5" t="n">
-        <v>151</v>
+        <v>156.48</v>
       </c>
       <c r="O5" t="n">
-        <v>159.24</v>
+        <v>162.04</v>
       </c>
       <c r="P5" t="n">
-        <v>144.1076</v>
+        <v>144.28</v>
       </c>
       <c r="R5" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S5" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>27 jul</t>
+          <t>28 jul</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>389.347</v>
+        <v>392.4213</v>
       </c>
       <c r="W5" t="n">
-        <v>393.4593</v>
+        <v>399.5678</v>
       </c>
       <c r="X5" t="n">
-        <v>387.261</v>
+        <v>390.5647</v>
       </c>
       <c r="Y5" t="n">
-        <v>388.3689</v>
+        <v>392.6109</v>
       </c>
       <c r="Z5" t="n">
-        <v>398.0172</v>
+        <v>397.7139</v>
       </c>
       <c r="AB5" t="n">
         <v>535.3375423278808</v>
@@ -3739,26 +3761,26 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>29 jul</t>
+          <t>30 jul</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>38.0653</v>
+        <v>38.6098</v>
       </c>
       <c r="C6" t="n">
-        <v>38.59</v>
+        <v>39.1444</v>
       </c>
       <c r="D6" t="n">
-        <v>37.7089</v>
+        <v>38.3277</v>
       </c>
       <c r="E6" t="n">
-        <v>38.4415</v>
+        <v>38.5108</v>
       </c>
       <c r="F6" t="n">
-        <v>35.9692</v>
+        <v>35.9978</v>
       </c>
       <c r="G6" t="n">
-        <v>33.9987</v>
+        <v>34.0424</v>
       </c>
       <c r="H6" t="n">
         <v>45.05751734733581</v>
@@ -3768,55 +3790,55 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>29 jul</t>
+          <t>30 jul</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>159.84</v>
+        <v>162.5</v>
       </c>
       <c r="M6" t="n">
-        <v>163.3</v>
+        <v>163.16</v>
       </c>
       <c r="N6" t="n">
-        <v>156.48</v>
+        <v>155.2</v>
       </c>
       <c r="O6" t="n">
-        <v>162.04</v>
+        <v>155.92</v>
       </c>
       <c r="P6" t="n">
-        <v>144.28</v>
+        <v>144.3804</v>
       </c>
       <c r="Q6" t="n">
-        <v>172.343</v>
+        <v>171.9849</v>
       </c>
       <c r="R6" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S6" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>28 jul</t>
+          <t>29 jul</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>392.4213</v>
+        <v>392.6608</v>
       </c>
       <c r="W6" t="n">
-        <v>399.5678</v>
+        <v>400.4961</v>
       </c>
       <c r="X6" t="n">
-        <v>390.5647</v>
+        <v>388.0095</v>
       </c>
       <c r="Y6" t="n">
-        <v>392.6109</v>
+        <v>389.8062</v>
       </c>
       <c r="Z6" t="n">
-        <v>397.7139</v>
+        <v>397.1057</v>
       </c>
       <c r="AA6" t="n">
-        <v>432.5982</v>
+        <v>431.9565</v>
       </c>
       <c r="AB6" t="n">
         <v>535.3375423278808</v>
@@ -3828,26 +3850,26 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>30 jul</t>
+          <t>31 jul</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>38.6098</v>
       </c>
       <c r="C7" t="n">
-        <v>39.1444</v>
+        <v>39.575</v>
       </c>
       <c r="D7" t="n">
-        <v>38.3277</v>
+        <v>38.4464</v>
       </c>
       <c r="E7" t="n">
-        <v>38.5108</v>
+        <v>39.3226</v>
       </c>
       <c r="F7" t="n">
-        <v>35.9978</v>
+        <v>36.0495</v>
       </c>
       <c r="G7" t="n">
-        <v>34.0424</v>
+        <v>34.0907</v>
       </c>
       <c r="H7" t="n">
         <v>45.05751734733581</v>
@@ -3857,55 +3879,55 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>30 jul</t>
+          <t>31 jul</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>162.5</v>
+        <v>154.9</v>
       </c>
       <c r="M7" t="n">
-        <v>163.16</v>
+        <v>158.26</v>
       </c>
       <c r="N7" t="n">
-        <v>155.2</v>
+        <v>153.6</v>
       </c>
       <c r="O7" t="n">
-        <v>155.92</v>
+        <v>157.68</v>
       </c>
       <c r="P7" t="n">
-        <v>144.3804</v>
+        <v>144.4984</v>
       </c>
       <c r="Q7" t="n">
-        <v>171.9849</v>
+        <v>171.6292</v>
       </c>
       <c r="R7" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S7" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>29 jul</t>
+          <t>30 jul</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>392.6608</v>
+        <v>437.0772</v>
       </c>
       <c r="W7" t="n">
-        <v>400.4961</v>
+        <v>457.8281</v>
       </c>
       <c r="X7" t="n">
-        <v>388.0095</v>
+        <v>431.6275</v>
       </c>
       <c r="Y7" t="n">
-        <v>389.8062</v>
+        <v>450.2524</v>
       </c>
       <c r="Z7" t="n">
-        <v>397.1057</v>
+        <v>397.6741</v>
       </c>
       <c r="AA7" t="n">
-        <v>431.9565</v>
+        <v>431.6738</v>
       </c>
       <c r="AB7" t="n">
         <v>535.3375423278808</v>
@@ -3917,26 +3939,26 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>31 jul</t>
+          <t>3 aug</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>38.6098</v>
+        <v>38.3128</v>
       </c>
       <c r="C8" t="n">
-        <v>39.575</v>
+        <v>39.4067</v>
       </c>
       <c r="D8" t="n">
-        <v>38.4464</v>
+        <v>38.2138</v>
       </c>
       <c r="E8" t="n">
-        <v>39.3226</v>
+        <v>39.4067</v>
       </c>
       <c r="F8" t="n">
-        <v>36.0495</v>
+        <v>36.1112</v>
       </c>
       <c r="G8" t="n">
-        <v>34.0907</v>
+        <v>34.1393</v>
       </c>
       <c r="H8" t="n">
         <v>45.05751734733581</v>
@@ -3946,55 +3968,55 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>31 jul</t>
+          <t>3 aug</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>154.9</v>
+        <v>160</v>
       </c>
       <c r="M8" t="n">
-        <v>158.26</v>
+        <v>168.7</v>
       </c>
       <c r="N8" t="n">
-        <v>153.6</v>
+        <v>159.6</v>
       </c>
       <c r="O8" t="n">
-        <v>157.68</v>
+        <v>164.64</v>
       </c>
       <c r="P8" t="n">
-        <v>144.4984</v>
+        <v>144.7016</v>
       </c>
       <c r="Q8" t="n">
-        <v>171.6292</v>
+        <v>171.301</v>
       </c>
       <c r="R8" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S8" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>30 jul</t>
+          <t>31 jul</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>437.0772</v>
+        <v>449.1545</v>
       </c>
       <c r="W8" t="n">
-        <v>457.8281</v>
+        <v>465.9628</v>
       </c>
       <c r="X8" t="n">
-        <v>431.6275</v>
+        <v>448.4857</v>
       </c>
       <c r="Y8" t="n">
-        <v>450.2524</v>
+        <v>463.8468</v>
       </c>
       <c r="Z8" t="n">
-        <v>397.6741</v>
+        <v>398.6364</v>
       </c>
       <c r="AA8" t="n">
-        <v>431.6738</v>
+        <v>431.4438</v>
       </c>
       <c r="AB8" t="n">
         <v>535.3375423278808</v>
@@ -4006,26 +4028,26 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3 aug</t>
+          <t>4 aug</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>38.3128</v>
+        <v>39.3028</v>
       </c>
       <c r="C9" t="n">
-        <v>39.4067</v>
+        <v>39.6443</v>
       </c>
       <c r="D9" t="n">
-        <v>38.2138</v>
+        <v>38.2039</v>
       </c>
       <c r="E9" t="n">
-        <v>39.4067</v>
+        <v>38.486</v>
       </c>
       <c r="F9" t="n">
-        <v>36.1112</v>
+        <v>36.1495</v>
       </c>
       <c r="G9" t="n">
-        <v>34.1393</v>
+        <v>34.1818</v>
       </c>
       <c r="H9" t="n">
         <v>45.05751734733581</v>
@@ -4035,55 +4057,55 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>3 aug</t>
+          <t>4 aug</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>160</v>
+        <v>162.86</v>
       </c>
       <c r="M9" t="n">
-        <v>168.7</v>
+        <v>168.56</v>
       </c>
       <c r="N9" t="n">
-        <v>159.6</v>
+        <v>162.4</v>
       </c>
       <c r="O9" t="n">
-        <v>164.64</v>
+        <v>167.38</v>
       </c>
       <c r="P9" t="n">
-        <v>144.7016</v>
+        <v>145.02</v>
       </c>
       <c r="Q9" t="n">
-        <v>171.301</v>
+        <v>170.9913</v>
       </c>
       <c r="R9" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S9" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>31 jul</t>
+          <t>3 aug</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>449.1545</v>
+        <v>475.2354</v>
       </c>
       <c r="W9" t="n">
-        <v>465.9628</v>
+        <v>490.7262</v>
       </c>
       <c r="X9" t="n">
-        <v>448.4857</v>
+        <v>474.1075</v>
       </c>
       <c r="Y9" t="n">
-        <v>463.8468</v>
+        <v>486.7337</v>
       </c>
       <c r="Z9" t="n">
-        <v>398.6364</v>
+        <v>399.9838</v>
       </c>
       <c r="AA9" t="n">
-        <v>431.4438</v>
+        <v>431.3306</v>
       </c>
       <c r="AB9" t="n">
         <v>535.3375423278808</v>
@@ -4095,26 +4117,26 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4 aug</t>
+          <t>5 aug</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>39.3028</v>
+        <v>38.4811</v>
       </c>
       <c r="C10" t="n">
-        <v>39.6443</v>
+        <v>38.7632</v>
       </c>
       <c r="D10" t="n">
-        <v>38.2039</v>
+        <v>37.9366</v>
       </c>
       <c r="E10" t="n">
-        <v>38.486</v>
+        <v>38.0307</v>
       </c>
       <c r="F10" t="n">
-        <v>36.1495</v>
+        <v>36.1966</v>
       </c>
       <c r="G10" t="n">
-        <v>34.1818</v>
+        <v>34.2215</v>
       </c>
       <c r="H10" t="n">
         <v>45.05751734733581</v>
@@ -4124,55 +4146,55 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>4 aug</t>
+          <t>5 aug</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>162.86</v>
+        <v>167.92</v>
       </c>
       <c r="M10" t="n">
-        <v>168.56</v>
+        <v>172.6</v>
       </c>
       <c r="N10" t="n">
-        <v>162.4</v>
+        <v>167.3</v>
       </c>
       <c r="O10" t="n">
-        <v>167.38</v>
+        <v>169.26</v>
       </c>
       <c r="P10" t="n">
-        <v>145.02</v>
+        <v>145.4052</v>
       </c>
       <c r="Q10" t="n">
-        <v>170.9913</v>
+        <v>170.7022</v>
       </c>
       <c r="R10" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S10" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>3 aug</t>
+          <t>4 aug</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>475.2354</v>
+        <v>479.9964</v>
       </c>
       <c r="W10" t="n">
-        <v>490.7262</v>
+        <v>498.5016</v>
       </c>
       <c r="X10" t="n">
-        <v>474.1075</v>
+        <v>478.2697</v>
       </c>
       <c r="Y10" t="n">
-        <v>486.7337</v>
+        <v>491.884</v>
       </c>
       <c r="Z10" t="n">
-        <v>399.9838</v>
+        <v>401.4555</v>
       </c>
       <c r="AA10" t="n">
-        <v>431.3306</v>
+        <v>431.2438</v>
       </c>
       <c r="AB10" t="n">
         <v>535.3375423278808</v>
@@ -4184,26 +4206,26 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5 aug</t>
+          <t>6 aug</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>38.4811</v>
+        <v>38.0752</v>
       </c>
       <c r="C11" t="n">
-        <v>38.7632</v>
+        <v>38.4069</v>
       </c>
       <c r="D11" t="n">
-        <v>37.9366</v>
+        <v>37.9168</v>
       </c>
       <c r="E11" t="n">
-        <v>38.0307</v>
+        <v>38.392</v>
       </c>
       <c r="F11" t="n">
-        <v>36.1966</v>
+        <v>36.2474</v>
       </c>
       <c r="G11" t="n">
-        <v>34.2215</v>
+        <v>34.2607</v>
       </c>
       <c r="H11" t="n">
         <v>45.05751734733581</v>
@@ -4213,55 +4235,55 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>5 aug</t>
+          <t>6 aug</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>167.92</v>
+        <v>171.44</v>
       </c>
       <c r="M11" t="n">
-        <v>172.6</v>
+        <v>173.1</v>
       </c>
       <c r="N11" t="n">
-        <v>167.3</v>
+        <v>168.08</v>
       </c>
       <c r="O11" t="n">
-        <v>169.26</v>
+        <v>170.98</v>
       </c>
       <c r="P11" t="n">
-        <v>145.4052</v>
+        <v>145.7928</v>
       </c>
       <c r="Q11" t="n">
-        <v>170.7022</v>
+        <v>170.384</v>
       </c>
       <c r="R11" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S11" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>4 aug</t>
+          <t>5 aug</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>479.9964</v>
+        <v>495.4273</v>
       </c>
       <c r="W11" t="n">
-        <v>498.5016</v>
+        <v>497.3038</v>
       </c>
       <c r="X11" t="n">
-        <v>478.2697</v>
+        <v>484.7674</v>
       </c>
       <c r="Y11" t="n">
-        <v>491.884</v>
+        <v>486.5441</v>
       </c>
       <c r="Z11" t="n">
-        <v>401.4555</v>
+        <v>402.8307</v>
       </c>
       <c r="AA11" t="n">
-        <v>431.2438</v>
+        <v>431.1393</v>
       </c>
       <c r="AB11" t="n">
         <v>535.3375423278808</v>
@@ -4273,26 +4295,26 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6 aug</t>
+          <t>7 aug</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>38.0752</v>
+        <v>38.5207</v>
       </c>
       <c r="C12" t="n">
-        <v>38.4069</v>
+        <v>38.5999</v>
       </c>
       <c r="D12" t="n">
-        <v>37.9168</v>
+        <v>37.897</v>
       </c>
       <c r="E12" t="n">
-        <v>38.392</v>
+        <v>38.0059</v>
       </c>
       <c r="F12" t="n">
-        <v>36.2474</v>
+        <v>36.2952</v>
       </c>
       <c r="G12" t="n">
-        <v>34.2607</v>
+        <v>34.294</v>
       </c>
       <c r="H12" t="n">
         <v>45.05751734733581</v>
@@ -4302,55 +4324,55 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>6 aug</t>
+          <t>7 aug</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>171.44</v>
+        <v>173.82</v>
       </c>
       <c r="M12" t="n">
-        <v>173.1</v>
+        <v>179.56</v>
       </c>
       <c r="N12" t="n">
-        <v>168.08</v>
+        <v>173.82</v>
       </c>
       <c r="O12" t="n">
-        <v>170.98</v>
+        <v>177.96</v>
       </c>
       <c r="P12" t="n">
-        <v>145.7928</v>
+        <v>146.2468</v>
       </c>
       <c r="Q12" t="n">
-        <v>170.384</v>
+        <v>170.0918</v>
       </c>
       <c r="R12" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S12" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>5 aug</t>
+          <t>6 aug</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>495.4273</v>
+        <v>487.632</v>
       </c>
       <c r="W12" t="n">
-        <v>497.3038</v>
+        <v>500.6176</v>
       </c>
       <c r="X12" t="n">
-        <v>484.7674</v>
+        <v>487.6021</v>
       </c>
       <c r="Y12" t="n">
-        <v>486.5441</v>
+        <v>498.9207</v>
       </c>
       <c r="Z12" t="n">
-        <v>402.8307</v>
+        <v>404.5041</v>
       </c>
       <c r="AA12" t="n">
-        <v>431.1393</v>
+        <v>431.087</v>
       </c>
       <c r="AB12" t="n">
         <v>535.3375423278808</v>
@@ -4362,26 +4384,26 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>7 aug</t>
+          <t>10 aug</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>38.5207</v>
+        <v>38.0356</v>
       </c>
       <c r="C13" t="n">
-        <v>38.5999</v>
+        <v>38.4366</v>
       </c>
       <c r="D13" t="n">
-        <v>37.897</v>
+        <v>37.803</v>
       </c>
       <c r="E13" t="n">
-        <v>38.0059</v>
+        <v>38.4019</v>
       </c>
       <c r="F13" t="n">
-        <v>36.2952</v>
+        <v>36.3315</v>
       </c>
       <c r="G13" t="n">
-        <v>34.294</v>
+        <v>34.3294</v>
       </c>
       <c r="H13" t="n">
         <v>45.05751734733581</v>
@@ -4391,55 +4413,55 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>7 aug</t>
+          <t>10 aug</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>173.82</v>
+        <v>178.92</v>
       </c>
       <c r="M13" t="n">
-        <v>179.56</v>
+        <v>179.96</v>
       </c>
       <c r="N13" t="n">
-        <v>173.82</v>
+        <v>175.86</v>
       </c>
       <c r="O13" t="n">
-        <v>177.96</v>
+        <v>179.3</v>
       </c>
       <c r="P13" t="n">
-        <v>146.2468</v>
+        <v>146.4748</v>
       </c>
       <c r="Q13" t="n">
-        <v>170.0918</v>
+        <v>169.8238</v>
       </c>
       <c r="R13" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S13" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>6 aug</t>
+          <t>7 aug</t>
         </is>
       </c>
       <c r="V13" t="n">
-        <v>487.632</v>
+        <v>498.272</v>
       </c>
       <c r="W13" t="n">
-        <v>500.6176</v>
+        <v>504.2308</v>
       </c>
       <c r="X13" t="n">
-        <v>487.6021</v>
+        <v>497.7929</v>
       </c>
       <c r="Y13" t="n">
-        <v>498.9207</v>
+        <v>499.0505</v>
       </c>
       <c r="Z13" t="n">
-        <v>404.5041</v>
+        <v>406.2472</v>
       </c>
       <c r="AA13" t="n">
-        <v>431.087</v>
+        <v>431.0194</v>
       </c>
       <c r="AB13" t="n">
         <v>535.3375423278808</v>
@@ -4451,26 +4473,26 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10 aug</t>
+          <t>11 aug</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>38.0356</v>
+        <v>38.7385</v>
       </c>
       <c r="C14" t="n">
-        <v>38.4366</v>
+        <v>39.0058</v>
       </c>
       <c r="D14" t="n">
-        <v>37.803</v>
+        <v>38.6148</v>
       </c>
       <c r="E14" t="n">
-        <v>38.4019</v>
+        <v>38.9662</v>
       </c>
       <c r="F14" t="n">
-        <v>36.3315</v>
+        <v>36.374</v>
       </c>
       <c r="G14" t="n">
-        <v>34.3294</v>
+        <v>34.3685</v>
       </c>
       <c r="H14" t="n">
         <v>45.05751734733581</v>
@@ -4480,55 +4502,55 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>10 aug</t>
+          <t>11 aug</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>178.92</v>
+        <v>180</v>
       </c>
       <c r="M14" t="n">
-        <v>179.96</v>
+        <v>183.24</v>
       </c>
       <c r="N14" t="n">
-        <v>175.86</v>
+        <v>178.14</v>
       </c>
       <c r="O14" t="n">
-        <v>179.3</v>
+        <v>180.7</v>
       </c>
       <c r="P14" t="n">
-        <v>146.4748</v>
+        <v>146.8316</v>
       </c>
       <c r="Q14" t="n">
-        <v>169.8238</v>
+        <v>169.5375</v>
       </c>
       <c r="R14" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S14" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>7 aug</t>
+          <t>10 aug</t>
         </is>
       </c>
       <c r="V14" t="n">
-        <v>498.272</v>
+        <v>502.4941</v>
       </c>
       <c r="W14" t="n">
-        <v>504.2308</v>
+        <v>512.7646999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>497.7929</v>
+        <v>501.3262</v>
       </c>
       <c r="Y14" t="n">
-        <v>499.0505</v>
+        <v>505.1091</v>
       </c>
       <c r="Z14" t="n">
-        <v>406.2472</v>
+        <v>407.8257</v>
       </c>
       <c r="AA14" t="n">
-        <v>431.0194</v>
+        <v>430.9778</v>
       </c>
       <c r="AB14" t="n">
         <v>535.3375423278808</v>
@@ -4540,26 +4562,26 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>11 aug</t>
+          <t>12 aug</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>38.7385</v>
+        <v>38.8573</v>
       </c>
       <c r="C15" t="n">
-        <v>39.0058</v>
+        <v>38.986</v>
       </c>
       <c r="D15" t="n">
-        <v>38.6148</v>
+        <v>38.3871</v>
       </c>
       <c r="E15" t="n">
-        <v>38.9662</v>
+        <v>38.6494</v>
       </c>
       <c r="F15" t="n">
-        <v>36.374</v>
+        <v>36.3981</v>
       </c>
       <c r="G15" t="n">
-        <v>34.3685</v>
+        <v>34.4068</v>
       </c>
       <c r="H15" t="n">
         <v>45.05751734733581</v>
@@ -4569,55 +4591,55 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>11 aug</t>
+          <t>12 aug</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>180</v>
+        <v>180.3</v>
       </c>
       <c r="M15" t="n">
-        <v>183.24</v>
+        <v>180.98</v>
       </c>
       <c r="N15" t="n">
-        <v>178.14</v>
+        <v>175.4</v>
       </c>
       <c r="O15" t="n">
-        <v>180.7</v>
+        <v>175.96</v>
       </c>
       <c r="P15" t="n">
-        <v>146.8316</v>
+        <v>147.232</v>
       </c>
       <c r="Q15" t="n">
-        <v>169.5375</v>
+        <v>169.2701</v>
       </c>
       <c r="R15" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S15" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>10 aug</t>
+          <t>11 aug</t>
         </is>
       </c>
       <c r="V15" t="n">
-        <v>502.4941</v>
+        <v>503.3824</v>
       </c>
       <c r="W15" t="n">
-        <v>512.7646999999999</v>
+        <v>504.3805</v>
       </c>
       <c r="X15" t="n">
-        <v>501.3262</v>
+        <v>498.6113</v>
       </c>
       <c r="Y15" t="n">
-        <v>505.1091</v>
+        <v>502.8633</v>
       </c>
       <c r="Z15" t="n">
-        <v>407.8257</v>
+        <v>408.895</v>
       </c>
       <c r="AA15" t="n">
-        <v>430.9778</v>
+        <v>430.9106</v>
       </c>
       <c r="AB15" t="n">
         <v>535.3375423278808</v>
@@ -4629,26 +4651,26 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>12 aug</t>
+          <t>13 aug</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>38.8573</v>
+        <v>39</v>
       </c>
       <c r="C16" t="n">
-        <v>38.986</v>
+        <v>39.005</v>
       </c>
       <c r="D16" t="n">
-        <v>38.3871</v>
+        <v>38.2</v>
       </c>
       <c r="E16" t="n">
-        <v>38.6494</v>
+        <v>38.605</v>
       </c>
       <c r="F16" t="n">
-        <v>36.3981</v>
+        <v>36.4313</v>
       </c>
       <c r="G16" t="n">
-        <v>34.4068</v>
+        <v>34.4429</v>
       </c>
       <c r="H16" t="n">
         <v>45.05751734733581</v>
@@ -4658,55 +4680,55 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>12 aug</t>
+          <t>13 aug</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>180.3</v>
+        <v>177.48</v>
       </c>
       <c r="M16" t="n">
-        <v>180.98</v>
+        <v>178.3</v>
       </c>
       <c r="N16" t="n">
-        <v>175.4</v>
+        <v>174.8</v>
       </c>
       <c r="O16" t="n">
-        <v>175.96</v>
+        <v>175.38</v>
       </c>
       <c r="P16" t="n">
-        <v>147.232</v>
+        <v>147.4496</v>
       </c>
       <c r="Q16" t="n">
-        <v>169.2701</v>
+        <v>168.9889</v>
       </c>
       <c r="R16" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S16" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>11 aug</t>
+          <t>12 aug</t>
         </is>
       </c>
       <c r="V16" t="n">
-        <v>503.3824</v>
+        <v>499.0505</v>
       </c>
       <c r="W16" t="n">
-        <v>504.3805</v>
+        <v>500.5577</v>
       </c>
       <c r="X16" t="n">
-        <v>498.6113</v>
+        <v>490.5964</v>
       </c>
       <c r="Y16" t="n">
-        <v>502.8633</v>
+        <v>491.5047</v>
       </c>
       <c r="Z16" t="n">
-        <v>408.895</v>
+        <v>409.532</v>
       </c>
       <c r="AA16" t="n">
-        <v>430.9106</v>
+        <v>430.7866</v>
       </c>
       <c r="AB16" t="n">
         <v>535.3375423278808</v>
@@ -4718,26 +4740,26 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>13 aug</t>
+          <t>14 aug</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>39</v>
+        <v>38.65</v>
       </c>
       <c r="C17" t="n">
-        <v>39.005</v>
+        <v>39.1</v>
       </c>
       <c r="D17" t="n">
-        <v>38.2</v>
+        <v>38.56</v>
       </c>
       <c r="E17" t="n">
-        <v>38.605</v>
+        <v>38.97</v>
       </c>
       <c r="F17" t="n">
-        <v>36.4313</v>
+        <v>36.4703</v>
       </c>
       <c r="G17" t="n">
-        <v>34.4429</v>
+        <v>34.4805</v>
       </c>
       <c r="H17" t="n">
         <v>45.05751734733581</v>
@@ -4747,55 +4769,55 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>13 aug</t>
+          <t>14 aug</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>177.48</v>
+        <v>182</v>
       </c>
       <c r="M17" t="n">
-        <v>178.3</v>
+        <v>185.74</v>
       </c>
       <c r="N17" t="n">
-        <v>174.8</v>
+        <v>179.28</v>
       </c>
       <c r="O17" t="n">
-        <v>175.38</v>
+        <v>180.14</v>
       </c>
       <c r="P17" t="n">
-        <v>147.4496</v>
+        <v>147.8228</v>
       </c>
       <c r="Q17" t="n">
-        <v>168.9889</v>
+        <v>168.7386</v>
       </c>
       <c r="R17" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S17" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>12 aug</t>
+          <t>13 aug</t>
         </is>
       </c>
       <c r="V17" t="n">
-        <v>499.0505</v>
+        <v>492.3431</v>
       </c>
       <c r="W17" t="n">
-        <v>500.5577</v>
+        <v>500.398</v>
       </c>
       <c r="X17" t="n">
-        <v>490.5964</v>
+        <v>492.0837</v>
       </c>
       <c r="Y17" t="n">
-        <v>491.5047</v>
+        <v>495.9464</v>
       </c>
       <c r="Z17" t="n">
-        <v>409.532</v>
+        <v>410.6414</v>
       </c>
       <c r="AA17" t="n">
-        <v>430.7866</v>
+        <v>430.6696</v>
       </c>
       <c r="AB17" t="n">
         <v>535.3375423278808</v>
@@ -4807,26 +4829,26 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>14 aug</t>
+          <t>17 aug</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>38.65</v>
+        <v>38.97</v>
       </c>
       <c r="C18" t="n">
-        <v>39.1</v>
+        <v>39.27</v>
       </c>
       <c r="D18" t="n">
-        <v>38.56</v>
+        <v>38.765</v>
       </c>
       <c r="E18" t="n">
-        <v>38.97</v>
+        <v>39.15</v>
       </c>
       <c r="F18" t="n">
-        <v>36.4703</v>
+        <v>36.5118</v>
       </c>
       <c r="G18" t="n">
-        <v>34.4805</v>
+        <v>34.5207</v>
       </c>
       <c r="H18" t="n">
         <v>45.05751734733581</v>
@@ -4836,55 +4858,55 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>14 aug</t>
+          <t>17 aug</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>182</v>
+        <v>178.94</v>
       </c>
       <c r="M18" t="n">
-        <v>185.74</v>
+        <v>180.9</v>
       </c>
       <c r="N18" t="n">
-        <v>179.28</v>
+        <v>177.66</v>
       </c>
       <c r="O18" t="n">
-        <v>180.14</v>
+        <v>179.58</v>
       </c>
       <c r="P18" t="n">
-        <v>147.8228</v>
+        <v>148.2524</v>
       </c>
       <c r="Q18" t="n">
-        <v>168.7386</v>
+        <v>168.5337</v>
       </c>
       <c r="R18" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S18" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>13 aug</t>
+          <t>14 aug</t>
         </is>
       </c>
       <c r="V18" t="n">
-        <v>492.3431</v>
+        <v>495.4273</v>
       </c>
       <c r="W18" t="n">
-        <v>500.398</v>
+        <v>499.0705</v>
       </c>
       <c r="X18" t="n">
-        <v>492.0837</v>
+        <v>492.9919</v>
       </c>
       <c r="Y18" t="n">
-        <v>495.9464</v>
+        <v>494.4691</v>
       </c>
       <c r="Z18" t="n">
-        <v>410.6414</v>
+        <v>412</v>
       </c>
       <c r="AA18" t="n">
-        <v>430.6696</v>
+        <v>430.5061</v>
       </c>
       <c r="AB18" t="n">
         <v>535.3375423278808</v>
@@ -4896,26 +4918,26 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>17 aug</t>
+          <t>18 aug</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>38.97</v>
+        <v>39.49</v>
       </c>
       <c r="C19" t="n">
-        <v>39.27</v>
+        <v>39.945</v>
       </c>
       <c r="D19" t="n">
-        <v>38.765</v>
+        <v>39.46</v>
       </c>
       <c r="E19" t="n">
-        <v>39.15</v>
+        <v>39.785</v>
       </c>
       <c r="F19" t="n">
-        <v>36.5118</v>
+        <v>36.5781</v>
       </c>
       <c r="G19" t="n">
-        <v>34.5207</v>
+        <v>34.5641</v>
       </c>
       <c r="H19" t="n">
         <v>45.05751734733581</v>
@@ -4925,55 +4947,55 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>17 aug</t>
+          <t>18 aug</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>178.94</v>
+        <v>179.14</v>
       </c>
       <c r="M19" t="n">
-        <v>180.9</v>
+        <v>183.9</v>
       </c>
       <c r="N19" t="n">
-        <v>177.66</v>
+        <v>177.98</v>
       </c>
       <c r="O19" t="n">
-        <v>179.58</v>
+        <v>182.5</v>
       </c>
       <c r="P19" t="n">
-        <v>148.2524</v>
+        <v>148.8084</v>
       </c>
       <c r="Q19" t="n">
-        <v>168.5337</v>
+        <v>168.3358</v>
       </c>
       <c r="R19" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S19" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>14 aug</t>
+          <t>17 aug</t>
         </is>
       </c>
       <c r="V19" t="n">
-        <v>495.4273</v>
+        <v>489.2191</v>
       </c>
       <c r="W19" t="n">
-        <v>499.0705</v>
+        <v>491.7343</v>
       </c>
       <c r="X19" t="n">
-        <v>492.9919</v>
+        <v>477.5111</v>
       </c>
       <c r="Y19" t="n">
-        <v>494.4691</v>
+        <v>479.4474</v>
       </c>
       <c r="Z19" t="n">
-        <v>412</v>
+        <v>413.044</v>
       </c>
       <c r="AA19" t="n">
-        <v>430.5061</v>
+        <v>430.2151</v>
       </c>
       <c r="AB19" t="n">
         <v>535.3375423278808</v>
@@ -4985,26 +5007,26 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>18 aug</t>
+          <t>19 aug</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>39.49</v>
+        <v>39.835</v>
       </c>
       <c r="C20" t="n">
-        <v>39.945</v>
+        <v>40.14</v>
       </c>
       <c r="D20" t="n">
-        <v>39.46</v>
+        <v>39.74</v>
       </c>
       <c r="E20" t="n">
-        <v>39.785</v>
+        <v>39.94</v>
       </c>
       <c r="F20" t="n">
-        <v>36.5781</v>
+        <v>36.6336</v>
       </c>
       <c r="G20" t="n">
-        <v>34.5641</v>
+        <v>34.6092</v>
       </c>
       <c r="H20" t="n">
         <v>45.05751734733581</v>
@@ -5014,55 +5036,55 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>18 aug</t>
+          <t>19 aug</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>179.14</v>
+        <v>181.7</v>
       </c>
       <c r="M20" t="n">
-        <v>183.9</v>
+        <v>186.98</v>
       </c>
       <c r="N20" t="n">
-        <v>177.98</v>
+        <v>180.38</v>
       </c>
       <c r="O20" t="n">
-        <v>182.5</v>
+        <v>185.9</v>
       </c>
       <c r="P20" t="n">
-        <v>148.8084</v>
+        <v>149.5324</v>
       </c>
       <c r="Q20" t="n">
-        <v>168.3358</v>
+        <v>168.1618</v>
       </c>
       <c r="R20" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S20" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>17 aug</t>
+          <t>18 aug</t>
         </is>
       </c>
       <c r="V20" t="n">
-        <v>489.2191</v>
+        <v>480.6352</v>
       </c>
       <c r="W20" t="n">
-        <v>491.7343</v>
+        <v>483.3601</v>
       </c>
       <c r="X20" t="n">
-        <v>477.5111</v>
+        <v>476.2534</v>
       </c>
       <c r="Y20" t="n">
-        <v>479.4474</v>
+        <v>480.725</v>
       </c>
       <c r="Z20" t="n">
-        <v>413.044</v>
+        <v>414.3408</v>
       </c>
       <c r="AA20" t="n">
-        <v>430.2151</v>
+        <v>429.933</v>
       </c>
       <c r="AB20" t="n">
         <v>535.3375423278808</v>
@@ -5074,26 +5096,26 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>19 aug</t>
+          <t>20 aug</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>39.835</v>
+        <v>39.865</v>
       </c>
       <c r="C21" t="n">
-        <v>40.14</v>
+        <v>40.51</v>
       </c>
       <c r="D21" t="n">
-        <v>39.74</v>
+        <v>39.8</v>
       </c>
       <c r="E21" t="n">
-        <v>39.94</v>
+        <v>40.28</v>
       </c>
       <c r="F21" t="n">
-        <v>36.6336</v>
+        <v>36.6884</v>
       </c>
       <c r="G21" t="n">
-        <v>34.6092</v>
+        <v>34.6545</v>
       </c>
       <c r="H21" t="n">
         <v>45.05751734733581</v>
@@ -5103,55 +5125,55 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>19 aug</t>
+          <t>20 aug</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>181.7</v>
+        <v>183.78</v>
       </c>
       <c r="M21" t="n">
-        <v>186.98</v>
+        <v>186.1</v>
       </c>
       <c r="N21" t="n">
-        <v>180.38</v>
+        <v>182.52</v>
       </c>
       <c r="O21" t="n">
-        <v>185.9</v>
+        <v>185.64</v>
       </c>
       <c r="P21" t="n">
-        <v>149.5324</v>
+        <v>150.4472</v>
       </c>
       <c r="Q21" t="n">
-        <v>168.1618</v>
+        <v>167.9648</v>
       </c>
       <c r="R21" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S21" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>18 aug</t>
+          <t>19 aug</t>
         </is>
       </c>
       <c r="V21" t="n">
-        <v>480.6352</v>
+        <v>479.168</v>
       </c>
       <c r="W21" t="n">
-        <v>483.3601</v>
+        <v>488.3806</v>
       </c>
       <c r="X21" t="n">
-        <v>476.2534</v>
+        <v>478.4593</v>
       </c>
       <c r="Y21" t="n">
-        <v>480.725</v>
+        <v>483.4</v>
       </c>
       <c r="Z21" t="n">
-        <v>414.3408</v>
+        <v>415.7895</v>
       </c>
       <c r="AA21" t="n">
-        <v>429.933</v>
+        <v>429.7427</v>
       </c>
       <c r="AB21" t="n">
         <v>535.3375423278808</v>
@@ -5163,26 +5185,26 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20 aug</t>
+          <t>21 aug</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>39.865</v>
+        <v>40.1</v>
       </c>
       <c r="C22" t="n">
-        <v>40.51</v>
+        <v>40.37</v>
       </c>
       <c r="D22" t="n">
-        <v>39.8</v>
+        <v>39.84</v>
       </c>
       <c r="E22" t="n">
-        <v>40.28</v>
+        <v>39.91</v>
       </c>
       <c r="F22" t="n">
-        <v>36.6884</v>
+        <v>36.7478</v>
       </c>
       <c r="G22" t="n">
-        <v>34.6545</v>
+        <v>34.6988</v>
       </c>
       <c r="H22" t="n">
         <v>45.05751734733581</v>
@@ -5192,55 +5214,55 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>20 aug</t>
+          <t>21 aug</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>183.78</v>
+        <v>185.18</v>
       </c>
       <c r="M22" t="n">
-        <v>186.1</v>
+        <v>188.4</v>
       </c>
       <c r="N22" t="n">
-        <v>182.52</v>
+        <v>183.6</v>
       </c>
       <c r="O22" t="n">
-        <v>185.64</v>
+        <v>188.12</v>
       </c>
       <c r="P22" t="n">
-        <v>150.4472</v>
+        <v>151.4044</v>
       </c>
       <c r="Q22" t="n">
-        <v>167.9648</v>
+        <v>167.794</v>
       </c>
       <c r="R22" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S22" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>19 aug</t>
+          <t>20 aug</t>
         </is>
       </c>
       <c r="V22" t="n">
-        <v>479.168</v>
+        <v>483.3</v>
       </c>
       <c r="W22" t="n">
-        <v>488.3806</v>
+        <v>484.16</v>
       </c>
       <c r="X22" t="n">
-        <v>478.4593</v>
+        <v>479.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>483.4</v>
+        <v>481.15</v>
       </c>
       <c r="Z22" t="n">
-        <v>415.7895</v>
+        <v>417.3594</v>
       </c>
       <c r="AA22" t="n">
-        <v>429.7427</v>
+        <v>429.5805</v>
       </c>
       <c r="AB22" t="n">
         <v>535.3375423278808</v>
@@ -5252,26 +5274,26 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>21 aug</t>
+          <t>24 aug</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>40.1</v>
+        <v>39.88</v>
       </c>
       <c r="C23" t="n">
-        <v>40.37</v>
+        <v>40.085</v>
       </c>
       <c r="D23" t="n">
-        <v>39.84</v>
+        <v>39.68</v>
       </c>
       <c r="E23" t="n">
-        <v>39.91</v>
+        <v>39.775</v>
       </c>
       <c r="F23" t="n">
-        <v>36.7478</v>
+        <v>36.8369</v>
       </c>
       <c r="G23" t="n">
-        <v>34.6988</v>
+        <v>34.7421</v>
       </c>
       <c r="H23" t="n">
         <v>45.05751734733581</v>
@@ -5281,55 +5303,55 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>21 aug</t>
+          <t>24 aug</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>185.18</v>
+        <v>186.86</v>
       </c>
       <c r="M23" t="n">
-        <v>188.4</v>
+        <v>188.16</v>
       </c>
       <c r="N23" t="n">
-        <v>183.6</v>
+        <v>185.52</v>
       </c>
       <c r="O23" t="n">
-        <v>188.12</v>
+        <v>187.2</v>
       </c>
       <c r="P23" t="n">
-        <v>151.4044</v>
+        <v>152.2848</v>
       </c>
       <c r="Q23" t="n">
-        <v>167.794</v>
+        <v>167.6093</v>
       </c>
       <c r="R23" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S23" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>20 aug</t>
+          <t>21 aug</t>
         </is>
       </c>
       <c r="V23" t="n">
-        <v>483.3</v>
+        <v>479.88</v>
       </c>
       <c r="W23" t="n">
-        <v>484.16</v>
+        <v>486.36</v>
       </c>
       <c r="X23" t="n">
-        <v>479.5</v>
+        <v>478.53</v>
       </c>
       <c r="Y23" t="n">
-        <v>481.15</v>
+        <v>483.24</v>
       </c>
       <c r="Z23" t="n">
-        <v>417.3594</v>
+        <v>419.092</v>
       </c>
       <c r="AA23" t="n">
-        <v>429.5805</v>
+        <v>429.4327</v>
       </c>
       <c r="AB23" t="n">
         <v>535.3375423278808</v>
@@ -5341,26 +5363,26 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>24 aug</t>
+          <t>25 aug</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>39.88</v>
+        <v>39.77</v>
       </c>
       <c r="C24" t="n">
-        <v>40.085</v>
+        <v>39.915</v>
       </c>
       <c r="D24" t="n">
-        <v>39.68</v>
+        <v>39.385</v>
       </c>
       <c r="E24" t="n">
-        <v>39.775</v>
+        <v>39.6</v>
       </c>
       <c r="F24" t="n">
-        <v>36.8369</v>
+        <v>36.926</v>
       </c>
       <c r="G24" t="n">
-        <v>34.7421</v>
+        <v>34.783</v>
       </c>
       <c r="H24" t="n">
         <v>45.05751734733581</v>
@@ -5370,55 +5392,55 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>24 aug</t>
+          <t>25 aug</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>186.86</v>
+        <v>186.4</v>
       </c>
       <c r="M24" t="n">
-        <v>188.16</v>
+        <v>187.62</v>
       </c>
       <c r="N24" t="n">
-        <v>185.52</v>
+        <v>182.74</v>
       </c>
       <c r="O24" t="n">
-        <v>187.2</v>
+        <v>185.46</v>
       </c>
       <c r="P24" t="n">
-        <v>152.2848</v>
+        <v>153.136</v>
       </c>
       <c r="Q24" t="n">
-        <v>167.6093</v>
+        <v>167.4651</v>
       </c>
       <c r="R24" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S24" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>21 aug</t>
+          <t>24 aug</t>
         </is>
       </c>
       <c r="V24" t="n">
-        <v>479.88</v>
+        <v>483.21</v>
       </c>
       <c r="W24" t="n">
-        <v>486.36</v>
+        <v>490.61</v>
       </c>
       <c r="X24" t="n">
-        <v>478.53</v>
+        <v>481.86</v>
       </c>
       <c r="Y24" t="n">
-        <v>483.24</v>
+        <v>487.31</v>
       </c>
       <c r="Z24" t="n">
-        <v>419.092</v>
+        <v>421.046</v>
       </c>
       <c r="AA24" t="n">
-        <v>429.4327</v>
+        <v>429.3185</v>
       </c>
       <c r="AB24" t="n">
         <v>535.3375423278808</v>
@@ -5430,26 +5452,26 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>25 aug</t>
+          <t>26 aug</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>39.77</v>
+        <v>39.275</v>
       </c>
       <c r="C25" t="n">
-        <v>39.915</v>
+        <v>39.47</v>
       </c>
       <c r="D25" t="n">
-        <v>39.385</v>
+        <v>38.91</v>
       </c>
       <c r="E25" t="n">
-        <v>39.6</v>
+        <v>39.42</v>
       </c>
       <c r="F25" t="n">
-        <v>36.926</v>
+        <v>37.0192</v>
       </c>
       <c r="G25" t="n">
-        <v>34.783</v>
+        <v>34.8202</v>
       </c>
       <c r="H25" t="n">
         <v>45.05751734733581</v>
@@ -5459,55 +5481,55 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>25 aug</t>
+          <t>26 aug</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>186.4</v>
+        <v>179.92</v>
       </c>
       <c r="M25" t="n">
-        <v>187.62</v>
+        <v>182.16</v>
       </c>
       <c r="N25" t="n">
-        <v>182.74</v>
+        <v>176.82</v>
       </c>
       <c r="O25" t="n">
-        <v>185.46</v>
+        <v>180.02</v>
       </c>
       <c r="P25" t="n">
-        <v>153.136</v>
+        <v>153.9128</v>
       </c>
       <c r="Q25" t="n">
-        <v>167.4651</v>
+        <v>167.3049</v>
       </c>
       <c r="R25" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S25" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>24 aug</t>
+          <t>25 aug</t>
         </is>
       </c>
       <c r="V25" t="n">
-        <v>483.21</v>
+        <v>485.44</v>
       </c>
       <c r="W25" t="n">
-        <v>490.61</v>
+        <v>492.44</v>
       </c>
       <c r="X25" t="n">
-        <v>481.86</v>
+        <v>484.3</v>
       </c>
       <c r="Y25" t="n">
-        <v>487.31</v>
+        <v>491.71</v>
       </c>
       <c r="Z25" t="n">
-        <v>421.046</v>
+        <v>423.0801</v>
       </c>
       <c r="AA25" t="n">
-        <v>429.3185</v>
+        <v>429.262</v>
       </c>
       <c r="AB25" t="n">
         <v>535.3375423278808</v>
@@ -5519,26 +5541,26 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>26 aug</t>
+          <t>27 aug</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>39.275</v>
+        <v>39.16</v>
       </c>
       <c r="C26" t="n">
-        <v>39.47</v>
+        <v>39.295</v>
       </c>
       <c r="D26" t="n">
-        <v>38.91</v>
+        <v>38.65</v>
       </c>
       <c r="E26" t="n">
-        <v>39.42</v>
+        <v>38.76</v>
       </c>
       <c r="F26" t="n">
-        <v>37.0192</v>
+        <v>37.117</v>
       </c>
       <c r="G26" t="n">
-        <v>34.8202</v>
+        <v>34.8559</v>
       </c>
       <c r="H26" t="n">
         <v>45.05751734733581</v>
@@ -5548,55 +5570,55 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>26 aug</t>
+          <t>27 aug</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>179.92</v>
+        <v>182.5</v>
       </c>
       <c r="M26" t="n">
-        <v>182.16</v>
+        <v>190.8</v>
       </c>
       <c r="N26" t="n">
-        <v>176.82</v>
+        <v>181.14</v>
       </c>
       <c r="O26" t="n">
-        <v>180.02</v>
+        <v>189.88</v>
       </c>
       <c r="P26" t="n">
-        <v>153.9128</v>
+        <v>155.0132</v>
       </c>
       <c r="Q26" t="n">
-        <v>167.3049</v>
+        <v>167.1911</v>
       </c>
       <c r="R26" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S26" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>25 aug</t>
+          <t>26 aug</t>
         </is>
       </c>
       <c r="V26" t="n">
-        <v>485.44</v>
+        <v>487.85</v>
       </c>
       <c r="W26" t="n">
-        <v>492.44</v>
+        <v>497.4</v>
       </c>
       <c r="X26" t="n">
-        <v>484.3</v>
+        <v>487.31</v>
       </c>
       <c r="Y26" t="n">
-        <v>491.71</v>
+        <v>496.37</v>
       </c>
       <c r="Z26" t="n">
-        <v>423.0801</v>
+        <v>425.0273</v>
       </c>
       <c r="AA26" t="n">
-        <v>429.262</v>
+        <v>429.2786</v>
       </c>
       <c r="AB26" t="n">
         <v>535.3375423278808</v>
@@ -5608,26 +5630,26 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>27 aug</t>
+          <t>28 aug</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>39.16</v>
+        <v>39</v>
       </c>
       <c r="C27" t="n">
-        <v>39.295</v>
+        <v>39.18</v>
       </c>
       <c r="D27" t="n">
-        <v>38.65</v>
+        <v>38.845</v>
       </c>
       <c r="E27" t="n">
-        <v>38.76</v>
+        <v>39.145</v>
       </c>
       <c r="F27" t="n">
-        <v>37.117</v>
+        <v>37.2162</v>
       </c>
       <c r="G27" t="n">
-        <v>34.8559</v>
+        <v>34.8941</v>
       </c>
       <c r="H27" t="n">
         <v>45.05751734733581</v>
@@ -5637,55 +5659,55 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>27 aug</t>
+          <t>28 aug</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>182.5</v>
+        <v>189.5</v>
       </c>
       <c r="M27" t="n">
-        <v>190.8</v>
+        <v>191.94</v>
       </c>
       <c r="N27" t="n">
-        <v>181.14</v>
+        <v>187.98</v>
       </c>
       <c r="O27" t="n">
-        <v>189.88</v>
+        <v>191.32</v>
       </c>
       <c r="P27" t="n">
-        <v>155.0132</v>
+        <v>156.1568</v>
       </c>
       <c r="Q27" t="n">
-        <v>167.1911</v>
+        <v>167.0806</v>
       </c>
       <c r="R27" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S27" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>26 aug</t>
+          <t>27 aug</t>
         </is>
       </c>
       <c r="V27" t="n">
-        <v>487.85</v>
+        <v>494.88</v>
       </c>
       <c r="W27" t="n">
-        <v>497.4</v>
+        <v>506.48</v>
       </c>
       <c r="X27" t="n">
-        <v>487.31</v>
+        <v>490.08</v>
       </c>
       <c r="Y27" t="n">
-        <v>496.37</v>
+        <v>505.06</v>
       </c>
       <c r="Z27" t="n">
-        <v>425.0273</v>
+        <v>427.2667</v>
       </c>
       <c r="AA27" t="n">
-        <v>429.2786</v>
+        <v>429.3401</v>
       </c>
       <c r="AB27" t="n">
         <v>535.3375423278808</v>
@@ -5697,26 +5719,26 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>28 aug</t>
+          <t>31 aug</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>39</v>
+        <v>39.54</v>
       </c>
       <c r="C28" t="n">
-        <v>39.18</v>
+        <v>39.91</v>
       </c>
       <c r="D28" t="n">
-        <v>38.845</v>
+        <v>39.24</v>
       </c>
       <c r="E28" t="n">
-        <v>39.145</v>
+        <v>39.335</v>
       </c>
       <c r="F28" t="n">
-        <v>37.2162</v>
+        <v>37.3111</v>
       </c>
       <c r="G28" t="n">
-        <v>34.8941</v>
+        <v>34.9333</v>
       </c>
       <c r="H28" t="n">
         <v>45.05751734733581</v>
@@ -5726,55 +5748,55 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>28 aug</t>
+          <t>31 aug</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>189.5</v>
+        <v>188.46</v>
       </c>
       <c r="M28" t="n">
-        <v>191.94</v>
+        <v>192.12</v>
       </c>
       <c r="N28" t="n">
-        <v>187.98</v>
+        <v>188.2</v>
       </c>
       <c r="O28" t="n">
-        <v>191.32</v>
+        <v>190.9</v>
       </c>
       <c r="P28" t="n">
-        <v>156.1568</v>
+        <v>157.3304</v>
       </c>
       <c r="Q28" t="n">
-        <v>167.0806</v>
+        <v>166.9613</v>
       </c>
       <c r="R28" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S28" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>27 aug</t>
+          <t>28 aug</t>
         </is>
       </c>
       <c r="V28" t="n">
-        <v>494.88</v>
+        <v>505.33</v>
       </c>
       <c r="W28" t="n">
-        <v>506.48</v>
+        <v>517.78</v>
       </c>
       <c r="X28" t="n">
-        <v>490.08</v>
+        <v>504.87</v>
       </c>
       <c r="Y28" t="n">
-        <v>505.06</v>
+        <v>513.53</v>
       </c>
       <c r="Z28" t="n">
-        <v>427.2667</v>
+        <v>429.9734</v>
       </c>
       <c r="AA28" t="n">
-        <v>429.3401</v>
+        <v>429.3984</v>
       </c>
       <c r="AB28" t="n">
         <v>535.3375423278808</v>
@@ -5786,26 +5808,26 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>31 aug</t>
+          <t>1 sep</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>39.54</v>
+        <v>39.77</v>
       </c>
       <c r="C29" t="n">
-        <v>39.91</v>
+        <v>40.19</v>
       </c>
       <c r="D29" t="n">
-        <v>39.24</v>
+        <v>39.645</v>
       </c>
       <c r="E29" t="n">
-        <v>39.335</v>
+        <v>40.155</v>
       </c>
       <c r="F29" t="n">
-        <v>37.3111</v>
+        <v>37.4239</v>
       </c>
       <c r="G29" t="n">
-        <v>34.9333</v>
+        <v>34.9763</v>
       </c>
       <c r="H29" t="n">
         <v>45.05751734733581</v>
@@ -5815,55 +5837,55 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>31 aug</t>
+          <t>1 sep</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>188.46</v>
+        <v>186</v>
       </c>
       <c r="M29" t="n">
-        <v>192.12</v>
+        <v>187.86</v>
       </c>
       <c r="N29" t="n">
-        <v>188.2</v>
+        <v>183.32</v>
       </c>
       <c r="O29" t="n">
-        <v>190.9</v>
+        <v>184.26</v>
       </c>
       <c r="P29" t="n">
-        <v>157.3304</v>
+        <v>158.3252</v>
       </c>
       <c r="Q29" t="n">
-        <v>166.9613</v>
+        <v>166.8103</v>
       </c>
       <c r="R29" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S29" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>28 aug</t>
+          <t>31 aug</t>
         </is>
       </c>
       <c r="V29" t="n">
-        <v>505.33</v>
+        <v>510.38</v>
       </c>
       <c r="W29" t="n">
-        <v>517.78</v>
+        <v>512.1900000000001</v>
       </c>
       <c r="X29" t="n">
-        <v>504.87</v>
+        <v>506.39</v>
       </c>
       <c r="Y29" t="n">
-        <v>513.53</v>
+        <v>507.29</v>
       </c>
       <c r="Z29" t="n">
-        <v>429.9734</v>
+        <v>432.5454</v>
       </c>
       <c r="AA29" t="n">
-        <v>429.3984</v>
+        <v>429.4122</v>
       </c>
       <c r="AB29" t="n">
         <v>535.3375423278808</v>
@@ -5875,26 +5897,26 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1 sep</t>
+          <t>2 sep</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>39.77</v>
+        <v>40.35</v>
       </c>
       <c r="C30" t="n">
-        <v>40.19</v>
+        <v>40.615</v>
       </c>
       <c r="D30" t="n">
-        <v>39.645</v>
+        <v>39.975</v>
       </c>
       <c r="E30" t="n">
-        <v>40.155</v>
+        <v>40.21</v>
       </c>
       <c r="F30" t="n">
-        <v>37.4239</v>
+        <v>37.5499</v>
       </c>
       <c r="G30" t="n">
-        <v>34.9763</v>
+        <v>35.0217</v>
       </c>
       <c r="H30" t="n">
         <v>45.05751734733581</v>
@@ -5904,55 +5926,55 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>1 sep</t>
+          <t>2 sep</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>186</v>
+        <v>182.18</v>
       </c>
       <c r="M30" t="n">
-        <v>187.86</v>
+        <v>184.7</v>
       </c>
       <c r="N30" t="n">
-        <v>183.32</v>
+        <v>180.72</v>
       </c>
       <c r="O30" t="n">
-        <v>184.26</v>
+        <v>181.44</v>
       </c>
       <c r="P30" t="n">
-        <v>158.3252</v>
+        <v>159.2568</v>
       </c>
       <c r="Q30" t="n">
-        <v>166.8103</v>
+        <v>166.6796</v>
       </c>
       <c r="R30" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S30" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>31 aug</t>
+          <t>1 sep</t>
         </is>
       </c>
       <c r="V30" t="n">
-        <v>510.38</v>
+        <v>497.52</v>
       </c>
       <c r="W30" t="n">
-        <v>512.1900000000001</v>
+        <v>505.97</v>
       </c>
       <c r="X30" t="n">
-        <v>506.39</v>
+        <v>496.78</v>
       </c>
       <c r="Y30" t="n">
-        <v>507.29</v>
+        <v>501.02</v>
       </c>
       <c r="Z30" t="n">
-        <v>432.5454</v>
+        <v>435.2328</v>
       </c>
       <c r="AA30" t="n">
-        <v>429.4122</v>
+        <v>429.3825</v>
       </c>
       <c r="AB30" t="n">
         <v>535.3375423278808</v>
@@ -5964,26 +5986,26 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2 sep</t>
+          <t>3 sep</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>40.35</v>
+        <v>40.095</v>
       </c>
       <c r="C31" t="n">
-        <v>40.615</v>
+        <v>40.215</v>
       </c>
       <c r="D31" t="n">
-        <v>39.975</v>
+        <v>39.54</v>
       </c>
       <c r="E31" t="n">
-        <v>40.21</v>
+        <v>40.04</v>
       </c>
       <c r="F31" t="n">
-        <v>37.5499</v>
+        <v>37.6767</v>
       </c>
       <c r="G31" t="n">
-        <v>35.0217</v>
+        <v>35.0679</v>
       </c>
       <c r="H31" t="n">
         <v>45.05751734733581</v>
@@ -5993,55 +6015,55 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2 sep</t>
+          <t>3 sep</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>182.18</v>
+        <v>182.08</v>
       </c>
       <c r="M31" t="n">
-        <v>184.7</v>
+        <v>187.56</v>
       </c>
       <c r="N31" t="n">
-        <v>180.72</v>
+        <v>182</v>
       </c>
       <c r="O31" t="n">
-        <v>181.44</v>
+        <v>185.58</v>
       </c>
       <c r="P31" t="n">
-        <v>159.2568</v>
+        <v>160.3228</v>
       </c>
       <c r="Q31" t="n">
-        <v>166.6796</v>
+        <v>166.5898</v>
       </c>
       <c r="R31" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S31" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>1 sep</t>
+          <t>2 sep</t>
         </is>
       </c>
       <c r="V31" t="n">
-        <v>497.52</v>
+        <v>499.85</v>
       </c>
       <c r="W31" t="n">
-        <v>505.97</v>
+        <v>500.27</v>
       </c>
       <c r="X31" t="n">
-        <v>496.78</v>
+        <v>493.81</v>
       </c>
       <c r="Y31" t="n">
-        <v>501.02</v>
+        <v>496.82</v>
       </c>
       <c r="Z31" t="n">
-        <v>435.2328</v>
+        <v>437.7045</v>
       </c>
       <c r="AA31" t="n">
-        <v>429.3825</v>
+        <v>429.3706</v>
       </c>
       <c r="AB31" t="n">
         <v>535.3375423278808</v>
@@ -6053,26 +6075,26 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3 sep</t>
+          <t>4 sep</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>40.095</v>
+        <v>40.145</v>
       </c>
       <c r="C32" t="n">
-        <v>40.215</v>
+        <v>40.28</v>
       </c>
       <c r="D32" t="n">
-        <v>39.54</v>
+        <v>39.665</v>
       </c>
       <c r="E32" t="n">
-        <v>40.04</v>
+        <v>40.105</v>
       </c>
       <c r="F32" t="n">
-        <v>37.6767</v>
+        <v>37.8115</v>
       </c>
       <c r="G32" t="n">
-        <v>35.0679</v>
+        <v>35.113</v>
       </c>
       <c r="H32" t="n">
         <v>45.05751734733581</v>
@@ -6082,55 +6104,55 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>3 sep</t>
+          <t>4 sep</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>182.08</v>
+        <v>187.8</v>
       </c>
       <c r="M32" t="n">
-        <v>187.56</v>
+        <v>189.9</v>
       </c>
       <c r="N32" t="n">
-        <v>182</v>
+        <v>184.96</v>
       </c>
       <c r="O32" t="n">
-        <v>185.58</v>
+        <v>185.68</v>
       </c>
       <c r="P32" t="n">
-        <v>160.3228</v>
+        <v>161.3336</v>
       </c>
       <c r="Q32" t="n">
-        <v>166.5898</v>
+        <v>166.5086</v>
       </c>
       <c r="R32" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S32" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>2 sep</t>
+          <t>3 sep</t>
         </is>
       </c>
       <c r="V32" t="n">
-        <v>499.85</v>
+        <v>501.66</v>
       </c>
       <c r="W32" t="n">
-        <v>500.27</v>
+        <v>515.65</v>
       </c>
       <c r="X32" t="n">
-        <v>493.81</v>
+        <v>500.8</v>
       </c>
       <c r="Y32" t="n">
-        <v>496.82</v>
+        <v>510.12</v>
       </c>
       <c r="Z32" t="n">
-        <v>437.7045</v>
+        <v>440.6114</v>
       </c>
       <c r="AA32" t="n">
-        <v>429.3706</v>
+        <v>429.3912</v>
       </c>
       <c r="AB32" t="n">
         <v>535.3375423278808</v>
@@ -6142,26 +6164,26 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4 sep</t>
+          <t>7 sep</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>40.145</v>
+        <v>40.26</v>
       </c>
       <c r="C33" t="n">
-        <v>40.28</v>
+        <v>40.845</v>
       </c>
       <c r="D33" t="n">
-        <v>39.665</v>
+        <v>40.12</v>
       </c>
       <c r="E33" t="n">
-        <v>40.105</v>
+        <v>40.56</v>
       </c>
       <c r="F33" t="n">
-        <v>37.8115</v>
+        <v>37.9551</v>
       </c>
       <c r="G33" t="n">
-        <v>35.113</v>
+        <v>35.1619</v>
       </c>
       <c r="H33" t="n">
         <v>45.05751734733581</v>
@@ -6171,55 +6193,55 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>4 sep</t>
+          <t>7 sep</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>187.8</v>
+        <v>183.56</v>
       </c>
       <c r="M33" t="n">
-        <v>189.9</v>
+        <v>184.3</v>
       </c>
       <c r="N33" t="n">
-        <v>184.96</v>
+        <v>179.92</v>
       </c>
       <c r="O33" t="n">
-        <v>185.68</v>
+        <v>182.8</v>
       </c>
       <c r="P33" t="n">
-        <v>161.3336</v>
+        <v>162.2568</v>
       </c>
       <c r="Q33" t="n">
-        <v>166.5086</v>
+        <v>166.4122</v>
       </c>
       <c r="R33" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S33" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>3 sep</t>
+          <t>4 sep</t>
         </is>
       </c>
       <c r="V33" t="n">
-        <v>501.66</v>
+        <v>510</v>
       </c>
       <c r="W33" t="n">
-        <v>515.65</v>
+        <v>511</v>
       </c>
       <c r="X33" t="n">
-        <v>500.8</v>
+        <v>499.36</v>
       </c>
       <c r="Y33" t="n">
-        <v>510.12</v>
+        <v>499.7</v>
       </c>
       <c r="Z33" t="n">
-        <v>440.6114</v>
+        <v>443.5621</v>
       </c>
       <c r="AA33" t="n">
-        <v>429.3912</v>
+        <v>429.3729</v>
       </c>
       <c r="AB33" t="n">
         <v>535.3375423278808</v>
@@ -6231,26 +6253,26 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>7 sep</t>
+          <t>8 sep</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>40.26</v>
+        <v>40.83</v>
       </c>
       <c r="C34" t="n">
-        <v>40.845</v>
+        <v>41.18</v>
       </c>
       <c r="D34" t="n">
-        <v>40.12</v>
+        <v>40.6325</v>
       </c>
       <c r="E34" t="n">
-        <v>40.56</v>
+        <v>40.855</v>
       </c>
       <c r="F34" t="n">
-        <v>37.9551</v>
+        <v>38.0977</v>
       </c>
       <c r="G34" t="n">
-        <v>35.1619</v>
+        <v>35.2131</v>
       </c>
       <c r="H34" t="n">
         <v>45.05751734733581</v>
@@ -6260,55 +6282,55 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>7 sep</t>
+          <t>8 sep</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>183.56</v>
+        <v>182.32</v>
       </c>
       <c r="M34" t="n">
-        <v>184.3</v>
+        <v>183.76</v>
       </c>
       <c r="N34" t="n">
-        <v>179.92</v>
+        <v>180.02</v>
       </c>
       <c r="O34" t="n">
-        <v>182.8</v>
+        <v>181.7</v>
       </c>
       <c r="P34" t="n">
-        <v>162.2568</v>
+        <v>163.2108</v>
       </c>
       <c r="Q34" t="n">
-        <v>166.4122</v>
+        <v>166.3049</v>
       </c>
       <c r="R34" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S34" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>4 sep</t>
+          <t>8 sep</t>
         </is>
       </c>
       <c r="V34" t="n">
-        <v>510</v>
+        <v>493.01</v>
       </c>
       <c r="W34" t="n">
-        <v>511</v>
+        <v>495.19</v>
       </c>
       <c r="X34" t="n">
-        <v>499.36</v>
+        <v>490.15</v>
       </c>
       <c r="Y34" t="n">
-        <v>499.7</v>
+        <v>493.95</v>
       </c>
       <c r="Z34" t="n">
-        <v>443.5621</v>
+        <v>445.9957</v>
       </c>
       <c r="AA34" t="n">
-        <v>429.3729</v>
+        <v>429.3939</v>
       </c>
       <c r="AB34" t="n">
         <v>535.3375423278808</v>
@@ -6320,26 +6342,26 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>8 sep</t>
+          <t>9 sep</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>40.83</v>
+        <v>41.1</v>
       </c>
       <c r="C35" t="n">
-        <v>41.18</v>
+        <v>41.385</v>
       </c>
       <c r="D35" t="n">
-        <v>40.6325</v>
+        <v>40.85</v>
       </c>
       <c r="E35" t="n">
-        <v>40.855</v>
+        <v>40.94</v>
       </c>
       <c r="F35" t="n">
-        <v>38.0977</v>
+        <v>38.2513</v>
       </c>
       <c r="G35" t="n">
-        <v>35.2131</v>
+        <v>35.2646</v>
       </c>
       <c r="H35" t="n">
         <v>45.05751734733581</v>
@@ -6349,55 +6371,55 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>8 sep</t>
+          <t>9 sep</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>182.32</v>
+        <v>183</v>
       </c>
       <c r="M35" t="n">
-        <v>183.76</v>
+        <v>187.04</v>
       </c>
       <c r="N35" t="n">
-        <v>180.02</v>
+        <v>181.36</v>
       </c>
       <c r="O35" t="n">
-        <v>181.7</v>
+        <v>182.86</v>
       </c>
       <c r="P35" t="n">
-        <v>163.2108</v>
+        <v>164.0504</v>
       </c>
       <c r="Q35" t="n">
-        <v>166.3049</v>
+        <v>166.2113</v>
       </c>
       <c r="R35" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S35" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>8 sep</t>
+          <t>9 sep</t>
         </is>
       </c>
       <c r="V35" t="n">
-        <v>493.01</v>
+        <v>493.07</v>
       </c>
       <c r="W35" t="n">
-        <v>495.19</v>
+        <v>494.39</v>
       </c>
       <c r="X35" t="n">
-        <v>490.15</v>
+        <v>489.8</v>
       </c>
       <c r="Y35" t="n">
-        <v>493.95</v>
+        <v>491.65</v>
       </c>
       <c r="Z35" t="n">
-        <v>445.9957</v>
+        <v>448.4712</v>
       </c>
       <c r="AA35" t="n">
-        <v>429.3939</v>
+        <v>429.4364</v>
       </c>
       <c r="AB35" t="n">
         <v>535.3375423278808</v>
@@ -6409,26 +6431,26 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>9 sep</t>
+          <t>10 sep</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>41.1</v>
+        <v>40.98</v>
       </c>
       <c r="C36" t="n">
-        <v>41.385</v>
+        <v>41.77</v>
       </c>
       <c r="D36" t="n">
-        <v>40.85</v>
+        <v>40.93</v>
       </c>
       <c r="E36" t="n">
-        <v>40.94</v>
+        <v>41.23</v>
       </c>
       <c r="F36" t="n">
-        <v>38.2513</v>
+        <v>38.4034</v>
       </c>
       <c r="G36" t="n">
-        <v>35.2646</v>
+        <v>35.3174</v>
       </c>
       <c r="H36" t="n">
         <v>45.05751734733581</v>
@@ -6438,55 +6460,55 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>9 sep</t>
+          <t>10 sep</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="M36" t="n">
-        <v>187.04</v>
+        <v>180.4</v>
       </c>
       <c r="N36" t="n">
-        <v>181.36</v>
+        <v>176.2</v>
       </c>
       <c r="O36" t="n">
-        <v>182.86</v>
+        <v>177.82</v>
       </c>
       <c r="P36" t="n">
-        <v>164.0504</v>
+        <v>164.7724</v>
       </c>
       <c r="Q36" t="n">
-        <v>166.2113</v>
+        <v>166.0803</v>
       </c>
       <c r="R36" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S36" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>9 sep</t>
+          <t>10 sep</t>
         </is>
       </c>
       <c r="V36" t="n">
-        <v>493.07</v>
+        <v>488.32</v>
       </c>
       <c r="W36" t="n">
-        <v>494.39</v>
+        <v>494.52</v>
       </c>
       <c r="X36" t="n">
-        <v>489.8</v>
+        <v>486</v>
       </c>
       <c r="Y36" t="n">
-        <v>491.65</v>
+        <v>492.44</v>
       </c>
       <c r="Z36" t="n">
-        <v>448.4712</v>
+        <v>450.8736</v>
       </c>
       <c r="AA36" t="n">
-        <v>429.4364</v>
+        <v>429.5215</v>
       </c>
       <c r="AB36" t="n">
         <v>535.3375423278808</v>
@@ -6498,26 +6520,26 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10 sep</t>
+          <t>11 sep</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>40.98</v>
+        <v>41.345</v>
       </c>
       <c r="C37" t="n">
-        <v>41.77</v>
+        <v>41.715</v>
       </c>
       <c r="D37" t="n">
-        <v>40.93</v>
+        <v>40.905</v>
       </c>
       <c r="E37" t="n">
-        <v>41.23</v>
+        <v>41.415</v>
       </c>
       <c r="F37" t="n">
-        <v>38.4034</v>
+        <v>38.5608</v>
       </c>
       <c r="G37" t="n">
-        <v>35.3174</v>
+        <v>35.3717</v>
       </c>
       <c r="H37" t="n">
         <v>45.05751734733581</v>
@@ -6527,55 +6549,55 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>10 sep</t>
+          <t>11 sep</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>180</v>
+        <v>175.68</v>
       </c>
       <c r="M37" t="n">
-        <v>180.4</v>
+        <v>178.84</v>
       </c>
       <c r="N37" t="n">
-        <v>176.2</v>
+        <v>172.16</v>
       </c>
       <c r="O37" t="n">
-        <v>177.82</v>
+        <v>177.26</v>
       </c>
       <c r="P37" t="n">
-        <v>164.7724</v>
+        <v>165.5248</v>
       </c>
       <c r="Q37" t="n">
-        <v>166.0803</v>
+        <v>165.9594</v>
       </c>
       <c r="R37" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S37" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>10 sep</t>
+          <t>11 sep</t>
         </is>
       </c>
       <c r="V37" t="n">
-        <v>488.32</v>
+        <v>495.65</v>
       </c>
       <c r="W37" t="n">
-        <v>494.52</v>
+        <v>498.97</v>
       </c>
       <c r="X37" t="n">
-        <v>486</v>
+        <v>492.58</v>
       </c>
       <c r="Y37" t="n">
-        <v>492.44</v>
+        <v>495.63</v>
       </c>
       <c r="Z37" t="n">
-        <v>450.8736</v>
+        <v>453.115</v>
       </c>
       <c r="AA37" t="n">
-        <v>429.5215</v>
+        <v>429.654</v>
       </c>
       <c r="AB37" t="n">
         <v>535.3375423278808</v>
@@ -6587,26 +6609,26 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>11 sep</t>
+          <t>14 sep</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>41.345</v>
+        <v>41.88</v>
       </c>
       <c r="C38" t="n">
-        <v>41.715</v>
+        <v>42.285</v>
       </c>
       <c r="D38" t="n">
-        <v>40.905</v>
+        <v>41.8</v>
       </c>
       <c r="E38" t="n">
-        <v>41.415</v>
+        <v>41.91</v>
       </c>
       <c r="F38" t="n">
-        <v>38.5608</v>
+        <v>38.7226</v>
       </c>
       <c r="G38" t="n">
-        <v>35.3717</v>
+        <v>35.4269</v>
       </c>
       <c r="H38" t="n">
         <v>45.05751734733581</v>
@@ -6616,55 +6638,55 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>11 sep</t>
+          <t>14 sep</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>175.68</v>
+        <v>180.82</v>
       </c>
       <c r="M38" t="n">
-        <v>178.84</v>
+        <v>186.76</v>
       </c>
       <c r="N38" t="n">
-        <v>172.16</v>
+        <v>180.82</v>
       </c>
       <c r="O38" t="n">
-        <v>177.26</v>
+        <v>186.26</v>
       </c>
       <c r="P38" t="n">
-        <v>165.5248</v>
+        <v>166.4488</v>
       </c>
       <c r="Q38" t="n">
-        <v>165.9594</v>
+        <v>165.8745</v>
       </c>
       <c r="R38" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S38" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>11 sep</t>
+          <t>14 sep</t>
         </is>
       </c>
       <c r="V38" t="n">
-        <v>495.65</v>
+        <v>497.06</v>
       </c>
       <c r="W38" t="n">
-        <v>498.97</v>
+        <v>509.95</v>
       </c>
       <c r="X38" t="n">
-        <v>492.58</v>
+        <v>495.34</v>
       </c>
       <c r="Y38" t="n">
-        <v>495.63</v>
+        <v>505.41</v>
       </c>
       <c r="Z38" t="n">
-        <v>453.115</v>
+        <v>455.4281</v>
       </c>
       <c r="AA38" t="n">
-        <v>429.6539</v>
+        <v>429.8259</v>
       </c>
       <c r="AB38" t="n">
         <v>535.3375423278808</v>
@@ -6676,26 +6698,26 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>14 sep</t>
+          <t>15 sep</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>41.88</v>
+        <v>41.845</v>
       </c>
       <c r="C39" t="n">
-        <v>42.285</v>
+        <v>42.7</v>
       </c>
       <c r="D39" t="n">
-        <v>41.8</v>
+        <v>41.72</v>
       </c>
       <c r="E39" t="n">
-        <v>41.91</v>
+        <v>42.7</v>
       </c>
       <c r="F39" t="n">
-        <v>38.7226</v>
+        <v>38.8782</v>
       </c>
       <c r="G39" t="n">
-        <v>35.4269</v>
+        <v>35.4854</v>
       </c>
       <c r="H39" t="n">
         <v>45.05751734733581</v>
@@ -6705,55 +6727,55 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>14 sep</t>
+          <t>15 sep</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>180.82</v>
+        <v>186.64</v>
       </c>
       <c r="M39" t="n">
-        <v>186.76</v>
+        <v>187.26</v>
       </c>
       <c r="N39" t="n">
-        <v>180.82</v>
+        <v>183.2</v>
       </c>
       <c r="O39" t="n">
-        <v>186.26</v>
+        <v>187.08</v>
       </c>
       <c r="P39" t="n">
-        <v>166.4488</v>
+        <v>167.3124</v>
       </c>
       <c r="Q39" t="n">
-        <v>165.8745</v>
+        <v>165.7921</v>
       </c>
       <c r="R39" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S39" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>14 sep</t>
+          <t>15 sep</t>
         </is>
       </c>
       <c r="V39" t="n">
-        <v>497.06</v>
+        <v>500.06</v>
       </c>
       <c r="W39" t="n">
-        <v>509.95</v>
+        <v>505.9</v>
       </c>
       <c r="X39" t="n">
-        <v>495.34</v>
+        <v>495.54</v>
       </c>
       <c r="Y39" t="n">
-        <v>505.41</v>
+        <v>497.12</v>
       </c>
       <c r="Z39" t="n">
-        <v>455.4281</v>
+        <v>457.6502</v>
       </c>
       <c r="AA39" t="n">
-        <v>429.8259</v>
+        <v>429.9416</v>
       </c>
       <c r="AB39" t="n">
         <v>535.3375423278808</v>
@@ -6765,26 +6787,26 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>15 sep</t>
+          <t>16 sep</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>41.845</v>
+        <v>42.72</v>
       </c>
       <c r="C40" t="n">
-        <v>42.7</v>
+        <v>42.85</v>
       </c>
       <c r="D40" t="n">
-        <v>41.72</v>
+        <v>41.67</v>
       </c>
       <c r="E40" t="n">
-        <v>42.7</v>
+        <v>41.825</v>
       </c>
       <c r="F40" t="n">
-        <v>38.8782</v>
+        <v>38.9989</v>
       </c>
       <c r="G40" t="n">
-        <v>35.4854</v>
+        <v>35.5403</v>
       </c>
       <c r="H40" t="n">
         <v>45.05751734733581</v>
@@ -6794,55 +6816,55 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>15 sep</t>
+          <t>16 sep</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>186.64</v>
+        <v>185.86</v>
       </c>
       <c r="M40" t="n">
-        <v>187.26</v>
+        <v>186.76</v>
       </c>
       <c r="N40" t="n">
-        <v>183.2</v>
+        <v>182.18</v>
       </c>
       <c r="O40" t="n">
-        <v>187.08</v>
+        <v>186.56</v>
       </c>
       <c r="P40" t="n">
-        <v>167.3124</v>
+        <v>168.2844</v>
       </c>
       <c r="Q40" t="n">
-        <v>165.7921</v>
+        <v>165.6996</v>
       </c>
       <c r="R40" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S40" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>15 sep</t>
+          <t>16 sep</t>
         </is>
       </c>
       <c r="V40" t="n">
-        <v>500.06</v>
+        <v>493.03</v>
       </c>
       <c r="W40" t="n">
-        <v>505.9</v>
+        <v>495.97</v>
       </c>
       <c r="X40" t="n">
-        <v>495.54</v>
+        <v>487.23</v>
       </c>
       <c r="Y40" t="n">
-        <v>497.12</v>
+        <v>490.3</v>
       </c>
       <c r="Z40" t="n">
-        <v>457.6502</v>
+        <v>459.694</v>
       </c>
       <c r="AA40" t="n">
-        <v>429.9416</v>
+        <v>429.9809</v>
       </c>
       <c r="AB40" t="n">
         <v>535.3375423278808</v>
@@ -6854,26 +6876,26 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>16 sep</t>
+          <t>17 sep</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>42.72</v>
+        <v>41.58</v>
       </c>
       <c r="C41" t="n">
-        <v>42.85</v>
+        <v>42.055</v>
       </c>
       <c r="D41" t="n">
-        <v>41.67</v>
+        <v>41.38</v>
       </c>
       <c r="E41" t="n">
-        <v>41.825</v>
+        <v>41.56</v>
       </c>
       <c r="F41" t="n">
-        <v>38.9989</v>
+        <v>39.1225</v>
       </c>
       <c r="G41" t="n">
-        <v>35.5403</v>
+        <v>35.5926</v>
       </c>
       <c r="H41" t="n">
         <v>45.05751734733581</v>
@@ -6883,55 +6905,55 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>16 sep</t>
+          <t>17 sep</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>185.86</v>
+        <v>188.54</v>
       </c>
       <c r="M41" t="n">
-        <v>186.76</v>
+        <v>189.2</v>
       </c>
       <c r="N41" t="n">
-        <v>182.18</v>
+        <v>184.62</v>
       </c>
       <c r="O41" t="n">
-        <v>186.56</v>
+        <v>188</v>
       </c>
       <c r="P41" t="n">
-        <v>168.2844</v>
+        <v>169.2896</v>
       </c>
       <c r="Q41" t="n">
-        <v>165.6996</v>
+        <v>165.6125</v>
       </c>
       <c r="R41" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S41" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>16 sep</t>
+          <t>17 sep</t>
         </is>
       </c>
       <c r="V41" t="n">
-        <v>493.03</v>
+        <v>497.8</v>
       </c>
       <c r="W41" t="n">
-        <v>495.97</v>
+        <v>501.47</v>
       </c>
       <c r="X41" t="n">
-        <v>487.23</v>
+        <v>493.17</v>
       </c>
       <c r="Y41" t="n">
-        <v>490.3</v>
+        <v>497.75</v>
       </c>
       <c r="Z41" t="n">
-        <v>459.694</v>
+        <v>461.9966</v>
       </c>
       <c r="AA41" t="n">
-        <v>429.9809</v>
+        <v>430.0251</v>
       </c>
       <c r="AB41" t="n">
         <v>535.3375423278808</v>
@@ -6943,26 +6965,26 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>17 sep</t>
+          <t>18 sep</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>41.58</v>
+        <v>41.465</v>
       </c>
       <c r="C42" t="n">
-        <v>42.055</v>
+        <v>41.5</v>
       </c>
       <c r="D42" t="n">
-        <v>41.38</v>
+        <v>40.955</v>
       </c>
       <c r="E42" t="n">
-        <v>41.56</v>
+        <v>41.315</v>
       </c>
       <c r="F42" t="n">
-        <v>39.1225</v>
+        <v>39.2414</v>
       </c>
       <c r="G42" t="n">
-        <v>35.5926</v>
+        <v>35.6436</v>
       </c>
       <c r="H42" t="n">
         <v>45.05751734733581</v>
@@ -6972,55 +6994,55 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>17 sep</t>
+          <t>18 sep</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>188.54</v>
+        <v>186.1</v>
       </c>
       <c r="M42" t="n">
-        <v>189.2</v>
+        <v>187.26</v>
       </c>
       <c r="N42" t="n">
-        <v>184.62</v>
+        <v>182.56</v>
       </c>
       <c r="O42" t="n">
-        <v>188</v>
+        <v>183.12</v>
       </c>
       <c r="P42" t="n">
-        <v>169.2896</v>
+        <v>170.2004</v>
       </c>
       <c r="Q42" t="n">
-        <v>165.6125</v>
+        <v>165.5062</v>
       </c>
       <c r="R42" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S42" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>17 sep</t>
+          <t>18 sep</t>
         </is>
       </c>
       <c r="V42" t="n">
-        <v>497.8</v>
+        <v>497.97</v>
       </c>
       <c r="W42" t="n">
-        <v>501.47</v>
+        <v>498.65</v>
       </c>
       <c r="X42" t="n">
-        <v>493.17</v>
+        <v>491.1</v>
       </c>
       <c r="Y42" t="n">
-        <v>497.75</v>
+        <v>493.78</v>
       </c>
       <c r="Z42" t="n">
-        <v>461.9966</v>
+        <v>464.1995</v>
       </c>
       <c r="AA42" t="n">
-        <v>430.0251</v>
+        <v>430.0757</v>
       </c>
       <c r="AB42" t="n">
         <v>535.3375423278808</v>
@@ -7032,26 +7054,26 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>18 sep</t>
+          <t>21 sep</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>41.465</v>
+        <v>41.04</v>
       </c>
       <c r="C43" t="n">
-        <v>41.5</v>
+        <v>41.4</v>
       </c>
       <c r="D43" t="n">
-        <v>40.955</v>
+        <v>40.775</v>
       </c>
       <c r="E43" t="n">
-        <v>41.315</v>
+        <v>40.775</v>
       </c>
       <c r="F43" t="n">
-        <v>39.2414</v>
+        <v>39.3341</v>
       </c>
       <c r="G43" t="n">
-        <v>35.6436</v>
+        <v>35.6939</v>
       </c>
       <c r="H43" t="n">
         <v>45.05751734733581</v>
@@ -7061,55 +7083,55 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>18 sep</t>
+          <t>21 sep</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>186.1</v>
+        <v>184.7</v>
       </c>
       <c r="M43" t="n">
-        <v>187.26</v>
+        <v>185.86</v>
       </c>
       <c r="N43" t="n">
-        <v>182.56</v>
+        <v>182.48</v>
       </c>
       <c r="O43" t="n">
-        <v>183.12</v>
+        <v>182.86</v>
       </c>
       <c r="P43" t="n">
-        <v>170.2004</v>
+        <v>171.0432</v>
       </c>
       <c r="Q43" t="n">
-        <v>165.5062</v>
+        <v>165.4052</v>
       </c>
       <c r="R43" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S43" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>18 sep</t>
+          <t>21 sep</t>
         </is>
       </c>
       <c r="V43" t="n">
-        <v>497.97</v>
+        <v>494.95</v>
       </c>
       <c r="W43" t="n">
-        <v>498.65</v>
+        <v>501.87</v>
       </c>
       <c r="X43" t="n">
-        <v>491.1</v>
+        <v>491.33</v>
       </c>
       <c r="Y43" t="n">
-        <v>493.78</v>
+        <v>501.61</v>
       </c>
       <c r="Z43" t="n">
-        <v>464.1995</v>
+        <v>466.5442</v>
       </c>
       <c r="AA43" t="n">
-        <v>430.0757</v>
+        <v>430.1492</v>
       </c>
       <c r="AB43" t="n">
         <v>535.3375423278808</v>
@@ -7121,26 +7143,26 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>21 sep</t>
+          <t>22 sep</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>41.04</v>
+        <v>40.84</v>
       </c>
       <c r="C44" t="n">
-        <v>41.4</v>
+        <v>41.165</v>
       </c>
       <c r="D44" t="n">
-        <v>40.775</v>
+        <v>40.215</v>
       </c>
       <c r="E44" t="n">
-        <v>40.775</v>
+        <v>41.01</v>
       </c>
       <c r="F44" t="n">
-        <v>39.3341</v>
+        <v>39.4244</v>
       </c>
       <c r="G44" t="n">
-        <v>35.6939</v>
+        <v>35.746</v>
       </c>
       <c r="H44" t="n">
         <v>45.05751734733581</v>
@@ -7150,55 +7172,55 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>21 sep</t>
+          <t>22 sep</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>184.7</v>
+        <v>182.14</v>
       </c>
       <c r="M44" t="n">
-        <v>185.86</v>
+        <v>187.48</v>
       </c>
       <c r="N44" t="n">
-        <v>182.48</v>
+        <v>181.52</v>
       </c>
       <c r="O44" t="n">
-        <v>182.86</v>
+        <v>182.32</v>
       </c>
       <c r="P44" t="n">
-        <v>171.0432</v>
+        <v>171.9552</v>
       </c>
       <c r="Q44" t="n">
-        <v>165.4052</v>
+        <v>165.2836</v>
       </c>
       <c r="R44" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S44" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>21 sep</t>
+          <t>22 sep</t>
         </is>
       </c>
       <c r="V44" t="n">
-        <v>494.95</v>
+        <v>507.32</v>
       </c>
       <c r="W44" t="n">
-        <v>501.87</v>
+        <v>508.5</v>
       </c>
       <c r="X44" t="n">
-        <v>491.33</v>
+        <v>493.65</v>
       </c>
       <c r="Y44" t="n">
-        <v>501.61</v>
+        <v>498</v>
       </c>
       <c r="Z44" t="n">
-        <v>466.5442</v>
+        <v>468.699</v>
       </c>
       <c r="AA44" t="n">
-        <v>430.1492</v>
+        <v>430.2656</v>
       </c>
       <c r="AB44" t="n">
         <v>535.3375423278808</v>
@@ -7210,26 +7232,26 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>22 sep</t>
+          <t>23 sep</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>40.84</v>
+        <v>41</v>
       </c>
       <c r="C45" t="n">
-        <v>41.165</v>
+        <v>41.755</v>
       </c>
       <c r="D45" t="n">
-        <v>40.215</v>
+        <v>40.995</v>
       </c>
       <c r="E45" t="n">
-        <v>41.01</v>
+        <v>41.69</v>
       </c>
       <c r="F45" t="n">
-        <v>39.4244</v>
+        <v>39.5272</v>
       </c>
       <c r="G45" t="n">
-        <v>35.746</v>
+        <v>35.8024</v>
       </c>
       <c r="H45" t="n">
         <v>45.05751734733581</v>
@@ -7239,55 +7261,55 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>22 sep</t>
+          <t>23 sep</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>182.14</v>
+        <v>184.9</v>
       </c>
       <c r="M45" t="n">
-        <v>187.48</v>
+        <v>187.8</v>
       </c>
       <c r="N45" t="n">
-        <v>181.52</v>
+        <v>183.48</v>
       </c>
       <c r="O45" t="n">
-        <v>182.32</v>
+        <v>186.46</v>
       </c>
       <c r="P45" t="n">
-        <v>171.9552</v>
+        <v>172.9448</v>
       </c>
       <c r="Q45" t="n">
-        <v>165.2836</v>
+        <v>165.1675</v>
       </c>
       <c r="R45" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S45" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>22 sep</t>
+          <t>23 sep</t>
         </is>
       </c>
       <c r="V45" t="n">
-        <v>507.32</v>
+        <v>500.76</v>
       </c>
       <c r="W45" t="n">
-        <v>508.5</v>
+        <v>509.44</v>
       </c>
       <c r="X45" t="n">
-        <v>493.65</v>
+        <v>495.88</v>
       </c>
       <c r="Y45" t="n">
-        <v>498</v>
+        <v>500.59</v>
       </c>
       <c r="Z45" t="n">
-        <v>468.699</v>
+        <v>471.0267</v>
       </c>
       <c r="AA45" t="n">
-        <v>430.2656</v>
+        <v>430.3795</v>
       </c>
       <c r="AB45" t="n">
         <v>535.3375423278808</v>
@@ -7299,26 +7321,26 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>23 sep</t>
+          <t>24 sep</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>41</v>
+        <v>41.825</v>
       </c>
       <c r="C46" t="n">
-        <v>41.755</v>
+        <v>42.52</v>
       </c>
       <c r="D46" t="n">
-        <v>40.995</v>
+        <v>41.78</v>
       </c>
       <c r="E46" t="n">
-        <v>41.69</v>
+        <v>42.43</v>
       </c>
       <c r="F46" t="n">
-        <v>39.5272</v>
+        <v>39.6382</v>
       </c>
       <c r="G46" t="n">
-        <v>35.8024</v>
+        <v>35.8638</v>
       </c>
       <c r="H46" t="n">
         <v>45.05751734733581</v>
@@ -7328,55 +7350,55 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>23 sep</t>
+          <t>24 sep</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>184.9</v>
+        <v>184.52</v>
       </c>
       <c r="M46" t="n">
-        <v>187.8</v>
+        <v>185.5</v>
       </c>
       <c r="N46" t="n">
-        <v>183.48</v>
+        <v>182.26</v>
       </c>
       <c r="O46" t="n">
-        <v>186.46</v>
+        <v>184.18</v>
       </c>
       <c r="P46" t="n">
-        <v>172.9448</v>
+        <v>173.8756</v>
       </c>
       <c r="Q46" t="n">
-        <v>165.1675</v>
+        <v>165.0554</v>
       </c>
       <c r="R46" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S46" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>23 sep</t>
+          <t>24 sep</t>
         </is>
       </c>
       <c r="V46" t="n">
-        <v>500.76</v>
+        <v>495.07</v>
       </c>
       <c r="W46" t="n">
-        <v>509.44</v>
+        <v>498.9</v>
       </c>
       <c r="X46" t="n">
-        <v>495.88</v>
+        <v>491.22</v>
       </c>
       <c r="Y46" t="n">
-        <v>500.59</v>
+        <v>497.93</v>
       </c>
       <c r="Z46" t="n">
-        <v>471.0267</v>
+        <v>473.0876</v>
       </c>
       <c r="AA46" t="n">
-        <v>430.3795</v>
+        <v>430.4686</v>
       </c>
       <c r="AB46" t="n">
         <v>535.3375423278808</v>
@@ -7388,26 +7410,26 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>24 sep</t>
+          <t>25 sep</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>41.825</v>
+        <v>41.99</v>
       </c>
       <c r="C47" t="n">
-        <v>42.52</v>
+        <v>42.33</v>
       </c>
       <c r="D47" t="n">
-        <v>41.78</v>
+        <v>41.71</v>
       </c>
       <c r="E47" t="n">
-        <v>42.43</v>
+        <v>42.06</v>
       </c>
       <c r="F47" t="n">
-        <v>39.6382</v>
+        <v>39.7263</v>
       </c>
       <c r="G47" t="n">
-        <v>35.8638</v>
+        <v>35.9239</v>
       </c>
       <c r="H47" t="n">
         <v>45.05751734733581</v>
@@ -7417,55 +7439,55 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>24 sep</t>
+          <t>25 sep</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>184.52</v>
+        <v>184.42</v>
       </c>
       <c r="M47" t="n">
-        <v>185.5</v>
+        <v>185.92</v>
       </c>
       <c r="N47" t="n">
-        <v>182.26</v>
+        <v>183.76</v>
       </c>
       <c r="O47" t="n">
-        <v>184.18</v>
+        <v>185.92</v>
       </c>
       <c r="P47" t="n">
-        <v>173.8756</v>
+        <v>174.8356</v>
       </c>
       <c r="Q47" t="n">
-        <v>165.0554</v>
+        <v>164.9525</v>
       </c>
       <c r="R47" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S47" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>24 sep</t>
+          <t>25 sep</t>
         </is>
       </c>
       <c r="V47" t="n">
-        <v>495.07</v>
+        <v>499.04</v>
       </c>
       <c r="W47" t="n">
-        <v>498.9</v>
+        <v>519.4</v>
       </c>
       <c r="X47" t="n">
-        <v>491.22</v>
+        <v>497.25</v>
       </c>
       <c r="Y47" t="n">
-        <v>497.93</v>
+        <v>516.17</v>
       </c>
       <c r="Z47" t="n">
-        <v>473.0876</v>
+        <v>475.4041</v>
       </c>
       <c r="AA47" t="n">
-        <v>430.4686</v>
+        <v>430.6098</v>
       </c>
       <c r="AB47" t="n">
         <v>535.3375423278808</v>
@@ -7477,26 +7499,26 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>25 sep</t>
+          <t>28 sep</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>41.99</v>
+        <v>42.45</v>
       </c>
       <c r="C48" t="n">
-        <v>42.33</v>
+        <v>42.995</v>
       </c>
       <c r="D48" t="n">
-        <v>41.71</v>
+        <v>42.38</v>
       </c>
       <c r="E48" t="n">
-        <v>42.06</v>
+        <v>42.725</v>
       </c>
       <c r="F48" t="n">
-        <v>39.7263</v>
+        <v>39.8301</v>
       </c>
       <c r="G48" t="n">
-        <v>35.9239</v>
+        <v>35.9888</v>
       </c>
       <c r="H48" t="n">
         <v>45.05751734733581</v>
@@ -7506,55 +7528,55 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>25 sep</t>
+          <t>28 sep</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>184.42</v>
+        <v>185.2</v>
       </c>
       <c r="M48" t="n">
-        <v>185.92</v>
+        <v>186.76</v>
       </c>
       <c r="N48" t="n">
-        <v>183.76</v>
+        <v>178.88</v>
       </c>
       <c r="O48" t="n">
-        <v>185.92</v>
+        <v>184.02</v>
       </c>
       <c r="P48" t="n">
-        <v>174.8356</v>
+        <v>175.7508</v>
       </c>
       <c r="Q48" t="n">
-        <v>164.9525</v>
+        <v>164.8355</v>
       </c>
       <c r="R48" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S48" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>25 sep</t>
+          <t>28 sep</t>
         </is>
       </c>
       <c r="V48" t="n">
-        <v>499.04</v>
+        <v>505.47</v>
       </c>
       <c r="W48" t="n">
-        <v>519.4</v>
+        <v>513.33</v>
       </c>
       <c r="X48" t="n">
-        <v>497.25</v>
+        <v>502.22</v>
       </c>
       <c r="Y48" t="n">
-        <v>516.17</v>
+        <v>509.22</v>
       </c>
       <c r="Z48" t="n">
-        <v>475.4041</v>
+        <v>477.7269</v>
       </c>
       <c r="AA48" t="n">
-        <v>430.6098</v>
+        <v>430.7113</v>
       </c>
       <c r="AB48" t="n">
         <v>535.3375423278808</v>
@@ -7566,26 +7588,26 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>28 sep</t>
+          <t>29 sep</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>42.45</v>
+        <v>42.57</v>
       </c>
       <c r="C49" t="n">
-        <v>42.995</v>
+        <v>42.665</v>
       </c>
       <c r="D49" t="n">
-        <v>42.38</v>
+        <v>41.73</v>
       </c>
       <c r="E49" t="n">
-        <v>42.725</v>
+        <v>42.05</v>
       </c>
       <c r="F49" t="n">
-        <v>39.8301</v>
+        <v>39.9146</v>
       </c>
       <c r="G49" t="n">
-        <v>35.9888</v>
+        <v>36.0498</v>
       </c>
       <c r="H49" t="n">
         <v>45.05751734733581</v>
@@ -7595,55 +7617,55 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>28 sep</t>
+          <t>29 sep</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>185.2</v>
+        <v>183.22</v>
       </c>
       <c r="M49" t="n">
-        <v>186.76</v>
+        <v>186.34</v>
       </c>
       <c r="N49" t="n">
-        <v>178.88</v>
+        <v>182.28</v>
       </c>
       <c r="O49" t="n">
-        <v>184.02</v>
+        <v>185.32</v>
       </c>
       <c r="P49" t="n">
-        <v>175.7508</v>
+        <v>176.7288</v>
       </c>
       <c r="Q49" t="n">
-        <v>164.8355</v>
+        <v>164.733</v>
       </c>
       <c r="R49" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S49" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>28 sep</t>
+          <t>29 sep</t>
         </is>
       </c>
       <c r="V49" t="n">
-        <v>505.47</v>
+        <v>508.31</v>
       </c>
       <c r="W49" t="n">
-        <v>513.33</v>
+        <v>513.64</v>
       </c>
       <c r="X49" t="n">
-        <v>502.22</v>
+        <v>502.4</v>
       </c>
       <c r="Y49" t="n">
-        <v>509.22</v>
+        <v>508.96</v>
       </c>
       <c r="Z49" t="n">
-        <v>477.7269</v>
+        <v>479.8754</v>
       </c>
       <c r="AA49" t="n">
-        <v>430.7113</v>
+        <v>430.8784</v>
       </c>
       <c r="AB49" t="n">
         <v>535.3375423278808</v>
@@ -7655,26 +7677,26 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>29 sep</t>
+          <t>30 sep</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>42.57</v>
+        <v>41.975</v>
       </c>
       <c r="C50" t="n">
-        <v>42.665</v>
+        <v>42.095</v>
       </c>
       <c r="D50" t="n">
-        <v>41.73</v>
+        <v>41.58</v>
       </c>
       <c r="E50" t="n">
-        <v>42.05</v>
+        <v>41.91</v>
       </c>
       <c r="F50" t="n">
-        <v>39.9146</v>
+        <v>39.9874</v>
       </c>
       <c r="G50" t="n">
-        <v>36.0498</v>
+        <v>36.1135</v>
       </c>
       <c r="H50" t="n">
         <v>45.05751734733581</v>
@@ -7684,55 +7706,55 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>29 sep</t>
+          <t>30 sep</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>183.22</v>
+        <v>184.5</v>
       </c>
       <c r="M50" t="n">
-        <v>186.34</v>
+        <v>186.2</v>
       </c>
       <c r="N50" t="n">
-        <v>182.28</v>
+        <v>181.06</v>
       </c>
       <c r="O50" t="n">
-        <v>185.32</v>
+        <v>185.66</v>
       </c>
       <c r="P50" t="n">
-        <v>176.7288</v>
+        <v>177.8012</v>
       </c>
       <c r="Q50" t="n">
-        <v>164.733</v>
+        <v>164.6377</v>
       </c>
       <c r="R50" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S50" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>29 sep</t>
+          <t>30 sep</t>
         </is>
       </c>
       <c r="V50" t="n">
-        <v>508.31</v>
+        <v>511.61</v>
       </c>
       <c r="W50" t="n">
-        <v>513.64</v>
+        <v>519.83</v>
       </c>
       <c r="X50" t="n">
-        <v>502.4</v>
+        <v>510.31</v>
       </c>
       <c r="Y50" t="n">
-        <v>508.96</v>
+        <v>512.9</v>
       </c>
       <c r="Z50" t="n">
-        <v>479.8754</v>
+        <v>482.1933</v>
       </c>
       <c r="AA50" t="n">
-        <v>430.8784</v>
+        <v>431.0408</v>
       </c>
       <c r="AB50" t="n">
         <v>535.3375423278808</v>
@@ -7744,26 +7766,26 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>30 sep</t>
+          <t>1 okt</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>41.975</v>
+        <v>41.625</v>
       </c>
       <c r="C51" t="n">
-        <v>42.095</v>
+        <v>42.36</v>
       </c>
       <c r="D51" t="n">
-        <v>41.58</v>
+        <v>41.165</v>
       </c>
       <c r="E51" t="n">
-        <v>41.91</v>
+        <v>42.24</v>
       </c>
       <c r="F51" t="n">
-        <v>39.9874</v>
+        <v>40.0562</v>
       </c>
       <c r="G51" t="n">
-        <v>36.1135</v>
+        <v>36.1777</v>
       </c>
       <c r="H51" t="n">
         <v>45.05751734733581</v>
@@ -7773,55 +7795,55 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>30 sep</t>
+          <t>1 okt</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>184.5</v>
+        <v>184.68</v>
       </c>
       <c r="M51" t="n">
-        <v>186.2</v>
+        <v>190.26</v>
       </c>
       <c r="N51" t="n">
-        <v>181.06</v>
+        <v>181.34</v>
       </c>
       <c r="O51" t="n">
-        <v>185.66</v>
+        <v>186.74</v>
       </c>
       <c r="P51" t="n">
-        <v>177.8012</v>
+        <v>178.9696</v>
       </c>
       <c r="Q51" t="n">
-        <v>164.6377</v>
+        <v>164.5407</v>
       </c>
       <c r="R51" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S51" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>30 sep</t>
+          <t>1 okt</t>
         </is>
       </c>
       <c r="V51" t="n">
-        <v>511.61</v>
+        <v>519.88</v>
       </c>
       <c r="W51" t="n">
-        <v>519.83</v>
+        <v>522.85</v>
       </c>
       <c r="X51" t="n">
-        <v>510.31</v>
+        <v>512.17</v>
       </c>
       <c r="Y51" t="n">
-        <v>512.9</v>
+        <v>512.8</v>
       </c>
       <c r="Z51" t="n">
-        <v>482.1933</v>
+        <v>484.6572</v>
       </c>
       <c r="AA51" t="n">
-        <v>431.0408</v>
+        <v>431.2272</v>
       </c>
       <c r="AB51" t="n">
         <v>535.3375423278808</v>
@@ -7833,26 +7855,26 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1 okt</t>
+          <t>2 okt</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>41.625</v>
+        <v>42.11</v>
       </c>
       <c r="C52" t="n">
-        <v>42.36</v>
+        <v>42.745</v>
       </c>
       <c r="D52" t="n">
-        <v>41.165</v>
+        <v>41.985</v>
       </c>
       <c r="E52" t="n">
-        <v>42.24</v>
+        <v>42.4</v>
       </c>
       <c r="F52" t="n">
-        <v>40.0562</v>
+        <v>40.1364</v>
       </c>
       <c r="G52" t="n">
-        <v>36.1777</v>
+        <v>36.2422</v>
       </c>
       <c r="H52" t="n">
         <v>45.05751734733581</v>
@@ -7862,55 +7884,55 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>1 okt</t>
+          <t>2 okt</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>184.68</v>
+        <v>187.82</v>
       </c>
       <c r="M52" t="n">
-        <v>190.26</v>
+        <v>188.74</v>
       </c>
       <c r="N52" t="n">
-        <v>181.34</v>
+        <v>183.92</v>
       </c>
       <c r="O52" t="n">
-        <v>186.74</v>
+        <v>183.92</v>
       </c>
       <c r="P52" t="n">
-        <v>178.9696</v>
+        <v>179.844</v>
       </c>
       <c r="Q52" t="n">
-        <v>164.5407</v>
+        <v>164.4442</v>
       </c>
       <c r="R52" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S52" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>1 okt</t>
+          <t>2 okt</t>
         </is>
       </c>
       <c r="V52" t="n">
-        <v>519.88</v>
+        <v>519.39</v>
       </c>
       <c r="W52" t="n">
-        <v>522.85</v>
+        <v>522.5</v>
       </c>
       <c r="X52" t="n">
-        <v>512.17</v>
+        <v>513.66</v>
       </c>
       <c r="Y52" t="n">
-        <v>512.8</v>
+        <v>517.53</v>
       </c>
       <c r="Z52" t="n">
-        <v>484.6572</v>
+        <v>487.3905</v>
       </c>
       <c r="AA52" t="n">
-        <v>431.2272</v>
+        <v>431.4557</v>
       </c>
       <c r="AB52" t="n">
         <v>535.3375423278808</v>
@@ -7922,26 +7944,26 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2 okt</t>
+          <t>5 okt</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>42.11</v>
+        <v>42.645</v>
       </c>
       <c r="C53" t="n">
-        <v>42.745</v>
+        <v>43.11</v>
       </c>
       <c r="D53" t="n">
-        <v>41.985</v>
+        <v>42.35</v>
       </c>
       <c r="E53" t="n">
-        <v>42.4</v>
+        <v>42.865</v>
       </c>
       <c r="F53" t="n">
-        <v>40.1364</v>
+        <v>40.2347</v>
       </c>
       <c r="G53" t="n">
-        <v>36.2422</v>
+        <v>36.3069</v>
       </c>
       <c r="H53" t="n">
         <v>45.05751734733581</v>
@@ -7951,55 +7973,55 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2 okt</t>
+          <t>5 okt</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>187.82</v>
+        <v>185.06</v>
       </c>
       <c r="M53" t="n">
-        <v>188.74</v>
+        <v>188.5</v>
       </c>
       <c r="N53" t="n">
-        <v>183.92</v>
+        <v>184.66</v>
       </c>
       <c r="O53" t="n">
-        <v>183.92</v>
+        <v>185.04</v>
       </c>
       <c r="P53" t="n">
-        <v>179.844</v>
+        <v>180.5192</v>
       </c>
       <c r="Q53" t="n">
-        <v>164.4442</v>
+        <v>164.3515</v>
       </c>
       <c r="R53" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S53" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>2 okt</t>
+          <t>5 okt</t>
         </is>
       </c>
       <c r="V53" t="n">
-        <v>519.39</v>
+        <v>521.62</v>
       </c>
       <c r="W53" t="n">
-        <v>522.5</v>
+        <v>532.35</v>
       </c>
       <c r="X53" t="n">
-        <v>513.66</v>
+        <v>521.47</v>
       </c>
       <c r="Y53" t="n">
-        <v>517.53</v>
+        <v>525.1799999999999</v>
       </c>
       <c r="Z53" t="n">
-        <v>487.3905</v>
+        <v>490.2745</v>
       </c>
       <c r="AA53" t="n">
-        <v>431.4557</v>
+        <v>431.7147</v>
       </c>
       <c r="AB53" t="n">
         <v>535.3375423278808</v>
@@ -8011,26 +8033,26 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>5 okt</t>
+          <t>6 okt</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>42.645</v>
+        <v>42.86</v>
       </c>
       <c r="C54" t="n">
-        <v>43.11</v>
+        <v>43.285</v>
       </c>
       <c r="D54" t="n">
-        <v>42.35</v>
+        <v>42.43</v>
       </c>
       <c r="E54" t="n">
-        <v>42.865</v>
+        <v>43.185</v>
       </c>
       <c r="F54" t="n">
-        <v>40.2347</v>
+        <v>40.349</v>
       </c>
       <c r="G54" t="n">
-        <v>36.3069</v>
+        <v>36.3726</v>
       </c>
       <c r="H54" t="n">
         <v>45.05751734733581</v>
@@ -8040,55 +8062,55 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>5 okt</t>
+          <t>6 okt</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>185.06</v>
+        <v>186.56</v>
       </c>
       <c r="M54" t="n">
-        <v>188.5</v>
+        <v>190.22</v>
       </c>
       <c r="N54" t="n">
-        <v>184.66</v>
+        <v>186.06</v>
       </c>
       <c r="O54" t="n">
-        <v>185.04</v>
+        <v>188.6</v>
       </c>
       <c r="P54" t="n">
-        <v>180.5192</v>
+        <v>181.1064</v>
       </c>
       <c r="Q54" t="n">
-        <v>164.3515</v>
+        <v>164.2647</v>
       </c>
       <c r="R54" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S54" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>5 okt</t>
+          <t>6 okt</t>
         </is>
       </c>
       <c r="V54" t="n">
-        <v>521.62</v>
+        <v>531.6799999999999</v>
       </c>
       <c r="W54" t="n">
-        <v>532.35</v>
+        <v>535.6900000000001</v>
       </c>
       <c r="X54" t="n">
-        <v>521.47</v>
+        <v>528.78</v>
       </c>
       <c r="Y54" t="n">
-        <v>525.1799999999999</v>
+        <v>529.3</v>
       </c>
       <c r="Z54" t="n">
-        <v>490.2745</v>
+        <v>493.0931</v>
       </c>
       <c r="AA54" t="n">
-        <v>431.7147</v>
+        <v>431.9956</v>
       </c>
       <c r="AB54" t="n">
         <v>535.3375423278808</v>
@@ -8100,26 +8122,26 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>6 okt</t>
+          <t>7 okt</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>42.86</v>
+        <v>43.37</v>
       </c>
       <c r="C55" t="n">
-        <v>43.285</v>
+        <v>43.835</v>
       </c>
       <c r="D55" t="n">
-        <v>42.43</v>
+        <v>43.145</v>
       </c>
       <c r="E55" t="n">
-        <v>43.185</v>
+        <v>43.25</v>
       </c>
       <c r="F55" t="n">
-        <v>40.349</v>
+        <v>40.4451</v>
       </c>
       <c r="G55" t="n">
-        <v>36.3726</v>
+        <v>36.4388</v>
       </c>
       <c r="H55" t="n">
         <v>45.05751734733581</v>
@@ -8129,55 +8151,55 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>6 okt</t>
+          <t>7 okt</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>186.56</v>
+        <v>187</v>
       </c>
       <c r="M55" t="n">
-        <v>190.22</v>
+        <v>188.72</v>
       </c>
       <c r="N55" t="n">
-        <v>186.06</v>
+        <v>186.04</v>
       </c>
       <c r="O55" t="n">
-        <v>188.6</v>
+        <v>187.62</v>
       </c>
       <c r="P55" t="n">
-        <v>181.1064</v>
+        <v>181.618</v>
       </c>
       <c r="Q55" t="n">
-        <v>164.2647</v>
+        <v>164.1762</v>
       </c>
       <c r="R55" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S55" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>6 okt</t>
+          <t>7 okt</t>
         </is>
       </c>
       <c r="V55" t="n">
-        <v>531.6799999999999</v>
+        <v>530.73</v>
       </c>
       <c r="W55" t="n">
-        <v>535.6900000000001</v>
+        <v>531.73</v>
       </c>
       <c r="X55" t="n">
-        <v>528.78</v>
+        <v>524.6900000000001</v>
       </c>
       <c r="Y55" t="n">
-        <v>529.3</v>
+        <v>529.76</v>
       </c>
       <c r="Z55" t="n">
-        <v>493.0931</v>
+        <v>495.8361</v>
       </c>
       <c r="AA55" t="n">
-        <v>431.9956</v>
+        <v>432.2398</v>
       </c>
       <c r="AB55" t="n">
         <v>535.3375423278808</v>
@@ -8189,26 +8211,26 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>7 okt</t>
+          <t>8 okt</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>43.37</v>
+        <v>43.555</v>
       </c>
       <c r="C56" t="n">
-        <v>43.835</v>
+        <v>44.815</v>
       </c>
       <c r="D56" t="n">
-        <v>43.145</v>
+        <v>43.5425</v>
       </c>
       <c r="E56" t="n">
-        <v>43.25</v>
+        <v>44.75</v>
       </c>
       <c r="F56" t="n">
-        <v>40.4451</v>
+        <v>40.5699</v>
       </c>
       <c r="G56" t="n">
-        <v>36.4388</v>
+        <v>36.5123</v>
       </c>
       <c r="H56" t="n">
         <v>45.05751734733581</v>
@@ -8218,55 +8240,55 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>7 okt</t>
+          <t>8 okt</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>187</v>
+        <v>187.04</v>
       </c>
       <c r="M56" t="n">
-        <v>188.72</v>
+        <v>189.82</v>
       </c>
       <c r="N56" t="n">
-        <v>186.04</v>
+        <v>183.76</v>
       </c>
       <c r="O56" t="n">
-        <v>187.62</v>
+        <v>184.62</v>
       </c>
       <c r="P56" t="n">
-        <v>181.618</v>
+        <v>182.192</v>
       </c>
       <c r="Q56" t="n">
-        <v>164.1762</v>
+        <v>164.074</v>
       </c>
       <c r="R56" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S56" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>7 okt</t>
+          <t>8 okt</t>
         </is>
       </c>
       <c r="V56" t="n">
-        <v>530.73</v>
+        <v>529.8099999999999</v>
       </c>
       <c r="W56" t="n">
-        <v>531.73</v>
+        <v>533.51</v>
       </c>
       <c r="X56" t="n">
-        <v>524.6900000000001</v>
+        <v>518.79</v>
       </c>
       <c r="Y56" t="n">
-        <v>529.76</v>
+        <v>522.61</v>
       </c>
       <c r="Z56" t="n">
-        <v>495.8361</v>
+        <v>498.4921</v>
       </c>
       <c r="AA56" t="n">
-        <v>432.2398</v>
+        <v>432.4385</v>
       </c>
       <c r="AB56" t="n">
         <v>535.3375423278808</v>
@@ -8278,26 +8300,26 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>8 okt</t>
+          <t>9 okt</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>43.555</v>
+        <v>44.42</v>
       </c>
       <c r="C57" t="n">
-        <v>44.815</v>
+        <v>45.155</v>
       </c>
       <c r="D57" t="n">
-        <v>43.5425</v>
+        <v>43.94</v>
       </c>
       <c r="E57" t="n">
-        <v>44.75</v>
+        <v>45.035</v>
       </c>
       <c r="F57" t="n">
-        <v>40.5699</v>
+        <v>40.6842</v>
       </c>
       <c r="G57" t="n">
-        <v>36.5123</v>
+        <v>36.5866</v>
       </c>
       <c r="H57" t="n">
         <v>45.05751734733581</v>
@@ -8307,55 +8329,55 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>8 okt</t>
+          <t>9 okt</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>187.04</v>
+        <v>188.98</v>
       </c>
       <c r="M57" t="n">
-        <v>189.82</v>
+        <v>192.58</v>
       </c>
       <c r="N57" t="n">
-        <v>183.76</v>
+        <v>188.86</v>
       </c>
       <c r="O57" t="n">
-        <v>184.62</v>
+        <v>191.46</v>
       </c>
       <c r="P57" t="n">
-        <v>182.192</v>
+        <v>182.8676</v>
       </c>
       <c r="Q57" t="n">
-        <v>164.074</v>
+        <v>164.0101</v>
       </c>
       <c r="R57" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S57" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>8 okt</t>
+          <t>9 okt</t>
         </is>
       </c>
       <c r="V57" t="n">
-        <v>529.8099999999999</v>
+        <v>528.24</v>
       </c>
       <c r="W57" t="n">
-        <v>533.51</v>
+        <v>537.22</v>
       </c>
       <c r="X57" t="n">
-        <v>518.79</v>
+        <v>526.24</v>
       </c>
       <c r="Y57" t="n">
-        <v>522.61</v>
+        <v>535.0700000000001</v>
       </c>
       <c r="Z57" t="n">
-        <v>498.4921</v>
+        <v>500.1885</v>
       </c>
       <c r="AA57" t="n">
-        <v>432.4385</v>
+        <v>432.7046</v>
       </c>
       <c r="AB57" t="n">
         <v>535.3375423278808</v>
@@ -8367,26 +8389,26 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>9 okt</t>
+          <t>12 okt</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>44.42</v>
+        <v>44.725</v>
       </c>
       <c r="C58" t="n">
-        <v>45.155</v>
+        <v>45.81</v>
       </c>
       <c r="D58" t="n">
-        <v>43.94</v>
+        <v>44.695</v>
       </c>
       <c r="E58" t="n">
-        <v>45.035</v>
+        <v>45.56</v>
       </c>
       <c r="F58" t="n">
-        <v>40.6842</v>
+        <v>40.8072</v>
       </c>
       <c r="G58" t="n">
-        <v>36.5866</v>
+        <v>36.6625</v>
       </c>
       <c r="H58" t="n">
         <v>45.05751734733581</v>
@@ -8396,55 +8418,55 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>9 okt</t>
+          <t>12 okt</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>188.98</v>
+        <v>190.58</v>
       </c>
       <c r="M58" t="n">
-        <v>192.58</v>
+        <v>197.88</v>
       </c>
       <c r="N58" t="n">
-        <v>188.86</v>
+        <v>189.78</v>
       </c>
       <c r="O58" t="n">
-        <v>191.46</v>
+        <v>194.46</v>
       </c>
       <c r="P58" t="n">
-        <v>182.8676</v>
+        <v>183.464</v>
       </c>
       <c r="Q58" t="n">
-        <v>164.0101</v>
+        <v>163.9576</v>
       </c>
       <c r="R58" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S58" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>9 okt</t>
+          <t>12 okt</t>
         </is>
       </c>
       <c r="V58" t="n">
-        <v>528.24</v>
+        <v>537.53</v>
       </c>
       <c r="W58" t="n">
-        <v>537.22</v>
+        <v>542.74</v>
       </c>
       <c r="X58" t="n">
-        <v>526.24</v>
+        <v>535.7</v>
       </c>
       <c r="Y58" t="n">
-        <v>535.0700000000001</v>
+        <v>541.15</v>
       </c>
       <c r="Z58" t="n">
-        <v>500.1885</v>
+        <v>501.7346</v>
       </c>
       <c r="AA58" t="n">
-        <v>432.7046</v>
+        <v>432.9914</v>
       </c>
       <c r="AB58" t="n">
         <v>535.3375423278808</v>
@@ -8456,26 +8478,26 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>12 okt</t>
+          <t>13 okt</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>44.725</v>
+        <v>45.69</v>
       </c>
       <c r="C59" t="n">
-        <v>45.81</v>
+        <v>45.97</v>
       </c>
       <c r="D59" t="n">
-        <v>44.695</v>
+        <v>45.35</v>
       </c>
       <c r="E59" t="n">
-        <v>45.56</v>
+        <v>45.95</v>
       </c>
       <c r="F59" t="n">
-        <v>40.8072</v>
+        <v>40.9565</v>
       </c>
       <c r="G59" t="n">
-        <v>36.6625</v>
+        <v>36.7398</v>
       </c>
       <c r="H59" t="n">
         <v>45.05751734733581</v>
@@ -8485,55 +8507,55 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>12 okt</t>
+          <t>13 okt</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>190.58</v>
+        <v>196</v>
       </c>
       <c r="M59" t="n">
-        <v>197.88</v>
+        <v>198.18</v>
       </c>
       <c r="N59" t="n">
-        <v>189.78</v>
+        <v>194.02</v>
       </c>
       <c r="O59" t="n">
-        <v>194.46</v>
+        <v>197.28</v>
       </c>
       <c r="P59" t="n">
-        <v>183.464</v>
+        <v>184.062</v>
       </c>
       <c r="Q59" t="n">
-        <v>163.9576</v>
+        <v>163.9196</v>
       </c>
       <c r="R59" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S59" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>12 okt</t>
+          <t>13 okt</t>
         </is>
       </c>
       <c r="V59" t="n">
-        <v>537.53</v>
+        <v>544.64</v>
       </c>
       <c r="W59" t="n">
-        <v>542.74</v>
+        <v>551.15</v>
       </c>
       <c r="X59" t="n">
-        <v>535.7</v>
+        <v>543.0599999999999</v>
       </c>
       <c r="Y59" t="n">
-        <v>541.15</v>
+        <v>543.45</v>
       </c>
       <c r="Z59" t="n">
-        <v>501.7346</v>
+        <v>502.8689</v>
       </c>
       <c r="AA59" t="n">
-        <v>432.9914</v>
+        <v>433.2839</v>
       </c>
       <c r="AB59" t="n">
         <v>535.3375423278808</v>
@@ -8545,26 +8567,26 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>13 okt</t>
+          <t>14 okt</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>45.69</v>
+        <v>45.95</v>
       </c>
       <c r="C60" t="n">
-        <v>45.97</v>
+        <v>46.675</v>
       </c>
       <c r="D60" t="n">
-        <v>45.35</v>
+        <v>45.91</v>
       </c>
       <c r="E60" t="n">
-        <v>45.95</v>
+        <v>46.455</v>
       </c>
       <c r="F60" t="n">
-        <v>40.9565</v>
+        <v>41.125</v>
       </c>
       <c r="G60" t="n">
-        <v>36.7398</v>
+        <v>36.8183</v>
       </c>
       <c r="H60" t="n">
         <v>45.05751734733581</v>
@@ -8574,55 +8596,55 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>13 okt</t>
+          <t>14 okt</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>196</v>
+        <v>196.6</v>
       </c>
       <c r="M60" t="n">
-        <v>198.18</v>
+        <v>199.36</v>
       </c>
       <c r="N60" t="n">
-        <v>194.02</v>
+        <v>195.26</v>
       </c>
       <c r="O60" t="n">
-        <v>197.28</v>
+        <v>196.94</v>
       </c>
       <c r="P60" t="n">
-        <v>184.062</v>
+        <v>184.6156</v>
       </c>
       <c r="Q60" t="n">
-        <v>163.9196</v>
+        <v>163.9114</v>
       </c>
       <c r="R60" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S60" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>13 okt</t>
+          <t>14 okt</t>
         </is>
       </c>
       <c r="V60" t="n">
-        <v>544.64</v>
+        <v>545.27</v>
       </c>
       <c r="W60" t="n">
-        <v>551.15</v>
+        <v>545.75</v>
       </c>
       <c r="X60" t="n">
-        <v>543.0599999999999</v>
+        <v>532.54</v>
       </c>
       <c r="Y60" t="n">
-        <v>543.45</v>
+        <v>533.6900000000001</v>
       </c>
       <c r="Z60" t="n">
-        <v>502.8689</v>
+        <v>503.705</v>
       </c>
       <c r="AA60" t="n">
-        <v>433.2839</v>
+        <v>433.5292</v>
       </c>
       <c r="AB60" t="n">
         <v>535.3375423278808</v>
@@ -8634,26 +8656,26 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>14 okt</t>
+          <t>15 okt</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>45.95</v>
+        <v>46.295</v>
       </c>
       <c r="C61" t="n">
-        <v>46.675</v>
+        <v>46.735</v>
       </c>
       <c r="D61" t="n">
-        <v>45.91</v>
+        <v>46.125</v>
       </c>
       <c r="E61" t="n">
-        <v>46.455</v>
+        <v>46.375</v>
       </c>
       <c r="F61" t="n">
-        <v>41.125</v>
+        <v>41.2847</v>
       </c>
       <c r="G61" t="n">
-        <v>36.8183</v>
+        <v>36.8966</v>
       </c>
       <c r="H61" t="n">
         <v>45.05751734733581</v>
@@ -8663,55 +8685,55 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>14 okt</t>
+          <t>15 okt</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>196.6</v>
+        <v>199.48</v>
       </c>
       <c r="M61" t="n">
-        <v>199.36</v>
+        <v>203</v>
       </c>
       <c r="N61" t="n">
-        <v>195.26</v>
+        <v>196.98</v>
       </c>
       <c r="O61" t="n">
-        <v>196.94</v>
+        <v>201.25</v>
       </c>
       <c r="P61" t="n">
-        <v>184.6156</v>
+        <v>185.221</v>
       </c>
       <c r="Q61" t="n">
-        <v>163.9114</v>
+        <v>163.9038</v>
       </c>
       <c r="R61" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S61" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>14 okt</t>
+          <t>15 okt</t>
         </is>
       </c>
       <c r="V61" t="n">
-        <v>545.27</v>
+        <v>533.3200000000001</v>
       </c>
       <c r="W61" t="n">
-        <v>545.75</v>
+        <v>541.13</v>
       </c>
       <c r="X61" t="n">
-        <v>532.54</v>
+        <v>531.22</v>
       </c>
       <c r="Y61" t="n">
-        <v>533.6900000000001</v>
+        <v>539.4400000000001</v>
       </c>
       <c r="Z61" t="n">
-        <v>503.705</v>
+        <v>504.7629</v>
       </c>
       <c r="AA61" t="n">
-        <v>433.5292</v>
+        <v>433.8063</v>
       </c>
       <c r="AB61" t="n">
         <v>535.3375423278808</v>
@@ -8723,26 +8745,26 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>15 okt</t>
+          <t>16 okt</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>46.295</v>
+        <v>46.14</v>
       </c>
       <c r="C62" t="n">
-        <v>46.735</v>
+        <v>47.025</v>
       </c>
       <c r="D62" t="n">
-        <v>46.125</v>
+        <v>46.075</v>
       </c>
       <c r="E62" t="n">
-        <v>46.375</v>
+        <v>46.88</v>
       </c>
       <c r="F62" t="n">
-        <v>41.2847</v>
+        <v>41.4622</v>
       </c>
       <c r="G62" t="n">
-        <v>36.8966</v>
+        <v>36.977</v>
       </c>
       <c r="H62" t="n">
         <v>45.05751734733581</v>
@@ -8752,55 +8774,55 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>15 okt</t>
+          <t>16 okt</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>199.48</v>
+        <v>200.6</v>
       </c>
       <c r="M62" t="n">
-        <v>203</v>
+        <v>204.2</v>
       </c>
       <c r="N62" t="n">
-        <v>196.98</v>
+        <v>198.68</v>
       </c>
       <c r="O62" t="n">
-        <v>201.25</v>
+        <v>199.22</v>
       </c>
       <c r="P62" t="n">
-        <v>185.221</v>
+        <v>185.6462</v>
       </c>
       <c r="Q62" t="n">
-        <v>163.9038</v>
+        <v>163.9066</v>
       </c>
       <c r="R62" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S62" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>15 okt</t>
+          <t>16 okt</t>
         </is>
       </c>
       <c r="V62" t="n">
-        <v>533.3200000000001</v>
+        <v>541.3099999999999</v>
       </c>
       <c r="W62" t="n">
-        <v>541.13</v>
+        <v>543.8200000000001</v>
       </c>
       <c r="X62" t="n">
-        <v>531.22</v>
+        <v>524.4299999999999</v>
       </c>
       <c r="Y62" t="n">
-        <v>539.4400000000001</v>
+        <v>529.05</v>
       </c>
       <c r="Z62" t="n">
-        <v>504.7629</v>
+        <v>505.3655</v>
       </c>
       <c r="AA62" t="n">
-        <v>433.8063</v>
+        <v>434.0295</v>
       </c>
       <c r="AB62" t="n">
         <v>535.3375423278808</v>
@@ -8812,26 +8834,26 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>16 okt</t>
+          <t>19 okt</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>46.14</v>
+        <v>47.37</v>
       </c>
       <c r="C63" t="n">
-        <v>47.025</v>
+        <v>47.45</v>
       </c>
       <c r="D63" t="n">
-        <v>46.075</v>
+        <v>46.74</v>
       </c>
       <c r="E63" t="n">
-        <v>46.88</v>
+        <v>46.86</v>
       </c>
       <c r="F63" t="n">
-        <v>41.4622</v>
+        <v>41.6313</v>
       </c>
       <c r="G63" t="n">
-        <v>36.977</v>
+        <v>37.0625</v>
       </c>
       <c r="H63" t="n">
         <v>45.05751734733581</v>
@@ -8841,55 +8863,55 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>16 okt</t>
+          <t>19 okt</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>200.6</v>
+        <v>199.56</v>
       </c>
       <c r="M63" t="n">
-        <v>204.2</v>
+        <v>200.8</v>
       </c>
       <c r="N63" t="n">
-        <v>198.68</v>
+        <v>197.32</v>
       </c>
       <c r="O63" t="n">
-        <v>199.22</v>
+        <v>199.84</v>
       </c>
       <c r="P63" t="n">
-        <v>185.6462</v>
+        <v>186.057</v>
       </c>
       <c r="Q63" t="n">
-        <v>163.9066</v>
+        <v>163.8811</v>
       </c>
       <c r="R63" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S63" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>16 okt</t>
+          <t>19 okt</t>
         </is>
       </c>
       <c r="V63" t="n">
-        <v>541.3099999999999</v>
+        <v>528.7</v>
       </c>
       <c r="W63" t="n">
-        <v>543.8200000000001</v>
+        <v>535.5700000000001</v>
       </c>
       <c r="X63" t="n">
-        <v>524.4299999999999</v>
+        <v>528.0599999999999</v>
       </c>
       <c r="Y63" t="n">
-        <v>529.05</v>
+        <v>533.52</v>
       </c>
       <c r="Z63" t="n">
-        <v>505.3655</v>
+        <v>506.0549</v>
       </c>
       <c r="AA63" t="n">
-        <v>434.0295</v>
+        <v>434.2942</v>
       </c>
       <c r="AB63" t="n">
         <v>535.3375423278808</v>
@@ -8901,26 +8923,26 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>19 okt</t>
+          <t>20 okt</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>47.37</v>
+        <v>46.875</v>
       </c>
       <c r="C64" t="n">
-        <v>47.45</v>
+        <v>47.505</v>
       </c>
       <c r="D64" t="n">
-        <v>46.74</v>
+        <v>46.36</v>
       </c>
       <c r="E64" t="n">
-        <v>46.86</v>
+        <v>46.57</v>
       </c>
       <c r="F64" t="n">
-        <v>41.6313</v>
+        <v>41.7834</v>
       </c>
       <c r="G64" t="n">
-        <v>37.0625</v>
+        <v>37.1516</v>
       </c>
       <c r="H64" t="n">
         <v>45.05751734733581</v>
@@ -8930,55 +8952,55 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>19 okt</t>
+          <t>20 okt</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>199.56</v>
+        <v>201.3</v>
       </c>
       <c r="M64" t="n">
-        <v>200.8</v>
+        <v>203.45</v>
       </c>
       <c r="N64" t="n">
-        <v>197.32</v>
+        <v>199.46</v>
       </c>
       <c r="O64" t="n">
-        <v>199.84</v>
+        <v>201.55</v>
       </c>
       <c r="P64" t="n">
-        <v>186.057</v>
+        <v>186.474</v>
       </c>
       <c r="Q64" t="n">
-        <v>163.8811</v>
+        <v>163.8736</v>
       </c>
       <c r="R64" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S64" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>19 okt</t>
+          <t>20 okt</t>
         </is>
       </c>
       <c r="V64" t="n">
-        <v>528.7</v>
+        <v>533.91</v>
       </c>
       <c r="W64" t="n">
-        <v>535.5700000000001</v>
+        <v>534.21</v>
       </c>
       <c r="X64" t="n">
-        <v>528.0599999999999</v>
+        <v>525.84</v>
       </c>
       <c r="Y64" t="n">
-        <v>533.52</v>
+        <v>531.87</v>
       </c>
       <c r="Z64" t="n">
-        <v>506.0549</v>
+        <v>506.5901</v>
       </c>
       <c r="AA64" t="n">
-        <v>434.2942</v>
+        <v>434.6038</v>
       </c>
       <c r="AB64" t="n">
         <v>535.3375423278808</v>
@@ -8990,26 +9012,26 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20 okt</t>
+          <t>21 okt</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>46.875</v>
+        <v>46.97</v>
       </c>
       <c r="C65" t="n">
-        <v>47.505</v>
+        <v>47.135</v>
       </c>
       <c r="D65" t="n">
-        <v>46.36</v>
+        <v>46.73</v>
       </c>
       <c r="E65" t="n">
-        <v>46.57</v>
+        <v>46.84</v>
       </c>
       <c r="F65" t="n">
-        <v>41.7834</v>
+        <v>41.9472</v>
       </c>
       <c r="G65" t="n">
-        <v>37.1516</v>
+        <v>37.2379</v>
       </c>
       <c r="H65" t="n">
         <v>45.05751734733581</v>
@@ -9019,55 +9041,55 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>20 okt</t>
+          <t>21 okt</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>201.3</v>
+        <v>201.8</v>
       </c>
       <c r="M65" t="n">
-        <v>203.45</v>
+        <v>208.65</v>
       </c>
       <c r="N65" t="n">
-        <v>199.46</v>
+        <v>200</v>
       </c>
       <c r="O65" t="n">
-        <v>201.55</v>
+        <v>208.65</v>
       </c>
       <c r="P65" t="n">
-        <v>186.474</v>
+        <v>187.1278</v>
       </c>
       <c r="Q65" t="n">
-        <v>163.8736</v>
+        <v>163.8728</v>
       </c>
       <c r="R65" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S65" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>20 okt</t>
+          <t>21 okt</t>
         </is>
       </c>
       <c r="V65" t="n">
-        <v>533.91</v>
+        <v>529.4400000000001</v>
       </c>
       <c r="W65" t="n">
-        <v>534.21</v>
+        <v>533.28</v>
       </c>
       <c r="X65" t="n">
-        <v>525.84</v>
+        <v>525.02</v>
       </c>
       <c r="Y65" t="n">
-        <v>531.87</v>
+        <v>532.95</v>
       </c>
       <c r="Z65" t="n">
-        <v>506.5901</v>
+        <v>507.1919</v>
       </c>
       <c r="AA65" t="n">
-        <v>434.6038</v>
+        <v>434.9192</v>
       </c>
       <c r="AB65" t="n">
         <v>535.3375423278808</v>
@@ -9079,26 +9101,26 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>21 okt</t>
+          <t>22 okt</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>46.97</v>
+        <v>47.05</v>
       </c>
       <c r="C66" t="n">
-        <v>47.135</v>
+        <v>47.6</v>
       </c>
       <c r="D66" t="n">
-        <v>46.73</v>
+        <v>46.59</v>
       </c>
       <c r="E66" t="n">
-        <v>46.82</v>
+        <v>46.625</v>
       </c>
       <c r="F66" t="n">
-        <v>41.9468</v>
+        <v>42.1076</v>
       </c>
       <c r="G66" t="n">
-        <v>37.2378</v>
+        <v>37.322</v>
       </c>
       <c r="H66" t="n">
         <v>45.05751734733581</v>
@@ -9108,55 +9130,55 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>21 okt</t>
+          <t>22 okt</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>201.8</v>
+        <v>207.75</v>
       </c>
       <c r="M66" t="n">
-        <v>208.65</v>
+        <v>216.55</v>
       </c>
       <c r="N66" t="n">
-        <v>200</v>
+        <v>205.1</v>
       </c>
       <c r="O66" t="n">
-        <v>208.55</v>
+        <v>216.45</v>
       </c>
       <c r="P66" t="n">
-        <v>187.1258</v>
+        <v>187.9492</v>
       </c>
       <c r="Q66" t="n">
-        <v>163.8723</v>
+        <v>163.9074</v>
       </c>
       <c r="R66" t="n">
         <v>191.5557367172241</v>
       </c>
       <c r="S66" t="n">
-        <v>192.4057115827288</v>
+        <v>198.8849934169224</v>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>21 okt</t>
+          <t>22 okt</t>
         </is>
       </c>
       <c r="V66" t="n">
-        <v>529.4400000000001</v>
+        <v>532.7</v>
       </c>
       <c r="W66" t="n">
-        <v>533.28</v>
+        <v>533.596</v>
       </c>
       <c r="X66" t="n">
-        <v>525.02</v>
+        <v>520.3</v>
       </c>
       <c r="Y66" t="n">
-        <v>532.8099999999999</v>
+        <v>521.58</v>
       </c>
       <c r="Z66" t="n">
-        <v>507.1891</v>
+        <v>507.7934</v>
       </c>
       <c r="AA66" t="n">
-        <v>434.9185</v>
+        <v>435.1496</v>
       </c>
       <c r="AB66" t="n">
         <v>535.3375423278808</v>

--- a/rapporten/trend-agent.xlsx
+++ b/rapporten/trend-agent.xlsx
@@ -1944,7 +1944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2190,6 +2190,28 @@
       </c>
       <c r="E11" s="3">
         <f>B11/$B$2-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>10075.73</v>
+      </c>
+      <c r="C12" s="2">
+        <f>B12-B11</f>
+        <v/>
+      </c>
+      <c r="D12" s="3">
+        <f>B12/B11-1</f>
+        <v/>
+      </c>
+      <c r="E12" s="3">
+        <f>B12/$B$2-1</f>
         <v/>
       </c>
     </row>
@@ -2333,38 +2355,38 @@
     <row r="6" ht="22" customHeight="1">
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Shell (SHELL.AS)  ·  46,62 EUR</t>
+          <t>Shell (SHELL.AS)  ·  48,35 EUR</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>SAP (SAP.DE)  ·  216,45 EUR</t>
+          <t>SAP (SAP.DE)  ·  214,35 EUR</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>Gestegen: 21,5% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +3,5% (winst). De bot verkoopt als de koers onder 44,25 zakt (-5,1%).</t>
+          <t>Gestegen: 27,4% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +7,3% (winst). De bot verkoopt als de koers onder 45,41 zakt (-6,1%).</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>Gestegen: 54,4% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +13,0% (winst). De bot verkoopt als de koers onder 198,88 zakt (-8,1%).</t>
+          <t>Gestegen: 41,7% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +11,9% (winst). De bot verkoopt als de koers onder 198,88 zakt (-7,2%).</t>
         </is>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Microsoft (MSFT)  ·  521,58 USD</t>
+          <t>Microsoft (MSFT)  ·  524,53 USD</t>
         </is>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Gestegen: 36,9% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: -2,6% (verlies). De bot verkoopt als de koers onder 510,08 zakt (-2,2%).</t>
+          <t>Gestegen: 37,7% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: -2,0% (verlies). De bot verkoopt als de koers onder 510,33 zakt (-2,7%).</t>
         </is>
       </c>
     </row>
@@ -2465,7 +2487,7 @@
         <v>45.06</v>
       </c>
       <c r="F2" t="n">
-        <v>44.25</v>
+        <v>45.41</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2543,7 +2565,7 @@
         <v>535.34</v>
       </c>
       <c r="F4" t="n">
-        <v>510.08</v>
+        <v>510.33</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -2843,19 +2865,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.163</v>
+        <v>0.191</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.2285431751901195</v>
+        <v>0.2901872546925657</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1183737475618283</v>
+        <v>0.1394061011780339</v>
       </c>
       <c r="H2" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="I2" t="n">
-        <v>46.62</v>
+        <v>48.35</v>
       </c>
     </row>
     <row r="3">
@@ -2878,19 +2900,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.157</v>
+        <v>0.139</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.4307905783633839</v>
+        <v>0.3460813784807195</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.1608387276334073</v>
+        <v>0.1638072246036177</v>
       </c>
       <c r="H3" t="n">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="I3" t="n">
-        <v>216.45</v>
+        <v>214.35</v>
       </c>
     </row>
     <row r="4">
@@ -2899,12 +2921,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>XLE</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Energie-ETF</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2913,19 +2935,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.136</v>
+        <v>0.123</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.1668063138699023</v>
+        <v>0.1950325890589528</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.1460223781510612</v>
+        <v>0.1075080434660998</v>
       </c>
       <c r="H4" t="n">
-        <v>0.98</v>
+        <v>1.05</v>
       </c>
       <c r="I4" t="n">
-        <v>414.31</v>
+        <v>69.33</v>
       </c>
     </row>
     <row r="5">
@@ -2948,19 +2970,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.128</v>
+        <v>0.118</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.3072365918928017</v>
+        <v>0.2440098033883189</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.2859259711371527</v>
+        <v>0.2804417776422821</v>
       </c>
       <c r="H5" t="n">
         <v>0.88</v>
       </c>
       <c r="I5" t="n">
-        <v>86.8</v>
+        <v>88.12</v>
       </c>
     </row>
     <row r="6">
@@ -2969,12 +2991,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>ExxonMobil</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2983,19 +3005,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.097</v>
+        <v>0.111</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.369038160307817</v>
+        <v>0.1914215590937345</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.04193056374579474</v>
+        <v>0.1299494720829752</v>
       </c>
       <c r="H6" t="n">
-        <v>0.83</v>
+        <v>0.88</v>
       </c>
       <c r="I6" t="n">
-        <v>521.58</v>
+        <v>183.21</v>
       </c>
     </row>
     <row r="7">
@@ -3004,12 +3026,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>XLE</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Energie-ETF</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -3018,19 +3040,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.092</v>
+        <v>0.103</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.1402498925928488</v>
+        <v>0.1273490588752719</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.08353379811437622</v>
+        <v>0.1085928318442351</v>
       </c>
       <c r="H7" t="n">
-        <v>1.06</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>67.58</v>
+        <v>407.94</v>
       </c>
     </row>
     <row r="8">
@@ -3039,33 +3061,33 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>OR.PA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>L'Oreal</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.092</v>
+        <v>0.099</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.5317135319600113</v>
+        <v>0.1377644315509203</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.05328732875047293</v>
+        <v>0.1325880691778327</v>
       </c>
       <c r="H8" t="n">
-        <v>0.67</v>
+        <v>1.03</v>
       </c>
       <c r="I8" t="n">
-        <v>250.24</v>
+        <v>435.65</v>
       </c>
     </row>
     <row r="9">
@@ -3074,12 +3096,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -3088,19 +3110,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.095</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.1430104559621492</v>
+        <v>0.3505845322893033</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.1054394371425038</v>
+        <v>0.05341118657135846</v>
       </c>
       <c r="H9" t="n">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="I9" t="n">
-        <v>178.23</v>
+        <v>524.53</v>
       </c>
     </row>
     <row r="10">
@@ -3109,33 +3131,33 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>TTE.PA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Palantir</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.076</v>
+        <v>0.08</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.5968922568347694</v>
+        <v>0.1480907311729238</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.02346316365570966</v>
+        <v>0.04510946897647328</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="I10" t="n">
-        <v>196.29</v>
+        <v>83.73</v>
       </c>
     </row>
     <row r="11">
@@ -3144,33 +3166,33 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>OR.PA</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>L'Oreal</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.074</v>
+        <v>0.076</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.1001198437642969</v>
+        <v>0.434316069197425</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.0858081311339931</v>
+        <v>0.04340524005081736</v>
       </c>
       <c r="H11" t="n">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I11" t="n">
-        <v>413.15</v>
+        <v>248.56</v>
       </c>
     </row>
   </sheetData>
@@ -3441,49 +3463,49 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>24 jul</t>
+          <t>27 jul</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>38.4019</v>
+        <v>37.5802</v>
       </c>
       <c r="C2" t="n">
-        <v>38.6593</v>
+        <v>38.1099</v>
       </c>
       <c r="D2" t="n">
-        <v>38.1594</v>
+        <v>37.4317</v>
       </c>
       <c r="E2" t="n">
-        <v>38.3871</v>
+        <v>37.9515</v>
       </c>
       <c r="F2" t="n">
-        <v>35.9135</v>
+        <v>35.931</v>
       </c>
       <c r="H2" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I2" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>24 jul</t>
+          <t>27 jul</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>130.88</v>
+        <v>142.38</v>
       </c>
       <c r="M2" t="n">
-        <v>141.32</v>
+        <v>151.56</v>
       </c>
       <c r="N2" t="n">
-        <v>130.86</v>
+        <v>142</v>
       </c>
       <c r="O2" t="n">
-        <v>140.2</v>
+        <v>151.28</v>
       </c>
       <c r="P2" t="n">
-        <v>143.9888</v>
+        <v>144.0572</v>
       </c>
       <c r="R2" t="n">
         <v>191.5557367172241</v>
@@ -3493,77 +3515,77 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>23 jul</t>
+          <t>24 jul</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>389.2373</v>
+        <v>386.3227</v>
       </c>
       <c r="W2" t="n">
-        <v>391.0439</v>
+        <v>388.299</v>
       </c>
       <c r="X2" t="n">
-        <v>376.6809</v>
+        <v>379.9348</v>
       </c>
       <c r="Y2" t="n">
-        <v>380.863</v>
+        <v>380.9828</v>
       </c>
       <c r="Z2" t="n">
-        <v>398.8242</v>
+        <v>398.3214</v>
       </c>
       <c r="AB2" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC2" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>27 jul</t>
+          <t>28 jul</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>37.5802</v>
+        <v>37.7139</v>
       </c>
       <c r="C3" t="n">
-        <v>38.1099</v>
+        <v>38.0109</v>
       </c>
       <c r="D3" t="n">
-        <v>37.4317</v>
+        <v>37.4713</v>
       </c>
       <c r="E3" t="n">
-        <v>37.9515</v>
+        <v>37.4713</v>
       </c>
       <c r="F3" t="n">
-        <v>35.931</v>
+        <v>35.9372</v>
       </c>
       <c r="H3" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I3" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>27 jul</t>
+          <t>28 jul</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>142.38</v>
+        <v>152.2</v>
       </c>
       <c r="M3" t="n">
-        <v>151.56</v>
+        <v>159.76</v>
       </c>
       <c r="N3" t="n">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="O3" t="n">
-        <v>151.28</v>
+        <v>159.24</v>
       </c>
       <c r="P3" t="n">
-        <v>144.0572</v>
+        <v>144.1076</v>
       </c>
       <c r="R3" t="n">
         <v>191.5557367172241</v>
@@ -3573,77 +3595,77 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>24 jul</t>
+          <t>27 jul</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>386.3227</v>
+        <v>389.347</v>
       </c>
       <c r="W3" t="n">
-        <v>388.299</v>
+        <v>393.4593</v>
       </c>
       <c r="X3" t="n">
-        <v>379.9348</v>
+        <v>387.261</v>
       </c>
       <c r="Y3" t="n">
-        <v>380.9828</v>
+        <v>388.3689</v>
       </c>
       <c r="Z3" t="n">
-        <v>398.3214</v>
+        <v>398.0172</v>
       </c>
       <c r="AB3" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC3" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>28 jul</t>
+          <t>29 jul</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>37.7139</v>
+        <v>38.0653</v>
       </c>
       <c r="C4" t="n">
-        <v>38.0109</v>
+        <v>38.59</v>
       </c>
       <c r="D4" t="n">
-        <v>37.4713</v>
+        <v>37.7089</v>
       </c>
       <c r="E4" t="n">
-        <v>37.4713</v>
+        <v>38.4415</v>
       </c>
       <c r="F4" t="n">
-        <v>35.9372</v>
+        <v>35.9692</v>
       </c>
       <c r="H4" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I4" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>28 jul</t>
+          <t>29 jul</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>152.2</v>
+        <v>159.84</v>
       </c>
       <c r="M4" t="n">
-        <v>159.76</v>
+        <v>163.3</v>
       </c>
       <c r="N4" t="n">
-        <v>151</v>
+        <v>156.48</v>
       </c>
       <c r="O4" t="n">
-        <v>159.24</v>
+        <v>162.04</v>
       </c>
       <c r="P4" t="n">
-        <v>144.1076</v>
+        <v>144.28</v>
       </c>
       <c r="R4" t="n">
         <v>191.5557367172241</v>
@@ -3653,77 +3675,77 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>27 jul</t>
+          <t>28 jul</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>389.347</v>
+        <v>392.4213</v>
       </c>
       <c r="W4" t="n">
-        <v>393.4593</v>
+        <v>399.5678</v>
       </c>
       <c r="X4" t="n">
-        <v>387.261</v>
+        <v>390.5647</v>
       </c>
       <c r="Y4" t="n">
-        <v>388.3689</v>
+        <v>392.6109</v>
       </c>
       <c r="Z4" t="n">
-        <v>398.0172</v>
+        <v>397.7139</v>
       </c>
       <c r="AB4" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC4" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>29 jul</t>
+          <t>30 jul</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>38.0653</v>
+        <v>38.6098</v>
       </c>
       <c r="C5" t="n">
-        <v>38.59</v>
+        <v>39.1444</v>
       </c>
       <c r="D5" t="n">
-        <v>37.7089</v>
+        <v>38.3277</v>
       </c>
       <c r="E5" t="n">
-        <v>38.4415</v>
+        <v>38.5108</v>
       </c>
       <c r="F5" t="n">
-        <v>35.9692</v>
+        <v>35.9978</v>
       </c>
       <c r="H5" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I5" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>29 jul</t>
+          <t>30 jul</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>159.84</v>
+        <v>162.5</v>
       </c>
       <c r="M5" t="n">
-        <v>163.3</v>
+        <v>163.16</v>
       </c>
       <c r="N5" t="n">
-        <v>156.48</v>
+        <v>155.2</v>
       </c>
       <c r="O5" t="n">
-        <v>162.04</v>
+        <v>155.92</v>
       </c>
       <c r="P5" t="n">
-        <v>144.28</v>
+        <v>144.3804</v>
       </c>
       <c r="R5" t="n">
         <v>191.5557367172241</v>
@@ -3733,83 +3755,83 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>28 jul</t>
+          <t>29 jul</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>392.4213</v>
+        <v>392.6608</v>
       </c>
       <c r="W5" t="n">
-        <v>399.5678</v>
+        <v>400.4961</v>
       </c>
       <c r="X5" t="n">
-        <v>390.5647</v>
+        <v>388.0095</v>
       </c>
       <c r="Y5" t="n">
-        <v>392.6109</v>
+        <v>389.8062</v>
       </c>
       <c r="Z5" t="n">
-        <v>397.7139</v>
+        <v>397.1057</v>
       </c>
       <c r="AB5" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC5" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>30 jul</t>
+          <t>31 jul</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>38.6098</v>
       </c>
       <c r="C6" t="n">
-        <v>39.1444</v>
+        <v>39.575</v>
       </c>
       <c r="D6" t="n">
-        <v>38.3277</v>
+        <v>38.4464</v>
       </c>
       <c r="E6" t="n">
-        <v>38.5108</v>
+        <v>39.3226</v>
       </c>
       <c r="F6" t="n">
-        <v>35.9978</v>
+        <v>36.0495</v>
       </c>
       <c r="G6" t="n">
-        <v>34.0424</v>
+        <v>34.0907</v>
       </c>
       <c r="H6" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I6" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>30 jul</t>
+          <t>31 jul</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>162.5</v>
+        <v>154.9</v>
       </c>
       <c r="M6" t="n">
-        <v>163.16</v>
+        <v>158.26</v>
       </c>
       <c r="N6" t="n">
-        <v>155.2</v>
+        <v>153.6</v>
       </c>
       <c r="O6" t="n">
-        <v>155.92</v>
+        <v>157.68</v>
       </c>
       <c r="P6" t="n">
-        <v>144.3804</v>
+        <v>144.4984</v>
       </c>
       <c r="Q6" t="n">
-        <v>171.9849</v>
+        <v>171.6292</v>
       </c>
       <c r="R6" t="n">
         <v>191.5557367172241</v>
@@ -3819,86 +3841,86 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>29 jul</t>
+          <t>30 jul</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>392.6608</v>
+        <v>437.0772</v>
       </c>
       <c r="W6" t="n">
-        <v>400.4961</v>
+        <v>457.8281</v>
       </c>
       <c r="X6" t="n">
-        <v>388.0095</v>
+        <v>431.6275</v>
       </c>
       <c r="Y6" t="n">
-        <v>389.8062</v>
+        <v>450.2524</v>
       </c>
       <c r="Z6" t="n">
-        <v>397.1057</v>
+        <v>397.6741</v>
       </c>
       <c r="AA6" t="n">
-        <v>431.9565</v>
+        <v>431.6738</v>
       </c>
       <c r="AB6" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC6" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>31 jul</t>
+          <t>3 aug</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>38.6098</v>
+        <v>38.3128</v>
       </c>
       <c r="C7" t="n">
-        <v>39.575</v>
+        <v>39.4067</v>
       </c>
       <c r="D7" t="n">
-        <v>38.4464</v>
+        <v>38.2138</v>
       </c>
       <c r="E7" t="n">
-        <v>39.3226</v>
+        <v>39.4067</v>
       </c>
       <c r="F7" t="n">
-        <v>36.0495</v>
+        <v>36.1112</v>
       </c>
       <c r="G7" t="n">
-        <v>34.0907</v>
+        <v>34.1393</v>
       </c>
       <c r="H7" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I7" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>31 jul</t>
+          <t>3 aug</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>154.9</v>
+        <v>160</v>
       </c>
       <c r="M7" t="n">
-        <v>158.26</v>
+        <v>168.7</v>
       </c>
       <c r="N7" t="n">
-        <v>153.6</v>
+        <v>159.6</v>
       </c>
       <c r="O7" t="n">
-        <v>157.68</v>
+        <v>164.64</v>
       </c>
       <c r="P7" t="n">
-        <v>144.4984</v>
+        <v>144.7016</v>
       </c>
       <c r="Q7" t="n">
-        <v>171.6292</v>
+        <v>171.301</v>
       </c>
       <c r="R7" t="n">
         <v>191.5557367172241</v>
@@ -3908,86 +3930,86 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>30 jul</t>
+          <t>31 jul</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>437.0772</v>
+        <v>449.1545</v>
       </c>
       <c r="W7" t="n">
-        <v>457.8281</v>
+        <v>465.9628</v>
       </c>
       <c r="X7" t="n">
-        <v>431.6275</v>
+        <v>448.4857</v>
       </c>
       <c r="Y7" t="n">
-        <v>450.2524</v>
+        <v>463.8468</v>
       </c>
       <c r="Z7" t="n">
-        <v>397.6741</v>
+        <v>398.6364</v>
       </c>
       <c r="AA7" t="n">
-        <v>431.6738</v>
+        <v>431.4438</v>
       </c>
       <c r="AB7" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC7" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3 aug</t>
+          <t>4 aug</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>38.3128</v>
+        <v>39.3028</v>
       </c>
       <c r="C8" t="n">
-        <v>39.4067</v>
+        <v>39.6443</v>
       </c>
       <c r="D8" t="n">
-        <v>38.2138</v>
+        <v>38.2039</v>
       </c>
       <c r="E8" t="n">
-        <v>39.4067</v>
+        <v>38.486</v>
       </c>
       <c r="F8" t="n">
-        <v>36.1112</v>
+        <v>36.1495</v>
       </c>
       <c r="G8" t="n">
-        <v>34.1393</v>
+        <v>34.1818</v>
       </c>
       <c r="H8" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I8" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>3 aug</t>
+          <t>4 aug</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>160</v>
+        <v>162.86</v>
       </c>
       <c r="M8" t="n">
-        <v>168.7</v>
+        <v>168.56</v>
       </c>
       <c r="N8" t="n">
-        <v>159.6</v>
+        <v>162.4</v>
       </c>
       <c r="O8" t="n">
-        <v>164.64</v>
+        <v>167.38</v>
       </c>
       <c r="P8" t="n">
-        <v>144.7016</v>
+        <v>145.02</v>
       </c>
       <c r="Q8" t="n">
-        <v>171.301</v>
+        <v>170.9913</v>
       </c>
       <c r="R8" t="n">
         <v>191.5557367172241</v>
@@ -3997,86 +4019,86 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>31 jul</t>
+          <t>3 aug</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>449.1545</v>
+        <v>475.2354</v>
       </c>
       <c r="W8" t="n">
-        <v>465.9628</v>
+        <v>490.7262</v>
       </c>
       <c r="X8" t="n">
-        <v>448.4857</v>
+        <v>474.1075</v>
       </c>
       <c r="Y8" t="n">
-        <v>463.8468</v>
+        <v>486.7337</v>
       </c>
       <c r="Z8" t="n">
-        <v>398.6364</v>
+        <v>399.9838</v>
       </c>
       <c r="AA8" t="n">
-        <v>431.4438</v>
+        <v>431.3306</v>
       </c>
       <c r="AB8" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC8" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4 aug</t>
+          <t>5 aug</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>39.3028</v>
+        <v>38.4811</v>
       </c>
       <c r="C9" t="n">
-        <v>39.6443</v>
+        <v>38.7632</v>
       </c>
       <c r="D9" t="n">
-        <v>38.2039</v>
+        <v>37.9366</v>
       </c>
       <c r="E9" t="n">
-        <v>38.486</v>
+        <v>38.0307</v>
       </c>
       <c r="F9" t="n">
-        <v>36.1495</v>
+        <v>36.1966</v>
       </c>
       <c r="G9" t="n">
-        <v>34.1818</v>
+        <v>34.2215</v>
       </c>
       <c r="H9" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I9" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>4 aug</t>
+          <t>5 aug</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>162.86</v>
+        <v>167.92</v>
       </c>
       <c r="M9" t="n">
-        <v>168.56</v>
+        <v>172.6</v>
       </c>
       <c r="N9" t="n">
-        <v>162.4</v>
+        <v>167.3</v>
       </c>
       <c r="O9" t="n">
-        <v>167.38</v>
+        <v>169.26</v>
       </c>
       <c r="P9" t="n">
-        <v>145.02</v>
+        <v>145.4052</v>
       </c>
       <c r="Q9" t="n">
-        <v>170.9913</v>
+        <v>170.7022</v>
       </c>
       <c r="R9" t="n">
         <v>191.5557367172241</v>
@@ -4086,86 +4108,86 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>3 aug</t>
+          <t>4 aug</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>475.2354</v>
+        <v>479.9964</v>
       </c>
       <c r="W9" t="n">
-        <v>490.7262</v>
+        <v>498.5016</v>
       </c>
       <c r="X9" t="n">
-        <v>474.1075</v>
+        <v>478.2697</v>
       </c>
       <c r="Y9" t="n">
-        <v>486.7337</v>
+        <v>491.884</v>
       </c>
       <c r="Z9" t="n">
-        <v>399.9838</v>
+        <v>401.4555</v>
       </c>
       <c r="AA9" t="n">
-        <v>431.3306</v>
+        <v>431.2438</v>
       </c>
       <c r="AB9" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC9" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5 aug</t>
+          <t>6 aug</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>38.4811</v>
+        <v>38.0752</v>
       </c>
       <c r="C10" t="n">
-        <v>38.7632</v>
+        <v>38.4069</v>
       </c>
       <c r="D10" t="n">
-        <v>37.9366</v>
+        <v>37.9168</v>
       </c>
       <c r="E10" t="n">
-        <v>38.0307</v>
+        <v>38.392</v>
       </c>
       <c r="F10" t="n">
-        <v>36.1966</v>
+        <v>36.2474</v>
       </c>
       <c r="G10" t="n">
-        <v>34.2215</v>
+        <v>34.2607</v>
       </c>
       <c r="H10" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I10" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>5 aug</t>
+          <t>6 aug</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>167.92</v>
+        <v>171.44</v>
       </c>
       <c r="M10" t="n">
-        <v>172.6</v>
+        <v>173.1</v>
       </c>
       <c r="N10" t="n">
-        <v>167.3</v>
+        <v>168.08</v>
       </c>
       <c r="O10" t="n">
-        <v>169.26</v>
+        <v>170.98</v>
       </c>
       <c r="P10" t="n">
-        <v>145.4052</v>
+        <v>145.7928</v>
       </c>
       <c r="Q10" t="n">
-        <v>170.7022</v>
+        <v>170.384</v>
       </c>
       <c r="R10" t="n">
         <v>191.5557367172241</v>
@@ -4175,86 +4197,86 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>4 aug</t>
+          <t>5 aug</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>479.9964</v>
+        <v>495.4273</v>
       </c>
       <c r="W10" t="n">
-        <v>498.5016</v>
+        <v>497.3038</v>
       </c>
       <c r="X10" t="n">
-        <v>478.2697</v>
+        <v>484.7674</v>
       </c>
       <c r="Y10" t="n">
-        <v>491.884</v>
+        <v>486.5441</v>
       </c>
       <c r="Z10" t="n">
-        <v>401.4555</v>
+        <v>402.8307</v>
       </c>
       <c r="AA10" t="n">
-        <v>431.2438</v>
+        <v>431.1393</v>
       </c>
       <c r="AB10" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC10" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>6 aug</t>
+          <t>7 aug</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>38.0752</v>
+        <v>38.5207</v>
       </c>
       <c r="C11" t="n">
-        <v>38.4069</v>
+        <v>38.5999</v>
       </c>
       <c r="D11" t="n">
-        <v>37.9168</v>
+        <v>37.897</v>
       </c>
       <c r="E11" t="n">
-        <v>38.392</v>
+        <v>38.0059</v>
       </c>
       <c r="F11" t="n">
-        <v>36.2474</v>
+        <v>36.2952</v>
       </c>
       <c r="G11" t="n">
-        <v>34.2607</v>
+        <v>34.294</v>
       </c>
       <c r="H11" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I11" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>6 aug</t>
+          <t>7 aug</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>171.44</v>
+        <v>173.82</v>
       </c>
       <c r="M11" t="n">
-        <v>173.1</v>
+        <v>179.56</v>
       </c>
       <c r="N11" t="n">
-        <v>168.08</v>
+        <v>173.82</v>
       </c>
       <c r="O11" t="n">
-        <v>170.98</v>
+        <v>177.96</v>
       </c>
       <c r="P11" t="n">
-        <v>145.7928</v>
+        <v>146.2468</v>
       </c>
       <c r="Q11" t="n">
-        <v>170.384</v>
+        <v>170.0918</v>
       </c>
       <c r="R11" t="n">
         <v>191.5557367172241</v>
@@ -4264,86 +4286,86 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>5 aug</t>
+          <t>6 aug</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>495.4273</v>
+        <v>487.632</v>
       </c>
       <c r="W11" t="n">
-        <v>497.3038</v>
+        <v>500.6176</v>
       </c>
       <c r="X11" t="n">
-        <v>484.7674</v>
+        <v>487.6021</v>
       </c>
       <c r="Y11" t="n">
-        <v>486.5441</v>
+        <v>498.9207</v>
       </c>
       <c r="Z11" t="n">
-        <v>402.8307</v>
+        <v>404.5041</v>
       </c>
       <c r="AA11" t="n">
-        <v>431.1393</v>
+        <v>431.087</v>
       </c>
       <c r="AB11" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC11" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>7 aug</t>
+          <t>10 aug</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>38.5207</v>
+        <v>38.0356</v>
       </c>
       <c r="C12" t="n">
-        <v>38.5999</v>
+        <v>38.4366</v>
       </c>
       <c r="D12" t="n">
-        <v>37.897</v>
+        <v>37.803</v>
       </c>
       <c r="E12" t="n">
-        <v>38.0059</v>
+        <v>38.4019</v>
       </c>
       <c r="F12" t="n">
-        <v>36.2952</v>
+        <v>36.3315</v>
       </c>
       <c r="G12" t="n">
-        <v>34.294</v>
+        <v>34.3294</v>
       </c>
       <c r="H12" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I12" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>7 aug</t>
+          <t>10 aug</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>173.82</v>
+        <v>178.92</v>
       </c>
       <c r="M12" t="n">
-        <v>179.56</v>
+        <v>179.96</v>
       </c>
       <c r="N12" t="n">
-        <v>173.82</v>
+        <v>175.86</v>
       </c>
       <c r="O12" t="n">
-        <v>177.96</v>
+        <v>179.3</v>
       </c>
       <c r="P12" t="n">
-        <v>146.2468</v>
+        <v>146.4748</v>
       </c>
       <c r="Q12" t="n">
-        <v>170.0918</v>
+        <v>169.8238</v>
       </c>
       <c r="R12" t="n">
         <v>191.5557367172241</v>
@@ -4353,86 +4375,86 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>6 aug</t>
+          <t>7 aug</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>487.632</v>
+        <v>498.272</v>
       </c>
       <c r="W12" t="n">
-        <v>500.6176</v>
+        <v>504.2308</v>
       </c>
       <c r="X12" t="n">
-        <v>487.6021</v>
+        <v>497.7929</v>
       </c>
       <c r="Y12" t="n">
-        <v>498.9207</v>
+        <v>499.0505</v>
       </c>
       <c r="Z12" t="n">
-        <v>404.5041</v>
+        <v>406.2472</v>
       </c>
       <c r="AA12" t="n">
-        <v>431.087</v>
+        <v>431.0194</v>
       </c>
       <c r="AB12" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC12" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10 aug</t>
+          <t>11 aug</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>38.0356</v>
+        <v>38.7385</v>
       </c>
       <c r="C13" t="n">
-        <v>38.4366</v>
+        <v>39.0058</v>
       </c>
       <c r="D13" t="n">
-        <v>37.803</v>
+        <v>38.6148</v>
       </c>
       <c r="E13" t="n">
-        <v>38.4019</v>
+        <v>38.9662</v>
       </c>
       <c r="F13" t="n">
-        <v>36.3315</v>
+        <v>36.374</v>
       </c>
       <c r="G13" t="n">
-        <v>34.3294</v>
+        <v>34.3685</v>
       </c>
       <c r="H13" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I13" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>10 aug</t>
+          <t>11 aug</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>178.92</v>
+        <v>180</v>
       </c>
       <c r="M13" t="n">
-        <v>179.96</v>
+        <v>183.24</v>
       </c>
       <c r="N13" t="n">
-        <v>175.86</v>
+        <v>178.14</v>
       </c>
       <c r="O13" t="n">
-        <v>179.3</v>
+        <v>180.7</v>
       </c>
       <c r="P13" t="n">
-        <v>146.4748</v>
+        <v>146.8316</v>
       </c>
       <c r="Q13" t="n">
-        <v>169.8238</v>
+        <v>169.5375</v>
       </c>
       <c r="R13" t="n">
         <v>191.5557367172241</v>
@@ -4442,86 +4464,86 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>7 aug</t>
+          <t>10 aug</t>
         </is>
       </c>
       <c r="V13" t="n">
-        <v>498.272</v>
+        <v>502.4941</v>
       </c>
       <c r="W13" t="n">
-        <v>504.2308</v>
+        <v>512.7646999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>497.7929</v>
+        <v>501.3262</v>
       </c>
       <c r="Y13" t="n">
-        <v>499.0505</v>
+        <v>505.1091</v>
       </c>
       <c r="Z13" t="n">
-        <v>406.2472</v>
+        <v>407.8257</v>
       </c>
       <c r="AA13" t="n">
-        <v>431.0194</v>
+        <v>430.9778</v>
       </c>
       <c r="AB13" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC13" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>11 aug</t>
+          <t>12 aug</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>38.7385</v>
+        <v>38.8573</v>
       </c>
       <c r="C14" t="n">
-        <v>39.0058</v>
+        <v>38.986</v>
       </c>
       <c r="D14" t="n">
-        <v>38.6148</v>
+        <v>38.3871</v>
       </c>
       <c r="E14" t="n">
-        <v>38.9662</v>
+        <v>38.6494</v>
       </c>
       <c r="F14" t="n">
-        <v>36.374</v>
+        <v>36.3981</v>
       </c>
       <c r="G14" t="n">
-        <v>34.3685</v>
+        <v>34.4068</v>
       </c>
       <c r="H14" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I14" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>11 aug</t>
+          <t>12 aug</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>180</v>
+        <v>180.3</v>
       </c>
       <c r="M14" t="n">
-        <v>183.24</v>
+        <v>180.98</v>
       </c>
       <c r="N14" t="n">
-        <v>178.14</v>
+        <v>175.4</v>
       </c>
       <c r="O14" t="n">
-        <v>180.7</v>
+        <v>175.96</v>
       </c>
       <c r="P14" t="n">
-        <v>146.8316</v>
+        <v>147.232</v>
       </c>
       <c r="Q14" t="n">
-        <v>169.5375</v>
+        <v>169.2701</v>
       </c>
       <c r="R14" t="n">
         <v>191.5557367172241</v>
@@ -4531,86 +4553,86 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>10 aug</t>
+          <t>11 aug</t>
         </is>
       </c>
       <c r="V14" t="n">
-        <v>502.4941</v>
+        <v>503.3824</v>
       </c>
       <c r="W14" t="n">
-        <v>512.7646999999999</v>
+        <v>504.3805</v>
       </c>
       <c r="X14" t="n">
-        <v>501.3262</v>
+        <v>498.6113</v>
       </c>
       <c r="Y14" t="n">
-        <v>505.1091</v>
+        <v>502.8633</v>
       </c>
       <c r="Z14" t="n">
-        <v>407.8257</v>
+        <v>408.895</v>
       </c>
       <c r="AA14" t="n">
-        <v>430.9778</v>
+        <v>430.9106</v>
       </c>
       <c r="AB14" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC14" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>12 aug</t>
+          <t>13 aug</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>38.8573</v>
+        <v>39</v>
       </c>
       <c r="C15" t="n">
-        <v>38.986</v>
+        <v>39.005</v>
       </c>
       <c r="D15" t="n">
-        <v>38.3871</v>
+        <v>38.2</v>
       </c>
       <c r="E15" t="n">
-        <v>38.6494</v>
+        <v>38.605</v>
       </c>
       <c r="F15" t="n">
-        <v>36.3981</v>
+        <v>36.4313</v>
       </c>
       <c r="G15" t="n">
-        <v>34.4068</v>
+        <v>34.4429</v>
       </c>
       <c r="H15" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I15" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>12 aug</t>
+          <t>13 aug</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>180.3</v>
+        <v>177.48</v>
       </c>
       <c r="M15" t="n">
-        <v>180.98</v>
+        <v>178.3</v>
       </c>
       <c r="N15" t="n">
-        <v>175.4</v>
+        <v>174.8</v>
       </c>
       <c r="O15" t="n">
-        <v>175.96</v>
+        <v>175.38</v>
       </c>
       <c r="P15" t="n">
-        <v>147.232</v>
+        <v>147.4496</v>
       </c>
       <c r="Q15" t="n">
-        <v>169.2701</v>
+        <v>168.9889</v>
       </c>
       <c r="R15" t="n">
         <v>191.5557367172241</v>
@@ -4620,86 +4642,86 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>11 aug</t>
+          <t>12 aug</t>
         </is>
       </c>
       <c r="V15" t="n">
-        <v>503.3824</v>
+        <v>499.0505</v>
       </c>
       <c r="W15" t="n">
-        <v>504.3805</v>
+        <v>500.5577</v>
       </c>
       <c r="X15" t="n">
-        <v>498.6113</v>
+        <v>490.5964</v>
       </c>
       <c r="Y15" t="n">
-        <v>502.8633</v>
+        <v>491.5047</v>
       </c>
       <c r="Z15" t="n">
-        <v>408.895</v>
+        <v>409.532</v>
       </c>
       <c r="AA15" t="n">
-        <v>430.9106</v>
+        <v>430.7866</v>
       </c>
       <c r="AB15" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC15" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>13 aug</t>
+          <t>14 aug</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>39</v>
+        <v>38.65</v>
       </c>
       <c r="C16" t="n">
-        <v>39.005</v>
+        <v>39.1</v>
       </c>
       <c r="D16" t="n">
-        <v>38.2</v>
+        <v>38.56</v>
       </c>
       <c r="E16" t="n">
-        <v>38.605</v>
+        <v>38.97</v>
       </c>
       <c r="F16" t="n">
-        <v>36.4313</v>
+        <v>36.4703</v>
       </c>
       <c r="G16" t="n">
-        <v>34.4429</v>
+        <v>34.4805</v>
       </c>
       <c r="H16" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I16" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>13 aug</t>
+          <t>14 aug</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>177.48</v>
+        <v>182</v>
       </c>
       <c r="M16" t="n">
-        <v>178.3</v>
+        <v>185.74</v>
       </c>
       <c r="N16" t="n">
-        <v>174.8</v>
+        <v>179.28</v>
       </c>
       <c r="O16" t="n">
-        <v>175.38</v>
+        <v>180.14</v>
       </c>
       <c r="P16" t="n">
-        <v>147.4496</v>
+        <v>147.8228</v>
       </c>
       <c r="Q16" t="n">
-        <v>168.9889</v>
+        <v>168.7386</v>
       </c>
       <c r="R16" t="n">
         <v>191.5557367172241</v>
@@ -4709,86 +4731,86 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>12 aug</t>
+          <t>13 aug</t>
         </is>
       </c>
       <c r="V16" t="n">
-        <v>499.0505</v>
+        <v>492.3431</v>
       </c>
       <c r="W16" t="n">
-        <v>500.5577</v>
+        <v>500.398</v>
       </c>
       <c r="X16" t="n">
-        <v>490.5964</v>
+        <v>492.0837</v>
       </c>
       <c r="Y16" t="n">
-        <v>491.5047</v>
+        <v>495.9464</v>
       </c>
       <c r="Z16" t="n">
-        <v>409.532</v>
+        <v>410.6414</v>
       </c>
       <c r="AA16" t="n">
-        <v>430.7866</v>
+        <v>430.6696</v>
       </c>
       <c r="AB16" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC16" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>14 aug</t>
+          <t>17 aug</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>38.65</v>
+        <v>38.97</v>
       </c>
       <c r="C17" t="n">
-        <v>39.1</v>
+        <v>39.27</v>
       </c>
       <c r="D17" t="n">
-        <v>38.56</v>
+        <v>38.765</v>
       </c>
       <c r="E17" t="n">
-        <v>38.97</v>
+        <v>39.15</v>
       </c>
       <c r="F17" t="n">
-        <v>36.4703</v>
+        <v>36.5118</v>
       </c>
       <c r="G17" t="n">
-        <v>34.4805</v>
+        <v>34.5207</v>
       </c>
       <c r="H17" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I17" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>14 aug</t>
+          <t>17 aug</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>182</v>
+        <v>178.94</v>
       </c>
       <c r="M17" t="n">
-        <v>185.74</v>
+        <v>180.9</v>
       </c>
       <c r="N17" t="n">
-        <v>179.28</v>
+        <v>177.66</v>
       </c>
       <c r="O17" t="n">
-        <v>180.14</v>
+        <v>179.58</v>
       </c>
       <c r="P17" t="n">
-        <v>147.8228</v>
+        <v>148.2524</v>
       </c>
       <c r="Q17" t="n">
-        <v>168.7386</v>
+        <v>168.5337</v>
       </c>
       <c r="R17" t="n">
         <v>191.5557367172241</v>
@@ -4798,86 +4820,86 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>13 aug</t>
+          <t>14 aug</t>
         </is>
       </c>
       <c r="V17" t="n">
-        <v>492.3431</v>
+        <v>495.4273</v>
       </c>
       <c r="W17" t="n">
-        <v>500.398</v>
+        <v>499.0705</v>
       </c>
       <c r="X17" t="n">
-        <v>492.0837</v>
+        <v>492.9919</v>
       </c>
       <c r="Y17" t="n">
-        <v>495.9464</v>
+        <v>494.4691</v>
       </c>
       <c r="Z17" t="n">
-        <v>410.6414</v>
+        <v>412</v>
       </c>
       <c r="AA17" t="n">
-        <v>430.6696</v>
+        <v>430.5061</v>
       </c>
       <c r="AB17" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC17" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>17 aug</t>
+          <t>18 aug</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>38.97</v>
+        <v>39.49</v>
       </c>
       <c r="C18" t="n">
-        <v>39.27</v>
+        <v>39.945</v>
       </c>
       <c r="D18" t="n">
-        <v>38.765</v>
+        <v>39.46</v>
       </c>
       <c r="E18" t="n">
-        <v>39.15</v>
+        <v>39.785</v>
       </c>
       <c r="F18" t="n">
-        <v>36.5118</v>
+        <v>36.5781</v>
       </c>
       <c r="G18" t="n">
-        <v>34.5207</v>
+        <v>34.5641</v>
       </c>
       <c r="H18" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I18" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>17 aug</t>
+          <t>18 aug</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>178.94</v>
+        <v>179.14</v>
       </c>
       <c r="M18" t="n">
-        <v>180.9</v>
+        <v>183.9</v>
       </c>
       <c r="N18" t="n">
-        <v>177.66</v>
+        <v>177.98</v>
       </c>
       <c r="O18" t="n">
-        <v>179.58</v>
+        <v>182.5</v>
       </c>
       <c r="P18" t="n">
-        <v>148.2524</v>
+        <v>148.8084</v>
       </c>
       <c r="Q18" t="n">
-        <v>168.5337</v>
+        <v>168.3358</v>
       </c>
       <c r="R18" t="n">
         <v>191.5557367172241</v>
@@ -4887,86 +4909,86 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>14 aug</t>
+          <t>17 aug</t>
         </is>
       </c>
       <c r="V18" t="n">
-        <v>495.4273</v>
+        <v>489.2191</v>
       </c>
       <c r="W18" t="n">
-        <v>499.0705</v>
+        <v>491.7343</v>
       </c>
       <c r="X18" t="n">
-        <v>492.9919</v>
+        <v>477.5111</v>
       </c>
       <c r="Y18" t="n">
-        <v>494.4691</v>
+        <v>479.4474</v>
       </c>
       <c r="Z18" t="n">
-        <v>412</v>
+        <v>413.044</v>
       </c>
       <c r="AA18" t="n">
-        <v>430.5061</v>
+        <v>430.2151</v>
       </c>
       <c r="AB18" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC18" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>18 aug</t>
+          <t>19 aug</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>39.49</v>
+        <v>39.835</v>
       </c>
       <c r="C19" t="n">
-        <v>39.945</v>
+        <v>40.14</v>
       </c>
       <c r="D19" t="n">
-        <v>39.46</v>
+        <v>39.74</v>
       </c>
       <c r="E19" t="n">
-        <v>39.785</v>
+        <v>39.94</v>
       </c>
       <c r="F19" t="n">
-        <v>36.5781</v>
+        <v>36.6336</v>
       </c>
       <c r="G19" t="n">
-        <v>34.5641</v>
+        <v>34.6092</v>
       </c>
       <c r="H19" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I19" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>18 aug</t>
+          <t>19 aug</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>179.14</v>
+        <v>181.7</v>
       </c>
       <c r="M19" t="n">
-        <v>183.9</v>
+        <v>186.98</v>
       </c>
       <c r="N19" t="n">
-        <v>177.98</v>
+        <v>180.38</v>
       </c>
       <c r="O19" t="n">
-        <v>182.5</v>
+        <v>185.9</v>
       </c>
       <c r="P19" t="n">
-        <v>148.8084</v>
+        <v>149.5324</v>
       </c>
       <c r="Q19" t="n">
-        <v>168.3358</v>
+        <v>168.1618</v>
       </c>
       <c r="R19" t="n">
         <v>191.5557367172241</v>
@@ -4976,86 +4998,86 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>17 aug</t>
+          <t>18 aug</t>
         </is>
       </c>
       <c r="V19" t="n">
-        <v>489.2191</v>
+        <v>480.6352</v>
       </c>
       <c r="W19" t="n">
-        <v>491.7343</v>
+        <v>483.3601</v>
       </c>
       <c r="X19" t="n">
-        <v>477.5111</v>
+        <v>476.2534</v>
       </c>
       <c r="Y19" t="n">
-        <v>479.4474</v>
+        <v>480.725</v>
       </c>
       <c r="Z19" t="n">
-        <v>413.044</v>
+        <v>414.3408</v>
       </c>
       <c r="AA19" t="n">
-        <v>430.2151</v>
+        <v>429.933</v>
       </c>
       <c r="AB19" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC19" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>19 aug</t>
+          <t>20 aug</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>39.835</v>
+        <v>39.865</v>
       </c>
       <c r="C20" t="n">
-        <v>40.14</v>
+        <v>40.51</v>
       </c>
       <c r="D20" t="n">
-        <v>39.74</v>
+        <v>39.8</v>
       </c>
       <c r="E20" t="n">
-        <v>39.94</v>
+        <v>40.28</v>
       </c>
       <c r="F20" t="n">
-        <v>36.6336</v>
+        <v>36.6884</v>
       </c>
       <c r="G20" t="n">
-        <v>34.6092</v>
+        <v>34.6545</v>
       </c>
       <c r="H20" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I20" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>19 aug</t>
+          <t>20 aug</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>181.7</v>
+        <v>183.78</v>
       </c>
       <c r="M20" t="n">
-        <v>186.98</v>
+        <v>186.1</v>
       </c>
       <c r="N20" t="n">
-        <v>180.38</v>
+        <v>182.52</v>
       </c>
       <c r="O20" t="n">
-        <v>185.9</v>
+        <v>185.64</v>
       </c>
       <c r="P20" t="n">
-        <v>149.5324</v>
+        <v>150.4472</v>
       </c>
       <c r="Q20" t="n">
-        <v>168.1618</v>
+        <v>167.9648</v>
       </c>
       <c r="R20" t="n">
         <v>191.5557367172241</v>
@@ -5065,86 +5087,86 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>18 aug</t>
+          <t>19 aug</t>
         </is>
       </c>
       <c r="V20" t="n">
-        <v>480.6352</v>
+        <v>479.168</v>
       </c>
       <c r="W20" t="n">
-        <v>483.3601</v>
+        <v>488.3806</v>
       </c>
       <c r="X20" t="n">
-        <v>476.2534</v>
+        <v>478.4593</v>
       </c>
       <c r="Y20" t="n">
-        <v>480.725</v>
+        <v>483.4</v>
       </c>
       <c r="Z20" t="n">
-        <v>414.3408</v>
+        <v>415.7895</v>
       </c>
       <c r="AA20" t="n">
-        <v>429.933</v>
+        <v>429.7427</v>
       </c>
       <c r="AB20" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC20" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20 aug</t>
+          <t>21 aug</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>39.865</v>
+        <v>40.1</v>
       </c>
       <c r="C21" t="n">
-        <v>40.51</v>
+        <v>40.37</v>
       </c>
       <c r="D21" t="n">
-        <v>39.8</v>
+        <v>39.84</v>
       </c>
       <c r="E21" t="n">
-        <v>40.28</v>
+        <v>39.91</v>
       </c>
       <c r="F21" t="n">
-        <v>36.6884</v>
+        <v>36.7478</v>
       </c>
       <c r="G21" t="n">
-        <v>34.6545</v>
+        <v>34.6988</v>
       </c>
       <c r="H21" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I21" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>20 aug</t>
+          <t>21 aug</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>183.78</v>
+        <v>185.18</v>
       </c>
       <c r="M21" t="n">
-        <v>186.1</v>
+        <v>188.4</v>
       </c>
       <c r="N21" t="n">
-        <v>182.52</v>
+        <v>183.6</v>
       </c>
       <c r="O21" t="n">
-        <v>185.64</v>
+        <v>188.12</v>
       </c>
       <c r="P21" t="n">
-        <v>150.4472</v>
+        <v>151.4044</v>
       </c>
       <c r="Q21" t="n">
-        <v>167.9648</v>
+        <v>167.794</v>
       </c>
       <c r="R21" t="n">
         <v>191.5557367172241</v>
@@ -5154,86 +5176,86 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>19 aug</t>
+          <t>20 aug</t>
         </is>
       </c>
       <c r="V21" t="n">
-        <v>479.168</v>
+        <v>483.3</v>
       </c>
       <c r="W21" t="n">
-        <v>488.3806</v>
+        <v>484.16</v>
       </c>
       <c r="X21" t="n">
-        <v>478.4593</v>
+        <v>479.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>483.4</v>
+        <v>481.15</v>
       </c>
       <c r="Z21" t="n">
-        <v>415.7895</v>
+        <v>417.3594</v>
       </c>
       <c r="AA21" t="n">
-        <v>429.7427</v>
+        <v>429.5805</v>
       </c>
       <c r="AB21" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC21" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>21 aug</t>
+          <t>24 aug</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>40.1</v>
+        <v>39.88</v>
       </c>
       <c r="C22" t="n">
-        <v>40.37</v>
+        <v>40.085</v>
       </c>
       <c r="D22" t="n">
-        <v>39.84</v>
+        <v>39.68</v>
       </c>
       <c r="E22" t="n">
-        <v>39.91</v>
+        <v>39.775</v>
       </c>
       <c r="F22" t="n">
-        <v>36.7478</v>
+        <v>36.8369</v>
       </c>
       <c r="G22" t="n">
-        <v>34.6988</v>
+        <v>34.7421</v>
       </c>
       <c r="H22" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I22" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>21 aug</t>
+          <t>24 aug</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>185.18</v>
+        <v>186.86</v>
       </c>
       <c r="M22" t="n">
-        <v>188.4</v>
+        <v>188.16</v>
       </c>
       <c r="N22" t="n">
-        <v>183.6</v>
+        <v>185.52</v>
       </c>
       <c r="O22" t="n">
-        <v>188.12</v>
+        <v>187.2</v>
       </c>
       <c r="P22" t="n">
-        <v>151.4044</v>
+        <v>152.2848</v>
       </c>
       <c r="Q22" t="n">
-        <v>167.794</v>
+        <v>167.6093</v>
       </c>
       <c r="R22" t="n">
         <v>191.5557367172241</v>
@@ -5243,86 +5265,86 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>20 aug</t>
+          <t>21 aug</t>
         </is>
       </c>
       <c r="V22" t="n">
-        <v>483.3</v>
+        <v>479.88</v>
       </c>
       <c r="W22" t="n">
-        <v>484.16</v>
+        <v>486.36</v>
       </c>
       <c r="X22" t="n">
-        <v>479.5</v>
+        <v>478.53</v>
       </c>
       <c r="Y22" t="n">
-        <v>481.15</v>
+        <v>483.24</v>
       </c>
       <c r="Z22" t="n">
-        <v>417.3594</v>
+        <v>419.092</v>
       </c>
       <c r="AA22" t="n">
-        <v>429.5805</v>
+        <v>429.4327</v>
       </c>
       <c r="AB22" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC22" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>24 aug</t>
+          <t>25 aug</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>39.88</v>
+        <v>39.77</v>
       </c>
       <c r="C23" t="n">
-        <v>40.085</v>
+        <v>39.915</v>
       </c>
       <c r="D23" t="n">
-        <v>39.68</v>
+        <v>39.385</v>
       </c>
       <c r="E23" t="n">
-        <v>39.775</v>
+        <v>39.6</v>
       </c>
       <c r="F23" t="n">
-        <v>36.8369</v>
+        <v>36.926</v>
       </c>
       <c r="G23" t="n">
-        <v>34.7421</v>
+        <v>34.783</v>
       </c>
       <c r="H23" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I23" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>24 aug</t>
+          <t>25 aug</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>186.86</v>
+        <v>186.4</v>
       </c>
       <c r="M23" t="n">
-        <v>188.16</v>
+        <v>187.62</v>
       </c>
       <c r="N23" t="n">
-        <v>185.52</v>
+        <v>182.74</v>
       </c>
       <c r="O23" t="n">
-        <v>187.2</v>
+        <v>185.46</v>
       </c>
       <c r="P23" t="n">
-        <v>152.2848</v>
+        <v>153.136</v>
       </c>
       <c r="Q23" t="n">
-        <v>167.6093</v>
+        <v>167.4651</v>
       </c>
       <c r="R23" t="n">
         <v>191.5557367172241</v>
@@ -5332,86 +5354,86 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>21 aug</t>
+          <t>24 aug</t>
         </is>
       </c>
       <c r="V23" t="n">
-        <v>479.88</v>
+        <v>483.21</v>
       </c>
       <c r="W23" t="n">
-        <v>486.36</v>
+        <v>490.61</v>
       </c>
       <c r="X23" t="n">
-        <v>478.53</v>
+        <v>481.86</v>
       </c>
       <c r="Y23" t="n">
-        <v>483.24</v>
+        <v>487.31</v>
       </c>
       <c r="Z23" t="n">
-        <v>419.092</v>
+        <v>421.046</v>
       </c>
       <c r="AA23" t="n">
-        <v>429.4327</v>
+        <v>429.3185</v>
       </c>
       <c r="AB23" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC23" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>25 aug</t>
+          <t>26 aug</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>39.77</v>
+        <v>39.275</v>
       </c>
       <c r="C24" t="n">
-        <v>39.915</v>
+        <v>39.47</v>
       </c>
       <c r="D24" t="n">
-        <v>39.385</v>
+        <v>38.91</v>
       </c>
       <c r="E24" t="n">
-        <v>39.6</v>
+        <v>39.42</v>
       </c>
       <c r="F24" t="n">
-        <v>36.926</v>
+        <v>37.0192</v>
       </c>
       <c r="G24" t="n">
-        <v>34.783</v>
+        <v>34.8202</v>
       </c>
       <c r="H24" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I24" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>25 aug</t>
+          <t>26 aug</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>186.4</v>
+        <v>179.92</v>
       </c>
       <c r="M24" t="n">
-        <v>187.62</v>
+        <v>182.16</v>
       </c>
       <c r="N24" t="n">
-        <v>182.74</v>
+        <v>176.82</v>
       </c>
       <c r="O24" t="n">
-        <v>185.46</v>
+        <v>180.02</v>
       </c>
       <c r="P24" t="n">
-        <v>153.136</v>
+        <v>153.9128</v>
       </c>
       <c r="Q24" t="n">
-        <v>167.4651</v>
+        <v>167.3049</v>
       </c>
       <c r="R24" t="n">
         <v>191.5557367172241</v>
@@ -5421,86 +5443,86 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>24 aug</t>
+          <t>25 aug</t>
         </is>
       </c>
       <c r="V24" t="n">
-        <v>483.21</v>
+        <v>485.44</v>
       </c>
       <c r="W24" t="n">
-        <v>490.61</v>
+        <v>492.44</v>
       </c>
       <c r="X24" t="n">
-        <v>481.86</v>
+        <v>484.3</v>
       </c>
       <c r="Y24" t="n">
-        <v>487.31</v>
+        <v>491.71</v>
       </c>
       <c r="Z24" t="n">
-        <v>421.046</v>
+        <v>423.0801</v>
       </c>
       <c r="AA24" t="n">
-        <v>429.3185</v>
+        <v>429.262</v>
       </c>
       <c r="AB24" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC24" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>26 aug</t>
+          <t>27 aug</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>39.275</v>
+        <v>39.16</v>
       </c>
       <c r="C25" t="n">
-        <v>39.47</v>
+        <v>39.295</v>
       </c>
       <c r="D25" t="n">
-        <v>38.91</v>
+        <v>38.65</v>
       </c>
       <c r="E25" t="n">
-        <v>39.42</v>
+        <v>38.76</v>
       </c>
       <c r="F25" t="n">
-        <v>37.0192</v>
+        <v>37.117</v>
       </c>
       <c r="G25" t="n">
-        <v>34.8202</v>
+        <v>34.8559</v>
       </c>
       <c r="H25" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I25" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>26 aug</t>
+          <t>27 aug</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>179.92</v>
+        <v>182.5</v>
       </c>
       <c r="M25" t="n">
-        <v>182.16</v>
+        <v>190.8</v>
       </c>
       <c r="N25" t="n">
-        <v>176.82</v>
+        <v>181.14</v>
       </c>
       <c r="O25" t="n">
-        <v>180.02</v>
+        <v>189.88</v>
       </c>
       <c r="P25" t="n">
-        <v>153.9128</v>
+        <v>155.0132</v>
       </c>
       <c r="Q25" t="n">
-        <v>167.3049</v>
+        <v>167.1911</v>
       </c>
       <c r="R25" t="n">
         <v>191.5557367172241</v>
@@ -5510,86 +5532,86 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>25 aug</t>
+          <t>26 aug</t>
         </is>
       </c>
       <c r="V25" t="n">
-        <v>485.44</v>
+        <v>487.85</v>
       </c>
       <c r="W25" t="n">
-        <v>492.44</v>
+        <v>497.4</v>
       </c>
       <c r="X25" t="n">
-        <v>484.3</v>
+        <v>487.31</v>
       </c>
       <c r="Y25" t="n">
-        <v>491.71</v>
+        <v>496.37</v>
       </c>
       <c r="Z25" t="n">
-        <v>423.0801</v>
+        <v>425.0273</v>
       </c>
       <c r="AA25" t="n">
-        <v>429.262</v>
+        <v>429.2786</v>
       </c>
       <c r="AB25" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC25" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>27 aug</t>
+          <t>28 aug</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>39.16</v>
+        <v>39</v>
       </c>
       <c r="C26" t="n">
-        <v>39.295</v>
+        <v>39.18</v>
       </c>
       <c r="D26" t="n">
-        <v>38.65</v>
+        <v>38.845</v>
       </c>
       <c r="E26" t="n">
-        <v>38.76</v>
+        <v>39.145</v>
       </c>
       <c r="F26" t="n">
-        <v>37.117</v>
+        <v>37.2162</v>
       </c>
       <c r="G26" t="n">
-        <v>34.8559</v>
+        <v>34.8941</v>
       </c>
       <c r="H26" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I26" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>27 aug</t>
+          <t>28 aug</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>182.5</v>
+        <v>189.5</v>
       </c>
       <c r="M26" t="n">
-        <v>190.8</v>
+        <v>191.94</v>
       </c>
       <c r="N26" t="n">
-        <v>181.14</v>
+        <v>187.98</v>
       </c>
       <c r="O26" t="n">
-        <v>189.88</v>
+        <v>191.32</v>
       </c>
       <c r="P26" t="n">
-        <v>155.0132</v>
+        <v>156.1568</v>
       </c>
       <c r="Q26" t="n">
-        <v>167.1911</v>
+        <v>167.0806</v>
       </c>
       <c r="R26" t="n">
         <v>191.5557367172241</v>
@@ -5599,86 +5621,86 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>26 aug</t>
+          <t>27 aug</t>
         </is>
       </c>
       <c r="V26" t="n">
-        <v>487.85</v>
+        <v>494.88</v>
       </c>
       <c r="W26" t="n">
-        <v>497.4</v>
+        <v>506.48</v>
       </c>
       <c r="X26" t="n">
-        <v>487.31</v>
+        <v>490.08</v>
       </c>
       <c r="Y26" t="n">
-        <v>496.37</v>
+        <v>505.06</v>
       </c>
       <c r="Z26" t="n">
-        <v>425.0273</v>
+        <v>427.2667</v>
       </c>
       <c r="AA26" t="n">
-        <v>429.2786</v>
+        <v>429.3401</v>
       </c>
       <c r="AB26" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC26" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>28 aug</t>
+          <t>31 aug</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>39</v>
+        <v>39.54</v>
       </c>
       <c r="C27" t="n">
-        <v>39.18</v>
+        <v>39.91</v>
       </c>
       <c r="D27" t="n">
-        <v>38.845</v>
+        <v>39.24</v>
       </c>
       <c r="E27" t="n">
-        <v>39.145</v>
+        <v>39.335</v>
       </c>
       <c r="F27" t="n">
-        <v>37.2162</v>
+        <v>37.3111</v>
       </c>
       <c r="G27" t="n">
-        <v>34.8941</v>
+        <v>34.9333</v>
       </c>
       <c r="H27" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I27" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>28 aug</t>
+          <t>31 aug</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>189.5</v>
+        <v>188.46</v>
       </c>
       <c r="M27" t="n">
-        <v>191.94</v>
+        <v>192.12</v>
       </c>
       <c r="N27" t="n">
-        <v>187.98</v>
+        <v>188.2</v>
       </c>
       <c r="O27" t="n">
-        <v>191.32</v>
+        <v>190.9</v>
       </c>
       <c r="P27" t="n">
-        <v>156.1568</v>
+        <v>157.3304</v>
       </c>
       <c r="Q27" t="n">
-        <v>167.0806</v>
+        <v>166.9613</v>
       </c>
       <c r="R27" t="n">
         <v>191.5557367172241</v>
@@ -5688,86 +5710,86 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>27 aug</t>
+          <t>28 aug</t>
         </is>
       </c>
       <c r="V27" t="n">
-        <v>494.88</v>
+        <v>505.33</v>
       </c>
       <c r="W27" t="n">
-        <v>506.48</v>
+        <v>517.78</v>
       </c>
       <c r="X27" t="n">
-        <v>490.08</v>
+        <v>504.87</v>
       </c>
       <c r="Y27" t="n">
-        <v>505.06</v>
+        <v>513.53</v>
       </c>
       <c r="Z27" t="n">
-        <v>427.2667</v>
+        <v>429.9734</v>
       </c>
       <c r="AA27" t="n">
-        <v>429.3401</v>
+        <v>429.3984</v>
       </c>
       <c r="AB27" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC27" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>31 aug</t>
+          <t>1 sep</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>39.54</v>
+        <v>39.77</v>
       </c>
       <c r="C28" t="n">
-        <v>39.91</v>
+        <v>40.19</v>
       </c>
       <c r="D28" t="n">
-        <v>39.24</v>
+        <v>39.645</v>
       </c>
       <c r="E28" t="n">
-        <v>39.335</v>
+        <v>40.155</v>
       </c>
       <c r="F28" t="n">
-        <v>37.3111</v>
+        <v>37.4239</v>
       </c>
       <c r="G28" t="n">
-        <v>34.9333</v>
+        <v>34.9763</v>
       </c>
       <c r="H28" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I28" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>31 aug</t>
+          <t>1 sep</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>188.46</v>
+        <v>186</v>
       </c>
       <c r="M28" t="n">
-        <v>192.12</v>
+        <v>187.86</v>
       </c>
       <c r="N28" t="n">
-        <v>188.2</v>
+        <v>183.32</v>
       </c>
       <c r="O28" t="n">
-        <v>190.9</v>
+        <v>184.26</v>
       </c>
       <c r="P28" t="n">
-        <v>157.3304</v>
+        <v>158.3252</v>
       </c>
       <c r="Q28" t="n">
-        <v>166.9613</v>
+        <v>166.8103</v>
       </c>
       <c r="R28" t="n">
         <v>191.5557367172241</v>
@@ -5777,86 +5799,86 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>28 aug</t>
+          <t>31 aug</t>
         </is>
       </c>
       <c r="V28" t="n">
-        <v>505.33</v>
+        <v>510.38</v>
       </c>
       <c r="W28" t="n">
-        <v>517.78</v>
+        <v>512.1900000000001</v>
       </c>
       <c r="X28" t="n">
-        <v>504.87</v>
+        <v>506.39</v>
       </c>
       <c r="Y28" t="n">
-        <v>513.53</v>
+        <v>507.29</v>
       </c>
       <c r="Z28" t="n">
-        <v>429.9734</v>
+        <v>432.5454</v>
       </c>
       <c r="AA28" t="n">
-        <v>429.3984</v>
+        <v>429.4122</v>
       </c>
       <c r="AB28" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC28" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1 sep</t>
+          <t>2 sep</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>39.77</v>
+        <v>40.35</v>
       </c>
       <c r="C29" t="n">
-        <v>40.19</v>
+        <v>40.615</v>
       </c>
       <c r="D29" t="n">
-        <v>39.645</v>
+        <v>39.975</v>
       </c>
       <c r="E29" t="n">
-        <v>40.155</v>
+        <v>40.21</v>
       </c>
       <c r="F29" t="n">
-        <v>37.4239</v>
+        <v>37.5499</v>
       </c>
       <c r="G29" t="n">
-        <v>34.9763</v>
+        <v>35.0217</v>
       </c>
       <c r="H29" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I29" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1 sep</t>
+          <t>2 sep</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>186</v>
+        <v>182.18</v>
       </c>
       <c r="M29" t="n">
-        <v>187.86</v>
+        <v>184.7</v>
       </c>
       <c r="N29" t="n">
-        <v>183.32</v>
+        <v>180.72</v>
       </c>
       <c r="O29" t="n">
-        <v>184.26</v>
+        <v>181.44</v>
       </c>
       <c r="P29" t="n">
-        <v>158.3252</v>
+        <v>159.2568</v>
       </c>
       <c r="Q29" t="n">
-        <v>166.8103</v>
+        <v>166.6796</v>
       </c>
       <c r="R29" t="n">
         <v>191.5557367172241</v>
@@ -5866,86 +5888,86 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>31 aug</t>
+          <t>1 sep</t>
         </is>
       </c>
       <c r="V29" t="n">
-        <v>510.38</v>
+        <v>497.52</v>
       </c>
       <c r="W29" t="n">
-        <v>512.1900000000001</v>
+        <v>505.97</v>
       </c>
       <c r="X29" t="n">
-        <v>506.39</v>
+        <v>496.78</v>
       </c>
       <c r="Y29" t="n">
-        <v>507.29</v>
+        <v>501.02</v>
       </c>
       <c r="Z29" t="n">
-        <v>432.5454</v>
+        <v>435.2328</v>
       </c>
       <c r="AA29" t="n">
-        <v>429.4122</v>
+        <v>429.3825</v>
       </c>
       <c r="AB29" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC29" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2 sep</t>
+          <t>3 sep</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>40.35</v>
+        <v>40.095</v>
       </c>
       <c r="C30" t="n">
-        <v>40.615</v>
+        <v>40.215</v>
       </c>
       <c r="D30" t="n">
-        <v>39.975</v>
+        <v>39.54</v>
       </c>
       <c r="E30" t="n">
-        <v>40.21</v>
+        <v>40.04</v>
       </c>
       <c r="F30" t="n">
-        <v>37.5499</v>
+        <v>37.6767</v>
       </c>
       <c r="G30" t="n">
-        <v>35.0217</v>
+        <v>35.0679</v>
       </c>
       <c r="H30" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I30" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2 sep</t>
+          <t>3 sep</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>182.18</v>
+        <v>182.08</v>
       </c>
       <c r="M30" t="n">
-        <v>184.7</v>
+        <v>187.56</v>
       </c>
       <c r="N30" t="n">
-        <v>180.72</v>
+        <v>182</v>
       </c>
       <c r="O30" t="n">
-        <v>181.44</v>
+        <v>185.58</v>
       </c>
       <c r="P30" t="n">
-        <v>159.2568</v>
+        <v>160.3228</v>
       </c>
       <c r="Q30" t="n">
-        <v>166.6796</v>
+        <v>166.5898</v>
       </c>
       <c r="R30" t="n">
         <v>191.5557367172241</v>
@@ -5955,86 +5977,86 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>1 sep</t>
+          <t>2 sep</t>
         </is>
       </c>
       <c r="V30" t="n">
-        <v>497.52</v>
+        <v>499.85</v>
       </c>
       <c r="W30" t="n">
-        <v>505.97</v>
+        <v>500.27</v>
       </c>
       <c r="X30" t="n">
-        <v>496.78</v>
+        <v>493.81</v>
       </c>
       <c r="Y30" t="n">
-        <v>501.02</v>
+        <v>496.82</v>
       </c>
       <c r="Z30" t="n">
-        <v>435.2328</v>
+        <v>437.7045</v>
       </c>
       <c r="AA30" t="n">
-        <v>429.3825</v>
+        <v>429.3706</v>
       </c>
       <c r="AB30" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC30" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3 sep</t>
+          <t>4 sep</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>40.095</v>
+        <v>40.145</v>
       </c>
       <c r="C31" t="n">
-        <v>40.215</v>
+        <v>40.28</v>
       </c>
       <c r="D31" t="n">
-        <v>39.54</v>
+        <v>39.665</v>
       </c>
       <c r="E31" t="n">
-        <v>40.04</v>
+        <v>40.105</v>
       </c>
       <c r="F31" t="n">
-        <v>37.6767</v>
+        <v>37.8115</v>
       </c>
       <c r="G31" t="n">
-        <v>35.0679</v>
+        <v>35.113</v>
       </c>
       <c r="H31" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I31" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>3 sep</t>
+          <t>4 sep</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>182.08</v>
+        <v>187.8</v>
       </c>
       <c r="M31" t="n">
-        <v>187.56</v>
+        <v>189.9</v>
       </c>
       <c r="N31" t="n">
-        <v>182</v>
+        <v>184.96</v>
       </c>
       <c r="O31" t="n">
-        <v>185.58</v>
+        <v>185.68</v>
       </c>
       <c r="P31" t="n">
-        <v>160.3228</v>
+        <v>161.3336</v>
       </c>
       <c r="Q31" t="n">
-        <v>166.5898</v>
+        <v>166.5086</v>
       </c>
       <c r="R31" t="n">
         <v>191.5557367172241</v>
@@ -6044,86 +6066,86 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>2 sep</t>
+          <t>3 sep</t>
         </is>
       </c>
       <c r="V31" t="n">
-        <v>499.85</v>
+        <v>501.66</v>
       </c>
       <c r="W31" t="n">
-        <v>500.27</v>
+        <v>515.65</v>
       </c>
       <c r="X31" t="n">
-        <v>493.81</v>
+        <v>500.8</v>
       </c>
       <c r="Y31" t="n">
-        <v>496.82</v>
+        <v>510.12</v>
       </c>
       <c r="Z31" t="n">
-        <v>437.7045</v>
+        <v>440.6114</v>
       </c>
       <c r="AA31" t="n">
-        <v>429.3706</v>
+        <v>429.3912</v>
       </c>
       <c r="AB31" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC31" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4 sep</t>
+          <t>7 sep</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>40.145</v>
+        <v>40.26</v>
       </c>
       <c r="C32" t="n">
-        <v>40.28</v>
+        <v>40.845</v>
       </c>
       <c r="D32" t="n">
-        <v>39.665</v>
+        <v>40.12</v>
       </c>
       <c r="E32" t="n">
-        <v>40.105</v>
+        <v>40.56</v>
       </c>
       <c r="F32" t="n">
-        <v>37.8115</v>
+        <v>37.9551</v>
       </c>
       <c r="G32" t="n">
-        <v>35.113</v>
+        <v>35.1619</v>
       </c>
       <c r="H32" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I32" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>4 sep</t>
+          <t>7 sep</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>187.8</v>
+        <v>183.56</v>
       </c>
       <c r="M32" t="n">
-        <v>189.9</v>
+        <v>184.3</v>
       </c>
       <c r="N32" t="n">
-        <v>184.96</v>
+        <v>179.92</v>
       </c>
       <c r="O32" t="n">
-        <v>185.68</v>
+        <v>182.8</v>
       </c>
       <c r="P32" t="n">
-        <v>161.3336</v>
+        <v>162.2568</v>
       </c>
       <c r="Q32" t="n">
-        <v>166.5086</v>
+        <v>166.4122</v>
       </c>
       <c r="R32" t="n">
         <v>191.5557367172241</v>
@@ -6133,86 +6155,86 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>3 sep</t>
+          <t>4 sep</t>
         </is>
       </c>
       <c r="V32" t="n">
-        <v>501.66</v>
+        <v>510</v>
       </c>
       <c r="W32" t="n">
-        <v>515.65</v>
+        <v>511</v>
       </c>
       <c r="X32" t="n">
-        <v>500.8</v>
+        <v>499.36</v>
       </c>
       <c r="Y32" t="n">
-        <v>510.12</v>
+        <v>499.7</v>
       </c>
       <c r="Z32" t="n">
-        <v>440.6114</v>
+        <v>443.5621</v>
       </c>
       <c r="AA32" t="n">
-        <v>429.3912</v>
+        <v>429.3729</v>
       </c>
       <c r="AB32" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC32" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>7 sep</t>
+          <t>8 sep</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>40.26</v>
+        <v>40.83</v>
       </c>
       <c r="C33" t="n">
-        <v>40.845</v>
+        <v>41.18</v>
       </c>
       <c r="D33" t="n">
-        <v>40.12</v>
+        <v>40.6325</v>
       </c>
       <c r="E33" t="n">
-        <v>40.56</v>
+        <v>40.855</v>
       </c>
       <c r="F33" t="n">
-        <v>37.9551</v>
+        <v>38.0977</v>
       </c>
       <c r="G33" t="n">
-        <v>35.1619</v>
+        <v>35.2131</v>
       </c>
       <c r="H33" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I33" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>7 sep</t>
+          <t>8 sep</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>183.56</v>
+        <v>182.32</v>
       </c>
       <c r="M33" t="n">
-        <v>184.3</v>
+        <v>183.76</v>
       </c>
       <c r="N33" t="n">
-        <v>179.92</v>
+        <v>180.02</v>
       </c>
       <c r="O33" t="n">
-        <v>182.8</v>
+        <v>181.7</v>
       </c>
       <c r="P33" t="n">
-        <v>162.2568</v>
+        <v>163.2108</v>
       </c>
       <c r="Q33" t="n">
-        <v>166.4122</v>
+        <v>166.3049</v>
       </c>
       <c r="R33" t="n">
         <v>191.5557367172241</v>
@@ -6222,86 +6244,86 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>4 sep</t>
+          <t>8 sep</t>
         </is>
       </c>
       <c r="V33" t="n">
-        <v>510</v>
+        <v>493.01</v>
       </c>
       <c r="W33" t="n">
-        <v>511</v>
+        <v>495.19</v>
       </c>
       <c r="X33" t="n">
-        <v>499.36</v>
+        <v>490.15</v>
       </c>
       <c r="Y33" t="n">
-        <v>499.7</v>
+        <v>493.95</v>
       </c>
       <c r="Z33" t="n">
-        <v>443.5621</v>
+        <v>445.9957</v>
       </c>
       <c r="AA33" t="n">
-        <v>429.3729</v>
+        <v>429.3939</v>
       </c>
       <c r="AB33" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC33" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>8 sep</t>
+          <t>9 sep</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>40.83</v>
+        <v>41.1</v>
       </c>
       <c r="C34" t="n">
-        <v>41.18</v>
+        <v>41.385</v>
       </c>
       <c r="D34" t="n">
-        <v>40.6325</v>
+        <v>40.85</v>
       </c>
       <c r="E34" t="n">
-        <v>40.855</v>
+        <v>40.94</v>
       </c>
       <c r="F34" t="n">
-        <v>38.0977</v>
+        <v>38.2513</v>
       </c>
       <c r="G34" t="n">
-        <v>35.2131</v>
+        <v>35.2646</v>
       </c>
       <c r="H34" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I34" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>8 sep</t>
+          <t>9 sep</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>182.32</v>
+        <v>183</v>
       </c>
       <c r="M34" t="n">
-        <v>183.76</v>
+        <v>187.04</v>
       </c>
       <c r="N34" t="n">
-        <v>180.02</v>
+        <v>181.36</v>
       </c>
       <c r="O34" t="n">
-        <v>181.7</v>
+        <v>182.86</v>
       </c>
       <c r="P34" t="n">
-        <v>163.2108</v>
+        <v>164.0504</v>
       </c>
       <c r="Q34" t="n">
-        <v>166.3049</v>
+        <v>166.2113</v>
       </c>
       <c r="R34" t="n">
         <v>191.5557367172241</v>
@@ -6311,86 +6333,86 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>8 sep</t>
+          <t>9 sep</t>
         </is>
       </c>
       <c r="V34" t="n">
-        <v>493.01</v>
+        <v>493.07</v>
       </c>
       <c r="W34" t="n">
-        <v>495.19</v>
+        <v>494.39</v>
       </c>
       <c r="X34" t="n">
-        <v>490.15</v>
+        <v>489.8</v>
       </c>
       <c r="Y34" t="n">
-        <v>493.95</v>
+        <v>491.65</v>
       </c>
       <c r="Z34" t="n">
-        <v>445.9957</v>
+        <v>448.4712</v>
       </c>
       <c r="AA34" t="n">
-        <v>429.3939</v>
+        <v>429.4364</v>
       </c>
       <c r="AB34" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC34" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>9 sep</t>
+          <t>10 sep</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>41.1</v>
+        <v>40.98</v>
       </c>
       <c r="C35" t="n">
-        <v>41.385</v>
+        <v>41.77</v>
       </c>
       <c r="D35" t="n">
-        <v>40.85</v>
+        <v>40.93</v>
       </c>
       <c r="E35" t="n">
-        <v>40.94</v>
+        <v>41.23</v>
       </c>
       <c r="F35" t="n">
-        <v>38.2513</v>
+        <v>38.4034</v>
       </c>
       <c r="G35" t="n">
-        <v>35.2646</v>
+        <v>35.3174</v>
       </c>
       <c r="H35" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I35" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>9 sep</t>
+          <t>10 sep</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="M35" t="n">
-        <v>187.04</v>
+        <v>180.4</v>
       </c>
       <c r="N35" t="n">
-        <v>181.36</v>
+        <v>176.2</v>
       </c>
       <c r="O35" t="n">
-        <v>182.86</v>
+        <v>177.82</v>
       </c>
       <c r="P35" t="n">
-        <v>164.0504</v>
+        <v>164.7724</v>
       </c>
       <c r="Q35" t="n">
-        <v>166.2113</v>
+        <v>166.0803</v>
       </c>
       <c r="R35" t="n">
         <v>191.5557367172241</v>
@@ -6400,86 +6422,86 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>9 sep</t>
+          <t>10 sep</t>
         </is>
       </c>
       <c r="V35" t="n">
-        <v>493.07</v>
+        <v>488.32</v>
       </c>
       <c r="W35" t="n">
-        <v>494.39</v>
+        <v>494.52</v>
       </c>
       <c r="X35" t="n">
-        <v>489.8</v>
+        <v>486</v>
       </c>
       <c r="Y35" t="n">
-        <v>491.65</v>
+        <v>492.44</v>
       </c>
       <c r="Z35" t="n">
-        <v>448.4712</v>
+        <v>450.8736</v>
       </c>
       <c r="AA35" t="n">
-        <v>429.4364</v>
+        <v>429.5215</v>
       </c>
       <c r="AB35" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC35" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10 sep</t>
+          <t>11 sep</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>40.98</v>
+        <v>41.345</v>
       </c>
       <c r="C36" t="n">
-        <v>41.77</v>
+        <v>41.715</v>
       </c>
       <c r="D36" t="n">
-        <v>40.93</v>
+        <v>40.905</v>
       </c>
       <c r="E36" t="n">
-        <v>41.23</v>
+        <v>41.415</v>
       </c>
       <c r="F36" t="n">
-        <v>38.4034</v>
+        <v>38.5608</v>
       </c>
       <c r="G36" t="n">
-        <v>35.3174</v>
+        <v>35.3717</v>
       </c>
       <c r="H36" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I36" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>10 sep</t>
+          <t>11 sep</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>180</v>
+        <v>175.68</v>
       </c>
       <c r="M36" t="n">
-        <v>180.4</v>
+        <v>178.84</v>
       </c>
       <c r="N36" t="n">
-        <v>176.2</v>
+        <v>172.16</v>
       </c>
       <c r="O36" t="n">
-        <v>177.82</v>
+        <v>177.26</v>
       </c>
       <c r="P36" t="n">
-        <v>164.7724</v>
+        <v>165.5248</v>
       </c>
       <c r="Q36" t="n">
-        <v>166.0803</v>
+        <v>165.9594</v>
       </c>
       <c r="R36" t="n">
         <v>191.5557367172241</v>
@@ -6489,86 +6511,86 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>10 sep</t>
+          <t>11 sep</t>
         </is>
       </c>
       <c r="V36" t="n">
-        <v>488.32</v>
+        <v>495.65</v>
       </c>
       <c r="W36" t="n">
-        <v>494.52</v>
+        <v>498.97</v>
       </c>
       <c r="X36" t="n">
-        <v>486</v>
+        <v>492.58</v>
       </c>
       <c r="Y36" t="n">
-        <v>492.44</v>
+        <v>495.63</v>
       </c>
       <c r="Z36" t="n">
-        <v>450.8736</v>
+        <v>453.115</v>
       </c>
       <c r="AA36" t="n">
-        <v>429.5215</v>
+        <v>429.654</v>
       </c>
       <c r="AB36" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC36" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>11 sep</t>
+          <t>14 sep</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>41.345</v>
+        <v>41.88</v>
       </c>
       <c r="C37" t="n">
-        <v>41.715</v>
+        <v>42.285</v>
       </c>
       <c r="D37" t="n">
-        <v>40.905</v>
+        <v>41.8</v>
       </c>
       <c r="E37" t="n">
-        <v>41.415</v>
+        <v>41.91</v>
       </c>
       <c r="F37" t="n">
-        <v>38.5608</v>
+        <v>38.7226</v>
       </c>
       <c r="G37" t="n">
-        <v>35.3717</v>
+        <v>35.4269</v>
       </c>
       <c r="H37" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I37" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>11 sep</t>
+          <t>14 sep</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>175.68</v>
+        <v>180.82</v>
       </c>
       <c r="M37" t="n">
-        <v>178.84</v>
+        <v>186.76</v>
       </c>
       <c r="N37" t="n">
-        <v>172.16</v>
+        <v>180.82</v>
       </c>
       <c r="O37" t="n">
-        <v>177.26</v>
+        <v>186.26</v>
       </c>
       <c r="P37" t="n">
-        <v>165.5248</v>
+        <v>166.4488</v>
       </c>
       <c r="Q37" t="n">
-        <v>165.9594</v>
+        <v>165.8745</v>
       </c>
       <c r="R37" t="n">
         <v>191.5557367172241</v>
@@ -6578,86 +6600,86 @@
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>11 sep</t>
+          <t>14 sep</t>
         </is>
       </c>
       <c r="V37" t="n">
-        <v>495.65</v>
+        <v>497.06</v>
       </c>
       <c r="W37" t="n">
-        <v>498.97</v>
+        <v>509.95</v>
       </c>
       <c r="X37" t="n">
-        <v>492.58</v>
+        <v>495.34</v>
       </c>
       <c r="Y37" t="n">
-        <v>495.63</v>
+        <v>505.41</v>
       </c>
       <c r="Z37" t="n">
-        <v>453.115</v>
+        <v>455.4281</v>
       </c>
       <c r="AA37" t="n">
-        <v>429.654</v>
+        <v>429.8259</v>
       </c>
       <c r="AB37" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC37" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>14 sep</t>
+          <t>15 sep</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>41.88</v>
+        <v>41.845</v>
       </c>
       <c r="C38" t="n">
-        <v>42.285</v>
+        <v>42.7</v>
       </c>
       <c r="D38" t="n">
-        <v>41.8</v>
+        <v>41.72</v>
       </c>
       <c r="E38" t="n">
-        <v>41.91</v>
+        <v>42.7</v>
       </c>
       <c r="F38" t="n">
-        <v>38.7226</v>
+        <v>38.8782</v>
       </c>
       <c r="G38" t="n">
-        <v>35.4269</v>
+        <v>35.4854</v>
       </c>
       <c r="H38" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I38" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>14 sep</t>
+          <t>15 sep</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>180.82</v>
+        <v>186.64</v>
       </c>
       <c r="M38" t="n">
-        <v>186.76</v>
+        <v>187.26</v>
       </c>
       <c r="N38" t="n">
-        <v>180.82</v>
+        <v>183.2</v>
       </c>
       <c r="O38" t="n">
-        <v>186.26</v>
+        <v>187.08</v>
       </c>
       <c r="P38" t="n">
-        <v>166.4488</v>
+        <v>167.3124</v>
       </c>
       <c r="Q38" t="n">
-        <v>165.8745</v>
+        <v>165.7921</v>
       </c>
       <c r="R38" t="n">
         <v>191.5557367172241</v>
@@ -6667,86 +6689,86 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>14 sep</t>
+          <t>15 sep</t>
         </is>
       </c>
       <c r="V38" t="n">
-        <v>497.06</v>
+        <v>500.06</v>
       </c>
       <c r="W38" t="n">
-        <v>509.95</v>
+        <v>505.9</v>
       </c>
       <c r="X38" t="n">
-        <v>495.34</v>
+        <v>495.54</v>
       </c>
       <c r="Y38" t="n">
-        <v>505.41</v>
+        <v>497.12</v>
       </c>
       <c r="Z38" t="n">
-        <v>455.4281</v>
+        <v>457.6502</v>
       </c>
       <c r="AA38" t="n">
-        <v>429.8259</v>
+        <v>429.9416</v>
       </c>
       <c r="AB38" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC38" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>15 sep</t>
+          <t>16 sep</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>41.845</v>
+        <v>42.72</v>
       </c>
       <c r="C39" t="n">
-        <v>42.7</v>
+        <v>42.85</v>
       </c>
       <c r="D39" t="n">
-        <v>41.72</v>
+        <v>41.67</v>
       </c>
       <c r="E39" t="n">
-        <v>42.7</v>
+        <v>41.825</v>
       </c>
       <c r="F39" t="n">
-        <v>38.8782</v>
+        <v>38.9989</v>
       </c>
       <c r="G39" t="n">
-        <v>35.4854</v>
+        <v>35.5403</v>
       </c>
       <c r="H39" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I39" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>15 sep</t>
+          <t>16 sep</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>186.64</v>
+        <v>185.86</v>
       </c>
       <c r="M39" t="n">
-        <v>187.26</v>
+        <v>186.76</v>
       </c>
       <c r="N39" t="n">
-        <v>183.2</v>
+        <v>182.18</v>
       </c>
       <c r="O39" t="n">
-        <v>187.08</v>
+        <v>186.56</v>
       </c>
       <c r="P39" t="n">
-        <v>167.3124</v>
+        <v>168.2844</v>
       </c>
       <c r="Q39" t="n">
-        <v>165.7921</v>
+        <v>165.6996</v>
       </c>
       <c r="R39" t="n">
         <v>191.5557367172241</v>
@@ -6756,86 +6778,86 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>15 sep</t>
+          <t>16 sep</t>
         </is>
       </c>
       <c r="V39" t="n">
-        <v>500.06</v>
+        <v>493.03</v>
       </c>
       <c r="W39" t="n">
-        <v>505.9</v>
+        <v>495.97</v>
       </c>
       <c r="X39" t="n">
-        <v>495.54</v>
+        <v>487.23</v>
       </c>
       <c r="Y39" t="n">
-        <v>497.12</v>
+        <v>490.3</v>
       </c>
       <c r="Z39" t="n">
-        <v>457.6502</v>
+        <v>459.694</v>
       </c>
       <c r="AA39" t="n">
-        <v>429.9416</v>
+        <v>429.9809</v>
       </c>
       <c r="AB39" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC39" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>16 sep</t>
+          <t>17 sep</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>42.72</v>
+        <v>41.58</v>
       </c>
       <c r="C40" t="n">
-        <v>42.85</v>
+        <v>42.055</v>
       </c>
       <c r="D40" t="n">
-        <v>41.67</v>
+        <v>41.38</v>
       </c>
       <c r="E40" t="n">
-        <v>41.825</v>
+        <v>41.56</v>
       </c>
       <c r="F40" t="n">
-        <v>38.9989</v>
+        <v>39.1225</v>
       </c>
       <c r="G40" t="n">
-        <v>35.5403</v>
+        <v>35.5926</v>
       </c>
       <c r="H40" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I40" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>16 sep</t>
+          <t>17 sep</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>185.86</v>
+        <v>188.54</v>
       </c>
       <c r="M40" t="n">
-        <v>186.76</v>
+        <v>189.2</v>
       </c>
       <c r="N40" t="n">
-        <v>182.18</v>
+        <v>184.62</v>
       </c>
       <c r="O40" t="n">
-        <v>186.56</v>
+        <v>188</v>
       </c>
       <c r="P40" t="n">
-        <v>168.2844</v>
+        <v>169.2896</v>
       </c>
       <c r="Q40" t="n">
-        <v>165.6996</v>
+        <v>165.6125</v>
       </c>
       <c r="R40" t="n">
         <v>191.5557367172241</v>
@@ -6845,86 +6867,86 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>16 sep</t>
+          <t>17 sep</t>
         </is>
       </c>
       <c r="V40" t="n">
-        <v>493.03</v>
+        <v>497.8</v>
       </c>
       <c r="W40" t="n">
-        <v>495.97</v>
+        <v>501.47</v>
       </c>
       <c r="X40" t="n">
-        <v>487.23</v>
+        <v>493.17</v>
       </c>
       <c r="Y40" t="n">
-        <v>490.3</v>
+        <v>497.75</v>
       </c>
       <c r="Z40" t="n">
-        <v>459.694</v>
+        <v>461.9966</v>
       </c>
       <c r="AA40" t="n">
-        <v>429.9809</v>
+        <v>430.0251</v>
       </c>
       <c r="AB40" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC40" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>17 sep</t>
+          <t>18 sep</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>41.58</v>
+        <v>41.465</v>
       </c>
       <c r="C41" t="n">
-        <v>42.055</v>
+        <v>41.5</v>
       </c>
       <c r="D41" t="n">
-        <v>41.38</v>
+        <v>40.955</v>
       </c>
       <c r="E41" t="n">
-        <v>41.56</v>
+        <v>41.315</v>
       </c>
       <c r="F41" t="n">
-        <v>39.1225</v>
+        <v>39.2414</v>
       </c>
       <c r="G41" t="n">
-        <v>35.5926</v>
+        <v>35.6436</v>
       </c>
       <c r="H41" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I41" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>17 sep</t>
+          <t>18 sep</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>188.54</v>
+        <v>186.1</v>
       </c>
       <c r="M41" t="n">
-        <v>189.2</v>
+        <v>187.26</v>
       </c>
       <c r="N41" t="n">
-        <v>184.62</v>
+        <v>182.56</v>
       </c>
       <c r="O41" t="n">
-        <v>188</v>
+        <v>183.12</v>
       </c>
       <c r="P41" t="n">
-        <v>169.2896</v>
+        <v>170.2004</v>
       </c>
       <c r="Q41" t="n">
-        <v>165.6125</v>
+        <v>165.5062</v>
       </c>
       <c r="R41" t="n">
         <v>191.5557367172241</v>
@@ -6934,86 +6956,86 @@
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>17 sep</t>
+          <t>18 sep</t>
         </is>
       </c>
       <c r="V41" t="n">
-        <v>497.8</v>
+        <v>497.97</v>
       </c>
       <c r="W41" t="n">
-        <v>501.47</v>
+        <v>498.65</v>
       </c>
       <c r="X41" t="n">
-        <v>493.17</v>
+        <v>491.1</v>
       </c>
       <c r="Y41" t="n">
-        <v>497.75</v>
+        <v>493.78</v>
       </c>
       <c r="Z41" t="n">
-        <v>461.9966</v>
+        <v>464.1995</v>
       </c>
       <c r="AA41" t="n">
-        <v>430.0251</v>
+        <v>430.0757</v>
       </c>
       <c r="AB41" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC41" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>18 sep</t>
+          <t>21 sep</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>41.465</v>
+        <v>41.04</v>
       </c>
       <c r="C42" t="n">
-        <v>41.5</v>
+        <v>41.4</v>
       </c>
       <c r="D42" t="n">
-        <v>40.955</v>
+        <v>40.775</v>
       </c>
       <c r="E42" t="n">
-        <v>41.315</v>
+        <v>40.775</v>
       </c>
       <c r="F42" t="n">
-        <v>39.2414</v>
+        <v>39.3341</v>
       </c>
       <c r="G42" t="n">
-        <v>35.6436</v>
+        <v>35.6939</v>
       </c>
       <c r="H42" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I42" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>18 sep</t>
+          <t>21 sep</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>186.1</v>
+        <v>184.7</v>
       </c>
       <c r="M42" t="n">
-        <v>187.26</v>
+        <v>185.86</v>
       </c>
       <c r="N42" t="n">
-        <v>182.56</v>
+        <v>182.48</v>
       </c>
       <c r="O42" t="n">
-        <v>183.12</v>
+        <v>182.86</v>
       </c>
       <c r="P42" t="n">
-        <v>170.2004</v>
+        <v>171.0432</v>
       </c>
       <c r="Q42" t="n">
-        <v>165.5062</v>
+        <v>165.4052</v>
       </c>
       <c r="R42" t="n">
         <v>191.5557367172241</v>
@@ -7023,86 +7045,86 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>18 sep</t>
+          <t>21 sep</t>
         </is>
       </c>
       <c r="V42" t="n">
-        <v>497.97</v>
+        <v>494.95</v>
       </c>
       <c r="W42" t="n">
-        <v>498.65</v>
+        <v>501.87</v>
       </c>
       <c r="X42" t="n">
-        <v>491.1</v>
+        <v>491.33</v>
       </c>
       <c r="Y42" t="n">
-        <v>493.78</v>
+        <v>501.61</v>
       </c>
       <c r="Z42" t="n">
-        <v>464.1995</v>
+        <v>466.5442</v>
       </c>
       <c r="AA42" t="n">
-        <v>430.0757</v>
+        <v>430.1492</v>
       </c>
       <c r="AB42" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC42" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>21 sep</t>
+          <t>22 sep</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>41.04</v>
+        <v>40.84</v>
       </c>
       <c r="C43" t="n">
-        <v>41.4</v>
+        <v>41.165</v>
       </c>
       <c r="D43" t="n">
-        <v>40.775</v>
+        <v>40.215</v>
       </c>
       <c r="E43" t="n">
-        <v>40.775</v>
+        <v>41.01</v>
       </c>
       <c r="F43" t="n">
-        <v>39.3341</v>
+        <v>39.4244</v>
       </c>
       <c r="G43" t="n">
-        <v>35.6939</v>
+        <v>35.746</v>
       </c>
       <c r="H43" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I43" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>21 sep</t>
+          <t>22 sep</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>184.7</v>
+        <v>182.14</v>
       </c>
       <c r="M43" t="n">
-        <v>185.86</v>
+        <v>187.48</v>
       </c>
       <c r="N43" t="n">
-        <v>182.48</v>
+        <v>181.52</v>
       </c>
       <c r="O43" t="n">
-        <v>182.86</v>
+        <v>182.32</v>
       </c>
       <c r="P43" t="n">
-        <v>171.0432</v>
+        <v>171.9552</v>
       </c>
       <c r="Q43" t="n">
-        <v>165.4052</v>
+        <v>165.2836</v>
       </c>
       <c r="R43" t="n">
         <v>191.5557367172241</v>
@@ -7112,86 +7134,86 @@
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>21 sep</t>
+          <t>22 sep</t>
         </is>
       </c>
       <c r="V43" t="n">
-        <v>494.95</v>
+        <v>507.32</v>
       </c>
       <c r="W43" t="n">
-        <v>501.87</v>
+        <v>508.5</v>
       </c>
       <c r="X43" t="n">
-        <v>491.33</v>
+        <v>493.65</v>
       </c>
       <c r="Y43" t="n">
-        <v>501.61</v>
+        <v>498</v>
       </c>
       <c r="Z43" t="n">
-        <v>466.5442</v>
+        <v>468.699</v>
       </c>
       <c r="AA43" t="n">
-        <v>430.1492</v>
+        <v>430.2656</v>
       </c>
       <c r="AB43" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC43" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>22 sep</t>
+          <t>23 sep</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>40.84</v>
+        <v>41</v>
       </c>
       <c r="C44" t="n">
-        <v>41.165</v>
+        <v>41.755</v>
       </c>
       <c r="D44" t="n">
-        <v>40.215</v>
+        <v>40.995</v>
       </c>
       <c r="E44" t="n">
-        <v>41.01</v>
+        <v>41.69</v>
       </c>
       <c r="F44" t="n">
-        <v>39.4244</v>
+        <v>39.5272</v>
       </c>
       <c r="G44" t="n">
-        <v>35.746</v>
+        <v>35.8024</v>
       </c>
       <c r="H44" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I44" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>22 sep</t>
+          <t>23 sep</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>182.14</v>
+        <v>184.9</v>
       </c>
       <c r="M44" t="n">
-        <v>187.48</v>
+        <v>187.8</v>
       </c>
       <c r="N44" t="n">
-        <v>181.52</v>
+        <v>183.48</v>
       </c>
       <c r="O44" t="n">
-        <v>182.32</v>
+        <v>186.46</v>
       </c>
       <c r="P44" t="n">
-        <v>171.9552</v>
+        <v>172.9448</v>
       </c>
       <c r="Q44" t="n">
-        <v>165.2836</v>
+        <v>165.1675</v>
       </c>
       <c r="R44" t="n">
         <v>191.5557367172241</v>
@@ -7201,86 +7223,86 @@
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>22 sep</t>
+          <t>23 sep</t>
         </is>
       </c>
       <c r="V44" t="n">
-        <v>507.32</v>
+        <v>500.76</v>
       </c>
       <c r="W44" t="n">
-        <v>508.5</v>
+        <v>509.44</v>
       </c>
       <c r="X44" t="n">
-        <v>493.65</v>
+        <v>495.88</v>
       </c>
       <c r="Y44" t="n">
-        <v>498</v>
+        <v>500.59</v>
       </c>
       <c r="Z44" t="n">
-        <v>468.699</v>
+        <v>471.0267</v>
       </c>
       <c r="AA44" t="n">
-        <v>430.2656</v>
+        <v>430.3795</v>
       </c>
       <c r="AB44" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC44" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>23 sep</t>
+          <t>24 sep</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>41</v>
+        <v>41.825</v>
       </c>
       <c r="C45" t="n">
-        <v>41.755</v>
+        <v>42.52</v>
       </c>
       <c r="D45" t="n">
-        <v>40.995</v>
+        <v>41.78</v>
       </c>
       <c r="E45" t="n">
-        <v>41.69</v>
+        <v>42.43</v>
       </c>
       <c r="F45" t="n">
-        <v>39.5272</v>
+        <v>39.6382</v>
       </c>
       <c r="G45" t="n">
-        <v>35.8024</v>
+        <v>35.8638</v>
       </c>
       <c r="H45" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I45" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>23 sep</t>
+          <t>24 sep</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>184.9</v>
+        <v>184.52</v>
       </c>
       <c r="M45" t="n">
-        <v>187.8</v>
+        <v>185.5</v>
       </c>
       <c r="N45" t="n">
-        <v>183.48</v>
+        <v>182.26</v>
       </c>
       <c r="O45" t="n">
-        <v>186.46</v>
+        <v>184.18</v>
       </c>
       <c r="P45" t="n">
-        <v>172.9448</v>
+        <v>173.8756</v>
       </c>
       <c r="Q45" t="n">
-        <v>165.1675</v>
+        <v>165.0554</v>
       </c>
       <c r="R45" t="n">
         <v>191.5557367172241</v>
@@ -7290,86 +7312,86 @@
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>23 sep</t>
+          <t>24 sep</t>
         </is>
       </c>
       <c r="V45" t="n">
-        <v>500.76</v>
+        <v>495.07</v>
       </c>
       <c r="W45" t="n">
-        <v>509.44</v>
+        <v>498.9</v>
       </c>
       <c r="X45" t="n">
-        <v>495.88</v>
+        <v>491.22</v>
       </c>
       <c r="Y45" t="n">
-        <v>500.59</v>
+        <v>497.93</v>
       </c>
       <c r="Z45" t="n">
-        <v>471.0267</v>
+        <v>473.0876</v>
       </c>
       <c r="AA45" t="n">
-        <v>430.3795</v>
+        <v>430.4686</v>
       </c>
       <c r="AB45" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC45" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>24 sep</t>
+          <t>25 sep</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>41.825</v>
+        <v>41.99</v>
       </c>
       <c r="C46" t="n">
-        <v>42.52</v>
+        <v>42.33</v>
       </c>
       <c r="D46" t="n">
-        <v>41.78</v>
+        <v>41.71</v>
       </c>
       <c r="E46" t="n">
-        <v>42.43</v>
+        <v>42.06</v>
       </c>
       <c r="F46" t="n">
-        <v>39.6382</v>
+        <v>39.7263</v>
       </c>
       <c r="G46" t="n">
-        <v>35.8638</v>
+        <v>35.9239</v>
       </c>
       <c r="H46" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I46" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>24 sep</t>
+          <t>25 sep</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>184.52</v>
+        <v>184.42</v>
       </c>
       <c r="M46" t="n">
-        <v>185.5</v>
+        <v>185.92</v>
       </c>
       <c r="N46" t="n">
-        <v>182.26</v>
+        <v>183.76</v>
       </c>
       <c r="O46" t="n">
-        <v>184.18</v>
+        <v>185.92</v>
       </c>
       <c r="P46" t="n">
-        <v>173.8756</v>
+        <v>174.8356</v>
       </c>
       <c r="Q46" t="n">
-        <v>165.0554</v>
+        <v>164.9525</v>
       </c>
       <c r="R46" t="n">
         <v>191.5557367172241</v>
@@ -7379,86 +7401,86 @@
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>24 sep</t>
+          <t>25 sep</t>
         </is>
       </c>
       <c r="V46" t="n">
-        <v>495.07</v>
+        <v>499.04</v>
       </c>
       <c r="W46" t="n">
-        <v>498.9</v>
+        <v>519.4</v>
       </c>
       <c r="X46" t="n">
-        <v>491.22</v>
+        <v>497.25</v>
       </c>
       <c r="Y46" t="n">
-        <v>497.93</v>
+        <v>516.17</v>
       </c>
       <c r="Z46" t="n">
-        <v>473.0876</v>
+        <v>475.4041</v>
       </c>
       <c r="AA46" t="n">
-        <v>430.4686</v>
+        <v>430.6098</v>
       </c>
       <c r="AB46" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC46" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>25 sep</t>
+          <t>28 sep</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>41.99</v>
+        <v>42.45</v>
       </c>
       <c r="C47" t="n">
-        <v>42.33</v>
+        <v>42.995</v>
       </c>
       <c r="D47" t="n">
-        <v>41.71</v>
+        <v>42.38</v>
       </c>
       <c r="E47" t="n">
-        <v>42.06</v>
+        <v>42.725</v>
       </c>
       <c r="F47" t="n">
-        <v>39.7263</v>
+        <v>39.8301</v>
       </c>
       <c r="G47" t="n">
-        <v>35.9239</v>
+        <v>35.9888</v>
       </c>
       <c r="H47" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I47" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>25 sep</t>
+          <t>28 sep</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>184.42</v>
+        <v>185.2</v>
       </c>
       <c r="M47" t="n">
-        <v>185.92</v>
+        <v>186.76</v>
       </c>
       <c r="N47" t="n">
-        <v>183.76</v>
+        <v>178.88</v>
       </c>
       <c r="O47" t="n">
-        <v>185.92</v>
+        <v>184.02</v>
       </c>
       <c r="P47" t="n">
-        <v>174.8356</v>
+        <v>175.7508</v>
       </c>
       <c r="Q47" t="n">
-        <v>164.9525</v>
+        <v>164.8355</v>
       </c>
       <c r="R47" t="n">
         <v>191.5557367172241</v>
@@ -7468,86 +7490,86 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>25 sep</t>
+          <t>28 sep</t>
         </is>
       </c>
       <c r="V47" t="n">
-        <v>499.04</v>
+        <v>505.47</v>
       </c>
       <c r="W47" t="n">
-        <v>519.4</v>
+        <v>513.33</v>
       </c>
       <c r="X47" t="n">
-        <v>497.25</v>
+        <v>502.22</v>
       </c>
       <c r="Y47" t="n">
-        <v>516.17</v>
+        <v>509.22</v>
       </c>
       <c r="Z47" t="n">
-        <v>475.4041</v>
+        <v>477.7269</v>
       </c>
       <c r="AA47" t="n">
-        <v>430.6098</v>
+        <v>430.7113</v>
       </c>
       <c r="AB47" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC47" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>28 sep</t>
+          <t>29 sep</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>42.45</v>
+        <v>42.57</v>
       </c>
       <c r="C48" t="n">
-        <v>42.995</v>
+        <v>42.665</v>
       </c>
       <c r="D48" t="n">
-        <v>42.38</v>
+        <v>41.73</v>
       </c>
       <c r="E48" t="n">
-        <v>42.725</v>
+        <v>42.05</v>
       </c>
       <c r="F48" t="n">
-        <v>39.8301</v>
+        <v>39.9146</v>
       </c>
       <c r="G48" t="n">
-        <v>35.9888</v>
+        <v>36.0498</v>
       </c>
       <c r="H48" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I48" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>28 sep</t>
+          <t>29 sep</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>185.2</v>
+        <v>183.22</v>
       </c>
       <c r="M48" t="n">
-        <v>186.76</v>
+        <v>186.34</v>
       </c>
       <c r="N48" t="n">
-        <v>178.88</v>
+        <v>182.28</v>
       </c>
       <c r="O48" t="n">
-        <v>184.02</v>
+        <v>185.32</v>
       </c>
       <c r="P48" t="n">
-        <v>175.7508</v>
+        <v>176.7288</v>
       </c>
       <c r="Q48" t="n">
-        <v>164.8355</v>
+        <v>164.733</v>
       </c>
       <c r="R48" t="n">
         <v>191.5557367172241</v>
@@ -7557,86 +7579,86 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>28 sep</t>
+          <t>29 sep</t>
         </is>
       </c>
       <c r="V48" t="n">
-        <v>505.47</v>
+        <v>508.31</v>
       </c>
       <c r="W48" t="n">
-        <v>513.33</v>
+        <v>513.64</v>
       </c>
       <c r="X48" t="n">
-        <v>502.22</v>
+        <v>502.4</v>
       </c>
       <c r="Y48" t="n">
-        <v>509.22</v>
+        <v>508.96</v>
       </c>
       <c r="Z48" t="n">
-        <v>477.7269</v>
+        <v>479.8754</v>
       </c>
       <c r="AA48" t="n">
-        <v>430.7113</v>
+        <v>430.8784</v>
       </c>
       <c r="AB48" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC48" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>29 sep</t>
+          <t>30 sep</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>42.57</v>
+        <v>41.975</v>
       </c>
       <c r="C49" t="n">
-        <v>42.665</v>
+        <v>42.095</v>
       </c>
       <c r="D49" t="n">
-        <v>41.73</v>
+        <v>41.58</v>
       </c>
       <c r="E49" t="n">
-        <v>42.05</v>
+        <v>41.91</v>
       </c>
       <c r="F49" t="n">
-        <v>39.9146</v>
+        <v>39.9874</v>
       </c>
       <c r="G49" t="n">
-        <v>36.0498</v>
+        <v>36.1135</v>
       </c>
       <c r="H49" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I49" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>29 sep</t>
+          <t>30 sep</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>183.22</v>
+        <v>184.5</v>
       </c>
       <c r="M49" t="n">
-        <v>186.34</v>
+        <v>186.2</v>
       </c>
       <c r="N49" t="n">
-        <v>182.28</v>
+        <v>181.06</v>
       </c>
       <c r="O49" t="n">
-        <v>185.32</v>
+        <v>185.66</v>
       </c>
       <c r="P49" t="n">
-        <v>176.7288</v>
+        <v>177.8012</v>
       </c>
       <c r="Q49" t="n">
-        <v>164.733</v>
+        <v>164.6377</v>
       </c>
       <c r="R49" t="n">
         <v>191.5557367172241</v>
@@ -7646,86 +7668,86 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>29 sep</t>
+          <t>30 sep</t>
         </is>
       </c>
       <c r="V49" t="n">
-        <v>508.31</v>
+        <v>511.61</v>
       </c>
       <c r="W49" t="n">
-        <v>513.64</v>
+        <v>519.83</v>
       </c>
       <c r="X49" t="n">
-        <v>502.4</v>
+        <v>510.31</v>
       </c>
       <c r="Y49" t="n">
-        <v>508.96</v>
+        <v>512.9</v>
       </c>
       <c r="Z49" t="n">
-        <v>479.8754</v>
+        <v>482.1933</v>
       </c>
       <c r="AA49" t="n">
-        <v>430.8784</v>
+        <v>431.0408</v>
       </c>
       <c r="AB49" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC49" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>30 sep</t>
+          <t>1 okt</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>41.975</v>
+        <v>41.625</v>
       </c>
       <c r="C50" t="n">
-        <v>42.095</v>
+        <v>42.36</v>
       </c>
       <c r="D50" t="n">
-        <v>41.58</v>
+        <v>41.165</v>
       </c>
       <c r="E50" t="n">
-        <v>41.91</v>
+        <v>42.24</v>
       </c>
       <c r="F50" t="n">
-        <v>39.9874</v>
+        <v>40.0562</v>
       </c>
       <c r="G50" t="n">
-        <v>36.1135</v>
+        <v>36.1777</v>
       </c>
       <c r="H50" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I50" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>30 sep</t>
+          <t>1 okt</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>184.5</v>
+        <v>184.68</v>
       </c>
       <c r="M50" t="n">
-        <v>186.2</v>
+        <v>190.26</v>
       </c>
       <c r="N50" t="n">
-        <v>181.06</v>
+        <v>181.34</v>
       </c>
       <c r="O50" t="n">
-        <v>185.66</v>
+        <v>186.74</v>
       </c>
       <c r="P50" t="n">
-        <v>177.8012</v>
+        <v>178.9696</v>
       </c>
       <c r="Q50" t="n">
-        <v>164.6377</v>
+        <v>164.5407</v>
       </c>
       <c r="R50" t="n">
         <v>191.5557367172241</v>
@@ -7735,86 +7757,86 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>30 sep</t>
+          <t>1 okt</t>
         </is>
       </c>
       <c r="V50" t="n">
-        <v>511.61</v>
+        <v>519.88</v>
       </c>
       <c r="W50" t="n">
-        <v>519.83</v>
+        <v>522.85</v>
       </c>
       <c r="X50" t="n">
-        <v>510.31</v>
+        <v>512.17</v>
       </c>
       <c r="Y50" t="n">
-        <v>512.9</v>
+        <v>512.8</v>
       </c>
       <c r="Z50" t="n">
-        <v>482.1933</v>
+        <v>484.6572</v>
       </c>
       <c r="AA50" t="n">
-        <v>431.0408</v>
+        <v>431.2272</v>
       </c>
       <c r="AB50" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC50" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1 okt</t>
+          <t>2 okt</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>41.625</v>
+        <v>42.11</v>
       </c>
       <c r="C51" t="n">
-        <v>42.36</v>
+        <v>42.745</v>
       </c>
       <c r="D51" t="n">
-        <v>41.165</v>
+        <v>41.985</v>
       </c>
       <c r="E51" t="n">
-        <v>42.24</v>
+        <v>42.4</v>
       </c>
       <c r="F51" t="n">
-        <v>40.0562</v>
+        <v>40.1364</v>
       </c>
       <c r="G51" t="n">
-        <v>36.1777</v>
+        <v>36.2422</v>
       </c>
       <c r="H51" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I51" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>1 okt</t>
+          <t>2 okt</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>184.68</v>
+        <v>187.82</v>
       </c>
       <c r="M51" t="n">
-        <v>190.26</v>
+        <v>188.74</v>
       </c>
       <c r="N51" t="n">
-        <v>181.34</v>
+        <v>183.92</v>
       </c>
       <c r="O51" t="n">
-        <v>186.74</v>
+        <v>183.92</v>
       </c>
       <c r="P51" t="n">
-        <v>178.9696</v>
+        <v>179.844</v>
       </c>
       <c r="Q51" t="n">
-        <v>164.5407</v>
+        <v>164.4442</v>
       </c>
       <c r="R51" t="n">
         <v>191.5557367172241</v>
@@ -7824,86 +7846,86 @@
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>1 okt</t>
+          <t>2 okt</t>
         </is>
       </c>
       <c r="V51" t="n">
-        <v>519.88</v>
+        <v>519.39</v>
       </c>
       <c r="W51" t="n">
-        <v>522.85</v>
+        <v>522.5</v>
       </c>
       <c r="X51" t="n">
-        <v>512.17</v>
+        <v>513.66</v>
       </c>
       <c r="Y51" t="n">
-        <v>512.8</v>
+        <v>517.53</v>
       </c>
       <c r="Z51" t="n">
-        <v>484.6572</v>
+        <v>487.3905</v>
       </c>
       <c r="AA51" t="n">
-        <v>431.2272</v>
+        <v>431.4557</v>
       </c>
       <c r="AB51" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC51" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2 okt</t>
+          <t>5 okt</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>42.11</v>
+        <v>42.645</v>
       </c>
       <c r="C52" t="n">
-        <v>42.745</v>
+        <v>43.11</v>
       </c>
       <c r="D52" t="n">
-        <v>41.985</v>
+        <v>42.35</v>
       </c>
       <c r="E52" t="n">
-        <v>42.4</v>
+        <v>42.865</v>
       </c>
       <c r="F52" t="n">
-        <v>40.1364</v>
+        <v>40.2347</v>
       </c>
       <c r="G52" t="n">
-        <v>36.2422</v>
+        <v>36.3069</v>
       </c>
       <c r="H52" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I52" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2 okt</t>
+          <t>5 okt</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>187.82</v>
+        <v>185.06</v>
       </c>
       <c r="M52" t="n">
-        <v>188.74</v>
+        <v>188.5</v>
       </c>
       <c r="N52" t="n">
-        <v>183.92</v>
+        <v>184.66</v>
       </c>
       <c r="O52" t="n">
-        <v>183.92</v>
+        <v>185.04</v>
       </c>
       <c r="P52" t="n">
-        <v>179.844</v>
+        <v>180.5192</v>
       </c>
       <c r="Q52" t="n">
-        <v>164.4442</v>
+        <v>164.3515</v>
       </c>
       <c r="R52" t="n">
         <v>191.5557367172241</v>
@@ -7913,86 +7935,86 @@
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>2 okt</t>
+          <t>5 okt</t>
         </is>
       </c>
       <c r="V52" t="n">
-        <v>519.39</v>
+        <v>521.62</v>
       </c>
       <c r="W52" t="n">
-        <v>522.5</v>
+        <v>532.35</v>
       </c>
       <c r="X52" t="n">
-        <v>513.66</v>
+        <v>521.47</v>
       </c>
       <c r="Y52" t="n">
-        <v>517.53</v>
+        <v>525.1799999999999</v>
       </c>
       <c r="Z52" t="n">
-        <v>487.3905</v>
+        <v>490.2745</v>
       </c>
       <c r="AA52" t="n">
-        <v>431.4557</v>
+        <v>431.7147</v>
       </c>
       <c r="AB52" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC52" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>5 okt</t>
+          <t>6 okt</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>42.645</v>
+        <v>42.86</v>
       </c>
       <c r="C53" t="n">
-        <v>43.11</v>
+        <v>43.285</v>
       </c>
       <c r="D53" t="n">
-        <v>42.35</v>
+        <v>42.43</v>
       </c>
       <c r="E53" t="n">
-        <v>42.865</v>
+        <v>43.185</v>
       </c>
       <c r="F53" t="n">
-        <v>40.2347</v>
+        <v>40.349</v>
       </c>
       <c r="G53" t="n">
-        <v>36.3069</v>
+        <v>36.3726</v>
       </c>
       <c r="H53" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I53" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>5 okt</t>
+          <t>6 okt</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>185.06</v>
+        <v>186.56</v>
       </c>
       <c r="M53" t="n">
-        <v>188.5</v>
+        <v>190.22</v>
       </c>
       <c r="N53" t="n">
-        <v>184.66</v>
+        <v>186.06</v>
       </c>
       <c r="O53" t="n">
-        <v>185.04</v>
+        <v>188.6</v>
       </c>
       <c r="P53" t="n">
-        <v>180.5192</v>
+        <v>181.1064</v>
       </c>
       <c r="Q53" t="n">
-        <v>164.3515</v>
+        <v>164.2647</v>
       </c>
       <c r="R53" t="n">
         <v>191.5557367172241</v>
@@ -8002,86 +8024,86 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>5 okt</t>
+          <t>6 okt</t>
         </is>
       </c>
       <c r="V53" t="n">
-        <v>521.62</v>
+        <v>531.6799999999999</v>
       </c>
       <c r="W53" t="n">
-        <v>532.35</v>
+        <v>535.6900000000001</v>
       </c>
       <c r="X53" t="n">
-        <v>521.47</v>
+        <v>528.78</v>
       </c>
       <c r="Y53" t="n">
-        <v>525.1799999999999</v>
+        <v>529.3</v>
       </c>
       <c r="Z53" t="n">
-        <v>490.2745</v>
+        <v>493.0931</v>
       </c>
       <c r="AA53" t="n">
-        <v>431.7147</v>
+        <v>431.9956</v>
       </c>
       <c r="AB53" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC53" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>6 okt</t>
+          <t>7 okt</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>42.86</v>
+        <v>43.37</v>
       </c>
       <c r="C54" t="n">
-        <v>43.285</v>
+        <v>43.835</v>
       </c>
       <c r="D54" t="n">
-        <v>42.43</v>
+        <v>43.145</v>
       </c>
       <c r="E54" t="n">
-        <v>43.185</v>
+        <v>43.25</v>
       </c>
       <c r="F54" t="n">
-        <v>40.349</v>
+        <v>40.4451</v>
       </c>
       <c r="G54" t="n">
-        <v>36.3726</v>
+        <v>36.4388</v>
       </c>
       <c r="H54" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I54" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>6 okt</t>
+          <t>7 okt</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>186.56</v>
+        <v>187</v>
       </c>
       <c r="M54" t="n">
-        <v>190.22</v>
+        <v>188.72</v>
       </c>
       <c r="N54" t="n">
-        <v>186.06</v>
+        <v>186.04</v>
       </c>
       <c r="O54" t="n">
-        <v>188.6</v>
+        <v>187.62</v>
       </c>
       <c r="P54" t="n">
-        <v>181.1064</v>
+        <v>181.618</v>
       </c>
       <c r="Q54" t="n">
-        <v>164.2647</v>
+        <v>164.1762</v>
       </c>
       <c r="R54" t="n">
         <v>191.5557367172241</v>
@@ -8091,86 +8113,86 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>6 okt</t>
+          <t>7 okt</t>
         </is>
       </c>
       <c r="V54" t="n">
-        <v>531.6799999999999</v>
+        <v>530.73</v>
       </c>
       <c r="W54" t="n">
-        <v>535.6900000000001</v>
+        <v>531.73</v>
       </c>
       <c r="X54" t="n">
-        <v>528.78</v>
+        <v>524.6900000000001</v>
       </c>
       <c r="Y54" t="n">
-        <v>529.3</v>
+        <v>529.76</v>
       </c>
       <c r="Z54" t="n">
-        <v>493.0931</v>
+        <v>495.8361</v>
       </c>
       <c r="AA54" t="n">
-        <v>431.9956</v>
+        <v>432.2398</v>
       </c>
       <c r="AB54" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC54" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>7 okt</t>
+          <t>8 okt</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>43.37</v>
+        <v>43.555</v>
       </c>
       <c r="C55" t="n">
-        <v>43.835</v>
+        <v>44.815</v>
       </c>
       <c r="D55" t="n">
-        <v>43.145</v>
+        <v>43.5425</v>
       </c>
       <c r="E55" t="n">
-        <v>43.25</v>
+        <v>44.75</v>
       </c>
       <c r="F55" t="n">
-        <v>40.4451</v>
+        <v>40.5699</v>
       </c>
       <c r="G55" t="n">
-        <v>36.4388</v>
+        <v>36.5123</v>
       </c>
       <c r="H55" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I55" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>7 okt</t>
+          <t>8 okt</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>187</v>
+        <v>187.04</v>
       </c>
       <c r="M55" t="n">
-        <v>188.72</v>
+        <v>189.82</v>
       </c>
       <c r="N55" t="n">
-        <v>186.04</v>
+        <v>183.76</v>
       </c>
       <c r="O55" t="n">
-        <v>187.62</v>
+        <v>184.62</v>
       </c>
       <c r="P55" t="n">
-        <v>181.618</v>
+        <v>182.192</v>
       </c>
       <c r="Q55" t="n">
-        <v>164.1762</v>
+        <v>164.074</v>
       </c>
       <c r="R55" t="n">
         <v>191.5557367172241</v>
@@ -8180,86 +8202,86 @@
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>7 okt</t>
+          <t>8 okt</t>
         </is>
       </c>
       <c r="V55" t="n">
-        <v>530.73</v>
+        <v>529.8099999999999</v>
       </c>
       <c r="W55" t="n">
-        <v>531.73</v>
+        <v>533.51</v>
       </c>
       <c r="X55" t="n">
-        <v>524.6900000000001</v>
+        <v>518.79</v>
       </c>
       <c r="Y55" t="n">
-        <v>529.76</v>
+        <v>522.61</v>
       </c>
       <c r="Z55" t="n">
-        <v>495.8361</v>
+        <v>498.4921</v>
       </c>
       <c r="AA55" t="n">
-        <v>432.2398</v>
+        <v>432.4385</v>
       </c>
       <c r="AB55" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC55" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>8 okt</t>
+          <t>9 okt</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>43.555</v>
+        <v>44.42</v>
       </c>
       <c r="C56" t="n">
-        <v>44.815</v>
+        <v>45.155</v>
       </c>
       <c r="D56" t="n">
-        <v>43.5425</v>
+        <v>43.94</v>
       </c>
       <c r="E56" t="n">
-        <v>44.75</v>
+        <v>45.035</v>
       </c>
       <c r="F56" t="n">
-        <v>40.5699</v>
+        <v>40.6842</v>
       </c>
       <c r="G56" t="n">
-        <v>36.5123</v>
+        <v>36.5866</v>
       </c>
       <c r="H56" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I56" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>8 okt</t>
+          <t>9 okt</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>187.04</v>
+        <v>188.98</v>
       </c>
       <c r="M56" t="n">
-        <v>189.82</v>
+        <v>192.58</v>
       </c>
       <c r="N56" t="n">
-        <v>183.76</v>
+        <v>188.86</v>
       </c>
       <c r="O56" t="n">
-        <v>184.62</v>
+        <v>191.46</v>
       </c>
       <c r="P56" t="n">
-        <v>182.192</v>
+        <v>182.8676</v>
       </c>
       <c r="Q56" t="n">
-        <v>164.074</v>
+        <v>164.0101</v>
       </c>
       <c r="R56" t="n">
         <v>191.5557367172241</v>
@@ -8269,86 +8291,86 @@
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>8 okt</t>
+          <t>9 okt</t>
         </is>
       </c>
       <c r="V56" t="n">
-        <v>529.8099999999999</v>
+        <v>528.24</v>
       </c>
       <c r="W56" t="n">
-        <v>533.51</v>
+        <v>537.22</v>
       </c>
       <c r="X56" t="n">
-        <v>518.79</v>
+        <v>526.24</v>
       </c>
       <c r="Y56" t="n">
-        <v>522.61</v>
+        <v>535.0700000000001</v>
       </c>
       <c r="Z56" t="n">
-        <v>498.4921</v>
+        <v>500.1885</v>
       </c>
       <c r="AA56" t="n">
-        <v>432.4385</v>
+        <v>432.7046</v>
       </c>
       <c r="AB56" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC56" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>9 okt</t>
+          <t>12 okt</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>44.42</v>
+        <v>44.725</v>
       </c>
       <c r="C57" t="n">
-        <v>45.155</v>
+        <v>45.81</v>
       </c>
       <c r="D57" t="n">
-        <v>43.94</v>
+        <v>44.695</v>
       </c>
       <c r="E57" t="n">
-        <v>45.035</v>
+        <v>45.56</v>
       </c>
       <c r="F57" t="n">
-        <v>40.6842</v>
+        <v>40.8072</v>
       </c>
       <c r="G57" t="n">
-        <v>36.5866</v>
+        <v>36.6625</v>
       </c>
       <c r="H57" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I57" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>9 okt</t>
+          <t>12 okt</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>188.98</v>
+        <v>190.58</v>
       </c>
       <c r="M57" t="n">
-        <v>192.58</v>
+        <v>197.88</v>
       </c>
       <c r="N57" t="n">
-        <v>188.86</v>
+        <v>189.78</v>
       </c>
       <c r="O57" t="n">
-        <v>191.46</v>
+        <v>194.46</v>
       </c>
       <c r="P57" t="n">
-        <v>182.8676</v>
+        <v>183.464</v>
       </c>
       <c r="Q57" t="n">
-        <v>164.0101</v>
+        <v>163.9576</v>
       </c>
       <c r="R57" t="n">
         <v>191.5557367172241</v>
@@ -8358,86 +8380,86 @@
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>9 okt</t>
+          <t>12 okt</t>
         </is>
       </c>
       <c r="V57" t="n">
-        <v>528.24</v>
+        <v>537.53</v>
       </c>
       <c r="W57" t="n">
-        <v>537.22</v>
+        <v>542.74</v>
       </c>
       <c r="X57" t="n">
-        <v>526.24</v>
+        <v>535.7</v>
       </c>
       <c r="Y57" t="n">
-        <v>535.0700000000001</v>
+        <v>541.15</v>
       </c>
       <c r="Z57" t="n">
-        <v>500.1885</v>
+        <v>501.7346</v>
       </c>
       <c r="AA57" t="n">
-        <v>432.7046</v>
+        <v>432.9914</v>
       </c>
       <c r="AB57" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC57" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>12 okt</t>
+          <t>13 okt</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>44.725</v>
+        <v>45.69</v>
       </c>
       <c r="C58" t="n">
-        <v>45.81</v>
+        <v>45.97</v>
       </c>
       <c r="D58" t="n">
-        <v>44.695</v>
+        <v>45.35</v>
       </c>
       <c r="E58" t="n">
-        <v>45.56</v>
+        <v>45.95</v>
       </c>
       <c r="F58" t="n">
-        <v>40.8072</v>
+        <v>40.9565</v>
       </c>
       <c r="G58" t="n">
-        <v>36.6625</v>
+        <v>36.7398</v>
       </c>
       <c r="H58" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I58" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>12 okt</t>
+          <t>13 okt</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>190.58</v>
+        <v>196</v>
       </c>
       <c r="M58" t="n">
-        <v>197.88</v>
+        <v>198.18</v>
       </c>
       <c r="N58" t="n">
-        <v>189.78</v>
+        <v>194.02</v>
       </c>
       <c r="O58" t="n">
-        <v>194.46</v>
+        <v>197.28</v>
       </c>
       <c r="P58" t="n">
-        <v>183.464</v>
+        <v>184.062</v>
       </c>
       <c r="Q58" t="n">
-        <v>163.9576</v>
+        <v>163.9196</v>
       </c>
       <c r="R58" t="n">
         <v>191.5557367172241</v>
@@ -8447,86 +8469,86 @@
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>12 okt</t>
+          <t>13 okt</t>
         </is>
       </c>
       <c r="V58" t="n">
-        <v>537.53</v>
+        <v>544.64</v>
       </c>
       <c r="W58" t="n">
-        <v>542.74</v>
+        <v>551.15</v>
       </c>
       <c r="X58" t="n">
-        <v>535.7</v>
+        <v>543.0599999999999</v>
       </c>
       <c r="Y58" t="n">
-        <v>541.15</v>
+        <v>543.45</v>
       </c>
       <c r="Z58" t="n">
-        <v>501.7346</v>
+        <v>502.8689</v>
       </c>
       <c r="AA58" t="n">
-        <v>432.9914</v>
+        <v>433.2839</v>
       </c>
       <c r="AB58" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC58" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>13 okt</t>
+          <t>14 okt</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>45.69</v>
+        <v>45.95</v>
       </c>
       <c r="C59" t="n">
-        <v>45.97</v>
+        <v>46.675</v>
       </c>
       <c r="D59" t="n">
-        <v>45.35</v>
+        <v>45.91</v>
       </c>
       <c r="E59" t="n">
-        <v>45.95</v>
+        <v>46.455</v>
       </c>
       <c r="F59" t="n">
-        <v>40.9565</v>
+        <v>41.125</v>
       </c>
       <c r="G59" t="n">
-        <v>36.7398</v>
+        <v>36.8183</v>
       </c>
       <c r="H59" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I59" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>13 okt</t>
+          <t>14 okt</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>196</v>
+        <v>196.6</v>
       </c>
       <c r="M59" t="n">
-        <v>198.18</v>
+        <v>199.36</v>
       </c>
       <c r="N59" t="n">
-        <v>194.02</v>
+        <v>195.26</v>
       </c>
       <c r="O59" t="n">
-        <v>197.28</v>
+        <v>196.94</v>
       </c>
       <c r="P59" t="n">
-        <v>184.062</v>
+        <v>184.6156</v>
       </c>
       <c r="Q59" t="n">
-        <v>163.9196</v>
+        <v>163.9114</v>
       </c>
       <c r="R59" t="n">
         <v>191.5557367172241</v>
@@ -8536,86 +8558,86 @@
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>13 okt</t>
+          <t>14 okt</t>
         </is>
       </c>
       <c r="V59" t="n">
-        <v>544.64</v>
+        <v>545.27</v>
       </c>
       <c r="W59" t="n">
-        <v>551.15</v>
+        <v>545.75</v>
       </c>
       <c r="X59" t="n">
-        <v>543.0599999999999</v>
+        <v>532.54</v>
       </c>
       <c r="Y59" t="n">
-        <v>543.45</v>
+        <v>533.6900000000001</v>
       </c>
       <c r="Z59" t="n">
-        <v>502.8689</v>
+        <v>503.705</v>
       </c>
       <c r="AA59" t="n">
-        <v>433.2839</v>
+        <v>433.5292</v>
       </c>
       <c r="AB59" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC59" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>14 okt</t>
+          <t>15 okt</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>45.95</v>
+        <v>46.295</v>
       </c>
       <c r="C60" t="n">
-        <v>46.675</v>
+        <v>46.735</v>
       </c>
       <c r="D60" t="n">
-        <v>45.91</v>
+        <v>46.125</v>
       </c>
       <c r="E60" t="n">
-        <v>46.455</v>
+        <v>46.375</v>
       </c>
       <c r="F60" t="n">
-        <v>41.125</v>
+        <v>41.2847</v>
       </c>
       <c r="G60" t="n">
-        <v>36.8183</v>
+        <v>36.8966</v>
       </c>
       <c r="H60" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I60" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>14 okt</t>
+          <t>15 okt</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>196.6</v>
+        <v>199.48</v>
       </c>
       <c r="M60" t="n">
-        <v>199.36</v>
+        <v>203</v>
       </c>
       <c r="N60" t="n">
-        <v>195.26</v>
+        <v>196.98</v>
       </c>
       <c r="O60" t="n">
-        <v>196.94</v>
+        <v>201.25</v>
       </c>
       <c r="P60" t="n">
-        <v>184.6156</v>
+        <v>185.221</v>
       </c>
       <c r="Q60" t="n">
-        <v>163.9114</v>
+        <v>163.9038</v>
       </c>
       <c r="R60" t="n">
         <v>191.5557367172241</v>
@@ -8625,86 +8647,86 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>14 okt</t>
+          <t>15 okt</t>
         </is>
       </c>
       <c r="V60" t="n">
-        <v>545.27</v>
+        <v>533.3200000000001</v>
       </c>
       <c r="W60" t="n">
-        <v>545.75</v>
+        <v>541.13</v>
       </c>
       <c r="X60" t="n">
-        <v>532.54</v>
+        <v>531.22</v>
       </c>
       <c r="Y60" t="n">
-        <v>533.6900000000001</v>
+        <v>539.4400000000001</v>
       </c>
       <c r="Z60" t="n">
-        <v>503.705</v>
+        <v>504.7629</v>
       </c>
       <c r="AA60" t="n">
-        <v>433.5292</v>
+        <v>433.8063</v>
       </c>
       <c r="AB60" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC60" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>15 okt</t>
+          <t>16 okt</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>46.295</v>
+        <v>46.14</v>
       </c>
       <c r="C61" t="n">
-        <v>46.735</v>
+        <v>47.025</v>
       </c>
       <c r="D61" t="n">
-        <v>46.125</v>
+        <v>46.075</v>
       </c>
       <c r="E61" t="n">
-        <v>46.375</v>
+        <v>46.88</v>
       </c>
       <c r="F61" t="n">
-        <v>41.2847</v>
+        <v>41.4622</v>
       </c>
       <c r="G61" t="n">
-        <v>36.8966</v>
+        <v>36.977</v>
       </c>
       <c r="H61" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I61" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>15 okt</t>
+          <t>16 okt</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>199.48</v>
+        <v>200.6</v>
       </c>
       <c r="M61" t="n">
-        <v>203</v>
+        <v>204.2</v>
       </c>
       <c r="N61" t="n">
-        <v>196.98</v>
+        <v>198.68</v>
       </c>
       <c r="O61" t="n">
-        <v>201.25</v>
+        <v>199.22</v>
       </c>
       <c r="P61" t="n">
-        <v>185.221</v>
+        <v>185.6462</v>
       </c>
       <c r="Q61" t="n">
-        <v>163.9038</v>
+        <v>163.9066</v>
       </c>
       <c r="R61" t="n">
         <v>191.5557367172241</v>
@@ -8714,86 +8736,86 @@
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>15 okt</t>
+          <t>16 okt</t>
         </is>
       </c>
       <c r="V61" t="n">
-        <v>533.3200000000001</v>
+        <v>541.3099999999999</v>
       </c>
       <c r="W61" t="n">
-        <v>541.13</v>
+        <v>543.8200000000001</v>
       </c>
       <c r="X61" t="n">
-        <v>531.22</v>
+        <v>524.4299999999999</v>
       </c>
       <c r="Y61" t="n">
-        <v>539.4400000000001</v>
+        <v>529.05</v>
       </c>
       <c r="Z61" t="n">
-        <v>504.7629</v>
+        <v>505.3655</v>
       </c>
       <c r="AA61" t="n">
-        <v>433.8063</v>
+        <v>434.0295</v>
       </c>
       <c r="AB61" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC61" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>16 okt</t>
+          <t>19 okt</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>46.14</v>
+        <v>47.37</v>
       </c>
       <c r="C62" t="n">
-        <v>47.025</v>
+        <v>47.45</v>
       </c>
       <c r="D62" t="n">
-        <v>46.075</v>
+        <v>46.74</v>
       </c>
       <c r="E62" t="n">
-        <v>46.88</v>
+        <v>46.86</v>
       </c>
       <c r="F62" t="n">
-        <v>41.4622</v>
+        <v>41.6313</v>
       </c>
       <c r="G62" t="n">
-        <v>36.977</v>
+        <v>37.0625</v>
       </c>
       <c r="H62" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I62" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>16 okt</t>
+          <t>19 okt</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>200.6</v>
+        <v>199.56</v>
       </c>
       <c r="M62" t="n">
-        <v>204.2</v>
+        <v>200.8</v>
       </c>
       <c r="N62" t="n">
-        <v>198.68</v>
+        <v>197.32</v>
       </c>
       <c r="O62" t="n">
-        <v>199.22</v>
+        <v>199.84</v>
       </c>
       <c r="P62" t="n">
-        <v>185.6462</v>
+        <v>186.057</v>
       </c>
       <c r="Q62" t="n">
-        <v>163.9066</v>
+        <v>163.8811</v>
       </c>
       <c r="R62" t="n">
         <v>191.5557367172241</v>
@@ -8803,86 +8825,86 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>16 okt</t>
+          <t>19 okt</t>
         </is>
       </c>
       <c r="V62" t="n">
-        <v>541.3099999999999</v>
+        <v>528.7</v>
       </c>
       <c r="W62" t="n">
-        <v>543.8200000000001</v>
+        <v>535.5700000000001</v>
       </c>
       <c r="X62" t="n">
-        <v>524.4299999999999</v>
+        <v>528.0599999999999</v>
       </c>
       <c r="Y62" t="n">
-        <v>529.05</v>
+        <v>533.52</v>
       </c>
       <c r="Z62" t="n">
-        <v>505.3655</v>
+        <v>506.0549</v>
       </c>
       <c r="AA62" t="n">
-        <v>434.0295</v>
+        <v>434.2942</v>
       </c>
       <c r="AB62" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC62" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>19 okt</t>
+          <t>20 okt</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>47.37</v>
+        <v>46.875</v>
       </c>
       <c r="C63" t="n">
-        <v>47.45</v>
+        <v>47.505</v>
       </c>
       <c r="D63" t="n">
-        <v>46.74</v>
+        <v>46.36</v>
       </c>
       <c r="E63" t="n">
-        <v>46.86</v>
+        <v>46.57</v>
       </c>
       <c r="F63" t="n">
-        <v>41.6313</v>
+        <v>41.7834</v>
       </c>
       <c r="G63" t="n">
-        <v>37.0625</v>
+        <v>37.1516</v>
       </c>
       <c r="H63" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I63" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>19 okt</t>
+          <t>20 okt</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>199.56</v>
+        <v>201.3</v>
       </c>
       <c r="M63" t="n">
-        <v>200.8</v>
+        <v>203.45</v>
       </c>
       <c r="N63" t="n">
-        <v>197.32</v>
+        <v>199.46</v>
       </c>
       <c r="O63" t="n">
-        <v>199.84</v>
+        <v>201.55</v>
       </c>
       <c r="P63" t="n">
-        <v>186.057</v>
+        <v>186.474</v>
       </c>
       <c r="Q63" t="n">
-        <v>163.8811</v>
+        <v>163.8736</v>
       </c>
       <c r="R63" t="n">
         <v>191.5557367172241</v>
@@ -8892,86 +8914,86 @@
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>19 okt</t>
+          <t>20 okt</t>
         </is>
       </c>
       <c r="V63" t="n">
-        <v>528.7</v>
+        <v>533.91</v>
       </c>
       <c r="W63" t="n">
-        <v>535.5700000000001</v>
+        <v>534.21</v>
       </c>
       <c r="X63" t="n">
-        <v>528.0599999999999</v>
+        <v>525.84</v>
       </c>
       <c r="Y63" t="n">
-        <v>533.52</v>
+        <v>531.87</v>
       </c>
       <c r="Z63" t="n">
-        <v>506.0549</v>
+        <v>506.5901</v>
       </c>
       <c r="AA63" t="n">
-        <v>434.2942</v>
+        <v>434.6038</v>
       </c>
       <c r="AB63" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC63" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20 okt</t>
+          <t>21 okt</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>46.875</v>
+        <v>46.97</v>
       </c>
       <c r="C64" t="n">
-        <v>47.505</v>
+        <v>47.135</v>
       </c>
       <c r="D64" t="n">
-        <v>46.36</v>
+        <v>46.73</v>
       </c>
       <c r="E64" t="n">
-        <v>46.57</v>
+        <v>46.84</v>
       </c>
       <c r="F64" t="n">
-        <v>41.7834</v>
+        <v>41.9472</v>
       </c>
       <c r="G64" t="n">
-        <v>37.1516</v>
+        <v>37.2379</v>
       </c>
       <c r="H64" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I64" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>20 okt</t>
+          <t>21 okt</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>201.3</v>
+        <v>201.8</v>
       </c>
       <c r="M64" t="n">
-        <v>203.45</v>
+        <v>208.65</v>
       </c>
       <c r="N64" t="n">
-        <v>199.46</v>
+        <v>200</v>
       </c>
       <c r="O64" t="n">
-        <v>201.55</v>
+        <v>208.65</v>
       </c>
       <c r="P64" t="n">
-        <v>186.474</v>
+        <v>187.1278</v>
       </c>
       <c r="Q64" t="n">
-        <v>163.8736</v>
+        <v>163.8728</v>
       </c>
       <c r="R64" t="n">
         <v>191.5557367172241</v>
@@ -8981,86 +9003,86 @@
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>20 okt</t>
+          <t>21 okt</t>
         </is>
       </c>
       <c r="V64" t="n">
-        <v>533.91</v>
+        <v>529.4400000000001</v>
       </c>
       <c r="W64" t="n">
-        <v>534.21</v>
+        <v>533.28</v>
       </c>
       <c r="X64" t="n">
-        <v>525.84</v>
+        <v>525.02</v>
       </c>
       <c r="Y64" t="n">
-        <v>531.87</v>
+        <v>532.95</v>
       </c>
       <c r="Z64" t="n">
-        <v>506.5901</v>
+        <v>507.1919</v>
       </c>
       <c r="AA64" t="n">
-        <v>434.6038</v>
+        <v>434.9192</v>
       </c>
       <c r="AB64" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC64" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>21 okt</t>
+          <t>22 okt</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>46.97</v>
+        <v>47.05</v>
       </c>
       <c r="C65" t="n">
-        <v>47.135</v>
+        <v>47.6</v>
       </c>
       <c r="D65" t="n">
-        <v>46.73</v>
+        <v>46.55</v>
       </c>
       <c r="E65" t="n">
-        <v>46.84</v>
+        <v>46.55</v>
       </c>
       <c r="F65" t="n">
-        <v>41.9472</v>
+        <v>42.1061</v>
       </c>
       <c r="G65" t="n">
-        <v>37.2379</v>
+        <v>37.3217</v>
       </c>
       <c r="H65" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I65" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>21 okt</t>
+          <t>22 okt</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>201.8</v>
+        <v>207.75</v>
       </c>
       <c r="M65" t="n">
-        <v>208.65</v>
+        <v>216.65</v>
       </c>
       <c r="N65" t="n">
-        <v>200</v>
+        <v>205.1</v>
       </c>
       <c r="O65" t="n">
-        <v>208.65</v>
+        <v>215.35</v>
       </c>
       <c r="P65" t="n">
-        <v>187.1278</v>
+        <v>187.9272</v>
       </c>
       <c r="Q65" t="n">
-        <v>163.8728</v>
+        <v>163.9019</v>
       </c>
       <c r="R65" t="n">
         <v>191.5557367172241</v>
@@ -9070,86 +9092,86 @@
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>21 okt</t>
+          <t>22 okt</t>
         </is>
       </c>
       <c r="V65" t="n">
-        <v>529.4400000000001</v>
+        <v>533.14</v>
       </c>
       <c r="W65" t="n">
-        <v>533.28</v>
+        <v>533.6</v>
       </c>
       <c r="X65" t="n">
-        <v>525.02</v>
+        <v>520.3</v>
       </c>
       <c r="Y65" t="n">
-        <v>532.95</v>
+        <v>521.08</v>
       </c>
       <c r="Z65" t="n">
-        <v>507.1919</v>
+        <v>507.7834</v>
       </c>
       <c r="AA65" t="n">
-        <v>434.9192</v>
+        <v>435.1471</v>
       </c>
       <c r="AB65" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC65" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>22 okt</t>
+          <t>23 okt</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>47.05</v>
+        <v>47.13</v>
       </c>
       <c r="C66" t="n">
-        <v>47.6</v>
+        <v>48.38</v>
       </c>
       <c r="D66" t="n">
-        <v>46.59</v>
+        <v>46.895</v>
       </c>
       <c r="E66" t="n">
-        <v>46.625</v>
+        <v>48.345</v>
       </c>
       <c r="F66" t="n">
-        <v>42.1076</v>
+        <v>42.2936</v>
       </c>
       <c r="G66" t="n">
-        <v>37.322</v>
+        <v>37.411</v>
       </c>
       <c r="H66" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I66" t="n">
-        <v>44.24892779758999</v>
+        <v>45.41250092642648</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>22 okt</t>
+          <t>23 okt</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>207.75</v>
+        <v>213.55</v>
       </c>
       <c r="M66" t="n">
-        <v>216.55</v>
+        <v>215.85</v>
       </c>
       <c r="N66" t="n">
-        <v>205.1</v>
+        <v>210.05</v>
       </c>
       <c r="O66" t="n">
-        <v>216.45</v>
+        <v>214.35</v>
       </c>
       <c r="P66" t="n">
-        <v>187.9492</v>
+        <v>188.6114</v>
       </c>
       <c r="Q66" t="n">
-        <v>163.9074</v>
+        <v>163.9242</v>
       </c>
       <c r="R66" t="n">
         <v>191.5557367172241</v>
@@ -9159,32 +9181,32 @@
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>22 okt</t>
+          <t>23 okt</t>
         </is>
       </c>
       <c r="V66" t="n">
-        <v>532.7</v>
+        <v>517.995</v>
       </c>
       <c r="W66" t="n">
-        <v>533.596</v>
+        <v>525.77</v>
       </c>
       <c r="X66" t="n">
-        <v>520.3</v>
+        <v>515.7</v>
       </c>
       <c r="Y66" t="n">
-        <v>521.58</v>
+        <v>524.525</v>
       </c>
       <c r="Z66" t="n">
-        <v>507.7934</v>
+        <v>508.3549</v>
       </c>
       <c r="AA66" t="n">
-        <v>435.1496</v>
+        <v>435.3676</v>
       </c>
       <c r="AB66" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC66" t="n">
-        <v>510.0814339773996</v>
+        <v>510.3278547014509</v>
       </c>
     </row>
   </sheetData>

--- a/rapporten/trend-agent.xlsx
+++ b/rapporten/trend-agent.xlsx
@@ -1944,7 +1944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2212,6 +2212,28 @@
       </c>
       <c r="E12" s="3">
         <f>B12/$B$2-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>10076.18</v>
+      </c>
+      <c r="C13" s="2">
+        <f>B13-B12</f>
+        <v/>
+      </c>
+      <c r="D13" s="3">
+        <f>B13/B12-1</f>
+        <v/>
+      </c>
+      <c r="E13" s="3">
+        <f>B13/$B$2-1</f>
         <v/>
       </c>
     </row>
@@ -2355,38 +2377,38 @@
     <row r="6" ht="22" customHeight="1">
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Shell (SHELL.AS)  ·  48,35 EUR</t>
+          <t>Shell (SHELL.AS)  ·  47,96 EUR</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>SAP (SAP.DE)  ·  214,35 EUR</t>
+          <t>SAP (SAP.DE)  ·  212,80 EUR</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>Gestegen: 27,4% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +7,3% (winst). De bot verkoopt als de koers onder 45,41 zakt (-6,1%).</t>
+          <t>Gestegen: 28,0% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +6,4% (winst). De bot verkoopt als de koers onder 45,41 zakt (-5,3%).</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>Gestegen: 41,7% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +11,9% (winst). De bot verkoopt als de koers onder 198,88 zakt (-7,2%).</t>
+          <t>Gestegen: 33,6% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +11,1% (winst). De bot verkoopt als de koers onder 198,88 zakt (-6,5%).</t>
         </is>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Microsoft (MSFT)  ·  524,53 USD</t>
+          <t>Microsoft (MSFT)  ·  532,75 USD</t>
         </is>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Gestegen: 37,7% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: -2,0% (verlies). De bot verkoopt als de koers onder 510,33 zakt (-2,7%).</t>
+          <t>Gestegen: 37,2% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: -0,5% (verlies). De bot verkoopt als de koers onder 510,33 zakt (-4,2%).</t>
         </is>
       </c>
     </row>
@@ -2865,19 +2887,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.191</v>
+        <v>0.175</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.2901872546925657</v>
+        <v>0.2474799321915424</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1394061011780339</v>
+        <v>0.1401569249949459</v>
       </c>
       <c r="H2" t="n">
         <v>0.97</v>
       </c>
       <c r="I2" t="n">
-        <v>48.35</v>
+        <v>47.96</v>
       </c>
     </row>
     <row r="3">
@@ -2886,33 +2908,33 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SAP.DE</t>
+          <t>XLE</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Energie-ETF</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.139</v>
+        <v>0.137</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.3460813784807195</v>
+        <v>0.216848042537038</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.1638072246036177</v>
+        <v>0.1225015854604696</v>
       </c>
       <c r="H3" t="n">
-        <v>0.86</v>
+        <v>1.04</v>
       </c>
       <c r="I3" t="n">
-        <v>214.35</v>
+        <v>69.64</v>
       </c>
     </row>
     <row r="4">
@@ -2921,12 +2943,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>XLE</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Energie-ETF</t>
+          <t>ExxonMobil</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2935,19 +2957,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.123</v>
+        <v>0.125</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.1950325890589528</v>
+        <v>0.2137022353203739</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.1075080434660998</v>
+        <v>0.1491998708528142</v>
       </c>
       <c r="H4" t="n">
-        <v>1.05</v>
+        <v>0.84</v>
       </c>
       <c r="I4" t="n">
-        <v>69.33</v>
+        <v>184.55</v>
       </c>
     </row>
     <row r="5">
@@ -2956,12 +2978,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>WKL.AS</t>
+          <t>SAP.DE</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Wolters Kluwer</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2970,19 +2992,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.118</v>
+        <v>0.125</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.2440098033883189</v>
+        <v>0.3132560594222698</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.2804417776422821</v>
+        <v>0.1445783409398846</v>
       </c>
       <c r="H5" t="n">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="I5" t="n">
-        <v>88.12</v>
+        <v>212.8</v>
       </c>
     </row>
     <row r="6">
@@ -2991,33 +3013,33 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>OR.PA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>L'Oreal</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.111</v>
+        <v>0.109</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.1914215590937345</v>
+        <v>0.1408083441981747</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.1299494720829752</v>
+        <v>0.1457378368651858</v>
       </c>
       <c r="H6" t="n">
-        <v>0.88</v>
+        <v>1.09</v>
       </c>
       <c r="I6" t="n">
-        <v>183.21</v>
+        <v>437.5</v>
       </c>
     </row>
     <row r="7">
@@ -3026,33 +3048,33 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>WKL.AS</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Wolters Kluwer</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.103</v>
+        <v>0.101</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.1273490588752719</v>
+        <v>0.1910707794893649</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.1085928318442351</v>
+        <v>0.2671132443881838</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="I7" t="n">
-        <v>407.94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8">
@@ -3061,33 +3083,33 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OR.PA</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>L'Oreal</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.099</v>
+        <v>0.093</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.1377644315509203</v>
+        <v>0.356941436947817</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.1325880691778327</v>
+        <v>0.0321212345521642</v>
       </c>
       <c r="H8" t="n">
-        <v>1.03</v>
+        <v>0.85</v>
       </c>
       <c r="I8" t="n">
-        <v>435.65</v>
+        <v>532.75</v>
       </c>
     </row>
     <row r="9">
@@ -3096,12 +3118,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -3110,19 +3132,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.095</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.3505845322893033</v>
+        <v>0.1048338360517045</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.05341118657135846</v>
+        <v>0.1004136960111006</v>
       </c>
       <c r="H9" t="n">
-        <v>0.86</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>524.53</v>
+        <v>404.27</v>
       </c>
     </row>
     <row r="10">
@@ -3131,33 +3153,33 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TTE.PA</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TotalEnergies</t>
+          <t>Palantir</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.08</v>
+        <v>0.082</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.1480907311729238</v>
+        <v>0.6098923102273786</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.04510946897647328</v>
+        <v>0.04850528305508517</v>
       </c>
       <c r="H10" t="n">
-        <v>1.03</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>83.73</v>
+        <v>198.87</v>
       </c>
     </row>
     <row r="11">
@@ -3166,33 +3188,33 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>TTE.PA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.076</v>
+        <v>0.074</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.434316069197425</v>
+        <v>0.1178534124458734</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.04340524005081736</v>
+        <v>0.05971778228284874</v>
       </c>
       <c r="H11" t="n">
-        <v>0.65</v>
+        <v>1.03</v>
       </c>
       <c r="I11" t="n">
-        <v>248.56</v>
+        <v>83.79000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -3463,23 +3485,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>27 jul</t>
+          <t>28 jul</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>37.5802</v>
+        <v>37.7139</v>
       </c>
       <c r="C2" t="n">
-        <v>38.1099</v>
+        <v>38.0109</v>
       </c>
       <c r="D2" t="n">
-        <v>37.4317</v>
+        <v>37.4713</v>
       </c>
       <c r="E2" t="n">
-        <v>37.9515</v>
+        <v>37.4713</v>
       </c>
       <c r="F2" t="n">
-        <v>35.931</v>
+        <v>35.9372</v>
       </c>
       <c r="H2" t="n">
         <v>45.05751734733581</v>
@@ -3489,23 +3511,23 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>27 jul</t>
+          <t>28 jul</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>142.38</v>
+        <v>152.2</v>
       </c>
       <c r="M2" t="n">
-        <v>151.56</v>
+        <v>159.76</v>
       </c>
       <c r="N2" t="n">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="O2" t="n">
-        <v>151.28</v>
+        <v>159.24</v>
       </c>
       <c r="P2" t="n">
-        <v>144.0572</v>
+        <v>144.1076</v>
       </c>
       <c r="R2" t="n">
         <v>191.5557367172241</v>
@@ -3515,23 +3537,23 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>24 jul</t>
+          <t>27 jul</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>386.3227</v>
+        <v>389.347</v>
       </c>
       <c r="W2" t="n">
-        <v>388.299</v>
+        <v>393.4593</v>
       </c>
       <c r="X2" t="n">
-        <v>379.9348</v>
+        <v>387.261</v>
       </c>
       <c r="Y2" t="n">
-        <v>380.9828</v>
+        <v>388.3689</v>
       </c>
       <c r="Z2" t="n">
-        <v>398.3214</v>
+        <v>398.0172</v>
       </c>
       <c r="AB2" t="n">
         <v>535.3375423278808</v>
@@ -3543,23 +3565,23 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>28 jul</t>
+          <t>29 jul</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>37.7139</v>
+        <v>38.0653</v>
       </c>
       <c r="C3" t="n">
-        <v>38.0109</v>
+        <v>38.59</v>
       </c>
       <c r="D3" t="n">
-        <v>37.4713</v>
+        <v>37.7089</v>
       </c>
       <c r="E3" t="n">
-        <v>37.4713</v>
+        <v>38.4415</v>
       </c>
       <c r="F3" t="n">
-        <v>35.9372</v>
+        <v>35.9692</v>
       </c>
       <c r="H3" t="n">
         <v>45.05751734733581</v>
@@ -3569,23 +3591,23 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>28 jul</t>
+          <t>29 jul</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>152.2</v>
+        <v>159.84</v>
       </c>
       <c r="M3" t="n">
-        <v>159.76</v>
+        <v>163.3</v>
       </c>
       <c r="N3" t="n">
-        <v>151</v>
+        <v>156.48</v>
       </c>
       <c r="O3" t="n">
-        <v>159.24</v>
+        <v>162.04</v>
       </c>
       <c r="P3" t="n">
-        <v>144.1076</v>
+        <v>144.28</v>
       </c>
       <c r="R3" t="n">
         <v>191.5557367172241</v>
@@ -3595,23 +3617,23 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>27 jul</t>
+          <t>28 jul</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>389.347</v>
+        <v>392.4213</v>
       </c>
       <c r="W3" t="n">
-        <v>393.4593</v>
+        <v>399.5678</v>
       </c>
       <c r="X3" t="n">
-        <v>387.261</v>
+        <v>390.5647</v>
       </c>
       <c r="Y3" t="n">
-        <v>388.3689</v>
+        <v>392.6109</v>
       </c>
       <c r="Z3" t="n">
-        <v>398.0172</v>
+        <v>397.7139</v>
       </c>
       <c r="AB3" t="n">
         <v>535.3375423278808</v>
@@ -3623,23 +3645,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>29 jul</t>
+          <t>30 jul</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38.0653</v>
+        <v>38.6098</v>
       </c>
       <c r="C4" t="n">
-        <v>38.59</v>
+        <v>39.1444</v>
       </c>
       <c r="D4" t="n">
-        <v>37.7089</v>
+        <v>38.3277</v>
       </c>
       <c r="E4" t="n">
-        <v>38.4415</v>
+        <v>38.5108</v>
       </c>
       <c r="F4" t="n">
-        <v>35.9692</v>
+        <v>35.9978</v>
       </c>
       <c r="H4" t="n">
         <v>45.05751734733581</v>
@@ -3649,23 +3671,23 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>29 jul</t>
+          <t>30 jul</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>159.84</v>
+        <v>162.5</v>
       </c>
       <c r="M4" t="n">
-        <v>163.3</v>
+        <v>163.16</v>
       </c>
       <c r="N4" t="n">
-        <v>156.48</v>
+        <v>155.2</v>
       </c>
       <c r="O4" t="n">
-        <v>162.04</v>
+        <v>155.92</v>
       </c>
       <c r="P4" t="n">
-        <v>144.28</v>
+        <v>144.3804</v>
       </c>
       <c r="R4" t="n">
         <v>191.5557367172241</v>
@@ -3675,23 +3697,23 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>28 jul</t>
+          <t>29 jul</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>392.4213</v>
+        <v>392.6608</v>
       </c>
       <c r="W4" t="n">
-        <v>399.5678</v>
+        <v>400.4961</v>
       </c>
       <c r="X4" t="n">
-        <v>390.5647</v>
+        <v>388.0095</v>
       </c>
       <c r="Y4" t="n">
-        <v>392.6109</v>
+        <v>389.8062</v>
       </c>
       <c r="Z4" t="n">
-        <v>397.7139</v>
+        <v>397.1057</v>
       </c>
       <c r="AB4" t="n">
         <v>535.3375423278808</v>
@@ -3703,23 +3725,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>30 jul</t>
+          <t>31 jul</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>38.6098</v>
       </c>
       <c r="C5" t="n">
-        <v>39.1444</v>
+        <v>39.575</v>
       </c>
       <c r="D5" t="n">
-        <v>38.3277</v>
+        <v>38.4464</v>
       </c>
       <c r="E5" t="n">
-        <v>38.5108</v>
+        <v>39.3226</v>
       </c>
       <c r="F5" t="n">
-        <v>35.9978</v>
+        <v>36.0495</v>
       </c>
       <c r="H5" t="n">
         <v>45.05751734733581</v>
@@ -3729,23 +3751,23 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>30 jul</t>
+          <t>31 jul</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>162.5</v>
+        <v>154.9</v>
       </c>
       <c r="M5" t="n">
-        <v>163.16</v>
+        <v>158.26</v>
       </c>
       <c r="N5" t="n">
-        <v>155.2</v>
+        <v>153.6</v>
       </c>
       <c r="O5" t="n">
-        <v>155.92</v>
+        <v>157.68</v>
       </c>
       <c r="P5" t="n">
-        <v>144.3804</v>
+        <v>144.4984</v>
       </c>
       <c r="R5" t="n">
         <v>191.5557367172241</v>
@@ -3755,23 +3777,23 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>29 jul</t>
+          <t>30 jul</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>392.6608</v>
+        <v>437.0772</v>
       </c>
       <c r="W5" t="n">
-        <v>400.4961</v>
+        <v>457.8281</v>
       </c>
       <c r="X5" t="n">
-        <v>388.0095</v>
+        <v>431.6275</v>
       </c>
       <c r="Y5" t="n">
-        <v>389.8062</v>
+        <v>450.2524</v>
       </c>
       <c r="Z5" t="n">
-        <v>397.1057</v>
+        <v>397.6741</v>
       </c>
       <c r="AB5" t="n">
         <v>535.3375423278808</v>
@@ -3783,26 +3805,26 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>31 jul</t>
+          <t>3 aug</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>38.6098</v>
+        <v>38.3128</v>
       </c>
       <c r="C6" t="n">
-        <v>39.575</v>
+        <v>39.4067</v>
       </c>
       <c r="D6" t="n">
-        <v>38.4464</v>
+        <v>38.2138</v>
       </c>
       <c r="E6" t="n">
-        <v>39.3226</v>
+        <v>39.4067</v>
       </c>
       <c r="F6" t="n">
-        <v>36.0495</v>
+        <v>36.1112</v>
       </c>
       <c r="G6" t="n">
-        <v>34.0907</v>
+        <v>34.1393</v>
       </c>
       <c r="H6" t="n">
         <v>45.05751734733581</v>
@@ -3812,26 +3834,26 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>31 jul</t>
+          <t>3 aug</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>154.9</v>
+        <v>160</v>
       </c>
       <c r="M6" t="n">
-        <v>158.26</v>
+        <v>168.7</v>
       </c>
       <c r="N6" t="n">
-        <v>153.6</v>
+        <v>159.6</v>
       </c>
       <c r="O6" t="n">
-        <v>157.68</v>
+        <v>164.64</v>
       </c>
       <c r="P6" t="n">
-        <v>144.4984</v>
+        <v>144.7016</v>
       </c>
       <c r="Q6" t="n">
-        <v>171.6292</v>
+        <v>171.301</v>
       </c>
       <c r="R6" t="n">
         <v>191.5557367172241</v>
@@ -3841,26 +3863,26 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>30 jul</t>
+          <t>31 jul</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>437.0772</v>
+        <v>449.1545</v>
       </c>
       <c r="W6" t="n">
-        <v>457.8281</v>
+        <v>465.9628</v>
       </c>
       <c r="X6" t="n">
-        <v>431.6275</v>
+        <v>448.4857</v>
       </c>
       <c r="Y6" t="n">
-        <v>450.2524</v>
+        <v>463.8468</v>
       </c>
       <c r="Z6" t="n">
-        <v>397.6741</v>
+        <v>398.6364</v>
       </c>
       <c r="AA6" t="n">
-        <v>431.6738</v>
+        <v>431.4438</v>
       </c>
       <c r="AB6" t="n">
         <v>535.3375423278808</v>
@@ -3872,26 +3894,26 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3 aug</t>
+          <t>4 aug</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>38.3128</v>
+        <v>39.3028</v>
       </c>
       <c r="C7" t="n">
-        <v>39.4067</v>
+        <v>39.6443</v>
       </c>
       <c r="D7" t="n">
-        <v>38.2138</v>
+        <v>38.2039</v>
       </c>
       <c r="E7" t="n">
-        <v>39.4067</v>
+        <v>38.486</v>
       </c>
       <c r="F7" t="n">
-        <v>36.1112</v>
+        <v>36.1495</v>
       </c>
       <c r="G7" t="n">
-        <v>34.1393</v>
+        <v>34.1818</v>
       </c>
       <c r="H7" t="n">
         <v>45.05751734733581</v>
@@ -3901,26 +3923,26 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>3 aug</t>
+          <t>4 aug</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>160</v>
+        <v>162.86</v>
       </c>
       <c r="M7" t="n">
-        <v>168.7</v>
+        <v>168.56</v>
       </c>
       <c r="N7" t="n">
-        <v>159.6</v>
+        <v>162.4</v>
       </c>
       <c r="O7" t="n">
-        <v>164.64</v>
+        <v>167.38</v>
       </c>
       <c r="P7" t="n">
-        <v>144.7016</v>
+        <v>145.02</v>
       </c>
       <c r="Q7" t="n">
-        <v>171.301</v>
+        <v>170.9913</v>
       </c>
       <c r="R7" t="n">
         <v>191.5557367172241</v>
@@ -3930,26 +3952,26 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>31 jul</t>
+          <t>3 aug</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>449.1545</v>
+        <v>475.2354</v>
       </c>
       <c r="W7" t="n">
-        <v>465.9628</v>
+        <v>490.7262</v>
       </c>
       <c r="X7" t="n">
-        <v>448.4857</v>
+        <v>474.1075</v>
       </c>
       <c r="Y7" t="n">
-        <v>463.8468</v>
+        <v>486.7337</v>
       </c>
       <c r="Z7" t="n">
-        <v>398.6364</v>
+        <v>399.9838</v>
       </c>
       <c r="AA7" t="n">
-        <v>431.4438</v>
+        <v>431.3306</v>
       </c>
       <c r="AB7" t="n">
         <v>535.3375423278808</v>
@@ -3961,26 +3983,26 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4 aug</t>
+          <t>5 aug</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>39.3028</v>
+        <v>38.4811</v>
       </c>
       <c r="C8" t="n">
-        <v>39.6443</v>
+        <v>38.7632</v>
       </c>
       <c r="D8" t="n">
-        <v>38.2039</v>
+        <v>37.9366</v>
       </c>
       <c r="E8" t="n">
-        <v>38.486</v>
+        <v>38.0307</v>
       </c>
       <c r="F8" t="n">
-        <v>36.1495</v>
+        <v>36.1966</v>
       </c>
       <c r="G8" t="n">
-        <v>34.1818</v>
+        <v>34.2215</v>
       </c>
       <c r="H8" t="n">
         <v>45.05751734733581</v>
@@ -3990,26 +4012,26 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>4 aug</t>
+          <t>5 aug</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>162.86</v>
+        <v>167.92</v>
       </c>
       <c r="M8" t="n">
-        <v>168.56</v>
+        <v>172.6</v>
       </c>
       <c r="N8" t="n">
-        <v>162.4</v>
+        <v>167.3</v>
       </c>
       <c r="O8" t="n">
-        <v>167.38</v>
+        <v>169.26</v>
       </c>
       <c r="P8" t="n">
-        <v>145.02</v>
+        <v>145.4052</v>
       </c>
       <c r="Q8" t="n">
-        <v>170.9913</v>
+        <v>170.7022</v>
       </c>
       <c r="R8" t="n">
         <v>191.5557367172241</v>
@@ -4019,26 +4041,26 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>3 aug</t>
+          <t>4 aug</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>475.2354</v>
+        <v>479.9964</v>
       </c>
       <c r="W8" t="n">
-        <v>490.7262</v>
+        <v>498.5016</v>
       </c>
       <c r="X8" t="n">
-        <v>474.1075</v>
+        <v>478.2697</v>
       </c>
       <c r="Y8" t="n">
-        <v>486.7337</v>
+        <v>491.884</v>
       </c>
       <c r="Z8" t="n">
-        <v>399.9838</v>
+        <v>401.4555</v>
       </c>
       <c r="AA8" t="n">
-        <v>431.3306</v>
+        <v>431.2438</v>
       </c>
       <c r="AB8" t="n">
         <v>535.3375423278808</v>
@@ -4050,26 +4072,26 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5 aug</t>
+          <t>6 aug</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>38.4811</v>
+        <v>38.0752</v>
       </c>
       <c r="C9" t="n">
-        <v>38.7632</v>
+        <v>38.4069</v>
       </c>
       <c r="D9" t="n">
-        <v>37.9366</v>
+        <v>37.9168</v>
       </c>
       <c r="E9" t="n">
-        <v>38.0307</v>
+        <v>38.392</v>
       </c>
       <c r="F9" t="n">
-        <v>36.1966</v>
+        <v>36.2474</v>
       </c>
       <c r="G9" t="n">
-        <v>34.2215</v>
+        <v>34.2607</v>
       </c>
       <c r="H9" t="n">
         <v>45.05751734733581</v>
@@ -4079,26 +4101,26 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>5 aug</t>
+          <t>6 aug</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>167.92</v>
+        <v>171.44</v>
       </c>
       <c r="M9" t="n">
-        <v>172.6</v>
+        <v>173.1</v>
       </c>
       <c r="N9" t="n">
-        <v>167.3</v>
+        <v>168.08</v>
       </c>
       <c r="O9" t="n">
-        <v>169.26</v>
+        <v>170.98</v>
       </c>
       <c r="P9" t="n">
-        <v>145.4052</v>
+        <v>145.7928</v>
       </c>
       <c r="Q9" t="n">
-        <v>170.7022</v>
+        <v>170.384</v>
       </c>
       <c r="R9" t="n">
         <v>191.5557367172241</v>
@@ -4108,26 +4130,26 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>4 aug</t>
+          <t>5 aug</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>479.9964</v>
+        <v>495.4273</v>
       </c>
       <c r="W9" t="n">
-        <v>498.5016</v>
+        <v>497.3038</v>
       </c>
       <c r="X9" t="n">
-        <v>478.2697</v>
+        <v>484.7674</v>
       </c>
       <c r="Y9" t="n">
-        <v>491.884</v>
+        <v>486.5441</v>
       </c>
       <c r="Z9" t="n">
-        <v>401.4555</v>
+        <v>402.8307</v>
       </c>
       <c r="AA9" t="n">
-        <v>431.2438</v>
+        <v>431.1393</v>
       </c>
       <c r="AB9" t="n">
         <v>535.3375423278808</v>
@@ -4139,26 +4161,26 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6 aug</t>
+          <t>7 aug</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>38.0752</v>
+        <v>38.5207</v>
       </c>
       <c r="C10" t="n">
-        <v>38.4069</v>
+        <v>38.5999</v>
       </c>
       <c r="D10" t="n">
-        <v>37.9168</v>
+        <v>37.897</v>
       </c>
       <c r="E10" t="n">
-        <v>38.392</v>
+        <v>38.0059</v>
       </c>
       <c r="F10" t="n">
-        <v>36.2474</v>
+        <v>36.2952</v>
       </c>
       <c r="G10" t="n">
-        <v>34.2607</v>
+        <v>34.294</v>
       </c>
       <c r="H10" t="n">
         <v>45.05751734733581</v>
@@ -4168,26 +4190,26 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>6 aug</t>
+          <t>7 aug</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>171.44</v>
+        <v>173.82</v>
       </c>
       <c r="M10" t="n">
-        <v>173.1</v>
+        <v>179.56</v>
       </c>
       <c r="N10" t="n">
-        <v>168.08</v>
+        <v>173.82</v>
       </c>
       <c r="O10" t="n">
-        <v>170.98</v>
+        <v>177.96</v>
       </c>
       <c r="P10" t="n">
-        <v>145.7928</v>
+        <v>146.2468</v>
       </c>
       <c r="Q10" t="n">
-        <v>170.384</v>
+        <v>170.0918</v>
       </c>
       <c r="R10" t="n">
         <v>191.5557367172241</v>
@@ -4197,26 +4219,26 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>5 aug</t>
+          <t>6 aug</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>495.4273</v>
+        <v>487.632</v>
       </c>
       <c r="W10" t="n">
-        <v>497.3038</v>
+        <v>500.6176</v>
       </c>
       <c r="X10" t="n">
-        <v>484.7674</v>
+        <v>487.6021</v>
       </c>
       <c r="Y10" t="n">
-        <v>486.5441</v>
+        <v>498.9207</v>
       </c>
       <c r="Z10" t="n">
-        <v>402.8307</v>
+        <v>404.5041</v>
       </c>
       <c r="AA10" t="n">
-        <v>431.1393</v>
+        <v>431.087</v>
       </c>
       <c r="AB10" t="n">
         <v>535.3375423278808</v>
@@ -4228,26 +4250,26 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>7 aug</t>
+          <t>10 aug</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>38.5207</v>
+        <v>38.0356</v>
       </c>
       <c r="C11" t="n">
-        <v>38.5999</v>
+        <v>38.4366</v>
       </c>
       <c r="D11" t="n">
-        <v>37.897</v>
+        <v>37.803</v>
       </c>
       <c r="E11" t="n">
-        <v>38.0059</v>
+        <v>38.4019</v>
       </c>
       <c r="F11" t="n">
-        <v>36.2952</v>
+        <v>36.3315</v>
       </c>
       <c r="G11" t="n">
-        <v>34.294</v>
+        <v>34.3294</v>
       </c>
       <c r="H11" t="n">
         <v>45.05751734733581</v>
@@ -4257,26 +4279,26 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>7 aug</t>
+          <t>10 aug</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>173.82</v>
+        <v>178.92</v>
       </c>
       <c r="M11" t="n">
-        <v>179.56</v>
+        <v>179.96</v>
       </c>
       <c r="N11" t="n">
-        <v>173.82</v>
+        <v>175.86</v>
       </c>
       <c r="O11" t="n">
-        <v>177.96</v>
+        <v>179.3</v>
       </c>
       <c r="P11" t="n">
-        <v>146.2468</v>
+        <v>146.4748</v>
       </c>
       <c r="Q11" t="n">
-        <v>170.0918</v>
+        <v>169.8238</v>
       </c>
       <c r="R11" t="n">
         <v>191.5557367172241</v>
@@ -4286,26 +4308,26 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>6 aug</t>
+          <t>7 aug</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>487.632</v>
+        <v>498.272</v>
       </c>
       <c r="W11" t="n">
-        <v>500.6176</v>
+        <v>504.2308</v>
       </c>
       <c r="X11" t="n">
-        <v>487.6021</v>
+        <v>497.7929</v>
       </c>
       <c r="Y11" t="n">
-        <v>498.9207</v>
+        <v>499.0505</v>
       </c>
       <c r="Z11" t="n">
-        <v>404.5041</v>
+        <v>406.2472</v>
       </c>
       <c r="AA11" t="n">
-        <v>431.087</v>
+        <v>431.0194</v>
       </c>
       <c r="AB11" t="n">
         <v>535.3375423278808</v>
@@ -4317,26 +4339,26 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10 aug</t>
+          <t>11 aug</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>38.0356</v>
+        <v>38.7385</v>
       </c>
       <c r="C12" t="n">
-        <v>38.4366</v>
+        <v>39.0058</v>
       </c>
       <c r="D12" t="n">
-        <v>37.803</v>
+        <v>38.6148</v>
       </c>
       <c r="E12" t="n">
-        <v>38.4019</v>
+        <v>38.9662</v>
       </c>
       <c r="F12" t="n">
-        <v>36.3315</v>
+        <v>36.374</v>
       </c>
       <c r="G12" t="n">
-        <v>34.3294</v>
+        <v>34.3685</v>
       </c>
       <c r="H12" t="n">
         <v>45.05751734733581</v>
@@ -4346,26 +4368,26 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>10 aug</t>
+          <t>11 aug</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>178.92</v>
+        <v>180</v>
       </c>
       <c r="M12" t="n">
-        <v>179.96</v>
+        <v>183.24</v>
       </c>
       <c r="N12" t="n">
-        <v>175.86</v>
+        <v>178.14</v>
       </c>
       <c r="O12" t="n">
-        <v>179.3</v>
+        <v>180.7</v>
       </c>
       <c r="P12" t="n">
-        <v>146.4748</v>
+        <v>146.8316</v>
       </c>
       <c r="Q12" t="n">
-        <v>169.8238</v>
+        <v>169.5375</v>
       </c>
       <c r="R12" t="n">
         <v>191.5557367172241</v>
@@ -4375,26 +4397,26 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>7 aug</t>
+          <t>10 aug</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>498.272</v>
+        <v>502.4941</v>
       </c>
       <c r="W12" t="n">
-        <v>504.2308</v>
+        <v>512.7646999999999</v>
       </c>
       <c r="X12" t="n">
-        <v>497.7929</v>
+        <v>501.3262</v>
       </c>
       <c r="Y12" t="n">
-        <v>499.0505</v>
+        <v>505.1091</v>
       </c>
       <c r="Z12" t="n">
-        <v>406.2472</v>
+        <v>407.8257</v>
       </c>
       <c r="AA12" t="n">
-        <v>431.0194</v>
+        <v>430.9778</v>
       </c>
       <c r="AB12" t="n">
         <v>535.3375423278808</v>
@@ -4406,26 +4428,26 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>11 aug</t>
+          <t>12 aug</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>38.7385</v>
+        <v>38.8573</v>
       </c>
       <c r="C13" t="n">
-        <v>39.0058</v>
+        <v>38.986</v>
       </c>
       <c r="D13" t="n">
-        <v>38.6148</v>
+        <v>38.3871</v>
       </c>
       <c r="E13" t="n">
-        <v>38.9662</v>
+        <v>38.6494</v>
       </c>
       <c r="F13" t="n">
-        <v>36.374</v>
+        <v>36.3981</v>
       </c>
       <c r="G13" t="n">
-        <v>34.3685</v>
+        <v>34.4068</v>
       </c>
       <c r="H13" t="n">
         <v>45.05751734733581</v>
@@ -4435,26 +4457,26 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>11 aug</t>
+          <t>12 aug</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>180</v>
+        <v>180.3</v>
       </c>
       <c r="M13" t="n">
-        <v>183.24</v>
+        <v>180.98</v>
       </c>
       <c r="N13" t="n">
-        <v>178.14</v>
+        <v>175.4</v>
       </c>
       <c r="O13" t="n">
-        <v>180.7</v>
+        <v>175.96</v>
       </c>
       <c r="P13" t="n">
-        <v>146.8316</v>
+        <v>147.232</v>
       </c>
       <c r="Q13" t="n">
-        <v>169.5375</v>
+        <v>169.2701</v>
       </c>
       <c r="R13" t="n">
         <v>191.5557367172241</v>
@@ -4464,26 +4486,26 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>10 aug</t>
+          <t>11 aug</t>
         </is>
       </c>
       <c r="V13" t="n">
-        <v>502.4941</v>
+        <v>503.3824</v>
       </c>
       <c r="W13" t="n">
-        <v>512.7646999999999</v>
+        <v>504.3805</v>
       </c>
       <c r="X13" t="n">
-        <v>501.3262</v>
+        <v>498.6113</v>
       </c>
       <c r="Y13" t="n">
-        <v>505.1091</v>
+        <v>502.8633</v>
       </c>
       <c r="Z13" t="n">
-        <v>407.8257</v>
+        <v>408.895</v>
       </c>
       <c r="AA13" t="n">
-        <v>430.9778</v>
+        <v>430.9106</v>
       </c>
       <c r="AB13" t="n">
         <v>535.3375423278808</v>
@@ -4495,26 +4517,26 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>12 aug</t>
+          <t>13 aug</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>38.8573</v>
+        <v>39</v>
       </c>
       <c r="C14" t="n">
-        <v>38.986</v>
+        <v>39.005</v>
       </c>
       <c r="D14" t="n">
-        <v>38.3871</v>
+        <v>38.2</v>
       </c>
       <c r="E14" t="n">
-        <v>38.6494</v>
+        <v>38.605</v>
       </c>
       <c r="F14" t="n">
-        <v>36.3981</v>
+        <v>36.4313</v>
       </c>
       <c r="G14" t="n">
-        <v>34.4068</v>
+        <v>34.4429</v>
       </c>
       <c r="H14" t="n">
         <v>45.05751734733581</v>
@@ -4524,26 +4546,26 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>12 aug</t>
+          <t>13 aug</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>180.3</v>
+        <v>177.48</v>
       </c>
       <c r="M14" t="n">
-        <v>180.98</v>
+        <v>178.3</v>
       </c>
       <c r="N14" t="n">
-        <v>175.4</v>
+        <v>174.8</v>
       </c>
       <c r="O14" t="n">
-        <v>175.96</v>
+        <v>175.38</v>
       </c>
       <c r="P14" t="n">
-        <v>147.232</v>
+        <v>147.4496</v>
       </c>
       <c r="Q14" t="n">
-        <v>169.2701</v>
+        <v>168.9889</v>
       </c>
       <c r="R14" t="n">
         <v>191.5557367172241</v>
@@ -4553,26 +4575,26 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>11 aug</t>
+          <t>12 aug</t>
         </is>
       </c>
       <c r="V14" t="n">
-        <v>503.3824</v>
+        <v>499.0505</v>
       </c>
       <c r="W14" t="n">
-        <v>504.3805</v>
+        <v>500.5577</v>
       </c>
       <c r="X14" t="n">
-        <v>498.6113</v>
+        <v>490.5964</v>
       </c>
       <c r="Y14" t="n">
-        <v>502.8633</v>
+        <v>491.5047</v>
       </c>
       <c r="Z14" t="n">
-        <v>408.895</v>
+        <v>409.532</v>
       </c>
       <c r="AA14" t="n">
-        <v>430.9106</v>
+        <v>430.7866</v>
       </c>
       <c r="AB14" t="n">
         <v>535.3375423278808</v>
@@ -4584,26 +4606,26 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>13 aug</t>
+          <t>14 aug</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>39</v>
+        <v>38.65</v>
       </c>
       <c r="C15" t="n">
-        <v>39.005</v>
+        <v>39.1</v>
       </c>
       <c r="D15" t="n">
-        <v>38.2</v>
+        <v>38.56</v>
       </c>
       <c r="E15" t="n">
-        <v>38.605</v>
+        <v>38.97</v>
       </c>
       <c r="F15" t="n">
-        <v>36.4313</v>
+        <v>36.4703</v>
       </c>
       <c r="G15" t="n">
-        <v>34.4429</v>
+        <v>34.4805</v>
       </c>
       <c r="H15" t="n">
         <v>45.05751734733581</v>
@@ -4613,26 +4635,26 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>13 aug</t>
+          <t>14 aug</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>177.48</v>
+        <v>182</v>
       </c>
       <c r="M15" t="n">
-        <v>178.3</v>
+        <v>185.74</v>
       </c>
       <c r="N15" t="n">
-        <v>174.8</v>
+        <v>179.28</v>
       </c>
       <c r="O15" t="n">
-        <v>175.38</v>
+        <v>180.14</v>
       </c>
       <c r="P15" t="n">
-        <v>147.4496</v>
+        <v>147.8228</v>
       </c>
       <c r="Q15" t="n">
-        <v>168.9889</v>
+        <v>168.7386</v>
       </c>
       <c r="R15" t="n">
         <v>191.5557367172241</v>
@@ -4642,26 +4664,26 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>12 aug</t>
+          <t>13 aug</t>
         </is>
       </c>
       <c r="V15" t="n">
-        <v>499.0505</v>
+        <v>492.3431</v>
       </c>
       <c r="W15" t="n">
-        <v>500.5577</v>
+        <v>500.398</v>
       </c>
       <c r="X15" t="n">
-        <v>490.5964</v>
+        <v>492.0837</v>
       </c>
       <c r="Y15" t="n">
-        <v>491.5047</v>
+        <v>495.9464</v>
       </c>
       <c r="Z15" t="n">
-        <v>409.532</v>
+        <v>410.6414</v>
       </c>
       <c r="AA15" t="n">
-        <v>430.7866</v>
+        <v>430.6696</v>
       </c>
       <c r="AB15" t="n">
         <v>535.3375423278808</v>
@@ -4673,26 +4695,26 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>14 aug</t>
+          <t>17 aug</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>38.65</v>
+        <v>38.97</v>
       </c>
       <c r="C16" t="n">
-        <v>39.1</v>
+        <v>39.27</v>
       </c>
       <c r="D16" t="n">
-        <v>38.56</v>
+        <v>38.765</v>
       </c>
       <c r="E16" t="n">
-        <v>38.97</v>
+        <v>39.15</v>
       </c>
       <c r="F16" t="n">
-        <v>36.4703</v>
+        <v>36.5118</v>
       </c>
       <c r="G16" t="n">
-        <v>34.4805</v>
+        <v>34.5207</v>
       </c>
       <c r="H16" t="n">
         <v>45.05751734733581</v>
@@ -4702,26 +4724,26 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>14 aug</t>
+          <t>17 aug</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>182</v>
+        <v>178.94</v>
       </c>
       <c r="M16" t="n">
-        <v>185.74</v>
+        <v>180.9</v>
       </c>
       <c r="N16" t="n">
-        <v>179.28</v>
+        <v>177.66</v>
       </c>
       <c r="O16" t="n">
-        <v>180.14</v>
+        <v>179.58</v>
       </c>
       <c r="P16" t="n">
-        <v>147.8228</v>
+        <v>148.2524</v>
       </c>
       <c r="Q16" t="n">
-        <v>168.7386</v>
+        <v>168.5337</v>
       </c>
       <c r="R16" t="n">
         <v>191.5557367172241</v>
@@ -4731,26 +4753,26 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>13 aug</t>
+          <t>14 aug</t>
         </is>
       </c>
       <c r="V16" t="n">
-        <v>492.3431</v>
+        <v>495.4273</v>
       </c>
       <c r="W16" t="n">
-        <v>500.398</v>
+        <v>499.0705</v>
       </c>
       <c r="X16" t="n">
-        <v>492.0837</v>
+        <v>492.9919</v>
       </c>
       <c r="Y16" t="n">
-        <v>495.9464</v>
+        <v>494.4691</v>
       </c>
       <c r="Z16" t="n">
-        <v>410.6414</v>
+        <v>412</v>
       </c>
       <c r="AA16" t="n">
-        <v>430.6696</v>
+        <v>430.5061</v>
       </c>
       <c r="AB16" t="n">
         <v>535.3375423278808</v>
@@ -4762,26 +4784,26 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>17 aug</t>
+          <t>18 aug</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>38.97</v>
+        <v>39.49</v>
       </c>
       <c r="C17" t="n">
-        <v>39.27</v>
+        <v>39.945</v>
       </c>
       <c r="D17" t="n">
-        <v>38.765</v>
+        <v>39.46</v>
       </c>
       <c r="E17" t="n">
-        <v>39.15</v>
+        <v>39.785</v>
       </c>
       <c r="F17" t="n">
-        <v>36.5118</v>
+        <v>36.5781</v>
       </c>
       <c r="G17" t="n">
-        <v>34.5207</v>
+        <v>34.5641</v>
       </c>
       <c r="H17" t="n">
         <v>45.05751734733581</v>
@@ -4791,26 +4813,26 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>17 aug</t>
+          <t>18 aug</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>178.94</v>
+        <v>179.14</v>
       </c>
       <c r="M17" t="n">
-        <v>180.9</v>
+        <v>183.9</v>
       </c>
       <c r="N17" t="n">
-        <v>177.66</v>
+        <v>177.98</v>
       </c>
       <c r="O17" t="n">
-        <v>179.58</v>
+        <v>182.5</v>
       </c>
       <c r="P17" t="n">
-        <v>148.2524</v>
+        <v>148.8084</v>
       </c>
       <c r="Q17" t="n">
-        <v>168.5337</v>
+        <v>168.3358</v>
       </c>
       <c r="R17" t="n">
         <v>191.5557367172241</v>
@@ -4820,26 +4842,26 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>14 aug</t>
+          <t>17 aug</t>
         </is>
       </c>
       <c r="V17" t="n">
-        <v>495.4273</v>
+        <v>489.2191</v>
       </c>
       <c r="W17" t="n">
-        <v>499.0705</v>
+        <v>491.7343</v>
       </c>
       <c r="X17" t="n">
-        <v>492.9919</v>
+        <v>477.5111</v>
       </c>
       <c r="Y17" t="n">
-        <v>494.4691</v>
+        <v>479.4474</v>
       </c>
       <c r="Z17" t="n">
-        <v>412</v>
+        <v>413.044</v>
       </c>
       <c r="AA17" t="n">
-        <v>430.5061</v>
+        <v>430.2151</v>
       </c>
       <c r="AB17" t="n">
         <v>535.3375423278808</v>
@@ -4851,26 +4873,26 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>18 aug</t>
+          <t>19 aug</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>39.49</v>
+        <v>39.835</v>
       </c>
       <c r="C18" t="n">
-        <v>39.945</v>
+        <v>40.14</v>
       </c>
       <c r="D18" t="n">
-        <v>39.46</v>
+        <v>39.74</v>
       </c>
       <c r="E18" t="n">
-        <v>39.785</v>
+        <v>39.94</v>
       </c>
       <c r="F18" t="n">
-        <v>36.5781</v>
+        <v>36.6336</v>
       </c>
       <c r="G18" t="n">
-        <v>34.5641</v>
+        <v>34.6092</v>
       </c>
       <c r="H18" t="n">
         <v>45.05751734733581</v>
@@ -4880,26 +4902,26 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>18 aug</t>
+          <t>19 aug</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>179.14</v>
+        <v>181.7</v>
       </c>
       <c r="M18" t="n">
-        <v>183.9</v>
+        <v>186.98</v>
       </c>
       <c r="N18" t="n">
-        <v>177.98</v>
+        <v>180.38</v>
       </c>
       <c r="O18" t="n">
-        <v>182.5</v>
+        <v>185.9</v>
       </c>
       <c r="P18" t="n">
-        <v>148.8084</v>
+        <v>149.5324</v>
       </c>
       <c r="Q18" t="n">
-        <v>168.3358</v>
+        <v>168.1618</v>
       </c>
       <c r="R18" t="n">
         <v>191.5557367172241</v>
@@ -4909,26 +4931,26 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>17 aug</t>
+          <t>18 aug</t>
         </is>
       </c>
       <c r="V18" t="n">
-        <v>489.2191</v>
+        <v>480.6352</v>
       </c>
       <c r="W18" t="n">
-        <v>491.7343</v>
+        <v>483.3601</v>
       </c>
       <c r="X18" t="n">
-        <v>477.5111</v>
+        <v>476.2534</v>
       </c>
       <c r="Y18" t="n">
-        <v>479.4474</v>
+        <v>480.725</v>
       </c>
       <c r="Z18" t="n">
-        <v>413.044</v>
+        <v>414.3408</v>
       </c>
       <c r="AA18" t="n">
-        <v>430.2151</v>
+        <v>429.933</v>
       </c>
       <c r="AB18" t="n">
         <v>535.3375423278808</v>
@@ -4940,26 +4962,26 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>19 aug</t>
+          <t>20 aug</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>39.835</v>
+        <v>39.865</v>
       </c>
       <c r="C19" t="n">
-        <v>40.14</v>
+        <v>40.51</v>
       </c>
       <c r="D19" t="n">
-        <v>39.74</v>
+        <v>39.8</v>
       </c>
       <c r="E19" t="n">
-        <v>39.94</v>
+        <v>40.28</v>
       </c>
       <c r="F19" t="n">
-        <v>36.6336</v>
+        <v>36.6884</v>
       </c>
       <c r="G19" t="n">
-        <v>34.6092</v>
+        <v>34.6545</v>
       </c>
       <c r="H19" t="n">
         <v>45.05751734733581</v>
@@ -4969,26 +4991,26 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>19 aug</t>
+          <t>20 aug</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>181.7</v>
+        <v>183.78</v>
       </c>
       <c r="M19" t="n">
-        <v>186.98</v>
+        <v>186.1</v>
       </c>
       <c r="N19" t="n">
-        <v>180.38</v>
+        <v>182.52</v>
       </c>
       <c r="O19" t="n">
-        <v>185.9</v>
+        <v>185.64</v>
       </c>
       <c r="P19" t="n">
-        <v>149.5324</v>
+        <v>150.4472</v>
       </c>
       <c r="Q19" t="n">
-        <v>168.1618</v>
+        <v>167.9648</v>
       </c>
       <c r="R19" t="n">
         <v>191.5557367172241</v>
@@ -4998,26 +5020,26 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>18 aug</t>
+          <t>19 aug</t>
         </is>
       </c>
       <c r="V19" t="n">
-        <v>480.6352</v>
+        <v>479.168</v>
       </c>
       <c r="W19" t="n">
-        <v>483.3601</v>
+        <v>488.3806</v>
       </c>
       <c r="X19" t="n">
-        <v>476.2534</v>
+        <v>478.4593</v>
       </c>
       <c r="Y19" t="n">
-        <v>480.725</v>
+        <v>483.4</v>
       </c>
       <c r="Z19" t="n">
-        <v>414.3408</v>
+        <v>415.7895</v>
       </c>
       <c r="AA19" t="n">
-        <v>429.933</v>
+        <v>429.7427</v>
       </c>
       <c r="AB19" t="n">
         <v>535.3375423278808</v>
@@ -5029,26 +5051,26 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20 aug</t>
+          <t>21 aug</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>39.865</v>
+        <v>40.1</v>
       </c>
       <c r="C20" t="n">
-        <v>40.51</v>
+        <v>40.37</v>
       </c>
       <c r="D20" t="n">
-        <v>39.8</v>
+        <v>39.84</v>
       </c>
       <c r="E20" t="n">
-        <v>40.28</v>
+        <v>39.91</v>
       </c>
       <c r="F20" t="n">
-        <v>36.6884</v>
+        <v>36.7478</v>
       </c>
       <c r="G20" t="n">
-        <v>34.6545</v>
+        <v>34.6988</v>
       </c>
       <c r="H20" t="n">
         <v>45.05751734733581</v>
@@ -5058,26 +5080,26 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>20 aug</t>
+          <t>21 aug</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>183.78</v>
+        <v>185.18</v>
       </c>
       <c r="M20" t="n">
-        <v>186.1</v>
+        <v>188.4</v>
       </c>
       <c r="N20" t="n">
-        <v>182.52</v>
+        <v>183.6</v>
       </c>
       <c r="O20" t="n">
-        <v>185.64</v>
+        <v>188.12</v>
       </c>
       <c r="P20" t="n">
-        <v>150.4472</v>
+        <v>151.4044</v>
       </c>
       <c r="Q20" t="n">
-        <v>167.9648</v>
+        <v>167.794</v>
       </c>
       <c r="R20" t="n">
         <v>191.5557367172241</v>
@@ -5087,26 +5109,26 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>19 aug</t>
+          <t>20 aug</t>
         </is>
       </c>
       <c r="V20" t="n">
-        <v>479.168</v>
+        <v>483.3</v>
       </c>
       <c r="W20" t="n">
-        <v>488.3806</v>
+        <v>484.16</v>
       </c>
       <c r="X20" t="n">
-        <v>478.4593</v>
+        <v>479.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>483.4</v>
+        <v>481.15</v>
       </c>
       <c r="Z20" t="n">
-        <v>415.7895</v>
+        <v>417.3594</v>
       </c>
       <c r="AA20" t="n">
-        <v>429.7427</v>
+        <v>429.5805</v>
       </c>
       <c r="AB20" t="n">
         <v>535.3375423278808</v>
@@ -5118,26 +5140,26 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>21 aug</t>
+          <t>24 aug</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>40.1</v>
+        <v>39.88</v>
       </c>
       <c r="C21" t="n">
-        <v>40.37</v>
+        <v>40.085</v>
       </c>
       <c r="D21" t="n">
-        <v>39.84</v>
+        <v>39.68</v>
       </c>
       <c r="E21" t="n">
-        <v>39.91</v>
+        <v>39.775</v>
       </c>
       <c r="F21" t="n">
-        <v>36.7478</v>
+        <v>36.8369</v>
       </c>
       <c r="G21" t="n">
-        <v>34.6988</v>
+        <v>34.7421</v>
       </c>
       <c r="H21" t="n">
         <v>45.05751734733581</v>
@@ -5147,26 +5169,26 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>21 aug</t>
+          <t>24 aug</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>185.18</v>
+        <v>186.86</v>
       </c>
       <c r="M21" t="n">
-        <v>188.4</v>
+        <v>188.16</v>
       </c>
       <c r="N21" t="n">
-        <v>183.6</v>
+        <v>185.52</v>
       </c>
       <c r="O21" t="n">
-        <v>188.12</v>
+        <v>187.2</v>
       </c>
       <c r="P21" t="n">
-        <v>151.4044</v>
+        <v>152.2848</v>
       </c>
       <c r="Q21" t="n">
-        <v>167.794</v>
+        <v>167.6093</v>
       </c>
       <c r="R21" t="n">
         <v>191.5557367172241</v>
@@ -5176,26 +5198,26 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>20 aug</t>
+          <t>21 aug</t>
         </is>
       </c>
       <c r="V21" t="n">
-        <v>483.3</v>
+        <v>479.88</v>
       </c>
       <c r="W21" t="n">
-        <v>484.16</v>
+        <v>486.36</v>
       </c>
       <c r="X21" t="n">
-        <v>479.5</v>
+        <v>478.53</v>
       </c>
       <c r="Y21" t="n">
-        <v>481.15</v>
+        <v>483.24</v>
       </c>
       <c r="Z21" t="n">
-        <v>417.3594</v>
+        <v>419.092</v>
       </c>
       <c r="AA21" t="n">
-        <v>429.5805</v>
+        <v>429.4327</v>
       </c>
       <c r="AB21" t="n">
         <v>535.3375423278808</v>
@@ -5207,26 +5229,26 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>24 aug</t>
+          <t>25 aug</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>39.88</v>
+        <v>39.77</v>
       </c>
       <c r="C22" t="n">
-        <v>40.085</v>
+        <v>39.915</v>
       </c>
       <c r="D22" t="n">
-        <v>39.68</v>
+        <v>39.385</v>
       </c>
       <c r="E22" t="n">
-        <v>39.775</v>
+        <v>39.6</v>
       </c>
       <c r="F22" t="n">
-        <v>36.8369</v>
+        <v>36.926</v>
       </c>
       <c r="G22" t="n">
-        <v>34.7421</v>
+        <v>34.783</v>
       </c>
       <c r="H22" t="n">
         <v>45.05751734733581</v>
@@ -5236,26 +5258,26 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>24 aug</t>
+          <t>25 aug</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>186.86</v>
+        <v>186.4</v>
       </c>
       <c r="M22" t="n">
-        <v>188.16</v>
+        <v>187.62</v>
       </c>
       <c r="N22" t="n">
-        <v>185.52</v>
+        <v>182.74</v>
       </c>
       <c r="O22" t="n">
-        <v>187.2</v>
+        <v>185.46</v>
       </c>
       <c r="P22" t="n">
-        <v>152.2848</v>
+        <v>153.136</v>
       </c>
       <c r="Q22" t="n">
-        <v>167.6093</v>
+        <v>167.4651</v>
       </c>
       <c r="R22" t="n">
         <v>191.5557367172241</v>
@@ -5265,26 +5287,26 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>21 aug</t>
+          <t>24 aug</t>
         </is>
       </c>
       <c r="V22" t="n">
-        <v>479.88</v>
+        <v>483.21</v>
       </c>
       <c r="W22" t="n">
-        <v>486.36</v>
+        <v>490.61</v>
       </c>
       <c r="X22" t="n">
-        <v>478.53</v>
+        <v>481.86</v>
       </c>
       <c r="Y22" t="n">
-        <v>483.24</v>
+        <v>487.31</v>
       </c>
       <c r="Z22" t="n">
-        <v>419.092</v>
+        <v>421.046</v>
       </c>
       <c r="AA22" t="n">
-        <v>429.4327</v>
+        <v>429.3185</v>
       </c>
       <c r="AB22" t="n">
         <v>535.3375423278808</v>
@@ -5296,26 +5318,26 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>25 aug</t>
+          <t>26 aug</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>39.77</v>
+        <v>39.275</v>
       </c>
       <c r="C23" t="n">
-        <v>39.915</v>
+        <v>39.47</v>
       </c>
       <c r="D23" t="n">
-        <v>39.385</v>
+        <v>38.91</v>
       </c>
       <c r="E23" t="n">
-        <v>39.6</v>
+        <v>39.42</v>
       </c>
       <c r="F23" t="n">
-        <v>36.926</v>
+        <v>37.0192</v>
       </c>
       <c r="G23" t="n">
-        <v>34.783</v>
+        <v>34.8202</v>
       </c>
       <c r="H23" t="n">
         <v>45.05751734733581</v>
@@ -5325,26 +5347,26 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>25 aug</t>
+          <t>26 aug</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>186.4</v>
+        <v>179.92</v>
       </c>
       <c r="M23" t="n">
-        <v>187.62</v>
+        <v>182.16</v>
       </c>
       <c r="N23" t="n">
-        <v>182.74</v>
+        <v>176.82</v>
       </c>
       <c r="O23" t="n">
-        <v>185.46</v>
+        <v>180.02</v>
       </c>
       <c r="P23" t="n">
-        <v>153.136</v>
+        <v>153.9128</v>
       </c>
       <c r="Q23" t="n">
-        <v>167.4651</v>
+        <v>167.3049</v>
       </c>
       <c r="R23" t="n">
         <v>191.5557367172241</v>
@@ -5354,26 +5376,26 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>24 aug</t>
+          <t>25 aug</t>
         </is>
       </c>
       <c r="V23" t="n">
-        <v>483.21</v>
+        <v>485.44</v>
       </c>
       <c r="W23" t="n">
-        <v>490.61</v>
+        <v>492.44</v>
       </c>
       <c r="X23" t="n">
-        <v>481.86</v>
+        <v>484.3</v>
       </c>
       <c r="Y23" t="n">
-        <v>487.31</v>
+        <v>491.71</v>
       </c>
       <c r="Z23" t="n">
-        <v>421.046</v>
+        <v>423.0801</v>
       </c>
       <c r="AA23" t="n">
-        <v>429.3185</v>
+        <v>429.262</v>
       </c>
       <c r="AB23" t="n">
         <v>535.3375423278808</v>
@@ -5385,26 +5407,26 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>26 aug</t>
+          <t>27 aug</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>39.275</v>
+        <v>39.16</v>
       </c>
       <c r="C24" t="n">
-        <v>39.47</v>
+        <v>39.295</v>
       </c>
       <c r="D24" t="n">
-        <v>38.91</v>
+        <v>38.65</v>
       </c>
       <c r="E24" t="n">
-        <v>39.42</v>
+        <v>38.76</v>
       </c>
       <c r="F24" t="n">
-        <v>37.0192</v>
+        <v>37.117</v>
       </c>
       <c r="G24" t="n">
-        <v>34.8202</v>
+        <v>34.8559</v>
       </c>
       <c r="H24" t="n">
         <v>45.05751734733581</v>
@@ -5414,26 +5436,26 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>26 aug</t>
+          <t>27 aug</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>179.92</v>
+        <v>182.5</v>
       </c>
       <c r="M24" t="n">
-        <v>182.16</v>
+        <v>190.8</v>
       </c>
       <c r="N24" t="n">
-        <v>176.82</v>
+        <v>181.14</v>
       </c>
       <c r="O24" t="n">
-        <v>180.02</v>
+        <v>189.88</v>
       </c>
       <c r="P24" t="n">
-        <v>153.9128</v>
+        <v>155.0132</v>
       </c>
       <c r="Q24" t="n">
-        <v>167.3049</v>
+        <v>167.1911</v>
       </c>
       <c r="R24" t="n">
         <v>191.5557367172241</v>
@@ -5443,26 +5465,26 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>25 aug</t>
+          <t>26 aug</t>
         </is>
       </c>
       <c r="V24" t="n">
-        <v>485.44</v>
+        <v>487.85</v>
       </c>
       <c r="W24" t="n">
-        <v>492.44</v>
+        <v>497.4</v>
       </c>
       <c r="X24" t="n">
-        <v>484.3</v>
+        <v>487.31</v>
       </c>
       <c r="Y24" t="n">
-        <v>491.71</v>
+        <v>496.37</v>
       </c>
       <c r="Z24" t="n">
-        <v>423.0801</v>
+        <v>425.0273</v>
       </c>
       <c r="AA24" t="n">
-        <v>429.262</v>
+        <v>429.2786</v>
       </c>
       <c r="AB24" t="n">
         <v>535.3375423278808</v>
@@ -5474,26 +5496,26 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>27 aug</t>
+          <t>28 aug</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>39.16</v>
+        <v>39</v>
       </c>
       <c r="C25" t="n">
-        <v>39.295</v>
+        <v>39.18</v>
       </c>
       <c r="D25" t="n">
-        <v>38.65</v>
+        <v>38.845</v>
       </c>
       <c r="E25" t="n">
-        <v>38.76</v>
+        <v>39.145</v>
       </c>
       <c r="F25" t="n">
-        <v>37.117</v>
+        <v>37.2162</v>
       </c>
       <c r="G25" t="n">
-        <v>34.8559</v>
+        <v>34.8941</v>
       </c>
       <c r="H25" t="n">
         <v>45.05751734733581</v>
@@ -5503,26 +5525,26 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>27 aug</t>
+          <t>28 aug</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>182.5</v>
+        <v>189.5</v>
       </c>
       <c r="M25" t="n">
-        <v>190.8</v>
+        <v>191.94</v>
       </c>
       <c r="N25" t="n">
-        <v>181.14</v>
+        <v>187.98</v>
       </c>
       <c r="O25" t="n">
-        <v>189.88</v>
+        <v>191.32</v>
       </c>
       <c r="P25" t="n">
-        <v>155.0132</v>
+        <v>156.1568</v>
       </c>
       <c r="Q25" t="n">
-        <v>167.1911</v>
+        <v>167.0806</v>
       </c>
       <c r="R25" t="n">
         <v>191.5557367172241</v>
@@ -5532,26 +5554,26 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>26 aug</t>
+          <t>27 aug</t>
         </is>
       </c>
       <c r="V25" t="n">
-        <v>487.85</v>
+        <v>494.88</v>
       </c>
       <c r="W25" t="n">
-        <v>497.4</v>
+        <v>506.48</v>
       </c>
       <c r="X25" t="n">
-        <v>487.31</v>
+        <v>490.08</v>
       </c>
       <c r="Y25" t="n">
-        <v>496.37</v>
+        <v>505.06</v>
       </c>
       <c r="Z25" t="n">
-        <v>425.0273</v>
+        <v>427.2667</v>
       </c>
       <c r="AA25" t="n">
-        <v>429.2786</v>
+        <v>429.3401</v>
       </c>
       <c r="AB25" t="n">
         <v>535.3375423278808</v>
@@ -5563,26 +5585,26 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>28 aug</t>
+          <t>31 aug</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>39</v>
+        <v>39.54</v>
       </c>
       <c r="C26" t="n">
-        <v>39.18</v>
+        <v>39.91</v>
       </c>
       <c r="D26" t="n">
-        <v>38.845</v>
+        <v>39.24</v>
       </c>
       <c r="E26" t="n">
-        <v>39.145</v>
+        <v>39.335</v>
       </c>
       <c r="F26" t="n">
-        <v>37.2162</v>
+        <v>37.3111</v>
       </c>
       <c r="G26" t="n">
-        <v>34.8941</v>
+        <v>34.9333</v>
       </c>
       <c r="H26" t="n">
         <v>45.05751734733581</v>
@@ -5592,26 +5614,26 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>28 aug</t>
+          <t>31 aug</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>189.5</v>
+        <v>188.46</v>
       </c>
       <c r="M26" t="n">
-        <v>191.94</v>
+        <v>192.12</v>
       </c>
       <c r="N26" t="n">
-        <v>187.98</v>
+        <v>188.2</v>
       </c>
       <c r="O26" t="n">
-        <v>191.32</v>
+        <v>190.9</v>
       </c>
       <c r="P26" t="n">
-        <v>156.1568</v>
+        <v>157.3304</v>
       </c>
       <c r="Q26" t="n">
-        <v>167.0806</v>
+        <v>166.9613</v>
       </c>
       <c r="R26" t="n">
         <v>191.5557367172241</v>
@@ -5621,26 +5643,26 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>27 aug</t>
+          <t>28 aug</t>
         </is>
       </c>
       <c r="V26" t="n">
-        <v>494.88</v>
+        <v>505.33</v>
       </c>
       <c r="W26" t="n">
-        <v>506.48</v>
+        <v>517.78</v>
       </c>
       <c r="X26" t="n">
-        <v>490.08</v>
+        <v>504.87</v>
       </c>
       <c r="Y26" t="n">
-        <v>505.06</v>
+        <v>513.53</v>
       </c>
       <c r="Z26" t="n">
-        <v>427.2667</v>
+        <v>429.9734</v>
       </c>
       <c r="AA26" t="n">
-        <v>429.3401</v>
+        <v>429.3984</v>
       </c>
       <c r="AB26" t="n">
         <v>535.3375423278808</v>
@@ -5652,26 +5674,26 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>31 aug</t>
+          <t>1 sep</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>39.54</v>
+        <v>39.77</v>
       </c>
       <c r="C27" t="n">
-        <v>39.91</v>
+        <v>40.19</v>
       </c>
       <c r="D27" t="n">
-        <v>39.24</v>
+        <v>39.645</v>
       </c>
       <c r="E27" t="n">
-        <v>39.335</v>
+        <v>40.155</v>
       </c>
       <c r="F27" t="n">
-        <v>37.3111</v>
+        <v>37.4239</v>
       </c>
       <c r="G27" t="n">
-        <v>34.9333</v>
+        <v>34.9763</v>
       </c>
       <c r="H27" t="n">
         <v>45.05751734733581</v>
@@ -5681,26 +5703,26 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>31 aug</t>
+          <t>1 sep</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>188.46</v>
+        <v>186</v>
       </c>
       <c r="M27" t="n">
-        <v>192.12</v>
+        <v>187.86</v>
       </c>
       <c r="N27" t="n">
-        <v>188.2</v>
+        <v>183.32</v>
       </c>
       <c r="O27" t="n">
-        <v>190.9</v>
+        <v>184.26</v>
       </c>
       <c r="P27" t="n">
-        <v>157.3304</v>
+        <v>158.3252</v>
       </c>
       <c r="Q27" t="n">
-        <v>166.9613</v>
+        <v>166.8103</v>
       </c>
       <c r="R27" t="n">
         <v>191.5557367172241</v>
@@ -5710,26 +5732,26 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>28 aug</t>
+          <t>31 aug</t>
         </is>
       </c>
       <c r="V27" t="n">
-        <v>505.33</v>
+        <v>510.38</v>
       </c>
       <c r="W27" t="n">
-        <v>517.78</v>
+        <v>512.1900000000001</v>
       </c>
       <c r="X27" t="n">
-        <v>504.87</v>
+        <v>506.39</v>
       </c>
       <c r="Y27" t="n">
-        <v>513.53</v>
+        <v>507.29</v>
       </c>
       <c r="Z27" t="n">
-        <v>429.9734</v>
+        <v>432.5454</v>
       </c>
       <c r="AA27" t="n">
-        <v>429.3984</v>
+        <v>429.4122</v>
       </c>
       <c r="AB27" t="n">
         <v>535.3375423278808</v>
@@ -5741,26 +5763,26 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1 sep</t>
+          <t>2 sep</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>39.77</v>
+        <v>40.35</v>
       </c>
       <c r="C28" t="n">
-        <v>40.19</v>
+        <v>40.615</v>
       </c>
       <c r="D28" t="n">
-        <v>39.645</v>
+        <v>39.975</v>
       </c>
       <c r="E28" t="n">
-        <v>40.155</v>
+        <v>40.21</v>
       </c>
       <c r="F28" t="n">
-        <v>37.4239</v>
+        <v>37.5499</v>
       </c>
       <c r="G28" t="n">
-        <v>34.9763</v>
+        <v>35.0217</v>
       </c>
       <c r="H28" t="n">
         <v>45.05751734733581</v>
@@ -5770,26 +5792,26 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>1 sep</t>
+          <t>2 sep</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>186</v>
+        <v>182.18</v>
       </c>
       <c r="M28" t="n">
-        <v>187.86</v>
+        <v>184.7</v>
       </c>
       <c r="N28" t="n">
-        <v>183.32</v>
+        <v>180.72</v>
       </c>
       <c r="O28" t="n">
-        <v>184.26</v>
+        <v>181.44</v>
       </c>
       <c r="P28" t="n">
-        <v>158.3252</v>
+        <v>159.2568</v>
       </c>
       <c r="Q28" t="n">
-        <v>166.8103</v>
+        <v>166.6796</v>
       </c>
       <c r="R28" t="n">
         <v>191.5557367172241</v>
@@ -5799,26 +5821,26 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>31 aug</t>
+          <t>1 sep</t>
         </is>
       </c>
       <c r="V28" t="n">
-        <v>510.38</v>
+        <v>497.52</v>
       </c>
       <c r="W28" t="n">
-        <v>512.1900000000001</v>
+        <v>505.97</v>
       </c>
       <c r="X28" t="n">
-        <v>506.39</v>
+        <v>496.78</v>
       </c>
       <c r="Y28" t="n">
-        <v>507.29</v>
+        <v>501.02</v>
       </c>
       <c r="Z28" t="n">
-        <v>432.5454</v>
+        <v>435.2328</v>
       </c>
       <c r="AA28" t="n">
-        <v>429.4122</v>
+        <v>429.3825</v>
       </c>
       <c r="AB28" t="n">
         <v>535.3375423278808</v>
@@ -5830,26 +5852,26 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2 sep</t>
+          <t>3 sep</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>40.35</v>
+        <v>40.095</v>
       </c>
       <c r="C29" t="n">
-        <v>40.615</v>
+        <v>40.215</v>
       </c>
       <c r="D29" t="n">
-        <v>39.975</v>
+        <v>39.54</v>
       </c>
       <c r="E29" t="n">
-        <v>40.21</v>
+        <v>40.04</v>
       </c>
       <c r="F29" t="n">
-        <v>37.5499</v>
+        <v>37.6767</v>
       </c>
       <c r="G29" t="n">
-        <v>35.0217</v>
+        <v>35.0679</v>
       </c>
       <c r="H29" t="n">
         <v>45.05751734733581</v>
@@ -5859,26 +5881,26 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2 sep</t>
+          <t>3 sep</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>182.18</v>
+        <v>182.08</v>
       </c>
       <c r="M29" t="n">
-        <v>184.7</v>
+        <v>187.56</v>
       </c>
       <c r="N29" t="n">
-        <v>180.72</v>
+        <v>182</v>
       </c>
       <c r="O29" t="n">
-        <v>181.44</v>
+        <v>185.58</v>
       </c>
       <c r="P29" t="n">
-        <v>159.2568</v>
+        <v>160.3228</v>
       </c>
       <c r="Q29" t="n">
-        <v>166.6796</v>
+        <v>166.5898</v>
       </c>
       <c r="R29" t="n">
         <v>191.5557367172241</v>
@@ -5888,26 +5910,26 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>1 sep</t>
+          <t>2 sep</t>
         </is>
       </c>
       <c r="V29" t="n">
-        <v>497.52</v>
+        <v>499.85</v>
       </c>
       <c r="W29" t="n">
-        <v>505.97</v>
+        <v>500.27</v>
       </c>
       <c r="X29" t="n">
-        <v>496.78</v>
+        <v>493.81</v>
       </c>
       <c r="Y29" t="n">
-        <v>501.02</v>
+        <v>496.82</v>
       </c>
       <c r="Z29" t="n">
-        <v>435.2328</v>
+        <v>437.7045</v>
       </c>
       <c r="AA29" t="n">
-        <v>429.3825</v>
+        <v>429.3706</v>
       </c>
       <c r="AB29" t="n">
         <v>535.3375423278808</v>
@@ -5919,26 +5941,26 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3 sep</t>
+          <t>4 sep</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>40.095</v>
+        <v>40.145</v>
       </c>
       <c r="C30" t="n">
-        <v>40.215</v>
+        <v>40.28</v>
       </c>
       <c r="D30" t="n">
-        <v>39.54</v>
+        <v>39.665</v>
       </c>
       <c r="E30" t="n">
-        <v>40.04</v>
+        <v>40.105</v>
       </c>
       <c r="F30" t="n">
-        <v>37.6767</v>
+        <v>37.8115</v>
       </c>
       <c r="G30" t="n">
-        <v>35.0679</v>
+        <v>35.113</v>
       </c>
       <c r="H30" t="n">
         <v>45.05751734733581</v>
@@ -5948,26 +5970,26 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>3 sep</t>
+          <t>4 sep</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>182.08</v>
+        <v>187.8</v>
       </c>
       <c r="M30" t="n">
-        <v>187.56</v>
+        <v>189.9</v>
       </c>
       <c r="N30" t="n">
-        <v>182</v>
+        <v>184.96</v>
       </c>
       <c r="O30" t="n">
-        <v>185.58</v>
+        <v>185.68</v>
       </c>
       <c r="P30" t="n">
-        <v>160.3228</v>
+        <v>161.3336</v>
       </c>
       <c r="Q30" t="n">
-        <v>166.5898</v>
+        <v>166.5086</v>
       </c>
       <c r="R30" t="n">
         <v>191.5557367172241</v>
@@ -5977,26 +5999,26 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>2 sep</t>
+          <t>3 sep</t>
         </is>
       </c>
       <c r="V30" t="n">
-        <v>499.85</v>
+        <v>501.66</v>
       </c>
       <c r="W30" t="n">
-        <v>500.27</v>
+        <v>515.65</v>
       </c>
       <c r="X30" t="n">
-        <v>493.81</v>
+        <v>500.8</v>
       </c>
       <c r="Y30" t="n">
-        <v>496.82</v>
+        <v>510.12</v>
       </c>
       <c r="Z30" t="n">
-        <v>437.7045</v>
+        <v>440.6114</v>
       </c>
       <c r="AA30" t="n">
-        <v>429.3706</v>
+        <v>429.3912</v>
       </c>
       <c r="AB30" t="n">
         <v>535.3375423278808</v>
@@ -6008,26 +6030,26 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>4 sep</t>
+          <t>7 sep</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>40.145</v>
+        <v>40.26</v>
       </c>
       <c r="C31" t="n">
-        <v>40.28</v>
+        <v>40.845</v>
       </c>
       <c r="D31" t="n">
-        <v>39.665</v>
+        <v>40.12</v>
       </c>
       <c r="E31" t="n">
-        <v>40.105</v>
+        <v>40.56</v>
       </c>
       <c r="F31" t="n">
-        <v>37.8115</v>
+        <v>37.9551</v>
       </c>
       <c r="G31" t="n">
-        <v>35.113</v>
+        <v>35.1619</v>
       </c>
       <c r="H31" t="n">
         <v>45.05751734733581</v>
@@ -6037,26 +6059,26 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>4 sep</t>
+          <t>7 sep</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>187.8</v>
+        <v>183.56</v>
       </c>
       <c r="M31" t="n">
-        <v>189.9</v>
+        <v>184.3</v>
       </c>
       <c r="N31" t="n">
-        <v>184.96</v>
+        <v>179.92</v>
       </c>
       <c r="O31" t="n">
-        <v>185.68</v>
+        <v>182.8</v>
       </c>
       <c r="P31" t="n">
-        <v>161.3336</v>
+        <v>162.2568</v>
       </c>
       <c r="Q31" t="n">
-        <v>166.5086</v>
+        <v>166.4122</v>
       </c>
       <c r="R31" t="n">
         <v>191.5557367172241</v>
@@ -6066,26 +6088,26 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>3 sep</t>
+          <t>4 sep</t>
         </is>
       </c>
       <c r="V31" t="n">
-        <v>501.66</v>
+        <v>510</v>
       </c>
       <c r="W31" t="n">
-        <v>515.65</v>
+        <v>511</v>
       </c>
       <c r="X31" t="n">
-        <v>500.8</v>
+        <v>499.36</v>
       </c>
       <c r="Y31" t="n">
-        <v>510.12</v>
+        <v>499.7</v>
       </c>
       <c r="Z31" t="n">
-        <v>440.6114</v>
+        <v>443.5621</v>
       </c>
       <c r="AA31" t="n">
-        <v>429.3912</v>
+        <v>429.3729</v>
       </c>
       <c r="AB31" t="n">
         <v>535.3375423278808</v>
@@ -6097,26 +6119,26 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>7 sep</t>
+          <t>8 sep</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>40.26</v>
+        <v>40.83</v>
       </c>
       <c r="C32" t="n">
-        <v>40.845</v>
+        <v>41.18</v>
       </c>
       <c r="D32" t="n">
-        <v>40.12</v>
+        <v>40.6325</v>
       </c>
       <c r="E32" t="n">
-        <v>40.56</v>
+        <v>40.855</v>
       </c>
       <c r="F32" t="n">
-        <v>37.9551</v>
+        <v>38.0977</v>
       </c>
       <c r="G32" t="n">
-        <v>35.1619</v>
+        <v>35.2131</v>
       </c>
       <c r="H32" t="n">
         <v>45.05751734733581</v>
@@ -6126,26 +6148,26 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>7 sep</t>
+          <t>8 sep</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>183.56</v>
+        <v>182.32</v>
       </c>
       <c r="M32" t="n">
-        <v>184.3</v>
+        <v>183.76</v>
       </c>
       <c r="N32" t="n">
-        <v>179.92</v>
+        <v>180.02</v>
       </c>
       <c r="O32" t="n">
-        <v>182.8</v>
+        <v>181.7</v>
       </c>
       <c r="P32" t="n">
-        <v>162.2568</v>
+        <v>163.2108</v>
       </c>
       <c r="Q32" t="n">
-        <v>166.4122</v>
+        <v>166.3049</v>
       </c>
       <c r="R32" t="n">
         <v>191.5557367172241</v>
@@ -6155,26 +6177,26 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>4 sep</t>
+          <t>8 sep</t>
         </is>
       </c>
       <c r="V32" t="n">
-        <v>510</v>
+        <v>493.01</v>
       </c>
       <c r="W32" t="n">
-        <v>511</v>
+        <v>495.19</v>
       </c>
       <c r="X32" t="n">
-        <v>499.36</v>
+        <v>490.15</v>
       </c>
       <c r="Y32" t="n">
-        <v>499.7</v>
+        <v>493.95</v>
       </c>
       <c r="Z32" t="n">
-        <v>443.5621</v>
+        <v>445.9957</v>
       </c>
       <c r="AA32" t="n">
-        <v>429.3729</v>
+        <v>429.3939</v>
       </c>
       <c r="AB32" t="n">
         <v>535.3375423278808</v>
@@ -6186,26 +6208,26 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>8 sep</t>
+          <t>9 sep</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>40.83</v>
+        <v>41.1</v>
       </c>
       <c r="C33" t="n">
-        <v>41.18</v>
+        <v>41.385</v>
       </c>
       <c r="D33" t="n">
-        <v>40.6325</v>
+        <v>40.85</v>
       </c>
       <c r="E33" t="n">
-        <v>40.855</v>
+        <v>40.94</v>
       </c>
       <c r="F33" t="n">
-        <v>38.0977</v>
+        <v>38.2513</v>
       </c>
       <c r="G33" t="n">
-        <v>35.2131</v>
+        <v>35.2646</v>
       </c>
       <c r="H33" t="n">
         <v>45.05751734733581</v>
@@ -6215,26 +6237,26 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>8 sep</t>
+          <t>9 sep</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>182.32</v>
+        <v>183</v>
       </c>
       <c r="M33" t="n">
-        <v>183.76</v>
+        <v>187.04</v>
       </c>
       <c r="N33" t="n">
-        <v>180.02</v>
+        <v>181.36</v>
       </c>
       <c r="O33" t="n">
-        <v>181.7</v>
+        <v>182.86</v>
       </c>
       <c r="P33" t="n">
-        <v>163.2108</v>
+        <v>164.0504</v>
       </c>
       <c r="Q33" t="n">
-        <v>166.3049</v>
+        <v>166.2113</v>
       </c>
       <c r="R33" t="n">
         <v>191.5557367172241</v>
@@ -6244,26 +6266,26 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>8 sep</t>
+          <t>9 sep</t>
         </is>
       </c>
       <c r="V33" t="n">
-        <v>493.01</v>
+        <v>493.07</v>
       </c>
       <c r="W33" t="n">
-        <v>495.19</v>
+        <v>494.39</v>
       </c>
       <c r="X33" t="n">
-        <v>490.15</v>
+        <v>489.8</v>
       </c>
       <c r="Y33" t="n">
-        <v>493.95</v>
+        <v>491.65</v>
       </c>
       <c r="Z33" t="n">
-        <v>445.9957</v>
+        <v>448.4712</v>
       </c>
       <c r="AA33" t="n">
-        <v>429.3939</v>
+        <v>429.4364</v>
       </c>
       <c r="AB33" t="n">
         <v>535.3375423278808</v>
@@ -6275,26 +6297,26 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>9 sep</t>
+          <t>10 sep</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>41.1</v>
+        <v>40.98</v>
       </c>
       <c r="C34" t="n">
-        <v>41.385</v>
+        <v>41.77</v>
       </c>
       <c r="D34" t="n">
-        <v>40.85</v>
+        <v>40.93</v>
       </c>
       <c r="E34" t="n">
-        <v>40.94</v>
+        <v>41.23</v>
       </c>
       <c r="F34" t="n">
-        <v>38.2513</v>
+        <v>38.4034</v>
       </c>
       <c r="G34" t="n">
-        <v>35.2646</v>
+        <v>35.3174</v>
       </c>
       <c r="H34" t="n">
         <v>45.05751734733581</v>
@@ -6304,26 +6326,26 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>9 sep</t>
+          <t>10 sep</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="M34" t="n">
-        <v>187.04</v>
+        <v>180.4</v>
       </c>
       <c r="N34" t="n">
-        <v>181.36</v>
+        <v>176.2</v>
       </c>
       <c r="O34" t="n">
-        <v>182.86</v>
+        <v>177.82</v>
       </c>
       <c r="P34" t="n">
-        <v>164.0504</v>
+        <v>164.7724</v>
       </c>
       <c r="Q34" t="n">
-        <v>166.2113</v>
+        <v>166.0803</v>
       </c>
       <c r="R34" t="n">
         <v>191.5557367172241</v>
@@ -6333,26 +6355,26 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>9 sep</t>
+          <t>10 sep</t>
         </is>
       </c>
       <c r="V34" t="n">
-        <v>493.07</v>
+        <v>488.32</v>
       </c>
       <c r="W34" t="n">
-        <v>494.39</v>
+        <v>494.52</v>
       </c>
       <c r="X34" t="n">
-        <v>489.8</v>
+        <v>486</v>
       </c>
       <c r="Y34" t="n">
-        <v>491.65</v>
+        <v>492.44</v>
       </c>
       <c r="Z34" t="n">
-        <v>448.4712</v>
+        <v>450.8736</v>
       </c>
       <c r="AA34" t="n">
-        <v>429.4364</v>
+        <v>429.5215</v>
       </c>
       <c r="AB34" t="n">
         <v>535.3375423278808</v>
@@ -6364,26 +6386,26 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10 sep</t>
+          <t>11 sep</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>40.98</v>
+        <v>41.345</v>
       </c>
       <c r="C35" t="n">
-        <v>41.77</v>
+        <v>41.715</v>
       </c>
       <c r="D35" t="n">
-        <v>40.93</v>
+        <v>40.905</v>
       </c>
       <c r="E35" t="n">
-        <v>41.23</v>
+        <v>41.415</v>
       </c>
       <c r="F35" t="n">
-        <v>38.4034</v>
+        <v>38.5608</v>
       </c>
       <c r="G35" t="n">
-        <v>35.3174</v>
+        <v>35.3717</v>
       </c>
       <c r="H35" t="n">
         <v>45.05751734733581</v>
@@ -6393,26 +6415,26 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>10 sep</t>
+          <t>11 sep</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>180</v>
+        <v>175.68</v>
       </c>
       <c r="M35" t="n">
-        <v>180.4</v>
+        <v>178.84</v>
       </c>
       <c r="N35" t="n">
-        <v>176.2</v>
+        <v>172.16</v>
       </c>
       <c r="O35" t="n">
-        <v>177.82</v>
+        <v>177.26</v>
       </c>
       <c r="P35" t="n">
-        <v>164.7724</v>
+        <v>165.5248</v>
       </c>
       <c r="Q35" t="n">
-        <v>166.0803</v>
+        <v>165.9594</v>
       </c>
       <c r="R35" t="n">
         <v>191.5557367172241</v>
@@ -6422,26 +6444,26 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>10 sep</t>
+          <t>11 sep</t>
         </is>
       </c>
       <c r="V35" t="n">
-        <v>488.32</v>
+        <v>495.65</v>
       </c>
       <c r="W35" t="n">
-        <v>494.52</v>
+        <v>498.97</v>
       </c>
       <c r="X35" t="n">
-        <v>486</v>
+        <v>492.58</v>
       </c>
       <c r="Y35" t="n">
-        <v>492.44</v>
+        <v>495.63</v>
       </c>
       <c r="Z35" t="n">
-        <v>450.8736</v>
+        <v>453.115</v>
       </c>
       <c r="AA35" t="n">
-        <v>429.5215</v>
+        <v>429.654</v>
       </c>
       <c r="AB35" t="n">
         <v>535.3375423278808</v>
@@ -6453,26 +6475,26 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>11 sep</t>
+          <t>14 sep</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>41.345</v>
+        <v>41.88</v>
       </c>
       <c r="C36" t="n">
-        <v>41.715</v>
+        <v>42.285</v>
       </c>
       <c r="D36" t="n">
-        <v>40.905</v>
+        <v>41.8</v>
       </c>
       <c r="E36" t="n">
-        <v>41.415</v>
+        <v>41.91</v>
       </c>
       <c r="F36" t="n">
-        <v>38.5608</v>
+        <v>38.7226</v>
       </c>
       <c r="G36" t="n">
-        <v>35.3717</v>
+        <v>35.4269</v>
       </c>
       <c r="H36" t="n">
         <v>45.05751734733581</v>
@@ -6482,26 +6504,26 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>11 sep</t>
+          <t>14 sep</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>175.68</v>
+        <v>180.82</v>
       </c>
       <c r="M36" t="n">
-        <v>178.84</v>
+        <v>186.76</v>
       </c>
       <c r="N36" t="n">
-        <v>172.16</v>
+        <v>180.82</v>
       </c>
       <c r="O36" t="n">
-        <v>177.26</v>
+        <v>186.26</v>
       </c>
       <c r="P36" t="n">
-        <v>165.5248</v>
+        <v>166.4488</v>
       </c>
       <c r="Q36" t="n">
-        <v>165.9594</v>
+        <v>165.8745</v>
       </c>
       <c r="R36" t="n">
         <v>191.5557367172241</v>
@@ -6511,26 +6533,26 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>11 sep</t>
+          <t>14 sep</t>
         </is>
       </c>
       <c r="V36" t="n">
-        <v>495.65</v>
+        <v>497.06</v>
       </c>
       <c r="W36" t="n">
-        <v>498.97</v>
+        <v>509.95</v>
       </c>
       <c r="X36" t="n">
-        <v>492.58</v>
+        <v>495.34</v>
       </c>
       <c r="Y36" t="n">
-        <v>495.63</v>
+        <v>505.41</v>
       </c>
       <c r="Z36" t="n">
-        <v>453.115</v>
+        <v>455.4281</v>
       </c>
       <c r="AA36" t="n">
-        <v>429.654</v>
+        <v>429.8259</v>
       </c>
       <c r="AB36" t="n">
         <v>535.3375423278808</v>
@@ -6542,26 +6564,26 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>14 sep</t>
+          <t>15 sep</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>41.88</v>
+        <v>41.845</v>
       </c>
       <c r="C37" t="n">
-        <v>42.285</v>
+        <v>42.7</v>
       </c>
       <c r="D37" t="n">
-        <v>41.8</v>
+        <v>41.72</v>
       </c>
       <c r="E37" t="n">
-        <v>41.91</v>
+        <v>42.7</v>
       </c>
       <c r="F37" t="n">
-        <v>38.7226</v>
+        <v>38.8782</v>
       </c>
       <c r="G37" t="n">
-        <v>35.4269</v>
+        <v>35.4854</v>
       </c>
       <c r="H37" t="n">
         <v>45.05751734733581</v>
@@ -6571,26 +6593,26 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>14 sep</t>
+          <t>15 sep</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>180.82</v>
+        <v>186.64</v>
       </c>
       <c r="M37" t="n">
-        <v>186.76</v>
+        <v>187.26</v>
       </c>
       <c r="N37" t="n">
-        <v>180.82</v>
+        <v>183.2</v>
       </c>
       <c r="O37" t="n">
-        <v>186.26</v>
+        <v>187.08</v>
       </c>
       <c r="P37" t="n">
-        <v>166.4488</v>
+        <v>167.3124</v>
       </c>
       <c r="Q37" t="n">
-        <v>165.8745</v>
+        <v>165.7921</v>
       </c>
       <c r="R37" t="n">
         <v>191.5557367172241</v>
@@ -6600,26 +6622,26 @@
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>14 sep</t>
+          <t>15 sep</t>
         </is>
       </c>
       <c r="V37" t="n">
-        <v>497.06</v>
+        <v>500.06</v>
       </c>
       <c r="W37" t="n">
-        <v>509.95</v>
+        <v>505.9</v>
       </c>
       <c r="X37" t="n">
-        <v>495.34</v>
+        <v>495.54</v>
       </c>
       <c r="Y37" t="n">
-        <v>505.41</v>
+        <v>497.12</v>
       </c>
       <c r="Z37" t="n">
-        <v>455.4281</v>
+        <v>457.6502</v>
       </c>
       <c r="AA37" t="n">
-        <v>429.8259</v>
+        <v>429.9416</v>
       </c>
       <c r="AB37" t="n">
         <v>535.3375423278808</v>
@@ -6631,26 +6653,26 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>15 sep</t>
+          <t>16 sep</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>41.845</v>
+        <v>42.72</v>
       </c>
       <c r="C38" t="n">
-        <v>42.7</v>
+        <v>42.85</v>
       </c>
       <c r="D38" t="n">
-        <v>41.72</v>
+        <v>41.67</v>
       </c>
       <c r="E38" t="n">
-        <v>42.7</v>
+        <v>41.825</v>
       </c>
       <c r="F38" t="n">
-        <v>38.8782</v>
+        <v>38.9989</v>
       </c>
       <c r="G38" t="n">
-        <v>35.4854</v>
+        <v>35.5403</v>
       </c>
       <c r="H38" t="n">
         <v>45.05751734733581</v>
@@ -6660,26 +6682,26 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>15 sep</t>
+          <t>16 sep</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>186.64</v>
+        <v>185.86</v>
       </c>
       <c r="M38" t="n">
-        <v>187.26</v>
+        <v>186.76</v>
       </c>
       <c r="N38" t="n">
-        <v>183.2</v>
+        <v>182.18</v>
       </c>
       <c r="O38" t="n">
-        <v>187.08</v>
+        <v>186.56</v>
       </c>
       <c r="P38" t="n">
-        <v>167.3124</v>
+        <v>168.2844</v>
       </c>
       <c r="Q38" t="n">
-        <v>165.7921</v>
+        <v>165.6996</v>
       </c>
       <c r="R38" t="n">
         <v>191.5557367172241</v>
@@ -6689,26 +6711,26 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>15 sep</t>
+          <t>16 sep</t>
         </is>
       </c>
       <c r="V38" t="n">
-        <v>500.06</v>
+        <v>493.03</v>
       </c>
       <c r="W38" t="n">
-        <v>505.9</v>
+        <v>495.97</v>
       </c>
       <c r="X38" t="n">
-        <v>495.54</v>
+        <v>487.23</v>
       </c>
       <c r="Y38" t="n">
-        <v>497.12</v>
+        <v>490.3</v>
       </c>
       <c r="Z38" t="n">
-        <v>457.6502</v>
+        <v>459.694</v>
       </c>
       <c r="AA38" t="n">
-        <v>429.9416</v>
+        <v>429.9809</v>
       </c>
       <c r="AB38" t="n">
         <v>535.3375423278808</v>
@@ -6720,26 +6742,26 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>16 sep</t>
+          <t>17 sep</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>42.72</v>
+        <v>41.58</v>
       </c>
       <c r="C39" t="n">
-        <v>42.85</v>
+        <v>42.055</v>
       </c>
       <c r="D39" t="n">
-        <v>41.67</v>
+        <v>41.38</v>
       </c>
       <c r="E39" t="n">
-        <v>41.825</v>
+        <v>41.56</v>
       </c>
       <c r="F39" t="n">
-        <v>38.9989</v>
+        <v>39.1225</v>
       </c>
       <c r="G39" t="n">
-        <v>35.5403</v>
+        <v>35.5926</v>
       </c>
       <c r="H39" t="n">
         <v>45.05751734733581</v>
@@ -6749,26 +6771,26 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>16 sep</t>
+          <t>17 sep</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>185.86</v>
+        <v>188.54</v>
       </c>
       <c r="M39" t="n">
-        <v>186.76</v>
+        <v>189.2</v>
       </c>
       <c r="N39" t="n">
-        <v>182.18</v>
+        <v>184.62</v>
       </c>
       <c r="O39" t="n">
-        <v>186.56</v>
+        <v>188</v>
       </c>
       <c r="P39" t="n">
-        <v>168.2844</v>
+        <v>169.2896</v>
       </c>
       <c r="Q39" t="n">
-        <v>165.6996</v>
+        <v>165.6125</v>
       </c>
       <c r="R39" t="n">
         <v>191.5557367172241</v>
@@ -6778,26 +6800,26 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>16 sep</t>
+          <t>17 sep</t>
         </is>
       </c>
       <c r="V39" t="n">
-        <v>493.03</v>
+        <v>497.8</v>
       </c>
       <c r="W39" t="n">
-        <v>495.97</v>
+        <v>501.47</v>
       </c>
       <c r="X39" t="n">
-        <v>487.23</v>
+        <v>493.17</v>
       </c>
       <c r="Y39" t="n">
-        <v>490.3</v>
+        <v>497.75</v>
       </c>
       <c r="Z39" t="n">
-        <v>459.694</v>
+        <v>461.9966</v>
       </c>
       <c r="AA39" t="n">
-        <v>429.9809</v>
+        <v>430.0251</v>
       </c>
       <c r="AB39" t="n">
         <v>535.3375423278808</v>
@@ -6809,26 +6831,26 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>17 sep</t>
+          <t>18 sep</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>41.58</v>
+        <v>41.465</v>
       </c>
       <c r="C40" t="n">
-        <v>42.055</v>
+        <v>41.5</v>
       </c>
       <c r="D40" t="n">
-        <v>41.38</v>
+        <v>40.955</v>
       </c>
       <c r="E40" t="n">
-        <v>41.56</v>
+        <v>41.315</v>
       </c>
       <c r="F40" t="n">
-        <v>39.1225</v>
+        <v>39.2414</v>
       </c>
       <c r="G40" t="n">
-        <v>35.5926</v>
+        <v>35.6436</v>
       </c>
       <c r="H40" t="n">
         <v>45.05751734733581</v>
@@ -6838,26 +6860,26 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>17 sep</t>
+          <t>18 sep</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>188.54</v>
+        <v>186.1</v>
       </c>
       <c r="M40" t="n">
-        <v>189.2</v>
+        <v>187.26</v>
       </c>
       <c r="N40" t="n">
-        <v>184.62</v>
+        <v>182.56</v>
       </c>
       <c r="O40" t="n">
-        <v>188</v>
+        <v>183.12</v>
       </c>
       <c r="P40" t="n">
-        <v>169.2896</v>
+        <v>170.2004</v>
       </c>
       <c r="Q40" t="n">
-        <v>165.6125</v>
+        <v>165.5062</v>
       </c>
       <c r="R40" t="n">
         <v>191.5557367172241</v>
@@ -6867,26 +6889,26 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>17 sep</t>
+          <t>18 sep</t>
         </is>
       </c>
       <c r="V40" t="n">
-        <v>497.8</v>
+        <v>497.97</v>
       </c>
       <c r="W40" t="n">
-        <v>501.47</v>
+        <v>498.65</v>
       </c>
       <c r="X40" t="n">
-        <v>493.17</v>
+        <v>491.1</v>
       </c>
       <c r="Y40" t="n">
-        <v>497.75</v>
+        <v>493.78</v>
       </c>
       <c r="Z40" t="n">
-        <v>461.9966</v>
+        <v>464.1995</v>
       </c>
       <c r="AA40" t="n">
-        <v>430.0251</v>
+        <v>430.0757</v>
       </c>
       <c r="AB40" t="n">
         <v>535.3375423278808</v>
@@ -6898,26 +6920,26 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>18 sep</t>
+          <t>21 sep</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>41.465</v>
+        <v>41.04</v>
       </c>
       <c r="C41" t="n">
-        <v>41.5</v>
+        <v>41.4</v>
       </c>
       <c r="D41" t="n">
-        <v>40.955</v>
+        <v>40.775</v>
       </c>
       <c r="E41" t="n">
-        <v>41.315</v>
+        <v>40.775</v>
       </c>
       <c r="F41" t="n">
-        <v>39.2414</v>
+        <v>39.3341</v>
       </c>
       <c r="G41" t="n">
-        <v>35.6436</v>
+        <v>35.6939</v>
       </c>
       <c r="H41" t="n">
         <v>45.05751734733581</v>
@@ -6927,26 +6949,26 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>18 sep</t>
+          <t>21 sep</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>186.1</v>
+        <v>184.7</v>
       </c>
       <c r="M41" t="n">
-        <v>187.26</v>
+        <v>185.86</v>
       </c>
       <c r="N41" t="n">
-        <v>182.56</v>
+        <v>182.48</v>
       </c>
       <c r="O41" t="n">
-        <v>183.12</v>
+        <v>182.86</v>
       </c>
       <c r="P41" t="n">
-        <v>170.2004</v>
+        <v>171.0432</v>
       </c>
       <c r="Q41" t="n">
-        <v>165.5062</v>
+        <v>165.4052</v>
       </c>
       <c r="R41" t="n">
         <v>191.5557367172241</v>
@@ -6956,26 +6978,26 @@
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>18 sep</t>
+          <t>21 sep</t>
         </is>
       </c>
       <c r="V41" t="n">
-        <v>497.97</v>
+        <v>494.95</v>
       </c>
       <c r="W41" t="n">
-        <v>498.65</v>
+        <v>501.87</v>
       </c>
       <c r="X41" t="n">
-        <v>491.1</v>
+        <v>491.33</v>
       </c>
       <c r="Y41" t="n">
-        <v>493.78</v>
+        <v>501.61</v>
       </c>
       <c r="Z41" t="n">
-        <v>464.1995</v>
+        <v>466.5442</v>
       </c>
       <c r="AA41" t="n">
-        <v>430.0757</v>
+        <v>430.1492</v>
       </c>
       <c r="AB41" t="n">
         <v>535.3375423278808</v>
@@ -6987,26 +7009,26 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>21 sep</t>
+          <t>22 sep</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>41.04</v>
+        <v>40.84</v>
       </c>
       <c r="C42" t="n">
-        <v>41.4</v>
+        <v>41.165</v>
       </c>
       <c r="D42" t="n">
-        <v>40.775</v>
+        <v>40.215</v>
       </c>
       <c r="E42" t="n">
-        <v>40.775</v>
+        <v>41.01</v>
       </c>
       <c r="F42" t="n">
-        <v>39.3341</v>
+        <v>39.4244</v>
       </c>
       <c r="G42" t="n">
-        <v>35.6939</v>
+        <v>35.746</v>
       </c>
       <c r="H42" t="n">
         <v>45.05751734733581</v>
@@ -7016,26 +7038,26 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>21 sep</t>
+          <t>22 sep</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>184.7</v>
+        <v>182.14</v>
       </c>
       <c r="M42" t="n">
-        <v>185.86</v>
+        <v>187.48</v>
       </c>
       <c r="N42" t="n">
-        <v>182.48</v>
+        <v>181.52</v>
       </c>
       <c r="O42" t="n">
-        <v>182.86</v>
+        <v>182.32</v>
       </c>
       <c r="P42" t="n">
-        <v>171.0432</v>
+        <v>171.9552</v>
       </c>
       <c r="Q42" t="n">
-        <v>165.4052</v>
+        <v>165.2836</v>
       </c>
       <c r="R42" t="n">
         <v>191.5557367172241</v>
@@ -7045,26 +7067,26 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>21 sep</t>
+          <t>22 sep</t>
         </is>
       </c>
       <c r="V42" t="n">
-        <v>494.95</v>
+        <v>507.32</v>
       </c>
       <c r="W42" t="n">
-        <v>501.87</v>
+        <v>508.5</v>
       </c>
       <c r="X42" t="n">
-        <v>491.33</v>
+        <v>493.65</v>
       </c>
       <c r="Y42" t="n">
-        <v>501.61</v>
+        <v>498</v>
       </c>
       <c r="Z42" t="n">
-        <v>466.5442</v>
+        <v>468.699</v>
       </c>
       <c r="AA42" t="n">
-        <v>430.1492</v>
+        <v>430.2656</v>
       </c>
       <c r="AB42" t="n">
         <v>535.3375423278808</v>
@@ -7076,26 +7098,26 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>22 sep</t>
+          <t>23 sep</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>40.84</v>
+        <v>41</v>
       </c>
       <c r="C43" t="n">
-        <v>41.165</v>
+        <v>41.755</v>
       </c>
       <c r="D43" t="n">
-        <v>40.215</v>
+        <v>40.995</v>
       </c>
       <c r="E43" t="n">
-        <v>41.01</v>
+        <v>41.69</v>
       </c>
       <c r="F43" t="n">
-        <v>39.4244</v>
+        <v>39.5272</v>
       </c>
       <c r="G43" t="n">
-        <v>35.746</v>
+        <v>35.8024</v>
       </c>
       <c r="H43" t="n">
         <v>45.05751734733581</v>
@@ -7105,26 +7127,26 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>22 sep</t>
+          <t>23 sep</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>182.14</v>
+        <v>184.9</v>
       </c>
       <c r="M43" t="n">
-        <v>187.48</v>
+        <v>187.8</v>
       </c>
       <c r="N43" t="n">
-        <v>181.52</v>
+        <v>183.48</v>
       </c>
       <c r="O43" t="n">
-        <v>182.32</v>
+        <v>186.46</v>
       </c>
       <c r="P43" t="n">
-        <v>171.9552</v>
+        <v>172.9448</v>
       </c>
       <c r="Q43" t="n">
-        <v>165.2836</v>
+        <v>165.1675</v>
       </c>
       <c r="R43" t="n">
         <v>191.5557367172241</v>
@@ -7134,26 +7156,26 @@
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>22 sep</t>
+          <t>23 sep</t>
         </is>
       </c>
       <c r="V43" t="n">
-        <v>507.32</v>
+        <v>500.76</v>
       </c>
       <c r="W43" t="n">
-        <v>508.5</v>
+        <v>509.44</v>
       </c>
       <c r="X43" t="n">
-        <v>493.65</v>
+        <v>495.88</v>
       </c>
       <c r="Y43" t="n">
-        <v>498</v>
+        <v>500.59</v>
       </c>
       <c r="Z43" t="n">
-        <v>468.699</v>
+        <v>471.0267</v>
       </c>
       <c r="AA43" t="n">
-        <v>430.2656</v>
+        <v>430.3795</v>
       </c>
       <c r="AB43" t="n">
         <v>535.3375423278808</v>
@@ -7165,26 +7187,26 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>23 sep</t>
+          <t>24 sep</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>41</v>
+        <v>41.825</v>
       </c>
       <c r="C44" t="n">
-        <v>41.755</v>
+        <v>42.52</v>
       </c>
       <c r="D44" t="n">
-        <v>40.995</v>
+        <v>41.78</v>
       </c>
       <c r="E44" t="n">
-        <v>41.69</v>
+        <v>42.43</v>
       </c>
       <c r="F44" t="n">
-        <v>39.5272</v>
+        <v>39.6382</v>
       </c>
       <c r="G44" t="n">
-        <v>35.8024</v>
+        <v>35.8638</v>
       </c>
       <c r="H44" t="n">
         <v>45.05751734733581</v>
@@ -7194,26 +7216,26 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>23 sep</t>
+          <t>24 sep</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>184.9</v>
+        <v>184.52</v>
       </c>
       <c r="M44" t="n">
-        <v>187.8</v>
+        <v>185.5</v>
       </c>
       <c r="N44" t="n">
-        <v>183.48</v>
+        <v>182.26</v>
       </c>
       <c r="O44" t="n">
-        <v>186.46</v>
+        <v>184.18</v>
       </c>
       <c r="P44" t="n">
-        <v>172.9448</v>
+        <v>173.8756</v>
       </c>
       <c r="Q44" t="n">
-        <v>165.1675</v>
+        <v>165.0554</v>
       </c>
       <c r="R44" t="n">
         <v>191.5557367172241</v>
@@ -7223,26 +7245,26 @@
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>23 sep</t>
+          <t>24 sep</t>
         </is>
       </c>
       <c r="V44" t="n">
-        <v>500.76</v>
+        <v>495.07</v>
       </c>
       <c r="W44" t="n">
-        <v>509.44</v>
+        <v>498.9</v>
       </c>
       <c r="X44" t="n">
-        <v>495.88</v>
+        <v>491.22</v>
       </c>
       <c r="Y44" t="n">
-        <v>500.59</v>
+        <v>497.93</v>
       </c>
       <c r="Z44" t="n">
-        <v>471.0267</v>
+        <v>473.0876</v>
       </c>
       <c r="AA44" t="n">
-        <v>430.3795</v>
+        <v>430.4686</v>
       </c>
       <c r="AB44" t="n">
         <v>535.3375423278808</v>
@@ -7254,26 +7276,26 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>24 sep</t>
+          <t>25 sep</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>41.825</v>
+        <v>41.99</v>
       </c>
       <c r="C45" t="n">
-        <v>42.52</v>
+        <v>42.33</v>
       </c>
       <c r="D45" t="n">
-        <v>41.78</v>
+        <v>41.71</v>
       </c>
       <c r="E45" t="n">
-        <v>42.43</v>
+        <v>42.06</v>
       </c>
       <c r="F45" t="n">
-        <v>39.6382</v>
+        <v>39.7263</v>
       </c>
       <c r="G45" t="n">
-        <v>35.8638</v>
+        <v>35.9239</v>
       </c>
       <c r="H45" t="n">
         <v>45.05751734733581</v>
@@ -7283,26 +7305,26 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>24 sep</t>
+          <t>25 sep</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>184.52</v>
+        <v>184.42</v>
       </c>
       <c r="M45" t="n">
-        <v>185.5</v>
+        <v>185.92</v>
       </c>
       <c r="N45" t="n">
-        <v>182.26</v>
+        <v>183.76</v>
       </c>
       <c r="O45" t="n">
-        <v>184.18</v>
+        <v>185.92</v>
       </c>
       <c r="P45" t="n">
-        <v>173.8756</v>
+        <v>174.8356</v>
       </c>
       <c r="Q45" t="n">
-        <v>165.0554</v>
+        <v>164.9525</v>
       </c>
       <c r="R45" t="n">
         <v>191.5557367172241</v>
@@ -7312,26 +7334,26 @@
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>24 sep</t>
+          <t>25 sep</t>
         </is>
       </c>
       <c r="V45" t="n">
-        <v>495.07</v>
+        <v>499.04</v>
       </c>
       <c r="W45" t="n">
-        <v>498.9</v>
+        <v>519.4</v>
       </c>
       <c r="X45" t="n">
-        <v>491.22</v>
+        <v>497.25</v>
       </c>
       <c r="Y45" t="n">
-        <v>497.93</v>
+        <v>516.17</v>
       </c>
       <c r="Z45" t="n">
-        <v>473.0876</v>
+        <v>475.4041</v>
       </c>
       <c r="AA45" t="n">
-        <v>430.4686</v>
+        <v>430.6098</v>
       </c>
       <c r="AB45" t="n">
         <v>535.3375423278808</v>
@@ -7343,26 +7365,26 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>25 sep</t>
+          <t>28 sep</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>41.99</v>
+        <v>42.45</v>
       </c>
       <c r="C46" t="n">
-        <v>42.33</v>
+        <v>42.995</v>
       </c>
       <c r="D46" t="n">
-        <v>41.71</v>
+        <v>42.38</v>
       </c>
       <c r="E46" t="n">
-        <v>42.06</v>
+        <v>42.725</v>
       </c>
       <c r="F46" t="n">
-        <v>39.7263</v>
+        <v>39.8301</v>
       </c>
       <c r="G46" t="n">
-        <v>35.9239</v>
+        <v>35.9888</v>
       </c>
       <c r="H46" t="n">
         <v>45.05751734733581</v>
@@ -7372,26 +7394,26 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>25 sep</t>
+          <t>28 sep</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>184.42</v>
+        <v>185.2</v>
       </c>
       <c r="M46" t="n">
-        <v>185.92</v>
+        <v>186.76</v>
       </c>
       <c r="N46" t="n">
-        <v>183.76</v>
+        <v>178.88</v>
       </c>
       <c r="O46" t="n">
-        <v>185.92</v>
+        <v>184.02</v>
       </c>
       <c r="P46" t="n">
-        <v>174.8356</v>
+        <v>175.7508</v>
       </c>
       <c r="Q46" t="n">
-        <v>164.9525</v>
+        <v>164.8355</v>
       </c>
       <c r="R46" t="n">
         <v>191.5557367172241</v>
@@ -7401,26 +7423,26 @@
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>25 sep</t>
+          <t>28 sep</t>
         </is>
       </c>
       <c r="V46" t="n">
-        <v>499.04</v>
+        <v>505.47</v>
       </c>
       <c r="W46" t="n">
-        <v>519.4</v>
+        <v>513.33</v>
       </c>
       <c r="X46" t="n">
-        <v>497.25</v>
+        <v>502.22</v>
       </c>
       <c r="Y46" t="n">
-        <v>516.17</v>
+        <v>509.22</v>
       </c>
       <c r="Z46" t="n">
-        <v>475.4041</v>
+        <v>477.7269</v>
       </c>
       <c r="AA46" t="n">
-        <v>430.6098</v>
+        <v>430.7113</v>
       </c>
       <c r="AB46" t="n">
         <v>535.3375423278808</v>
@@ -7432,26 +7454,26 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>28 sep</t>
+          <t>29 sep</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>42.45</v>
+        <v>42.57</v>
       </c>
       <c r="C47" t="n">
-        <v>42.995</v>
+        <v>42.665</v>
       </c>
       <c r="D47" t="n">
-        <v>42.38</v>
+        <v>41.73</v>
       </c>
       <c r="E47" t="n">
-        <v>42.725</v>
+        <v>42.05</v>
       </c>
       <c r="F47" t="n">
-        <v>39.8301</v>
+        <v>39.9146</v>
       </c>
       <c r="G47" t="n">
-        <v>35.9888</v>
+        <v>36.0498</v>
       </c>
       <c r="H47" t="n">
         <v>45.05751734733581</v>
@@ -7461,26 +7483,26 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>28 sep</t>
+          <t>29 sep</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>185.2</v>
+        <v>183.22</v>
       </c>
       <c r="M47" t="n">
-        <v>186.76</v>
+        <v>186.34</v>
       </c>
       <c r="N47" t="n">
-        <v>178.88</v>
+        <v>182.28</v>
       </c>
       <c r="O47" t="n">
-        <v>184.02</v>
+        <v>185.32</v>
       </c>
       <c r="P47" t="n">
-        <v>175.7508</v>
+        <v>176.7288</v>
       </c>
       <c r="Q47" t="n">
-        <v>164.8355</v>
+        <v>164.733</v>
       </c>
       <c r="R47" t="n">
         <v>191.5557367172241</v>
@@ -7490,26 +7512,26 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>28 sep</t>
+          <t>29 sep</t>
         </is>
       </c>
       <c r="V47" t="n">
-        <v>505.47</v>
+        <v>508.31</v>
       </c>
       <c r="W47" t="n">
-        <v>513.33</v>
+        <v>513.64</v>
       </c>
       <c r="X47" t="n">
-        <v>502.22</v>
+        <v>502.4</v>
       </c>
       <c r="Y47" t="n">
-        <v>509.22</v>
+        <v>508.96</v>
       </c>
       <c r="Z47" t="n">
-        <v>477.7269</v>
+        <v>479.8754</v>
       </c>
       <c r="AA47" t="n">
-        <v>430.7113</v>
+        <v>430.8784</v>
       </c>
       <c r="AB47" t="n">
         <v>535.3375423278808</v>
@@ -7521,26 +7543,26 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>29 sep</t>
+          <t>30 sep</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>42.57</v>
+        <v>41.975</v>
       </c>
       <c r="C48" t="n">
-        <v>42.665</v>
+        <v>42.095</v>
       </c>
       <c r="D48" t="n">
-        <v>41.73</v>
+        <v>41.58</v>
       </c>
       <c r="E48" t="n">
-        <v>42.05</v>
+        <v>41.91</v>
       </c>
       <c r="F48" t="n">
-        <v>39.9146</v>
+        <v>39.9874</v>
       </c>
       <c r="G48" t="n">
-        <v>36.0498</v>
+        <v>36.1135</v>
       </c>
       <c r="H48" t="n">
         <v>45.05751734733581</v>
@@ -7550,26 +7572,26 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>29 sep</t>
+          <t>30 sep</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>183.22</v>
+        <v>184.5</v>
       </c>
       <c r="M48" t="n">
-        <v>186.34</v>
+        <v>186.2</v>
       </c>
       <c r="N48" t="n">
-        <v>182.28</v>
+        <v>181.06</v>
       </c>
       <c r="O48" t="n">
-        <v>185.32</v>
+        <v>185.66</v>
       </c>
       <c r="P48" t="n">
-        <v>176.7288</v>
+        <v>177.8012</v>
       </c>
       <c r="Q48" t="n">
-        <v>164.733</v>
+        <v>164.6377</v>
       </c>
       <c r="R48" t="n">
         <v>191.5557367172241</v>
@@ -7579,26 +7601,26 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>29 sep</t>
+          <t>30 sep</t>
         </is>
       </c>
       <c r="V48" t="n">
-        <v>508.31</v>
+        <v>511.61</v>
       </c>
       <c r="W48" t="n">
-        <v>513.64</v>
+        <v>519.83</v>
       </c>
       <c r="X48" t="n">
-        <v>502.4</v>
+        <v>510.31</v>
       </c>
       <c r="Y48" t="n">
-        <v>508.96</v>
+        <v>512.9</v>
       </c>
       <c r="Z48" t="n">
-        <v>479.8754</v>
+        <v>482.1933</v>
       </c>
       <c r="AA48" t="n">
-        <v>430.8784</v>
+        <v>431.0408</v>
       </c>
       <c r="AB48" t="n">
         <v>535.3375423278808</v>
@@ -7610,26 +7632,26 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>30 sep</t>
+          <t>1 okt</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>41.975</v>
+        <v>41.625</v>
       </c>
       <c r="C49" t="n">
-        <v>42.095</v>
+        <v>42.36</v>
       </c>
       <c r="D49" t="n">
-        <v>41.58</v>
+        <v>41.165</v>
       </c>
       <c r="E49" t="n">
-        <v>41.91</v>
+        <v>42.24</v>
       </c>
       <c r="F49" t="n">
-        <v>39.9874</v>
+        <v>40.0562</v>
       </c>
       <c r="G49" t="n">
-        <v>36.1135</v>
+        <v>36.1777</v>
       </c>
       <c r="H49" t="n">
         <v>45.05751734733581</v>
@@ -7639,26 +7661,26 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>30 sep</t>
+          <t>1 okt</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>184.5</v>
+        <v>184.68</v>
       </c>
       <c r="M49" t="n">
-        <v>186.2</v>
+        <v>190.26</v>
       </c>
       <c r="N49" t="n">
-        <v>181.06</v>
+        <v>181.34</v>
       </c>
       <c r="O49" t="n">
-        <v>185.66</v>
+        <v>186.74</v>
       </c>
       <c r="P49" t="n">
-        <v>177.8012</v>
+        <v>178.9696</v>
       </c>
       <c r="Q49" t="n">
-        <v>164.6377</v>
+        <v>164.5407</v>
       </c>
       <c r="R49" t="n">
         <v>191.5557367172241</v>
@@ -7668,26 +7690,26 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>30 sep</t>
+          <t>1 okt</t>
         </is>
       </c>
       <c r="V49" t="n">
-        <v>511.61</v>
+        <v>519.88</v>
       </c>
       <c r="W49" t="n">
-        <v>519.83</v>
+        <v>522.85</v>
       </c>
       <c r="X49" t="n">
-        <v>510.31</v>
+        <v>512.17</v>
       </c>
       <c r="Y49" t="n">
-        <v>512.9</v>
+        <v>512.8</v>
       </c>
       <c r="Z49" t="n">
-        <v>482.1933</v>
+        <v>484.6572</v>
       </c>
       <c r="AA49" t="n">
-        <v>431.0408</v>
+        <v>431.2272</v>
       </c>
       <c r="AB49" t="n">
         <v>535.3375423278808</v>
@@ -7699,26 +7721,26 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1 okt</t>
+          <t>2 okt</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>41.625</v>
+        <v>42.11</v>
       </c>
       <c r="C50" t="n">
-        <v>42.36</v>
+        <v>42.745</v>
       </c>
       <c r="D50" t="n">
-        <v>41.165</v>
+        <v>41.985</v>
       </c>
       <c r="E50" t="n">
-        <v>42.24</v>
+        <v>42.4</v>
       </c>
       <c r="F50" t="n">
-        <v>40.0562</v>
+        <v>40.1364</v>
       </c>
       <c r="G50" t="n">
-        <v>36.1777</v>
+        <v>36.2422</v>
       </c>
       <c r="H50" t="n">
         <v>45.05751734733581</v>
@@ -7728,26 +7750,26 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>1 okt</t>
+          <t>2 okt</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>184.68</v>
+        <v>187.82</v>
       </c>
       <c r="M50" t="n">
-        <v>190.26</v>
+        <v>188.74</v>
       </c>
       <c r="N50" t="n">
-        <v>181.34</v>
+        <v>183.92</v>
       </c>
       <c r="O50" t="n">
-        <v>186.74</v>
+        <v>183.92</v>
       </c>
       <c r="P50" t="n">
-        <v>178.9696</v>
+        <v>179.844</v>
       </c>
       <c r="Q50" t="n">
-        <v>164.5407</v>
+        <v>164.4442</v>
       </c>
       <c r="R50" t="n">
         <v>191.5557367172241</v>
@@ -7757,26 +7779,26 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>1 okt</t>
+          <t>2 okt</t>
         </is>
       </c>
       <c r="V50" t="n">
-        <v>519.88</v>
+        <v>519.39</v>
       </c>
       <c r="W50" t="n">
-        <v>522.85</v>
+        <v>522.5</v>
       </c>
       <c r="X50" t="n">
-        <v>512.17</v>
+        <v>513.66</v>
       </c>
       <c r="Y50" t="n">
-        <v>512.8</v>
+        <v>517.53</v>
       </c>
       <c r="Z50" t="n">
-        <v>484.6572</v>
+        <v>487.3905</v>
       </c>
       <c r="AA50" t="n">
-        <v>431.2272</v>
+        <v>431.4557</v>
       </c>
       <c r="AB50" t="n">
         <v>535.3375423278808</v>
@@ -7788,26 +7810,26 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2 okt</t>
+          <t>5 okt</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>42.11</v>
+        <v>42.645</v>
       </c>
       <c r="C51" t="n">
-        <v>42.745</v>
+        <v>43.11</v>
       </c>
       <c r="D51" t="n">
-        <v>41.985</v>
+        <v>42.35</v>
       </c>
       <c r="E51" t="n">
-        <v>42.4</v>
+        <v>42.865</v>
       </c>
       <c r="F51" t="n">
-        <v>40.1364</v>
+        <v>40.2347</v>
       </c>
       <c r="G51" t="n">
-        <v>36.2422</v>
+        <v>36.3069</v>
       </c>
       <c r="H51" t="n">
         <v>45.05751734733581</v>
@@ -7817,26 +7839,26 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2 okt</t>
+          <t>5 okt</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>187.82</v>
+        <v>185.06</v>
       </c>
       <c r="M51" t="n">
-        <v>188.74</v>
+        <v>188.5</v>
       </c>
       <c r="N51" t="n">
-        <v>183.92</v>
+        <v>184.66</v>
       </c>
       <c r="O51" t="n">
-        <v>183.92</v>
+        <v>185.04</v>
       </c>
       <c r="P51" t="n">
-        <v>179.844</v>
+        <v>180.5192</v>
       </c>
       <c r="Q51" t="n">
-        <v>164.4442</v>
+        <v>164.3515</v>
       </c>
       <c r="R51" t="n">
         <v>191.5557367172241</v>
@@ -7846,26 +7868,26 @@
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>2 okt</t>
+          <t>5 okt</t>
         </is>
       </c>
       <c r="V51" t="n">
-        <v>519.39</v>
+        <v>521.62</v>
       </c>
       <c r="W51" t="n">
-        <v>522.5</v>
+        <v>532.35</v>
       </c>
       <c r="X51" t="n">
-        <v>513.66</v>
+        <v>521.47</v>
       </c>
       <c r="Y51" t="n">
-        <v>517.53</v>
+        <v>525.1799999999999</v>
       </c>
       <c r="Z51" t="n">
-        <v>487.3905</v>
+        <v>490.2745</v>
       </c>
       <c r="AA51" t="n">
-        <v>431.4557</v>
+        <v>431.7147</v>
       </c>
       <c r="AB51" t="n">
         <v>535.3375423278808</v>
@@ -7877,26 +7899,26 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>5 okt</t>
+          <t>6 okt</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>42.645</v>
+        <v>42.86</v>
       </c>
       <c r="C52" t="n">
-        <v>43.11</v>
+        <v>43.285</v>
       </c>
       <c r="D52" t="n">
-        <v>42.35</v>
+        <v>42.43</v>
       </c>
       <c r="E52" t="n">
-        <v>42.865</v>
+        <v>43.185</v>
       </c>
       <c r="F52" t="n">
-        <v>40.2347</v>
+        <v>40.349</v>
       </c>
       <c r="G52" t="n">
-        <v>36.3069</v>
+        <v>36.3726</v>
       </c>
       <c r="H52" t="n">
         <v>45.05751734733581</v>
@@ -7906,26 +7928,26 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>5 okt</t>
+          <t>6 okt</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>185.06</v>
+        <v>186.56</v>
       </c>
       <c r="M52" t="n">
-        <v>188.5</v>
+        <v>190.22</v>
       </c>
       <c r="N52" t="n">
-        <v>184.66</v>
+        <v>186.06</v>
       </c>
       <c r="O52" t="n">
-        <v>185.04</v>
+        <v>188.6</v>
       </c>
       <c r="P52" t="n">
-        <v>180.5192</v>
+        <v>181.1064</v>
       </c>
       <c r="Q52" t="n">
-        <v>164.3515</v>
+        <v>164.2647</v>
       </c>
       <c r="R52" t="n">
         <v>191.5557367172241</v>
@@ -7935,26 +7957,26 @@
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>5 okt</t>
+          <t>6 okt</t>
         </is>
       </c>
       <c r="V52" t="n">
-        <v>521.62</v>
+        <v>531.6799999999999</v>
       </c>
       <c r="W52" t="n">
-        <v>532.35</v>
+        <v>535.6900000000001</v>
       </c>
       <c r="X52" t="n">
-        <v>521.47</v>
+        <v>528.78</v>
       </c>
       <c r="Y52" t="n">
-        <v>525.1799999999999</v>
+        <v>529.3</v>
       </c>
       <c r="Z52" t="n">
-        <v>490.2745</v>
+        <v>493.0931</v>
       </c>
       <c r="AA52" t="n">
-        <v>431.7147</v>
+        <v>431.9956</v>
       </c>
       <c r="AB52" t="n">
         <v>535.3375423278808</v>
@@ -7966,26 +7988,26 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>6 okt</t>
+          <t>7 okt</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>42.86</v>
+        <v>43.37</v>
       </c>
       <c r="C53" t="n">
-        <v>43.285</v>
+        <v>43.835</v>
       </c>
       <c r="D53" t="n">
-        <v>42.43</v>
+        <v>43.145</v>
       </c>
       <c r="E53" t="n">
-        <v>43.185</v>
+        <v>43.25</v>
       </c>
       <c r="F53" t="n">
-        <v>40.349</v>
+        <v>40.4451</v>
       </c>
       <c r="G53" t="n">
-        <v>36.3726</v>
+        <v>36.4388</v>
       </c>
       <c r="H53" t="n">
         <v>45.05751734733581</v>
@@ -7995,26 +8017,26 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>6 okt</t>
+          <t>7 okt</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>186.56</v>
+        <v>187</v>
       </c>
       <c r="M53" t="n">
-        <v>190.22</v>
+        <v>188.72</v>
       </c>
       <c r="N53" t="n">
-        <v>186.06</v>
+        <v>186.04</v>
       </c>
       <c r="O53" t="n">
-        <v>188.6</v>
+        <v>187.62</v>
       </c>
       <c r="P53" t="n">
-        <v>181.1064</v>
+        <v>181.618</v>
       </c>
       <c r="Q53" t="n">
-        <v>164.2647</v>
+        <v>164.1762</v>
       </c>
       <c r="R53" t="n">
         <v>191.5557367172241</v>
@@ -8024,26 +8046,26 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>6 okt</t>
+          <t>7 okt</t>
         </is>
       </c>
       <c r="V53" t="n">
-        <v>531.6799999999999</v>
+        <v>530.73</v>
       </c>
       <c r="W53" t="n">
-        <v>535.6900000000001</v>
+        <v>531.73</v>
       </c>
       <c r="X53" t="n">
-        <v>528.78</v>
+        <v>524.6900000000001</v>
       </c>
       <c r="Y53" t="n">
-        <v>529.3</v>
+        <v>529.76</v>
       </c>
       <c r="Z53" t="n">
-        <v>493.0931</v>
+        <v>495.8361</v>
       </c>
       <c r="AA53" t="n">
-        <v>431.9956</v>
+        <v>432.2398</v>
       </c>
       <c r="AB53" t="n">
         <v>535.3375423278808</v>
@@ -8055,26 +8077,26 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>7 okt</t>
+          <t>8 okt</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>43.37</v>
+        <v>43.555</v>
       </c>
       <c r="C54" t="n">
-        <v>43.835</v>
+        <v>44.815</v>
       </c>
       <c r="D54" t="n">
-        <v>43.145</v>
+        <v>43.5425</v>
       </c>
       <c r="E54" t="n">
-        <v>43.25</v>
+        <v>44.75</v>
       </c>
       <c r="F54" t="n">
-        <v>40.4451</v>
+        <v>40.5699</v>
       </c>
       <c r="G54" t="n">
-        <v>36.4388</v>
+        <v>36.5123</v>
       </c>
       <c r="H54" t="n">
         <v>45.05751734733581</v>
@@ -8084,26 +8106,26 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>7 okt</t>
+          <t>8 okt</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>187</v>
+        <v>187.04</v>
       </c>
       <c r="M54" t="n">
-        <v>188.72</v>
+        <v>189.82</v>
       </c>
       <c r="N54" t="n">
-        <v>186.04</v>
+        <v>183.76</v>
       </c>
       <c r="O54" t="n">
-        <v>187.62</v>
+        <v>184.62</v>
       </c>
       <c r="P54" t="n">
-        <v>181.618</v>
+        <v>182.192</v>
       </c>
       <c r="Q54" t="n">
-        <v>164.1762</v>
+        <v>164.074</v>
       </c>
       <c r="R54" t="n">
         <v>191.5557367172241</v>
@@ -8113,26 +8135,26 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>7 okt</t>
+          <t>8 okt</t>
         </is>
       </c>
       <c r="V54" t="n">
-        <v>530.73</v>
+        <v>529.8099999999999</v>
       </c>
       <c r="W54" t="n">
-        <v>531.73</v>
+        <v>533.51</v>
       </c>
       <c r="X54" t="n">
-        <v>524.6900000000001</v>
+        <v>518.79</v>
       </c>
       <c r="Y54" t="n">
-        <v>529.76</v>
+        <v>522.61</v>
       </c>
       <c r="Z54" t="n">
-        <v>495.8361</v>
+        <v>498.4921</v>
       </c>
       <c r="AA54" t="n">
-        <v>432.2398</v>
+        <v>432.4385</v>
       </c>
       <c r="AB54" t="n">
         <v>535.3375423278808</v>
@@ -8144,26 +8166,26 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>8 okt</t>
+          <t>9 okt</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>43.555</v>
+        <v>44.42</v>
       </c>
       <c r="C55" t="n">
-        <v>44.815</v>
+        <v>45.155</v>
       </c>
       <c r="D55" t="n">
-        <v>43.5425</v>
+        <v>43.94</v>
       </c>
       <c r="E55" t="n">
-        <v>44.75</v>
+        <v>45.035</v>
       </c>
       <c r="F55" t="n">
-        <v>40.5699</v>
+        <v>40.6842</v>
       </c>
       <c r="G55" t="n">
-        <v>36.5123</v>
+        <v>36.5866</v>
       </c>
       <c r="H55" t="n">
         <v>45.05751734733581</v>
@@ -8173,26 +8195,26 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>8 okt</t>
+          <t>9 okt</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>187.04</v>
+        <v>188.98</v>
       </c>
       <c r="M55" t="n">
-        <v>189.82</v>
+        <v>192.58</v>
       </c>
       <c r="N55" t="n">
-        <v>183.76</v>
+        <v>188.86</v>
       </c>
       <c r="O55" t="n">
-        <v>184.62</v>
+        <v>191.46</v>
       </c>
       <c r="P55" t="n">
-        <v>182.192</v>
+        <v>182.8676</v>
       </c>
       <c r="Q55" t="n">
-        <v>164.074</v>
+        <v>164.0101</v>
       </c>
       <c r="R55" t="n">
         <v>191.5557367172241</v>
@@ -8202,26 +8224,26 @@
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>8 okt</t>
+          <t>9 okt</t>
         </is>
       </c>
       <c r="V55" t="n">
-        <v>529.8099999999999</v>
+        <v>528.24</v>
       </c>
       <c r="W55" t="n">
-        <v>533.51</v>
+        <v>537.22</v>
       </c>
       <c r="X55" t="n">
-        <v>518.79</v>
+        <v>526.24</v>
       </c>
       <c r="Y55" t="n">
-        <v>522.61</v>
+        <v>535.0700000000001</v>
       </c>
       <c r="Z55" t="n">
-        <v>498.4921</v>
+        <v>500.1885</v>
       </c>
       <c r="AA55" t="n">
-        <v>432.4385</v>
+        <v>432.7046</v>
       </c>
       <c r="AB55" t="n">
         <v>535.3375423278808</v>
@@ -8233,26 +8255,26 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>9 okt</t>
+          <t>12 okt</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>44.42</v>
+        <v>44.725</v>
       </c>
       <c r="C56" t="n">
-        <v>45.155</v>
+        <v>45.81</v>
       </c>
       <c r="D56" t="n">
-        <v>43.94</v>
+        <v>44.695</v>
       </c>
       <c r="E56" t="n">
-        <v>45.035</v>
+        <v>45.56</v>
       </c>
       <c r="F56" t="n">
-        <v>40.6842</v>
+        <v>40.8072</v>
       </c>
       <c r="G56" t="n">
-        <v>36.5866</v>
+        <v>36.6625</v>
       </c>
       <c r="H56" t="n">
         <v>45.05751734733581</v>
@@ -8262,26 +8284,26 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>9 okt</t>
+          <t>12 okt</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>188.98</v>
+        <v>190.58</v>
       </c>
       <c r="M56" t="n">
-        <v>192.58</v>
+        <v>197.88</v>
       </c>
       <c r="N56" t="n">
-        <v>188.86</v>
+        <v>189.78</v>
       </c>
       <c r="O56" t="n">
-        <v>191.46</v>
+        <v>194.46</v>
       </c>
       <c r="P56" t="n">
-        <v>182.8676</v>
+        <v>183.464</v>
       </c>
       <c r="Q56" t="n">
-        <v>164.0101</v>
+        <v>163.9576</v>
       </c>
       <c r="R56" t="n">
         <v>191.5557367172241</v>
@@ -8291,26 +8313,26 @@
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>9 okt</t>
+          <t>12 okt</t>
         </is>
       </c>
       <c r="V56" t="n">
-        <v>528.24</v>
+        <v>537.53</v>
       </c>
       <c r="W56" t="n">
-        <v>537.22</v>
+        <v>542.74</v>
       </c>
       <c r="X56" t="n">
-        <v>526.24</v>
+        <v>535.7</v>
       </c>
       <c r="Y56" t="n">
-        <v>535.0700000000001</v>
+        <v>541.15</v>
       </c>
       <c r="Z56" t="n">
-        <v>500.1885</v>
+        <v>501.7346</v>
       </c>
       <c r="AA56" t="n">
-        <v>432.7046</v>
+        <v>432.9914</v>
       </c>
       <c r="AB56" t="n">
         <v>535.3375423278808</v>
@@ -8322,26 +8344,26 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>12 okt</t>
+          <t>13 okt</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>44.725</v>
+        <v>45.69</v>
       </c>
       <c r="C57" t="n">
-        <v>45.81</v>
+        <v>45.97</v>
       </c>
       <c r="D57" t="n">
-        <v>44.695</v>
+        <v>45.35</v>
       </c>
       <c r="E57" t="n">
-        <v>45.56</v>
+        <v>45.95</v>
       </c>
       <c r="F57" t="n">
-        <v>40.8072</v>
+        <v>40.9565</v>
       </c>
       <c r="G57" t="n">
-        <v>36.6625</v>
+        <v>36.7398</v>
       </c>
       <c r="H57" t="n">
         <v>45.05751734733581</v>
@@ -8351,26 +8373,26 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>12 okt</t>
+          <t>13 okt</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>190.58</v>
+        <v>196</v>
       </c>
       <c r="M57" t="n">
-        <v>197.88</v>
+        <v>198.18</v>
       </c>
       <c r="N57" t="n">
-        <v>189.78</v>
+        <v>194.02</v>
       </c>
       <c r="O57" t="n">
-        <v>194.46</v>
+        <v>197.28</v>
       </c>
       <c r="P57" t="n">
-        <v>183.464</v>
+        <v>184.062</v>
       </c>
       <c r="Q57" t="n">
-        <v>163.9576</v>
+        <v>163.9196</v>
       </c>
       <c r="R57" t="n">
         <v>191.5557367172241</v>
@@ -8380,26 +8402,26 @@
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>12 okt</t>
+          <t>13 okt</t>
         </is>
       </c>
       <c r="V57" t="n">
-        <v>537.53</v>
+        <v>544.64</v>
       </c>
       <c r="W57" t="n">
-        <v>542.74</v>
+        <v>551.15</v>
       </c>
       <c r="X57" t="n">
-        <v>535.7</v>
+        <v>543.0599999999999</v>
       </c>
       <c r="Y57" t="n">
-        <v>541.15</v>
+        <v>543.45</v>
       </c>
       <c r="Z57" t="n">
-        <v>501.7346</v>
+        <v>502.8689</v>
       </c>
       <c r="AA57" t="n">
-        <v>432.9914</v>
+        <v>433.2839</v>
       </c>
       <c r="AB57" t="n">
         <v>535.3375423278808</v>
@@ -8411,26 +8433,26 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>13 okt</t>
+          <t>14 okt</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>45.69</v>
+        <v>45.95</v>
       </c>
       <c r="C58" t="n">
-        <v>45.97</v>
+        <v>46.675</v>
       </c>
       <c r="D58" t="n">
-        <v>45.35</v>
+        <v>45.91</v>
       </c>
       <c r="E58" t="n">
-        <v>45.95</v>
+        <v>46.455</v>
       </c>
       <c r="F58" t="n">
-        <v>40.9565</v>
+        <v>41.125</v>
       </c>
       <c r="G58" t="n">
-        <v>36.7398</v>
+        <v>36.8183</v>
       </c>
       <c r="H58" t="n">
         <v>45.05751734733581</v>
@@ -8440,26 +8462,26 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>13 okt</t>
+          <t>14 okt</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>196</v>
+        <v>196.6</v>
       </c>
       <c r="M58" t="n">
-        <v>198.18</v>
+        <v>199.36</v>
       </c>
       <c r="N58" t="n">
-        <v>194.02</v>
+        <v>195.26</v>
       </c>
       <c r="O58" t="n">
-        <v>197.28</v>
+        <v>196.94</v>
       </c>
       <c r="P58" t="n">
-        <v>184.062</v>
+        <v>184.6156</v>
       </c>
       <c r="Q58" t="n">
-        <v>163.9196</v>
+        <v>163.9114</v>
       </c>
       <c r="R58" t="n">
         <v>191.5557367172241</v>
@@ -8469,26 +8491,26 @@
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>13 okt</t>
+          <t>14 okt</t>
         </is>
       </c>
       <c r="V58" t="n">
-        <v>544.64</v>
+        <v>545.27</v>
       </c>
       <c r="W58" t="n">
-        <v>551.15</v>
+        <v>545.75</v>
       </c>
       <c r="X58" t="n">
-        <v>543.0599999999999</v>
+        <v>532.54</v>
       </c>
       <c r="Y58" t="n">
-        <v>543.45</v>
+        <v>533.6900000000001</v>
       </c>
       <c r="Z58" t="n">
-        <v>502.8689</v>
+        <v>503.705</v>
       </c>
       <c r="AA58" t="n">
-        <v>433.2839</v>
+        <v>433.5292</v>
       </c>
       <c r="AB58" t="n">
         <v>535.3375423278808</v>
@@ -8500,26 +8522,26 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>14 okt</t>
+          <t>15 okt</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>45.95</v>
+        <v>46.295</v>
       </c>
       <c r="C59" t="n">
-        <v>46.675</v>
+        <v>46.735</v>
       </c>
       <c r="D59" t="n">
-        <v>45.91</v>
+        <v>46.125</v>
       </c>
       <c r="E59" t="n">
-        <v>46.455</v>
+        <v>46.375</v>
       </c>
       <c r="F59" t="n">
-        <v>41.125</v>
+        <v>41.2847</v>
       </c>
       <c r="G59" t="n">
-        <v>36.8183</v>
+        <v>36.8966</v>
       </c>
       <c r="H59" t="n">
         <v>45.05751734733581</v>
@@ -8529,26 +8551,26 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>14 okt</t>
+          <t>15 okt</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>196.6</v>
+        <v>199.48</v>
       </c>
       <c r="M59" t="n">
-        <v>199.36</v>
+        <v>203</v>
       </c>
       <c r="N59" t="n">
-        <v>195.26</v>
+        <v>196.98</v>
       </c>
       <c r="O59" t="n">
-        <v>196.94</v>
+        <v>201.25</v>
       </c>
       <c r="P59" t="n">
-        <v>184.6156</v>
+        <v>185.221</v>
       </c>
       <c r="Q59" t="n">
-        <v>163.9114</v>
+        <v>163.9038</v>
       </c>
       <c r="R59" t="n">
         <v>191.5557367172241</v>
@@ -8558,26 +8580,26 @@
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>14 okt</t>
+          <t>15 okt</t>
         </is>
       </c>
       <c r="V59" t="n">
-        <v>545.27</v>
+        <v>533.3200000000001</v>
       </c>
       <c r="W59" t="n">
-        <v>545.75</v>
+        <v>541.13</v>
       </c>
       <c r="X59" t="n">
-        <v>532.54</v>
+        <v>531.22</v>
       </c>
       <c r="Y59" t="n">
-        <v>533.6900000000001</v>
+        <v>539.4400000000001</v>
       </c>
       <c r="Z59" t="n">
-        <v>503.705</v>
+        <v>504.7629</v>
       </c>
       <c r="AA59" t="n">
-        <v>433.5292</v>
+        <v>433.8063</v>
       </c>
       <c r="AB59" t="n">
         <v>535.3375423278808</v>
@@ -8589,26 +8611,26 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>15 okt</t>
+          <t>16 okt</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>46.295</v>
+        <v>46.14</v>
       </c>
       <c r="C60" t="n">
-        <v>46.735</v>
+        <v>47.025</v>
       </c>
       <c r="D60" t="n">
-        <v>46.125</v>
+        <v>46.075</v>
       </c>
       <c r="E60" t="n">
-        <v>46.375</v>
+        <v>46.88</v>
       </c>
       <c r="F60" t="n">
-        <v>41.2847</v>
+        <v>41.4622</v>
       </c>
       <c r="G60" t="n">
-        <v>36.8966</v>
+        <v>36.977</v>
       </c>
       <c r="H60" t="n">
         <v>45.05751734733581</v>
@@ -8618,26 +8640,26 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>15 okt</t>
+          <t>16 okt</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>199.48</v>
+        <v>200.6</v>
       </c>
       <c r="M60" t="n">
-        <v>203</v>
+        <v>204.2</v>
       </c>
       <c r="N60" t="n">
-        <v>196.98</v>
+        <v>198.68</v>
       </c>
       <c r="O60" t="n">
-        <v>201.25</v>
+        <v>199.22</v>
       </c>
       <c r="P60" t="n">
-        <v>185.221</v>
+        <v>185.6462</v>
       </c>
       <c r="Q60" t="n">
-        <v>163.9038</v>
+        <v>163.9066</v>
       </c>
       <c r="R60" t="n">
         <v>191.5557367172241</v>
@@ -8647,26 +8669,26 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>15 okt</t>
+          <t>16 okt</t>
         </is>
       </c>
       <c r="V60" t="n">
-        <v>533.3200000000001</v>
+        <v>541.3099999999999</v>
       </c>
       <c r="W60" t="n">
-        <v>541.13</v>
+        <v>543.8200000000001</v>
       </c>
       <c r="X60" t="n">
-        <v>531.22</v>
+        <v>524.4299999999999</v>
       </c>
       <c r="Y60" t="n">
-        <v>539.4400000000001</v>
+        <v>529.05</v>
       </c>
       <c r="Z60" t="n">
-        <v>504.7629</v>
+        <v>505.3655</v>
       </c>
       <c r="AA60" t="n">
-        <v>433.8063</v>
+        <v>434.0295</v>
       </c>
       <c r="AB60" t="n">
         <v>535.3375423278808</v>
@@ -8678,26 +8700,26 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>16 okt</t>
+          <t>19 okt</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>46.14</v>
+        <v>47.37</v>
       </c>
       <c r="C61" t="n">
-        <v>47.025</v>
+        <v>47.45</v>
       </c>
       <c r="D61" t="n">
-        <v>46.075</v>
+        <v>46.74</v>
       </c>
       <c r="E61" t="n">
-        <v>46.88</v>
+        <v>46.86</v>
       </c>
       <c r="F61" t="n">
-        <v>41.4622</v>
+        <v>41.6313</v>
       </c>
       <c r="G61" t="n">
-        <v>36.977</v>
+        <v>37.0625</v>
       </c>
       <c r="H61" t="n">
         <v>45.05751734733581</v>
@@ -8707,26 +8729,26 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>16 okt</t>
+          <t>19 okt</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>200.6</v>
+        <v>199.56</v>
       </c>
       <c r="M61" t="n">
-        <v>204.2</v>
+        <v>200.8</v>
       </c>
       <c r="N61" t="n">
-        <v>198.68</v>
+        <v>197.32</v>
       </c>
       <c r="O61" t="n">
-        <v>199.22</v>
+        <v>199.84</v>
       </c>
       <c r="P61" t="n">
-        <v>185.6462</v>
+        <v>186.057</v>
       </c>
       <c r="Q61" t="n">
-        <v>163.9066</v>
+        <v>163.8811</v>
       </c>
       <c r="R61" t="n">
         <v>191.5557367172241</v>
@@ -8736,26 +8758,26 @@
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>16 okt</t>
+          <t>19 okt</t>
         </is>
       </c>
       <c r="V61" t="n">
-        <v>541.3099999999999</v>
+        <v>528.7</v>
       </c>
       <c r="W61" t="n">
-        <v>543.8200000000001</v>
+        <v>535.5700000000001</v>
       </c>
       <c r="X61" t="n">
-        <v>524.4299999999999</v>
+        <v>528.0599999999999</v>
       </c>
       <c r="Y61" t="n">
-        <v>529.05</v>
+        <v>533.52</v>
       </c>
       <c r="Z61" t="n">
-        <v>505.3655</v>
+        <v>506.0549</v>
       </c>
       <c r="AA61" t="n">
-        <v>434.0295</v>
+        <v>434.2942</v>
       </c>
       <c r="AB61" t="n">
         <v>535.3375423278808</v>
@@ -8767,26 +8789,26 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>19 okt</t>
+          <t>20 okt</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>47.37</v>
+        <v>46.875</v>
       </c>
       <c r="C62" t="n">
-        <v>47.45</v>
+        <v>47.505</v>
       </c>
       <c r="D62" t="n">
-        <v>46.74</v>
+        <v>46.36</v>
       </c>
       <c r="E62" t="n">
-        <v>46.86</v>
+        <v>46.57</v>
       </c>
       <c r="F62" t="n">
-        <v>41.6313</v>
+        <v>41.7834</v>
       </c>
       <c r="G62" t="n">
-        <v>37.0625</v>
+        <v>37.1516</v>
       </c>
       <c r="H62" t="n">
         <v>45.05751734733581</v>
@@ -8796,26 +8818,26 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>19 okt</t>
+          <t>20 okt</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>199.56</v>
+        <v>201.3</v>
       </c>
       <c r="M62" t="n">
-        <v>200.8</v>
+        <v>203.45</v>
       </c>
       <c r="N62" t="n">
-        <v>197.32</v>
+        <v>199.46</v>
       </c>
       <c r="O62" t="n">
-        <v>199.84</v>
+        <v>201.55</v>
       </c>
       <c r="P62" t="n">
-        <v>186.057</v>
+        <v>186.474</v>
       </c>
       <c r="Q62" t="n">
-        <v>163.8811</v>
+        <v>163.8736</v>
       </c>
       <c r="R62" t="n">
         <v>191.5557367172241</v>
@@ -8825,26 +8847,26 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>19 okt</t>
+          <t>20 okt</t>
         </is>
       </c>
       <c r="V62" t="n">
-        <v>528.7</v>
+        <v>533.91</v>
       </c>
       <c r="W62" t="n">
-        <v>535.5700000000001</v>
+        <v>534.21</v>
       </c>
       <c r="X62" t="n">
-        <v>528.0599999999999</v>
+        <v>525.84</v>
       </c>
       <c r="Y62" t="n">
-        <v>533.52</v>
+        <v>531.87</v>
       </c>
       <c r="Z62" t="n">
-        <v>506.0549</v>
+        <v>506.5901</v>
       </c>
       <c r="AA62" t="n">
-        <v>434.2942</v>
+        <v>434.6038</v>
       </c>
       <c r="AB62" t="n">
         <v>535.3375423278808</v>
@@ -8856,26 +8878,26 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20 okt</t>
+          <t>21 okt</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>46.875</v>
+        <v>46.97</v>
       </c>
       <c r="C63" t="n">
-        <v>47.505</v>
+        <v>47.135</v>
       </c>
       <c r="D63" t="n">
-        <v>46.36</v>
+        <v>46.73</v>
       </c>
       <c r="E63" t="n">
-        <v>46.57</v>
+        <v>46.84</v>
       </c>
       <c r="F63" t="n">
-        <v>41.7834</v>
+        <v>41.9472</v>
       </c>
       <c r="G63" t="n">
-        <v>37.1516</v>
+        <v>37.2379</v>
       </c>
       <c r="H63" t="n">
         <v>45.05751734733581</v>
@@ -8885,26 +8907,26 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>20 okt</t>
+          <t>21 okt</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>201.3</v>
+        <v>201.8</v>
       </c>
       <c r="M63" t="n">
-        <v>203.45</v>
+        <v>208.65</v>
       </c>
       <c r="N63" t="n">
-        <v>199.46</v>
+        <v>200</v>
       </c>
       <c r="O63" t="n">
-        <v>201.55</v>
+        <v>208.65</v>
       </c>
       <c r="P63" t="n">
-        <v>186.474</v>
+        <v>187.1278</v>
       </c>
       <c r="Q63" t="n">
-        <v>163.8736</v>
+        <v>163.8728</v>
       </c>
       <c r="R63" t="n">
         <v>191.5557367172241</v>
@@ -8914,26 +8936,26 @@
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>20 okt</t>
+          <t>21 okt</t>
         </is>
       </c>
       <c r="V63" t="n">
-        <v>533.91</v>
+        <v>529.4400000000001</v>
       </c>
       <c r="W63" t="n">
-        <v>534.21</v>
+        <v>533.28</v>
       </c>
       <c r="X63" t="n">
-        <v>525.84</v>
+        <v>525.02</v>
       </c>
       <c r="Y63" t="n">
-        <v>531.87</v>
+        <v>532.95</v>
       </c>
       <c r="Z63" t="n">
-        <v>506.5901</v>
+        <v>507.1919</v>
       </c>
       <c r="AA63" t="n">
-        <v>434.6038</v>
+        <v>434.9192</v>
       </c>
       <c r="AB63" t="n">
         <v>535.3375423278808</v>
@@ -8945,26 +8967,26 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>21 okt</t>
+          <t>22 okt</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>46.97</v>
+        <v>47.05</v>
       </c>
       <c r="C64" t="n">
-        <v>47.135</v>
+        <v>47.6</v>
       </c>
       <c r="D64" t="n">
-        <v>46.73</v>
+        <v>46.55</v>
       </c>
       <c r="E64" t="n">
-        <v>46.84</v>
+        <v>46.55</v>
       </c>
       <c r="F64" t="n">
-        <v>41.9472</v>
+        <v>42.1061</v>
       </c>
       <c r="G64" t="n">
-        <v>37.2379</v>
+        <v>37.3217</v>
       </c>
       <c r="H64" t="n">
         <v>45.05751734733581</v>
@@ -8974,26 +8996,26 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>21 okt</t>
+          <t>22 okt</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>201.8</v>
+        <v>207.75</v>
       </c>
       <c r="M64" t="n">
-        <v>208.65</v>
+        <v>216.65</v>
       </c>
       <c r="N64" t="n">
-        <v>200</v>
+        <v>205.1</v>
       </c>
       <c r="O64" t="n">
-        <v>208.65</v>
+        <v>215.35</v>
       </c>
       <c r="P64" t="n">
-        <v>187.1278</v>
+        <v>187.9272</v>
       </c>
       <c r="Q64" t="n">
-        <v>163.8728</v>
+        <v>163.9019</v>
       </c>
       <c r="R64" t="n">
         <v>191.5557367172241</v>
@@ -9003,26 +9025,26 @@
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>21 okt</t>
+          <t>22 okt</t>
         </is>
       </c>
       <c r="V64" t="n">
-        <v>529.4400000000001</v>
+        <v>533.14</v>
       </c>
       <c r="W64" t="n">
-        <v>533.28</v>
+        <v>533.6</v>
       </c>
       <c r="X64" t="n">
-        <v>525.02</v>
+        <v>520.3</v>
       </c>
       <c r="Y64" t="n">
-        <v>532.95</v>
+        <v>521.08</v>
       </c>
       <c r="Z64" t="n">
-        <v>507.1919</v>
+        <v>507.7834</v>
       </c>
       <c r="AA64" t="n">
-        <v>434.9192</v>
+        <v>435.1471</v>
       </c>
       <c r="AB64" t="n">
         <v>535.3375423278808</v>
@@ -9034,26 +9056,26 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>22 okt</t>
+          <t>23 okt</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>47.05</v>
+        <v>47.13</v>
       </c>
       <c r="C65" t="n">
-        <v>47.6</v>
+        <v>48.38</v>
       </c>
       <c r="D65" t="n">
-        <v>46.55</v>
+        <v>46.895</v>
       </c>
       <c r="E65" t="n">
-        <v>46.55</v>
+        <v>48.295</v>
       </c>
       <c r="F65" t="n">
-        <v>42.1061</v>
+        <v>42.2926</v>
       </c>
       <c r="G65" t="n">
-        <v>37.3217</v>
+        <v>37.4107</v>
       </c>
       <c r="H65" t="n">
         <v>45.05751734733581</v>
@@ -9063,26 +9085,26 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>22 okt</t>
+          <t>23 okt</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>207.75</v>
+        <v>213.55</v>
       </c>
       <c r="M65" t="n">
-        <v>216.65</v>
+        <v>215.85</v>
       </c>
       <c r="N65" t="n">
-        <v>205.1</v>
+        <v>210.05</v>
       </c>
       <c r="O65" t="n">
-        <v>215.35</v>
+        <v>214.4</v>
       </c>
       <c r="P65" t="n">
-        <v>187.9272</v>
+        <v>188.6124</v>
       </c>
       <c r="Q65" t="n">
-        <v>163.9019</v>
+        <v>163.9244</v>
       </c>
       <c r="R65" t="n">
         <v>191.5557367172241</v>
@@ -9092,26 +9114,26 @@
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>22 okt</t>
+          <t>23 okt</t>
         </is>
       </c>
       <c r="V65" t="n">
-        <v>533.14</v>
+        <v>517.75</v>
       </c>
       <c r="W65" t="n">
-        <v>533.6</v>
+        <v>525.77</v>
       </c>
       <c r="X65" t="n">
-        <v>520.3</v>
+        <v>515.7</v>
       </c>
       <c r="Y65" t="n">
-        <v>521.08</v>
+        <v>524.51</v>
       </c>
       <c r="Z65" t="n">
-        <v>507.7834</v>
+        <v>508.3546</v>
       </c>
       <c r="AA65" t="n">
-        <v>435.1471</v>
+        <v>435.3676</v>
       </c>
       <c r="AB65" t="n">
         <v>535.3375423278808</v>
@@ -9123,26 +9145,26 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>23 okt</t>
+          <t>26 okt</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>47.13</v>
+        <v>48</v>
       </c>
       <c r="C66" t="n">
-        <v>48.38</v>
+        <v>48.21</v>
       </c>
       <c r="D66" t="n">
-        <v>46.895</v>
+        <v>47.37</v>
       </c>
       <c r="E66" t="n">
-        <v>48.345</v>
+        <v>47.955</v>
       </c>
       <c r="F66" t="n">
-        <v>42.2936</v>
+        <v>42.4687</v>
       </c>
       <c r="G66" t="n">
-        <v>37.411</v>
+        <v>37.497</v>
       </c>
       <c r="H66" t="n">
         <v>45.05751734733581</v>
@@ -9152,26 +9174,26 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>23 okt</t>
+          <t>26 okt</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>213.55</v>
+        <v>213.5</v>
       </c>
       <c r="M66" t="n">
-        <v>215.85</v>
+        <v>216.55</v>
       </c>
       <c r="N66" t="n">
-        <v>210.05</v>
+        <v>212.45</v>
       </c>
       <c r="O66" t="n">
-        <v>214.35</v>
+        <v>212.8</v>
       </c>
       <c r="P66" t="n">
-        <v>188.6114</v>
+        <v>189.2768</v>
       </c>
       <c r="Q66" t="n">
-        <v>163.9242</v>
+        <v>163.9751</v>
       </c>
       <c r="R66" t="n">
         <v>191.5557367172241</v>
@@ -9181,26 +9203,26 @@
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>23 okt</t>
+          <t>26 okt</t>
         </is>
       </c>
       <c r="V66" t="n">
-        <v>517.995</v>
+        <v>527.41</v>
       </c>
       <c r="W66" t="n">
-        <v>525.77</v>
+        <v>533.25</v>
       </c>
       <c r="X66" t="n">
-        <v>515.7</v>
+        <v>521.6900000000001</v>
       </c>
       <c r="Y66" t="n">
-        <v>524.525</v>
+        <v>532.75</v>
       </c>
       <c r="Z66" t="n">
-        <v>508.3549</v>
+        <v>509.1203</v>
       </c>
       <c r="AA66" t="n">
-        <v>435.3676</v>
+        <v>435.6558</v>
       </c>
       <c r="AB66" t="n">
         <v>535.3375423278808</v>

--- a/rapporten/trend-agent.xlsx
+++ b/rapporten/trend-agent.xlsx
@@ -1944,7 +1944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2234,6 +2234,28 @@
       </c>
       <c r="E13" s="3">
         <f>B13/$B$2-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>10067.25</v>
+      </c>
+      <c r="C14" s="2">
+        <f>B14-B13</f>
+        <v/>
+      </c>
+      <c r="D14" s="3">
+        <f>B14/B13-1</f>
+        <v/>
+      </c>
+      <c r="E14" s="3">
+        <f>B14/$B$2-1</f>
         <v/>
       </c>
     </row>
@@ -2377,38 +2399,38 @@
     <row r="6" ht="22" customHeight="1">
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Shell (SHELL.AS)  ·  47,96 EUR</t>
+          <t>Shell (SHELL.AS)  ·  47,13 EUR</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>SAP (SAP.DE)  ·  212,80 EUR</t>
+          <t>SAP (SAP.DE)  ·  213,20 EUR</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>Gestegen: 28,0% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +6,4% (winst). De bot verkoopt als de koers onder 45,41 zakt (-5,3%).</t>
+          <t>Gestegen: 22,6% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +4,6% (winst). De bot verkoopt als de koers onder 45,41 zakt (-3,6%).</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>Gestegen: 33,6% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +11,1% (winst). De bot verkoopt als de koers onder 198,88 zakt (-6,5%).</t>
+          <t>Gestegen: 31,6% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +11,3% (winst). De bot verkoopt als de koers onder 198,88 zakt (-6,7%).</t>
         </is>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Microsoft (MSFT)  ·  532,75 USD</t>
+          <t>Microsoft (MSFT)  ·  531,60 USD</t>
         </is>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Gestegen: 37,2% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: -0,5% (verlies). De bot verkoopt als de koers onder 510,33 zakt (-4,2%).</t>
+          <t>Gestegen: 35,4% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: -0,7% (verlies). De bot verkoopt als de koers onder 510,33 zakt (-4,0%).</t>
         </is>
       </c>
     </row>
@@ -2873,12 +2895,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SHELL.AS</t>
+          <t>SAP.DE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Shell</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -2887,19 +2909,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.175</v>
+        <v>0.15</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.2474799321915424</v>
+        <v>0.3673678774497662</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1401569249949459</v>
+        <v>0.1585696771997527</v>
       </c>
       <c r="H2" t="n">
-        <v>0.97</v>
+        <v>0.89</v>
       </c>
       <c r="I2" t="n">
-        <v>47.96</v>
+        <v>213.2</v>
       </c>
     </row>
     <row r="3">
@@ -2908,33 +2930,33 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>XLE</t>
+          <t>SHELL.AS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Energie-ETF</t>
+          <t>Shell</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.137</v>
+        <v>0.146</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.216848042537038</v>
+        <v>0.2238124662221594</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.1225015854604696</v>
+        <v>0.1031012931846513</v>
       </c>
       <c r="H3" t="n">
-        <v>1.04</v>
+        <v>0.98</v>
       </c>
       <c r="I3" t="n">
-        <v>69.64</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="4">
@@ -2943,33 +2965,33 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>WKL.AS</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>Wolters Kluwer</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.125</v>
+        <v>0.138</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.2137022353203739</v>
+        <v>0.2693332961237478</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.1491998708528142</v>
+        <v>0.2753407421066918</v>
       </c>
       <c r="H4" t="n">
-        <v>0.84</v>
+        <v>0.89</v>
       </c>
       <c r="I4" t="n">
-        <v>184.55</v>
+        <v>86.06</v>
       </c>
     </row>
     <row r="5">
@@ -2978,33 +3000,33 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SAP.DE</t>
+          <t>XLE</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Energie-ETF</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.125</v>
+        <v>0.108</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.3132560594222698</v>
+        <v>0.170256828460907</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.1445783409398846</v>
+        <v>0.09871183628719504</v>
       </c>
       <c r="H5" t="n">
-        <v>0.87</v>
+        <v>1.04</v>
       </c>
       <c r="I5" t="n">
-        <v>212.8</v>
+        <v>68.23</v>
       </c>
     </row>
     <row r="6">
@@ -3013,33 +3035,33 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OR.PA</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>L'Oreal</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.109</v>
+        <v>0.097</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.1408083441981747</v>
+        <v>0.3637546015401503</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.1457378368651858</v>
+        <v>0.04394951948388726</v>
       </c>
       <c r="H6" t="n">
-        <v>1.09</v>
+        <v>0.9</v>
       </c>
       <c r="I6" t="n">
-        <v>437.5</v>
+        <v>531.6</v>
       </c>
     </row>
     <row r="7">
@@ -3048,33 +3070,33 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>WKL.AS</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Wolters Kluwer</t>
+          <t>ExxonMobil</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.101</v>
+        <v>0.09</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.1910707794893649</v>
+        <v>0.1550546612717674</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.2671132443881838</v>
+        <v>0.1068791204808679</v>
       </c>
       <c r="H7" t="n">
-        <v>0.88</v>
+        <v>0.86</v>
       </c>
       <c r="I7" t="n">
-        <v>87</v>
+        <v>179.89</v>
       </c>
     </row>
     <row r="8">
@@ -3083,33 +3105,33 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>OR.PA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>L'Oreal</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.093</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.356941436947817</v>
+        <v>0.09454314720812174</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.0321212345521642</v>
+        <v>0.1201298701298701</v>
       </c>
       <c r="H8" t="n">
-        <v>0.85</v>
+        <v>1.12</v>
       </c>
       <c r="I8" t="n">
-        <v>532.75</v>
+        <v>431.25</v>
       </c>
     </row>
     <row r="9">
@@ -3118,12 +3140,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Palantir</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -3132,19 +3154,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.1048338360517045</v>
+        <v>0.6158536585365855</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.1004136960111006</v>
+        <v>0.06011310288719773</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="I9" t="n">
-        <v>404.27</v>
+        <v>198.75</v>
       </c>
     </row>
     <row r="10">
@@ -3153,12 +3175,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Palantir</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -3167,19 +3189,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.082</v>
+        <v>0.079</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.6098923102273786</v>
+        <v>0.09168342987726508</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.04850528305508517</v>
+        <v>0.09259264484356322</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="I10" t="n">
-        <v>198.87</v>
+        <v>401.79</v>
       </c>
     </row>
     <row r="11">
@@ -3202,19 +3224,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.074</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.1178534124458734</v>
+        <v>0.1125962213337843</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.05971778228284874</v>
+        <v>0.05098618166690239</v>
       </c>
       <c r="H11" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="I11" t="n">
-        <v>83.79000000000001</v>
+        <v>83.11</v>
       </c>
     </row>
   </sheetData>
@@ -3485,23 +3507,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>28 jul</t>
+          <t>29 jul</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>37.7139</v>
+        <v>38.0653</v>
       </c>
       <c r="C2" t="n">
-        <v>38.0109</v>
+        <v>38.59</v>
       </c>
       <c r="D2" t="n">
-        <v>37.4713</v>
+        <v>37.7089</v>
       </c>
       <c r="E2" t="n">
-        <v>37.4713</v>
+        <v>38.4415</v>
       </c>
       <c r="F2" t="n">
-        <v>35.9372</v>
+        <v>35.9692</v>
       </c>
       <c r="H2" t="n">
         <v>45.05751734733581</v>
@@ -3511,23 +3533,23 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>28 jul</t>
+          <t>29 jul</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>152.2</v>
+        <v>159.84</v>
       </c>
       <c r="M2" t="n">
-        <v>159.76</v>
+        <v>163.3</v>
       </c>
       <c r="N2" t="n">
-        <v>151</v>
+        <v>156.48</v>
       </c>
       <c r="O2" t="n">
-        <v>159.24</v>
+        <v>162.04</v>
       </c>
       <c r="P2" t="n">
-        <v>144.1076</v>
+        <v>144.28</v>
       </c>
       <c r="R2" t="n">
         <v>191.5557367172241</v>
@@ -3537,23 +3559,23 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>27 jul</t>
+          <t>28 jul</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>389.347</v>
+        <v>392.4213</v>
       </c>
       <c r="W2" t="n">
-        <v>393.4593</v>
+        <v>399.5678</v>
       </c>
       <c r="X2" t="n">
-        <v>387.261</v>
+        <v>390.5647</v>
       </c>
       <c r="Y2" t="n">
-        <v>388.3689</v>
+        <v>392.6109</v>
       </c>
       <c r="Z2" t="n">
-        <v>398.0172</v>
+        <v>397.7139</v>
       </c>
       <c r="AB2" t="n">
         <v>535.3375423278808</v>
@@ -3565,23 +3587,23 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>29 jul</t>
+          <t>30 jul</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38.0653</v>
+        <v>38.6098</v>
       </c>
       <c r="C3" t="n">
-        <v>38.59</v>
+        <v>39.1444</v>
       </c>
       <c r="D3" t="n">
-        <v>37.7089</v>
+        <v>38.3277</v>
       </c>
       <c r="E3" t="n">
-        <v>38.4415</v>
+        <v>38.5108</v>
       </c>
       <c r="F3" t="n">
-        <v>35.9692</v>
+        <v>35.9978</v>
       </c>
       <c r="H3" t="n">
         <v>45.05751734733581</v>
@@ -3591,23 +3613,23 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>29 jul</t>
+          <t>30 jul</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>159.84</v>
+        <v>162.5</v>
       </c>
       <c r="M3" t="n">
-        <v>163.3</v>
+        <v>163.16</v>
       </c>
       <c r="N3" t="n">
-        <v>156.48</v>
+        <v>155.2</v>
       </c>
       <c r="O3" t="n">
-        <v>162.04</v>
+        <v>155.92</v>
       </c>
       <c r="P3" t="n">
-        <v>144.28</v>
+        <v>144.3804</v>
       </c>
       <c r="R3" t="n">
         <v>191.5557367172241</v>
@@ -3617,23 +3639,23 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>28 jul</t>
+          <t>29 jul</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>392.4213</v>
+        <v>392.6608</v>
       </c>
       <c r="W3" t="n">
-        <v>399.5678</v>
+        <v>400.4961</v>
       </c>
       <c r="X3" t="n">
-        <v>390.5647</v>
+        <v>388.0095</v>
       </c>
       <c r="Y3" t="n">
-        <v>392.6109</v>
+        <v>389.8062</v>
       </c>
       <c r="Z3" t="n">
-        <v>397.7139</v>
+        <v>397.1057</v>
       </c>
       <c r="AB3" t="n">
         <v>535.3375423278808</v>
@@ -3645,23 +3667,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>30 jul</t>
+          <t>31 jul</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>38.6098</v>
       </c>
       <c r="C4" t="n">
-        <v>39.1444</v>
+        <v>39.575</v>
       </c>
       <c r="D4" t="n">
-        <v>38.3277</v>
+        <v>38.4464</v>
       </c>
       <c r="E4" t="n">
-        <v>38.5108</v>
+        <v>39.3226</v>
       </c>
       <c r="F4" t="n">
-        <v>35.9978</v>
+        <v>36.0495</v>
       </c>
       <c r="H4" t="n">
         <v>45.05751734733581</v>
@@ -3671,23 +3693,23 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>30 jul</t>
+          <t>31 jul</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>162.5</v>
+        <v>154.9</v>
       </c>
       <c r="M4" t="n">
-        <v>163.16</v>
+        <v>158.26</v>
       </c>
       <c r="N4" t="n">
-        <v>155.2</v>
+        <v>153.6</v>
       </c>
       <c r="O4" t="n">
-        <v>155.92</v>
+        <v>157.68</v>
       </c>
       <c r="P4" t="n">
-        <v>144.3804</v>
+        <v>144.4984</v>
       </c>
       <c r="R4" t="n">
         <v>191.5557367172241</v>
@@ -3697,23 +3719,23 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>29 jul</t>
+          <t>30 jul</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>392.6608</v>
+        <v>437.0772</v>
       </c>
       <c r="W4" t="n">
-        <v>400.4961</v>
+        <v>457.8281</v>
       </c>
       <c r="X4" t="n">
-        <v>388.0095</v>
+        <v>431.6275</v>
       </c>
       <c r="Y4" t="n">
-        <v>389.8062</v>
+        <v>450.2524</v>
       </c>
       <c r="Z4" t="n">
-        <v>397.1057</v>
+        <v>397.6741</v>
       </c>
       <c r="AB4" t="n">
         <v>535.3375423278808</v>
@@ -3725,23 +3747,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>31 jul</t>
+          <t>3 aug</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>38.6098</v>
+        <v>38.3128</v>
       </c>
       <c r="C5" t="n">
-        <v>39.575</v>
+        <v>39.4067</v>
       </c>
       <c r="D5" t="n">
-        <v>38.4464</v>
+        <v>38.2138</v>
       </c>
       <c r="E5" t="n">
-        <v>39.3226</v>
+        <v>39.4067</v>
       </c>
       <c r="F5" t="n">
-        <v>36.0495</v>
+        <v>36.1112</v>
       </c>
       <c r="H5" t="n">
         <v>45.05751734733581</v>
@@ -3751,23 +3773,23 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>31 jul</t>
+          <t>3 aug</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>154.9</v>
+        <v>160</v>
       </c>
       <c r="M5" t="n">
-        <v>158.26</v>
+        <v>168.7</v>
       </c>
       <c r="N5" t="n">
-        <v>153.6</v>
+        <v>159.6</v>
       </c>
       <c r="O5" t="n">
-        <v>157.68</v>
+        <v>164.64</v>
       </c>
       <c r="P5" t="n">
-        <v>144.4984</v>
+        <v>144.7016</v>
       </c>
       <c r="R5" t="n">
         <v>191.5557367172241</v>
@@ -3777,23 +3799,23 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>30 jul</t>
+          <t>31 jul</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>437.0772</v>
+        <v>449.1545</v>
       </c>
       <c r="W5" t="n">
-        <v>457.8281</v>
+        <v>465.9628</v>
       </c>
       <c r="X5" t="n">
-        <v>431.6275</v>
+        <v>448.4857</v>
       </c>
       <c r="Y5" t="n">
-        <v>450.2524</v>
+        <v>463.8468</v>
       </c>
       <c r="Z5" t="n">
-        <v>397.6741</v>
+        <v>398.6364</v>
       </c>
       <c r="AB5" t="n">
         <v>535.3375423278808</v>
@@ -3805,26 +3827,26 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3 aug</t>
+          <t>4 aug</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>38.3128</v>
+        <v>39.3028</v>
       </c>
       <c r="C6" t="n">
-        <v>39.4067</v>
+        <v>39.6443</v>
       </c>
       <c r="D6" t="n">
-        <v>38.2138</v>
+        <v>38.2039</v>
       </c>
       <c r="E6" t="n">
-        <v>39.4067</v>
+        <v>38.486</v>
       </c>
       <c r="F6" t="n">
-        <v>36.1112</v>
+        <v>36.1495</v>
       </c>
       <c r="G6" t="n">
-        <v>34.1393</v>
+        <v>34.1818</v>
       </c>
       <c r="H6" t="n">
         <v>45.05751734733581</v>
@@ -3834,26 +3856,26 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>3 aug</t>
+          <t>4 aug</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>160</v>
+        <v>162.86</v>
       </c>
       <c r="M6" t="n">
-        <v>168.7</v>
+        <v>168.56</v>
       </c>
       <c r="N6" t="n">
-        <v>159.6</v>
+        <v>162.4</v>
       </c>
       <c r="O6" t="n">
-        <v>164.64</v>
+        <v>167.38</v>
       </c>
       <c r="P6" t="n">
-        <v>144.7016</v>
+        <v>145.02</v>
       </c>
       <c r="Q6" t="n">
-        <v>171.301</v>
+        <v>170.9913</v>
       </c>
       <c r="R6" t="n">
         <v>191.5557367172241</v>
@@ -3863,26 +3885,26 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>31 jul</t>
+          <t>3 aug</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>449.1545</v>
+        <v>475.2354</v>
       </c>
       <c r="W6" t="n">
-        <v>465.9628</v>
+        <v>490.7262</v>
       </c>
       <c r="X6" t="n">
-        <v>448.4857</v>
+        <v>474.1075</v>
       </c>
       <c r="Y6" t="n">
-        <v>463.8468</v>
+        <v>486.7337</v>
       </c>
       <c r="Z6" t="n">
-        <v>398.6364</v>
+        <v>399.9838</v>
       </c>
       <c r="AA6" t="n">
-        <v>431.4438</v>
+        <v>431.3306</v>
       </c>
       <c r="AB6" t="n">
         <v>535.3375423278808</v>
@@ -3894,26 +3916,26 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4 aug</t>
+          <t>5 aug</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>39.3028</v>
+        <v>38.4811</v>
       </c>
       <c r="C7" t="n">
-        <v>39.6443</v>
+        <v>38.7632</v>
       </c>
       <c r="D7" t="n">
-        <v>38.2039</v>
+        <v>37.9366</v>
       </c>
       <c r="E7" t="n">
-        <v>38.486</v>
+        <v>38.0307</v>
       </c>
       <c r="F7" t="n">
-        <v>36.1495</v>
+        <v>36.1966</v>
       </c>
       <c r="G7" t="n">
-        <v>34.1818</v>
+        <v>34.2215</v>
       </c>
       <c r="H7" t="n">
         <v>45.05751734733581</v>
@@ -3923,26 +3945,26 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>4 aug</t>
+          <t>5 aug</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>162.86</v>
+        <v>167.92</v>
       </c>
       <c r="M7" t="n">
-        <v>168.56</v>
+        <v>172.6</v>
       </c>
       <c r="N7" t="n">
-        <v>162.4</v>
+        <v>167.3</v>
       </c>
       <c r="O7" t="n">
-        <v>167.38</v>
+        <v>169.26</v>
       </c>
       <c r="P7" t="n">
-        <v>145.02</v>
+        <v>145.4052</v>
       </c>
       <c r="Q7" t="n">
-        <v>170.9913</v>
+        <v>170.7022</v>
       </c>
       <c r="R7" t="n">
         <v>191.5557367172241</v>
@@ -3952,26 +3974,26 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>3 aug</t>
+          <t>4 aug</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>475.2354</v>
+        <v>479.9964</v>
       </c>
       <c r="W7" t="n">
-        <v>490.7262</v>
+        <v>498.5016</v>
       </c>
       <c r="X7" t="n">
-        <v>474.1075</v>
+        <v>478.2697</v>
       </c>
       <c r="Y7" t="n">
-        <v>486.7337</v>
+        <v>491.884</v>
       </c>
       <c r="Z7" t="n">
-        <v>399.9838</v>
+        <v>401.4555</v>
       </c>
       <c r="AA7" t="n">
-        <v>431.3306</v>
+        <v>431.2438</v>
       </c>
       <c r="AB7" t="n">
         <v>535.3375423278808</v>
@@ -3983,26 +4005,26 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5 aug</t>
+          <t>6 aug</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>38.4811</v>
+        <v>38.0752</v>
       </c>
       <c r="C8" t="n">
-        <v>38.7632</v>
+        <v>38.4069</v>
       </c>
       <c r="D8" t="n">
-        <v>37.9366</v>
+        <v>37.9168</v>
       </c>
       <c r="E8" t="n">
-        <v>38.0307</v>
+        <v>38.392</v>
       </c>
       <c r="F8" t="n">
-        <v>36.1966</v>
+        <v>36.2474</v>
       </c>
       <c r="G8" t="n">
-        <v>34.2215</v>
+        <v>34.2607</v>
       </c>
       <c r="H8" t="n">
         <v>45.05751734733581</v>
@@ -4012,26 +4034,26 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>5 aug</t>
+          <t>6 aug</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>167.92</v>
+        <v>171.44</v>
       </c>
       <c r="M8" t="n">
-        <v>172.6</v>
+        <v>173.1</v>
       </c>
       <c r="N8" t="n">
-        <v>167.3</v>
+        <v>168.08</v>
       </c>
       <c r="O8" t="n">
-        <v>169.26</v>
+        <v>170.98</v>
       </c>
       <c r="P8" t="n">
-        <v>145.4052</v>
+        <v>145.7928</v>
       </c>
       <c r="Q8" t="n">
-        <v>170.7022</v>
+        <v>170.384</v>
       </c>
       <c r="R8" t="n">
         <v>191.5557367172241</v>
@@ -4041,26 +4063,26 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>4 aug</t>
+          <t>5 aug</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>479.9964</v>
+        <v>495.4273</v>
       </c>
       <c r="W8" t="n">
-        <v>498.5016</v>
+        <v>497.3038</v>
       </c>
       <c r="X8" t="n">
-        <v>478.2697</v>
+        <v>484.7674</v>
       </c>
       <c r="Y8" t="n">
-        <v>491.884</v>
+        <v>486.5441</v>
       </c>
       <c r="Z8" t="n">
-        <v>401.4555</v>
+        <v>402.8307</v>
       </c>
       <c r="AA8" t="n">
-        <v>431.2438</v>
+        <v>431.1393</v>
       </c>
       <c r="AB8" t="n">
         <v>535.3375423278808</v>
@@ -4072,26 +4094,26 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6 aug</t>
+          <t>7 aug</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>38.0752</v>
+        <v>38.5207</v>
       </c>
       <c r="C9" t="n">
-        <v>38.4069</v>
+        <v>38.5999</v>
       </c>
       <c r="D9" t="n">
-        <v>37.9168</v>
+        <v>37.897</v>
       </c>
       <c r="E9" t="n">
-        <v>38.392</v>
+        <v>38.0059</v>
       </c>
       <c r="F9" t="n">
-        <v>36.2474</v>
+        <v>36.2952</v>
       </c>
       <c r="G9" t="n">
-        <v>34.2607</v>
+        <v>34.294</v>
       </c>
       <c r="H9" t="n">
         <v>45.05751734733581</v>
@@ -4101,26 +4123,26 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>6 aug</t>
+          <t>7 aug</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>171.44</v>
+        <v>173.82</v>
       </c>
       <c r="M9" t="n">
-        <v>173.1</v>
+        <v>179.56</v>
       </c>
       <c r="N9" t="n">
-        <v>168.08</v>
+        <v>173.82</v>
       </c>
       <c r="O9" t="n">
-        <v>170.98</v>
+        <v>177.96</v>
       </c>
       <c r="P9" t="n">
-        <v>145.7928</v>
+        <v>146.2468</v>
       </c>
       <c r="Q9" t="n">
-        <v>170.384</v>
+        <v>170.0918</v>
       </c>
       <c r="R9" t="n">
         <v>191.5557367172241</v>
@@ -4130,26 +4152,26 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>5 aug</t>
+          <t>6 aug</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>495.4273</v>
+        <v>487.632</v>
       </c>
       <c r="W9" t="n">
-        <v>497.3038</v>
+        <v>500.6176</v>
       </c>
       <c r="X9" t="n">
-        <v>484.7674</v>
+        <v>487.6021</v>
       </c>
       <c r="Y9" t="n">
-        <v>486.5441</v>
+        <v>498.9207</v>
       </c>
       <c r="Z9" t="n">
-        <v>402.8307</v>
+        <v>404.5041</v>
       </c>
       <c r="AA9" t="n">
-        <v>431.1393</v>
+        <v>431.087</v>
       </c>
       <c r="AB9" t="n">
         <v>535.3375423278808</v>
@@ -4161,26 +4183,26 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>7 aug</t>
+          <t>10 aug</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>38.5207</v>
+        <v>38.0356</v>
       </c>
       <c r="C10" t="n">
-        <v>38.5999</v>
+        <v>38.4366</v>
       </c>
       <c r="D10" t="n">
-        <v>37.897</v>
+        <v>37.803</v>
       </c>
       <c r="E10" t="n">
-        <v>38.0059</v>
+        <v>38.4019</v>
       </c>
       <c r="F10" t="n">
-        <v>36.2952</v>
+        <v>36.3315</v>
       </c>
       <c r="G10" t="n">
-        <v>34.294</v>
+        <v>34.3294</v>
       </c>
       <c r="H10" t="n">
         <v>45.05751734733581</v>
@@ -4190,26 +4212,26 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>7 aug</t>
+          <t>10 aug</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>173.82</v>
+        <v>178.92</v>
       </c>
       <c r="M10" t="n">
-        <v>179.56</v>
+        <v>179.96</v>
       </c>
       <c r="N10" t="n">
-        <v>173.82</v>
+        <v>175.86</v>
       </c>
       <c r="O10" t="n">
-        <v>177.96</v>
+        <v>179.3</v>
       </c>
       <c r="P10" t="n">
-        <v>146.2468</v>
+        <v>146.4748</v>
       </c>
       <c r="Q10" t="n">
-        <v>170.0918</v>
+        <v>169.8238</v>
       </c>
       <c r="R10" t="n">
         <v>191.5557367172241</v>
@@ -4219,26 +4241,26 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>6 aug</t>
+          <t>7 aug</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>487.632</v>
+        <v>498.272</v>
       </c>
       <c r="W10" t="n">
-        <v>500.6176</v>
+        <v>504.2308</v>
       </c>
       <c r="X10" t="n">
-        <v>487.6021</v>
+        <v>497.7929</v>
       </c>
       <c r="Y10" t="n">
-        <v>498.9207</v>
+        <v>499.0505</v>
       </c>
       <c r="Z10" t="n">
-        <v>404.5041</v>
+        <v>406.2472</v>
       </c>
       <c r="AA10" t="n">
-        <v>431.087</v>
+        <v>431.0194</v>
       </c>
       <c r="AB10" t="n">
         <v>535.3375423278808</v>
@@ -4250,26 +4272,26 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10 aug</t>
+          <t>11 aug</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>38.0356</v>
+        <v>38.7385</v>
       </c>
       <c r="C11" t="n">
-        <v>38.4366</v>
+        <v>39.0058</v>
       </c>
       <c r="D11" t="n">
-        <v>37.803</v>
+        <v>38.6148</v>
       </c>
       <c r="E11" t="n">
-        <v>38.4019</v>
+        <v>38.9662</v>
       </c>
       <c r="F11" t="n">
-        <v>36.3315</v>
+        <v>36.374</v>
       </c>
       <c r="G11" t="n">
-        <v>34.3294</v>
+        <v>34.3685</v>
       </c>
       <c r="H11" t="n">
         <v>45.05751734733581</v>
@@ -4279,26 +4301,26 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>10 aug</t>
+          <t>11 aug</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>178.92</v>
+        <v>180</v>
       </c>
       <c r="M11" t="n">
-        <v>179.96</v>
+        <v>183.24</v>
       </c>
       <c r="N11" t="n">
-        <v>175.86</v>
+        <v>178.14</v>
       </c>
       <c r="O11" t="n">
-        <v>179.3</v>
+        <v>180.7</v>
       </c>
       <c r="P11" t="n">
-        <v>146.4748</v>
+        <v>146.8316</v>
       </c>
       <c r="Q11" t="n">
-        <v>169.8238</v>
+        <v>169.5375</v>
       </c>
       <c r="R11" t="n">
         <v>191.5557367172241</v>
@@ -4308,26 +4330,26 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>7 aug</t>
+          <t>10 aug</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>498.272</v>
+        <v>502.4941</v>
       </c>
       <c r="W11" t="n">
-        <v>504.2308</v>
+        <v>512.7646999999999</v>
       </c>
       <c r="X11" t="n">
-        <v>497.7929</v>
+        <v>501.3262</v>
       </c>
       <c r="Y11" t="n">
-        <v>499.0505</v>
+        <v>505.1091</v>
       </c>
       <c r="Z11" t="n">
-        <v>406.2472</v>
+        <v>407.8257</v>
       </c>
       <c r="AA11" t="n">
-        <v>431.0194</v>
+        <v>430.9778</v>
       </c>
       <c r="AB11" t="n">
         <v>535.3375423278808</v>
@@ -4339,26 +4361,26 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>11 aug</t>
+          <t>12 aug</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>38.7385</v>
+        <v>38.8573</v>
       </c>
       <c r="C12" t="n">
-        <v>39.0058</v>
+        <v>38.986</v>
       </c>
       <c r="D12" t="n">
-        <v>38.6148</v>
+        <v>38.3871</v>
       </c>
       <c r="E12" t="n">
-        <v>38.9662</v>
+        <v>38.6494</v>
       </c>
       <c r="F12" t="n">
-        <v>36.374</v>
+        <v>36.3981</v>
       </c>
       <c r="G12" t="n">
-        <v>34.3685</v>
+        <v>34.4068</v>
       </c>
       <c r="H12" t="n">
         <v>45.05751734733581</v>
@@ -4368,26 +4390,26 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>11 aug</t>
+          <t>12 aug</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>180</v>
+        <v>180.3</v>
       </c>
       <c r="M12" t="n">
-        <v>183.24</v>
+        <v>180.98</v>
       </c>
       <c r="N12" t="n">
-        <v>178.14</v>
+        <v>175.4</v>
       </c>
       <c r="O12" t="n">
-        <v>180.7</v>
+        <v>175.96</v>
       </c>
       <c r="P12" t="n">
-        <v>146.8316</v>
+        <v>147.232</v>
       </c>
       <c r="Q12" t="n">
-        <v>169.5375</v>
+        <v>169.2701</v>
       </c>
       <c r="R12" t="n">
         <v>191.5557367172241</v>
@@ -4397,26 +4419,26 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>10 aug</t>
+          <t>11 aug</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>502.4941</v>
+        <v>503.3824</v>
       </c>
       <c r="W12" t="n">
-        <v>512.7646999999999</v>
+        <v>504.3805</v>
       </c>
       <c r="X12" t="n">
-        <v>501.3262</v>
+        <v>498.6113</v>
       </c>
       <c r="Y12" t="n">
-        <v>505.1091</v>
+        <v>502.8633</v>
       </c>
       <c r="Z12" t="n">
-        <v>407.8257</v>
+        <v>408.895</v>
       </c>
       <c r="AA12" t="n">
-        <v>430.9778</v>
+        <v>430.9106</v>
       </c>
       <c r="AB12" t="n">
         <v>535.3375423278808</v>
@@ -4428,26 +4450,26 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>12 aug</t>
+          <t>13 aug</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>38.8573</v>
+        <v>39</v>
       </c>
       <c r="C13" t="n">
-        <v>38.986</v>
+        <v>39.005</v>
       </c>
       <c r="D13" t="n">
-        <v>38.3871</v>
+        <v>38.2</v>
       </c>
       <c r="E13" t="n">
-        <v>38.6494</v>
+        <v>38.605</v>
       </c>
       <c r="F13" t="n">
-        <v>36.3981</v>
+        <v>36.4313</v>
       </c>
       <c r="G13" t="n">
-        <v>34.4068</v>
+        <v>34.4429</v>
       </c>
       <c r="H13" t="n">
         <v>45.05751734733581</v>
@@ -4457,26 +4479,26 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>12 aug</t>
+          <t>13 aug</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>180.3</v>
+        <v>177.48</v>
       </c>
       <c r="M13" t="n">
-        <v>180.98</v>
+        <v>178.3</v>
       </c>
       <c r="N13" t="n">
-        <v>175.4</v>
+        <v>174.8</v>
       </c>
       <c r="O13" t="n">
-        <v>175.96</v>
+        <v>175.38</v>
       </c>
       <c r="P13" t="n">
-        <v>147.232</v>
+        <v>147.4496</v>
       </c>
       <c r="Q13" t="n">
-        <v>169.2701</v>
+        <v>168.9889</v>
       </c>
       <c r="R13" t="n">
         <v>191.5557367172241</v>
@@ -4486,26 +4508,26 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>11 aug</t>
+          <t>12 aug</t>
         </is>
       </c>
       <c r="V13" t="n">
-        <v>503.3824</v>
+        <v>499.0505</v>
       </c>
       <c r="W13" t="n">
-        <v>504.3805</v>
+        <v>500.5577</v>
       </c>
       <c r="X13" t="n">
-        <v>498.6113</v>
+        <v>490.5964</v>
       </c>
       <c r="Y13" t="n">
-        <v>502.8633</v>
+        <v>491.5047</v>
       </c>
       <c r="Z13" t="n">
-        <v>408.895</v>
+        <v>409.532</v>
       </c>
       <c r="AA13" t="n">
-        <v>430.9106</v>
+        <v>430.7866</v>
       </c>
       <c r="AB13" t="n">
         <v>535.3375423278808</v>
@@ -4517,26 +4539,26 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>13 aug</t>
+          <t>14 aug</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>39</v>
+        <v>38.65</v>
       </c>
       <c r="C14" t="n">
-        <v>39.005</v>
+        <v>39.1</v>
       </c>
       <c r="D14" t="n">
-        <v>38.2</v>
+        <v>38.56</v>
       </c>
       <c r="E14" t="n">
-        <v>38.605</v>
+        <v>38.97</v>
       </c>
       <c r="F14" t="n">
-        <v>36.4313</v>
+        <v>36.4703</v>
       </c>
       <c r="G14" t="n">
-        <v>34.4429</v>
+        <v>34.4805</v>
       </c>
       <c r="H14" t="n">
         <v>45.05751734733581</v>
@@ -4546,26 +4568,26 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>13 aug</t>
+          <t>14 aug</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>177.48</v>
+        <v>182</v>
       </c>
       <c r="M14" t="n">
-        <v>178.3</v>
+        <v>185.74</v>
       </c>
       <c r="N14" t="n">
-        <v>174.8</v>
+        <v>179.28</v>
       </c>
       <c r="O14" t="n">
-        <v>175.38</v>
+        <v>180.14</v>
       </c>
       <c r="P14" t="n">
-        <v>147.4496</v>
+        <v>147.8228</v>
       </c>
       <c r="Q14" t="n">
-        <v>168.9889</v>
+        <v>168.7386</v>
       </c>
       <c r="R14" t="n">
         <v>191.5557367172241</v>
@@ -4575,26 +4597,26 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>12 aug</t>
+          <t>13 aug</t>
         </is>
       </c>
       <c r="V14" t="n">
-        <v>499.0505</v>
+        <v>492.3431</v>
       </c>
       <c r="W14" t="n">
-        <v>500.5577</v>
+        <v>500.398</v>
       </c>
       <c r="X14" t="n">
-        <v>490.5964</v>
+        <v>492.0837</v>
       </c>
       <c r="Y14" t="n">
-        <v>491.5047</v>
+        <v>495.9464</v>
       </c>
       <c r="Z14" t="n">
-        <v>409.532</v>
+        <v>410.6414</v>
       </c>
       <c r="AA14" t="n">
-        <v>430.7866</v>
+        <v>430.6696</v>
       </c>
       <c r="AB14" t="n">
         <v>535.3375423278808</v>
@@ -4606,26 +4628,26 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>14 aug</t>
+          <t>17 aug</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>38.65</v>
+        <v>38.97</v>
       </c>
       <c r="C15" t="n">
-        <v>39.1</v>
+        <v>39.27</v>
       </c>
       <c r="D15" t="n">
-        <v>38.56</v>
+        <v>38.765</v>
       </c>
       <c r="E15" t="n">
-        <v>38.97</v>
+        <v>39.15</v>
       </c>
       <c r="F15" t="n">
-        <v>36.4703</v>
+        <v>36.5118</v>
       </c>
       <c r="G15" t="n">
-        <v>34.4805</v>
+        <v>34.5207</v>
       </c>
       <c r="H15" t="n">
         <v>45.05751734733581</v>
@@ -4635,26 +4657,26 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>14 aug</t>
+          <t>17 aug</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>182</v>
+        <v>178.94</v>
       </c>
       <c r="M15" t="n">
-        <v>185.74</v>
+        <v>180.9</v>
       </c>
       <c r="N15" t="n">
-        <v>179.28</v>
+        <v>177.66</v>
       </c>
       <c r="O15" t="n">
-        <v>180.14</v>
+        <v>179.58</v>
       </c>
       <c r="P15" t="n">
-        <v>147.8228</v>
+        <v>148.2524</v>
       </c>
       <c r="Q15" t="n">
-        <v>168.7386</v>
+        <v>168.5337</v>
       </c>
       <c r="R15" t="n">
         <v>191.5557367172241</v>
@@ -4664,26 +4686,26 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>13 aug</t>
+          <t>14 aug</t>
         </is>
       </c>
       <c r="V15" t="n">
-        <v>492.3431</v>
+        <v>495.4273</v>
       </c>
       <c r="W15" t="n">
-        <v>500.398</v>
+        <v>499.0705</v>
       </c>
       <c r="X15" t="n">
-        <v>492.0837</v>
+        <v>492.9919</v>
       </c>
       <c r="Y15" t="n">
-        <v>495.9464</v>
+        <v>494.4691</v>
       </c>
       <c r="Z15" t="n">
-        <v>410.6414</v>
+        <v>412</v>
       </c>
       <c r="AA15" t="n">
-        <v>430.6696</v>
+        <v>430.5061</v>
       </c>
       <c r="AB15" t="n">
         <v>535.3375423278808</v>
@@ -4695,26 +4717,26 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>17 aug</t>
+          <t>18 aug</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>38.97</v>
+        <v>39.49</v>
       </c>
       <c r="C16" t="n">
-        <v>39.27</v>
+        <v>39.945</v>
       </c>
       <c r="D16" t="n">
-        <v>38.765</v>
+        <v>39.46</v>
       </c>
       <c r="E16" t="n">
-        <v>39.15</v>
+        <v>39.785</v>
       </c>
       <c r="F16" t="n">
-        <v>36.5118</v>
+        <v>36.5781</v>
       </c>
       <c r="G16" t="n">
-        <v>34.5207</v>
+        <v>34.5641</v>
       </c>
       <c r="H16" t="n">
         <v>45.05751734733581</v>
@@ -4724,26 +4746,26 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>17 aug</t>
+          <t>18 aug</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>178.94</v>
+        <v>179.14</v>
       </c>
       <c r="M16" t="n">
-        <v>180.9</v>
+        <v>183.9</v>
       </c>
       <c r="N16" t="n">
-        <v>177.66</v>
+        <v>177.98</v>
       </c>
       <c r="O16" t="n">
-        <v>179.58</v>
+        <v>182.5</v>
       </c>
       <c r="P16" t="n">
-        <v>148.2524</v>
+        <v>148.8084</v>
       </c>
       <c r="Q16" t="n">
-        <v>168.5337</v>
+        <v>168.3358</v>
       </c>
       <c r="R16" t="n">
         <v>191.5557367172241</v>
@@ -4753,26 +4775,26 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>14 aug</t>
+          <t>17 aug</t>
         </is>
       </c>
       <c r="V16" t="n">
-        <v>495.4273</v>
+        <v>489.2191</v>
       </c>
       <c r="W16" t="n">
-        <v>499.0705</v>
+        <v>491.7343</v>
       </c>
       <c r="X16" t="n">
-        <v>492.9919</v>
+        <v>477.5111</v>
       </c>
       <c r="Y16" t="n">
-        <v>494.4691</v>
+        <v>479.4474</v>
       </c>
       <c r="Z16" t="n">
-        <v>412</v>
+        <v>413.044</v>
       </c>
       <c r="AA16" t="n">
-        <v>430.5061</v>
+        <v>430.2151</v>
       </c>
       <c r="AB16" t="n">
         <v>535.3375423278808</v>
@@ -4784,26 +4806,26 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>18 aug</t>
+          <t>19 aug</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>39.49</v>
+        <v>39.835</v>
       </c>
       <c r="C17" t="n">
-        <v>39.945</v>
+        <v>40.14</v>
       </c>
       <c r="D17" t="n">
-        <v>39.46</v>
+        <v>39.74</v>
       </c>
       <c r="E17" t="n">
-        <v>39.785</v>
+        <v>39.94</v>
       </c>
       <c r="F17" t="n">
-        <v>36.5781</v>
+        <v>36.6336</v>
       </c>
       <c r="G17" t="n">
-        <v>34.5641</v>
+        <v>34.6092</v>
       </c>
       <c r="H17" t="n">
         <v>45.05751734733581</v>
@@ -4813,26 +4835,26 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>18 aug</t>
+          <t>19 aug</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>179.14</v>
+        <v>181.7</v>
       </c>
       <c r="M17" t="n">
-        <v>183.9</v>
+        <v>186.98</v>
       </c>
       <c r="N17" t="n">
-        <v>177.98</v>
+        <v>180.38</v>
       </c>
       <c r="O17" t="n">
-        <v>182.5</v>
+        <v>185.9</v>
       </c>
       <c r="P17" t="n">
-        <v>148.8084</v>
+        <v>149.5324</v>
       </c>
       <c r="Q17" t="n">
-        <v>168.3358</v>
+        <v>168.1618</v>
       </c>
       <c r="R17" t="n">
         <v>191.5557367172241</v>
@@ -4842,26 +4864,26 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>17 aug</t>
+          <t>18 aug</t>
         </is>
       </c>
       <c r="V17" t="n">
-        <v>489.2191</v>
+        <v>480.6352</v>
       </c>
       <c r="W17" t="n">
-        <v>491.7343</v>
+        <v>483.3601</v>
       </c>
       <c r="X17" t="n">
-        <v>477.5111</v>
+        <v>476.2534</v>
       </c>
       <c r="Y17" t="n">
-        <v>479.4474</v>
+        <v>480.725</v>
       </c>
       <c r="Z17" t="n">
-        <v>413.044</v>
+        <v>414.3408</v>
       </c>
       <c r="AA17" t="n">
-        <v>430.2151</v>
+        <v>429.933</v>
       </c>
       <c r="AB17" t="n">
         <v>535.3375423278808</v>
@@ -4873,26 +4895,26 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>19 aug</t>
+          <t>20 aug</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>39.835</v>
+        <v>39.865</v>
       </c>
       <c r="C18" t="n">
-        <v>40.14</v>
+        <v>40.51</v>
       </c>
       <c r="D18" t="n">
-        <v>39.74</v>
+        <v>39.8</v>
       </c>
       <c r="E18" t="n">
-        <v>39.94</v>
+        <v>40.28</v>
       </c>
       <c r="F18" t="n">
-        <v>36.6336</v>
+        <v>36.6884</v>
       </c>
       <c r="G18" t="n">
-        <v>34.6092</v>
+        <v>34.6545</v>
       </c>
       <c r="H18" t="n">
         <v>45.05751734733581</v>
@@ -4902,26 +4924,26 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>19 aug</t>
+          <t>20 aug</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>181.7</v>
+        <v>183.78</v>
       </c>
       <c r="M18" t="n">
-        <v>186.98</v>
+        <v>186.1</v>
       </c>
       <c r="N18" t="n">
-        <v>180.38</v>
+        <v>182.52</v>
       </c>
       <c r="O18" t="n">
-        <v>185.9</v>
+        <v>185.64</v>
       </c>
       <c r="P18" t="n">
-        <v>149.5324</v>
+        <v>150.4472</v>
       </c>
       <c r="Q18" t="n">
-        <v>168.1618</v>
+        <v>167.9648</v>
       </c>
       <c r="R18" t="n">
         <v>191.5557367172241</v>
@@ -4931,26 +4953,26 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>18 aug</t>
+          <t>19 aug</t>
         </is>
       </c>
       <c r="V18" t="n">
-        <v>480.6352</v>
+        <v>479.168</v>
       </c>
       <c r="W18" t="n">
-        <v>483.3601</v>
+        <v>488.3806</v>
       </c>
       <c r="X18" t="n">
-        <v>476.2534</v>
+        <v>478.4593</v>
       </c>
       <c r="Y18" t="n">
-        <v>480.725</v>
+        <v>483.4</v>
       </c>
       <c r="Z18" t="n">
-        <v>414.3408</v>
+        <v>415.7895</v>
       </c>
       <c r="AA18" t="n">
-        <v>429.933</v>
+        <v>429.7427</v>
       </c>
       <c r="AB18" t="n">
         <v>535.3375423278808</v>
@@ -4962,26 +4984,26 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20 aug</t>
+          <t>21 aug</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>39.865</v>
+        <v>40.1</v>
       </c>
       <c r="C19" t="n">
-        <v>40.51</v>
+        <v>40.37</v>
       </c>
       <c r="D19" t="n">
-        <v>39.8</v>
+        <v>39.84</v>
       </c>
       <c r="E19" t="n">
-        <v>40.28</v>
+        <v>39.91</v>
       </c>
       <c r="F19" t="n">
-        <v>36.6884</v>
+        <v>36.7478</v>
       </c>
       <c r="G19" t="n">
-        <v>34.6545</v>
+        <v>34.6988</v>
       </c>
       <c r="H19" t="n">
         <v>45.05751734733581</v>
@@ -4991,26 +5013,26 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>20 aug</t>
+          <t>21 aug</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>183.78</v>
+        <v>185.18</v>
       </c>
       <c r="M19" t="n">
-        <v>186.1</v>
+        <v>188.4</v>
       </c>
       <c r="N19" t="n">
-        <v>182.52</v>
+        <v>183.6</v>
       </c>
       <c r="O19" t="n">
-        <v>185.64</v>
+        <v>188.12</v>
       </c>
       <c r="P19" t="n">
-        <v>150.4472</v>
+        <v>151.4044</v>
       </c>
       <c r="Q19" t="n">
-        <v>167.9648</v>
+        <v>167.794</v>
       </c>
       <c r="R19" t="n">
         <v>191.5557367172241</v>
@@ -5020,26 +5042,26 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>19 aug</t>
+          <t>20 aug</t>
         </is>
       </c>
       <c r="V19" t="n">
-        <v>479.168</v>
+        <v>483.3</v>
       </c>
       <c r="W19" t="n">
-        <v>488.3806</v>
+        <v>484.16</v>
       </c>
       <c r="X19" t="n">
-        <v>478.4593</v>
+        <v>479.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>483.4</v>
+        <v>481.15</v>
       </c>
       <c r="Z19" t="n">
-        <v>415.7895</v>
+        <v>417.3594</v>
       </c>
       <c r="AA19" t="n">
-        <v>429.7427</v>
+        <v>429.5805</v>
       </c>
       <c r="AB19" t="n">
         <v>535.3375423278808</v>
@@ -5051,26 +5073,26 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>21 aug</t>
+          <t>24 aug</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>40.1</v>
+        <v>39.88</v>
       </c>
       <c r="C20" t="n">
-        <v>40.37</v>
+        <v>40.085</v>
       </c>
       <c r="D20" t="n">
-        <v>39.84</v>
+        <v>39.68</v>
       </c>
       <c r="E20" t="n">
-        <v>39.91</v>
+        <v>39.775</v>
       </c>
       <c r="F20" t="n">
-        <v>36.7478</v>
+        <v>36.8369</v>
       </c>
       <c r="G20" t="n">
-        <v>34.6988</v>
+        <v>34.7421</v>
       </c>
       <c r="H20" t="n">
         <v>45.05751734733581</v>
@@ -5080,26 +5102,26 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>21 aug</t>
+          <t>24 aug</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>185.18</v>
+        <v>186.86</v>
       </c>
       <c r="M20" t="n">
-        <v>188.4</v>
+        <v>188.16</v>
       </c>
       <c r="N20" t="n">
-        <v>183.6</v>
+        <v>185.52</v>
       </c>
       <c r="O20" t="n">
-        <v>188.12</v>
+        <v>187.2</v>
       </c>
       <c r="P20" t="n">
-        <v>151.4044</v>
+        <v>152.2848</v>
       </c>
       <c r="Q20" t="n">
-        <v>167.794</v>
+        <v>167.6093</v>
       </c>
       <c r="R20" t="n">
         <v>191.5557367172241</v>
@@ -5109,26 +5131,26 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>20 aug</t>
+          <t>21 aug</t>
         </is>
       </c>
       <c r="V20" t="n">
-        <v>483.3</v>
+        <v>479.88</v>
       </c>
       <c r="W20" t="n">
-        <v>484.16</v>
+        <v>486.36</v>
       </c>
       <c r="X20" t="n">
-        <v>479.5</v>
+        <v>478.53</v>
       </c>
       <c r="Y20" t="n">
-        <v>481.15</v>
+        <v>483.24</v>
       </c>
       <c r="Z20" t="n">
-        <v>417.3594</v>
+        <v>419.092</v>
       </c>
       <c r="AA20" t="n">
-        <v>429.5805</v>
+        <v>429.4327</v>
       </c>
       <c r="AB20" t="n">
         <v>535.3375423278808</v>
@@ -5140,26 +5162,26 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>24 aug</t>
+          <t>25 aug</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>39.88</v>
+        <v>39.77</v>
       </c>
       <c r="C21" t="n">
-        <v>40.085</v>
+        <v>39.915</v>
       </c>
       <c r="D21" t="n">
-        <v>39.68</v>
+        <v>39.385</v>
       </c>
       <c r="E21" t="n">
-        <v>39.775</v>
+        <v>39.6</v>
       </c>
       <c r="F21" t="n">
-        <v>36.8369</v>
+        <v>36.926</v>
       </c>
       <c r="G21" t="n">
-        <v>34.7421</v>
+        <v>34.783</v>
       </c>
       <c r="H21" t="n">
         <v>45.05751734733581</v>
@@ -5169,26 +5191,26 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>24 aug</t>
+          <t>25 aug</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>186.86</v>
+        <v>186.4</v>
       </c>
       <c r="M21" t="n">
-        <v>188.16</v>
+        <v>187.62</v>
       </c>
       <c r="N21" t="n">
-        <v>185.52</v>
+        <v>182.74</v>
       </c>
       <c r="O21" t="n">
-        <v>187.2</v>
+        <v>185.46</v>
       </c>
       <c r="P21" t="n">
-        <v>152.2848</v>
+        <v>153.136</v>
       </c>
       <c r="Q21" t="n">
-        <v>167.6093</v>
+        <v>167.4651</v>
       </c>
       <c r="R21" t="n">
         <v>191.5557367172241</v>
@@ -5198,26 +5220,26 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>21 aug</t>
+          <t>24 aug</t>
         </is>
       </c>
       <c r="V21" t="n">
-        <v>479.88</v>
+        <v>483.21</v>
       </c>
       <c r="W21" t="n">
-        <v>486.36</v>
+        <v>490.61</v>
       </c>
       <c r="X21" t="n">
-        <v>478.53</v>
+        <v>481.86</v>
       </c>
       <c r="Y21" t="n">
-        <v>483.24</v>
+        <v>487.31</v>
       </c>
       <c r="Z21" t="n">
-        <v>419.092</v>
+        <v>421.046</v>
       </c>
       <c r="AA21" t="n">
-        <v>429.4327</v>
+        <v>429.3186</v>
       </c>
       <c r="AB21" t="n">
         <v>535.3375423278808</v>
@@ -5229,26 +5251,26 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>25 aug</t>
+          <t>26 aug</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>39.77</v>
+        <v>39.275</v>
       </c>
       <c r="C22" t="n">
-        <v>39.915</v>
+        <v>39.47</v>
       </c>
       <c r="D22" t="n">
-        <v>39.385</v>
+        <v>38.91</v>
       </c>
       <c r="E22" t="n">
-        <v>39.6</v>
+        <v>39.42</v>
       </c>
       <c r="F22" t="n">
-        <v>36.926</v>
+        <v>37.0192</v>
       </c>
       <c r="G22" t="n">
-        <v>34.783</v>
+        <v>34.8202</v>
       </c>
       <c r="H22" t="n">
         <v>45.05751734733581</v>
@@ -5258,26 +5280,26 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>25 aug</t>
+          <t>26 aug</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>186.4</v>
+        <v>179.92</v>
       </c>
       <c r="M22" t="n">
-        <v>187.62</v>
+        <v>182.16</v>
       </c>
       <c r="N22" t="n">
-        <v>182.74</v>
+        <v>176.82</v>
       </c>
       <c r="O22" t="n">
-        <v>185.46</v>
+        <v>180.02</v>
       </c>
       <c r="P22" t="n">
-        <v>153.136</v>
+        <v>153.9128</v>
       </c>
       <c r="Q22" t="n">
-        <v>167.4651</v>
+        <v>167.3049</v>
       </c>
       <c r="R22" t="n">
         <v>191.5557367172241</v>
@@ -5287,26 +5309,26 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>24 aug</t>
+          <t>25 aug</t>
         </is>
       </c>
       <c r="V22" t="n">
-        <v>483.21</v>
+        <v>485.44</v>
       </c>
       <c r="W22" t="n">
-        <v>490.61</v>
+        <v>492.44</v>
       </c>
       <c r="X22" t="n">
-        <v>481.86</v>
+        <v>484.3</v>
       </c>
       <c r="Y22" t="n">
-        <v>487.31</v>
+        <v>491.71</v>
       </c>
       <c r="Z22" t="n">
-        <v>421.046</v>
+        <v>423.0801</v>
       </c>
       <c r="AA22" t="n">
-        <v>429.3185</v>
+        <v>429.262</v>
       </c>
       <c r="AB22" t="n">
         <v>535.3375423278808</v>
@@ -5318,26 +5340,26 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>26 aug</t>
+          <t>27 aug</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>39.275</v>
+        <v>39.16</v>
       </c>
       <c r="C23" t="n">
-        <v>39.47</v>
+        <v>39.295</v>
       </c>
       <c r="D23" t="n">
-        <v>38.91</v>
+        <v>38.65</v>
       </c>
       <c r="E23" t="n">
-        <v>39.42</v>
+        <v>38.76</v>
       </c>
       <c r="F23" t="n">
-        <v>37.0192</v>
+        <v>37.117</v>
       </c>
       <c r="G23" t="n">
-        <v>34.8202</v>
+        <v>34.8559</v>
       </c>
       <c r="H23" t="n">
         <v>45.05751734733581</v>
@@ -5347,26 +5369,26 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>26 aug</t>
+          <t>27 aug</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>179.92</v>
+        <v>182.5</v>
       </c>
       <c r="M23" t="n">
-        <v>182.16</v>
+        <v>190.8</v>
       </c>
       <c r="N23" t="n">
-        <v>176.82</v>
+        <v>181.14</v>
       </c>
       <c r="O23" t="n">
-        <v>180.02</v>
+        <v>189.88</v>
       </c>
       <c r="P23" t="n">
-        <v>153.9128</v>
+        <v>155.0132</v>
       </c>
       <c r="Q23" t="n">
-        <v>167.3049</v>
+        <v>167.1911</v>
       </c>
       <c r="R23" t="n">
         <v>191.5557367172241</v>
@@ -5376,26 +5398,26 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>25 aug</t>
+          <t>26 aug</t>
         </is>
       </c>
       <c r="V23" t="n">
-        <v>485.44</v>
+        <v>487.85</v>
       </c>
       <c r="W23" t="n">
-        <v>492.44</v>
+        <v>497.4</v>
       </c>
       <c r="X23" t="n">
-        <v>484.3</v>
+        <v>487.31</v>
       </c>
       <c r="Y23" t="n">
-        <v>491.71</v>
+        <v>496.37</v>
       </c>
       <c r="Z23" t="n">
-        <v>423.0801</v>
+        <v>425.0273</v>
       </c>
       <c r="AA23" t="n">
-        <v>429.262</v>
+        <v>429.2786</v>
       </c>
       <c r="AB23" t="n">
         <v>535.3375423278808</v>
@@ -5407,26 +5429,26 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>27 aug</t>
+          <t>28 aug</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>39.16</v>
+        <v>39</v>
       </c>
       <c r="C24" t="n">
-        <v>39.295</v>
+        <v>39.18</v>
       </c>
       <c r="D24" t="n">
-        <v>38.65</v>
+        <v>38.845</v>
       </c>
       <c r="E24" t="n">
-        <v>38.76</v>
+        <v>39.145</v>
       </c>
       <c r="F24" t="n">
-        <v>37.117</v>
+        <v>37.2162</v>
       </c>
       <c r="G24" t="n">
-        <v>34.8559</v>
+        <v>34.8941</v>
       </c>
       <c r="H24" t="n">
         <v>45.05751734733581</v>
@@ -5436,26 +5458,26 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>27 aug</t>
+          <t>28 aug</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>182.5</v>
+        <v>189.5</v>
       </c>
       <c r="M24" t="n">
-        <v>190.8</v>
+        <v>191.94</v>
       </c>
       <c r="N24" t="n">
-        <v>181.14</v>
+        <v>187.98</v>
       </c>
       <c r="O24" t="n">
-        <v>189.88</v>
+        <v>191.32</v>
       </c>
       <c r="P24" t="n">
-        <v>155.0132</v>
+        <v>156.1568</v>
       </c>
       <c r="Q24" t="n">
-        <v>167.1911</v>
+        <v>167.0806</v>
       </c>
       <c r="R24" t="n">
         <v>191.5557367172241</v>
@@ -5465,26 +5487,26 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>26 aug</t>
+          <t>27 aug</t>
         </is>
       </c>
       <c r="V24" t="n">
-        <v>487.85</v>
+        <v>494.88</v>
       </c>
       <c r="W24" t="n">
-        <v>497.4</v>
+        <v>506.48</v>
       </c>
       <c r="X24" t="n">
-        <v>487.31</v>
+        <v>490.08</v>
       </c>
       <c r="Y24" t="n">
-        <v>496.37</v>
+        <v>505.06</v>
       </c>
       <c r="Z24" t="n">
-        <v>425.0273</v>
+        <v>427.2667</v>
       </c>
       <c r="AA24" t="n">
-        <v>429.2786</v>
+        <v>429.3401</v>
       </c>
       <c r="AB24" t="n">
         <v>535.3375423278808</v>
@@ -5496,26 +5518,26 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>28 aug</t>
+          <t>31 aug</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>39</v>
+        <v>39.54</v>
       </c>
       <c r="C25" t="n">
-        <v>39.18</v>
+        <v>39.91</v>
       </c>
       <c r="D25" t="n">
-        <v>38.845</v>
+        <v>39.24</v>
       </c>
       <c r="E25" t="n">
-        <v>39.145</v>
+        <v>39.335</v>
       </c>
       <c r="F25" t="n">
-        <v>37.2162</v>
+        <v>37.3111</v>
       </c>
       <c r="G25" t="n">
-        <v>34.8941</v>
+        <v>34.9333</v>
       </c>
       <c r="H25" t="n">
         <v>45.05751734733581</v>
@@ -5525,26 +5547,26 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>28 aug</t>
+          <t>31 aug</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>189.5</v>
+        <v>188.46</v>
       </c>
       <c r="M25" t="n">
-        <v>191.94</v>
+        <v>192.12</v>
       </c>
       <c r="N25" t="n">
-        <v>187.98</v>
+        <v>188.2</v>
       </c>
       <c r="O25" t="n">
-        <v>191.32</v>
+        <v>190.9</v>
       </c>
       <c r="P25" t="n">
-        <v>156.1568</v>
+        <v>157.3304</v>
       </c>
       <c r="Q25" t="n">
-        <v>167.0806</v>
+        <v>166.9613</v>
       </c>
       <c r="R25" t="n">
         <v>191.5557367172241</v>
@@ -5554,26 +5576,26 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>27 aug</t>
+          <t>28 aug</t>
         </is>
       </c>
       <c r="V25" t="n">
-        <v>494.88</v>
+        <v>505.33</v>
       </c>
       <c r="W25" t="n">
-        <v>506.48</v>
+        <v>517.78</v>
       </c>
       <c r="X25" t="n">
-        <v>490.08</v>
+        <v>504.87</v>
       </c>
       <c r="Y25" t="n">
-        <v>505.06</v>
+        <v>513.53</v>
       </c>
       <c r="Z25" t="n">
-        <v>427.2667</v>
+        <v>429.9734</v>
       </c>
       <c r="AA25" t="n">
-        <v>429.3401</v>
+        <v>429.3984</v>
       </c>
       <c r="AB25" t="n">
         <v>535.3375423278808</v>
@@ -5585,26 +5607,26 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>31 aug</t>
+          <t>1 sep</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>39.54</v>
+        <v>39.77</v>
       </c>
       <c r="C26" t="n">
-        <v>39.91</v>
+        <v>40.19</v>
       </c>
       <c r="D26" t="n">
-        <v>39.24</v>
+        <v>39.645</v>
       </c>
       <c r="E26" t="n">
-        <v>39.335</v>
+        <v>40.155</v>
       </c>
       <c r="F26" t="n">
-        <v>37.3111</v>
+        <v>37.4239</v>
       </c>
       <c r="G26" t="n">
-        <v>34.9333</v>
+        <v>34.9763</v>
       </c>
       <c r="H26" t="n">
         <v>45.05751734733581</v>
@@ -5614,26 +5636,26 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>31 aug</t>
+          <t>1 sep</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>188.46</v>
+        <v>186</v>
       </c>
       <c r="M26" t="n">
-        <v>192.12</v>
+        <v>187.86</v>
       </c>
       <c r="N26" t="n">
-        <v>188.2</v>
+        <v>183.32</v>
       </c>
       <c r="O26" t="n">
-        <v>190.9</v>
+        <v>184.26</v>
       </c>
       <c r="P26" t="n">
-        <v>157.3304</v>
+        <v>158.3252</v>
       </c>
       <c r="Q26" t="n">
-        <v>166.9613</v>
+        <v>166.8103</v>
       </c>
       <c r="R26" t="n">
         <v>191.5557367172241</v>
@@ -5643,26 +5665,26 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>28 aug</t>
+          <t>31 aug</t>
         </is>
       </c>
       <c r="V26" t="n">
-        <v>505.33</v>
+        <v>510.38</v>
       </c>
       <c r="W26" t="n">
-        <v>517.78</v>
+        <v>512.1900000000001</v>
       </c>
       <c r="X26" t="n">
-        <v>504.87</v>
+        <v>506.39</v>
       </c>
       <c r="Y26" t="n">
-        <v>513.53</v>
+        <v>507.29</v>
       </c>
       <c r="Z26" t="n">
-        <v>429.9734</v>
+        <v>432.5454</v>
       </c>
       <c r="AA26" t="n">
-        <v>429.3984</v>
+        <v>429.4122</v>
       </c>
       <c r="AB26" t="n">
         <v>535.3375423278808</v>
@@ -5674,26 +5696,26 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1 sep</t>
+          <t>2 sep</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>39.77</v>
+        <v>40.35</v>
       </c>
       <c r="C27" t="n">
-        <v>40.19</v>
+        <v>40.615</v>
       </c>
       <c r="D27" t="n">
-        <v>39.645</v>
+        <v>39.975</v>
       </c>
       <c r="E27" t="n">
-        <v>40.155</v>
+        <v>40.21</v>
       </c>
       <c r="F27" t="n">
-        <v>37.4239</v>
+        <v>37.5499</v>
       </c>
       <c r="G27" t="n">
-        <v>34.9763</v>
+        <v>35.0217</v>
       </c>
       <c r="H27" t="n">
         <v>45.05751734733581</v>
@@ -5703,26 +5725,26 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>1 sep</t>
+          <t>2 sep</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>186</v>
+        <v>182.18</v>
       </c>
       <c r="M27" t="n">
-        <v>187.86</v>
+        <v>184.7</v>
       </c>
       <c r="N27" t="n">
-        <v>183.32</v>
+        <v>180.72</v>
       </c>
       <c r="O27" t="n">
-        <v>184.26</v>
+        <v>181.44</v>
       </c>
       <c r="P27" t="n">
-        <v>158.3252</v>
+        <v>159.2568</v>
       </c>
       <c r="Q27" t="n">
-        <v>166.8103</v>
+        <v>166.6796</v>
       </c>
       <c r="R27" t="n">
         <v>191.5557367172241</v>
@@ -5732,26 +5754,26 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>31 aug</t>
+          <t>1 sep</t>
         </is>
       </c>
       <c r="V27" t="n">
-        <v>510.38</v>
+        <v>497.52</v>
       </c>
       <c r="W27" t="n">
-        <v>512.1900000000001</v>
+        <v>505.97</v>
       </c>
       <c r="X27" t="n">
-        <v>506.39</v>
+        <v>496.78</v>
       </c>
       <c r="Y27" t="n">
-        <v>507.29</v>
+        <v>501.02</v>
       </c>
       <c r="Z27" t="n">
-        <v>432.5454</v>
+        <v>435.2328</v>
       </c>
       <c r="AA27" t="n">
-        <v>429.4122</v>
+        <v>429.3825</v>
       </c>
       <c r="AB27" t="n">
         <v>535.3375423278808</v>
@@ -5763,26 +5785,26 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2 sep</t>
+          <t>3 sep</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>40.35</v>
+        <v>40.095</v>
       </c>
       <c r="C28" t="n">
-        <v>40.615</v>
+        <v>40.215</v>
       </c>
       <c r="D28" t="n">
-        <v>39.975</v>
+        <v>39.54</v>
       </c>
       <c r="E28" t="n">
-        <v>40.21</v>
+        <v>40.04</v>
       </c>
       <c r="F28" t="n">
-        <v>37.5499</v>
+        <v>37.6767</v>
       </c>
       <c r="G28" t="n">
-        <v>35.0217</v>
+        <v>35.0679</v>
       </c>
       <c r="H28" t="n">
         <v>45.05751734733581</v>
@@ -5792,26 +5814,26 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2 sep</t>
+          <t>3 sep</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>182.18</v>
+        <v>182.08</v>
       </c>
       <c r="M28" t="n">
-        <v>184.7</v>
+        <v>187.56</v>
       </c>
       <c r="N28" t="n">
-        <v>180.72</v>
+        <v>182</v>
       </c>
       <c r="O28" t="n">
-        <v>181.44</v>
+        <v>185.58</v>
       </c>
       <c r="P28" t="n">
-        <v>159.2568</v>
+        <v>160.3228</v>
       </c>
       <c r="Q28" t="n">
-        <v>166.6796</v>
+        <v>166.5898</v>
       </c>
       <c r="R28" t="n">
         <v>191.5557367172241</v>
@@ -5821,26 +5843,26 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>1 sep</t>
+          <t>2 sep</t>
         </is>
       </c>
       <c r="V28" t="n">
-        <v>497.52</v>
+        <v>499.85</v>
       </c>
       <c r="W28" t="n">
-        <v>505.97</v>
+        <v>500.27</v>
       </c>
       <c r="X28" t="n">
-        <v>496.78</v>
+        <v>493.81</v>
       </c>
       <c r="Y28" t="n">
-        <v>501.02</v>
+        <v>496.82</v>
       </c>
       <c r="Z28" t="n">
-        <v>435.2328</v>
+        <v>437.7045</v>
       </c>
       <c r="AA28" t="n">
-        <v>429.3825</v>
+        <v>429.3706</v>
       </c>
       <c r="AB28" t="n">
         <v>535.3375423278808</v>
@@ -5852,26 +5874,26 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3 sep</t>
+          <t>4 sep</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>40.095</v>
+        <v>40.145</v>
       </c>
       <c r="C29" t="n">
-        <v>40.215</v>
+        <v>40.28</v>
       </c>
       <c r="D29" t="n">
-        <v>39.54</v>
+        <v>39.665</v>
       </c>
       <c r="E29" t="n">
-        <v>40.04</v>
+        <v>40.105</v>
       </c>
       <c r="F29" t="n">
-        <v>37.6767</v>
+        <v>37.8115</v>
       </c>
       <c r="G29" t="n">
-        <v>35.0679</v>
+        <v>35.113</v>
       </c>
       <c r="H29" t="n">
         <v>45.05751734733581</v>
@@ -5881,26 +5903,26 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>3 sep</t>
+          <t>4 sep</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>182.08</v>
+        <v>187.8</v>
       </c>
       <c r="M29" t="n">
-        <v>187.56</v>
+        <v>189.9</v>
       </c>
       <c r="N29" t="n">
-        <v>182</v>
+        <v>184.96</v>
       </c>
       <c r="O29" t="n">
-        <v>185.58</v>
+        <v>185.68</v>
       </c>
       <c r="P29" t="n">
-        <v>160.3228</v>
+        <v>161.3336</v>
       </c>
       <c r="Q29" t="n">
-        <v>166.5898</v>
+        <v>166.5086</v>
       </c>
       <c r="R29" t="n">
         <v>191.5557367172241</v>
@@ -5910,26 +5932,26 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>2 sep</t>
+          <t>3 sep</t>
         </is>
       </c>
       <c r="V29" t="n">
-        <v>499.85</v>
+        <v>501.66</v>
       </c>
       <c r="W29" t="n">
-        <v>500.27</v>
+        <v>515.65</v>
       </c>
       <c r="X29" t="n">
-        <v>493.81</v>
+        <v>500.8</v>
       </c>
       <c r="Y29" t="n">
-        <v>496.82</v>
+        <v>510.12</v>
       </c>
       <c r="Z29" t="n">
-        <v>437.7045</v>
+        <v>440.6114</v>
       </c>
       <c r="AA29" t="n">
-        <v>429.3706</v>
+        <v>429.3912</v>
       </c>
       <c r="AB29" t="n">
         <v>535.3375423278808</v>
@@ -5941,26 +5963,26 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>4 sep</t>
+          <t>7 sep</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>40.145</v>
+        <v>40.26</v>
       </c>
       <c r="C30" t="n">
-        <v>40.28</v>
+        <v>40.845</v>
       </c>
       <c r="D30" t="n">
-        <v>39.665</v>
+        <v>40.12</v>
       </c>
       <c r="E30" t="n">
-        <v>40.105</v>
+        <v>40.56</v>
       </c>
       <c r="F30" t="n">
-        <v>37.8115</v>
+        <v>37.9551</v>
       </c>
       <c r="G30" t="n">
-        <v>35.113</v>
+        <v>35.1619</v>
       </c>
       <c r="H30" t="n">
         <v>45.05751734733581</v>
@@ -5970,26 +5992,26 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>4 sep</t>
+          <t>7 sep</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>187.8</v>
+        <v>183.56</v>
       </c>
       <c r="M30" t="n">
-        <v>189.9</v>
+        <v>184.3</v>
       </c>
       <c r="N30" t="n">
-        <v>184.96</v>
+        <v>179.92</v>
       </c>
       <c r="O30" t="n">
-        <v>185.68</v>
+        <v>182.8</v>
       </c>
       <c r="P30" t="n">
-        <v>161.3336</v>
+        <v>162.2568</v>
       </c>
       <c r="Q30" t="n">
-        <v>166.5086</v>
+        <v>166.4122</v>
       </c>
       <c r="R30" t="n">
         <v>191.5557367172241</v>
@@ -5999,26 +6021,26 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>3 sep</t>
+          <t>4 sep</t>
         </is>
       </c>
       <c r="V30" t="n">
-        <v>501.66</v>
+        <v>510</v>
       </c>
       <c r="W30" t="n">
-        <v>515.65</v>
+        <v>511</v>
       </c>
       <c r="X30" t="n">
-        <v>500.8</v>
+        <v>499.36</v>
       </c>
       <c r="Y30" t="n">
-        <v>510.12</v>
+        <v>499.7</v>
       </c>
       <c r="Z30" t="n">
-        <v>440.6114</v>
+        <v>443.5621</v>
       </c>
       <c r="AA30" t="n">
-        <v>429.3912</v>
+        <v>429.3729</v>
       </c>
       <c r="AB30" t="n">
         <v>535.3375423278808</v>
@@ -6030,26 +6052,26 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>7 sep</t>
+          <t>8 sep</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>40.26</v>
+        <v>40.83</v>
       </c>
       <c r="C31" t="n">
-        <v>40.845</v>
+        <v>41.18</v>
       </c>
       <c r="D31" t="n">
-        <v>40.12</v>
+        <v>40.6325</v>
       </c>
       <c r="E31" t="n">
-        <v>40.56</v>
+        <v>40.855</v>
       </c>
       <c r="F31" t="n">
-        <v>37.9551</v>
+        <v>38.0977</v>
       </c>
       <c r="G31" t="n">
-        <v>35.1619</v>
+        <v>35.2131</v>
       </c>
       <c r="H31" t="n">
         <v>45.05751734733581</v>
@@ -6059,26 +6081,26 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>7 sep</t>
+          <t>8 sep</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>183.56</v>
+        <v>182.32</v>
       </c>
       <c r="M31" t="n">
-        <v>184.3</v>
+        <v>183.76</v>
       </c>
       <c r="N31" t="n">
-        <v>179.92</v>
+        <v>180.02</v>
       </c>
       <c r="O31" t="n">
-        <v>182.8</v>
+        <v>181.7</v>
       </c>
       <c r="P31" t="n">
-        <v>162.2568</v>
+        <v>163.2108</v>
       </c>
       <c r="Q31" t="n">
-        <v>166.4122</v>
+        <v>166.3049</v>
       </c>
       <c r="R31" t="n">
         <v>191.5557367172241</v>
@@ -6088,26 +6110,26 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>4 sep</t>
+          <t>8 sep</t>
         </is>
       </c>
       <c r="V31" t="n">
-        <v>510</v>
+        <v>493.01</v>
       </c>
       <c r="W31" t="n">
-        <v>511</v>
+        <v>495.19</v>
       </c>
       <c r="X31" t="n">
-        <v>499.36</v>
+        <v>490.15</v>
       </c>
       <c r="Y31" t="n">
-        <v>499.7</v>
+        <v>493.95</v>
       </c>
       <c r="Z31" t="n">
-        <v>443.5621</v>
+        <v>445.9957</v>
       </c>
       <c r="AA31" t="n">
-        <v>429.3729</v>
+        <v>429.3939</v>
       </c>
       <c r="AB31" t="n">
         <v>535.3375423278808</v>
@@ -6119,26 +6141,26 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>8 sep</t>
+          <t>9 sep</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>40.83</v>
+        <v>41.1</v>
       </c>
       <c r="C32" t="n">
-        <v>41.18</v>
+        <v>41.385</v>
       </c>
       <c r="D32" t="n">
-        <v>40.6325</v>
+        <v>40.85</v>
       </c>
       <c r="E32" t="n">
-        <v>40.855</v>
+        <v>40.94</v>
       </c>
       <c r="F32" t="n">
-        <v>38.0977</v>
+        <v>38.2513</v>
       </c>
       <c r="G32" t="n">
-        <v>35.2131</v>
+        <v>35.2646</v>
       </c>
       <c r="H32" t="n">
         <v>45.05751734733581</v>
@@ -6148,26 +6170,26 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>8 sep</t>
+          <t>9 sep</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>182.32</v>
+        <v>183</v>
       </c>
       <c r="M32" t="n">
-        <v>183.76</v>
+        <v>187.04</v>
       </c>
       <c r="N32" t="n">
-        <v>180.02</v>
+        <v>181.36</v>
       </c>
       <c r="O32" t="n">
-        <v>181.7</v>
+        <v>182.86</v>
       </c>
       <c r="P32" t="n">
-        <v>163.2108</v>
+        <v>164.0504</v>
       </c>
       <c r="Q32" t="n">
-        <v>166.3049</v>
+        <v>166.2113</v>
       </c>
       <c r="R32" t="n">
         <v>191.5557367172241</v>
@@ -6177,26 +6199,26 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>8 sep</t>
+          <t>9 sep</t>
         </is>
       </c>
       <c r="V32" t="n">
-        <v>493.01</v>
+        <v>493.07</v>
       </c>
       <c r="W32" t="n">
-        <v>495.19</v>
+        <v>494.39</v>
       </c>
       <c r="X32" t="n">
-        <v>490.15</v>
+        <v>489.8</v>
       </c>
       <c r="Y32" t="n">
-        <v>493.95</v>
+        <v>491.65</v>
       </c>
       <c r="Z32" t="n">
-        <v>445.9957</v>
+        <v>448.4712</v>
       </c>
       <c r="AA32" t="n">
-        <v>429.3939</v>
+        <v>429.4364</v>
       </c>
       <c r="AB32" t="n">
         <v>535.3375423278808</v>
@@ -6208,26 +6230,26 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>9 sep</t>
+          <t>10 sep</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>41.1</v>
+        <v>40.98</v>
       </c>
       <c r="C33" t="n">
-        <v>41.385</v>
+        <v>41.77</v>
       </c>
       <c r="D33" t="n">
-        <v>40.85</v>
+        <v>40.93</v>
       </c>
       <c r="E33" t="n">
-        <v>40.94</v>
+        <v>41.23</v>
       </c>
       <c r="F33" t="n">
-        <v>38.2513</v>
+        <v>38.4034</v>
       </c>
       <c r="G33" t="n">
-        <v>35.2646</v>
+        <v>35.3174</v>
       </c>
       <c r="H33" t="n">
         <v>45.05751734733581</v>
@@ -6237,26 +6259,26 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>9 sep</t>
+          <t>10 sep</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="M33" t="n">
-        <v>187.04</v>
+        <v>180.4</v>
       </c>
       <c r="N33" t="n">
-        <v>181.36</v>
+        <v>176.2</v>
       </c>
       <c r="O33" t="n">
-        <v>182.86</v>
+        <v>177.82</v>
       </c>
       <c r="P33" t="n">
-        <v>164.0504</v>
+        <v>164.7724</v>
       </c>
       <c r="Q33" t="n">
-        <v>166.2113</v>
+        <v>166.0803</v>
       </c>
       <c r="R33" t="n">
         <v>191.5557367172241</v>
@@ -6266,26 +6288,26 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>9 sep</t>
+          <t>10 sep</t>
         </is>
       </c>
       <c r="V33" t="n">
-        <v>493.07</v>
+        <v>488.32</v>
       </c>
       <c r="W33" t="n">
-        <v>494.39</v>
+        <v>494.52</v>
       </c>
       <c r="X33" t="n">
-        <v>489.8</v>
+        <v>486</v>
       </c>
       <c r="Y33" t="n">
-        <v>491.65</v>
+        <v>492.44</v>
       </c>
       <c r="Z33" t="n">
-        <v>448.4712</v>
+        <v>450.8736</v>
       </c>
       <c r="AA33" t="n">
-        <v>429.4364</v>
+        <v>429.5215</v>
       </c>
       <c r="AB33" t="n">
         <v>535.3375423278808</v>
@@ -6297,26 +6319,26 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10 sep</t>
+          <t>11 sep</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>40.98</v>
+        <v>41.345</v>
       </c>
       <c r="C34" t="n">
-        <v>41.77</v>
+        <v>41.715</v>
       </c>
       <c r="D34" t="n">
-        <v>40.93</v>
+        <v>40.905</v>
       </c>
       <c r="E34" t="n">
-        <v>41.23</v>
+        <v>41.415</v>
       </c>
       <c r="F34" t="n">
-        <v>38.4034</v>
+        <v>38.5608</v>
       </c>
       <c r="G34" t="n">
-        <v>35.3174</v>
+        <v>35.3717</v>
       </c>
       <c r="H34" t="n">
         <v>45.05751734733581</v>
@@ -6326,26 +6348,26 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>10 sep</t>
+          <t>11 sep</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>180</v>
+        <v>175.68</v>
       </c>
       <c r="M34" t="n">
-        <v>180.4</v>
+        <v>178.84</v>
       </c>
       <c r="N34" t="n">
-        <v>176.2</v>
+        <v>172.16</v>
       </c>
       <c r="O34" t="n">
-        <v>177.82</v>
+        <v>177.26</v>
       </c>
       <c r="P34" t="n">
-        <v>164.7724</v>
+        <v>165.5248</v>
       </c>
       <c r="Q34" t="n">
-        <v>166.0803</v>
+        <v>165.9594</v>
       </c>
       <c r="R34" t="n">
         <v>191.5557367172241</v>
@@ -6355,26 +6377,26 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>10 sep</t>
+          <t>11 sep</t>
         </is>
       </c>
       <c r="V34" t="n">
-        <v>488.32</v>
+        <v>495.65</v>
       </c>
       <c r="W34" t="n">
-        <v>494.52</v>
+        <v>498.97</v>
       </c>
       <c r="X34" t="n">
-        <v>486</v>
+        <v>492.58</v>
       </c>
       <c r="Y34" t="n">
-        <v>492.44</v>
+        <v>495.63</v>
       </c>
       <c r="Z34" t="n">
-        <v>450.8736</v>
+        <v>453.115</v>
       </c>
       <c r="AA34" t="n">
-        <v>429.5215</v>
+        <v>429.654</v>
       </c>
       <c r="AB34" t="n">
         <v>535.3375423278808</v>
@@ -6386,26 +6408,26 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>11 sep</t>
+          <t>14 sep</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>41.345</v>
+        <v>41.88</v>
       </c>
       <c r="C35" t="n">
-        <v>41.715</v>
+        <v>42.285</v>
       </c>
       <c r="D35" t="n">
-        <v>40.905</v>
+        <v>41.8</v>
       </c>
       <c r="E35" t="n">
-        <v>41.415</v>
+        <v>41.91</v>
       </c>
       <c r="F35" t="n">
-        <v>38.5608</v>
+        <v>38.7226</v>
       </c>
       <c r="G35" t="n">
-        <v>35.3717</v>
+        <v>35.4269</v>
       </c>
       <c r="H35" t="n">
         <v>45.05751734733581</v>
@@ -6415,26 +6437,26 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>11 sep</t>
+          <t>14 sep</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>175.68</v>
+        <v>180.82</v>
       </c>
       <c r="M35" t="n">
-        <v>178.84</v>
+        <v>186.76</v>
       </c>
       <c r="N35" t="n">
-        <v>172.16</v>
+        <v>180.82</v>
       </c>
       <c r="O35" t="n">
-        <v>177.26</v>
+        <v>186.26</v>
       </c>
       <c r="P35" t="n">
-        <v>165.5248</v>
+        <v>166.4488</v>
       </c>
       <c r="Q35" t="n">
-        <v>165.9594</v>
+        <v>165.8745</v>
       </c>
       <c r="R35" t="n">
         <v>191.5557367172241</v>
@@ -6444,26 +6466,26 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>11 sep</t>
+          <t>14 sep</t>
         </is>
       </c>
       <c r="V35" t="n">
-        <v>495.65</v>
+        <v>497.06</v>
       </c>
       <c r="W35" t="n">
-        <v>498.97</v>
+        <v>509.95</v>
       </c>
       <c r="X35" t="n">
-        <v>492.58</v>
+        <v>495.34</v>
       </c>
       <c r="Y35" t="n">
-        <v>495.63</v>
+        <v>505.41</v>
       </c>
       <c r="Z35" t="n">
-        <v>453.115</v>
+        <v>455.4281</v>
       </c>
       <c r="AA35" t="n">
-        <v>429.654</v>
+        <v>429.8259</v>
       </c>
       <c r="AB35" t="n">
         <v>535.3375423278808</v>
@@ -6475,26 +6497,26 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>14 sep</t>
+          <t>15 sep</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>41.88</v>
+        <v>41.845</v>
       </c>
       <c r="C36" t="n">
-        <v>42.285</v>
+        <v>42.7</v>
       </c>
       <c r="D36" t="n">
-        <v>41.8</v>
+        <v>41.72</v>
       </c>
       <c r="E36" t="n">
-        <v>41.91</v>
+        <v>42.7</v>
       </c>
       <c r="F36" t="n">
-        <v>38.7226</v>
+        <v>38.8782</v>
       </c>
       <c r="G36" t="n">
-        <v>35.4269</v>
+        <v>35.4854</v>
       </c>
       <c r="H36" t="n">
         <v>45.05751734733581</v>
@@ -6504,26 +6526,26 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>14 sep</t>
+          <t>15 sep</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>180.82</v>
+        <v>186.64</v>
       </c>
       <c r="M36" t="n">
-        <v>186.76</v>
+        <v>187.26</v>
       </c>
       <c r="N36" t="n">
-        <v>180.82</v>
+        <v>183.2</v>
       </c>
       <c r="O36" t="n">
-        <v>186.26</v>
+        <v>187.08</v>
       </c>
       <c r="P36" t="n">
-        <v>166.4488</v>
+        <v>167.3124</v>
       </c>
       <c r="Q36" t="n">
-        <v>165.8745</v>
+        <v>165.7921</v>
       </c>
       <c r="R36" t="n">
         <v>191.5557367172241</v>
@@ -6533,26 +6555,26 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>14 sep</t>
+          <t>15 sep</t>
         </is>
       </c>
       <c r="V36" t="n">
-        <v>497.06</v>
+        <v>500.06</v>
       </c>
       <c r="W36" t="n">
-        <v>509.95</v>
+        <v>505.9</v>
       </c>
       <c r="X36" t="n">
-        <v>495.34</v>
+        <v>495.54</v>
       </c>
       <c r="Y36" t="n">
-        <v>505.41</v>
+        <v>497.12</v>
       </c>
       <c r="Z36" t="n">
-        <v>455.4281</v>
+        <v>457.6502</v>
       </c>
       <c r="AA36" t="n">
-        <v>429.8259</v>
+        <v>429.9416</v>
       </c>
       <c r="AB36" t="n">
         <v>535.3375423278808</v>
@@ -6564,26 +6586,26 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>15 sep</t>
+          <t>16 sep</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>41.845</v>
+        <v>42.72</v>
       </c>
       <c r="C37" t="n">
-        <v>42.7</v>
+        <v>42.85</v>
       </c>
       <c r="D37" t="n">
-        <v>41.72</v>
+        <v>41.67</v>
       </c>
       <c r="E37" t="n">
-        <v>42.7</v>
+        <v>41.825</v>
       </c>
       <c r="F37" t="n">
-        <v>38.8782</v>
+        <v>38.9989</v>
       </c>
       <c r="G37" t="n">
-        <v>35.4854</v>
+        <v>35.5403</v>
       </c>
       <c r="H37" t="n">
         <v>45.05751734733581</v>
@@ -6593,26 +6615,26 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>15 sep</t>
+          <t>16 sep</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>186.64</v>
+        <v>185.86</v>
       </c>
       <c r="M37" t="n">
-        <v>187.26</v>
+        <v>186.76</v>
       </c>
       <c r="N37" t="n">
-        <v>183.2</v>
+        <v>182.18</v>
       </c>
       <c r="O37" t="n">
-        <v>187.08</v>
+        <v>186.56</v>
       </c>
       <c r="P37" t="n">
-        <v>167.3124</v>
+        <v>168.2844</v>
       </c>
       <c r="Q37" t="n">
-        <v>165.7921</v>
+        <v>165.6996</v>
       </c>
       <c r="R37" t="n">
         <v>191.5557367172241</v>
@@ -6622,26 +6644,26 @@
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>15 sep</t>
+          <t>16 sep</t>
         </is>
       </c>
       <c r="V37" t="n">
-        <v>500.06</v>
+        <v>493.03</v>
       </c>
       <c r="W37" t="n">
-        <v>505.9</v>
+        <v>495.97</v>
       </c>
       <c r="X37" t="n">
-        <v>495.54</v>
+        <v>487.23</v>
       </c>
       <c r="Y37" t="n">
-        <v>497.12</v>
+        <v>490.3</v>
       </c>
       <c r="Z37" t="n">
-        <v>457.6502</v>
+        <v>459.694</v>
       </c>
       <c r="AA37" t="n">
-        <v>429.9416</v>
+        <v>429.9809</v>
       </c>
       <c r="AB37" t="n">
         <v>535.3375423278808</v>
@@ -6653,26 +6675,26 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>16 sep</t>
+          <t>17 sep</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>42.72</v>
+        <v>41.58</v>
       </c>
       <c r="C38" t="n">
-        <v>42.85</v>
+        <v>42.055</v>
       </c>
       <c r="D38" t="n">
-        <v>41.67</v>
+        <v>41.38</v>
       </c>
       <c r="E38" t="n">
-        <v>41.825</v>
+        <v>41.56</v>
       </c>
       <c r="F38" t="n">
-        <v>38.9989</v>
+        <v>39.1225</v>
       </c>
       <c r="G38" t="n">
-        <v>35.5403</v>
+        <v>35.5926</v>
       </c>
       <c r="H38" t="n">
         <v>45.05751734733581</v>
@@ -6682,26 +6704,26 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>16 sep</t>
+          <t>17 sep</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>185.86</v>
+        <v>188.54</v>
       </c>
       <c r="M38" t="n">
-        <v>186.76</v>
+        <v>189.2</v>
       </c>
       <c r="N38" t="n">
-        <v>182.18</v>
+        <v>184.62</v>
       </c>
       <c r="O38" t="n">
-        <v>186.56</v>
+        <v>188</v>
       </c>
       <c r="P38" t="n">
-        <v>168.2844</v>
+        <v>169.2896</v>
       </c>
       <c r="Q38" t="n">
-        <v>165.6996</v>
+        <v>165.6125</v>
       </c>
       <c r="R38" t="n">
         <v>191.5557367172241</v>
@@ -6711,26 +6733,26 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>16 sep</t>
+          <t>17 sep</t>
         </is>
       </c>
       <c r="V38" t="n">
-        <v>493.03</v>
+        <v>497.8</v>
       </c>
       <c r="W38" t="n">
-        <v>495.97</v>
+        <v>501.47</v>
       </c>
       <c r="X38" t="n">
-        <v>487.23</v>
+        <v>493.17</v>
       </c>
       <c r="Y38" t="n">
-        <v>490.3</v>
+        <v>497.75</v>
       </c>
       <c r="Z38" t="n">
-        <v>459.694</v>
+        <v>461.9966</v>
       </c>
       <c r="AA38" t="n">
-        <v>429.9809</v>
+        <v>430.0251</v>
       </c>
       <c r="AB38" t="n">
         <v>535.3375423278808</v>
@@ -6742,26 +6764,26 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>17 sep</t>
+          <t>18 sep</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>41.58</v>
+        <v>41.465</v>
       </c>
       <c r="C39" t="n">
-        <v>42.055</v>
+        <v>41.5</v>
       </c>
       <c r="D39" t="n">
-        <v>41.38</v>
+        <v>40.955</v>
       </c>
       <c r="E39" t="n">
-        <v>41.56</v>
+        <v>41.315</v>
       </c>
       <c r="F39" t="n">
-        <v>39.1225</v>
+        <v>39.2414</v>
       </c>
       <c r="G39" t="n">
-        <v>35.5926</v>
+        <v>35.6436</v>
       </c>
       <c r="H39" t="n">
         <v>45.05751734733581</v>
@@ -6771,26 +6793,26 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>17 sep</t>
+          <t>18 sep</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>188.54</v>
+        <v>186.1</v>
       </c>
       <c r="M39" t="n">
-        <v>189.2</v>
+        <v>187.26</v>
       </c>
       <c r="N39" t="n">
-        <v>184.62</v>
+        <v>182.56</v>
       </c>
       <c r="O39" t="n">
-        <v>188</v>
+        <v>183.12</v>
       </c>
       <c r="P39" t="n">
-        <v>169.2896</v>
+        <v>170.2004</v>
       </c>
       <c r="Q39" t="n">
-        <v>165.6125</v>
+        <v>165.5062</v>
       </c>
       <c r="R39" t="n">
         <v>191.5557367172241</v>
@@ -6800,26 +6822,26 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>17 sep</t>
+          <t>18 sep</t>
         </is>
       </c>
       <c r="V39" t="n">
-        <v>497.8</v>
+        <v>497.97</v>
       </c>
       <c r="W39" t="n">
-        <v>501.47</v>
+        <v>498.65</v>
       </c>
       <c r="X39" t="n">
-        <v>493.17</v>
+        <v>491.1</v>
       </c>
       <c r="Y39" t="n">
-        <v>497.75</v>
+        <v>493.78</v>
       </c>
       <c r="Z39" t="n">
-        <v>461.9966</v>
+        <v>464.1995</v>
       </c>
       <c r="AA39" t="n">
-        <v>430.0251</v>
+        <v>430.0757</v>
       </c>
       <c r="AB39" t="n">
         <v>535.3375423278808</v>
@@ -6831,26 +6853,26 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>18 sep</t>
+          <t>21 sep</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>41.465</v>
+        <v>41.04</v>
       </c>
       <c r="C40" t="n">
-        <v>41.5</v>
+        <v>41.4</v>
       </c>
       <c r="D40" t="n">
-        <v>40.955</v>
+        <v>40.775</v>
       </c>
       <c r="E40" t="n">
-        <v>41.315</v>
+        <v>40.775</v>
       </c>
       <c r="F40" t="n">
-        <v>39.2414</v>
+        <v>39.3341</v>
       </c>
       <c r="G40" t="n">
-        <v>35.6436</v>
+        <v>35.6939</v>
       </c>
       <c r="H40" t="n">
         <v>45.05751734733581</v>
@@ -6860,26 +6882,26 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>18 sep</t>
+          <t>21 sep</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>186.1</v>
+        <v>184.7</v>
       </c>
       <c r="M40" t="n">
-        <v>187.26</v>
+        <v>185.86</v>
       </c>
       <c r="N40" t="n">
-        <v>182.56</v>
+        <v>182.48</v>
       </c>
       <c r="O40" t="n">
-        <v>183.12</v>
+        <v>182.86</v>
       </c>
       <c r="P40" t="n">
-        <v>170.2004</v>
+        <v>171.0432</v>
       </c>
       <c r="Q40" t="n">
-        <v>165.5062</v>
+        <v>165.4052</v>
       </c>
       <c r="R40" t="n">
         <v>191.5557367172241</v>
@@ -6889,26 +6911,26 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>18 sep</t>
+          <t>21 sep</t>
         </is>
       </c>
       <c r="V40" t="n">
-        <v>497.97</v>
+        <v>494.95</v>
       </c>
       <c r="W40" t="n">
-        <v>498.65</v>
+        <v>501.87</v>
       </c>
       <c r="X40" t="n">
-        <v>491.1</v>
+        <v>491.33</v>
       </c>
       <c r="Y40" t="n">
-        <v>493.78</v>
+        <v>501.61</v>
       </c>
       <c r="Z40" t="n">
-        <v>464.1995</v>
+        <v>466.5442</v>
       </c>
       <c r="AA40" t="n">
-        <v>430.0757</v>
+        <v>430.1492</v>
       </c>
       <c r="AB40" t="n">
         <v>535.3375423278808</v>
@@ -6920,26 +6942,26 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>21 sep</t>
+          <t>22 sep</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>41.04</v>
+        <v>40.84</v>
       </c>
       <c r="C41" t="n">
-        <v>41.4</v>
+        <v>41.165</v>
       </c>
       <c r="D41" t="n">
-        <v>40.775</v>
+        <v>40.215</v>
       </c>
       <c r="E41" t="n">
-        <v>40.775</v>
+        <v>41.01</v>
       </c>
       <c r="F41" t="n">
-        <v>39.3341</v>
+        <v>39.4244</v>
       </c>
       <c r="G41" t="n">
-        <v>35.6939</v>
+        <v>35.746</v>
       </c>
       <c r="H41" t="n">
         <v>45.05751734733581</v>
@@ -6949,26 +6971,26 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>21 sep</t>
+          <t>22 sep</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>184.7</v>
+        <v>182.14</v>
       </c>
       <c r="M41" t="n">
-        <v>185.86</v>
+        <v>187.48</v>
       </c>
       <c r="N41" t="n">
-        <v>182.48</v>
+        <v>181.52</v>
       </c>
       <c r="O41" t="n">
-        <v>182.86</v>
+        <v>182.32</v>
       </c>
       <c r="P41" t="n">
-        <v>171.0432</v>
+        <v>171.9552</v>
       </c>
       <c r="Q41" t="n">
-        <v>165.4052</v>
+        <v>165.2836</v>
       </c>
       <c r="R41" t="n">
         <v>191.5557367172241</v>
@@ -6978,26 +7000,26 @@
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>21 sep</t>
+          <t>22 sep</t>
         </is>
       </c>
       <c r="V41" t="n">
-        <v>494.95</v>
+        <v>507.32</v>
       </c>
       <c r="W41" t="n">
-        <v>501.87</v>
+        <v>508.5</v>
       </c>
       <c r="X41" t="n">
-        <v>491.33</v>
+        <v>493.65</v>
       </c>
       <c r="Y41" t="n">
-        <v>501.61</v>
+        <v>498</v>
       </c>
       <c r="Z41" t="n">
-        <v>466.5442</v>
+        <v>468.699</v>
       </c>
       <c r="AA41" t="n">
-        <v>430.1492</v>
+        <v>430.2656</v>
       </c>
       <c r="AB41" t="n">
         <v>535.3375423278808</v>
@@ -7009,26 +7031,26 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>22 sep</t>
+          <t>23 sep</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>40.84</v>
+        <v>41</v>
       </c>
       <c r="C42" t="n">
-        <v>41.165</v>
+        <v>41.755</v>
       </c>
       <c r="D42" t="n">
-        <v>40.215</v>
+        <v>40.995</v>
       </c>
       <c r="E42" t="n">
-        <v>41.01</v>
+        <v>41.69</v>
       </c>
       <c r="F42" t="n">
-        <v>39.4244</v>
+        <v>39.5272</v>
       </c>
       <c r="G42" t="n">
-        <v>35.746</v>
+        <v>35.8024</v>
       </c>
       <c r="H42" t="n">
         <v>45.05751734733581</v>
@@ -7038,26 +7060,26 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>22 sep</t>
+          <t>23 sep</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>182.14</v>
+        <v>184.9</v>
       </c>
       <c r="M42" t="n">
-        <v>187.48</v>
+        <v>187.8</v>
       </c>
       <c r="N42" t="n">
-        <v>181.52</v>
+        <v>183.48</v>
       </c>
       <c r="O42" t="n">
-        <v>182.32</v>
+        <v>186.46</v>
       </c>
       <c r="P42" t="n">
-        <v>171.9552</v>
+        <v>172.9448</v>
       </c>
       <c r="Q42" t="n">
-        <v>165.2836</v>
+        <v>165.1675</v>
       </c>
       <c r="R42" t="n">
         <v>191.5557367172241</v>
@@ -7067,26 +7089,26 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>22 sep</t>
+          <t>23 sep</t>
         </is>
       </c>
       <c r="V42" t="n">
-        <v>507.32</v>
+        <v>500.76</v>
       </c>
       <c r="W42" t="n">
-        <v>508.5</v>
+        <v>509.44</v>
       </c>
       <c r="X42" t="n">
-        <v>493.65</v>
+        <v>495.88</v>
       </c>
       <c r="Y42" t="n">
-        <v>498</v>
+        <v>500.59</v>
       </c>
       <c r="Z42" t="n">
-        <v>468.699</v>
+        <v>471.0267</v>
       </c>
       <c r="AA42" t="n">
-        <v>430.2656</v>
+        <v>430.3795</v>
       </c>
       <c r="AB42" t="n">
         <v>535.3375423278808</v>
@@ -7098,26 +7120,26 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>23 sep</t>
+          <t>24 sep</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>41</v>
+        <v>41.825</v>
       </c>
       <c r="C43" t="n">
-        <v>41.755</v>
+        <v>42.52</v>
       </c>
       <c r="D43" t="n">
-        <v>40.995</v>
+        <v>41.78</v>
       </c>
       <c r="E43" t="n">
-        <v>41.69</v>
+        <v>42.43</v>
       </c>
       <c r="F43" t="n">
-        <v>39.5272</v>
+        <v>39.6382</v>
       </c>
       <c r="G43" t="n">
-        <v>35.8024</v>
+        <v>35.8638</v>
       </c>
       <c r="H43" t="n">
         <v>45.05751734733581</v>
@@ -7127,26 +7149,26 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>23 sep</t>
+          <t>24 sep</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>184.9</v>
+        <v>184.52</v>
       </c>
       <c r="M43" t="n">
-        <v>187.8</v>
+        <v>185.5</v>
       </c>
       <c r="N43" t="n">
-        <v>183.48</v>
+        <v>182.26</v>
       </c>
       <c r="O43" t="n">
-        <v>186.46</v>
+        <v>184.18</v>
       </c>
       <c r="P43" t="n">
-        <v>172.9448</v>
+        <v>173.8756</v>
       </c>
       <c r="Q43" t="n">
-        <v>165.1675</v>
+        <v>165.0554</v>
       </c>
       <c r="R43" t="n">
         <v>191.5557367172241</v>
@@ -7156,26 +7178,26 @@
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>23 sep</t>
+          <t>24 sep</t>
         </is>
       </c>
       <c r="V43" t="n">
-        <v>500.76</v>
+        <v>495.07</v>
       </c>
       <c r="W43" t="n">
-        <v>509.44</v>
+        <v>498.9</v>
       </c>
       <c r="X43" t="n">
-        <v>495.88</v>
+        <v>491.22</v>
       </c>
       <c r="Y43" t="n">
-        <v>500.59</v>
+        <v>497.93</v>
       </c>
       <c r="Z43" t="n">
-        <v>471.0267</v>
+        <v>473.0876</v>
       </c>
       <c r="AA43" t="n">
-        <v>430.3795</v>
+        <v>430.4686</v>
       </c>
       <c r="AB43" t="n">
         <v>535.3375423278808</v>
@@ -7187,26 +7209,26 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>24 sep</t>
+          <t>25 sep</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>41.825</v>
+        <v>41.99</v>
       </c>
       <c r="C44" t="n">
-        <v>42.52</v>
+        <v>42.33</v>
       </c>
       <c r="D44" t="n">
-        <v>41.78</v>
+        <v>41.71</v>
       </c>
       <c r="E44" t="n">
-        <v>42.43</v>
+        <v>42.06</v>
       </c>
       <c r="F44" t="n">
-        <v>39.6382</v>
+        <v>39.7263</v>
       </c>
       <c r="G44" t="n">
-        <v>35.8638</v>
+        <v>35.9239</v>
       </c>
       <c r="H44" t="n">
         <v>45.05751734733581</v>
@@ -7216,26 +7238,26 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>24 sep</t>
+          <t>25 sep</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>184.52</v>
+        <v>184.42</v>
       </c>
       <c r="M44" t="n">
-        <v>185.5</v>
+        <v>185.92</v>
       </c>
       <c r="N44" t="n">
-        <v>182.26</v>
+        <v>183.76</v>
       </c>
       <c r="O44" t="n">
-        <v>184.18</v>
+        <v>185.92</v>
       </c>
       <c r="P44" t="n">
-        <v>173.8756</v>
+        <v>174.8356</v>
       </c>
       <c r="Q44" t="n">
-        <v>165.0554</v>
+        <v>164.9525</v>
       </c>
       <c r="R44" t="n">
         <v>191.5557367172241</v>
@@ -7245,26 +7267,26 @@
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>24 sep</t>
+          <t>25 sep</t>
         </is>
       </c>
       <c r="V44" t="n">
-        <v>495.07</v>
+        <v>499.04</v>
       </c>
       <c r="W44" t="n">
-        <v>498.9</v>
+        <v>519.4</v>
       </c>
       <c r="X44" t="n">
-        <v>491.22</v>
+        <v>497.25</v>
       </c>
       <c r="Y44" t="n">
-        <v>497.93</v>
+        <v>516.17</v>
       </c>
       <c r="Z44" t="n">
-        <v>473.0876</v>
+        <v>475.4041</v>
       </c>
       <c r="AA44" t="n">
-        <v>430.4686</v>
+        <v>430.6098</v>
       </c>
       <c r="AB44" t="n">
         <v>535.3375423278808</v>
@@ -7276,26 +7298,26 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>25 sep</t>
+          <t>28 sep</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>41.99</v>
+        <v>42.45</v>
       </c>
       <c r="C45" t="n">
-        <v>42.33</v>
+        <v>42.995</v>
       </c>
       <c r="D45" t="n">
-        <v>41.71</v>
+        <v>42.38</v>
       </c>
       <c r="E45" t="n">
-        <v>42.06</v>
+        <v>42.725</v>
       </c>
       <c r="F45" t="n">
-        <v>39.7263</v>
+        <v>39.8301</v>
       </c>
       <c r="G45" t="n">
-        <v>35.9239</v>
+        <v>35.9888</v>
       </c>
       <c r="H45" t="n">
         <v>45.05751734733581</v>
@@ -7305,26 +7327,26 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>25 sep</t>
+          <t>28 sep</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>184.42</v>
+        <v>185.2</v>
       </c>
       <c r="M45" t="n">
-        <v>185.92</v>
+        <v>186.76</v>
       </c>
       <c r="N45" t="n">
-        <v>183.76</v>
+        <v>178.88</v>
       </c>
       <c r="O45" t="n">
-        <v>185.92</v>
+        <v>184.02</v>
       </c>
       <c r="P45" t="n">
-        <v>174.8356</v>
+        <v>175.7508</v>
       </c>
       <c r="Q45" t="n">
-        <v>164.9525</v>
+        <v>164.8355</v>
       </c>
       <c r="R45" t="n">
         <v>191.5557367172241</v>
@@ -7334,26 +7356,26 @@
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>25 sep</t>
+          <t>28 sep</t>
         </is>
       </c>
       <c r="V45" t="n">
-        <v>499.04</v>
+        <v>505.47</v>
       </c>
       <c r="W45" t="n">
-        <v>519.4</v>
+        <v>513.33</v>
       </c>
       <c r="X45" t="n">
-        <v>497.25</v>
+        <v>502.22</v>
       </c>
       <c r="Y45" t="n">
-        <v>516.17</v>
+        <v>509.22</v>
       </c>
       <c r="Z45" t="n">
-        <v>475.4041</v>
+        <v>477.7269</v>
       </c>
       <c r="AA45" t="n">
-        <v>430.6098</v>
+        <v>430.7113</v>
       </c>
       <c r="AB45" t="n">
         <v>535.3375423278808</v>
@@ -7365,26 +7387,26 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>28 sep</t>
+          <t>29 sep</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>42.45</v>
+        <v>42.57</v>
       </c>
       <c r="C46" t="n">
-        <v>42.995</v>
+        <v>42.665</v>
       </c>
       <c r="D46" t="n">
-        <v>42.38</v>
+        <v>41.73</v>
       </c>
       <c r="E46" t="n">
-        <v>42.725</v>
+        <v>42.05</v>
       </c>
       <c r="F46" t="n">
-        <v>39.8301</v>
+        <v>39.9146</v>
       </c>
       <c r="G46" t="n">
-        <v>35.9888</v>
+        <v>36.0498</v>
       </c>
       <c r="H46" t="n">
         <v>45.05751734733581</v>
@@ -7394,26 +7416,26 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>28 sep</t>
+          <t>29 sep</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>185.2</v>
+        <v>183.22</v>
       </c>
       <c r="M46" t="n">
-        <v>186.76</v>
+        <v>186.34</v>
       </c>
       <c r="N46" t="n">
-        <v>178.88</v>
+        <v>182.28</v>
       </c>
       <c r="O46" t="n">
-        <v>184.02</v>
+        <v>185.32</v>
       </c>
       <c r="P46" t="n">
-        <v>175.7508</v>
+        <v>176.7288</v>
       </c>
       <c r="Q46" t="n">
-        <v>164.8355</v>
+        <v>164.733</v>
       </c>
       <c r="R46" t="n">
         <v>191.5557367172241</v>
@@ -7423,26 +7445,26 @@
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>28 sep</t>
+          <t>29 sep</t>
         </is>
       </c>
       <c r="V46" t="n">
-        <v>505.47</v>
+        <v>508.31</v>
       </c>
       <c r="W46" t="n">
-        <v>513.33</v>
+        <v>513.64</v>
       </c>
       <c r="X46" t="n">
-        <v>502.22</v>
+        <v>502.4</v>
       </c>
       <c r="Y46" t="n">
-        <v>509.22</v>
+        <v>508.96</v>
       </c>
       <c r="Z46" t="n">
-        <v>477.7269</v>
+        <v>479.8754</v>
       </c>
       <c r="AA46" t="n">
-        <v>430.7113</v>
+        <v>430.8784</v>
       </c>
       <c r="AB46" t="n">
         <v>535.3375423278808</v>
@@ -7454,26 +7476,26 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>29 sep</t>
+          <t>30 sep</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>42.57</v>
+        <v>41.975</v>
       </c>
       <c r="C47" t="n">
-        <v>42.665</v>
+        <v>42.095</v>
       </c>
       <c r="D47" t="n">
-        <v>41.73</v>
+        <v>41.58</v>
       </c>
       <c r="E47" t="n">
-        <v>42.05</v>
+        <v>41.91</v>
       </c>
       <c r="F47" t="n">
-        <v>39.9146</v>
+        <v>39.9874</v>
       </c>
       <c r="G47" t="n">
-        <v>36.0498</v>
+        <v>36.1135</v>
       </c>
       <c r="H47" t="n">
         <v>45.05751734733581</v>
@@ -7483,26 +7505,26 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>29 sep</t>
+          <t>30 sep</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>183.22</v>
+        <v>184.5</v>
       </c>
       <c r="M47" t="n">
-        <v>186.34</v>
+        <v>186.2</v>
       </c>
       <c r="N47" t="n">
-        <v>182.28</v>
+        <v>181.06</v>
       </c>
       <c r="O47" t="n">
-        <v>185.32</v>
+        <v>185.66</v>
       </c>
       <c r="P47" t="n">
-        <v>176.7288</v>
+        <v>177.8012</v>
       </c>
       <c r="Q47" t="n">
-        <v>164.733</v>
+        <v>164.6377</v>
       </c>
       <c r="R47" t="n">
         <v>191.5557367172241</v>
@@ -7512,26 +7534,26 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>29 sep</t>
+          <t>30 sep</t>
         </is>
       </c>
       <c r="V47" t="n">
-        <v>508.31</v>
+        <v>511.61</v>
       </c>
       <c r="W47" t="n">
-        <v>513.64</v>
+        <v>519.83</v>
       </c>
       <c r="X47" t="n">
-        <v>502.4</v>
+        <v>510.31</v>
       </c>
       <c r="Y47" t="n">
-        <v>508.96</v>
+        <v>512.9</v>
       </c>
       <c r="Z47" t="n">
-        <v>479.8754</v>
+        <v>482.1933</v>
       </c>
       <c r="AA47" t="n">
-        <v>430.8784</v>
+        <v>431.0408</v>
       </c>
       <c r="AB47" t="n">
         <v>535.3375423278808</v>
@@ -7543,26 +7565,26 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>30 sep</t>
+          <t>1 okt</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>41.975</v>
+        <v>41.625</v>
       </c>
       <c r="C48" t="n">
-        <v>42.095</v>
+        <v>42.36</v>
       </c>
       <c r="D48" t="n">
-        <v>41.58</v>
+        <v>41.165</v>
       </c>
       <c r="E48" t="n">
-        <v>41.91</v>
+        <v>42.24</v>
       </c>
       <c r="F48" t="n">
-        <v>39.9874</v>
+        <v>40.0562</v>
       </c>
       <c r="G48" t="n">
-        <v>36.1135</v>
+        <v>36.1777</v>
       </c>
       <c r="H48" t="n">
         <v>45.05751734733581</v>
@@ -7572,26 +7594,26 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>30 sep</t>
+          <t>1 okt</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>184.5</v>
+        <v>184.68</v>
       </c>
       <c r="M48" t="n">
-        <v>186.2</v>
+        <v>190.26</v>
       </c>
       <c r="N48" t="n">
-        <v>181.06</v>
+        <v>181.34</v>
       </c>
       <c r="O48" t="n">
-        <v>185.66</v>
+        <v>186.74</v>
       </c>
       <c r="P48" t="n">
-        <v>177.8012</v>
+        <v>178.9696</v>
       </c>
       <c r="Q48" t="n">
-        <v>164.6377</v>
+        <v>164.5407</v>
       </c>
       <c r="R48" t="n">
         <v>191.5557367172241</v>
@@ -7601,26 +7623,26 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>30 sep</t>
+          <t>1 okt</t>
         </is>
       </c>
       <c r="V48" t="n">
-        <v>511.61</v>
+        <v>519.88</v>
       </c>
       <c r="W48" t="n">
-        <v>519.83</v>
+        <v>522.85</v>
       </c>
       <c r="X48" t="n">
-        <v>510.31</v>
+        <v>512.17</v>
       </c>
       <c r="Y48" t="n">
-        <v>512.9</v>
+        <v>512.8</v>
       </c>
       <c r="Z48" t="n">
-        <v>482.1933</v>
+        <v>484.6572</v>
       </c>
       <c r="AA48" t="n">
-        <v>431.0408</v>
+        <v>431.2272</v>
       </c>
       <c r="AB48" t="n">
         <v>535.3375423278808</v>
@@ -7632,26 +7654,26 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1 okt</t>
+          <t>2 okt</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>41.625</v>
+        <v>42.11</v>
       </c>
       <c r="C49" t="n">
-        <v>42.36</v>
+        <v>42.745</v>
       </c>
       <c r="D49" t="n">
-        <v>41.165</v>
+        <v>41.985</v>
       </c>
       <c r="E49" t="n">
-        <v>42.24</v>
+        <v>42.4</v>
       </c>
       <c r="F49" t="n">
-        <v>40.0562</v>
+        <v>40.1364</v>
       </c>
       <c r="G49" t="n">
-        <v>36.1777</v>
+        <v>36.2422</v>
       </c>
       <c r="H49" t="n">
         <v>45.05751734733581</v>
@@ -7661,26 +7683,26 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>1 okt</t>
+          <t>2 okt</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>184.68</v>
+        <v>187.82</v>
       </c>
       <c r="M49" t="n">
-        <v>190.26</v>
+        <v>188.74</v>
       </c>
       <c r="N49" t="n">
-        <v>181.34</v>
+        <v>183.92</v>
       </c>
       <c r="O49" t="n">
-        <v>186.74</v>
+        <v>183.92</v>
       </c>
       <c r="P49" t="n">
-        <v>178.9696</v>
+        <v>179.844</v>
       </c>
       <c r="Q49" t="n">
-        <v>164.5407</v>
+        <v>164.4442</v>
       </c>
       <c r="R49" t="n">
         <v>191.5557367172241</v>
@@ -7690,26 +7712,26 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>1 okt</t>
+          <t>2 okt</t>
         </is>
       </c>
       <c r="V49" t="n">
-        <v>519.88</v>
+        <v>519.39</v>
       </c>
       <c r="W49" t="n">
-        <v>522.85</v>
+        <v>522.5</v>
       </c>
       <c r="X49" t="n">
-        <v>512.17</v>
+        <v>513.66</v>
       </c>
       <c r="Y49" t="n">
-        <v>512.8</v>
+        <v>517.53</v>
       </c>
       <c r="Z49" t="n">
-        <v>484.6572</v>
+        <v>487.3905</v>
       </c>
       <c r="AA49" t="n">
-        <v>431.2272</v>
+        <v>431.4557</v>
       </c>
       <c r="AB49" t="n">
         <v>535.3375423278808</v>
@@ -7721,26 +7743,26 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2 okt</t>
+          <t>5 okt</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>42.11</v>
+        <v>42.645</v>
       </c>
       <c r="C50" t="n">
-        <v>42.745</v>
+        <v>43.11</v>
       </c>
       <c r="D50" t="n">
-        <v>41.985</v>
+        <v>42.35</v>
       </c>
       <c r="E50" t="n">
-        <v>42.4</v>
+        <v>42.865</v>
       </c>
       <c r="F50" t="n">
-        <v>40.1364</v>
+        <v>40.2347</v>
       </c>
       <c r="G50" t="n">
-        <v>36.2422</v>
+        <v>36.3069</v>
       </c>
       <c r="H50" t="n">
         <v>45.05751734733581</v>
@@ -7750,26 +7772,26 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2 okt</t>
+          <t>5 okt</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>187.82</v>
+        <v>185.06</v>
       </c>
       <c r="M50" t="n">
-        <v>188.74</v>
+        <v>188.5</v>
       </c>
       <c r="N50" t="n">
-        <v>183.92</v>
+        <v>184.66</v>
       </c>
       <c r="O50" t="n">
-        <v>183.92</v>
+        <v>185.04</v>
       </c>
       <c r="P50" t="n">
-        <v>179.844</v>
+        <v>180.5192</v>
       </c>
       <c r="Q50" t="n">
-        <v>164.4442</v>
+        <v>164.3515</v>
       </c>
       <c r="R50" t="n">
         <v>191.5557367172241</v>
@@ -7779,26 +7801,26 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>2 okt</t>
+          <t>5 okt</t>
         </is>
       </c>
       <c r="V50" t="n">
-        <v>519.39</v>
+        <v>521.62</v>
       </c>
       <c r="W50" t="n">
-        <v>522.5</v>
+        <v>532.35</v>
       </c>
       <c r="X50" t="n">
-        <v>513.66</v>
+        <v>521.47</v>
       </c>
       <c r="Y50" t="n">
-        <v>517.53</v>
+        <v>525.1799999999999</v>
       </c>
       <c r="Z50" t="n">
-        <v>487.3905</v>
+        <v>490.2745</v>
       </c>
       <c r="AA50" t="n">
-        <v>431.4557</v>
+        <v>431.7147</v>
       </c>
       <c r="AB50" t="n">
         <v>535.3375423278808</v>
@@ -7810,26 +7832,26 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>5 okt</t>
+          <t>6 okt</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>42.645</v>
+        <v>42.86</v>
       </c>
       <c r="C51" t="n">
-        <v>43.11</v>
+        <v>43.285</v>
       </c>
       <c r="D51" t="n">
-        <v>42.35</v>
+        <v>42.43</v>
       </c>
       <c r="E51" t="n">
-        <v>42.865</v>
+        <v>43.185</v>
       </c>
       <c r="F51" t="n">
-        <v>40.2347</v>
+        <v>40.349</v>
       </c>
       <c r="G51" t="n">
-        <v>36.3069</v>
+        <v>36.3726</v>
       </c>
       <c r="H51" t="n">
         <v>45.05751734733581</v>
@@ -7839,26 +7861,26 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>5 okt</t>
+          <t>6 okt</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>185.06</v>
+        <v>186.56</v>
       </c>
       <c r="M51" t="n">
-        <v>188.5</v>
+        <v>190.22</v>
       </c>
       <c r="N51" t="n">
-        <v>184.66</v>
+        <v>186.06</v>
       </c>
       <c r="O51" t="n">
-        <v>185.04</v>
+        <v>188.6</v>
       </c>
       <c r="P51" t="n">
-        <v>180.5192</v>
+        <v>181.1064</v>
       </c>
       <c r="Q51" t="n">
-        <v>164.3515</v>
+        <v>164.2647</v>
       </c>
       <c r="R51" t="n">
         <v>191.5557367172241</v>
@@ -7868,26 +7890,26 @@
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>5 okt</t>
+          <t>6 okt</t>
         </is>
       </c>
       <c r="V51" t="n">
-        <v>521.62</v>
+        <v>531.6799999999999</v>
       </c>
       <c r="W51" t="n">
-        <v>532.35</v>
+        <v>535.6900000000001</v>
       </c>
       <c r="X51" t="n">
-        <v>521.47</v>
+        <v>528.78</v>
       </c>
       <c r="Y51" t="n">
-        <v>525.1799999999999</v>
+        <v>529.3</v>
       </c>
       <c r="Z51" t="n">
-        <v>490.2745</v>
+        <v>493.0931</v>
       </c>
       <c r="AA51" t="n">
-        <v>431.7147</v>
+        <v>431.9956</v>
       </c>
       <c r="AB51" t="n">
         <v>535.3375423278808</v>
@@ -7899,26 +7921,26 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>6 okt</t>
+          <t>7 okt</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>42.86</v>
+        <v>43.37</v>
       </c>
       <c r="C52" t="n">
-        <v>43.285</v>
+        <v>43.835</v>
       </c>
       <c r="D52" t="n">
-        <v>42.43</v>
+        <v>43.145</v>
       </c>
       <c r="E52" t="n">
-        <v>43.185</v>
+        <v>43.25</v>
       </c>
       <c r="F52" t="n">
-        <v>40.349</v>
+        <v>40.4451</v>
       </c>
       <c r="G52" t="n">
-        <v>36.3726</v>
+        <v>36.4388</v>
       </c>
       <c r="H52" t="n">
         <v>45.05751734733581</v>
@@ -7928,26 +7950,26 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>6 okt</t>
+          <t>7 okt</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>186.56</v>
+        <v>187</v>
       </c>
       <c r="M52" t="n">
-        <v>190.22</v>
+        <v>188.72</v>
       </c>
       <c r="N52" t="n">
-        <v>186.06</v>
+        <v>186.04</v>
       </c>
       <c r="O52" t="n">
-        <v>188.6</v>
+        <v>187.62</v>
       </c>
       <c r="P52" t="n">
-        <v>181.1064</v>
+        <v>181.618</v>
       </c>
       <c r="Q52" t="n">
-        <v>164.2647</v>
+        <v>164.1762</v>
       </c>
       <c r="R52" t="n">
         <v>191.5557367172241</v>
@@ -7957,26 +7979,26 @@
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>6 okt</t>
+          <t>7 okt</t>
         </is>
       </c>
       <c r="V52" t="n">
-        <v>531.6799999999999</v>
+        <v>530.73</v>
       </c>
       <c r="W52" t="n">
-        <v>535.6900000000001</v>
+        <v>531.73</v>
       </c>
       <c r="X52" t="n">
-        <v>528.78</v>
+        <v>524.6900000000001</v>
       </c>
       <c r="Y52" t="n">
-        <v>529.3</v>
+        <v>529.76</v>
       </c>
       <c r="Z52" t="n">
-        <v>493.0931</v>
+        <v>495.8361</v>
       </c>
       <c r="AA52" t="n">
-        <v>431.9956</v>
+        <v>432.2398</v>
       </c>
       <c r="AB52" t="n">
         <v>535.3375423278808</v>
@@ -7988,26 +8010,26 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>7 okt</t>
+          <t>8 okt</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>43.37</v>
+        <v>43.555</v>
       </c>
       <c r="C53" t="n">
-        <v>43.835</v>
+        <v>44.815</v>
       </c>
       <c r="D53" t="n">
-        <v>43.145</v>
+        <v>43.5425</v>
       </c>
       <c r="E53" t="n">
-        <v>43.25</v>
+        <v>44.75</v>
       </c>
       <c r="F53" t="n">
-        <v>40.4451</v>
+        <v>40.5699</v>
       </c>
       <c r="G53" t="n">
-        <v>36.4388</v>
+        <v>36.5123</v>
       </c>
       <c r="H53" t="n">
         <v>45.05751734733581</v>
@@ -8017,26 +8039,26 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>7 okt</t>
+          <t>8 okt</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>187</v>
+        <v>187.04</v>
       </c>
       <c r="M53" t="n">
-        <v>188.72</v>
+        <v>189.82</v>
       </c>
       <c r="N53" t="n">
-        <v>186.04</v>
+        <v>183.76</v>
       </c>
       <c r="O53" t="n">
-        <v>187.62</v>
+        <v>184.62</v>
       </c>
       <c r="P53" t="n">
-        <v>181.618</v>
+        <v>182.192</v>
       </c>
       <c r="Q53" t="n">
-        <v>164.1762</v>
+        <v>164.074</v>
       </c>
       <c r="R53" t="n">
         <v>191.5557367172241</v>
@@ -8046,26 +8068,26 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>7 okt</t>
+          <t>8 okt</t>
         </is>
       </c>
       <c r="V53" t="n">
-        <v>530.73</v>
+        <v>529.8099999999999</v>
       </c>
       <c r="W53" t="n">
-        <v>531.73</v>
+        <v>533.51</v>
       </c>
       <c r="X53" t="n">
-        <v>524.6900000000001</v>
+        <v>518.79</v>
       </c>
       <c r="Y53" t="n">
-        <v>529.76</v>
+        <v>522.61</v>
       </c>
       <c r="Z53" t="n">
-        <v>495.8361</v>
+        <v>498.4921</v>
       </c>
       <c r="AA53" t="n">
-        <v>432.2398</v>
+        <v>432.4385</v>
       </c>
       <c r="AB53" t="n">
         <v>535.3375423278808</v>
@@ -8077,26 +8099,26 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>8 okt</t>
+          <t>9 okt</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>43.555</v>
+        <v>44.42</v>
       </c>
       <c r="C54" t="n">
-        <v>44.815</v>
+        <v>45.155</v>
       </c>
       <c r="D54" t="n">
-        <v>43.5425</v>
+        <v>43.94</v>
       </c>
       <c r="E54" t="n">
-        <v>44.75</v>
+        <v>45.035</v>
       </c>
       <c r="F54" t="n">
-        <v>40.5699</v>
+        <v>40.6842</v>
       </c>
       <c r="G54" t="n">
-        <v>36.5123</v>
+        <v>36.5866</v>
       </c>
       <c r="H54" t="n">
         <v>45.05751734733581</v>
@@ -8106,26 +8128,26 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>8 okt</t>
+          <t>9 okt</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>187.04</v>
+        <v>188.98</v>
       </c>
       <c r="M54" t="n">
-        <v>189.82</v>
+        <v>192.58</v>
       </c>
       <c r="N54" t="n">
-        <v>183.76</v>
+        <v>188.86</v>
       </c>
       <c r="O54" t="n">
-        <v>184.62</v>
+        <v>191.46</v>
       </c>
       <c r="P54" t="n">
-        <v>182.192</v>
+        <v>182.8676</v>
       </c>
       <c r="Q54" t="n">
-        <v>164.074</v>
+        <v>164.0101</v>
       </c>
       <c r="R54" t="n">
         <v>191.5557367172241</v>
@@ -8135,26 +8157,26 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>8 okt</t>
+          <t>9 okt</t>
         </is>
       </c>
       <c r="V54" t="n">
-        <v>529.8099999999999</v>
+        <v>528.24</v>
       </c>
       <c r="W54" t="n">
-        <v>533.51</v>
+        <v>537.22</v>
       </c>
       <c r="X54" t="n">
-        <v>518.79</v>
+        <v>526.24</v>
       </c>
       <c r="Y54" t="n">
-        <v>522.61</v>
+        <v>535.0700000000001</v>
       </c>
       <c r="Z54" t="n">
-        <v>498.4921</v>
+        <v>500.1885</v>
       </c>
       <c r="AA54" t="n">
-        <v>432.4385</v>
+        <v>432.7046</v>
       </c>
       <c r="AB54" t="n">
         <v>535.3375423278808</v>
@@ -8166,26 +8188,26 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>9 okt</t>
+          <t>12 okt</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>44.42</v>
+        <v>44.725</v>
       </c>
       <c r="C55" t="n">
-        <v>45.155</v>
+        <v>45.81</v>
       </c>
       <c r="D55" t="n">
-        <v>43.94</v>
+        <v>44.695</v>
       </c>
       <c r="E55" t="n">
-        <v>45.035</v>
+        <v>45.56</v>
       </c>
       <c r="F55" t="n">
-        <v>40.6842</v>
+        <v>40.8072</v>
       </c>
       <c r="G55" t="n">
-        <v>36.5866</v>
+        <v>36.6625</v>
       </c>
       <c r="H55" t="n">
         <v>45.05751734733581</v>
@@ -8195,26 +8217,26 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>9 okt</t>
+          <t>12 okt</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>188.98</v>
+        <v>190.58</v>
       </c>
       <c r="M55" t="n">
-        <v>192.58</v>
+        <v>197.88</v>
       </c>
       <c r="N55" t="n">
-        <v>188.86</v>
+        <v>189.78</v>
       </c>
       <c r="O55" t="n">
-        <v>191.46</v>
+        <v>194.46</v>
       </c>
       <c r="P55" t="n">
-        <v>182.8676</v>
+        <v>183.464</v>
       </c>
       <c r="Q55" t="n">
-        <v>164.0101</v>
+        <v>163.9576</v>
       </c>
       <c r="R55" t="n">
         <v>191.5557367172241</v>
@@ -8224,26 +8246,26 @@
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>9 okt</t>
+          <t>12 okt</t>
         </is>
       </c>
       <c r="V55" t="n">
-        <v>528.24</v>
+        <v>537.53</v>
       </c>
       <c r="W55" t="n">
-        <v>537.22</v>
+        <v>542.74</v>
       </c>
       <c r="X55" t="n">
-        <v>526.24</v>
+        <v>535.7</v>
       </c>
       <c r="Y55" t="n">
-        <v>535.0700000000001</v>
+        <v>541.15</v>
       </c>
       <c r="Z55" t="n">
-        <v>500.1885</v>
+        <v>501.7346</v>
       </c>
       <c r="AA55" t="n">
-        <v>432.7046</v>
+        <v>432.9914</v>
       </c>
       <c r="AB55" t="n">
         <v>535.3375423278808</v>
@@ -8255,26 +8277,26 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>12 okt</t>
+          <t>13 okt</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>44.725</v>
+        <v>45.69</v>
       </c>
       <c r="C56" t="n">
-        <v>45.81</v>
+        <v>45.97</v>
       </c>
       <c r="D56" t="n">
-        <v>44.695</v>
+        <v>45.35</v>
       </c>
       <c r="E56" t="n">
-        <v>45.56</v>
+        <v>45.95</v>
       </c>
       <c r="F56" t="n">
-        <v>40.8072</v>
+        <v>40.9565</v>
       </c>
       <c r="G56" t="n">
-        <v>36.6625</v>
+        <v>36.7398</v>
       </c>
       <c r="H56" t="n">
         <v>45.05751734733581</v>
@@ -8284,26 +8306,26 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>12 okt</t>
+          <t>13 okt</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>190.58</v>
+        <v>196</v>
       </c>
       <c r="M56" t="n">
-        <v>197.88</v>
+        <v>198.18</v>
       </c>
       <c r="N56" t="n">
-        <v>189.78</v>
+        <v>194.02</v>
       </c>
       <c r="O56" t="n">
-        <v>194.46</v>
+        <v>197.28</v>
       </c>
       <c r="P56" t="n">
-        <v>183.464</v>
+        <v>184.062</v>
       </c>
       <c r="Q56" t="n">
-        <v>163.9576</v>
+        <v>163.9196</v>
       </c>
       <c r="R56" t="n">
         <v>191.5557367172241</v>
@@ -8313,26 +8335,26 @@
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>12 okt</t>
+          <t>13 okt</t>
         </is>
       </c>
       <c r="V56" t="n">
-        <v>537.53</v>
+        <v>544.64</v>
       </c>
       <c r="W56" t="n">
-        <v>542.74</v>
+        <v>551.15</v>
       </c>
       <c r="X56" t="n">
-        <v>535.7</v>
+        <v>543.0599999999999</v>
       </c>
       <c r="Y56" t="n">
-        <v>541.15</v>
+        <v>543.45</v>
       </c>
       <c r="Z56" t="n">
-        <v>501.7346</v>
+        <v>502.8689</v>
       </c>
       <c r="AA56" t="n">
-        <v>432.9914</v>
+        <v>433.2839</v>
       </c>
       <c r="AB56" t="n">
         <v>535.3375423278808</v>
@@ -8344,26 +8366,26 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>13 okt</t>
+          <t>14 okt</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>45.69</v>
+        <v>45.95</v>
       </c>
       <c r="C57" t="n">
-        <v>45.97</v>
+        <v>46.675</v>
       </c>
       <c r="D57" t="n">
-        <v>45.35</v>
+        <v>45.91</v>
       </c>
       <c r="E57" t="n">
-        <v>45.95</v>
+        <v>46.455</v>
       </c>
       <c r="F57" t="n">
-        <v>40.9565</v>
+        <v>41.125</v>
       </c>
       <c r="G57" t="n">
-        <v>36.7398</v>
+        <v>36.8183</v>
       </c>
       <c r="H57" t="n">
         <v>45.05751734733581</v>
@@ -8373,26 +8395,26 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>13 okt</t>
+          <t>14 okt</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>196</v>
+        <v>196.6</v>
       </c>
       <c r="M57" t="n">
-        <v>198.18</v>
+        <v>199.36</v>
       </c>
       <c r="N57" t="n">
-        <v>194.02</v>
+        <v>195.26</v>
       </c>
       <c r="O57" t="n">
-        <v>197.28</v>
+        <v>196.94</v>
       </c>
       <c r="P57" t="n">
-        <v>184.062</v>
+        <v>184.6156</v>
       </c>
       <c r="Q57" t="n">
-        <v>163.9196</v>
+        <v>163.9114</v>
       </c>
       <c r="R57" t="n">
         <v>191.5557367172241</v>
@@ -8402,26 +8424,26 @@
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>13 okt</t>
+          <t>14 okt</t>
         </is>
       </c>
       <c r="V57" t="n">
-        <v>544.64</v>
+        <v>545.27</v>
       </c>
       <c r="W57" t="n">
-        <v>551.15</v>
+        <v>545.75</v>
       </c>
       <c r="X57" t="n">
-        <v>543.0599999999999</v>
+        <v>532.54</v>
       </c>
       <c r="Y57" t="n">
-        <v>543.45</v>
+        <v>533.6900000000001</v>
       </c>
       <c r="Z57" t="n">
-        <v>502.8689</v>
+        <v>503.705</v>
       </c>
       <c r="AA57" t="n">
-        <v>433.2839</v>
+        <v>433.5292</v>
       </c>
       <c r="AB57" t="n">
         <v>535.3375423278808</v>
@@ -8433,26 +8455,26 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>14 okt</t>
+          <t>15 okt</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>45.95</v>
+        <v>46.295</v>
       </c>
       <c r="C58" t="n">
-        <v>46.675</v>
+        <v>46.735</v>
       </c>
       <c r="D58" t="n">
-        <v>45.91</v>
+        <v>46.125</v>
       </c>
       <c r="E58" t="n">
-        <v>46.455</v>
+        <v>46.375</v>
       </c>
       <c r="F58" t="n">
-        <v>41.125</v>
+        <v>41.2847</v>
       </c>
       <c r="G58" t="n">
-        <v>36.8183</v>
+        <v>36.8966</v>
       </c>
       <c r="H58" t="n">
         <v>45.05751734733581</v>
@@ -8462,26 +8484,26 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>14 okt</t>
+          <t>15 okt</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>196.6</v>
+        <v>199.48</v>
       </c>
       <c r="M58" t="n">
-        <v>199.36</v>
+        <v>203</v>
       </c>
       <c r="N58" t="n">
-        <v>195.26</v>
+        <v>196.98</v>
       </c>
       <c r="O58" t="n">
-        <v>196.94</v>
+        <v>201.25</v>
       </c>
       <c r="P58" t="n">
-        <v>184.6156</v>
+        <v>185.221</v>
       </c>
       <c r="Q58" t="n">
-        <v>163.9114</v>
+        <v>163.9038</v>
       </c>
       <c r="R58" t="n">
         <v>191.5557367172241</v>
@@ -8491,26 +8513,26 @@
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>14 okt</t>
+          <t>15 okt</t>
         </is>
       </c>
       <c r="V58" t="n">
-        <v>545.27</v>
+        <v>533.3200000000001</v>
       </c>
       <c r="W58" t="n">
-        <v>545.75</v>
+        <v>541.13</v>
       </c>
       <c r="X58" t="n">
-        <v>532.54</v>
+        <v>531.22</v>
       </c>
       <c r="Y58" t="n">
-        <v>533.6900000000001</v>
+        <v>539.4400000000001</v>
       </c>
       <c r="Z58" t="n">
-        <v>503.705</v>
+        <v>504.7629</v>
       </c>
       <c r="AA58" t="n">
-        <v>433.5292</v>
+        <v>433.8063</v>
       </c>
       <c r="AB58" t="n">
         <v>535.3375423278808</v>
@@ -8522,26 +8544,26 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>15 okt</t>
+          <t>16 okt</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>46.295</v>
+        <v>46.14</v>
       </c>
       <c r="C59" t="n">
-        <v>46.735</v>
+        <v>47.025</v>
       </c>
       <c r="D59" t="n">
-        <v>46.125</v>
+        <v>46.075</v>
       </c>
       <c r="E59" t="n">
-        <v>46.375</v>
+        <v>46.88</v>
       </c>
       <c r="F59" t="n">
-        <v>41.2847</v>
+        <v>41.4622</v>
       </c>
       <c r="G59" t="n">
-        <v>36.8966</v>
+        <v>36.977</v>
       </c>
       <c r="H59" t="n">
         <v>45.05751734733581</v>
@@ -8551,26 +8573,26 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>15 okt</t>
+          <t>16 okt</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>199.48</v>
+        <v>200.6</v>
       </c>
       <c r="M59" t="n">
-        <v>203</v>
+        <v>204.2</v>
       </c>
       <c r="N59" t="n">
-        <v>196.98</v>
+        <v>198.68</v>
       </c>
       <c r="O59" t="n">
-        <v>201.25</v>
+        <v>199.22</v>
       </c>
       <c r="P59" t="n">
-        <v>185.221</v>
+        <v>185.6462</v>
       </c>
       <c r="Q59" t="n">
-        <v>163.9038</v>
+        <v>163.9066</v>
       </c>
       <c r="R59" t="n">
         <v>191.5557367172241</v>
@@ -8580,26 +8602,26 @@
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>15 okt</t>
+          <t>16 okt</t>
         </is>
       </c>
       <c r="V59" t="n">
-        <v>533.3200000000001</v>
+        <v>541.3099999999999</v>
       </c>
       <c r="W59" t="n">
-        <v>541.13</v>
+        <v>543.8200000000001</v>
       </c>
       <c r="X59" t="n">
-        <v>531.22</v>
+        <v>524.4299999999999</v>
       </c>
       <c r="Y59" t="n">
-        <v>539.4400000000001</v>
+        <v>529.05</v>
       </c>
       <c r="Z59" t="n">
-        <v>504.7629</v>
+        <v>505.3655</v>
       </c>
       <c r="AA59" t="n">
-        <v>433.8063</v>
+        <v>434.0295</v>
       </c>
       <c r="AB59" t="n">
         <v>535.3375423278808</v>
@@ -8611,26 +8633,26 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>16 okt</t>
+          <t>19 okt</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>46.14</v>
+        <v>47.37</v>
       </c>
       <c r="C60" t="n">
-        <v>47.025</v>
+        <v>47.45</v>
       </c>
       <c r="D60" t="n">
-        <v>46.075</v>
+        <v>46.74</v>
       </c>
       <c r="E60" t="n">
-        <v>46.88</v>
+        <v>46.86</v>
       </c>
       <c r="F60" t="n">
-        <v>41.4622</v>
+        <v>41.6313</v>
       </c>
       <c r="G60" t="n">
-        <v>36.977</v>
+        <v>37.0625</v>
       </c>
       <c r="H60" t="n">
         <v>45.05751734733581</v>
@@ -8640,26 +8662,26 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>16 okt</t>
+          <t>19 okt</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>200.6</v>
+        <v>199.56</v>
       </c>
       <c r="M60" t="n">
-        <v>204.2</v>
+        <v>200.8</v>
       </c>
       <c r="N60" t="n">
-        <v>198.68</v>
+        <v>197.32</v>
       </c>
       <c r="O60" t="n">
-        <v>199.22</v>
+        <v>199.84</v>
       </c>
       <c r="P60" t="n">
-        <v>185.6462</v>
+        <v>186.057</v>
       </c>
       <c r="Q60" t="n">
-        <v>163.9066</v>
+        <v>163.8811</v>
       </c>
       <c r="R60" t="n">
         <v>191.5557367172241</v>
@@ -8669,26 +8691,26 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>16 okt</t>
+          <t>19 okt</t>
         </is>
       </c>
       <c r="V60" t="n">
-        <v>541.3099999999999</v>
+        <v>528.7</v>
       </c>
       <c r="W60" t="n">
-        <v>543.8200000000001</v>
+        <v>535.5700000000001</v>
       </c>
       <c r="X60" t="n">
-        <v>524.4299999999999</v>
+        <v>528.0599999999999</v>
       </c>
       <c r="Y60" t="n">
-        <v>529.05</v>
+        <v>533.52</v>
       </c>
       <c r="Z60" t="n">
-        <v>505.3655</v>
+        <v>506.0549</v>
       </c>
       <c r="AA60" t="n">
-        <v>434.0295</v>
+        <v>434.2942</v>
       </c>
       <c r="AB60" t="n">
         <v>535.3375423278808</v>
@@ -8700,26 +8722,26 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>19 okt</t>
+          <t>20 okt</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>47.37</v>
+        <v>46.875</v>
       </c>
       <c r="C61" t="n">
-        <v>47.45</v>
+        <v>47.505</v>
       </c>
       <c r="D61" t="n">
-        <v>46.74</v>
+        <v>46.36</v>
       </c>
       <c r="E61" t="n">
-        <v>46.86</v>
+        <v>46.57</v>
       </c>
       <c r="F61" t="n">
-        <v>41.6313</v>
+        <v>41.7834</v>
       </c>
       <c r="G61" t="n">
-        <v>37.0625</v>
+        <v>37.1516</v>
       </c>
       <c r="H61" t="n">
         <v>45.05751734733581</v>
@@ -8729,26 +8751,26 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>19 okt</t>
+          <t>20 okt</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>199.56</v>
+        <v>201.3</v>
       </c>
       <c r="M61" t="n">
-        <v>200.8</v>
+        <v>203.45</v>
       </c>
       <c r="N61" t="n">
-        <v>197.32</v>
+        <v>199.46</v>
       </c>
       <c r="O61" t="n">
-        <v>199.84</v>
+        <v>201.55</v>
       </c>
       <c r="P61" t="n">
-        <v>186.057</v>
+        <v>186.474</v>
       </c>
       <c r="Q61" t="n">
-        <v>163.8811</v>
+        <v>163.8736</v>
       </c>
       <c r="R61" t="n">
         <v>191.5557367172241</v>
@@ -8758,26 +8780,26 @@
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>19 okt</t>
+          <t>20 okt</t>
         </is>
       </c>
       <c r="V61" t="n">
-        <v>528.7</v>
+        <v>533.91</v>
       </c>
       <c r="W61" t="n">
-        <v>535.5700000000001</v>
+        <v>534.21</v>
       </c>
       <c r="X61" t="n">
-        <v>528.0599999999999</v>
+        <v>525.84</v>
       </c>
       <c r="Y61" t="n">
-        <v>533.52</v>
+        <v>531.87</v>
       </c>
       <c r="Z61" t="n">
-        <v>506.0549</v>
+        <v>506.5901</v>
       </c>
       <c r="AA61" t="n">
-        <v>434.2942</v>
+        <v>434.6038</v>
       </c>
       <c r="AB61" t="n">
         <v>535.3375423278808</v>
@@ -8789,26 +8811,26 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20 okt</t>
+          <t>21 okt</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>46.875</v>
+        <v>46.97</v>
       </c>
       <c r="C62" t="n">
-        <v>47.505</v>
+        <v>47.135</v>
       </c>
       <c r="D62" t="n">
-        <v>46.36</v>
+        <v>46.73</v>
       </c>
       <c r="E62" t="n">
-        <v>46.57</v>
+        <v>46.84</v>
       </c>
       <c r="F62" t="n">
-        <v>41.7834</v>
+        <v>41.9472</v>
       </c>
       <c r="G62" t="n">
-        <v>37.1516</v>
+        <v>37.2379</v>
       </c>
       <c r="H62" t="n">
         <v>45.05751734733581</v>
@@ -8818,26 +8840,26 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>20 okt</t>
+          <t>21 okt</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>201.3</v>
+        <v>201.8</v>
       </c>
       <c r="M62" t="n">
-        <v>203.45</v>
+        <v>208.65</v>
       </c>
       <c r="N62" t="n">
-        <v>199.46</v>
+        <v>200</v>
       </c>
       <c r="O62" t="n">
-        <v>201.55</v>
+        <v>208.65</v>
       </c>
       <c r="P62" t="n">
-        <v>186.474</v>
+        <v>187.1278</v>
       </c>
       <c r="Q62" t="n">
-        <v>163.8736</v>
+        <v>163.8728</v>
       </c>
       <c r="R62" t="n">
         <v>191.5557367172241</v>
@@ -8847,26 +8869,26 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>20 okt</t>
+          <t>21 okt</t>
         </is>
       </c>
       <c r="V62" t="n">
-        <v>533.91</v>
+        <v>529.4400000000001</v>
       </c>
       <c r="W62" t="n">
-        <v>534.21</v>
+        <v>533.28</v>
       </c>
       <c r="X62" t="n">
-        <v>525.84</v>
+        <v>525.02</v>
       </c>
       <c r="Y62" t="n">
-        <v>531.87</v>
+        <v>532.95</v>
       </c>
       <c r="Z62" t="n">
-        <v>506.5901</v>
+        <v>507.1919</v>
       </c>
       <c r="AA62" t="n">
-        <v>434.6038</v>
+        <v>434.9192</v>
       </c>
       <c r="AB62" t="n">
         <v>535.3375423278808</v>
@@ -8878,26 +8900,26 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>21 okt</t>
+          <t>22 okt</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>46.97</v>
+        <v>47.05</v>
       </c>
       <c r="C63" t="n">
-        <v>47.135</v>
+        <v>47.6</v>
       </c>
       <c r="D63" t="n">
-        <v>46.73</v>
+        <v>46.55</v>
       </c>
       <c r="E63" t="n">
-        <v>46.84</v>
+        <v>46.55</v>
       </c>
       <c r="F63" t="n">
-        <v>41.9472</v>
+        <v>42.1061</v>
       </c>
       <c r="G63" t="n">
-        <v>37.2379</v>
+        <v>37.3217</v>
       </c>
       <c r="H63" t="n">
         <v>45.05751734733581</v>
@@ -8907,26 +8929,26 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>21 okt</t>
+          <t>22 okt</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>201.8</v>
+        <v>207.75</v>
       </c>
       <c r="M63" t="n">
-        <v>208.65</v>
+        <v>216.65</v>
       </c>
       <c r="N63" t="n">
-        <v>200</v>
+        <v>205.1</v>
       </c>
       <c r="O63" t="n">
-        <v>208.65</v>
+        <v>215.35</v>
       </c>
       <c r="P63" t="n">
-        <v>187.1278</v>
+        <v>187.9272</v>
       </c>
       <c r="Q63" t="n">
-        <v>163.8728</v>
+        <v>163.9019</v>
       </c>
       <c r="R63" t="n">
         <v>191.5557367172241</v>
@@ -8936,26 +8958,26 @@
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>21 okt</t>
+          <t>22 okt</t>
         </is>
       </c>
       <c r="V63" t="n">
-        <v>529.4400000000001</v>
+        <v>533.14</v>
       </c>
       <c r="W63" t="n">
-        <v>533.28</v>
+        <v>533.6</v>
       </c>
       <c r="X63" t="n">
-        <v>525.02</v>
+        <v>520.3</v>
       </c>
       <c r="Y63" t="n">
-        <v>532.95</v>
+        <v>521.08</v>
       </c>
       <c r="Z63" t="n">
-        <v>507.1919</v>
+        <v>507.7834</v>
       </c>
       <c r="AA63" t="n">
-        <v>434.9192</v>
+        <v>435.1471</v>
       </c>
       <c r="AB63" t="n">
         <v>535.3375423278808</v>
@@ -8967,26 +8989,26 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>22 okt</t>
+          <t>23 okt</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>47.05</v>
+        <v>47.13</v>
       </c>
       <c r="C64" t="n">
-        <v>47.6</v>
+        <v>48.38</v>
       </c>
       <c r="D64" t="n">
-        <v>46.55</v>
+        <v>46.895</v>
       </c>
       <c r="E64" t="n">
-        <v>46.55</v>
+        <v>48.295</v>
       </c>
       <c r="F64" t="n">
-        <v>42.1061</v>
+        <v>42.2926</v>
       </c>
       <c r="G64" t="n">
-        <v>37.3217</v>
+        <v>37.4107</v>
       </c>
       <c r="H64" t="n">
         <v>45.05751734733581</v>
@@ -8996,26 +9018,26 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>22 okt</t>
+          <t>23 okt</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>207.75</v>
+        <v>213.55</v>
       </c>
       <c r="M64" t="n">
-        <v>216.65</v>
+        <v>215.85</v>
       </c>
       <c r="N64" t="n">
-        <v>205.1</v>
+        <v>210.05</v>
       </c>
       <c r="O64" t="n">
-        <v>215.35</v>
+        <v>214.4</v>
       </c>
       <c r="P64" t="n">
-        <v>187.9272</v>
+        <v>188.6124</v>
       </c>
       <c r="Q64" t="n">
-        <v>163.9019</v>
+        <v>163.9244</v>
       </c>
       <c r="R64" t="n">
         <v>191.5557367172241</v>
@@ -9025,26 +9047,26 @@
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>22 okt</t>
+          <t>23 okt</t>
         </is>
       </c>
       <c r="V64" t="n">
-        <v>533.14</v>
+        <v>517.75</v>
       </c>
       <c r="W64" t="n">
-        <v>533.6</v>
+        <v>525.77</v>
       </c>
       <c r="X64" t="n">
-        <v>520.3</v>
+        <v>515.7</v>
       </c>
       <c r="Y64" t="n">
-        <v>521.08</v>
+        <v>524.51</v>
       </c>
       <c r="Z64" t="n">
-        <v>507.7834</v>
+        <v>508.3546</v>
       </c>
       <c r="AA64" t="n">
-        <v>435.1471</v>
+        <v>435.3676</v>
       </c>
       <c r="AB64" t="n">
         <v>535.3375423278808</v>
@@ -9056,26 +9078,26 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>23 okt</t>
+          <t>26 okt</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>47.13</v>
+        <v>48</v>
       </c>
       <c r="C65" t="n">
-        <v>48.38</v>
+        <v>48.21</v>
       </c>
       <c r="D65" t="n">
-        <v>46.895</v>
+        <v>47.37</v>
       </c>
       <c r="E65" t="n">
-        <v>48.295</v>
+        <v>47.91</v>
       </c>
       <c r="F65" t="n">
-        <v>42.2926</v>
+        <v>42.4678</v>
       </c>
       <c r="G65" t="n">
-        <v>37.4107</v>
+        <v>37.4967</v>
       </c>
       <c r="H65" t="n">
         <v>45.05751734733581</v>
@@ -9085,26 +9107,26 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>23 okt</t>
+          <t>26 okt</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>213.55</v>
+        <v>213.5</v>
       </c>
       <c r="M65" t="n">
-        <v>215.85</v>
+        <v>216.55</v>
       </c>
       <c r="N65" t="n">
-        <v>210.05</v>
+        <v>212.25</v>
       </c>
       <c r="O65" t="n">
-        <v>214.4</v>
+        <v>212.25</v>
       </c>
       <c r="P65" t="n">
-        <v>188.6124</v>
+        <v>189.2658</v>
       </c>
       <c r="Q65" t="n">
-        <v>163.9244</v>
+        <v>163.9724</v>
       </c>
       <c r="R65" t="n">
         <v>191.5557367172241</v>
@@ -9114,26 +9136,26 @@
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>23 okt</t>
+          <t>26 okt</t>
         </is>
       </c>
       <c r="V65" t="n">
-        <v>517.75</v>
+        <v>527.4</v>
       </c>
       <c r="W65" t="n">
-        <v>525.77</v>
+        <v>533.25</v>
       </c>
       <c r="X65" t="n">
-        <v>515.7</v>
+        <v>521.6900000000001</v>
       </c>
       <c r="Y65" t="n">
-        <v>524.51</v>
+        <v>532.6</v>
       </c>
       <c r="Z65" t="n">
-        <v>508.3546</v>
+        <v>509.1173</v>
       </c>
       <c r="AA65" t="n">
-        <v>435.3676</v>
+        <v>435.6551</v>
       </c>
       <c r="AB65" t="n">
         <v>535.3375423278808</v>
@@ -9145,26 +9167,26 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>26 okt</t>
+          <t>27 okt</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>48</v>
+        <v>47.83</v>
       </c>
       <c r="C66" t="n">
-        <v>48.21</v>
+        <v>47.91</v>
       </c>
       <c r="D66" t="n">
-        <v>47.37</v>
+        <v>47.05</v>
       </c>
       <c r="E66" t="n">
-        <v>47.955</v>
+        <v>47.13</v>
       </c>
       <c r="F66" t="n">
-        <v>42.4687</v>
+        <v>42.6147</v>
       </c>
       <c r="G66" t="n">
-        <v>37.497</v>
+        <v>37.5784</v>
       </c>
       <c r="H66" t="n">
         <v>45.05751734733581</v>
@@ -9174,26 +9196,26 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>26 okt</t>
+          <t>27 okt</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>213.5</v>
+        <v>212.75</v>
       </c>
       <c r="M66" t="n">
-        <v>216.55</v>
+        <v>215.25</v>
       </c>
       <c r="N66" t="n">
-        <v>212.45</v>
+        <v>211.7</v>
       </c>
       <c r="O66" t="n">
-        <v>212.8</v>
+        <v>213.2</v>
       </c>
       <c r="P66" t="n">
-        <v>189.2768</v>
+        <v>189.8798</v>
       </c>
       <c r="Q66" t="n">
-        <v>163.9751</v>
+        <v>164.0275</v>
       </c>
       <c r="R66" t="n">
         <v>191.5557367172241</v>
@@ -9203,26 +9225,26 @@
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>26 okt</t>
+          <t>27 okt</t>
         </is>
       </c>
       <c r="V66" t="n">
-        <v>527.41</v>
+        <v>532.35</v>
       </c>
       <c r="W66" t="n">
-        <v>533.25</v>
+        <v>534.7</v>
       </c>
       <c r="X66" t="n">
-        <v>521.6900000000001</v>
+        <v>528.331</v>
       </c>
       <c r="Y66" t="n">
-        <v>532.75</v>
+        <v>531.6</v>
       </c>
       <c r="Z66" t="n">
-        <v>509.1203</v>
+        <v>510.1603</v>
       </c>
       <c r="AA66" t="n">
-        <v>435.6558</v>
+        <v>435.9318</v>
       </c>
       <c r="AB66" t="n">
         <v>535.3375423278808</v>

--- a/rapporten/trend-agent.xlsx
+++ b/rapporten/trend-agent.xlsx
@@ -1075,7 +1075,7 @@
         <scaling>
           <orientation val="minMax"/>
           <max val="240"/>
-          <min val="120"/>
+          <min val="140"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -1944,7 +1944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2256,6 +2256,28 @@
       </c>
       <c r="E14" s="3">
         <f>B14/$B$2-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>10066.75</v>
+      </c>
+      <c r="C15" s="2">
+        <f>B15-B14</f>
+        <v/>
+      </c>
+      <c r="D15" s="3">
+        <f>B15/B14-1</f>
+        <v/>
+      </c>
+      <c r="E15" s="3">
+        <f>B15/$B$2-1</f>
         <v/>
       </c>
     </row>
@@ -2399,38 +2421,38 @@
     <row r="6" ht="22" customHeight="1">
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Shell (SHELL.AS)  ·  47,13 EUR</t>
+          <t>Shell (SHELL.AS)  ·  47,44 EUR</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>SAP (SAP.DE)  ·  213,20 EUR</t>
+          <t>SAP (SAP.DE)  ·  211,60 EUR</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>Gestegen: 22,6% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +4,6% (winst). De bot verkoopt als de koers onder 45,41 zakt (-3,6%).</t>
+          <t>Gestegen: 23,2% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +5,3% (winst). De bot verkoopt als de koers onder 45,60 zakt (-3,9%).</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>Gestegen: 31,6% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +11,3% (winst). De bot verkoopt als de koers onder 198,88 zakt (-6,7%).</t>
+          <t>Gestegen: 35,7% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: +10,5% (winst). De bot verkoopt als de koers onder 198,88 zakt (-6,0%).</t>
         </is>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Microsoft (MSFT)  ·  531,60 USD</t>
+          <t>Microsoft (MSFT)  ·  531,01 USD</t>
         </is>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>Gestegen: 35,4% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: -0,7% (verlies). De bot verkoopt als de koers onder 510,33 zakt (-4,0%).</t>
+          <t>Gestegen: 36,2% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: -0,8% (verlies). De bot verkoopt als de koers onder 511,50 zakt (-3,7%).</t>
         </is>
       </c>
     </row>
@@ -2531,7 +2553,7 @@
         <v>45.06</v>
       </c>
       <c r="F2" t="n">
-        <v>45.41</v>
+        <v>45.6</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2609,7 +2631,7 @@
         <v>535.34</v>
       </c>
       <c r="F4" t="n">
-        <v>510.33</v>
+        <v>511.5</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -2895,12 +2917,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SAP.DE</t>
+          <t>SHELL.AS</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Shell</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -2909,19 +2931,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.15</v>
+        <v>0.149</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.3673678774497662</v>
+        <v>0.206430949081909</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1585696771997527</v>
+        <v>0.1281807250283609</v>
       </c>
       <c r="H2" t="n">
-        <v>0.89</v>
+        <v>0.97</v>
       </c>
       <c r="I2" t="n">
-        <v>213.2</v>
+        <v>47.44</v>
       </c>
     </row>
     <row r="3">
@@ -2930,12 +2952,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SHELL.AS</t>
+          <t>SAP.DE</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Shell</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2944,19 +2966,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.146</v>
+        <v>0.138</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.2238124662221594</v>
+        <v>0.3419584977949848</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.1031012931846513</v>
+        <v>0.1418087510288073</v>
       </c>
       <c r="H3" t="n">
-        <v>0.98</v>
+        <v>0.88</v>
       </c>
       <c r="I3" t="n">
-        <v>47.13</v>
+        <v>211.6</v>
       </c>
     </row>
     <row r="4">
@@ -2979,19 +3001,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.138</v>
+        <v>0.122</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.2693332961237478</v>
+        <v>0.2517896732569271</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.2753407421066918</v>
+        <v>0.2317647372975069</v>
       </c>
       <c r="H4" t="n">
         <v>0.89</v>
       </c>
       <c r="I4" t="n">
-        <v>86.06</v>
+        <v>83.76000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -3014,19 +3036,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.108</v>
+        <v>0.112</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.170256828460907</v>
+        <v>0.1678572976648653</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.09871183628719504</v>
+        <v>0.1122846267454534</v>
       </c>
       <c r="H5" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="I5" t="n">
-        <v>68.23</v>
+        <v>68.45</v>
       </c>
     </row>
     <row r="6">
@@ -3035,12 +3057,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>ExxonMobil</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -3049,19 +3071,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.097</v>
+        <v>0.1</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.3637546015401503</v>
+        <v>0.1670930761792091</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.04394951948388726</v>
+        <v>0.128106584363463</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="I6" t="n">
-        <v>531.6</v>
+        <v>182.02</v>
       </c>
     </row>
     <row r="7">
@@ -3070,33 +3092,33 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>OR.PA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>L'Oreal</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.09</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.1550546612717674</v>
+        <v>0.0980746362378937</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.1068791204808679</v>
+        <v>0.115955335250123</v>
       </c>
       <c r="H7" t="n">
-        <v>0.86</v>
+        <v>1.11</v>
       </c>
       <c r="I7" t="n">
-        <v>179.89</v>
+        <v>424.9</v>
       </c>
     </row>
     <row r="8">
@@ -3105,33 +3127,33 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OR.PA</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>L'Oreal</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.083</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.09454314720812174</v>
+        <v>0.1793607250598843</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.1201298701298701</v>
+        <v>0.04332367706842244</v>
       </c>
       <c r="H8" t="n">
-        <v>1.12</v>
+        <v>0.91</v>
       </c>
       <c r="I8" t="n">
-        <v>431.25</v>
+        <v>531.01</v>
       </c>
     </row>
     <row r="9">
@@ -3154,19 +3176,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.082</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.6158536585365855</v>
+        <v>0.6097660242087561</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.06011310288719773</v>
+        <v>0.05262874404260875</v>
       </c>
       <c r="H9" t="n">
-        <v>0.72</v>
+        <v>0.8</v>
       </c>
       <c r="I9" t="n">
-        <v>198.75</v>
+        <v>196.81</v>
       </c>
     </row>
     <row r="10">
@@ -3189,19 +3211,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.079</v>
+        <v>0.082</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.09168342987726508</v>
+        <v>0.0957605712339562</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.09259264484356322</v>
+        <v>0.09489450299921032</v>
       </c>
       <c r="H10" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="I10" t="n">
-        <v>401.79</v>
+        <v>400.6</v>
       </c>
     </row>
     <row r="11">
@@ -3224,19 +3246,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.076</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.1125962213337843</v>
+        <v>0.1089582515873244</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.05098618166690239</v>
+        <v>0.08510362635414337</v>
       </c>
       <c r="H11" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="I11" t="n">
-        <v>83.11</v>
+        <v>83.77</v>
       </c>
     </row>
   </sheetData>
@@ -3507,49 +3529,49 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>29 jul</t>
+          <t>30 jul</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>38.0653</v>
+        <v>38.6098</v>
       </c>
       <c r="C2" t="n">
-        <v>38.59</v>
+        <v>39.1444</v>
       </c>
       <c r="D2" t="n">
-        <v>37.7089</v>
+        <v>38.3277</v>
       </c>
       <c r="E2" t="n">
-        <v>38.4415</v>
+        <v>38.5108</v>
       </c>
       <c r="F2" t="n">
-        <v>35.9692</v>
+        <v>35.9978</v>
       </c>
       <c r="H2" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I2" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>29 jul</t>
+          <t>30 jul</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>159.84</v>
+        <v>162.5</v>
       </c>
       <c r="M2" t="n">
-        <v>163.3</v>
+        <v>163.16</v>
       </c>
       <c r="N2" t="n">
-        <v>156.48</v>
+        <v>155.2</v>
       </c>
       <c r="O2" t="n">
-        <v>162.04</v>
+        <v>155.92</v>
       </c>
       <c r="P2" t="n">
-        <v>144.28</v>
+        <v>144.3804</v>
       </c>
       <c r="R2" t="n">
         <v>191.5557367172241</v>
@@ -3559,77 +3581,77 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>28 jul</t>
+          <t>29 jul</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>392.4213</v>
+        <v>392.6608</v>
       </c>
       <c r="W2" t="n">
-        <v>399.5678</v>
+        <v>400.4961</v>
       </c>
       <c r="X2" t="n">
-        <v>390.5647</v>
+        <v>388.0095</v>
       </c>
       <c r="Y2" t="n">
-        <v>392.6109</v>
+        <v>389.8062</v>
       </c>
       <c r="Z2" t="n">
-        <v>397.7139</v>
+        <v>397.1057</v>
       </c>
       <c r="AB2" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC2" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>30 jul</t>
+          <t>31 jul</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>38.6098</v>
       </c>
       <c r="C3" t="n">
-        <v>39.1444</v>
+        <v>39.575</v>
       </c>
       <c r="D3" t="n">
-        <v>38.3277</v>
+        <v>38.4464</v>
       </c>
       <c r="E3" t="n">
-        <v>38.5108</v>
+        <v>39.3226</v>
       </c>
       <c r="F3" t="n">
-        <v>35.9978</v>
+        <v>36.0495</v>
       </c>
       <c r="H3" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I3" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>30 jul</t>
+          <t>31 jul</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>162.5</v>
+        <v>154.9</v>
       </c>
       <c r="M3" t="n">
-        <v>163.16</v>
+        <v>158.26</v>
       </c>
       <c r="N3" t="n">
-        <v>155.2</v>
+        <v>153.6</v>
       </c>
       <c r="O3" t="n">
-        <v>155.92</v>
+        <v>157.68</v>
       </c>
       <c r="P3" t="n">
-        <v>144.3804</v>
+        <v>144.4984</v>
       </c>
       <c r="R3" t="n">
         <v>191.5557367172241</v>
@@ -3639,77 +3661,77 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>29 jul</t>
+          <t>30 jul</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>392.6608</v>
+        <v>437.0772</v>
       </c>
       <c r="W3" t="n">
-        <v>400.4961</v>
+        <v>457.8281</v>
       </c>
       <c r="X3" t="n">
-        <v>388.0095</v>
+        <v>431.6275</v>
       </c>
       <c r="Y3" t="n">
-        <v>389.8062</v>
+        <v>450.2524</v>
       </c>
       <c r="Z3" t="n">
-        <v>397.1057</v>
+        <v>397.6741</v>
       </c>
       <c r="AB3" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC3" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>31 jul</t>
+          <t>3 aug</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38.6098</v>
+        <v>38.3128</v>
       </c>
       <c r="C4" t="n">
-        <v>39.575</v>
+        <v>39.4067</v>
       </c>
       <c r="D4" t="n">
-        <v>38.4464</v>
+        <v>38.2138</v>
       </c>
       <c r="E4" t="n">
-        <v>39.3226</v>
+        <v>39.4067</v>
       </c>
       <c r="F4" t="n">
-        <v>36.0495</v>
+        <v>36.1112</v>
       </c>
       <c r="H4" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I4" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>31 jul</t>
+          <t>3 aug</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>154.9</v>
+        <v>160</v>
       </c>
       <c r="M4" t="n">
-        <v>158.26</v>
+        <v>168.7</v>
       </c>
       <c r="N4" t="n">
-        <v>153.6</v>
+        <v>159.6</v>
       </c>
       <c r="O4" t="n">
-        <v>157.68</v>
+        <v>164.64</v>
       </c>
       <c r="P4" t="n">
-        <v>144.4984</v>
+        <v>144.7016</v>
       </c>
       <c r="R4" t="n">
         <v>191.5557367172241</v>
@@ -3719,77 +3741,77 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>30 jul</t>
+          <t>31 jul</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>437.0772</v>
+        <v>449.1545</v>
       </c>
       <c r="W4" t="n">
-        <v>457.8281</v>
+        <v>465.9628</v>
       </c>
       <c r="X4" t="n">
-        <v>431.6275</v>
+        <v>448.4857</v>
       </c>
       <c r="Y4" t="n">
-        <v>450.2524</v>
+        <v>463.8468</v>
       </c>
       <c r="Z4" t="n">
-        <v>397.6741</v>
+        <v>398.6364</v>
       </c>
       <c r="AB4" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC4" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3 aug</t>
+          <t>4 aug</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>38.3128</v>
+        <v>39.3028</v>
       </c>
       <c r="C5" t="n">
-        <v>39.4067</v>
+        <v>39.6443</v>
       </c>
       <c r="D5" t="n">
-        <v>38.2138</v>
+        <v>38.2039</v>
       </c>
       <c r="E5" t="n">
-        <v>39.4067</v>
+        <v>38.486</v>
       </c>
       <c r="F5" t="n">
-        <v>36.1112</v>
+        <v>36.1495</v>
       </c>
       <c r="H5" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I5" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>3 aug</t>
+          <t>4 aug</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>160</v>
+        <v>162.86</v>
       </c>
       <c r="M5" t="n">
-        <v>168.7</v>
+        <v>168.56</v>
       </c>
       <c r="N5" t="n">
-        <v>159.6</v>
+        <v>162.4</v>
       </c>
       <c r="O5" t="n">
-        <v>164.64</v>
+        <v>167.38</v>
       </c>
       <c r="P5" t="n">
-        <v>144.7016</v>
+        <v>145.02</v>
       </c>
       <c r="R5" t="n">
         <v>191.5557367172241</v>
@@ -3799,83 +3821,83 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>31 jul</t>
+          <t>3 aug</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>449.1545</v>
+        <v>475.2354</v>
       </c>
       <c r="W5" t="n">
-        <v>465.9628</v>
+        <v>490.7262</v>
       </c>
       <c r="X5" t="n">
-        <v>448.4857</v>
+        <v>474.1075</v>
       </c>
       <c r="Y5" t="n">
-        <v>463.8468</v>
+        <v>486.7337</v>
       </c>
       <c r="Z5" t="n">
-        <v>398.6364</v>
+        <v>399.9838</v>
       </c>
       <c r="AB5" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC5" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4 aug</t>
+          <t>5 aug</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>39.3028</v>
+        <v>38.4811</v>
       </c>
       <c r="C6" t="n">
-        <v>39.6443</v>
+        <v>38.7632</v>
       </c>
       <c r="D6" t="n">
-        <v>38.2039</v>
+        <v>37.9366</v>
       </c>
       <c r="E6" t="n">
-        <v>38.486</v>
+        <v>38.0307</v>
       </c>
       <c r="F6" t="n">
-        <v>36.1495</v>
+        <v>36.1966</v>
       </c>
       <c r="G6" t="n">
-        <v>34.1818</v>
+        <v>34.2215</v>
       </c>
       <c r="H6" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I6" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>4 aug</t>
+          <t>5 aug</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>162.86</v>
+        <v>167.92</v>
       </c>
       <c r="M6" t="n">
-        <v>168.56</v>
+        <v>172.6</v>
       </c>
       <c r="N6" t="n">
-        <v>162.4</v>
+        <v>167.3</v>
       </c>
       <c r="O6" t="n">
-        <v>167.38</v>
+        <v>169.26</v>
       </c>
       <c r="P6" t="n">
-        <v>145.02</v>
+        <v>145.4052</v>
       </c>
       <c r="Q6" t="n">
-        <v>170.9913</v>
+        <v>170.7022</v>
       </c>
       <c r="R6" t="n">
         <v>191.5557367172241</v>
@@ -3885,86 +3907,86 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>3 aug</t>
+          <t>4 aug</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>475.2354</v>
+        <v>479.9964</v>
       </c>
       <c r="W6" t="n">
-        <v>490.7262</v>
+        <v>498.5016</v>
       </c>
       <c r="X6" t="n">
-        <v>474.1075</v>
+        <v>478.2697</v>
       </c>
       <c r="Y6" t="n">
-        <v>486.7337</v>
+        <v>491.884</v>
       </c>
       <c r="Z6" t="n">
-        <v>399.9838</v>
+        <v>401.4555</v>
       </c>
       <c r="AA6" t="n">
-        <v>431.3306</v>
+        <v>431.2438</v>
       </c>
       <c r="AB6" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC6" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5 aug</t>
+          <t>6 aug</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>38.4811</v>
+        <v>38.0752</v>
       </c>
       <c r="C7" t="n">
-        <v>38.7632</v>
+        <v>38.4069</v>
       </c>
       <c r="D7" t="n">
-        <v>37.9366</v>
+        <v>37.9168</v>
       </c>
       <c r="E7" t="n">
-        <v>38.0307</v>
+        <v>38.392</v>
       </c>
       <c r="F7" t="n">
-        <v>36.1966</v>
+        <v>36.2474</v>
       </c>
       <c r="G7" t="n">
-        <v>34.2215</v>
+        <v>34.2607</v>
       </c>
       <c r="H7" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I7" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>5 aug</t>
+          <t>6 aug</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>167.92</v>
+        <v>171.44</v>
       </c>
       <c r="M7" t="n">
-        <v>172.6</v>
+        <v>173.1</v>
       </c>
       <c r="N7" t="n">
-        <v>167.3</v>
+        <v>168.08</v>
       </c>
       <c r="O7" t="n">
-        <v>169.26</v>
+        <v>170.98</v>
       </c>
       <c r="P7" t="n">
-        <v>145.4052</v>
+        <v>145.7928</v>
       </c>
       <c r="Q7" t="n">
-        <v>170.7022</v>
+        <v>170.384</v>
       </c>
       <c r="R7" t="n">
         <v>191.5557367172241</v>
@@ -3974,86 +3996,86 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>4 aug</t>
+          <t>5 aug</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>479.9964</v>
+        <v>495.4273</v>
       </c>
       <c r="W7" t="n">
-        <v>498.5016</v>
+        <v>497.3038</v>
       </c>
       <c r="X7" t="n">
-        <v>478.2697</v>
+        <v>484.7674</v>
       </c>
       <c r="Y7" t="n">
-        <v>491.884</v>
+        <v>486.5441</v>
       </c>
       <c r="Z7" t="n">
-        <v>401.4555</v>
+        <v>402.8307</v>
       </c>
       <c r="AA7" t="n">
-        <v>431.2438</v>
+        <v>431.1393</v>
       </c>
       <c r="AB7" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC7" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6 aug</t>
+          <t>7 aug</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>38.0752</v>
+        <v>38.5207</v>
       </c>
       <c r="C8" t="n">
-        <v>38.4069</v>
+        <v>38.5999</v>
       </c>
       <c r="D8" t="n">
-        <v>37.9168</v>
+        <v>37.897</v>
       </c>
       <c r="E8" t="n">
-        <v>38.392</v>
+        <v>38.0059</v>
       </c>
       <c r="F8" t="n">
-        <v>36.2474</v>
+        <v>36.2952</v>
       </c>
       <c r="G8" t="n">
-        <v>34.2607</v>
+        <v>34.294</v>
       </c>
       <c r="H8" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I8" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>6 aug</t>
+          <t>7 aug</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>171.44</v>
+        <v>173.82</v>
       </c>
       <c r="M8" t="n">
-        <v>173.1</v>
+        <v>179.56</v>
       </c>
       <c r="N8" t="n">
-        <v>168.08</v>
+        <v>173.82</v>
       </c>
       <c r="O8" t="n">
-        <v>170.98</v>
+        <v>177.96</v>
       </c>
       <c r="P8" t="n">
-        <v>145.7928</v>
+        <v>146.2468</v>
       </c>
       <c r="Q8" t="n">
-        <v>170.384</v>
+        <v>170.0918</v>
       </c>
       <c r="R8" t="n">
         <v>191.5557367172241</v>
@@ -4063,86 +4085,86 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>5 aug</t>
+          <t>6 aug</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>495.4273</v>
+        <v>487.632</v>
       </c>
       <c r="W8" t="n">
-        <v>497.3038</v>
+        <v>500.6176</v>
       </c>
       <c r="X8" t="n">
-        <v>484.7674</v>
+        <v>487.6021</v>
       </c>
       <c r="Y8" t="n">
-        <v>486.5441</v>
+        <v>498.9207</v>
       </c>
       <c r="Z8" t="n">
-        <v>402.8307</v>
+        <v>404.5041</v>
       </c>
       <c r="AA8" t="n">
-        <v>431.1393</v>
+        <v>431.087</v>
       </c>
       <c r="AB8" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC8" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>7 aug</t>
+          <t>10 aug</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>38.5207</v>
+        <v>38.0356</v>
       </c>
       <c r="C9" t="n">
-        <v>38.5999</v>
+        <v>38.4366</v>
       </c>
       <c r="D9" t="n">
-        <v>37.897</v>
+        <v>37.803</v>
       </c>
       <c r="E9" t="n">
-        <v>38.0059</v>
+        <v>38.4019</v>
       </c>
       <c r="F9" t="n">
-        <v>36.2952</v>
+        <v>36.3315</v>
       </c>
       <c r="G9" t="n">
-        <v>34.294</v>
+        <v>34.3294</v>
       </c>
       <c r="H9" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I9" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>7 aug</t>
+          <t>10 aug</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>173.82</v>
+        <v>178.92</v>
       </c>
       <c r="M9" t="n">
-        <v>179.56</v>
+        <v>179.96</v>
       </c>
       <c r="N9" t="n">
-        <v>173.82</v>
+        <v>175.86</v>
       </c>
       <c r="O9" t="n">
-        <v>177.96</v>
+        <v>179.3</v>
       </c>
       <c r="P9" t="n">
-        <v>146.2468</v>
+        <v>146.4748</v>
       </c>
       <c r="Q9" t="n">
-        <v>170.0918</v>
+        <v>169.8238</v>
       </c>
       <c r="R9" t="n">
         <v>191.5557367172241</v>
@@ -4152,86 +4174,86 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>6 aug</t>
+          <t>7 aug</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>487.632</v>
+        <v>498.272</v>
       </c>
       <c r="W9" t="n">
-        <v>500.6176</v>
+        <v>504.2308</v>
       </c>
       <c r="X9" t="n">
-        <v>487.6021</v>
+        <v>497.7929</v>
       </c>
       <c r="Y9" t="n">
-        <v>498.9207</v>
+        <v>499.0505</v>
       </c>
       <c r="Z9" t="n">
-        <v>404.5041</v>
+        <v>406.2472</v>
       </c>
       <c r="AA9" t="n">
-        <v>431.087</v>
+        <v>431.0194</v>
       </c>
       <c r="AB9" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC9" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10 aug</t>
+          <t>11 aug</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>38.0356</v>
+        <v>38.7385</v>
       </c>
       <c r="C10" t="n">
-        <v>38.4366</v>
+        <v>39.0058</v>
       </c>
       <c r="D10" t="n">
-        <v>37.803</v>
+        <v>38.6148</v>
       </c>
       <c r="E10" t="n">
-        <v>38.4019</v>
+        <v>38.9662</v>
       </c>
       <c r="F10" t="n">
-        <v>36.3315</v>
+        <v>36.374</v>
       </c>
       <c r="G10" t="n">
-        <v>34.3294</v>
+        <v>34.3685</v>
       </c>
       <c r="H10" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I10" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>10 aug</t>
+          <t>11 aug</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>178.92</v>
+        <v>180</v>
       </c>
       <c r="M10" t="n">
-        <v>179.96</v>
+        <v>183.24</v>
       </c>
       <c r="N10" t="n">
-        <v>175.86</v>
+        <v>178.14</v>
       </c>
       <c r="O10" t="n">
-        <v>179.3</v>
+        <v>180.7</v>
       </c>
       <c r="P10" t="n">
-        <v>146.4748</v>
+        <v>146.8316</v>
       </c>
       <c r="Q10" t="n">
-        <v>169.8238</v>
+        <v>169.5375</v>
       </c>
       <c r="R10" t="n">
         <v>191.5557367172241</v>
@@ -4241,86 +4263,86 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>7 aug</t>
+          <t>10 aug</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>498.272</v>
+        <v>502.4941</v>
       </c>
       <c r="W10" t="n">
-        <v>504.2308</v>
+        <v>512.7646999999999</v>
       </c>
       <c r="X10" t="n">
-        <v>497.7929</v>
+        <v>501.3262</v>
       </c>
       <c r="Y10" t="n">
-        <v>499.0505</v>
+        <v>505.1091</v>
       </c>
       <c r="Z10" t="n">
-        <v>406.2472</v>
+        <v>407.8257</v>
       </c>
       <c r="AA10" t="n">
-        <v>431.0194</v>
+        <v>430.9778</v>
       </c>
       <c r="AB10" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC10" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>11 aug</t>
+          <t>12 aug</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>38.7385</v>
+        <v>38.8573</v>
       </c>
       <c r="C11" t="n">
-        <v>39.0058</v>
+        <v>38.986</v>
       </c>
       <c r="D11" t="n">
-        <v>38.6148</v>
+        <v>38.3871</v>
       </c>
       <c r="E11" t="n">
-        <v>38.9662</v>
+        <v>38.6494</v>
       </c>
       <c r="F11" t="n">
-        <v>36.374</v>
+        <v>36.3981</v>
       </c>
       <c r="G11" t="n">
-        <v>34.3685</v>
+        <v>34.4068</v>
       </c>
       <c r="H11" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I11" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>11 aug</t>
+          <t>12 aug</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>180</v>
+        <v>180.3</v>
       </c>
       <c r="M11" t="n">
-        <v>183.24</v>
+        <v>180.98</v>
       </c>
       <c r="N11" t="n">
-        <v>178.14</v>
+        <v>175.4</v>
       </c>
       <c r="O11" t="n">
-        <v>180.7</v>
+        <v>175.96</v>
       </c>
       <c r="P11" t="n">
-        <v>146.8316</v>
+        <v>147.232</v>
       </c>
       <c r="Q11" t="n">
-        <v>169.5375</v>
+        <v>169.2701</v>
       </c>
       <c r="R11" t="n">
         <v>191.5557367172241</v>
@@ -4330,86 +4352,86 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>10 aug</t>
+          <t>11 aug</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>502.4941</v>
+        <v>503.3824</v>
       </c>
       <c r="W11" t="n">
-        <v>512.7646999999999</v>
+        <v>504.3805</v>
       </c>
       <c r="X11" t="n">
-        <v>501.3262</v>
+        <v>498.6113</v>
       </c>
       <c r="Y11" t="n">
-        <v>505.1091</v>
+        <v>502.8633</v>
       </c>
       <c r="Z11" t="n">
-        <v>407.8257</v>
+        <v>408.895</v>
       </c>
       <c r="AA11" t="n">
-        <v>430.9778</v>
+        <v>430.9106</v>
       </c>
       <c r="AB11" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC11" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>12 aug</t>
+          <t>13 aug</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>38.8573</v>
+        <v>39</v>
       </c>
       <c r="C12" t="n">
-        <v>38.986</v>
+        <v>39.005</v>
       </c>
       <c r="D12" t="n">
-        <v>38.3871</v>
+        <v>38.2</v>
       </c>
       <c r="E12" t="n">
-        <v>38.6494</v>
+        <v>38.605</v>
       </c>
       <c r="F12" t="n">
-        <v>36.3981</v>
+        <v>36.4313</v>
       </c>
       <c r="G12" t="n">
-        <v>34.4068</v>
+        <v>34.4429</v>
       </c>
       <c r="H12" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I12" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>12 aug</t>
+          <t>13 aug</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>180.3</v>
+        <v>177.48</v>
       </c>
       <c r="M12" t="n">
-        <v>180.98</v>
+        <v>178.3</v>
       </c>
       <c r="N12" t="n">
-        <v>175.4</v>
+        <v>174.8</v>
       </c>
       <c r="O12" t="n">
-        <v>175.96</v>
+        <v>175.38</v>
       </c>
       <c r="P12" t="n">
-        <v>147.232</v>
+        <v>147.4496</v>
       </c>
       <c r="Q12" t="n">
-        <v>169.2701</v>
+        <v>168.9889</v>
       </c>
       <c r="R12" t="n">
         <v>191.5557367172241</v>
@@ -4419,86 +4441,86 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>11 aug</t>
+          <t>12 aug</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>503.3824</v>
+        <v>499.0505</v>
       </c>
       <c r="W12" t="n">
-        <v>504.3805</v>
+        <v>500.5577</v>
       </c>
       <c r="X12" t="n">
-        <v>498.6113</v>
+        <v>490.5964</v>
       </c>
       <c r="Y12" t="n">
-        <v>502.8633</v>
+        <v>491.5047</v>
       </c>
       <c r="Z12" t="n">
-        <v>408.895</v>
+        <v>409.532</v>
       </c>
       <c r="AA12" t="n">
-        <v>430.9106</v>
+        <v>430.7866</v>
       </c>
       <c r="AB12" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC12" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>13 aug</t>
+          <t>14 aug</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>39</v>
+        <v>38.65</v>
       </c>
       <c r="C13" t="n">
-        <v>39.005</v>
+        <v>39.1</v>
       </c>
       <c r="D13" t="n">
-        <v>38.2</v>
+        <v>38.56</v>
       </c>
       <c r="E13" t="n">
-        <v>38.605</v>
+        <v>38.97</v>
       </c>
       <c r="F13" t="n">
-        <v>36.4313</v>
+        <v>36.4703</v>
       </c>
       <c r="G13" t="n">
-        <v>34.4429</v>
+        <v>34.4805</v>
       </c>
       <c r="H13" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I13" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>13 aug</t>
+          <t>14 aug</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>177.48</v>
+        <v>182</v>
       </c>
       <c r="M13" t="n">
-        <v>178.3</v>
+        <v>185.74</v>
       </c>
       <c r="N13" t="n">
-        <v>174.8</v>
+        <v>179.28</v>
       </c>
       <c r="O13" t="n">
-        <v>175.38</v>
+        <v>180.14</v>
       </c>
       <c r="P13" t="n">
-        <v>147.4496</v>
+        <v>147.8228</v>
       </c>
       <c r="Q13" t="n">
-        <v>168.9889</v>
+        <v>168.7386</v>
       </c>
       <c r="R13" t="n">
         <v>191.5557367172241</v>
@@ -4508,86 +4530,86 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>12 aug</t>
+          <t>13 aug</t>
         </is>
       </c>
       <c r="V13" t="n">
-        <v>499.0505</v>
+        <v>492.3431</v>
       </c>
       <c r="W13" t="n">
-        <v>500.5577</v>
+        <v>500.398</v>
       </c>
       <c r="X13" t="n">
-        <v>490.5964</v>
+        <v>492.0837</v>
       </c>
       <c r="Y13" t="n">
-        <v>491.5047</v>
+        <v>495.9464</v>
       </c>
       <c r="Z13" t="n">
-        <v>409.532</v>
+        <v>410.6414</v>
       </c>
       <c r="AA13" t="n">
-        <v>430.7866</v>
+        <v>430.6696</v>
       </c>
       <c r="AB13" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC13" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>14 aug</t>
+          <t>17 aug</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>38.65</v>
+        <v>38.97</v>
       </c>
       <c r="C14" t="n">
-        <v>39.1</v>
+        <v>39.27</v>
       </c>
       <c r="D14" t="n">
-        <v>38.56</v>
+        <v>38.765</v>
       </c>
       <c r="E14" t="n">
-        <v>38.97</v>
+        <v>39.15</v>
       </c>
       <c r="F14" t="n">
-        <v>36.4703</v>
+        <v>36.5118</v>
       </c>
       <c r="G14" t="n">
-        <v>34.4805</v>
+        <v>34.5207</v>
       </c>
       <c r="H14" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I14" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>14 aug</t>
+          <t>17 aug</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>182</v>
+        <v>178.94</v>
       </c>
       <c r="M14" t="n">
-        <v>185.74</v>
+        <v>180.9</v>
       </c>
       <c r="N14" t="n">
-        <v>179.28</v>
+        <v>177.66</v>
       </c>
       <c r="O14" t="n">
-        <v>180.14</v>
+        <v>179.58</v>
       </c>
       <c r="P14" t="n">
-        <v>147.8228</v>
+        <v>148.2524</v>
       </c>
       <c r="Q14" t="n">
-        <v>168.7386</v>
+        <v>168.5337</v>
       </c>
       <c r="R14" t="n">
         <v>191.5557367172241</v>
@@ -4597,86 +4619,86 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>13 aug</t>
+          <t>14 aug</t>
         </is>
       </c>
       <c r="V14" t="n">
-        <v>492.3431</v>
+        <v>495.4273</v>
       </c>
       <c r="W14" t="n">
-        <v>500.398</v>
+        <v>499.0705</v>
       </c>
       <c r="X14" t="n">
-        <v>492.0837</v>
+        <v>492.9919</v>
       </c>
       <c r="Y14" t="n">
-        <v>495.9464</v>
+        <v>494.4691</v>
       </c>
       <c r="Z14" t="n">
-        <v>410.6414</v>
+        <v>412</v>
       </c>
       <c r="AA14" t="n">
-        <v>430.6696</v>
+        <v>430.5061</v>
       </c>
       <c r="AB14" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC14" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>17 aug</t>
+          <t>18 aug</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>38.97</v>
+        <v>39.49</v>
       </c>
       <c r="C15" t="n">
-        <v>39.27</v>
+        <v>39.945</v>
       </c>
       <c r="D15" t="n">
-        <v>38.765</v>
+        <v>39.46</v>
       </c>
       <c r="E15" t="n">
-        <v>39.15</v>
+        <v>39.785</v>
       </c>
       <c r="F15" t="n">
-        <v>36.5118</v>
+        <v>36.5781</v>
       </c>
       <c r="G15" t="n">
-        <v>34.5207</v>
+        <v>34.5641</v>
       </c>
       <c r="H15" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I15" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>17 aug</t>
+          <t>18 aug</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>178.94</v>
+        <v>179.14</v>
       </c>
       <c r="M15" t="n">
-        <v>180.9</v>
+        <v>183.9</v>
       </c>
       <c r="N15" t="n">
-        <v>177.66</v>
+        <v>177.98</v>
       </c>
       <c r="O15" t="n">
-        <v>179.58</v>
+        <v>182.5</v>
       </c>
       <c r="P15" t="n">
-        <v>148.2524</v>
+        <v>148.8084</v>
       </c>
       <c r="Q15" t="n">
-        <v>168.5337</v>
+        <v>168.3358</v>
       </c>
       <c r="R15" t="n">
         <v>191.5557367172241</v>
@@ -4686,86 +4708,86 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>14 aug</t>
+          <t>17 aug</t>
         </is>
       </c>
       <c r="V15" t="n">
-        <v>495.4273</v>
+        <v>489.2191</v>
       </c>
       <c r="W15" t="n">
-        <v>499.0705</v>
+        <v>491.7343</v>
       </c>
       <c r="X15" t="n">
-        <v>492.9919</v>
+        <v>477.5111</v>
       </c>
       <c r="Y15" t="n">
-        <v>494.4691</v>
+        <v>479.4474</v>
       </c>
       <c r="Z15" t="n">
-        <v>412</v>
+        <v>413.044</v>
       </c>
       <c r="AA15" t="n">
-        <v>430.5061</v>
+        <v>430.2151</v>
       </c>
       <c r="AB15" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC15" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>18 aug</t>
+          <t>19 aug</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>39.49</v>
+        <v>39.835</v>
       </c>
       <c r="C16" t="n">
-        <v>39.945</v>
+        <v>40.14</v>
       </c>
       <c r="D16" t="n">
-        <v>39.46</v>
+        <v>39.74</v>
       </c>
       <c r="E16" t="n">
-        <v>39.785</v>
+        <v>39.94</v>
       </c>
       <c r="F16" t="n">
-        <v>36.5781</v>
+        <v>36.6336</v>
       </c>
       <c r="G16" t="n">
-        <v>34.5641</v>
+        <v>34.6092</v>
       </c>
       <c r="H16" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I16" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>18 aug</t>
+          <t>19 aug</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>179.14</v>
+        <v>181.7</v>
       </c>
       <c r="M16" t="n">
-        <v>183.9</v>
+        <v>186.98</v>
       </c>
       <c r="N16" t="n">
-        <v>177.98</v>
+        <v>180.38</v>
       </c>
       <c r="O16" t="n">
-        <v>182.5</v>
+        <v>185.9</v>
       </c>
       <c r="P16" t="n">
-        <v>148.8084</v>
+        <v>149.5324</v>
       </c>
       <c r="Q16" t="n">
-        <v>168.3358</v>
+        <v>168.1618</v>
       </c>
       <c r="R16" t="n">
         <v>191.5557367172241</v>
@@ -4775,86 +4797,86 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>17 aug</t>
+          <t>18 aug</t>
         </is>
       </c>
       <c r="V16" t="n">
-        <v>489.2191</v>
+        <v>480.6352</v>
       </c>
       <c r="W16" t="n">
-        <v>491.7343</v>
+        <v>483.3601</v>
       </c>
       <c r="X16" t="n">
-        <v>477.5111</v>
+        <v>476.2534</v>
       </c>
       <c r="Y16" t="n">
-        <v>479.4474</v>
+        <v>480.725</v>
       </c>
       <c r="Z16" t="n">
-        <v>413.044</v>
+        <v>414.3408</v>
       </c>
       <c r="AA16" t="n">
-        <v>430.2151</v>
+        <v>429.933</v>
       </c>
       <c r="AB16" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC16" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>19 aug</t>
+          <t>20 aug</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>39.835</v>
+        <v>39.865</v>
       </c>
       <c r="C17" t="n">
-        <v>40.14</v>
+        <v>40.51</v>
       </c>
       <c r="D17" t="n">
-        <v>39.74</v>
+        <v>39.8</v>
       </c>
       <c r="E17" t="n">
-        <v>39.94</v>
+        <v>40.28</v>
       </c>
       <c r="F17" t="n">
-        <v>36.6336</v>
+        <v>36.6884</v>
       </c>
       <c r="G17" t="n">
-        <v>34.6092</v>
+        <v>34.6545</v>
       </c>
       <c r="H17" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I17" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>19 aug</t>
+          <t>20 aug</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>181.7</v>
+        <v>183.78</v>
       </c>
       <c r="M17" t="n">
-        <v>186.98</v>
+        <v>186.1</v>
       </c>
       <c r="N17" t="n">
-        <v>180.38</v>
+        <v>182.52</v>
       </c>
       <c r="O17" t="n">
-        <v>185.9</v>
+        <v>185.64</v>
       </c>
       <c r="P17" t="n">
-        <v>149.5324</v>
+        <v>150.4472</v>
       </c>
       <c r="Q17" t="n">
-        <v>168.1618</v>
+        <v>167.9648</v>
       </c>
       <c r="R17" t="n">
         <v>191.5557367172241</v>
@@ -4864,86 +4886,86 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>18 aug</t>
+          <t>19 aug</t>
         </is>
       </c>
       <c r="V17" t="n">
-        <v>480.6352</v>
+        <v>479.168</v>
       </c>
       <c r="W17" t="n">
-        <v>483.3601</v>
+        <v>488.3806</v>
       </c>
       <c r="X17" t="n">
-        <v>476.2534</v>
+        <v>478.4593</v>
       </c>
       <c r="Y17" t="n">
-        <v>480.725</v>
+        <v>483.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>414.3408</v>
+        <v>415.7895</v>
       </c>
       <c r="AA17" t="n">
-        <v>429.933</v>
+        <v>429.7427</v>
       </c>
       <c r="AB17" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC17" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20 aug</t>
+          <t>21 aug</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>39.865</v>
+        <v>40.1</v>
       </c>
       <c r="C18" t="n">
-        <v>40.51</v>
+        <v>40.37</v>
       </c>
       <c r="D18" t="n">
-        <v>39.8</v>
+        <v>39.84</v>
       </c>
       <c r="E18" t="n">
-        <v>40.28</v>
+        <v>39.91</v>
       </c>
       <c r="F18" t="n">
-        <v>36.6884</v>
+        <v>36.7478</v>
       </c>
       <c r="G18" t="n">
-        <v>34.6545</v>
+        <v>34.6988</v>
       </c>
       <c r="H18" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I18" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>20 aug</t>
+          <t>21 aug</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>183.78</v>
+        <v>185.18</v>
       </c>
       <c r="M18" t="n">
-        <v>186.1</v>
+        <v>188.4</v>
       </c>
       <c r="N18" t="n">
-        <v>182.52</v>
+        <v>183.6</v>
       </c>
       <c r="O18" t="n">
-        <v>185.64</v>
+        <v>188.12</v>
       </c>
       <c r="P18" t="n">
-        <v>150.4472</v>
+        <v>151.4044</v>
       </c>
       <c r="Q18" t="n">
-        <v>167.9648</v>
+        <v>167.794</v>
       </c>
       <c r="R18" t="n">
         <v>191.5557367172241</v>
@@ -4953,86 +4975,86 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>19 aug</t>
+          <t>20 aug</t>
         </is>
       </c>
       <c r="V18" t="n">
-        <v>479.168</v>
+        <v>483.3</v>
       </c>
       <c r="W18" t="n">
-        <v>488.3806</v>
+        <v>484.16</v>
       </c>
       <c r="X18" t="n">
-        <v>478.4593</v>
+        <v>479.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>483.4</v>
+        <v>481.15</v>
       </c>
       <c r="Z18" t="n">
-        <v>415.7895</v>
+        <v>417.3594</v>
       </c>
       <c r="AA18" t="n">
-        <v>429.7427</v>
+        <v>429.5805</v>
       </c>
       <c r="AB18" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC18" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>21 aug</t>
+          <t>24 aug</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>40.1</v>
+        <v>39.88</v>
       </c>
       <c r="C19" t="n">
-        <v>40.37</v>
+        <v>40.085</v>
       </c>
       <c r="D19" t="n">
-        <v>39.84</v>
+        <v>39.68</v>
       </c>
       <c r="E19" t="n">
-        <v>39.91</v>
+        <v>39.775</v>
       </c>
       <c r="F19" t="n">
-        <v>36.7478</v>
+        <v>36.8369</v>
       </c>
       <c r="G19" t="n">
-        <v>34.6988</v>
+        <v>34.7421</v>
       </c>
       <c r="H19" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I19" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>21 aug</t>
+          <t>24 aug</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>185.18</v>
+        <v>186.86</v>
       </c>
       <c r="M19" t="n">
-        <v>188.4</v>
+        <v>188.16</v>
       </c>
       <c r="N19" t="n">
-        <v>183.6</v>
+        <v>185.52</v>
       </c>
       <c r="O19" t="n">
-        <v>188.12</v>
+        <v>187.2</v>
       </c>
       <c r="P19" t="n">
-        <v>151.4044</v>
+        <v>152.2848</v>
       </c>
       <c r="Q19" t="n">
-        <v>167.794</v>
+        <v>167.6093</v>
       </c>
       <c r="R19" t="n">
         <v>191.5557367172241</v>
@@ -5042,86 +5064,86 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>20 aug</t>
+          <t>21 aug</t>
         </is>
       </c>
       <c r="V19" t="n">
-        <v>483.3</v>
+        <v>479.88</v>
       </c>
       <c r="W19" t="n">
-        <v>484.16</v>
+        <v>486.36</v>
       </c>
       <c r="X19" t="n">
-        <v>479.5</v>
+        <v>478.53</v>
       </c>
       <c r="Y19" t="n">
-        <v>481.15</v>
+        <v>483.24</v>
       </c>
       <c r="Z19" t="n">
-        <v>417.3594</v>
+        <v>419.092</v>
       </c>
       <c r="AA19" t="n">
-        <v>429.5805</v>
+        <v>429.4327</v>
       </c>
       <c r="AB19" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC19" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>24 aug</t>
+          <t>25 aug</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>39.88</v>
+        <v>39.77</v>
       </c>
       <c r="C20" t="n">
-        <v>40.085</v>
+        <v>39.915</v>
       </c>
       <c r="D20" t="n">
-        <v>39.68</v>
+        <v>39.385</v>
       </c>
       <c r="E20" t="n">
-        <v>39.775</v>
+        <v>39.6</v>
       </c>
       <c r="F20" t="n">
-        <v>36.8369</v>
+        <v>36.926</v>
       </c>
       <c r="G20" t="n">
-        <v>34.7421</v>
+        <v>34.783</v>
       </c>
       <c r="H20" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I20" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>24 aug</t>
+          <t>25 aug</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>186.86</v>
+        <v>186.4</v>
       </c>
       <c r="M20" t="n">
-        <v>188.16</v>
+        <v>187.62</v>
       </c>
       <c r="N20" t="n">
-        <v>185.52</v>
+        <v>182.74</v>
       </c>
       <c r="O20" t="n">
-        <v>187.2</v>
+        <v>185.46</v>
       </c>
       <c r="P20" t="n">
-        <v>152.2848</v>
+        <v>153.136</v>
       </c>
       <c r="Q20" t="n">
-        <v>167.6093</v>
+        <v>167.4651</v>
       </c>
       <c r="R20" t="n">
         <v>191.5557367172241</v>
@@ -5131,86 +5153,86 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>21 aug</t>
+          <t>24 aug</t>
         </is>
       </c>
       <c r="V20" t="n">
-        <v>479.88</v>
+        <v>483.21</v>
       </c>
       <c r="W20" t="n">
-        <v>486.36</v>
+        <v>490.61</v>
       </c>
       <c r="X20" t="n">
-        <v>478.53</v>
+        <v>481.86</v>
       </c>
       <c r="Y20" t="n">
-        <v>483.24</v>
+        <v>487.31</v>
       </c>
       <c r="Z20" t="n">
-        <v>419.092</v>
+        <v>421.046</v>
       </c>
       <c r="AA20" t="n">
-        <v>429.4327</v>
+        <v>429.3185</v>
       </c>
       <c r="AB20" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC20" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>25 aug</t>
+          <t>26 aug</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>39.77</v>
+        <v>39.275</v>
       </c>
       <c r="C21" t="n">
-        <v>39.915</v>
+        <v>39.47</v>
       </c>
       <c r="D21" t="n">
-        <v>39.385</v>
+        <v>38.91</v>
       </c>
       <c r="E21" t="n">
-        <v>39.6</v>
+        <v>39.42</v>
       </c>
       <c r="F21" t="n">
-        <v>36.926</v>
+        <v>37.0192</v>
       </c>
       <c r="G21" t="n">
-        <v>34.783</v>
+        <v>34.8202</v>
       </c>
       <c r="H21" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I21" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>25 aug</t>
+          <t>26 aug</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>186.4</v>
+        <v>179.92</v>
       </c>
       <c r="M21" t="n">
-        <v>187.62</v>
+        <v>182.16</v>
       </c>
       <c r="N21" t="n">
-        <v>182.74</v>
+        <v>176.82</v>
       </c>
       <c r="O21" t="n">
-        <v>185.46</v>
+        <v>180.02</v>
       </c>
       <c r="P21" t="n">
-        <v>153.136</v>
+        <v>153.9128</v>
       </c>
       <c r="Q21" t="n">
-        <v>167.4651</v>
+        <v>167.3049</v>
       </c>
       <c r="R21" t="n">
         <v>191.5557367172241</v>
@@ -5220,86 +5242,86 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>24 aug</t>
+          <t>25 aug</t>
         </is>
       </c>
       <c r="V21" t="n">
-        <v>483.21</v>
+        <v>485.44</v>
       </c>
       <c r="W21" t="n">
-        <v>490.61</v>
+        <v>492.44</v>
       </c>
       <c r="X21" t="n">
-        <v>481.86</v>
+        <v>484.3</v>
       </c>
       <c r="Y21" t="n">
-        <v>487.31</v>
+        <v>491.71</v>
       </c>
       <c r="Z21" t="n">
-        <v>421.046</v>
+        <v>423.0801</v>
       </c>
       <c r="AA21" t="n">
-        <v>429.3186</v>
+        <v>429.262</v>
       </c>
       <c r="AB21" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC21" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>26 aug</t>
+          <t>27 aug</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>39.275</v>
+        <v>39.16</v>
       </c>
       <c r="C22" t="n">
-        <v>39.47</v>
+        <v>39.295</v>
       </c>
       <c r="D22" t="n">
-        <v>38.91</v>
+        <v>38.65</v>
       </c>
       <c r="E22" t="n">
-        <v>39.42</v>
+        <v>38.76</v>
       </c>
       <c r="F22" t="n">
-        <v>37.0192</v>
+        <v>37.117</v>
       </c>
       <c r="G22" t="n">
-        <v>34.8202</v>
+        <v>34.8559</v>
       </c>
       <c r="H22" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I22" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>26 aug</t>
+          <t>27 aug</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>179.92</v>
+        <v>182.5</v>
       </c>
       <c r="M22" t="n">
-        <v>182.16</v>
+        <v>190.8</v>
       </c>
       <c r="N22" t="n">
-        <v>176.82</v>
+        <v>181.14</v>
       </c>
       <c r="O22" t="n">
-        <v>180.02</v>
+        <v>189.88</v>
       </c>
       <c r="P22" t="n">
-        <v>153.9128</v>
+        <v>155.0132</v>
       </c>
       <c r="Q22" t="n">
-        <v>167.3049</v>
+        <v>167.1911</v>
       </c>
       <c r="R22" t="n">
         <v>191.5557367172241</v>
@@ -5309,86 +5331,86 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>25 aug</t>
+          <t>26 aug</t>
         </is>
       </c>
       <c r="V22" t="n">
-        <v>485.44</v>
+        <v>487.85</v>
       </c>
       <c r="W22" t="n">
-        <v>492.44</v>
+        <v>497.4</v>
       </c>
       <c r="X22" t="n">
-        <v>484.3</v>
+        <v>487.31</v>
       </c>
       <c r="Y22" t="n">
-        <v>491.71</v>
+        <v>496.37</v>
       </c>
       <c r="Z22" t="n">
-        <v>423.0801</v>
+        <v>425.0273</v>
       </c>
       <c r="AA22" t="n">
-        <v>429.262</v>
+        <v>429.2786</v>
       </c>
       <c r="AB22" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC22" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>27 aug</t>
+          <t>28 aug</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>39.16</v>
+        <v>39</v>
       </c>
       <c r="C23" t="n">
-        <v>39.295</v>
+        <v>39.18</v>
       </c>
       <c r="D23" t="n">
-        <v>38.65</v>
+        <v>38.845</v>
       </c>
       <c r="E23" t="n">
-        <v>38.76</v>
+        <v>39.145</v>
       </c>
       <c r="F23" t="n">
-        <v>37.117</v>
+        <v>37.2162</v>
       </c>
       <c r="G23" t="n">
-        <v>34.8559</v>
+        <v>34.8941</v>
       </c>
       <c r="H23" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I23" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>27 aug</t>
+          <t>28 aug</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>182.5</v>
+        <v>189.5</v>
       </c>
       <c r="M23" t="n">
-        <v>190.8</v>
+        <v>191.94</v>
       </c>
       <c r="N23" t="n">
-        <v>181.14</v>
+        <v>187.98</v>
       </c>
       <c r="O23" t="n">
-        <v>189.88</v>
+        <v>191.32</v>
       </c>
       <c r="P23" t="n">
-        <v>155.0132</v>
+        <v>156.1568</v>
       </c>
       <c r="Q23" t="n">
-        <v>167.1911</v>
+        <v>167.0806</v>
       </c>
       <c r="R23" t="n">
         <v>191.5557367172241</v>
@@ -5398,86 +5420,86 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>26 aug</t>
+          <t>27 aug</t>
         </is>
       </c>
       <c r="V23" t="n">
-        <v>487.85</v>
+        <v>494.88</v>
       </c>
       <c r="W23" t="n">
-        <v>497.4</v>
+        <v>506.48</v>
       </c>
       <c r="X23" t="n">
-        <v>487.31</v>
+        <v>490.08</v>
       </c>
       <c r="Y23" t="n">
-        <v>496.37</v>
+        <v>505.06</v>
       </c>
       <c r="Z23" t="n">
-        <v>425.0273</v>
+        <v>427.2667</v>
       </c>
       <c r="AA23" t="n">
-        <v>429.2786</v>
+        <v>429.3401</v>
       </c>
       <c r="AB23" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC23" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>28 aug</t>
+          <t>31 aug</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>39</v>
+        <v>39.54</v>
       </c>
       <c r="C24" t="n">
-        <v>39.18</v>
+        <v>39.91</v>
       </c>
       <c r="D24" t="n">
-        <v>38.845</v>
+        <v>39.24</v>
       </c>
       <c r="E24" t="n">
-        <v>39.145</v>
+        <v>39.335</v>
       </c>
       <c r="F24" t="n">
-        <v>37.2162</v>
+        <v>37.3111</v>
       </c>
       <c r="G24" t="n">
-        <v>34.8941</v>
+        <v>34.9333</v>
       </c>
       <c r="H24" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I24" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>28 aug</t>
+          <t>31 aug</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>189.5</v>
+        <v>188.46</v>
       </c>
       <c r="M24" t="n">
-        <v>191.94</v>
+        <v>192.12</v>
       </c>
       <c r="N24" t="n">
-        <v>187.98</v>
+        <v>188.2</v>
       </c>
       <c r="O24" t="n">
-        <v>191.32</v>
+        <v>190.9</v>
       </c>
       <c r="P24" t="n">
-        <v>156.1568</v>
+        <v>157.3304</v>
       </c>
       <c r="Q24" t="n">
-        <v>167.0806</v>
+        <v>166.9613</v>
       </c>
       <c r="R24" t="n">
         <v>191.5557367172241</v>
@@ -5487,86 +5509,86 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>27 aug</t>
+          <t>28 aug</t>
         </is>
       </c>
       <c r="V24" t="n">
-        <v>494.88</v>
+        <v>505.33</v>
       </c>
       <c r="W24" t="n">
-        <v>506.48</v>
+        <v>517.78</v>
       </c>
       <c r="X24" t="n">
-        <v>490.08</v>
+        <v>504.87</v>
       </c>
       <c r="Y24" t="n">
-        <v>505.06</v>
+        <v>513.53</v>
       </c>
       <c r="Z24" t="n">
-        <v>427.2667</v>
+        <v>429.9734</v>
       </c>
       <c r="AA24" t="n">
-        <v>429.3401</v>
+        <v>429.3984</v>
       </c>
       <c r="AB24" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC24" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>31 aug</t>
+          <t>1 sep</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>39.54</v>
+        <v>39.77</v>
       </c>
       <c r="C25" t="n">
-        <v>39.91</v>
+        <v>40.19</v>
       </c>
       <c r="D25" t="n">
-        <v>39.24</v>
+        <v>39.645</v>
       </c>
       <c r="E25" t="n">
-        <v>39.335</v>
+        <v>40.155</v>
       </c>
       <c r="F25" t="n">
-        <v>37.3111</v>
+        <v>37.4239</v>
       </c>
       <c r="G25" t="n">
-        <v>34.9333</v>
+        <v>34.9763</v>
       </c>
       <c r="H25" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I25" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>31 aug</t>
+          <t>1 sep</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>188.46</v>
+        <v>186</v>
       </c>
       <c r="M25" t="n">
-        <v>192.12</v>
+        <v>187.86</v>
       </c>
       <c r="N25" t="n">
-        <v>188.2</v>
+        <v>183.32</v>
       </c>
       <c r="O25" t="n">
-        <v>190.9</v>
+        <v>184.26</v>
       </c>
       <c r="P25" t="n">
-        <v>157.3304</v>
+        <v>158.3252</v>
       </c>
       <c r="Q25" t="n">
-        <v>166.9613</v>
+        <v>166.8103</v>
       </c>
       <c r="R25" t="n">
         <v>191.5557367172241</v>
@@ -5576,86 +5598,86 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>28 aug</t>
+          <t>31 aug</t>
         </is>
       </c>
       <c r="V25" t="n">
-        <v>505.33</v>
+        <v>510.38</v>
       </c>
       <c r="W25" t="n">
-        <v>517.78</v>
+        <v>512.1900000000001</v>
       </c>
       <c r="X25" t="n">
-        <v>504.87</v>
+        <v>506.39</v>
       </c>
       <c r="Y25" t="n">
-        <v>513.53</v>
+        <v>507.29</v>
       </c>
       <c r="Z25" t="n">
-        <v>429.9734</v>
+        <v>432.5454</v>
       </c>
       <c r="AA25" t="n">
-        <v>429.3984</v>
+        <v>429.4122</v>
       </c>
       <c r="AB25" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC25" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1 sep</t>
+          <t>2 sep</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>39.77</v>
+        <v>40.35</v>
       </c>
       <c r="C26" t="n">
-        <v>40.19</v>
+        <v>40.615</v>
       </c>
       <c r="D26" t="n">
-        <v>39.645</v>
+        <v>39.975</v>
       </c>
       <c r="E26" t="n">
-        <v>40.155</v>
+        <v>40.21</v>
       </c>
       <c r="F26" t="n">
-        <v>37.4239</v>
+        <v>37.5499</v>
       </c>
       <c r="G26" t="n">
-        <v>34.9763</v>
+        <v>35.0217</v>
       </c>
       <c r="H26" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I26" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1 sep</t>
+          <t>2 sep</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>186</v>
+        <v>182.18</v>
       </c>
       <c r="M26" t="n">
-        <v>187.86</v>
+        <v>184.7</v>
       </c>
       <c r="N26" t="n">
-        <v>183.32</v>
+        <v>180.72</v>
       </c>
       <c r="O26" t="n">
-        <v>184.26</v>
+        <v>181.44</v>
       </c>
       <c r="P26" t="n">
-        <v>158.3252</v>
+        <v>159.2568</v>
       </c>
       <c r="Q26" t="n">
-        <v>166.8103</v>
+        <v>166.6796</v>
       </c>
       <c r="R26" t="n">
         <v>191.5557367172241</v>
@@ -5665,86 +5687,86 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>31 aug</t>
+          <t>1 sep</t>
         </is>
       </c>
       <c r="V26" t="n">
-        <v>510.38</v>
+        <v>497.52</v>
       </c>
       <c r="W26" t="n">
-        <v>512.1900000000001</v>
+        <v>505.97</v>
       </c>
       <c r="X26" t="n">
-        <v>506.39</v>
+        <v>496.78</v>
       </c>
       <c r="Y26" t="n">
-        <v>507.29</v>
+        <v>501.02</v>
       </c>
       <c r="Z26" t="n">
-        <v>432.5454</v>
+        <v>435.2328</v>
       </c>
       <c r="AA26" t="n">
-        <v>429.4122</v>
+        <v>429.3825</v>
       </c>
       <c r="AB26" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC26" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2 sep</t>
+          <t>3 sep</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>40.35</v>
+        <v>40.095</v>
       </c>
       <c r="C27" t="n">
-        <v>40.615</v>
+        <v>40.215</v>
       </c>
       <c r="D27" t="n">
-        <v>39.975</v>
+        <v>39.54</v>
       </c>
       <c r="E27" t="n">
-        <v>40.21</v>
+        <v>40.04</v>
       </c>
       <c r="F27" t="n">
-        <v>37.5499</v>
+        <v>37.6767</v>
       </c>
       <c r="G27" t="n">
-        <v>35.0217</v>
+        <v>35.0679</v>
       </c>
       <c r="H27" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I27" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2 sep</t>
+          <t>3 sep</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>182.18</v>
+        <v>182.08</v>
       </c>
       <c r="M27" t="n">
-        <v>184.7</v>
+        <v>187.56</v>
       </c>
       <c r="N27" t="n">
-        <v>180.72</v>
+        <v>182</v>
       </c>
       <c r="O27" t="n">
-        <v>181.44</v>
+        <v>185.58</v>
       </c>
       <c r="P27" t="n">
-        <v>159.2568</v>
+        <v>160.3228</v>
       </c>
       <c r="Q27" t="n">
-        <v>166.6796</v>
+        <v>166.5898</v>
       </c>
       <c r="R27" t="n">
         <v>191.5557367172241</v>
@@ -5754,86 +5776,86 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>1 sep</t>
+          <t>2 sep</t>
         </is>
       </c>
       <c r="V27" t="n">
-        <v>497.52</v>
+        <v>499.85</v>
       </c>
       <c r="W27" t="n">
-        <v>505.97</v>
+        <v>500.27</v>
       </c>
       <c r="X27" t="n">
-        <v>496.78</v>
+        <v>493.81</v>
       </c>
       <c r="Y27" t="n">
-        <v>501.02</v>
+        <v>496.82</v>
       </c>
       <c r="Z27" t="n">
-        <v>435.2328</v>
+        <v>437.7045</v>
       </c>
       <c r="AA27" t="n">
-        <v>429.3825</v>
+        <v>429.3706</v>
       </c>
       <c r="AB27" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC27" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3 sep</t>
+          <t>4 sep</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>40.095</v>
+        <v>40.145</v>
       </c>
       <c r="C28" t="n">
-        <v>40.215</v>
+        <v>40.28</v>
       </c>
       <c r="D28" t="n">
-        <v>39.54</v>
+        <v>39.665</v>
       </c>
       <c r="E28" t="n">
-        <v>40.04</v>
+        <v>40.105</v>
       </c>
       <c r="F28" t="n">
-        <v>37.6767</v>
+        <v>37.8115</v>
       </c>
       <c r="G28" t="n">
-        <v>35.0679</v>
+        <v>35.113</v>
       </c>
       <c r="H28" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I28" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>3 sep</t>
+          <t>4 sep</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>182.08</v>
+        <v>187.8</v>
       </c>
       <c r="M28" t="n">
-        <v>187.56</v>
+        <v>189.9</v>
       </c>
       <c r="N28" t="n">
-        <v>182</v>
+        <v>184.96</v>
       </c>
       <c r="O28" t="n">
-        <v>185.58</v>
+        <v>185.68</v>
       </c>
       <c r="P28" t="n">
-        <v>160.3228</v>
+        <v>161.3336</v>
       </c>
       <c r="Q28" t="n">
-        <v>166.5898</v>
+        <v>166.5086</v>
       </c>
       <c r="R28" t="n">
         <v>191.5557367172241</v>
@@ -5843,86 +5865,86 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>2 sep</t>
+          <t>3 sep</t>
         </is>
       </c>
       <c r="V28" t="n">
-        <v>499.85</v>
+        <v>501.66</v>
       </c>
       <c r="W28" t="n">
-        <v>500.27</v>
+        <v>515.65</v>
       </c>
       <c r="X28" t="n">
-        <v>493.81</v>
+        <v>500.8</v>
       </c>
       <c r="Y28" t="n">
-        <v>496.82</v>
+        <v>510.12</v>
       </c>
       <c r="Z28" t="n">
-        <v>437.7045</v>
+        <v>440.6114</v>
       </c>
       <c r="AA28" t="n">
-        <v>429.3706</v>
+        <v>429.3912</v>
       </c>
       <c r="AB28" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC28" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>4 sep</t>
+          <t>7 sep</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>40.145</v>
+        <v>40.26</v>
       </c>
       <c r="C29" t="n">
-        <v>40.28</v>
+        <v>40.845</v>
       </c>
       <c r="D29" t="n">
-        <v>39.665</v>
+        <v>40.12</v>
       </c>
       <c r="E29" t="n">
-        <v>40.105</v>
+        <v>40.56</v>
       </c>
       <c r="F29" t="n">
-        <v>37.8115</v>
+        <v>37.9551</v>
       </c>
       <c r="G29" t="n">
-        <v>35.113</v>
+        <v>35.1619</v>
       </c>
       <c r="H29" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I29" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>4 sep</t>
+          <t>7 sep</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>187.8</v>
+        <v>183.56</v>
       </c>
       <c r="M29" t="n">
-        <v>189.9</v>
+        <v>184.3</v>
       </c>
       <c r="N29" t="n">
-        <v>184.96</v>
+        <v>179.92</v>
       </c>
       <c r="O29" t="n">
-        <v>185.68</v>
+        <v>182.8</v>
       </c>
       <c r="P29" t="n">
-        <v>161.3336</v>
+        <v>162.2568</v>
       </c>
       <c r="Q29" t="n">
-        <v>166.5086</v>
+        <v>166.4122</v>
       </c>
       <c r="R29" t="n">
         <v>191.5557367172241</v>
@@ -5932,86 +5954,86 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>3 sep</t>
+          <t>4 sep</t>
         </is>
       </c>
       <c r="V29" t="n">
-        <v>501.66</v>
+        <v>510</v>
       </c>
       <c r="W29" t="n">
-        <v>515.65</v>
+        <v>511</v>
       </c>
       <c r="X29" t="n">
-        <v>500.8</v>
+        <v>499.36</v>
       </c>
       <c r="Y29" t="n">
-        <v>510.12</v>
+        <v>499.7</v>
       </c>
       <c r="Z29" t="n">
-        <v>440.6114</v>
+        <v>443.5621</v>
       </c>
       <c r="AA29" t="n">
-        <v>429.3912</v>
+        <v>429.3729</v>
       </c>
       <c r="AB29" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC29" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>7 sep</t>
+          <t>8 sep</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>40.26</v>
+        <v>40.83</v>
       </c>
       <c r="C30" t="n">
-        <v>40.845</v>
+        <v>41.18</v>
       </c>
       <c r="D30" t="n">
-        <v>40.12</v>
+        <v>40.6325</v>
       </c>
       <c r="E30" t="n">
-        <v>40.56</v>
+        <v>40.855</v>
       </c>
       <c r="F30" t="n">
-        <v>37.9551</v>
+        <v>38.0977</v>
       </c>
       <c r="G30" t="n">
-        <v>35.1619</v>
+        <v>35.2131</v>
       </c>
       <c r="H30" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I30" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>7 sep</t>
+          <t>8 sep</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>183.56</v>
+        <v>182.32</v>
       </c>
       <c r="M30" t="n">
-        <v>184.3</v>
+        <v>183.76</v>
       </c>
       <c r="N30" t="n">
-        <v>179.92</v>
+        <v>180.02</v>
       </c>
       <c r="O30" t="n">
-        <v>182.8</v>
+        <v>181.7</v>
       </c>
       <c r="P30" t="n">
-        <v>162.2568</v>
+        <v>163.2108</v>
       </c>
       <c r="Q30" t="n">
-        <v>166.4122</v>
+        <v>166.3049</v>
       </c>
       <c r="R30" t="n">
         <v>191.5557367172241</v>
@@ -6021,86 +6043,86 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>4 sep</t>
+          <t>8 sep</t>
         </is>
       </c>
       <c r="V30" t="n">
-        <v>510</v>
+        <v>493.01</v>
       </c>
       <c r="W30" t="n">
-        <v>511</v>
+        <v>495.19</v>
       </c>
       <c r="X30" t="n">
-        <v>499.36</v>
+        <v>490.15</v>
       </c>
       <c r="Y30" t="n">
-        <v>499.7</v>
+        <v>493.95</v>
       </c>
       <c r="Z30" t="n">
-        <v>443.5621</v>
+        <v>445.9957</v>
       </c>
       <c r="AA30" t="n">
-        <v>429.3729</v>
+        <v>429.3939</v>
       </c>
       <c r="AB30" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC30" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>8 sep</t>
+          <t>9 sep</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>40.83</v>
+        <v>41.1</v>
       </c>
       <c r="C31" t="n">
-        <v>41.18</v>
+        <v>41.385</v>
       </c>
       <c r="D31" t="n">
-        <v>40.6325</v>
+        <v>40.85</v>
       </c>
       <c r="E31" t="n">
-        <v>40.855</v>
+        <v>40.94</v>
       </c>
       <c r="F31" t="n">
-        <v>38.0977</v>
+        <v>38.2513</v>
       </c>
       <c r="G31" t="n">
-        <v>35.2131</v>
+        <v>35.2646</v>
       </c>
       <c r="H31" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I31" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>8 sep</t>
+          <t>9 sep</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>182.32</v>
+        <v>183</v>
       </c>
       <c r="M31" t="n">
-        <v>183.76</v>
+        <v>187.04</v>
       </c>
       <c r="N31" t="n">
-        <v>180.02</v>
+        <v>181.36</v>
       </c>
       <c r="O31" t="n">
-        <v>181.7</v>
+        <v>182.86</v>
       </c>
       <c r="P31" t="n">
-        <v>163.2108</v>
+        <v>164.0504</v>
       </c>
       <c r="Q31" t="n">
-        <v>166.3049</v>
+        <v>166.2113</v>
       </c>
       <c r="R31" t="n">
         <v>191.5557367172241</v>
@@ -6110,86 +6132,86 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>8 sep</t>
+          <t>9 sep</t>
         </is>
       </c>
       <c r="V31" t="n">
-        <v>493.01</v>
+        <v>493.07</v>
       </c>
       <c r="W31" t="n">
-        <v>495.19</v>
+        <v>494.39</v>
       </c>
       <c r="X31" t="n">
-        <v>490.15</v>
+        <v>489.8</v>
       </c>
       <c r="Y31" t="n">
-        <v>493.95</v>
+        <v>491.65</v>
       </c>
       <c r="Z31" t="n">
-        <v>445.9957</v>
+        <v>448.4712</v>
       </c>
       <c r="AA31" t="n">
-        <v>429.3939</v>
+        <v>429.4364</v>
       </c>
       <c r="AB31" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC31" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>9 sep</t>
+          <t>10 sep</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>41.1</v>
+        <v>40.98</v>
       </c>
       <c r="C32" t="n">
-        <v>41.385</v>
+        <v>41.77</v>
       </c>
       <c r="D32" t="n">
-        <v>40.85</v>
+        <v>40.93</v>
       </c>
       <c r="E32" t="n">
-        <v>40.94</v>
+        <v>41.23</v>
       </c>
       <c r="F32" t="n">
-        <v>38.2513</v>
+        <v>38.4034</v>
       </c>
       <c r="G32" t="n">
-        <v>35.2646</v>
+        <v>35.3174</v>
       </c>
       <c r="H32" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I32" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>9 sep</t>
+          <t>10 sep</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="M32" t="n">
-        <v>187.04</v>
+        <v>180.4</v>
       </c>
       <c r="N32" t="n">
-        <v>181.36</v>
+        <v>176.2</v>
       </c>
       <c r="O32" t="n">
-        <v>182.86</v>
+        <v>177.82</v>
       </c>
       <c r="P32" t="n">
-        <v>164.0504</v>
+        <v>164.7724</v>
       </c>
       <c r="Q32" t="n">
-        <v>166.2113</v>
+        <v>166.0803</v>
       </c>
       <c r="R32" t="n">
         <v>191.5557367172241</v>
@@ -6199,86 +6221,86 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>9 sep</t>
+          <t>10 sep</t>
         </is>
       </c>
       <c r="V32" t="n">
-        <v>493.07</v>
+        <v>488.32</v>
       </c>
       <c r="W32" t="n">
-        <v>494.39</v>
+        <v>494.52</v>
       </c>
       <c r="X32" t="n">
-        <v>489.8</v>
+        <v>486</v>
       </c>
       <c r="Y32" t="n">
-        <v>491.65</v>
+        <v>492.44</v>
       </c>
       <c r="Z32" t="n">
-        <v>448.4712</v>
+        <v>450.8736</v>
       </c>
       <c r="AA32" t="n">
-        <v>429.4364</v>
+        <v>429.5215</v>
       </c>
       <c r="AB32" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC32" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10 sep</t>
+          <t>11 sep</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>40.98</v>
+        <v>41.345</v>
       </c>
       <c r="C33" t="n">
-        <v>41.77</v>
+        <v>41.715</v>
       </c>
       <c r="D33" t="n">
-        <v>40.93</v>
+        <v>40.905</v>
       </c>
       <c r="E33" t="n">
-        <v>41.23</v>
+        <v>41.415</v>
       </c>
       <c r="F33" t="n">
-        <v>38.4034</v>
+        <v>38.5608</v>
       </c>
       <c r="G33" t="n">
-        <v>35.3174</v>
+        <v>35.3717</v>
       </c>
       <c r="H33" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I33" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>10 sep</t>
+          <t>11 sep</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>180</v>
+        <v>175.68</v>
       </c>
       <c r="M33" t="n">
-        <v>180.4</v>
+        <v>178.84</v>
       </c>
       <c r="N33" t="n">
-        <v>176.2</v>
+        <v>172.16</v>
       </c>
       <c r="O33" t="n">
-        <v>177.82</v>
+        <v>177.26</v>
       </c>
       <c r="P33" t="n">
-        <v>164.7724</v>
+        <v>165.5248</v>
       </c>
       <c r="Q33" t="n">
-        <v>166.0803</v>
+        <v>165.9594</v>
       </c>
       <c r="R33" t="n">
         <v>191.5557367172241</v>
@@ -6288,86 +6310,86 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>10 sep</t>
+          <t>11 sep</t>
         </is>
       </c>
       <c r="V33" t="n">
-        <v>488.32</v>
+        <v>495.65</v>
       </c>
       <c r="W33" t="n">
-        <v>494.52</v>
+        <v>498.97</v>
       </c>
       <c r="X33" t="n">
-        <v>486</v>
+        <v>492.58</v>
       </c>
       <c r="Y33" t="n">
-        <v>492.44</v>
+        <v>495.63</v>
       </c>
       <c r="Z33" t="n">
-        <v>450.8736</v>
+        <v>453.115</v>
       </c>
       <c r="AA33" t="n">
-        <v>429.5215</v>
+        <v>429.654</v>
       </c>
       <c r="AB33" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC33" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>11 sep</t>
+          <t>14 sep</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>41.345</v>
+        <v>41.88</v>
       </c>
       <c r="C34" t="n">
-        <v>41.715</v>
+        <v>42.285</v>
       </c>
       <c r="D34" t="n">
-        <v>40.905</v>
+        <v>41.8</v>
       </c>
       <c r="E34" t="n">
-        <v>41.415</v>
+        <v>41.91</v>
       </c>
       <c r="F34" t="n">
-        <v>38.5608</v>
+        <v>38.7226</v>
       </c>
       <c r="G34" t="n">
-        <v>35.3717</v>
+        <v>35.4269</v>
       </c>
       <c r="H34" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I34" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>11 sep</t>
+          <t>14 sep</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>175.68</v>
+        <v>180.82</v>
       </c>
       <c r="M34" t="n">
-        <v>178.84</v>
+        <v>186.76</v>
       </c>
       <c r="N34" t="n">
-        <v>172.16</v>
+        <v>180.82</v>
       </c>
       <c r="O34" t="n">
-        <v>177.26</v>
+        <v>186.26</v>
       </c>
       <c r="P34" t="n">
-        <v>165.5248</v>
+        <v>166.4488</v>
       </c>
       <c r="Q34" t="n">
-        <v>165.9594</v>
+        <v>165.8745</v>
       </c>
       <c r="R34" t="n">
         <v>191.5557367172241</v>
@@ -6377,86 +6399,86 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>11 sep</t>
+          <t>14 sep</t>
         </is>
       </c>
       <c r="V34" t="n">
-        <v>495.65</v>
+        <v>497.06</v>
       </c>
       <c r="W34" t="n">
-        <v>498.97</v>
+        <v>509.95</v>
       </c>
       <c r="X34" t="n">
-        <v>492.58</v>
+        <v>495.34</v>
       </c>
       <c r="Y34" t="n">
-        <v>495.63</v>
+        <v>505.41</v>
       </c>
       <c r="Z34" t="n">
-        <v>453.115</v>
+        <v>455.4281</v>
       </c>
       <c r="AA34" t="n">
-        <v>429.654</v>
+        <v>429.8259</v>
       </c>
       <c r="AB34" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC34" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>14 sep</t>
+          <t>15 sep</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>41.88</v>
+        <v>41.845</v>
       </c>
       <c r="C35" t="n">
-        <v>42.285</v>
+        <v>42.7</v>
       </c>
       <c r="D35" t="n">
-        <v>41.8</v>
+        <v>41.72</v>
       </c>
       <c r="E35" t="n">
-        <v>41.91</v>
+        <v>42.7</v>
       </c>
       <c r="F35" t="n">
-        <v>38.7226</v>
+        <v>38.8782</v>
       </c>
       <c r="G35" t="n">
-        <v>35.4269</v>
+        <v>35.4854</v>
       </c>
       <c r="H35" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I35" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>14 sep</t>
+          <t>15 sep</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>180.82</v>
+        <v>186.64</v>
       </c>
       <c r="M35" t="n">
-        <v>186.76</v>
+        <v>187.26</v>
       </c>
       <c r="N35" t="n">
-        <v>180.82</v>
+        <v>183.2</v>
       </c>
       <c r="O35" t="n">
-        <v>186.26</v>
+        <v>187.08</v>
       </c>
       <c r="P35" t="n">
-        <v>166.4488</v>
+        <v>167.3124</v>
       </c>
       <c r="Q35" t="n">
-        <v>165.8745</v>
+        <v>165.7921</v>
       </c>
       <c r="R35" t="n">
         <v>191.5557367172241</v>
@@ -6466,86 +6488,86 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>14 sep</t>
+          <t>15 sep</t>
         </is>
       </c>
       <c r="V35" t="n">
-        <v>497.06</v>
+        <v>500.06</v>
       </c>
       <c r="W35" t="n">
-        <v>509.95</v>
+        <v>505.9</v>
       </c>
       <c r="X35" t="n">
-        <v>495.34</v>
+        <v>495.54</v>
       </c>
       <c r="Y35" t="n">
-        <v>505.41</v>
+        <v>497.12</v>
       </c>
       <c r="Z35" t="n">
-        <v>455.4281</v>
+        <v>457.6502</v>
       </c>
       <c r="AA35" t="n">
-        <v>429.8259</v>
+        <v>429.9416</v>
       </c>
       <c r="AB35" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC35" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>15 sep</t>
+          <t>16 sep</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>41.845</v>
+        <v>42.72</v>
       </c>
       <c r="C36" t="n">
-        <v>42.7</v>
+        <v>42.85</v>
       </c>
       <c r="D36" t="n">
-        <v>41.72</v>
+        <v>41.67</v>
       </c>
       <c r="E36" t="n">
-        <v>42.7</v>
+        <v>41.825</v>
       </c>
       <c r="F36" t="n">
-        <v>38.8782</v>
+        <v>38.9989</v>
       </c>
       <c r="G36" t="n">
-        <v>35.4854</v>
+        <v>35.5403</v>
       </c>
       <c r="H36" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I36" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>15 sep</t>
+          <t>16 sep</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>186.64</v>
+        <v>185.86</v>
       </c>
       <c r="M36" t="n">
-        <v>187.26</v>
+        <v>186.76</v>
       </c>
       <c r="N36" t="n">
-        <v>183.2</v>
+        <v>182.18</v>
       </c>
       <c r="O36" t="n">
-        <v>187.08</v>
+        <v>186.56</v>
       </c>
       <c r="P36" t="n">
-        <v>167.3124</v>
+        <v>168.2844</v>
       </c>
       <c r="Q36" t="n">
-        <v>165.7921</v>
+        <v>165.6996</v>
       </c>
       <c r="R36" t="n">
         <v>191.5557367172241</v>
@@ -6555,86 +6577,86 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>15 sep</t>
+          <t>16 sep</t>
         </is>
       </c>
       <c r="V36" t="n">
-        <v>500.06</v>
+        <v>493.03</v>
       </c>
       <c r="W36" t="n">
-        <v>505.9</v>
+        <v>495.97</v>
       </c>
       <c r="X36" t="n">
-        <v>495.54</v>
+        <v>487.23</v>
       </c>
       <c r="Y36" t="n">
-        <v>497.12</v>
+        <v>490.3</v>
       </c>
       <c r="Z36" t="n">
-        <v>457.6502</v>
+        <v>459.694</v>
       </c>
       <c r="AA36" t="n">
-        <v>429.9416</v>
+        <v>429.9809</v>
       </c>
       <c r="AB36" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC36" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>16 sep</t>
+          <t>17 sep</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>42.72</v>
+        <v>41.58</v>
       </c>
       <c r="C37" t="n">
-        <v>42.85</v>
+        <v>42.055</v>
       </c>
       <c r="D37" t="n">
-        <v>41.67</v>
+        <v>41.38</v>
       </c>
       <c r="E37" t="n">
-        <v>41.825</v>
+        <v>41.56</v>
       </c>
       <c r="F37" t="n">
-        <v>38.9989</v>
+        <v>39.1225</v>
       </c>
       <c r="G37" t="n">
-        <v>35.5403</v>
+        <v>35.5926</v>
       </c>
       <c r="H37" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I37" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>16 sep</t>
+          <t>17 sep</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>185.86</v>
+        <v>188.54</v>
       </c>
       <c r="M37" t="n">
-        <v>186.76</v>
+        <v>189.2</v>
       </c>
       <c r="N37" t="n">
-        <v>182.18</v>
+        <v>184.62</v>
       </c>
       <c r="O37" t="n">
-        <v>186.56</v>
+        <v>188</v>
       </c>
       <c r="P37" t="n">
-        <v>168.2844</v>
+        <v>169.2896</v>
       </c>
       <c r="Q37" t="n">
-        <v>165.6996</v>
+        <v>165.6125</v>
       </c>
       <c r="R37" t="n">
         <v>191.5557367172241</v>
@@ -6644,86 +6666,86 @@
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>16 sep</t>
+          <t>17 sep</t>
         </is>
       </c>
       <c r="V37" t="n">
-        <v>493.03</v>
+        <v>497.8</v>
       </c>
       <c r="W37" t="n">
-        <v>495.97</v>
+        <v>501.47</v>
       </c>
       <c r="X37" t="n">
-        <v>487.23</v>
+        <v>493.17</v>
       </c>
       <c r="Y37" t="n">
-        <v>490.3</v>
+        <v>497.75</v>
       </c>
       <c r="Z37" t="n">
-        <v>459.694</v>
+        <v>461.9966</v>
       </c>
       <c r="AA37" t="n">
-        <v>429.9809</v>
+        <v>430.0251</v>
       </c>
       <c r="AB37" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC37" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>17 sep</t>
+          <t>18 sep</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>41.58</v>
+        <v>41.465</v>
       </c>
       <c r="C38" t="n">
-        <v>42.055</v>
+        <v>41.5</v>
       </c>
       <c r="D38" t="n">
-        <v>41.38</v>
+        <v>40.955</v>
       </c>
       <c r="E38" t="n">
-        <v>41.56</v>
+        <v>41.315</v>
       </c>
       <c r="F38" t="n">
-        <v>39.1225</v>
+        <v>39.2414</v>
       </c>
       <c r="G38" t="n">
-        <v>35.5926</v>
+        <v>35.6436</v>
       </c>
       <c r="H38" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I38" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>17 sep</t>
+          <t>18 sep</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>188.54</v>
+        <v>186.1</v>
       </c>
       <c r="M38" t="n">
-        <v>189.2</v>
+        <v>187.26</v>
       </c>
       <c r="N38" t="n">
-        <v>184.62</v>
+        <v>182.56</v>
       </c>
       <c r="O38" t="n">
-        <v>188</v>
+        <v>183.12</v>
       </c>
       <c r="P38" t="n">
-        <v>169.2896</v>
+        <v>170.2004</v>
       </c>
       <c r="Q38" t="n">
-        <v>165.6125</v>
+        <v>165.5062</v>
       </c>
       <c r="R38" t="n">
         <v>191.5557367172241</v>
@@ -6733,86 +6755,86 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>17 sep</t>
+          <t>18 sep</t>
         </is>
       </c>
       <c r="V38" t="n">
-        <v>497.8</v>
+        <v>497.97</v>
       </c>
       <c r="W38" t="n">
-        <v>501.47</v>
+        <v>498.65</v>
       </c>
       <c r="X38" t="n">
-        <v>493.17</v>
+        <v>491.1</v>
       </c>
       <c r="Y38" t="n">
-        <v>497.75</v>
+        <v>493.78</v>
       </c>
       <c r="Z38" t="n">
-        <v>461.9966</v>
+        <v>464.1995</v>
       </c>
       <c r="AA38" t="n">
-        <v>430.0251</v>
+        <v>430.0757</v>
       </c>
       <c r="AB38" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC38" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>18 sep</t>
+          <t>21 sep</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>41.465</v>
+        <v>41.04</v>
       </c>
       <c r="C39" t="n">
-        <v>41.5</v>
+        <v>41.4</v>
       </c>
       <c r="D39" t="n">
-        <v>40.955</v>
+        <v>40.775</v>
       </c>
       <c r="E39" t="n">
-        <v>41.315</v>
+        <v>40.775</v>
       </c>
       <c r="F39" t="n">
-        <v>39.2414</v>
+        <v>39.3341</v>
       </c>
       <c r="G39" t="n">
-        <v>35.6436</v>
+        <v>35.6939</v>
       </c>
       <c r="H39" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I39" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>18 sep</t>
+          <t>21 sep</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>186.1</v>
+        <v>184.7</v>
       </c>
       <c r="M39" t="n">
-        <v>187.26</v>
+        <v>185.86</v>
       </c>
       <c r="N39" t="n">
-        <v>182.56</v>
+        <v>182.48</v>
       </c>
       <c r="O39" t="n">
-        <v>183.12</v>
+        <v>182.86</v>
       </c>
       <c r="P39" t="n">
-        <v>170.2004</v>
+        <v>171.0432</v>
       </c>
       <c r="Q39" t="n">
-        <v>165.5062</v>
+        <v>165.4052</v>
       </c>
       <c r="R39" t="n">
         <v>191.5557367172241</v>
@@ -6822,86 +6844,86 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>18 sep</t>
+          <t>21 sep</t>
         </is>
       </c>
       <c r="V39" t="n">
-        <v>497.97</v>
+        <v>494.95</v>
       </c>
       <c r="W39" t="n">
-        <v>498.65</v>
+        <v>501.87</v>
       </c>
       <c r="X39" t="n">
-        <v>491.1</v>
+        <v>491.33</v>
       </c>
       <c r="Y39" t="n">
-        <v>493.78</v>
+        <v>501.61</v>
       </c>
       <c r="Z39" t="n">
-        <v>464.1995</v>
+        <v>466.5442</v>
       </c>
       <c r="AA39" t="n">
-        <v>430.0757</v>
+        <v>430.1492</v>
       </c>
       <c r="AB39" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC39" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>21 sep</t>
+          <t>22 sep</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>41.04</v>
+        <v>40.84</v>
       </c>
       <c r="C40" t="n">
-        <v>41.4</v>
+        <v>41.165</v>
       </c>
       <c r="D40" t="n">
-        <v>40.775</v>
+        <v>40.215</v>
       </c>
       <c r="E40" t="n">
-        <v>40.775</v>
+        <v>41.01</v>
       </c>
       <c r="F40" t="n">
-        <v>39.3341</v>
+        <v>39.4244</v>
       </c>
       <c r="G40" t="n">
-        <v>35.6939</v>
+        <v>35.746</v>
       </c>
       <c r="H40" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I40" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>21 sep</t>
+          <t>22 sep</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>184.7</v>
+        <v>182.14</v>
       </c>
       <c r="M40" t="n">
-        <v>185.86</v>
+        <v>187.48</v>
       </c>
       <c r="N40" t="n">
-        <v>182.48</v>
+        <v>181.52</v>
       </c>
       <c r="O40" t="n">
-        <v>182.86</v>
+        <v>182.32</v>
       </c>
       <c r="P40" t="n">
-        <v>171.0432</v>
+        <v>171.9552</v>
       </c>
       <c r="Q40" t="n">
-        <v>165.4052</v>
+        <v>165.2836</v>
       </c>
       <c r="R40" t="n">
         <v>191.5557367172241</v>
@@ -6911,86 +6933,86 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>21 sep</t>
+          <t>22 sep</t>
         </is>
       </c>
       <c r="V40" t="n">
-        <v>494.95</v>
+        <v>507.32</v>
       </c>
       <c r="W40" t="n">
-        <v>501.87</v>
+        <v>508.5</v>
       </c>
       <c r="X40" t="n">
-        <v>491.33</v>
+        <v>493.65</v>
       </c>
       <c r="Y40" t="n">
-        <v>501.61</v>
+        <v>498</v>
       </c>
       <c r="Z40" t="n">
-        <v>466.5442</v>
+        <v>468.699</v>
       </c>
       <c r="AA40" t="n">
-        <v>430.1492</v>
+        <v>430.2656</v>
       </c>
       <c r="AB40" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC40" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>22 sep</t>
+          <t>23 sep</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>40.84</v>
+        <v>41</v>
       </c>
       <c r="C41" t="n">
-        <v>41.165</v>
+        <v>41.755</v>
       </c>
       <c r="D41" t="n">
-        <v>40.215</v>
+        <v>40.995</v>
       </c>
       <c r="E41" t="n">
-        <v>41.01</v>
+        <v>41.69</v>
       </c>
       <c r="F41" t="n">
-        <v>39.4244</v>
+        <v>39.5272</v>
       </c>
       <c r="G41" t="n">
-        <v>35.746</v>
+        <v>35.8024</v>
       </c>
       <c r="H41" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I41" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>22 sep</t>
+          <t>23 sep</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>182.14</v>
+        <v>184.9</v>
       </c>
       <c r="M41" t="n">
-        <v>187.48</v>
+        <v>187.8</v>
       </c>
       <c r="N41" t="n">
-        <v>181.52</v>
+        <v>183.48</v>
       </c>
       <c r="O41" t="n">
-        <v>182.32</v>
+        <v>186.46</v>
       </c>
       <c r="P41" t="n">
-        <v>171.9552</v>
+        <v>172.9448</v>
       </c>
       <c r="Q41" t="n">
-        <v>165.2836</v>
+        <v>165.1675</v>
       </c>
       <c r="R41" t="n">
         <v>191.5557367172241</v>
@@ -7000,86 +7022,86 @@
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>22 sep</t>
+          <t>23 sep</t>
         </is>
       </c>
       <c r="V41" t="n">
-        <v>507.32</v>
+        <v>500.76</v>
       </c>
       <c r="W41" t="n">
-        <v>508.5</v>
+        <v>509.44</v>
       </c>
       <c r="X41" t="n">
-        <v>493.65</v>
+        <v>495.88</v>
       </c>
       <c r="Y41" t="n">
-        <v>498</v>
+        <v>500.59</v>
       </c>
       <c r="Z41" t="n">
-        <v>468.699</v>
+        <v>471.0267</v>
       </c>
       <c r="AA41" t="n">
-        <v>430.2656</v>
+        <v>430.3795</v>
       </c>
       <c r="AB41" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC41" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>23 sep</t>
+          <t>24 sep</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>41</v>
+        <v>41.825</v>
       </c>
       <c r="C42" t="n">
-        <v>41.755</v>
+        <v>42.52</v>
       </c>
       <c r="D42" t="n">
-        <v>40.995</v>
+        <v>41.78</v>
       </c>
       <c r="E42" t="n">
-        <v>41.69</v>
+        <v>42.43</v>
       </c>
       <c r="F42" t="n">
-        <v>39.5272</v>
+        <v>39.6382</v>
       </c>
       <c r="G42" t="n">
-        <v>35.8024</v>
+        <v>35.8638</v>
       </c>
       <c r="H42" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I42" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>23 sep</t>
+          <t>24 sep</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>184.9</v>
+        <v>184.52</v>
       </c>
       <c r="M42" t="n">
-        <v>187.8</v>
+        <v>185.5</v>
       </c>
       <c r="N42" t="n">
-        <v>183.48</v>
+        <v>182.26</v>
       </c>
       <c r="O42" t="n">
-        <v>186.46</v>
+        <v>184.18</v>
       </c>
       <c r="P42" t="n">
-        <v>172.9448</v>
+        <v>173.8756</v>
       </c>
       <c r="Q42" t="n">
-        <v>165.1675</v>
+        <v>165.0554</v>
       </c>
       <c r="R42" t="n">
         <v>191.5557367172241</v>
@@ -7089,86 +7111,86 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>23 sep</t>
+          <t>24 sep</t>
         </is>
       </c>
       <c r="V42" t="n">
-        <v>500.76</v>
+        <v>495.07</v>
       </c>
       <c r="W42" t="n">
-        <v>509.44</v>
+        <v>498.9</v>
       </c>
       <c r="X42" t="n">
-        <v>495.88</v>
+        <v>491.22</v>
       </c>
       <c r="Y42" t="n">
-        <v>500.59</v>
+        <v>497.93</v>
       </c>
       <c r="Z42" t="n">
-        <v>471.0267</v>
+        <v>473.0876</v>
       </c>
       <c r="AA42" t="n">
-        <v>430.3795</v>
+        <v>430.4686</v>
       </c>
       <c r="AB42" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC42" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>24 sep</t>
+          <t>25 sep</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>41.825</v>
+        <v>41.99</v>
       </c>
       <c r="C43" t="n">
-        <v>42.52</v>
+        <v>42.33</v>
       </c>
       <c r="D43" t="n">
-        <v>41.78</v>
+        <v>41.71</v>
       </c>
       <c r="E43" t="n">
-        <v>42.43</v>
+        <v>42.06</v>
       </c>
       <c r="F43" t="n">
-        <v>39.6382</v>
+        <v>39.7263</v>
       </c>
       <c r="G43" t="n">
-        <v>35.8638</v>
+        <v>35.9239</v>
       </c>
       <c r="H43" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I43" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>24 sep</t>
+          <t>25 sep</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>184.52</v>
+        <v>184.42</v>
       </c>
       <c r="M43" t="n">
-        <v>185.5</v>
+        <v>185.92</v>
       </c>
       <c r="N43" t="n">
-        <v>182.26</v>
+        <v>183.76</v>
       </c>
       <c r="O43" t="n">
-        <v>184.18</v>
+        <v>185.92</v>
       </c>
       <c r="P43" t="n">
-        <v>173.8756</v>
+        <v>174.8356</v>
       </c>
       <c r="Q43" t="n">
-        <v>165.0554</v>
+        <v>164.9525</v>
       </c>
       <c r="R43" t="n">
         <v>191.5557367172241</v>
@@ -7178,86 +7200,86 @@
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>24 sep</t>
+          <t>25 sep</t>
         </is>
       </c>
       <c r="V43" t="n">
-        <v>495.07</v>
+        <v>499.04</v>
       </c>
       <c r="W43" t="n">
-        <v>498.9</v>
+        <v>519.4</v>
       </c>
       <c r="X43" t="n">
-        <v>491.22</v>
+        <v>497.25</v>
       </c>
       <c r="Y43" t="n">
-        <v>497.93</v>
+        <v>516.17</v>
       </c>
       <c r="Z43" t="n">
-        <v>473.0876</v>
+        <v>475.4041</v>
       </c>
       <c r="AA43" t="n">
-        <v>430.4686</v>
+        <v>430.6098</v>
       </c>
       <c r="AB43" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC43" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>25 sep</t>
+          <t>28 sep</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>41.99</v>
+        <v>42.45</v>
       </c>
       <c r="C44" t="n">
-        <v>42.33</v>
+        <v>42.995</v>
       </c>
       <c r="D44" t="n">
-        <v>41.71</v>
+        <v>42.38</v>
       </c>
       <c r="E44" t="n">
-        <v>42.06</v>
+        <v>42.725</v>
       </c>
       <c r="F44" t="n">
-        <v>39.7263</v>
+        <v>39.8301</v>
       </c>
       <c r="G44" t="n">
-        <v>35.9239</v>
+        <v>35.9888</v>
       </c>
       <c r="H44" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I44" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>25 sep</t>
+          <t>28 sep</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>184.42</v>
+        <v>185.2</v>
       </c>
       <c r="M44" t="n">
-        <v>185.92</v>
+        <v>186.76</v>
       </c>
       <c r="N44" t="n">
-        <v>183.76</v>
+        <v>178.88</v>
       </c>
       <c r="O44" t="n">
-        <v>185.92</v>
+        <v>184.02</v>
       </c>
       <c r="P44" t="n">
-        <v>174.8356</v>
+        <v>175.7508</v>
       </c>
       <c r="Q44" t="n">
-        <v>164.9525</v>
+        <v>164.8355</v>
       </c>
       <c r="R44" t="n">
         <v>191.5557367172241</v>
@@ -7267,86 +7289,86 @@
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>25 sep</t>
+          <t>28 sep</t>
         </is>
       </c>
       <c r="V44" t="n">
-        <v>499.04</v>
+        <v>505.47</v>
       </c>
       <c r="W44" t="n">
-        <v>519.4</v>
+        <v>513.33</v>
       </c>
       <c r="X44" t="n">
-        <v>497.25</v>
+        <v>502.22</v>
       </c>
       <c r="Y44" t="n">
-        <v>516.17</v>
+        <v>509.22</v>
       </c>
       <c r="Z44" t="n">
-        <v>475.4041</v>
+        <v>477.7269</v>
       </c>
       <c r="AA44" t="n">
-        <v>430.6098</v>
+        <v>430.7113</v>
       </c>
       <c r="AB44" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC44" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>28 sep</t>
+          <t>29 sep</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>42.45</v>
+        <v>42.57</v>
       </c>
       <c r="C45" t="n">
-        <v>42.995</v>
+        <v>42.665</v>
       </c>
       <c r="D45" t="n">
-        <v>42.38</v>
+        <v>41.73</v>
       </c>
       <c r="E45" t="n">
-        <v>42.725</v>
+        <v>42.05</v>
       </c>
       <c r="F45" t="n">
-        <v>39.8301</v>
+        <v>39.9146</v>
       </c>
       <c r="G45" t="n">
-        <v>35.9888</v>
+        <v>36.0498</v>
       </c>
       <c r="H45" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I45" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>28 sep</t>
+          <t>29 sep</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>185.2</v>
+        <v>183.22</v>
       </c>
       <c r="M45" t="n">
-        <v>186.76</v>
+        <v>186.34</v>
       </c>
       <c r="N45" t="n">
-        <v>178.88</v>
+        <v>182.28</v>
       </c>
       <c r="O45" t="n">
-        <v>184.02</v>
+        <v>185.32</v>
       </c>
       <c r="P45" t="n">
-        <v>175.7508</v>
+        <v>176.7288</v>
       </c>
       <c r="Q45" t="n">
-        <v>164.8355</v>
+        <v>164.733</v>
       </c>
       <c r="R45" t="n">
         <v>191.5557367172241</v>
@@ -7356,86 +7378,86 @@
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>28 sep</t>
+          <t>29 sep</t>
         </is>
       </c>
       <c r="V45" t="n">
-        <v>505.47</v>
+        <v>508.31</v>
       </c>
       <c r="W45" t="n">
-        <v>513.33</v>
+        <v>513.64</v>
       </c>
       <c r="X45" t="n">
-        <v>502.22</v>
+        <v>502.4</v>
       </c>
       <c r="Y45" t="n">
-        <v>509.22</v>
+        <v>508.96</v>
       </c>
       <c r="Z45" t="n">
-        <v>477.7269</v>
+        <v>479.8754</v>
       </c>
       <c r="AA45" t="n">
-        <v>430.7113</v>
+        <v>430.8784</v>
       </c>
       <c r="AB45" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC45" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>29 sep</t>
+          <t>30 sep</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>42.57</v>
+        <v>41.975</v>
       </c>
       <c r="C46" t="n">
-        <v>42.665</v>
+        <v>42.095</v>
       </c>
       <c r="D46" t="n">
-        <v>41.73</v>
+        <v>41.58</v>
       </c>
       <c r="E46" t="n">
-        <v>42.05</v>
+        <v>41.91</v>
       </c>
       <c r="F46" t="n">
-        <v>39.9146</v>
+        <v>39.9874</v>
       </c>
       <c r="G46" t="n">
-        <v>36.0498</v>
+        <v>36.1135</v>
       </c>
       <c r="H46" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I46" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>29 sep</t>
+          <t>30 sep</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>183.22</v>
+        <v>184.5</v>
       </c>
       <c r="M46" t="n">
-        <v>186.34</v>
+        <v>186.2</v>
       </c>
       <c r="N46" t="n">
-        <v>182.28</v>
+        <v>181.06</v>
       </c>
       <c r="O46" t="n">
-        <v>185.32</v>
+        <v>185.66</v>
       </c>
       <c r="P46" t="n">
-        <v>176.7288</v>
+        <v>177.8012</v>
       </c>
       <c r="Q46" t="n">
-        <v>164.733</v>
+        <v>164.6377</v>
       </c>
       <c r="R46" t="n">
         <v>191.5557367172241</v>
@@ -7445,86 +7467,86 @@
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>29 sep</t>
+          <t>30 sep</t>
         </is>
       </c>
       <c r="V46" t="n">
-        <v>508.31</v>
+        <v>511.61</v>
       </c>
       <c r="W46" t="n">
-        <v>513.64</v>
+        <v>519.83</v>
       </c>
       <c r="X46" t="n">
-        <v>502.4</v>
+        <v>510.31</v>
       </c>
       <c r="Y46" t="n">
-        <v>508.96</v>
+        <v>512.9</v>
       </c>
       <c r="Z46" t="n">
-        <v>479.8754</v>
+        <v>482.1933</v>
       </c>
       <c r="AA46" t="n">
-        <v>430.8784</v>
+        <v>431.0408</v>
       </c>
       <c r="AB46" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC46" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>30 sep</t>
+          <t>1 okt</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>41.975</v>
+        <v>41.625</v>
       </c>
       <c r="C47" t="n">
-        <v>42.095</v>
+        <v>42.36</v>
       </c>
       <c r="D47" t="n">
-        <v>41.58</v>
+        <v>41.165</v>
       </c>
       <c r="E47" t="n">
-        <v>41.91</v>
+        <v>42.24</v>
       </c>
       <c r="F47" t="n">
-        <v>39.9874</v>
+        <v>40.0562</v>
       </c>
       <c r="G47" t="n">
-        <v>36.1135</v>
+        <v>36.1777</v>
       </c>
       <c r="H47" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I47" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>30 sep</t>
+          <t>1 okt</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>184.5</v>
+        <v>184.68</v>
       </c>
       <c r="M47" t="n">
-        <v>186.2</v>
+        <v>190.26</v>
       </c>
       <c r="N47" t="n">
-        <v>181.06</v>
+        <v>181.34</v>
       </c>
       <c r="O47" t="n">
-        <v>185.66</v>
+        <v>186.74</v>
       </c>
       <c r="P47" t="n">
-        <v>177.8012</v>
+        <v>178.9696</v>
       </c>
       <c r="Q47" t="n">
-        <v>164.6377</v>
+        <v>164.5407</v>
       </c>
       <c r="R47" t="n">
         <v>191.5557367172241</v>
@@ -7534,86 +7556,86 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>30 sep</t>
+          <t>1 okt</t>
         </is>
       </c>
       <c r="V47" t="n">
-        <v>511.61</v>
+        <v>519.88</v>
       </c>
       <c r="W47" t="n">
-        <v>519.83</v>
+        <v>522.85</v>
       </c>
       <c r="X47" t="n">
-        <v>510.31</v>
+        <v>512.17</v>
       </c>
       <c r="Y47" t="n">
-        <v>512.9</v>
+        <v>512.8</v>
       </c>
       <c r="Z47" t="n">
-        <v>482.1933</v>
+        <v>484.6572</v>
       </c>
       <c r="AA47" t="n">
-        <v>431.0408</v>
+        <v>431.2272</v>
       </c>
       <c r="AB47" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC47" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1 okt</t>
+          <t>2 okt</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>41.625</v>
+        <v>42.11</v>
       </c>
       <c r="C48" t="n">
-        <v>42.36</v>
+        <v>42.745</v>
       </c>
       <c r="D48" t="n">
-        <v>41.165</v>
+        <v>41.985</v>
       </c>
       <c r="E48" t="n">
-        <v>42.24</v>
+        <v>42.4</v>
       </c>
       <c r="F48" t="n">
-        <v>40.0562</v>
+        <v>40.1364</v>
       </c>
       <c r="G48" t="n">
-        <v>36.1777</v>
+        <v>36.2422</v>
       </c>
       <c r="H48" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I48" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>1 okt</t>
+          <t>2 okt</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>184.68</v>
+        <v>187.82</v>
       </c>
       <c r="M48" t="n">
-        <v>190.26</v>
+        <v>188.74</v>
       </c>
       <c r="N48" t="n">
-        <v>181.34</v>
+        <v>183.92</v>
       </c>
       <c r="O48" t="n">
-        <v>186.74</v>
+        <v>183.92</v>
       </c>
       <c r="P48" t="n">
-        <v>178.9696</v>
+        <v>179.844</v>
       </c>
       <c r="Q48" t="n">
-        <v>164.5407</v>
+        <v>164.4442</v>
       </c>
       <c r="R48" t="n">
         <v>191.5557367172241</v>
@@ -7623,86 +7645,86 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>1 okt</t>
+          <t>2 okt</t>
         </is>
       </c>
       <c r="V48" t="n">
-        <v>519.88</v>
+        <v>519.39</v>
       </c>
       <c r="W48" t="n">
-        <v>522.85</v>
+        <v>522.5</v>
       </c>
       <c r="X48" t="n">
-        <v>512.17</v>
+        <v>513.66</v>
       </c>
       <c r="Y48" t="n">
-        <v>512.8</v>
+        <v>517.53</v>
       </c>
       <c r="Z48" t="n">
-        <v>484.6572</v>
+        <v>487.3905</v>
       </c>
       <c r="AA48" t="n">
-        <v>431.2272</v>
+        <v>431.4557</v>
       </c>
       <c r="AB48" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC48" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2 okt</t>
+          <t>5 okt</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>42.11</v>
+        <v>42.645</v>
       </c>
       <c r="C49" t="n">
-        <v>42.745</v>
+        <v>43.11</v>
       </c>
       <c r="D49" t="n">
-        <v>41.985</v>
+        <v>42.35</v>
       </c>
       <c r="E49" t="n">
-        <v>42.4</v>
+        <v>42.865</v>
       </c>
       <c r="F49" t="n">
-        <v>40.1364</v>
+        <v>40.2347</v>
       </c>
       <c r="G49" t="n">
-        <v>36.2422</v>
+        <v>36.3069</v>
       </c>
       <c r="H49" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I49" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2 okt</t>
+          <t>5 okt</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>187.82</v>
+        <v>185.06</v>
       </c>
       <c r="M49" t="n">
-        <v>188.74</v>
+        <v>188.5</v>
       </c>
       <c r="N49" t="n">
-        <v>183.92</v>
+        <v>184.66</v>
       </c>
       <c r="O49" t="n">
-        <v>183.92</v>
+        <v>185.04</v>
       </c>
       <c r="P49" t="n">
-        <v>179.844</v>
+        <v>180.5192</v>
       </c>
       <c r="Q49" t="n">
-        <v>164.4442</v>
+        <v>164.3515</v>
       </c>
       <c r="R49" t="n">
         <v>191.5557367172241</v>
@@ -7712,86 +7734,86 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>2 okt</t>
+          <t>5 okt</t>
         </is>
       </c>
       <c r="V49" t="n">
-        <v>519.39</v>
+        <v>521.62</v>
       </c>
       <c r="W49" t="n">
-        <v>522.5</v>
+        <v>532.35</v>
       </c>
       <c r="X49" t="n">
-        <v>513.66</v>
+        <v>521.47</v>
       </c>
       <c r="Y49" t="n">
-        <v>517.53</v>
+        <v>525.1799999999999</v>
       </c>
       <c r="Z49" t="n">
-        <v>487.3905</v>
+        <v>490.2745</v>
       </c>
       <c r="AA49" t="n">
-        <v>431.4557</v>
+        <v>431.7147</v>
       </c>
       <c r="AB49" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC49" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>5 okt</t>
+          <t>6 okt</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>42.645</v>
+        <v>42.86</v>
       </c>
       <c r="C50" t="n">
-        <v>43.11</v>
+        <v>43.285</v>
       </c>
       <c r="D50" t="n">
-        <v>42.35</v>
+        <v>42.43</v>
       </c>
       <c r="E50" t="n">
-        <v>42.865</v>
+        <v>43.185</v>
       </c>
       <c r="F50" t="n">
-        <v>40.2347</v>
+        <v>40.349</v>
       </c>
       <c r="G50" t="n">
-        <v>36.3069</v>
+        <v>36.3726</v>
       </c>
       <c r="H50" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I50" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>5 okt</t>
+          <t>6 okt</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>185.06</v>
+        <v>186.56</v>
       </c>
       <c r="M50" t="n">
-        <v>188.5</v>
+        <v>190.22</v>
       </c>
       <c r="N50" t="n">
-        <v>184.66</v>
+        <v>186.06</v>
       </c>
       <c r="O50" t="n">
-        <v>185.04</v>
+        <v>188.6</v>
       </c>
       <c r="P50" t="n">
-        <v>180.5192</v>
+        <v>181.1064</v>
       </c>
       <c r="Q50" t="n">
-        <v>164.3515</v>
+        <v>164.2647</v>
       </c>
       <c r="R50" t="n">
         <v>191.5557367172241</v>
@@ -7801,86 +7823,86 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>5 okt</t>
+          <t>6 okt</t>
         </is>
       </c>
       <c r="V50" t="n">
-        <v>521.62</v>
+        <v>531.6799999999999</v>
       </c>
       <c r="W50" t="n">
-        <v>532.35</v>
+        <v>535.6900000000001</v>
       </c>
       <c r="X50" t="n">
-        <v>521.47</v>
+        <v>528.78</v>
       </c>
       <c r="Y50" t="n">
-        <v>525.1799999999999</v>
+        <v>529.3</v>
       </c>
       <c r="Z50" t="n">
-        <v>490.2745</v>
+        <v>493.0931</v>
       </c>
       <c r="AA50" t="n">
-        <v>431.7147</v>
+        <v>431.9956</v>
       </c>
       <c r="AB50" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC50" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>6 okt</t>
+          <t>7 okt</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>42.86</v>
+        <v>43.37</v>
       </c>
       <c r="C51" t="n">
-        <v>43.285</v>
+        <v>43.835</v>
       </c>
       <c r="D51" t="n">
-        <v>42.43</v>
+        <v>43.145</v>
       </c>
       <c r="E51" t="n">
-        <v>43.185</v>
+        <v>43.25</v>
       </c>
       <c r="F51" t="n">
-        <v>40.349</v>
+        <v>40.4451</v>
       </c>
       <c r="G51" t="n">
-        <v>36.3726</v>
+        <v>36.4388</v>
       </c>
       <c r="H51" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I51" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>6 okt</t>
+          <t>7 okt</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>186.56</v>
+        <v>187</v>
       </c>
       <c r="M51" t="n">
-        <v>190.22</v>
+        <v>188.72</v>
       </c>
       <c r="N51" t="n">
-        <v>186.06</v>
+        <v>186.04</v>
       </c>
       <c r="O51" t="n">
-        <v>188.6</v>
+        <v>187.62</v>
       </c>
       <c r="P51" t="n">
-        <v>181.1064</v>
+        <v>181.618</v>
       </c>
       <c r="Q51" t="n">
-        <v>164.2647</v>
+        <v>164.1762</v>
       </c>
       <c r="R51" t="n">
         <v>191.5557367172241</v>
@@ -7890,86 +7912,86 @@
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>6 okt</t>
+          <t>7 okt</t>
         </is>
       </c>
       <c r="V51" t="n">
-        <v>531.6799999999999</v>
+        <v>530.73</v>
       </c>
       <c r="W51" t="n">
-        <v>535.6900000000001</v>
+        <v>531.73</v>
       </c>
       <c r="X51" t="n">
-        <v>528.78</v>
+        <v>524.6900000000001</v>
       </c>
       <c r="Y51" t="n">
-        <v>529.3</v>
+        <v>529.76</v>
       </c>
       <c r="Z51" t="n">
-        <v>493.0931</v>
+        <v>495.8361</v>
       </c>
       <c r="AA51" t="n">
-        <v>431.9956</v>
+        <v>432.2398</v>
       </c>
       <c r="AB51" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC51" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>7 okt</t>
+          <t>8 okt</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>43.37</v>
+        <v>43.555</v>
       </c>
       <c r="C52" t="n">
-        <v>43.835</v>
+        <v>44.815</v>
       </c>
       <c r="D52" t="n">
-        <v>43.145</v>
+        <v>43.5425</v>
       </c>
       <c r="E52" t="n">
-        <v>43.25</v>
+        <v>44.75</v>
       </c>
       <c r="F52" t="n">
-        <v>40.4451</v>
+        <v>40.5699</v>
       </c>
       <c r="G52" t="n">
-        <v>36.4388</v>
+        <v>36.5123</v>
       </c>
       <c r="H52" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I52" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>7 okt</t>
+          <t>8 okt</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>187</v>
+        <v>187.04</v>
       </c>
       <c r="M52" t="n">
-        <v>188.72</v>
+        <v>189.82</v>
       </c>
       <c r="N52" t="n">
-        <v>186.04</v>
+        <v>183.76</v>
       </c>
       <c r="O52" t="n">
-        <v>187.62</v>
+        <v>184.62</v>
       </c>
       <c r="P52" t="n">
-        <v>181.618</v>
+        <v>182.192</v>
       </c>
       <c r="Q52" t="n">
-        <v>164.1762</v>
+        <v>164.074</v>
       </c>
       <c r="R52" t="n">
         <v>191.5557367172241</v>
@@ -7979,86 +8001,86 @@
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>7 okt</t>
+          <t>8 okt</t>
         </is>
       </c>
       <c r="V52" t="n">
-        <v>530.73</v>
+        <v>529.8099999999999</v>
       </c>
       <c r="W52" t="n">
-        <v>531.73</v>
+        <v>533.51</v>
       </c>
       <c r="X52" t="n">
-        <v>524.6900000000001</v>
+        <v>518.79</v>
       </c>
       <c r="Y52" t="n">
-        <v>529.76</v>
+        <v>522.61</v>
       </c>
       <c r="Z52" t="n">
-        <v>495.8361</v>
+        <v>498.4921</v>
       </c>
       <c r="AA52" t="n">
-        <v>432.2398</v>
+        <v>432.4385</v>
       </c>
       <c r="AB52" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC52" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>8 okt</t>
+          <t>9 okt</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>43.555</v>
+        <v>44.42</v>
       </c>
       <c r="C53" t="n">
-        <v>44.815</v>
+        <v>45.155</v>
       </c>
       <c r="D53" t="n">
-        <v>43.5425</v>
+        <v>43.94</v>
       </c>
       <c r="E53" t="n">
-        <v>44.75</v>
+        <v>45.035</v>
       </c>
       <c r="F53" t="n">
-        <v>40.5699</v>
+        <v>40.6842</v>
       </c>
       <c r="G53" t="n">
-        <v>36.5123</v>
+        <v>36.5866</v>
       </c>
       <c r="H53" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I53" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>8 okt</t>
+          <t>9 okt</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>187.04</v>
+        <v>188.98</v>
       </c>
       <c r="M53" t="n">
-        <v>189.82</v>
+        <v>192.58</v>
       </c>
       <c r="N53" t="n">
-        <v>183.76</v>
+        <v>188.86</v>
       </c>
       <c r="O53" t="n">
-        <v>184.62</v>
+        <v>191.46</v>
       </c>
       <c r="P53" t="n">
-        <v>182.192</v>
+        <v>182.8676</v>
       </c>
       <c r="Q53" t="n">
-        <v>164.074</v>
+        <v>164.0101</v>
       </c>
       <c r="R53" t="n">
         <v>191.5557367172241</v>
@@ -8068,86 +8090,86 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>8 okt</t>
+          <t>9 okt</t>
         </is>
       </c>
       <c r="V53" t="n">
-        <v>529.8099999999999</v>
+        <v>528.24</v>
       </c>
       <c r="W53" t="n">
-        <v>533.51</v>
+        <v>537.22</v>
       </c>
       <c r="X53" t="n">
-        <v>518.79</v>
+        <v>526.24</v>
       </c>
       <c r="Y53" t="n">
-        <v>522.61</v>
+        <v>535.0700000000001</v>
       </c>
       <c r="Z53" t="n">
-        <v>498.4921</v>
+        <v>500.1885</v>
       </c>
       <c r="AA53" t="n">
-        <v>432.4385</v>
+        <v>432.7046</v>
       </c>
       <c r="AB53" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC53" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>9 okt</t>
+          <t>12 okt</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>44.42</v>
+        <v>44.725</v>
       </c>
       <c r="C54" t="n">
-        <v>45.155</v>
+        <v>45.81</v>
       </c>
       <c r="D54" t="n">
-        <v>43.94</v>
+        <v>44.695</v>
       </c>
       <c r="E54" t="n">
-        <v>45.035</v>
+        <v>45.56</v>
       </c>
       <c r="F54" t="n">
-        <v>40.6842</v>
+        <v>40.8072</v>
       </c>
       <c r="G54" t="n">
-        <v>36.5866</v>
+        <v>36.6625</v>
       </c>
       <c r="H54" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I54" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>9 okt</t>
+          <t>12 okt</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>188.98</v>
+        <v>190.58</v>
       </c>
       <c r="M54" t="n">
-        <v>192.58</v>
+        <v>197.88</v>
       </c>
       <c r="N54" t="n">
-        <v>188.86</v>
+        <v>189.78</v>
       </c>
       <c r="O54" t="n">
-        <v>191.46</v>
+        <v>194.46</v>
       </c>
       <c r="P54" t="n">
-        <v>182.8676</v>
+        <v>183.464</v>
       </c>
       <c r="Q54" t="n">
-        <v>164.0101</v>
+        <v>163.9576</v>
       </c>
       <c r="R54" t="n">
         <v>191.5557367172241</v>
@@ -8157,86 +8179,86 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>9 okt</t>
+          <t>12 okt</t>
         </is>
       </c>
       <c r="V54" t="n">
-        <v>528.24</v>
+        <v>537.53</v>
       </c>
       <c r="W54" t="n">
-        <v>537.22</v>
+        <v>542.74</v>
       </c>
       <c r="X54" t="n">
-        <v>526.24</v>
+        <v>535.7</v>
       </c>
       <c r="Y54" t="n">
-        <v>535.0700000000001</v>
+        <v>541.15</v>
       </c>
       <c r="Z54" t="n">
-        <v>500.1885</v>
+        <v>501.7346</v>
       </c>
       <c r="AA54" t="n">
-        <v>432.7046</v>
+        <v>432.9914</v>
       </c>
       <c r="AB54" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC54" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>12 okt</t>
+          <t>13 okt</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>44.725</v>
+        <v>45.69</v>
       </c>
       <c r="C55" t="n">
-        <v>45.81</v>
+        <v>45.97</v>
       </c>
       <c r="D55" t="n">
-        <v>44.695</v>
+        <v>45.35</v>
       </c>
       <c r="E55" t="n">
-        <v>45.56</v>
+        <v>45.95</v>
       </c>
       <c r="F55" t="n">
-        <v>40.8072</v>
+        <v>40.9565</v>
       </c>
       <c r="G55" t="n">
-        <v>36.6625</v>
+        <v>36.7398</v>
       </c>
       <c r="H55" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I55" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>12 okt</t>
+          <t>13 okt</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>190.58</v>
+        <v>196</v>
       </c>
       <c r="M55" t="n">
-        <v>197.88</v>
+        <v>198.18</v>
       </c>
       <c r="N55" t="n">
-        <v>189.78</v>
+        <v>194.02</v>
       </c>
       <c r="O55" t="n">
-        <v>194.46</v>
+        <v>197.28</v>
       </c>
       <c r="P55" t="n">
-        <v>183.464</v>
+        <v>184.062</v>
       </c>
       <c r="Q55" t="n">
-        <v>163.9576</v>
+        <v>163.9196</v>
       </c>
       <c r="R55" t="n">
         <v>191.5557367172241</v>
@@ -8246,86 +8268,86 @@
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>12 okt</t>
+          <t>13 okt</t>
         </is>
       </c>
       <c r="V55" t="n">
-        <v>537.53</v>
+        <v>544.64</v>
       </c>
       <c r="W55" t="n">
-        <v>542.74</v>
+        <v>551.15</v>
       </c>
       <c r="X55" t="n">
-        <v>535.7</v>
+        <v>543.0599999999999</v>
       </c>
       <c r="Y55" t="n">
-        <v>541.15</v>
+        <v>543.45</v>
       </c>
       <c r="Z55" t="n">
-        <v>501.7346</v>
+        <v>502.8689</v>
       </c>
       <c r="AA55" t="n">
-        <v>432.9914</v>
+        <v>433.2839</v>
       </c>
       <c r="AB55" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC55" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>13 okt</t>
+          <t>14 okt</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>45.69</v>
+        <v>45.95</v>
       </c>
       <c r="C56" t="n">
-        <v>45.97</v>
+        <v>46.675</v>
       </c>
       <c r="D56" t="n">
-        <v>45.35</v>
+        <v>45.91</v>
       </c>
       <c r="E56" t="n">
-        <v>45.95</v>
+        <v>46.455</v>
       </c>
       <c r="F56" t="n">
-        <v>40.9565</v>
+        <v>41.125</v>
       </c>
       <c r="G56" t="n">
-        <v>36.7398</v>
+        <v>36.8183</v>
       </c>
       <c r="H56" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I56" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>13 okt</t>
+          <t>14 okt</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>196</v>
+        <v>196.6</v>
       </c>
       <c r="M56" t="n">
-        <v>198.18</v>
+        <v>199.36</v>
       </c>
       <c r="N56" t="n">
-        <v>194.02</v>
+        <v>195.26</v>
       </c>
       <c r="O56" t="n">
-        <v>197.28</v>
+        <v>196.94</v>
       </c>
       <c r="P56" t="n">
-        <v>184.062</v>
+        <v>184.6156</v>
       </c>
       <c r="Q56" t="n">
-        <v>163.9196</v>
+        <v>163.9114</v>
       </c>
       <c r="R56" t="n">
         <v>191.5557367172241</v>
@@ -8335,86 +8357,86 @@
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>13 okt</t>
+          <t>14 okt</t>
         </is>
       </c>
       <c r="V56" t="n">
-        <v>544.64</v>
+        <v>545.27</v>
       </c>
       <c r="W56" t="n">
-        <v>551.15</v>
+        <v>545.75</v>
       </c>
       <c r="X56" t="n">
-        <v>543.0599999999999</v>
+        <v>532.54</v>
       </c>
       <c r="Y56" t="n">
-        <v>543.45</v>
+        <v>533.6900000000001</v>
       </c>
       <c r="Z56" t="n">
-        <v>502.8689</v>
+        <v>503.705</v>
       </c>
       <c r="AA56" t="n">
-        <v>433.2839</v>
+        <v>433.5292</v>
       </c>
       <c r="AB56" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC56" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>14 okt</t>
+          <t>15 okt</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>45.95</v>
+        <v>46.295</v>
       </c>
       <c r="C57" t="n">
-        <v>46.675</v>
+        <v>46.735</v>
       </c>
       <c r="D57" t="n">
-        <v>45.91</v>
+        <v>46.125</v>
       </c>
       <c r="E57" t="n">
-        <v>46.455</v>
+        <v>46.375</v>
       </c>
       <c r="F57" t="n">
-        <v>41.125</v>
+        <v>41.2847</v>
       </c>
       <c r="G57" t="n">
-        <v>36.8183</v>
+        <v>36.8966</v>
       </c>
       <c r="H57" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I57" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>14 okt</t>
+          <t>15 okt</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>196.6</v>
+        <v>199.48</v>
       </c>
       <c r="M57" t="n">
-        <v>199.36</v>
+        <v>203</v>
       </c>
       <c r="N57" t="n">
-        <v>195.26</v>
+        <v>196.98</v>
       </c>
       <c r="O57" t="n">
-        <v>196.94</v>
+        <v>201.25</v>
       </c>
       <c r="P57" t="n">
-        <v>184.6156</v>
+        <v>185.221</v>
       </c>
       <c r="Q57" t="n">
-        <v>163.9114</v>
+        <v>163.9038</v>
       </c>
       <c r="R57" t="n">
         <v>191.5557367172241</v>
@@ -8424,86 +8446,86 @@
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>14 okt</t>
+          <t>15 okt</t>
         </is>
       </c>
       <c r="V57" t="n">
-        <v>545.27</v>
+        <v>533.3200000000001</v>
       </c>
       <c r="W57" t="n">
-        <v>545.75</v>
+        <v>541.13</v>
       </c>
       <c r="X57" t="n">
-        <v>532.54</v>
+        <v>531.22</v>
       </c>
       <c r="Y57" t="n">
-        <v>533.6900000000001</v>
+        <v>539.4400000000001</v>
       </c>
       <c r="Z57" t="n">
-        <v>503.705</v>
+        <v>504.7629</v>
       </c>
       <c r="AA57" t="n">
-        <v>433.5292</v>
+        <v>433.8063</v>
       </c>
       <c r="AB57" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC57" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>15 okt</t>
+          <t>16 okt</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>46.295</v>
+        <v>46.14</v>
       </c>
       <c r="C58" t="n">
-        <v>46.735</v>
+        <v>47.025</v>
       </c>
       <c r="D58" t="n">
-        <v>46.125</v>
+        <v>46.075</v>
       </c>
       <c r="E58" t="n">
-        <v>46.375</v>
+        <v>46.88</v>
       </c>
       <c r="F58" t="n">
-        <v>41.2847</v>
+        <v>41.4622</v>
       </c>
       <c r="G58" t="n">
-        <v>36.8966</v>
+        <v>36.977</v>
       </c>
       <c r="H58" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I58" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>15 okt</t>
+          <t>16 okt</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>199.48</v>
+        <v>200.6</v>
       </c>
       <c r="M58" t="n">
-        <v>203</v>
+        <v>204.2</v>
       </c>
       <c r="N58" t="n">
-        <v>196.98</v>
+        <v>198.68</v>
       </c>
       <c r="O58" t="n">
-        <v>201.25</v>
+        <v>199.22</v>
       </c>
       <c r="P58" t="n">
-        <v>185.221</v>
+        <v>185.6462</v>
       </c>
       <c r="Q58" t="n">
-        <v>163.9038</v>
+        <v>163.9066</v>
       </c>
       <c r="R58" t="n">
         <v>191.5557367172241</v>
@@ -8513,86 +8535,86 @@
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>15 okt</t>
+          <t>16 okt</t>
         </is>
       </c>
       <c r="V58" t="n">
-        <v>533.3200000000001</v>
+        <v>541.3099999999999</v>
       </c>
       <c r="W58" t="n">
-        <v>541.13</v>
+        <v>543.8200000000001</v>
       </c>
       <c r="X58" t="n">
-        <v>531.22</v>
+        <v>524.4299999999999</v>
       </c>
       <c r="Y58" t="n">
-        <v>539.4400000000001</v>
+        <v>529.05</v>
       </c>
       <c r="Z58" t="n">
-        <v>504.7629</v>
+        <v>505.3655</v>
       </c>
       <c r="AA58" t="n">
-        <v>433.8063</v>
+        <v>434.0295</v>
       </c>
       <c r="AB58" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC58" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>16 okt</t>
+          <t>19 okt</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>46.14</v>
+        <v>47.37</v>
       </c>
       <c r="C59" t="n">
-        <v>47.025</v>
+        <v>47.45</v>
       </c>
       <c r="D59" t="n">
-        <v>46.075</v>
+        <v>46.74</v>
       </c>
       <c r="E59" t="n">
-        <v>46.88</v>
+        <v>46.86</v>
       </c>
       <c r="F59" t="n">
-        <v>41.4622</v>
+        <v>41.6313</v>
       </c>
       <c r="G59" t="n">
-        <v>36.977</v>
+        <v>37.0625</v>
       </c>
       <c r="H59" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I59" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>16 okt</t>
+          <t>19 okt</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>200.6</v>
+        <v>199.56</v>
       </c>
       <c r="M59" t="n">
-        <v>204.2</v>
+        <v>200.8</v>
       </c>
       <c r="N59" t="n">
-        <v>198.68</v>
+        <v>197.32</v>
       </c>
       <c r="O59" t="n">
-        <v>199.22</v>
+        <v>199.84</v>
       </c>
       <c r="P59" t="n">
-        <v>185.6462</v>
+        <v>186.057</v>
       </c>
       <c r="Q59" t="n">
-        <v>163.9066</v>
+        <v>163.8811</v>
       </c>
       <c r="R59" t="n">
         <v>191.5557367172241</v>
@@ -8602,86 +8624,86 @@
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>16 okt</t>
+          <t>19 okt</t>
         </is>
       </c>
       <c r="V59" t="n">
-        <v>541.3099999999999</v>
+        <v>528.7</v>
       </c>
       <c r="W59" t="n">
-        <v>543.8200000000001</v>
+        <v>535.5700000000001</v>
       </c>
       <c r="X59" t="n">
-        <v>524.4299999999999</v>
+        <v>528.0599999999999</v>
       </c>
       <c r="Y59" t="n">
-        <v>529.05</v>
+        <v>533.52</v>
       </c>
       <c r="Z59" t="n">
-        <v>505.3655</v>
+        <v>506.0549</v>
       </c>
       <c r="AA59" t="n">
-        <v>434.0295</v>
+        <v>434.2942</v>
       </c>
       <c r="AB59" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC59" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>19 okt</t>
+          <t>20 okt</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>47.37</v>
+        <v>46.875</v>
       </c>
       <c r="C60" t="n">
-        <v>47.45</v>
+        <v>47.505</v>
       </c>
       <c r="D60" t="n">
-        <v>46.74</v>
+        <v>46.36</v>
       </c>
       <c r="E60" t="n">
-        <v>46.86</v>
+        <v>46.57</v>
       </c>
       <c r="F60" t="n">
-        <v>41.6313</v>
+        <v>41.7834</v>
       </c>
       <c r="G60" t="n">
-        <v>37.0625</v>
+        <v>37.1516</v>
       </c>
       <c r="H60" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I60" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>19 okt</t>
+          <t>20 okt</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>199.56</v>
+        <v>201.3</v>
       </c>
       <c r="M60" t="n">
-        <v>200.8</v>
+        <v>203.45</v>
       </c>
       <c r="N60" t="n">
-        <v>197.32</v>
+        <v>199.46</v>
       </c>
       <c r="O60" t="n">
-        <v>199.84</v>
+        <v>201.55</v>
       </c>
       <c r="P60" t="n">
-        <v>186.057</v>
+        <v>186.474</v>
       </c>
       <c r="Q60" t="n">
-        <v>163.8811</v>
+        <v>163.8736</v>
       </c>
       <c r="R60" t="n">
         <v>191.5557367172241</v>
@@ -8691,86 +8713,86 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>19 okt</t>
+          <t>20 okt</t>
         </is>
       </c>
       <c r="V60" t="n">
-        <v>528.7</v>
+        <v>533.91</v>
       </c>
       <c r="W60" t="n">
-        <v>535.5700000000001</v>
+        <v>534.21</v>
       </c>
       <c r="X60" t="n">
-        <v>528.0599999999999</v>
+        <v>525.84</v>
       </c>
       <c r="Y60" t="n">
-        <v>533.52</v>
+        <v>531.87</v>
       </c>
       <c r="Z60" t="n">
-        <v>506.0549</v>
+        <v>506.5901</v>
       </c>
       <c r="AA60" t="n">
-        <v>434.2942</v>
+        <v>434.6038</v>
       </c>
       <c r="AB60" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC60" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20 okt</t>
+          <t>21 okt</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>46.875</v>
+        <v>46.97</v>
       </c>
       <c r="C61" t="n">
-        <v>47.505</v>
+        <v>47.135</v>
       </c>
       <c r="D61" t="n">
-        <v>46.36</v>
+        <v>46.73</v>
       </c>
       <c r="E61" t="n">
-        <v>46.57</v>
+        <v>46.84</v>
       </c>
       <c r="F61" t="n">
-        <v>41.7834</v>
+        <v>41.9472</v>
       </c>
       <c r="G61" t="n">
-        <v>37.1516</v>
+        <v>37.2379</v>
       </c>
       <c r="H61" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I61" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>20 okt</t>
+          <t>21 okt</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>201.3</v>
+        <v>201.8</v>
       </c>
       <c r="M61" t="n">
-        <v>203.45</v>
+        <v>208.65</v>
       </c>
       <c r="N61" t="n">
-        <v>199.46</v>
+        <v>200</v>
       </c>
       <c r="O61" t="n">
-        <v>201.55</v>
+        <v>208.65</v>
       </c>
       <c r="P61" t="n">
-        <v>186.474</v>
+        <v>187.1278</v>
       </c>
       <c r="Q61" t="n">
-        <v>163.8736</v>
+        <v>163.8728</v>
       </c>
       <c r="R61" t="n">
         <v>191.5557367172241</v>
@@ -8780,86 +8802,86 @@
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>20 okt</t>
+          <t>21 okt</t>
         </is>
       </c>
       <c r="V61" t="n">
-        <v>533.91</v>
+        <v>529.4400000000001</v>
       </c>
       <c r="W61" t="n">
-        <v>534.21</v>
+        <v>533.28</v>
       </c>
       <c r="X61" t="n">
-        <v>525.84</v>
+        <v>525.02</v>
       </c>
       <c r="Y61" t="n">
-        <v>531.87</v>
+        <v>532.95</v>
       </c>
       <c r="Z61" t="n">
-        <v>506.5901</v>
+        <v>507.1919</v>
       </c>
       <c r="AA61" t="n">
-        <v>434.6038</v>
+        <v>434.9192</v>
       </c>
       <c r="AB61" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC61" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>21 okt</t>
+          <t>22 okt</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>46.97</v>
+        <v>47.05</v>
       </c>
       <c r="C62" t="n">
-        <v>47.135</v>
+        <v>47.6</v>
       </c>
       <c r="D62" t="n">
-        <v>46.73</v>
+        <v>46.55</v>
       </c>
       <c r="E62" t="n">
-        <v>46.84</v>
+        <v>46.55</v>
       </c>
       <c r="F62" t="n">
-        <v>41.9472</v>
+        <v>42.1061</v>
       </c>
       <c r="G62" t="n">
-        <v>37.2379</v>
+        <v>37.3217</v>
       </c>
       <c r="H62" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I62" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>21 okt</t>
+          <t>22 okt</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>201.8</v>
+        <v>207.75</v>
       </c>
       <c r="M62" t="n">
-        <v>208.65</v>
+        <v>216.65</v>
       </c>
       <c r="N62" t="n">
-        <v>200</v>
+        <v>205.1</v>
       </c>
       <c r="O62" t="n">
-        <v>208.65</v>
+        <v>215.35</v>
       </c>
       <c r="P62" t="n">
-        <v>187.1278</v>
+        <v>187.9272</v>
       </c>
       <c r="Q62" t="n">
-        <v>163.8728</v>
+        <v>163.9019</v>
       </c>
       <c r="R62" t="n">
         <v>191.5557367172241</v>
@@ -8869,86 +8891,86 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>21 okt</t>
+          <t>22 okt</t>
         </is>
       </c>
       <c r="V62" t="n">
-        <v>529.4400000000001</v>
+        <v>533.14</v>
       </c>
       <c r="W62" t="n">
-        <v>533.28</v>
+        <v>533.6</v>
       </c>
       <c r="X62" t="n">
-        <v>525.02</v>
+        <v>520.3</v>
       </c>
       <c r="Y62" t="n">
-        <v>532.95</v>
+        <v>521.08</v>
       </c>
       <c r="Z62" t="n">
-        <v>507.1919</v>
+        <v>507.7834</v>
       </c>
       <c r="AA62" t="n">
-        <v>434.9192</v>
+        <v>435.1471</v>
       </c>
       <c r="AB62" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC62" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>22 okt</t>
+          <t>23 okt</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>47.05</v>
+        <v>47.13</v>
       </c>
       <c r="C63" t="n">
-        <v>47.6</v>
+        <v>48.38</v>
       </c>
       <c r="D63" t="n">
-        <v>46.55</v>
+        <v>46.895</v>
       </c>
       <c r="E63" t="n">
-        <v>46.55</v>
+        <v>48.295</v>
       </c>
       <c r="F63" t="n">
-        <v>42.1061</v>
+        <v>42.2926</v>
       </c>
       <c r="G63" t="n">
-        <v>37.3217</v>
+        <v>37.4107</v>
       </c>
       <c r="H63" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I63" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>22 okt</t>
+          <t>23 okt</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>207.75</v>
+        <v>213.55</v>
       </c>
       <c r="M63" t="n">
-        <v>216.65</v>
+        <v>215.85</v>
       </c>
       <c r="N63" t="n">
-        <v>205.1</v>
+        <v>210.05</v>
       </c>
       <c r="O63" t="n">
-        <v>215.35</v>
+        <v>214.4</v>
       </c>
       <c r="P63" t="n">
-        <v>187.9272</v>
+        <v>188.6124</v>
       </c>
       <c r="Q63" t="n">
-        <v>163.9019</v>
+        <v>163.9244</v>
       </c>
       <c r="R63" t="n">
         <v>191.5557367172241</v>
@@ -8958,86 +8980,86 @@
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>22 okt</t>
+          <t>23 okt</t>
         </is>
       </c>
       <c r="V63" t="n">
-        <v>533.14</v>
+        <v>517.75</v>
       </c>
       <c r="W63" t="n">
-        <v>533.6</v>
+        <v>525.77</v>
       </c>
       <c r="X63" t="n">
-        <v>520.3</v>
+        <v>515.7</v>
       </c>
       <c r="Y63" t="n">
-        <v>521.08</v>
+        <v>524.51</v>
       </c>
       <c r="Z63" t="n">
-        <v>507.7834</v>
+        <v>508.3546</v>
       </c>
       <c r="AA63" t="n">
-        <v>435.1471</v>
+        <v>435.3676</v>
       </c>
       <c r="AB63" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC63" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>23 okt</t>
+          <t>26 okt</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>47.13</v>
+        <v>48</v>
       </c>
       <c r="C64" t="n">
-        <v>48.38</v>
+        <v>48.21</v>
       </c>
       <c r="D64" t="n">
-        <v>46.895</v>
+        <v>47.37</v>
       </c>
       <c r="E64" t="n">
-        <v>48.295</v>
+        <v>47.91</v>
       </c>
       <c r="F64" t="n">
-        <v>42.2926</v>
+        <v>42.4678</v>
       </c>
       <c r="G64" t="n">
-        <v>37.4107</v>
+        <v>37.4967</v>
       </c>
       <c r="H64" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I64" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>23 okt</t>
+          <t>26 okt</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>213.55</v>
+        <v>213.5</v>
       </c>
       <c r="M64" t="n">
-        <v>215.85</v>
+        <v>216.55</v>
       </c>
       <c r="N64" t="n">
-        <v>210.05</v>
+        <v>212.25</v>
       </c>
       <c r="O64" t="n">
-        <v>214.4</v>
+        <v>212.25</v>
       </c>
       <c r="P64" t="n">
-        <v>188.6124</v>
+        <v>189.2658</v>
       </c>
       <c r="Q64" t="n">
-        <v>163.9244</v>
+        <v>163.9724</v>
       </c>
       <c r="R64" t="n">
         <v>191.5557367172241</v>
@@ -9047,86 +9069,86 @@
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>23 okt</t>
+          <t>26 okt</t>
         </is>
       </c>
       <c r="V64" t="n">
-        <v>517.75</v>
+        <v>527.4</v>
       </c>
       <c r="W64" t="n">
-        <v>525.77</v>
+        <v>533.25</v>
       </c>
       <c r="X64" t="n">
-        <v>515.7</v>
+        <v>521.6900000000001</v>
       </c>
       <c r="Y64" t="n">
-        <v>524.51</v>
+        <v>532.6</v>
       </c>
       <c r="Z64" t="n">
-        <v>508.3546</v>
+        <v>509.1173</v>
       </c>
       <c r="AA64" t="n">
-        <v>435.3676</v>
+        <v>435.6551</v>
       </c>
       <c r="AB64" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC64" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>26 okt</t>
+          <t>27 okt</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>48</v>
+        <v>47.83</v>
       </c>
       <c r="C65" t="n">
-        <v>48.21</v>
+        <v>47.91</v>
       </c>
       <c r="D65" t="n">
-        <v>47.37</v>
+        <v>47.05</v>
       </c>
       <c r="E65" t="n">
-        <v>47.91</v>
+        <v>47.13</v>
       </c>
       <c r="F65" t="n">
-        <v>42.4678</v>
+        <v>42.6147</v>
       </c>
       <c r="G65" t="n">
-        <v>37.4967</v>
+        <v>37.5784</v>
       </c>
       <c r="H65" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I65" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>26 okt</t>
+          <t>27 okt</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>213.5</v>
+        <v>212.75</v>
       </c>
       <c r="M65" t="n">
-        <v>216.55</v>
+        <v>215.25</v>
       </c>
       <c r="N65" t="n">
-        <v>212.25</v>
+        <v>211.7</v>
       </c>
       <c r="O65" t="n">
-        <v>212.25</v>
+        <v>213.15</v>
       </c>
       <c r="P65" t="n">
-        <v>189.2658</v>
+        <v>189.8788</v>
       </c>
       <c r="Q65" t="n">
-        <v>163.9724</v>
+        <v>164.0273</v>
       </c>
       <c r="R65" t="n">
         <v>191.5557367172241</v>
@@ -9136,86 +9158,86 @@
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>26 okt</t>
+          <t>27 okt</t>
         </is>
       </c>
       <c r="V65" t="n">
-        <v>527.4</v>
+        <v>532.35</v>
       </c>
       <c r="W65" t="n">
-        <v>533.25</v>
+        <v>534.7</v>
       </c>
       <c r="X65" t="n">
-        <v>521.6900000000001</v>
+        <v>528.33</v>
       </c>
       <c r="Y65" t="n">
-        <v>532.6</v>
+        <v>531.33</v>
       </c>
       <c r="Z65" t="n">
-        <v>509.1173</v>
+        <v>510.1549</v>
       </c>
       <c r="AA65" t="n">
-        <v>435.6551</v>
+        <v>435.9304</v>
       </c>
       <c r="AB65" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC65" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>27 okt</t>
+          <t>28 okt</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>47.83</v>
+        <v>47.125</v>
       </c>
       <c r="C66" t="n">
-        <v>47.91</v>
+        <v>47.445</v>
       </c>
       <c r="D66" t="n">
-        <v>47.05</v>
+        <v>46.98</v>
       </c>
       <c r="E66" t="n">
-        <v>47.13</v>
+        <v>47.44</v>
       </c>
       <c r="F66" t="n">
-        <v>42.6147</v>
+        <v>42.7647</v>
       </c>
       <c r="G66" t="n">
-        <v>37.5784</v>
+        <v>37.6612</v>
       </c>
       <c r="H66" t="n">
         <v>45.05751734733581</v>
       </c>
       <c r="I66" t="n">
-        <v>45.41250092642648</v>
+        <v>45.59678595406668</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>27 okt</t>
+          <t>28 okt</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>212.75</v>
+        <v>212.95</v>
       </c>
       <c r="M66" t="n">
-        <v>215.25</v>
+        <v>214.35</v>
       </c>
       <c r="N66" t="n">
-        <v>211.7</v>
+        <v>209.2</v>
       </c>
       <c r="O66" t="n">
-        <v>213.2</v>
+        <v>211.6</v>
       </c>
       <c r="P66" t="n">
-        <v>189.8798</v>
+        <v>190.3928</v>
       </c>
       <c r="Q66" t="n">
-        <v>164.0275</v>
+        <v>164.0914</v>
       </c>
       <c r="R66" t="n">
         <v>191.5557367172241</v>
@@ -9225,32 +9247,32 @@
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>27 okt</t>
+          <t>28 okt</t>
         </is>
       </c>
       <c r="V66" t="n">
-        <v>532.35</v>
+        <v>531.8200000000001</v>
       </c>
       <c r="W66" t="n">
-        <v>534.7</v>
+        <v>535</v>
       </c>
       <c r="X66" t="n">
-        <v>528.331</v>
+        <v>526.14</v>
       </c>
       <c r="Y66" t="n">
-        <v>531.6</v>
+        <v>531.01</v>
       </c>
       <c r="Z66" t="n">
-        <v>510.1603</v>
+        <v>511.1606</v>
       </c>
       <c r="AA66" t="n">
-        <v>435.9318</v>
+        <v>436.2146</v>
       </c>
       <c r="AB66" t="n">
         <v>535.3375423278808</v>
       </c>
       <c r="AC66" t="n">
-        <v>510.3278547014509</v>
+        <v>511.5021493094308</v>
       </c>
     </row>
   </sheetData>

--- a/rapporten/trend-agent.xlsx
+++ b/rapporten/trend-agent.xlsx
@@ -4755,7 +4755,7 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>10083.15</v>
+        <v>10078.53</v>
       </c>
       <c r="C17" s="2">
         <f>B17-B16</f>
@@ -4982,7 +4982,7 @@
     <row r="69" ht="22" customHeight="1">
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>Energie-ETF (XLE)  ·  70,00 USD</t>
+          <t>Energie-ETF (XLE)  ·  70,02 USD</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
@@ -4994,7 +4994,7 @@
     <row r="70" ht="30" customHeight="1">
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t>Gestegen: 18,2% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: nog vrijwel gelijk. De bot verkoopt als de koers onder 67,18 zakt (-4,0%).</t>
+          <t>Gestegen: 18,3% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden. Sinds de bot kocht: nog vrijwel gelijk. De bot verkoopt als de koers onder 67,18 zakt (-4,1%).</t>
         </is>
       </c>
       <c r="D70" s="10" t="inlineStr">
@@ -6003,7 +6003,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.128</v>
+        <v>0.129</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>0.2659372534894664</v>
@@ -6012,7 +6012,7 @@
         <v>0.23280433896618</v>
       </c>
       <c r="H6" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="I6" t="n">
         <v>1417.54</v>
@@ -6038,19 +6038,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.126</v>
+        <v>0.125</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.1977561132454866</v>
+        <v>0.1980982718380175</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.1164274186321128</v>
+        <v>0.116746344354969</v>
       </c>
       <c r="H7" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="I7" t="n">
-        <v>70</v>
+        <v>70.02</v>
       </c>
     </row>
     <row r="8">
@@ -6117,7 +6117,7 @@
         <v>0.1430227788319567</v>
       </c>
       <c r="H9" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="I9" t="n">
         <v>187.25</v>
@@ -21718,10 +21718,10 @@
         <v>234.01</v>
       </c>
       <c r="BA66" t="n">
-        <v>236.46</v>
+        <v>236.48</v>
       </c>
       <c r="BB66" t="n">
-        <v>233.2224</v>
+        <v>233.22</v>
       </c>
       <c r="BC66" t="n">
         <v>235.52</v>
@@ -21747,19 +21747,19 @@
         <v>69.52</v>
       </c>
       <c r="BK66" t="n">
-        <v>70.151</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="BL66" t="n">
-        <v>69.29000000000001</v>
+        <v>69.28</v>
       </c>
       <c r="BM66" t="n">
-        <v>70</v>
+        <v>70.02</v>
       </c>
       <c r="BN66" t="n">
-        <v>64.7769</v>
+        <v>64.7773</v>
       </c>
       <c r="BO66" t="n">
-        <v>58.1515</v>
+        <v>58.1516</v>
       </c>
       <c r="BP66" t="n">
         <v>70.035</v>
